--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yuhang/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{778E0CE1-4C73-F045-A934-241C3ED39172}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{83755A73-C422-6841-B77E-DBE23215E65D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1584" uniqueCount="491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1577" uniqueCount="489">
   <si>
     <t>所在市</t>
   </si>
@@ -1443,12 +1443,6 @@
   </si>
   <si>
     <t>116.678255,39.908680</t>
-  </si>
-  <si>
-    <t>新光大中心5A</t>
-  </si>
-  <si>
-    <t>116.660425,39.916231</t>
   </si>
   <si>
     <t>Linda</t>
@@ -1882,7 +1876,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B280671-4AFA-4641-88D4-A51F39483890}">
-  <dimension ref="A1:N193"/>
+  <dimension ref="A1:N192"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="5.6640625" bestFit="1" customWidth="1"/>
@@ -1902,22 +1896,22 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" t="s">
+        <v>475</v>
+      </c>
+      <c r="B1" t="s">
         <v>477</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
+        <v>478</v>
+      </c>
+      <c r="D1" t="s">
         <v>479</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="F1" t="s">
         <v>480</v>
-      </c>
-      <c r="D1" t="s">
-        <v>481</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>487</v>
-      </c>
-      <c r="F1" t="s">
-        <v>482</v>
       </c>
       <c r="G1" t="s">
         <v>0</v>
@@ -1929,19 +1923,19 @@
         <v>2</v>
       </c>
       <c r="J1" t="s">
+        <v>481</v>
+      </c>
+      <c r="K1" t="s">
+        <v>476</v>
+      </c>
+      <c r="L1" t="s">
+        <v>482</v>
+      </c>
+      <c r="M1" t="s">
         <v>483</v>
       </c>
-      <c r="K1" t="s">
-        <v>478</v>
-      </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>484</v>
-      </c>
-      <c r="M1" t="s">
-        <v>485</v>
-      </c>
-      <c r="N1" t="s">
-        <v>486</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -1970,7 +1964,7 @@
         <v>9</v>
       </c>
       <c r="J2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="K2">
         <v>72308</v>
@@ -2011,7 +2005,7 @@
         <v>12</v>
       </c>
       <c r="J3" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="K3">
         <v>72308</v>
@@ -2055,7 +2049,7 @@
         <v>17</v>
       </c>
       <c r="J4" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="K4">
         <v>130769</v>
@@ -2099,7 +2093,7 @@
         <v>20</v>
       </c>
       <c r="J5" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="K5">
         <v>64615</v>
@@ -2143,7 +2137,7 @@
         <v>24</v>
       </c>
       <c r="J6" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="K6">
         <v>80091</v>
@@ -2184,7 +2178,7 @@
         <v>27</v>
       </c>
       <c r="J7" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="K7">
         <v>70673</v>
@@ -2228,7 +2222,7 @@
         <v>30</v>
       </c>
       <c r="J8" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="K8">
         <v>90466</v>
@@ -2269,7 +2263,7 @@
         <v>32</v>
       </c>
       <c r="J9" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="K9">
         <v>46720</v>
@@ -2313,7 +2307,7 @@
         <v>35</v>
       </c>
       <c r="J10" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="K10">
         <v>95000</v>
@@ -2357,7 +2351,7 @@
         <v>38</v>
       </c>
       <c r="J11" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="K11">
         <v>85300</v>
@@ -2401,7 +2395,7 @@
         <v>41</v>
       </c>
       <c r="J12" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="K12">
         <v>33305</v>
@@ -2445,7 +2439,7 @@
         <v>43</v>
       </c>
       <c r="J13" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="K13">
         <v>120245.21</v>
@@ -2489,7 +2483,7 @@
         <v>43</v>
       </c>
       <c r="J14" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="K14">
         <v>70425.53</v>
@@ -2533,7 +2527,7 @@
         <v>47</v>
       </c>
       <c r="J15" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="K15">
         <v>78000</v>
@@ -2577,7 +2571,7 @@
         <v>50</v>
       </c>
       <c r="J16" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="K16">
         <v>102796</v>
@@ -2621,7 +2615,7 @@
         <v>52</v>
       </c>
       <c r="J17" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="K17">
         <v>49200</v>
@@ -2665,7 +2659,7 @@
         <v>54</v>
       </c>
       <c r="J18" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="K18">
         <v>65096</v>
@@ -2709,7 +2703,7 @@
         <v>57</v>
       </c>
       <c r="J19" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="K19">
         <v>56000</v>
@@ -2753,7 +2747,7 @@
         <v>60</v>
       </c>
       <c r="J20" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="K20">
         <v>177847</v>
@@ -2797,7 +2791,7 @@
         <v>63</v>
       </c>
       <c r="J21" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="K21">
         <v>83000</v>
@@ -2838,7 +2832,7 @@
         <v>66</v>
       </c>
       <c r="J22" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="K22">
         <v>26000</v>
@@ -2879,7 +2873,7 @@
         <v>68</v>
       </c>
       <c r="J23" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="K23">
         <v>85887</v>
@@ -2920,7 +2914,7 @@
         <v>70</v>
       </c>
       <c r="J24" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="K24">
         <v>20000</v>
@@ -2964,7 +2958,7 @@
         <v>73</v>
       </c>
       <c r="J25" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="K25">
         <v>146385</v>
@@ -3008,7 +3002,7 @@
         <v>76</v>
       </c>
       <c r="J26" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="K26">
         <v>87000</v>
@@ -3052,7 +3046,7 @@
         <v>79</v>
       </c>
       <c r="J27" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="K27">
         <v>147166.79999999999</v>
@@ -3096,7 +3090,7 @@
         <v>82</v>
       </c>
       <c r="J28" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="K28">
         <v>46063</v>
@@ -3140,7 +3134,7 @@
         <v>85</v>
       </c>
       <c r="J29" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="K29">
         <v>47261</v>
@@ -3184,7 +3178,7 @@
         <v>89</v>
       </c>
       <c r="J30" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="K30">
         <v>119000</v>
@@ -3225,7 +3219,7 @@
         <v>92</v>
       </c>
       <c r="J31" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="K31">
         <v>47000</v>
@@ -3269,7 +3263,7 @@
         <v>94</v>
       </c>
       <c r="J32" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="K32">
         <v>186000</v>
@@ -3307,7 +3301,7 @@
         <v>96</v>
       </c>
       <c r="J33" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="K33">
         <v>40800</v>
@@ -3348,7 +3342,7 @@
         <v>96</v>
       </c>
       <c r="J34" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="K34">
         <v>55200</v>
@@ -3392,7 +3386,7 @@
         <v>100</v>
       </c>
       <c r="J35" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="K35">
         <v>350000</v>
@@ -3433,7 +3427,7 @@
         <v>102</v>
       </c>
       <c r="J36" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="K36">
         <v>65000</v>
@@ -3474,7 +3468,7 @@
         <v>102</v>
       </c>
       <c r="J37" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="K37">
         <v>35000</v>
@@ -3515,7 +3509,7 @@
         <v>105</v>
       </c>
       <c r="J38" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="K38">
         <v>47000</v>
@@ -3559,7 +3553,7 @@
         <v>108</v>
       </c>
       <c r="J39" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="K39">
         <v>120000</v>
@@ -3600,7 +3594,7 @@
         <v>110</v>
       </c>
       <c r="J40" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="K40">
         <v>83000</v>
@@ -3641,7 +3635,7 @@
         <v>112</v>
       </c>
       <c r="J41" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="K41">
         <v>66030</v>
@@ -3679,7 +3673,7 @@
         <v>114</v>
       </c>
       <c r="J42" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="K42">
         <v>40000</v>
@@ -3723,7 +3717,7 @@
         <v>119</v>
       </c>
       <c r="J43" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="K43">
         <v>40000</v>
@@ -3764,7 +3758,7 @@
         <v>122</v>
       </c>
       <c r="J44" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="K44">
         <v>54100</v>
@@ -3808,7 +3802,7 @@
         <v>125</v>
       </c>
       <c r="J45" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="K45">
         <v>100000</v>
@@ -3852,7 +3846,7 @@
         <v>128</v>
       </c>
       <c r="J46" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="K46">
         <v>150000</v>
@@ -3896,7 +3890,7 @@
         <v>131</v>
       </c>
       <c r="J47" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="K47">
         <v>50000</v>
@@ -3940,7 +3934,7 @@
         <v>134</v>
       </c>
       <c r="J48" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="K48">
         <v>43000</v>
@@ -3981,7 +3975,7 @@
         <v>137</v>
       </c>
       <c r="J49" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="K49">
         <v>65000</v>
@@ -4022,7 +4016,7 @@
         <v>140</v>
       </c>
       <c r="J50" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="51" spans="1:14">
@@ -4054,7 +4048,7 @@
         <v>142</v>
       </c>
       <c r="J51" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="K51">
         <v>56000</v>
@@ -4095,7 +4089,7 @@
         <v>144</v>
       </c>
       <c r="J52" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="K52">
         <v>160000</v>
@@ -4136,7 +4130,7 @@
         <v>146</v>
       </c>
       <c r="J53" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="K53">
         <v>33000</v>
@@ -4180,7 +4174,7 @@
         <v>149</v>
       </c>
       <c r="J54" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="K54">
         <v>41318</v>
@@ -4221,7 +4215,7 @@
         <v>151</v>
       </c>
       <c r="J55" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="K55">
         <v>34131</v>
@@ -4262,7 +4256,7 @@
         <v>154</v>
       </c>
       <c r="J56" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="K56">
         <v>48000</v>
@@ -4303,7 +4297,7 @@
         <v>119</v>
       </c>
       <c r="J57" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="K57">
         <v>16000</v>
@@ -4347,7 +4341,7 @@
         <v>158</v>
       </c>
       <c r="J58" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="K58">
         <v>30000</v>
@@ -4391,7 +4385,7 @@
         <v>161</v>
       </c>
       <c r="J59" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="K59">
         <v>56000</v>
@@ -4435,7 +4429,7 @@
         <v>164</v>
       </c>
       <c r="J60" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="K60">
         <v>43000</v>
@@ -4476,7 +4470,7 @@
         <v>166</v>
       </c>
       <c r="J61" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="K61">
         <v>110000</v>
@@ -4514,7 +4508,7 @@
         <v>168</v>
       </c>
       <c r="J62" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="K62">
         <v>56160</v>
@@ -4555,7 +4549,7 @@
         <v>170</v>
       </c>
       <c r="J63" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="K63">
         <v>138444</v>
@@ -4599,7 +4593,7 @@
         <v>174</v>
       </c>
       <c r="J64" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K64">
         <v>31000</v>
@@ -4640,7 +4634,7 @@
         <v>177</v>
       </c>
       <c r="J65" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K65">
         <v>120000</v>
@@ -4681,7 +4675,7 @@
         <v>179</v>
       </c>
       <c r="J66" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K66">
         <v>25900</v>
@@ -4722,7 +4716,7 @@
         <v>182</v>
       </c>
       <c r="J67" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K67">
         <v>47986</v>
@@ -4766,7 +4760,7 @@
         <v>184</v>
       </c>
       <c r="J68" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K68">
         <v>194000</v>
@@ -4810,7 +4804,7 @@
         <v>186</v>
       </c>
       <c r="J69" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K69">
         <v>39724</v>
@@ -4851,7 +4845,7 @@
         <v>188</v>
       </c>
       <c r="J70" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K70">
         <v>48437.45</v>
@@ -4892,7 +4886,7 @@
         <v>191</v>
       </c>
       <c r="J71" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K71">
         <v>37910</v>
@@ -4933,7 +4927,7 @@
         <v>193</v>
       </c>
       <c r="J72" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K72">
         <v>21220</v>
@@ -4974,7 +4968,7 @@
         <v>195</v>
       </c>
       <c r="J73" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K73">
         <v>77877</v>
@@ -5018,7 +5012,7 @@
         <v>197</v>
       </c>
       <c r="J74" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K74">
         <v>80311.53</v>
@@ -5062,7 +5056,7 @@
         <v>200</v>
       </c>
       <c r="J75" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K75">
         <v>38000</v>
@@ -5103,7 +5097,7 @@
         <v>203</v>
       </c>
       <c r="J76" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K76">
         <v>37800</v>
@@ -5147,7 +5141,7 @@
         <v>206</v>
       </c>
       <c r="J77" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K77">
         <v>54581</v>
@@ -5191,7 +5185,7 @@
         <v>89</v>
       </c>
       <c r="J78" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K78">
         <v>25000</v>
@@ -5235,7 +5229,7 @@
         <v>210</v>
       </c>
       <c r="J79" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K79">
         <v>52698</v>
@@ -5276,7 +5270,7 @@
         <v>214</v>
       </c>
       <c r="J80" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K80">
         <v>38500</v>
@@ -5314,7 +5308,7 @@
         <v>217</v>
       </c>
       <c r="J81" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K81">
         <v>27200</v>
@@ -5358,7 +5352,7 @@
         <v>220</v>
       </c>
       <c r="J82" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="K82">
         <v>60000</v>
@@ -5399,7 +5393,7 @@
         <v>223</v>
       </c>
       <c r="J83" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="K83">
         <v>50000</v>
@@ -5443,7 +5437,7 @@
         <v>225</v>
       </c>
       <c r="J84" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="K84">
         <v>131575</v>
@@ -5484,7 +5478,7 @@
         <v>227</v>
       </c>
       <c r="J85" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="K85">
         <v>99500</v>
@@ -5525,7 +5519,7 @@
         <v>230</v>
       </c>
       <c r="J86" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="K86">
         <v>32000</v>
@@ -5569,7 +5563,7 @@
         <v>232</v>
       </c>
       <c r="J87" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="K87">
         <v>52170</v>
@@ -5610,7 +5604,7 @@
         <v>235</v>
       </c>
       <c r="J88" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="K88">
         <v>46000</v>
@@ -5654,7 +5648,7 @@
         <v>238</v>
       </c>
       <c r="J89" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="K89">
         <v>45013</v>
@@ -5695,7 +5689,7 @@
         <v>240</v>
       </c>
       <c r="J90" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="K90">
         <v>48566</v>
@@ -5736,7 +5730,7 @@
         <v>243</v>
       </c>
       <c r="J91" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="K91">
         <v>55618</v>
@@ -5777,7 +5771,7 @@
         <v>245</v>
       </c>
       <c r="J92" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="K92">
         <v>47000</v>
@@ -5821,7 +5815,7 @@
         <v>248</v>
       </c>
       <c r="J93" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="K93">
         <v>87763</v>
@@ -5865,7 +5859,7 @@
         <v>251</v>
       </c>
       <c r="J94" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="K94">
         <v>100658</v>
@@ -5906,7 +5900,7 @@
         <v>254</v>
       </c>
       <c r="J95" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="K95">
         <v>67000</v>
@@ -5950,7 +5944,7 @@
         <v>256</v>
       </c>
       <c r="J96" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="K96">
         <v>39431</v>
@@ -5991,7 +5985,7 @@
         <v>258</v>
       </c>
       <c r="J97" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="K97">
         <v>34273</v>
@@ -6029,7 +6023,7 @@
         <v>73</v>
       </c>
       <c r="J98" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="K98">
         <v>40000</v>
@@ -6070,7 +6064,7 @@
         <v>261</v>
       </c>
       <c r="J99" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="K99">
         <v>65000</v>
@@ -6114,7 +6108,7 @@
         <v>265</v>
       </c>
       <c r="J100" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="K100">
         <v>49000</v>
@@ -6158,7 +6152,7 @@
         <v>268</v>
       </c>
       <c r="J101" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="K101">
         <v>95000</v>
@@ -6202,7 +6196,7 @@
         <v>271</v>
       </c>
       <c r="J102" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="K102">
         <v>45000</v>
@@ -6243,7 +6237,7 @@
         <v>273</v>
       </c>
       <c r="J103" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="K103">
         <v>124500</v>
@@ -6284,7 +6278,7 @@
         <v>275</v>
       </c>
       <c r="J104" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="K104">
         <v>64000</v>
@@ -6325,7 +6319,7 @@
         <v>277</v>
       </c>
       <c r="J105" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="K105">
         <v>25000</v>
@@ -6366,7 +6360,7 @@
         <v>279</v>
       </c>
       <c r="J106" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="K106">
         <v>38498</v>
@@ -6404,7 +6398,7 @@
         <v>281</v>
       </c>
       <c r="J107" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="K107">
         <v>166433</v>
@@ -6448,7 +6442,7 @@
         <v>283</v>
       </c>
       <c r="J108" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="K108">
         <v>58000</v>
@@ -6489,7 +6483,7 @@
         <v>286</v>
       </c>
       <c r="J109" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="K109">
         <v>51872</v>
@@ -6530,7 +6524,7 @@
         <v>288</v>
       </c>
       <c r="J110" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="K110">
         <v>21632</v>
@@ -6571,7 +6565,7 @@
         <v>290</v>
       </c>
       <c r="J111" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="K111">
         <v>69000</v>
@@ -6612,7 +6606,7 @@
         <v>293</v>
       </c>
       <c r="J112" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="K112">
         <v>54000</v>
@@ -6653,7 +6647,7 @@
         <v>295</v>
       </c>
       <c r="J113" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="K113">
         <v>57400</v>
@@ -6694,7 +6688,7 @@
         <v>297</v>
       </c>
       <c r="J114" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="K114">
         <v>60000</v>
@@ -6735,7 +6729,7 @@
         <v>297</v>
       </c>
       <c r="J115" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="K115">
         <v>60000</v>
@@ -6773,7 +6767,7 @@
         <v>300</v>
       </c>
       <c r="J116" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="K116">
         <v>33000</v>
@@ -6811,7 +6805,7 @@
         <v>302</v>
       </c>
       <c r="J117" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="K117">
         <v>88786</v>
@@ -6849,7 +6843,7 @@
         <v>304</v>
       </c>
       <c r="J118" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="K118">
         <v>134000</v>
@@ -6887,7 +6881,7 @@
         <v>306</v>
       </c>
       <c r="J119" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="K119">
         <v>35000</v>
@@ -6925,7 +6919,7 @@
         <v>308</v>
       </c>
       <c r="J120" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="K120">
         <v>18000</v>
@@ -6966,7 +6960,7 @@
         <v>310</v>
       </c>
       <c r="J121" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="K121">
         <v>105741</v>
@@ -7004,7 +6998,7 @@
         <v>312</v>
       </c>
       <c r="J122" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="K122">
         <v>51000</v>
@@ -7045,7 +7039,7 @@
         <v>314</v>
       </c>
       <c r="J123" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="K123">
         <v>130143</v>
@@ -7080,7 +7074,7 @@
         <v>316</v>
       </c>
       <c r="J124" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="K124">
         <v>121551.47</v>
@@ -7124,7 +7118,7 @@
         <v>320</v>
       </c>
       <c r="J125" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="K125">
         <v>110000</v>
@@ -7168,7 +7162,7 @@
         <v>322</v>
       </c>
       <c r="J126" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="K126">
         <v>56000</v>
@@ -7209,7 +7203,7 @@
         <v>324</v>
       </c>
       <c r="J127" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="K127">
         <v>89177</v>
@@ -7253,7 +7247,7 @@
         <v>327</v>
       </c>
       <c r="J128" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="K128">
         <v>30000</v>
@@ -7297,7 +7291,7 @@
         <v>329</v>
       </c>
       <c r="J129" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="K129">
         <v>54550</v>
@@ -7341,7 +7335,7 @@
         <v>331</v>
       </c>
       <c r="J130" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="K130">
         <v>125000</v>
@@ -7385,7 +7379,7 @@
         <v>334</v>
       </c>
       <c r="J131" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="K131">
         <v>69100</v>
@@ -7429,7 +7423,7 @@
         <v>336</v>
       </c>
       <c r="J132" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="K132">
         <v>118290</v>
@@ -7470,7 +7464,7 @@
         <v>339</v>
       </c>
       <c r="J133" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="K133">
         <v>79900</v>
@@ -7511,7 +7505,7 @@
         <v>341</v>
       </c>
       <c r="J134" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="K134">
         <v>39742.379999999997</v>
@@ -7555,7 +7549,7 @@
         <v>343</v>
       </c>
       <c r="J135" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="K135">
         <v>48000</v>
@@ -7596,7 +7590,7 @@
         <v>345</v>
       </c>
       <c r="J136" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="K136">
         <v>74722</v>
@@ -7634,7 +7628,7 @@
         <v>347</v>
       </c>
       <c r="J137" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="K137">
         <v>55000</v>
@@ -7672,7 +7666,7 @@
         <v>350</v>
       </c>
       <c r="J138" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="K138">
         <v>128000</v>
@@ -7716,7 +7710,7 @@
         <v>352</v>
       </c>
       <c r="J139" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="K139">
         <v>122000</v>
@@ -7757,7 +7751,7 @@
         <v>354</v>
       </c>
       <c r="J140" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="K140">
         <v>22000</v>
@@ -7798,7 +7792,7 @@
         <v>356</v>
       </c>
       <c r="J141" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="K141">
         <v>10000</v>
@@ -7839,7 +7833,7 @@
         <v>358</v>
       </c>
       <c r="J142" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="K142">
         <v>64000</v>
@@ -7880,7 +7874,7 @@
         <v>360</v>
       </c>
       <c r="J143" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="K143">
         <v>95628</v>
@@ -7921,7 +7915,7 @@
         <v>363</v>
       </c>
       <c r="J144" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="K144">
         <v>39562</v>
@@ -7965,7 +7959,7 @@
         <v>366</v>
       </c>
       <c r="J145" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="K145">
         <v>105000</v>
@@ -8009,7 +8003,7 @@
         <v>368</v>
       </c>
       <c r="J146" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="K146">
         <v>60000</v>
@@ -8050,7 +8044,7 @@
         <v>370</v>
       </c>
       <c r="J147" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="K147">
         <v>39964</v>
@@ -8091,7 +8085,7 @@
         <v>372</v>
       </c>
       <c r="J148" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="K148">
         <v>94000</v>
@@ -8135,7 +8129,7 @@
         <v>368</v>
       </c>
       <c r="J149" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="K149">
         <v>75000</v>
@@ -8176,7 +8170,7 @@
         <v>188</v>
       </c>
       <c r="J150" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="K150">
         <v>48767</v>
@@ -8220,7 +8214,7 @@
         <v>376</v>
       </c>
       <c r="J151" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="K151">
         <v>63824</v>
@@ -8264,7 +8258,7 @@
         <v>378</v>
       </c>
       <c r="J152" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="K152">
         <v>117000</v>
@@ -8302,7 +8296,7 @@
         <v>380</v>
       </c>
       <c r="J153" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="K153">
         <v>41000</v>
@@ -8340,7 +8334,7 @@
         <v>382</v>
       </c>
       <c r="J154" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="K154">
         <v>96446</v>
@@ -8384,7 +8378,7 @@
         <v>386</v>
       </c>
       <c r="J155" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="K155">
         <v>76600</v>
@@ -8425,7 +8419,7 @@
         <v>388</v>
       </c>
       <c r="J156" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="K156">
         <v>125569</v>
@@ -8466,7 +8460,7 @@
         <v>391</v>
       </c>
       <c r="J157" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="K157">
         <v>51234</v>
@@ -8510,7 +8504,7 @@
         <v>393</v>
       </c>
       <c r="J158" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="K158">
         <v>123780</v>
@@ -8551,7 +8545,7 @@
         <v>396</v>
       </c>
       <c r="J159" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="K159">
         <v>46000</v>
@@ -8589,7 +8583,7 @@
         <v>398</v>
       </c>
       <c r="J160" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="K160">
         <v>35600</v>
@@ -8630,7 +8624,7 @@
         <v>400</v>
       </c>
       <c r="J161" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="K161">
         <v>199950</v>
@@ -8671,7 +8665,7 @@
         <v>402</v>
       </c>
       <c r="J162" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="K162">
         <v>108000</v>
@@ -8712,7 +8706,7 @@
         <v>404</v>
       </c>
       <c r="J163" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="K163">
         <v>142808</v>
@@ -8753,7 +8747,7 @@
         <v>406</v>
       </c>
       <c r="J164" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="K164">
         <v>80463</v>
@@ -8794,7 +8788,7 @@
         <v>408</v>
       </c>
       <c r="J165" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="K165">
         <v>83000</v>
@@ -8832,7 +8826,7 @@
         <v>410</v>
       </c>
       <c r="J166" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="K166">
         <v>129000</v>
@@ -8873,7 +8867,7 @@
         <v>413</v>
       </c>
       <c r="J167" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="K167">
         <v>62209</v>
@@ -8914,7 +8908,7 @@
         <v>415</v>
       </c>
       <c r="J168" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="K168">
         <v>36117</v>
@@ -8958,7 +8952,7 @@
         <v>417</v>
       </c>
       <c r="J169" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="K169">
         <v>49900</v>
@@ -9002,7 +8996,7 @@
         <v>420</v>
       </c>
       <c r="J170" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="K170">
         <v>39000</v>
@@ -9043,7 +9037,7 @@
         <v>422</v>
       </c>
       <c r="J171" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="K171">
         <v>49000</v>
@@ -9081,7 +9075,7 @@
         <v>424</v>
       </c>
       <c r="J172" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="K172">
         <v>59400</v>
@@ -9122,7 +9116,7 @@
         <v>426</v>
       </c>
       <c r="J173" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="K173">
         <v>65000</v>
@@ -9166,7 +9160,7 @@
         <v>431</v>
       </c>
       <c r="J174" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="K174">
         <v>47000</v>
@@ -9207,7 +9201,7 @@
         <v>433</v>
       </c>
       <c r="J175" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="K175">
         <v>29000</v>
@@ -9251,7 +9245,7 @@
         <v>435</v>
       </c>
       <c r="J176" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="K176">
         <v>132239</v>
@@ -9292,7 +9286,7 @@
         <v>437</v>
       </c>
       <c r="J177" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="K177">
         <v>35016</v>
@@ -9330,7 +9324,7 @@
         <v>439</v>
       </c>
       <c r="J178" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="K178">
         <v>60000</v>
@@ -9371,7 +9365,7 @@
         <v>442</v>
       </c>
       <c r="J179" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="K179">
         <v>90244</v>
@@ -9409,7 +9403,7 @@
         <v>444</v>
       </c>
       <c r="J180" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="K180">
         <v>38700</v>
@@ -9447,7 +9441,7 @@
         <v>446</v>
       </c>
       <c r="J181" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="K181">
         <v>62414</v>
@@ -9485,7 +9479,7 @@
         <v>448</v>
       </c>
       <c r="J182" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="K182">
         <v>51000</v>
@@ -9526,7 +9520,7 @@
         <v>450</v>
       </c>
       <c r="J183" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="K183">
         <v>53115</v>
@@ -9564,7 +9558,7 @@
         <v>452</v>
       </c>
       <c r="J184" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="K184">
         <v>120000</v>
@@ -9605,7 +9599,7 @@
         <v>454</v>
       </c>
       <c r="J185" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="K185">
         <v>66477</v>
@@ -9872,44 +9866,6 @@
       </c>
       <c r="N192">
         <v>15800</v>
-      </c>
-    </row>
-    <row r="193" spans="1:14">
-      <c r="A193">
-        <v>192</v>
-      </c>
-      <c r="B193" t="s">
-        <v>470</v>
-      </c>
-      <c r="C193" t="s">
-        <v>456</v>
-      </c>
-      <c r="D193" t="s">
-        <v>5</v>
-      </c>
-      <c r="E193" t="s">
-        <v>16</v>
-      </c>
-      <c r="G193" t="s">
-        <v>7</v>
-      </c>
-      <c r="H193" t="s">
-        <v>457</v>
-      </c>
-      <c r="I193" t="s">
-        <v>471</v>
-      </c>
-      <c r="K193">
-        <v>76210</v>
-      </c>
-      <c r="L193">
-        <v>84.4444444444444</v>
-      </c>
-      <c r="M193">
-        <v>0.38052748983073098</v>
-      </c>
-      <c r="N193">
-        <v>29000</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yuhang/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{83755A73-C422-6841-B77E-DBE23215E65D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{778E0CE1-4C73-F045-A934-241C3ED39172}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1577" uniqueCount="489">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1584" uniqueCount="491">
   <si>
     <t>所在市</t>
   </si>
@@ -1443,6 +1443,12 @@
   </si>
   <si>
     <t>116.678255,39.908680</t>
+  </si>
+  <si>
+    <t>新光大中心5A</t>
+  </si>
+  <si>
+    <t>116.660425,39.916231</t>
   </si>
   <si>
     <t>Linda</t>
@@ -1876,7 +1882,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B280671-4AFA-4641-88D4-A51F39483890}">
-  <dimension ref="A1:N192"/>
+  <dimension ref="A1:N193"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="5.6640625" bestFit="1" customWidth="1"/>
@@ -1896,22 +1902,22 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B1" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="D1" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="F1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="G1" t="s">
         <v>0</v>
@@ -1923,19 +1929,19 @@
         <v>2</v>
       </c>
       <c r="J1" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="K1" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="L1" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="M1" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="N1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -1964,7 +1970,7 @@
         <v>9</v>
       </c>
       <c r="J2" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K2">
         <v>72308</v>
@@ -2005,7 +2011,7 @@
         <v>12</v>
       </c>
       <c r="J3" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K3">
         <v>72308</v>
@@ -2049,7 +2055,7 @@
         <v>17</v>
       </c>
       <c r="J4" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K4">
         <v>130769</v>
@@ -2093,7 +2099,7 @@
         <v>20</v>
       </c>
       <c r="J5" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K5">
         <v>64615</v>
@@ -2137,7 +2143,7 @@
         <v>24</v>
       </c>
       <c r="J6" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K6">
         <v>80091</v>
@@ -2178,7 +2184,7 @@
         <v>27</v>
       </c>
       <c r="J7" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="K7">
         <v>70673</v>
@@ -2222,7 +2228,7 @@
         <v>30</v>
       </c>
       <c r="J8" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K8">
         <v>90466</v>
@@ -2263,7 +2269,7 @@
         <v>32</v>
       </c>
       <c r="J9" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="K9">
         <v>46720</v>
@@ -2307,7 +2313,7 @@
         <v>35</v>
       </c>
       <c r="J10" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="K10">
         <v>95000</v>
@@ -2351,7 +2357,7 @@
         <v>38</v>
       </c>
       <c r="J11" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K11">
         <v>85300</v>
@@ -2395,7 +2401,7 @@
         <v>41</v>
       </c>
       <c r="J12" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="K12">
         <v>33305</v>
@@ -2439,7 +2445,7 @@
         <v>43</v>
       </c>
       <c r="J13" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K13">
         <v>120245.21</v>
@@ -2483,7 +2489,7 @@
         <v>43</v>
       </c>
       <c r="J14" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K14">
         <v>70425.53</v>
@@ -2527,7 +2533,7 @@
         <v>47</v>
       </c>
       <c r="J15" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K15">
         <v>78000</v>
@@ -2571,7 +2577,7 @@
         <v>50</v>
       </c>
       <c r="J16" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="K16">
         <v>102796</v>
@@ -2615,7 +2621,7 @@
         <v>52</v>
       </c>
       <c r="J17" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="K17">
         <v>49200</v>
@@ -2659,7 +2665,7 @@
         <v>54</v>
       </c>
       <c r="J18" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="K18">
         <v>65096</v>
@@ -2703,7 +2709,7 @@
         <v>57</v>
       </c>
       <c r="J19" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K19">
         <v>56000</v>
@@ -2747,7 +2753,7 @@
         <v>60</v>
       </c>
       <c r="J20" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="K20">
         <v>177847</v>
@@ -2791,7 +2797,7 @@
         <v>63</v>
       </c>
       <c r="J21" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K21">
         <v>83000</v>
@@ -2832,7 +2838,7 @@
         <v>66</v>
       </c>
       <c r="J22" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="K22">
         <v>26000</v>
@@ -2873,7 +2879,7 @@
         <v>68</v>
       </c>
       <c r="J23" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K23">
         <v>85887</v>
@@ -2914,7 +2920,7 @@
         <v>70</v>
       </c>
       <c r="J24" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K24">
         <v>20000</v>
@@ -2958,7 +2964,7 @@
         <v>73</v>
       </c>
       <c r="J25" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K25">
         <v>146385</v>
@@ -3002,7 +3008,7 @@
         <v>76</v>
       </c>
       <c r="J26" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K26">
         <v>87000</v>
@@ -3046,7 +3052,7 @@
         <v>79</v>
       </c>
       <c r="J27" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K27">
         <v>147166.79999999999</v>
@@ -3090,7 +3096,7 @@
         <v>82</v>
       </c>
       <c r="J28" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K28">
         <v>46063</v>
@@ -3134,7 +3140,7 @@
         <v>85</v>
       </c>
       <c r="J29" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="K29">
         <v>47261</v>
@@ -3178,7 +3184,7 @@
         <v>89</v>
       </c>
       <c r="J30" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K30">
         <v>119000</v>
@@ -3219,7 +3225,7 @@
         <v>92</v>
       </c>
       <c r="J31" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="K31">
         <v>47000</v>
@@ -3263,7 +3269,7 @@
         <v>94</v>
       </c>
       <c r="J32" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="K32">
         <v>186000</v>
@@ -3301,7 +3307,7 @@
         <v>96</v>
       </c>
       <c r="J33" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K33">
         <v>40800</v>
@@ -3342,7 +3348,7 @@
         <v>96</v>
       </c>
       <c r="J34" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K34">
         <v>55200</v>
@@ -3386,7 +3392,7 @@
         <v>100</v>
       </c>
       <c r="J35" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="K35">
         <v>350000</v>
@@ -3427,7 +3433,7 @@
         <v>102</v>
       </c>
       <c r="J36" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K36">
         <v>65000</v>
@@ -3468,7 +3474,7 @@
         <v>102</v>
       </c>
       <c r="J37" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K37">
         <v>35000</v>
@@ -3509,7 +3515,7 @@
         <v>105</v>
       </c>
       <c r="J38" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="K38">
         <v>47000</v>
@@ -3553,7 +3559,7 @@
         <v>108</v>
       </c>
       <c r="J39" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="K39">
         <v>120000</v>
@@ -3594,7 +3600,7 @@
         <v>110</v>
       </c>
       <c r="J40" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K40">
         <v>83000</v>
@@ -3635,7 +3641,7 @@
         <v>112</v>
       </c>
       <c r="J41" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="K41">
         <v>66030</v>
@@ -3673,7 +3679,7 @@
         <v>114</v>
       </c>
       <c r="J42" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="K42">
         <v>40000</v>
@@ -3717,7 +3723,7 @@
         <v>119</v>
       </c>
       <c r="J43" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K43">
         <v>40000</v>
@@ -3758,7 +3764,7 @@
         <v>122</v>
       </c>
       <c r="J44" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K44">
         <v>54100</v>
@@ -3802,7 +3808,7 @@
         <v>125</v>
       </c>
       <c r="J45" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K45">
         <v>100000</v>
@@ -3846,7 +3852,7 @@
         <v>128</v>
       </c>
       <c r="J46" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K46">
         <v>150000</v>
@@ -3890,7 +3896,7 @@
         <v>131</v>
       </c>
       <c r="J47" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K47">
         <v>50000</v>
@@ -3934,7 +3940,7 @@
         <v>134</v>
       </c>
       <c r="J48" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="K48">
         <v>43000</v>
@@ -3975,7 +3981,7 @@
         <v>137</v>
       </c>
       <c r="J49" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="K49">
         <v>65000</v>
@@ -4016,7 +4022,7 @@
         <v>140</v>
       </c>
       <c r="J50" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="51" spans="1:14">
@@ -4048,7 +4054,7 @@
         <v>142</v>
       </c>
       <c r="J51" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="K51">
         <v>56000</v>
@@ -4089,7 +4095,7 @@
         <v>144</v>
       </c>
       <c r="J52" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="K52">
         <v>160000</v>
@@ -4130,7 +4136,7 @@
         <v>146</v>
       </c>
       <c r="J53" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="K53">
         <v>33000</v>
@@ -4174,7 +4180,7 @@
         <v>149</v>
       </c>
       <c r="J54" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="K54">
         <v>41318</v>
@@ -4215,7 +4221,7 @@
         <v>151</v>
       </c>
       <c r="J55" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K55">
         <v>34131</v>
@@ -4256,7 +4262,7 @@
         <v>154</v>
       </c>
       <c r="J56" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K56">
         <v>48000</v>
@@ -4297,7 +4303,7 @@
         <v>119</v>
       </c>
       <c r="J57" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K57">
         <v>16000</v>
@@ -4341,7 +4347,7 @@
         <v>158</v>
       </c>
       <c r="J58" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="K58">
         <v>30000</v>
@@ -4385,7 +4391,7 @@
         <v>161</v>
       </c>
       <c r="J59" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="K59">
         <v>56000</v>
@@ -4429,7 +4435,7 @@
         <v>164</v>
       </c>
       <c r="J60" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K60">
         <v>43000</v>
@@ -4470,7 +4476,7 @@
         <v>166</v>
       </c>
       <c r="J61" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="K61">
         <v>110000</v>
@@ -4508,7 +4514,7 @@
         <v>168</v>
       </c>
       <c r="J62" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K62">
         <v>56160</v>
@@ -4549,7 +4555,7 @@
         <v>170</v>
       </c>
       <c r="J63" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K63">
         <v>138444</v>
@@ -4593,7 +4599,7 @@
         <v>174</v>
       </c>
       <c r="J64" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="K64">
         <v>31000</v>
@@ -4634,7 +4640,7 @@
         <v>177</v>
       </c>
       <c r="J65" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="K65">
         <v>120000</v>
@@ -4675,7 +4681,7 @@
         <v>179</v>
       </c>
       <c r="J66" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="K66">
         <v>25900</v>
@@ -4716,7 +4722,7 @@
         <v>182</v>
       </c>
       <c r="J67" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="K67">
         <v>47986</v>
@@ -4760,7 +4766,7 @@
         <v>184</v>
       </c>
       <c r="J68" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="K68">
         <v>194000</v>
@@ -4804,7 +4810,7 @@
         <v>186</v>
       </c>
       <c r="J69" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="K69">
         <v>39724</v>
@@ -4845,7 +4851,7 @@
         <v>188</v>
       </c>
       <c r="J70" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="K70">
         <v>48437.45</v>
@@ -4886,7 +4892,7 @@
         <v>191</v>
       </c>
       <c r="J71" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="K71">
         <v>37910</v>
@@ -4927,7 +4933,7 @@
         <v>193</v>
       </c>
       <c r="J72" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="K72">
         <v>21220</v>
@@ -4968,7 +4974,7 @@
         <v>195</v>
       </c>
       <c r="J73" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="K73">
         <v>77877</v>
@@ -5012,7 +5018,7 @@
         <v>197</v>
       </c>
       <c r="J74" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="K74">
         <v>80311.53</v>
@@ -5056,7 +5062,7 @@
         <v>200</v>
       </c>
       <c r="J75" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="K75">
         <v>38000</v>
@@ -5097,7 +5103,7 @@
         <v>203</v>
       </c>
       <c r="J76" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="K76">
         <v>37800</v>
@@ -5141,7 +5147,7 @@
         <v>206</v>
       </c>
       <c r="J77" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="K77">
         <v>54581</v>
@@ -5185,7 +5191,7 @@
         <v>89</v>
       </c>
       <c r="J78" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="K78">
         <v>25000</v>
@@ -5229,7 +5235,7 @@
         <v>210</v>
       </c>
       <c r="J79" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="K79">
         <v>52698</v>
@@ -5270,7 +5276,7 @@
         <v>214</v>
       </c>
       <c r="J80" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="K80">
         <v>38500</v>
@@ -5308,7 +5314,7 @@
         <v>217</v>
       </c>
       <c r="J81" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="K81">
         <v>27200</v>
@@ -5352,7 +5358,7 @@
         <v>220</v>
       </c>
       <c r="J82" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="K82">
         <v>60000</v>
@@ -5393,7 +5399,7 @@
         <v>223</v>
       </c>
       <c r="J83" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K83">
         <v>50000</v>
@@ -5437,7 +5443,7 @@
         <v>225</v>
       </c>
       <c r="J84" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="K84">
         <v>131575</v>
@@ -5478,7 +5484,7 @@
         <v>227</v>
       </c>
       <c r="J85" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K85">
         <v>99500</v>
@@ -5519,7 +5525,7 @@
         <v>230</v>
       </c>
       <c r="J86" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="K86">
         <v>32000</v>
@@ -5563,7 +5569,7 @@
         <v>232</v>
       </c>
       <c r="J87" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="K87">
         <v>52170</v>
@@ -5604,7 +5610,7 @@
         <v>235</v>
       </c>
       <c r="J88" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="K88">
         <v>46000</v>
@@ -5648,7 +5654,7 @@
         <v>238</v>
       </c>
       <c r="J89" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K89">
         <v>45013</v>
@@ -5689,7 +5695,7 @@
         <v>240</v>
       </c>
       <c r="J90" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="K90">
         <v>48566</v>
@@ -5730,7 +5736,7 @@
         <v>243</v>
       </c>
       <c r="J91" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K91">
         <v>55618</v>
@@ -5771,7 +5777,7 @@
         <v>245</v>
       </c>
       <c r="J92" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="K92">
         <v>47000</v>
@@ -5815,7 +5821,7 @@
         <v>248</v>
       </c>
       <c r="J93" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K93">
         <v>87763</v>
@@ -5859,7 +5865,7 @@
         <v>251</v>
       </c>
       <c r="J94" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="K94">
         <v>100658</v>
@@ -5900,7 +5906,7 @@
         <v>254</v>
       </c>
       <c r="J95" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="K95">
         <v>67000</v>
@@ -5944,7 +5950,7 @@
         <v>256</v>
       </c>
       <c r="J96" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="K96">
         <v>39431</v>
@@ -5985,7 +5991,7 @@
         <v>258</v>
       </c>
       <c r="J97" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="K97">
         <v>34273</v>
@@ -6023,7 +6029,7 @@
         <v>73</v>
       </c>
       <c r="J98" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K98">
         <v>40000</v>
@@ -6064,7 +6070,7 @@
         <v>261</v>
       </c>
       <c r="J99" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="K99">
         <v>65000</v>
@@ -6108,7 +6114,7 @@
         <v>265</v>
       </c>
       <c r="J100" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="K100">
         <v>49000</v>
@@ -6152,7 +6158,7 @@
         <v>268</v>
       </c>
       <c r="J101" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="K101">
         <v>95000</v>
@@ -6196,7 +6202,7 @@
         <v>271</v>
       </c>
       <c r="J102" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="K102">
         <v>45000</v>
@@ -6237,7 +6243,7 @@
         <v>273</v>
       </c>
       <c r="J103" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="K103">
         <v>124500</v>
@@ -6278,7 +6284,7 @@
         <v>275</v>
       </c>
       <c r="J104" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="K104">
         <v>64000</v>
@@ -6319,7 +6325,7 @@
         <v>277</v>
       </c>
       <c r="J105" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="K105">
         <v>25000</v>
@@ -6360,7 +6366,7 @@
         <v>279</v>
       </c>
       <c r="J106" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="K106">
         <v>38498</v>
@@ -6398,7 +6404,7 @@
         <v>281</v>
       </c>
       <c r="J107" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="K107">
         <v>166433</v>
@@ -6442,7 +6448,7 @@
         <v>283</v>
       </c>
       <c r="J108" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="K108">
         <v>58000</v>
@@ -6483,7 +6489,7 @@
         <v>286</v>
       </c>
       <c r="J109" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="K109">
         <v>51872</v>
@@ -6524,7 +6530,7 @@
         <v>288</v>
       </c>
       <c r="J110" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="K110">
         <v>21632</v>
@@ -6565,7 +6571,7 @@
         <v>290</v>
       </c>
       <c r="J111" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="K111">
         <v>69000</v>
@@ -6606,7 +6612,7 @@
         <v>293</v>
       </c>
       <c r="J112" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="K112">
         <v>54000</v>
@@ -6647,7 +6653,7 @@
         <v>295</v>
       </c>
       <c r="J113" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="K113">
         <v>57400</v>
@@ -6688,7 +6694,7 @@
         <v>297</v>
       </c>
       <c r="J114" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="K114">
         <v>60000</v>
@@ -6729,7 +6735,7 @@
         <v>297</v>
       </c>
       <c r="J115" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="K115">
         <v>60000</v>
@@ -6767,7 +6773,7 @@
         <v>300</v>
       </c>
       <c r="J116" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="K116">
         <v>33000</v>
@@ -6805,7 +6811,7 @@
         <v>302</v>
       </c>
       <c r="J117" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="K117">
         <v>88786</v>
@@ -6843,7 +6849,7 @@
         <v>304</v>
       </c>
       <c r="J118" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="K118">
         <v>134000</v>
@@ -6881,7 +6887,7 @@
         <v>306</v>
       </c>
       <c r="J119" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="K119">
         <v>35000</v>
@@ -6919,7 +6925,7 @@
         <v>308</v>
       </c>
       <c r="J120" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="K120">
         <v>18000</v>
@@ -6960,7 +6966,7 @@
         <v>310</v>
       </c>
       <c r="J121" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="K121">
         <v>105741</v>
@@ -6998,7 +7004,7 @@
         <v>312</v>
       </c>
       <c r="J122" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="K122">
         <v>51000</v>
@@ -7039,7 +7045,7 @@
         <v>314</v>
       </c>
       <c r="J123" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="K123">
         <v>130143</v>
@@ -7074,7 +7080,7 @@
         <v>316</v>
       </c>
       <c r="J124" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="K124">
         <v>121551.47</v>
@@ -7118,7 +7124,7 @@
         <v>320</v>
       </c>
       <c r="J125" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="K125">
         <v>110000</v>
@@ -7162,7 +7168,7 @@
         <v>322</v>
       </c>
       <c r="J126" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="K126">
         <v>56000</v>
@@ -7203,7 +7209,7 @@
         <v>324</v>
       </c>
       <c r="J127" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="K127">
         <v>89177</v>
@@ -7247,7 +7253,7 @@
         <v>327</v>
       </c>
       <c r="J128" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="K128">
         <v>30000</v>
@@ -7291,7 +7297,7 @@
         <v>329</v>
       </c>
       <c r="J129" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="K129">
         <v>54550</v>
@@ -7335,7 +7341,7 @@
         <v>331</v>
       </c>
       <c r="J130" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="K130">
         <v>125000</v>
@@ -7379,7 +7385,7 @@
         <v>334</v>
       </c>
       <c r="J131" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="K131">
         <v>69100</v>
@@ -7423,7 +7429,7 @@
         <v>336</v>
       </c>
       <c r="J132" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="K132">
         <v>118290</v>
@@ -7464,7 +7470,7 @@
         <v>339</v>
       </c>
       <c r="J133" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="K133">
         <v>79900</v>
@@ -7505,7 +7511,7 @@
         <v>341</v>
       </c>
       <c r="J134" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="K134">
         <v>39742.379999999997</v>
@@ -7549,7 +7555,7 @@
         <v>343</v>
       </c>
       <c r="J135" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="K135">
         <v>48000</v>
@@ -7590,7 +7596,7 @@
         <v>345</v>
       </c>
       <c r="J136" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="K136">
         <v>74722</v>
@@ -7628,7 +7634,7 @@
         <v>347</v>
       </c>
       <c r="J137" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="K137">
         <v>55000</v>
@@ -7666,7 +7672,7 @@
         <v>350</v>
       </c>
       <c r="J138" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K138">
         <v>128000</v>
@@ -7710,7 +7716,7 @@
         <v>352</v>
       </c>
       <c r="J139" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K139">
         <v>122000</v>
@@ -7751,7 +7757,7 @@
         <v>354</v>
       </c>
       <c r="J140" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K140">
         <v>22000</v>
@@ -7792,7 +7798,7 @@
         <v>356</v>
       </c>
       <c r="J141" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K141">
         <v>10000</v>
@@ -7833,7 +7839,7 @@
         <v>358</v>
       </c>
       <c r="J142" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="K142">
         <v>64000</v>
@@ -7874,7 +7880,7 @@
         <v>360</v>
       </c>
       <c r="J143" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="K143">
         <v>95628</v>
@@ -7915,7 +7921,7 @@
         <v>363</v>
       </c>
       <c r="J144" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="K144">
         <v>39562</v>
@@ -7959,7 +7965,7 @@
         <v>366</v>
       </c>
       <c r="J145" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K145">
         <v>105000</v>
@@ -8003,7 +8009,7 @@
         <v>368</v>
       </c>
       <c r="J146" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K146">
         <v>60000</v>
@@ -8044,7 +8050,7 @@
         <v>370</v>
       </c>
       <c r="J147" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="K147">
         <v>39964</v>
@@ -8085,7 +8091,7 @@
         <v>372</v>
       </c>
       <c r="J148" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K148">
         <v>94000</v>
@@ -8129,7 +8135,7 @@
         <v>368</v>
       </c>
       <c r="J149" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K149">
         <v>75000</v>
@@ -8170,7 +8176,7 @@
         <v>188</v>
       </c>
       <c r="J150" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K150">
         <v>48767</v>
@@ -8214,7 +8220,7 @@
         <v>376</v>
       </c>
       <c r="J151" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K151">
         <v>63824</v>
@@ -8258,7 +8264,7 @@
         <v>378</v>
       </c>
       <c r="J152" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K152">
         <v>117000</v>
@@ -8296,7 +8302,7 @@
         <v>380</v>
       </c>
       <c r="J153" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K153">
         <v>41000</v>
@@ -8334,7 +8340,7 @@
         <v>382</v>
       </c>
       <c r="J154" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="K154">
         <v>96446</v>
@@ -8378,7 +8384,7 @@
         <v>386</v>
       </c>
       <c r="J155" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K155">
         <v>76600</v>
@@ -8419,7 +8425,7 @@
         <v>388</v>
       </c>
       <c r="J156" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="K156">
         <v>125569</v>
@@ -8460,7 +8466,7 @@
         <v>391</v>
       </c>
       <c r="J157" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K157">
         <v>51234</v>
@@ -8504,7 +8510,7 @@
         <v>393</v>
       </c>
       <c r="J158" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="K158">
         <v>123780</v>
@@ -8545,7 +8551,7 @@
         <v>396</v>
       </c>
       <c r="J159" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K159">
         <v>46000</v>
@@ -8583,7 +8589,7 @@
         <v>398</v>
       </c>
       <c r="J160" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K160">
         <v>35600</v>
@@ -8624,7 +8630,7 @@
         <v>400</v>
       </c>
       <c r="J161" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="K161">
         <v>199950</v>
@@ -8665,7 +8671,7 @@
         <v>402</v>
       </c>
       <c r="J162" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="K162">
         <v>108000</v>
@@ -8706,7 +8712,7 @@
         <v>404</v>
       </c>
       <c r="J163" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="K163">
         <v>142808</v>
@@ -8747,7 +8753,7 @@
         <v>406</v>
       </c>
       <c r="J164" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="K164">
         <v>80463</v>
@@ -8788,7 +8794,7 @@
         <v>408</v>
       </c>
       <c r="J165" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K165">
         <v>83000</v>
@@ -8826,7 +8832,7 @@
         <v>410</v>
       </c>
       <c r="J166" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K166">
         <v>129000</v>
@@ -8867,7 +8873,7 @@
         <v>413</v>
       </c>
       <c r="J167" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K167">
         <v>62209</v>
@@ -8908,7 +8914,7 @@
         <v>415</v>
       </c>
       <c r="J168" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="K168">
         <v>36117</v>
@@ -8952,7 +8958,7 @@
         <v>417</v>
       </c>
       <c r="J169" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="K169">
         <v>49900</v>
@@ -8996,7 +9002,7 @@
         <v>420</v>
       </c>
       <c r="J170" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="K170">
         <v>39000</v>
@@ -9037,7 +9043,7 @@
         <v>422</v>
       </c>
       <c r="J171" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="K171">
         <v>49000</v>
@@ -9075,7 +9081,7 @@
         <v>424</v>
       </c>
       <c r="J172" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="K172">
         <v>59400</v>
@@ -9116,7 +9122,7 @@
         <v>426</v>
       </c>
       <c r="J173" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="K173">
         <v>65000</v>
@@ -9160,7 +9166,7 @@
         <v>431</v>
       </c>
       <c r="J174" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K174">
         <v>47000</v>
@@ -9201,7 +9207,7 @@
         <v>433</v>
       </c>
       <c r="J175" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K175">
         <v>29000</v>
@@ -9245,7 +9251,7 @@
         <v>435</v>
       </c>
       <c r="J176" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K176">
         <v>132239</v>
@@ -9286,7 +9292,7 @@
         <v>437</v>
       </c>
       <c r="J177" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K177">
         <v>35016</v>
@@ -9324,7 +9330,7 @@
         <v>439</v>
       </c>
       <c r="J178" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K178">
         <v>60000</v>
@@ -9365,7 +9371,7 @@
         <v>442</v>
       </c>
       <c r="J179" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="K179">
         <v>90244</v>
@@ -9403,7 +9409,7 @@
         <v>444</v>
       </c>
       <c r="J180" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K180">
         <v>38700</v>
@@ -9441,7 +9447,7 @@
         <v>446</v>
       </c>
       <c r="J181" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="K181">
         <v>62414</v>
@@ -9479,7 +9485,7 @@
         <v>448</v>
       </c>
       <c r="J182" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K182">
         <v>51000</v>
@@ -9520,7 +9526,7 @@
         <v>450</v>
       </c>
       <c r="J183" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K183">
         <v>53115</v>
@@ -9558,7 +9564,7 @@
         <v>452</v>
       </c>
       <c r="J184" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K184">
         <v>120000</v>
@@ -9599,7 +9605,7 @@
         <v>454</v>
       </c>
       <c r="J185" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="K185">
         <v>66477</v>
@@ -9866,6 +9872,44 @@
       </c>
       <c r="N192">
         <v>15800</v>
+      </c>
+    </row>
+    <row r="193" spans="1:14">
+      <c r="A193">
+        <v>192</v>
+      </c>
+      <c r="B193" t="s">
+        <v>470</v>
+      </c>
+      <c r="C193" t="s">
+        <v>456</v>
+      </c>
+      <c r="D193" t="s">
+        <v>5</v>
+      </c>
+      <c r="E193" t="s">
+        <v>16</v>
+      </c>
+      <c r="G193" t="s">
+        <v>7</v>
+      </c>
+      <c r="H193" t="s">
+        <v>457</v>
+      </c>
+      <c r="I193" t="s">
+        <v>471</v>
+      </c>
+      <c r="K193">
+        <v>76210</v>
+      </c>
+      <c r="L193">
+        <v>84.4444444444444</v>
+      </c>
+      <c r="M193">
+        <v>0.38052748983073098</v>
+      </c>
+      <c r="N193">
+        <v>29000</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yuhang/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yuhang/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{778E0CE1-4C73-F045-A934-241C3ED39172}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD82D224-D7F9-6141-80BC-9EF445000A53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1584" uniqueCount="491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1587" uniqueCount="446">
   <si>
     <t>所在市</t>
   </si>
@@ -53,9 +53,6 @@
     <t>A</t>
   </si>
   <si>
-    <t>1990 Q3</t>
-  </si>
-  <si>
     <t>北京市</t>
   </si>
   <si>
@@ -68,9 +65,6 @@
     <t>国贸写字楼2座</t>
   </si>
   <si>
-    <t>1999 Q4</t>
-  </si>
-  <si>
     <t>116.460469,39.910838</t>
   </si>
   <si>
@@ -80,9 +74,6 @@
     <t>P</t>
   </si>
   <si>
-    <t>2010 Q3</t>
-  </si>
-  <si>
     <t>Gold</t>
   </si>
   <si>
@@ -92,18 +83,12 @@
     <t>国贸大厦B座(三期)</t>
   </si>
   <si>
-    <t>2017 Q2</t>
-  </si>
-  <si>
     <t>116.460515,39.912938</t>
   </si>
   <si>
     <t>嘉里中心</t>
   </si>
   <si>
-    <t>1998 Q4</t>
-  </si>
-  <si>
     <t>Platinum</t>
   </si>
   <si>
@@ -113,18 +98,12 @@
     <t>新华保险大厦（NCI）</t>
   </si>
   <si>
-    <t>2005 Q1</t>
-  </si>
-  <si>
     <t>116.446972,39.907680</t>
   </si>
   <si>
     <t>汇京双子座大厦</t>
   </si>
   <si>
-    <t>2005 Q4</t>
-  </si>
-  <si>
     <t>116.448639,39.907750</t>
   </si>
   <si>
@@ -137,27 +116,18 @@
     <t>世界财富大厦（福佳大厦）（SK大厦）</t>
   </si>
   <si>
-    <t>2006 Q2</t>
-  </si>
-  <si>
     <t>116.456470,39.907620</t>
   </si>
   <si>
     <t>远洋国际中心A座</t>
   </si>
   <si>
-    <t>2007 Q1</t>
-  </si>
-  <si>
     <t>116.491620,39.914782</t>
   </si>
   <si>
     <t>万通中心D座</t>
   </si>
   <si>
-    <t>2007 Q2</t>
-  </si>
-  <si>
     <t>116.456973,39.919557</t>
   </si>
   <si>
@@ -170,9 +140,6 @@
     <t>华贸中心三座</t>
   </si>
   <si>
-    <t>2008 Q1</t>
-  </si>
-  <si>
     <t>银泰中心</t>
   </si>
   <si>
@@ -182,9 +149,6 @@
     <t>金地中心</t>
   </si>
   <si>
-    <t>2007 Q3</t>
-  </si>
-  <si>
     <t>116.474482,39.909105</t>
   </si>
   <si>
@@ -203,36 +167,24 @@
     <t>乐成中心</t>
   </si>
   <si>
-    <t>2008 Q3</t>
-  </si>
-  <si>
     <t>116.462324,39.894899</t>
   </si>
   <si>
     <t>环球金融中心</t>
   </si>
   <si>
-    <t>2008 Q4</t>
-  </si>
-  <si>
     <t>116.459044,39.918732</t>
   </si>
   <si>
     <t>中海广场</t>
   </si>
   <si>
-    <t>2009 Q2</t>
-  </si>
-  <si>
     <t>116.456420,39.910934</t>
   </si>
   <si>
     <t>PICC大厦</t>
   </si>
   <si>
-    <t>2009 Q4</t>
-  </si>
-  <si>
     <t>116.466313,39.891861</t>
   </si>
   <si>
@@ -251,54 +203,36 @@
     <t>财源国际中心（IFC）</t>
   </si>
   <si>
-    <t>2011 Q1</t>
-  </si>
-  <si>
     <t>116.462761,39.920249</t>
   </si>
   <si>
     <t>北京侨福芳草地</t>
   </si>
   <si>
-    <t>2011 Q4</t>
-  </si>
-  <si>
     <t>116.449285,39.919803</t>
   </si>
   <si>
     <t xml:space="preserve">财富金融中心（FFC） </t>
   </si>
   <si>
-    <t>2013 Q4</t>
-  </si>
-  <si>
     <t>116.460552,39.917729</t>
   </si>
   <si>
     <t>远洋国际中心二期</t>
   </si>
   <si>
-    <t>2014 Q3</t>
-  </si>
-  <si>
     <t>116.491350,39.914073</t>
   </si>
   <si>
     <t>英皇集团中心</t>
   </si>
   <si>
-    <t>2017 Q1</t>
-  </si>
-  <si>
     <t>116.444738,39.907772</t>
   </si>
   <si>
     <t>中国人寿金融中心</t>
   </si>
   <si>
-    <t>2019 Q1</t>
-  </si>
-  <si>
     <t>西城区</t>
   </si>
   <si>
@@ -308,9 +242,6 @@
     <t>北京国际俱乐部二期（C座）</t>
   </si>
   <si>
-    <t>2019 Q3</t>
-  </si>
-  <si>
     <t>116.439750,39.909582</t>
   </si>
   <si>
@@ -329,9 +260,6 @@
     <t>众秀大厦-清华自己租赁部分</t>
   </si>
   <si>
-    <t>2019Q4</t>
-  </si>
-  <si>
     <t>中信大厦</t>
   </si>
   <si>
@@ -356,9 +284,6 @@
     <t>泰康集团大厦</t>
   </si>
   <si>
-    <t>2021 Q2</t>
-  </si>
-  <si>
     <t>116.467692,39.911215</t>
   </si>
   <si>
@@ -386,9 +311,6 @@
     <t>东城商务区</t>
   </si>
   <si>
-    <t>1996 Q?</t>
-  </si>
-  <si>
     <t>东城区</t>
   </si>
   <si>
@@ -398,63 +320,42 @@
     <t>北京华润大厦</t>
   </si>
   <si>
-    <t>1999 Q2</t>
-  </si>
-  <si>
     <t>116.434079,39.912909</t>
   </si>
   <si>
     <t>东方广场西区</t>
   </si>
   <si>
-    <t>2000 Q2</t>
-  </si>
-  <si>
     <t>116.414316,39.909603</t>
   </si>
   <si>
     <t>东方广场东区</t>
   </si>
   <si>
-    <t>2001 Q2</t>
-  </si>
-  <si>
     <t>116.414483,39.909740</t>
   </si>
   <si>
     <t>东方广场中区</t>
   </si>
   <si>
-    <t>2002 Q4</t>
-  </si>
-  <si>
     <t>116.414278,39.909829</t>
   </si>
   <si>
     <t>金宝大厦</t>
   </si>
   <si>
-    <t>2005 Q2</t>
-  </si>
-  <si>
     <t>116.419957,39.916098</t>
   </si>
   <si>
     <t>中青旅大厦</t>
   </si>
   <si>
-    <t>2006 Q1</t>
-  </si>
-  <si>
     <t>116.432560,39.937841</t>
   </si>
   <si>
     <t>国华投资大厦</t>
   </si>
   <si>
-    <t>2007 Q?</t>
-  </si>
-  <si>
     <t>116.432428,39.939081</t>
   </si>
   <si>
@@ -494,9 +395,6 @@
     <t>天润财富中心</t>
   </si>
   <si>
-    <t>2016 Q4</t>
-  </si>
-  <si>
     <t>116.427741,39.911344</t>
   </si>
   <si>
@@ -506,27 +404,18 @@
     <t>哈德门广场东塔</t>
   </si>
   <si>
-    <t>2017 Q3</t>
-  </si>
-  <si>
     <t>116.421270,39.899689</t>
   </si>
   <si>
     <t>哈德门广场西塔</t>
   </si>
   <si>
-    <t>2018 Q1</t>
-  </si>
-  <si>
     <t>116.420148,39.899582</t>
   </si>
   <si>
     <t>玖安广场（中粮置地广场）</t>
   </si>
   <si>
-    <t>2018 Q3</t>
-  </si>
-  <si>
     <t>116.408915,39.952121</t>
   </si>
   <si>
@@ -554,18 +443,12 @@
     <t>金融街</t>
   </si>
   <si>
-    <t>2000 Q1</t>
-  </si>
-  <si>
     <t>116.359889,39.906132</t>
   </si>
   <si>
     <t>英蓝国际金融中心</t>
   </si>
   <si>
-    <t>2005 Q3</t>
-  </si>
-  <si>
     <t>116.357825,39.920574</t>
   </si>
   <si>
@@ -578,9 +461,6 @@
     <t>长安兴融中心-4号楼</t>
   </si>
   <si>
-    <t>2006 Q4</t>
-  </si>
-  <si>
     <t>116.361343,39.904939</t>
   </si>
   <si>
@@ -605,9 +485,6 @@
     <t>泰康国际大厦</t>
   </si>
   <si>
-    <t>2007 Q4</t>
-  </si>
-  <si>
     <t>116.362589,39.917659</t>
   </si>
   <si>
@@ -632,36 +509,24 @@
     <t>太平洋保险大厦</t>
   </si>
   <si>
-    <t>2010 Q4</t>
-  </si>
-  <si>
     <t>116.366067,39.918211</t>
   </si>
   <si>
     <t>丰铭国际大厦</t>
   </si>
   <si>
-    <t>2013 Q1</t>
-  </si>
-  <si>
     <t>116.367302,39.918021</t>
   </si>
   <si>
     <t>锦什坊街叁拾伍号</t>
   </si>
   <si>
-    <t>2015 Q1</t>
-  </si>
-  <si>
     <t>116.362665,39.921274</t>
   </si>
   <si>
     <t>月坛金融中心E座</t>
   </si>
   <si>
-    <t>2016 Q?</t>
-  </si>
-  <si>
     <t>金嘉大厦</t>
   </si>
   <si>
@@ -671,9 +536,6 @@
     <t>新时代大厦</t>
   </si>
   <si>
-    <t>2007Q3</t>
-  </si>
-  <si>
     <t>海淀区</t>
   </si>
   <si>
@@ -692,18 +554,12 @@
     <t>盈科中心（AB座）</t>
   </si>
   <si>
-    <t>1999 Q1</t>
-  </si>
-  <si>
     <t>116.458974,39.932654</t>
   </si>
   <si>
     <t>现代汽车大厦</t>
   </si>
   <si>
-    <t>2000 Q3</t>
-  </si>
-  <si>
     <t>116.462588,39.956004</t>
   </si>
   <si>
@@ -722,9 +578,6 @@
     <t>凤凰置地广场A座</t>
   </si>
   <si>
-    <t>2010 Q1</t>
-  </si>
-  <si>
     <t>116.454820,39.961195</t>
   </si>
   <si>
@@ -737,18 +590,12 @@
     <t>凤凰置地广场F&amp;H座</t>
   </si>
   <si>
-    <t>2011 Q3</t>
-  </si>
-  <si>
     <t>116.455377,39.961514</t>
   </si>
   <si>
     <t>友邦金融中心（原凯德 星贸/博瑞大厦）</t>
   </si>
   <si>
-    <t>2012 Q1</t>
-  </si>
-  <si>
     <t>116.462524,39.927680</t>
   </si>
   <si>
@@ -761,9 +608,6 @@
     <t>亮马桥外交办公大楼</t>
   </si>
   <si>
-    <t>2014 Q4</t>
-  </si>
-  <si>
     <t>116.463427,39.950882</t>
   </si>
   <si>
@@ -776,27 +620,18 @@
     <t>国航世纪大厦</t>
   </si>
   <si>
-    <t>2016 Q1</t>
-  </si>
-  <si>
     <t>116.462344,39.955026</t>
   </si>
   <si>
     <t>启皓北京</t>
   </si>
   <si>
-    <t>2016 Q2</t>
-  </si>
-  <si>
     <t>116.456336,39.947734</t>
   </si>
   <si>
     <t>盈科中心-商业改办公</t>
   </si>
   <si>
-    <t>2015 Q?</t>
-  </si>
-  <si>
     <t>116.454766,39.919709</t>
   </si>
   <si>
@@ -827,27 +662,18 @@
     <t>中关村</t>
   </si>
   <si>
-    <t>2002 Q1</t>
-  </si>
-  <si>
     <t>116.325236,39.984261</t>
   </si>
   <si>
     <t>融科资讯中心C座</t>
   </si>
   <si>
-    <t>2004 Q3</t>
-  </si>
-  <si>
     <t>116.326695,39.983200</t>
   </si>
   <si>
     <t>理想国际大厦</t>
   </si>
   <si>
-    <t>2004 Q4</t>
-  </si>
-  <si>
     <t>116.310060,39.984499</t>
   </si>
   <si>
@@ -890,9 +716,6 @@
     <t>中航广场一期</t>
   </si>
   <si>
-    <t>2015 Q3</t>
-  </si>
-  <si>
     <t>116.328911,39.972012</t>
   </si>
   <si>
@@ -911,9 +734,6 @@
     <t>中关村资本大厦</t>
   </si>
   <si>
-    <t>2017 Q?</t>
-  </si>
-  <si>
     <t>116.337732,39.957118</t>
   </si>
   <si>
@@ -992,9 +812,6 @@
     <t>望京-酒仙桥</t>
   </si>
   <si>
-    <t>2008 Q2</t>
-  </si>
-  <si>
     <t>116.482346,39.994131</t>
   </si>
   <si>
@@ -1013,9 +830,6 @@
     <t>诺金写字楼</t>
   </si>
   <si>
-    <t>2015 Q2</t>
-  </si>
-  <si>
     <t>116.481365,39.977279</t>
   </si>
   <si>
@@ -1034,9 +848,6 @@
     <t>金辉大厦</t>
   </si>
   <si>
-    <t>2016 Q3</t>
-  </si>
-  <si>
     <t>116.488731,40.002813</t>
   </si>
   <si>
@@ -1049,9 +860,6 @@
     <t>中航产融大厦（中航资本大厦）</t>
   </si>
   <si>
-    <t>2018 Q2</t>
-  </si>
-  <si>
     <t>116.491357,40.000633</t>
   </si>
   <si>
@@ -1121,18 +929,12 @@
     <t>国家会议中心</t>
   </si>
   <si>
-    <t>2009 Q?</t>
-  </si>
-  <si>
     <t>116.389432,40.002901</t>
   </si>
   <si>
     <t>钰珵大厦（盘古大观）</t>
   </si>
   <si>
-    <t>2010 Q2</t>
-  </si>
-  <si>
     <t>116.386738,39.989441</t>
   </si>
   <si>
@@ -1157,9 +959,6 @@
     <t>奥南五号-B座（恒毅大厦）</t>
   </si>
   <si>
-    <t>2017 Q4</t>
-  </si>
-  <si>
     <t>城奥大厦</t>
   </si>
   <si>
@@ -1205,9 +1004,6 @@
     <t>铭丰中心</t>
   </si>
   <si>
-    <t>2019 Q2</t>
-  </si>
-  <si>
     <t>116.334611,39.867173</t>
   </si>
   <si>
@@ -1220,9 +1016,6 @@
     <t>青海金融大厦</t>
   </si>
   <si>
-    <t>2019 Q4</t>
-  </si>
-  <si>
     <t>116.322521,39.864006</t>
   </si>
   <si>
@@ -1292,9 +1085,6 @@
     <t>中融信托大厦</t>
   </si>
   <si>
-    <t>2018 Q4</t>
-  </si>
-  <si>
     <t>116.373533,39.887097</t>
   </si>
   <si>
@@ -1319,9 +1109,6 @@
     <t>中海大厦C、D座</t>
   </si>
   <si>
-    <t>2020 Q4</t>
-  </si>
-  <si>
     <t>Silver</t>
   </si>
   <si>
@@ -1356,9 +1143,6 @@
   </si>
   <si>
     <t>京印国际中心</t>
-  </si>
-  <si>
-    <t>2023 Q2</t>
   </si>
   <si>
     <t>116.375727,39.868418</t>
@@ -1507,6 +1291,87 @@
   </si>
   <si>
     <t>Jayden</t>
+  </si>
+  <si>
+    <t>1990</t>
+  </si>
+  <si>
+    <t>1999</t>
+  </si>
+  <si>
+    <t>2010</t>
+  </si>
+  <si>
+    <t>2017</t>
+  </si>
+  <si>
+    <t>1998</t>
+  </si>
+  <si>
+    <t>2005</t>
+  </si>
+  <si>
+    <t>2006</t>
+  </si>
+  <si>
+    <t>2007</t>
+  </si>
+  <si>
+    <t>2008</t>
+  </si>
+  <si>
+    <t>2009</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>2011</t>
+  </si>
+  <si>
+    <t>2013</t>
+  </si>
+  <si>
+    <t>2014</t>
+  </si>
+  <si>
+    <t>2019</t>
+  </si>
+  <si>
+    <t>2021</t>
+  </si>
+  <si>
+    <t>1996</t>
+  </si>
+  <si>
+    <t>2000</t>
+  </si>
+  <si>
+    <t>2001</t>
+  </si>
+  <si>
+    <t>2002</t>
+  </si>
+  <si>
+    <t>2016</t>
+  </si>
+  <si>
+    <t>2018</t>
+  </si>
+  <si>
+    <t>2015</t>
+  </si>
+  <si>
+    <t>2012</t>
+  </si>
+  <si>
+    <t>2004</t>
+  </si>
+  <si>
+    <t>2020</t>
+  </si>
+  <si>
+    <t>2023</t>
   </si>
 </sst>
 </file>
@@ -1568,9 +1433,13 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1890,7 +1759,7 @@
     <col min="3" max="3" width="7.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.1640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.33203125" style="2" customWidth="1"/>
     <col min="7" max="8" width="7.5" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="23.1640625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9" bestFit="1" customWidth="1"/>
@@ -1902,22 +1771,22 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" t="s">
-        <v>477</v>
+        <v>405</v>
       </c>
       <c r="B1" t="s">
-        <v>479</v>
+        <v>407</v>
       </c>
       <c r="C1" t="s">
-        <v>480</v>
+        <v>408</v>
       </c>
       <c r="D1" t="s">
-        <v>481</v>
+        <v>409</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>487</v>
+        <v>415</v>
       </c>
       <c r="F1" t="s">
-        <v>482</v>
+        <v>410</v>
       </c>
       <c r="G1" t="s">
         <v>0</v>
@@ -1929,19 +1798,19 @@
         <v>2</v>
       </c>
       <c r="J1" t="s">
-        <v>483</v>
+        <v>411</v>
       </c>
       <c r="K1" t="s">
-        <v>478</v>
+        <v>406</v>
       </c>
       <c r="L1" t="s">
-        <v>484</v>
+        <v>412</v>
       </c>
       <c r="M1" t="s">
-        <v>485</v>
+        <v>413</v>
       </c>
       <c r="N1" t="s">
-        <v>486</v>
+        <v>414</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -1957,20 +1826,20 @@
       <c r="D2" t="s">
         <v>5</v>
       </c>
-      <c r="F2" t="s">
-        <v>6</v>
+      <c r="F2" s="3" t="s">
+        <v>419</v>
       </c>
       <c r="G2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" t="s">
         <v>7</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>8</v>
       </c>
-      <c r="I2" t="s">
-        <v>9</v>
-      </c>
       <c r="J2" t="s">
-        <v>488</v>
+        <v>416</v>
       </c>
       <c r="K2">
         <v>72308</v>
@@ -1990,7 +1859,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
         <v>4</v>
@@ -1998,20 +1867,20 @@
       <c r="D3" t="s">
         <v>5</v>
       </c>
-      <c r="F3" t="s">
-        <v>11</v>
+      <c r="F3" s="3" t="s">
+        <v>420</v>
       </c>
       <c r="G3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H3" t="s">
         <v>7</v>
       </c>
-      <c r="H3" t="s">
-        <v>8</v>
-      </c>
       <c r="I3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J3" t="s">
-        <v>488</v>
+        <v>416</v>
       </c>
       <c r="K3">
         <v>72308</v>
@@ -2031,31 +1900,31 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
         <v>4</v>
       </c>
       <c r="D4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="G4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I4" t="s">
         <v>14</v>
       </c>
-      <c r="E4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4" t="s">
-        <v>7</v>
-      </c>
-      <c r="H4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I4" t="s">
-        <v>17</v>
-      </c>
       <c r="J4" t="s">
-        <v>488</v>
+        <v>416</v>
       </c>
       <c r="K4">
         <v>130769</v>
@@ -2075,31 +1944,31 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="G5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I5" t="s">
         <v>16</v>
       </c>
-      <c r="F5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G5" t="s">
-        <v>7</v>
-      </c>
-      <c r="H5" t="s">
-        <v>8</v>
-      </c>
-      <c r="I5" t="s">
-        <v>20</v>
-      </c>
       <c r="J5" t="s">
-        <v>488</v>
+        <v>416</v>
       </c>
       <c r="K5">
         <v>64615</v>
@@ -2119,7 +1988,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
         <v>4</v>
@@ -2128,22 +1997,22 @@
         <v>5</v>
       </c>
       <c r="E6" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6" t="s">
-        <v>22</v>
+        <v>18</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>423</v>
       </c>
       <c r="G6" t="s">
+        <v>6</v>
+      </c>
+      <c r="H6" t="s">
         <v>7</v>
       </c>
-      <c r="H6" t="s">
-        <v>8</v>
-      </c>
       <c r="I6" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J6" t="s">
-        <v>488</v>
+        <v>416</v>
       </c>
       <c r="K6">
         <v>80091</v>
@@ -2163,7 +2032,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
         <v>4</v>
@@ -2171,20 +2040,20 @@
       <c r="D7" t="s">
         <v>5</v>
       </c>
-      <c r="F7" t="s">
-        <v>26</v>
+      <c r="F7" s="3" t="s">
+        <v>424</v>
       </c>
       <c r="G7" t="s">
+        <v>6</v>
+      </c>
+      <c r="H7" t="s">
         <v>7</v>
       </c>
-      <c r="H7" t="s">
-        <v>8</v>
-      </c>
       <c r="I7" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J7" t="s">
-        <v>476</v>
+        <v>404</v>
       </c>
       <c r="K7">
         <v>70673</v>
@@ -2204,7 +2073,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s">
         <v>4</v>
@@ -2213,22 +2082,22 @@
         <v>5</v>
       </c>
       <c r="E8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="G8" t="s">
+        <v>6</v>
+      </c>
+      <c r="H8" t="s">
+        <v>7</v>
+      </c>
+      <c r="I8" t="s">
         <v>23</v>
       </c>
-      <c r="F8" t="s">
-        <v>29</v>
-      </c>
-      <c r="G8" t="s">
-        <v>7</v>
-      </c>
-      <c r="H8" t="s">
-        <v>8</v>
-      </c>
-      <c r="I8" t="s">
-        <v>30</v>
-      </c>
       <c r="J8" t="s">
-        <v>488</v>
+        <v>416</v>
       </c>
       <c r="K8">
         <v>90466</v>
@@ -2248,7 +2117,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C9" t="s">
         <v>4</v>
@@ -2256,20 +2125,20 @@
       <c r="D9" t="s">
         <v>5</v>
       </c>
-      <c r="F9" t="s">
-        <v>29</v>
+      <c r="F9" s="3" t="s">
+        <v>424</v>
       </c>
       <c r="G9" t="s">
+        <v>6</v>
+      </c>
+      <c r="H9" t="s">
         <v>7</v>
       </c>
-      <c r="H9" t="s">
-        <v>8</v>
-      </c>
       <c r="I9" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="J9" t="s">
-        <v>476</v>
+        <v>404</v>
       </c>
       <c r="K9">
         <v>46720</v>
@@ -2289,7 +2158,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C10" t="s">
         <v>4</v>
@@ -2298,22 +2167,22 @@
         <v>5</v>
       </c>
       <c r="E10" t="s">
-        <v>23</v>
-      </c>
-      <c r="F10" t="s">
-        <v>34</v>
+        <v>18</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>425</v>
       </c>
       <c r="G10" t="s">
+        <v>6</v>
+      </c>
+      <c r="H10" t="s">
         <v>7</v>
       </c>
-      <c r="H10" t="s">
-        <v>8</v>
-      </c>
       <c r="I10" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="J10" t="s">
-        <v>476</v>
+        <v>404</v>
       </c>
       <c r="K10">
         <v>95000</v>
@@ -2333,7 +2202,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C11" t="s">
         <v>4</v>
@@ -2342,22 +2211,22 @@
         <v>5</v>
       </c>
       <c r="E11" t="s">
-        <v>23</v>
-      </c>
-      <c r="F11" t="s">
-        <v>37</v>
+        <v>18</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>426</v>
       </c>
       <c r="G11" t="s">
+        <v>6</v>
+      </c>
+      <c r="H11" t="s">
         <v>7</v>
       </c>
-      <c r="H11" t="s">
-        <v>8</v>
-      </c>
       <c r="I11" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="J11" t="s">
-        <v>488</v>
+        <v>416</v>
       </c>
       <c r="K11">
         <v>85300</v>
@@ -2377,7 +2246,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C12" t="s">
         <v>4</v>
@@ -2386,22 +2255,22 @@
         <v>5</v>
       </c>
       <c r="E12" t="s">
-        <v>16</v>
-      </c>
-      <c r="F12" t="s">
-        <v>40</v>
+        <v>13</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>426</v>
       </c>
       <c r="G12" t="s">
+        <v>6</v>
+      </c>
+      <c r="H12" t="s">
         <v>7</v>
       </c>
-      <c r="H12" t="s">
-        <v>8</v>
-      </c>
       <c r="I12" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="J12" t="s">
-        <v>476</v>
+        <v>404</v>
       </c>
       <c r="K12">
         <v>33305</v>
@@ -2421,31 +2290,31 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="C13" t="s">
         <v>4</v>
       </c>
       <c r="D13" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E13" t="s">
-        <v>23</v>
-      </c>
-      <c r="F13" t="s">
-        <v>40</v>
+        <v>18</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>426</v>
       </c>
       <c r="G13" t="s">
+        <v>6</v>
+      </c>
+      <c r="H13" t="s">
         <v>7</v>
       </c>
-      <c r="H13" t="s">
-        <v>8</v>
-      </c>
       <c r="I13" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J13" t="s">
-        <v>488</v>
+        <v>416</v>
       </c>
       <c r="K13">
         <v>120245.21</v>
@@ -2465,31 +2334,31 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C14" t="s">
         <v>4</v>
       </c>
       <c r="D14" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E14" t="s">
-        <v>23</v>
-      </c>
-      <c r="F14" t="s">
-        <v>45</v>
+        <v>18</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>427</v>
       </c>
       <c r="G14" t="s">
+        <v>6</v>
+      </c>
+      <c r="H14" t="s">
         <v>7</v>
       </c>
-      <c r="H14" t="s">
-        <v>8</v>
-      </c>
       <c r="I14" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J14" t="s">
-        <v>488</v>
+        <v>416</v>
       </c>
       <c r="K14">
         <v>70425.53</v>
@@ -2509,31 +2378,31 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="C15" t="s">
         <v>4</v>
       </c>
       <c r="D15" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E15" t="s">
-        <v>23</v>
-      </c>
-      <c r="F15" t="s">
-        <v>40</v>
+        <v>18</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>426</v>
       </c>
       <c r="G15" t="s">
+        <v>6</v>
+      </c>
+      <c r="H15" t="s">
         <v>7</v>
       </c>
-      <c r="H15" t="s">
-        <v>8</v>
-      </c>
       <c r="I15" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="J15" t="s">
-        <v>488</v>
+        <v>416</v>
       </c>
       <c r="K15">
         <v>78000</v>
@@ -2553,7 +2422,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="C16" t="s">
         <v>4</v>
@@ -2562,22 +2431,22 @@
         <v>5</v>
       </c>
       <c r="E16" t="s">
-        <v>23</v>
-      </c>
-      <c r="F16" t="s">
-        <v>49</v>
+        <v>18</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>426</v>
       </c>
       <c r="G16" t="s">
+        <v>6</v>
+      </c>
+      <c r="H16" t="s">
         <v>7</v>
       </c>
-      <c r="H16" t="s">
-        <v>8</v>
-      </c>
       <c r="I16" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="J16" t="s">
-        <v>476</v>
+        <v>404</v>
       </c>
       <c r="K16">
         <v>102796</v>
@@ -2597,7 +2466,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="C17" t="s">
         <v>4</v>
@@ -2606,22 +2475,22 @@
         <v>5</v>
       </c>
       <c r="E17" t="s">
-        <v>16</v>
-      </c>
-      <c r="F17" t="s">
-        <v>49</v>
+        <v>13</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>426</v>
       </c>
       <c r="G17" t="s">
+        <v>6</v>
+      </c>
+      <c r="H17" t="s">
         <v>7</v>
       </c>
-      <c r="H17" t="s">
-        <v>8</v>
-      </c>
       <c r="I17" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="J17" t="s">
-        <v>476</v>
+        <v>404</v>
       </c>
       <c r="K17">
         <v>49200</v>
@@ -2641,7 +2510,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="C18" t="s">
         <v>4</v>
@@ -2650,22 +2519,22 @@
         <v>5</v>
       </c>
       <c r="E18" t="s">
-        <v>23</v>
-      </c>
-      <c r="F18" t="s">
-        <v>45</v>
+        <v>18</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>427</v>
       </c>
       <c r="G18" t="s">
+        <v>6</v>
+      </c>
+      <c r="H18" t="s">
         <v>7</v>
       </c>
-      <c r="H18" t="s">
-        <v>8</v>
-      </c>
       <c r="I18" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="J18" t="s">
-        <v>476</v>
+        <v>404</v>
       </c>
       <c r="K18">
         <v>65096</v>
@@ -2685,7 +2554,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="C19" t="s">
         <v>4</v>
@@ -2694,22 +2563,22 @@
         <v>5</v>
       </c>
       <c r="E19" t="s">
-        <v>16</v>
-      </c>
-      <c r="F19" t="s">
-        <v>56</v>
+        <v>13</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>427</v>
       </c>
       <c r="G19" t="s">
+        <v>6</v>
+      </c>
+      <c r="H19" t="s">
         <v>7</v>
       </c>
-      <c r="H19" t="s">
-        <v>8</v>
-      </c>
       <c r="I19" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="J19" t="s">
-        <v>488</v>
+        <v>416</v>
       </c>
       <c r="K19">
         <v>56000</v>
@@ -2729,31 +2598,31 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="C20" t="s">
         <v>4</v>
       </c>
       <c r="D20" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E20" t="s">
-        <v>23</v>
-      </c>
-      <c r="F20" t="s">
-        <v>59</v>
+        <v>18</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>427</v>
       </c>
       <c r="G20" t="s">
+        <v>6</v>
+      </c>
+      <c r="H20" t="s">
         <v>7</v>
       </c>
-      <c r="H20" t="s">
-        <v>8</v>
-      </c>
       <c r="I20" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="J20" t="s">
-        <v>476</v>
+        <v>404</v>
       </c>
       <c r="K20">
         <v>177847</v>
@@ -2773,7 +2642,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="C21" t="s">
         <v>4</v>
@@ -2782,22 +2651,22 @@
         <v>5</v>
       </c>
       <c r="E21" t="s">
-        <v>23</v>
-      </c>
-      <c r="F21" t="s">
-        <v>62</v>
+        <v>18</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>428</v>
       </c>
       <c r="G21" t="s">
+        <v>6</v>
+      </c>
+      <c r="H21" t="s">
         <v>7</v>
       </c>
-      <c r="H21" t="s">
-        <v>8</v>
-      </c>
       <c r="I21" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="J21" t="s">
-        <v>488</v>
+        <v>416</v>
       </c>
       <c r="K21">
         <v>83000</v>
@@ -2817,7 +2686,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="C22" t="s">
         <v>4</v>
@@ -2825,20 +2694,20 @@
       <c r="D22" t="s">
         <v>5</v>
       </c>
-      <c r="F22" t="s">
-        <v>65</v>
+      <c r="F22" s="3" t="s">
+        <v>428</v>
       </c>
       <c r="G22" t="s">
+        <v>6</v>
+      </c>
+      <c r="H22" t="s">
         <v>7</v>
       </c>
-      <c r="H22" t="s">
-        <v>8</v>
-      </c>
       <c r="I22" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="J22" t="s">
-        <v>476</v>
+        <v>404</v>
       </c>
       <c r="K22">
         <v>26000</v>
@@ -2858,7 +2727,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="C23" t="s">
         <v>4</v>
@@ -2867,19 +2736,22 @@
         <v>5</v>
       </c>
       <c r="E23" t="s">
-        <v>23</v>
+        <v>18</v>
+      </c>
+      <c r="F23" s="3">
+        <v>2009</v>
       </c>
       <c r="G23" t="s">
+        <v>6</v>
+      </c>
+      <c r="H23" t="s">
         <v>7</v>
       </c>
-      <c r="H23" t="s">
-        <v>8</v>
-      </c>
       <c r="I23" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="J23" t="s">
-        <v>488</v>
+        <v>416</v>
       </c>
       <c r="K23">
         <v>85887</v>
@@ -2899,7 +2771,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="C24" t="s">
         <v>4</v>
@@ -2908,19 +2780,22 @@
         <v>5</v>
       </c>
       <c r="E24" t="s">
-        <v>23</v>
+        <v>18</v>
+      </c>
+      <c r="F24" s="3">
+        <v>2009</v>
       </c>
       <c r="G24" t="s">
+        <v>6</v>
+      </c>
+      <c r="H24" t="s">
         <v>7</v>
       </c>
-      <c r="H24" t="s">
-        <v>8</v>
-      </c>
       <c r="I24" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="J24" t="s">
-        <v>488</v>
+        <v>416</v>
       </c>
       <c r="K24">
         <v>20000</v>
@@ -2940,7 +2815,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="C25" t="s">
         <v>4</v>
@@ -2949,22 +2824,22 @@
         <v>5</v>
       </c>
       <c r="E25" t="s">
-        <v>23</v>
-      </c>
-      <c r="F25" t="s">
-        <v>72</v>
+        <v>18</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>430</v>
       </c>
       <c r="G25" t="s">
+        <v>6</v>
+      </c>
+      <c r="H25" t="s">
         <v>7</v>
       </c>
-      <c r="H25" t="s">
-        <v>8</v>
-      </c>
       <c r="I25" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="J25" t="s">
-        <v>488</v>
+        <v>416</v>
       </c>
       <c r="K25">
         <v>146385</v>
@@ -2984,31 +2859,31 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="C26" t="s">
         <v>4</v>
       </c>
       <c r="D26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E26" t="s">
-        <v>23</v>
-      </c>
-      <c r="F26" t="s">
-        <v>75</v>
+        <v>18</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>430</v>
       </c>
       <c r="G26" t="s">
+        <v>6</v>
+      </c>
+      <c r="H26" t="s">
         <v>7</v>
       </c>
-      <c r="H26" t="s">
-        <v>8</v>
-      </c>
       <c r="I26" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="J26" t="s">
-        <v>488</v>
+        <v>416</v>
       </c>
       <c r="K26">
         <v>87000</v>
@@ -3028,31 +2903,31 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="C27" t="s">
         <v>4</v>
       </c>
       <c r="D27" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E27" t="s">
-        <v>23</v>
-      </c>
-      <c r="F27" t="s">
-        <v>78</v>
+        <v>18</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>431</v>
       </c>
       <c r="G27" t="s">
+        <v>6</v>
+      </c>
+      <c r="H27" t="s">
         <v>7</v>
       </c>
-      <c r="H27" t="s">
-        <v>8</v>
-      </c>
       <c r="I27" t="s">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="J27" t="s">
-        <v>488</v>
+        <v>416</v>
       </c>
       <c r="K27">
         <v>147166.79999999999</v>
@@ -3072,7 +2947,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="C28" t="s">
         <v>4</v>
@@ -3081,22 +2956,22 @@
         <v>5</v>
       </c>
       <c r="E28" t="s">
-        <v>16</v>
-      </c>
-      <c r="F28" t="s">
-        <v>81</v>
+        <v>13</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>432</v>
       </c>
       <c r="G28" t="s">
+        <v>6</v>
+      </c>
+      <c r="H28" t="s">
         <v>7</v>
       </c>
-      <c r="H28" t="s">
-        <v>8</v>
-      </c>
       <c r="I28" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="J28" t="s">
-        <v>488</v>
+        <v>416</v>
       </c>
       <c r="K28">
         <v>46063</v>
@@ -3116,7 +2991,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="C29" t="s">
         <v>4</v>
@@ -3125,22 +3000,22 @@
         <v>5</v>
       </c>
       <c r="E29" t="s">
-        <v>23</v>
-      </c>
-      <c r="F29" t="s">
-        <v>84</v>
+        <v>18</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>422</v>
       </c>
       <c r="G29" t="s">
+        <v>6</v>
+      </c>
+      <c r="H29" t="s">
         <v>7</v>
       </c>
-      <c r="H29" t="s">
-        <v>8</v>
-      </c>
       <c r="I29" t="s">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="J29" t="s">
-        <v>476</v>
+        <v>404</v>
       </c>
       <c r="K29">
         <v>47261</v>
@@ -3160,31 +3035,31 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="C30" t="s">
         <v>4</v>
       </c>
       <c r="D30" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E30" t="s">
-        <v>23</v>
-      </c>
-      <c r="F30" t="s">
-        <v>87</v>
+        <v>18</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>433</v>
       </c>
       <c r="G30" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H30" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="I30" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="J30" t="s">
-        <v>488</v>
+        <v>416</v>
       </c>
       <c r="K30">
         <v>119000</v>
@@ -3204,7 +3079,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="C31" t="s">
         <v>4</v>
@@ -3212,20 +3087,20 @@
       <c r="D31" t="s">
         <v>5</v>
       </c>
-      <c r="F31" t="s">
-        <v>91</v>
+      <c r="F31" s="3" t="s">
+        <v>433</v>
       </c>
       <c r="G31" t="s">
+        <v>6</v>
+      </c>
+      <c r="H31" t="s">
         <v>7</v>
       </c>
-      <c r="H31" t="s">
-        <v>8</v>
-      </c>
       <c r="I31" t="s">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="J31" t="s">
-        <v>476</v>
+        <v>404</v>
       </c>
       <c r="K31">
         <v>47000</v>
@@ -3245,31 +3120,31 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>93</v>
+        <v>70</v>
       </c>
       <c r="C32" t="s">
         <v>4</v>
       </c>
       <c r="D32" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E32" t="s">
-        <v>16</v>
-      </c>
-      <c r="F32" t="s">
-        <v>91</v>
+        <v>13</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>433</v>
       </c>
       <c r="G32" t="s">
+        <v>6</v>
+      </c>
+      <c r="H32" t="s">
         <v>7</v>
       </c>
-      <c r="H32" t="s">
-        <v>8</v>
-      </c>
       <c r="I32" t="s">
-        <v>94</v>
+        <v>71</v>
       </c>
       <c r="J32" t="s">
-        <v>476</v>
+        <v>404</v>
       </c>
       <c r="K32">
         <v>186000</v>
@@ -3289,7 +3164,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="C33" t="s">
         <v>4</v>
@@ -3297,17 +3172,20 @@
       <c r="D33" t="s">
         <v>5</v>
       </c>
+      <c r="F33" s="3">
+        <v>2019</v>
+      </c>
       <c r="G33" t="s">
+        <v>6</v>
+      </c>
+      <c r="H33" t="s">
         <v>7</v>
       </c>
-      <c r="H33" t="s">
-        <v>8</v>
-      </c>
       <c r="I33" t="s">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="J33" t="s">
-        <v>488</v>
+        <v>416</v>
       </c>
       <c r="K33">
         <v>40800</v>
@@ -3327,7 +3205,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>97</v>
+        <v>74</v>
       </c>
       <c r="C34" t="s">
         <v>4</v>
@@ -3335,20 +3213,20 @@
       <c r="D34" t="s">
         <v>5</v>
       </c>
-      <c r="F34" t="s">
-        <v>98</v>
+      <c r="F34" s="3" t="s">
+        <v>433</v>
       </c>
       <c r="G34" t="s">
+        <v>6</v>
+      </c>
+      <c r="H34" t="s">
         <v>7</v>
       </c>
-      <c r="H34" t="s">
-        <v>8</v>
-      </c>
       <c r="I34" t="s">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="J34" t="s">
-        <v>488</v>
+        <v>416</v>
       </c>
       <c r="K34">
         <v>55200</v>
@@ -3368,31 +3246,31 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="C35" t="s">
         <v>4</v>
       </c>
       <c r="D35" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E35" t="s">
-        <v>16</v>
-      </c>
-      <c r="F35" t="s">
-        <v>98</v>
+        <v>13</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>433</v>
       </c>
       <c r="G35" t="s">
+        <v>6</v>
+      </c>
+      <c r="H35" t="s">
         <v>7</v>
       </c>
-      <c r="H35" t="s">
-        <v>8</v>
-      </c>
       <c r="I35" t="s">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="J35" t="s">
-        <v>476</v>
+        <v>404</v>
       </c>
       <c r="K35">
         <v>350000</v>
@@ -3412,28 +3290,31 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="C36" t="s">
         <v>4</v>
       </c>
       <c r="D36" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E36" t="s">
-        <v>23</v>
+        <v>18</v>
+      </c>
+      <c r="F36" s="3">
+        <v>2020</v>
       </c>
       <c r="G36" t="s">
+        <v>6</v>
+      </c>
+      <c r="H36" t="s">
         <v>7</v>
       </c>
-      <c r="H36" t="s">
-        <v>8</v>
-      </c>
       <c r="I36" t="s">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="J36" t="s">
-        <v>488</v>
+        <v>416</v>
       </c>
       <c r="K36">
         <v>65000</v>
@@ -3453,28 +3334,31 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="C37" t="s">
         <v>4</v>
       </c>
       <c r="D37" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E37" t="s">
-        <v>23</v>
+        <v>18</v>
+      </c>
+      <c r="F37" s="3">
+        <v>2020</v>
       </c>
       <c r="G37" t="s">
+        <v>6</v>
+      </c>
+      <c r="H37" t="s">
         <v>7</v>
       </c>
-      <c r="H37" t="s">
-        <v>8</v>
-      </c>
       <c r="I37" t="s">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="J37" t="s">
-        <v>488</v>
+        <v>416</v>
       </c>
       <c r="K37">
         <v>35000</v>
@@ -3494,7 +3378,7 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="C38" t="s">
         <v>4</v>
@@ -3503,19 +3387,22 @@
         <v>5</v>
       </c>
       <c r="E38" t="s">
-        <v>23</v>
+        <v>18</v>
+      </c>
+      <c r="F38" s="3">
+        <v>2010</v>
       </c>
       <c r="G38" t="s">
+        <v>6</v>
+      </c>
+      <c r="H38" t="s">
         <v>7</v>
       </c>
-      <c r="H38" t="s">
-        <v>8</v>
-      </c>
       <c r="I38" t="s">
-        <v>105</v>
+        <v>81</v>
       </c>
       <c r="J38" t="s">
-        <v>476</v>
+        <v>404</v>
       </c>
       <c r="K38">
         <v>47000</v>
@@ -3535,31 +3422,31 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="C39" t="s">
         <v>4</v>
       </c>
       <c r="D39" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E39" t="s">
-        <v>23</v>
-      </c>
-      <c r="F39" t="s">
-        <v>107</v>
+        <v>18</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>434</v>
       </c>
       <c r="G39" t="s">
+        <v>6</v>
+      </c>
+      <c r="H39" t="s">
         <v>7</v>
       </c>
-      <c r="H39" t="s">
-        <v>8</v>
-      </c>
       <c r="I39" t="s">
-        <v>108</v>
+        <v>83</v>
       </c>
       <c r="J39" t="s">
-        <v>476</v>
+        <v>404</v>
       </c>
       <c r="K39">
         <v>120000</v>
@@ -3579,7 +3466,7 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>109</v>
+        <v>84</v>
       </c>
       <c r="C40" t="s">
         <v>4</v>
@@ -3587,20 +3474,20 @@
       <c r="D40" t="s">
         <v>5</v>
       </c>
-      <c r="F40">
-        <v>2021</v>
+      <c r="F40" s="3" t="s">
+        <v>434</v>
       </c>
       <c r="G40" t="s">
+        <v>6</v>
+      </c>
+      <c r="H40" t="s">
         <v>7</v>
       </c>
-      <c r="H40" t="s">
-        <v>8</v>
-      </c>
       <c r="I40" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="J40" t="s">
-        <v>488</v>
+        <v>416</v>
       </c>
       <c r="K40">
         <v>83000</v>
@@ -3620,28 +3507,31 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="C41" t="s">
         <v>4</v>
       </c>
       <c r="D41" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E41" t="s">
-        <v>16</v>
+        <v>13</v>
+      </c>
+      <c r="F41" s="3">
+        <v>2021</v>
       </c>
       <c r="G41" t="s">
+        <v>6</v>
+      </c>
+      <c r="H41" t="s">
         <v>7</v>
       </c>
-      <c r="H41" t="s">
-        <v>8</v>
-      </c>
       <c r="I41" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="J41" t="s">
-        <v>476</v>
+        <v>404</v>
       </c>
       <c r="K41">
         <v>66030</v>
@@ -3661,7 +3551,7 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="C42" t="s">
         <v>4</v>
@@ -3669,17 +3559,20 @@
       <c r="D42" t="s">
         <v>5</v>
       </c>
+      <c r="F42" s="3">
+        <v>2009</v>
+      </c>
       <c r="G42" t="s">
+        <v>6</v>
+      </c>
+      <c r="H42" t="s">
         <v>7</v>
       </c>
-      <c r="H42" t="s">
-        <v>8</v>
-      </c>
       <c r="I42" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="J42" t="s">
-        <v>476</v>
+        <v>404</v>
       </c>
       <c r="K42">
         <v>40000</v>
@@ -3699,31 +3592,31 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>115</v>
+        <v>90</v>
       </c>
       <c r="C43" t="s">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="D43" t="s">
         <v>5</v>
       </c>
       <c r="E43" t="s">
-        <v>16</v>
-      </c>
-      <c r="F43" t="s">
-        <v>117</v>
+        <v>13</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>435</v>
       </c>
       <c r="G43" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H43" t="s">
-        <v>118</v>
+        <v>92</v>
       </c>
       <c r="I43" t="s">
-        <v>119</v>
+        <v>93</v>
       </c>
       <c r="J43" t="s">
-        <v>488</v>
+        <v>416</v>
       </c>
       <c r="K43">
         <v>40000</v>
@@ -3743,28 +3636,28 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>120</v>
+        <v>94</v>
       </c>
       <c r="C44" t="s">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="D44" t="s">
         <v>5</v>
       </c>
-      <c r="F44" t="s">
-        <v>121</v>
+      <c r="F44" s="3" t="s">
+        <v>420</v>
       </c>
       <c r="G44" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H44" t="s">
-        <v>118</v>
+        <v>92</v>
       </c>
       <c r="I44" t="s">
-        <v>122</v>
+        <v>95</v>
       </c>
       <c r="J44" t="s">
-        <v>488</v>
+        <v>416</v>
       </c>
       <c r="K44">
         <v>54100</v>
@@ -3784,31 +3677,31 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>123</v>
+        <v>96</v>
       </c>
       <c r="C45" t="s">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="D45" t="s">
         <v>5</v>
       </c>
       <c r="E45" t="s">
-        <v>23</v>
-      </c>
-      <c r="F45" t="s">
-        <v>124</v>
+        <v>18</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>436</v>
       </c>
       <c r="G45" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H45" t="s">
-        <v>118</v>
+        <v>92</v>
       </c>
       <c r="I45" t="s">
-        <v>125</v>
+        <v>97</v>
       </c>
       <c r="J45" t="s">
-        <v>488</v>
+        <v>416</v>
       </c>
       <c r="K45">
         <v>100000</v>
@@ -3828,31 +3721,31 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>126</v>
+        <v>98</v>
       </c>
       <c r="C46" t="s">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="D46" t="s">
         <v>5</v>
       </c>
       <c r="E46" t="s">
-        <v>23</v>
-      </c>
-      <c r="F46" t="s">
-        <v>127</v>
+        <v>18</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>437</v>
       </c>
       <c r="G46" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H46" t="s">
-        <v>118</v>
+        <v>92</v>
       </c>
       <c r="I46" t="s">
-        <v>128</v>
+        <v>99</v>
       </c>
       <c r="J46" t="s">
-        <v>488</v>
+        <v>416</v>
       </c>
       <c r="K46">
         <v>150000</v>
@@ -3872,31 +3765,31 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>129</v>
+        <v>100</v>
       </c>
       <c r="C47" t="s">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="D47" t="s">
         <v>5</v>
       </c>
       <c r="E47" t="s">
-        <v>23</v>
-      </c>
-      <c r="F47" t="s">
-        <v>130</v>
+        <v>18</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>438</v>
       </c>
       <c r="G47" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H47" t="s">
-        <v>118</v>
+        <v>92</v>
       </c>
       <c r="I47" t="s">
-        <v>131</v>
+        <v>101</v>
       </c>
       <c r="J47" t="s">
-        <v>488</v>
+        <v>416</v>
       </c>
       <c r="K47">
         <v>50000</v>
@@ -3916,31 +3809,31 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>132</v>
+        <v>102</v>
       </c>
       <c r="C48" t="s">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="D48" t="s">
         <v>5</v>
       </c>
       <c r="E48" t="s">
-        <v>23</v>
-      </c>
-      <c r="F48" t="s">
-        <v>133</v>
+        <v>18</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>424</v>
       </c>
       <c r="G48" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H48" t="s">
-        <v>118</v>
+        <v>92</v>
       </c>
       <c r="I48" t="s">
-        <v>134</v>
+        <v>103</v>
       </c>
       <c r="J48" t="s">
-        <v>489</v>
+        <v>417</v>
       </c>
       <c r="K48">
         <v>43000</v>
@@ -3960,28 +3853,28 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>135</v>
+        <v>104</v>
       </c>
       <c r="C49" t="s">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="D49" t="s">
         <v>5</v>
       </c>
-      <c r="F49" t="s">
-        <v>136</v>
+      <c r="F49" s="3" t="s">
+        <v>425</v>
       </c>
       <c r="G49" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H49" t="s">
-        <v>118</v>
+        <v>92</v>
       </c>
       <c r="I49" t="s">
-        <v>137</v>
+        <v>105</v>
       </c>
       <c r="J49" t="s">
-        <v>489</v>
+        <v>417</v>
       </c>
       <c r="K49">
         <v>65000</v>
@@ -4001,28 +3894,28 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>138</v>
+        <v>106</v>
       </c>
       <c r="C50" t="s">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="D50" t="s">
         <v>5</v>
       </c>
-      <c r="F50" t="s">
-        <v>139</v>
+      <c r="F50" s="3" t="s">
+        <v>426</v>
       </c>
       <c r="G50" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H50" t="s">
-        <v>118</v>
+        <v>92</v>
       </c>
       <c r="I50" t="s">
-        <v>140</v>
+        <v>107</v>
       </c>
       <c r="J50" t="s">
-        <v>489</v>
+        <v>417</v>
       </c>
     </row>
     <row r="51" spans="1:14">
@@ -4030,31 +3923,31 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>141</v>
+        <v>108</v>
       </c>
       <c r="C51" t="s">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="D51" t="s">
         <v>5</v>
       </c>
       <c r="E51" t="s">
-        <v>23</v>
-      </c>
-      <c r="F51" t="s">
-        <v>45</v>
+        <v>18</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>427</v>
       </c>
       <c r="G51" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H51" t="s">
-        <v>118</v>
+        <v>92</v>
       </c>
       <c r="I51" t="s">
-        <v>142</v>
+        <v>109</v>
       </c>
       <c r="J51" t="s">
-        <v>489</v>
+        <v>417</v>
       </c>
       <c r="K51">
         <v>56000</v>
@@ -4074,28 +3967,28 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>143</v>
+        <v>110</v>
       </c>
       <c r="C52" t="s">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="D52" t="s">
         <v>5</v>
       </c>
-      <c r="F52" t="s">
-        <v>59</v>
+      <c r="F52" s="3" t="s">
+        <v>427</v>
       </c>
       <c r="G52" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H52" t="s">
-        <v>118</v>
+        <v>92</v>
       </c>
       <c r="I52" t="s">
-        <v>144</v>
+        <v>111</v>
       </c>
       <c r="J52" t="s">
-        <v>489</v>
+        <v>417</v>
       </c>
       <c r="K52">
         <v>160000</v>
@@ -4115,28 +4008,28 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>145</v>
+        <v>112</v>
       </c>
       <c r="C53" t="s">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="D53" t="s">
         <v>5</v>
       </c>
-      <c r="F53" t="s">
+      <c r="F53" s="3" t="s">
         <v>4</v>
       </c>
       <c r="G53" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H53" t="s">
-        <v>118</v>
+        <v>92</v>
       </c>
       <c r="I53" t="s">
-        <v>146</v>
+        <v>113</v>
       </c>
       <c r="J53" t="s">
-        <v>489</v>
+        <v>417</v>
       </c>
       <c r="K53">
         <v>33000</v>
@@ -4156,31 +4049,31 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>147</v>
+        <v>114</v>
       </c>
       <c r="C54" t="s">
+        <v>91</v>
+      </c>
+      <c r="D54" t="s">
+        <v>5</v>
+      </c>
+      <c r="E54" t="s">
+        <v>13</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="G54" t="s">
+        <v>6</v>
+      </c>
+      <c r="H54" t="s">
+        <v>92</v>
+      </c>
+      <c r="I54" t="s">
         <v>116</v>
       </c>
-      <c r="D54" t="s">
-        <v>5</v>
-      </c>
-      <c r="E54" t="s">
-        <v>16</v>
-      </c>
-      <c r="F54" t="s">
-        <v>148</v>
-      </c>
-      <c r="G54" t="s">
-        <v>7</v>
-      </c>
-      <c r="H54" t="s">
-        <v>118</v>
-      </c>
-      <c r="I54" t="s">
-        <v>149</v>
-      </c>
       <c r="J54" t="s">
-        <v>489</v>
+        <v>417</v>
       </c>
       <c r="K54">
         <v>41318</v>
@@ -4200,28 +4093,28 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>150</v>
+        <v>117</v>
       </c>
       <c r="C55" t="s">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="D55" t="s">
         <v>5</v>
       </c>
-      <c r="F55" t="s">
-        <v>139</v>
+      <c r="F55" s="3" t="s">
+        <v>426</v>
       </c>
       <c r="G55" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H55" t="s">
+        <v>92</v>
+      </c>
+      <c r="I55" t="s">
         <v>118</v>
       </c>
-      <c r="I55" t="s">
-        <v>151</v>
-      </c>
       <c r="J55" t="s">
-        <v>488</v>
+        <v>416</v>
       </c>
       <c r="K55">
         <v>34131</v>
@@ -4241,28 +4134,28 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>152</v>
+        <v>119</v>
       </c>
       <c r="C56" t="s">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="D56" t="s">
         <v>5</v>
       </c>
-      <c r="F56" t="s">
-        <v>153</v>
+      <c r="F56" s="3" t="s">
+        <v>439</v>
       </c>
       <c r="G56" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H56" t="s">
-        <v>118</v>
+        <v>92</v>
       </c>
       <c r="I56" t="s">
-        <v>154</v>
+        <v>120</v>
       </c>
       <c r="J56" t="s">
-        <v>488</v>
+        <v>416</v>
       </c>
       <c r="K56">
         <v>48000</v>
@@ -4282,28 +4175,28 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>155</v>
+        <v>121</v>
       </c>
       <c r="C57" t="s">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="D57" t="s">
         <v>5</v>
       </c>
-      <c r="F57">
-        <v>2017</v>
+      <c r="F57" s="3" t="s">
+        <v>422</v>
       </c>
       <c r="G57" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H57" t="s">
-        <v>118</v>
+        <v>92</v>
       </c>
       <c r="I57" t="s">
-        <v>119</v>
+        <v>93</v>
       </c>
       <c r="J57" t="s">
-        <v>488</v>
+        <v>416</v>
       </c>
       <c r="K57">
         <v>16000</v>
@@ -4323,31 +4216,31 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>156</v>
+        <v>122</v>
       </c>
       <c r="C58" t="s">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="D58" t="s">
         <v>5</v>
       </c>
       <c r="E58" t="s">
-        <v>16</v>
-      </c>
-      <c r="F58" t="s">
-        <v>157</v>
+        <v>13</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>422</v>
       </c>
       <c r="G58" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H58" t="s">
-        <v>118</v>
+        <v>92</v>
       </c>
       <c r="I58" t="s">
-        <v>158</v>
+        <v>123</v>
       </c>
       <c r="J58" t="s">
-        <v>489</v>
+        <v>417</v>
       </c>
       <c r="K58">
         <v>30000</v>
@@ -4367,31 +4260,31 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>159</v>
+        <v>124</v>
       </c>
       <c r="C59" t="s">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="D59" t="s">
         <v>5</v>
       </c>
       <c r="E59" t="s">
-        <v>16</v>
-      </c>
-      <c r="F59" t="s">
-        <v>160</v>
+        <v>13</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>440</v>
       </c>
       <c r="G59" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H59" t="s">
-        <v>118</v>
+        <v>92</v>
       </c>
       <c r="I59" t="s">
-        <v>161</v>
+        <v>125</v>
       </c>
       <c r="J59" t="s">
-        <v>489</v>
+        <v>417</v>
       </c>
       <c r="K59">
         <v>56000</v>
@@ -4411,31 +4304,31 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>162</v>
+        <v>126</v>
       </c>
       <c r="C60" t="s">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="D60" t="s">
         <v>5</v>
       </c>
       <c r="E60" t="s">
-        <v>16</v>
-      </c>
-      <c r="F60" t="s">
-        <v>163</v>
+        <v>13</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>440</v>
       </c>
       <c r="G60" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H60" t="s">
-        <v>118</v>
+        <v>92</v>
       </c>
       <c r="I60" t="s">
-        <v>164</v>
+        <v>127</v>
       </c>
       <c r="J60" t="s">
-        <v>488</v>
+        <v>416</v>
       </c>
       <c r="K60">
         <v>43000</v>
@@ -4455,28 +4348,31 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>165</v>
+        <v>128</v>
       </c>
       <c r="C61" t="s">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="D61" t="s">
         <v>5</v>
       </c>
       <c r="E61" t="s">
-        <v>16</v>
+        <v>13</v>
+      </c>
+      <c r="F61" s="3">
+        <v>2020</v>
       </c>
       <c r="G61" t="s">
+        <v>6</v>
+      </c>
+      <c r="H61" t="s">
         <v>7</v>
       </c>
-      <c r="H61" t="s">
-        <v>8</v>
-      </c>
       <c r="I61" t="s">
-        <v>166</v>
+        <v>129</v>
       </c>
       <c r="J61" t="s">
-        <v>489</v>
+        <v>417</v>
       </c>
       <c r="K61">
         <v>110000</v>
@@ -4496,25 +4392,28 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>167</v>
+        <v>130</v>
       </c>
       <c r="C62" t="s">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="D62" t="s">
         <v>5</v>
       </c>
+      <c r="F62" s="3">
+        <v>2021</v>
+      </c>
       <c r="G62" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H62" t="s">
-        <v>118</v>
+        <v>92</v>
       </c>
       <c r="I62" t="s">
-        <v>168</v>
+        <v>131</v>
       </c>
       <c r="J62" t="s">
-        <v>488</v>
+        <v>416</v>
       </c>
       <c r="K62">
         <v>56160</v>
@@ -4534,28 +4433,31 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>169</v>
+        <v>132</v>
       </c>
       <c r="C63" t="s">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="D63" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E63" t="s">
-        <v>23</v>
+        <v>18</v>
+      </c>
+      <c r="F63" s="3">
+        <v>2023</v>
       </c>
       <c r="G63" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H63" t="s">
-        <v>118</v>
+        <v>92</v>
       </c>
       <c r="I63" t="s">
-        <v>170</v>
+        <v>133</v>
       </c>
       <c r="J63" t="s">
-        <v>488</v>
+        <v>416</v>
       </c>
       <c r="K63">
         <v>138444</v>
@@ -4575,31 +4477,31 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>171</v>
+        <v>134</v>
       </c>
       <c r="C64" t="s">
-        <v>172</v>
+        <v>135</v>
       </c>
       <c r="D64" t="s">
         <v>5</v>
       </c>
       <c r="E64" t="s">
-        <v>16</v>
-      </c>
-      <c r="F64" t="s">
-        <v>173</v>
+        <v>13</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>436</v>
       </c>
       <c r="G64" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H64" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="I64" t="s">
-        <v>174</v>
+        <v>136</v>
       </c>
       <c r="J64" t="s">
-        <v>472</v>
+        <v>400</v>
       </c>
       <c r="K64">
         <v>31000</v>
@@ -4619,28 +4521,28 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>175</v>
+        <v>137</v>
       </c>
       <c r="C65" t="s">
-        <v>172</v>
+        <v>135</v>
       </c>
       <c r="D65" t="s">
-        <v>14</v>
-      </c>
-      <c r="F65" t="s">
-        <v>176</v>
+        <v>12</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>424</v>
       </c>
       <c r="G65" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H65" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="I65" t="s">
-        <v>177</v>
+        <v>138</v>
       </c>
       <c r="J65" t="s">
-        <v>472</v>
+        <v>400</v>
       </c>
       <c r="K65">
         <v>120000</v>
@@ -4660,28 +4562,28 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>178</v>
+        <v>139</v>
       </c>
       <c r="C66" t="s">
-        <v>172</v>
+        <v>135</v>
       </c>
       <c r="D66" t="s">
         <v>5</v>
       </c>
-      <c r="F66" t="s">
-        <v>34</v>
+      <c r="F66" s="3" t="s">
+        <v>425</v>
       </c>
       <c r="G66" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H66" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="I66" t="s">
-        <v>179</v>
+        <v>140</v>
       </c>
       <c r="J66" t="s">
-        <v>472</v>
+        <v>400</v>
       </c>
       <c r="K66">
         <v>25900</v>
@@ -4701,28 +4603,28 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>180</v>
+        <v>141</v>
       </c>
       <c r="C67" t="s">
-        <v>172</v>
+        <v>135</v>
       </c>
       <c r="D67" t="s">
         <v>5</v>
       </c>
-      <c r="F67" t="s">
-        <v>181</v>
+      <c r="F67" s="3" t="s">
+        <v>425</v>
       </c>
       <c r="G67" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H67" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="I67" t="s">
-        <v>182</v>
+        <v>142</v>
       </c>
       <c r="J67" t="s">
-        <v>472</v>
+        <v>400</v>
       </c>
       <c r="K67">
         <v>47986</v>
@@ -4742,31 +4644,31 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>183</v>
+        <v>143</v>
       </c>
       <c r="C68" t="s">
-        <v>172</v>
+        <v>135</v>
       </c>
       <c r="D68" t="s">
         <v>5</v>
       </c>
       <c r="E68" t="s">
-        <v>23</v>
-      </c>
-      <c r="F68" t="s">
-        <v>37</v>
+        <v>18</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>426</v>
       </c>
       <c r="G68" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H68" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="I68" t="s">
-        <v>184</v>
+        <v>144</v>
       </c>
       <c r="J68" t="s">
-        <v>472</v>
+        <v>400</v>
       </c>
       <c r="K68">
         <v>194000</v>
@@ -4786,31 +4688,31 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>185</v>
+        <v>145</v>
       </c>
       <c r="C69" t="s">
-        <v>172</v>
+        <v>135</v>
       </c>
       <c r="D69" t="s">
         <v>5</v>
       </c>
       <c r="E69" t="s">
-        <v>16</v>
-      </c>
-      <c r="F69" t="s">
-        <v>40</v>
+        <v>13</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>426</v>
       </c>
       <c r="G69" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H69" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="I69" t="s">
-        <v>186</v>
+        <v>146</v>
       </c>
       <c r="J69" t="s">
-        <v>472</v>
+        <v>400</v>
       </c>
       <c r="K69">
         <v>39724</v>
@@ -4830,28 +4732,28 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>187</v>
+        <v>147</v>
       </c>
       <c r="C70" t="s">
-        <v>172</v>
+        <v>135</v>
       </c>
       <c r="D70" t="s">
         <v>5</v>
       </c>
-      <c r="F70" t="s">
-        <v>49</v>
+      <c r="F70" s="3" t="s">
+        <v>426</v>
       </c>
       <c r="G70" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H70" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="I70" t="s">
-        <v>188</v>
+        <v>148</v>
       </c>
       <c r="J70" t="s">
-        <v>472</v>
+        <v>400</v>
       </c>
       <c r="K70">
         <v>48437.45</v>
@@ -4871,28 +4773,28 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>189</v>
+        <v>149</v>
       </c>
       <c r="C71" t="s">
-        <v>172</v>
+        <v>135</v>
       </c>
       <c r="D71" t="s">
         <v>5</v>
       </c>
-      <c r="F71" t="s">
-        <v>190</v>
+      <c r="F71" s="3" t="s">
+        <v>426</v>
       </c>
       <c r="G71" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H71" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="I71" t="s">
-        <v>191</v>
+        <v>150</v>
       </c>
       <c r="J71" t="s">
-        <v>472</v>
+        <v>400</v>
       </c>
       <c r="K71">
         <v>37910</v>
@@ -4912,28 +4814,28 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>192</v>
+        <v>151</v>
       </c>
       <c r="C72" t="s">
-        <v>172</v>
+        <v>135</v>
       </c>
       <c r="D72" t="s">
         <v>5</v>
       </c>
-      <c r="F72" t="s">
-        <v>190</v>
+      <c r="F72" s="3" t="s">
+        <v>426</v>
       </c>
       <c r="G72" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H72" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="I72" t="s">
-        <v>193</v>
+        <v>152</v>
       </c>
       <c r="J72" t="s">
-        <v>472</v>
+        <v>400</v>
       </c>
       <c r="K72">
         <v>21220</v>
@@ -4953,28 +4855,28 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>194</v>
+        <v>153</v>
       </c>
       <c r="C73" t="s">
-        <v>172</v>
+        <v>135</v>
       </c>
       <c r="D73" t="s">
         <v>5</v>
       </c>
-      <c r="F73" t="s">
-        <v>56</v>
+      <c r="F73" s="3" t="s">
+        <v>427</v>
       </c>
       <c r="G73" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H73" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="I73" t="s">
-        <v>195</v>
+        <v>154</v>
       </c>
       <c r="J73" t="s">
-        <v>472</v>
+        <v>400</v>
       </c>
       <c r="K73">
         <v>77877</v>
@@ -4994,31 +4896,31 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>196</v>
+        <v>155</v>
       </c>
       <c r="C74" t="s">
-        <v>172</v>
+        <v>135</v>
       </c>
       <c r="D74" t="s">
         <v>5</v>
       </c>
       <c r="E74" t="s">
-        <v>16</v>
-      </c>
-      <c r="F74" t="s">
-        <v>62</v>
+        <v>13</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>428</v>
       </c>
       <c r="G74" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H74" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="I74" t="s">
-        <v>197</v>
+        <v>156</v>
       </c>
       <c r="J74" t="s">
-        <v>472</v>
+        <v>400</v>
       </c>
       <c r="K74">
         <v>80311.53</v>
@@ -5038,31 +4940,31 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>198</v>
+        <v>157</v>
       </c>
       <c r="C75" t="s">
-        <v>172</v>
+        <v>135</v>
       </c>
       <c r="D75" t="s">
         <v>5</v>
       </c>
       <c r="E75" t="s">
-        <v>23</v>
-      </c>
-      <c r="F75" t="s">
-        <v>199</v>
+        <v>18</v>
+      </c>
+      <c r="F75" s="3" t="s">
+        <v>421</v>
       </c>
       <c r="G75" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H75" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="I75" t="s">
-        <v>200</v>
+        <v>158</v>
       </c>
       <c r="J75" t="s">
-        <v>472</v>
+        <v>400</v>
       </c>
       <c r="K75">
         <v>38000</v>
@@ -5082,28 +4984,28 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>201</v>
+        <v>159</v>
       </c>
       <c r="C76" t="s">
-        <v>172</v>
+        <v>135</v>
       </c>
       <c r="D76" t="s">
         <v>5</v>
       </c>
-      <c r="F76" t="s">
-        <v>202</v>
+      <c r="F76" s="3" t="s">
+        <v>431</v>
       </c>
       <c r="G76" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H76" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="I76" t="s">
-        <v>203</v>
+        <v>160</v>
       </c>
       <c r="J76" t="s">
-        <v>472</v>
+        <v>400</v>
       </c>
       <c r="K76">
         <v>37800</v>
@@ -5123,31 +5025,31 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>204</v>
+        <v>161</v>
       </c>
       <c r="C77" t="s">
-        <v>172</v>
+        <v>135</v>
       </c>
       <c r="D77" t="s">
         <v>5</v>
       </c>
       <c r="E77" t="s">
-        <v>16</v>
-      </c>
-      <c r="F77" t="s">
-        <v>205</v>
+        <v>13</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>441</v>
       </c>
       <c r="G77" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H77" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="I77" t="s">
-        <v>206</v>
+        <v>162</v>
       </c>
       <c r="J77" t="s">
-        <v>472</v>
+        <v>400</v>
       </c>
       <c r="K77">
         <v>54581</v>
@@ -5167,31 +5069,31 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>207</v>
+        <v>163</v>
       </c>
       <c r="C78" t="s">
-        <v>172</v>
+        <v>135</v>
       </c>
       <c r="D78" t="s">
         <v>5</v>
       </c>
       <c r="E78" t="s">
-        <v>16</v>
-      </c>
-      <c r="F78" t="s">
-        <v>208</v>
+        <v>13</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>439</v>
       </c>
       <c r="G78" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H78" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="I78" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="J78" t="s">
-        <v>472</v>
+        <v>400</v>
       </c>
       <c r="K78">
         <v>25000</v>
@@ -5211,31 +5113,31 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>209</v>
+        <v>164</v>
       </c>
       <c r="C79" t="s">
-        <v>172</v>
+        <v>135</v>
       </c>
       <c r="D79" t="s">
         <v>5</v>
       </c>
       <c r="E79" t="s">
-        <v>16</v>
-      </c>
-      <c r="F79" t="s">
-        <v>91</v>
+        <v>13</v>
+      </c>
+      <c r="F79" s="3" t="s">
+        <v>433</v>
       </c>
       <c r="G79" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H79" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="I79" t="s">
-        <v>210</v>
+        <v>165</v>
       </c>
       <c r="J79" t="s">
-        <v>472</v>
+        <v>400</v>
       </c>
       <c r="K79">
         <v>52698</v>
@@ -5255,28 +5157,28 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>211</v>
+        <v>166</v>
       </c>
       <c r="C80" t="s">
-        <v>172</v>
+        <v>135</v>
       </c>
       <c r="D80" t="s">
         <v>5</v>
       </c>
-      <c r="F80" t="s">
-        <v>212</v>
+      <c r="F80" s="3" t="s">
+        <v>426</v>
       </c>
       <c r="G80" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H80" t="s">
-        <v>213</v>
+        <v>167</v>
       </c>
       <c r="I80" t="s">
-        <v>214</v>
+        <v>168</v>
       </c>
       <c r="J80" t="s">
-        <v>472</v>
+        <v>400</v>
       </c>
       <c r="K80">
         <v>38500</v>
@@ -5296,25 +5198,28 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>215</v>
+        <v>169</v>
       </c>
       <c r="C81" t="s">
-        <v>172</v>
+        <v>135</v>
       </c>
       <c r="D81" t="s">
-        <v>216</v>
+        <v>170</v>
+      </c>
+      <c r="F81" s="3">
+        <v>2011</v>
       </c>
       <c r="G81" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H81" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="I81" t="s">
-        <v>217</v>
+        <v>171</v>
       </c>
       <c r="J81" t="s">
-        <v>472</v>
+        <v>400</v>
       </c>
       <c r="K81">
         <v>27200</v>
@@ -5334,31 +5239,31 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>218</v>
+        <v>172</v>
       </c>
       <c r="C82" t="s">
-        <v>148</v>
+        <v>115</v>
       </c>
       <c r="D82" t="s">
         <v>5</v>
       </c>
       <c r="E82" t="s">
-        <v>16</v>
-      </c>
-      <c r="F82" t="s">
-        <v>219</v>
+        <v>13</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>420</v>
       </c>
       <c r="G82" t="s">
+        <v>6</v>
+      </c>
+      <c r="H82" t="s">
         <v>7</v>
       </c>
-      <c r="H82" t="s">
-        <v>8</v>
-      </c>
       <c r="I82" t="s">
-        <v>220</v>
+        <v>173</v>
       </c>
       <c r="J82" t="s">
-        <v>473</v>
+        <v>401</v>
       </c>
       <c r="K82">
         <v>60000</v>
@@ -5378,28 +5283,28 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>221</v>
+        <v>174</v>
       </c>
       <c r="C83" t="s">
-        <v>148</v>
+        <v>115</v>
       </c>
       <c r="D83" t="s">
         <v>5</v>
       </c>
-      <c r="F83" t="s">
-        <v>222</v>
+      <c r="F83" s="3" t="s">
+        <v>436</v>
       </c>
       <c r="G83" t="s">
+        <v>6</v>
+      </c>
+      <c r="H83" t="s">
         <v>7</v>
       </c>
-      <c r="H83" t="s">
-        <v>8</v>
-      </c>
       <c r="I83" t="s">
-        <v>223</v>
+        <v>175</v>
       </c>
       <c r="J83" t="s">
-        <v>488</v>
+        <v>416</v>
       </c>
       <c r="K83">
         <v>50000</v>
@@ -5419,31 +5324,31 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>224</v>
+        <v>176</v>
       </c>
       <c r="C84" t="s">
-        <v>148</v>
+        <v>115</v>
       </c>
       <c r="D84" t="s">
         <v>5</v>
       </c>
       <c r="E84" t="s">
-        <v>23</v>
-      </c>
-      <c r="F84" t="s">
-        <v>133</v>
+        <v>18</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>424</v>
       </c>
       <c r="G84" t="s">
+        <v>6</v>
+      </c>
+      <c r="H84" t="s">
         <v>7</v>
       </c>
-      <c r="H84" t="s">
-        <v>8</v>
-      </c>
       <c r="I84" t="s">
-        <v>225</v>
+        <v>177</v>
       </c>
       <c r="J84" t="s">
-        <v>473</v>
+        <v>401</v>
       </c>
       <c r="K84">
         <v>131575</v>
@@ -5463,28 +5368,28 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>226</v>
+        <v>178</v>
       </c>
       <c r="C85" t="s">
-        <v>148</v>
+        <v>115</v>
       </c>
       <c r="D85" t="s">
         <v>5</v>
       </c>
-      <c r="F85" t="s">
-        <v>56</v>
+      <c r="F85" s="3" t="s">
+        <v>427</v>
       </c>
       <c r="G85" t="s">
+        <v>6</v>
+      </c>
+      <c r="H85" t="s">
         <v>7</v>
       </c>
-      <c r="H85" t="s">
-        <v>8</v>
-      </c>
       <c r="I85" t="s">
-        <v>227</v>
+        <v>179</v>
       </c>
       <c r="J85" t="s">
-        <v>488</v>
+        <v>416</v>
       </c>
       <c r="K85">
         <v>99500</v>
@@ -5504,28 +5409,28 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>228</v>
+        <v>180</v>
       </c>
       <c r="C86" t="s">
-        <v>148</v>
+        <v>115</v>
       </c>
       <c r="D86" t="s">
         <v>5</v>
       </c>
-      <c r="F86" t="s">
-        <v>229</v>
+      <c r="F86" s="3" t="s">
+        <v>421</v>
       </c>
       <c r="G86" t="s">
+        <v>6</v>
+      </c>
+      <c r="H86" t="s">
         <v>7</v>
       </c>
-      <c r="H86" t="s">
-        <v>8</v>
-      </c>
       <c r="I86" t="s">
-        <v>230</v>
+        <v>181</v>
       </c>
       <c r="J86" t="s">
-        <v>473</v>
+        <v>401</v>
       </c>
       <c r="K86">
         <v>32000</v>
@@ -5545,31 +5450,31 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>231</v>
+        <v>182</v>
       </c>
       <c r="C87" t="s">
-        <v>148</v>
+        <v>115</v>
       </c>
       <c r="D87" t="s">
         <v>5</v>
       </c>
       <c r="E87" t="s">
-        <v>23</v>
-      </c>
-      <c r="F87" t="s">
-        <v>199</v>
+        <v>18</v>
+      </c>
+      <c r="F87" s="3" t="s">
+        <v>421</v>
       </c>
       <c r="G87" t="s">
+        <v>6</v>
+      </c>
+      <c r="H87" t="s">
         <v>7</v>
       </c>
-      <c r="H87" t="s">
-        <v>8</v>
-      </c>
       <c r="I87" t="s">
-        <v>232</v>
+        <v>183</v>
       </c>
       <c r="J87" t="s">
-        <v>473</v>
+        <v>401</v>
       </c>
       <c r="K87">
         <v>52170</v>
@@ -5589,28 +5494,28 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>233</v>
+        <v>184</v>
       </c>
       <c r="C88" t="s">
-        <v>148</v>
+        <v>115</v>
       </c>
       <c r="D88" t="s">
         <v>5</v>
       </c>
-      <c r="F88" t="s">
-        <v>234</v>
+      <c r="F88" s="3" t="s">
+        <v>430</v>
       </c>
       <c r="G88" t="s">
+        <v>6</v>
+      </c>
+      <c r="H88" t="s">
         <v>7</v>
       </c>
-      <c r="H88" t="s">
-        <v>8</v>
-      </c>
       <c r="I88" t="s">
-        <v>235</v>
+        <v>185</v>
       </c>
       <c r="J88" t="s">
-        <v>473</v>
+        <v>401</v>
       </c>
       <c r="K88">
         <v>46000</v>
@@ -5630,31 +5535,31 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>236</v>
+        <v>186</v>
       </c>
       <c r="C89" t="s">
-        <v>148</v>
+        <v>115</v>
       </c>
       <c r="D89" t="s">
         <v>5</v>
       </c>
       <c r="E89" t="s">
-        <v>23</v>
-      </c>
-      <c r="F89" t="s">
-        <v>237</v>
+        <v>18</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>442</v>
       </c>
       <c r="G89" t="s">
+        <v>6</v>
+      </c>
+      <c r="H89" t="s">
         <v>7</v>
       </c>
-      <c r="H89" t="s">
-        <v>8</v>
-      </c>
       <c r="I89" t="s">
-        <v>238</v>
+        <v>187</v>
       </c>
       <c r="J89" t="s">
-        <v>488</v>
+        <v>416</v>
       </c>
       <c r="K89">
         <v>45013</v>
@@ -5674,28 +5579,28 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>239</v>
+        <v>188</v>
       </c>
       <c r="C90" t="s">
-        <v>148</v>
+        <v>115</v>
       </c>
       <c r="D90" t="s">
         <v>5</v>
       </c>
-      <c r="F90" t="s">
-        <v>78</v>
+      <c r="F90" s="3" t="s">
+        <v>431</v>
       </c>
       <c r="G90" t="s">
+        <v>6</v>
+      </c>
+      <c r="H90" t="s">
         <v>7</v>
       </c>
-      <c r="H90" t="s">
-        <v>8</v>
-      </c>
       <c r="I90" t="s">
-        <v>240</v>
+        <v>189</v>
       </c>
       <c r="J90" t="s">
-        <v>473</v>
+        <v>401</v>
       </c>
       <c r="K90">
         <v>48566</v>
@@ -5715,28 +5620,28 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>241</v>
+        <v>190</v>
       </c>
       <c r="C91" t="s">
-        <v>148</v>
+        <v>115</v>
       </c>
       <c r="D91" t="s">
         <v>5</v>
       </c>
-      <c r="F91" t="s">
-        <v>242</v>
+      <c r="F91" s="3" t="s">
+        <v>432</v>
       </c>
       <c r="G91" t="s">
+        <v>6</v>
+      </c>
+      <c r="H91" t="s">
         <v>7</v>
       </c>
-      <c r="H91" t="s">
-        <v>8</v>
-      </c>
       <c r="I91" t="s">
-        <v>243</v>
+        <v>191</v>
       </c>
       <c r="J91" t="s">
-        <v>488</v>
+        <v>416</v>
       </c>
       <c r="K91">
         <v>55618</v>
@@ -5756,28 +5661,28 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>244</v>
+        <v>192</v>
       </c>
       <c r="C92" t="s">
-        <v>148</v>
+        <v>115</v>
       </c>
       <c r="D92" t="s">
         <v>5</v>
       </c>
-      <c r="F92" t="s">
-        <v>205</v>
+      <c r="F92" s="3" t="s">
+        <v>441</v>
       </c>
       <c r="G92" t="s">
+        <v>6</v>
+      </c>
+      <c r="H92" t="s">
         <v>7</v>
       </c>
-      <c r="H92" t="s">
-        <v>8</v>
-      </c>
       <c r="I92" t="s">
-        <v>245</v>
+        <v>193</v>
       </c>
       <c r="J92" t="s">
-        <v>473</v>
+        <v>401</v>
       </c>
       <c r="K92">
         <v>47000</v>
@@ -5797,31 +5702,31 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>246</v>
+        <v>194</v>
       </c>
       <c r="C93" t="s">
-        <v>148</v>
+        <v>115</v>
       </c>
       <c r="D93" t="s">
         <v>5</v>
       </c>
       <c r="E93" t="s">
-        <v>23</v>
-      </c>
-      <c r="F93" t="s">
-        <v>247</v>
+        <v>18</v>
+      </c>
+      <c r="F93" s="3" t="s">
+        <v>439</v>
       </c>
       <c r="G93" t="s">
+        <v>6</v>
+      </c>
+      <c r="H93" t="s">
         <v>7</v>
       </c>
-      <c r="H93" t="s">
-        <v>8</v>
-      </c>
       <c r="I93" t="s">
-        <v>248</v>
+        <v>195</v>
       </c>
       <c r="J93" t="s">
-        <v>488</v>
+        <v>416</v>
       </c>
       <c r="K93">
         <v>87763</v>
@@ -5841,31 +5746,31 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>249</v>
+        <v>196</v>
       </c>
       <c r="C94" t="s">
-        <v>148</v>
+        <v>115</v>
       </c>
       <c r="D94" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E94" t="s">
-        <v>16</v>
-      </c>
-      <c r="F94" t="s">
-        <v>250</v>
+        <v>13</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>439</v>
       </c>
       <c r="G94" t="s">
+        <v>6</v>
+      </c>
+      <c r="H94" t="s">
         <v>7</v>
       </c>
-      <c r="H94" t="s">
-        <v>8</v>
-      </c>
       <c r="I94" t="s">
-        <v>251</v>
+        <v>197</v>
       </c>
       <c r="J94" t="s">
-        <v>473</v>
+        <v>401</v>
       </c>
       <c r="K94">
         <v>100658</v>
@@ -5885,28 +5790,28 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>252</v>
+        <v>198</v>
       </c>
       <c r="C95" t="s">
-        <v>148</v>
+        <v>115</v>
       </c>
       <c r="D95" t="s">
         <v>5</v>
       </c>
-      <c r="F95" t="s">
-        <v>253</v>
+      <c r="F95" s="3" t="s">
+        <v>441</v>
       </c>
       <c r="G95" t="s">
+        <v>6</v>
+      </c>
+      <c r="H95" t="s">
         <v>7</v>
       </c>
-      <c r="H95" t="s">
-        <v>8</v>
-      </c>
       <c r="I95" t="s">
-        <v>254</v>
+        <v>199</v>
       </c>
       <c r="J95" t="s">
-        <v>473</v>
+        <v>401</v>
       </c>
       <c r="K95">
         <v>67000</v>
@@ -5926,31 +5831,31 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>255</v>
+        <v>200</v>
       </c>
       <c r="C96" t="s">
-        <v>148</v>
+        <v>115</v>
       </c>
       <c r="D96" t="s">
         <v>5</v>
       </c>
       <c r="E96" t="s">
-        <v>16</v>
-      </c>
-      <c r="F96" t="s">
-        <v>84</v>
+        <v>13</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>422</v>
       </c>
       <c r="G96" t="s">
+        <v>6</v>
+      </c>
+      <c r="H96" t="s">
         <v>7</v>
       </c>
-      <c r="H96" t="s">
-        <v>8</v>
-      </c>
       <c r="I96" t="s">
-        <v>256</v>
+        <v>201</v>
       </c>
       <c r="J96" t="s">
-        <v>473</v>
+        <v>401</v>
       </c>
       <c r="K96">
         <v>39431</v>
@@ -5970,28 +5875,28 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>257</v>
+        <v>202</v>
       </c>
       <c r="C97" t="s">
-        <v>148</v>
+        <v>115</v>
       </c>
       <c r="D97" t="s">
         <v>5</v>
       </c>
-      <c r="F97" t="s">
-        <v>87</v>
+      <c r="F97" s="3" t="s">
+        <v>433</v>
       </c>
       <c r="G97" t="s">
+        <v>6</v>
+      </c>
+      <c r="H97" t="s">
         <v>7</v>
       </c>
-      <c r="H97" t="s">
-        <v>8</v>
-      </c>
       <c r="I97" t="s">
-        <v>258</v>
+        <v>203</v>
       </c>
       <c r="J97" t="s">
-        <v>473</v>
+        <v>401</v>
       </c>
       <c r="K97">
         <v>34273</v>
@@ -6011,25 +5916,28 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>259</v>
+        <v>204</v>
       </c>
       <c r="C98" t="s">
-        <v>148</v>
+        <v>115</v>
       </c>
       <c r="D98" t="s">
         <v>5</v>
       </c>
+      <c r="F98" s="3">
+        <v>2020</v>
+      </c>
       <c r="G98" t="s">
+        <v>6</v>
+      </c>
+      <c r="H98" t="s">
         <v>7</v>
       </c>
-      <c r="H98" t="s">
-        <v>8</v>
-      </c>
       <c r="I98" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="J98" t="s">
-        <v>488</v>
+        <v>416</v>
       </c>
       <c r="K98">
         <v>40000</v>
@@ -6049,28 +5957,31 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>260</v>
+        <v>205</v>
       </c>
       <c r="C99" t="s">
-        <v>148</v>
+        <v>115</v>
       </c>
       <c r="D99" t="s">
         <v>5</v>
       </c>
       <c r="E99" t="s">
-        <v>16</v>
+        <v>13</v>
+      </c>
+      <c r="F99" s="3">
+        <v>2022</v>
       </c>
       <c r="G99" t="s">
+        <v>6</v>
+      </c>
+      <c r="H99" t="s">
         <v>7</v>
       </c>
-      <c r="H99" t="s">
-        <v>8</v>
-      </c>
       <c r="I99" t="s">
-        <v>261</v>
+        <v>206</v>
       </c>
       <c r="J99" t="s">
-        <v>473</v>
+        <v>401</v>
       </c>
       <c r="K99">
         <v>65000</v>
@@ -6090,31 +6001,31 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>262</v>
+        <v>207</v>
       </c>
       <c r="C100" t="s">
-        <v>263</v>
+        <v>208</v>
       </c>
       <c r="D100" t="s">
         <v>5</v>
       </c>
       <c r="E100" t="s">
-        <v>23</v>
-      </c>
-      <c r="F100" t="s">
-        <v>264</v>
+        <v>18</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>438</v>
       </c>
       <c r="G100" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H100" t="s">
-        <v>213</v>
+        <v>167</v>
       </c>
       <c r="I100" t="s">
-        <v>265</v>
+        <v>209</v>
       </c>
       <c r="J100" t="s">
-        <v>490</v>
+        <v>418</v>
       </c>
       <c r="K100">
         <v>49000</v>
@@ -6134,31 +6045,31 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>266</v>
+        <v>210</v>
       </c>
       <c r="C101" t="s">
-        <v>263</v>
+        <v>208</v>
       </c>
       <c r="D101" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E101" t="s">
-        <v>23</v>
-      </c>
-      <c r="F101" t="s">
-        <v>267</v>
+        <v>18</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>443</v>
       </c>
       <c r="G101" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H101" t="s">
-        <v>213</v>
+        <v>167</v>
       </c>
       <c r="I101" t="s">
-        <v>268</v>
+        <v>211</v>
       </c>
       <c r="J101" t="s">
-        <v>490</v>
+        <v>418</v>
       </c>
       <c r="K101">
         <v>95000</v>
@@ -6178,31 +6089,31 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>269</v>
+        <v>212</v>
       </c>
       <c r="C102" t="s">
-        <v>263</v>
+        <v>208</v>
       </c>
       <c r="D102" t="s">
         <v>5</v>
       </c>
       <c r="E102" t="s">
-        <v>23</v>
-      </c>
-      <c r="F102" t="s">
-        <v>270</v>
+        <v>18</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>443</v>
       </c>
       <c r="G102" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H102" t="s">
+        <v>167</v>
+      </c>
+      <c r="I102" t="s">
         <v>213</v>
       </c>
-      <c r="I102" t="s">
-        <v>271</v>
-      </c>
       <c r="J102" t="s">
-        <v>490</v>
+        <v>418</v>
       </c>
       <c r="K102">
         <v>45000</v>
@@ -6222,28 +6133,28 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>272</v>
+        <v>214</v>
       </c>
       <c r="C103" t="s">
-        <v>263</v>
+        <v>208</v>
       </c>
       <c r="D103" t="s">
         <v>5</v>
       </c>
-      <c r="F103" t="s">
-        <v>26</v>
+      <c r="F103" s="3" t="s">
+        <v>424</v>
       </c>
       <c r="G103" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H103" t="s">
-        <v>213</v>
+        <v>167</v>
       </c>
       <c r="I103" t="s">
-        <v>273</v>
+        <v>215</v>
       </c>
       <c r="J103" t="s">
-        <v>490</v>
+        <v>418</v>
       </c>
       <c r="K103">
         <v>124500</v>
@@ -6263,28 +6174,28 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>274</v>
+        <v>216</v>
       </c>
       <c r="C104" t="s">
-        <v>263</v>
+        <v>208</v>
       </c>
       <c r="D104" t="s">
         <v>5</v>
       </c>
-      <c r="F104" t="s">
-        <v>133</v>
+      <c r="F104" s="3" t="s">
+        <v>424</v>
       </c>
       <c r="G104" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H104" t="s">
-        <v>213</v>
+        <v>167</v>
       </c>
       <c r="I104" t="s">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="J104" t="s">
-        <v>490</v>
+        <v>418</v>
       </c>
       <c r="K104">
         <v>64000</v>
@@ -6304,28 +6215,28 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>276</v>
+        <v>218</v>
       </c>
       <c r="C105" t="s">
-        <v>263</v>
+        <v>208</v>
       </c>
       <c r="D105" t="s">
         <v>5</v>
       </c>
-      <c r="F105" t="s">
-        <v>65</v>
+      <c r="F105" s="3" t="s">
+        <v>428</v>
       </c>
       <c r="G105" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H105" t="s">
-        <v>213</v>
+        <v>167</v>
       </c>
       <c r="I105" t="s">
-        <v>277</v>
+        <v>219</v>
       </c>
       <c r="J105" t="s">
-        <v>490</v>
+        <v>418</v>
       </c>
       <c r="K105">
         <v>25000</v>
@@ -6345,28 +6256,28 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>278</v>
+        <v>220</v>
       </c>
       <c r="C106" t="s">
-        <v>263</v>
+        <v>208</v>
       </c>
       <c r="D106" t="s">
         <v>5</v>
       </c>
-      <c r="F106" t="s">
-        <v>81</v>
+      <c r="F106" s="3" t="s">
+        <v>432</v>
       </c>
       <c r="G106" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H106" t="s">
-        <v>213</v>
+        <v>167</v>
       </c>
       <c r="I106" t="s">
-        <v>279</v>
+        <v>221</v>
       </c>
       <c r="J106" t="s">
-        <v>490</v>
+        <v>418</v>
       </c>
       <c r="K106">
         <v>38498</v>
@@ -6386,25 +6297,28 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>280</v>
+        <v>222</v>
       </c>
       <c r="C107" t="s">
-        <v>263</v>
+        <v>208</v>
       </c>
       <c r="D107" t="s">
-        <v>216</v>
+        <v>170</v>
+      </c>
+      <c r="F107" s="3">
+        <v>2014</v>
       </c>
       <c r="G107" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H107" t="s">
-        <v>213</v>
+        <v>167</v>
       </c>
       <c r="I107" t="s">
-        <v>281</v>
+        <v>223</v>
       </c>
       <c r="J107" t="s">
-        <v>474</v>
+        <v>402</v>
       </c>
       <c r="K107">
         <v>166433</v>
@@ -6424,31 +6338,31 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>282</v>
+        <v>224</v>
       </c>
       <c r="C108" t="s">
-        <v>263</v>
+        <v>208</v>
       </c>
       <c r="D108" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E108" t="s">
-        <v>23</v>
-      </c>
-      <c r="F108" t="s">
-        <v>205</v>
+        <v>18</v>
+      </c>
+      <c r="F108" s="3" t="s">
+        <v>441</v>
       </c>
       <c r="G108" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H108" t="s">
-        <v>213</v>
+        <v>167</v>
       </c>
       <c r="I108" t="s">
-        <v>283</v>
+        <v>225</v>
       </c>
       <c r="J108" t="s">
-        <v>490</v>
+        <v>418</v>
       </c>
       <c r="K108">
         <v>58000</v>
@@ -6468,28 +6382,28 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>284</v>
+        <v>226</v>
       </c>
       <c r="C109" t="s">
-        <v>263</v>
+        <v>208</v>
       </c>
       <c r="D109" t="s">
         <v>5</v>
       </c>
-      <c r="F109" t="s">
-        <v>285</v>
+      <c r="F109" s="3" t="s">
+        <v>441</v>
       </c>
       <c r="G109" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H109" t="s">
-        <v>213</v>
+        <v>167</v>
       </c>
       <c r="I109" t="s">
-        <v>286</v>
+        <v>227</v>
       </c>
       <c r="J109" t="s">
-        <v>474</v>
+        <v>402</v>
       </c>
       <c r="K109">
         <v>51872</v>
@@ -6509,28 +6423,28 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>287</v>
+        <v>228</v>
       </c>
       <c r="C110" t="s">
-        <v>263</v>
+        <v>208</v>
       </c>
       <c r="D110" t="s">
         <v>5</v>
       </c>
-      <c r="F110" t="s">
-        <v>208</v>
+      <c r="F110" s="3" t="s">
+        <v>439</v>
       </c>
       <c r="G110" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H110" t="s">
-        <v>213</v>
+        <v>167</v>
       </c>
       <c r="I110" t="s">
-        <v>288</v>
+        <v>229</v>
       </c>
       <c r="J110" t="s">
-        <v>474</v>
+        <v>402</v>
       </c>
       <c r="K110">
         <v>21632</v>
@@ -6550,28 +6464,28 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>289</v>
+        <v>230</v>
       </c>
       <c r="C111" t="s">
-        <v>263</v>
+        <v>208</v>
       </c>
       <c r="D111" t="s">
         <v>5</v>
       </c>
-      <c r="F111" t="s">
-        <v>208</v>
+      <c r="F111" s="3" t="s">
+        <v>439</v>
       </c>
       <c r="G111" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H111" t="s">
-        <v>213</v>
+        <v>167</v>
       </c>
       <c r="I111" t="s">
-        <v>290</v>
+        <v>231</v>
       </c>
       <c r="J111" t="s">
-        <v>474</v>
+        <v>402</v>
       </c>
       <c r="K111">
         <v>69000</v>
@@ -6591,28 +6505,28 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>291</v>
+        <v>232</v>
       </c>
       <c r="C112" t="s">
-        <v>263</v>
+        <v>208</v>
       </c>
       <c r="D112" t="s">
         <v>5</v>
       </c>
-      <c r="F112" t="s">
-        <v>292</v>
+      <c r="F112" s="3" t="s">
+        <v>422</v>
       </c>
       <c r="G112" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H112" t="s">
-        <v>213</v>
+        <v>167</v>
       </c>
       <c r="I112" t="s">
-        <v>293</v>
+        <v>233</v>
       </c>
       <c r="J112" t="s">
-        <v>474</v>
+        <v>402</v>
       </c>
       <c r="K112">
         <v>54000</v>
@@ -6632,28 +6546,31 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>294</v>
+        <v>234</v>
       </c>
       <c r="C113" t="s">
-        <v>263</v>
+        <v>208</v>
       </c>
       <c r="D113" t="s">
         <v>5</v>
       </c>
       <c r="E113" t="s">
-        <v>16</v>
+        <v>13</v>
+      </c>
+      <c r="F113" s="3">
+        <v>2021</v>
       </c>
       <c r="G113" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H113" t="s">
-        <v>213</v>
+        <v>167</v>
       </c>
       <c r="I113" t="s">
-        <v>295</v>
+        <v>235</v>
       </c>
       <c r="J113" t="s">
-        <v>474</v>
+        <v>402</v>
       </c>
       <c r="K113">
         <v>57400</v>
@@ -6673,28 +6590,31 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>296</v>
+        <v>236</v>
       </c>
       <c r="C114" t="s">
-        <v>263</v>
+        <v>208</v>
       </c>
       <c r="D114" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E114" t="s">
-        <v>16</v>
+        <v>13</v>
+      </c>
+      <c r="F114" s="3">
+        <v>2023</v>
       </c>
       <c r="G114" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H114" t="s">
-        <v>213</v>
+        <v>167</v>
       </c>
       <c r="I114" t="s">
-        <v>297</v>
+        <v>237</v>
       </c>
       <c r="J114" t="s">
-        <v>474</v>
+        <v>402</v>
       </c>
       <c r="K114">
         <v>60000</v>
@@ -6714,28 +6634,31 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>298</v>
+        <v>238</v>
       </c>
       <c r="C115" t="s">
-        <v>263</v>
+        <v>208</v>
       </c>
       <c r="D115" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E115" t="s">
-        <v>16</v>
+        <v>13</v>
+      </c>
+      <c r="F115" s="3">
+        <v>2023</v>
       </c>
       <c r="G115" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H115" t="s">
-        <v>213</v>
+        <v>167</v>
       </c>
       <c r="I115" t="s">
-        <v>297</v>
+        <v>237</v>
       </c>
       <c r="J115" t="s">
-        <v>474</v>
+        <v>402</v>
       </c>
       <c r="K115">
         <v>60000</v>
@@ -6755,25 +6678,28 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>299</v>
+        <v>239</v>
       </c>
       <c r="C116" t="s">
-        <v>263</v>
+        <v>208</v>
       </c>
       <c r="D116" t="s">
         <v>5</v>
       </c>
+      <c r="F116" s="3">
+        <v>2023</v>
+      </c>
       <c r="G116" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H116" t="s">
-        <v>213</v>
+        <v>167</v>
       </c>
       <c r="I116" t="s">
-        <v>300</v>
+        <v>240</v>
       </c>
       <c r="J116" t="s">
-        <v>474</v>
+        <v>402</v>
       </c>
       <c r="K116">
         <v>33000</v>
@@ -6793,25 +6719,28 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>301</v>
+        <v>241</v>
       </c>
       <c r="C117" t="s">
-        <v>263</v>
+        <v>208</v>
       </c>
       <c r="D117" t="s">
-        <v>216</v>
+        <v>170</v>
+      </c>
+      <c r="F117" s="3">
+        <v>2009</v>
       </c>
       <c r="G117" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H117" t="s">
-        <v>213</v>
+        <v>167</v>
       </c>
       <c r="I117" t="s">
-        <v>302</v>
+        <v>242</v>
       </c>
       <c r="J117" t="s">
-        <v>474</v>
+        <v>402</v>
       </c>
       <c r="K117">
         <v>88786</v>
@@ -6831,25 +6760,28 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>303</v>
+        <v>243</v>
       </c>
       <c r="C118" t="s">
-        <v>263</v>
+        <v>208</v>
       </c>
       <c r="D118" t="s">
-        <v>216</v>
+        <v>170</v>
+      </c>
+      <c r="F118" s="3">
+        <v>2016</v>
       </c>
       <c r="G118" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H118" t="s">
-        <v>213</v>
+        <v>167</v>
       </c>
       <c r="I118" t="s">
-        <v>304</v>
+        <v>244</v>
       </c>
       <c r="J118" t="s">
-        <v>474</v>
+        <v>402</v>
       </c>
       <c r="K118">
         <v>134000</v>
@@ -6869,25 +6801,28 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>305</v>
+        <v>245</v>
       </c>
       <c r="C119" t="s">
-        <v>263</v>
+        <v>208</v>
       </c>
       <c r="D119" t="s">
-        <v>216</v>
+        <v>170</v>
+      </c>
+      <c r="F119" s="3">
+        <v>2021</v>
       </c>
       <c r="G119" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H119" t="s">
-        <v>213</v>
+        <v>167</v>
       </c>
       <c r="I119" t="s">
-        <v>306</v>
+        <v>246</v>
       </c>
       <c r="J119" t="s">
-        <v>474</v>
+        <v>402</v>
       </c>
       <c r="K119">
         <v>35000</v>
@@ -6907,25 +6842,28 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>307</v>
+        <v>247</v>
       </c>
       <c r="C120" t="s">
-        <v>263</v>
+        <v>208</v>
       </c>
       <c r="D120" t="s">
-        <v>216</v>
+        <v>170</v>
+      </c>
+      <c r="F120" s="3">
+        <v>2004</v>
       </c>
       <c r="G120" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H120" t="s">
-        <v>213</v>
+        <v>167</v>
       </c>
       <c r="I120" t="s">
-        <v>308</v>
+        <v>248</v>
       </c>
       <c r="J120" t="s">
-        <v>474</v>
+        <v>402</v>
       </c>
       <c r="K120">
         <v>18000</v>
@@ -6945,28 +6883,31 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>309</v>
+        <v>249</v>
       </c>
       <c r="C121" t="s">
-        <v>263</v>
+        <v>208</v>
       </c>
       <c r="D121" t="s">
-        <v>216</v>
+        <v>170</v>
       </c>
       <c r="E121" t="s">
-        <v>16</v>
+        <v>13</v>
+      </c>
+      <c r="F121" s="3">
+        <v>2006</v>
       </c>
       <c r="G121" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H121" t="s">
-        <v>213</v>
+        <v>167</v>
       </c>
       <c r="I121" t="s">
-        <v>310</v>
+        <v>250</v>
       </c>
       <c r="J121" t="s">
-        <v>474</v>
+        <v>402</v>
       </c>
       <c r="K121">
         <v>105741</v>
@@ -6986,25 +6927,28 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>311</v>
+        <v>251</v>
       </c>
       <c r="C122" t="s">
-        <v>263</v>
+        <v>208</v>
       </c>
       <c r="D122" t="s">
-        <v>216</v>
+        <v>170</v>
+      </c>
+      <c r="F122" s="3">
+        <v>2024</v>
       </c>
       <c r="G122" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H122" t="s">
-        <v>213</v>
+        <v>167</v>
       </c>
       <c r="I122" t="s">
-        <v>312</v>
+        <v>252</v>
       </c>
       <c r="J122" t="s">
-        <v>474</v>
+        <v>402</v>
       </c>
       <c r="K122">
         <v>51000</v>
@@ -7024,28 +6968,31 @@
         <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>313</v>
+        <v>253</v>
       </c>
       <c r="C123" t="s">
-        <v>263</v>
+        <v>208</v>
       </c>
       <c r="D123" t="s">
         <v>5</v>
       </c>
       <c r="E123" t="s">
-        <v>16</v>
+        <v>13</v>
+      </c>
+      <c r="F123" s="3">
+        <v>2024</v>
       </c>
       <c r="G123" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H123" t="s">
-        <v>213</v>
+        <v>167</v>
       </c>
       <c r="I123" t="s">
-        <v>314</v>
+        <v>254</v>
       </c>
       <c r="J123" t="s">
-        <v>474</v>
+        <v>402</v>
       </c>
       <c r="K123">
         <v>130143</v>
@@ -7065,22 +7012,25 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>315</v>
+        <v>255</v>
       </c>
       <c r="C124" t="s">
-        <v>263</v>
+        <v>208</v>
+      </c>
+      <c r="F124" s="3">
+        <v>2025</v>
       </c>
       <c r="G124" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H124" t="s">
-        <v>213</v>
+        <v>167</v>
       </c>
       <c r="I124" t="s">
-        <v>316</v>
+        <v>256</v>
       </c>
       <c r="J124" t="s">
-        <v>474</v>
+        <v>402</v>
       </c>
       <c r="K124">
         <v>121551.47</v>
@@ -7100,31 +7050,31 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>317</v>
+        <v>257</v>
       </c>
       <c r="C125" t="s">
-        <v>318</v>
+        <v>258</v>
       </c>
       <c r="D125" t="s">
         <v>5</v>
       </c>
       <c r="E125" t="s">
-        <v>16</v>
-      </c>
-      <c r="F125" t="s">
-        <v>319</v>
+        <v>13</v>
+      </c>
+      <c r="F125" s="3" t="s">
+        <v>427</v>
       </c>
       <c r="G125" t="s">
+        <v>6</v>
+      </c>
+      <c r="H125" t="s">
         <v>7</v>
       </c>
-      <c r="H125" t="s">
-        <v>8</v>
-      </c>
       <c r="I125" t="s">
-        <v>320</v>
+        <v>259</v>
       </c>
       <c r="J125" t="s">
-        <v>475</v>
+        <v>403</v>
       </c>
       <c r="K125">
         <v>110000</v>
@@ -7144,31 +7094,31 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>321</v>
+        <v>260</v>
       </c>
       <c r="C126" t="s">
-        <v>318</v>
+        <v>258</v>
       </c>
       <c r="D126" t="s">
         <v>5</v>
       </c>
       <c r="E126" t="s">
-        <v>23</v>
-      </c>
-      <c r="F126" t="s">
-        <v>234</v>
+        <v>18</v>
+      </c>
+      <c r="F126" s="3" t="s">
+        <v>430</v>
       </c>
       <c r="G126" t="s">
+        <v>6</v>
+      </c>
+      <c r="H126" t="s">
         <v>7</v>
       </c>
-      <c r="H126" t="s">
-        <v>8</v>
-      </c>
       <c r="I126" t="s">
-        <v>322</v>
+        <v>261</v>
       </c>
       <c r="J126" t="s">
-        <v>475</v>
+        <v>403</v>
       </c>
       <c r="K126">
         <v>56000</v>
@@ -7188,28 +7138,28 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>323</v>
+        <v>262</v>
       </c>
       <c r="C127" t="s">
-        <v>318</v>
+        <v>258</v>
       </c>
       <c r="D127" t="s">
         <v>5</v>
       </c>
-      <c r="F127" t="s">
-        <v>205</v>
+      <c r="F127" s="3" t="s">
+        <v>441</v>
       </c>
       <c r="G127" t="s">
+        <v>6</v>
+      </c>
+      <c r="H127" t="s">
         <v>7</v>
       </c>
-      <c r="H127" t="s">
-        <v>8</v>
-      </c>
       <c r="I127" t="s">
-        <v>324</v>
+        <v>263</v>
       </c>
       <c r="J127" t="s">
-        <v>475</v>
+        <v>403</v>
       </c>
       <c r="K127">
         <v>89177</v>
@@ -7229,31 +7179,31 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>325</v>
+        <v>264</v>
       </c>
       <c r="C128" t="s">
-        <v>318</v>
+        <v>258</v>
       </c>
       <c r="D128" t="s">
         <v>5</v>
       </c>
       <c r="E128" t="s">
-        <v>23</v>
-      </c>
-      <c r="F128" t="s">
-        <v>326</v>
+        <v>18</v>
+      </c>
+      <c r="F128" s="3" t="s">
+        <v>441</v>
       </c>
       <c r="G128" t="s">
+        <v>6</v>
+      </c>
+      <c r="H128" t="s">
         <v>7</v>
       </c>
-      <c r="H128" t="s">
-        <v>8</v>
-      </c>
       <c r="I128" t="s">
-        <v>327</v>
+        <v>265</v>
       </c>
       <c r="J128" t="s">
-        <v>475</v>
+        <v>403</v>
       </c>
       <c r="K128">
         <v>30000</v>
@@ -7273,31 +7223,31 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>328</v>
+        <v>266</v>
       </c>
       <c r="C129" t="s">
-        <v>318</v>
+        <v>258</v>
       </c>
       <c r="D129" t="s">
         <v>5</v>
       </c>
       <c r="E129" t="s">
-        <v>16</v>
-      </c>
-      <c r="F129" t="s">
-        <v>326</v>
+        <v>13</v>
+      </c>
+      <c r="F129" s="3" t="s">
+        <v>441</v>
       </c>
       <c r="G129" t="s">
+        <v>6</v>
+      </c>
+      <c r="H129" t="s">
         <v>7</v>
       </c>
-      <c r="H129" t="s">
-        <v>8</v>
-      </c>
       <c r="I129" t="s">
-        <v>329</v>
+        <v>267</v>
       </c>
       <c r="J129" t="s">
-        <v>475</v>
+        <v>403</v>
       </c>
       <c r="K129">
         <v>54550</v>
@@ -7317,31 +7267,31 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>330</v>
+        <v>268</v>
       </c>
       <c r="C130" t="s">
-        <v>318</v>
+        <v>258</v>
       </c>
       <c r="D130" t="s">
         <v>5</v>
       </c>
       <c r="E130" t="s">
-        <v>16</v>
-      </c>
-      <c r="F130" t="s">
-        <v>250</v>
+        <v>13</v>
+      </c>
+      <c r="F130" s="3" t="s">
+        <v>439</v>
       </c>
       <c r="G130" t="s">
+        <v>6</v>
+      </c>
+      <c r="H130" t="s">
         <v>7</v>
       </c>
-      <c r="H130" t="s">
-        <v>8</v>
-      </c>
       <c r="I130" t="s">
-        <v>331</v>
+        <v>269</v>
       </c>
       <c r="J130" t="s">
-        <v>475</v>
+        <v>403</v>
       </c>
       <c r="K130">
         <v>125000</v>
@@ -7361,31 +7311,31 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>332</v>
+        <v>270</v>
       </c>
       <c r="C131" t="s">
-        <v>318</v>
+        <v>258</v>
       </c>
       <c r="D131" t="s">
         <v>5</v>
       </c>
       <c r="E131" t="s">
-        <v>16</v>
-      </c>
-      <c r="F131" t="s">
-        <v>333</v>
+        <v>13</v>
+      </c>
+      <c r="F131" s="3" t="s">
+        <v>439</v>
       </c>
       <c r="G131" t="s">
+        <v>6</v>
+      </c>
+      <c r="H131" t="s">
         <v>7</v>
       </c>
-      <c r="H131" t="s">
-        <v>8</v>
-      </c>
       <c r="I131" t="s">
-        <v>334</v>
+        <v>271</v>
       </c>
       <c r="J131" t="s">
-        <v>475</v>
+        <v>403</v>
       </c>
       <c r="K131">
         <v>69100</v>
@@ -7405,31 +7355,31 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>335</v>
+        <v>272</v>
       </c>
       <c r="C132" t="s">
-        <v>318</v>
+        <v>258</v>
       </c>
       <c r="D132" t="s">
         <v>5</v>
       </c>
       <c r="E132" t="s">
-        <v>23</v>
-      </c>
-      <c r="F132" t="s">
-        <v>160</v>
+        <v>18</v>
+      </c>
+      <c r="F132" s="3" t="s">
+        <v>440</v>
       </c>
       <c r="G132" t="s">
+        <v>6</v>
+      </c>
+      <c r="H132" t="s">
         <v>7</v>
       </c>
-      <c r="H132" t="s">
-        <v>8</v>
-      </c>
       <c r="I132" t="s">
-        <v>336</v>
+        <v>273</v>
       </c>
       <c r="J132" t="s">
-        <v>475</v>
+        <v>403</v>
       </c>
       <c r="K132">
         <v>118290</v>
@@ -7449,28 +7399,28 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>337</v>
+        <v>274</v>
       </c>
       <c r="C133" t="s">
-        <v>318</v>
+        <v>258</v>
       </c>
       <c r="D133" t="s">
         <v>5</v>
       </c>
-      <c r="F133" t="s">
-        <v>338</v>
+      <c r="F133" s="3" t="s">
+        <v>440</v>
       </c>
       <c r="G133" t="s">
+        <v>6</v>
+      </c>
+      <c r="H133" t="s">
         <v>7</v>
       </c>
-      <c r="H133" t="s">
-        <v>8</v>
-      </c>
       <c r="I133" t="s">
-        <v>339</v>
+        <v>275</v>
       </c>
       <c r="J133" t="s">
-        <v>475</v>
+        <v>403</v>
       </c>
       <c r="K133">
         <v>79900</v>
@@ -7490,28 +7440,28 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>340</v>
+        <v>276</v>
       </c>
       <c r="C134" t="s">
-        <v>318</v>
+        <v>258</v>
       </c>
       <c r="D134" t="s">
         <v>5</v>
       </c>
-      <c r="F134" t="s">
-        <v>163</v>
+      <c r="F134" s="3" t="s">
+        <v>440</v>
       </c>
       <c r="G134" t="s">
+        <v>6</v>
+      </c>
+      <c r="H134" t="s">
         <v>7</v>
       </c>
-      <c r="H134" t="s">
-        <v>8</v>
-      </c>
       <c r="I134" t="s">
-        <v>341</v>
+        <v>277</v>
       </c>
       <c r="J134" t="s">
-        <v>475</v>
+        <v>403</v>
       </c>
       <c r="K134">
         <v>39742.379999999997</v>
@@ -7531,31 +7481,31 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
-        <v>342</v>
+        <v>278</v>
       </c>
       <c r="C135" t="s">
-        <v>318</v>
+        <v>258</v>
       </c>
       <c r="D135" t="s">
         <v>5</v>
       </c>
       <c r="E135" t="s">
-        <v>16</v>
-      </c>
-      <c r="F135" t="s">
-        <v>87</v>
+        <v>13</v>
+      </c>
+      <c r="F135" s="3" t="s">
+        <v>433</v>
       </c>
       <c r="G135" t="s">
+        <v>6</v>
+      </c>
+      <c r="H135" t="s">
         <v>7</v>
       </c>
-      <c r="H135" t="s">
-        <v>8</v>
-      </c>
       <c r="I135" t="s">
-        <v>343</v>
+        <v>279</v>
       </c>
       <c r="J135" t="s">
-        <v>475</v>
+        <v>403</v>
       </c>
       <c r="K135">
         <v>48000</v>
@@ -7575,28 +7525,31 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>344</v>
+        <v>280</v>
       </c>
       <c r="C136" t="s">
-        <v>318</v>
+        <v>258</v>
       </c>
       <c r="D136" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E136" t="s">
-        <v>23</v>
+        <v>18</v>
+      </c>
+      <c r="F136" s="3">
+        <v>2018</v>
       </c>
       <c r="G136" t="s">
+        <v>6</v>
+      </c>
+      <c r="H136" t="s">
         <v>7</v>
       </c>
-      <c r="H136" t="s">
-        <v>8</v>
-      </c>
       <c r="I136" t="s">
-        <v>345</v>
+        <v>281</v>
       </c>
       <c r="J136" t="s">
-        <v>475</v>
+        <v>403</v>
       </c>
       <c r="K136">
         <v>74722</v>
@@ -7616,25 +7569,28 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>346</v>
+        <v>282</v>
       </c>
       <c r="C137" t="s">
-        <v>318</v>
+        <v>258</v>
       </c>
       <c r="D137" t="s">
-        <v>216</v>
+        <v>170</v>
+      </c>
+      <c r="F137" s="3">
+        <v>2015</v>
       </c>
       <c r="G137" t="s">
+        <v>6</v>
+      </c>
+      <c r="H137" t="s">
         <v>7</v>
       </c>
-      <c r="H137" t="s">
-        <v>8</v>
-      </c>
       <c r="I137" t="s">
-        <v>347</v>
+        <v>283</v>
       </c>
       <c r="J137" t="s">
-        <v>475</v>
+        <v>403</v>
       </c>
       <c r="K137">
         <v>55000</v>
@@ -7654,25 +7610,28 @@
         <v>137</v>
       </c>
       <c r="B138" t="s">
-        <v>348</v>
+        <v>284</v>
       </c>
       <c r="C138" t="s">
-        <v>349</v>
+        <v>285</v>
       </c>
       <c r="D138" t="s">
         <v>5</v>
       </c>
+      <c r="F138" s="3" t="s">
+        <v>429</v>
+      </c>
       <c r="G138" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H138" t="s">
-        <v>118</v>
+        <v>92</v>
       </c>
       <c r="I138" t="s">
-        <v>350</v>
+        <v>286</v>
       </c>
       <c r="J138" t="s">
-        <v>488</v>
+        <v>416</v>
       </c>
       <c r="K138">
         <v>128000</v>
@@ -7692,31 +7651,31 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>351</v>
+        <v>287</v>
       </c>
       <c r="C139" t="s">
-        <v>349</v>
+        <v>285</v>
       </c>
       <c r="D139" t="s">
         <v>5</v>
       </c>
       <c r="E139" t="s">
-        <v>16</v>
-      </c>
-      <c r="F139" t="s">
-        <v>59</v>
+        <v>13</v>
+      </c>
+      <c r="F139" s="3" t="s">
+        <v>427</v>
       </c>
       <c r="G139" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H139" t="s">
-        <v>118</v>
+        <v>92</v>
       </c>
       <c r="I139" t="s">
-        <v>352</v>
+        <v>288</v>
       </c>
       <c r="J139" t="s">
-        <v>488</v>
+        <v>416</v>
       </c>
       <c r="K139">
         <v>122000</v>
@@ -7736,28 +7695,28 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>353</v>
+        <v>289</v>
       </c>
       <c r="C140" t="s">
-        <v>349</v>
+        <v>285</v>
       </c>
       <c r="D140" t="s">
         <v>5</v>
       </c>
-      <c r="F140" t="s">
-        <v>15</v>
+      <c r="F140" s="3" t="s">
+        <v>421</v>
       </c>
       <c r="G140" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H140" t="s">
-        <v>118</v>
+        <v>92</v>
       </c>
       <c r="I140" t="s">
-        <v>354</v>
+        <v>290</v>
       </c>
       <c r="J140" t="s">
-        <v>488</v>
+        <v>416</v>
       </c>
       <c r="K140">
         <v>22000</v>
@@ -7777,28 +7736,28 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>355</v>
+        <v>291</v>
       </c>
       <c r="C141" t="s">
-        <v>349</v>
+        <v>285</v>
       </c>
       <c r="D141" t="s">
         <v>5</v>
       </c>
-      <c r="F141" t="s">
-        <v>15</v>
+      <c r="F141" s="3" t="s">
+        <v>421</v>
       </c>
       <c r="G141" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H141" t="s">
-        <v>118</v>
+        <v>92</v>
       </c>
       <c r="I141" t="s">
-        <v>356</v>
+        <v>292</v>
       </c>
       <c r="J141" t="s">
-        <v>488</v>
+        <v>416</v>
       </c>
       <c r="K141">
         <v>10000</v>
@@ -7818,28 +7777,28 @@
         <v>141</v>
       </c>
       <c r="B142" t="s">
-        <v>357</v>
+        <v>293</v>
       </c>
       <c r="C142" t="s">
-        <v>349</v>
+        <v>285</v>
       </c>
       <c r="D142" t="s">
         <v>5</v>
       </c>
-      <c r="F142" t="s">
-        <v>56</v>
+      <c r="F142" s="3" t="s">
+        <v>427</v>
       </c>
       <c r="G142" t="s">
+        <v>6</v>
+      </c>
+      <c r="H142" t="s">
         <v>7</v>
       </c>
-      <c r="H142" t="s">
-        <v>8</v>
-      </c>
       <c r="I142" t="s">
-        <v>358</v>
+        <v>294</v>
       </c>
       <c r="J142" t="s">
-        <v>473</v>
+        <v>401</v>
       </c>
       <c r="K142">
         <v>64000</v>
@@ -7859,28 +7818,28 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>359</v>
+        <v>295</v>
       </c>
       <c r="C143" t="s">
-        <v>349</v>
+        <v>285</v>
       </c>
       <c r="D143" t="s">
         <v>5</v>
       </c>
-      <c r="F143" t="s">
-        <v>65</v>
+      <c r="F143" s="3" t="s">
+        <v>428</v>
       </c>
       <c r="G143" t="s">
+        <v>6</v>
+      </c>
+      <c r="H143" t="s">
         <v>7</v>
       </c>
-      <c r="H143" t="s">
-        <v>8</v>
-      </c>
       <c r="I143" t="s">
-        <v>360</v>
+        <v>296</v>
       </c>
       <c r="J143" t="s">
-        <v>473</v>
+        <v>401</v>
       </c>
       <c r="K143">
         <v>95628</v>
@@ -7900,28 +7859,28 @@
         <v>143</v>
       </c>
       <c r="B144" t="s">
-        <v>361</v>
+        <v>297</v>
       </c>
       <c r="C144" t="s">
-        <v>349</v>
+        <v>285</v>
       </c>
       <c r="D144" t="s">
         <v>5</v>
       </c>
-      <c r="F144" t="s">
-        <v>362</v>
+      <c r="F144" s="3" t="s">
+        <v>428</v>
       </c>
       <c r="G144" t="s">
+        <v>6</v>
+      </c>
+      <c r="H144" t="s">
         <v>7</v>
       </c>
-      <c r="H144" t="s">
-        <v>8</v>
-      </c>
       <c r="I144" t="s">
-        <v>363</v>
+        <v>298</v>
       </c>
       <c r="J144" t="s">
-        <v>473</v>
+        <v>401</v>
       </c>
       <c r="K144">
         <v>39562</v>
@@ -7941,31 +7900,31 @@
         <v>144</v>
       </c>
       <c r="B145" t="s">
-        <v>364</v>
+        <v>299</v>
       </c>
       <c r="C145" t="s">
-        <v>349</v>
+        <v>285</v>
       </c>
       <c r="D145" t="s">
         <v>5</v>
       </c>
       <c r="E145" t="s">
-        <v>16</v>
-      </c>
-      <c r="F145" t="s">
-        <v>365</v>
+        <v>13</v>
+      </c>
+      <c r="F145" s="3" t="s">
+        <v>421</v>
       </c>
       <c r="G145" t="s">
+        <v>6</v>
+      </c>
+      <c r="H145" t="s">
         <v>7</v>
       </c>
-      <c r="H145" t="s">
-        <v>8</v>
-      </c>
       <c r="I145" t="s">
-        <v>366</v>
+        <v>300</v>
       </c>
       <c r="J145" t="s">
-        <v>488</v>
+        <v>416</v>
       </c>
       <c r="K145">
         <v>105000</v>
@@ -7985,31 +7944,31 @@
         <v>145</v>
       </c>
       <c r="B146" t="s">
-        <v>367</v>
+        <v>301</v>
       </c>
       <c r="C146" t="s">
-        <v>349</v>
+        <v>285</v>
       </c>
       <c r="D146" t="s">
         <v>5</v>
       </c>
       <c r="E146" t="s">
-        <v>23</v>
-      </c>
-      <c r="F146" t="s">
-        <v>333</v>
+        <v>18</v>
+      </c>
+      <c r="F146" s="3" t="s">
+        <v>439</v>
       </c>
       <c r="G146" t="s">
+        <v>6</v>
+      </c>
+      <c r="H146" t="s">
         <v>7</v>
       </c>
-      <c r="H146" t="s">
-        <v>8</v>
-      </c>
       <c r="I146" t="s">
-        <v>368</v>
+        <v>302</v>
       </c>
       <c r="J146" t="s">
-        <v>488</v>
+        <v>416</v>
       </c>
       <c r="K146">
         <v>60000</v>
@@ -8029,28 +7988,28 @@
         <v>146</v>
       </c>
       <c r="B147" t="s">
-        <v>369</v>
+        <v>303</v>
       </c>
       <c r="C147" t="s">
-        <v>349</v>
+        <v>285</v>
       </c>
       <c r="D147" t="s">
         <v>5</v>
       </c>
-      <c r="F147" t="s">
-        <v>153</v>
+      <c r="F147" s="3" t="s">
+        <v>439</v>
       </c>
       <c r="G147" t="s">
+        <v>6</v>
+      </c>
+      <c r="H147" t="s">
         <v>7</v>
       </c>
-      <c r="H147" t="s">
-        <v>8</v>
-      </c>
       <c r="I147" t="s">
-        <v>370</v>
+        <v>304</v>
       </c>
       <c r="J147" t="s">
-        <v>473</v>
+        <v>401</v>
       </c>
       <c r="K147">
         <v>39964</v>
@@ -8070,28 +8029,28 @@
         <v>147</v>
       </c>
       <c r="B148" t="s">
-        <v>371</v>
+        <v>305</v>
       </c>
       <c r="C148" t="s">
-        <v>349</v>
+        <v>285</v>
       </c>
       <c r="D148" t="s">
         <v>5</v>
       </c>
-      <c r="F148" t="s">
-        <v>19</v>
+      <c r="F148" s="3" t="s">
+        <v>422</v>
       </c>
       <c r="G148" t="s">
+        <v>6</v>
+      </c>
+      <c r="H148" t="s">
         <v>7</v>
       </c>
-      <c r="H148" t="s">
-        <v>8</v>
-      </c>
       <c r="I148" t="s">
-        <v>372</v>
+        <v>306</v>
       </c>
       <c r="J148" t="s">
-        <v>488</v>
+        <v>416</v>
       </c>
       <c r="K148">
         <v>94000</v>
@@ -8111,31 +8070,31 @@
         <v>148</v>
       </c>
       <c r="B149" t="s">
-        <v>373</v>
+        <v>307</v>
       </c>
       <c r="C149" t="s">
-        <v>349</v>
+        <v>285</v>
       </c>
       <c r="D149" t="s">
         <v>5</v>
       </c>
       <c r="E149" t="s">
-        <v>23</v>
-      </c>
-      <c r="F149" t="s">
-        <v>157</v>
+        <v>18</v>
+      </c>
+      <c r="F149" s="3" t="s">
+        <v>422</v>
       </c>
       <c r="G149" t="s">
+        <v>6</v>
+      </c>
+      <c r="H149" t="s">
         <v>7</v>
       </c>
-      <c r="H149" t="s">
-        <v>8</v>
-      </c>
       <c r="I149" t="s">
-        <v>368</v>
+        <v>302</v>
       </c>
       <c r="J149" t="s">
-        <v>488</v>
+        <v>416</v>
       </c>
       <c r="K149">
         <v>75000</v>
@@ -8155,28 +8114,28 @@
         <v>149</v>
       </c>
       <c r="B150" t="s">
-        <v>187</v>
+        <v>147</v>
       </c>
       <c r="C150" t="s">
-        <v>349</v>
+        <v>285</v>
       </c>
       <c r="D150" t="s">
         <v>5</v>
       </c>
-      <c r="F150" t="s">
-        <v>374</v>
+      <c r="F150" s="3" t="s">
+        <v>422</v>
       </c>
       <c r="G150" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H150" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="I150" t="s">
-        <v>188</v>
+        <v>148</v>
       </c>
       <c r="J150" t="s">
-        <v>488</v>
+        <v>416</v>
       </c>
       <c r="K150">
         <v>48767</v>
@@ -8196,31 +8155,31 @@
         <v>150</v>
       </c>
       <c r="B151" t="s">
-        <v>375</v>
+        <v>308</v>
       </c>
       <c r="C151" t="s">
-        <v>349</v>
+        <v>285</v>
       </c>
       <c r="D151" t="s">
         <v>5</v>
       </c>
       <c r="E151" t="s">
-        <v>16</v>
-      </c>
-      <c r="F151" t="s">
-        <v>87</v>
+        <v>13</v>
+      </c>
+      <c r="F151" s="3" t="s">
+        <v>433</v>
       </c>
       <c r="G151" t="s">
+        <v>6</v>
+      </c>
+      <c r="H151" t="s">
         <v>7</v>
       </c>
-      <c r="H151" t="s">
-        <v>8</v>
-      </c>
       <c r="I151" t="s">
-        <v>376</v>
+        <v>309</v>
       </c>
       <c r="J151" t="s">
-        <v>488</v>
+        <v>416</v>
       </c>
       <c r="K151">
         <v>63824</v>
@@ -8240,31 +8199,31 @@
         <v>151</v>
       </c>
       <c r="B152" t="s">
-        <v>377</v>
+        <v>310</v>
       </c>
       <c r="C152" t="s">
-        <v>349</v>
+        <v>285</v>
       </c>
       <c r="D152" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E152" t="s">
-        <v>23</v>
-      </c>
-      <c r="F152" t="s">
-        <v>91</v>
+        <v>18</v>
+      </c>
+      <c r="F152" s="3" t="s">
+        <v>433</v>
       </c>
       <c r="G152" t="s">
+        <v>6</v>
+      </c>
+      <c r="H152" t="s">
         <v>7</v>
       </c>
-      <c r="H152" t="s">
-        <v>8</v>
-      </c>
       <c r="I152" t="s">
-        <v>378</v>
+        <v>311</v>
       </c>
       <c r="J152" t="s">
-        <v>488</v>
+        <v>416</v>
       </c>
       <c r="K152">
         <v>117000</v>
@@ -8284,25 +8243,28 @@
         <v>152</v>
       </c>
       <c r="B153" t="s">
-        <v>379</v>
+        <v>312</v>
       </c>
       <c r="C153" t="s">
-        <v>349</v>
+        <v>285</v>
       </c>
       <c r="D153" t="s">
         <v>5</v>
       </c>
+      <c r="F153" s="3">
+        <v>2021</v>
+      </c>
       <c r="G153" t="s">
+        <v>6</v>
+      </c>
+      <c r="H153" t="s">
         <v>7</v>
       </c>
-      <c r="H153" t="s">
-        <v>8</v>
-      </c>
       <c r="I153" t="s">
-        <v>380</v>
+        <v>313</v>
       </c>
       <c r="J153" t="s">
-        <v>488</v>
+        <v>416</v>
       </c>
       <c r="K153">
         <v>41000</v>
@@ -8322,25 +8284,28 @@
         <v>153</v>
       </c>
       <c r="B154" t="s">
-        <v>381</v>
+        <v>314</v>
       </c>
       <c r="C154" t="s">
-        <v>349</v>
+        <v>285</v>
       </c>
       <c r="D154" t="s">
         <v>5</v>
       </c>
+      <c r="F154" s="3">
+        <v>2023</v>
+      </c>
       <c r="G154" t="s">
+        <v>6</v>
+      </c>
+      <c r="H154" t="s">
         <v>7</v>
       </c>
-      <c r="H154" t="s">
-        <v>8</v>
-      </c>
       <c r="I154" t="s">
-        <v>382</v>
+        <v>315</v>
       </c>
       <c r="J154" t="s">
-        <v>473</v>
+        <v>401</v>
       </c>
       <c r="K154">
         <v>96446</v>
@@ -8360,31 +8325,31 @@
         <v>154</v>
       </c>
       <c r="B155" t="s">
-        <v>383</v>
+        <v>316</v>
       </c>
       <c r="C155" t="s">
-        <v>384</v>
+        <v>317</v>
       </c>
       <c r="D155" t="s">
         <v>5</v>
       </c>
       <c r="E155" t="s">
-        <v>16</v>
-      </c>
-      <c r="F155" t="s">
-        <v>163</v>
+        <v>13</v>
+      </c>
+      <c r="F155" s="3" t="s">
+        <v>440</v>
       </c>
       <c r="G155" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H155" t="s">
-        <v>385</v>
+        <v>318</v>
       </c>
       <c r="I155" t="s">
-        <v>386</v>
+        <v>319</v>
       </c>
       <c r="J155" t="s">
-        <v>488</v>
+        <v>416</v>
       </c>
       <c r="K155">
         <v>76600</v>
@@ -8404,28 +8369,28 @@
         <v>155</v>
       </c>
       <c r="B156" t="s">
-        <v>387</v>
+        <v>320</v>
       </c>
       <c r="C156" t="s">
-        <v>384</v>
+        <v>317</v>
       </c>
       <c r="D156" t="s">
         <v>5</v>
       </c>
-      <c r="F156" t="s">
-        <v>163</v>
+      <c r="F156" s="3" t="s">
+        <v>440</v>
       </c>
       <c r="G156" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H156" t="s">
-        <v>385</v>
+        <v>318</v>
       </c>
       <c r="I156" t="s">
-        <v>388</v>
+        <v>321</v>
       </c>
       <c r="J156" t="s">
-        <v>476</v>
+        <v>404</v>
       </c>
       <c r="K156">
         <v>125569</v>
@@ -8445,28 +8410,28 @@
         <v>156</v>
       </c>
       <c r="B157" t="s">
-        <v>389</v>
+        <v>322</v>
       </c>
       <c r="C157" t="s">
-        <v>384</v>
+        <v>317</v>
       </c>
       <c r="D157" t="s">
         <v>5</v>
       </c>
-      <c r="F157" t="s">
-        <v>390</v>
+      <c r="F157" s="3" t="s">
+        <v>433</v>
       </c>
       <c r="G157" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H157" t="s">
-        <v>385</v>
+        <v>318</v>
       </c>
       <c r="I157" t="s">
-        <v>391</v>
+        <v>323</v>
       </c>
       <c r="J157" t="s">
-        <v>488</v>
+        <v>416</v>
       </c>
       <c r="K157">
         <v>51234</v>
@@ -8486,31 +8451,31 @@
         <v>157</v>
       </c>
       <c r="B158" t="s">
-        <v>392</v>
+        <v>324</v>
       </c>
       <c r="C158" t="s">
-        <v>384</v>
+        <v>317</v>
       </c>
       <c r="D158" t="s">
         <v>5</v>
       </c>
       <c r="E158" t="s">
-        <v>16</v>
-      </c>
-      <c r="F158" t="s">
-        <v>91</v>
+        <v>13</v>
+      </c>
+      <c r="F158" s="3" t="s">
+        <v>433</v>
       </c>
       <c r="G158" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H158" t="s">
-        <v>385</v>
+        <v>318</v>
       </c>
       <c r="I158" t="s">
-        <v>393</v>
+        <v>325</v>
       </c>
       <c r="J158" t="s">
-        <v>476</v>
+        <v>404</v>
       </c>
       <c r="K158">
         <v>123780</v>
@@ -8530,28 +8495,28 @@
         <v>158</v>
       </c>
       <c r="B159" t="s">
-        <v>394</v>
+        <v>326</v>
       </c>
       <c r="C159" t="s">
-        <v>384</v>
+        <v>317</v>
       </c>
       <c r="D159" t="s">
         <v>5</v>
       </c>
-      <c r="F159" t="s">
-        <v>395</v>
+      <c r="F159" s="3" t="s">
+        <v>433</v>
       </c>
       <c r="G159" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H159" t="s">
-        <v>385</v>
+        <v>318</v>
       </c>
       <c r="I159" t="s">
-        <v>396</v>
+        <v>327</v>
       </c>
       <c r="J159" t="s">
-        <v>488</v>
+        <v>416</v>
       </c>
       <c r="K159">
         <v>46000</v>
@@ -8571,25 +8536,28 @@
         <v>159</v>
       </c>
       <c r="B160" t="s">
-        <v>397</v>
+        <v>328</v>
       </c>
       <c r="C160" t="s">
-        <v>384</v>
+        <v>317</v>
       </c>
       <c r="D160" t="s">
         <v>5</v>
       </c>
+      <c r="F160" s="3">
+        <v>2018</v>
+      </c>
       <c r="G160" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H160" t="s">
-        <v>385</v>
+        <v>318</v>
       </c>
       <c r="I160" t="s">
-        <v>398</v>
+        <v>329</v>
       </c>
       <c r="J160" t="s">
-        <v>488</v>
+        <v>416</v>
       </c>
       <c r="K160">
         <v>35600</v>
@@ -8609,28 +8577,31 @@
         <v>160</v>
       </c>
       <c r="B161" t="s">
-        <v>399</v>
+        <v>330</v>
       </c>
       <c r="C161" t="s">
-        <v>384</v>
+        <v>317</v>
       </c>
       <c r="D161" t="s">
         <v>5</v>
       </c>
       <c r="E161" t="s">
-        <v>23</v>
+        <v>18</v>
+      </c>
+      <c r="F161" s="3">
+        <v>2020</v>
       </c>
       <c r="G161" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H161" t="s">
-        <v>385</v>
+        <v>318</v>
       </c>
       <c r="I161" t="s">
-        <v>400</v>
+        <v>331</v>
       </c>
       <c r="J161" t="s">
-        <v>476</v>
+        <v>404</v>
       </c>
       <c r="K161">
         <v>199950</v>
@@ -8650,28 +8621,31 @@
         <v>161</v>
       </c>
       <c r="B162" t="s">
-        <v>401</v>
+        <v>332</v>
       </c>
       <c r="C162" t="s">
-        <v>384</v>
+        <v>317</v>
       </c>
       <c r="D162" t="s">
         <v>5</v>
       </c>
       <c r="E162" t="s">
-        <v>16</v>
+        <v>13</v>
+      </c>
+      <c r="F162" s="3">
+        <v>2020</v>
       </c>
       <c r="G162" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H162" t="s">
-        <v>385</v>
+        <v>318</v>
       </c>
       <c r="I162" t="s">
-        <v>402</v>
+        <v>333</v>
       </c>
       <c r="J162" t="s">
-        <v>476</v>
+        <v>404</v>
       </c>
       <c r="K162">
         <v>108000</v>
@@ -8691,28 +8665,31 @@
         <v>162</v>
       </c>
       <c r="B163" t="s">
-        <v>403</v>
+        <v>334</v>
       </c>
       <c r="C163" t="s">
-        <v>384</v>
+        <v>317</v>
       </c>
       <c r="D163" t="s">
         <v>5</v>
       </c>
       <c r="E163" t="s">
-        <v>16</v>
+        <v>13</v>
+      </c>
+      <c r="F163" s="3">
+        <v>2021</v>
       </c>
       <c r="G163" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H163" t="s">
-        <v>385</v>
+        <v>318</v>
       </c>
       <c r="I163" t="s">
+        <v>335</v>
+      </c>
+      <c r="J163" t="s">
         <v>404</v>
-      </c>
-      <c r="J163" t="s">
-        <v>476</v>
       </c>
       <c r="K163">
         <v>142808</v>
@@ -8732,28 +8709,31 @@
         <v>163</v>
       </c>
       <c r="B164" t="s">
-        <v>405</v>
+        <v>336</v>
       </c>
       <c r="C164" t="s">
-        <v>384</v>
+        <v>317</v>
       </c>
       <c r="D164" t="s">
         <v>5</v>
       </c>
       <c r="E164" t="s">
-        <v>16</v>
+        <v>13</v>
+      </c>
+      <c r="F164" s="3">
+        <v>2021</v>
       </c>
       <c r="G164" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H164" t="s">
-        <v>385</v>
+        <v>318</v>
       </c>
       <c r="I164" t="s">
-        <v>406</v>
+        <v>337</v>
       </c>
       <c r="J164" t="s">
-        <v>476</v>
+        <v>404</v>
       </c>
       <c r="K164">
         <v>80463</v>
@@ -8773,28 +8753,31 @@
         <v>164</v>
       </c>
       <c r="B165" t="s">
-        <v>407</v>
+        <v>338</v>
       </c>
       <c r="C165" t="s">
-        <v>384</v>
+        <v>317</v>
       </c>
       <c r="D165" t="s">
         <v>5</v>
       </c>
       <c r="E165" t="s">
-        <v>23</v>
+        <v>18</v>
+      </c>
+      <c r="F165" s="3">
+        <v>2023</v>
       </c>
       <c r="G165" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H165" t="s">
-        <v>385</v>
+        <v>318</v>
       </c>
       <c r="I165" t="s">
-        <v>408</v>
+        <v>339</v>
       </c>
       <c r="J165" t="s">
-        <v>488</v>
+        <v>416</v>
       </c>
       <c r="K165">
         <v>83000</v>
@@ -8814,25 +8797,28 @@
         <v>165</v>
       </c>
       <c r="B166" t="s">
-        <v>409</v>
+        <v>340</v>
       </c>
       <c r="C166" t="s">
-        <v>384</v>
+        <v>317</v>
       </c>
       <c r="D166" t="s">
         <v>5</v>
       </c>
+      <c r="F166" s="3">
+        <v>2024</v>
+      </c>
       <c r="G166" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H166" t="s">
-        <v>385</v>
+        <v>318</v>
       </c>
       <c r="I166" t="s">
-        <v>410</v>
+        <v>341</v>
       </c>
       <c r="J166" t="s">
-        <v>488</v>
+        <v>416</v>
       </c>
       <c r="K166">
         <v>129000</v>
@@ -8852,28 +8838,28 @@
         <v>166</v>
       </c>
       <c r="B167" t="s">
-        <v>411</v>
+        <v>342</v>
       </c>
       <c r="C167" t="s">
-        <v>412</v>
+        <v>343</v>
       </c>
       <c r="D167" t="s">
         <v>5</v>
       </c>
-      <c r="F167" t="s">
-        <v>234</v>
+      <c r="F167" s="3" t="s">
+        <v>430</v>
       </c>
       <c r="G167" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H167" t="s">
-        <v>118</v>
+        <v>92</v>
       </c>
       <c r="I167" t="s">
-        <v>413</v>
+        <v>344</v>
       </c>
       <c r="J167" t="s">
-        <v>488</v>
+        <v>416</v>
       </c>
       <c r="K167">
         <v>62209</v>
@@ -8893,28 +8879,28 @@
         <v>167</v>
       </c>
       <c r="B168" t="s">
-        <v>414</v>
+        <v>345</v>
       </c>
       <c r="C168" t="s">
-        <v>412</v>
+        <v>343</v>
       </c>
       <c r="D168" t="s">
         <v>5</v>
       </c>
-      <c r="F168" t="s">
-        <v>326</v>
+      <c r="F168" s="3" t="s">
+        <v>441</v>
       </c>
       <c r="G168" t="s">
+        <v>6</v>
+      </c>
+      <c r="H168" t="s">
         <v>7</v>
       </c>
-      <c r="H168" t="s">
-        <v>8</v>
-      </c>
       <c r="I168" t="s">
-        <v>415</v>
+        <v>346</v>
       </c>
       <c r="J168" t="s">
-        <v>473</v>
+        <v>401</v>
       </c>
       <c r="K168">
         <v>36117</v>
@@ -8934,31 +8920,31 @@
         <v>168</v>
       </c>
       <c r="B169" t="s">
-        <v>416</v>
+        <v>347</v>
       </c>
       <c r="C169" t="s">
-        <v>412</v>
+        <v>343</v>
       </c>
       <c r="D169" t="s">
         <v>5</v>
       </c>
       <c r="E169" t="s">
-        <v>23</v>
-      </c>
-      <c r="F169" t="s">
-        <v>163</v>
+        <v>18</v>
+      </c>
+      <c r="F169" s="3" t="s">
+        <v>440</v>
       </c>
       <c r="G169" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H169" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="I169" t="s">
-        <v>417</v>
+        <v>348</v>
       </c>
       <c r="J169" t="s">
-        <v>473</v>
+        <v>401</v>
       </c>
       <c r="K169">
         <v>49900</v>
@@ -8978,31 +8964,31 @@
         <v>169</v>
       </c>
       <c r="B170" t="s">
-        <v>418</v>
+        <v>349</v>
       </c>
       <c r="C170" t="s">
-        <v>412</v>
+        <v>343</v>
       </c>
       <c r="D170" t="s">
         <v>5</v>
       </c>
       <c r="E170" t="s">
-        <v>16</v>
-      </c>
-      <c r="F170" t="s">
-        <v>419</v>
+        <v>13</v>
+      </c>
+      <c r="F170" s="3" t="s">
+        <v>440</v>
       </c>
       <c r="G170" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H170" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="I170" t="s">
-        <v>420</v>
+        <v>350</v>
       </c>
       <c r="J170" t="s">
-        <v>473</v>
+        <v>401</v>
       </c>
       <c r="K170">
         <v>39000</v>
@@ -9022,28 +9008,28 @@
         <v>170</v>
       </c>
       <c r="B171" t="s">
-        <v>421</v>
+        <v>351</v>
       </c>
       <c r="C171" t="s">
-        <v>412</v>
+        <v>343</v>
       </c>
       <c r="D171" t="s">
         <v>5</v>
       </c>
-      <c r="F171" t="s">
-        <v>390</v>
+      <c r="F171" s="3" t="s">
+        <v>433</v>
       </c>
       <c r="G171" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H171" t="s">
-        <v>213</v>
+        <v>167</v>
       </c>
       <c r="I171" t="s">
-        <v>422</v>
+        <v>352</v>
       </c>
       <c r="J171" t="s">
-        <v>473</v>
+        <v>401</v>
       </c>
       <c r="K171">
         <v>49000</v>
@@ -9063,25 +9049,28 @@
         <v>171</v>
       </c>
       <c r="B172" t="s">
-        <v>423</v>
+        <v>353</v>
       </c>
       <c r="C172" t="s">
-        <v>412</v>
+        <v>343</v>
       </c>
       <c r="D172" t="s">
-        <v>216</v>
+        <v>170</v>
+      </c>
+      <c r="F172" s="3">
+        <v>2018</v>
       </c>
       <c r="G172" t="s">
+        <v>6</v>
+      </c>
+      <c r="H172" t="s">
         <v>7</v>
       </c>
-      <c r="H172" t="s">
-        <v>8</v>
-      </c>
       <c r="I172" t="s">
-        <v>424</v>
+        <v>354</v>
       </c>
       <c r="J172" t="s">
-        <v>473</v>
+        <v>401</v>
       </c>
       <c r="K172">
         <v>59400</v>
@@ -9101,28 +9090,31 @@
         <v>172</v>
       </c>
       <c r="B173" t="s">
-        <v>425</v>
+        <v>355</v>
       </c>
       <c r="C173" t="s">
-        <v>412</v>
+        <v>343</v>
       </c>
       <c r="D173" t="s">
         <v>5</v>
       </c>
       <c r="E173" t="s">
-        <v>16</v>
+        <v>13</v>
+      </c>
+      <c r="F173" s="3">
+        <v>2018</v>
       </c>
       <c r="G173" t="s">
+        <v>6</v>
+      </c>
+      <c r="H173" t="s">
         <v>7</v>
       </c>
-      <c r="H173" t="s">
-        <v>8</v>
-      </c>
       <c r="I173" t="s">
-        <v>426</v>
+        <v>356</v>
       </c>
       <c r="J173" t="s">
-        <v>473</v>
+        <v>401</v>
       </c>
       <c r="K173">
         <v>65000</v>
@@ -9142,31 +9134,31 @@
         <v>173</v>
       </c>
       <c r="B174" t="s">
-        <v>427</v>
+        <v>357</v>
       </c>
       <c r="C174" t="s">
-        <v>412</v>
+        <v>343</v>
       </c>
       <c r="D174" t="s">
         <v>5</v>
       </c>
       <c r="E174" t="s">
-        <v>429</v>
-      </c>
-      <c r="F174" t="s">
-        <v>428</v>
+        <v>358</v>
+      </c>
+      <c r="F174" s="3" t="s">
+        <v>444</v>
       </c>
       <c r="G174" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H174" t="s">
-        <v>430</v>
+        <v>359</v>
       </c>
       <c r="I174" t="s">
-        <v>431</v>
+        <v>360</v>
       </c>
       <c r="J174" t="s">
-        <v>488</v>
+        <v>416</v>
       </c>
       <c r="K174">
         <v>47000</v>
@@ -9186,28 +9178,31 @@
         <v>174</v>
       </c>
       <c r="B175" t="s">
-        <v>432</v>
+        <v>361</v>
       </c>
       <c r="C175" t="s">
-        <v>412</v>
+        <v>343</v>
       </c>
       <c r="D175" t="s">
         <v>5</v>
       </c>
       <c r="E175" t="s">
-        <v>429</v>
+        <v>358</v>
+      </c>
+      <c r="F175" s="3">
+        <v>2021</v>
       </c>
       <c r="G175" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H175" t="s">
-        <v>430</v>
+        <v>359</v>
       </c>
       <c r="I175" t="s">
-        <v>433</v>
+        <v>362</v>
       </c>
       <c r="J175" t="s">
-        <v>488</v>
+        <v>416</v>
       </c>
       <c r="K175">
         <v>29000</v>
@@ -9227,31 +9222,31 @@
         <v>175</v>
       </c>
       <c r="B176" t="s">
+        <v>363</v>
+      </c>
+      <c r="C176" t="s">
+        <v>343</v>
+      </c>
+      <c r="D176" t="s">
+        <v>5</v>
+      </c>
+      <c r="E176" t="s">
+        <v>18</v>
+      </c>
+      <c r="F176" s="3" t="s">
         <v>434</v>
       </c>
-      <c r="C176" t="s">
-        <v>412</v>
-      </c>
-      <c r="D176" t="s">
-        <v>5</v>
-      </c>
-      <c r="E176" t="s">
-        <v>23</v>
-      </c>
-      <c r="F176" t="s">
-        <v>107</v>
-      </c>
       <c r="G176" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H176" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="I176" t="s">
-        <v>435</v>
+        <v>364</v>
       </c>
       <c r="J176" t="s">
-        <v>488</v>
+        <v>416</v>
       </c>
       <c r="K176">
         <v>132239</v>
@@ -9271,28 +9266,31 @@
         <v>176</v>
       </c>
       <c r="B177" t="s">
-        <v>436</v>
+        <v>365</v>
       </c>
       <c r="C177" t="s">
-        <v>412</v>
+        <v>343</v>
       </c>
       <c r="D177" t="s">
         <v>5</v>
       </c>
       <c r="E177" t="s">
-        <v>16</v>
+        <v>13</v>
+      </c>
+      <c r="F177" s="3">
+        <v>2019</v>
       </c>
       <c r="G177" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H177" t="s">
-        <v>430</v>
+        <v>359</v>
       </c>
       <c r="I177" t="s">
-        <v>437</v>
+        <v>366</v>
       </c>
       <c r="J177" t="s">
-        <v>488</v>
+        <v>416</v>
       </c>
       <c r="K177">
         <v>35016</v>
@@ -9312,25 +9310,28 @@
         <v>177</v>
       </c>
       <c r="B178" t="s">
-        <v>438</v>
+        <v>367</v>
       </c>
       <c r="C178" t="s">
-        <v>412</v>
+        <v>343</v>
       </c>
       <c r="D178" t="s">
         <v>5</v>
       </c>
+      <c r="F178" s="3">
+        <v>2023</v>
+      </c>
       <c r="G178" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H178" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="I178" t="s">
-        <v>439</v>
+        <v>368</v>
       </c>
       <c r="J178" t="s">
-        <v>488</v>
+        <v>416</v>
       </c>
       <c r="K178">
         <v>60000</v>
@@ -9350,28 +9351,28 @@
         <v>178</v>
       </c>
       <c r="B179" t="s">
-        <v>440</v>
+        <v>369</v>
       </c>
       <c r="C179" t="s">
-        <v>412</v>
+        <v>343</v>
       </c>
       <c r="D179" t="s">
         <v>5</v>
       </c>
-      <c r="F179" t="s">
-        <v>441</v>
+      <c r="F179" s="3" t="s">
+        <v>445</v>
       </c>
       <c r="G179" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H179" t="s">
-        <v>385</v>
+        <v>318</v>
       </c>
       <c r="I179" t="s">
-        <v>442</v>
+        <v>370</v>
       </c>
       <c r="J179" t="s">
-        <v>473</v>
+        <v>401</v>
       </c>
       <c r="K179">
         <v>90244</v>
@@ -9391,25 +9392,28 @@
         <v>179</v>
       </c>
       <c r="B180" t="s">
-        <v>443</v>
+        <v>371</v>
       </c>
       <c r="C180" t="s">
-        <v>412</v>
+        <v>343</v>
       </c>
       <c r="D180" t="s">
         <v>5</v>
       </c>
+      <c r="F180" s="3">
+        <v>2022</v>
+      </c>
       <c r="G180" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H180" t="s">
-        <v>385</v>
+        <v>318</v>
       </c>
       <c r="I180" t="s">
-        <v>444</v>
+        <v>372</v>
       </c>
       <c r="J180" t="s">
-        <v>488</v>
+        <v>416</v>
       </c>
       <c r="K180">
         <v>38700</v>
@@ -9429,25 +9433,28 @@
         <v>180</v>
       </c>
       <c r="B181" t="s">
-        <v>445</v>
+        <v>373</v>
       </c>
       <c r="C181" t="s">
-        <v>412</v>
+        <v>343</v>
       </c>
       <c r="D181" t="s">
         <v>5</v>
       </c>
+      <c r="F181" s="3">
+        <v>2023</v>
+      </c>
       <c r="G181" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H181" t="s">
-        <v>385</v>
+        <v>318</v>
       </c>
       <c r="I181" t="s">
-        <v>446</v>
+        <v>374</v>
       </c>
       <c r="J181" t="s">
-        <v>489</v>
+        <v>417</v>
       </c>
       <c r="K181">
         <v>62414</v>
@@ -9467,25 +9474,28 @@
         <v>181</v>
       </c>
       <c r="B182" t="s">
-        <v>447</v>
+        <v>375</v>
       </c>
       <c r="C182" t="s">
-        <v>412</v>
+        <v>343</v>
       </c>
       <c r="D182" t="s">
         <v>5</v>
       </c>
+      <c r="F182" s="3">
+        <v>2023</v>
+      </c>
       <c r="G182" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H182" t="s">
-        <v>430</v>
+        <v>359</v>
       </c>
       <c r="I182" t="s">
-        <v>448</v>
+        <v>376</v>
       </c>
       <c r="J182" t="s">
-        <v>488</v>
+        <v>416</v>
       </c>
       <c r="K182">
         <v>51000</v>
@@ -9505,28 +9515,31 @@
         <v>182</v>
       </c>
       <c r="B183" t="s">
-        <v>449</v>
+        <v>377</v>
       </c>
       <c r="C183" t="s">
-        <v>412</v>
+        <v>343</v>
       </c>
       <c r="D183" t="s">
         <v>5</v>
       </c>
       <c r="E183" t="s">
-        <v>16</v>
+        <v>13</v>
+      </c>
+      <c r="F183" s="3">
+        <v>2024</v>
       </c>
       <c r="G183" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H183" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="I183" t="s">
-        <v>450</v>
+        <v>378</v>
       </c>
       <c r="J183" t="s">
-        <v>488</v>
+        <v>416</v>
       </c>
       <c r="K183">
         <v>53115</v>
@@ -9546,25 +9559,28 @@
         <v>183</v>
       </c>
       <c r="B184" t="s">
-        <v>451</v>
+        <v>379</v>
       </c>
       <c r="C184" t="s">
-        <v>412</v>
+        <v>343</v>
       </c>
       <c r="D184" t="s">
         <v>5</v>
       </c>
+      <c r="F184" s="3">
+        <v>2016</v>
+      </c>
       <c r="G184" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H184" t="s">
-        <v>385</v>
+        <v>318</v>
       </c>
       <c r="I184" t="s">
-        <v>452</v>
+        <v>380</v>
       </c>
       <c r="J184" t="s">
-        <v>488</v>
+        <v>416</v>
       </c>
       <c r="K184">
         <v>120000</v>
@@ -9584,28 +9600,31 @@
         <v>184</v>
       </c>
       <c r="B185" t="s">
-        <v>453</v>
+        <v>381</v>
       </c>
       <c r="C185" t="s">
-        <v>412</v>
+        <v>343</v>
       </c>
       <c r="D185" t="s">
         <v>5</v>
       </c>
       <c r="E185" t="s">
-        <v>16</v>
+        <v>13</v>
+      </c>
+      <c r="F185" s="3">
+        <v>2025</v>
       </c>
       <c r="G185" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H185" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="I185" t="s">
-        <v>454</v>
+        <v>382</v>
       </c>
       <c r="J185" t="s">
-        <v>488</v>
+        <v>416</v>
       </c>
       <c r="K185">
         <v>66477</v>
@@ -9625,25 +9644,28 @@
         <v>185</v>
       </c>
       <c r="B186" t="s">
-        <v>455</v>
+        <v>383</v>
       </c>
       <c r="C186" t="s">
-        <v>456</v>
+        <v>384</v>
       </c>
       <c r="D186" t="s">
         <v>5</v>
       </c>
       <c r="E186" t="s">
-        <v>16</v>
+        <v>13</v>
+      </c>
+      <c r="F186" s="3">
+        <v>2023</v>
       </c>
       <c r="G186" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H186" t="s">
-        <v>457</v>
+        <v>385</v>
       </c>
       <c r="I186" t="s">
-        <v>458</v>
+        <v>386</v>
       </c>
       <c r="K186">
         <v>59300</v>
@@ -9663,22 +9685,25 @@
         <v>186</v>
       </c>
       <c r="B187" t="s">
-        <v>459</v>
+        <v>387</v>
       </c>
       <c r="C187" t="s">
-        <v>456</v>
+        <v>384</v>
       </c>
       <c r="D187" t="s">
         <v>5</v>
       </c>
+      <c r="F187" s="3">
+        <v>2018</v>
+      </c>
       <c r="G187" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H187" t="s">
-        <v>457</v>
+        <v>385</v>
       </c>
       <c r="I187" t="s">
-        <v>460</v>
+        <v>388</v>
       </c>
       <c r="K187">
         <v>44000</v>
@@ -9698,22 +9723,25 @@
         <v>187</v>
       </c>
       <c r="B188" t="s">
-        <v>461</v>
+        <v>389</v>
       </c>
       <c r="C188" t="s">
-        <v>456</v>
+        <v>384</v>
       </c>
       <c r="D188" t="s">
         <v>5</v>
       </c>
+      <c r="F188" s="3">
+        <v>2018</v>
+      </c>
       <c r="G188" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H188" t="s">
-        <v>457</v>
+        <v>385</v>
       </c>
       <c r="I188" t="s">
-        <v>462</v>
+        <v>390</v>
       </c>
       <c r="K188">
         <v>26528</v>
@@ -9733,25 +9761,28 @@
         <v>188</v>
       </c>
       <c r="B189" t="s">
-        <v>463</v>
+        <v>391</v>
       </c>
       <c r="C189" t="s">
-        <v>456</v>
+        <v>384</v>
       </c>
       <c r="D189" t="s">
         <v>5</v>
       </c>
       <c r="E189" t="s">
-        <v>16</v>
+        <v>13</v>
+      </c>
+      <c r="F189" s="3">
+        <v>2017</v>
       </c>
       <c r="G189" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H189" t="s">
-        <v>457</v>
+        <v>385</v>
       </c>
       <c r="I189" t="s">
-        <v>464</v>
+        <v>392</v>
       </c>
       <c r="K189">
         <v>95684</v>
@@ -9771,22 +9802,25 @@
         <v>189</v>
       </c>
       <c r="B190" t="s">
-        <v>465</v>
+        <v>393</v>
       </c>
       <c r="C190" t="s">
-        <v>456</v>
+        <v>384</v>
       </c>
       <c r="D190" t="s">
         <v>5</v>
       </c>
+      <c r="F190" s="3">
+        <v>2021</v>
+      </c>
       <c r="G190" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H190" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="I190" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="K190">
         <v>26737</v>
@@ -9806,25 +9840,28 @@
         <v>190</v>
       </c>
       <c r="B191" t="s">
-        <v>466</v>
+        <v>394</v>
       </c>
       <c r="C191" t="s">
-        <v>456</v>
+        <v>384</v>
       </c>
       <c r="D191" t="s">
         <v>5</v>
       </c>
       <c r="E191" t="s">
-        <v>16</v>
+        <v>13</v>
+      </c>
+      <c r="F191" s="3">
+        <v>2023</v>
       </c>
       <c r="G191" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H191" t="s">
-        <v>457</v>
+        <v>385</v>
       </c>
       <c r="I191" t="s">
-        <v>467</v>
+        <v>395</v>
       </c>
       <c r="K191">
         <v>60000</v>
@@ -9844,22 +9881,25 @@
         <v>191</v>
       </c>
       <c r="B192" t="s">
-        <v>468</v>
+        <v>396</v>
       </c>
       <c r="C192" t="s">
-        <v>456</v>
+        <v>384</v>
       </c>
       <c r="D192" t="s">
         <v>5</v>
       </c>
+      <c r="F192" s="3">
+        <v>2019</v>
+      </c>
       <c r="G192" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H192" t="s">
-        <v>457</v>
+        <v>385</v>
       </c>
       <c r="I192" t="s">
-        <v>469</v>
+        <v>397</v>
       </c>
       <c r="K192">
         <v>34895</v>
@@ -9879,25 +9919,28 @@
         <v>192</v>
       </c>
       <c r="B193" t="s">
-        <v>470</v>
+        <v>398</v>
       </c>
       <c r="C193" t="s">
-        <v>456</v>
+        <v>384</v>
       </c>
       <c r="D193" t="s">
         <v>5</v>
       </c>
       <c r="E193" t="s">
-        <v>16</v>
+        <v>13</v>
+      </c>
+      <c r="F193" s="3">
+        <v>2022</v>
       </c>
       <c r="G193" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H193" t="s">
-        <v>457</v>
+        <v>385</v>
       </c>
       <c r="I193" t="s">
-        <v>471</v>
+        <v>399</v>
       </c>
       <c r="K193">
         <v>76210</v>
@@ -9916,6 +9959,9 @@
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <ignoredErrors>
+    <ignoredError sqref="F2:F26 F43:F60 F27:F32 F34:F35 F39:F40 F64:F80 F82:F97 F100:F106 F108:F112 F125:F135 F138:F152 F155:F159 F167:F171 F174 F176 F179" numberStoredAsText="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 

--- a/data.xlsx
+++ b/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yuhang/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\intern.bjres\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD82D224-D7F9-6141-80BC-9EF445000A53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB4D5EC1-FCC0-42F2-9F57-D68676696921}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1587" uniqueCount="446">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1591" uniqueCount="450">
   <si>
     <t>所在市</t>
   </si>
@@ -1372,6 +1372,18 @@
   </si>
   <si>
     <t>2023</t>
+  </si>
+  <si>
+    <t>上季度租金报价</t>
+  </si>
+  <si>
+    <t>上季度物业费</t>
+  </si>
+  <si>
+    <t>上季度表面租金</t>
+  </si>
+  <si>
+    <t>上季度免租期</t>
   </si>
 </sst>
 </file>
@@ -1382,14 +1394,14 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1397,14 +1409,14 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1433,16 +1445,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2" xfId="1" xr:uid="{81D4EE7A-49F9-4559-B92D-CA7C8AC626DC}"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1459,11 +1470,7 @@
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <person displayName="Lu, Ming" id="{5082D207-AEA0-4BFE-AD66-E999121DF51A}" userId="S::ming.lu@colliers.com::32ed6a1f-6094-49ff-9223-1ec24026be8e" providerId="AD"/>
-  <person displayName="Gao, Cassie" id="{5D34FAD7-9A91-4AF2-9BF2-44013CCF14CA}" userId="S::cassie.gao@colliers.com::4a65d78a-bee0-4019-98ea-63fb6685db53" providerId="AD"/>
-  <person displayName="Zhao, Danni" id="{5427DF3F-99FD-4443-A208-B99A4A464D38}" userId="S::danni.zhao@colliers.com::342a9774-4ff6-4a8f-b5fb-e015adf797d2" providerId="AD"/>
-</personList>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1751,25 +1758,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B280671-4AFA-4641-88D4-A51F39483890}">
-  <dimension ref="A1:N193"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
+  <dimension ref="A1:R193"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="5.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="41.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.33203125" style="2" customWidth="1"/>
-    <col min="7" max="8" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="41.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.36328125" customWidth="1"/>
+    <col min="7" max="8" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.1796875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.36328125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.36328125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:18">
       <c r="A1" t="s">
         <v>405</v>
       </c>
@@ -1812,8 +1822,20 @@
       <c r="N1" t="s">
         <v>414</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" t="s">
+        <v>446</v>
+      </c>
+      <c r="P1" t="s">
+        <v>447</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>448</v>
+      </c>
+      <c r="R1" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1826,7 +1848,7 @@
       <c r="D2" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="2" t="s">
         <v>419</v>
       </c>
       <c r="G2" t="s">
@@ -1853,8 +1875,20 @@
       <c r="N2">
         <v>9400</v>
       </c>
-    </row>
-    <row r="3" spans="1:14">
+      <c r="O2">
+        <v>460</v>
+      </c>
+      <c r="P2">
+        <v>45</v>
+      </c>
+      <c r="Q2">
+        <v>315</v>
+      </c>
+      <c r="R2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1867,7 +1901,7 @@
       <c r="D3" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="2" t="s">
         <v>420</v>
       </c>
       <c r="G3" t="s">
@@ -1894,8 +1928,20 @@
       <c r="N3">
         <v>1450</v>
       </c>
-    </row>
-    <row r="4" spans="1:14">
+      <c r="O3">
+        <v>460</v>
+      </c>
+      <c r="P3">
+        <v>45</v>
+      </c>
+      <c r="Q3">
+        <v>335</v>
+      </c>
+      <c r="R3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1911,7 +1957,7 @@
       <c r="E4" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="2" t="s">
         <v>421</v>
       </c>
       <c r="G4" t="s">
@@ -1938,8 +1984,20 @@
       <c r="N4">
         <v>13100</v>
       </c>
-    </row>
-    <row r="5" spans="1:14">
+      <c r="O4">
+        <v>700</v>
+      </c>
+      <c r="P4">
+        <v>49</v>
+      </c>
+      <c r="Q4">
+        <v>385</v>
+      </c>
+      <c r="R4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1955,7 +2013,7 @@
       <c r="E5" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="2" t="s">
         <v>422</v>
       </c>
       <c r="G5" t="s">
@@ -1982,8 +2040,20 @@
       <c r="N5">
         <v>1950</v>
       </c>
-    </row>
-    <row r="6" spans="1:14">
+      <c r="O5">
+        <v>850</v>
+      </c>
+      <c r="P5">
+        <v>49</v>
+      </c>
+      <c r="Q5">
+        <v>400</v>
+      </c>
+      <c r="R5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1999,7 +2069,7 @@
       <c r="E6" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="F6" s="2" t="s">
         <v>423</v>
       </c>
       <c r="G6" t="s">
@@ -2026,8 +2096,20 @@
       <c r="N6">
         <v>5962</v>
       </c>
-    </row>
-    <row r="7" spans="1:14">
+      <c r="O6">
+        <v>450</v>
+      </c>
+      <c r="P6">
+        <v>43</v>
+      </c>
+      <c r="Q6">
+        <v>255</v>
+      </c>
+      <c r="R6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2040,7 +2122,7 @@
       <c r="D7" t="s">
         <v>5</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="2" t="s">
         <v>424</v>
       </c>
       <c r="G7" t="s">
@@ -2067,8 +2149,20 @@
       <c r="N7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:14">
+      <c r="O7">
+        <v>350</v>
+      </c>
+      <c r="P7">
+        <v>43</v>
+      </c>
+      <c r="Q7">
+        <v>265</v>
+      </c>
+      <c r="R7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2084,7 +2178,7 @@
       <c r="E8" t="s">
         <v>18</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="F8" s="2" t="s">
         <v>424</v>
       </c>
       <c r="G8" t="s">
@@ -2111,8 +2205,20 @@
       <c r="N8">
         <v>21706</v>
       </c>
-    </row>
-    <row r="9" spans="1:14">
+      <c r="O8">
+        <v>350</v>
+      </c>
+      <c r="P8">
+        <v>35</v>
+      </c>
+      <c r="Q8">
+        <v>200</v>
+      </c>
+      <c r="R8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2125,7 +2231,7 @@
       <c r="D9" t="s">
         <v>5</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="F9" s="2" t="s">
         <v>424</v>
       </c>
       <c r="G9" t="s">
@@ -2152,8 +2258,20 @@
       <c r="N9">
         <v>3478.47</v>
       </c>
-    </row>
-    <row r="10" spans="1:14">
+      <c r="O9">
+        <v>260</v>
+      </c>
+      <c r="P9">
+        <v>33</v>
+      </c>
+      <c r="Q9">
+        <v>260</v>
+      </c>
+      <c r="R9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2169,7 +2287,7 @@
       <c r="E10" t="s">
         <v>18</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="F10" s="2" t="s">
         <v>425</v>
       </c>
       <c r="G10" t="s">
@@ -2196,8 +2314,20 @@
       <c r="N10">
         <v>23242</v>
       </c>
-    </row>
-    <row r="11" spans="1:14">
+      <c r="O10">
+        <v>240</v>
+      </c>
+      <c r="P10">
+        <v>33</v>
+      </c>
+      <c r="Q10">
+        <v>240</v>
+      </c>
+      <c r="R10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2213,7 +2343,7 @@
       <c r="E11" t="s">
         <v>18</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="F11" s="2" t="s">
         <v>426</v>
       </c>
       <c r="G11" t="s">
@@ -2240,8 +2370,20 @@
       <c r="N11">
         <v>17000</v>
       </c>
-    </row>
-    <row r="12" spans="1:14">
+      <c r="O11">
+        <v>240</v>
+      </c>
+      <c r="P11">
+        <v>30</v>
+      </c>
+      <c r="Q11">
+        <v>175</v>
+      </c>
+      <c r="R11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2257,7 +2399,7 @@
       <c r="E12" t="s">
         <v>13</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="F12" s="2" t="s">
         <v>426</v>
       </c>
       <c r="G12" t="s">
@@ -2284,8 +2426,20 @@
       <c r="N12">
         <v>4929</v>
       </c>
-    </row>
-    <row r="13" spans="1:14">
+      <c r="O12">
+        <v>290</v>
+      </c>
+      <c r="P12">
+        <v>28</v>
+      </c>
+      <c r="Q12">
+        <v>210</v>
+      </c>
+      <c r="R12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2301,7 +2455,7 @@
       <c r="E13" t="s">
         <v>18</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="F13" s="2" t="s">
         <v>426</v>
       </c>
       <c r="G13" t="s">
@@ -2328,8 +2482,20 @@
       <c r="N13">
         <v>8018</v>
       </c>
-    </row>
-    <row r="14" spans="1:14">
+      <c r="O13">
+        <v>465</v>
+      </c>
+      <c r="P13">
+        <v>38</v>
+      </c>
+      <c r="Q13">
+        <v>290</v>
+      </c>
+      <c r="R13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2345,7 +2511,7 @@
       <c r="E14" t="s">
         <v>18</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="F14" s="2" t="s">
         <v>427</v>
       </c>
       <c r="G14" t="s">
@@ -2372,8 +2538,20 @@
       <c r="N14">
         <v>6556</v>
       </c>
-    </row>
-    <row r="15" spans="1:14">
+      <c r="O14">
+        <v>465</v>
+      </c>
+      <c r="P14">
+        <v>38</v>
+      </c>
+      <c r="Q14">
+        <v>290</v>
+      </c>
+      <c r="R14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2389,7 +2567,7 @@
       <c r="E15" t="s">
         <v>18</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="F15" s="2" t="s">
         <v>426</v>
       </c>
       <c r="G15" t="s">
@@ -2416,8 +2594,20 @@
       <c r="N15">
         <v>12000</v>
       </c>
-    </row>
-    <row r="16" spans="1:14">
+      <c r="O15">
+        <v>490</v>
+      </c>
+      <c r="P15">
+        <v>38</v>
+      </c>
+      <c r="Q15">
+        <v>310</v>
+      </c>
+      <c r="R15">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2433,7 +2623,7 @@
       <c r="E16" t="s">
         <v>18</v>
       </c>
-      <c r="F16" s="3" t="s">
+      <c r="F16" s="2" t="s">
         <v>426</v>
       </c>
       <c r="G16" t="s">
@@ -2460,8 +2650,20 @@
       <c r="N16">
         <v>17573.5</v>
       </c>
-    </row>
-    <row r="17" spans="1:14">
+      <c r="O16">
+        <v>450</v>
+      </c>
+      <c r="P16">
+        <v>35</v>
+      </c>
+      <c r="Q16">
+        <v>240</v>
+      </c>
+      <c r="R16">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18">
       <c r="A17">
         <v>16</v>
       </c>
@@ -2477,7 +2679,7 @@
       <c r="E17" t="s">
         <v>13</v>
       </c>
-      <c r="F17" s="3" t="s">
+      <c r="F17" s="2" t="s">
         <v>426</v>
       </c>
       <c r="G17" t="s">
@@ -2504,8 +2706,20 @@
       <c r="N17">
         <v>4608.3500000000004</v>
       </c>
-    </row>
-    <row r="18" spans="1:14">
+      <c r="O17">
+        <v>360</v>
+      </c>
+      <c r="P17">
+        <v>36</v>
+      </c>
+      <c r="Q17">
+        <v>240</v>
+      </c>
+      <c r="R17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2521,7 +2735,7 @@
       <c r="E18" t="s">
         <v>18</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="F18" s="2" t="s">
         <v>427</v>
       </c>
       <c r="G18" t="s">
@@ -2548,8 +2762,20 @@
       <c r="N18">
         <v>7891</v>
       </c>
-    </row>
-    <row r="19" spans="1:14">
+      <c r="O18">
+        <v>400</v>
+      </c>
+      <c r="P18">
+        <v>33</v>
+      </c>
+      <c r="Q18">
+        <v>240</v>
+      </c>
+      <c r="R18">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2565,7 +2791,7 @@
       <c r="E19" t="s">
         <v>13</v>
       </c>
-      <c r="F19" s="3" t="s">
+      <c r="F19" s="2" t="s">
         <v>427</v>
       </c>
       <c r="G19" t="s">
@@ -2592,8 +2818,20 @@
       <c r="N19">
         <v>4617</v>
       </c>
-    </row>
-    <row r="20" spans="1:14">
+      <c r="O19">
+        <v>300</v>
+      </c>
+      <c r="P19">
+        <v>36</v>
+      </c>
+      <c r="Q19">
+        <v>220</v>
+      </c>
+      <c r="R19">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2609,7 +2847,7 @@
       <c r="E20" t="s">
         <v>18</v>
       </c>
-      <c r="F20" s="3" t="s">
+      <c r="F20" s="2" t="s">
         <v>427</v>
       </c>
       <c r="G20" t="s">
@@ -2636,8 +2874,20 @@
       <c r="N20">
         <v>48600</v>
       </c>
-    </row>
-    <row r="21" spans="1:14">
+      <c r="O20">
+        <v>400</v>
+      </c>
+      <c r="P20">
+        <v>38</v>
+      </c>
+      <c r="Q20">
+        <v>300</v>
+      </c>
+      <c r="R20">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18">
       <c r="A21">
         <v>20</v>
       </c>
@@ -2653,7 +2903,7 @@
       <c r="E21" t="s">
         <v>18</v>
       </c>
-      <c r="F21" s="3" t="s">
+      <c r="F21" s="2" t="s">
         <v>428</v>
       </c>
       <c r="G21" t="s">
@@ -2680,8 +2930,20 @@
       <c r="N21">
         <v>10000</v>
       </c>
-    </row>
-    <row r="22" spans="1:14">
+      <c r="O21">
+        <v>420</v>
+      </c>
+      <c r="P21">
+        <v>32</v>
+      </c>
+      <c r="Q21">
+        <v>215</v>
+      </c>
+      <c r="R21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18">
       <c r="A22">
         <v>21</v>
       </c>
@@ -2694,7 +2956,7 @@
       <c r="D22" t="s">
         <v>5</v>
       </c>
-      <c r="F22" s="3" t="s">
+      <c r="F22" s="2" t="s">
         <v>428</v>
       </c>
       <c r="G22" t="s">
@@ -2721,8 +2983,20 @@
       <c r="N22">
         <v>1000</v>
       </c>
-    </row>
-    <row r="23" spans="1:14">
+      <c r="O22">
+        <v>270</v>
+      </c>
+      <c r="P22">
+        <v>32</v>
+      </c>
+      <c r="Q22">
+        <v>250</v>
+      </c>
+      <c r="R22">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18">
       <c r="A23">
         <v>22</v>
       </c>
@@ -2738,7 +3012,7 @@
       <c r="E23" t="s">
         <v>18</v>
       </c>
-      <c r="F23" s="3">
+      <c r="F23" s="2">
         <v>2009</v>
       </c>
       <c r="G23" t="s">
@@ -2765,8 +3039,20 @@
       <c r="N23">
         <v>18122</v>
       </c>
-    </row>
-    <row r="24" spans="1:14">
+      <c r="O23">
+        <v>300</v>
+      </c>
+      <c r="P23">
+        <v>32</v>
+      </c>
+      <c r="Q23">
+        <v>230</v>
+      </c>
+      <c r="R23">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18">
       <c r="A24">
         <v>23</v>
       </c>
@@ -2782,7 +3068,7 @@
       <c r="E24" t="s">
         <v>18</v>
       </c>
-      <c r="F24" s="3">
+      <c r="F24" s="2">
         <v>2009</v>
       </c>
       <c r="G24" t="s">
@@ -2809,8 +3095,20 @@
       <c r="N24">
         <v>11713</v>
       </c>
-    </row>
-    <row r="25" spans="1:14">
+      <c r="O24">
+        <v>300</v>
+      </c>
+      <c r="P24">
+        <v>32</v>
+      </c>
+      <c r="Q24">
+        <v>197</v>
+      </c>
+      <c r="R24">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18">
       <c r="A25">
         <v>24</v>
       </c>
@@ -2826,7 +3124,7 @@
       <c r="E25" t="s">
         <v>18</v>
       </c>
-      <c r="F25" s="3" t="s">
+      <c r="F25" s="2" t="s">
         <v>430</v>
       </c>
       <c r="G25" t="s">
@@ -2853,8 +3151,20 @@
       <c r="N25">
         <v>11256</v>
       </c>
-    </row>
-    <row r="26" spans="1:14">
+      <c r="O25">
+        <v>420</v>
+      </c>
+      <c r="P25">
+        <v>32</v>
+      </c>
+      <c r="Q25">
+        <v>285</v>
+      </c>
+      <c r="R25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18">
       <c r="A26">
         <v>25</v>
       </c>
@@ -2870,7 +3180,7 @@
       <c r="E26" t="s">
         <v>18</v>
       </c>
-      <c r="F26" s="3" t="s">
+      <c r="F26" s="2" t="s">
         <v>430</v>
       </c>
       <c r="G26" t="s">
@@ -2897,8 +3207,20 @@
       <c r="N26">
         <v>15305</v>
       </c>
-    </row>
-    <row r="27" spans="1:14">
+      <c r="O26">
+        <v>430</v>
+      </c>
+      <c r="P26">
+        <v>43</v>
+      </c>
+      <c r="Q26">
+        <v>270</v>
+      </c>
+      <c r="R26">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18">
       <c r="A27">
         <v>26</v>
       </c>
@@ -2914,7 +3236,7 @@
       <c r="E27" t="s">
         <v>18</v>
       </c>
-      <c r="F27" s="3" t="s">
+      <c r="F27" s="2" t="s">
         <v>431</v>
       </c>
       <c r="G27" t="s">
@@ -2941,8 +3263,20 @@
       <c r="N27">
         <v>20603</v>
       </c>
-    </row>
-    <row r="28" spans="1:14">
+      <c r="O27">
+        <v>450</v>
+      </c>
+      <c r="P27">
+        <v>39</v>
+      </c>
+      <c r="Q27">
+        <v>295</v>
+      </c>
+      <c r="R27">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18">
       <c r="A28">
         <v>27</v>
       </c>
@@ -2958,7 +3292,7 @@
       <c r="E28" t="s">
         <v>13</v>
       </c>
-      <c r="F28" s="3" t="s">
+      <c r="F28" s="2" t="s">
         <v>432</v>
       </c>
       <c r="G28" t="s">
@@ -2985,8 +3319,20 @@
       <c r="N28">
         <v>4211</v>
       </c>
-    </row>
-    <row r="29" spans="1:14">
+      <c r="O28">
+        <v>300</v>
+      </c>
+      <c r="P28">
+        <v>35</v>
+      </c>
+      <c r="Q28">
+        <v>180</v>
+      </c>
+      <c r="R28">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18">
       <c r="A29">
         <v>28</v>
       </c>
@@ -3002,7 +3348,7 @@
       <c r="E29" t="s">
         <v>18</v>
       </c>
-      <c r="F29" s="3" t="s">
+      <c r="F29" s="2" t="s">
         <v>422</v>
       </c>
       <c r="G29" t="s">
@@ -3029,8 +3375,20 @@
       <c r="N29">
         <v>11019.17</v>
       </c>
-    </row>
-    <row r="30" spans="1:14">
+      <c r="O29">
+        <v>550</v>
+      </c>
+      <c r="P29">
+        <v>37</v>
+      </c>
+      <c r="Q29">
+        <v>300</v>
+      </c>
+      <c r="R29">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18">
       <c r="A30">
         <v>29</v>
       </c>
@@ -3046,7 +3404,7 @@
       <c r="E30" t="s">
         <v>18</v>
       </c>
-      <c r="F30" s="3" t="s">
+      <c r="F30" s="2" t="s">
         <v>433</v>
       </c>
       <c r="G30" t="s">
@@ -3073,8 +3431,20 @@
       <c r="N30">
         <v>18500</v>
       </c>
-    </row>
-    <row r="31" spans="1:14">
+      <c r="O30">
+        <v>560</v>
+      </c>
+      <c r="P30">
+        <v>50</v>
+      </c>
+      <c r="Q30">
+        <v>400</v>
+      </c>
+      <c r="R30">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18">
       <c r="A31">
         <v>30</v>
       </c>
@@ -3087,7 +3457,7 @@
       <c r="D31" t="s">
         <v>5</v>
       </c>
-      <c r="F31" s="3" t="s">
+      <c r="F31" s="2" t="s">
         <v>433</v>
       </c>
       <c r="G31" t="s">
@@ -3114,8 +3484,20 @@
       <c r="N31">
         <v>5885.75</v>
       </c>
-    </row>
-    <row r="32" spans="1:14">
+      <c r="O31">
+        <v>650</v>
+      </c>
+      <c r="P31">
+        <v>38</v>
+      </c>
+      <c r="Q31">
+        <v>350</v>
+      </c>
+      <c r="R31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18">
       <c r="A32">
         <v>31</v>
       </c>
@@ -3131,7 +3513,7 @@
       <c r="E32" t="s">
         <v>13</v>
       </c>
-      <c r="F32" s="3" t="s">
+      <c r="F32" s="2" t="s">
         <v>433</v>
       </c>
       <c r="G32" t="s">
@@ -3158,8 +3540,20 @@
       <c r="N32">
         <v>18000</v>
       </c>
-    </row>
-    <row r="33" spans="1:14">
+      <c r="O32">
+        <v>550</v>
+      </c>
+      <c r="P32">
+        <v>42</v>
+      </c>
+      <c r="Q32">
+        <v>300</v>
+      </c>
+      <c r="R32">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18">
       <c r="A33">
         <v>32</v>
       </c>
@@ -3172,7 +3566,7 @@
       <c r="D33" t="s">
         <v>5</v>
       </c>
-      <c r="F33" s="3">
+      <c r="F33" s="2">
         <v>2019</v>
       </c>
       <c r="G33" t="s">
@@ -3199,8 +3593,20 @@
       <c r="N33">
         <v>20200</v>
       </c>
-    </row>
-    <row r="34" spans="1:14">
+      <c r="O33">
+        <v>400</v>
+      </c>
+      <c r="P33">
+        <v>36</v>
+      </c>
+      <c r="Q33">
+        <v>206</v>
+      </c>
+      <c r="R33">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18">
       <c r="A34">
         <v>33</v>
       </c>
@@ -3213,7 +3619,7 @@
       <c r="D34" t="s">
         <v>5</v>
       </c>
-      <c r="F34" s="3" t="s">
+      <c r="F34" s="2" t="s">
         <v>433</v>
       </c>
       <c r="G34" t="s">
@@ -3240,8 +3646,20 @@
       <c r="N34">
         <v>52400</v>
       </c>
-    </row>
-    <row r="35" spans="1:14">
+      <c r="O34">
+        <v>400</v>
+      </c>
+      <c r="P34">
+        <v>36</v>
+      </c>
+      <c r="Q34">
+        <v>230</v>
+      </c>
+      <c r="R34">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18">
       <c r="A35">
         <v>34</v>
       </c>
@@ -3257,7 +3675,7 @@
       <c r="E35" t="s">
         <v>13</v>
       </c>
-      <c r="F35" s="3" t="s">
+      <c r="F35" s="2" t="s">
         <v>433</v>
       </c>
       <c r="G35" t="s">
@@ -3284,8 +3702,20 @@
       <c r="N35">
         <v>21965</v>
       </c>
-    </row>
-    <row r="36" spans="1:14">
+      <c r="O35">
+        <v>600</v>
+      </c>
+      <c r="P35">
+        <v>58</v>
+      </c>
+      <c r="Q35">
+        <v>490</v>
+      </c>
+      <c r="R35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18">
       <c r="A36">
         <v>35</v>
       </c>
@@ -3301,7 +3731,7 @@
       <c r="E36" t="s">
         <v>18</v>
       </c>
-      <c r="F36" s="3">
+      <c r="F36" s="2">
         <v>2020</v>
       </c>
       <c r="G36" t="s">
@@ -3328,8 +3758,20 @@
       <c r="N36">
         <v>20356</v>
       </c>
-    </row>
-    <row r="37" spans="1:14">
+      <c r="O36">
+        <v>520</v>
+      </c>
+      <c r="P36">
+        <v>38</v>
+      </c>
+      <c r="Q36">
+        <v>240</v>
+      </c>
+      <c r="R36">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18">
       <c r="A37">
         <v>36</v>
       </c>
@@ -3345,7 +3787,7 @@
       <c r="E37" t="s">
         <v>18</v>
       </c>
-      <c r="F37" s="3">
+      <c r="F37" s="2">
         <v>2020</v>
       </c>
       <c r="G37" t="s">
@@ -3372,8 +3814,20 @@
       <c r="N37">
         <v>8300</v>
       </c>
-    </row>
-    <row r="38" spans="1:14">
+      <c r="O37">
+        <v>520</v>
+      </c>
+      <c r="P37">
+        <v>38</v>
+      </c>
+      <c r="Q37">
+        <v>260</v>
+      </c>
+      <c r="R37">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18">
       <c r="A38">
         <v>37</v>
       </c>
@@ -3389,7 +3843,7 @@
       <c r="E38" t="s">
         <v>18</v>
       </c>
-      <c r="F38" s="3">
+      <c r="F38" s="2">
         <v>2010</v>
       </c>
       <c r="G38" t="s">
@@ -3416,8 +3870,20 @@
       <c r="N38">
         <v>2700</v>
       </c>
-    </row>
-    <row r="39" spans="1:14">
+      <c r="O38">
+        <v>330</v>
+      </c>
+      <c r="P38">
+        <v>34</v>
+      </c>
+      <c r="Q38">
+        <v>210</v>
+      </c>
+      <c r="R38">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18">
       <c r="A39">
         <v>38</v>
       </c>
@@ -3433,7 +3899,7 @@
       <c r="E39" t="s">
         <v>18</v>
       </c>
-      <c r="F39" s="3" t="s">
+      <c r="F39" s="2" t="s">
         <v>434</v>
       </c>
       <c r="G39" t="s">
@@ -3460,8 +3926,20 @@
       <c r="N39">
         <v>3600</v>
       </c>
-    </row>
-    <row r="40" spans="1:14">
+      <c r="O39">
+        <v>500</v>
+      </c>
+      <c r="P39">
+        <v>40</v>
+      </c>
+      <c r="Q39">
+        <v>300</v>
+      </c>
+      <c r="R39">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18">
       <c r="A40">
         <v>39</v>
       </c>
@@ -3474,7 +3952,7 @@
       <c r="D40" t="s">
         <v>5</v>
       </c>
-      <c r="F40" s="3" t="s">
+      <c r="F40" s="2" t="s">
         <v>434</v>
       </c>
       <c r="G40" t="s">
@@ -3501,8 +3979,20 @@
       <c r="N40">
         <v>18218</v>
       </c>
-    </row>
-    <row r="41" spans="1:14">
+      <c r="O40">
+        <v>166</v>
+      </c>
+      <c r="P40">
+        <v>32</v>
+      </c>
+      <c r="Q40">
+        <v>140</v>
+      </c>
+      <c r="R40">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18">
       <c r="A41">
         <v>40</v>
       </c>
@@ -3518,7 +4008,7 @@
       <c r="E41" t="s">
         <v>13</v>
       </c>
-      <c r="F41" s="3">
+      <c r="F41" s="2">
         <v>2021</v>
       </c>
       <c r="G41" t="s">
@@ -3545,8 +4035,20 @@
       <c r="N41">
         <v>9351.27</v>
       </c>
-    </row>
-    <row r="42" spans="1:14">
+      <c r="O41">
+        <v>450</v>
+      </c>
+      <c r="P41">
+        <v>38</v>
+      </c>
+      <c r="Q41">
+        <v>330</v>
+      </c>
+      <c r="R41">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18">
       <c r="A42">
         <v>41</v>
       </c>
@@ -3559,7 +4061,7 @@
       <c r="D42" t="s">
         <v>5</v>
       </c>
-      <c r="F42" s="3">
+      <c r="F42" s="2">
         <v>2009</v>
       </c>
       <c r="G42" t="s">
@@ -3586,8 +4088,20 @@
       <c r="N42">
         <v>2400</v>
       </c>
-    </row>
-    <row r="43" spans="1:14">
+      <c r="O42">
+        <v>270</v>
+      </c>
+      <c r="P42">
+        <v>36</v>
+      </c>
+      <c r="Q42">
+        <v>210</v>
+      </c>
+      <c r="R42">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18">
       <c r="A43">
         <v>42</v>
       </c>
@@ -3603,7 +4117,7 @@
       <c r="E43" t="s">
         <v>13</v>
       </c>
-      <c r="F43" s="3" t="s">
+      <c r="F43" s="2" t="s">
         <v>435</v>
       </c>
       <c r="G43" t="s">
@@ -3630,8 +4144,20 @@
       <c r="N43">
         <v>4355</v>
       </c>
-    </row>
-    <row r="44" spans="1:14">
+      <c r="O43">
+        <v>325</v>
+      </c>
+      <c r="P43">
+        <v>35</v>
+      </c>
+      <c r="Q43">
+        <v>200</v>
+      </c>
+      <c r="R43">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18">
       <c r="A44">
         <v>43</v>
       </c>
@@ -3644,7 +4170,7 @@
       <c r="D44" t="s">
         <v>5</v>
       </c>
-      <c r="F44" s="3" t="s">
+      <c r="F44" s="2" t="s">
         <v>420</v>
       </c>
       <c r="G44" t="s">
@@ -3671,8 +4197,20 @@
       <c r="N44">
         <v>11339</v>
       </c>
-    </row>
-    <row r="45" spans="1:14">
+      <c r="O44">
+        <v>484</v>
+      </c>
+      <c r="P44">
+        <v>33</v>
+      </c>
+      <c r="Q44">
+        <v>240</v>
+      </c>
+      <c r="R44">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18">
       <c r="A45">
         <v>44</v>
       </c>
@@ -3688,7 +4226,7 @@
       <c r="E45" t="s">
         <v>18</v>
       </c>
-      <c r="F45" s="3" t="s">
+      <c r="F45" s="2" t="s">
         <v>436</v>
       </c>
       <c r="G45" t="s">
@@ -3715,8 +4253,20 @@
       <c r="N45">
         <v>10000</v>
       </c>
-    </row>
-    <row r="46" spans="1:14">
+      <c r="O45">
+        <v>360</v>
+      </c>
+      <c r="P45">
+        <v>47</v>
+      </c>
+      <c r="Q45">
+        <v>250</v>
+      </c>
+      <c r="R45">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18">
       <c r="A46">
         <v>45</v>
       </c>
@@ -3732,7 +4282,7 @@
       <c r="E46" t="s">
         <v>18</v>
       </c>
-      <c r="F46" s="3" t="s">
+      <c r="F46" s="2" t="s">
         <v>437</v>
       </c>
       <c r="G46" t="s">
@@ -3759,8 +4309,20 @@
       <c r="N46">
         <v>7500</v>
       </c>
-    </row>
-    <row r="47" spans="1:14">
+      <c r="O46">
+        <v>360</v>
+      </c>
+      <c r="P46">
+        <v>47</v>
+      </c>
+      <c r="Q46">
+        <v>250</v>
+      </c>
+      <c r="R46">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18">
       <c r="A47">
         <v>46</v>
       </c>
@@ -3776,7 +4338,7 @@
       <c r="E47" t="s">
         <v>18</v>
       </c>
-      <c r="F47" s="3" t="s">
+      <c r="F47" s="2" t="s">
         <v>438</v>
       </c>
       <c r="G47" t="s">
@@ -3803,8 +4365,20 @@
       <c r="N47">
         <v>1000</v>
       </c>
-    </row>
-    <row r="48" spans="1:14">
+      <c r="O47">
+        <v>360</v>
+      </c>
+      <c r="P47">
+        <v>47</v>
+      </c>
+      <c r="Q47">
+        <v>260</v>
+      </c>
+      <c r="R47">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18">
       <c r="A48">
         <v>47</v>
       </c>
@@ -3820,7 +4394,7 @@
       <c r="E48" t="s">
         <v>18</v>
       </c>
-      <c r="F48" s="3" t="s">
+      <c r="F48" s="2" t="s">
         <v>424</v>
       </c>
       <c r="G48" t="s">
@@ -3847,8 +4421,20 @@
       <c r="N48">
         <v>16314.69</v>
       </c>
-    </row>
-    <row r="49" spans="1:14">
+      <c r="O48">
+        <v>400</v>
+      </c>
+      <c r="P48">
+        <v>33</v>
+      </c>
+      <c r="Q48">
+        <v>190</v>
+      </c>
+      <c r="R48">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18">
       <c r="A49">
         <v>48</v>
       </c>
@@ -3861,7 +4447,7 @@
       <c r="D49" t="s">
         <v>5</v>
       </c>
-      <c r="F49" s="3" t="s">
+      <c r="F49" s="2" t="s">
         <v>425</v>
       </c>
       <c r="G49" t="s">
@@ -3888,8 +4474,20 @@
       <c r="N49">
         <v>6400</v>
       </c>
-    </row>
-    <row r="50" spans="1:14">
+      <c r="O49">
+        <v>300</v>
+      </c>
+      <c r="P49">
+        <v>30</v>
+      </c>
+      <c r="Q49">
+        <v>270</v>
+      </c>
+      <c r="R49">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18">
       <c r="A50">
         <v>49</v>
       </c>
@@ -3902,7 +4500,7 @@
       <c r="D50" t="s">
         <v>5</v>
       </c>
-      <c r="F50" s="3" t="s">
+      <c r="F50" s="2" t="s">
         <v>426</v>
       </c>
       <c r="G50" t="s">
@@ -3918,7 +4516,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="51" spans="1:14">
+    <row r="51" spans="1:18">
       <c r="A51">
         <v>50</v>
       </c>
@@ -3934,7 +4532,7 @@
       <c r="E51" t="s">
         <v>18</v>
       </c>
-      <c r="F51" s="3" t="s">
+      <c r="F51" s="2" t="s">
         <v>427</v>
       </c>
       <c r="G51" t="s">
@@ -3961,8 +4559,20 @@
       <c r="N51">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="1:14">
+      <c r="O51">
+        <v>400</v>
+      </c>
+      <c r="P51">
+        <v>32</v>
+      </c>
+      <c r="Q51">
+        <v>340</v>
+      </c>
+      <c r="R51">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18">
       <c r="A52">
         <v>51</v>
       </c>
@@ -3975,7 +4585,7 @@
       <c r="D52" t="s">
         <v>5</v>
       </c>
-      <c r="F52" s="3" t="s">
+      <c r="F52" s="2" t="s">
         <v>427</v>
       </c>
       <c r="G52" t="s">
@@ -4002,8 +4612,20 @@
       <c r="N52">
         <v>78130</v>
       </c>
-    </row>
-    <row r="53" spans="1:14">
+      <c r="O52">
+        <v>417</v>
+      </c>
+      <c r="P52">
+        <v>33</v>
+      </c>
+      <c r="Q52">
+        <v>240</v>
+      </c>
+      <c r="R52">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18">
       <c r="A53">
         <v>52</v>
       </c>
@@ -4016,7 +4638,7 @@
       <c r="D53" t="s">
         <v>5</v>
       </c>
-      <c r="F53" s="3" t="s">
+      <c r="F53" s="2" t="s">
         <v>4</v>
       </c>
       <c r="G53" t="s">
@@ -4043,8 +4665,20 @@
       <c r="N53">
         <v>14000</v>
       </c>
-    </row>
-    <row r="54" spans="1:14">
+      <c r="O53">
+        <v>300</v>
+      </c>
+      <c r="P53">
+        <v>30</v>
+      </c>
+      <c r="Q53">
+        <v>210</v>
+      </c>
+      <c r="R53">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18">
       <c r="A54">
         <v>53</v>
       </c>
@@ -4060,7 +4694,7 @@
       <c r="E54" t="s">
         <v>13</v>
       </c>
-      <c r="F54" s="3" t="s">
+      <c r="F54" s="2" t="s">
         <v>115</v>
       </c>
       <c r="G54" t="s">
@@ -4087,8 +4721,20 @@
       <c r="N54">
         <v>6151.66</v>
       </c>
-    </row>
-    <row r="55" spans="1:14">
+      <c r="O54">
+        <v>390</v>
+      </c>
+      <c r="P54">
+        <v>36</v>
+      </c>
+      <c r="Q54">
+        <v>240</v>
+      </c>
+      <c r="R54">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18">
       <c r="A55">
         <v>54</v>
       </c>
@@ -4101,7 +4747,7 @@
       <c r="D55" t="s">
         <v>5</v>
       </c>
-      <c r="F55" s="3" t="s">
+      <c r="F55" s="2" t="s">
         <v>426</v>
       </c>
       <c r="G55" t="s">
@@ -4128,8 +4774,20 @@
       <c r="N55">
         <v>20901</v>
       </c>
-    </row>
-    <row r="56" spans="1:14">
+      <c r="O55">
+        <v>360</v>
+      </c>
+      <c r="P55">
+        <v>34</v>
+      </c>
+      <c r="Q55">
+        <v>210</v>
+      </c>
+      <c r="R55">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18">
       <c r="A56">
         <v>55</v>
       </c>
@@ -4142,7 +4800,7 @@
       <c r="D56" t="s">
         <v>5</v>
       </c>
-      <c r="F56" s="3" t="s">
+      <c r="F56" s="2" t="s">
         <v>439</v>
       </c>
       <c r="G56" t="s">
@@ -4169,8 +4827,20 @@
       <c r="N56">
         <v>12583</v>
       </c>
-    </row>
-    <row r="57" spans="1:14">
+      <c r="O56">
+        <v>480</v>
+      </c>
+      <c r="P56">
+        <v>35</v>
+      </c>
+      <c r="Q56">
+        <v>232</v>
+      </c>
+      <c r="R56">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18">
       <c r="A57">
         <v>56</v>
       </c>
@@ -4183,7 +4853,7 @@
       <c r="D57" t="s">
         <v>5</v>
       </c>
-      <c r="F57" s="3" t="s">
+      <c r="F57" s="2" t="s">
         <v>422</v>
       </c>
       <c r="G57" t="s">
@@ -4210,8 +4880,20 @@
       <c r="N57">
         <v>4021</v>
       </c>
-    </row>
-    <row r="58" spans="1:14">
+      <c r="O57">
+        <v>385</v>
+      </c>
+      <c r="P57">
+        <v>35</v>
+      </c>
+      <c r="Q57">
+        <v>220</v>
+      </c>
+      <c r="R57">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18">
       <c r="A58">
         <v>57</v>
       </c>
@@ -4227,7 +4909,7 @@
       <c r="E58" t="s">
         <v>13</v>
       </c>
-      <c r="F58" s="3" t="s">
+      <c r="F58" s="2" t="s">
         <v>422</v>
       </c>
       <c r="G58" t="s">
@@ -4254,8 +4936,20 @@
       <c r="N58">
         <v>7270.57</v>
       </c>
-    </row>
-    <row r="59" spans="1:14">
+      <c r="O58">
+        <v>240</v>
+      </c>
+      <c r="P58">
+        <v>33</v>
+      </c>
+      <c r="Q58">
+        <v>180</v>
+      </c>
+      <c r="R58">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18">
       <c r="A59">
         <v>58</v>
       </c>
@@ -4271,7 +4965,7 @@
       <c r="E59" t="s">
         <v>13</v>
       </c>
-      <c r="F59" s="3" t="s">
+      <c r="F59" s="2" t="s">
         <v>440</v>
       </c>
       <c r="G59" t="s">
@@ -4298,8 +4992,20 @@
       <c r="N59">
         <v>21243.3</v>
       </c>
-    </row>
-    <row r="60" spans="1:14">
+      <c r="O59">
+        <v>240</v>
+      </c>
+      <c r="P59">
+        <v>33</v>
+      </c>
+      <c r="Q59">
+        <v>180</v>
+      </c>
+      <c r="R59">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18">
       <c r="A60">
         <v>59</v>
       </c>
@@ -4315,7 +5021,7 @@
       <c r="E60" t="s">
         <v>13</v>
       </c>
-      <c r="F60" s="3" t="s">
+      <c r="F60" s="2" t="s">
         <v>440</v>
       </c>
       <c r="G60" t="s">
@@ -4342,8 +5048,20 @@
       <c r="N60">
         <v>3734</v>
       </c>
-    </row>
-    <row r="61" spans="1:14">
+      <c r="O60">
+        <v>480</v>
+      </c>
+      <c r="P60">
+        <v>36</v>
+      </c>
+      <c r="Q60">
+        <v>290</v>
+      </c>
+      <c r="R60">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18">
       <c r="A61">
         <v>60</v>
       </c>
@@ -4359,7 +5077,7 @@
       <c r="E61" t="s">
         <v>13</v>
       </c>
-      <c r="F61" s="3">
+      <c r="F61" s="2">
         <v>2020</v>
       </c>
       <c r="G61" t="s">
@@ -4386,8 +5104,20 @@
       <c r="N61">
         <v>3019.89</v>
       </c>
-    </row>
-    <row r="62" spans="1:14">
+      <c r="O61">
+        <v>480</v>
+      </c>
+      <c r="P61">
+        <v>36</v>
+      </c>
+      <c r="Q61">
+        <v>270</v>
+      </c>
+      <c r="R61">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18">
       <c r="A62">
         <v>61</v>
       </c>
@@ -4400,7 +5130,7 @@
       <c r="D62" t="s">
         <v>5</v>
       </c>
-      <c r="F62" s="3">
+      <c r="F62" s="2">
         <v>2021</v>
       </c>
       <c r="G62" t="s">
@@ -4427,8 +5157,20 @@
       <c r="N62">
         <v>4208</v>
       </c>
-    </row>
-    <row r="63" spans="1:14">
+      <c r="O62">
+        <v>420</v>
+      </c>
+      <c r="P62">
+        <v>36</v>
+      </c>
+      <c r="Q62">
+        <v>330</v>
+      </c>
+      <c r="R62">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18">
       <c r="A63">
         <v>62</v>
       </c>
@@ -4444,7 +5186,7 @@
       <c r="E63" t="s">
         <v>18</v>
       </c>
-      <c r="F63" s="3">
+      <c r="F63" s="2">
         <v>2023</v>
       </c>
       <c r="G63" t="s">
@@ -4471,8 +5213,20 @@
       <c r="N63">
         <v>59000</v>
       </c>
-    </row>
-    <row r="64" spans="1:14">
+      <c r="O63">
+        <v>450</v>
+      </c>
+      <c r="P63">
+        <v>38</v>
+      </c>
+      <c r="Q63">
+        <v>330</v>
+      </c>
+      <c r="R63">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18">
       <c r="A64">
         <v>63</v>
       </c>
@@ -4488,7 +5242,7 @@
       <c r="E64" t="s">
         <v>13</v>
       </c>
-      <c r="F64" s="3" t="s">
+      <c r="F64" s="2" t="s">
         <v>436</v>
       </c>
       <c r="G64" t="s">
@@ -4515,8 +5269,20 @@
       <c r="N64">
         <v>4800</v>
       </c>
-    </row>
-    <row r="65" spans="1:14">
+      <c r="O64">
+        <v>510</v>
+      </c>
+      <c r="P64">
+        <v>32</v>
+      </c>
+      <c r="Q64">
+        <v>350</v>
+      </c>
+      <c r="R64">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="65" spans="1:18">
       <c r="A65">
         <v>64</v>
       </c>
@@ -4529,7 +5295,7 @@
       <c r="D65" t="s">
         <v>12</v>
       </c>
-      <c r="F65" s="3" t="s">
+      <c r="F65" s="2" t="s">
         <v>424</v>
       </c>
       <c r="G65" t="s">
@@ -4556,8 +5322,20 @@
       <c r="N65">
         <v>10500</v>
       </c>
-    </row>
-    <row r="66" spans="1:14">
+      <c r="O65">
+        <v>650</v>
+      </c>
+      <c r="P65">
+        <v>34</v>
+      </c>
+      <c r="Q65">
+        <v>550</v>
+      </c>
+      <c r="R65">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="66" spans="1:18">
       <c r="A66">
         <v>65</v>
       </c>
@@ -4570,7 +5348,7 @@
       <c r="D66" t="s">
         <v>5</v>
       </c>
-      <c r="F66" s="3" t="s">
+      <c r="F66" s="2" t="s">
         <v>425</v>
       </c>
       <c r="G66" t="s">
@@ -4597,8 +5375,20 @@
       <c r="N66">
         <v>7586</v>
       </c>
-    </row>
-    <row r="67" spans="1:14">
+      <c r="O66">
+        <v>300</v>
+      </c>
+      <c r="P66">
+        <v>32</v>
+      </c>
+      <c r="Q66">
+        <v>360</v>
+      </c>
+      <c r="R66">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="1:18">
       <c r="A67">
         <v>66</v>
       </c>
@@ -4611,7 +5401,7 @@
       <c r="D67" t="s">
         <v>5</v>
       </c>
-      <c r="F67" s="3" t="s">
+      <c r="F67" s="2" t="s">
         <v>425</v>
       </c>
       <c r="G67" t="s">
@@ -4638,8 +5428,20 @@
       <c r="N67">
         <v>4300</v>
       </c>
-    </row>
-    <row r="68" spans="1:14">
+      <c r="O67">
+        <v>400</v>
+      </c>
+      <c r="P67">
+        <v>29</v>
+      </c>
+      <c r="Q67">
+        <v>400</v>
+      </c>
+      <c r="R67">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="68" spans="1:18">
       <c r="A68">
         <v>67</v>
       </c>
@@ -4655,7 +5457,7 @@
       <c r="E68" t="s">
         <v>18</v>
       </c>
-      <c r="F68" s="3" t="s">
+      <c r="F68" s="2" t="s">
         <v>426</v>
       </c>
       <c r="G68" t="s">
@@ -4682,8 +5484,20 @@
       <c r="N68">
         <v>17418</v>
       </c>
-    </row>
-    <row r="69" spans="1:14">
+      <c r="O68">
+        <v>627</v>
+      </c>
+      <c r="P68">
+        <v>33</v>
+      </c>
+      <c r="Q68">
+        <v>500</v>
+      </c>
+      <c r="R68">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="69" spans="1:18">
       <c r="A69">
         <v>68</v>
       </c>
@@ -4699,7 +5513,7 @@
       <c r="E69" t="s">
         <v>13</v>
       </c>
-      <c r="F69" s="3" t="s">
+      <c r="F69" s="2" t="s">
         <v>426</v>
       </c>
       <c r="G69" t="s">
@@ -4726,8 +5540,20 @@
       <c r="N69">
         <v>3600</v>
       </c>
-    </row>
-    <row r="70" spans="1:14">
+      <c r="O69">
+        <v>550</v>
+      </c>
+      <c r="P69">
+        <v>34</v>
+      </c>
+      <c r="Q69">
+        <v>350</v>
+      </c>
+      <c r="R69">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="70" spans="1:18">
       <c r="A70">
         <v>69</v>
       </c>
@@ -4740,7 +5566,7 @@
       <c r="D70" t="s">
         <v>5</v>
       </c>
-      <c r="F70" s="3" t="s">
+      <c r="F70" s="2" t="s">
         <v>426</v>
       </c>
       <c r="G70" t="s">
@@ -4767,8 +5593,20 @@
       <c r="N70">
         <v>3749</v>
       </c>
-    </row>
-    <row r="71" spans="1:14">
+      <c r="O70">
+        <v>360</v>
+      </c>
+      <c r="P70">
+        <v>30</v>
+      </c>
+      <c r="Q70">
+        <v>320</v>
+      </c>
+      <c r="R70">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="1:18">
       <c r="A71">
         <v>70</v>
       </c>
@@ -4781,7 +5619,7 @@
       <c r="D71" t="s">
         <v>5</v>
       </c>
-      <c r="F71" s="3" t="s">
+      <c r="F71" s="2" t="s">
         <v>426</v>
       </c>
       <c r="G71" t="s">
@@ -4808,8 +5646,20 @@
       <c r="N71">
         <v>2500</v>
       </c>
-    </row>
-    <row r="72" spans="1:14">
+      <c r="O71">
+        <v>480</v>
+      </c>
+      <c r="P71">
+        <v>34</v>
+      </c>
+      <c r="Q71">
+        <v>330</v>
+      </c>
+      <c r="R71">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="72" spans="1:18">
       <c r="A72">
         <v>71</v>
       </c>
@@ -4822,7 +5672,7 @@
       <c r="D72" t="s">
         <v>5</v>
       </c>
-      <c r="F72" s="3" t="s">
+      <c r="F72" s="2" t="s">
         <v>426</v>
       </c>
       <c r="G72" t="s">
@@ -4849,8 +5699,20 @@
       <c r="N72">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="1:14">
+      <c r="O72">
+        <v>650</v>
+      </c>
+      <c r="P72">
+        <v>38</v>
+      </c>
+      <c r="Q72">
+        <v>560</v>
+      </c>
+      <c r="R72">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="1:18">
       <c r="A73">
         <v>72</v>
       </c>
@@ -4863,7 +5725,7 @@
       <c r="D73" t="s">
         <v>5</v>
       </c>
-      <c r="F73" s="3" t="s">
+      <c r="F73" s="2" t="s">
         <v>427</v>
       </c>
       <c r="G73" t="s">
@@ -4890,8 +5752,20 @@
       <c r="N73">
         <v>5000</v>
       </c>
-    </row>
-    <row r="74" spans="1:14">
+      <c r="O73">
+        <v>550</v>
+      </c>
+      <c r="P73">
+        <v>33</v>
+      </c>
+      <c r="Q73">
+        <v>450</v>
+      </c>
+      <c r="R73">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="74" spans="1:18">
       <c r="A74">
         <v>73</v>
       </c>
@@ -4907,7 +5781,7 @@
       <c r="E74" t="s">
         <v>13</v>
       </c>
-      <c r="F74" s="3" t="s">
+      <c r="F74" s="2" t="s">
         <v>428</v>
       </c>
       <c r="G74" t="s">
@@ -4934,8 +5808,20 @@
       <c r="N74">
         <v>8881</v>
       </c>
-    </row>
-    <row r="75" spans="1:14">
+      <c r="O74">
+        <v>600</v>
+      </c>
+      <c r="P74">
+        <v>36</v>
+      </c>
+      <c r="Q74">
+        <v>520</v>
+      </c>
+      <c r="R74">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="75" spans="1:18">
       <c r="A75">
         <v>74</v>
       </c>
@@ -4951,7 +5837,7 @@
       <c r="E75" t="s">
         <v>18</v>
       </c>
-      <c r="F75" s="3" t="s">
+      <c r="F75" s="2" t="s">
         <v>421</v>
       </c>
       <c r="G75" t="s">
@@ -4978,8 +5864,20 @@
       <c r="N75">
         <v>13000</v>
       </c>
-    </row>
-    <row r="76" spans="1:14">
+      <c r="O75">
+        <v>500</v>
+      </c>
+      <c r="P75">
+        <v>35</v>
+      </c>
+      <c r="Q75">
+        <v>420</v>
+      </c>
+      <c r="R75">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="76" spans="1:18">
       <c r="A76">
         <v>75</v>
       </c>
@@ -4992,7 +5890,7 @@
       <c r="D76" t="s">
         <v>5</v>
       </c>
-      <c r="F76" s="3" t="s">
+      <c r="F76" s="2" t="s">
         <v>431</v>
       </c>
       <c r="G76" t="s">
@@ -5019,8 +5917,20 @@
       <c r="N76">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="1:14">
+      <c r="O76">
+        <v>550</v>
+      </c>
+      <c r="P76">
+        <v>33</v>
+      </c>
+      <c r="Q76">
+        <v>450</v>
+      </c>
+      <c r="R76">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="77" spans="1:18">
       <c r="A77">
         <v>76</v>
       </c>
@@ -5036,7 +5946,7 @@
       <c r="E77" t="s">
         <v>13</v>
       </c>
-      <c r="F77" s="3" t="s">
+      <c r="F77" s="2" t="s">
         <v>441</v>
       </c>
       <c r="G77" t="s">
@@ -5063,8 +5973,20 @@
       <c r="N77">
         <v>3157</v>
       </c>
-    </row>
-    <row r="78" spans="1:14">
+      <c r="O77">
+        <v>650</v>
+      </c>
+      <c r="P77">
+        <v>34</v>
+      </c>
+      <c r="Q77">
+        <v>420</v>
+      </c>
+      <c r="R77">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="78" spans="1:18">
       <c r="A78">
         <v>77</v>
       </c>
@@ -5080,7 +6002,7 @@
       <c r="E78" t="s">
         <v>13</v>
       </c>
-      <c r="F78" s="3" t="s">
+      <c r="F78" s="2" t="s">
         <v>439</v>
       </c>
       <c r="G78" t="s">
@@ -5107,8 +6029,20 @@
       <c r="N78">
         <v>9537</v>
       </c>
-    </row>
-    <row r="79" spans="1:14">
+      <c r="O78">
+        <v>500</v>
+      </c>
+      <c r="P78">
+        <v>30</v>
+      </c>
+      <c r="Q78">
+        <v>450</v>
+      </c>
+      <c r="R78">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="79" spans="1:18">
       <c r="A79">
         <v>78</v>
       </c>
@@ -5124,7 +6058,7 @@
       <c r="E79" t="s">
         <v>13</v>
       </c>
-      <c r="F79" s="3" t="s">
+      <c r="F79" s="2" t="s">
         <v>433</v>
       </c>
       <c r="G79" t="s">
@@ -5151,8 +6085,20 @@
       <c r="N79">
         <v>3400</v>
       </c>
-    </row>
-    <row r="80" spans="1:14">
+      <c r="O79">
+        <v>750</v>
+      </c>
+      <c r="P79">
+        <v>30</v>
+      </c>
+      <c r="Q79">
+        <v>590</v>
+      </c>
+      <c r="R79">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="80" spans="1:18">
       <c r="A80">
         <v>79</v>
       </c>
@@ -5165,7 +6111,7 @@
       <c r="D80" t="s">
         <v>5</v>
       </c>
-      <c r="F80" s="3" t="s">
+      <c r="F80" s="2" t="s">
         <v>426</v>
       </c>
       <c r="G80" t="s">
@@ -5192,8 +6138,20 @@
       <c r="N80">
         <v>8574</v>
       </c>
-    </row>
-    <row r="81" spans="1:14">
+      <c r="O80">
+        <v>330</v>
+      </c>
+      <c r="P80">
+        <v>45</v>
+      </c>
+      <c r="Q80">
+        <v>230</v>
+      </c>
+      <c r="R80">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="1:18">
       <c r="A81">
         <v>80</v>
       </c>
@@ -5206,7 +6164,7 @@
       <c r="D81" t="s">
         <v>170</v>
       </c>
-      <c r="F81" s="3">
+      <c r="F81" s="2">
         <v>2011</v>
       </c>
       <c r="G81" t="s">
@@ -5233,8 +6191,20 @@
       <c r="N81">
         <v>7150</v>
       </c>
-    </row>
-    <row r="82" spans="1:14">
+      <c r="O81">
+        <v>330</v>
+      </c>
+      <c r="P81">
+        <v>30</v>
+      </c>
+      <c r="Q81">
+        <v>220</v>
+      </c>
+      <c r="R81">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="1:18">
       <c r="A82">
         <v>81</v>
       </c>
@@ -5250,7 +6220,7 @@
       <c r="E82" t="s">
         <v>13</v>
       </c>
-      <c r="F82" s="3" t="s">
+      <c r="F82" s="2" t="s">
         <v>420</v>
       </c>
       <c r="G82" t="s">
@@ -5277,8 +6247,20 @@
       <c r="N82">
         <v>19235</v>
       </c>
-    </row>
-    <row r="83" spans="1:14">
+      <c r="O82">
+        <v>370</v>
+      </c>
+      <c r="P82">
+        <v>32.86</v>
+      </c>
+      <c r="Q82">
+        <v>245</v>
+      </c>
+      <c r="R82">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="83" spans="1:18">
       <c r="A83">
         <v>82</v>
       </c>
@@ -5291,7 +6273,7 @@
       <c r="D83" t="s">
         <v>5</v>
       </c>
-      <c r="F83" s="3" t="s">
+      <c r="F83" s="2" t="s">
         <v>436</v>
       </c>
       <c r="G83" t="s">
@@ -5318,8 +6300,20 @@
       <c r="N83">
         <v>7500</v>
       </c>
-    </row>
-    <row r="84" spans="1:14">
+      <c r="O83">
+        <v>330</v>
+      </c>
+      <c r="P83">
+        <v>32</v>
+      </c>
+      <c r="Q83">
+        <v>225</v>
+      </c>
+      <c r="R83">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="1:18">
       <c r="A84">
         <v>83</v>
       </c>
@@ -5335,7 +6329,7 @@
       <c r="E84" t="s">
         <v>18</v>
       </c>
-      <c r="F84" s="3" t="s">
+      <c r="F84" s="2" t="s">
         <v>424</v>
       </c>
       <c r="G84" t="s">
@@ -5362,8 +6356,20 @@
       <c r="N84">
         <v>10000</v>
       </c>
-    </row>
-    <row r="85" spans="1:14">
+      <c r="O84">
+        <v>400</v>
+      </c>
+      <c r="P84">
+        <v>33</v>
+      </c>
+      <c r="Q84">
+        <v>250</v>
+      </c>
+      <c r="R84">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="85" spans="1:18">
       <c r="A85">
         <v>84</v>
       </c>
@@ -5376,7 +6382,7 @@
       <c r="D85" t="s">
         <v>5</v>
       </c>
-      <c r="F85" s="3" t="s">
+      <c r="F85" s="2" t="s">
         <v>427</v>
       </c>
       <c r="G85" t="s">
@@ -5403,8 +6409,20 @@
       <c r="N85">
         <v>22971</v>
       </c>
-    </row>
-    <row r="86" spans="1:14">
+      <c r="O85">
+        <v>420</v>
+      </c>
+      <c r="P85">
+        <v>33</v>
+      </c>
+      <c r="Q85">
+        <v>220</v>
+      </c>
+      <c r="R85">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="86" spans="1:18">
       <c r="A86">
         <v>85</v>
       </c>
@@ -5417,7 +6435,7 @@
       <c r="D86" t="s">
         <v>5</v>
       </c>
-      <c r="F86" s="3" t="s">
+      <c r="F86" s="2" t="s">
         <v>421</v>
       </c>
       <c r="G86" t="s">
@@ -5444,8 +6462,20 @@
       <c r="N86">
         <v>3800</v>
       </c>
-    </row>
-    <row r="87" spans="1:14">
+      <c r="O86">
+        <v>480</v>
+      </c>
+      <c r="P86">
+        <v>32</v>
+      </c>
+      <c r="Q86">
+        <v>250</v>
+      </c>
+      <c r="R86">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="87" spans="1:18">
       <c r="A87">
         <v>86</v>
       </c>
@@ -5461,7 +6491,7 @@
       <c r="E87" t="s">
         <v>18</v>
       </c>
-      <c r="F87" s="3" t="s">
+      <c r="F87" s="2" t="s">
         <v>421</v>
       </c>
       <c r="G87" t="s">
@@ -5488,8 +6518,20 @@
       <c r="N87">
         <v>8139</v>
       </c>
-    </row>
-    <row r="88" spans="1:14">
+      <c r="O87">
+        <v>500</v>
+      </c>
+      <c r="P87">
+        <v>38</v>
+      </c>
+      <c r="Q87">
+        <v>270</v>
+      </c>
+      <c r="R87">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="88" spans="1:18">
       <c r="A88">
         <v>87</v>
       </c>
@@ -5502,7 +6544,7 @@
       <c r="D88" t="s">
         <v>5</v>
       </c>
-      <c r="F88" s="3" t="s">
+      <c r="F88" s="2" t="s">
         <v>430</v>
       </c>
       <c r="G88" t="s">
@@ -5529,8 +6571,20 @@
       <c r="N88">
         <v>4700</v>
       </c>
-    </row>
-    <row r="89" spans="1:14">
+      <c r="O88">
+        <v>480</v>
+      </c>
+      <c r="P88">
+        <v>32</v>
+      </c>
+      <c r="Q88">
+        <v>270</v>
+      </c>
+      <c r="R88">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="89" spans="1:18">
       <c r="A89">
         <v>88</v>
       </c>
@@ -5546,7 +6600,7 @@
       <c r="E89" t="s">
         <v>18</v>
       </c>
-      <c r="F89" s="3" t="s">
+      <c r="F89" s="2" t="s">
         <v>442</v>
       </c>
       <c r="G89" t="s">
@@ -5573,8 +6627,20 @@
       <c r="N89">
         <v>6300</v>
       </c>
-    </row>
-    <row r="90" spans="1:14">
+      <c r="O89">
+        <v>340</v>
+      </c>
+      <c r="P89">
+        <v>32</v>
+      </c>
+      <c r="Q89">
+        <v>230</v>
+      </c>
+      <c r="R89">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="1:18">
       <c r="A90">
         <v>89</v>
       </c>
@@ -5587,7 +6653,7 @@
       <c r="D90" t="s">
         <v>5</v>
       </c>
-      <c r="F90" s="3" t="s">
+      <c r="F90" s="2" t="s">
         <v>431</v>
       </c>
       <c r="G90" t="s">
@@ -5614,8 +6680,20 @@
       <c r="N90">
         <v>36930</v>
       </c>
-    </row>
-    <row r="91" spans="1:14">
+      <c r="O90">
+        <v>300</v>
+      </c>
+      <c r="P90">
+        <v>33</v>
+      </c>
+      <c r="Q90">
+        <v>260</v>
+      </c>
+      <c r="R90">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:18">
       <c r="A91">
         <v>90</v>
       </c>
@@ -5628,7 +6706,7 @@
       <c r="D91" t="s">
         <v>5</v>
       </c>
-      <c r="F91" s="3" t="s">
+      <c r="F91" s="2" t="s">
         <v>432</v>
       </c>
       <c r="G91" t="s">
@@ -5655,8 +6733,20 @@
       <c r="N91">
         <v>11123.6</v>
       </c>
-    </row>
-    <row r="92" spans="1:14">
+      <c r="O91">
+        <v>330</v>
+      </c>
+      <c r="P91">
+        <v>30</v>
+      </c>
+      <c r="Q91">
+        <v>270</v>
+      </c>
+      <c r="R91">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="1:18">
       <c r="A92">
         <v>91</v>
       </c>
@@ -5669,7 +6759,7 @@
       <c r="D92" t="s">
         <v>5</v>
       </c>
-      <c r="F92" s="3" t="s">
+      <c r="F92" s="2" t="s">
         <v>441</v>
       </c>
       <c r="G92" t="s">
@@ -5696,8 +6786,20 @@
       <c r="N92">
         <v>1898</v>
       </c>
-    </row>
-    <row r="93" spans="1:14">
+      <c r="O92">
+        <v>360</v>
+      </c>
+      <c r="P92">
+        <v>26</v>
+      </c>
+      <c r="Q92">
+        <v>250</v>
+      </c>
+      <c r="R92">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="93" spans="1:18">
       <c r="A93">
         <v>92</v>
       </c>
@@ -5713,7 +6815,7 @@
       <c r="E93" t="s">
         <v>18</v>
       </c>
-      <c r="F93" s="3" t="s">
+      <c r="F93" s="2" t="s">
         <v>439</v>
       </c>
       <c r="G93" t="s">
@@ -5740,8 +6842,20 @@
       <c r="N93">
         <v>20000</v>
       </c>
-    </row>
-    <row r="94" spans="1:14">
+      <c r="O93">
+        <v>290</v>
+      </c>
+      <c r="P93">
+        <v>30</v>
+      </c>
+      <c r="Q93">
+        <v>200</v>
+      </c>
+      <c r="R93">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="94" spans="1:18">
       <c r="A94">
         <v>93</v>
       </c>
@@ -5757,7 +6871,7 @@
       <c r="E94" t="s">
         <v>13</v>
       </c>
-      <c r="F94" s="3" t="s">
+      <c r="F94" s="2" t="s">
         <v>439</v>
       </c>
       <c r="G94" t="s">
@@ -5784,8 +6898,20 @@
       <c r="N94">
         <v>34000</v>
       </c>
-    </row>
-    <row r="95" spans="1:14">
+      <c r="O94">
+        <v>500</v>
+      </c>
+      <c r="P94">
+        <v>36</v>
+      </c>
+      <c r="Q94">
+        <v>310</v>
+      </c>
+      <c r="R94">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="1:18">
       <c r="A95">
         <v>94</v>
       </c>
@@ -5798,7 +6924,7 @@
       <c r="D95" t="s">
         <v>5</v>
       </c>
-      <c r="F95" s="3" t="s">
+      <c r="F95" s="2" t="s">
         <v>441</v>
       </c>
       <c r="G95" t="s">
@@ -5825,8 +6951,20 @@
       <c r="N95">
         <v>11981</v>
       </c>
-    </row>
-    <row r="96" spans="1:14">
+      <c r="O95">
+        <v>370</v>
+      </c>
+      <c r="P95">
+        <v>37.1</v>
+      </c>
+      <c r="Q95">
+        <v>240</v>
+      </c>
+      <c r="R95">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="96" spans="1:18">
       <c r="A96">
         <v>95</v>
       </c>
@@ -5842,7 +6980,7 @@
       <c r="E96" t="s">
         <v>13</v>
       </c>
-      <c r="F96" s="3" t="s">
+      <c r="F96" s="2" t="s">
         <v>422</v>
       </c>
       <c r="G96" t="s">
@@ -5869,8 +7007,20 @@
       <c r="N96">
         <v>12000</v>
       </c>
-    </row>
-    <row r="97" spans="1:14">
+      <c r="O96">
+        <v>435</v>
+      </c>
+      <c r="P96">
+        <v>31</v>
+      </c>
+      <c r="Q96">
+        <v>260</v>
+      </c>
+      <c r="R96">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="97" spans="1:18">
       <c r="A97">
         <v>96</v>
       </c>
@@ -5883,7 +7033,7 @@
       <c r="D97" t="s">
         <v>5</v>
       </c>
-      <c r="F97" s="3" t="s">
+      <c r="F97" s="2" t="s">
         <v>433</v>
       </c>
       <c r="G97" t="s">
@@ -5910,8 +7060,20 @@
       <c r="N97">
         <v>5000</v>
       </c>
-    </row>
-    <row r="98" spans="1:14">
+      <c r="O97">
+        <v>340</v>
+      </c>
+      <c r="P97">
+        <v>36</v>
+      </c>
+      <c r="Q97">
+        <v>200</v>
+      </c>
+      <c r="R97">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="98" spans="1:18">
       <c r="A98">
         <v>97</v>
       </c>
@@ -5924,7 +7086,7 @@
       <c r="D98" t="s">
         <v>5</v>
       </c>
-      <c r="F98" s="3">
+      <c r="F98" s="2">
         <v>2020</v>
       </c>
       <c r="G98" t="s">
@@ -5951,8 +7113,20 @@
       <c r="N98">
         <v>40000</v>
       </c>
-    </row>
-    <row r="99" spans="1:14">
+      <c r="O98">
+        <v>480</v>
+      </c>
+      <c r="P98">
+        <v>38</v>
+      </c>
+      <c r="Q98">
+        <v>200</v>
+      </c>
+      <c r="R98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:18">
       <c r="A99">
         <v>98</v>
       </c>
@@ -5968,7 +7142,7 @@
       <c r="E99" t="s">
         <v>13</v>
       </c>
-      <c r="F99" s="3">
+      <c r="F99" s="2">
         <v>2022</v>
       </c>
       <c r="G99" t="s">
@@ -5995,8 +7169,20 @@
       <c r="N99">
         <v>31248</v>
       </c>
-    </row>
-    <row r="100" spans="1:14">
+      <c r="O99">
+        <v>500</v>
+      </c>
+      <c r="P99">
+        <v>36</v>
+      </c>
+      <c r="Q99">
+        <v>280</v>
+      </c>
+      <c r="R99">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="100" spans="1:18">
       <c r="A100">
         <v>99</v>
       </c>
@@ -6012,7 +7198,7 @@
       <c r="E100" t="s">
         <v>18</v>
       </c>
-      <c r="F100" s="3" t="s">
+      <c r="F100" s="2" t="s">
         <v>438</v>
       </c>
       <c r="G100" t="s">
@@ -6039,8 +7225,20 @@
       <c r="N100">
         <v>11955</v>
       </c>
-    </row>
-    <row r="101" spans="1:14">
+      <c r="O100">
+        <v>550</v>
+      </c>
+      <c r="P100">
+        <v>29</v>
+      </c>
+      <c r="Q100">
+        <v>390</v>
+      </c>
+      <c r="R100">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="1:18">
       <c r="A101">
         <v>100</v>
       </c>
@@ -6056,7 +7254,7 @@
       <c r="E101" t="s">
         <v>18</v>
       </c>
-      <c r="F101" s="3" t="s">
+      <c r="F101" s="2" t="s">
         <v>443</v>
       </c>
       <c r="G101" t="s">
@@ -6083,8 +7281,20 @@
       <c r="N101">
         <v>11718</v>
       </c>
-    </row>
-    <row r="102" spans="1:14">
+      <c r="O101">
+        <v>550</v>
+      </c>
+      <c r="P101">
+        <v>29</v>
+      </c>
+      <c r="Q101">
+        <v>390</v>
+      </c>
+      <c r="R101">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="1:18">
       <c r="A102">
         <v>101</v>
       </c>
@@ -6100,7 +7310,7 @@
       <c r="E102" t="s">
         <v>18</v>
       </c>
-      <c r="F102" s="3" t="s">
+      <c r="F102" s="2" t="s">
         <v>443</v>
       </c>
       <c r="G102" t="s">
@@ -6127,8 +7337,20 @@
       <c r="N102">
         <v>14206</v>
       </c>
-    </row>
-    <row r="103" spans="1:14">
+      <c r="O102">
+        <v>480</v>
+      </c>
+      <c r="P102">
+        <v>35</v>
+      </c>
+      <c r="Q102">
+        <v>280</v>
+      </c>
+      <c r="R102">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="103" spans="1:18">
       <c r="A103">
         <v>102</v>
       </c>
@@ -6141,7 +7363,7 @@
       <c r="D103" t="s">
         <v>5</v>
       </c>
-      <c r="F103" s="3" t="s">
+      <c r="F103" s="2" t="s">
         <v>424</v>
       </c>
       <c r="G103" t="s">
@@ -6168,8 +7390,20 @@
       <c r="N103">
         <v>7003</v>
       </c>
-    </row>
-    <row r="104" spans="1:14">
+      <c r="O103">
+        <v>360</v>
+      </c>
+      <c r="P103">
+        <v>35</v>
+      </c>
+      <c r="Q103">
+        <v>210</v>
+      </c>
+      <c r="R103">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="104" spans="1:18">
       <c r="A104">
         <v>103</v>
       </c>
@@ -6182,7 +7416,7 @@
       <c r="D104" t="s">
         <v>5</v>
       </c>
-      <c r="F104" s="3" t="s">
+      <c r="F104" s="2" t="s">
         <v>424</v>
       </c>
       <c r="G104" t="s">
@@ -6209,8 +7443,20 @@
       <c r="N104">
         <v>5862</v>
       </c>
-    </row>
-    <row r="105" spans="1:14">
+      <c r="O104">
+        <v>360</v>
+      </c>
+      <c r="P104">
+        <v>45</v>
+      </c>
+      <c r="Q104">
+        <v>225</v>
+      </c>
+      <c r="R104">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="105" spans="1:18">
       <c r="A105">
         <v>104</v>
       </c>
@@ -6223,7 +7469,7 @@
       <c r="D105" t="s">
         <v>5</v>
       </c>
-      <c r="F105" s="3" t="s">
+      <c r="F105" s="2" t="s">
         <v>428</v>
       </c>
       <c r="G105" t="s">
@@ -6250,8 +7496,20 @@
       <c r="N105">
         <v>0</v>
       </c>
-    </row>
-    <row r="106" spans="1:14">
+      <c r="O105">
+        <v>420</v>
+      </c>
+      <c r="P105">
+        <v>35</v>
+      </c>
+      <c r="Q105">
+        <v>310</v>
+      </c>
+      <c r="R105">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="106" spans="1:18">
       <c r="A106">
         <v>105</v>
       </c>
@@ -6264,7 +7522,7 @@
       <c r="D106" t="s">
         <v>5</v>
       </c>
-      <c r="F106" s="3" t="s">
+      <c r="F106" s="2" t="s">
         <v>432</v>
       </c>
       <c r="G106" t="s">
@@ -6291,8 +7549,20 @@
       <c r="N106">
         <v>120.9</v>
       </c>
-    </row>
-    <row r="107" spans="1:14">
+      <c r="O106">
+        <v>235</v>
+      </c>
+      <c r="P106">
+        <v>35</v>
+      </c>
+      <c r="Q106">
+        <v>200</v>
+      </c>
+      <c r="R106">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="107" spans="1:18">
       <c r="A107">
         <v>106</v>
       </c>
@@ -6305,7 +7575,7 @@
       <c r="D107" t="s">
         <v>170</v>
       </c>
-      <c r="F107" s="3">
+      <c r="F107" s="2">
         <v>2014</v>
       </c>
       <c r="G107" t="s">
@@ -6332,8 +7602,20 @@
       <c r="N107">
         <v>23200</v>
       </c>
-    </row>
-    <row r="108" spans="1:14">
+      <c r="O107">
+        <v>365</v>
+      </c>
+      <c r="P107">
+        <v>30</v>
+      </c>
+      <c r="Q107">
+        <v>220</v>
+      </c>
+      <c r="R107">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="108" spans="1:18">
       <c r="A108">
         <v>107</v>
       </c>
@@ -6349,7 +7631,7 @@
       <c r="E108" t="s">
         <v>18</v>
       </c>
-      <c r="F108" s="3" t="s">
+      <c r="F108" s="2" t="s">
         <v>441</v>
       </c>
       <c r="G108" t="s">
@@ -6376,8 +7658,20 @@
       <c r="N108">
         <v>1500</v>
       </c>
-    </row>
-    <row r="109" spans="1:14">
+      <c r="O108">
+        <v>600</v>
+      </c>
+      <c r="P108">
+        <v>33</v>
+      </c>
+      <c r="Q108">
+        <v>450</v>
+      </c>
+      <c r="R108">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="109" spans="1:18">
       <c r="A109">
         <v>108</v>
       </c>
@@ -6390,7 +7684,7 @@
       <c r="D109" t="s">
         <v>5</v>
       </c>
-      <c r="F109" s="3" t="s">
+      <c r="F109" s="2" t="s">
         <v>441</v>
       </c>
       <c r="G109" t="s">
@@ -6417,8 +7711,20 @@
       <c r="N109">
         <v>0</v>
       </c>
-    </row>
-    <row r="110" spans="1:14">
+      <c r="O109">
+        <v>360</v>
+      </c>
+      <c r="P109">
+        <v>30</v>
+      </c>
+      <c r="Q109">
+        <v>330</v>
+      </c>
+      <c r="R109">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="110" spans="1:18">
       <c r="A110">
         <v>109</v>
       </c>
@@ -6431,7 +7737,7 @@
       <c r="D110" t="s">
         <v>5</v>
       </c>
-      <c r="F110" s="3" t="s">
+      <c r="F110" s="2" t="s">
         <v>439</v>
       </c>
       <c r="G110" t="s">
@@ -6458,8 +7764,20 @@
       <c r="N110">
         <v>0</v>
       </c>
-    </row>
-    <row r="111" spans="1:14">
+      <c r="O110">
+        <v>390</v>
+      </c>
+      <c r="P110">
+        <v>25</v>
+      </c>
+      <c r="Q110">
+        <v>243</v>
+      </c>
+      <c r="R110">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="111" spans="1:18">
       <c r="A111">
         <v>110</v>
       </c>
@@ -6472,7 +7790,7 @@
       <c r="D111" t="s">
         <v>5</v>
       </c>
-      <c r="F111" s="3" t="s">
+      <c r="F111" s="2" t="s">
         <v>439</v>
       </c>
       <c r="G111" t="s">
@@ -6499,8 +7817,20 @@
       <c r="N111">
         <v>15830</v>
       </c>
-    </row>
-    <row r="112" spans="1:14">
+      <c r="O111">
+        <v>274</v>
+      </c>
+      <c r="P111">
+        <v>30</v>
+      </c>
+      <c r="Q111">
+        <v>210</v>
+      </c>
+      <c r="R111">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="112" spans="1:18">
       <c r="A112">
         <v>111</v>
       </c>
@@ -6513,7 +7843,7 @@
       <c r="D112" t="s">
         <v>5</v>
       </c>
-      <c r="F112" s="3" t="s">
+      <c r="F112" s="2" t="s">
         <v>422</v>
       </c>
       <c r="G112" t="s">
@@ -6540,8 +7870,20 @@
       <c r="N112">
         <v>19941.5</v>
       </c>
-    </row>
-    <row r="113" spans="1:14">
+      <c r="O112">
+        <v>268</v>
+      </c>
+      <c r="P112">
+        <v>30</v>
+      </c>
+      <c r="Q112">
+        <v>170</v>
+      </c>
+      <c r="R112">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="113" spans="1:18">
       <c r="A113">
         <v>112</v>
       </c>
@@ -6557,7 +7899,7 @@
       <c r="E113" t="s">
         <v>13</v>
       </c>
-      <c r="F113" s="3">
+      <c r="F113" s="2">
         <v>2021</v>
       </c>
       <c r="G113" t="s">
@@ -6584,8 +7926,20 @@
       <c r="N113">
         <v>1000</v>
       </c>
-    </row>
-    <row r="114" spans="1:14">
+      <c r="O113">
+        <v>550</v>
+      </c>
+      <c r="P113">
+        <v>36</v>
+      </c>
+      <c r="Q113">
+        <v>360</v>
+      </c>
+      <c r="R113">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="114" spans="1:18">
       <c r="A114">
         <v>113</v>
       </c>
@@ -6601,7 +7955,7 @@
       <c r="E114" t="s">
         <v>13</v>
       </c>
-      <c r="F114" s="3">
+      <c r="F114" s="2">
         <v>2023</v>
       </c>
       <c r="G114" t="s">
@@ -6628,8 +7982,20 @@
       <c r="N114">
         <v>427</v>
       </c>
-    </row>
-    <row r="115" spans="1:14">
+      <c r="O114">
+        <v>500</v>
+      </c>
+      <c r="P114">
+        <v>36</v>
+      </c>
+      <c r="Q114">
+        <v>330</v>
+      </c>
+      <c r="R114">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="115" spans="1:18">
       <c r="A115">
         <v>114</v>
       </c>
@@ -6645,7 +8011,7 @@
       <c r="E115" t="s">
         <v>13</v>
       </c>
-      <c r="F115" s="3">
+      <c r="F115" s="2">
         <v>2023</v>
       </c>
       <c r="G115" t="s">
@@ -6672,8 +8038,20 @@
       <c r="N115">
         <v>11500</v>
       </c>
-    </row>
-    <row r="116" spans="1:14">
+      <c r="O115">
+        <v>270</v>
+      </c>
+      <c r="P115">
+        <v>36</v>
+      </c>
+      <c r="Q115">
+        <v>245</v>
+      </c>
+      <c r="R115">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="116" spans="1:18">
       <c r="A116">
         <v>115</v>
       </c>
@@ -6686,7 +8064,7 @@
       <c r="D116" t="s">
         <v>5</v>
       </c>
-      <c r="F116" s="3">
+      <c r="F116" s="2">
         <v>2023</v>
       </c>
       <c r="G116" t="s">
@@ -6713,8 +8091,20 @@
       <c r="N116">
         <v>0</v>
       </c>
-    </row>
-    <row r="117" spans="1:14">
+      <c r="O116">
+        <v>340</v>
+      </c>
+      <c r="P116">
+        <v>36</v>
+      </c>
+      <c r="Q116">
+        <v>340</v>
+      </c>
+      <c r="R116">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="117" spans="1:18">
       <c r="A117">
         <v>116</v>
       </c>
@@ -6727,7 +8117,7 @@
       <c r="D117" t="s">
         <v>170</v>
       </c>
-      <c r="F117" s="3">
+      <c r="F117" s="2">
         <v>2009</v>
       </c>
       <c r="G117" t="s">
@@ -6754,8 +8144,20 @@
       <c r="N117">
         <v>21000</v>
       </c>
-    </row>
-    <row r="118" spans="1:14">
+      <c r="O117">
+        <v>300</v>
+      </c>
+      <c r="P117">
+        <v>30</v>
+      </c>
+      <c r="Q117">
+        <v>210</v>
+      </c>
+      <c r="R117">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="118" spans="1:18">
       <c r="A118">
         <v>117</v>
       </c>
@@ -6768,7 +8170,7 @@
       <c r="D118" t="s">
         <v>170</v>
       </c>
-      <c r="F118" s="3">
+      <c r="F118" s="2">
         <v>2016</v>
       </c>
       <c r="G118" t="s">
@@ -6795,8 +8197,20 @@
       <c r="N118">
         <v>31890</v>
       </c>
-    </row>
-    <row r="119" spans="1:14">
+      <c r="O118">
+        <v>360</v>
+      </c>
+      <c r="P118">
+        <v>30</v>
+      </c>
+      <c r="Q118">
+        <v>230</v>
+      </c>
+      <c r="R118">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="119" spans="1:18">
       <c r="A119">
         <v>118</v>
       </c>
@@ -6809,7 +8223,7 @@
       <c r="D119" t="s">
         <v>170</v>
       </c>
-      <c r="F119" s="3">
+      <c r="F119" s="2">
         <v>2021</v>
       </c>
       <c r="G119" t="s">
@@ -6836,8 +8250,20 @@
       <c r="N119">
         <v>1116</v>
       </c>
-    </row>
-    <row r="120" spans="1:14">
+      <c r="O119">
+        <v>360</v>
+      </c>
+      <c r="P119">
+        <v>30</v>
+      </c>
+      <c r="Q119">
+        <v>270</v>
+      </c>
+      <c r="R119">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="120" spans="1:18">
       <c r="A120">
         <v>119</v>
       </c>
@@ -6850,7 +8276,7 @@
       <c r="D120" t="s">
         <v>170</v>
       </c>
-      <c r="F120" s="3">
+      <c r="F120" s="2">
         <v>2004</v>
       </c>
       <c r="G120" t="s">
@@ -6877,8 +8303,20 @@
       <c r="N120">
         <v>0</v>
       </c>
-    </row>
-    <row r="121" spans="1:14">
+      <c r="O120">
+        <v>360</v>
+      </c>
+      <c r="P120">
+        <v>33</v>
+      </c>
+      <c r="Q120">
+        <v>270</v>
+      </c>
+      <c r="R120">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="121" spans="1:18">
       <c r="A121">
         <v>120</v>
       </c>
@@ -6894,7 +8332,7 @@
       <c r="E121" t="s">
         <v>13</v>
       </c>
-      <c r="F121" s="3">
+      <c r="F121" s="2">
         <v>2006</v>
       </c>
       <c r="G121" t="s">
@@ -6921,8 +8359,20 @@
       <c r="N121">
         <v>5600</v>
       </c>
-    </row>
-    <row r="122" spans="1:14">
+      <c r="O121">
+        <v>285</v>
+      </c>
+      <c r="P121">
+        <v>27</v>
+      </c>
+      <c r="Q121">
+        <v>200</v>
+      </c>
+      <c r="R121">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="122" spans="1:18">
       <c r="A122">
         <v>121</v>
       </c>
@@ -6935,7 +8385,7 @@
       <c r="D122" t="s">
         <v>170</v>
       </c>
-      <c r="F122" s="3">
+      <c r="F122" s="2">
         <v>2024</v>
       </c>
       <c r="G122" t="s">
@@ -6962,8 +8412,20 @@
       <c r="N122">
         <v>0</v>
       </c>
-    </row>
-    <row r="123" spans="1:14">
+      <c r="O122">
+        <v>500</v>
+      </c>
+      <c r="P122">
+        <v>36</v>
+      </c>
+      <c r="Q122">
+        <v>300</v>
+      </c>
+      <c r="R122">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="123" spans="1:18">
       <c r="A123">
         <v>122</v>
       </c>
@@ -6979,7 +8441,7 @@
       <c r="E123" t="s">
         <v>13</v>
       </c>
-      <c r="F123" s="3">
+      <c r="F123" s="2">
         <v>2024</v>
       </c>
       <c r="G123" t="s">
@@ -7006,8 +8468,20 @@
       <c r="N123">
         <v>36000</v>
       </c>
-    </row>
-    <row r="124" spans="1:14">
+      <c r="O123">
+        <v>190</v>
+      </c>
+      <c r="P123">
+        <v>38</v>
+      </c>
+      <c r="Q123">
+        <v>150</v>
+      </c>
+      <c r="R123">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="124" spans="1:18">
       <c r="A124">
         <v>123</v>
       </c>
@@ -7017,7 +8491,7 @@
       <c r="C124" t="s">
         <v>208</v>
       </c>
-      <c r="F124" s="3">
+      <c r="F124" s="2">
         <v>2025</v>
       </c>
       <c r="G124" t="s">
@@ -7045,7 +8519,7 @@
         <v>97326.47</v>
       </c>
     </row>
-    <row r="125" spans="1:14">
+    <row r="125" spans="1:18">
       <c r="A125">
         <v>124</v>
       </c>
@@ -7061,7 +8535,7 @@
       <c r="E125" t="s">
         <v>13</v>
       </c>
-      <c r="F125" s="3" t="s">
+      <c r="F125" s="2" t="s">
         <v>427</v>
       </c>
       <c r="G125" t="s">
@@ -7088,8 +8562,20 @@
       <c r="N125">
         <v>15956.21</v>
       </c>
-    </row>
-    <row r="126" spans="1:14">
+      <c r="O125">
+        <v>304.16666666666669</v>
+      </c>
+      <c r="P125">
+        <v>30</v>
+      </c>
+      <c r="Q125">
+        <v>210</v>
+      </c>
+      <c r="R125">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="126" spans="1:18">
       <c r="A126">
         <v>125</v>
       </c>
@@ -7105,7 +8591,7 @@
       <c r="E126" t="s">
         <v>18</v>
       </c>
-      <c r="F126" s="3" t="s">
+      <c r="F126" s="2" t="s">
         <v>430</v>
       </c>
       <c r="G126" t="s">
@@ -7132,8 +8618,20 @@
       <c r="N126">
         <v>6631</v>
       </c>
-    </row>
-    <row r="127" spans="1:14">
+      <c r="O126">
+        <v>240</v>
+      </c>
+      <c r="P126">
+        <v>48.76</v>
+      </c>
+      <c r="Q126">
+        <v>190</v>
+      </c>
+      <c r="R126">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="127" spans="1:18">
       <c r="A127">
         <v>126</v>
       </c>
@@ -7146,7 +8644,7 @@
       <c r="D127" t="s">
         <v>5</v>
       </c>
-      <c r="F127" s="3" t="s">
+      <c r="F127" s="2" t="s">
         <v>441</v>
       </c>
       <c r="G127" t="s">
@@ -7173,8 +8671,20 @@
       <c r="N127">
         <v>14329.850000000002</v>
       </c>
-    </row>
-    <row r="128" spans="1:14">
+      <c r="O127">
+        <v>212.91666666666666</v>
+      </c>
+      <c r="P127">
+        <v>33</v>
+      </c>
+      <c r="Q127">
+        <v>145</v>
+      </c>
+      <c r="R127">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="128" spans="1:18">
       <c r="A128">
         <v>127</v>
       </c>
@@ -7190,7 +8700,7 @@
       <c r="E128" t="s">
         <v>18</v>
       </c>
-      <c r="F128" s="3" t="s">
+      <c r="F128" s="2" t="s">
         <v>441</v>
       </c>
       <c r="G128" t="s">
@@ -7217,8 +8727,20 @@
       <c r="N128">
         <v>6594</v>
       </c>
-    </row>
-    <row r="129" spans="1:14">
+      <c r="O128">
+        <v>280</v>
+      </c>
+      <c r="P128">
+        <v>50</v>
+      </c>
+      <c r="Q128">
+        <v>190</v>
+      </c>
+      <c r="R128">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="129" spans="1:18">
       <c r="A129">
         <v>128</v>
       </c>
@@ -7234,7 +8756,7 @@
       <c r="E129" t="s">
         <v>13</v>
       </c>
-      <c r="F129" s="3" t="s">
+      <c r="F129" s="2" t="s">
         <v>441</v>
       </c>
       <c r="G129" t="s">
@@ -7261,8 +8783,20 @@
       <c r="N129">
         <v>10000</v>
       </c>
-    </row>
-    <row r="130" spans="1:14">
+      <c r="O129">
+        <v>228.125</v>
+      </c>
+      <c r="P129">
+        <v>33</v>
+      </c>
+      <c r="Q129">
+        <v>150</v>
+      </c>
+      <c r="R129">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="130" spans="1:18">
       <c r="A130">
         <v>129</v>
       </c>
@@ -7278,7 +8812,7 @@
       <c r="E130" t="s">
         <v>13</v>
       </c>
-      <c r="F130" s="3" t="s">
+      <c r="F130" s="2" t="s">
         <v>439</v>
       </c>
       <c r="G130" t="s">
@@ -7305,8 +8839,20 @@
       <c r="N130">
         <v>35707.82</v>
       </c>
-    </row>
-    <row r="131" spans="1:14">
+      <c r="O130">
+        <v>334.58333333333331</v>
+      </c>
+      <c r="P130">
+        <v>32</v>
+      </c>
+      <c r="Q130">
+        <v>225</v>
+      </c>
+      <c r="R130">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="131" spans="1:18">
       <c r="A131">
         <v>130</v>
       </c>
@@ -7322,7 +8868,7 @@
       <c r="E131" t="s">
         <v>13</v>
       </c>
-      <c r="F131" s="3" t="s">
+      <c r="F131" s="2" t="s">
         <v>439</v>
       </c>
       <c r="G131" t="s">
@@ -7349,8 +8895,20 @@
       <c r="N131">
         <v>4100</v>
       </c>
-    </row>
-    <row r="132" spans="1:14">
+      <c r="O131">
+        <v>365</v>
+      </c>
+      <c r="P131">
+        <v>35</v>
+      </c>
+      <c r="Q131">
+        <v>190</v>
+      </c>
+      <c r="R131">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="132" spans="1:18">
       <c r="A132">
         <v>131</v>
       </c>
@@ -7366,7 +8924,7 @@
       <c r="E132" t="s">
         <v>18</v>
       </c>
-      <c r="F132" s="3" t="s">
+      <c r="F132" s="2" t="s">
         <v>440</v>
       </c>
       <c r="G132" t="s">
@@ -7393,8 +8951,20 @@
       <c r="N132">
         <v>19710</v>
       </c>
-    </row>
-    <row r="133" spans="1:14">
+      <c r="O132">
+        <v>349.79166666666669</v>
+      </c>
+      <c r="P132">
+        <v>30</v>
+      </c>
+      <c r="Q132">
+        <v>195</v>
+      </c>
+      <c r="R132">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="133" spans="1:18">
       <c r="A133">
         <v>132</v>
       </c>
@@ -7407,7 +8977,7 @@
       <c r="D133" t="s">
         <v>5</v>
       </c>
-      <c r="F133" s="3" t="s">
+      <c r="F133" s="2" t="s">
         <v>440</v>
       </c>
       <c r="G133" t="s">
@@ -7434,8 +9004,20 @@
       <c r="N133">
         <v>11436.280000000002</v>
       </c>
-    </row>
-    <row r="134" spans="1:14">
+      <c r="O133">
+        <v>304.16666666666669</v>
+      </c>
+      <c r="P133">
+        <v>33</v>
+      </c>
+      <c r="Q133">
+        <v>190</v>
+      </c>
+      <c r="R133">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="134" spans="1:18">
       <c r="A134">
         <v>133</v>
       </c>
@@ -7448,7 +9030,7 @@
       <c r="D134" t="s">
         <v>5</v>
       </c>
-      <c r="F134" s="3" t="s">
+      <c r="F134" s="2" t="s">
         <v>440</v>
       </c>
       <c r="G134" t="s">
@@ -7475,8 +9057,20 @@
       <c r="N134">
         <v>5860.63</v>
       </c>
-    </row>
-    <row r="135" spans="1:14">
+      <c r="O134">
+        <v>273.75</v>
+      </c>
+      <c r="P134">
+        <v>30</v>
+      </c>
+      <c r="Q134">
+        <v>155</v>
+      </c>
+      <c r="R134">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="135" spans="1:18">
       <c r="A135">
         <v>134</v>
       </c>
@@ -7492,7 +9086,7 @@
       <c r="E135" t="s">
         <v>13</v>
       </c>
-      <c r="F135" s="3" t="s">
+      <c r="F135" s="2" t="s">
         <v>433</v>
       </c>
       <c r="G135" t="s">
@@ -7519,8 +9113,20 @@
       <c r="N135">
         <v>6669.369999999999</v>
       </c>
-    </row>
-    <row r="136" spans="1:14">
+      <c r="O135">
+        <v>330</v>
+      </c>
+      <c r="P135">
+        <v>30</v>
+      </c>
+      <c r="Q135">
+        <v>190</v>
+      </c>
+      <c r="R135">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="136" spans="1:18">
       <c r="A136">
         <v>135</v>
       </c>
@@ -7536,7 +9142,7 @@
       <c r="E136" t="s">
         <v>18</v>
       </c>
-      <c r="F136" s="3">
+      <c r="F136" s="2">
         <v>2018</v>
       </c>
       <c r="G136" t="s">
@@ -7563,8 +9169,20 @@
       <c r="N136">
         <v>32274.100000000002</v>
       </c>
-    </row>
-    <row r="137" spans="1:14">
+      <c r="O136">
+        <v>270</v>
+      </c>
+      <c r="P136">
+        <v>35</v>
+      </c>
+      <c r="Q136">
+        <v>210</v>
+      </c>
+      <c r="R136">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="137" spans="1:18">
       <c r="A137">
         <v>136</v>
       </c>
@@ -7577,7 +9195,7 @@
       <c r="D137" t="s">
         <v>170</v>
       </c>
-      <c r="F137" s="3">
+      <c r="F137" s="2">
         <v>2015</v>
       </c>
       <c r="G137" t="s">
@@ -7604,8 +9222,20 @@
       <c r="N137">
         <v>1901</v>
       </c>
-    </row>
-    <row r="138" spans="1:14">
+      <c r="O137">
+        <v>152.08333333333334</v>
+      </c>
+      <c r="P137">
+        <v>30</v>
+      </c>
+      <c r="Q137">
+        <v>140</v>
+      </c>
+      <c r="R137">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="138" spans="1:18">
       <c r="A138">
         <v>137</v>
       </c>
@@ -7618,7 +9248,7 @@
       <c r="D138" t="s">
         <v>5</v>
       </c>
-      <c r="F138" s="3" t="s">
+      <c r="F138" s="2" t="s">
         <v>429</v>
       </c>
       <c r="G138" t="s">
@@ -7645,8 +9275,20 @@
       <c r="N138">
         <v>6126</v>
       </c>
-    </row>
-    <row r="139" spans="1:14">
+      <c r="O138">
+        <v>420</v>
+      </c>
+      <c r="P138">
+        <v>30</v>
+      </c>
+      <c r="Q138">
+        <v>215</v>
+      </c>
+      <c r="R138">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="139" spans="1:18">
       <c r="A139">
         <v>138</v>
       </c>
@@ -7662,7 +9304,7 @@
       <c r="E139" t="s">
         <v>13</v>
       </c>
-      <c r="F139" s="3" t="s">
+      <c r="F139" s="2" t="s">
         <v>427</v>
       </c>
       <c r="G139" t="s">
@@ -7689,8 +9331,20 @@
       <c r="N139">
         <v>2182</v>
       </c>
-    </row>
-    <row r="140" spans="1:14">
+      <c r="O139">
+        <v>300</v>
+      </c>
+      <c r="P139">
+        <v>30</v>
+      </c>
+      <c r="Q139">
+        <v>220</v>
+      </c>
+      <c r="R139">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="140" spans="1:18">
       <c r="A140">
         <v>139</v>
       </c>
@@ -7703,7 +9357,7 @@
       <c r="D140" t="s">
         <v>5</v>
       </c>
-      <c r="F140" s="3" t="s">
+      <c r="F140" s="2" t="s">
         <v>421</v>
       </c>
       <c r="G140" t="s">
@@ -7730,8 +9384,20 @@
       <c r="N140">
         <v>4616</v>
       </c>
-    </row>
-    <row r="141" spans="1:14">
+      <c r="O140">
+        <v>280</v>
+      </c>
+      <c r="P140">
+        <v>30</v>
+      </c>
+      <c r="Q140">
+        <v>215</v>
+      </c>
+      <c r="R140">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="141" spans="1:18">
       <c r="A141">
         <v>140</v>
       </c>
@@ -7744,7 +9410,7 @@
       <c r="D141" t="s">
         <v>5</v>
       </c>
-      <c r="F141" s="3" t="s">
+      <c r="F141" s="2" t="s">
         <v>421</v>
       </c>
       <c r="G141" t="s">
@@ -7771,8 +9437,20 @@
       <c r="N141">
         <v>0</v>
       </c>
-    </row>
-    <row r="142" spans="1:14">
+      <c r="O141">
+        <v>300</v>
+      </c>
+      <c r="P141">
+        <v>30</v>
+      </c>
+      <c r="Q141">
+        <v>270</v>
+      </c>
+      <c r="R141">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:18">
       <c r="A142">
         <v>141</v>
       </c>
@@ -7785,7 +9463,7 @@
       <c r="D142" t="s">
         <v>5</v>
       </c>
-      <c r="F142" s="3" t="s">
+      <c r="F142" s="2" t="s">
         <v>427</v>
       </c>
       <c r="G142" t="s">
@@ -7812,8 +9490,20 @@
       <c r="N142">
         <v>18000</v>
       </c>
-    </row>
-    <row r="143" spans="1:14">
+      <c r="O142">
+        <v>270</v>
+      </c>
+      <c r="P142">
+        <v>30</v>
+      </c>
+      <c r="Q142">
+        <v>200</v>
+      </c>
+      <c r="R142">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="143" spans="1:18">
       <c r="A143">
         <v>142</v>
       </c>
@@ -7826,7 +9516,7 @@
       <c r="D143" t="s">
         <v>5</v>
       </c>
-      <c r="F143" s="3" t="s">
+      <c r="F143" s="2" t="s">
         <v>428</v>
       </c>
       <c r="G143" t="s">
@@ -7853,8 +9543,20 @@
       <c r="N143">
         <v>23660</v>
       </c>
-    </row>
-    <row r="144" spans="1:14">
+      <c r="O143">
+        <v>250</v>
+      </c>
+      <c r="P143">
+        <v>27</v>
+      </c>
+      <c r="Q143">
+        <v>180</v>
+      </c>
+      <c r="R143">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="144" spans="1:18">
       <c r="A144">
         <v>143</v>
       </c>
@@ -7867,7 +9569,7 @@
       <c r="D144" t="s">
         <v>5</v>
       </c>
-      <c r="F144" s="3" t="s">
+      <c r="F144" s="2" t="s">
         <v>428</v>
       </c>
       <c r="G144" t="s">
@@ -7894,8 +9596,20 @@
       <c r="N144">
         <v>7276</v>
       </c>
-    </row>
-    <row r="145" spans="1:14">
+      <c r="O144">
+        <v>240</v>
+      </c>
+      <c r="P144">
+        <v>27</v>
+      </c>
+      <c r="Q144">
+        <v>170</v>
+      </c>
+      <c r="R144">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="145" spans="1:18">
       <c r="A145">
         <v>144</v>
       </c>
@@ -7911,7 +9625,7 @@
       <c r="E145" t="s">
         <v>13</v>
       </c>
-      <c r="F145" s="3" t="s">
+      <c r="F145" s="2" t="s">
         <v>421</v>
       </c>
       <c r="G145" t="s">
@@ -7938,8 +9652,20 @@
       <c r="N145">
         <v>78750</v>
       </c>
-    </row>
-    <row r="146" spans="1:14">
+      <c r="O145">
+        <v>450</v>
+      </c>
+      <c r="P145">
+        <v>38</v>
+      </c>
+      <c r="Q145">
+        <v>200</v>
+      </c>
+      <c r="R145">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="146" spans="1:18">
       <c r="A146">
         <v>145</v>
       </c>
@@ -7955,7 +9681,7 @@
       <c r="E146" t="s">
         <v>18</v>
       </c>
-      <c r="F146" s="3" t="s">
+      <c r="F146" s="2" t="s">
         <v>439</v>
       </c>
       <c r="G146" t="s">
@@ -7982,8 +9708,20 @@
       <c r="N146">
         <v>40000</v>
       </c>
-    </row>
-    <row r="147" spans="1:14">
+      <c r="O146">
+        <v>510</v>
+      </c>
+      <c r="P146">
+        <v>35</v>
+      </c>
+      <c r="Q146">
+        <v>230</v>
+      </c>
+      <c r="R146">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="147" spans="1:18">
       <c r="A147">
         <v>146</v>
       </c>
@@ -7996,7 +9734,7 @@
       <c r="D147" t="s">
         <v>5</v>
       </c>
-      <c r="F147" s="3" t="s">
+      <c r="F147" s="2" t="s">
         <v>439</v>
       </c>
       <c r="G147" t="s">
@@ -8023,8 +9761,20 @@
       <c r="N147">
         <v>1300</v>
       </c>
-    </row>
-    <row r="148" spans="1:14">
+      <c r="O147">
+        <v>420</v>
+      </c>
+      <c r="P147">
+        <v>34</v>
+      </c>
+      <c r="Q147">
+        <v>320</v>
+      </c>
+      <c r="R147">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="148" spans="1:18">
       <c r="A148">
         <v>147</v>
       </c>
@@ -8037,7 +9787,7 @@
       <c r="D148" t="s">
         <v>5</v>
       </c>
-      <c r="F148" s="3" t="s">
+      <c r="F148" s="2" t="s">
         <v>422</v>
       </c>
       <c r="G148" t="s">
@@ -8064,8 +9814,20 @@
       <c r="N148">
         <v>12000</v>
       </c>
-    </row>
-    <row r="149" spans="1:14">
+      <c r="O148">
+        <v>450</v>
+      </c>
+      <c r="P148">
+        <v>33</v>
+      </c>
+      <c r="Q148">
+        <v>300</v>
+      </c>
+      <c r="R148">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="149" spans="1:18">
       <c r="A149">
         <v>148</v>
       </c>
@@ -8081,7 +9843,7 @@
       <c r="E149" t="s">
         <v>18</v>
       </c>
-      <c r="F149" s="3" t="s">
+      <c r="F149" s="2" t="s">
         <v>422</v>
       </c>
       <c r="G149" t="s">
@@ -8108,8 +9870,20 @@
       <c r="N149">
         <v>31153</v>
       </c>
-    </row>
-    <row r="150" spans="1:14">
+      <c r="O149">
+        <v>480</v>
+      </c>
+      <c r="P149">
+        <v>35</v>
+      </c>
+      <c r="Q149">
+        <v>200</v>
+      </c>
+      <c r="R149">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="150" spans="1:18">
       <c r="A150">
         <v>149</v>
       </c>
@@ -8122,7 +9896,7 @@
       <c r="D150" t="s">
         <v>5</v>
       </c>
-      <c r="F150" s="3" t="s">
+      <c r="F150" s="2" t="s">
         <v>422</v>
       </c>
       <c r="G150" t="s">
@@ -8149,8 +9923,20 @@
       <c r="N150">
         <v>490</v>
       </c>
-    </row>
-    <row r="151" spans="1:14">
+      <c r="O150">
+        <v>450</v>
+      </c>
+      <c r="P150">
+        <v>30</v>
+      </c>
+      <c r="Q150">
+        <v>340</v>
+      </c>
+      <c r="R150">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="151" spans="1:18">
       <c r="A151">
         <v>150</v>
       </c>
@@ -8166,7 +9952,7 @@
       <c r="E151" t="s">
         <v>13</v>
       </c>
-      <c r="F151" s="3" t="s">
+      <c r="F151" s="2" t="s">
         <v>433</v>
       </c>
       <c r="G151" t="s">
@@ -8193,8 +9979,20 @@
       <c r="N151">
         <v>9233</v>
       </c>
-    </row>
-    <row r="152" spans="1:14">
+      <c r="O151">
+        <v>450</v>
+      </c>
+      <c r="P151">
+        <v>38</v>
+      </c>
+      <c r="Q151">
+        <v>260</v>
+      </c>
+      <c r="R151">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="152" spans="1:18">
       <c r="A152">
         <v>151</v>
       </c>
@@ -8210,7 +10008,7 @@
       <c r="E152" t="s">
         <v>18</v>
       </c>
-      <c r="F152" s="3" t="s">
+      <c r="F152" s="2" t="s">
         <v>433</v>
       </c>
       <c r="G152" t="s">
@@ -8237,8 +10035,20 @@
       <c r="N152">
         <v>0</v>
       </c>
-    </row>
-    <row r="153" spans="1:14">
+      <c r="O152">
+        <v>450</v>
+      </c>
+      <c r="P152">
+        <v>46</v>
+      </c>
+      <c r="Q152">
+        <v>340</v>
+      </c>
+      <c r="R152">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="153" spans="1:18">
       <c r="A153">
         <v>152</v>
       </c>
@@ -8251,7 +10061,7 @@
       <c r="D153" t="s">
         <v>5</v>
       </c>
-      <c r="F153" s="3">
+      <c r="F153" s="2">
         <v>2021</v>
       </c>
       <c r="G153" t="s">
@@ -8278,8 +10088,20 @@
       <c r="N153">
         <v>4600</v>
       </c>
-    </row>
-    <row r="154" spans="1:14">
+      <c r="O153">
+        <v>370</v>
+      </c>
+      <c r="P153">
+        <v>38</v>
+      </c>
+      <c r="Q153">
+        <v>230</v>
+      </c>
+      <c r="R153">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="154" spans="1:18">
       <c r="A154">
         <v>153</v>
       </c>
@@ -8292,7 +10114,7 @@
       <c r="D154" t="s">
         <v>5</v>
       </c>
-      <c r="F154" s="3">
+      <c r="F154" s="2">
         <v>2023</v>
       </c>
       <c r="G154" t="s">
@@ -8319,8 +10141,20 @@
       <c r="N154">
         <v>32300</v>
       </c>
-    </row>
-    <row r="155" spans="1:14">
+      <c r="O154">
+        <v>480</v>
+      </c>
+      <c r="P154">
+        <v>35</v>
+      </c>
+      <c r="Q154">
+        <v>320</v>
+      </c>
+      <c r="R154">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="155" spans="1:18">
       <c r="A155">
         <v>154</v>
       </c>
@@ -8336,7 +10170,7 @@
       <c r="E155" t="s">
         <v>13</v>
       </c>
-      <c r="F155" s="3" t="s">
+      <c r="F155" s="2" t="s">
         <v>440</v>
       </c>
       <c r="G155" t="s">
@@ -8363,8 +10197,20 @@
       <c r="N155">
         <v>18531</v>
       </c>
-    </row>
-    <row r="156" spans="1:14">
+      <c r="O155">
+        <v>220</v>
+      </c>
+      <c r="P155">
+        <v>32</v>
+      </c>
+      <c r="Q155">
+        <v>160</v>
+      </c>
+      <c r="R155">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="156" spans="1:18">
       <c r="A156">
         <v>155</v>
       </c>
@@ -8377,7 +10223,7 @@
       <c r="D156" t="s">
         <v>5</v>
       </c>
-      <c r="F156" s="3" t="s">
+      <c r="F156" s="2" t="s">
         <v>440</v>
       </c>
       <c r="G156" t="s">
@@ -8404,8 +10250,20 @@
       <c r="N156">
         <v>31700</v>
       </c>
-    </row>
-    <row r="157" spans="1:14">
+      <c r="O156">
+        <v>270</v>
+      </c>
+      <c r="P156">
+        <v>33</v>
+      </c>
+      <c r="Q156">
+        <v>165</v>
+      </c>
+      <c r="R156">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="157" spans="1:18">
       <c r="A157">
         <v>156</v>
       </c>
@@ -8418,7 +10276,7 @@
       <c r="D157" t="s">
         <v>5</v>
       </c>
-      <c r="F157" s="3" t="s">
+      <c r="F157" s="2" t="s">
         <v>433</v>
       </c>
       <c r="G157" t="s">
@@ -8445,8 +10303,20 @@
       <c r="N157">
         <v>4092</v>
       </c>
-    </row>
-    <row r="158" spans="1:14">
+      <c r="O157">
+        <v>190</v>
+      </c>
+      <c r="P157">
+        <v>33</v>
+      </c>
+      <c r="Q157">
+        <v>150</v>
+      </c>
+      <c r="R157">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="158" spans="1:18">
       <c r="A158">
         <v>157</v>
       </c>
@@ -8462,7 +10332,7 @@
       <c r="E158" t="s">
         <v>13</v>
       </c>
-      <c r="F158" s="3" t="s">
+      <c r="F158" s="2" t="s">
         <v>433</v>
       </c>
       <c r="G158" t="s">
@@ -8489,8 +10359,20 @@
       <c r="N158">
         <v>15371</v>
       </c>
-    </row>
-    <row r="159" spans="1:14">
+      <c r="O158">
+        <v>200</v>
+      </c>
+      <c r="P158">
+        <v>30</v>
+      </c>
+      <c r="Q158">
+        <v>135</v>
+      </c>
+      <c r="R158">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="159" spans="1:18">
       <c r="A159">
         <v>158</v>
       </c>
@@ -8503,7 +10385,7 @@
       <c r="D159" t="s">
         <v>5</v>
       </c>
-      <c r="F159" s="3" t="s">
+      <c r="F159" s="2" t="s">
         <v>433</v>
       </c>
       <c r="G159" t="s">
@@ -8530,8 +10412,20 @@
       <c r="N159">
         <v>0</v>
       </c>
-    </row>
-    <row r="160" spans="1:14">
+      <c r="O159">
+        <v>300</v>
+      </c>
+      <c r="P159">
+        <v>33</v>
+      </c>
+      <c r="Q159">
+        <v>185</v>
+      </c>
+      <c r="R159">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:18">
       <c r="A160">
         <v>159</v>
       </c>
@@ -8544,7 +10438,7 @@
       <c r="D160" t="s">
         <v>5</v>
       </c>
-      <c r="F160" s="3">
+      <c r="F160" s="2">
         <v>2018</v>
       </c>
       <c r="G160" t="s">
@@ -8571,8 +10465,20 @@
       <c r="N160">
         <v>4279</v>
       </c>
-    </row>
-    <row r="161" spans="1:14">
+      <c r="O160">
+        <v>220</v>
+      </c>
+      <c r="P160">
+        <v>32</v>
+      </c>
+      <c r="Q160">
+        <v>170</v>
+      </c>
+      <c r="R160">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="161" spans="1:18">
       <c r="A161">
         <v>160</v>
       </c>
@@ -8588,7 +10494,7 @@
       <c r="E161" t="s">
         <v>18</v>
       </c>
-      <c r="F161" s="3">
+      <c r="F161" s="2">
         <v>2020</v>
       </c>
       <c r="G161" t="s">
@@ -8615,8 +10521,20 @@
       <c r="N161">
         <v>30000</v>
       </c>
-    </row>
-    <row r="162" spans="1:14">
+      <c r="O161">
+        <v>300</v>
+      </c>
+      <c r="P161">
+        <v>32</v>
+      </c>
+      <c r="Q161">
+        <v>180</v>
+      </c>
+      <c r="R161">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="162" spans="1:18">
       <c r="A162">
         <v>161</v>
       </c>
@@ -8632,7 +10550,7 @@
       <c r="E162" t="s">
         <v>13</v>
       </c>
-      <c r="F162" s="3">
+      <c r="F162" s="2">
         <v>2020</v>
       </c>
       <c r="G162" t="s">
@@ -8659,8 +10577,20 @@
       <c r="N162">
         <v>19440</v>
       </c>
-    </row>
-    <row r="163" spans="1:14">
+      <c r="O162">
+        <v>270</v>
+      </c>
+      <c r="P162">
+        <v>45</v>
+      </c>
+      <c r="Q162">
+        <v>160</v>
+      </c>
+      <c r="R162">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="163" spans="1:18">
       <c r="A163">
         <v>162</v>
       </c>
@@ -8676,7 +10606,7 @@
       <c r="E163" t="s">
         <v>13</v>
       </c>
-      <c r="F163" s="3">
+      <c r="F163" s="2">
         <v>2021</v>
       </c>
       <c r="G163" t="s">
@@ -8703,8 +10633,20 @@
       <c r="N163">
         <v>10166</v>
       </c>
-    </row>
-    <row r="164" spans="1:14">
+      <c r="O163">
+        <v>240</v>
+      </c>
+      <c r="P163">
+        <v>33</v>
+      </c>
+      <c r="Q163">
+        <v>170</v>
+      </c>
+      <c r="R163">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="164" spans="1:18">
       <c r="A164">
         <v>163</v>
       </c>
@@ -8720,7 +10662,7 @@
       <c r="E164" t="s">
         <v>13</v>
       </c>
-      <c r="F164" s="3">
+      <c r="F164" s="2">
         <v>2021</v>
       </c>
       <c r="G164" t="s">
@@ -8747,8 +10689,20 @@
       <c r="N164">
         <v>9014</v>
       </c>
-    </row>
-    <row r="165" spans="1:14">
+      <c r="O164">
+        <v>210</v>
+      </c>
+      <c r="P164">
+        <v>35</v>
+      </c>
+      <c r="Q164">
+        <v>150</v>
+      </c>
+      <c r="R164">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="165" spans="1:18">
       <c r="A165">
         <v>164</v>
       </c>
@@ -8764,7 +10718,7 @@
       <c r="E165" t="s">
         <v>18</v>
       </c>
-      <c r="F165" s="3">
+      <c r="F165" s="2">
         <v>2023</v>
       </c>
       <c r="G165" t="s">
@@ -8791,8 +10745,20 @@
       <c r="N165">
         <v>50100</v>
       </c>
-    </row>
-    <row r="166" spans="1:14">
+      <c r="O165">
+        <v>180</v>
+      </c>
+      <c r="P165">
+        <v>26.9</v>
+      </c>
+      <c r="Q165">
+        <v>170</v>
+      </c>
+      <c r="R165">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="166" spans="1:18">
       <c r="A166">
         <v>165</v>
       </c>
@@ -8805,7 +10771,7 @@
       <c r="D166" t="s">
         <v>5</v>
       </c>
-      <c r="F166" s="3">
+      <c r="F166" s="2">
         <v>2024</v>
       </c>
       <c r="G166" t="s">
@@ -8832,8 +10798,14 @@
       <c r="N166">
         <v>51204</v>
       </c>
-    </row>
-    <row r="167" spans="1:14">
+      <c r="Q166">
+        <v>220</v>
+      </c>
+      <c r="R166">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="167" spans="1:18">
       <c r="A167">
         <v>166</v>
       </c>
@@ -8846,7 +10818,7 @@
       <c r="D167" t="s">
         <v>5</v>
       </c>
-      <c r="F167" s="3" t="s">
+      <c r="F167" s="2" t="s">
         <v>430</v>
       </c>
       <c r="G167" t="s">
@@ -8873,8 +10845,20 @@
       <c r="N167">
         <v>8589</v>
       </c>
-    </row>
-    <row r="168" spans="1:14">
+      <c r="O167">
+        <v>240</v>
+      </c>
+      <c r="P167">
+        <v>27</v>
+      </c>
+      <c r="Q167">
+        <v>145</v>
+      </c>
+      <c r="R167">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="168" spans="1:18">
       <c r="A168">
         <v>167</v>
       </c>
@@ -8887,7 +10871,7 @@
       <c r="D168" t="s">
         <v>5</v>
       </c>
-      <c r="F168" s="3" t="s">
+      <c r="F168" s="2" t="s">
         <v>441</v>
       </c>
       <c r="G168" t="s">
@@ -8914,8 +10898,20 @@
       <c r="N168">
         <v>8967</v>
       </c>
-    </row>
-    <row r="169" spans="1:14">
+      <c r="O168">
+        <v>220</v>
+      </c>
+      <c r="P168">
+        <v>33</v>
+      </c>
+      <c r="Q168">
+        <v>155</v>
+      </c>
+      <c r="R168">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="169" spans="1:18">
       <c r="A169">
         <v>168</v>
       </c>
@@ -8931,7 +10927,7 @@
       <c r="E169" t="s">
         <v>18</v>
       </c>
-      <c r="F169" s="3" t="s">
+      <c r="F169" s="2" t="s">
         <v>440</v>
       </c>
       <c r="G169" t="s">
@@ -8958,8 +10954,20 @@
       <c r="N169">
         <v>3493</v>
       </c>
-    </row>
-    <row r="170" spans="1:14">
+      <c r="O169">
+        <v>400</v>
+      </c>
+      <c r="P169">
+        <v>32</v>
+      </c>
+      <c r="Q169">
+        <v>270</v>
+      </c>
+      <c r="R169">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="170" spans="1:18">
       <c r="A170">
         <v>169</v>
       </c>
@@ -8975,7 +10983,7 @@
       <c r="E170" t="s">
         <v>13</v>
       </c>
-      <c r="F170" s="3" t="s">
+      <c r="F170" s="2" t="s">
         <v>440</v>
       </c>
       <c r="G170" t="s">
@@ -9002,8 +11010,20 @@
       <c r="N170">
         <v>17000</v>
       </c>
-    </row>
-    <row r="171" spans="1:14">
+      <c r="O170">
+        <v>300</v>
+      </c>
+      <c r="P170">
+        <v>32</v>
+      </c>
+      <c r="Q170">
+        <v>280</v>
+      </c>
+      <c r="R170">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="171" spans="1:18">
       <c r="A171">
         <v>170</v>
       </c>
@@ -9016,7 +11036,7 @@
       <c r="D171" t="s">
         <v>5</v>
       </c>
-      <c r="F171" s="3" t="s">
+      <c r="F171" s="2" t="s">
         <v>433</v>
       </c>
       <c r="G171" t="s">
@@ -9043,8 +11063,20 @@
       <c r="N171">
         <v>1330</v>
       </c>
-    </row>
-    <row r="172" spans="1:14">
+      <c r="O171">
+        <v>330</v>
+      </c>
+      <c r="P171">
+        <v>35</v>
+      </c>
+      <c r="Q171">
+        <v>235</v>
+      </c>
+      <c r="R171">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:18">
       <c r="A172">
         <v>171</v>
       </c>
@@ -9057,7 +11089,7 @@
       <c r="D172" t="s">
         <v>170</v>
       </c>
-      <c r="F172" s="3">
+      <c r="F172" s="2">
         <v>2018</v>
       </c>
       <c r="G172" t="s">
@@ -9084,8 +11116,20 @@
       <c r="N172">
         <v>18039</v>
       </c>
-    </row>
-    <row r="173" spans="1:14">
+      <c r="O172">
+        <v>210</v>
+      </c>
+      <c r="P172">
+        <v>30</v>
+      </c>
+      <c r="Q172">
+        <v>180</v>
+      </c>
+      <c r="R172">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="173" spans="1:18">
       <c r="A173">
         <v>172</v>
       </c>
@@ -9101,7 +11145,7 @@
       <c r="E173" t="s">
         <v>13</v>
       </c>
-      <c r="F173" s="3">
+      <c r="F173" s="2">
         <v>2018</v>
       </c>
       <c r="G173" t="s">
@@ -9128,8 +11172,20 @@
       <c r="N173">
         <v>10527</v>
       </c>
-    </row>
-    <row r="174" spans="1:14">
+      <c r="O173">
+        <v>200</v>
+      </c>
+      <c r="P173">
+        <v>28</v>
+      </c>
+      <c r="Q173">
+        <v>180</v>
+      </c>
+      <c r="R173">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="174" spans="1:18">
       <c r="A174">
         <v>173</v>
       </c>
@@ -9145,7 +11201,7 @@
       <c r="E174" t="s">
         <v>358</v>
       </c>
-      <c r="F174" s="3" t="s">
+      <c r="F174" s="2" t="s">
         <v>444</v>
       </c>
       <c r="G174" t="s">
@@ -9172,8 +11228,20 @@
       <c r="N174">
         <v>2350</v>
       </c>
-    </row>
-    <row r="175" spans="1:14">
+      <c r="O174">
+        <v>122</v>
+      </c>
+      <c r="P174">
+        <v>24</v>
+      </c>
+      <c r="Q174">
+        <v>100</v>
+      </c>
+      <c r="R174">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="175" spans="1:18">
       <c r="A175">
         <v>174</v>
       </c>
@@ -9189,7 +11257,7 @@
       <c r="E175" t="s">
         <v>358</v>
       </c>
-      <c r="F175" s="3">
+      <c r="F175" s="2">
         <v>2021</v>
       </c>
       <c r="G175" t="s">
@@ -9216,8 +11284,20 @@
       <c r="N175">
         <v>3480</v>
       </c>
-    </row>
-    <row r="176" spans="1:14">
+      <c r="O175">
+        <v>120</v>
+      </c>
+      <c r="P175">
+        <v>23</v>
+      </c>
+      <c r="Q175">
+        <v>100</v>
+      </c>
+      <c r="R175">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="176" spans="1:18">
       <c r="A176">
         <v>175</v>
       </c>
@@ -9233,7 +11313,7 @@
       <c r="E176" t="s">
         <v>18</v>
       </c>
-      <c r="F176" s="3" t="s">
+      <c r="F176" s="2" t="s">
         <v>434</v>
       </c>
       <c r="G176" t="s">
@@ -9260,8 +11340,20 @@
       <c r="N176">
         <v>29000</v>
       </c>
-    </row>
-    <row r="177" spans="1:14">
+      <c r="O176">
+        <v>158</v>
+      </c>
+      <c r="P176">
+        <v>25</v>
+      </c>
+      <c r="Q176">
+        <v>100</v>
+      </c>
+      <c r="R176">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="177" spans="1:18">
       <c r="A177">
         <v>176</v>
       </c>
@@ -9277,7 +11369,7 @@
       <c r="E177" t="s">
         <v>13</v>
       </c>
-      <c r="F177" s="3">
+      <c r="F177" s="2">
         <v>2019</v>
       </c>
       <c r="G177" t="s">
@@ -9304,8 +11396,20 @@
       <c r="N177">
         <v>35016</v>
       </c>
-    </row>
-    <row r="178" spans="1:14">
+      <c r="O177">
+        <v>140</v>
+      </c>
+      <c r="P177">
+        <v>26</v>
+      </c>
+      <c r="Q177">
+        <v>90</v>
+      </c>
+      <c r="R177">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="178" spans="1:18">
       <c r="A178">
         <v>177</v>
       </c>
@@ -9318,7 +11422,7 @@
       <c r="D178" t="s">
         <v>5</v>
       </c>
-      <c r="F178" s="3">
+      <c r="F178" s="2">
         <v>2023</v>
       </c>
       <c r="G178" t="s">
@@ -9345,8 +11449,20 @@
       <c r="N178">
         <v>8416</v>
       </c>
-    </row>
-    <row r="179" spans="1:14">
+      <c r="O178">
+        <v>360</v>
+      </c>
+      <c r="P178">
+        <v>28</v>
+      </c>
+      <c r="Q178">
+        <v>250</v>
+      </c>
+      <c r="R178">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="179" spans="1:18">
       <c r="A179">
         <v>178</v>
       </c>
@@ -9359,7 +11475,7 @@
       <c r="D179" t="s">
         <v>5</v>
       </c>
-      <c r="F179" s="3" t="s">
+      <c r="F179" s="2" t="s">
         <v>445</v>
       </c>
       <c r="G179" t="s">
@@ -9386,8 +11502,20 @@
       <c r="N179">
         <v>14000</v>
       </c>
-    </row>
-    <row r="180" spans="1:14">
+      <c r="O179">
+        <v>240</v>
+      </c>
+      <c r="P179">
+        <v>35</v>
+      </c>
+      <c r="Q179">
+        <v>135</v>
+      </c>
+      <c r="R179">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="180" spans="1:18">
       <c r="A180">
         <v>179</v>
       </c>
@@ -9400,7 +11528,7 @@
       <c r="D180" t="s">
         <v>5</v>
       </c>
-      <c r="F180" s="3">
+      <c r="F180" s="2">
         <v>2022</v>
       </c>
       <c r="G180" t="s">
@@ -9427,8 +11555,20 @@
       <c r="N180">
         <v>22912</v>
       </c>
-    </row>
-    <row r="181" spans="1:14">
+      <c r="O180">
+        <v>144</v>
+      </c>
+      <c r="P180">
+        <v>30</v>
+      </c>
+      <c r="Q180">
+        <v>110</v>
+      </c>
+      <c r="R180">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="181" spans="1:18">
       <c r="A181">
         <v>180</v>
       </c>
@@ -9441,7 +11581,7 @@
       <c r="D181" t="s">
         <v>5</v>
       </c>
-      <c r="F181" s="3">
+      <c r="F181" s="2">
         <v>2023</v>
       </c>
       <c r="G181" t="s">
@@ -9468,8 +11608,20 @@
       <c r="N181">
         <v>15800</v>
       </c>
-    </row>
-    <row r="182" spans="1:14">
+      <c r="O181">
+        <v>360</v>
+      </c>
+      <c r="P181">
+        <v>30</v>
+      </c>
+      <c r="Q181">
+        <v>240</v>
+      </c>
+      <c r="R181">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="182" spans="1:18">
       <c r="A182">
         <v>181</v>
       </c>
@@ -9482,7 +11634,7 @@
       <c r="D182" t="s">
         <v>5</v>
       </c>
-      <c r="F182" s="3">
+      <c r="F182" s="2">
         <v>2023</v>
       </c>
       <c r="G182" t="s">
@@ -9509,8 +11661,20 @@
       <c r="N182">
         <v>28050</v>
       </c>
-    </row>
-    <row r="183" spans="1:14">
+      <c r="O182">
+        <v>124</v>
+      </c>
+      <c r="P182">
+        <v>28</v>
+      </c>
+      <c r="Q182">
+        <v>90</v>
+      </c>
+      <c r="R182">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="183" spans="1:18">
       <c r="A183">
         <v>182</v>
       </c>
@@ -9526,7 +11690,7 @@
       <c r="E183" t="s">
         <v>13</v>
       </c>
-      <c r="F183" s="3">
+      <c r="F183" s="2">
         <v>2024</v>
       </c>
       <c r="G183" t="s">
@@ -9553,8 +11717,20 @@
       <c r="N183">
         <v>7200</v>
       </c>
-    </row>
-    <row r="184" spans="1:14">
+      <c r="O183">
+        <v>517</v>
+      </c>
+      <c r="P183">
+        <v>36</v>
+      </c>
+      <c r="Q183">
+        <v>350</v>
+      </c>
+      <c r="R183">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="184" spans="1:18">
       <c r="A184">
         <v>183</v>
       </c>
@@ -9567,7 +11743,7 @@
       <c r="D184" t="s">
         <v>5</v>
       </c>
-      <c r="F184" s="3">
+      <c r="F184" s="2">
         <v>2016</v>
       </c>
       <c r="G184" t="s">
@@ -9594,8 +11770,20 @@
       <c r="N184">
         <v>22000</v>
       </c>
-    </row>
-    <row r="185" spans="1:14">
+      <c r="O184">
+        <v>170</v>
+      </c>
+      <c r="P184">
+        <v>27</v>
+      </c>
+      <c r="Q184">
+        <v>140</v>
+      </c>
+      <c r="R184">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="185" spans="1:18">
       <c r="A185">
         <v>184</v>
       </c>
@@ -9611,7 +11799,7 @@
       <c r="E185" t="s">
         <v>13</v>
       </c>
-      <c r="F185" s="3">
+      <c r="F185" s="2">
         <v>2025</v>
       </c>
       <c r="G185" t="s">
@@ -9638,8 +11826,20 @@
       <c r="N185">
         <v>60477</v>
       </c>
-    </row>
-    <row r="186" spans="1:14">
+      <c r="O185">
+        <v>360</v>
+      </c>
+      <c r="P185">
+        <v>30</v>
+      </c>
+      <c r="Q185">
+        <v>300</v>
+      </c>
+      <c r="R185">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="186" spans="1:18">
       <c r="A186">
         <v>185</v>
       </c>
@@ -9655,7 +11855,7 @@
       <c r="E186" t="s">
         <v>13</v>
       </c>
-      <c r="F186" s="3">
+      <c r="F186" s="2">
         <v>2023</v>
       </c>
       <c r="G186" t="s">
@@ -9679,8 +11879,20 @@
       <c r="N186">
         <v>46900</v>
       </c>
-    </row>
-    <row r="187" spans="1:14">
+      <c r="O186">
+        <v>115</v>
+      </c>
+      <c r="P186">
+        <v>32</v>
+      </c>
+      <c r="Q186">
+        <v>100</v>
+      </c>
+      <c r="R186">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="187" spans="1:18">
       <c r="A187">
         <v>186</v>
       </c>
@@ -9693,7 +11905,7 @@
       <c r="D187" t="s">
         <v>5</v>
       </c>
-      <c r="F187" s="3">
+      <c r="F187" s="2">
         <v>2018</v>
       </c>
       <c r="G187" t="s">
@@ -9717,8 +11929,20 @@
       <c r="N187">
         <v>19800</v>
       </c>
-    </row>
-    <row r="188" spans="1:14">
+      <c r="O187">
+        <v>105</v>
+      </c>
+      <c r="P187">
+        <v>20</v>
+      </c>
+      <c r="Q187">
+        <v>90</v>
+      </c>
+      <c r="R187">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="188" spans="1:18">
       <c r="A188">
         <v>187</v>
       </c>
@@ -9731,7 +11955,7 @@
       <c r="D188" t="s">
         <v>5</v>
       </c>
-      <c r="F188" s="3">
+      <c r="F188" s="2">
         <v>2018</v>
       </c>
       <c r="G188" t="s">
@@ -9755,8 +11979,20 @@
       <c r="N188">
         <v>8800</v>
       </c>
-    </row>
-    <row r="189" spans="1:14">
+      <c r="O188">
+        <v>105</v>
+      </c>
+      <c r="P188">
+        <v>20</v>
+      </c>
+      <c r="Q188">
+        <v>92</v>
+      </c>
+      <c r="R188">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="189" spans="1:18">
       <c r="A189">
         <v>188</v>
       </c>
@@ -9772,7 +12008,7 @@
       <c r="E189" t="s">
         <v>13</v>
       </c>
-      <c r="F189" s="3">
+      <c r="F189" s="2">
         <v>2017</v>
       </c>
       <c r="G189" t="s">
@@ -9796,8 +12032,20 @@
       <c r="N189">
         <v>57000</v>
       </c>
-    </row>
-    <row r="190" spans="1:14">
+      <c r="O189">
+        <v>120</v>
+      </c>
+      <c r="P189">
+        <v>31</v>
+      </c>
+      <c r="Q189">
+        <v>100</v>
+      </c>
+      <c r="R189">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="190" spans="1:18">
       <c r="A190">
         <v>189</v>
       </c>
@@ -9810,7 +12058,7 @@
       <c r="D190" t="s">
         <v>5</v>
       </c>
-      <c r="F190" s="3">
+      <c r="F190" s="2">
         <v>2021</v>
       </c>
       <c r="G190" t="s">
@@ -9834,8 +12082,20 @@
       <c r="N190">
         <v>10700</v>
       </c>
-    </row>
-    <row r="191" spans="1:14">
+      <c r="O190">
+        <v>120</v>
+      </c>
+      <c r="P190">
+        <v>35</v>
+      </c>
+      <c r="Q190">
+        <v>98</v>
+      </c>
+      <c r="R190">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="191" spans="1:18">
       <c r="A191">
         <v>190</v>
       </c>
@@ -9851,7 +12111,7 @@
       <c r="E191" t="s">
         <v>13</v>
       </c>
-      <c r="F191" s="3">
+      <c r="F191" s="2">
         <v>2023</v>
       </c>
       <c r="G191" t="s">
@@ -9875,8 +12135,20 @@
       <c r="N191">
         <v>30000</v>
       </c>
-    </row>
-    <row r="192" spans="1:14">
+      <c r="O191">
+        <v>120</v>
+      </c>
+      <c r="P191">
+        <v>32</v>
+      </c>
+      <c r="Q191">
+        <v>90</v>
+      </c>
+      <c r="R191">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="192" spans="1:18">
       <c r="A192">
         <v>191</v>
       </c>
@@ -9889,7 +12161,7 @@
       <c r="D192" t="s">
         <v>5</v>
       </c>
-      <c r="F192" s="3">
+      <c r="F192" s="2">
         <v>2019</v>
       </c>
       <c r="G192" t="s">
@@ -9913,8 +12185,20 @@
       <c r="N192">
         <v>15800</v>
       </c>
-    </row>
-    <row r="193" spans="1:14">
+      <c r="O192">
+        <v>90</v>
+      </c>
+      <c r="P192">
+        <v>30</v>
+      </c>
+      <c r="Q192">
+        <v>85</v>
+      </c>
+      <c r="R192">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="193" spans="1:18">
       <c r="A193">
         <v>192</v>
       </c>
@@ -9930,7 +12214,7 @@
       <c r="E193" t="s">
         <v>13</v>
       </c>
-      <c r="F193" s="3">
+      <c r="F193" s="2">
         <v>2022</v>
       </c>
       <c r="G193" t="s">
@@ -9953,6 +12237,15 @@
       </c>
       <c r="N193">
         <v>29000</v>
+      </c>
+      <c r="P193">
+        <v>35</v>
+      </c>
+      <c r="Q193">
+        <v>95</v>
+      </c>
+      <c r="R193">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\intern.bjres\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB4D5EC1-FCC0-42F2-9F57-D68676696921}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4418A411-CD78-437E-8C54-3AB01827D95B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="45" yWindow="-16200" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1591" uniqueCount="450">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1591" uniqueCount="451">
   <si>
     <t>所在市</t>
   </si>
@@ -1384,6 +1384,9 @@
   </si>
   <si>
     <t>上季度免租期</t>
+  </si>
+  <si>
+    <t>116.680295,39.907589</t>
   </si>
 </sst>
 </file>
@@ -1467,10 +1470,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -12068,7 +12067,7 @@
         <v>66</v>
       </c>
       <c r="I190" t="s">
-        <v>67</v>
+        <v>450</v>
       </c>
       <c r="K190">
         <v>26737</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\intern.bjres\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4418A411-CD78-437E-8C54-3AB01827D95B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A47EFD3-9202-4E70-B625-7980C7E5182F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="45" yWindow="-16200" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\intern.bjres\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A47EFD3-9202-4E70-B625-7980C7E5182F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4F71E934-A578-4CF6-882C-2C627295C1B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="45" yWindow="-16200" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yuhang/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B15553B2-B512-8A47-997F-A2869AE9CC2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F864998-EBAA-264A-A418-BB1E38A02A7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -959,9 +959,6 @@
     <t>中关村东升科技园三期（东畔创新中心）</t>
   </si>
   <si>
-    <t>116.358199,40.044056</t>
-  </si>
-  <si>
     <t>学院路科技园东升园</t>
   </si>
   <si>
@@ -1514,6 +1511,10 @@
   </si>
   <si>
     <t>116.412452,39.909603</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>116.365799,40.001522</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1919,22 +1920,22 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B1" t="s">
+        <v>470</v>
+      </c>
+      <c r="C1" t="s">
         <v>471</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>472</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="F1" t="s">
         <v>473</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>479</v>
-      </c>
-      <c r="F1" t="s">
-        <v>474</v>
       </c>
       <c r="G1" t="s">
         <v>0</v>
@@ -1946,19 +1947,19 @@
         <v>2</v>
       </c>
       <c r="J1" t="s">
+        <v>474</v>
+      </c>
+      <c r="K1" t="s">
+        <v>469</v>
+      </c>
+      <c r="L1" t="s">
         <v>475</v>
       </c>
-      <c r="K1" t="s">
-        <v>470</v>
-      </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>476</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>477</v>
-      </c>
-      <c r="N1" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -1987,7 +1988,7 @@
         <v>9</v>
       </c>
       <c r="J2" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K2">
         <v>72308</v>
@@ -2028,7 +2029,7 @@
         <v>12</v>
       </c>
       <c r="J3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K3">
         <v>72308</v>
@@ -2072,7 +2073,7 @@
         <v>17</v>
       </c>
       <c r="J4" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K4">
         <v>130769</v>
@@ -2116,7 +2117,7 @@
         <v>20</v>
       </c>
       <c r="J5" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K5">
         <v>64615</v>
@@ -2160,7 +2161,7 @@
         <v>24</v>
       </c>
       <c r="J6" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K6">
         <v>80091</v>
@@ -2201,7 +2202,7 @@
         <v>27</v>
       </c>
       <c r="J7" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="K7">
         <v>70673</v>
@@ -2245,7 +2246,7 @@
         <v>30</v>
       </c>
       <c r="J8" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K8">
         <v>90466</v>
@@ -2286,7 +2287,7 @@
         <v>32</v>
       </c>
       <c r="J9" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="K9">
         <v>46720</v>
@@ -2330,7 +2331,7 @@
         <v>35</v>
       </c>
       <c r="J10" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="K10">
         <v>95000</v>
@@ -2374,7 +2375,7 @@
         <v>38</v>
       </c>
       <c r="J11" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K11">
         <v>85300</v>
@@ -2418,7 +2419,7 @@
         <v>41</v>
       </c>
       <c r="J12" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="K12">
         <v>33305</v>
@@ -2462,7 +2463,7 @@
         <v>43</v>
       </c>
       <c r="J13" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K13">
         <v>120245.21</v>
@@ -2506,7 +2507,7 @@
         <v>43</v>
       </c>
       <c r="J14" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K14">
         <v>70425.53</v>
@@ -2550,7 +2551,7 @@
         <v>47</v>
       </c>
       <c r="J15" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K15">
         <v>78000</v>
@@ -2594,7 +2595,7 @@
         <v>50</v>
       </c>
       <c r="J16" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="K16">
         <v>102796</v>
@@ -2638,7 +2639,7 @@
         <v>52</v>
       </c>
       <c r="J17" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="K17">
         <v>49200</v>
@@ -2682,7 +2683,7 @@
         <v>54</v>
       </c>
       <c r="J18" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="K18">
         <v>65096</v>
@@ -2726,7 +2727,7 @@
         <v>57</v>
       </c>
       <c r="J19" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K19">
         <v>56000</v>
@@ -2770,7 +2771,7 @@
         <v>60</v>
       </c>
       <c r="J20" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="K20">
         <v>177847</v>
@@ -2814,7 +2815,7 @@
         <v>63</v>
       </c>
       <c r="J21" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K21">
         <v>83000</v>
@@ -2855,7 +2856,7 @@
         <v>66</v>
       </c>
       <c r="J22" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="K22">
         <v>26000</v>
@@ -2896,7 +2897,7 @@
         <v>68</v>
       </c>
       <c r="J23" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K23">
         <v>85887</v>
@@ -2937,7 +2938,7 @@
         <v>70</v>
       </c>
       <c r="J24" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K24">
         <v>20000</v>
@@ -2981,7 +2982,7 @@
         <v>73</v>
       </c>
       <c r="J25" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K25">
         <v>146385</v>
@@ -3025,7 +3026,7 @@
         <v>76</v>
       </c>
       <c r="J26" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K26">
         <v>87000</v>
@@ -3069,7 +3070,7 @@
         <v>79</v>
       </c>
       <c r="J27" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K27">
         <v>147166.79999999999</v>
@@ -3113,7 +3114,7 @@
         <v>82</v>
       </c>
       <c r="J28" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K28">
         <v>46063</v>
@@ -3157,7 +3158,7 @@
         <v>85</v>
       </c>
       <c r="J29" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="K29">
         <v>47261</v>
@@ -3177,7 +3178,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C30" t="s">
         <v>4</v>
@@ -3195,13 +3196,13 @@
         <v>7</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="J30" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K30">
         <v>119000</v>
@@ -3242,7 +3243,7 @@
         <v>91</v>
       </c>
       <c r="J31" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="K31">
         <v>47000</v>
@@ -3286,7 +3287,7 @@
         <v>93</v>
       </c>
       <c r="J32" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="K32">
         <v>186000</v>
@@ -3324,7 +3325,7 @@
         <v>95</v>
       </c>
       <c r="J33" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K33">
         <v>40800</v>
@@ -3365,7 +3366,7 @@
         <v>95</v>
       </c>
       <c r="J34" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K34">
         <v>55200</v>
@@ -3409,7 +3410,7 @@
         <v>99</v>
       </c>
       <c r="J35" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="K35">
         <v>350000</v>
@@ -3450,7 +3451,7 @@
         <v>101</v>
       </c>
       <c r="J36" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K36">
         <v>65000</v>
@@ -3491,7 +3492,7 @@
         <v>101</v>
       </c>
       <c r="J37" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K37">
         <v>35000</v>
@@ -3532,7 +3533,7 @@
         <v>104</v>
       </c>
       <c r="J38" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="K38">
         <v>47000</v>
@@ -3576,7 +3577,7 @@
         <v>107</v>
       </c>
       <c r="J39" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="K39">
         <v>120000</v>
@@ -3617,7 +3618,7 @@
         <v>109</v>
       </c>
       <c r="J40" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K40">
         <v>83000</v>
@@ -3658,7 +3659,7 @@
         <v>111</v>
       </c>
       <c r="J41" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="K41">
         <v>66030</v>
@@ -3696,7 +3697,7 @@
         <v>113</v>
       </c>
       <c r="J42" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="K42">
         <v>40000</v>
@@ -3740,7 +3741,7 @@
         <v>118</v>
       </c>
       <c r="J43" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K43">
         <v>40000</v>
@@ -3781,7 +3782,7 @@
         <v>121</v>
       </c>
       <c r="J44" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K44">
         <v>54100</v>
@@ -3822,10 +3823,10 @@
         <v>117</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="J45" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K45">
         <v>100000</v>
@@ -3866,10 +3867,10 @@
         <v>117</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="J46" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K46">
         <v>150000</v>
@@ -3910,10 +3911,10 @@
         <v>117</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="J47" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K47">
         <v>50000</v>
@@ -3957,7 +3958,7 @@
         <v>130</v>
       </c>
       <c r="J48" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="K48">
         <v>43000</v>
@@ -3998,7 +3999,7 @@
         <v>133</v>
       </c>
       <c r="J49" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="K49">
         <v>65000</v>
@@ -4039,7 +4040,7 @@
         <v>136</v>
       </c>
       <c r="J50" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="51" spans="1:14">
@@ -4071,7 +4072,7 @@
         <v>138</v>
       </c>
       <c r="J51" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="K51">
         <v>56000</v>
@@ -4112,7 +4113,7 @@
         <v>140</v>
       </c>
       <c r="J52" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="K52">
         <v>160000</v>
@@ -4153,7 +4154,7 @@
         <v>142</v>
       </c>
       <c r="J53" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="K53">
         <v>33000</v>
@@ -4197,7 +4198,7 @@
         <v>145</v>
       </c>
       <c r="J54" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="K54">
         <v>41318</v>
@@ -4238,7 +4239,7 @@
         <v>147</v>
       </c>
       <c r="J55" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K55">
         <v>34131</v>
@@ -4279,7 +4280,7 @@
         <v>150</v>
       </c>
       <c r="J56" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K56">
         <v>48000</v>
@@ -4320,7 +4321,7 @@
         <v>118</v>
       </c>
       <c r="J57" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K57">
         <v>16000</v>
@@ -4364,7 +4365,7 @@
         <v>154</v>
       </c>
       <c r="J58" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="K58">
         <v>30000</v>
@@ -4408,7 +4409,7 @@
         <v>157</v>
       </c>
       <c r="J59" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="K59">
         <v>56000</v>
@@ -4452,7 +4453,7 @@
         <v>160</v>
       </c>
       <c r="J60" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K60">
         <v>43000</v>
@@ -4493,7 +4494,7 @@
         <v>162</v>
       </c>
       <c r="J61" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="K61">
         <v>110000</v>
@@ -4531,7 +4532,7 @@
         <v>164</v>
       </c>
       <c r="J62" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K62">
         <v>56160</v>
@@ -4572,7 +4573,7 @@
         <v>166</v>
       </c>
       <c r="J63" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K63">
         <v>138444</v>
@@ -4616,7 +4617,7 @@
         <v>170</v>
       </c>
       <c r="J64" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="K64">
         <v>31000</v>
@@ -4657,7 +4658,7 @@
         <v>173</v>
       </c>
       <c r="J65" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="K65">
         <v>120000</v>
@@ -4698,7 +4699,7 @@
         <v>175</v>
       </c>
       <c r="J66" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="K66">
         <v>25900</v>
@@ -4739,7 +4740,7 @@
         <v>178</v>
       </c>
       <c r="J67" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="K67">
         <v>47986</v>
@@ -4783,7 +4784,7 @@
         <v>180</v>
       </c>
       <c r="J68" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="K68">
         <v>194000</v>
@@ -4827,7 +4828,7 @@
         <v>182</v>
       </c>
       <c r="J69" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="K69">
         <v>39724</v>
@@ -4868,7 +4869,7 @@
         <v>184</v>
       </c>
       <c r="J70" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="K70">
         <v>48437.45</v>
@@ -4909,7 +4910,7 @@
         <v>187</v>
       </c>
       <c r="J71" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="K71">
         <v>37910</v>
@@ -4929,7 +4930,7 @@
         <v>71</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C72" t="s">
         <v>168</v>
@@ -4947,10 +4948,10 @@
         <v>87</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="J72" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="K72">
         <v>21220</v>
@@ -4991,7 +4992,7 @@
         <v>189</v>
       </c>
       <c r="J73" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="K73">
         <v>77877</v>
@@ -5035,7 +5036,7 @@
         <v>191</v>
       </c>
       <c r="J74" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="K74">
         <v>80311.53</v>
@@ -5079,7 +5080,7 @@
         <v>194</v>
       </c>
       <c r="J75" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="K75">
         <v>38000</v>
@@ -5120,7 +5121,7 @@
         <v>197</v>
       </c>
       <c r="J76" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="K76">
         <v>37800</v>
@@ -5164,7 +5165,7 @@
         <v>200</v>
       </c>
       <c r="J77" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="K77">
         <v>54581</v>
@@ -5208,7 +5209,7 @@
         <v>88</v>
       </c>
       <c r="J78" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="K78">
         <v>25000</v>
@@ -5252,7 +5253,7 @@
         <v>204</v>
       </c>
       <c r="J79" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="K79">
         <v>52698</v>
@@ -5293,7 +5294,7 @@
         <v>208</v>
       </c>
       <c r="J80" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="K80">
         <v>38500</v>
@@ -5331,7 +5332,7 @@
         <v>211</v>
       </c>
       <c r="J81" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="K81">
         <v>27200</v>
@@ -5375,7 +5376,7 @@
         <v>214</v>
       </c>
       <c r="J82" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="K82">
         <v>60000</v>
@@ -5416,7 +5417,7 @@
         <v>217</v>
       </c>
       <c r="J83" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K83">
         <v>50000</v>
@@ -5460,7 +5461,7 @@
         <v>219</v>
       </c>
       <c r="J84" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="K84">
         <v>131575</v>
@@ -5501,7 +5502,7 @@
         <v>221</v>
       </c>
       <c r="J85" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K85">
         <v>99500</v>
@@ -5542,7 +5543,7 @@
         <v>224</v>
       </c>
       <c r="J86" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="K86">
         <v>32000</v>
@@ -5586,7 +5587,7 @@
         <v>226</v>
       </c>
       <c r="J87" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="K87">
         <v>52170</v>
@@ -5627,7 +5628,7 @@
         <v>229</v>
       </c>
       <c r="J88" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="K88">
         <v>46000</v>
@@ -5671,7 +5672,7 @@
         <v>232</v>
       </c>
       <c r="J89" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K89">
         <v>45013</v>
@@ -5712,7 +5713,7 @@
         <v>234</v>
       </c>
       <c r="J90" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="K90">
         <v>48566</v>
@@ -5753,7 +5754,7 @@
         <v>237</v>
       </c>
       <c r="J91" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K91">
         <v>55618</v>
@@ -5794,7 +5795,7 @@
         <v>239</v>
       </c>
       <c r="J92" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="K92">
         <v>47000</v>
@@ -5838,7 +5839,7 @@
         <v>242</v>
       </c>
       <c r="J93" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K93">
         <v>87763</v>
@@ -5882,7 +5883,7 @@
         <v>245</v>
       </c>
       <c r="J94" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="K94">
         <v>100658</v>
@@ -5923,7 +5924,7 @@
         <v>248</v>
       </c>
       <c r="J95" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="K95">
         <v>67000</v>
@@ -5967,7 +5968,7 @@
         <v>250</v>
       </c>
       <c r="J96" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="K96">
         <v>39431</v>
@@ -6008,7 +6009,7 @@
         <v>252</v>
       </c>
       <c r="J97" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="K97">
         <v>34273</v>
@@ -6046,7 +6047,7 @@
         <v>73</v>
       </c>
       <c r="J98" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K98">
         <v>40000</v>
@@ -6087,7 +6088,7 @@
         <v>255</v>
       </c>
       <c r="J99" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="K99">
         <v>65000</v>
@@ -6131,7 +6132,7 @@
         <v>259</v>
       </c>
       <c r="J100" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="K100">
         <v>49000</v>
@@ -6175,7 +6176,7 @@
         <v>262</v>
       </c>
       <c r="J101" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="K101">
         <v>95000</v>
@@ -6219,7 +6220,7 @@
         <v>265</v>
       </c>
       <c r="J102" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="K102">
         <v>45000</v>
@@ -6260,7 +6261,7 @@
         <v>267</v>
       </c>
       <c r="J103" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="K103">
         <v>124500</v>
@@ -6301,7 +6302,7 @@
         <v>269</v>
       </c>
       <c r="J104" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="K104">
         <v>64000</v>
@@ -6342,7 +6343,7 @@
         <v>271</v>
       </c>
       <c r="J105" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="K105">
         <v>25000</v>
@@ -6383,7 +6384,7 @@
         <v>273</v>
       </c>
       <c r="J106" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="K106">
         <v>38498</v>
@@ -6421,7 +6422,7 @@
         <v>275</v>
       </c>
       <c r="J107" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="K107">
         <v>166433</v>
@@ -6465,7 +6466,7 @@
         <v>277</v>
       </c>
       <c r="J108" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="K108">
         <v>58000</v>
@@ -6506,7 +6507,7 @@
         <v>280</v>
       </c>
       <c r="J109" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="K109">
         <v>51872</v>
@@ -6547,7 +6548,7 @@
         <v>282</v>
       </c>
       <c r="J110" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="K110">
         <v>21632</v>
@@ -6588,7 +6589,7 @@
         <v>284</v>
       </c>
       <c r="J111" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="K111">
         <v>69000</v>
@@ -6629,7 +6630,7 @@
         <v>287</v>
       </c>
       <c r="J112" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="K112">
         <v>54000</v>
@@ -6670,7 +6671,7 @@
         <v>289</v>
       </c>
       <c r="J113" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="K113">
         <v>57400</v>
@@ -6711,7 +6712,7 @@
         <v>291</v>
       </c>
       <c r="J114" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="K114">
         <v>60000</v>
@@ -6752,7 +6753,7 @@
         <v>291</v>
       </c>
       <c r="J115" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="K115">
         <v>60000</v>
@@ -6790,7 +6791,7 @@
         <v>294</v>
       </c>
       <c r="J116" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="K116">
         <v>33000</v>
@@ -6828,7 +6829,7 @@
         <v>296</v>
       </c>
       <c r="J117" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="K117">
         <v>88786</v>
@@ -6866,7 +6867,7 @@
         <v>298</v>
       </c>
       <c r="J118" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="K118">
         <v>134000</v>
@@ -6904,7 +6905,7 @@
         <v>300</v>
       </c>
       <c r="J119" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="K119">
         <v>35000</v>
@@ -6942,7 +6943,7 @@
         <v>302</v>
       </c>
       <c r="J120" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="K120">
         <v>18000</v>
@@ -6983,7 +6984,7 @@
         <v>304</v>
       </c>
       <c r="J121" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="K121">
         <v>105741</v>
@@ -7021,7 +7022,7 @@
         <v>306</v>
       </c>
       <c r="J122" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="K122">
         <v>51000</v>
@@ -7040,7 +7041,7 @@
       <c r="A123">
         <v>122</v>
       </c>
-      <c r="B123" t="s">
+      <c r="B123" s="2" t="s">
         <v>307</v>
       </c>
       <c r="C123" t="s">
@@ -7058,11 +7059,11 @@
       <c r="H123" t="s">
         <v>207</v>
       </c>
-      <c r="I123" t="s">
-        <v>308</v>
+      <c r="I123" s="1" t="s">
+        <v>490</v>
       </c>
       <c r="J123" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="K123">
         <v>130143</v>
@@ -7082,7 +7083,7 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C124" t="s">
         <v>257</v>
@@ -7094,10 +7095,10 @@
         <v>207</v>
       </c>
       <c r="I124" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="J124" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="K124">
         <v>121551.47</v>
@@ -7117,10 +7118,10 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
+        <v>310</v>
+      </c>
+      <c r="C125" t="s">
         <v>311</v>
-      </c>
-      <c r="C125" t="s">
-        <v>312</v>
       </c>
       <c r="D125" t="s">
         <v>5</v>
@@ -7129,7 +7130,7 @@
         <v>16</v>
       </c>
       <c r="F125" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="G125" t="s">
         <v>7</v>
@@ -7138,10 +7139,10 @@
         <v>8</v>
       </c>
       <c r="I125" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="J125" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K125">
         <v>110000</v>
@@ -7161,10 +7162,10 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C126" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D126" t="s">
         <v>5</v>
@@ -7182,10 +7183,10 @@
         <v>8</v>
       </c>
       <c r="I126" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="J126" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K126">
         <v>56000</v>
@@ -7205,10 +7206,10 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C127" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D127" t="s">
         <v>5</v>
@@ -7223,10 +7224,10 @@
         <v>8</v>
       </c>
       <c r="I127" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="J127" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K127">
         <v>89177</v>
@@ -7246,10 +7247,10 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C128" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D128" t="s">
         <v>5</v>
@@ -7258,7 +7259,7 @@
         <v>23</v>
       </c>
       <c r="F128" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="G128" t="s">
         <v>7</v>
@@ -7267,10 +7268,10 @@
         <v>8</v>
       </c>
       <c r="I128" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="J128" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K128">
         <v>30000</v>
@@ -7290,10 +7291,10 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C129" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D129" t="s">
         <v>5</v>
@@ -7302,7 +7303,7 @@
         <v>16</v>
       </c>
       <c r="F129" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="G129" t="s">
         <v>7</v>
@@ -7311,10 +7312,10 @@
         <v>8</v>
       </c>
       <c r="I129" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="J129" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K129">
         <v>54550</v>
@@ -7334,10 +7335,10 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C130" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D130" t="s">
         <v>5</v>
@@ -7355,10 +7356,10 @@
         <v>8</v>
       </c>
       <c r="I130" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J130" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K130">
         <v>125000</v>
@@ -7378,10 +7379,10 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C131" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D131" t="s">
         <v>5</v>
@@ -7390,7 +7391,7 @@
         <v>16</v>
       </c>
       <c r="F131" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G131" t="s">
         <v>7</v>
@@ -7399,10 +7400,10 @@
         <v>8</v>
       </c>
       <c r="I131" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="J131" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K131">
         <v>69100</v>
@@ -7422,10 +7423,10 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C132" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D132" t="s">
         <v>5</v>
@@ -7443,10 +7444,10 @@
         <v>8</v>
       </c>
       <c r="I132" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J132" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K132">
         <v>118290</v>
@@ -7466,16 +7467,16 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
+        <v>330</v>
+      </c>
+      <c r="C133" t="s">
+        <v>311</v>
+      </c>
+      <c r="D133" t="s">
+        <v>5</v>
+      </c>
+      <c r="F133" t="s">
         <v>331</v>
-      </c>
-      <c r="C133" t="s">
-        <v>312</v>
-      </c>
-      <c r="D133" t="s">
-        <v>5</v>
-      </c>
-      <c r="F133" t="s">
-        <v>332</v>
       </c>
       <c r="G133" t="s">
         <v>7</v>
@@ -7484,10 +7485,10 @@
         <v>8</v>
       </c>
       <c r="I133" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="J133" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K133">
         <v>79900</v>
@@ -7507,10 +7508,10 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C134" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D134" t="s">
         <v>5</v>
@@ -7525,10 +7526,10 @@
         <v>8</v>
       </c>
       <c r="I134" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="J134" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K134">
         <v>39742.379999999997</v>
@@ -7548,10 +7549,10 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C135" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D135" t="s">
         <v>5</v>
@@ -7569,10 +7570,10 @@
         <v>8</v>
       </c>
       <c r="I135" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="J135" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K135">
         <v>48000</v>
@@ -7592,10 +7593,10 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C136" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D136" t="s">
         <v>14</v>
@@ -7610,10 +7611,10 @@
         <v>8</v>
       </c>
       <c r="I136" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="J136" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K136">
         <v>74722</v>
@@ -7633,10 +7634,10 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C137" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D137" t="s">
         <v>210</v>
@@ -7648,10 +7649,10 @@
         <v>8</v>
       </c>
       <c r="I137" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="J137" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="K137">
         <v>55000</v>
@@ -7671,10 +7672,10 @@
         <v>137</v>
       </c>
       <c r="B138" t="s">
+        <v>341</v>
+      </c>
+      <c r="C138" t="s">
         <v>342</v>
-      </c>
-      <c r="C138" t="s">
-        <v>343</v>
       </c>
       <c r="D138" t="s">
         <v>5</v>
@@ -7686,10 +7687,10 @@
         <v>117</v>
       </c>
       <c r="I138" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="J138" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K138">
         <v>128000</v>
@@ -7709,10 +7710,10 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C139" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D139" t="s">
         <v>5</v>
@@ -7730,10 +7731,10 @@
         <v>117</v>
       </c>
       <c r="I139" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="J139" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K139">
         <v>122000</v>
@@ -7753,10 +7754,10 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C140" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D140" t="s">
         <v>5</v>
@@ -7771,10 +7772,10 @@
         <v>117</v>
       </c>
       <c r="I140" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J140" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K140">
         <v>22000</v>
@@ -7794,10 +7795,10 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C141" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D141" t="s">
         <v>5</v>
@@ -7812,10 +7813,10 @@
         <v>117</v>
       </c>
       <c r="I141" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="J141" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K141">
         <v>10000</v>
@@ -7835,10 +7836,10 @@
         <v>141</v>
       </c>
       <c r="B142" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C142" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D142" t="s">
         <v>5</v>
@@ -7853,10 +7854,10 @@
         <v>8</v>
       </c>
       <c r="I142" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="J142" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="K142">
         <v>64000</v>
@@ -7876,10 +7877,10 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C143" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D143" t="s">
         <v>5</v>
@@ -7894,10 +7895,10 @@
         <v>8</v>
       </c>
       <c r="I143" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="J143" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="K143">
         <v>95628</v>
@@ -7917,16 +7918,16 @@
         <v>143</v>
       </c>
       <c r="B144" t="s">
+        <v>354</v>
+      </c>
+      <c r="C144" t="s">
+        <v>342</v>
+      </c>
+      <c r="D144" t="s">
+        <v>5</v>
+      </c>
+      <c r="F144" t="s">
         <v>355</v>
-      </c>
-      <c r="C144" t="s">
-        <v>343</v>
-      </c>
-      <c r="D144" t="s">
-        <v>5</v>
-      </c>
-      <c r="F144" t="s">
-        <v>356</v>
       </c>
       <c r="G144" t="s">
         <v>7</v>
@@ -7935,10 +7936,10 @@
         <v>8</v>
       </c>
       <c r="I144" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="J144" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="K144">
         <v>39562</v>
@@ -7958,10 +7959,10 @@
         <v>144</v>
       </c>
       <c r="B145" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C145" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D145" t="s">
         <v>5</v>
@@ -7970,7 +7971,7 @@
         <v>16</v>
       </c>
       <c r="F145" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G145" t="s">
         <v>7</v>
@@ -7979,10 +7980,10 @@
         <v>8</v>
       </c>
       <c r="I145" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="J145" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K145">
         <v>105000</v>
@@ -8002,10 +8003,10 @@
         <v>145</v>
       </c>
       <c r="B146" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C146" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D146" t="s">
         <v>5</v>
@@ -8014,7 +8015,7 @@
         <v>23</v>
       </c>
       <c r="F146" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G146" t="s">
         <v>7</v>
@@ -8023,10 +8024,10 @@
         <v>8</v>
       </c>
       <c r="I146" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="J146" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K146">
         <v>60000</v>
@@ -8046,10 +8047,10 @@
         <v>146</v>
       </c>
       <c r="B147" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C147" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D147" t="s">
         <v>5</v>
@@ -8064,10 +8065,10 @@
         <v>8</v>
       </c>
       <c r="I147" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="J147" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="K147">
         <v>39964</v>
@@ -8087,10 +8088,10 @@
         <v>147</v>
       </c>
       <c r="B148" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C148" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D148" t="s">
         <v>5</v>
@@ -8105,10 +8106,10 @@
         <v>8</v>
       </c>
       <c r="I148" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="J148" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K148">
         <v>94000</v>
@@ -8128,10 +8129,10 @@
         <v>148</v>
       </c>
       <c r="B149" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C149" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D149" t="s">
         <v>5</v>
@@ -8149,10 +8150,10 @@
         <v>8</v>
       </c>
       <c r="I149" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="J149" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K149">
         <v>75000</v>
@@ -8175,13 +8176,13 @@
         <v>183</v>
       </c>
       <c r="C150" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D150" t="s">
         <v>5</v>
       </c>
       <c r="F150" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G150" t="s">
         <v>7</v>
@@ -8193,7 +8194,7 @@
         <v>184</v>
       </c>
       <c r="J150" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K150">
         <v>48767</v>
@@ -8213,10 +8214,10 @@
         <v>150</v>
       </c>
       <c r="B151" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C151" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D151" t="s">
         <v>5</v>
@@ -8234,10 +8235,10 @@
         <v>8</v>
       </c>
       <c r="I151" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="J151" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K151">
         <v>63824</v>
@@ -8257,10 +8258,10 @@
         <v>151</v>
       </c>
       <c r="B152" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C152" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D152" t="s">
         <v>14</v>
@@ -8278,10 +8279,10 @@
         <v>8</v>
       </c>
       <c r="I152" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="J152" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K152">
         <v>117000</v>
@@ -8301,10 +8302,10 @@
         <v>152</v>
       </c>
       <c r="B153" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C153" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D153" t="s">
         <v>5</v>
@@ -8316,10 +8317,10 @@
         <v>8</v>
       </c>
       <c r="I153" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="J153" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K153">
         <v>41000</v>
@@ -8339,10 +8340,10 @@
         <v>153</v>
       </c>
       <c r="B154" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C154" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D154" t="s">
         <v>5</v>
@@ -8354,10 +8355,10 @@
         <v>8</v>
       </c>
       <c r="I154" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="J154" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="K154">
         <v>96446</v>
@@ -8377,10 +8378,10 @@
         <v>154</v>
       </c>
       <c r="B155" t="s">
+        <v>376</v>
+      </c>
+      <c r="C155" t="s">
         <v>377</v>
-      </c>
-      <c r="C155" t="s">
-        <v>378</v>
       </c>
       <c r="D155" t="s">
         <v>5</v>
@@ -8395,13 +8396,13 @@
         <v>7</v>
       </c>
       <c r="H155" t="s">
+        <v>378</v>
+      </c>
+      <c r="I155" t="s">
         <v>379</v>
       </c>
-      <c r="I155" t="s">
-        <v>380</v>
-      </c>
       <c r="J155" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K155">
         <v>76600</v>
@@ -8421,10 +8422,10 @@
         <v>155</v>
       </c>
       <c r="B156" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C156" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D156" t="s">
         <v>5</v>
@@ -8436,13 +8437,13 @@
         <v>7</v>
       </c>
       <c r="H156" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="I156" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="J156" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="K156">
         <v>125569</v>
@@ -8462,28 +8463,28 @@
         <v>156</v>
       </c>
       <c r="B157" t="s">
+        <v>382</v>
+      </c>
+      <c r="C157" t="s">
+        <v>377</v>
+      </c>
+      <c r="D157" t="s">
+        <v>5</v>
+      </c>
+      <c r="F157" t="s">
         <v>383</v>
       </c>
-      <c r="C157" t="s">
+      <c r="G157" t="s">
+        <v>7</v>
+      </c>
+      <c r="H157" t="s">
         <v>378</v>
       </c>
-      <c r="D157" t="s">
-        <v>5</v>
-      </c>
-      <c r="F157" t="s">
+      <c r="I157" t="s">
         <v>384</v>
       </c>
-      <c r="G157" t="s">
-        <v>7</v>
-      </c>
-      <c r="H157" t="s">
-        <v>379</v>
-      </c>
-      <c r="I157" t="s">
-        <v>385</v>
-      </c>
       <c r="J157" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K157">
         <v>51234</v>
@@ -8503,10 +8504,10 @@
         <v>157</v>
       </c>
       <c r="B158" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C158" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D158" t="s">
         <v>5</v>
@@ -8521,13 +8522,13 @@
         <v>7</v>
       </c>
       <c r="H158" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="I158" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="J158" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="K158">
         <v>123780</v>
@@ -8547,28 +8548,28 @@
         <v>158</v>
       </c>
       <c r="B159" t="s">
+        <v>387</v>
+      </c>
+      <c r="C159" t="s">
+        <v>377</v>
+      </c>
+      <c r="D159" t="s">
+        <v>5</v>
+      </c>
+      <c r="F159" t="s">
         <v>388</v>
       </c>
-      <c r="C159" t="s">
+      <c r="G159" t="s">
+        <v>7</v>
+      </c>
+      <c r="H159" t="s">
         <v>378</v>
       </c>
-      <c r="D159" t="s">
-        <v>5</v>
-      </c>
-      <c r="F159" t="s">
+      <c r="I159" t="s">
         <v>389</v>
       </c>
-      <c r="G159" t="s">
-        <v>7</v>
-      </c>
-      <c r="H159" t="s">
-        <v>379</v>
-      </c>
-      <c r="I159" t="s">
-        <v>390</v>
-      </c>
       <c r="J159" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K159">
         <v>46000</v>
@@ -8588,25 +8589,25 @@
         <v>159</v>
       </c>
       <c r="B160" t="s">
+        <v>390</v>
+      </c>
+      <c r="C160" t="s">
+        <v>377</v>
+      </c>
+      <c r="D160" t="s">
+        <v>5</v>
+      </c>
+      <c r="G160" t="s">
+        <v>7</v>
+      </c>
+      <c r="H160" t="s">
+        <v>378</v>
+      </c>
+      <c r="I160" t="s">
         <v>391</v>
       </c>
-      <c r="C160" t="s">
-        <v>378</v>
-      </c>
-      <c r="D160" t="s">
-        <v>5</v>
-      </c>
-      <c r="G160" t="s">
-        <v>7</v>
-      </c>
-      <c r="H160" t="s">
-        <v>379</v>
-      </c>
-      <c r="I160" t="s">
-        <v>392</v>
-      </c>
       <c r="J160" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K160">
         <v>35600</v>
@@ -8626,10 +8627,10 @@
         <v>160</v>
       </c>
       <c r="B161" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C161" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D161" t="s">
         <v>5</v>
@@ -8641,13 +8642,13 @@
         <v>7</v>
       </c>
       <c r="H161" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="I161" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="J161" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="K161">
         <v>199950</v>
@@ -8667,10 +8668,10 @@
         <v>161</v>
       </c>
       <c r="B162" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C162" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D162" t="s">
         <v>5</v>
@@ -8682,13 +8683,13 @@
         <v>7</v>
       </c>
       <c r="H162" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="I162" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="J162" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="K162">
         <v>108000</v>
@@ -8708,10 +8709,10 @@
         <v>162</v>
       </c>
       <c r="B163" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C163" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D163" t="s">
         <v>5</v>
@@ -8723,13 +8724,13 @@
         <v>7</v>
       </c>
       <c r="H163" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="I163" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="J163" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="K163">
         <v>142808</v>
@@ -8749,10 +8750,10 @@
         <v>163</v>
       </c>
       <c r="B164" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C164" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D164" t="s">
         <v>5</v>
@@ -8764,13 +8765,13 @@
         <v>7</v>
       </c>
       <c r="H164" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="I164" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="J164" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="K164">
         <v>80463</v>
@@ -8790,10 +8791,10 @@
         <v>164</v>
       </c>
       <c r="B165" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C165" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D165" t="s">
         <v>5</v>
@@ -8805,13 +8806,13 @@
         <v>7</v>
       </c>
       <c r="H165" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="I165" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="J165" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K165">
         <v>83000</v>
@@ -8831,25 +8832,25 @@
         <v>165</v>
       </c>
       <c r="B166" t="s">
+        <v>402</v>
+      </c>
+      <c r="C166" t="s">
+        <v>377</v>
+      </c>
+      <c r="D166" t="s">
+        <v>5</v>
+      </c>
+      <c r="G166" t="s">
+        <v>7</v>
+      </c>
+      <c r="H166" t="s">
+        <v>378</v>
+      </c>
+      <c r="I166" t="s">
         <v>403</v>
       </c>
-      <c r="C166" t="s">
-        <v>378</v>
-      </c>
-      <c r="D166" t="s">
-        <v>5</v>
-      </c>
-      <c r="G166" t="s">
-        <v>7</v>
-      </c>
-      <c r="H166" t="s">
-        <v>379</v>
-      </c>
-      <c r="I166" t="s">
-        <v>404</v>
-      </c>
       <c r="J166" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K166">
         <v>129000</v>
@@ -8869,10 +8870,10 @@
         <v>166</v>
       </c>
       <c r="B167" t="s">
+        <v>404</v>
+      </c>
+      <c r="C167" t="s">
         <v>405</v>
-      </c>
-      <c r="C167" t="s">
-        <v>406</v>
       </c>
       <c r="D167" t="s">
         <v>5</v>
@@ -8887,10 +8888,10 @@
         <v>117</v>
       </c>
       <c r="I167" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="J167" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K167">
         <v>62209</v>
@@ -8910,16 +8911,16 @@
         <v>167</v>
       </c>
       <c r="B168" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C168" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D168" t="s">
         <v>5</v>
       </c>
       <c r="F168" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="G168" t="s">
         <v>7</v>
@@ -8928,10 +8929,10 @@
         <v>8</v>
       </c>
       <c r="I168" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="J168" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="K168">
         <v>36117</v>
@@ -8951,10 +8952,10 @@
         <v>168</v>
       </c>
       <c r="B169" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C169" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D169" t="s">
         <v>5</v>
@@ -8972,10 +8973,10 @@
         <v>87</v>
       </c>
       <c r="I169" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="J169" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="K169">
         <v>49900</v>
@@ -8995,10 +8996,10 @@
         <v>169</v>
       </c>
       <c r="B170" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C170" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D170" t="s">
         <v>5</v>
@@ -9007,7 +9008,7 @@
         <v>16</v>
       </c>
       <c r="F170" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="G170" t="s">
         <v>7</v>
@@ -9016,10 +9017,10 @@
         <v>87</v>
       </c>
       <c r="I170" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="J170" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="K170">
         <v>39000</v>
@@ -9039,16 +9040,16 @@
         <v>170</v>
       </c>
       <c r="B171" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C171" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D171" t="s">
         <v>5</v>
       </c>
       <c r="F171" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="G171" t="s">
         <v>7</v>
@@ -9057,10 +9058,10 @@
         <v>207</v>
       </c>
       <c r="I171" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="J171" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="K171">
         <v>49000</v>
@@ -9080,10 +9081,10 @@
         <v>171</v>
       </c>
       <c r="B172" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C172" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D172" t="s">
         <v>210</v>
@@ -9095,10 +9096,10 @@
         <v>8</v>
       </c>
       <c r="I172" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="J172" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="K172">
         <v>59400</v>
@@ -9118,10 +9119,10 @@
         <v>172</v>
       </c>
       <c r="B173" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C173" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D173" t="s">
         <v>5</v>
@@ -9136,10 +9137,10 @@
         <v>8</v>
       </c>
       <c r="I173" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="J173" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="K173">
         <v>65000</v>
@@ -9159,31 +9160,31 @@
         <v>173</v>
       </c>
       <c r="B174" t="s">
+        <v>420</v>
+      </c>
+      <c r="C174" t="s">
+        <v>405</v>
+      </c>
+      <c r="D174" t="s">
+        <v>5</v>
+      </c>
+      <c r="E174" t="s">
+        <v>422</v>
+      </c>
+      <c r="F174" t="s">
         <v>421</v>
       </c>
-      <c r="C174" t="s">
-        <v>406</v>
-      </c>
-      <c r="D174" t="s">
-        <v>5</v>
-      </c>
-      <c r="E174" t="s">
+      <c r="G174" t="s">
+        <v>7</v>
+      </c>
+      <c r="H174" t="s">
         <v>423</v>
       </c>
-      <c r="F174" t="s">
-        <v>422</v>
-      </c>
-      <c r="G174" t="s">
-        <v>7</v>
-      </c>
-      <c r="H174" t="s">
+      <c r="I174" t="s">
         <v>424</v>
       </c>
-      <c r="I174" t="s">
-        <v>425</v>
-      </c>
       <c r="J174" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K174">
         <v>47000</v>
@@ -9203,28 +9204,28 @@
         <v>174</v>
       </c>
       <c r="B175" t="s">
+        <v>425</v>
+      </c>
+      <c r="C175" t="s">
+        <v>405</v>
+      </c>
+      <c r="D175" t="s">
+        <v>5</v>
+      </c>
+      <c r="E175" t="s">
+        <v>422</v>
+      </c>
+      <c r="G175" t="s">
+        <v>7</v>
+      </c>
+      <c r="H175" t="s">
+        <v>423</v>
+      </c>
+      <c r="I175" t="s">
         <v>426</v>
       </c>
-      <c r="C175" t="s">
-        <v>406</v>
-      </c>
-      <c r="D175" t="s">
-        <v>5</v>
-      </c>
-      <c r="E175" t="s">
-        <v>423</v>
-      </c>
-      <c r="G175" t="s">
-        <v>7</v>
-      </c>
-      <c r="H175" t="s">
-        <v>424</v>
-      </c>
-      <c r="I175" t="s">
-        <v>427</v>
-      </c>
       <c r="J175" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K175">
         <v>29000</v>
@@ -9244,10 +9245,10 @@
         <v>175</v>
       </c>
       <c r="B176" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C176" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D176" t="s">
         <v>5</v>
@@ -9265,10 +9266,10 @@
         <v>87</v>
       </c>
       <c r="I176" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="J176" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K176">
         <v>132239</v>
@@ -9288,10 +9289,10 @@
         <v>176</v>
       </c>
       <c r="B177" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C177" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D177" t="s">
         <v>5</v>
@@ -9303,13 +9304,13 @@
         <v>7</v>
       </c>
       <c r="H177" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="I177" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="J177" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K177">
         <v>35016</v>
@@ -9329,10 +9330,10 @@
         <v>177</v>
       </c>
       <c r="B178" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C178" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D178" t="s">
         <v>5</v>
@@ -9344,10 +9345,10 @@
         <v>87</v>
       </c>
       <c r="I178" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="J178" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K178">
         <v>60000</v>
@@ -9367,28 +9368,28 @@
         <v>178</v>
       </c>
       <c r="B179" t="s">
+        <v>433</v>
+      </c>
+      <c r="C179" t="s">
+        <v>405</v>
+      </c>
+      <c r="D179" t="s">
+        <v>5</v>
+      </c>
+      <c r="F179" t="s">
         <v>434</v>
       </c>
-      <c r="C179" t="s">
-        <v>406</v>
-      </c>
-      <c r="D179" t="s">
-        <v>5</v>
-      </c>
-      <c r="F179" t="s">
+      <c r="G179" t="s">
+        <v>7</v>
+      </c>
+      <c r="H179" t="s">
+        <v>378</v>
+      </c>
+      <c r="I179" t="s">
         <v>435</v>
       </c>
-      <c r="G179" t="s">
-        <v>7</v>
-      </c>
-      <c r="H179" t="s">
-        <v>379</v>
-      </c>
-      <c r="I179" t="s">
-        <v>436</v>
-      </c>
       <c r="J179" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="K179">
         <v>90244</v>
@@ -9408,25 +9409,25 @@
         <v>179</v>
       </c>
       <c r="B180" t="s">
+        <v>436</v>
+      </c>
+      <c r="C180" t="s">
+        <v>405</v>
+      </c>
+      <c r="D180" t="s">
+        <v>5</v>
+      </c>
+      <c r="G180" t="s">
+        <v>7</v>
+      </c>
+      <c r="H180" t="s">
+        <v>378</v>
+      </c>
+      <c r="I180" t="s">
         <v>437</v>
       </c>
-      <c r="C180" t="s">
-        <v>406</v>
-      </c>
-      <c r="D180" t="s">
-        <v>5</v>
-      </c>
-      <c r="G180" t="s">
-        <v>7</v>
-      </c>
-      <c r="H180" t="s">
-        <v>379</v>
-      </c>
-      <c r="I180" t="s">
-        <v>438</v>
-      </c>
       <c r="J180" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K180">
         <v>38700</v>
@@ -9446,25 +9447,25 @@
         <v>180</v>
       </c>
       <c r="B181" t="s">
+        <v>438</v>
+      </c>
+      <c r="C181" t="s">
+        <v>405</v>
+      </c>
+      <c r="D181" t="s">
+        <v>5</v>
+      </c>
+      <c r="G181" t="s">
+        <v>7</v>
+      </c>
+      <c r="H181" t="s">
+        <v>378</v>
+      </c>
+      <c r="I181" t="s">
         <v>439</v>
       </c>
-      <c r="C181" t="s">
-        <v>406</v>
-      </c>
-      <c r="D181" t="s">
-        <v>5</v>
-      </c>
-      <c r="G181" t="s">
-        <v>7</v>
-      </c>
-      <c r="H181" t="s">
-        <v>379</v>
-      </c>
-      <c r="I181" t="s">
-        <v>440</v>
-      </c>
       <c r="J181" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="K181">
         <v>62414</v>
@@ -9484,25 +9485,25 @@
         <v>181</v>
       </c>
       <c r="B182" t="s">
+        <v>440</v>
+      </c>
+      <c r="C182" t="s">
+        <v>405</v>
+      </c>
+      <c r="D182" t="s">
+        <v>5</v>
+      </c>
+      <c r="G182" t="s">
+        <v>7</v>
+      </c>
+      <c r="H182" t="s">
+        <v>423</v>
+      </c>
+      <c r="I182" t="s">
         <v>441</v>
       </c>
-      <c r="C182" t="s">
-        <v>406</v>
-      </c>
-      <c r="D182" t="s">
-        <v>5</v>
-      </c>
-      <c r="G182" t="s">
-        <v>7</v>
-      </c>
-      <c r="H182" t="s">
-        <v>424</v>
-      </c>
-      <c r="I182" t="s">
-        <v>442</v>
-      </c>
       <c r="J182" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K182">
         <v>51000</v>
@@ -9522,10 +9523,10 @@
         <v>182</v>
       </c>
       <c r="B183" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C183" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D183" t="s">
         <v>5</v>
@@ -9540,10 +9541,10 @@
         <v>87</v>
       </c>
       <c r="I183" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="J183" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K183">
         <v>53115</v>
@@ -9563,25 +9564,25 @@
         <v>183</v>
       </c>
       <c r="B184" t="s">
+        <v>444</v>
+      </c>
+      <c r="C184" t="s">
+        <v>405</v>
+      </c>
+      <c r="D184" t="s">
+        <v>5</v>
+      </c>
+      <c r="G184" t="s">
+        <v>7</v>
+      </c>
+      <c r="H184" t="s">
+        <v>378</v>
+      </c>
+      <c r="I184" t="s">
         <v>445</v>
       </c>
-      <c r="C184" t="s">
-        <v>406</v>
-      </c>
-      <c r="D184" t="s">
-        <v>5</v>
-      </c>
-      <c r="G184" t="s">
-        <v>7</v>
-      </c>
-      <c r="H184" t="s">
-        <v>379</v>
-      </c>
-      <c r="I184" t="s">
-        <v>446</v>
-      </c>
       <c r="J184" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K184">
         <v>120000</v>
@@ -9601,10 +9602,10 @@
         <v>184</v>
       </c>
       <c r="B185" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C185" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D185" t="s">
         <v>5</v>
@@ -9619,10 +9620,10 @@
         <v>87</v>
       </c>
       <c r="I185" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="J185" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K185">
         <v>66477</v>
@@ -9642,10 +9643,10 @@
         <v>185</v>
       </c>
       <c r="B186" t="s">
+        <v>448</v>
+      </c>
+      <c r="C186" t="s">
         <v>449</v>
-      </c>
-      <c r="C186" t="s">
-        <v>450</v>
       </c>
       <c r="D186" t="s">
         <v>5</v>
@@ -9657,10 +9658,10 @@
         <v>7</v>
       </c>
       <c r="H186" t="s">
+        <v>450</v>
+      </c>
+      <c r="I186" t="s">
         <v>451</v>
-      </c>
-      <c r="I186" t="s">
-        <v>452</v>
       </c>
       <c r="K186">
         <v>59300</v>
@@ -9680,22 +9681,22 @@
         <v>186</v>
       </c>
       <c r="B187" t="s">
+        <v>452</v>
+      </c>
+      <c r="C187" t="s">
+        <v>449</v>
+      </c>
+      <c r="D187" t="s">
+        <v>5</v>
+      </c>
+      <c r="G187" t="s">
+        <v>7</v>
+      </c>
+      <c r="H187" t="s">
+        <v>450</v>
+      </c>
+      <c r="I187" t="s">
         <v>453</v>
-      </c>
-      <c r="C187" t="s">
-        <v>450</v>
-      </c>
-      <c r="D187" t="s">
-        <v>5</v>
-      </c>
-      <c r="G187" t="s">
-        <v>7</v>
-      </c>
-      <c r="H187" t="s">
-        <v>451</v>
-      </c>
-      <c r="I187" t="s">
-        <v>454</v>
       </c>
       <c r="K187">
         <v>44000</v>
@@ -9715,22 +9716,22 @@
         <v>187</v>
       </c>
       <c r="B188" t="s">
+        <v>454</v>
+      </c>
+      <c r="C188" t="s">
+        <v>449</v>
+      </c>
+      <c r="D188" t="s">
+        <v>5</v>
+      </c>
+      <c r="G188" t="s">
+        <v>7</v>
+      </c>
+      <c r="H188" t="s">
+        <v>450</v>
+      </c>
+      <c r="I188" t="s">
         <v>455</v>
-      </c>
-      <c r="C188" t="s">
-        <v>450</v>
-      </c>
-      <c r="D188" t="s">
-        <v>5</v>
-      </c>
-      <c r="G188" t="s">
-        <v>7</v>
-      </c>
-      <c r="H188" t="s">
-        <v>451</v>
-      </c>
-      <c r="I188" t="s">
-        <v>456</v>
       </c>
       <c r="K188">
         <v>26528</v>
@@ -9750,10 +9751,10 @@
         <v>188</v>
       </c>
       <c r="B189" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C189" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="D189" t="s">
         <v>5</v>
@@ -9765,10 +9766,10 @@
         <v>7</v>
       </c>
       <c r="H189" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="I189" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K189">
         <v>95684</v>
@@ -9788,10 +9789,10 @@
         <v>189</v>
       </c>
       <c r="B190" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C190" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="D190" t="s">
         <v>5</v>
@@ -9823,10 +9824,10 @@
         <v>190</v>
       </c>
       <c r="B191" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C191" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="D191" t="s">
         <v>5</v>
@@ -9838,10 +9839,10 @@
         <v>7</v>
       </c>
       <c r="H191" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="I191" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="K191">
         <v>60000</v>
@@ -9861,22 +9862,22 @@
         <v>191</v>
       </c>
       <c r="B192" t="s">
+        <v>461</v>
+      </c>
+      <c r="C192" t="s">
+        <v>449</v>
+      </c>
+      <c r="D192" t="s">
+        <v>5</v>
+      </c>
+      <c r="G192" t="s">
+        <v>7</v>
+      </c>
+      <c r="H192" t="s">
+        <v>450</v>
+      </c>
+      <c r="I192" t="s">
         <v>462</v>
-      </c>
-      <c r="C192" t="s">
-        <v>450</v>
-      </c>
-      <c r="D192" t="s">
-        <v>5</v>
-      </c>
-      <c r="G192" t="s">
-        <v>7</v>
-      </c>
-      <c r="H192" t="s">
-        <v>451</v>
-      </c>
-      <c r="I192" t="s">
-        <v>463</v>
       </c>
       <c r="K192">
         <v>34895</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yuhang/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F864998-EBAA-264A-A418-BB1E38A02A7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4DA1E64-0579-D14E-B177-65A9FD024ADB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1577" uniqueCount="491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1577" uniqueCount="492">
   <si>
     <t>所在市</t>
   </si>
@@ -587,9 +587,6 @@
     <t>中海国际中心</t>
   </si>
   <si>
-    <t>116.357257,39.931640</t>
-  </si>
-  <si>
     <t>泰康国际大厦</t>
   </si>
   <si>
@@ -959,12 +956,6 @@
     <t>中关村东升科技园三期（东畔创新中心）</t>
   </si>
   <si>
-    <t>学院路科技园东升园</t>
-  </si>
-  <si>
-    <t>116.333038,39.990445</t>
-  </si>
-  <si>
     <t>利星行广场（一期）</t>
   </si>
   <si>
@@ -1115,12 +1106,6 @@
     <t>116.386738,39.989441</t>
   </si>
   <si>
-    <t>奥南五号-A座（天圆祥泰大厦）</t>
-  </si>
-  <si>
-    <t>116.406387,39.981515</t>
-  </si>
-  <si>
     <t>招商局广场（外运大厦A座）</t>
   </si>
   <si>
@@ -1131,9 +1116,6 @@
   </si>
   <si>
     <t>116.406354,39.979452</t>
-  </si>
-  <si>
-    <t>奥南五号-B座（恒毅大厦）</t>
   </si>
   <si>
     <t>2017 Q4</t>
@@ -1515,6 +1497,34 @@
   </si>
   <si>
     <t>116.365799,40.001522</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>中关村东升科技园·学北园</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>116.352247,40.015235</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>116.349697,39.932894</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>奥南五号-B座（恒毅大厦）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>奥南五号-A座（天圆祥泰大厦）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>116.406387,39.981515</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>116.406387,39.980615</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1562,12 +1572,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -1585,10 +1601,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1920,22 +1937,22 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="B1" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="C1" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="D1" t="s">
+        <v>466</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>478</v>
-      </c>
       <c r="F1" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="G1" t="s">
         <v>0</v>
@@ -1947,19 +1964,19 @@
         <v>2</v>
       </c>
       <c r="J1" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="K1" t="s">
+        <v>463</v>
+      </c>
+      <c r="L1" t="s">
         <v>469</v>
       </c>
-      <c r="L1" t="s">
-        <v>475</v>
-      </c>
       <c r="M1" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="N1" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -1988,7 +2005,7 @@
         <v>9</v>
       </c>
       <c r="J2" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="K2">
         <v>72308</v>
@@ -2029,7 +2046,7 @@
         <v>12</v>
       </c>
       <c r="J3" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="K3">
         <v>72308</v>
@@ -2073,7 +2090,7 @@
         <v>17</v>
       </c>
       <c r="J4" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="K4">
         <v>130769</v>
@@ -2117,7 +2134,7 @@
         <v>20</v>
       </c>
       <c r="J5" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="K5">
         <v>64615</v>
@@ -2161,7 +2178,7 @@
         <v>24</v>
       </c>
       <c r="J6" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="K6">
         <v>80091</v>
@@ -2202,7 +2219,7 @@
         <v>27</v>
       </c>
       <c r="J7" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="K7">
         <v>70673</v>
@@ -2246,7 +2263,7 @@
         <v>30</v>
       </c>
       <c r="J8" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="K8">
         <v>90466</v>
@@ -2287,7 +2304,7 @@
         <v>32</v>
       </c>
       <c r="J9" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="K9">
         <v>46720</v>
@@ -2331,7 +2348,7 @@
         <v>35</v>
       </c>
       <c r="J10" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="K10">
         <v>95000</v>
@@ -2375,7 +2392,7 @@
         <v>38</v>
       </c>
       <c r="J11" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="K11">
         <v>85300</v>
@@ -2419,7 +2436,7 @@
         <v>41</v>
       </c>
       <c r="J12" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="K12">
         <v>33305</v>
@@ -2463,7 +2480,7 @@
         <v>43</v>
       </c>
       <c r="J13" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="K13">
         <v>120245.21</v>
@@ -2507,7 +2524,7 @@
         <v>43</v>
       </c>
       <c r="J14" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="K14">
         <v>70425.53</v>
@@ -2551,7 +2568,7 @@
         <v>47</v>
       </c>
       <c r="J15" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="K15">
         <v>78000</v>
@@ -2595,7 +2612,7 @@
         <v>50</v>
       </c>
       <c r="J16" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="K16">
         <v>102796</v>
@@ -2639,7 +2656,7 @@
         <v>52</v>
       </c>
       <c r="J17" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="K17">
         <v>49200</v>
@@ -2683,7 +2700,7 @@
         <v>54</v>
       </c>
       <c r="J18" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="K18">
         <v>65096</v>
@@ -2727,7 +2744,7 @@
         <v>57</v>
       </c>
       <c r="J19" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="K19">
         <v>56000</v>
@@ -2771,7 +2788,7 @@
         <v>60</v>
       </c>
       <c r="J20" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="K20">
         <v>177847</v>
@@ -2815,7 +2832,7 @@
         <v>63</v>
       </c>
       <c r="J21" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="K21">
         <v>83000</v>
@@ -2856,7 +2873,7 @@
         <v>66</v>
       </c>
       <c r="J22" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="K22">
         <v>26000</v>
@@ -2897,7 +2914,7 @@
         <v>68</v>
       </c>
       <c r="J23" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="K23">
         <v>85887</v>
@@ -2938,7 +2955,7 @@
         <v>70</v>
       </c>
       <c r="J24" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="K24">
         <v>20000</v>
@@ -2982,7 +2999,7 @@
         <v>73</v>
       </c>
       <c r="J25" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="K25">
         <v>146385</v>
@@ -3026,7 +3043,7 @@
         <v>76</v>
       </c>
       <c r="J26" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="K26">
         <v>87000</v>
@@ -3070,7 +3087,7 @@
         <v>79</v>
       </c>
       <c r="J27" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="K27">
         <v>147166.79999999999</v>
@@ -3114,7 +3131,7 @@
         <v>82</v>
       </c>
       <c r="J28" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="K28">
         <v>46063</v>
@@ -3158,7 +3175,7 @@
         <v>85</v>
       </c>
       <c r="J29" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="K29">
         <v>47261</v>
@@ -3178,7 +3195,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="C30" t="s">
         <v>4</v>
@@ -3196,13 +3213,13 @@
         <v>7</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="J30" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="K30">
         <v>119000</v>
@@ -3243,7 +3260,7 @@
         <v>91</v>
       </c>
       <c r="J31" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="K31">
         <v>47000</v>
@@ -3287,7 +3304,7 @@
         <v>93</v>
       </c>
       <c r="J32" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="K32">
         <v>186000</v>
@@ -3325,7 +3342,7 @@
         <v>95</v>
       </c>
       <c r="J33" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="K33">
         <v>40800</v>
@@ -3366,7 +3383,7 @@
         <v>95</v>
       </c>
       <c r="J34" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="K34">
         <v>55200</v>
@@ -3410,7 +3427,7 @@
         <v>99</v>
       </c>
       <c r="J35" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="K35">
         <v>350000</v>
@@ -3451,7 +3468,7 @@
         <v>101</v>
       </c>
       <c r="J36" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="K36">
         <v>65000</v>
@@ -3492,7 +3509,7 @@
         <v>101</v>
       </c>
       <c r="J37" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="K37">
         <v>35000</v>
@@ -3533,7 +3550,7 @@
         <v>104</v>
       </c>
       <c r="J38" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="K38">
         <v>47000</v>
@@ -3577,7 +3594,7 @@
         <v>107</v>
       </c>
       <c r="J39" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="K39">
         <v>120000</v>
@@ -3618,7 +3635,7 @@
         <v>109</v>
       </c>
       <c r="J40" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="K40">
         <v>83000</v>
@@ -3659,7 +3676,7 @@
         <v>111</v>
       </c>
       <c r="J41" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="K41">
         <v>66030</v>
@@ -3697,7 +3714,7 @@
         <v>113</v>
       </c>
       <c r="J42" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="K42">
         <v>40000</v>
@@ -3741,7 +3758,7 @@
         <v>118</v>
       </c>
       <c r="J43" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="K43">
         <v>40000</v>
@@ -3782,7 +3799,7 @@
         <v>121</v>
       </c>
       <c r="J44" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="K44">
         <v>54100</v>
@@ -3823,10 +3840,10 @@
         <v>117</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="J45" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="K45">
         <v>100000</v>
@@ -3867,10 +3884,10 @@
         <v>117</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="J46" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="K46">
         <v>150000</v>
@@ -3911,10 +3928,10 @@
         <v>117</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="J47" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="K47">
         <v>50000</v>
@@ -3958,7 +3975,7 @@
         <v>130</v>
       </c>
       <c r="J48" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="K48">
         <v>43000</v>
@@ -3999,7 +4016,7 @@
         <v>133</v>
       </c>
       <c r="J49" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="K49">
         <v>65000</v>
@@ -4040,7 +4057,7 @@
         <v>136</v>
       </c>
       <c r="J50" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
     </row>
     <row r="51" spans="1:14">
@@ -4072,7 +4089,7 @@
         <v>138</v>
       </c>
       <c r="J51" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="K51">
         <v>56000</v>
@@ -4113,7 +4130,7 @@
         <v>140</v>
       </c>
       <c r="J52" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="K52">
         <v>160000</v>
@@ -4154,7 +4171,7 @@
         <v>142</v>
       </c>
       <c r="J53" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="K53">
         <v>33000</v>
@@ -4198,7 +4215,7 @@
         <v>145</v>
       </c>
       <c r="J54" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="K54">
         <v>41318</v>
@@ -4239,7 +4256,7 @@
         <v>147</v>
       </c>
       <c r="J55" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="K55">
         <v>34131</v>
@@ -4280,7 +4297,7 @@
         <v>150</v>
       </c>
       <c r="J56" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="K56">
         <v>48000</v>
@@ -4321,7 +4338,7 @@
         <v>118</v>
       </c>
       <c r="J57" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="K57">
         <v>16000</v>
@@ -4365,7 +4382,7 @@
         <v>154</v>
       </c>
       <c r="J58" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="K58">
         <v>30000</v>
@@ -4409,7 +4426,7 @@
         <v>157</v>
       </c>
       <c r="J59" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="K59">
         <v>56000</v>
@@ -4453,7 +4470,7 @@
         <v>160</v>
       </c>
       <c r="J60" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="K60">
         <v>43000</v>
@@ -4494,7 +4511,7 @@
         <v>162</v>
       </c>
       <c r="J61" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="K61">
         <v>110000</v>
@@ -4532,7 +4549,7 @@
         <v>164</v>
       </c>
       <c r="J62" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="K62">
         <v>56160</v>
@@ -4573,7 +4590,7 @@
         <v>166</v>
       </c>
       <c r="J63" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="K63">
         <v>138444</v>
@@ -4617,7 +4634,7 @@
         <v>170</v>
       </c>
       <c r="J64" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="K64">
         <v>31000</v>
@@ -4658,7 +4675,7 @@
         <v>173</v>
       </c>
       <c r="J65" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="K65">
         <v>120000</v>
@@ -4699,7 +4716,7 @@
         <v>175</v>
       </c>
       <c r="J66" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="K66">
         <v>25900</v>
@@ -4740,7 +4757,7 @@
         <v>178</v>
       </c>
       <c r="J67" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="K67">
         <v>47986</v>
@@ -4784,7 +4801,7 @@
         <v>180</v>
       </c>
       <c r="J68" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="K68">
         <v>194000</v>
@@ -4828,7 +4845,7 @@
         <v>182</v>
       </c>
       <c r="J69" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="K69">
         <v>39724</v>
@@ -4865,11 +4882,11 @@
       <c r="H70" t="s">
         <v>87</v>
       </c>
-      <c r="I70" t="s">
-        <v>184</v>
+      <c r="I70" s="1" t="s">
+        <v>487</v>
       </c>
       <c r="J70" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="K70">
         <v>48437.45</v>
@@ -4889,7 +4906,7 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C71" t="s">
         <v>168</v>
@@ -4898,7 +4915,7 @@
         <v>5</v>
       </c>
       <c r="F71" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G71" t="s">
         <v>7</v>
@@ -4907,10 +4924,10 @@
         <v>87</v>
       </c>
       <c r="I71" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="J71" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="K71">
         <v>37910</v>
@@ -4930,7 +4947,7 @@
         <v>71</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="C72" t="s">
         <v>168</v>
@@ -4939,7 +4956,7 @@
         <v>5</v>
       </c>
       <c r="F72" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G72" t="s">
         <v>7</v>
@@ -4948,10 +4965,10 @@
         <v>87</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="J72" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="K72">
         <v>21220</v>
@@ -4971,7 +4988,7 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C73" t="s">
         <v>168</v>
@@ -4989,10 +5006,10 @@
         <v>87</v>
       </c>
       <c r="I73" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="J73" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="K73">
         <v>77877</v>
@@ -5012,7 +5029,7 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C74" t="s">
         <v>168</v>
@@ -5033,10 +5050,10 @@
         <v>87</v>
       </c>
       <c r="I74" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="J74" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="K74">
         <v>80311.53</v>
@@ -5056,7 +5073,7 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C75" t="s">
         <v>168</v>
@@ -5068,7 +5085,7 @@
         <v>23</v>
       </c>
       <c r="F75" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G75" t="s">
         <v>7</v>
@@ -5077,10 +5094,10 @@
         <v>87</v>
       </c>
       <c r="I75" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="J75" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="K75">
         <v>38000</v>
@@ -5100,7 +5117,7 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C76" t="s">
         <v>168</v>
@@ -5109,7 +5126,7 @@
         <v>5</v>
       </c>
       <c r="F76" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G76" t="s">
         <v>7</v>
@@ -5118,10 +5135,10 @@
         <v>87</v>
       </c>
       <c r="I76" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J76" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="K76">
         <v>37800</v>
@@ -5141,7 +5158,7 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C77" t="s">
         <v>168</v>
@@ -5153,7 +5170,7 @@
         <v>16</v>
       </c>
       <c r="F77" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G77" t="s">
         <v>7</v>
@@ -5162,10 +5179,10 @@
         <v>87</v>
       </c>
       <c r="I77" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="J77" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="K77">
         <v>54581</v>
@@ -5185,7 +5202,7 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C78" t="s">
         <v>168</v>
@@ -5197,7 +5214,7 @@
         <v>16</v>
       </c>
       <c r="F78" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G78" t="s">
         <v>7</v>
@@ -5209,7 +5226,7 @@
         <v>88</v>
       </c>
       <c r="J78" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="K78">
         <v>25000</v>
@@ -5229,7 +5246,7 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C79" t="s">
         <v>168</v>
@@ -5250,10 +5267,10 @@
         <v>87</v>
       </c>
       <c r="I79" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="J79" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="K79">
         <v>52698</v>
@@ -5273,7 +5290,7 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C80" t="s">
         <v>168</v>
@@ -5282,19 +5299,19 @@
         <v>5</v>
       </c>
       <c r="F80" t="s">
+        <v>205</v>
+      </c>
+      <c r="G80" t="s">
+        <v>7</v>
+      </c>
+      <c r="H80" t="s">
         <v>206</v>
       </c>
-      <c r="G80" t="s">
-        <v>7</v>
-      </c>
-      <c r="H80" t="s">
+      <c r="I80" t="s">
         <v>207</v>
       </c>
-      <c r="I80" t="s">
-        <v>208</v>
-      </c>
       <c r="J80" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="K80">
         <v>38500</v>
@@ -5314,13 +5331,13 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C81" t="s">
         <v>168</v>
       </c>
       <c r="D81" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G81" t="s">
         <v>7</v>
@@ -5329,10 +5346,10 @@
         <v>87</v>
       </c>
       <c r="I81" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J81" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="K81">
         <v>27200</v>
@@ -5352,7 +5369,7 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C82" t="s">
         <v>144</v>
@@ -5364,7 +5381,7 @@
         <v>16</v>
       </c>
       <c r="F82" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G82" t="s">
         <v>7</v>
@@ -5373,10 +5390,10 @@
         <v>8</v>
       </c>
       <c r="I82" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="J82" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="K82">
         <v>60000</v>
@@ -5396,7 +5413,7 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C83" t="s">
         <v>144</v>
@@ -5405,7 +5422,7 @@
         <v>5</v>
       </c>
       <c r="F83" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G83" t="s">
         <v>7</v>
@@ -5414,10 +5431,10 @@
         <v>8</v>
       </c>
       <c r="I83" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="J83" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="K83">
         <v>50000</v>
@@ -5437,7 +5454,7 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C84" t="s">
         <v>144</v>
@@ -5458,10 +5475,10 @@
         <v>8</v>
       </c>
       <c r="I84" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="J84" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="K84">
         <v>131575</v>
@@ -5481,7 +5498,7 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C85" t="s">
         <v>144</v>
@@ -5499,10 +5516,10 @@
         <v>8</v>
       </c>
       <c r="I85" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="J85" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="K85">
         <v>99500</v>
@@ -5522,7 +5539,7 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C86" t="s">
         <v>144</v>
@@ -5531,7 +5548,7 @@
         <v>5</v>
       </c>
       <c r="F86" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G86" t="s">
         <v>7</v>
@@ -5540,10 +5557,10 @@
         <v>8</v>
       </c>
       <c r="I86" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="J86" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="K86">
         <v>32000</v>
@@ -5563,7 +5580,7 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C87" t="s">
         <v>144</v>
@@ -5575,7 +5592,7 @@
         <v>23</v>
       </c>
       <c r="F87" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G87" t="s">
         <v>7</v>
@@ -5584,10 +5601,10 @@
         <v>8</v>
       </c>
       <c r="I87" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="J87" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="K87">
         <v>52170</v>
@@ -5607,7 +5624,7 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C88" t="s">
         <v>144</v>
@@ -5616,7 +5633,7 @@
         <v>5</v>
       </c>
       <c r="F88" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G88" t="s">
         <v>7</v>
@@ -5625,10 +5642,10 @@
         <v>8</v>
       </c>
       <c r="I88" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="J88" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="K88">
         <v>46000</v>
@@ -5648,7 +5665,7 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C89" t="s">
         <v>144</v>
@@ -5660,7 +5677,7 @@
         <v>23</v>
       </c>
       <c r="F89" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G89" t="s">
         <v>7</v>
@@ -5669,10 +5686,10 @@
         <v>8</v>
       </c>
       <c r="I89" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="J89" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="K89">
         <v>45013</v>
@@ -5692,7 +5709,7 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C90" t="s">
         <v>144</v>
@@ -5710,10 +5727,10 @@
         <v>8</v>
       </c>
       <c r="I90" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J90" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="K90">
         <v>48566</v>
@@ -5733,7 +5750,7 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C91" t="s">
         <v>144</v>
@@ -5742,7 +5759,7 @@
         <v>5</v>
       </c>
       <c r="F91" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G91" t="s">
         <v>7</v>
@@ -5751,10 +5768,10 @@
         <v>8</v>
       </c>
       <c r="I91" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J91" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="K91">
         <v>55618</v>
@@ -5774,7 +5791,7 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C92" t="s">
         <v>144</v>
@@ -5783,7 +5800,7 @@
         <v>5</v>
       </c>
       <c r="F92" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G92" t="s">
         <v>7</v>
@@ -5792,10 +5809,10 @@
         <v>8</v>
       </c>
       <c r="I92" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="J92" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="K92">
         <v>47000</v>
@@ -5815,7 +5832,7 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C93" t="s">
         <v>144</v>
@@ -5827,7 +5844,7 @@
         <v>23</v>
       </c>
       <c r="F93" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G93" t="s">
         <v>7</v>
@@ -5836,10 +5853,10 @@
         <v>8</v>
       </c>
       <c r="I93" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J93" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="K93">
         <v>87763</v>
@@ -5859,7 +5876,7 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C94" t="s">
         <v>144</v>
@@ -5871,7 +5888,7 @@
         <v>16</v>
       </c>
       <c r="F94" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G94" t="s">
         <v>7</v>
@@ -5880,10 +5897,10 @@
         <v>8</v>
       </c>
       <c r="I94" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="J94" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="K94">
         <v>100658</v>
@@ -5903,7 +5920,7 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C95" t="s">
         <v>144</v>
@@ -5912,7 +5929,7 @@
         <v>5</v>
       </c>
       <c r="F95" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G95" t="s">
         <v>7</v>
@@ -5921,10 +5938,10 @@
         <v>8</v>
       </c>
       <c r="I95" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="J95" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="K95">
         <v>67000</v>
@@ -5944,7 +5961,7 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C96" t="s">
         <v>144</v>
@@ -5965,10 +5982,10 @@
         <v>8</v>
       </c>
       <c r="I96" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="J96" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="K96">
         <v>39431</v>
@@ -5988,7 +6005,7 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C97" t="s">
         <v>144</v>
@@ -6006,10 +6023,10 @@
         <v>8</v>
       </c>
       <c r="I97" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="J97" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="K97">
         <v>34273</v>
@@ -6029,7 +6046,7 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C98" t="s">
         <v>144</v>
@@ -6047,7 +6064,7 @@
         <v>73</v>
       </c>
       <c r="J98" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="K98">
         <v>40000</v>
@@ -6067,7 +6084,7 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C99" t="s">
         <v>144</v>
@@ -6085,10 +6102,10 @@
         <v>8</v>
       </c>
       <c r="I99" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="J99" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="K99">
         <v>65000</v>
@@ -6108,10 +6125,10 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
+        <v>255</v>
+      </c>
+      <c r="C100" t="s">
         <v>256</v>
-      </c>
-      <c r="C100" t="s">
-        <v>257</v>
       </c>
       <c r="D100" t="s">
         <v>5</v>
@@ -6120,19 +6137,19 @@
         <v>23</v>
       </c>
       <c r="F100" t="s">
+        <v>257</v>
+      </c>
+      <c r="G100" t="s">
+        <v>7</v>
+      </c>
+      <c r="H100" t="s">
+        <v>206</v>
+      </c>
+      <c r="I100" t="s">
         <v>258</v>
       </c>
-      <c r="G100" t="s">
-        <v>7</v>
-      </c>
-      <c r="H100" t="s">
-        <v>207</v>
-      </c>
-      <c r="I100" t="s">
-        <v>259</v>
-      </c>
       <c r="J100" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="K100">
         <v>49000</v>
@@ -6152,10 +6169,10 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C101" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D101" t="s">
         <v>14</v>
@@ -6164,19 +6181,19 @@
         <v>23</v>
       </c>
       <c r="F101" t="s">
+        <v>260</v>
+      </c>
+      <c r="G101" t="s">
+        <v>7</v>
+      </c>
+      <c r="H101" t="s">
+        <v>206</v>
+      </c>
+      <c r="I101" t="s">
         <v>261</v>
       </c>
-      <c r="G101" t="s">
-        <v>7</v>
-      </c>
-      <c r="H101" t="s">
-        <v>207</v>
-      </c>
-      <c r="I101" t="s">
-        <v>262</v>
-      </c>
       <c r="J101" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="K101">
         <v>95000</v>
@@ -6196,10 +6213,10 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C102" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D102" t="s">
         <v>5</v>
@@ -6208,19 +6225,19 @@
         <v>23</v>
       </c>
       <c r="F102" t="s">
+        <v>263</v>
+      </c>
+      <c r="G102" t="s">
+        <v>7</v>
+      </c>
+      <c r="H102" t="s">
+        <v>206</v>
+      </c>
+      <c r="I102" t="s">
         <v>264</v>
       </c>
-      <c r="G102" t="s">
-        <v>7</v>
-      </c>
-      <c r="H102" t="s">
-        <v>207</v>
-      </c>
-      <c r="I102" t="s">
-        <v>265</v>
-      </c>
       <c r="J102" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="K102">
         <v>45000</v>
@@ -6240,10 +6257,10 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C103" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D103" t="s">
         <v>5</v>
@@ -6255,13 +6272,13 @@
         <v>7</v>
       </c>
       <c r="H103" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I103" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="J103" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="K103">
         <v>124500</v>
@@ -6281,10 +6298,10 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C104" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D104" t="s">
         <v>5</v>
@@ -6296,13 +6313,13 @@
         <v>7</v>
       </c>
       <c r="H104" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I104" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="J104" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="K104">
         <v>64000</v>
@@ -6322,10 +6339,10 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C105" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D105" t="s">
         <v>5</v>
@@ -6337,13 +6354,13 @@
         <v>7</v>
       </c>
       <c r="H105" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I105" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="J105" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="K105">
         <v>25000</v>
@@ -6363,10 +6380,10 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C106" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D106" t="s">
         <v>5</v>
@@ -6378,13 +6395,13 @@
         <v>7</v>
       </c>
       <c r="H106" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I106" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="J106" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="K106">
         <v>38498</v>
@@ -6404,25 +6421,25 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
+        <v>273</v>
+      </c>
+      <c r="C107" t="s">
+        <v>256</v>
+      </c>
+      <c r="D107" t="s">
+        <v>209</v>
+      </c>
+      <c r="G107" t="s">
+        <v>7</v>
+      </c>
+      <c r="H107" t="s">
+        <v>206</v>
+      </c>
+      <c r="I107" t="s">
         <v>274</v>
       </c>
-      <c r="C107" t="s">
-        <v>257</v>
-      </c>
-      <c r="D107" t="s">
-        <v>210</v>
-      </c>
-      <c r="G107" t="s">
-        <v>7</v>
-      </c>
-      <c r="H107" t="s">
-        <v>207</v>
-      </c>
-      <c r="I107" t="s">
-        <v>275</v>
-      </c>
       <c r="J107" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="K107">
         <v>166433</v>
@@ -6442,10 +6459,10 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C108" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D108" t="s">
         <v>14</v>
@@ -6454,19 +6471,19 @@
         <v>23</v>
       </c>
       <c r="F108" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G108" t="s">
         <v>7</v>
       </c>
       <c r="H108" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I108" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J108" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="K108">
         <v>58000</v>
@@ -6486,28 +6503,28 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
+        <v>277</v>
+      </c>
+      <c r="C109" t="s">
+        <v>256</v>
+      </c>
+      <c r="D109" t="s">
+        <v>5</v>
+      </c>
+      <c r="F109" t="s">
         <v>278</v>
       </c>
-      <c r="C109" t="s">
-        <v>257</v>
-      </c>
-      <c r="D109" t="s">
-        <v>5</v>
-      </c>
-      <c r="F109" t="s">
+      <c r="G109" t="s">
+        <v>7</v>
+      </c>
+      <c r="H109" t="s">
+        <v>206</v>
+      </c>
+      <c r="I109" t="s">
         <v>279</v>
       </c>
-      <c r="G109" t="s">
-        <v>7</v>
-      </c>
-      <c r="H109" t="s">
-        <v>207</v>
-      </c>
-      <c r="I109" t="s">
-        <v>280</v>
-      </c>
       <c r="J109" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="K109">
         <v>51872</v>
@@ -6527,28 +6544,28 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
+        <v>280</v>
+      </c>
+      <c r="C110" t="s">
+        <v>256</v>
+      </c>
+      <c r="D110" t="s">
+        <v>5</v>
+      </c>
+      <c r="F110" t="s">
+        <v>201</v>
+      </c>
+      <c r="G110" t="s">
+        <v>7</v>
+      </c>
+      <c r="H110" t="s">
+        <v>206</v>
+      </c>
+      <c r="I110" t="s">
         <v>281</v>
       </c>
-      <c r="C110" t="s">
-        <v>257</v>
-      </c>
-      <c r="D110" t="s">
-        <v>5</v>
-      </c>
-      <c r="F110" t="s">
-        <v>202</v>
-      </c>
-      <c r="G110" t="s">
-        <v>7</v>
-      </c>
-      <c r="H110" t="s">
-        <v>207</v>
-      </c>
-      <c r="I110" t="s">
-        <v>282</v>
-      </c>
       <c r="J110" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="K110">
         <v>21632</v>
@@ -6568,28 +6585,28 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
+        <v>282</v>
+      </c>
+      <c r="C111" t="s">
+        <v>256</v>
+      </c>
+      <c r="D111" t="s">
+        <v>5</v>
+      </c>
+      <c r="F111" t="s">
+        <v>201</v>
+      </c>
+      <c r="G111" t="s">
+        <v>7</v>
+      </c>
+      <c r="H111" t="s">
+        <v>206</v>
+      </c>
+      <c r="I111" t="s">
         <v>283</v>
       </c>
-      <c r="C111" t="s">
-        <v>257</v>
-      </c>
-      <c r="D111" t="s">
-        <v>5</v>
-      </c>
-      <c r="F111" t="s">
-        <v>202</v>
-      </c>
-      <c r="G111" t="s">
-        <v>7</v>
-      </c>
-      <c r="H111" t="s">
-        <v>207</v>
-      </c>
-      <c r="I111" t="s">
-        <v>284</v>
-      </c>
       <c r="J111" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="K111">
         <v>69000</v>
@@ -6609,28 +6626,28 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
+        <v>284</v>
+      </c>
+      <c r="C112" t="s">
+        <v>256</v>
+      </c>
+      <c r="D112" t="s">
+        <v>5</v>
+      </c>
+      <c r="F112" t="s">
         <v>285</v>
       </c>
-      <c r="C112" t="s">
-        <v>257</v>
-      </c>
-      <c r="D112" t="s">
-        <v>5</v>
-      </c>
-      <c r="F112" t="s">
+      <c r="G112" t="s">
+        <v>7</v>
+      </c>
+      <c r="H112" t="s">
+        <v>206</v>
+      </c>
+      <c r="I112" t="s">
         <v>286</v>
       </c>
-      <c r="G112" t="s">
-        <v>7</v>
-      </c>
-      <c r="H112" t="s">
-        <v>207</v>
-      </c>
-      <c r="I112" t="s">
-        <v>287</v>
-      </c>
       <c r="J112" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="K112">
         <v>54000</v>
@@ -6650,10 +6667,10 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C113" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D113" t="s">
         <v>5</v>
@@ -6665,13 +6682,13 @@
         <v>7</v>
       </c>
       <c r="H113" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I113" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J113" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="K113">
         <v>57400</v>
@@ -6691,10 +6708,10 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C114" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D114" t="s">
         <v>14</v>
@@ -6706,13 +6723,13 @@
         <v>7</v>
       </c>
       <c r="H114" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I114" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J114" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="K114">
         <v>60000</v>
@@ -6732,10 +6749,10 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C115" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D115" t="s">
         <v>14</v>
@@ -6747,13 +6764,13 @@
         <v>7</v>
       </c>
       <c r="H115" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I115" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J115" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="K115">
         <v>60000</v>
@@ -6773,25 +6790,25 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
+        <v>292</v>
+      </c>
+      <c r="C116" t="s">
+        <v>256</v>
+      </c>
+      <c r="D116" t="s">
+        <v>5</v>
+      </c>
+      <c r="G116" t="s">
+        <v>7</v>
+      </c>
+      <c r="H116" t="s">
+        <v>206</v>
+      </c>
+      <c r="I116" t="s">
         <v>293</v>
       </c>
-      <c r="C116" t="s">
-        <v>257</v>
-      </c>
-      <c r="D116" t="s">
-        <v>5</v>
-      </c>
-      <c r="G116" t="s">
-        <v>7</v>
-      </c>
-      <c r="H116" t="s">
-        <v>207</v>
-      </c>
-      <c r="I116" t="s">
-        <v>294</v>
-      </c>
       <c r="J116" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="K116">
         <v>33000</v>
@@ -6811,25 +6828,25 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
+        <v>294</v>
+      </c>
+      <c r="C117" t="s">
+        <v>256</v>
+      </c>
+      <c r="D117" t="s">
+        <v>209</v>
+      </c>
+      <c r="G117" t="s">
+        <v>7</v>
+      </c>
+      <c r="H117" t="s">
+        <v>206</v>
+      </c>
+      <c r="I117" t="s">
         <v>295</v>
       </c>
-      <c r="C117" t="s">
-        <v>257</v>
-      </c>
-      <c r="D117" t="s">
-        <v>210</v>
-      </c>
-      <c r="G117" t="s">
-        <v>7</v>
-      </c>
-      <c r="H117" t="s">
-        <v>207</v>
-      </c>
-      <c r="I117" t="s">
-        <v>296</v>
-      </c>
       <c r="J117" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="K117">
         <v>88786</v>
@@ -6849,25 +6866,25 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
+        <v>296</v>
+      </c>
+      <c r="C118" t="s">
+        <v>256</v>
+      </c>
+      <c r="D118" t="s">
+        <v>209</v>
+      </c>
+      <c r="G118" t="s">
+        <v>7</v>
+      </c>
+      <c r="H118" t="s">
+        <v>206</v>
+      </c>
+      <c r="I118" t="s">
         <v>297</v>
       </c>
-      <c r="C118" t="s">
-        <v>257</v>
-      </c>
-      <c r="D118" t="s">
-        <v>210</v>
-      </c>
-      <c r="G118" t="s">
-        <v>7</v>
-      </c>
-      <c r="H118" t="s">
-        <v>207</v>
-      </c>
-      <c r="I118" t="s">
-        <v>298</v>
-      </c>
       <c r="J118" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="K118">
         <v>134000</v>
@@ -6887,25 +6904,25 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
+        <v>298</v>
+      </c>
+      <c r="C119" t="s">
+        <v>256</v>
+      </c>
+      <c r="D119" t="s">
+        <v>209</v>
+      </c>
+      <c r="G119" t="s">
+        <v>7</v>
+      </c>
+      <c r="H119" t="s">
+        <v>206</v>
+      </c>
+      <c r="I119" t="s">
         <v>299</v>
       </c>
-      <c r="C119" t="s">
-        <v>257</v>
-      </c>
-      <c r="D119" t="s">
-        <v>210</v>
-      </c>
-      <c r="G119" t="s">
-        <v>7</v>
-      </c>
-      <c r="H119" t="s">
-        <v>207</v>
-      </c>
-      <c r="I119" t="s">
-        <v>300</v>
-      </c>
       <c r="J119" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="K119">
         <v>35000</v>
@@ -6925,25 +6942,25 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
+        <v>300</v>
+      </c>
+      <c r="C120" t="s">
+        <v>256</v>
+      </c>
+      <c r="D120" t="s">
+        <v>209</v>
+      </c>
+      <c r="G120" t="s">
+        <v>7</v>
+      </c>
+      <c r="H120" t="s">
+        <v>206</v>
+      </c>
+      <c r="I120" t="s">
         <v>301</v>
       </c>
-      <c r="C120" t="s">
-        <v>257</v>
-      </c>
-      <c r="D120" t="s">
-        <v>210</v>
-      </c>
-      <c r="G120" t="s">
-        <v>7</v>
-      </c>
-      <c r="H120" t="s">
-        <v>207</v>
-      </c>
-      <c r="I120" t="s">
-        <v>302</v>
-      </c>
       <c r="J120" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="K120">
         <v>18000</v>
@@ -6963,13 +6980,13 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C121" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D121" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E121" t="s">
         <v>16</v>
@@ -6978,13 +6995,13 @@
         <v>7</v>
       </c>
       <c r="H121" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I121" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="J121" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="K121">
         <v>105741</v>
@@ -7004,25 +7021,25 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
+        <v>304</v>
+      </c>
+      <c r="C122" t="s">
+        <v>256</v>
+      </c>
+      <c r="D122" t="s">
+        <v>209</v>
+      </c>
+      <c r="G122" t="s">
+        <v>7</v>
+      </c>
+      <c r="H122" t="s">
+        <v>206</v>
+      </c>
+      <c r="I122" t="s">
         <v>305</v>
       </c>
-      <c r="C122" t="s">
-        <v>257</v>
-      </c>
-      <c r="D122" t="s">
-        <v>210</v>
-      </c>
-      <c r="G122" t="s">
-        <v>7</v>
-      </c>
-      <c r="H122" t="s">
-        <v>207</v>
-      </c>
-      <c r="I122" t="s">
-        <v>306</v>
-      </c>
       <c r="J122" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="K122">
         <v>51000</v>
@@ -7042,10 +7059,10 @@
         <v>122</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C123" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D123" t="s">
         <v>5</v>
@@ -7057,13 +7074,13 @@
         <v>7</v>
       </c>
       <c r="H123" t="s">
-        <v>207</v>
-      </c>
-      <c r="I123" s="1" t="s">
-        <v>490</v>
+        <v>206</v>
+      </c>
+      <c r="I123" s="3" t="s">
+        <v>484</v>
       </c>
       <c r="J123" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="K123">
         <v>130143</v>
@@ -7082,23 +7099,23 @@
       <c r="A124">
         <v>123</v>
       </c>
-      <c r="B124" t="s">
-        <v>308</v>
+      <c r="B124" s="2" t="s">
+        <v>485</v>
       </c>
       <c r="C124" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G124" t="s">
         <v>7</v>
       </c>
       <c r="H124" t="s">
-        <v>207</v>
-      </c>
-      <c r="I124" t="s">
-        <v>309</v>
+        <v>206</v>
+      </c>
+      <c r="I124" s="3" t="s">
+        <v>486</v>
       </c>
       <c r="J124" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="K124">
         <v>121551.47</v>
@@ -7118,10 +7135,10 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="C125" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="D125" t="s">
         <v>5</v>
@@ -7130,7 +7147,7 @@
         <v>16</v>
       </c>
       <c r="F125" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="G125" t="s">
         <v>7</v>
@@ -7139,10 +7156,10 @@
         <v>8</v>
       </c>
       <c r="I125" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="J125" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="K125">
         <v>110000</v>
@@ -7162,10 +7179,10 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="C126" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="D126" t="s">
         <v>5</v>
@@ -7174,7 +7191,7 @@
         <v>23</v>
       </c>
       <c r="F126" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G126" t="s">
         <v>7</v>
@@ -7183,10 +7200,10 @@
         <v>8</v>
       </c>
       <c r="I126" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="J126" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="K126">
         <v>56000</v>
@@ -7206,16 +7223,16 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="C127" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="D127" t="s">
         <v>5</v>
       </c>
       <c r="F127" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G127" t="s">
         <v>7</v>
@@ -7224,10 +7241,10 @@
         <v>8</v>
       </c>
       <c r="I127" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="J127" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="K127">
         <v>89177</v>
@@ -7247,10 +7264,10 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C128" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="D128" t="s">
         <v>5</v>
@@ -7259,7 +7276,7 @@
         <v>23</v>
       </c>
       <c r="F128" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="G128" t="s">
         <v>7</v>
@@ -7268,10 +7285,10 @@
         <v>8</v>
       </c>
       <c r="I128" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="J128" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="K128">
         <v>30000</v>
@@ -7291,10 +7308,10 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C129" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="D129" t="s">
         <v>5</v>
@@ -7303,7 +7320,7 @@
         <v>16</v>
       </c>
       <c r="F129" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="G129" t="s">
         <v>7</v>
@@ -7312,10 +7329,10 @@
         <v>8</v>
       </c>
       <c r="I129" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="J129" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="K129">
         <v>54550</v>
@@ -7335,10 +7352,10 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="C130" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="D130" t="s">
         <v>5</v>
@@ -7347,7 +7364,7 @@
         <v>16</v>
       </c>
       <c r="F130" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G130" t="s">
         <v>7</v>
@@ -7356,10 +7373,10 @@
         <v>8</v>
       </c>
       <c r="I130" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="J130" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="K130">
         <v>125000</v>
@@ -7379,10 +7396,10 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="C131" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="D131" t="s">
         <v>5</v>
@@ -7391,7 +7408,7 @@
         <v>16</v>
       </c>
       <c r="F131" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="G131" t="s">
         <v>7</v>
@@ -7400,10 +7417,10 @@
         <v>8</v>
       </c>
       <c r="I131" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="J131" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="K131">
         <v>69100</v>
@@ -7423,10 +7440,10 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="C132" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="D132" t="s">
         <v>5</v>
@@ -7444,10 +7461,10 @@
         <v>8</v>
       </c>
       <c r="I132" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="J132" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="K132">
         <v>118290</v>
@@ -7467,16 +7484,16 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C133" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="D133" t="s">
         <v>5</v>
       </c>
       <c r="F133" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="G133" t="s">
         <v>7</v>
@@ -7485,10 +7502,10 @@
         <v>8</v>
       </c>
       <c r="I133" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="J133" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="K133">
         <v>79900</v>
@@ -7508,10 +7525,10 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C134" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="D134" t="s">
         <v>5</v>
@@ -7526,10 +7543,10 @@
         <v>8</v>
       </c>
       <c r="I134" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="J134" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="K134">
         <v>39742.379999999997</v>
@@ -7549,10 +7566,10 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="C135" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="D135" t="s">
         <v>5</v>
@@ -7570,10 +7587,10 @@
         <v>8</v>
       </c>
       <c r="I135" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="J135" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="K135">
         <v>48000</v>
@@ -7593,10 +7610,10 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="C136" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="D136" t="s">
         <v>14</v>
@@ -7611,10 +7628,10 @@
         <v>8</v>
       </c>
       <c r="I136" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="J136" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="K136">
         <v>74722</v>
@@ -7634,13 +7651,13 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="C137" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="D137" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G137" t="s">
         <v>7</v>
@@ -7649,10 +7666,10 @@
         <v>8</v>
       </c>
       <c r="I137" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="J137" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="K137">
         <v>55000</v>
@@ -7672,10 +7689,10 @@
         <v>137</v>
       </c>
       <c r="B138" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C138" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="D138" t="s">
         <v>5</v>
@@ -7687,10 +7704,10 @@
         <v>117</v>
       </c>
       <c r="I138" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="J138" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="K138">
         <v>128000</v>
@@ -7710,10 +7727,10 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="C139" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="D139" t="s">
         <v>5</v>
@@ -7731,10 +7748,10 @@
         <v>117</v>
       </c>
       <c r="I139" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="J139" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="K139">
         <v>122000</v>
@@ -7754,10 +7771,10 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C140" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="D140" t="s">
         <v>5</v>
@@ -7772,10 +7789,10 @@
         <v>117</v>
       </c>
       <c r="I140" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="J140" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="K140">
         <v>22000</v>
@@ -7795,10 +7812,10 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C141" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="D141" t="s">
         <v>5</v>
@@ -7813,10 +7830,10 @@
         <v>117</v>
       </c>
       <c r="I141" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="J141" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="K141">
         <v>10000</v>
@@ -7836,10 +7853,10 @@
         <v>141</v>
       </c>
       <c r="B142" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="C142" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="D142" t="s">
         <v>5</v>
@@ -7854,10 +7871,10 @@
         <v>8</v>
       </c>
       <c r="I142" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="J142" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="K142">
         <v>64000</v>
@@ -7877,10 +7894,10 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="C143" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="D143" t="s">
         <v>5</v>
@@ -7895,10 +7912,10 @@
         <v>8</v>
       </c>
       <c r="I143" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="J143" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="K143">
         <v>95628</v>
@@ -7918,16 +7935,16 @@
         <v>143</v>
       </c>
       <c r="B144" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C144" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="D144" t="s">
         <v>5</v>
       </c>
       <c r="F144" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="G144" t="s">
         <v>7</v>
@@ -7936,10 +7953,10 @@
         <v>8</v>
       </c>
       <c r="I144" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="J144" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="K144">
         <v>39562</v>
@@ -7959,10 +7976,10 @@
         <v>144</v>
       </c>
       <c r="B145" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="C145" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="D145" t="s">
         <v>5</v>
@@ -7971,7 +7988,7 @@
         <v>16</v>
       </c>
       <c r="F145" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="G145" t="s">
         <v>7</v>
@@ -7980,10 +7997,10 @@
         <v>8</v>
       </c>
       <c r="I145" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="J145" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="K145">
         <v>105000</v>
@@ -8002,11 +8019,11 @@
       <c r="A146">
         <v>145</v>
       </c>
-      <c r="B146" t="s">
-        <v>360</v>
+      <c r="B146" s="2" t="s">
+        <v>489</v>
       </c>
       <c r="C146" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="D146" t="s">
         <v>5</v>
@@ -8015,7 +8032,7 @@
         <v>23</v>
       </c>
       <c r="F146" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="G146" t="s">
         <v>7</v>
@@ -8023,11 +8040,11 @@
       <c r="H146" t="s">
         <v>8</v>
       </c>
-      <c r="I146" t="s">
-        <v>361</v>
+      <c r="I146" s="2" t="s">
+        <v>490</v>
       </c>
       <c r="J146" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="K146">
         <v>60000</v>
@@ -8047,10 +8064,10 @@
         <v>146</v>
       </c>
       <c r="B147" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="C147" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="D147" t="s">
         <v>5</v>
@@ -8065,10 +8082,10 @@
         <v>8</v>
       </c>
       <c r="I147" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="J147" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="K147">
         <v>39964</v>
@@ -8088,10 +8105,10 @@
         <v>147</v>
       </c>
       <c r="B148" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C148" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="D148" t="s">
         <v>5</v>
@@ -8106,10 +8123,10 @@
         <v>8</v>
       </c>
       <c r="I148" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="J148" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="K148">
         <v>94000</v>
@@ -8128,11 +8145,11 @@
       <c r="A149">
         <v>148</v>
       </c>
-      <c r="B149" t="s">
-        <v>366</v>
+      <c r="B149" s="2" t="s">
+        <v>488</v>
       </c>
       <c r="C149" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="D149" t="s">
         <v>5</v>
@@ -8149,11 +8166,11 @@
       <c r="H149" t="s">
         <v>8</v>
       </c>
-      <c r="I149" t="s">
-        <v>361</v>
+      <c r="I149" s="2" t="s">
+        <v>491</v>
       </c>
       <c r="J149" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="K149">
         <v>75000</v>
@@ -8172,17 +8189,17 @@
       <c r="A150">
         <v>149</v>
       </c>
-      <c r="B150" t="s">
+      <c r="B150" s="2" t="s">
         <v>183</v>
       </c>
       <c r="C150" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="D150" t="s">
         <v>5</v>
       </c>
       <c r="F150" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="G150" t="s">
         <v>7</v>
@@ -8190,11 +8207,11 @@
       <c r="H150" t="s">
         <v>87</v>
       </c>
-      <c r="I150" t="s">
-        <v>184</v>
+      <c r="I150" s="2" t="s">
+        <v>487</v>
       </c>
       <c r="J150" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="K150">
         <v>48767</v>
@@ -8214,10 +8231,10 @@
         <v>150</v>
       </c>
       <c r="B151" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="C151" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="D151" t="s">
         <v>5</v>
@@ -8235,10 +8252,10 @@
         <v>8</v>
       </c>
       <c r="I151" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="J151" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="K151">
         <v>63824</v>
@@ -8258,10 +8275,10 @@
         <v>151</v>
       </c>
       <c r="B152" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="C152" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="D152" t="s">
         <v>14</v>
@@ -8279,10 +8296,10 @@
         <v>8</v>
       </c>
       <c r="I152" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="J152" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="K152">
         <v>117000</v>
@@ -8302,10 +8319,10 @@
         <v>152</v>
       </c>
       <c r="B153" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="C153" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="D153" t="s">
         <v>5</v>
@@ -8317,10 +8334,10 @@
         <v>8</v>
       </c>
       <c r="I153" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="J153" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="K153">
         <v>41000</v>
@@ -8340,10 +8357,10 @@
         <v>153</v>
       </c>
       <c r="B154" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="C154" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="D154" t="s">
         <v>5</v>
@@ -8355,10 +8372,10 @@
         <v>8</v>
       </c>
       <c r="I154" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="J154" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="K154">
         <v>96446</v>
@@ -8378,10 +8395,10 @@
         <v>154</v>
       </c>
       <c r="B155" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="C155" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="D155" t="s">
         <v>5</v>
@@ -8396,13 +8413,13 @@
         <v>7</v>
       </c>
       <c r="H155" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="I155" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="J155" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="K155">
         <v>76600</v>
@@ -8422,10 +8439,10 @@
         <v>155</v>
       </c>
       <c r="B156" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="C156" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="D156" t="s">
         <v>5</v>
@@ -8437,13 +8454,13 @@
         <v>7</v>
       </c>
       <c r="H156" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="I156" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="J156" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="K156">
         <v>125569</v>
@@ -8463,28 +8480,28 @@
         <v>156</v>
       </c>
       <c r="B157" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="C157" t="s">
+        <v>371</v>
+      </c>
+      <c r="D157" t="s">
+        <v>5</v>
+      </c>
+      <c r="F157" t="s">
         <v>377</v>
       </c>
-      <c r="D157" t="s">
-        <v>5</v>
-      </c>
-      <c r="F157" t="s">
-        <v>383</v>
-      </c>
       <c r="G157" t="s">
         <v>7</v>
       </c>
       <c r="H157" t="s">
+        <v>372</v>
+      </c>
+      <c r="I157" t="s">
         <v>378</v>
       </c>
-      <c r="I157" t="s">
-        <v>384</v>
-      </c>
       <c r="J157" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="K157">
         <v>51234</v>
@@ -8504,10 +8521,10 @@
         <v>157</v>
       </c>
       <c r="B158" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="C158" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="D158" t="s">
         <v>5</v>
@@ -8522,13 +8539,13 @@
         <v>7</v>
       </c>
       <c r="H158" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="I158" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="J158" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="K158">
         <v>123780</v>
@@ -8548,28 +8565,28 @@
         <v>158</v>
       </c>
       <c r="B159" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="C159" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="D159" t="s">
         <v>5</v>
       </c>
       <c r="F159" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="G159" t="s">
         <v>7</v>
       </c>
       <c r="H159" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="I159" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="J159" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="K159">
         <v>46000</v>
@@ -8589,10 +8606,10 @@
         <v>159</v>
       </c>
       <c r="B160" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="C160" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="D160" t="s">
         <v>5</v>
@@ -8601,13 +8618,13 @@
         <v>7</v>
       </c>
       <c r="H160" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="I160" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="J160" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="K160">
         <v>35600</v>
@@ -8627,10 +8644,10 @@
         <v>160</v>
       </c>
       <c r="B161" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="C161" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="D161" t="s">
         <v>5</v>
@@ -8642,13 +8659,13 @@
         <v>7</v>
       </c>
       <c r="H161" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="I161" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="J161" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="K161">
         <v>199950</v>
@@ -8668,10 +8685,10 @@
         <v>161</v>
       </c>
       <c r="B162" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="C162" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="D162" t="s">
         <v>5</v>
@@ -8683,13 +8700,13 @@
         <v>7</v>
       </c>
       <c r="H162" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="I162" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="J162" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="K162">
         <v>108000</v>
@@ -8709,10 +8726,10 @@
         <v>162</v>
       </c>
       <c r="B163" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="C163" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="D163" t="s">
         <v>5</v>
@@ -8724,13 +8741,13 @@
         <v>7</v>
       </c>
       <c r="H163" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="I163" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="J163" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="K163">
         <v>142808</v>
@@ -8750,10 +8767,10 @@
         <v>163</v>
       </c>
       <c r="B164" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="C164" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="D164" t="s">
         <v>5</v>
@@ -8765,13 +8782,13 @@
         <v>7</v>
       </c>
       <c r="H164" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="I164" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="J164" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="K164">
         <v>80463</v>
@@ -8791,10 +8808,10 @@
         <v>164</v>
       </c>
       <c r="B165" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="C165" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="D165" t="s">
         <v>5</v>
@@ -8806,13 +8823,13 @@
         <v>7</v>
       </c>
       <c r="H165" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="I165" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="J165" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="K165">
         <v>83000</v>
@@ -8832,10 +8849,10 @@
         <v>165</v>
       </c>
       <c r="B166" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="C166" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="D166" t="s">
         <v>5</v>
@@ -8844,13 +8861,13 @@
         <v>7</v>
       </c>
       <c r="H166" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="I166" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="J166" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="K166">
         <v>129000</v>
@@ -8870,16 +8887,16 @@
         <v>166</v>
       </c>
       <c r="B167" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="C167" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="D167" t="s">
         <v>5</v>
       </c>
       <c r="F167" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G167" t="s">
         <v>7</v>
@@ -8888,10 +8905,10 @@
         <v>117</v>
       </c>
       <c r="I167" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="J167" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="K167">
         <v>62209</v>
@@ -8911,16 +8928,16 @@
         <v>167</v>
       </c>
       <c r="B168" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="C168" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="D168" t="s">
         <v>5</v>
       </c>
       <c r="F168" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="G168" t="s">
         <v>7</v>
@@ -8929,10 +8946,10 @@
         <v>8</v>
       </c>
       <c r="I168" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="J168" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="K168">
         <v>36117</v>
@@ -8952,10 +8969,10 @@
         <v>168</v>
       </c>
       <c r="B169" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="C169" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="D169" t="s">
         <v>5</v>
@@ -8973,10 +8990,10 @@
         <v>87</v>
       </c>
       <c r="I169" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="J169" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="K169">
         <v>49900</v>
@@ -8996,10 +9013,10 @@
         <v>169</v>
       </c>
       <c r="B170" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="C170" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="D170" t="s">
         <v>5</v>
@@ -9008,7 +9025,7 @@
         <v>16</v>
       </c>
       <c r="F170" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="G170" t="s">
         <v>7</v>
@@ -9017,10 +9034,10 @@
         <v>87</v>
       </c>
       <c r="I170" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="J170" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="K170">
         <v>39000</v>
@@ -9040,28 +9057,28 @@
         <v>170</v>
       </c>
       <c r="B171" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="C171" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="D171" t="s">
         <v>5</v>
       </c>
       <c r="F171" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="G171" t="s">
         <v>7</v>
       </c>
       <c r="H171" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I171" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="J171" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="K171">
         <v>49000</v>
@@ -9081,13 +9098,13 @@
         <v>171</v>
       </c>
       <c r="B172" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="C172" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="D172" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G172" t="s">
         <v>7</v>
@@ -9096,10 +9113,10 @@
         <v>8</v>
       </c>
       <c r="I172" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="J172" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="K172">
         <v>59400</v>
@@ -9119,10 +9136,10 @@
         <v>172</v>
       </c>
       <c r="B173" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="C173" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="D173" t="s">
         <v>5</v>
@@ -9137,10 +9154,10 @@
         <v>8</v>
       </c>
       <c r="I173" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="J173" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="K173">
         <v>65000</v>
@@ -9160,31 +9177,31 @@
         <v>173</v>
       </c>
       <c r="B174" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="C174" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="D174" t="s">
         <v>5</v>
       </c>
       <c r="E174" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="F174" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="G174" t="s">
         <v>7</v>
       </c>
       <c r="H174" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="I174" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="J174" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="K174">
         <v>47000</v>
@@ -9204,28 +9221,28 @@
         <v>174</v>
       </c>
       <c r="B175" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="C175" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="D175" t="s">
         <v>5</v>
       </c>
       <c r="E175" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="G175" t="s">
         <v>7</v>
       </c>
       <c r="H175" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="I175" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="J175" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="K175">
         <v>29000</v>
@@ -9245,10 +9262,10 @@
         <v>175</v>
       </c>
       <c r="B176" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="C176" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="D176" t="s">
         <v>5</v>
@@ -9266,10 +9283,10 @@
         <v>87</v>
       </c>
       <c r="I176" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="J176" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="K176">
         <v>132239</v>
@@ -9289,10 +9306,10 @@
         <v>176</v>
       </c>
       <c r="B177" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="C177" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="D177" t="s">
         <v>5</v>
@@ -9304,13 +9321,13 @@
         <v>7</v>
       </c>
       <c r="H177" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="I177" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="J177" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="K177">
         <v>35016</v>
@@ -9330,10 +9347,10 @@
         <v>177</v>
       </c>
       <c r="B178" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="C178" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="D178" t="s">
         <v>5</v>
@@ -9345,10 +9362,10 @@
         <v>87</v>
       </c>
       <c r="I178" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="J178" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="K178">
         <v>60000</v>
@@ -9368,28 +9385,28 @@
         <v>178</v>
       </c>
       <c r="B179" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="C179" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="D179" t="s">
         <v>5</v>
       </c>
       <c r="F179" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="G179" t="s">
         <v>7</v>
       </c>
       <c r="H179" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="I179" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="J179" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="K179">
         <v>90244</v>
@@ -9409,10 +9426,10 @@
         <v>179</v>
       </c>
       <c r="B180" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="C180" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="D180" t="s">
         <v>5</v>
@@ -9421,13 +9438,13 @@
         <v>7</v>
       </c>
       <c r="H180" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="I180" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="J180" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="K180">
         <v>38700</v>
@@ -9447,10 +9464,10 @@
         <v>180</v>
       </c>
       <c r="B181" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="C181" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="D181" t="s">
         <v>5</v>
@@ -9459,13 +9476,13 @@
         <v>7</v>
       </c>
       <c r="H181" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="I181" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="J181" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="K181">
         <v>62414</v>
@@ -9485,10 +9502,10 @@
         <v>181</v>
       </c>
       <c r="B182" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="C182" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="D182" t="s">
         <v>5</v>
@@ -9497,13 +9514,13 @@
         <v>7</v>
       </c>
       <c r="H182" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="I182" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="J182" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="K182">
         <v>51000</v>
@@ -9523,10 +9540,10 @@
         <v>182</v>
       </c>
       <c r="B183" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="C183" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="D183" t="s">
         <v>5</v>
@@ -9541,10 +9558,10 @@
         <v>87</v>
       </c>
       <c r="I183" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="J183" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="K183">
         <v>53115</v>
@@ -9564,10 +9581,10 @@
         <v>183</v>
       </c>
       <c r="B184" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="C184" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="D184" t="s">
         <v>5</v>
@@ -9576,13 +9593,13 @@
         <v>7</v>
       </c>
       <c r="H184" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="I184" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="J184" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="K184">
         <v>120000</v>
@@ -9602,10 +9619,10 @@
         <v>184</v>
       </c>
       <c r="B185" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="C185" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="D185" t="s">
         <v>5</v>
@@ -9620,10 +9637,10 @@
         <v>87</v>
       </c>
       <c r="I185" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="J185" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="K185">
         <v>66477</v>
@@ -9643,10 +9660,10 @@
         <v>185</v>
       </c>
       <c r="B186" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="C186" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="D186" t="s">
         <v>5</v>
@@ -9658,10 +9675,10 @@
         <v>7</v>
       </c>
       <c r="H186" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="I186" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="K186">
         <v>59300</v>
@@ -9681,10 +9698,10 @@
         <v>186</v>
       </c>
       <c r="B187" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="C187" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="D187" t="s">
         <v>5</v>
@@ -9693,10 +9710,10 @@
         <v>7</v>
       </c>
       <c r="H187" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="I187" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="K187">
         <v>44000</v>
@@ -9716,22 +9733,22 @@
         <v>187</v>
       </c>
       <c r="B188" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="C188" t="s">
+        <v>443</v>
+      </c>
+      <c r="D188" t="s">
+        <v>5</v>
+      </c>
+      <c r="G188" t="s">
+        <v>7</v>
+      </c>
+      <c r="H188" t="s">
+        <v>444</v>
+      </c>
+      <c r="I188" t="s">
         <v>449</v>
-      </c>
-      <c r="D188" t="s">
-        <v>5</v>
-      </c>
-      <c r="G188" t="s">
-        <v>7</v>
-      </c>
-      <c r="H188" t="s">
-        <v>450</v>
-      </c>
-      <c r="I188" t="s">
-        <v>455</v>
       </c>
       <c r="K188">
         <v>26528</v>
@@ -9751,10 +9768,10 @@
         <v>188</v>
       </c>
       <c r="B189" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="C189" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="D189" t="s">
         <v>5</v>
@@ -9766,10 +9783,10 @@
         <v>7</v>
       </c>
       <c r="H189" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="I189" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="K189">
         <v>95684</v>
@@ -9789,10 +9806,10 @@
         <v>189</v>
       </c>
       <c r="B190" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="C190" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="D190" t="s">
         <v>5</v>
@@ -9824,10 +9841,10 @@
         <v>190</v>
       </c>
       <c r="B191" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="C191" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="D191" t="s">
         <v>5</v>
@@ -9839,10 +9856,10 @@
         <v>7</v>
       </c>
       <c r="H191" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="I191" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="K191">
         <v>60000</v>
@@ -9862,10 +9879,10 @@
         <v>191</v>
       </c>
       <c r="B192" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="C192" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="D192" t="s">
         <v>5</v>
@@ -9874,10 +9891,10 @@
         <v>7</v>
       </c>
       <c r="H192" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="I192" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="K192">
         <v>34895</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yuhang/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4DA1E64-0579-D14E-B177-65A9FD024ADB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BD0F26C-52C8-2B42-B2C2-031F7567C299}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1577" uniqueCount="492">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1577" uniqueCount="493">
   <si>
     <t>所在市</t>
   </si>
@@ -1389,9 +1389,6 @@
   </si>
   <si>
     <t>116.657902,39.915044</t>
-  </si>
-  <si>
-    <t>合景国际金融广场（4B)</t>
   </si>
   <si>
     <t>通州C01(富力中心C01（中银）)</t>
@@ -1525,6 +1522,14 @@
   </si>
   <si>
     <t>116.406387,39.980615</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>合景国际金融广场（4B)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>116.680295,39.907589</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1532,7 +1537,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1571,6 +1576,13 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1601,11 +1613,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1937,22 +1950,22 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B1" t="s">
+        <v>463</v>
+      </c>
+      <c r="C1" t="s">
         <v>464</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>465</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="F1" t="s">
         <v>466</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>472</v>
-      </c>
-      <c r="F1" t="s">
-        <v>467</v>
       </c>
       <c r="G1" t="s">
         <v>0</v>
@@ -1964,19 +1977,19 @@
         <v>2</v>
       </c>
       <c r="J1" t="s">
+        <v>467</v>
+      </c>
+      <c r="K1" t="s">
+        <v>462</v>
+      </c>
+      <c r="L1" t="s">
         <v>468</v>
       </c>
-      <c r="K1" t="s">
-        <v>463</v>
-      </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>469</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>470</v>
-      </c>
-      <c r="N1" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -2005,7 +2018,7 @@
         <v>9</v>
       </c>
       <c r="J2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K2">
         <v>72308</v>
@@ -2046,7 +2059,7 @@
         <v>12</v>
       </c>
       <c r="J3" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K3">
         <v>72308</v>
@@ -2090,7 +2103,7 @@
         <v>17</v>
       </c>
       <c r="J4" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K4">
         <v>130769</v>
@@ -2134,7 +2147,7 @@
         <v>20</v>
       </c>
       <c r="J5" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K5">
         <v>64615</v>
@@ -2178,7 +2191,7 @@
         <v>24</v>
       </c>
       <c r="J6" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K6">
         <v>80091</v>
@@ -2219,7 +2232,7 @@
         <v>27</v>
       </c>
       <c r="J7" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="K7">
         <v>70673</v>
@@ -2263,7 +2276,7 @@
         <v>30</v>
       </c>
       <c r="J8" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K8">
         <v>90466</v>
@@ -2304,7 +2317,7 @@
         <v>32</v>
       </c>
       <c r="J9" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="K9">
         <v>46720</v>
@@ -2348,7 +2361,7 @@
         <v>35</v>
       </c>
       <c r="J10" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="K10">
         <v>95000</v>
@@ -2392,7 +2405,7 @@
         <v>38</v>
       </c>
       <c r="J11" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K11">
         <v>85300</v>
@@ -2436,7 +2449,7 @@
         <v>41</v>
       </c>
       <c r="J12" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="K12">
         <v>33305</v>
@@ -2480,7 +2493,7 @@
         <v>43</v>
       </c>
       <c r="J13" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K13">
         <v>120245.21</v>
@@ -2524,7 +2537,7 @@
         <v>43</v>
       </c>
       <c r="J14" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K14">
         <v>70425.53</v>
@@ -2568,7 +2581,7 @@
         <v>47</v>
       </c>
       <c r="J15" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K15">
         <v>78000</v>
@@ -2612,7 +2625,7 @@
         <v>50</v>
       </c>
       <c r="J16" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="K16">
         <v>102796</v>
@@ -2656,7 +2669,7 @@
         <v>52</v>
       </c>
       <c r="J17" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="K17">
         <v>49200</v>
@@ -2700,7 +2713,7 @@
         <v>54</v>
       </c>
       <c r="J18" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="K18">
         <v>65096</v>
@@ -2744,7 +2757,7 @@
         <v>57</v>
       </c>
       <c r="J19" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K19">
         <v>56000</v>
@@ -2788,7 +2801,7 @@
         <v>60</v>
       </c>
       <c r="J20" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="K20">
         <v>177847</v>
@@ -2832,7 +2845,7 @@
         <v>63</v>
       </c>
       <c r="J21" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K21">
         <v>83000</v>
@@ -2873,7 +2886,7 @@
         <v>66</v>
       </c>
       <c r="J22" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="K22">
         <v>26000</v>
@@ -2914,7 +2927,7 @@
         <v>68</v>
       </c>
       <c r="J23" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K23">
         <v>85887</v>
@@ -2955,7 +2968,7 @@
         <v>70</v>
       </c>
       <c r="J24" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K24">
         <v>20000</v>
@@ -2999,7 +3012,7 @@
         <v>73</v>
       </c>
       <c r="J25" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K25">
         <v>146385</v>
@@ -3043,7 +3056,7 @@
         <v>76</v>
       </c>
       <c r="J26" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K26">
         <v>87000</v>
@@ -3087,7 +3100,7 @@
         <v>79</v>
       </c>
       <c r="J27" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K27">
         <v>147166.79999999999</v>
@@ -3131,7 +3144,7 @@
         <v>82</v>
       </c>
       <c r="J28" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K28">
         <v>46063</v>
@@ -3175,7 +3188,7 @@
         <v>85</v>
       </c>
       <c r="J29" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="K29">
         <v>47261</v>
@@ -3195,7 +3208,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C30" t="s">
         <v>4</v>
@@ -3213,13 +3226,13 @@
         <v>7</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="J30" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K30">
         <v>119000</v>
@@ -3260,7 +3273,7 @@
         <v>91</v>
       </c>
       <c r="J31" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="K31">
         <v>47000</v>
@@ -3304,7 +3317,7 @@
         <v>93</v>
       </c>
       <c r="J32" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="K32">
         <v>186000</v>
@@ -3342,7 +3355,7 @@
         <v>95</v>
       </c>
       <c r="J33" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K33">
         <v>40800</v>
@@ -3383,7 +3396,7 @@
         <v>95</v>
       </c>
       <c r="J34" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K34">
         <v>55200</v>
@@ -3427,7 +3440,7 @@
         <v>99</v>
       </c>
       <c r="J35" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="K35">
         <v>350000</v>
@@ -3468,7 +3481,7 @@
         <v>101</v>
       </c>
       <c r="J36" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K36">
         <v>65000</v>
@@ -3509,7 +3522,7 @@
         <v>101</v>
       </c>
       <c r="J37" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K37">
         <v>35000</v>
@@ -3550,7 +3563,7 @@
         <v>104</v>
       </c>
       <c r="J38" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="K38">
         <v>47000</v>
@@ -3594,7 +3607,7 @@
         <v>107</v>
       </c>
       <c r="J39" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="K39">
         <v>120000</v>
@@ -3635,7 +3648,7 @@
         <v>109</v>
       </c>
       <c r="J40" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K40">
         <v>83000</v>
@@ -3676,7 +3689,7 @@
         <v>111</v>
       </c>
       <c r="J41" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="K41">
         <v>66030</v>
@@ -3714,7 +3727,7 @@
         <v>113</v>
       </c>
       <c r="J42" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="K42">
         <v>40000</v>
@@ -3758,7 +3771,7 @@
         <v>118</v>
       </c>
       <c r="J43" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K43">
         <v>40000</v>
@@ -3799,7 +3812,7 @@
         <v>121</v>
       </c>
       <c r="J44" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K44">
         <v>54100</v>
@@ -3840,10 +3853,10 @@
         <v>117</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="J45" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K45">
         <v>100000</v>
@@ -3884,10 +3897,10 @@
         <v>117</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="J46" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K46">
         <v>150000</v>
@@ -3928,10 +3941,10 @@
         <v>117</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="J47" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K47">
         <v>50000</v>
@@ -3975,7 +3988,7 @@
         <v>130</v>
       </c>
       <c r="J48" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="K48">
         <v>43000</v>
@@ -4016,7 +4029,7 @@
         <v>133</v>
       </c>
       <c r="J49" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="K49">
         <v>65000</v>
@@ -4057,7 +4070,7 @@
         <v>136</v>
       </c>
       <c r="J50" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="51" spans="1:14">
@@ -4089,7 +4102,7 @@
         <v>138</v>
       </c>
       <c r="J51" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="K51">
         <v>56000</v>
@@ -4130,7 +4143,7 @@
         <v>140</v>
       </c>
       <c r="J52" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="K52">
         <v>160000</v>
@@ -4171,7 +4184,7 @@
         <v>142</v>
       </c>
       <c r="J53" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="K53">
         <v>33000</v>
@@ -4215,7 +4228,7 @@
         <v>145</v>
       </c>
       <c r="J54" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="K54">
         <v>41318</v>
@@ -4256,7 +4269,7 @@
         <v>147</v>
       </c>
       <c r="J55" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K55">
         <v>34131</v>
@@ -4297,7 +4310,7 @@
         <v>150</v>
       </c>
       <c r="J56" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K56">
         <v>48000</v>
@@ -4338,7 +4351,7 @@
         <v>118</v>
       </c>
       <c r="J57" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K57">
         <v>16000</v>
@@ -4382,7 +4395,7 @@
         <v>154</v>
       </c>
       <c r="J58" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="K58">
         <v>30000</v>
@@ -4426,7 +4439,7 @@
         <v>157</v>
       </c>
       <c r="J59" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="K59">
         <v>56000</v>
@@ -4470,7 +4483,7 @@
         <v>160</v>
       </c>
       <c r="J60" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K60">
         <v>43000</v>
@@ -4511,7 +4524,7 @@
         <v>162</v>
       </c>
       <c r="J61" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="K61">
         <v>110000</v>
@@ -4549,7 +4562,7 @@
         <v>164</v>
       </c>
       <c r="J62" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K62">
         <v>56160</v>
@@ -4590,7 +4603,7 @@
         <v>166</v>
       </c>
       <c r="J63" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K63">
         <v>138444</v>
@@ -4634,7 +4647,7 @@
         <v>170</v>
       </c>
       <c r="J64" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="K64">
         <v>31000</v>
@@ -4675,7 +4688,7 @@
         <v>173</v>
       </c>
       <c r="J65" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="K65">
         <v>120000</v>
@@ -4716,7 +4729,7 @@
         <v>175</v>
       </c>
       <c r="J66" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="K66">
         <v>25900</v>
@@ -4757,7 +4770,7 @@
         <v>178</v>
       </c>
       <c r="J67" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="K67">
         <v>47986</v>
@@ -4801,7 +4814,7 @@
         <v>180</v>
       </c>
       <c r="J68" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="K68">
         <v>194000</v>
@@ -4845,7 +4858,7 @@
         <v>182</v>
       </c>
       <c r="J69" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="K69">
         <v>39724</v>
@@ -4883,10 +4896,10 @@
         <v>87</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="J70" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="K70">
         <v>48437.45</v>
@@ -4927,7 +4940,7 @@
         <v>186</v>
       </c>
       <c r="J71" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="K71">
         <v>37910</v>
@@ -4947,7 +4960,7 @@
         <v>71</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C72" t="s">
         <v>168</v>
@@ -4965,10 +4978,10 @@
         <v>87</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="J72" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="K72">
         <v>21220</v>
@@ -5009,7 +5022,7 @@
         <v>188</v>
       </c>
       <c r="J73" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="K73">
         <v>77877</v>
@@ -5053,7 +5066,7 @@
         <v>190</v>
       </c>
       <c r="J74" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="K74">
         <v>80311.53</v>
@@ -5097,7 +5110,7 @@
         <v>193</v>
       </c>
       <c r="J75" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="K75">
         <v>38000</v>
@@ -5138,7 +5151,7 @@
         <v>196</v>
       </c>
       <c r="J76" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="K76">
         <v>37800</v>
@@ -5182,7 +5195,7 @@
         <v>199</v>
       </c>
       <c r="J77" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="K77">
         <v>54581</v>
@@ -5226,7 +5239,7 @@
         <v>88</v>
       </c>
       <c r="J78" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="K78">
         <v>25000</v>
@@ -5270,7 +5283,7 @@
         <v>203</v>
       </c>
       <c r="J79" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="K79">
         <v>52698</v>
@@ -5311,7 +5324,7 @@
         <v>207</v>
       </c>
       <c r="J80" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="K80">
         <v>38500</v>
@@ -5349,7 +5362,7 @@
         <v>210</v>
       </c>
       <c r="J81" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="K81">
         <v>27200</v>
@@ -5393,7 +5406,7 @@
         <v>213</v>
       </c>
       <c r="J82" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K82">
         <v>60000</v>
@@ -5434,7 +5447,7 @@
         <v>216</v>
       </c>
       <c r="J83" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K83">
         <v>50000</v>
@@ -5478,7 +5491,7 @@
         <v>218</v>
       </c>
       <c r="J84" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K84">
         <v>131575</v>
@@ -5519,7 +5532,7 @@
         <v>220</v>
       </c>
       <c r="J85" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K85">
         <v>99500</v>
@@ -5560,7 +5573,7 @@
         <v>223</v>
       </c>
       <c r="J86" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K86">
         <v>32000</v>
@@ -5604,7 +5617,7 @@
         <v>225</v>
       </c>
       <c r="J87" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K87">
         <v>52170</v>
@@ -5645,7 +5658,7 @@
         <v>228</v>
       </c>
       <c r="J88" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K88">
         <v>46000</v>
@@ -5689,7 +5702,7 @@
         <v>231</v>
       </c>
       <c r="J89" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K89">
         <v>45013</v>
@@ -5730,7 +5743,7 @@
         <v>233</v>
       </c>
       <c r="J90" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K90">
         <v>48566</v>
@@ -5771,7 +5784,7 @@
         <v>236</v>
       </c>
       <c r="J91" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K91">
         <v>55618</v>
@@ -5812,7 +5825,7 @@
         <v>238</v>
       </c>
       <c r="J92" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K92">
         <v>47000</v>
@@ -5856,7 +5869,7 @@
         <v>241</v>
       </c>
       <c r="J93" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K93">
         <v>87763</v>
@@ -5900,7 +5913,7 @@
         <v>244</v>
       </c>
       <c r="J94" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K94">
         <v>100658</v>
@@ -5941,7 +5954,7 @@
         <v>247</v>
       </c>
       <c r="J95" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K95">
         <v>67000</v>
@@ -5985,7 +5998,7 @@
         <v>249</v>
       </c>
       <c r="J96" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K96">
         <v>39431</v>
@@ -6026,7 +6039,7 @@
         <v>251</v>
       </c>
       <c r="J97" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K97">
         <v>34273</v>
@@ -6064,7 +6077,7 @@
         <v>73</v>
       </c>
       <c r="J98" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K98">
         <v>40000</v>
@@ -6105,7 +6118,7 @@
         <v>254</v>
       </c>
       <c r="J99" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K99">
         <v>65000</v>
@@ -6149,7 +6162,7 @@
         <v>258</v>
       </c>
       <c r="J100" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="K100">
         <v>49000</v>
@@ -6193,7 +6206,7 @@
         <v>261</v>
       </c>
       <c r="J101" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="K101">
         <v>95000</v>
@@ -6237,7 +6250,7 @@
         <v>264</v>
       </c>
       <c r="J102" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="K102">
         <v>45000</v>
@@ -6278,7 +6291,7 @@
         <v>266</v>
       </c>
       <c r="J103" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="K103">
         <v>124500</v>
@@ -6319,7 +6332,7 @@
         <v>268</v>
       </c>
       <c r="J104" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="K104">
         <v>64000</v>
@@ -6360,7 +6373,7 @@
         <v>270</v>
       </c>
       <c r="J105" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="K105">
         <v>25000</v>
@@ -6401,7 +6414,7 @@
         <v>272</v>
       </c>
       <c r="J106" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="K106">
         <v>38498</v>
@@ -6439,7 +6452,7 @@
         <v>274</v>
       </c>
       <c r="J107" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="K107">
         <v>166433</v>
@@ -6483,7 +6496,7 @@
         <v>276</v>
       </c>
       <c r="J108" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="K108">
         <v>58000</v>
@@ -6524,7 +6537,7 @@
         <v>279</v>
       </c>
       <c r="J109" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="K109">
         <v>51872</v>
@@ -6565,7 +6578,7 @@
         <v>281</v>
       </c>
       <c r="J110" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="K110">
         <v>21632</v>
@@ -6606,7 +6619,7 @@
         <v>283</v>
       </c>
       <c r="J111" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="K111">
         <v>69000</v>
@@ -6647,7 +6660,7 @@
         <v>286</v>
       </c>
       <c r="J112" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="K112">
         <v>54000</v>
@@ -6688,7 +6701,7 @@
         <v>288</v>
       </c>
       <c r="J113" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="K113">
         <v>57400</v>
@@ -6729,7 +6742,7 @@
         <v>290</v>
       </c>
       <c r="J114" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="K114">
         <v>60000</v>
@@ -6770,7 +6783,7 @@
         <v>290</v>
       </c>
       <c r="J115" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="K115">
         <v>60000</v>
@@ -6808,7 +6821,7 @@
         <v>293</v>
       </c>
       <c r="J116" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="K116">
         <v>33000</v>
@@ -6846,7 +6859,7 @@
         <v>295</v>
       </c>
       <c r="J117" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="K117">
         <v>88786</v>
@@ -6884,7 +6897,7 @@
         <v>297</v>
       </c>
       <c r="J118" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="K118">
         <v>134000</v>
@@ -6922,7 +6935,7 @@
         <v>299</v>
       </c>
       <c r="J119" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="K119">
         <v>35000</v>
@@ -6960,7 +6973,7 @@
         <v>301</v>
       </c>
       <c r="J120" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="K120">
         <v>18000</v>
@@ -7001,7 +7014,7 @@
         <v>303</v>
       </c>
       <c r="J121" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="K121">
         <v>105741</v>
@@ -7039,7 +7052,7 @@
         <v>305</v>
       </c>
       <c r="J122" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="K122">
         <v>51000</v>
@@ -7077,10 +7090,10 @@
         <v>206</v>
       </c>
       <c r="I123" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="J123" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="K123">
         <v>130143</v>
@@ -7100,7 +7113,7 @@
         <v>123</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C124" t="s">
         <v>256</v>
@@ -7112,10 +7125,10 @@
         <v>206</v>
       </c>
       <c r="I124" s="3" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="J124" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="K124">
         <v>121551.47</v>
@@ -7159,7 +7172,7 @@
         <v>310</v>
       </c>
       <c r="J125" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="K125">
         <v>110000</v>
@@ -7203,7 +7216,7 @@
         <v>312</v>
       </c>
       <c r="J126" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="K126">
         <v>56000</v>
@@ -7244,7 +7257,7 @@
         <v>314</v>
       </c>
       <c r="J127" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="K127">
         <v>89177</v>
@@ -7288,7 +7301,7 @@
         <v>317</v>
       </c>
       <c r="J128" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="K128">
         <v>30000</v>
@@ -7332,7 +7345,7 @@
         <v>319</v>
       </c>
       <c r="J129" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="K129">
         <v>54550</v>
@@ -7376,7 +7389,7 @@
         <v>321</v>
       </c>
       <c r="J130" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="K130">
         <v>125000</v>
@@ -7420,7 +7433,7 @@
         <v>324</v>
       </c>
       <c r="J131" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="K131">
         <v>69100</v>
@@ -7464,7 +7477,7 @@
         <v>326</v>
       </c>
       <c r="J132" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="K132">
         <v>118290</v>
@@ -7505,7 +7518,7 @@
         <v>329</v>
       </c>
       <c r="J133" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="K133">
         <v>79900</v>
@@ -7546,7 +7559,7 @@
         <v>331</v>
       </c>
       <c r="J134" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="K134">
         <v>39742.379999999997</v>
@@ -7590,7 +7603,7 @@
         <v>333</v>
       </c>
       <c r="J135" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="K135">
         <v>48000</v>
@@ -7631,7 +7644,7 @@
         <v>335</v>
       </c>
       <c r="J136" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="K136">
         <v>74722</v>
@@ -7669,7 +7682,7 @@
         <v>337</v>
       </c>
       <c r="J137" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="K137">
         <v>55000</v>
@@ -7707,7 +7720,7 @@
         <v>340</v>
       </c>
       <c r="J138" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K138">
         <v>128000</v>
@@ -7751,7 +7764,7 @@
         <v>342</v>
       </c>
       <c r="J139" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K139">
         <v>122000</v>
@@ -7792,7 +7805,7 @@
         <v>344</v>
       </c>
       <c r="J140" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K140">
         <v>22000</v>
@@ -7833,7 +7846,7 @@
         <v>346</v>
       </c>
       <c r="J141" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K141">
         <v>10000</v>
@@ -7874,7 +7887,7 @@
         <v>348</v>
       </c>
       <c r="J142" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K142">
         <v>64000</v>
@@ -7915,7 +7928,7 @@
         <v>350</v>
       </c>
       <c r="J143" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K143">
         <v>95628</v>
@@ -7956,7 +7969,7 @@
         <v>353</v>
       </c>
       <c r="J144" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K144">
         <v>39562</v>
@@ -8000,7 +8013,7 @@
         <v>356</v>
       </c>
       <c r="J145" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K145">
         <v>105000</v>
@@ -8020,7 +8033,7 @@
         <v>145</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C146" t="s">
         <v>339</v>
@@ -8041,10 +8054,10 @@
         <v>8</v>
       </c>
       <c r="I146" s="2" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="J146" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K146">
         <v>60000</v>
@@ -8085,7 +8098,7 @@
         <v>358</v>
       </c>
       <c r="J147" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K147">
         <v>39964</v>
@@ -8126,7 +8139,7 @@
         <v>360</v>
       </c>
       <c r="J148" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K148">
         <v>94000</v>
@@ -8146,7 +8159,7 @@
         <v>148</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C149" t="s">
         <v>339</v>
@@ -8167,10 +8180,10 @@
         <v>8</v>
       </c>
       <c r="I149" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="J149" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K149">
         <v>75000</v>
@@ -8208,10 +8221,10 @@
         <v>87</v>
       </c>
       <c r="I150" s="2" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="J150" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K150">
         <v>48767</v>
@@ -8255,7 +8268,7 @@
         <v>363</v>
       </c>
       <c r="J151" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K151">
         <v>63824</v>
@@ -8299,7 +8312,7 @@
         <v>365</v>
       </c>
       <c r="J152" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K152">
         <v>117000</v>
@@ -8337,7 +8350,7 @@
         <v>367</v>
       </c>
       <c r="J153" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K153">
         <v>41000</v>
@@ -8375,7 +8388,7 @@
         <v>369</v>
       </c>
       <c r="J154" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K154">
         <v>96446</v>
@@ -8419,7 +8432,7 @@
         <v>373</v>
       </c>
       <c r="J155" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K155">
         <v>76600</v>
@@ -8460,7 +8473,7 @@
         <v>375</v>
       </c>
       <c r="J156" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="K156">
         <v>125569</v>
@@ -8501,7 +8514,7 @@
         <v>378</v>
       </c>
       <c r="J157" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K157">
         <v>51234</v>
@@ -8545,7 +8558,7 @@
         <v>380</v>
       </c>
       <c r="J158" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="K158">
         <v>123780</v>
@@ -8586,7 +8599,7 @@
         <v>383</v>
       </c>
       <c r="J159" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K159">
         <v>46000</v>
@@ -8624,7 +8637,7 @@
         <v>385</v>
       </c>
       <c r="J160" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K160">
         <v>35600</v>
@@ -8665,7 +8678,7 @@
         <v>387</v>
       </c>
       <c r="J161" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="K161">
         <v>199950</v>
@@ -8706,7 +8719,7 @@
         <v>389</v>
       </c>
       <c r="J162" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="K162">
         <v>108000</v>
@@ -8747,7 +8760,7 @@
         <v>391</v>
       </c>
       <c r="J163" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="K163">
         <v>142808</v>
@@ -8788,7 +8801,7 @@
         <v>393</v>
       </c>
       <c r="J164" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="K164">
         <v>80463</v>
@@ -8829,7 +8842,7 @@
         <v>395</v>
       </c>
       <c r="J165" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K165">
         <v>83000</v>
@@ -8867,7 +8880,7 @@
         <v>397</v>
       </c>
       <c r="J166" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K166">
         <v>129000</v>
@@ -8908,7 +8921,7 @@
         <v>400</v>
       </c>
       <c r="J167" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K167">
         <v>62209</v>
@@ -8949,7 +8962,7 @@
         <v>402</v>
       </c>
       <c r="J168" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K168">
         <v>36117</v>
@@ -8993,7 +9006,7 @@
         <v>404</v>
       </c>
       <c r="J169" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K169">
         <v>49900</v>
@@ -9037,7 +9050,7 @@
         <v>407</v>
       </c>
       <c r="J170" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K170">
         <v>39000</v>
@@ -9078,7 +9091,7 @@
         <v>409</v>
       </c>
       <c r="J171" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K171">
         <v>49000</v>
@@ -9116,7 +9129,7 @@
         <v>411</v>
       </c>
       <c r="J172" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K172">
         <v>59400</v>
@@ -9157,7 +9170,7 @@
         <v>413</v>
       </c>
       <c r="J173" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K173">
         <v>65000</v>
@@ -9201,7 +9214,7 @@
         <v>418</v>
       </c>
       <c r="J174" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K174">
         <v>47000</v>
@@ -9242,7 +9255,7 @@
         <v>420</v>
       </c>
       <c r="J175" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K175">
         <v>29000</v>
@@ -9286,7 +9299,7 @@
         <v>422</v>
       </c>
       <c r="J176" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K176">
         <v>132239</v>
@@ -9327,7 +9340,7 @@
         <v>424</v>
       </c>
       <c r="J177" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K177">
         <v>35016</v>
@@ -9365,7 +9378,7 @@
         <v>426</v>
       </c>
       <c r="J178" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K178">
         <v>60000</v>
@@ -9406,7 +9419,7 @@
         <v>429</v>
       </c>
       <c r="J179" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K179">
         <v>90244</v>
@@ -9444,7 +9457,7 @@
         <v>431</v>
       </c>
       <c r="J180" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K180">
         <v>38700</v>
@@ -9482,7 +9495,7 @@
         <v>433</v>
       </c>
       <c r="J181" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="K181">
         <v>62414</v>
@@ -9520,7 +9533,7 @@
         <v>435</v>
       </c>
       <c r="J182" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K182">
         <v>51000</v>
@@ -9561,7 +9574,7 @@
         <v>437</v>
       </c>
       <c r="J183" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K183">
         <v>53115</v>
@@ -9599,7 +9612,7 @@
         <v>439</v>
       </c>
       <c r="J184" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K184">
         <v>120000</v>
@@ -9640,7 +9653,7 @@
         <v>441</v>
       </c>
       <c r="J185" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K185">
         <v>66477</v>
@@ -9805,8 +9818,8 @@
       <c r="A190">
         <v>189</v>
       </c>
-      <c r="B190" t="s">
-        <v>452</v>
+      <c r="B190" s="2" t="s">
+        <v>491</v>
       </c>
       <c r="C190" t="s">
         <v>443</v>
@@ -9820,8 +9833,8 @@
       <c r="H190" t="s">
         <v>87</v>
       </c>
-      <c r="I190" t="s">
-        <v>88</v>
+      <c r="I190" s="4" t="s">
+        <v>492</v>
       </c>
       <c r="K190">
         <v>26737</v>
@@ -9841,7 +9854,7 @@
         <v>190</v>
       </c>
       <c r="B191" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C191" t="s">
         <v>443</v>
@@ -9859,7 +9872,7 @@
         <v>444</v>
       </c>
       <c r="I191" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="K191">
         <v>60000</v>
@@ -9879,7 +9892,7 @@
         <v>191</v>
       </c>
       <c r="B192" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C192" t="s">
         <v>443</v>
@@ -9894,7 +9907,7 @@
         <v>444</v>
       </c>
       <c r="I192" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="K192">
         <v>34895</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yuhang/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BD0F26C-52C8-2B42-B2C2-031F7567C299}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7947D7E-7740-1A43-874F-4D42D0BC2C70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1577" uniqueCount="493">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1579" uniqueCount="494">
   <si>
     <t>所在市</t>
   </si>
@@ -632,9 +632,6 @@
     <t>2015 Q1</t>
   </si>
   <si>
-    <t>116.362665,39.921274</t>
-  </si>
-  <si>
     <t>月坛金融中心E座</t>
   </si>
   <si>
@@ -654,9 +651,6 @@
   </si>
   <si>
     <t>海淀区</t>
-  </si>
-  <si>
-    <t>116.365264,39.974346</t>
   </si>
   <si>
     <t>航宇大厦B座</t>
@@ -1530,6 +1524,18 @@
   </si>
   <si>
     <t>116.680295,39.907589</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>116.358503,39.931864</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>这个还有问题</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>116.362230,39.920558</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1930,7 +1936,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B280671-4AFA-4641-88D4-A51F39483890}">
-  <dimension ref="A1:N192"/>
+  <dimension ref="A1:P192"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="5.6640625" bestFit="1" customWidth="1"/>
@@ -1950,22 +1956,22 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" t="s">
+        <v>459</v>
+      </c>
+      <c r="B1" t="s">
         <v>461</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
+        <v>462</v>
+      </c>
+      <c r="D1" t="s">
         <v>463</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="F1" t="s">
         <v>464</v>
-      </c>
-      <c r="D1" t="s">
-        <v>465</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>471</v>
-      </c>
-      <c r="F1" t="s">
-        <v>466</v>
       </c>
       <c r="G1" t="s">
         <v>0</v>
@@ -1977,19 +1983,19 @@
         <v>2</v>
       </c>
       <c r="J1" t="s">
+        <v>465</v>
+      </c>
+      <c r="K1" t="s">
+        <v>460</v>
+      </c>
+      <c r="L1" t="s">
+        <v>466</v>
+      </c>
+      <c r="M1" t="s">
         <v>467</v>
       </c>
-      <c r="K1" t="s">
-        <v>462</v>
-      </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>468</v>
-      </c>
-      <c r="M1" t="s">
-        <v>469</v>
-      </c>
-      <c r="N1" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -2018,7 +2024,7 @@
         <v>9</v>
       </c>
       <c r="J2" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K2">
         <v>72308</v>
@@ -2059,7 +2065,7 @@
         <v>12</v>
       </c>
       <c r="J3" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K3">
         <v>72308</v>
@@ -2103,7 +2109,7 @@
         <v>17</v>
       </c>
       <c r="J4" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K4">
         <v>130769</v>
@@ -2147,7 +2153,7 @@
         <v>20</v>
       </c>
       <c r="J5" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K5">
         <v>64615</v>
@@ -2191,7 +2197,7 @@
         <v>24</v>
       </c>
       <c r="J6" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K6">
         <v>80091</v>
@@ -2232,7 +2238,7 @@
         <v>27</v>
       </c>
       <c r="J7" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="K7">
         <v>70673</v>
@@ -2276,7 +2282,7 @@
         <v>30</v>
       </c>
       <c r="J8" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K8">
         <v>90466</v>
@@ -2317,7 +2323,7 @@
         <v>32</v>
       </c>
       <c r="J9" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="K9">
         <v>46720</v>
@@ -2361,7 +2367,7 @@
         <v>35</v>
       </c>
       <c r="J10" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="K10">
         <v>95000</v>
@@ -2405,7 +2411,7 @@
         <v>38</v>
       </c>
       <c r="J11" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K11">
         <v>85300</v>
@@ -2449,7 +2455,7 @@
         <v>41</v>
       </c>
       <c r="J12" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="K12">
         <v>33305</v>
@@ -2493,7 +2499,7 @@
         <v>43</v>
       </c>
       <c r="J13" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K13">
         <v>120245.21</v>
@@ -2537,7 +2543,7 @@
         <v>43</v>
       </c>
       <c r="J14" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K14">
         <v>70425.53</v>
@@ -2581,7 +2587,7 @@
         <v>47</v>
       </c>
       <c r="J15" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K15">
         <v>78000</v>
@@ -2625,7 +2631,7 @@
         <v>50</v>
       </c>
       <c r="J16" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="K16">
         <v>102796</v>
@@ -2669,7 +2675,7 @@
         <v>52</v>
       </c>
       <c r="J17" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="K17">
         <v>49200</v>
@@ -2713,7 +2719,7 @@
         <v>54</v>
       </c>
       <c r="J18" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="K18">
         <v>65096</v>
@@ -2757,7 +2763,7 @@
         <v>57</v>
       </c>
       <c r="J19" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K19">
         <v>56000</v>
@@ -2801,7 +2807,7 @@
         <v>60</v>
       </c>
       <c r="J20" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="K20">
         <v>177847</v>
@@ -2845,7 +2851,7 @@
         <v>63</v>
       </c>
       <c r="J21" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K21">
         <v>83000</v>
@@ -2886,7 +2892,7 @@
         <v>66</v>
       </c>
       <c r="J22" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="K22">
         <v>26000</v>
@@ -2927,7 +2933,7 @@
         <v>68</v>
       </c>
       <c r="J23" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K23">
         <v>85887</v>
@@ -2968,7 +2974,7 @@
         <v>70</v>
       </c>
       <c r="J24" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K24">
         <v>20000</v>
@@ -3012,7 +3018,7 @@
         <v>73</v>
       </c>
       <c r="J25" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K25">
         <v>146385</v>
@@ -3056,7 +3062,7 @@
         <v>76</v>
       </c>
       <c r="J26" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K26">
         <v>87000</v>
@@ -3100,7 +3106,7 @@
         <v>79</v>
       </c>
       <c r="J27" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K27">
         <v>147166.79999999999</v>
@@ -3144,7 +3150,7 @@
         <v>82</v>
       </c>
       <c r="J28" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K28">
         <v>46063</v>
@@ -3188,7 +3194,7 @@
         <v>85</v>
       </c>
       <c r="J29" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="K29">
         <v>47261</v>
@@ -3208,7 +3214,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C30" t="s">
         <v>4</v>
@@ -3226,13 +3232,13 @@
         <v>7</v>
       </c>
       <c r="H30" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="I30" s="2" t="s">
         <v>476</v>
       </c>
-      <c r="I30" s="2" t="s">
-        <v>478</v>
-      </c>
       <c r="J30" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K30">
         <v>119000</v>
@@ -3273,7 +3279,7 @@
         <v>91</v>
       </c>
       <c r="J31" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="K31">
         <v>47000</v>
@@ -3317,7 +3323,7 @@
         <v>93</v>
       </c>
       <c r="J32" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="K32">
         <v>186000</v>
@@ -3355,7 +3361,7 @@
         <v>95</v>
       </c>
       <c r="J33" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K33">
         <v>40800</v>
@@ -3396,7 +3402,7 @@
         <v>95</v>
       </c>
       <c r="J34" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K34">
         <v>55200</v>
@@ -3440,7 +3446,7 @@
         <v>99</v>
       </c>
       <c r="J35" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="K35">
         <v>350000</v>
@@ -3481,7 +3487,7 @@
         <v>101</v>
       </c>
       <c r="J36" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K36">
         <v>65000</v>
@@ -3522,7 +3528,7 @@
         <v>101</v>
       </c>
       <c r="J37" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K37">
         <v>35000</v>
@@ -3563,7 +3569,7 @@
         <v>104</v>
       </c>
       <c r="J38" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="K38">
         <v>47000</v>
@@ -3607,7 +3613,7 @@
         <v>107</v>
       </c>
       <c r="J39" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="K39">
         <v>120000</v>
@@ -3648,7 +3654,7 @@
         <v>109</v>
       </c>
       <c r="J40" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K40">
         <v>83000</v>
@@ -3689,7 +3695,7 @@
         <v>111</v>
       </c>
       <c r="J41" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="K41">
         <v>66030</v>
@@ -3727,7 +3733,7 @@
         <v>113</v>
       </c>
       <c r="J42" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="K42">
         <v>40000</v>
@@ -3771,7 +3777,7 @@
         <v>118</v>
       </c>
       <c r="J43" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K43">
         <v>40000</v>
@@ -3812,7 +3818,7 @@
         <v>121</v>
       </c>
       <c r="J44" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K44">
         <v>54100</v>
@@ -3853,10 +3859,10 @@
         <v>117</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="J45" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K45">
         <v>100000</v>
@@ -3897,10 +3903,10 @@
         <v>117</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="J46" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K46">
         <v>150000</v>
@@ -3941,10 +3947,10 @@
         <v>117</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="J47" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K47">
         <v>50000</v>
@@ -3988,7 +3994,7 @@
         <v>130</v>
       </c>
       <c r="J48" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="K48">
         <v>43000</v>
@@ -4029,7 +4035,7 @@
         <v>133</v>
       </c>
       <c r="J49" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="K49">
         <v>65000</v>
@@ -4070,7 +4076,7 @@
         <v>136</v>
       </c>
       <c r="J50" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="51" spans="1:14">
@@ -4102,7 +4108,7 @@
         <v>138</v>
       </c>
       <c r="J51" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="K51">
         <v>56000</v>
@@ -4143,7 +4149,7 @@
         <v>140</v>
       </c>
       <c r="J52" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="K52">
         <v>160000</v>
@@ -4184,7 +4190,7 @@
         <v>142</v>
       </c>
       <c r="J53" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="K53">
         <v>33000</v>
@@ -4228,7 +4234,7 @@
         <v>145</v>
       </c>
       <c r="J54" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="K54">
         <v>41318</v>
@@ -4269,7 +4275,7 @@
         <v>147</v>
       </c>
       <c r="J55" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K55">
         <v>34131</v>
@@ -4310,7 +4316,7 @@
         <v>150</v>
       </c>
       <c r="J56" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K56">
         <v>48000</v>
@@ -4351,7 +4357,7 @@
         <v>118</v>
       </c>
       <c r="J57" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K57">
         <v>16000</v>
@@ -4395,7 +4401,7 @@
         <v>154</v>
       </c>
       <c r="J58" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="K58">
         <v>30000</v>
@@ -4439,7 +4445,7 @@
         <v>157</v>
       </c>
       <c r="J59" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="K59">
         <v>56000</v>
@@ -4483,7 +4489,7 @@
         <v>160</v>
       </c>
       <c r="J60" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K60">
         <v>43000</v>
@@ -4524,7 +4530,7 @@
         <v>162</v>
       </c>
       <c r="J61" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="K61">
         <v>110000</v>
@@ -4562,7 +4568,7 @@
         <v>164</v>
       </c>
       <c r="J62" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K62">
         <v>56160</v>
@@ -4603,7 +4609,7 @@
         <v>166</v>
       </c>
       <c r="J63" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K63">
         <v>138444</v>
@@ -4647,7 +4653,7 @@
         <v>170</v>
       </c>
       <c r="J64" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="K64">
         <v>31000</v>
@@ -4688,7 +4694,7 @@
         <v>173</v>
       </c>
       <c r="J65" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="K65">
         <v>120000</v>
@@ -4729,7 +4735,7 @@
         <v>175</v>
       </c>
       <c r="J66" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="K66">
         <v>25900</v>
@@ -4770,7 +4776,7 @@
         <v>178</v>
       </c>
       <c r="J67" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="K67">
         <v>47986</v>
@@ -4814,7 +4820,7 @@
         <v>180</v>
       </c>
       <c r="J68" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="K68">
         <v>194000</v>
@@ -4858,7 +4864,7 @@
         <v>182</v>
       </c>
       <c r="J69" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="K69">
         <v>39724</v>
@@ -4896,10 +4902,10 @@
         <v>87</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="J70" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="K70">
         <v>48437.45</v>
@@ -4940,7 +4946,7 @@
         <v>186</v>
       </c>
       <c r="J71" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="K71">
         <v>37910</v>
@@ -4960,7 +4966,7 @@
         <v>71</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C72" t="s">
         <v>168</v>
@@ -4978,10 +4984,10 @@
         <v>87</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J72" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="K72">
         <v>21220</v>
@@ -5022,7 +5028,7 @@
         <v>188</v>
       </c>
       <c r="J73" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="K73">
         <v>77877</v>
@@ -5066,7 +5072,7 @@
         <v>190</v>
       </c>
       <c r="J74" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="K74">
         <v>80311.53</v>
@@ -5110,7 +5116,7 @@
         <v>193</v>
       </c>
       <c r="J75" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="K75">
         <v>38000</v>
@@ -5151,7 +5157,7 @@
         <v>196</v>
       </c>
       <c r="J76" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="K76">
         <v>37800</v>
@@ -5191,11 +5197,11 @@
       <c r="H77" t="s">
         <v>87</v>
       </c>
-      <c r="I77" t="s">
-        <v>199</v>
+      <c r="I77" s="1" t="s">
+        <v>493</v>
       </c>
       <c r="J77" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="K77">
         <v>54581</v>
@@ -5215,7 +5221,7 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C78" t="s">
         <v>168</v>
@@ -5227,7 +5233,7 @@
         <v>16</v>
       </c>
       <c r="F78" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G78" t="s">
         <v>7</v>
@@ -5239,7 +5245,7 @@
         <v>88</v>
       </c>
       <c r="J78" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="K78">
         <v>25000</v>
@@ -5259,7 +5265,7 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C79" t="s">
         <v>168</v>
@@ -5280,10 +5286,10 @@
         <v>87</v>
       </c>
       <c r="I79" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="J79" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="K79">
         <v>52698</v>
@@ -5302,8 +5308,8 @@
       <c r="A80">
         <v>79</v>
       </c>
-      <c r="B80" t="s">
-        <v>204</v>
+      <c r="B80" s="2" t="s">
+        <v>203</v>
       </c>
       <c r="C80" t="s">
         <v>168</v>
@@ -5312,19 +5318,19 @@
         <v>5</v>
       </c>
       <c r="F80" t="s">
+        <v>204</v>
+      </c>
+      <c r="G80" t="s">
+        <v>7</v>
+      </c>
+      <c r="H80" t="s">
         <v>205</v>
       </c>
-      <c r="G80" t="s">
-        <v>7</v>
-      </c>
-      <c r="H80" t="s">
-        <v>206</v>
-      </c>
-      <c r="I80" t="s">
-        <v>207</v>
+      <c r="I80" s="2" t="s">
+        <v>491</v>
       </c>
       <c r="J80" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="K80">
         <v>38500</v>
@@ -5344,13 +5350,13 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C81" t="s">
         <v>168</v>
       </c>
       <c r="D81" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G81" t="s">
         <v>7</v>
@@ -5359,10 +5365,10 @@
         <v>87</v>
       </c>
       <c r="I81" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J81" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="K81">
         <v>27200</v>
@@ -5382,7 +5388,7 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C82" t="s">
         <v>144</v>
@@ -5394,7 +5400,7 @@
         <v>16</v>
       </c>
       <c r="F82" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="G82" t="s">
         <v>7</v>
@@ -5403,10 +5409,10 @@
         <v>8</v>
       </c>
       <c r="I82" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="J82" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="K82">
         <v>60000</v>
@@ -5426,7 +5432,7 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C83" t="s">
         <v>144</v>
@@ -5435,7 +5441,7 @@
         <v>5</v>
       </c>
       <c r="F83" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="G83" t="s">
         <v>7</v>
@@ -5444,10 +5450,10 @@
         <v>8</v>
       </c>
       <c r="I83" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="J83" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K83">
         <v>50000</v>
@@ -5467,7 +5473,7 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C84" t="s">
         <v>144</v>
@@ -5488,10 +5494,10 @@
         <v>8</v>
       </c>
       <c r="I84" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="J84" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="K84">
         <v>131575</v>
@@ -5511,7 +5517,7 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C85" t="s">
         <v>144</v>
@@ -5529,10 +5535,10 @@
         <v>8</v>
       </c>
       <c r="I85" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="J85" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K85">
         <v>99500</v>
@@ -5552,7 +5558,7 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C86" t="s">
         <v>144</v>
@@ -5561,7 +5567,7 @@
         <v>5</v>
       </c>
       <c r="F86" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G86" t="s">
         <v>7</v>
@@ -5570,10 +5576,10 @@
         <v>8</v>
       </c>
       <c r="I86" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="J86" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="K86">
         <v>32000</v>
@@ -5593,7 +5599,7 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C87" t="s">
         <v>144</v>
@@ -5614,10 +5620,10 @@
         <v>8</v>
       </c>
       <c r="I87" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="J87" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="K87">
         <v>52170</v>
@@ -5637,7 +5643,7 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C88" t="s">
         <v>144</v>
@@ -5646,7 +5652,7 @@
         <v>5</v>
       </c>
       <c r="F88" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G88" t="s">
         <v>7</v>
@@ -5655,10 +5661,10 @@
         <v>8</v>
       </c>
       <c r="I88" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="J88" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="K88">
         <v>46000</v>
@@ -5678,7 +5684,7 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C89" t="s">
         <v>144</v>
@@ -5690,7 +5696,7 @@
         <v>23</v>
       </c>
       <c r="F89" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="G89" t="s">
         <v>7</v>
@@ -5699,10 +5705,10 @@
         <v>8</v>
       </c>
       <c r="I89" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="J89" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K89">
         <v>45013</v>
@@ -5722,7 +5728,7 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C90" t="s">
         <v>144</v>
@@ -5740,10 +5746,10 @@
         <v>8</v>
       </c>
       <c r="I90" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="J90" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="K90">
         <v>48566</v>
@@ -5763,7 +5769,7 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C91" t="s">
         <v>144</v>
@@ -5772,7 +5778,7 @@
         <v>5</v>
       </c>
       <c r="F91" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="G91" t="s">
         <v>7</v>
@@ -5781,10 +5787,10 @@
         <v>8</v>
       </c>
       <c r="I91" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="J91" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K91">
         <v>55618</v>
@@ -5804,7 +5810,7 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C92" t="s">
         <v>144</v>
@@ -5822,10 +5828,10 @@
         <v>8</v>
       </c>
       <c r="I92" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="J92" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="K92">
         <v>47000</v>
@@ -5845,7 +5851,7 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C93" t="s">
         <v>144</v>
@@ -5857,7 +5863,7 @@
         <v>23</v>
       </c>
       <c r="F93" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G93" t="s">
         <v>7</v>
@@ -5866,10 +5872,10 @@
         <v>8</v>
       </c>
       <c r="I93" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="J93" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K93">
         <v>87763</v>
@@ -5889,7 +5895,7 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C94" t="s">
         <v>144</v>
@@ -5901,7 +5907,7 @@
         <v>16</v>
       </c>
       <c r="F94" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="G94" t="s">
         <v>7</v>
@@ -5910,10 +5916,10 @@
         <v>8</v>
       </c>
       <c r="I94" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="J94" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="K94">
         <v>100658</v>
@@ -5933,7 +5939,7 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C95" t="s">
         <v>144</v>
@@ -5942,7 +5948,7 @@
         <v>5</v>
       </c>
       <c r="F95" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="G95" t="s">
         <v>7</v>
@@ -5951,10 +5957,10 @@
         <v>8</v>
       </c>
       <c r="I95" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="J95" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="K95">
         <v>67000</v>
@@ -5974,7 +5980,7 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C96" t="s">
         <v>144</v>
@@ -5995,10 +6001,10 @@
         <v>8</v>
       </c>
       <c r="I96" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="J96" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="K96">
         <v>39431</v>
@@ -6018,7 +6024,7 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C97" t="s">
         <v>144</v>
@@ -6036,10 +6042,10 @@
         <v>8</v>
       </c>
       <c r="I97" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="J97" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="K97">
         <v>34273</v>
@@ -6059,7 +6065,7 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C98" t="s">
         <v>144</v>
@@ -6077,7 +6083,7 @@
         <v>73</v>
       </c>
       <c r="J98" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K98">
         <v>40000</v>
@@ -6097,7 +6103,7 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C99" t="s">
         <v>144</v>
@@ -6115,10 +6121,10 @@
         <v>8</v>
       </c>
       <c r="I99" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="J99" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="K99">
         <v>65000</v>
@@ -6138,10 +6144,10 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C100" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D100" t="s">
         <v>5</v>
@@ -6150,19 +6156,19 @@
         <v>23</v>
       </c>
       <c r="F100" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="G100" t="s">
         <v>7</v>
       </c>
       <c r="H100" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I100" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="J100" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="K100">
         <v>49000</v>
@@ -6182,10 +6188,10 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C101" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D101" t="s">
         <v>14</v>
@@ -6194,19 +6200,19 @@
         <v>23</v>
       </c>
       <c r="F101" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="G101" t="s">
         <v>7</v>
       </c>
       <c r="H101" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I101" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="J101" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="K101">
         <v>95000</v>
@@ -6226,10 +6232,10 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C102" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D102" t="s">
         <v>5</v>
@@ -6238,19 +6244,19 @@
         <v>23</v>
       </c>
       <c r="F102" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="G102" t="s">
         <v>7</v>
       </c>
       <c r="H102" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I102" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="J102" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="K102">
         <v>45000</v>
@@ -6270,10 +6276,10 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C103" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D103" t="s">
         <v>5</v>
@@ -6285,13 +6291,13 @@
         <v>7</v>
       </c>
       <c r="H103" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I103" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="J103" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="K103">
         <v>124500</v>
@@ -6311,10 +6317,10 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C104" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D104" t="s">
         <v>5</v>
@@ -6326,13 +6332,13 @@
         <v>7</v>
       </c>
       <c r="H104" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I104" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="J104" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="K104">
         <v>64000</v>
@@ -6352,10 +6358,10 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C105" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D105" t="s">
         <v>5</v>
@@ -6367,13 +6373,13 @@
         <v>7</v>
       </c>
       <c r="H105" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I105" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="J105" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="K105">
         <v>25000</v>
@@ -6393,10 +6399,10 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C106" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D106" t="s">
         <v>5</v>
@@ -6408,13 +6414,13 @@
         <v>7</v>
       </c>
       <c r="H106" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I106" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="J106" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="K106">
         <v>38498</v>
@@ -6434,25 +6440,25 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C107" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D107" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G107" t="s">
         <v>7</v>
       </c>
       <c r="H107" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I107" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="J107" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="K107">
         <v>166433</v>
@@ -6472,10 +6478,10 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C108" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D108" t="s">
         <v>14</v>
@@ -6490,13 +6496,13 @@
         <v>7</v>
       </c>
       <c r="H108" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I108" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="J108" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="K108">
         <v>58000</v>
@@ -6516,28 +6522,28 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
+        <v>275</v>
+      </c>
+      <c r="C109" t="s">
+        <v>254</v>
+      </c>
+      <c r="D109" t="s">
+        <v>5</v>
+      </c>
+      <c r="F109" t="s">
+        <v>276</v>
+      </c>
+      <c r="G109" t="s">
+        <v>7</v>
+      </c>
+      <c r="H109" t="s">
+        <v>205</v>
+      </c>
+      <c r="I109" t="s">
         <v>277</v>
       </c>
-      <c r="C109" t="s">
-        <v>256</v>
-      </c>
-      <c r="D109" t="s">
-        <v>5</v>
-      </c>
-      <c r="F109" t="s">
-        <v>278</v>
-      </c>
-      <c r="G109" t="s">
-        <v>7</v>
-      </c>
-      <c r="H109" t="s">
-        <v>206</v>
-      </c>
-      <c r="I109" t="s">
-        <v>279</v>
-      </c>
       <c r="J109" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="K109">
         <v>51872</v>
@@ -6557,28 +6563,28 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C110" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D110" t="s">
         <v>5</v>
       </c>
       <c r="F110" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G110" t="s">
         <v>7</v>
       </c>
       <c r="H110" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I110" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="J110" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="K110">
         <v>21632</v>
@@ -6598,28 +6604,28 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C111" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D111" t="s">
         <v>5</v>
       </c>
       <c r="F111" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G111" t="s">
         <v>7</v>
       </c>
       <c r="H111" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I111" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="J111" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="K111">
         <v>69000</v>
@@ -6639,28 +6645,28 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
+        <v>282</v>
+      </c>
+      <c r="C112" t="s">
+        <v>254</v>
+      </c>
+      <c r="D112" t="s">
+        <v>5</v>
+      </c>
+      <c r="F112" t="s">
+        <v>283</v>
+      </c>
+      <c r="G112" t="s">
+        <v>7</v>
+      </c>
+      <c r="H112" t="s">
+        <v>205</v>
+      </c>
+      <c r="I112" t="s">
         <v>284</v>
       </c>
-      <c r="C112" t="s">
-        <v>256</v>
-      </c>
-      <c r="D112" t="s">
-        <v>5</v>
-      </c>
-      <c r="F112" t="s">
-        <v>285</v>
-      </c>
-      <c r="G112" t="s">
-        <v>7</v>
-      </c>
-      <c r="H112" t="s">
-        <v>206</v>
-      </c>
-      <c r="I112" t="s">
-        <v>286</v>
-      </c>
       <c r="J112" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="K112">
         <v>54000</v>
@@ -6675,15 +6681,15 @@
         <v>19941.5</v>
       </c>
     </row>
-    <row r="113" spans="1:14">
+    <row r="113" spans="1:16">
       <c r="A113">
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C113" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D113" t="s">
         <v>5</v>
@@ -6695,13 +6701,13 @@
         <v>7</v>
       </c>
       <c r="H113" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I113" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="J113" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="K113">
         <v>57400</v>
@@ -6716,15 +6722,15 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="114" spans="1:14">
+    <row r="114" spans="1:16">
       <c r="A114">
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C114" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D114" t="s">
         <v>14</v>
@@ -6736,13 +6742,13 @@
         <v>7</v>
       </c>
       <c r="H114" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I114" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="J114" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="K114">
         <v>60000</v>
@@ -6757,15 +6763,15 @@
         <v>427</v>
       </c>
     </row>
-    <row r="115" spans="1:14">
+    <row r="115" spans="1:16">
       <c r="A115">
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C115" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D115" t="s">
         <v>14</v>
@@ -6777,13 +6783,13 @@
         <v>7</v>
       </c>
       <c r="H115" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I115" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="J115" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="K115">
         <v>60000</v>
@@ -6798,15 +6804,15 @@
         <v>11500</v>
       </c>
     </row>
-    <row r="116" spans="1:14">
+    <row r="116" spans="1:16">
       <c r="A116">
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C116" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D116" t="s">
         <v>5</v>
@@ -6815,13 +6821,13 @@
         <v>7</v>
       </c>
       <c r="H116" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I116" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="J116" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="K116">
         <v>33000</v>
@@ -6836,30 +6842,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:14">
+    <row r="117" spans="1:16">
       <c r="A117">
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C117" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D117" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G117" t="s">
         <v>7</v>
       </c>
       <c r="H117" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I117" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="J117" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="K117">
         <v>88786</v>
@@ -6874,30 +6880,30 @@
         <v>21000</v>
       </c>
     </row>
-    <row r="118" spans="1:14">
+    <row r="118" spans="1:16">
       <c r="A118">
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C118" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D118" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G118" t="s">
         <v>7</v>
       </c>
       <c r="H118" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I118" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="J118" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="K118">
         <v>134000</v>
@@ -6912,30 +6918,30 @@
         <v>31890</v>
       </c>
     </row>
-    <row r="119" spans="1:14">
+    <row r="119" spans="1:16">
       <c r="A119">
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C119" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D119" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G119" t="s">
         <v>7</v>
       </c>
       <c r="H119" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I119" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="J119" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="K119">
         <v>35000</v>
@@ -6950,30 +6956,30 @@
         <v>1116</v>
       </c>
     </row>
-    <row r="120" spans="1:14">
+    <row r="120" spans="1:16">
       <c r="A120">
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C120" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D120" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G120" t="s">
         <v>7</v>
       </c>
       <c r="H120" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I120" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="J120" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="K120">
         <v>18000</v>
@@ -6988,18 +6994,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:14">
+    <row r="121" spans="1:16">
       <c r="A121">
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C121" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D121" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E121" t="s">
         <v>16</v>
@@ -7008,13 +7014,13 @@
         <v>7</v>
       </c>
       <c r="H121" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I121" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="J121" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="K121">
         <v>105741</v>
@@ -7029,30 +7035,30 @@
         <v>5600</v>
       </c>
     </row>
-    <row r="122" spans="1:14">
+    <row r="122" spans="1:16">
       <c r="A122">
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C122" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D122" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G122" t="s">
         <v>7</v>
       </c>
       <c r="H122" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I122" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="J122" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="K122">
         <v>51000</v>
@@ -7067,15 +7073,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:14">
+    <row r="123" spans="1:16">
       <c r="A123">
         <v>122</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C123" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D123" t="s">
         <v>5</v>
@@ -7087,13 +7093,13 @@
         <v>7</v>
       </c>
       <c r="H123" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I123" s="3" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="J123" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="K123">
         <v>130143</v>
@@ -7107,28 +7113,31 @@
       <c r="N123">
         <v>36000</v>
       </c>
-    </row>
-    <row r="124" spans="1:14">
+      <c r="P123" s="1" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="124" spans="1:16">
       <c r="A124">
         <v>123</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C124" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="G124" t="s">
         <v>7</v>
       </c>
       <c r="H124" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I124" s="3" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="J124" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="K124">
         <v>121551.47</v>
@@ -7142,16 +7151,19 @@
       <c r="N124">
         <v>97326.47</v>
       </c>
-    </row>
-    <row r="125" spans="1:14">
+      <c r="P124" s="1" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="125" spans="1:16">
       <c r="A125">
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C125" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D125" t="s">
         <v>5</v>
@@ -7160,7 +7172,7 @@
         <v>16</v>
       </c>
       <c r="F125" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="G125" t="s">
         <v>7</v>
@@ -7169,10 +7181,10 @@
         <v>8</v>
       </c>
       <c r="I125" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J125" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K125">
         <v>110000</v>
@@ -7187,15 +7199,15 @@
         <v>15956.21</v>
       </c>
     </row>
-    <row r="126" spans="1:14">
+    <row r="126" spans="1:16">
       <c r="A126">
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C126" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D126" t="s">
         <v>5</v>
@@ -7204,7 +7216,7 @@
         <v>23</v>
       </c>
       <c r="F126" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G126" t="s">
         <v>7</v>
@@ -7213,10 +7225,10 @@
         <v>8</v>
       </c>
       <c r="I126" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="J126" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K126">
         <v>56000</v>
@@ -7231,15 +7243,15 @@
         <v>6631</v>
       </c>
     </row>
-    <row r="127" spans="1:14">
+    <row r="127" spans="1:16">
       <c r="A127">
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C127" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D127" t="s">
         <v>5</v>
@@ -7254,10 +7266,10 @@
         <v>8</v>
       </c>
       <c r="I127" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="J127" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K127">
         <v>89177</v>
@@ -7272,15 +7284,15 @@
         <v>14329.850000000002</v>
       </c>
     </row>
-    <row r="128" spans="1:14">
+    <row r="128" spans="1:16">
       <c r="A128">
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C128" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D128" t="s">
         <v>5</v>
@@ -7289,7 +7301,7 @@
         <v>23</v>
       </c>
       <c r="F128" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="G128" t="s">
         <v>7</v>
@@ -7298,10 +7310,10 @@
         <v>8</v>
       </c>
       <c r="I128" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="J128" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K128">
         <v>30000</v>
@@ -7321,10 +7333,10 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C129" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D129" t="s">
         <v>5</v>
@@ -7333,7 +7345,7 @@
         <v>16</v>
       </c>
       <c r="F129" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="G129" t="s">
         <v>7</v>
@@ -7342,10 +7354,10 @@
         <v>8</v>
       </c>
       <c r="I129" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J129" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K129">
         <v>54550</v>
@@ -7365,10 +7377,10 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C130" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D130" t="s">
         <v>5</v>
@@ -7377,7 +7389,7 @@
         <v>16</v>
       </c>
       <c r="F130" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="G130" t="s">
         <v>7</v>
@@ -7386,10 +7398,10 @@
         <v>8</v>
       </c>
       <c r="I130" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="J130" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K130">
         <v>125000</v>
@@ -7409,10 +7421,10 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C131" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D131" t="s">
         <v>5</v>
@@ -7421,7 +7433,7 @@
         <v>16</v>
       </c>
       <c r="F131" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="G131" t="s">
         <v>7</v>
@@ -7430,10 +7442,10 @@
         <v>8</v>
       </c>
       <c r="I131" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J131" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K131">
         <v>69100</v>
@@ -7453,10 +7465,10 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C132" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D132" t="s">
         <v>5</v>
@@ -7474,10 +7486,10 @@
         <v>8</v>
       </c>
       <c r="I132" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="J132" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K132">
         <v>118290</v>
@@ -7497,16 +7509,16 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C133" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D133" t="s">
         <v>5</v>
       </c>
       <c r="F133" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="G133" t="s">
         <v>7</v>
@@ -7515,10 +7527,10 @@
         <v>8</v>
       </c>
       <c r="I133" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="J133" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K133">
         <v>79900</v>
@@ -7538,10 +7550,10 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C134" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D134" t="s">
         <v>5</v>
@@ -7556,10 +7568,10 @@
         <v>8</v>
       </c>
       <c r="I134" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="J134" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K134">
         <v>39742.379999999997</v>
@@ -7579,10 +7591,10 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C135" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D135" t="s">
         <v>5</v>
@@ -7600,10 +7612,10 @@
         <v>8</v>
       </c>
       <c r="I135" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="J135" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K135">
         <v>48000</v>
@@ -7623,10 +7635,10 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C136" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D136" t="s">
         <v>14</v>
@@ -7641,10 +7653,10 @@
         <v>8</v>
       </c>
       <c r="I136" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="J136" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K136">
         <v>74722</v>
@@ -7664,13 +7676,13 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C137" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D137" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G137" t="s">
         <v>7</v>
@@ -7679,10 +7691,10 @@
         <v>8</v>
       </c>
       <c r="I137" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="J137" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K137">
         <v>55000</v>
@@ -7702,10 +7714,10 @@
         <v>137</v>
       </c>
       <c r="B138" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C138" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D138" t="s">
         <v>5</v>
@@ -7717,10 +7729,10 @@
         <v>117</v>
       </c>
       <c r="I138" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="J138" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K138">
         <v>128000</v>
@@ -7740,10 +7752,10 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C139" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D139" t="s">
         <v>5</v>
@@ -7761,10 +7773,10 @@
         <v>117</v>
       </c>
       <c r="I139" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="J139" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K139">
         <v>122000</v>
@@ -7784,10 +7796,10 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C140" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D140" t="s">
         <v>5</v>
@@ -7802,10 +7814,10 @@
         <v>117</v>
       </c>
       <c r="I140" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="J140" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K140">
         <v>22000</v>
@@ -7825,10 +7837,10 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C141" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D141" t="s">
         <v>5</v>
@@ -7843,10 +7855,10 @@
         <v>117</v>
       </c>
       <c r="I141" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="J141" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K141">
         <v>10000</v>
@@ -7866,10 +7878,10 @@
         <v>141</v>
       </c>
       <c r="B142" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C142" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D142" t="s">
         <v>5</v>
@@ -7884,10 +7896,10 @@
         <v>8</v>
       </c>
       <c r="I142" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="J142" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="K142">
         <v>64000</v>
@@ -7907,10 +7919,10 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C143" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D143" t="s">
         <v>5</v>
@@ -7925,10 +7937,10 @@
         <v>8</v>
       </c>
       <c r="I143" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="J143" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="K143">
         <v>95628</v>
@@ -7948,16 +7960,16 @@
         <v>143</v>
       </c>
       <c r="B144" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C144" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D144" t="s">
         <v>5</v>
       </c>
       <c r="F144" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="G144" t="s">
         <v>7</v>
@@ -7966,10 +7978,10 @@
         <v>8</v>
       </c>
       <c r="I144" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="J144" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="K144">
         <v>39562</v>
@@ -7989,10 +8001,10 @@
         <v>144</v>
       </c>
       <c r="B145" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C145" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D145" t="s">
         <v>5</v>
@@ -8001,7 +8013,7 @@
         <v>16</v>
       </c>
       <c r="F145" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="G145" t="s">
         <v>7</v>
@@ -8010,10 +8022,10 @@
         <v>8</v>
       </c>
       <c r="I145" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="J145" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K145">
         <v>105000</v>
@@ -8033,10 +8045,10 @@
         <v>145</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="C146" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D146" t="s">
         <v>5</v>
@@ -8045,7 +8057,7 @@
         <v>23</v>
       </c>
       <c r="F146" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="G146" t="s">
         <v>7</v>
@@ -8054,10 +8066,10 @@
         <v>8</v>
       </c>
       <c r="I146" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="J146" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K146">
         <v>60000</v>
@@ -8077,10 +8089,10 @@
         <v>146</v>
       </c>
       <c r="B147" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C147" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D147" t="s">
         <v>5</v>
@@ -8095,10 +8107,10 @@
         <v>8</v>
       </c>
       <c r="I147" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="J147" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="K147">
         <v>39964</v>
@@ -8118,10 +8130,10 @@
         <v>147</v>
       </c>
       <c r="B148" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C148" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D148" t="s">
         <v>5</v>
@@ -8136,10 +8148,10 @@
         <v>8</v>
       </c>
       <c r="I148" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="J148" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K148">
         <v>94000</v>
@@ -8159,10 +8171,10 @@
         <v>148</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C149" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D149" t="s">
         <v>5</v>
@@ -8180,10 +8192,10 @@
         <v>8</v>
       </c>
       <c r="I149" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="J149" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K149">
         <v>75000</v>
@@ -8206,13 +8218,13 @@
         <v>183</v>
       </c>
       <c r="C150" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D150" t="s">
         <v>5</v>
       </c>
       <c r="F150" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="G150" t="s">
         <v>7</v>
@@ -8221,10 +8233,10 @@
         <v>87</v>
       </c>
       <c r="I150" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="J150" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K150">
         <v>48767</v>
@@ -8244,10 +8256,10 @@
         <v>150</v>
       </c>
       <c r="B151" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C151" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D151" t="s">
         <v>5</v>
@@ -8265,10 +8277,10 @@
         <v>8</v>
       </c>
       <c r="I151" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="J151" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K151">
         <v>63824</v>
@@ -8288,10 +8300,10 @@
         <v>151</v>
       </c>
       <c r="B152" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C152" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D152" t="s">
         <v>14</v>
@@ -8309,10 +8321,10 @@
         <v>8</v>
       </c>
       <c r="I152" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="J152" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K152">
         <v>117000</v>
@@ -8332,10 +8344,10 @@
         <v>152</v>
       </c>
       <c r="B153" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C153" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D153" t="s">
         <v>5</v>
@@ -8347,10 +8359,10 @@
         <v>8</v>
       </c>
       <c r="I153" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="J153" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K153">
         <v>41000</v>
@@ -8370,10 +8382,10 @@
         <v>153</v>
       </c>
       <c r="B154" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C154" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D154" t="s">
         <v>5</v>
@@ -8385,10 +8397,10 @@
         <v>8</v>
       </c>
       <c r="I154" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="J154" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="K154">
         <v>96446</v>
@@ -8408,10 +8420,10 @@
         <v>154</v>
       </c>
       <c r="B155" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C155" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D155" t="s">
         <v>5</v>
@@ -8426,13 +8438,13 @@
         <v>7</v>
       </c>
       <c r="H155" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="I155" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="J155" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K155">
         <v>76600</v>
@@ -8452,10 +8464,10 @@
         <v>155</v>
       </c>
       <c r="B156" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C156" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D156" t="s">
         <v>5</v>
@@ -8467,13 +8479,13 @@
         <v>7</v>
       </c>
       <c r="H156" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="I156" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="J156" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="K156">
         <v>125569</v>
@@ -8493,28 +8505,28 @@
         <v>156</v>
       </c>
       <c r="B157" t="s">
+        <v>374</v>
+      </c>
+      <c r="C157" t="s">
+        <v>369</v>
+      </c>
+      <c r="D157" t="s">
+        <v>5</v>
+      </c>
+      <c r="F157" t="s">
+        <v>375</v>
+      </c>
+      <c r="G157" t="s">
+        <v>7</v>
+      </c>
+      <c r="H157" t="s">
+        <v>370</v>
+      </c>
+      <c r="I157" t="s">
         <v>376</v>
       </c>
-      <c r="C157" t="s">
-        <v>371</v>
-      </c>
-      <c r="D157" t="s">
-        <v>5</v>
-      </c>
-      <c r="F157" t="s">
-        <v>377</v>
-      </c>
-      <c r="G157" t="s">
-        <v>7</v>
-      </c>
-      <c r="H157" t="s">
-        <v>372</v>
-      </c>
-      <c r="I157" t="s">
-        <v>378</v>
-      </c>
       <c r="J157" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K157">
         <v>51234</v>
@@ -8534,10 +8546,10 @@
         <v>157</v>
       </c>
       <c r="B158" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C158" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D158" t="s">
         <v>5</v>
@@ -8552,13 +8564,13 @@
         <v>7</v>
       </c>
       <c r="H158" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="I158" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="J158" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="K158">
         <v>123780</v>
@@ -8578,28 +8590,28 @@
         <v>158</v>
       </c>
       <c r="B159" t="s">
+        <v>379</v>
+      </c>
+      <c r="C159" t="s">
+        <v>369</v>
+      </c>
+      <c r="D159" t="s">
+        <v>5</v>
+      </c>
+      <c r="F159" t="s">
+        <v>380</v>
+      </c>
+      <c r="G159" t="s">
+        <v>7</v>
+      </c>
+      <c r="H159" t="s">
+        <v>370</v>
+      </c>
+      <c r="I159" t="s">
         <v>381</v>
       </c>
-      <c r="C159" t="s">
-        <v>371</v>
-      </c>
-      <c r="D159" t="s">
-        <v>5</v>
-      </c>
-      <c r="F159" t="s">
-        <v>382</v>
-      </c>
-      <c r="G159" t="s">
-        <v>7</v>
-      </c>
-      <c r="H159" t="s">
-        <v>372</v>
-      </c>
-      <c r="I159" t="s">
-        <v>383</v>
-      </c>
       <c r="J159" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K159">
         <v>46000</v>
@@ -8619,10 +8631,10 @@
         <v>159</v>
       </c>
       <c r="B160" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C160" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D160" t="s">
         <v>5</v>
@@ -8631,13 +8643,13 @@
         <v>7</v>
       </c>
       <c r="H160" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="I160" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="J160" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K160">
         <v>35600</v>
@@ -8657,10 +8669,10 @@
         <v>160</v>
       </c>
       <c r="B161" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C161" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D161" t="s">
         <v>5</v>
@@ -8672,13 +8684,13 @@
         <v>7</v>
       </c>
       <c r="H161" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="I161" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="J161" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="K161">
         <v>199950</v>
@@ -8698,10 +8710,10 @@
         <v>161</v>
       </c>
       <c r="B162" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C162" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D162" t="s">
         <v>5</v>
@@ -8713,13 +8725,13 @@
         <v>7</v>
       </c>
       <c r="H162" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="I162" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J162" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="K162">
         <v>108000</v>
@@ -8739,10 +8751,10 @@
         <v>162</v>
       </c>
       <c r="B163" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C163" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D163" t="s">
         <v>5</v>
@@ -8754,13 +8766,13 @@
         <v>7</v>
       </c>
       <c r="H163" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="I163" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="J163" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="K163">
         <v>142808</v>
@@ -8780,10 +8792,10 @@
         <v>163</v>
       </c>
       <c r="B164" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C164" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D164" t="s">
         <v>5</v>
@@ -8795,13 +8807,13 @@
         <v>7</v>
       </c>
       <c r="H164" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="I164" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="J164" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="K164">
         <v>80463</v>
@@ -8821,10 +8833,10 @@
         <v>164</v>
       </c>
       <c r="B165" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C165" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D165" t="s">
         <v>5</v>
@@ -8836,13 +8848,13 @@
         <v>7</v>
       </c>
       <c r="H165" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="I165" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="J165" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K165">
         <v>83000</v>
@@ -8862,10 +8874,10 @@
         <v>165</v>
       </c>
       <c r="B166" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C166" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D166" t="s">
         <v>5</v>
@@ -8874,13 +8886,13 @@
         <v>7</v>
       </c>
       <c r="H166" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="I166" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="J166" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K166">
         <v>129000</v>
@@ -8900,16 +8912,16 @@
         <v>166</v>
       </c>
       <c r="B167" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C167" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D167" t="s">
         <v>5</v>
       </c>
       <c r="F167" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G167" t="s">
         <v>7</v>
@@ -8918,10 +8930,10 @@
         <v>117</v>
       </c>
       <c r="I167" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="J167" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K167">
         <v>62209</v>
@@ -8941,16 +8953,16 @@
         <v>167</v>
       </c>
       <c r="B168" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C168" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D168" t="s">
         <v>5</v>
       </c>
       <c r="F168" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="G168" t="s">
         <v>7</v>
@@ -8959,10 +8971,10 @@
         <v>8</v>
       </c>
       <c r="I168" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="J168" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="K168">
         <v>36117</v>
@@ -8982,10 +8994,10 @@
         <v>168</v>
       </c>
       <c r="B169" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C169" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D169" t="s">
         <v>5</v>
@@ -9003,10 +9015,10 @@
         <v>87</v>
       </c>
       <c r="I169" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="J169" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="K169">
         <v>49900</v>
@@ -9026,10 +9038,10 @@
         <v>169</v>
       </c>
       <c r="B170" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C170" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D170" t="s">
         <v>5</v>
@@ -9038,7 +9050,7 @@
         <v>16</v>
       </c>
       <c r="F170" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="G170" t="s">
         <v>7</v>
@@ -9047,10 +9059,10 @@
         <v>87</v>
       </c>
       <c r="I170" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="J170" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="K170">
         <v>39000</v>
@@ -9070,28 +9082,28 @@
         <v>170</v>
       </c>
       <c r="B171" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C171" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D171" t="s">
         <v>5</v>
       </c>
       <c r="F171" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="G171" t="s">
         <v>7</v>
       </c>
       <c r="H171" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I171" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="J171" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="K171">
         <v>49000</v>
@@ -9111,13 +9123,13 @@
         <v>171</v>
       </c>
       <c r="B172" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C172" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D172" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G172" t="s">
         <v>7</v>
@@ -9126,10 +9138,10 @@
         <v>8</v>
       </c>
       <c r="I172" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="J172" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="K172">
         <v>59400</v>
@@ -9149,10 +9161,10 @@
         <v>172</v>
       </c>
       <c r="B173" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C173" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D173" t="s">
         <v>5</v>
@@ -9167,10 +9179,10 @@
         <v>8</v>
       </c>
       <c r="I173" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="J173" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="K173">
         <v>65000</v>
@@ -9190,31 +9202,31 @@
         <v>173</v>
       </c>
       <c r="B174" t="s">
+        <v>412</v>
+      </c>
+      <c r="C174" t="s">
+        <v>397</v>
+      </c>
+      <c r="D174" t="s">
+        <v>5</v>
+      </c>
+      <c r="E174" t="s">
         <v>414</v>
       </c>
-      <c r="C174" t="s">
-        <v>399</v>
-      </c>
-      <c r="D174" t="s">
-        <v>5</v>
-      </c>
-      <c r="E174" t="s">
+      <c r="F174" t="s">
+        <v>413</v>
+      </c>
+      <c r="G174" t="s">
+        <v>7</v>
+      </c>
+      <c r="H174" t="s">
+        <v>415</v>
+      </c>
+      <c r="I174" t="s">
         <v>416</v>
       </c>
-      <c r="F174" t="s">
-        <v>415</v>
-      </c>
-      <c r="G174" t="s">
-        <v>7</v>
-      </c>
-      <c r="H174" t="s">
-        <v>417</v>
-      </c>
-      <c r="I174" t="s">
-        <v>418</v>
-      </c>
       <c r="J174" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K174">
         <v>47000</v>
@@ -9234,28 +9246,28 @@
         <v>174</v>
       </c>
       <c r="B175" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C175" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D175" t="s">
         <v>5</v>
       </c>
       <c r="E175" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="G175" t="s">
         <v>7</v>
       </c>
       <c r="H175" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="I175" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="J175" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K175">
         <v>29000</v>
@@ -9275,10 +9287,10 @@
         <v>175</v>
       </c>
       <c r="B176" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C176" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D176" t="s">
         <v>5</v>
@@ -9296,10 +9308,10 @@
         <v>87</v>
       </c>
       <c r="I176" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="J176" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K176">
         <v>132239</v>
@@ -9319,10 +9331,10 @@
         <v>176</v>
       </c>
       <c r="B177" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C177" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D177" t="s">
         <v>5</v>
@@ -9334,13 +9346,13 @@
         <v>7</v>
       </c>
       <c r="H177" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="I177" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="J177" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K177">
         <v>35016</v>
@@ -9360,10 +9372,10 @@
         <v>177</v>
       </c>
       <c r="B178" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C178" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D178" t="s">
         <v>5</v>
@@ -9375,10 +9387,10 @@
         <v>87</v>
       </c>
       <c r="I178" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="J178" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K178">
         <v>60000</v>
@@ -9398,28 +9410,28 @@
         <v>178</v>
       </c>
       <c r="B179" t="s">
+        <v>425</v>
+      </c>
+      <c r="C179" t="s">
+        <v>397</v>
+      </c>
+      <c r="D179" t="s">
+        <v>5</v>
+      </c>
+      <c r="F179" t="s">
+        <v>426</v>
+      </c>
+      <c r="G179" t="s">
+        <v>7</v>
+      </c>
+      <c r="H179" t="s">
+        <v>370</v>
+      </c>
+      <c r="I179" t="s">
         <v>427</v>
       </c>
-      <c r="C179" t="s">
-        <v>399</v>
-      </c>
-      <c r="D179" t="s">
-        <v>5</v>
-      </c>
-      <c r="F179" t="s">
-        <v>428</v>
-      </c>
-      <c r="G179" t="s">
-        <v>7</v>
-      </c>
-      <c r="H179" t="s">
-        <v>372</v>
-      </c>
-      <c r="I179" t="s">
-        <v>429</v>
-      </c>
       <c r="J179" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="K179">
         <v>90244</v>
@@ -9439,10 +9451,10 @@
         <v>179</v>
       </c>
       <c r="B180" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C180" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D180" t="s">
         <v>5</v>
@@ -9451,13 +9463,13 @@
         <v>7</v>
       </c>
       <c r="H180" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="I180" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="J180" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K180">
         <v>38700</v>
@@ -9477,10 +9489,10 @@
         <v>180</v>
       </c>
       <c r="B181" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C181" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D181" t="s">
         <v>5</v>
@@ -9489,13 +9501,13 @@
         <v>7</v>
       </c>
       <c r="H181" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="I181" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="J181" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="K181">
         <v>62414</v>
@@ -9515,10 +9527,10 @@
         <v>181</v>
       </c>
       <c r="B182" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C182" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D182" t="s">
         <v>5</v>
@@ -9527,13 +9539,13 @@
         <v>7</v>
       </c>
       <c r="H182" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="I182" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="J182" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K182">
         <v>51000</v>
@@ -9553,10 +9565,10 @@
         <v>182</v>
       </c>
       <c r="B183" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C183" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D183" t="s">
         <v>5</v>
@@ -9571,10 +9583,10 @@
         <v>87</v>
       </c>
       <c r="I183" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="J183" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K183">
         <v>53115</v>
@@ -9594,10 +9606,10 @@
         <v>183</v>
       </c>
       <c r="B184" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C184" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D184" t="s">
         <v>5</v>
@@ -9606,13 +9618,13 @@
         <v>7</v>
       </c>
       <c r="H184" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="I184" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="J184" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K184">
         <v>120000</v>
@@ -9632,10 +9644,10 @@
         <v>184</v>
       </c>
       <c r="B185" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C185" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D185" t="s">
         <v>5</v>
@@ -9650,10 +9662,10 @@
         <v>87</v>
       </c>
       <c r="I185" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="J185" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K185">
         <v>66477</v>
@@ -9673,10 +9685,10 @@
         <v>185</v>
       </c>
       <c r="B186" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C186" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D186" t="s">
         <v>5</v>
@@ -9688,10 +9700,10 @@
         <v>7</v>
       </c>
       <c r="H186" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="I186" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="K186">
         <v>59300</v>
@@ -9711,10 +9723,10 @@
         <v>186</v>
       </c>
       <c r="B187" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C187" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D187" t="s">
         <v>5</v>
@@ -9723,10 +9735,10 @@
         <v>7</v>
       </c>
       <c r="H187" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="I187" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="K187">
         <v>44000</v>
@@ -9746,10 +9758,10 @@
         <v>187</v>
       </c>
       <c r="B188" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C188" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D188" t="s">
         <v>5</v>
@@ -9758,10 +9770,10 @@
         <v>7</v>
       </c>
       <c r="H188" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="I188" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="K188">
         <v>26528</v>
@@ -9781,10 +9793,10 @@
         <v>188</v>
       </c>
       <c r="B189" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C189" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D189" t="s">
         <v>5</v>
@@ -9796,10 +9808,10 @@
         <v>7</v>
       </c>
       <c r="H189" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="I189" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="K189">
         <v>95684</v>
@@ -9819,10 +9831,10 @@
         <v>189</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C190" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D190" t="s">
         <v>5</v>
@@ -9834,7 +9846,7 @@
         <v>87</v>
       </c>
       <c r="I190" s="4" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="K190">
         <v>26737</v>
@@ -9854,10 +9866,10 @@
         <v>190</v>
       </c>
       <c r="B191" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C191" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D191" t="s">
         <v>5</v>
@@ -9869,10 +9881,10 @@
         <v>7</v>
       </c>
       <c r="H191" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="I191" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="K191">
         <v>60000</v>
@@ -9892,10 +9904,10 @@
         <v>191</v>
       </c>
       <c r="B192" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C192" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D192" t="s">
         <v>5</v>
@@ -9904,10 +9916,10 @@
         <v>7</v>
       </c>
       <c r="H192" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="I192" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="K192">
         <v>34895</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yuhang/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7947D7E-7740-1A43-874F-4D42D0BC2C70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{676B3433-4BDB-384E-B716-4BED7122BF59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -833,9 +833,6 @@
     <t>中钢国际广场</t>
   </si>
   <si>
-    <t>116.312185,39.981535</t>
-  </si>
-  <si>
     <t>欧美汇大厦</t>
   </si>
   <si>
@@ -1536,6 +1533,10 @@
   </si>
   <si>
     <t>116.362230,39.920558</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>116.313304,39.982116</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1956,22 +1957,22 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B1" t="s">
+        <v>460</v>
+      </c>
+      <c r="C1" t="s">
         <v>461</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>462</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="F1" t="s">
         <v>463</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>469</v>
-      </c>
-      <c r="F1" t="s">
-        <v>464</v>
       </c>
       <c r="G1" t="s">
         <v>0</v>
@@ -1983,19 +1984,19 @@
         <v>2</v>
       </c>
       <c r="J1" t="s">
+        <v>464</v>
+      </c>
+      <c r="K1" t="s">
+        <v>459</v>
+      </c>
+      <c r="L1" t="s">
         <v>465</v>
       </c>
-      <c r="K1" t="s">
-        <v>460</v>
-      </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>466</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>467</v>
-      </c>
-      <c r="N1" t="s">
-        <v>468</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -2024,7 +2025,7 @@
         <v>9</v>
       </c>
       <c r="J2" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K2">
         <v>72308</v>
@@ -2065,7 +2066,7 @@
         <v>12</v>
       </c>
       <c r="J3" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K3">
         <v>72308</v>
@@ -2109,7 +2110,7 @@
         <v>17</v>
       </c>
       <c r="J4" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K4">
         <v>130769</v>
@@ -2153,7 +2154,7 @@
         <v>20</v>
       </c>
       <c r="J5" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K5">
         <v>64615</v>
@@ -2197,7 +2198,7 @@
         <v>24</v>
       </c>
       <c r="J6" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K6">
         <v>80091</v>
@@ -2238,7 +2239,7 @@
         <v>27</v>
       </c>
       <c r="J7" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K7">
         <v>70673</v>
@@ -2282,7 +2283,7 @@
         <v>30</v>
       </c>
       <c r="J8" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K8">
         <v>90466</v>
@@ -2323,7 +2324,7 @@
         <v>32</v>
       </c>
       <c r="J9" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K9">
         <v>46720</v>
@@ -2367,7 +2368,7 @@
         <v>35</v>
       </c>
       <c r="J10" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K10">
         <v>95000</v>
@@ -2411,7 +2412,7 @@
         <v>38</v>
       </c>
       <c r="J11" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K11">
         <v>85300</v>
@@ -2455,7 +2456,7 @@
         <v>41</v>
       </c>
       <c r="J12" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K12">
         <v>33305</v>
@@ -2499,7 +2500,7 @@
         <v>43</v>
       </c>
       <c r="J13" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K13">
         <v>120245.21</v>
@@ -2543,7 +2544,7 @@
         <v>43</v>
       </c>
       <c r="J14" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K14">
         <v>70425.53</v>
@@ -2587,7 +2588,7 @@
         <v>47</v>
       </c>
       <c r="J15" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K15">
         <v>78000</v>
@@ -2631,7 +2632,7 @@
         <v>50</v>
       </c>
       <c r="J16" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K16">
         <v>102796</v>
@@ -2675,7 +2676,7 @@
         <v>52</v>
       </c>
       <c r="J17" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K17">
         <v>49200</v>
@@ -2719,7 +2720,7 @@
         <v>54</v>
       </c>
       <c r="J18" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K18">
         <v>65096</v>
@@ -2763,7 +2764,7 @@
         <v>57</v>
       </c>
       <c r="J19" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K19">
         <v>56000</v>
@@ -2807,7 +2808,7 @@
         <v>60</v>
       </c>
       <c r="J20" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K20">
         <v>177847</v>
@@ -2851,7 +2852,7 @@
         <v>63</v>
       </c>
       <c r="J21" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K21">
         <v>83000</v>
@@ -2892,7 +2893,7 @@
         <v>66</v>
       </c>
       <c r="J22" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K22">
         <v>26000</v>
@@ -2933,7 +2934,7 @@
         <v>68</v>
       </c>
       <c r="J23" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K23">
         <v>85887</v>
@@ -2974,7 +2975,7 @@
         <v>70</v>
       </c>
       <c r="J24" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K24">
         <v>20000</v>
@@ -3018,7 +3019,7 @@
         <v>73</v>
       </c>
       <c r="J25" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K25">
         <v>146385</v>
@@ -3062,7 +3063,7 @@
         <v>76</v>
       </c>
       <c r="J26" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K26">
         <v>87000</v>
@@ -3106,7 +3107,7 @@
         <v>79</v>
       </c>
       <c r="J27" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K27">
         <v>147166.79999999999</v>
@@ -3150,7 +3151,7 @@
         <v>82</v>
       </c>
       <c r="J28" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K28">
         <v>46063</v>
@@ -3194,7 +3195,7 @@
         <v>85</v>
       </c>
       <c r="J29" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K29">
         <v>47261</v>
@@ -3214,7 +3215,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C30" t="s">
         <v>4</v>
@@ -3232,13 +3233,13 @@
         <v>7</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="J30" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K30">
         <v>119000</v>
@@ -3279,7 +3280,7 @@
         <v>91</v>
       </c>
       <c r="J31" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K31">
         <v>47000</v>
@@ -3323,7 +3324,7 @@
         <v>93</v>
       </c>
       <c r="J32" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K32">
         <v>186000</v>
@@ -3361,7 +3362,7 @@
         <v>95</v>
       </c>
       <c r="J33" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K33">
         <v>40800</v>
@@ -3402,7 +3403,7 @@
         <v>95</v>
       </c>
       <c r="J34" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K34">
         <v>55200</v>
@@ -3446,7 +3447,7 @@
         <v>99</v>
       </c>
       <c r="J35" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K35">
         <v>350000</v>
@@ -3487,7 +3488,7 @@
         <v>101</v>
       </c>
       <c r="J36" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K36">
         <v>65000</v>
@@ -3528,7 +3529,7 @@
         <v>101</v>
       </c>
       <c r="J37" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K37">
         <v>35000</v>
@@ -3569,7 +3570,7 @@
         <v>104</v>
       </c>
       <c r="J38" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K38">
         <v>47000</v>
@@ -3613,7 +3614,7 @@
         <v>107</v>
       </c>
       <c r="J39" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K39">
         <v>120000</v>
@@ -3654,7 +3655,7 @@
         <v>109</v>
       </c>
       <c r="J40" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K40">
         <v>83000</v>
@@ -3695,7 +3696,7 @@
         <v>111</v>
       </c>
       <c r="J41" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K41">
         <v>66030</v>
@@ -3733,7 +3734,7 @@
         <v>113</v>
       </c>
       <c r="J42" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K42">
         <v>40000</v>
@@ -3777,7 +3778,7 @@
         <v>118</v>
       </c>
       <c r="J43" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K43">
         <v>40000</v>
@@ -3818,7 +3819,7 @@
         <v>121</v>
       </c>
       <c r="J44" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K44">
         <v>54100</v>
@@ -3859,10 +3860,10 @@
         <v>117</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="J45" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K45">
         <v>100000</v>
@@ -3903,10 +3904,10 @@
         <v>117</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="J46" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K46">
         <v>150000</v>
@@ -3947,10 +3948,10 @@
         <v>117</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="J47" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K47">
         <v>50000</v>
@@ -3994,7 +3995,7 @@
         <v>130</v>
       </c>
       <c r="J48" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="K48">
         <v>43000</v>
@@ -4035,7 +4036,7 @@
         <v>133</v>
       </c>
       <c r="J49" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="K49">
         <v>65000</v>
@@ -4076,7 +4077,7 @@
         <v>136</v>
       </c>
       <c r="J50" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="51" spans="1:14">
@@ -4108,7 +4109,7 @@
         <v>138</v>
       </c>
       <c r="J51" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="K51">
         <v>56000</v>
@@ -4149,7 +4150,7 @@
         <v>140</v>
       </c>
       <c r="J52" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="K52">
         <v>160000</v>
@@ -4190,7 +4191,7 @@
         <v>142</v>
       </c>
       <c r="J53" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="K53">
         <v>33000</v>
@@ -4234,7 +4235,7 @@
         <v>145</v>
       </c>
       <c r="J54" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="K54">
         <v>41318</v>
@@ -4275,7 +4276,7 @@
         <v>147</v>
       </c>
       <c r="J55" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K55">
         <v>34131</v>
@@ -4316,7 +4317,7 @@
         <v>150</v>
       </c>
       <c r="J56" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K56">
         <v>48000</v>
@@ -4357,7 +4358,7 @@
         <v>118</v>
       </c>
       <c r="J57" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K57">
         <v>16000</v>
@@ -4401,7 +4402,7 @@
         <v>154</v>
       </c>
       <c r="J58" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="K58">
         <v>30000</v>
@@ -4445,7 +4446,7 @@
         <v>157</v>
       </c>
       <c r="J59" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="K59">
         <v>56000</v>
@@ -4489,7 +4490,7 @@
         <v>160</v>
       </c>
       <c r="J60" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K60">
         <v>43000</v>
@@ -4530,7 +4531,7 @@
         <v>162</v>
       </c>
       <c r="J61" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="K61">
         <v>110000</v>
@@ -4568,7 +4569,7 @@
         <v>164</v>
       </c>
       <c r="J62" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K62">
         <v>56160</v>
@@ -4609,7 +4610,7 @@
         <v>166</v>
       </c>
       <c r="J63" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K63">
         <v>138444</v>
@@ -4653,7 +4654,7 @@
         <v>170</v>
       </c>
       <c r="J64" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="K64">
         <v>31000</v>
@@ -4694,7 +4695,7 @@
         <v>173</v>
       </c>
       <c r="J65" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="K65">
         <v>120000</v>
@@ -4735,7 +4736,7 @@
         <v>175</v>
       </c>
       <c r="J66" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="K66">
         <v>25900</v>
@@ -4776,7 +4777,7 @@
         <v>178</v>
       </c>
       <c r="J67" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="K67">
         <v>47986</v>
@@ -4820,7 +4821,7 @@
         <v>180</v>
       </c>
       <c r="J68" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="K68">
         <v>194000</v>
@@ -4864,7 +4865,7 @@
         <v>182</v>
       </c>
       <c r="J69" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="K69">
         <v>39724</v>
@@ -4902,10 +4903,10 @@
         <v>87</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="J70" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="K70">
         <v>48437.45</v>
@@ -4946,7 +4947,7 @@
         <v>186</v>
       </c>
       <c r="J71" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="K71">
         <v>37910</v>
@@ -4966,7 +4967,7 @@
         <v>71</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C72" t="s">
         <v>168</v>
@@ -4984,10 +4985,10 @@
         <v>87</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="J72" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="K72">
         <v>21220</v>
@@ -5028,7 +5029,7 @@
         <v>188</v>
       </c>
       <c r="J73" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="K73">
         <v>77877</v>
@@ -5072,7 +5073,7 @@
         <v>190</v>
       </c>
       <c r="J74" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="K74">
         <v>80311.53</v>
@@ -5116,7 +5117,7 @@
         <v>193</v>
       </c>
       <c r="J75" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="K75">
         <v>38000</v>
@@ -5157,7 +5158,7 @@
         <v>196</v>
       </c>
       <c r="J76" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="K76">
         <v>37800</v>
@@ -5176,7 +5177,7 @@
       <c r="A77">
         <v>76</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B77" s="2" t="s">
         <v>197</v>
       </c>
       <c r="C77" t="s">
@@ -5197,11 +5198,11 @@
       <c r="H77" t="s">
         <v>87</v>
       </c>
-      <c r="I77" s="1" t="s">
-        <v>493</v>
+      <c r="I77" s="2" t="s">
+        <v>492</v>
       </c>
       <c r="J77" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="K77">
         <v>54581</v>
@@ -5245,7 +5246,7 @@
         <v>88</v>
       </c>
       <c r="J78" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="K78">
         <v>25000</v>
@@ -5289,7 +5290,7 @@
         <v>202</v>
       </c>
       <c r="J79" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="K79">
         <v>52698</v>
@@ -5327,10 +5328,10 @@
         <v>205</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="J80" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="K80">
         <v>38500</v>
@@ -5368,7 +5369,7 @@
         <v>208</v>
       </c>
       <c r="J81" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="K81">
         <v>27200</v>
@@ -5412,7 +5413,7 @@
         <v>211</v>
       </c>
       <c r="J82" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="K82">
         <v>60000</v>
@@ -5453,7 +5454,7 @@
         <v>214</v>
       </c>
       <c r="J83" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K83">
         <v>50000</v>
@@ -5497,7 +5498,7 @@
         <v>216</v>
       </c>
       <c r="J84" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="K84">
         <v>131575</v>
@@ -5538,7 +5539,7 @@
         <v>218</v>
       </c>
       <c r="J85" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K85">
         <v>99500</v>
@@ -5579,7 +5580,7 @@
         <v>221</v>
       </c>
       <c r="J86" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="K86">
         <v>32000</v>
@@ -5623,7 +5624,7 @@
         <v>223</v>
       </c>
       <c r="J87" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="K87">
         <v>52170</v>
@@ -5664,7 +5665,7 @@
         <v>226</v>
       </c>
       <c r="J88" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="K88">
         <v>46000</v>
@@ -5708,7 +5709,7 @@
         <v>229</v>
       </c>
       <c r="J89" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K89">
         <v>45013</v>
@@ -5749,7 +5750,7 @@
         <v>231</v>
       </c>
       <c r="J90" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="K90">
         <v>48566</v>
@@ -5790,7 +5791,7 @@
         <v>234</v>
       </c>
       <c r="J91" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K91">
         <v>55618</v>
@@ -5831,7 +5832,7 @@
         <v>236</v>
       </c>
       <c r="J92" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="K92">
         <v>47000</v>
@@ -5875,7 +5876,7 @@
         <v>239</v>
       </c>
       <c r="J93" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K93">
         <v>87763</v>
@@ -5919,7 +5920,7 @@
         <v>242</v>
       </c>
       <c r="J94" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="K94">
         <v>100658</v>
@@ -5960,7 +5961,7 @@
         <v>245</v>
       </c>
       <c r="J95" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="K95">
         <v>67000</v>
@@ -6004,7 +6005,7 @@
         <v>247</v>
       </c>
       <c r="J96" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="K96">
         <v>39431</v>
@@ -6045,7 +6046,7 @@
         <v>249</v>
       </c>
       <c r="J97" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="K97">
         <v>34273</v>
@@ -6083,7 +6084,7 @@
         <v>73</v>
       </c>
       <c r="J98" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K98">
         <v>40000</v>
@@ -6124,7 +6125,7 @@
         <v>252</v>
       </c>
       <c r="J99" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="K99">
         <v>65000</v>
@@ -6168,7 +6169,7 @@
         <v>256</v>
       </c>
       <c r="J100" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="K100">
         <v>49000</v>
@@ -6212,7 +6213,7 @@
         <v>259</v>
       </c>
       <c r="J101" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="K101">
         <v>95000</v>
@@ -6256,7 +6257,7 @@
         <v>262</v>
       </c>
       <c r="J102" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="K102">
         <v>45000</v>
@@ -6297,7 +6298,7 @@
         <v>264</v>
       </c>
       <c r="J103" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="K103">
         <v>124500</v>
@@ -6316,7 +6317,7 @@
       <c r="A104">
         <v>103</v>
       </c>
-      <c r="B104" t="s">
+      <c r="B104" s="2" t="s">
         <v>265</v>
       </c>
       <c r="C104" t="s">
@@ -6334,11 +6335,11 @@
       <c r="H104" t="s">
         <v>205</v>
       </c>
-      <c r="I104" t="s">
-        <v>266</v>
+      <c r="I104" s="2" t="s">
+        <v>493</v>
       </c>
       <c r="J104" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="K104">
         <v>64000</v>
@@ -6358,7 +6359,7 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C105" t="s">
         <v>254</v>
@@ -6376,10 +6377,10 @@
         <v>205</v>
       </c>
       <c r="I105" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="J105" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="K105">
         <v>25000</v>
@@ -6399,7 +6400,7 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C106" t="s">
         <v>254</v>
@@ -6417,10 +6418,10 @@
         <v>205</v>
       </c>
       <c r="I106" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="J106" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="K106">
         <v>38498</v>
@@ -6440,7 +6441,7 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C107" t="s">
         <v>254</v>
@@ -6455,10 +6456,10 @@
         <v>205</v>
       </c>
       <c r="I107" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J107" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="K107">
         <v>166433</v>
@@ -6478,7 +6479,7 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C108" t="s">
         <v>254</v>
@@ -6499,10 +6500,10 @@
         <v>205</v>
       </c>
       <c r="I108" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="J108" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="K108">
         <v>58000</v>
@@ -6522,7 +6523,7 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C109" t="s">
         <v>254</v>
@@ -6531,7 +6532,7 @@
         <v>5</v>
       </c>
       <c r="F109" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G109" t="s">
         <v>7</v>
@@ -6540,10 +6541,10 @@
         <v>205</v>
       </c>
       <c r="I109" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J109" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="K109">
         <v>51872</v>
@@ -6563,7 +6564,7 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C110" t="s">
         <v>254</v>
@@ -6581,10 +6582,10 @@
         <v>205</v>
       </c>
       <c r="I110" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J110" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="K110">
         <v>21632</v>
@@ -6604,7 +6605,7 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C111" t="s">
         <v>254</v>
@@ -6622,10 +6623,10 @@
         <v>205</v>
       </c>
       <c r="I111" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J111" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="K111">
         <v>69000</v>
@@ -6645,7 +6646,7 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C112" t="s">
         <v>254</v>
@@ -6654,7 +6655,7 @@
         <v>5</v>
       </c>
       <c r="F112" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="G112" t="s">
         <v>7</v>
@@ -6663,10 +6664,10 @@
         <v>205</v>
       </c>
       <c r="I112" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="J112" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="K112">
         <v>54000</v>
@@ -6686,7 +6687,7 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C113" t="s">
         <v>254</v>
@@ -6704,10 +6705,10 @@
         <v>205</v>
       </c>
       <c r="I113" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="J113" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="K113">
         <v>57400</v>
@@ -6727,7 +6728,7 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C114" t="s">
         <v>254</v>
@@ -6745,10 +6746,10 @@
         <v>205</v>
       </c>
       <c r="I114" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J114" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="K114">
         <v>60000</v>
@@ -6768,7 +6769,7 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C115" t="s">
         <v>254</v>
@@ -6786,10 +6787,10 @@
         <v>205</v>
       </c>
       <c r="I115" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J115" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="K115">
         <v>60000</v>
@@ -6809,7 +6810,7 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C116" t="s">
         <v>254</v>
@@ -6824,10 +6825,10 @@
         <v>205</v>
       </c>
       <c r="I116" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J116" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="K116">
         <v>33000</v>
@@ -6847,7 +6848,7 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C117" t="s">
         <v>254</v>
@@ -6862,10 +6863,10 @@
         <v>205</v>
       </c>
       <c r="I117" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="J117" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="K117">
         <v>88786</v>
@@ -6885,7 +6886,7 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C118" t="s">
         <v>254</v>
@@ -6900,10 +6901,10 @@
         <v>205</v>
       </c>
       <c r="I118" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="J118" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="K118">
         <v>134000</v>
@@ -6923,7 +6924,7 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C119" t="s">
         <v>254</v>
@@ -6938,10 +6939,10 @@
         <v>205</v>
       </c>
       <c r="I119" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="J119" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="K119">
         <v>35000</v>
@@ -6961,7 +6962,7 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C120" t="s">
         <v>254</v>
@@ -6976,10 +6977,10 @@
         <v>205</v>
       </c>
       <c r="I120" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="J120" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="K120">
         <v>18000</v>
@@ -6999,7 +7000,7 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C121" t="s">
         <v>254</v>
@@ -7017,10 +7018,10 @@
         <v>205</v>
       </c>
       <c r="I121" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="J121" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="K121">
         <v>105741</v>
@@ -7040,7 +7041,7 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C122" t="s">
         <v>254</v>
@@ -7055,10 +7056,10 @@
         <v>205</v>
       </c>
       <c r="I122" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="J122" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="K122">
         <v>51000</v>
@@ -7078,7 +7079,7 @@
         <v>122</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C123" t="s">
         <v>254</v>
@@ -7096,10 +7097,10 @@
         <v>205</v>
       </c>
       <c r="I123" s="3" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="J123" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="K123">
         <v>130143</v>
@@ -7114,7 +7115,7 @@
         <v>36000</v>
       </c>
       <c r="P123" s="1" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7122,7 +7123,7 @@
         <v>123</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C124" t="s">
         <v>254</v>
@@ -7134,10 +7135,10 @@
         <v>205</v>
       </c>
       <c r="I124" s="3" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="J124" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="K124">
         <v>121551.47</v>
@@ -7152,7 +7153,7 @@
         <v>97326.47</v>
       </c>
       <c r="P124" s="1" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7160,10 +7161,10 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
+        <v>304</v>
+      </c>
+      <c r="C125" t="s">
         <v>305</v>
-      </c>
-      <c r="C125" t="s">
-        <v>306</v>
       </c>
       <c r="D125" t="s">
         <v>5</v>
@@ -7172,7 +7173,7 @@
         <v>16</v>
       </c>
       <c r="F125" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G125" t="s">
         <v>7</v>
@@ -7181,10 +7182,10 @@
         <v>8</v>
       </c>
       <c r="I125" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="J125" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="K125">
         <v>110000</v>
@@ -7204,10 +7205,10 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C126" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D126" t="s">
         <v>5</v>
@@ -7225,10 +7226,10 @@
         <v>8</v>
       </c>
       <c r="I126" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="J126" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="K126">
         <v>56000</v>
@@ -7248,10 +7249,10 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C127" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D127" t="s">
         <v>5</v>
@@ -7266,10 +7267,10 @@
         <v>8</v>
       </c>
       <c r="I127" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J127" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="K127">
         <v>89177</v>
@@ -7289,10 +7290,10 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C128" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D128" t="s">
         <v>5</v>
@@ -7301,7 +7302,7 @@
         <v>23</v>
       </c>
       <c r="F128" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="G128" t="s">
         <v>7</v>
@@ -7310,10 +7311,10 @@
         <v>8</v>
       </c>
       <c r="I128" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="J128" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="K128">
         <v>30000</v>
@@ -7333,10 +7334,10 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C129" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D129" t="s">
         <v>5</v>
@@ -7345,7 +7346,7 @@
         <v>16</v>
       </c>
       <c r="F129" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="G129" t="s">
         <v>7</v>
@@ -7354,10 +7355,10 @@
         <v>8</v>
       </c>
       <c r="I129" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="J129" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="K129">
         <v>54550</v>
@@ -7377,10 +7378,10 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C130" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D130" t="s">
         <v>5</v>
@@ -7398,10 +7399,10 @@
         <v>8</v>
       </c>
       <c r="I130" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="J130" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="K130">
         <v>125000</v>
@@ -7421,10 +7422,10 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C131" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D131" t="s">
         <v>5</v>
@@ -7433,7 +7434,7 @@
         <v>16</v>
       </c>
       <c r="F131" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G131" t="s">
         <v>7</v>
@@ -7442,10 +7443,10 @@
         <v>8</v>
       </c>
       <c r="I131" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="J131" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="K131">
         <v>69100</v>
@@ -7465,10 +7466,10 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C132" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D132" t="s">
         <v>5</v>
@@ -7486,10 +7487,10 @@
         <v>8</v>
       </c>
       <c r="I132" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="J132" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="K132">
         <v>118290</v>
@@ -7509,16 +7510,16 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
+        <v>324</v>
+      </c>
+      <c r="C133" t="s">
+        <v>305</v>
+      </c>
+      <c r="D133" t="s">
+        <v>5</v>
+      </c>
+      <c r="F133" t="s">
         <v>325</v>
-      </c>
-      <c r="C133" t="s">
-        <v>306</v>
-      </c>
-      <c r="D133" t="s">
-        <v>5</v>
-      </c>
-      <c r="F133" t="s">
-        <v>326</v>
       </c>
       <c r="G133" t="s">
         <v>7</v>
@@ -7527,10 +7528,10 @@
         <v>8</v>
       </c>
       <c r="I133" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="J133" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="K133">
         <v>79900</v>
@@ -7550,10 +7551,10 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C134" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D134" t="s">
         <v>5</v>
@@ -7568,10 +7569,10 @@
         <v>8</v>
       </c>
       <c r="I134" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J134" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="K134">
         <v>39742.379999999997</v>
@@ -7591,10 +7592,10 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C135" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D135" t="s">
         <v>5</v>
@@ -7612,10 +7613,10 @@
         <v>8</v>
       </c>
       <c r="I135" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="J135" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="K135">
         <v>48000</v>
@@ -7635,10 +7636,10 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C136" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D136" t="s">
         <v>14</v>
@@ -7653,10 +7654,10 @@
         <v>8</v>
       </c>
       <c r="I136" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="J136" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="K136">
         <v>74722</v>
@@ -7676,10 +7677,10 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C137" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D137" t="s">
         <v>207</v>
@@ -7691,10 +7692,10 @@
         <v>8</v>
       </c>
       <c r="I137" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="J137" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="K137">
         <v>55000</v>
@@ -7714,10 +7715,10 @@
         <v>137</v>
       </c>
       <c r="B138" t="s">
+        <v>335</v>
+      </c>
+      <c r="C138" t="s">
         <v>336</v>
-      </c>
-      <c r="C138" t="s">
-        <v>337</v>
       </c>
       <c r="D138" t="s">
         <v>5</v>
@@ -7729,10 +7730,10 @@
         <v>117</v>
       </c>
       <c r="I138" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J138" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K138">
         <v>128000</v>
@@ -7752,10 +7753,10 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C139" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D139" t="s">
         <v>5</v>
@@ -7773,10 +7774,10 @@
         <v>117</v>
       </c>
       <c r="I139" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="J139" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K139">
         <v>122000</v>
@@ -7796,10 +7797,10 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C140" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D140" t="s">
         <v>5</v>
@@ -7814,10 +7815,10 @@
         <v>117</v>
       </c>
       <c r="I140" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="J140" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K140">
         <v>22000</v>
@@ -7837,10 +7838,10 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C141" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D141" t="s">
         <v>5</v>
@@ -7855,10 +7856,10 @@
         <v>117</v>
       </c>
       <c r="I141" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="J141" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K141">
         <v>10000</v>
@@ -7878,10 +7879,10 @@
         <v>141</v>
       </c>
       <c r="B142" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C142" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D142" t="s">
         <v>5</v>
@@ -7896,10 +7897,10 @@
         <v>8</v>
       </c>
       <c r="I142" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="J142" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="K142">
         <v>64000</v>
@@ -7919,10 +7920,10 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C143" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D143" t="s">
         <v>5</v>
@@ -7937,10 +7938,10 @@
         <v>8</v>
       </c>
       <c r="I143" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J143" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="K143">
         <v>95628</v>
@@ -7960,16 +7961,16 @@
         <v>143</v>
       </c>
       <c r="B144" t="s">
+        <v>348</v>
+      </c>
+      <c r="C144" t="s">
+        <v>336</v>
+      </c>
+      <c r="D144" t="s">
+        <v>5</v>
+      </c>
+      <c r="F144" t="s">
         <v>349</v>
-      </c>
-      <c r="C144" t="s">
-        <v>337</v>
-      </c>
-      <c r="D144" t="s">
-        <v>5</v>
-      </c>
-      <c r="F144" t="s">
-        <v>350</v>
       </c>
       <c r="G144" t="s">
         <v>7</v>
@@ -7978,10 +7979,10 @@
         <v>8</v>
       </c>
       <c r="I144" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="J144" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="K144">
         <v>39562</v>
@@ -8001,10 +8002,10 @@
         <v>144</v>
       </c>
       <c r="B145" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C145" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D145" t="s">
         <v>5</v>
@@ -8013,7 +8014,7 @@
         <v>16</v>
       </c>
       <c r="F145" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="G145" t="s">
         <v>7</v>
@@ -8022,10 +8023,10 @@
         <v>8</v>
       </c>
       <c r="I145" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="J145" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K145">
         <v>105000</v>
@@ -8045,10 +8046,10 @@
         <v>145</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C146" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D146" t="s">
         <v>5</v>
@@ -8057,7 +8058,7 @@
         <v>23</v>
       </c>
       <c r="F146" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G146" t="s">
         <v>7</v>
@@ -8066,10 +8067,10 @@
         <v>8</v>
       </c>
       <c r="I146" s="2" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="J146" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K146">
         <v>60000</v>
@@ -8089,10 +8090,10 @@
         <v>146</v>
       </c>
       <c r="B147" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C147" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D147" t="s">
         <v>5</v>
@@ -8107,10 +8108,10 @@
         <v>8</v>
       </c>
       <c r="I147" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="J147" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="K147">
         <v>39964</v>
@@ -8130,10 +8131,10 @@
         <v>147</v>
       </c>
       <c r="B148" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C148" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D148" t="s">
         <v>5</v>
@@ -8148,10 +8149,10 @@
         <v>8</v>
       </c>
       <c r="I148" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="J148" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K148">
         <v>94000</v>
@@ -8171,10 +8172,10 @@
         <v>148</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C149" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D149" t="s">
         <v>5</v>
@@ -8192,10 +8193,10 @@
         <v>8</v>
       </c>
       <c r="I149" s="2" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="J149" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K149">
         <v>75000</v>
@@ -8218,13 +8219,13 @@
         <v>183</v>
       </c>
       <c r="C150" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D150" t="s">
         <v>5</v>
       </c>
       <c r="F150" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G150" t="s">
         <v>7</v>
@@ -8233,10 +8234,10 @@
         <v>87</v>
       </c>
       <c r="I150" s="2" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="J150" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K150">
         <v>48767</v>
@@ -8256,10 +8257,10 @@
         <v>150</v>
       </c>
       <c r="B151" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C151" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D151" t="s">
         <v>5</v>
@@ -8277,10 +8278,10 @@
         <v>8</v>
       </c>
       <c r="I151" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="J151" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K151">
         <v>63824</v>
@@ -8300,10 +8301,10 @@
         <v>151</v>
       </c>
       <c r="B152" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C152" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D152" t="s">
         <v>14</v>
@@ -8321,10 +8322,10 @@
         <v>8</v>
       </c>
       <c r="I152" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="J152" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K152">
         <v>117000</v>
@@ -8344,10 +8345,10 @@
         <v>152</v>
       </c>
       <c r="B153" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C153" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D153" t="s">
         <v>5</v>
@@ -8359,10 +8360,10 @@
         <v>8</v>
       </c>
       <c r="I153" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="J153" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K153">
         <v>41000</v>
@@ -8382,10 +8383,10 @@
         <v>153</v>
       </c>
       <c r="B154" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C154" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D154" t="s">
         <v>5</v>
@@ -8397,10 +8398,10 @@
         <v>8</v>
       </c>
       <c r="I154" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="J154" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="K154">
         <v>96446</v>
@@ -8420,10 +8421,10 @@
         <v>154</v>
       </c>
       <c r="B155" t="s">
+        <v>367</v>
+      </c>
+      <c r="C155" t="s">
         <v>368</v>
-      </c>
-      <c r="C155" t="s">
-        <v>369</v>
       </c>
       <c r="D155" t="s">
         <v>5</v>
@@ -8438,13 +8439,13 @@
         <v>7</v>
       </c>
       <c r="H155" t="s">
+        <v>369</v>
+      </c>
+      <c r="I155" t="s">
         <v>370</v>
       </c>
-      <c r="I155" t="s">
-        <v>371</v>
-      </c>
       <c r="J155" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K155">
         <v>76600</v>
@@ -8464,10 +8465,10 @@
         <v>155</v>
       </c>
       <c r="B156" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C156" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D156" t="s">
         <v>5</v>
@@ -8479,13 +8480,13 @@
         <v>7</v>
       </c>
       <c r="H156" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="I156" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="J156" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K156">
         <v>125569</v>
@@ -8505,28 +8506,28 @@
         <v>156</v>
       </c>
       <c r="B157" t="s">
+        <v>373</v>
+      </c>
+      <c r="C157" t="s">
+        <v>368</v>
+      </c>
+      <c r="D157" t="s">
+        <v>5</v>
+      </c>
+      <c r="F157" t="s">
         <v>374</v>
       </c>
-      <c r="C157" t="s">
+      <c r="G157" t="s">
+        <v>7</v>
+      </c>
+      <c r="H157" t="s">
         <v>369</v>
       </c>
-      <c r="D157" t="s">
-        <v>5</v>
-      </c>
-      <c r="F157" t="s">
+      <c r="I157" t="s">
         <v>375</v>
       </c>
-      <c r="G157" t="s">
-        <v>7</v>
-      </c>
-      <c r="H157" t="s">
-        <v>370</v>
-      </c>
-      <c r="I157" t="s">
-        <v>376</v>
-      </c>
       <c r="J157" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K157">
         <v>51234</v>
@@ -8546,10 +8547,10 @@
         <v>157</v>
       </c>
       <c r="B158" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C158" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D158" t="s">
         <v>5</v>
@@ -8564,13 +8565,13 @@
         <v>7</v>
       </c>
       <c r="H158" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="I158" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J158" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K158">
         <v>123780</v>
@@ -8590,28 +8591,28 @@
         <v>158</v>
       </c>
       <c r="B159" t="s">
+        <v>378</v>
+      </c>
+      <c r="C159" t="s">
+        <v>368</v>
+      </c>
+      <c r="D159" t="s">
+        <v>5</v>
+      </c>
+      <c r="F159" t="s">
         <v>379</v>
       </c>
-      <c r="C159" t="s">
+      <c r="G159" t="s">
+        <v>7</v>
+      </c>
+      <c r="H159" t="s">
         <v>369</v>
       </c>
-      <c r="D159" t="s">
-        <v>5</v>
-      </c>
-      <c r="F159" t="s">
+      <c r="I159" t="s">
         <v>380</v>
       </c>
-      <c r="G159" t="s">
-        <v>7</v>
-      </c>
-      <c r="H159" t="s">
-        <v>370</v>
-      </c>
-      <c r="I159" t="s">
-        <v>381</v>
-      </c>
       <c r="J159" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K159">
         <v>46000</v>
@@ -8631,25 +8632,25 @@
         <v>159</v>
       </c>
       <c r="B160" t="s">
+        <v>381</v>
+      </c>
+      <c r="C160" t="s">
+        <v>368</v>
+      </c>
+      <c r="D160" t="s">
+        <v>5</v>
+      </c>
+      <c r="G160" t="s">
+        <v>7</v>
+      </c>
+      <c r="H160" t="s">
+        <v>369</v>
+      </c>
+      <c r="I160" t="s">
         <v>382</v>
       </c>
-      <c r="C160" t="s">
-        <v>369</v>
-      </c>
-      <c r="D160" t="s">
-        <v>5</v>
-      </c>
-      <c r="G160" t="s">
-        <v>7</v>
-      </c>
-      <c r="H160" t="s">
-        <v>370</v>
-      </c>
-      <c r="I160" t="s">
-        <v>383</v>
-      </c>
       <c r="J160" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K160">
         <v>35600</v>
@@ -8669,10 +8670,10 @@
         <v>160</v>
       </c>
       <c r="B161" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C161" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D161" t="s">
         <v>5</v>
@@ -8684,13 +8685,13 @@
         <v>7</v>
       </c>
       <c r="H161" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="I161" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="J161" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K161">
         <v>199950</v>
@@ -8710,10 +8711,10 @@
         <v>161</v>
       </c>
       <c r="B162" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C162" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D162" t="s">
         <v>5</v>
@@ -8725,13 +8726,13 @@
         <v>7</v>
       </c>
       <c r="H162" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="I162" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="J162" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K162">
         <v>108000</v>
@@ -8751,10 +8752,10 @@
         <v>162</v>
       </c>
       <c r="B163" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C163" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D163" t="s">
         <v>5</v>
@@ -8766,13 +8767,13 @@
         <v>7</v>
       </c>
       <c r="H163" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="I163" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="J163" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K163">
         <v>142808</v>
@@ -8792,10 +8793,10 @@
         <v>163</v>
       </c>
       <c r="B164" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C164" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D164" t="s">
         <v>5</v>
@@ -8807,13 +8808,13 @@
         <v>7</v>
       </c>
       <c r="H164" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="I164" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="J164" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K164">
         <v>80463</v>
@@ -8833,10 +8834,10 @@
         <v>164</v>
       </c>
       <c r="B165" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C165" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D165" t="s">
         <v>5</v>
@@ -8848,13 +8849,13 @@
         <v>7</v>
       </c>
       <c r="H165" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="I165" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="J165" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K165">
         <v>83000</v>
@@ -8874,25 +8875,25 @@
         <v>165</v>
       </c>
       <c r="B166" t="s">
+        <v>393</v>
+      </c>
+      <c r="C166" t="s">
+        <v>368</v>
+      </c>
+      <c r="D166" t="s">
+        <v>5</v>
+      </c>
+      <c r="G166" t="s">
+        <v>7</v>
+      </c>
+      <c r="H166" t="s">
+        <v>369</v>
+      </c>
+      <c r="I166" t="s">
         <v>394</v>
       </c>
-      <c r="C166" t="s">
-        <v>369</v>
-      </c>
-      <c r="D166" t="s">
-        <v>5</v>
-      </c>
-      <c r="G166" t="s">
-        <v>7</v>
-      </c>
-      <c r="H166" t="s">
-        <v>370</v>
-      </c>
-      <c r="I166" t="s">
-        <v>395</v>
-      </c>
       <c r="J166" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K166">
         <v>129000</v>
@@ -8912,10 +8913,10 @@
         <v>166</v>
       </c>
       <c r="B167" t="s">
+        <v>395</v>
+      </c>
+      <c r="C167" t="s">
         <v>396</v>
-      </c>
-      <c r="C167" t="s">
-        <v>397</v>
       </c>
       <c r="D167" t="s">
         <v>5</v>
@@ -8930,10 +8931,10 @@
         <v>117</v>
       </c>
       <c r="I167" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="J167" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K167">
         <v>62209</v>
@@ -8953,16 +8954,16 @@
         <v>167</v>
       </c>
       <c r="B168" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C168" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D168" t="s">
         <v>5</v>
       </c>
       <c r="F168" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="G168" t="s">
         <v>7</v>
@@ -8971,10 +8972,10 @@
         <v>8</v>
       </c>
       <c r="I168" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="J168" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="K168">
         <v>36117</v>
@@ -8994,10 +8995,10 @@
         <v>168</v>
       </c>
       <c r="B169" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C169" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D169" t="s">
         <v>5</v>
@@ -9015,10 +9016,10 @@
         <v>87</v>
       </c>
       <c r="I169" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="J169" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="K169">
         <v>49900</v>
@@ -9038,10 +9039,10 @@
         <v>169</v>
       </c>
       <c r="B170" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C170" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D170" t="s">
         <v>5</v>
@@ -9050,7 +9051,7 @@
         <v>16</v>
       </c>
       <c r="F170" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="G170" t="s">
         <v>7</v>
@@ -9059,10 +9060,10 @@
         <v>87</v>
       </c>
       <c r="I170" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="J170" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="K170">
         <v>39000</v>
@@ -9082,16 +9083,16 @@
         <v>170</v>
       </c>
       <c r="B171" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C171" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D171" t="s">
         <v>5</v>
       </c>
       <c r="F171" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="G171" t="s">
         <v>7</v>
@@ -9100,10 +9101,10 @@
         <v>205</v>
       </c>
       <c r="I171" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="J171" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="K171">
         <v>49000</v>
@@ -9123,10 +9124,10 @@
         <v>171</v>
       </c>
       <c r="B172" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C172" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D172" t="s">
         <v>207</v>
@@ -9138,10 +9139,10 @@
         <v>8</v>
       </c>
       <c r="I172" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="J172" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="K172">
         <v>59400</v>
@@ -9161,10 +9162,10 @@
         <v>172</v>
       </c>
       <c r="B173" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C173" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D173" t="s">
         <v>5</v>
@@ -9179,10 +9180,10 @@
         <v>8</v>
       </c>
       <c r="I173" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="J173" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="K173">
         <v>65000</v>
@@ -9202,31 +9203,31 @@
         <v>173</v>
       </c>
       <c r="B174" t="s">
+        <v>411</v>
+      </c>
+      <c r="C174" t="s">
+        <v>396</v>
+      </c>
+      <c r="D174" t="s">
+        <v>5</v>
+      </c>
+      <c r="E174" t="s">
+        <v>413</v>
+      </c>
+      <c r="F174" t="s">
         <v>412</v>
       </c>
-      <c r="C174" t="s">
-        <v>397</v>
-      </c>
-      <c r="D174" t="s">
-        <v>5</v>
-      </c>
-      <c r="E174" t="s">
+      <c r="G174" t="s">
+        <v>7</v>
+      </c>
+      <c r="H174" t="s">
         <v>414</v>
       </c>
-      <c r="F174" t="s">
-        <v>413</v>
-      </c>
-      <c r="G174" t="s">
-        <v>7</v>
-      </c>
-      <c r="H174" t="s">
+      <c r="I174" t="s">
         <v>415</v>
       </c>
-      <c r="I174" t="s">
-        <v>416</v>
-      </c>
       <c r="J174" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K174">
         <v>47000</v>
@@ -9246,28 +9247,28 @@
         <v>174</v>
       </c>
       <c r="B175" t="s">
+        <v>416</v>
+      </c>
+      <c r="C175" t="s">
+        <v>396</v>
+      </c>
+      <c r="D175" t="s">
+        <v>5</v>
+      </c>
+      <c r="E175" t="s">
+        <v>413</v>
+      </c>
+      <c r="G175" t="s">
+        <v>7</v>
+      </c>
+      <c r="H175" t="s">
+        <v>414</v>
+      </c>
+      <c r="I175" t="s">
         <v>417</v>
       </c>
-      <c r="C175" t="s">
-        <v>397</v>
-      </c>
-      <c r="D175" t="s">
-        <v>5</v>
-      </c>
-      <c r="E175" t="s">
-        <v>414</v>
-      </c>
-      <c r="G175" t="s">
-        <v>7</v>
-      </c>
-      <c r="H175" t="s">
-        <v>415</v>
-      </c>
-      <c r="I175" t="s">
-        <v>418</v>
-      </c>
       <c r="J175" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K175">
         <v>29000</v>
@@ -9287,10 +9288,10 @@
         <v>175</v>
       </c>
       <c r="B176" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C176" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D176" t="s">
         <v>5</v>
@@ -9308,10 +9309,10 @@
         <v>87</v>
       </c>
       <c r="I176" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="J176" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K176">
         <v>132239</v>
@@ -9331,10 +9332,10 @@
         <v>176</v>
       </c>
       <c r="B177" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C177" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D177" t="s">
         <v>5</v>
@@ -9346,13 +9347,13 @@
         <v>7</v>
       </c>
       <c r="H177" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="I177" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="J177" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K177">
         <v>35016</v>
@@ -9372,10 +9373,10 @@
         <v>177</v>
       </c>
       <c r="B178" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C178" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D178" t="s">
         <v>5</v>
@@ -9387,10 +9388,10 @@
         <v>87</v>
       </c>
       <c r="I178" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="J178" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K178">
         <v>60000</v>
@@ -9410,28 +9411,28 @@
         <v>178</v>
       </c>
       <c r="B179" t="s">
+        <v>424</v>
+      </c>
+      <c r="C179" t="s">
+        <v>396</v>
+      </c>
+      <c r="D179" t="s">
+        <v>5</v>
+      </c>
+      <c r="F179" t="s">
         <v>425</v>
       </c>
-      <c r="C179" t="s">
-        <v>397</v>
-      </c>
-      <c r="D179" t="s">
-        <v>5</v>
-      </c>
-      <c r="F179" t="s">
+      <c r="G179" t="s">
+        <v>7</v>
+      </c>
+      <c r="H179" t="s">
+        <v>369</v>
+      </c>
+      <c r="I179" t="s">
         <v>426</v>
       </c>
-      <c r="G179" t="s">
-        <v>7</v>
-      </c>
-      <c r="H179" t="s">
-        <v>370</v>
-      </c>
-      <c r="I179" t="s">
-        <v>427</v>
-      </c>
       <c r="J179" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="K179">
         <v>90244</v>
@@ -9451,25 +9452,25 @@
         <v>179</v>
       </c>
       <c r="B180" t="s">
+        <v>427</v>
+      </c>
+      <c r="C180" t="s">
+        <v>396</v>
+      </c>
+      <c r="D180" t="s">
+        <v>5</v>
+      </c>
+      <c r="G180" t="s">
+        <v>7</v>
+      </c>
+      <c r="H180" t="s">
+        <v>369</v>
+      </c>
+      <c r="I180" t="s">
         <v>428</v>
       </c>
-      <c r="C180" t="s">
-        <v>397</v>
-      </c>
-      <c r="D180" t="s">
-        <v>5</v>
-      </c>
-      <c r="G180" t="s">
-        <v>7</v>
-      </c>
-      <c r="H180" t="s">
-        <v>370</v>
-      </c>
-      <c r="I180" t="s">
-        <v>429</v>
-      </c>
       <c r="J180" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K180">
         <v>38700</v>
@@ -9489,25 +9490,25 @@
         <v>180</v>
       </c>
       <c r="B181" t="s">
+        <v>429</v>
+      </c>
+      <c r="C181" t="s">
+        <v>396</v>
+      </c>
+      <c r="D181" t="s">
+        <v>5</v>
+      </c>
+      <c r="G181" t="s">
+        <v>7</v>
+      </c>
+      <c r="H181" t="s">
+        <v>369</v>
+      </c>
+      <c r="I181" t="s">
         <v>430</v>
       </c>
-      <c r="C181" t="s">
-        <v>397</v>
-      </c>
-      <c r="D181" t="s">
-        <v>5</v>
-      </c>
-      <c r="G181" t="s">
-        <v>7</v>
-      </c>
-      <c r="H181" t="s">
-        <v>370</v>
-      </c>
-      <c r="I181" t="s">
-        <v>431</v>
-      </c>
       <c r="J181" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="K181">
         <v>62414</v>
@@ -9527,25 +9528,25 @@
         <v>181</v>
       </c>
       <c r="B182" t="s">
+        <v>431</v>
+      </c>
+      <c r="C182" t="s">
+        <v>396</v>
+      </c>
+      <c r="D182" t="s">
+        <v>5</v>
+      </c>
+      <c r="G182" t="s">
+        <v>7</v>
+      </c>
+      <c r="H182" t="s">
+        <v>414</v>
+      </c>
+      <c r="I182" t="s">
         <v>432</v>
       </c>
-      <c r="C182" t="s">
-        <v>397</v>
-      </c>
-      <c r="D182" t="s">
-        <v>5</v>
-      </c>
-      <c r="G182" t="s">
-        <v>7</v>
-      </c>
-      <c r="H182" t="s">
-        <v>415</v>
-      </c>
-      <c r="I182" t="s">
-        <v>433</v>
-      </c>
       <c r="J182" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K182">
         <v>51000</v>
@@ -9565,10 +9566,10 @@
         <v>182</v>
       </c>
       <c r="B183" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C183" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D183" t="s">
         <v>5</v>
@@ -9583,10 +9584,10 @@
         <v>87</v>
       </c>
       <c r="I183" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="J183" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K183">
         <v>53115</v>
@@ -9606,25 +9607,25 @@
         <v>183</v>
       </c>
       <c r="B184" t="s">
+        <v>435</v>
+      </c>
+      <c r="C184" t="s">
+        <v>396</v>
+      </c>
+      <c r="D184" t="s">
+        <v>5</v>
+      </c>
+      <c r="G184" t="s">
+        <v>7</v>
+      </c>
+      <c r="H184" t="s">
+        <v>369</v>
+      </c>
+      <c r="I184" t="s">
         <v>436</v>
       </c>
-      <c r="C184" t="s">
-        <v>397</v>
-      </c>
-      <c r="D184" t="s">
-        <v>5</v>
-      </c>
-      <c r="G184" t="s">
-        <v>7</v>
-      </c>
-      <c r="H184" t="s">
-        <v>370</v>
-      </c>
-      <c r="I184" t="s">
-        <v>437</v>
-      </c>
       <c r="J184" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K184">
         <v>120000</v>
@@ -9644,10 +9645,10 @@
         <v>184</v>
       </c>
       <c r="B185" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C185" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D185" t="s">
         <v>5</v>
@@ -9662,10 +9663,10 @@
         <v>87</v>
       </c>
       <c r="I185" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J185" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K185">
         <v>66477</v>
@@ -9685,10 +9686,10 @@
         <v>185</v>
       </c>
       <c r="B186" t="s">
+        <v>439</v>
+      </c>
+      <c r="C186" t="s">
         <v>440</v>
-      </c>
-      <c r="C186" t="s">
-        <v>441</v>
       </c>
       <c r="D186" t="s">
         <v>5</v>
@@ -9700,10 +9701,10 @@
         <v>7</v>
       </c>
       <c r="H186" t="s">
+        <v>441</v>
+      </c>
+      <c r="I186" t="s">
         <v>442</v>
-      </c>
-      <c r="I186" t="s">
-        <v>443</v>
       </c>
       <c r="K186">
         <v>59300</v>
@@ -9723,22 +9724,22 @@
         <v>186</v>
       </c>
       <c r="B187" t="s">
+        <v>443</v>
+      </c>
+      <c r="C187" t="s">
+        <v>440</v>
+      </c>
+      <c r="D187" t="s">
+        <v>5</v>
+      </c>
+      <c r="G187" t="s">
+        <v>7</v>
+      </c>
+      <c r="H187" t="s">
+        <v>441</v>
+      </c>
+      <c r="I187" t="s">
         <v>444</v>
-      </c>
-      <c r="C187" t="s">
-        <v>441</v>
-      </c>
-      <c r="D187" t="s">
-        <v>5</v>
-      </c>
-      <c r="G187" t="s">
-        <v>7</v>
-      </c>
-      <c r="H187" t="s">
-        <v>442</v>
-      </c>
-      <c r="I187" t="s">
-        <v>445</v>
       </c>
       <c r="K187">
         <v>44000</v>
@@ -9758,22 +9759,22 @@
         <v>187</v>
       </c>
       <c r="B188" t="s">
+        <v>445</v>
+      </c>
+      <c r="C188" t="s">
+        <v>440</v>
+      </c>
+      <c r="D188" t="s">
+        <v>5</v>
+      </c>
+      <c r="G188" t="s">
+        <v>7</v>
+      </c>
+      <c r="H188" t="s">
+        <v>441</v>
+      </c>
+      <c r="I188" t="s">
         <v>446</v>
-      </c>
-      <c r="C188" t="s">
-        <v>441</v>
-      </c>
-      <c r="D188" t="s">
-        <v>5</v>
-      </c>
-      <c r="G188" t="s">
-        <v>7</v>
-      </c>
-      <c r="H188" t="s">
-        <v>442</v>
-      </c>
-      <c r="I188" t="s">
-        <v>447</v>
       </c>
       <c r="K188">
         <v>26528</v>
@@ -9793,10 +9794,10 @@
         <v>188</v>
       </c>
       <c r="B189" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C189" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="D189" t="s">
         <v>5</v>
@@ -9808,10 +9809,10 @@
         <v>7</v>
       </c>
       <c r="H189" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="I189" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="K189">
         <v>95684</v>
@@ -9831,10 +9832,10 @@
         <v>189</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C190" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="D190" t="s">
         <v>5</v>
@@ -9846,7 +9847,7 @@
         <v>87</v>
       </c>
       <c r="I190" s="4" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="K190">
         <v>26737</v>
@@ -9866,10 +9867,10 @@
         <v>190</v>
       </c>
       <c r="B191" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C191" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="D191" t="s">
         <v>5</v>
@@ -9881,10 +9882,10 @@
         <v>7</v>
       </c>
       <c r="H191" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="I191" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="K191">
         <v>60000</v>
@@ -9904,22 +9905,22 @@
         <v>191</v>
       </c>
       <c r="B192" t="s">
+        <v>451</v>
+      </c>
+      <c r="C192" t="s">
+        <v>440</v>
+      </c>
+      <c r="D192" t="s">
+        <v>5</v>
+      </c>
+      <c r="G192" t="s">
+        <v>7</v>
+      </c>
+      <c r="H192" t="s">
+        <v>441</v>
+      </c>
+      <c r="I192" t="s">
         <v>452</v>
-      </c>
-      <c r="C192" t="s">
-        <v>441</v>
-      </c>
-      <c r="D192" t="s">
-        <v>5</v>
-      </c>
-      <c r="G192" t="s">
-        <v>7</v>
-      </c>
-      <c r="H192" t="s">
-        <v>442</v>
-      </c>
-      <c r="I192" t="s">
-        <v>453</v>
       </c>
       <c r="K192">
         <v>34895</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yuhang/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{676B3433-4BDB-384E-B716-4BED7122BF59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC039BB0-4061-154B-A967-F8D996A5E570}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-7900" yWindow="-28200" windowWidth="25620" windowHeight="28200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1579" uniqueCount="494">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1581" uniqueCount="496">
   <si>
     <t>所在市</t>
   </si>
@@ -896,16 +896,10 @@
     <t>丽金智地中心</t>
   </si>
   <si>
-    <t>116.320104,39.956309</t>
-  </si>
-  <si>
     <t>丽金智地中心-蚂蚁金服面积</t>
   </si>
   <si>
     <t>和泓大厦</t>
-  </si>
-  <si>
-    <t>116.328270,39.960285</t>
   </si>
   <si>
     <t>西海国际中心</t>
@@ -1537,6 +1531,22 @@
   </si>
   <si>
     <t>116.313304,39.982116</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>116.320807,39.956309</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>116.319635,39.956309</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>已经更改</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>116.329228,39.958832</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1620,12 +1630,13 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1957,22 +1968,22 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" t="s">
+        <v>456</v>
+      </c>
+      <c r="B1" t="s">
         <v>458</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
+        <v>459</v>
+      </c>
+      <c r="D1" t="s">
         <v>460</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="F1" t="s">
         <v>461</v>
-      </c>
-      <c r="D1" t="s">
-        <v>462</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>468</v>
-      </c>
-      <c r="F1" t="s">
-        <v>463</v>
       </c>
       <c r="G1" t="s">
         <v>0</v>
@@ -1984,19 +1995,19 @@
         <v>2</v>
       </c>
       <c r="J1" t="s">
+        <v>462</v>
+      </c>
+      <c r="K1" t="s">
+        <v>457</v>
+      </c>
+      <c r="L1" t="s">
+        <v>463</v>
+      </c>
+      <c r="M1" t="s">
         <v>464</v>
       </c>
-      <c r="K1" t="s">
-        <v>459</v>
-      </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>465</v>
-      </c>
-      <c r="M1" t="s">
-        <v>466</v>
-      </c>
-      <c r="N1" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -2025,7 +2036,7 @@
         <v>9</v>
       </c>
       <c r="J2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K2">
         <v>72308</v>
@@ -2066,7 +2077,7 @@
         <v>12</v>
       </c>
       <c r="J3" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K3">
         <v>72308</v>
@@ -2110,7 +2121,7 @@
         <v>17</v>
       </c>
       <c r="J4" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K4">
         <v>130769</v>
@@ -2154,7 +2165,7 @@
         <v>20</v>
       </c>
       <c r="J5" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K5">
         <v>64615</v>
@@ -2198,7 +2209,7 @@
         <v>24</v>
       </c>
       <c r="J6" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K6">
         <v>80091</v>
@@ -2239,7 +2250,7 @@
         <v>27</v>
       </c>
       <c r="J7" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="K7">
         <v>70673</v>
@@ -2283,7 +2294,7 @@
         <v>30</v>
       </c>
       <c r="J8" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K8">
         <v>90466</v>
@@ -2324,7 +2335,7 @@
         <v>32</v>
       </c>
       <c r="J9" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="K9">
         <v>46720</v>
@@ -2368,7 +2379,7 @@
         <v>35</v>
       </c>
       <c r="J10" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="K10">
         <v>95000</v>
@@ -2412,7 +2423,7 @@
         <v>38</v>
       </c>
       <c r="J11" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K11">
         <v>85300</v>
@@ -2456,7 +2467,7 @@
         <v>41</v>
       </c>
       <c r="J12" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="K12">
         <v>33305</v>
@@ -2500,7 +2511,7 @@
         <v>43</v>
       </c>
       <c r="J13" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K13">
         <v>120245.21</v>
@@ -2544,7 +2555,7 @@
         <v>43</v>
       </c>
       <c r="J14" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K14">
         <v>70425.53</v>
@@ -2588,7 +2599,7 @@
         <v>47</v>
       </c>
       <c r="J15" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K15">
         <v>78000</v>
@@ -2632,7 +2643,7 @@
         <v>50</v>
       </c>
       <c r="J16" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="K16">
         <v>102796</v>
@@ -2676,7 +2687,7 @@
         <v>52</v>
       </c>
       <c r="J17" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="K17">
         <v>49200</v>
@@ -2720,7 +2731,7 @@
         <v>54</v>
       </c>
       <c r="J18" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="K18">
         <v>65096</v>
@@ -2764,7 +2775,7 @@
         <v>57</v>
       </c>
       <c r="J19" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K19">
         <v>56000</v>
@@ -2808,7 +2819,7 @@
         <v>60</v>
       </c>
       <c r="J20" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="K20">
         <v>177847</v>
@@ -2852,7 +2863,7 @@
         <v>63</v>
       </c>
       <c r="J21" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K21">
         <v>83000</v>
@@ -2893,7 +2904,7 @@
         <v>66</v>
       </c>
       <c r="J22" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="K22">
         <v>26000</v>
@@ -2934,7 +2945,7 @@
         <v>68</v>
       </c>
       <c r="J23" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K23">
         <v>85887</v>
@@ -2975,7 +2986,7 @@
         <v>70</v>
       </c>
       <c r="J24" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K24">
         <v>20000</v>
@@ -3019,7 +3030,7 @@
         <v>73</v>
       </c>
       <c r="J25" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K25">
         <v>146385</v>
@@ -3063,7 +3074,7 @@
         <v>76</v>
       </c>
       <c r="J26" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K26">
         <v>87000</v>
@@ -3107,7 +3118,7 @@
         <v>79</v>
       </c>
       <c r="J27" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K27">
         <v>147166.79999999999</v>
@@ -3151,7 +3162,7 @@
         <v>82</v>
       </c>
       <c r="J28" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K28">
         <v>46063</v>
@@ -3195,7 +3206,7 @@
         <v>85</v>
       </c>
       <c r="J29" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="K29">
         <v>47261</v>
@@ -3215,7 +3226,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C30" t="s">
         <v>4</v>
@@ -3233,13 +3244,13 @@
         <v>7</v>
       </c>
       <c r="H30" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="I30" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="I30" s="2" t="s">
-        <v>475</v>
-      </c>
       <c r="J30" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K30">
         <v>119000</v>
@@ -3280,7 +3291,7 @@
         <v>91</v>
       </c>
       <c r="J31" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="K31">
         <v>47000</v>
@@ -3324,7 +3335,7 @@
         <v>93</v>
       </c>
       <c r="J32" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="K32">
         <v>186000</v>
@@ -3362,7 +3373,7 @@
         <v>95</v>
       </c>
       <c r="J33" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K33">
         <v>40800</v>
@@ -3403,7 +3414,7 @@
         <v>95</v>
       </c>
       <c r="J34" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K34">
         <v>55200</v>
@@ -3447,7 +3458,7 @@
         <v>99</v>
       </c>
       <c r="J35" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="K35">
         <v>350000</v>
@@ -3488,7 +3499,7 @@
         <v>101</v>
       </c>
       <c r="J36" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K36">
         <v>65000</v>
@@ -3529,7 +3540,7 @@
         <v>101</v>
       </c>
       <c r="J37" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K37">
         <v>35000</v>
@@ -3570,7 +3581,7 @@
         <v>104</v>
       </c>
       <c r="J38" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="K38">
         <v>47000</v>
@@ -3614,7 +3625,7 @@
         <v>107</v>
       </c>
       <c r="J39" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="K39">
         <v>120000</v>
@@ -3655,7 +3666,7 @@
         <v>109</v>
       </c>
       <c r="J40" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K40">
         <v>83000</v>
@@ -3696,7 +3707,7 @@
         <v>111</v>
       </c>
       <c r="J41" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="K41">
         <v>66030</v>
@@ -3734,7 +3745,7 @@
         <v>113</v>
       </c>
       <c r="J42" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="K42">
         <v>40000</v>
@@ -3778,7 +3789,7 @@
         <v>118</v>
       </c>
       <c r="J43" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K43">
         <v>40000</v>
@@ -3819,7 +3830,7 @@
         <v>121</v>
       </c>
       <c r="J44" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K44">
         <v>54100</v>
@@ -3860,10 +3871,10 @@
         <v>117</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J45" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K45">
         <v>100000</v>
@@ -3904,10 +3915,10 @@
         <v>117</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="J46" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K46">
         <v>150000</v>
@@ -3948,10 +3959,10 @@
         <v>117</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="J47" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K47">
         <v>50000</v>
@@ -3995,7 +4006,7 @@
         <v>130</v>
       </c>
       <c r="J48" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="K48">
         <v>43000</v>
@@ -4036,7 +4047,7 @@
         <v>133</v>
       </c>
       <c r="J49" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="K49">
         <v>65000</v>
@@ -4077,7 +4088,7 @@
         <v>136</v>
       </c>
       <c r="J50" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="51" spans="1:14">
@@ -4109,7 +4120,7 @@
         <v>138</v>
       </c>
       <c r="J51" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="K51">
         <v>56000</v>
@@ -4150,7 +4161,7 @@
         <v>140</v>
       </c>
       <c r="J52" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="K52">
         <v>160000</v>
@@ -4191,7 +4202,7 @@
         <v>142</v>
       </c>
       <c r="J53" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="K53">
         <v>33000</v>
@@ -4235,7 +4246,7 @@
         <v>145</v>
       </c>
       <c r="J54" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="K54">
         <v>41318</v>
@@ -4276,7 +4287,7 @@
         <v>147</v>
       </c>
       <c r="J55" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K55">
         <v>34131</v>
@@ -4317,7 +4328,7 @@
         <v>150</v>
       </c>
       <c r="J56" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K56">
         <v>48000</v>
@@ -4358,7 +4369,7 @@
         <v>118</v>
       </c>
       <c r="J57" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K57">
         <v>16000</v>
@@ -4402,7 +4413,7 @@
         <v>154</v>
       </c>
       <c r="J58" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="K58">
         <v>30000</v>
@@ -4446,7 +4457,7 @@
         <v>157</v>
       </c>
       <c r="J59" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="K59">
         <v>56000</v>
@@ -4490,7 +4501,7 @@
         <v>160</v>
       </c>
       <c r="J60" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K60">
         <v>43000</v>
@@ -4531,7 +4542,7 @@
         <v>162</v>
       </c>
       <c r="J61" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="K61">
         <v>110000</v>
@@ -4569,7 +4580,7 @@
         <v>164</v>
       </c>
       <c r="J62" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K62">
         <v>56160</v>
@@ -4610,7 +4621,7 @@
         <v>166</v>
       </c>
       <c r="J63" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K63">
         <v>138444</v>
@@ -4654,7 +4665,7 @@
         <v>170</v>
       </c>
       <c r="J64" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="K64">
         <v>31000</v>
@@ -4695,7 +4706,7 @@
         <v>173</v>
       </c>
       <c r="J65" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="K65">
         <v>120000</v>
@@ -4736,7 +4747,7 @@
         <v>175</v>
       </c>
       <c r="J66" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="K66">
         <v>25900</v>
@@ -4777,7 +4788,7 @@
         <v>178</v>
       </c>
       <c r="J67" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="K67">
         <v>47986</v>
@@ -4821,7 +4832,7 @@
         <v>180</v>
       </c>
       <c r="J68" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="K68">
         <v>194000</v>
@@ -4865,7 +4876,7 @@
         <v>182</v>
       </c>
       <c r="J69" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="K69">
         <v>39724</v>
@@ -4903,10 +4914,10 @@
         <v>87</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="J70" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="K70">
         <v>48437.45</v>
@@ -4947,7 +4958,7 @@
         <v>186</v>
       </c>
       <c r="J71" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="K71">
         <v>37910</v>
@@ -4967,7 +4978,7 @@
         <v>71</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C72" t="s">
         <v>168</v>
@@ -4985,10 +4996,10 @@
         <v>87</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="J72" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="K72">
         <v>21220</v>
@@ -5029,7 +5040,7 @@
         <v>188</v>
       </c>
       <c r="J73" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="K73">
         <v>77877</v>
@@ -5073,7 +5084,7 @@
         <v>190</v>
       </c>
       <c r="J74" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="K74">
         <v>80311.53</v>
@@ -5117,7 +5128,7 @@
         <v>193</v>
       </c>
       <c r="J75" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="K75">
         <v>38000</v>
@@ -5158,7 +5169,7 @@
         <v>196</v>
       </c>
       <c r="J76" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="K76">
         <v>37800</v>
@@ -5199,10 +5210,10 @@
         <v>87</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="J77" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="K77">
         <v>54581</v>
@@ -5246,7 +5257,7 @@
         <v>88</v>
       </c>
       <c r="J78" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="K78">
         <v>25000</v>
@@ -5290,7 +5301,7 @@
         <v>202</v>
       </c>
       <c r="J79" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="K79">
         <v>52698</v>
@@ -5328,10 +5339,10 @@
         <v>205</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="J80" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="K80">
         <v>38500</v>
@@ -5369,7 +5380,7 @@
         <v>208</v>
       </c>
       <c r="J81" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="K81">
         <v>27200</v>
@@ -5413,7 +5424,7 @@
         <v>211</v>
       </c>
       <c r="J82" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="K82">
         <v>60000</v>
@@ -5454,7 +5465,7 @@
         <v>214</v>
       </c>
       <c r="J83" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K83">
         <v>50000</v>
@@ -5498,7 +5509,7 @@
         <v>216</v>
       </c>
       <c r="J84" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="K84">
         <v>131575</v>
@@ -5539,7 +5550,7 @@
         <v>218</v>
       </c>
       <c r="J85" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K85">
         <v>99500</v>
@@ -5580,7 +5591,7 @@
         <v>221</v>
       </c>
       <c r="J86" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="K86">
         <v>32000</v>
@@ -5624,7 +5635,7 @@
         <v>223</v>
       </c>
       <c r="J87" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="K87">
         <v>52170</v>
@@ -5665,7 +5676,7 @@
         <v>226</v>
       </c>
       <c r="J88" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="K88">
         <v>46000</v>
@@ -5709,7 +5720,7 @@
         <v>229</v>
       </c>
       <c r="J89" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K89">
         <v>45013</v>
@@ -5750,7 +5761,7 @@
         <v>231</v>
       </c>
       <c r="J90" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="K90">
         <v>48566</v>
@@ -5791,7 +5802,7 @@
         <v>234</v>
       </c>
       <c r="J91" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K91">
         <v>55618</v>
@@ -5832,7 +5843,7 @@
         <v>236</v>
       </c>
       <c r="J92" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="K92">
         <v>47000</v>
@@ -5876,7 +5887,7 @@
         <v>239</v>
       </c>
       <c r="J93" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K93">
         <v>87763</v>
@@ -5920,7 +5931,7 @@
         <v>242</v>
       </c>
       <c r="J94" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="K94">
         <v>100658</v>
@@ -5961,7 +5972,7 @@
         <v>245</v>
       </c>
       <c r="J95" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="K95">
         <v>67000</v>
@@ -6005,7 +6016,7 @@
         <v>247</v>
       </c>
       <c r="J96" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="K96">
         <v>39431</v>
@@ -6046,7 +6057,7 @@
         <v>249</v>
       </c>
       <c r="J97" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="K97">
         <v>34273</v>
@@ -6084,7 +6095,7 @@
         <v>73</v>
       </c>
       <c r="J98" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K98">
         <v>40000</v>
@@ -6125,7 +6136,7 @@
         <v>252</v>
       </c>
       <c r="J99" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="K99">
         <v>65000</v>
@@ -6169,7 +6180,7 @@
         <v>256</v>
       </c>
       <c r="J100" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="K100">
         <v>49000</v>
@@ -6213,7 +6224,7 @@
         <v>259</v>
       </c>
       <c r="J101" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="K101">
         <v>95000</v>
@@ -6257,7 +6268,7 @@
         <v>262</v>
       </c>
       <c r="J102" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="K102">
         <v>45000</v>
@@ -6298,7 +6309,7 @@
         <v>264</v>
       </c>
       <c r="J103" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="K103">
         <v>124500</v>
@@ -6336,10 +6347,10 @@
         <v>205</v>
       </c>
       <c r="I104" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="J104" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="K104">
         <v>64000</v>
@@ -6380,7 +6391,7 @@
         <v>267</v>
       </c>
       <c r="J105" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="K105">
         <v>25000</v>
@@ -6421,7 +6432,7 @@
         <v>269</v>
       </c>
       <c r="J106" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="K106">
         <v>38498</v>
@@ -6459,7 +6470,7 @@
         <v>271</v>
       </c>
       <c r="J107" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="K107">
         <v>166433</v>
@@ -6503,7 +6514,7 @@
         <v>273</v>
       </c>
       <c r="J108" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="K108">
         <v>58000</v>
@@ -6544,7 +6555,7 @@
         <v>276</v>
       </c>
       <c r="J109" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="K109">
         <v>51872</v>
@@ -6585,7 +6596,7 @@
         <v>278</v>
       </c>
       <c r="J110" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="K110">
         <v>21632</v>
@@ -6626,7 +6637,7 @@
         <v>280</v>
       </c>
       <c r="J111" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="K111">
         <v>69000</v>
@@ -6667,7 +6678,7 @@
         <v>283</v>
       </c>
       <c r="J112" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="K112">
         <v>54000</v>
@@ -6708,7 +6719,7 @@
         <v>285</v>
       </c>
       <c r="J113" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="K113">
         <v>57400</v>
@@ -6727,7 +6738,7 @@
       <c r="A114">
         <v>113</v>
       </c>
-      <c r="B114" t="s">
+      <c r="B114" s="2" t="s">
         <v>286</v>
       </c>
       <c r="C114" t="s">
@@ -6745,11 +6756,11 @@
       <c r="H114" t="s">
         <v>205</v>
       </c>
-      <c r="I114" t="s">
-        <v>287</v>
+      <c r="I114" s="2" t="s">
+        <v>493</v>
       </c>
       <c r="J114" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="K114">
         <v>60000</v>
@@ -6762,14 +6773,17 @@
       </c>
       <c r="N114">
         <v>427</v>
+      </c>
+      <c r="P114" s="1" t="s">
+        <v>494</v>
       </c>
     </row>
     <row r="115" spans="1:16">
       <c r="A115">
         <v>114</v>
       </c>
-      <c r="B115" t="s">
-        <v>288</v>
+      <c r="B115" s="2" t="s">
+        <v>287</v>
       </c>
       <c r="C115" t="s">
         <v>254</v>
@@ -6786,11 +6800,11 @@
       <c r="H115" t="s">
         <v>205</v>
       </c>
-      <c r="I115" t="s">
-        <v>287</v>
+      <c r="I115" s="2" t="s">
+        <v>492</v>
       </c>
       <c r="J115" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="K115">
         <v>60000</v>
@@ -6803,14 +6817,17 @@
       </c>
       <c r="N115">
         <v>11500</v>
+      </c>
+      <c r="P115" s="1" t="s">
+        <v>494</v>
       </c>
     </row>
     <row r="116" spans="1:16">
       <c r="A116">
         <v>115</v>
       </c>
-      <c r="B116" t="s">
-        <v>289</v>
+      <c r="B116" s="2" t="s">
+        <v>288</v>
       </c>
       <c r="C116" t="s">
         <v>254</v>
@@ -6824,11 +6841,11 @@
       <c r="H116" t="s">
         <v>205</v>
       </c>
-      <c r="I116" t="s">
-        <v>290</v>
+      <c r="I116" s="5" t="s">
+        <v>495</v>
       </c>
       <c r="J116" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="K116">
         <v>33000</v>
@@ -6848,7 +6865,7 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C117" t="s">
         <v>254</v>
@@ -6863,10 +6880,10 @@
         <v>205</v>
       </c>
       <c r="I117" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="J117" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="K117">
         <v>88786</v>
@@ -6886,7 +6903,7 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C118" t="s">
         <v>254</v>
@@ -6901,10 +6918,10 @@
         <v>205</v>
       </c>
       <c r="I118" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="J118" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="K118">
         <v>134000</v>
@@ -6924,7 +6941,7 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C119" t="s">
         <v>254</v>
@@ -6939,10 +6956,10 @@
         <v>205</v>
       </c>
       <c r="I119" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="J119" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="K119">
         <v>35000</v>
@@ -6962,7 +6979,7 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C120" t="s">
         <v>254</v>
@@ -6977,10 +6994,10 @@
         <v>205</v>
       </c>
       <c r="I120" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="J120" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="K120">
         <v>18000</v>
@@ -7000,7 +7017,7 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C121" t="s">
         <v>254</v>
@@ -7018,10 +7035,10 @@
         <v>205</v>
       </c>
       <c r="I121" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="J121" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="K121">
         <v>105741</v>
@@ -7041,7 +7058,7 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C122" t="s">
         <v>254</v>
@@ -7056,10 +7073,10 @@
         <v>205</v>
       </c>
       <c r="I122" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="J122" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="K122">
         <v>51000</v>
@@ -7079,7 +7096,7 @@
         <v>122</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C123" t="s">
         <v>254</v>
@@ -7097,10 +7114,10 @@
         <v>205</v>
       </c>
       <c r="I123" s="3" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="J123" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="K123">
         <v>130143</v>
@@ -7115,7 +7132,7 @@
         <v>36000</v>
       </c>
       <c r="P123" s="1" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7123,7 +7140,7 @@
         <v>123</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C124" t="s">
         <v>254</v>
@@ -7135,10 +7152,10 @@
         <v>205</v>
       </c>
       <c r="I124" s="3" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="J124" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="K124">
         <v>121551.47</v>
@@ -7153,7 +7170,7 @@
         <v>97326.47</v>
       </c>
       <c r="P124" s="1" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7161,10 +7178,10 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C125" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D125" t="s">
         <v>5</v>
@@ -7173,7 +7190,7 @@
         <v>16</v>
       </c>
       <c r="F125" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="G125" t="s">
         <v>7</v>
@@ -7182,10 +7199,10 @@
         <v>8</v>
       </c>
       <c r="I125" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="J125" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="K125">
         <v>110000</v>
@@ -7205,10 +7222,10 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C126" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D126" t="s">
         <v>5</v>
@@ -7226,10 +7243,10 @@
         <v>8</v>
       </c>
       <c r="I126" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="J126" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="K126">
         <v>56000</v>
@@ -7249,10 +7266,10 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C127" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D127" t="s">
         <v>5</v>
@@ -7267,10 +7284,10 @@
         <v>8</v>
       </c>
       <c r="I127" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="J127" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="K127">
         <v>89177</v>
@@ -7290,10 +7307,10 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C128" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D128" t="s">
         <v>5</v>
@@ -7302,7 +7319,7 @@
         <v>23</v>
       </c>
       <c r="F128" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="G128" t="s">
         <v>7</v>
@@ -7311,10 +7328,10 @@
         <v>8</v>
       </c>
       <c r="I128" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="J128" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="K128">
         <v>30000</v>
@@ -7334,10 +7351,10 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C129" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D129" t="s">
         <v>5</v>
@@ -7346,7 +7363,7 @@
         <v>16</v>
       </c>
       <c r="F129" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="G129" t="s">
         <v>7</v>
@@ -7355,10 +7372,10 @@
         <v>8</v>
       </c>
       <c r="I129" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="J129" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="K129">
         <v>54550</v>
@@ -7378,10 +7395,10 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C130" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D130" t="s">
         <v>5</v>
@@ -7399,10 +7416,10 @@
         <v>8</v>
       </c>
       <c r="I130" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="J130" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="K130">
         <v>125000</v>
@@ -7422,10 +7439,10 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C131" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D131" t="s">
         <v>5</v>
@@ -7434,7 +7451,7 @@
         <v>16</v>
       </c>
       <c r="F131" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="G131" t="s">
         <v>7</v>
@@ -7443,10 +7460,10 @@
         <v>8</v>
       </c>
       <c r="I131" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="J131" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="K131">
         <v>69100</v>
@@ -7466,10 +7483,10 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C132" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D132" t="s">
         <v>5</v>
@@ -7487,10 +7504,10 @@
         <v>8</v>
       </c>
       <c r="I132" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="J132" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="K132">
         <v>118290</v>
@@ -7510,16 +7527,16 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C133" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D133" t="s">
         <v>5</v>
       </c>
       <c r="F133" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="G133" t="s">
         <v>7</v>
@@ -7528,10 +7545,10 @@
         <v>8</v>
       </c>
       <c r="I133" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="J133" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="K133">
         <v>79900</v>
@@ -7551,10 +7568,10 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C134" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D134" t="s">
         <v>5</v>
@@ -7569,10 +7586,10 @@
         <v>8</v>
       </c>
       <c r="I134" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="J134" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="K134">
         <v>39742.379999999997</v>
@@ -7592,10 +7609,10 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C135" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D135" t="s">
         <v>5</v>
@@ -7613,10 +7630,10 @@
         <v>8</v>
       </c>
       <c r="I135" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="J135" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="K135">
         <v>48000</v>
@@ -7636,10 +7653,10 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C136" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D136" t="s">
         <v>14</v>
@@ -7654,10 +7671,10 @@
         <v>8</v>
       </c>
       <c r="I136" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="J136" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="K136">
         <v>74722</v>
@@ -7677,10 +7694,10 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C137" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D137" t="s">
         <v>207</v>
@@ -7692,10 +7709,10 @@
         <v>8</v>
       </c>
       <c r="I137" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="J137" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="K137">
         <v>55000</v>
@@ -7715,10 +7732,10 @@
         <v>137</v>
       </c>
       <c r="B138" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C138" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D138" t="s">
         <v>5</v>
@@ -7730,10 +7747,10 @@
         <v>117</v>
       </c>
       <c r="I138" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="J138" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K138">
         <v>128000</v>
@@ -7753,10 +7770,10 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C139" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D139" t="s">
         <v>5</v>
@@ -7774,10 +7791,10 @@
         <v>117</v>
       </c>
       <c r="I139" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="J139" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K139">
         <v>122000</v>
@@ -7797,10 +7814,10 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C140" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D140" t="s">
         <v>5</v>
@@ -7815,10 +7832,10 @@
         <v>117</v>
       </c>
       <c r="I140" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="J140" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K140">
         <v>22000</v>
@@ -7838,10 +7855,10 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C141" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D141" t="s">
         <v>5</v>
@@ -7856,10 +7873,10 @@
         <v>117</v>
       </c>
       <c r="I141" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="J141" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K141">
         <v>10000</v>
@@ -7879,10 +7896,10 @@
         <v>141</v>
       </c>
       <c r="B142" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C142" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D142" t="s">
         <v>5</v>
@@ -7897,10 +7914,10 @@
         <v>8</v>
       </c>
       <c r="I142" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="J142" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="K142">
         <v>64000</v>
@@ -7920,10 +7937,10 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C143" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D143" t="s">
         <v>5</v>
@@ -7938,10 +7955,10 @@
         <v>8</v>
       </c>
       <c r="I143" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="J143" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="K143">
         <v>95628</v>
@@ -7961,16 +7978,16 @@
         <v>143</v>
       </c>
       <c r="B144" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C144" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D144" t="s">
         <v>5</v>
       </c>
       <c r="F144" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="G144" t="s">
         <v>7</v>
@@ -7979,10 +7996,10 @@
         <v>8</v>
       </c>
       <c r="I144" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="J144" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="K144">
         <v>39562</v>
@@ -8002,10 +8019,10 @@
         <v>144</v>
       </c>
       <c r="B145" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C145" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D145" t="s">
         <v>5</v>
@@ -8014,7 +8031,7 @@
         <v>16</v>
       </c>
       <c r="F145" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="G145" t="s">
         <v>7</v>
@@ -8023,10 +8040,10 @@
         <v>8</v>
       </c>
       <c r="I145" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="J145" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K145">
         <v>105000</v>
@@ -8046,10 +8063,10 @@
         <v>145</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C146" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D146" t="s">
         <v>5</v>
@@ -8058,7 +8075,7 @@
         <v>23</v>
       </c>
       <c r="F146" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="G146" t="s">
         <v>7</v>
@@ -8067,10 +8084,10 @@
         <v>8</v>
       </c>
       <c r="I146" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="J146" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K146">
         <v>60000</v>
@@ -8090,10 +8107,10 @@
         <v>146</v>
       </c>
       <c r="B147" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C147" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D147" t="s">
         <v>5</v>
@@ -8108,10 +8125,10 @@
         <v>8</v>
       </c>
       <c r="I147" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="J147" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="K147">
         <v>39964</v>
@@ -8131,10 +8148,10 @@
         <v>147</v>
       </c>
       <c r="B148" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C148" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D148" t="s">
         <v>5</v>
@@ -8149,10 +8166,10 @@
         <v>8</v>
       </c>
       <c r="I148" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="J148" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K148">
         <v>94000</v>
@@ -8172,10 +8189,10 @@
         <v>148</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C149" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D149" t="s">
         <v>5</v>
@@ -8193,10 +8210,10 @@
         <v>8</v>
       </c>
       <c r="I149" s="2" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="J149" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K149">
         <v>75000</v>
@@ -8219,13 +8236,13 @@
         <v>183</v>
       </c>
       <c r="C150" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D150" t="s">
         <v>5</v>
       </c>
       <c r="F150" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="G150" t="s">
         <v>7</v>
@@ -8234,10 +8251,10 @@
         <v>87</v>
       </c>
       <c r="I150" s="2" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="J150" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K150">
         <v>48767</v>
@@ -8257,10 +8274,10 @@
         <v>150</v>
       </c>
       <c r="B151" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C151" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D151" t="s">
         <v>5</v>
@@ -8278,10 +8295,10 @@
         <v>8</v>
       </c>
       <c r="I151" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="J151" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K151">
         <v>63824</v>
@@ -8301,10 +8318,10 @@
         <v>151</v>
       </c>
       <c r="B152" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C152" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D152" t="s">
         <v>14</v>
@@ -8322,10 +8339,10 @@
         <v>8</v>
       </c>
       <c r="I152" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="J152" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K152">
         <v>117000</v>
@@ -8345,10 +8362,10 @@
         <v>152</v>
       </c>
       <c r="B153" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C153" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D153" t="s">
         <v>5</v>
@@ -8360,10 +8377,10 @@
         <v>8</v>
       </c>
       <c r="I153" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="J153" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K153">
         <v>41000</v>
@@ -8383,10 +8400,10 @@
         <v>153</v>
       </c>
       <c r="B154" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C154" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D154" t="s">
         <v>5</v>
@@ -8398,10 +8415,10 @@
         <v>8</v>
       </c>
       <c r="I154" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="J154" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="K154">
         <v>96446</v>
@@ -8421,10 +8438,10 @@
         <v>154</v>
       </c>
       <c r="B155" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C155" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D155" t="s">
         <v>5</v>
@@ -8439,13 +8456,13 @@
         <v>7</v>
       </c>
       <c r="H155" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="I155" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="J155" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K155">
         <v>76600</v>
@@ -8465,10 +8482,10 @@
         <v>155</v>
       </c>
       <c r="B156" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C156" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D156" t="s">
         <v>5</v>
@@ -8480,13 +8497,13 @@
         <v>7</v>
       </c>
       <c r="H156" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="I156" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="J156" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="K156">
         <v>125569</v>
@@ -8506,28 +8523,28 @@
         <v>156</v>
       </c>
       <c r="B157" t="s">
+        <v>371</v>
+      </c>
+      <c r="C157" t="s">
+        <v>366</v>
+      </c>
+      <c r="D157" t="s">
+        <v>5</v>
+      </c>
+      <c r="F157" t="s">
+        <v>372</v>
+      </c>
+      <c r="G157" t="s">
+        <v>7</v>
+      </c>
+      <c r="H157" t="s">
+        <v>367</v>
+      </c>
+      <c r="I157" t="s">
         <v>373</v>
       </c>
-      <c r="C157" t="s">
-        <v>368</v>
-      </c>
-      <c r="D157" t="s">
-        <v>5</v>
-      </c>
-      <c r="F157" t="s">
-        <v>374</v>
-      </c>
-      <c r="G157" t="s">
-        <v>7</v>
-      </c>
-      <c r="H157" t="s">
-        <v>369</v>
-      </c>
-      <c r="I157" t="s">
-        <v>375</v>
-      </c>
       <c r="J157" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K157">
         <v>51234</v>
@@ -8547,10 +8564,10 @@
         <v>157</v>
       </c>
       <c r="B158" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C158" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D158" t="s">
         <v>5</v>
@@ -8565,13 +8582,13 @@
         <v>7</v>
       </c>
       <c r="H158" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="I158" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="J158" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="K158">
         <v>123780</v>
@@ -8591,28 +8608,28 @@
         <v>158</v>
       </c>
       <c r="B159" t="s">
+        <v>376</v>
+      </c>
+      <c r="C159" t="s">
+        <v>366</v>
+      </c>
+      <c r="D159" t="s">
+        <v>5</v>
+      </c>
+      <c r="F159" t="s">
+        <v>377</v>
+      </c>
+      <c r="G159" t="s">
+        <v>7</v>
+      </c>
+      <c r="H159" t="s">
+        <v>367</v>
+      </c>
+      <c r="I159" t="s">
         <v>378</v>
       </c>
-      <c r="C159" t="s">
-        <v>368</v>
-      </c>
-      <c r="D159" t="s">
-        <v>5</v>
-      </c>
-      <c r="F159" t="s">
-        <v>379</v>
-      </c>
-      <c r="G159" t="s">
-        <v>7</v>
-      </c>
-      <c r="H159" t="s">
-        <v>369</v>
-      </c>
-      <c r="I159" t="s">
-        <v>380</v>
-      </c>
       <c r="J159" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K159">
         <v>46000</v>
@@ -8632,10 +8649,10 @@
         <v>159</v>
       </c>
       <c r="B160" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C160" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D160" t="s">
         <v>5</v>
@@ -8644,13 +8661,13 @@
         <v>7</v>
       </c>
       <c r="H160" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="I160" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="J160" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K160">
         <v>35600</v>
@@ -8670,10 +8687,10 @@
         <v>160</v>
       </c>
       <c r="B161" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C161" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D161" t="s">
         <v>5</v>
@@ -8685,13 +8702,13 @@
         <v>7</v>
       </c>
       <c r="H161" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="I161" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="J161" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="K161">
         <v>199950</v>
@@ -8711,10 +8728,10 @@
         <v>161</v>
       </c>
       <c r="B162" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C162" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D162" t="s">
         <v>5</v>
@@ -8726,13 +8743,13 @@
         <v>7</v>
       </c>
       <c r="H162" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="I162" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="J162" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="K162">
         <v>108000</v>
@@ -8752,10 +8769,10 @@
         <v>162</v>
       </c>
       <c r="B163" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C163" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D163" t="s">
         <v>5</v>
@@ -8767,13 +8784,13 @@
         <v>7</v>
       </c>
       <c r="H163" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="I163" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="J163" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="K163">
         <v>142808</v>
@@ -8793,10 +8810,10 @@
         <v>163</v>
       </c>
       <c r="B164" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C164" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D164" t="s">
         <v>5</v>
@@ -8808,13 +8825,13 @@
         <v>7</v>
       </c>
       <c r="H164" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="I164" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="J164" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="K164">
         <v>80463</v>
@@ -8834,10 +8851,10 @@
         <v>164</v>
       </c>
       <c r="B165" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C165" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D165" t="s">
         <v>5</v>
@@ -8849,13 +8866,13 @@
         <v>7</v>
       </c>
       <c r="H165" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="I165" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="J165" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K165">
         <v>83000</v>
@@ -8875,10 +8892,10 @@
         <v>165</v>
       </c>
       <c r="B166" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C166" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D166" t="s">
         <v>5</v>
@@ -8887,13 +8904,13 @@
         <v>7</v>
       </c>
       <c r="H166" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="I166" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="J166" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K166">
         <v>129000</v>
@@ -8913,10 +8930,10 @@
         <v>166</v>
       </c>
       <c r="B167" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C167" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D167" t="s">
         <v>5</v>
@@ -8931,10 +8948,10 @@
         <v>117</v>
       </c>
       <c r="I167" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="J167" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K167">
         <v>62209</v>
@@ -8954,16 +8971,16 @@
         <v>167</v>
       </c>
       <c r="B168" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C168" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D168" t="s">
         <v>5</v>
       </c>
       <c r="F168" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="G168" t="s">
         <v>7</v>
@@ -8972,10 +8989,10 @@
         <v>8</v>
       </c>
       <c r="I168" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="J168" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="K168">
         <v>36117</v>
@@ -8995,10 +9012,10 @@
         <v>168</v>
       </c>
       <c r="B169" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C169" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D169" t="s">
         <v>5</v>
@@ -9016,10 +9033,10 @@
         <v>87</v>
       </c>
       <c r="I169" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="J169" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="K169">
         <v>49900</v>
@@ -9039,10 +9056,10 @@
         <v>169</v>
       </c>
       <c r="B170" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C170" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D170" t="s">
         <v>5</v>
@@ -9051,7 +9068,7 @@
         <v>16</v>
       </c>
       <c r="F170" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="G170" t="s">
         <v>7</v>
@@ -9060,10 +9077,10 @@
         <v>87</v>
       </c>
       <c r="I170" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="J170" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="K170">
         <v>39000</v>
@@ -9083,16 +9100,16 @@
         <v>170</v>
       </c>
       <c r="B171" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C171" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D171" t="s">
         <v>5</v>
       </c>
       <c r="F171" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="G171" t="s">
         <v>7</v>
@@ -9101,10 +9118,10 @@
         <v>205</v>
       </c>
       <c r="I171" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="J171" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="K171">
         <v>49000</v>
@@ -9124,10 +9141,10 @@
         <v>171</v>
       </c>
       <c r="B172" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C172" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D172" t="s">
         <v>207</v>
@@ -9139,10 +9156,10 @@
         <v>8</v>
       </c>
       <c r="I172" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="J172" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="K172">
         <v>59400</v>
@@ -9162,10 +9179,10 @@
         <v>172</v>
       </c>
       <c r="B173" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C173" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D173" t="s">
         <v>5</v>
@@ -9180,10 +9197,10 @@
         <v>8</v>
       </c>
       <c r="I173" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="J173" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="K173">
         <v>65000</v>
@@ -9203,31 +9220,31 @@
         <v>173</v>
       </c>
       <c r="B174" t="s">
+        <v>409</v>
+      </c>
+      <c r="C174" t="s">
+        <v>394</v>
+      </c>
+      <c r="D174" t="s">
+        <v>5</v>
+      </c>
+      <c r="E174" t="s">
         <v>411</v>
       </c>
-      <c r="C174" t="s">
-        <v>396</v>
-      </c>
-      <c r="D174" t="s">
-        <v>5</v>
-      </c>
-      <c r="E174" t="s">
+      <c r="F174" t="s">
+        <v>410</v>
+      </c>
+      <c r="G174" t="s">
+        <v>7</v>
+      </c>
+      <c r="H174" t="s">
+        <v>412</v>
+      </c>
+      <c r="I174" t="s">
         <v>413</v>
       </c>
-      <c r="F174" t="s">
-        <v>412</v>
-      </c>
-      <c r="G174" t="s">
-        <v>7</v>
-      </c>
-      <c r="H174" t="s">
-        <v>414</v>
-      </c>
-      <c r="I174" t="s">
-        <v>415</v>
-      </c>
       <c r="J174" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K174">
         <v>47000</v>
@@ -9247,28 +9264,28 @@
         <v>174</v>
       </c>
       <c r="B175" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C175" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D175" t="s">
         <v>5</v>
       </c>
       <c r="E175" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="G175" t="s">
         <v>7</v>
       </c>
       <c r="H175" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="I175" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="J175" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K175">
         <v>29000</v>
@@ -9288,10 +9305,10 @@
         <v>175</v>
       </c>
       <c r="B176" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C176" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D176" t="s">
         <v>5</v>
@@ -9309,10 +9326,10 @@
         <v>87</v>
       </c>
       <c r="I176" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="J176" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K176">
         <v>132239</v>
@@ -9332,10 +9349,10 @@
         <v>176</v>
       </c>
       <c r="B177" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C177" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D177" t="s">
         <v>5</v>
@@ -9347,13 +9364,13 @@
         <v>7</v>
       </c>
       <c r="H177" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="I177" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="J177" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K177">
         <v>35016</v>
@@ -9373,10 +9390,10 @@
         <v>177</v>
       </c>
       <c r="B178" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C178" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D178" t="s">
         <v>5</v>
@@ -9388,10 +9405,10 @@
         <v>87</v>
       </c>
       <c r="I178" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="J178" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K178">
         <v>60000</v>
@@ -9411,28 +9428,28 @@
         <v>178</v>
       </c>
       <c r="B179" t="s">
+        <v>422</v>
+      </c>
+      <c r="C179" t="s">
+        <v>394</v>
+      </c>
+      <c r="D179" t="s">
+        <v>5</v>
+      </c>
+      <c r="F179" t="s">
+        <v>423</v>
+      </c>
+      <c r="G179" t="s">
+        <v>7</v>
+      </c>
+      <c r="H179" t="s">
+        <v>367</v>
+      </c>
+      <c r="I179" t="s">
         <v>424</v>
       </c>
-      <c r="C179" t="s">
-        <v>396</v>
-      </c>
-      <c r="D179" t="s">
-        <v>5</v>
-      </c>
-      <c r="F179" t="s">
-        <v>425</v>
-      </c>
-      <c r="G179" t="s">
-        <v>7</v>
-      </c>
-      <c r="H179" t="s">
-        <v>369</v>
-      </c>
-      <c r="I179" t="s">
-        <v>426</v>
-      </c>
       <c r="J179" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="K179">
         <v>90244</v>
@@ -9452,10 +9469,10 @@
         <v>179</v>
       </c>
       <c r="B180" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C180" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D180" t="s">
         <v>5</v>
@@ -9464,13 +9481,13 @@
         <v>7</v>
       </c>
       <c r="H180" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="I180" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="J180" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K180">
         <v>38700</v>
@@ -9490,10 +9507,10 @@
         <v>180</v>
       </c>
       <c r="B181" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C181" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D181" t="s">
         <v>5</v>
@@ -9502,13 +9519,13 @@
         <v>7</v>
       </c>
       <c r="H181" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="I181" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="J181" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="K181">
         <v>62414</v>
@@ -9528,10 +9545,10 @@
         <v>181</v>
       </c>
       <c r="B182" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C182" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D182" t="s">
         <v>5</v>
@@ -9540,13 +9557,13 @@
         <v>7</v>
       </c>
       <c r="H182" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="I182" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="J182" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K182">
         <v>51000</v>
@@ -9566,10 +9583,10 @@
         <v>182</v>
       </c>
       <c r="B183" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C183" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D183" t="s">
         <v>5</v>
@@ -9584,10 +9601,10 @@
         <v>87</v>
       </c>
       <c r="I183" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="J183" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K183">
         <v>53115</v>
@@ -9607,10 +9624,10 @@
         <v>183</v>
       </c>
       <c r="B184" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C184" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D184" t="s">
         <v>5</v>
@@ -9619,13 +9636,13 @@
         <v>7</v>
       </c>
       <c r="H184" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="I184" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="J184" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K184">
         <v>120000</v>
@@ -9645,10 +9662,10 @@
         <v>184</v>
       </c>
       <c r="B185" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C185" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D185" t="s">
         <v>5</v>
@@ -9663,10 +9680,10 @@
         <v>87</v>
       </c>
       <c r="I185" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="J185" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K185">
         <v>66477</v>
@@ -9686,10 +9703,10 @@
         <v>185</v>
       </c>
       <c r="B186" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C186" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="D186" t="s">
         <v>5</v>
@@ -9701,10 +9718,10 @@
         <v>7</v>
       </c>
       <c r="H186" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="I186" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="K186">
         <v>59300</v>
@@ -9724,10 +9741,10 @@
         <v>186</v>
       </c>
       <c r="B187" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C187" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="D187" t="s">
         <v>5</v>
@@ -9736,10 +9753,10 @@
         <v>7</v>
       </c>
       <c r="H187" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="I187" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="K187">
         <v>44000</v>
@@ -9759,10 +9776,10 @@
         <v>187</v>
       </c>
       <c r="B188" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C188" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="D188" t="s">
         <v>5</v>
@@ -9771,10 +9788,10 @@
         <v>7</v>
       </c>
       <c r="H188" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="I188" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="K188">
         <v>26528</v>
@@ -9794,10 +9811,10 @@
         <v>188</v>
       </c>
       <c r="B189" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C189" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="D189" t="s">
         <v>5</v>
@@ -9809,10 +9826,10 @@
         <v>7</v>
       </c>
       <c r="H189" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="I189" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="K189">
         <v>95684</v>
@@ -9832,10 +9849,10 @@
         <v>189</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="C190" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="D190" t="s">
         <v>5</v>
@@ -9847,7 +9864,7 @@
         <v>87</v>
       </c>
       <c r="I190" s="4" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="K190">
         <v>26737</v>
@@ -9867,10 +9884,10 @@
         <v>190</v>
       </c>
       <c r="B191" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C191" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="D191" t="s">
         <v>5</v>
@@ -9882,10 +9899,10 @@
         <v>7</v>
       </c>
       <c r="H191" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="I191" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="K191">
         <v>60000</v>
@@ -9905,10 +9922,10 @@
         <v>191</v>
       </c>
       <c r="B192" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C192" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="D192" t="s">
         <v>5</v>
@@ -9917,10 +9934,10 @@
         <v>7</v>
       </c>
       <c r="H192" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="I192" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="K192">
         <v>34895</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yuhang/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC039BB0-4061-154B-A967-F8D996A5E570}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10339ACE-865F-6743-A3AB-CDF5EB068284}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-7900" yWindow="-28200" windowWidth="25620" windowHeight="28200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1546,7 +1546,7 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>116.329228,39.958832</t>
+    <t>116.351517,39.984524</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yuhang/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10339ACE-865F-6743-A3AB-CDF5EB068284}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F9B27D5-6039-4A4A-9880-AA81EBAD86C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-7900" yWindow="-28200" windowWidth="25620" windowHeight="28200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1546,7 +1546,7 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>116.351517,39.984524</t>
+    <t>116.324067,39.957634</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yuhang/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F9B27D5-6039-4A4A-9880-AA81EBAD86C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F1B8D6E-FF4B-D14D-AF9B-CCE8F54CB829}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-7900" yWindow="-28200" windowWidth="25620" windowHeight="28200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1581" uniqueCount="496">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1580" uniqueCount="503">
   <si>
     <t>所在市</t>
   </si>
@@ -308,9 +308,6 @@
     <t>2019 Q3</t>
   </si>
   <si>
-    <t>116.439750,39.909582</t>
-  </si>
-  <si>
     <t>正大中心</t>
   </si>
   <si>
@@ -338,9 +335,6 @@
     <t>三星大厦 （中区+低区）</t>
   </si>
   <si>
-    <t>116.464736,39.912160</t>
-  </si>
-  <si>
     <t>三星大厦（高区 CBD管委会）</t>
   </si>
   <si>
@@ -437,15 +431,9 @@
     <t>116.432560,39.937841</t>
   </si>
   <si>
-    <t>国华投资大厦</t>
-  </si>
-  <si>
     <t>2007 Q?</t>
   </si>
   <si>
-    <t>116.432428,39.939081</t>
-  </si>
-  <si>
     <t>五矿广场</t>
   </si>
   <si>
@@ -521,9 +509,6 @@
     <t>兆泰国际中心二期</t>
   </si>
   <si>
-    <t>116.436279,39.919463</t>
-  </si>
-  <si>
     <t>泓晟国际中心</t>
   </si>
   <si>
@@ -545,9 +530,6 @@
     <t>2000 Q1</t>
   </si>
   <si>
-    <t>116.359889,39.906132</t>
-  </si>
-  <si>
     <t>英蓝国际金融中心</t>
   </si>
   <si>
@@ -728,9 +710,6 @@
     <t>润世中心</t>
   </si>
   <si>
-    <t>116.470255,39.955100</t>
-  </si>
-  <si>
     <t>亮马桥外交办公大楼</t>
   </si>
   <si>
@@ -770,9 +749,6 @@
     <t>2015 Q?</t>
   </si>
   <si>
-    <t>116.454766,39.919709</t>
-  </si>
-  <si>
     <t>骏豪中央公园A1</t>
   </si>
   <si>
@@ -1319,9 +1295,6 @@
     <t>有研科技创新中心</t>
   </si>
   <si>
-    <t>116.301791,39.821288</t>
-  </si>
-  <si>
     <t>翔鹰大厦</t>
   </si>
   <si>
@@ -1341,9 +1314,6 @@
   </si>
   <si>
     <t>中海金融中心T1&amp;T4</t>
-  </si>
-  <si>
-    <t>116.374843,39.887276</t>
   </si>
   <si>
     <t>远洋乐堤港二座</t>
@@ -1546,8 +1516,73 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>116.324067,39.957634</t>
+    <t>116.323984,39.958472</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>116.377078,39.888674</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>116.371113,39.967322</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>116.470221,39.955076</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>116.459281,39.960483</t>
+  </si>
+  <si>
+    <t>116.458823,39.932631</t>
+  </si>
+  <si>
+    <t>CBD</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>北京市</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>IFC国际财源中心</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>116.452709,39.907549</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>116.43926,39.909474</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>116.435881,39.919317</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>116.429644,39.906833</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>116.491439,39.914113</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>华贸中心一座</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>华贸中心二座</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>116.464627,39.912332</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>116.464467,39.912049</t>
   </si>
 </sst>
 </file>
@@ -1948,7 +1983,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B280671-4AFA-4641-88D4-A51F39483890}">
-  <dimension ref="A1:P192"/>
+  <dimension ref="A1:P194"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="5.6640625" bestFit="1" customWidth="1"/>
@@ -1968,22 +2003,22 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" t="s">
+        <v>446</v>
+      </c>
+      <c r="B1" t="s">
+        <v>448</v>
+      </c>
+      <c r="C1" t="s">
+        <v>449</v>
+      </c>
+      <c r="D1" t="s">
+        <v>450</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="B1" t="s">
-        <v>458</v>
-      </c>
-      <c r="C1" t="s">
-        <v>459</v>
-      </c>
-      <c r="D1" t="s">
-        <v>460</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>466</v>
-      </c>
       <c r="F1" t="s">
-        <v>461</v>
+        <v>451</v>
       </c>
       <c r="G1" t="s">
         <v>0</v>
@@ -1995,19 +2030,19 @@
         <v>2</v>
       </c>
       <c r="J1" t="s">
-        <v>462</v>
+        <v>452</v>
       </c>
       <c r="K1" t="s">
-        <v>457</v>
+        <v>447</v>
       </c>
       <c r="L1" t="s">
-        <v>463</v>
+        <v>453</v>
       </c>
       <c r="M1" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="N1" t="s">
-        <v>465</v>
+        <v>455</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -2036,7 +2071,7 @@
         <v>9</v>
       </c>
       <c r="J2" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="K2">
         <v>72308</v>
@@ -2077,7 +2112,7 @@
         <v>12</v>
       </c>
       <c r="J3" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="K3">
         <v>72308</v>
@@ -2121,7 +2156,7 @@
         <v>17</v>
       </c>
       <c r="J4" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="K4">
         <v>130769</v>
@@ -2165,7 +2200,7 @@
         <v>20</v>
       </c>
       <c r="J5" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="K5">
         <v>64615</v>
@@ -2209,7 +2244,7 @@
         <v>24</v>
       </c>
       <c r="J6" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="K6">
         <v>80091</v>
@@ -2250,7 +2285,7 @@
         <v>27</v>
       </c>
       <c r="J7" t="s">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="K7">
         <v>70673</v>
@@ -2294,7 +2329,7 @@
         <v>30</v>
       </c>
       <c r="J8" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="K8">
         <v>90466</v>
@@ -2335,7 +2370,7 @@
         <v>32</v>
       </c>
       <c r="J9" t="s">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="K9">
         <v>46720</v>
@@ -2379,7 +2414,7 @@
         <v>35</v>
       </c>
       <c r="J10" t="s">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="K10">
         <v>95000</v>
@@ -2423,7 +2458,7 @@
         <v>38</v>
       </c>
       <c r="J11" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="K11">
         <v>85300</v>
@@ -2467,7 +2502,7 @@
         <v>41</v>
       </c>
       <c r="J12" t="s">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="K12">
         <v>33305</v>
@@ -2511,7 +2546,7 @@
         <v>43</v>
       </c>
       <c r="J13" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="K13">
         <v>120245.21</v>
@@ -2555,7 +2590,7 @@
         <v>43</v>
       </c>
       <c r="J14" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="K14">
         <v>70425.53</v>
@@ -2599,7 +2634,7 @@
         <v>47</v>
       </c>
       <c r="J15" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="K15">
         <v>78000</v>
@@ -2643,7 +2678,7 @@
         <v>50</v>
       </c>
       <c r="J16" t="s">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="K16">
         <v>102796</v>
@@ -2687,7 +2722,7 @@
         <v>52</v>
       </c>
       <c r="J17" t="s">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="K17">
         <v>49200</v>
@@ -2731,7 +2766,7 @@
         <v>54</v>
       </c>
       <c r="J18" t="s">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="K18">
         <v>65096</v>
@@ -2775,7 +2810,7 @@
         <v>57</v>
       </c>
       <c r="J19" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="K19">
         <v>56000</v>
@@ -2819,7 +2854,7 @@
         <v>60</v>
       </c>
       <c r="J20" t="s">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="K20">
         <v>177847</v>
@@ -2863,7 +2898,7 @@
         <v>63</v>
       </c>
       <c r="J21" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="K21">
         <v>83000</v>
@@ -2904,7 +2939,7 @@
         <v>66</v>
       </c>
       <c r="J22" t="s">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="K22">
         <v>26000</v>
@@ -2945,7 +2980,7 @@
         <v>68</v>
       </c>
       <c r="J23" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="K23">
         <v>85887</v>
@@ -2986,7 +3021,7 @@
         <v>70</v>
       </c>
       <c r="J24" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="K24">
         <v>20000</v>
@@ -3030,7 +3065,7 @@
         <v>73</v>
       </c>
       <c r="J25" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="K25">
         <v>146385</v>
@@ -3074,7 +3109,7 @@
         <v>76</v>
       </c>
       <c r="J26" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="K26">
         <v>87000</v>
@@ -3118,7 +3153,7 @@
         <v>79</v>
       </c>
       <c r="J27" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="K27">
         <v>147166.79999999999</v>
@@ -3162,7 +3197,7 @@
         <v>82</v>
       </c>
       <c r="J28" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="K28">
         <v>46063</v>
@@ -3206,7 +3241,7 @@
         <v>85</v>
       </c>
       <c r="J29" t="s">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="K29">
         <v>47261</v>
@@ -3226,7 +3261,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>472</v>
+        <v>462</v>
       </c>
       <c r="C30" t="s">
         <v>4</v>
@@ -3244,13 +3279,13 @@
         <v>7</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>471</v>
+        <v>461</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>473</v>
+        <v>463</v>
       </c>
       <c r="J30" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="K30">
         <v>119000</v>
@@ -3287,11 +3322,11 @@
       <c r="H31" t="s">
         <v>8</v>
       </c>
-      <c r="I31" t="s">
-        <v>91</v>
+      <c r="I31" s="1" t="s">
+        <v>495</v>
       </c>
       <c r="J31" t="s">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="K31">
         <v>47000</v>
@@ -3311,7 +3346,7 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C32" t="s">
         <v>4</v>
@@ -3332,10 +3367,10 @@
         <v>8</v>
       </c>
       <c r="I32" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J32" t="s">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="K32">
         <v>186000</v>
@@ -3355,7 +3390,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C33" t="s">
         <v>4</v>
@@ -3370,10 +3405,10 @@
         <v>8</v>
       </c>
       <c r="I33" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="J33" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="K33">
         <v>40800</v>
@@ -3393,7 +3428,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C34" t="s">
         <v>4</v>
@@ -3402,7 +3437,7 @@
         <v>5</v>
       </c>
       <c r="F34" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G34" t="s">
         <v>7</v>
@@ -3411,10 +3446,10 @@
         <v>8</v>
       </c>
       <c r="I34" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="J34" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="K34">
         <v>55200</v>
@@ -3434,7 +3469,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C35" t="s">
         <v>4</v>
@@ -3446,7 +3481,7 @@
         <v>16</v>
       </c>
       <c r="F35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G35" t="s">
         <v>7</v>
@@ -3455,10 +3490,10 @@
         <v>8</v>
       </c>
       <c r="I35" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="J35" t="s">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="K35">
         <v>350000</v>
@@ -3478,7 +3513,7 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C36" t="s">
         <v>4</v>
@@ -3495,11 +3530,11 @@
       <c r="H36" t="s">
         <v>8</v>
       </c>
-      <c r="I36" t="s">
-        <v>101</v>
+      <c r="I36" s="1" t="s">
+        <v>501</v>
       </c>
       <c r="J36" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="K36">
         <v>65000</v>
@@ -3519,7 +3554,7 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C37" t="s">
         <v>4</v>
@@ -3537,10 +3572,10 @@
         <v>8</v>
       </c>
       <c r="I37" t="s">
-        <v>101</v>
+        <v>502</v>
       </c>
       <c r="J37" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="K37">
         <v>35000</v>
@@ -3560,7 +3595,7 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C38" t="s">
         <v>4</v>
@@ -3578,10 +3613,10 @@
         <v>8</v>
       </c>
       <c r="I38" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="J38" t="s">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="K38">
         <v>47000</v>
@@ -3601,7 +3636,7 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C39" t="s">
         <v>4</v>
@@ -3613,7 +3648,7 @@
         <v>23</v>
       </c>
       <c r="F39" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G39" t="s">
         <v>7</v>
@@ -3622,10 +3657,10 @@
         <v>8</v>
       </c>
       <c r="I39" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="J39" t="s">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="K39">
         <v>120000</v>
@@ -3645,7 +3680,7 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C40" t="s">
         <v>4</v>
@@ -3663,10 +3698,10 @@
         <v>8</v>
       </c>
       <c r="I40" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="J40" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="K40">
         <v>83000</v>
@@ -3686,7 +3721,7 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C41" t="s">
         <v>4</v>
@@ -3704,10 +3739,10 @@
         <v>8</v>
       </c>
       <c r="I41" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="J41" t="s">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="K41">
         <v>66030</v>
@@ -3727,7 +3762,7 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C42" t="s">
         <v>4</v>
@@ -3742,10 +3777,10 @@
         <v>8</v>
       </c>
       <c r="I42" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="J42" t="s">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="K42">
         <v>40000</v>
@@ -3765,10 +3800,10 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C43" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D43" t="s">
         <v>5</v>
@@ -3777,19 +3812,19 @@
         <v>16</v>
       </c>
       <c r="F43" t="s">
+        <v>114</v>
+      </c>
+      <c r="G43" t="s">
+        <v>7</v>
+      </c>
+      <c r="H43" t="s">
+        <v>115</v>
+      </c>
+      <c r="I43" t="s">
         <v>116</v>
       </c>
-      <c r="G43" t="s">
-        <v>7</v>
-      </c>
-      <c r="H43" t="s">
-        <v>117</v>
-      </c>
-      <c r="I43" t="s">
-        <v>118</v>
-      </c>
       <c r="J43" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="K43">
         <v>40000</v>
@@ -3809,28 +3844,28 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
+        <v>117</v>
+      </c>
+      <c r="C44" t="s">
+        <v>113</v>
+      </c>
+      <c r="D44" t="s">
+        <v>5</v>
+      </c>
+      <c r="F44" t="s">
+        <v>118</v>
+      </c>
+      <c r="G44" t="s">
+        <v>7</v>
+      </c>
+      <c r="H44" t="s">
+        <v>115</v>
+      </c>
+      <c r="I44" t="s">
         <v>119</v>
       </c>
-      <c r="C44" t="s">
-        <v>115</v>
-      </c>
-      <c r="D44" t="s">
-        <v>5</v>
-      </c>
-      <c r="F44" t="s">
-        <v>120</v>
-      </c>
-      <c r="G44" t="s">
-        <v>7</v>
-      </c>
-      <c r="H44" t="s">
-        <v>117</v>
-      </c>
-      <c r="I44" t="s">
-        <v>121</v>
-      </c>
       <c r="J44" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="K44">
         <v>54100</v>
@@ -3850,10 +3885,10 @@
         <v>44</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C45" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D45" t="s">
         <v>5</v>
@@ -3862,19 +3897,19 @@
         <v>23</v>
       </c>
       <c r="F45" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G45" t="s">
         <v>7</v>
       </c>
       <c r="H45" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>477</v>
+        <v>467</v>
       </c>
       <c r="J45" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="K45">
         <v>100000</v>
@@ -3894,10 +3929,10 @@
         <v>45</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C46" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D46" t="s">
         <v>5</v>
@@ -3906,19 +3941,19 @@
         <v>23</v>
       </c>
       <c r="F46" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="G46" t="s">
         <v>7</v>
       </c>
       <c r="H46" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>476</v>
+        <v>466</v>
       </c>
       <c r="J46" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="K46">
         <v>150000</v>
@@ -3938,10 +3973,10 @@
         <v>46</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C47" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D47" t="s">
         <v>5</v>
@@ -3950,19 +3985,19 @@
         <v>23</v>
       </c>
       <c r="F47" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G47" t="s">
         <v>7</v>
       </c>
       <c r="H47" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="J47" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="K47">
         <v>50000</v>
@@ -3982,10 +4017,10 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C48" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D48" t="s">
         <v>5</v>
@@ -3994,19 +4029,19 @@
         <v>23</v>
       </c>
       <c r="F48" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G48" t="s">
         <v>7</v>
       </c>
       <c r="H48" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I48" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="J48" t="s">
-        <v>468</v>
+        <v>458</v>
       </c>
       <c r="K48">
         <v>43000</v>
@@ -4026,28 +4061,28 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
+        <v>129</v>
+      </c>
+      <c r="C49" t="s">
+        <v>113</v>
+      </c>
+      <c r="D49" t="s">
+        <v>5</v>
+      </c>
+      <c r="F49" t="s">
+        <v>130</v>
+      </c>
+      <c r="G49" t="s">
+        <v>7</v>
+      </c>
+      <c r="H49" t="s">
+        <v>115</v>
+      </c>
+      <c r="I49" t="s">
         <v>131</v>
       </c>
-      <c r="C49" t="s">
-        <v>115</v>
-      </c>
-      <c r="D49" t="s">
-        <v>5</v>
-      </c>
-      <c r="F49" t="s">
-        <v>132</v>
-      </c>
-      <c r="G49" t="s">
-        <v>7</v>
-      </c>
-      <c r="H49" t="s">
-        <v>117</v>
-      </c>
-      <c r="I49" t="s">
-        <v>133</v>
-      </c>
       <c r="J49" t="s">
-        <v>468</v>
+        <v>458</v>
       </c>
       <c r="K49">
         <v>65000</v>
@@ -4067,28 +4102,43 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
+        <v>133</v>
+      </c>
+      <c r="C50" t="s">
+        <v>113</v>
+      </c>
+      <c r="D50" t="s">
+        <v>5</v>
+      </c>
+      <c r="E50" t="s">
+        <v>23</v>
+      </c>
+      <c r="F50" t="s">
+        <v>45</v>
+      </c>
+      <c r="G50" t="s">
+        <v>7</v>
+      </c>
+      <c r="H50" t="s">
+        <v>115</v>
+      </c>
+      <c r="I50" t="s">
         <v>134</v>
       </c>
-      <c r="C50" t="s">
-        <v>115</v>
-      </c>
-      <c r="D50" t="s">
-        <v>5</v>
-      </c>
-      <c r="F50" t="s">
-        <v>135</v>
-      </c>
-      <c r="G50" t="s">
-        <v>7</v>
-      </c>
-      <c r="H50" t="s">
-        <v>117</v>
-      </c>
-      <c r="I50" t="s">
-        <v>136</v>
-      </c>
       <c r="J50" t="s">
-        <v>468</v>
+        <v>458</v>
+      </c>
+      <c r="K50">
+        <v>56000</v>
+      </c>
+      <c r="L50">
+        <v>311.66666666666703</v>
+      </c>
+      <c r="M50">
+        <v>0</v>
+      </c>
+      <c r="N50">
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:14">
@@ -4096,43 +4146,40 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C51" t="s">
+        <v>113</v>
+      </c>
+      <c r="D51" t="s">
+        <v>5</v>
+      </c>
+      <c r="F51" t="s">
+        <v>59</v>
+      </c>
+      <c r="G51" t="s">
+        <v>7</v>
+      </c>
+      <c r="H51" t="s">
         <v>115</v>
       </c>
-      <c r="D51" t="s">
-        <v>5</v>
-      </c>
-      <c r="E51" t="s">
-        <v>23</v>
-      </c>
-      <c r="F51" t="s">
-        <v>45</v>
-      </c>
-      <c r="G51" t="s">
-        <v>7</v>
-      </c>
-      <c r="H51" t="s">
-        <v>117</v>
-      </c>
       <c r="I51" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J51" t="s">
-        <v>468</v>
+        <v>458</v>
       </c>
       <c r="K51">
-        <v>56000</v>
+        <v>160000</v>
       </c>
       <c r="L51">
-        <v>311.66666666666703</v>
+        <v>198.055555555555</v>
       </c>
       <c r="M51">
-        <v>0</v>
+        <v>0.48831249999999998</v>
       </c>
       <c r="N51">
-        <v>0</v>
+        <v>78130</v>
       </c>
     </row>
     <row r="52" spans="1:14">
@@ -4140,40 +4187,40 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C52" t="s">
+        <v>113</v>
+      </c>
+      <c r="D52" t="s">
+        <v>5</v>
+      </c>
+      <c r="F52" t="s">
+        <v>4</v>
+      </c>
+      <c r="G52" t="s">
+        <v>7</v>
+      </c>
+      <c r="H52" t="s">
         <v>115</v>
       </c>
-      <c r="D52" t="s">
-        <v>5</v>
-      </c>
-      <c r="F52" t="s">
-        <v>59</v>
-      </c>
-      <c r="G52" t="s">
-        <v>7</v>
-      </c>
-      <c r="H52" t="s">
-        <v>117</v>
-      </c>
       <c r="I52" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="J52" t="s">
-        <v>468</v>
+        <v>458</v>
       </c>
       <c r="K52">
-        <v>160000</v>
+        <v>33000</v>
       </c>
       <c r="L52">
-        <v>198.055555555555</v>
+        <v>175</v>
       </c>
       <c r="M52">
-        <v>0.48831249999999998</v>
+        <v>0.42424242424242398</v>
       </c>
       <c r="N52">
-        <v>78130</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="53" spans="1:14">
@@ -4181,40 +4228,43 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
+        <v>139</v>
+      </c>
+      <c r="C53" t="s">
+        <v>113</v>
+      </c>
+      <c r="D53" t="s">
+        <v>5</v>
+      </c>
+      <c r="E53" t="s">
+        <v>16</v>
+      </c>
+      <c r="F53" t="s">
+        <v>140</v>
+      </c>
+      <c r="G53" t="s">
+        <v>7</v>
+      </c>
+      <c r="H53" t="s">
+        <v>115</v>
+      </c>
+      <c r="I53" t="s">
         <v>141</v>
       </c>
-      <c r="C53" t="s">
-        <v>115</v>
-      </c>
-      <c r="D53" t="s">
-        <v>5</v>
-      </c>
-      <c r="F53" t="s">
-        <v>4</v>
-      </c>
-      <c r="G53" t="s">
-        <v>7</v>
-      </c>
-      <c r="H53" t="s">
-        <v>117</v>
-      </c>
-      <c r="I53" t="s">
-        <v>142</v>
-      </c>
       <c r="J53" t="s">
-        <v>468</v>
+        <v>458</v>
       </c>
       <c r="K53">
-        <v>33000</v>
+        <v>41318</v>
       </c>
       <c r="L53">
-        <v>175</v>
+        <v>186.666666666667</v>
       </c>
       <c r="M53">
-        <v>0.42424242424242398</v>
+        <v>0.148885715668716</v>
       </c>
       <c r="N53">
-        <v>14000</v>
+        <v>6151.66</v>
       </c>
     </row>
     <row r="54" spans="1:14">
@@ -4222,43 +4272,40 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
+        <v>142</v>
+      </c>
+      <c r="C54" t="s">
+        <v>113</v>
+      </c>
+      <c r="D54" t="s">
+        <v>5</v>
+      </c>
+      <c r="F54" t="s">
+        <v>132</v>
+      </c>
+      <c r="G54" t="s">
+        <v>7</v>
+      </c>
+      <c r="H54" t="s">
+        <v>115</v>
+      </c>
+      <c r="I54" t="s">
         <v>143</v>
       </c>
-      <c r="C54" t="s">
-        <v>115</v>
-      </c>
-      <c r="D54" t="s">
-        <v>5</v>
-      </c>
-      <c r="E54" t="s">
-        <v>16</v>
-      </c>
-      <c r="F54" t="s">
-        <v>144</v>
-      </c>
-      <c r="G54" t="s">
-        <v>7</v>
-      </c>
-      <c r="H54" t="s">
-        <v>117</v>
-      </c>
-      <c r="I54" t="s">
-        <v>145</v>
-      </c>
       <c r="J54" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="K54">
-        <v>41318</v>
+        <v>34131</v>
       </c>
       <c r="L54">
-        <v>186.666666666667</v>
+        <v>175</v>
       </c>
       <c r="M54">
-        <v>0.148885715668716</v>
+        <v>0.61237584600509798</v>
       </c>
       <c r="N54">
-        <v>6151.66</v>
+        <v>20901</v>
       </c>
     </row>
     <row r="55" spans="1:14">
@@ -4266,40 +4313,40 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
+        <v>144</v>
+      </c>
+      <c r="C55" t="s">
+        <v>113</v>
+      </c>
+      <c r="D55" t="s">
+        <v>5</v>
+      </c>
+      <c r="F55" t="s">
+        <v>145</v>
+      </c>
+      <c r="G55" t="s">
+        <v>7</v>
+      </c>
+      <c r="H55" t="s">
+        <v>115</v>
+      </c>
+      <c r="I55" t="s">
         <v>146</v>
       </c>
-      <c r="C55" t="s">
-        <v>115</v>
-      </c>
-      <c r="D55" t="s">
-        <v>5</v>
-      </c>
-      <c r="F55" t="s">
-        <v>135</v>
-      </c>
-      <c r="G55" t="s">
-        <v>7</v>
-      </c>
-      <c r="H55" t="s">
-        <v>117</v>
-      </c>
-      <c r="I55" t="s">
-        <v>147</v>
-      </c>
       <c r="J55" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="K55">
-        <v>34131</v>
+        <v>48000</v>
       </c>
       <c r="L55">
         <v>175</v>
       </c>
       <c r="M55">
-        <v>0.61237584600509798</v>
+        <v>0.26214583333333302</v>
       </c>
       <c r="N55">
-        <v>20901</v>
+        <v>12583</v>
       </c>
     </row>
     <row r="56" spans="1:14">
@@ -4307,40 +4354,40 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C56" t="s">
+        <v>113</v>
+      </c>
+      <c r="D56" t="s">
+        <v>5</v>
+      </c>
+      <c r="F56">
+        <v>2017</v>
+      </c>
+      <c r="G56" t="s">
+        <v>7</v>
+      </c>
+      <c r="H56" t="s">
         <v>115</v>
       </c>
-      <c r="D56" t="s">
-        <v>5</v>
-      </c>
-      <c r="F56" t="s">
-        <v>149</v>
-      </c>
-      <c r="G56" t="s">
-        <v>7</v>
-      </c>
-      <c r="H56" t="s">
-        <v>117</v>
-      </c>
-      <c r="I56" t="s">
-        <v>150</v>
+      <c r="I56" s="1" t="s">
+        <v>497</v>
       </c>
       <c r="J56" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="K56">
-        <v>48000</v>
+        <v>16000</v>
       </c>
       <c r="L56">
-        <v>175</v>
+        <v>197.083333333333</v>
       </c>
       <c r="M56">
-        <v>0.26214583333333302</v>
+        <v>0.25131249999999999</v>
       </c>
       <c r="N56">
-        <v>12583</v>
+        <v>4021</v>
       </c>
     </row>
     <row r="57" spans="1:14">
@@ -4348,40 +4395,43 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C57" t="s">
+        <v>113</v>
+      </c>
+      <c r="D57" t="s">
+        <v>5</v>
+      </c>
+      <c r="E57" t="s">
+        <v>16</v>
+      </c>
+      <c r="F57" t="s">
+        <v>149</v>
+      </c>
+      <c r="G57" t="s">
+        <v>7</v>
+      </c>
+      <c r="H57" t="s">
         <v>115</v>
       </c>
-      <c r="D57" t="s">
-        <v>5</v>
-      </c>
-      <c r="F57">
-        <v>2017</v>
-      </c>
-      <c r="G57" t="s">
-        <v>7</v>
-      </c>
-      <c r="H57" t="s">
-        <v>117</v>
-      </c>
       <c r="I57" t="s">
-        <v>118</v>
+        <v>150</v>
       </c>
       <c r="J57" t="s">
-        <v>467</v>
+        <v>458</v>
       </c>
       <c r="K57">
-        <v>16000</v>
+        <v>30000</v>
       </c>
       <c r="L57">
-        <v>197.083333333333</v>
+        <v>145</v>
       </c>
       <c r="M57">
-        <v>0.25131249999999999</v>
+        <v>0.242352333333333</v>
       </c>
       <c r="N57">
-        <v>4021</v>
+        <v>7270.57</v>
       </c>
     </row>
     <row r="58" spans="1:14">
@@ -4389,10 +4439,10 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C58" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D58" t="s">
         <v>5</v>
@@ -4401,31 +4451,31 @@
         <v>16</v>
       </c>
       <c r="F58" t="s">
+        <v>152</v>
+      </c>
+      <c r="G58" t="s">
+        <v>7</v>
+      </c>
+      <c r="H58" t="s">
+        <v>115</v>
+      </c>
+      <c r="I58" t="s">
         <v>153</v>
       </c>
-      <c r="G58" t="s">
-        <v>7</v>
-      </c>
-      <c r="H58" t="s">
-        <v>117</v>
-      </c>
-      <c r="I58" t="s">
-        <v>154</v>
-      </c>
       <c r="J58" t="s">
-        <v>468</v>
+        <v>458</v>
       </c>
       <c r="K58">
-        <v>30000</v>
+        <v>56000</v>
       </c>
       <c r="L58">
         <v>145</v>
       </c>
       <c r="M58">
-        <v>0.242352333333333</v>
+        <v>0.37934464285714298</v>
       </c>
       <c r="N58">
-        <v>7270.57</v>
+        <v>21243.3</v>
       </c>
     </row>
     <row r="59" spans="1:14">
@@ -4433,10 +4483,10 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C59" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D59" t="s">
         <v>5</v>
@@ -4445,31 +4495,31 @@
         <v>16</v>
       </c>
       <c r="F59" t="s">
+        <v>155</v>
+      </c>
+      <c r="G59" t="s">
+        <v>7</v>
+      </c>
+      <c r="H59" t="s">
+        <v>115</v>
+      </c>
+      <c r="I59" t="s">
         <v>156</v>
       </c>
-      <c r="G59" t="s">
-        <v>7</v>
-      </c>
-      <c r="H59" t="s">
-        <v>117</v>
-      </c>
-      <c r="I59" t="s">
-        <v>157</v>
-      </c>
       <c r="J59" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="K59">
-        <v>56000</v>
+        <v>43000</v>
       </c>
       <c r="L59">
-        <v>145</v>
+        <v>261.25</v>
       </c>
       <c r="M59">
-        <v>0.37934464285714298</v>
+        <v>8.6837209302325594E-2</v>
       </c>
       <c r="N59">
-        <v>21243.3</v>
+        <v>3734</v>
       </c>
     </row>
     <row r="60" spans="1:14">
@@ -4477,10 +4527,10 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C60" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D60" t="s">
         <v>5</v>
@@ -4488,32 +4538,29 @@
       <c r="E60" t="s">
         <v>16</v>
       </c>
-      <c r="F60" t="s">
-        <v>159</v>
-      </c>
       <c r="G60" t="s">
         <v>7</v>
       </c>
       <c r="H60" t="s">
-        <v>117</v>
-      </c>
-      <c r="I60" t="s">
-        <v>160</v>
+        <v>8</v>
+      </c>
+      <c r="I60" s="1" t="s">
+        <v>496</v>
       </c>
       <c r="J60" t="s">
-        <v>467</v>
+        <v>458</v>
       </c>
       <c r="K60">
-        <v>43000</v>
+        <v>110000</v>
       </c>
       <c r="L60">
-        <v>261.25</v>
+        <v>240</v>
       </c>
       <c r="M60">
-        <v>8.6837209302325594E-2</v>
+        <v>2.7453545454545401E-2</v>
       </c>
       <c r="N60">
-        <v>3734</v>
+        <v>3019.89</v>
       </c>
     </row>
     <row r="61" spans="1:14">
@@ -4521,40 +4568,37 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C61" t="s">
+        <v>113</v>
+      </c>
+      <c r="D61" t="s">
+        <v>5</v>
+      </c>
+      <c r="G61" t="s">
+        <v>7</v>
+      </c>
+      <c r="H61" t="s">
         <v>115</v>
       </c>
-      <c r="D61" t="s">
-        <v>5</v>
-      </c>
-      <c r="E61" t="s">
-        <v>16</v>
-      </c>
-      <c r="G61" t="s">
-        <v>7</v>
-      </c>
-      <c r="H61" t="s">
-        <v>8</v>
-      </c>
       <c r="I61" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="J61" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="K61">
-        <v>110000</v>
+        <v>56160</v>
       </c>
       <c r="L61">
-        <v>240</v>
+        <v>266.94444444444503</v>
       </c>
       <c r="M61">
-        <v>2.7453545454545401E-2</v>
+        <v>7.4928774928774894E-2</v>
       </c>
       <c r="N61">
-        <v>3019.89</v>
+        <v>4208</v>
       </c>
     </row>
     <row r="62" spans="1:14">
@@ -4562,37 +4606,40 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C62" t="s">
+        <v>113</v>
+      </c>
+      <c r="D62" t="s">
+        <v>14</v>
+      </c>
+      <c r="E62" t="s">
+        <v>23</v>
+      </c>
+      <c r="G62" t="s">
+        <v>7</v>
+      </c>
+      <c r="H62" t="s">
         <v>115</v>
       </c>
-      <c r="D62" t="s">
-        <v>5</v>
-      </c>
-      <c r="G62" t="s">
-        <v>7</v>
-      </c>
-      <c r="H62" t="s">
-        <v>117</v>
-      </c>
       <c r="I62" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="J62" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="K62">
-        <v>56160</v>
+        <v>138444</v>
       </c>
       <c r="L62">
-        <v>266.94444444444503</v>
+        <v>297.91666666666703</v>
       </c>
       <c r="M62">
-        <v>7.4928774928774894E-2</v>
+        <v>0.42616509202276698</v>
       </c>
       <c r="N62">
-        <v>4208</v>
+        <v>59000</v>
       </c>
     </row>
     <row r="63" spans="1:14">
@@ -4600,40 +4647,43 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C63" t="s">
-        <v>115</v>
+        <v>163</v>
       </c>
       <c r="D63" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E63" t="s">
-        <v>23</v>
+        <v>16</v>
+      </c>
+      <c r="F63" t="s">
+        <v>164</v>
       </c>
       <c r="G63" t="s">
         <v>7</v>
       </c>
       <c r="H63" t="s">
-        <v>117</v>
-      </c>
-      <c r="I63" t="s">
-        <v>166</v>
+        <v>87</v>
+      </c>
+      <c r="I63" s="1" t="s">
+        <v>498</v>
       </c>
       <c r="J63" t="s">
-        <v>467</v>
+        <v>441</v>
       </c>
       <c r="K63">
-        <v>138444</v>
+        <v>31000</v>
       </c>
       <c r="L63">
-        <v>297.91666666666703</v>
+        <v>281.94444444444503</v>
       </c>
       <c r="M63">
-        <v>0.42616509202276698</v>
+        <v>0.154838709677419</v>
       </c>
       <c r="N63">
-        <v>59000</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="64" spans="1:14">
@@ -4641,19 +4691,16 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C64" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="D64" t="s">
-        <v>5</v>
-      </c>
-      <c r="E64" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F64" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="G64" t="s">
         <v>7</v>
@@ -4662,22 +4709,22 @@
         <v>87</v>
       </c>
       <c r="I64" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="J64" t="s">
-        <v>451</v>
+        <v>441</v>
       </c>
       <c r="K64">
-        <v>31000</v>
+        <v>120000</v>
       </c>
       <c r="L64">
-        <v>281.94444444444503</v>
+        <v>471.11111111111097</v>
       </c>
       <c r="M64">
-        <v>0.154838709677419</v>
+        <v>8.7499999999999994E-2</v>
       </c>
       <c r="N64">
-        <v>4800</v>
+        <v>10500</v>
       </c>
     </row>
     <row r="65" spans="1:14">
@@ -4685,16 +4732,16 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C65" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="D65" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="F65" t="s">
-        <v>172</v>
+        <v>34</v>
       </c>
       <c r="G65" t="s">
         <v>7</v>
@@ -4703,22 +4750,22 @@
         <v>87</v>
       </c>
       <c r="I65" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="J65" t="s">
-        <v>451</v>
+        <v>441</v>
       </c>
       <c r="K65">
-        <v>120000</v>
+        <v>25900</v>
       </c>
       <c r="L65">
-        <v>471.11111111111097</v>
+        <v>311.66666666666703</v>
       </c>
       <c r="M65">
-        <v>8.7499999999999994E-2</v>
+        <v>0.29289575289575298</v>
       </c>
       <c r="N65">
-        <v>10500</v>
+        <v>7586</v>
       </c>
     </row>
     <row r="66" spans="1:14">
@@ -4726,16 +4773,16 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C66" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="D66" t="s">
         <v>5</v>
       </c>
       <c r="F66" t="s">
-        <v>34</v>
+        <v>171</v>
       </c>
       <c r="G66" t="s">
         <v>7</v>
@@ -4744,22 +4791,22 @@
         <v>87</v>
       </c>
       <c r="I66" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="J66" t="s">
-        <v>451</v>
+        <v>441</v>
       </c>
       <c r="K66">
-        <v>25900</v>
+        <v>47986</v>
       </c>
       <c r="L66">
-        <v>311.66666666666703</v>
+        <v>316.66666666666703</v>
       </c>
       <c r="M66">
-        <v>0.29289575289575298</v>
+        <v>8.9609469428583305E-2</v>
       </c>
       <c r="N66">
-        <v>7586</v>
+        <v>4300</v>
       </c>
     </row>
     <row r="67" spans="1:14">
@@ -4767,16 +4814,19 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C67" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="D67" t="s">
         <v>5</v>
       </c>
+      <c r="E67" t="s">
+        <v>23</v>
+      </c>
       <c r="F67" t="s">
-        <v>177</v>
+        <v>37</v>
       </c>
       <c r="G67" t="s">
         <v>7</v>
@@ -4785,22 +4835,22 @@
         <v>87</v>
       </c>
       <c r="I67" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="J67" t="s">
-        <v>451</v>
+        <v>441</v>
       </c>
       <c r="K67">
-        <v>47986</v>
+        <v>194000</v>
       </c>
       <c r="L67">
-        <v>316.66666666666703</v>
+        <v>416.66666666666703</v>
       </c>
       <c r="M67">
-        <v>8.9609469428583305E-2</v>
+        <v>8.9783505154639204E-2</v>
       </c>
       <c r="N67">
-        <v>4300</v>
+        <v>17418</v>
       </c>
     </row>
     <row r="68" spans="1:14">
@@ -4808,19 +4858,19 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C68" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="D68" t="s">
         <v>5</v>
       </c>
       <c r="E68" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F68" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G68" t="s">
         <v>7</v>
@@ -4829,22 +4879,22 @@
         <v>87</v>
       </c>
       <c r="I68" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="J68" t="s">
-        <v>451</v>
+        <v>441</v>
       </c>
       <c r="K68">
-        <v>194000</v>
+        <v>39724</v>
       </c>
       <c r="L68">
-        <v>416.66666666666703</v>
+        <v>281.94444444444503</v>
       </c>
       <c r="M68">
-        <v>8.9783505154639204E-2</v>
+        <v>9.0625314671231499E-2</v>
       </c>
       <c r="N68">
-        <v>17418</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="69" spans="1:14">
@@ -4852,19 +4902,16 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C69" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="D69" t="s">
         <v>5</v>
       </c>
-      <c r="E69" t="s">
-        <v>16</v>
-      </c>
       <c r="F69" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="G69" t="s">
         <v>7</v>
@@ -4872,23 +4919,23 @@
       <c r="H69" t="s">
         <v>87</v>
       </c>
-      <c r="I69" t="s">
-        <v>182</v>
+      <c r="I69" s="1" t="s">
+        <v>471</v>
       </c>
       <c r="J69" t="s">
-        <v>451</v>
+        <v>441</v>
       </c>
       <c r="K69">
-        <v>39724</v>
+        <v>48437.45</v>
       </c>
       <c r="L69">
-        <v>281.94444444444503</v>
+        <v>266.66666666666703</v>
       </c>
       <c r="M69">
-        <v>9.0625314671231499E-2</v>
+        <v>7.7398789572944104E-2</v>
       </c>
       <c r="N69">
-        <v>3600</v>
+        <v>3749</v>
       </c>
     </row>
     <row r="70" spans="1:14">
@@ -4896,16 +4943,16 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="C70" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="D70" t="s">
         <v>5</v>
       </c>
       <c r="F70" t="s">
-        <v>49</v>
+        <v>179</v>
       </c>
       <c r="G70" t="s">
         <v>7</v>
@@ -4913,40 +4960,40 @@
       <c r="H70" t="s">
         <v>87</v>
       </c>
-      <c r="I70" s="1" t="s">
-        <v>481</v>
+      <c r="I70" t="s">
+        <v>180</v>
       </c>
       <c r="J70" t="s">
-        <v>451</v>
+        <v>441</v>
       </c>
       <c r="K70">
-        <v>48437.45</v>
+        <v>37910</v>
       </c>
       <c r="L70">
-        <v>266.66666666666703</v>
+        <v>275</v>
       </c>
       <c r="M70">
-        <v>7.7398789572944104E-2</v>
+        <v>6.5945660775520998E-2</v>
       </c>
       <c r="N70">
-        <v>3749</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="71" spans="1:14">
       <c r="A71">
         <v>70</v>
       </c>
-      <c r="B71" t="s">
-        <v>184</v>
+      <c r="B71" s="2" t="s">
+        <v>460</v>
       </c>
       <c r="C71" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="D71" t="s">
         <v>5</v>
       </c>
       <c r="F71" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="G71" t="s">
         <v>7</v>
@@ -4954,40 +5001,40 @@
       <c r="H71" t="s">
         <v>87</v>
       </c>
-      <c r="I71" t="s">
-        <v>186</v>
+      <c r="I71" s="2" t="s">
+        <v>464</v>
       </c>
       <c r="J71" t="s">
-        <v>451</v>
+        <v>441</v>
       </c>
       <c r="K71">
-        <v>37910</v>
+        <v>21220</v>
       </c>
       <c r="L71">
-        <v>275</v>
+        <v>513.33333333333303</v>
       </c>
       <c r="M71">
-        <v>6.5945660775520998E-2</v>
+        <v>0</v>
       </c>
       <c r="N71">
-        <v>2500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:14">
       <c r="A72">
         <v>71</v>
       </c>
-      <c r="B72" s="2" t="s">
-        <v>470</v>
+      <c r="B72" t="s">
+        <v>181</v>
       </c>
       <c r="C72" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="D72" t="s">
         <v>5</v>
       </c>
       <c r="F72" t="s">
-        <v>185</v>
+        <v>56</v>
       </c>
       <c r="G72" t="s">
         <v>7</v>
@@ -4995,23 +5042,23 @@
       <c r="H72" t="s">
         <v>87</v>
       </c>
-      <c r="I72" s="2" t="s">
-        <v>474</v>
+      <c r="I72" t="s">
+        <v>182</v>
       </c>
       <c r="J72" t="s">
-        <v>451</v>
+        <v>441</v>
       </c>
       <c r="K72">
-        <v>21220</v>
+        <v>77877</v>
       </c>
       <c r="L72">
-        <v>513.33333333333303</v>
+        <v>350</v>
       </c>
       <c r="M72">
-        <v>0</v>
+        <v>6.42038085699244E-2</v>
       </c>
       <c r="N72">
-        <v>0</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="73" spans="1:14">
@@ -5019,16 +5066,19 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C73" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="D73" t="s">
         <v>5</v>
       </c>
+      <c r="E73" t="s">
+        <v>16</v>
+      </c>
       <c r="F73" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="G73" t="s">
         <v>7</v>
@@ -5037,22 +5087,22 @@
         <v>87</v>
       </c>
       <c r="I73" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="J73" t="s">
-        <v>451</v>
+        <v>441</v>
       </c>
       <c r="K73">
-        <v>77877</v>
+        <v>80311.53</v>
       </c>
       <c r="L73">
-        <v>350</v>
+        <v>430.55555555555497</v>
       </c>
       <c r="M73">
-        <v>6.42038085699244E-2</v>
+        <v>0.110581880335239</v>
       </c>
       <c r="N73">
-        <v>5000</v>
+        <v>8881</v>
       </c>
     </row>
     <row r="74" spans="1:14">
@@ -5060,19 +5110,19 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C74" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="D74" t="s">
         <v>5</v>
       </c>
       <c r="E74" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F74" t="s">
-        <v>62</v>
+        <v>186</v>
       </c>
       <c r="G74" t="s">
         <v>7</v>
@@ -5081,22 +5131,22 @@
         <v>87</v>
       </c>
       <c r="I74" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="J74" t="s">
-        <v>451</v>
+        <v>441</v>
       </c>
       <c r="K74">
-        <v>80311.53</v>
+        <v>38000</v>
       </c>
       <c r="L74">
-        <v>430.55555555555497</v>
+        <v>350</v>
       </c>
       <c r="M74">
-        <v>0.110581880335239</v>
+        <v>0.34210526315789502</v>
       </c>
       <c r="N74">
-        <v>8881</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="75" spans="1:14">
@@ -5104,19 +5154,16 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C75" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="D75" t="s">
         <v>5</v>
       </c>
-      <c r="E75" t="s">
-        <v>23</v>
-      </c>
       <c r="F75" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="G75" t="s">
         <v>7</v>
@@ -5125,39 +5172,42 @@
         <v>87</v>
       </c>
       <c r="I75" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="J75" t="s">
-        <v>451</v>
+        <v>441</v>
       </c>
       <c r="K75">
-        <v>38000</v>
+        <v>37800</v>
       </c>
       <c r="L75">
-        <v>350</v>
+        <v>387.5</v>
       </c>
       <c r="M75">
-        <v>0.34210526315789502</v>
+        <v>0</v>
       </c>
       <c r="N75">
-        <v>13000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:14">
       <c r="A76">
         <v>75</v>
       </c>
-      <c r="B76" t="s">
-        <v>194</v>
+      <c r="B76" s="2" t="s">
+        <v>191</v>
       </c>
       <c r="C76" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="D76" t="s">
         <v>5</v>
       </c>
+      <c r="E76" t="s">
+        <v>16</v>
+      </c>
       <c r="F76" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="G76" t="s">
         <v>7</v>
@@ -5165,34 +5215,34 @@
       <c r="H76" t="s">
         <v>87</v>
       </c>
-      <c r="I76" t="s">
-        <v>196</v>
+      <c r="I76" s="2" t="s">
+        <v>480</v>
       </c>
       <c r="J76" t="s">
-        <v>451</v>
+        <v>441</v>
       </c>
       <c r="K76">
-        <v>37800</v>
+        <v>54581</v>
       </c>
       <c r="L76">
-        <v>387.5</v>
+        <v>350</v>
       </c>
       <c r="M76">
-        <v>0</v>
+        <v>5.7840640515930401E-2</v>
       </c>
       <c r="N76">
-        <v>0</v>
+        <v>3157</v>
       </c>
     </row>
     <row r="77" spans="1:14">
       <c r="A77">
         <v>76</v>
       </c>
-      <c r="B77" s="2" t="s">
-        <v>197</v>
+      <c r="B77" t="s">
+        <v>193</v>
       </c>
       <c r="C77" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="D77" t="s">
         <v>5</v>
@@ -5201,7 +5251,7 @@
         <v>16</v>
       </c>
       <c r="F77" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="G77" t="s">
         <v>7</v>
@@ -5209,23 +5259,23 @@
       <c r="H77" t="s">
         <v>87</v>
       </c>
-      <c r="I77" s="2" t="s">
-        <v>490</v>
+      <c r="I77" t="s">
+        <v>88</v>
       </c>
       <c r="J77" t="s">
-        <v>451</v>
+        <v>441</v>
       </c>
       <c r="K77">
-        <v>54581</v>
+        <v>25000</v>
       </c>
       <c r="L77">
-        <v>350</v>
+        <v>362.5</v>
       </c>
       <c r="M77">
-        <v>5.7840640515930401E-2</v>
+        <v>0.38147999999999999</v>
       </c>
       <c r="N77">
-        <v>3157</v>
+        <v>9537</v>
       </c>
     </row>
     <row r="78" spans="1:14">
@@ -5233,10 +5283,10 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C78" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="D78" t="s">
         <v>5</v>
@@ -5245,7 +5295,7 @@
         <v>16</v>
       </c>
       <c r="F78" t="s">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="G78" t="s">
         <v>7</v>
@@ -5254,107 +5304,101 @@
         <v>87</v>
       </c>
       <c r="I78" t="s">
-        <v>88</v>
+        <v>196</v>
       </c>
       <c r="J78" t="s">
-        <v>451</v>
+        <v>441</v>
       </c>
       <c r="K78">
-        <v>25000</v>
+        <v>52698</v>
       </c>
       <c r="L78">
-        <v>362.5</v>
+        <v>540.83333333333303</v>
       </c>
       <c r="M78">
-        <v>0.38147999999999999</v>
+        <v>6.4518577555125398E-2</v>
       </c>
       <c r="N78">
-        <v>9537</v>
+        <v>3400</v>
       </c>
     </row>
     <row r="79" spans="1:14">
       <c r="A79">
         <v>78</v>
       </c>
-      <c r="B79" t="s">
-        <v>201</v>
+      <c r="B79" s="2" t="s">
+        <v>197</v>
       </c>
       <c r="C79" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="D79" t="s">
         <v>5</v>
       </c>
-      <c r="E79" t="s">
-        <v>16</v>
-      </c>
       <c r="F79" t="s">
-        <v>90</v>
+        <v>198</v>
       </c>
       <c r="G79" t="s">
         <v>7</v>
       </c>
       <c r="H79" t="s">
-        <v>87</v>
-      </c>
-      <c r="I79" t="s">
-        <v>202</v>
+        <v>199</v>
+      </c>
+      <c r="I79" s="2" t="s">
+        <v>478</v>
       </c>
       <c r="J79" t="s">
-        <v>451</v>
+        <v>441</v>
       </c>
       <c r="K79">
-        <v>52698</v>
+        <v>38500</v>
       </c>
       <c r="L79">
-        <v>540.83333333333303</v>
+        <v>210.833333333333</v>
       </c>
       <c r="M79">
-        <v>6.4518577555125398E-2</v>
+        <v>0.22270129870129901</v>
       </c>
       <c r="N79">
-        <v>3400</v>
+        <v>8574</v>
       </c>
     </row>
     <row r="80" spans="1:14">
       <c r="A80">
         <v>79</v>
       </c>
-      <c r="B80" s="2" t="s">
-        <v>203</v>
+      <c r="B80" t="s">
+        <v>200</v>
       </c>
       <c r="C80" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="D80" t="s">
-        <v>5</v>
-      </c>
-      <c r="F80" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="G80" t="s">
         <v>7</v>
       </c>
       <c r="H80" t="s">
-        <v>205</v>
-      </c>
-      <c r="I80" s="2" t="s">
-        <v>488</v>
+        <v>87</v>
+      </c>
+      <c r="I80" t="s">
+        <v>202</v>
       </c>
       <c r="J80" t="s">
-        <v>451</v>
+        <v>441</v>
       </c>
       <c r="K80">
-        <v>38500</v>
+        <v>27200</v>
       </c>
       <c r="L80">
-        <v>210.833333333333</v>
+        <v>195.555555555555</v>
       </c>
       <c r="M80">
-        <v>0.22270129870129901</v>
+        <v>0.26286764705882298</v>
       </c>
       <c r="N80">
-        <v>8574</v>
+        <v>7150</v>
       </c>
     </row>
     <row r="81" spans="1:14">
@@ -5362,37 +5406,43 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="C81" t="s">
-        <v>168</v>
+        <v>140</v>
       </c>
       <c r="D81" t="s">
-        <v>207</v>
+        <v>5</v>
+      </c>
+      <c r="E81" t="s">
+        <v>16</v>
+      </c>
+      <c r="F81" t="s">
+        <v>204</v>
       </c>
       <c r="G81" t="s">
         <v>7</v>
       </c>
       <c r="H81" t="s">
-        <v>87</v>
+        <v>8</v>
       </c>
       <c r="I81" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="J81" t="s">
-        <v>451</v>
+        <v>442</v>
       </c>
       <c r="K81">
-        <v>27200</v>
+        <v>60000</v>
       </c>
       <c r="L81">
-        <v>195.555555555555</v>
+        <v>200</v>
       </c>
       <c r="M81">
-        <v>0.26286764705882298</v>
+        <v>0.320583333333333</v>
       </c>
       <c r="N81">
-        <v>7150</v>
+        <v>19235</v>
       </c>
     </row>
     <row r="82" spans="1:14">
@@ -5400,19 +5450,16 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C82" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D82" t="s">
         <v>5</v>
       </c>
-      <c r="E82" t="s">
-        <v>16</v>
-      </c>
       <c r="F82" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="G82" t="s">
         <v>7</v>
@@ -5421,22 +5468,22 @@
         <v>8</v>
       </c>
       <c r="I82" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="J82" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="K82">
-        <v>60000</v>
+        <v>50000</v>
       </c>
       <c r="L82">
-        <v>200</v>
+        <v>195.555555555555</v>
       </c>
       <c r="M82">
-        <v>0.320583333333333</v>
+        <v>0.15</v>
       </c>
       <c r="N82">
-        <v>19235</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="83" spans="1:14">
@@ -5444,16 +5491,19 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C83" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D83" t="s">
         <v>5</v>
       </c>
+      <c r="E83" t="s">
+        <v>23</v>
+      </c>
       <c r="F83" t="s">
-        <v>213</v>
+        <v>127</v>
       </c>
       <c r="G83" t="s">
         <v>7</v>
@@ -5462,22 +5512,22 @@
         <v>8</v>
       </c>
       <c r="I83" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="J83" t="s">
-        <v>467</v>
+        <v>442</v>
       </c>
       <c r="K83">
-        <v>50000</v>
+        <v>131575</v>
       </c>
       <c r="L83">
-        <v>195.555555555555</v>
+        <v>204.444444444445</v>
       </c>
       <c r="M83">
-        <v>0.15</v>
+        <v>7.6002280068402095E-2</v>
       </c>
       <c r="N83">
-        <v>7500</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="84" spans="1:14">
@@ -5485,19 +5535,16 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="C84" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D84" t="s">
         <v>5</v>
       </c>
-      <c r="E84" t="s">
-        <v>23</v>
-      </c>
       <c r="F84" t="s">
-        <v>129</v>
+        <v>56</v>
       </c>
       <c r="G84" t="s">
         <v>7</v>
@@ -5506,22 +5553,22 @@
         <v>8</v>
       </c>
       <c r="I84" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="J84" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="K84">
-        <v>131575</v>
+        <v>99500</v>
       </c>
       <c r="L84">
-        <v>204.444444444445</v>
+        <v>195.555555555555</v>
       </c>
       <c r="M84">
-        <v>7.6002280068402095E-2</v>
+        <v>0.23086432160803999</v>
       </c>
       <c r="N84">
-        <v>10000</v>
+        <v>22971</v>
       </c>
     </row>
     <row r="85" spans="1:14">
@@ -5529,16 +5576,16 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="C85" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D85" t="s">
         <v>5</v>
       </c>
       <c r="F85" t="s">
-        <v>56</v>
+        <v>214</v>
       </c>
       <c r="G85" t="s">
         <v>7</v>
@@ -5547,22 +5594,22 @@
         <v>8</v>
       </c>
       <c r="I85" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="J85" t="s">
-        <v>467</v>
+        <v>442</v>
       </c>
       <c r="K85">
-        <v>99500</v>
+        <v>32000</v>
       </c>
       <c r="L85">
-        <v>195.555555555555</v>
+        <v>178.888888888889</v>
       </c>
       <c r="M85">
-        <v>0.23086432160803999</v>
+        <v>0.11874999999999999</v>
       </c>
       <c r="N85">
-        <v>22971</v>
+        <v>3800</v>
       </c>
     </row>
     <row r="86" spans="1:14">
@@ -5570,16 +5617,19 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C86" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D86" t="s">
         <v>5</v>
       </c>
+      <c r="E86" t="s">
+        <v>23</v>
+      </c>
       <c r="F86" t="s">
-        <v>220</v>
+        <v>186</v>
       </c>
       <c r="G86" t="s">
         <v>7</v>
@@ -5588,22 +5638,22 @@
         <v>8</v>
       </c>
       <c r="I86" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="J86" t="s">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="K86">
-        <v>32000</v>
+        <v>52170</v>
       </c>
       <c r="L86">
-        <v>178.888888888889</v>
+        <v>208.333333333333</v>
       </c>
       <c r="M86">
-        <v>0.11874999999999999</v>
+        <v>0.156009200690052</v>
       </c>
       <c r="N86">
-        <v>3800</v>
+        <v>8139</v>
       </c>
     </row>
     <row r="87" spans="1:14">
@@ -5611,19 +5661,16 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C87" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D87" t="s">
         <v>5</v>
       </c>
-      <c r="E87" t="s">
-        <v>23</v>
-      </c>
       <c r="F87" t="s">
-        <v>192</v>
+        <v>219</v>
       </c>
       <c r="G87" t="s">
         <v>7</v>
@@ -5632,22 +5679,22 @@
         <v>8</v>
       </c>
       <c r="I87" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="J87" t="s">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="K87">
-        <v>52170</v>
+        <v>46000</v>
       </c>
       <c r="L87">
-        <v>208.333333333333</v>
+        <v>186.666666666667</v>
       </c>
       <c r="M87">
-        <v>0.156009200690052</v>
+        <v>0.102173913043478</v>
       </c>
       <c r="N87">
-        <v>8139</v>
+        <v>4700</v>
       </c>
     </row>
     <row r="88" spans="1:14">
@@ -5655,16 +5702,19 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C88" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D88" t="s">
         <v>5</v>
       </c>
+      <c r="E88" t="s">
+        <v>23</v>
+      </c>
       <c r="F88" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="G88" t="s">
         <v>7</v>
@@ -5673,22 +5723,22 @@
         <v>8</v>
       </c>
       <c r="I88" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="J88" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="K88">
-        <v>46000</v>
+        <v>45013</v>
       </c>
       <c r="L88">
-        <v>186.666666666667</v>
+        <v>206.25</v>
       </c>
       <c r="M88">
-        <v>0.102173913043478</v>
+        <v>0.13995956723613201</v>
       </c>
       <c r="N88">
-        <v>4700</v>
+        <v>6300</v>
       </c>
     </row>
     <row r="89" spans="1:14">
@@ -5696,19 +5746,16 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C89" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D89" t="s">
         <v>5</v>
       </c>
-      <c r="E89" t="s">
-        <v>23</v>
-      </c>
       <c r="F89" t="s">
-        <v>228</v>
+        <v>78</v>
       </c>
       <c r="G89" t="s">
         <v>7</v>
@@ -5716,23 +5763,23 @@
       <c r="H89" t="s">
         <v>8</v>
       </c>
-      <c r="I89" t="s">
-        <v>229</v>
+      <c r="I89" s="1" t="s">
+        <v>488</v>
       </c>
       <c r="J89" t="s">
-        <v>467</v>
+        <v>442</v>
       </c>
       <c r="K89">
-        <v>45013</v>
+        <v>48566</v>
       </c>
       <c r="L89">
-        <v>206.25</v>
+        <v>220</v>
       </c>
       <c r="M89">
-        <v>0.13995956723613201</v>
+        <v>0.76040851624593297</v>
       </c>
       <c r="N89">
-        <v>6300</v>
+        <v>36930</v>
       </c>
     </row>
     <row r="90" spans="1:14">
@@ -5740,16 +5787,16 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C90" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D90" t="s">
         <v>5</v>
       </c>
       <c r="F90" t="s">
-        <v>78</v>
+        <v>226</v>
       </c>
       <c r="G90" t="s">
         <v>7</v>
@@ -5758,22 +5805,22 @@
         <v>8</v>
       </c>
       <c r="I90" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="J90" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="K90">
-        <v>48566</v>
+        <v>55618</v>
       </c>
       <c r="L90">
-        <v>220</v>
+        <v>238.333333333333</v>
       </c>
       <c r="M90">
-        <v>0.76040851624593297</v>
+        <v>0.2</v>
       </c>
       <c r="N90">
-        <v>36930</v>
+        <v>11123.6</v>
       </c>
     </row>
     <row r="91" spans="1:14">
@@ -5781,16 +5828,16 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="C91" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D91" t="s">
         <v>5</v>
       </c>
       <c r="F91" t="s">
-        <v>233</v>
+        <v>192</v>
       </c>
       <c r="G91" t="s">
         <v>7</v>
@@ -5799,22 +5846,22 @@
         <v>8</v>
       </c>
       <c r="I91" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="J91" t="s">
-        <v>467</v>
+        <v>442</v>
       </c>
       <c r="K91">
-        <v>55618</v>
+        <v>47000</v>
       </c>
       <c r="L91">
-        <v>238.333333333333</v>
+        <v>229.166666666667</v>
       </c>
       <c r="M91">
-        <v>0.2</v>
+        <v>4.0382978723404302E-2</v>
       </c>
       <c r="N91">
-        <v>11123.6</v>
+        <v>1898</v>
       </c>
     </row>
     <row r="92" spans="1:14">
@@ -5822,16 +5869,19 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C92" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D92" t="s">
         <v>5</v>
       </c>
+      <c r="E92" t="s">
+        <v>23</v>
+      </c>
       <c r="F92" t="s">
-        <v>198</v>
+        <v>231</v>
       </c>
       <c r="G92" t="s">
         <v>7</v>
@@ -5840,22 +5890,22 @@
         <v>8</v>
       </c>
       <c r="I92" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="J92" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="K92">
-        <v>47000</v>
+        <v>87763</v>
       </c>
       <c r="L92">
-        <v>229.166666666667</v>
+        <v>177.777777777778</v>
       </c>
       <c r="M92">
-        <v>4.0382978723404302E-2</v>
+        <v>0.227886466962159</v>
       </c>
       <c r="N92">
-        <v>1898</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="93" spans="1:14">
@@ -5863,19 +5913,19 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="C93" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D93" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E93" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F93" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="G93" t="s">
         <v>7</v>
@@ -5884,22 +5934,22 @@
         <v>8</v>
       </c>
       <c r="I93" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="J93" t="s">
-        <v>467</v>
+        <v>442</v>
       </c>
       <c r="K93">
-        <v>87763</v>
+        <v>100658</v>
       </c>
       <c r="L93">
-        <v>177.777777777778</v>
+        <v>275.55555555555497</v>
       </c>
       <c r="M93">
-        <v>0.227886466962159</v>
+        <v>0.33777742454648402</v>
       </c>
       <c r="N93">
-        <v>20000</v>
+        <v>34000</v>
       </c>
     </row>
     <row r="94" spans="1:14">
@@ -5907,19 +5957,16 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="C94" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D94" t="s">
-        <v>14</v>
-      </c>
-      <c r="E94" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="F94" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="G94" t="s">
         <v>7</v>
@@ -5928,22 +5975,22 @@
         <v>8</v>
       </c>
       <c r="I94" t="s">
-        <v>242</v>
+        <v>490</v>
       </c>
       <c r="J94" t="s">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="K94">
-        <v>100658</v>
+        <v>67000</v>
       </c>
       <c r="L94">
-        <v>275.55555555555497</v>
+        <v>206.666666666667</v>
       </c>
       <c r="M94">
-        <v>0.33777742454648402</v>
+        <v>0.178820895522388</v>
       </c>
       <c r="N94">
-        <v>34000</v>
+        <v>11981</v>
       </c>
     </row>
     <row r="95" spans="1:14">
@@ -5951,16 +5998,19 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C95" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D95" t="s">
         <v>5</v>
       </c>
+      <c r="E95" t="s">
+        <v>16</v>
+      </c>
       <c r="F95" t="s">
-        <v>244</v>
+        <v>84</v>
       </c>
       <c r="G95" t="s">
         <v>7</v>
@@ -5969,22 +6019,22 @@
         <v>8</v>
       </c>
       <c r="I95" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="J95" t="s">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="K95">
-        <v>67000</v>
+        <v>39431</v>
       </c>
       <c r="L95">
-        <v>206.666666666667</v>
+        <v>216.666666666667</v>
       </c>
       <c r="M95">
-        <v>0.178820895522388</v>
+        <v>0.30432908117978202</v>
       </c>
       <c r="N95">
-        <v>11981</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="96" spans="1:14">
@@ -5992,19 +6042,16 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="C96" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D96" t="s">
         <v>5</v>
       </c>
-      <c r="E96" t="s">
-        <v>16</v>
-      </c>
       <c r="F96" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G96" t="s">
         <v>7</v>
@@ -6013,22 +6060,22 @@
         <v>8</v>
       </c>
       <c r="I96" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="J96" t="s">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="K96">
-        <v>39431</v>
+        <v>34273</v>
       </c>
       <c r="L96">
-        <v>216.666666666667</v>
+        <v>166.666666666667</v>
       </c>
       <c r="M96">
-        <v>0.30432908117978202</v>
+        <v>0.145887433256499</v>
       </c>
       <c r="N96">
-        <v>12000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="97" spans="1:14">
@@ -6036,16 +6083,13 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="C97" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D97" t="s">
         <v>5</v>
-      </c>
-      <c r="F97" t="s">
-        <v>86</v>
       </c>
       <c r="G97" t="s">
         <v>7</v>
@@ -6054,22 +6098,22 @@
         <v>8</v>
       </c>
       <c r="I97" t="s">
-        <v>249</v>
+        <v>489</v>
       </c>
       <c r="J97" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="K97">
-        <v>34273</v>
+        <v>40000</v>
       </c>
       <c r="L97">
-        <v>166.666666666667</v>
+        <v>200</v>
       </c>
       <c r="M97">
-        <v>0.145887433256499</v>
+        <v>1</v>
       </c>
       <c r="N97">
-        <v>5000</v>
+        <v>40000</v>
       </c>
     </row>
     <row r="98" spans="1:14">
@@ -6077,13 +6121,16 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="C98" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D98" t="s">
         <v>5</v>
+      </c>
+      <c r="E98" t="s">
+        <v>16</v>
       </c>
       <c r="G98" t="s">
         <v>7</v>
@@ -6092,22 +6139,22 @@
         <v>8</v>
       </c>
       <c r="I98" t="s">
-        <v>73</v>
+        <v>244</v>
       </c>
       <c r="J98" t="s">
-        <v>467</v>
+        <v>442</v>
       </c>
       <c r="K98">
-        <v>40000</v>
+        <v>65000</v>
       </c>
       <c r="L98">
-        <v>200</v>
+        <v>201.388888888889</v>
       </c>
       <c r="M98">
-        <v>1</v>
+        <v>0.480738461538462</v>
       </c>
       <c r="N98">
-        <v>40000</v>
+        <v>31248</v>
       </c>
     </row>
     <row r="99" spans="1:14">
@@ -6115,40 +6162,43 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="C99" t="s">
-        <v>144</v>
+        <v>246</v>
       </c>
       <c r="D99" t="s">
         <v>5</v>
       </c>
       <c r="E99" t="s">
-        <v>16</v>
+        <v>23</v>
+      </c>
+      <c r="F99" t="s">
+        <v>247</v>
       </c>
       <c r="G99" t="s">
         <v>7</v>
       </c>
       <c r="H99" t="s">
-        <v>8</v>
+        <v>199</v>
       </c>
       <c r="I99" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="J99" t="s">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="K99">
-        <v>65000</v>
+        <v>49000</v>
       </c>
       <c r="L99">
-        <v>201.388888888889</v>
+        <v>335.83333333333297</v>
       </c>
       <c r="M99">
-        <v>0.480738461538462</v>
+        <v>0.24397959183673501</v>
       </c>
       <c r="N99">
-        <v>31248</v>
+        <v>11955</v>
       </c>
     </row>
     <row r="100" spans="1:14">
@@ -6156,43 +6206,43 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="C100" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="D100" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E100" t="s">
         <v>23</v>
       </c>
       <c r="F100" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="G100" t="s">
         <v>7</v>
       </c>
       <c r="H100" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="I100" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="J100" t="s">
-        <v>469</v>
+        <v>459</v>
       </c>
       <c r="K100">
-        <v>49000</v>
+        <v>95000</v>
       </c>
       <c r="L100">
         <v>335.83333333333297</v>
       </c>
       <c r="M100">
-        <v>0.24397959183673501</v>
+        <v>0.123347368421053</v>
       </c>
       <c r="N100">
-        <v>11955</v>
+        <v>11718</v>
       </c>
     </row>
     <row r="101" spans="1:14">
@@ -6200,43 +6250,43 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="C101" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="D101" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E101" t="s">
         <v>23</v>
       </c>
       <c r="F101" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="G101" t="s">
         <v>7</v>
       </c>
       <c r="H101" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="I101" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="J101" t="s">
-        <v>469</v>
+        <v>459</v>
       </c>
       <c r="K101">
-        <v>95000</v>
+        <v>45000</v>
       </c>
       <c r="L101">
-        <v>335.83333333333297</v>
+        <v>241.111111111111</v>
       </c>
       <c r="M101">
-        <v>0.123347368421053</v>
+        <v>0.31568888888888902</v>
       </c>
       <c r="N101">
-        <v>11718</v>
+        <v>14206</v>
       </c>
     </row>
     <row r="102" spans="1:14">
@@ -6244,125 +6294,122 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="C102" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="D102" t="s">
         <v>5</v>
       </c>
-      <c r="E102" t="s">
-        <v>23</v>
-      </c>
       <c r="F102" t="s">
-        <v>261</v>
+        <v>26</v>
       </c>
       <c r="G102" t="s">
         <v>7</v>
       </c>
       <c r="H102" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="I102" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="J102" t="s">
-        <v>469</v>
+        <v>459</v>
       </c>
       <c r="K102">
-        <v>45000</v>
+        <v>124500</v>
       </c>
       <c r="L102">
-        <v>241.111111111111</v>
+        <v>172.222222222222</v>
       </c>
       <c r="M102">
-        <v>0.31568888888888902</v>
+        <v>5.62489959839357E-2</v>
       </c>
       <c r="N102">
-        <v>14206</v>
+        <v>7003</v>
       </c>
     </row>
     <row r="103" spans="1:14">
       <c r="A103">
         <v>102</v>
       </c>
-      <c r="B103" t="s">
-        <v>263</v>
+      <c r="B103" s="2" t="s">
+        <v>257</v>
       </c>
       <c r="C103" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="D103" t="s">
         <v>5</v>
       </c>
       <c r="F103" t="s">
-        <v>26</v>
+        <v>127</v>
       </c>
       <c r="G103" t="s">
         <v>7</v>
       </c>
       <c r="H103" t="s">
-        <v>205</v>
-      </c>
-      <c r="I103" t="s">
-        <v>264</v>
+        <v>199</v>
+      </c>
+      <c r="I103" s="2" t="s">
+        <v>481</v>
       </c>
       <c r="J103" t="s">
-        <v>469</v>
+        <v>459</v>
       </c>
       <c r="K103">
-        <v>124500</v>
+        <v>64000</v>
       </c>
       <c r="L103">
-        <v>172.222222222222</v>
+        <v>183.333333333333</v>
       </c>
       <c r="M103">
-        <v>5.62489959839357E-2</v>
+        <v>9.1593750000000002E-2</v>
       </c>
       <c r="N103">
-        <v>7003</v>
+        <v>5862</v>
       </c>
     </row>
     <row r="104" spans="1:14">
       <c r="A104">
         <v>103</v>
       </c>
-      <c r="B104" s="2" t="s">
-        <v>265</v>
+      <c r="B104" t="s">
+        <v>258</v>
       </c>
       <c r="C104" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="D104" t="s">
         <v>5</v>
       </c>
       <c r="F104" t="s">
-        <v>129</v>
+        <v>65</v>
       </c>
       <c r="G104" t="s">
         <v>7</v>
       </c>
       <c r="H104" t="s">
-        <v>205</v>
-      </c>
-      <c r="I104" s="2" t="s">
-        <v>491</v>
+        <v>199</v>
+      </c>
+      <c r="I104" t="s">
+        <v>259</v>
       </c>
       <c r="J104" t="s">
-        <v>469</v>
+        <v>459</v>
       </c>
       <c r="K104">
-        <v>64000</v>
+        <v>25000</v>
       </c>
       <c r="L104">
-        <v>183.333333333333</v>
+        <v>284.16666666666703</v>
       </c>
       <c r="M104">
-        <v>9.1593750000000002E-2</v>
+        <v>0</v>
       </c>
       <c r="N104">
-        <v>5862</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:14">
@@ -6370,40 +6417,40 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="C105" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="D105" t="s">
         <v>5</v>
       </c>
       <c r="F105" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="G105" t="s">
         <v>7</v>
       </c>
       <c r="H105" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="I105" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="J105" t="s">
-        <v>469</v>
+        <v>459</v>
       </c>
       <c r="K105">
-        <v>25000</v>
+        <v>38498</v>
       </c>
       <c r="L105">
-        <v>284.16666666666703</v>
+        <v>177.777777777778</v>
       </c>
       <c r="M105">
-        <v>0</v>
+        <v>3.1404228791106002E-3</v>
       </c>
       <c r="N105">
-        <v>0</v>
+        <v>120.9</v>
       </c>
     </row>
     <row r="106" spans="1:14">
@@ -6411,40 +6458,37 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="C106" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="D106" t="s">
-        <v>5</v>
-      </c>
-      <c r="F106" t="s">
-        <v>81</v>
+        <v>201</v>
       </c>
       <c r="G106" t="s">
         <v>7</v>
       </c>
       <c r="H106" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="I106" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="J106" t="s">
-        <v>469</v>
+        <v>443</v>
       </c>
       <c r="K106">
-        <v>38498</v>
+        <v>166433</v>
       </c>
       <c r="L106">
-        <v>177.777777777778</v>
+        <v>186.666666666667</v>
       </c>
       <c r="M106">
-        <v>3.1404228791106002E-3</v>
+        <v>0.13939543239621899</v>
       </c>
       <c r="N106">
-        <v>120.9</v>
+        <v>23200</v>
       </c>
     </row>
     <row r="107" spans="1:14">
@@ -6452,37 +6496,43 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="C107" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="D107" t="s">
-        <v>207</v>
+        <v>14</v>
+      </c>
+      <c r="E107" t="s">
+        <v>23</v>
+      </c>
+      <c r="F107" t="s">
+        <v>192</v>
       </c>
       <c r="G107" t="s">
         <v>7</v>
       </c>
       <c r="H107" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="I107" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="J107" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="K107">
-        <v>166433</v>
+        <v>58000</v>
       </c>
       <c r="L107">
-        <v>186.666666666667</v>
+        <v>373.33333333333297</v>
       </c>
       <c r="M107">
-        <v>0.13939543239621899</v>
+        <v>2.5862068965517199E-2</v>
       </c>
       <c r="N107">
-        <v>23200</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="108" spans="1:14">
@@ -6490,43 +6540,40 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="C108" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="D108" t="s">
-        <v>14</v>
-      </c>
-      <c r="E108" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="F108" t="s">
-        <v>198</v>
+        <v>267</v>
       </c>
       <c r="G108" t="s">
         <v>7</v>
       </c>
       <c r="H108" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="I108" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="J108" t="s">
-        <v>469</v>
+        <v>443</v>
       </c>
       <c r="K108">
-        <v>58000</v>
+        <v>51872</v>
       </c>
       <c r="L108">
-        <v>373.33333333333297</v>
+        <v>302.5</v>
       </c>
       <c r="M108">
-        <v>2.5862068965517199E-2</v>
+        <v>0</v>
       </c>
       <c r="N108">
-        <v>1500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:14">
@@ -6534,34 +6581,34 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="C109" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="D109" t="s">
         <v>5</v>
       </c>
       <c r="F109" t="s">
-        <v>275</v>
+        <v>194</v>
       </c>
       <c r="G109" t="s">
         <v>7</v>
       </c>
       <c r="H109" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="I109" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="J109" t="s">
-        <v>453</v>
+        <v>443</v>
       </c>
       <c r="K109">
-        <v>51872</v>
+        <v>21632</v>
       </c>
       <c r="L109">
-        <v>302.5</v>
+        <v>229.5</v>
       </c>
       <c r="M109">
         <v>0</v>
@@ -6575,40 +6622,40 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="C110" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="D110" t="s">
         <v>5</v>
       </c>
       <c r="F110" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="G110" t="s">
         <v>7</v>
       </c>
       <c r="H110" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="I110" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="J110" t="s">
-        <v>453</v>
+        <v>443</v>
       </c>
       <c r="K110">
-        <v>21632</v>
+        <v>69000</v>
       </c>
       <c r="L110">
-        <v>229.5</v>
+        <v>186.666666666667</v>
       </c>
       <c r="M110">
-        <v>0</v>
+        <v>0.22942028985507301</v>
       </c>
       <c r="N110">
-        <v>0</v>
+        <v>15830</v>
       </c>
     </row>
     <row r="111" spans="1:14">
@@ -6616,40 +6663,40 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="C111" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="D111" t="s">
         <v>5</v>
       </c>
       <c r="F111" t="s">
-        <v>200</v>
+        <v>274</v>
       </c>
       <c r="G111" t="s">
         <v>7</v>
       </c>
       <c r="H111" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="I111" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="J111" t="s">
-        <v>453</v>
+        <v>443</v>
       </c>
       <c r="K111">
-        <v>69000</v>
+        <v>54000</v>
       </c>
       <c r="L111">
-        <v>186.666666666667</v>
+        <v>151.111111111111</v>
       </c>
       <c r="M111">
-        <v>0.22942028985507301</v>
+        <v>0.36928703703703702</v>
       </c>
       <c r="N111">
-        <v>15830</v>
+        <v>19941.5</v>
       </c>
     </row>
     <row r="112" spans="1:14">
@@ -6657,54 +6704,54 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="C112" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="D112" t="s">
         <v>5</v>
       </c>
-      <c r="F112" t="s">
-        <v>282</v>
+      <c r="E112" t="s">
+        <v>16</v>
       </c>
       <c r="G112" t="s">
         <v>7</v>
       </c>
       <c r="H112" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="I112" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="J112" t="s">
-        <v>453</v>
+        <v>443</v>
       </c>
       <c r="K112">
-        <v>54000</v>
+        <v>57400</v>
       </c>
       <c r="L112">
-        <v>151.111111111111</v>
+        <v>280</v>
       </c>
       <c r="M112">
-        <v>0.36928703703703702</v>
+        <v>1.74216027874564E-2</v>
       </c>
       <c r="N112">
-        <v>19941.5</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="113" spans="1:16">
       <c r="A113">
         <v>112</v>
       </c>
-      <c r="B113" t="s">
-        <v>284</v>
+      <c r="B113" s="2" t="s">
+        <v>278</v>
       </c>
       <c r="C113" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="D113" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E113" t="s">
         <v>16</v>
@@ -6713,25 +6760,28 @@
         <v>7</v>
       </c>
       <c r="H113" t="s">
-        <v>205</v>
-      </c>
-      <c r="I113" t="s">
-        <v>285</v>
+        <v>199</v>
+      </c>
+      <c r="I113" s="2" t="s">
+        <v>483</v>
       </c>
       <c r="J113" t="s">
-        <v>453</v>
+        <v>443</v>
       </c>
       <c r="K113">
-        <v>57400</v>
+        <v>60000</v>
       </c>
       <c r="L113">
-        <v>280</v>
+        <v>284.16666666666703</v>
       </c>
       <c r="M113">
-        <v>1.74216027874564E-2</v>
+        <v>7.1166666666666696E-3</v>
       </c>
       <c r="N113">
-        <v>1000</v>
+        <v>427</v>
+      </c>
+      <c r="P113" s="1" t="s">
+        <v>484</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -6739,10 +6789,10 @@
         <v>113</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="C114" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="D114" t="s">
         <v>14</v>
@@ -6754,28 +6804,28 @@
         <v>7</v>
       </c>
       <c r="H114" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="I114" s="2" t="s">
-        <v>493</v>
+        <v>482</v>
       </c>
       <c r="J114" t="s">
-        <v>453</v>
+        <v>443</v>
       </c>
       <c r="K114">
         <v>60000</v>
       </c>
       <c r="L114">
-        <v>284.16666666666703</v>
+        <v>231.388888888889</v>
       </c>
       <c r="M114">
-        <v>7.1166666666666696E-3</v>
+        <v>0.19166666666666701</v>
       </c>
       <c r="N114">
-        <v>427</v>
+        <v>11500</v>
       </c>
       <c r="P114" s="1" t="s">
-        <v>494</v>
+        <v>484</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -6783,81 +6833,75 @@
         <v>114</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="C115" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="D115" t="s">
-        <v>14</v>
-      </c>
-      <c r="E115" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="G115" t="s">
         <v>7</v>
       </c>
       <c r="H115" t="s">
-        <v>205</v>
-      </c>
-      <c r="I115" s="2" t="s">
-        <v>492</v>
+        <v>199</v>
+      </c>
+      <c r="I115" s="5" t="s">
+        <v>485</v>
       </c>
       <c r="J115" t="s">
-        <v>453</v>
+        <v>443</v>
       </c>
       <c r="K115">
-        <v>60000</v>
+        <v>33000</v>
       </c>
       <c r="L115">
-        <v>231.388888888889</v>
+        <v>311.66666666666703</v>
       </c>
       <c r="M115">
-        <v>0.19166666666666701</v>
+        <v>0</v>
       </c>
       <c r="N115">
-        <v>11500</v>
-      </c>
-      <c r="P115" s="1" t="s">
-        <v>494</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116" spans="1:16">
       <c r="A116">
         <v>115</v>
       </c>
-      <c r="B116" s="2" t="s">
-        <v>288</v>
+      <c r="B116" t="s">
+        <v>281</v>
       </c>
       <c r="C116" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="D116" t="s">
-        <v>5</v>
+        <v>201</v>
       </c>
       <c r="G116" t="s">
         <v>7</v>
       </c>
       <c r="H116" t="s">
-        <v>205</v>
-      </c>
-      <c r="I116" s="5" t="s">
-        <v>495</v>
+        <v>199</v>
+      </c>
+      <c r="I116" t="s">
+        <v>282</v>
       </c>
       <c r="J116" t="s">
-        <v>453</v>
+        <v>443</v>
       </c>
       <c r="K116">
-        <v>33000</v>
+        <v>88786</v>
       </c>
       <c r="L116">
-        <v>311.66666666666703</v>
+        <v>180.833333333333</v>
       </c>
       <c r="M116">
-        <v>0</v>
+        <v>0.23652377627103399</v>
       </c>
       <c r="N116">
-        <v>0</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -6865,37 +6909,37 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="C117" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="D117" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G117" t="s">
         <v>7</v>
       </c>
       <c r="H117" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="I117" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="J117" t="s">
-        <v>453</v>
+        <v>443</v>
       </c>
       <c r="K117">
-        <v>88786</v>
+        <v>134000</v>
       </c>
       <c r="L117">
-        <v>180.833333333333</v>
+        <v>193.75</v>
       </c>
       <c r="M117">
-        <v>0.23652377627103399</v>
+        <v>0.23798507462686599</v>
       </c>
       <c r="N117">
-        <v>21000</v>
+        <v>31890</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -6903,37 +6947,37 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="C118" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="D118" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G118" t="s">
         <v>7</v>
       </c>
       <c r="H118" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="I118" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="J118" t="s">
-        <v>453</v>
+        <v>443</v>
       </c>
       <c r="K118">
-        <v>134000</v>
+        <v>35000</v>
       </c>
       <c r="L118">
-        <v>193.75</v>
+        <v>225</v>
       </c>
       <c r="M118">
-        <v>0.23798507462686599</v>
+        <v>3.1885714285714302E-2</v>
       </c>
       <c r="N118">
-        <v>31890</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -6941,37 +6985,37 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="C119" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="D119" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="G119" t="s">
         <v>7</v>
       </c>
       <c r="H119" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="I119" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="J119" t="s">
-        <v>453</v>
+        <v>443</v>
       </c>
       <c r="K119">
-        <v>35000</v>
+        <v>18000</v>
       </c>
       <c r="L119">
-        <v>225</v>
+        <v>232.5</v>
       </c>
       <c r="M119">
-        <v>3.1885714285714302E-2</v>
+        <v>0</v>
       </c>
       <c r="N119">
-        <v>1116</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -6979,37 +7023,40 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="C120" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="D120" t="s">
-        <v>207</v>
+        <v>201</v>
+      </c>
+      <c r="E120" t="s">
+        <v>16</v>
       </c>
       <c r="G120" t="s">
         <v>7</v>
       </c>
       <c r="H120" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="I120" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="J120" t="s">
-        <v>453</v>
+        <v>443</v>
       </c>
       <c r="K120">
-        <v>18000</v>
+        <v>105741</v>
       </c>
       <c r="L120">
-        <v>232.5</v>
+        <v>172.222222222222</v>
       </c>
       <c r="M120">
-        <v>0</v>
+        <v>5.2959589941460702E-2</v>
       </c>
       <c r="N120">
-        <v>0</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7017,78 +7064,81 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="C121" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="D121" t="s">
-        <v>207</v>
-      </c>
-      <c r="E121" t="s">
-        <v>16</v>
+        <v>201</v>
       </c>
       <c r="G121" t="s">
         <v>7</v>
       </c>
       <c r="H121" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="I121" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="J121" t="s">
-        <v>453</v>
+        <v>443</v>
       </c>
       <c r="K121">
-        <v>105741</v>
+        <v>51000</v>
       </c>
       <c r="L121">
-        <v>172.222222222222</v>
+        <v>250</v>
       </c>
       <c r="M121">
-        <v>5.2959589941460702E-2</v>
+        <v>0</v>
       </c>
       <c r="N121">
-        <v>5600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122" spans="1:16">
       <c r="A122">
         <v>121</v>
       </c>
-      <c r="B122" t="s">
-        <v>299</v>
+      <c r="B122" s="2" t="s">
+        <v>293</v>
       </c>
       <c r="C122" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="D122" t="s">
-        <v>207</v>
+        <v>5</v>
+      </c>
+      <c r="E122" t="s">
+        <v>16</v>
       </c>
       <c r="G122" t="s">
         <v>7</v>
       </c>
       <c r="H122" t="s">
-        <v>205</v>
-      </c>
-      <c r="I122" t="s">
-        <v>300</v>
+        <v>199</v>
+      </c>
+      <c r="I122" s="3" t="s">
+        <v>468</v>
       </c>
       <c r="J122" t="s">
-        <v>453</v>
+        <v>443</v>
       </c>
       <c r="K122">
-        <v>51000</v>
+        <v>130143</v>
       </c>
       <c r="L122">
-        <v>250</v>
+        <v>125</v>
       </c>
       <c r="M122">
-        <v>0</v>
+        <v>0.27661879624720498</v>
       </c>
       <c r="N122">
-        <v>0</v>
+        <v>36000</v>
+      </c>
+      <c r="P122" s="1" t="s">
+        <v>479</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7096,81 +7146,81 @@
         <v>122</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>301</v>
+        <v>469</v>
       </c>
       <c r="C123" t="s">
-        <v>254</v>
-      </c>
-      <c r="D123" t="s">
-        <v>5</v>
-      </c>
-      <c r="E123" t="s">
-        <v>16</v>
+        <v>246</v>
       </c>
       <c r="G123" t="s">
         <v>7</v>
       </c>
       <c r="H123" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="I123" s="3" t="s">
-        <v>478</v>
+        <v>470</v>
       </c>
       <c r="J123" t="s">
-        <v>453</v>
+        <v>443</v>
       </c>
       <c r="K123">
-        <v>130143</v>
+        <v>121551.47</v>
       </c>
       <c r="L123">
-        <v>125</v>
+        <v>151.111111111111</v>
       </c>
       <c r="M123">
-        <v>0.27661879624720498</v>
+        <v>0.800701710970669</v>
       </c>
       <c r="N123">
-        <v>36000</v>
+        <v>97326.47</v>
       </c>
       <c r="P123" s="1" t="s">
-        <v>489</v>
+        <v>479</v>
       </c>
     </row>
     <row r="124" spans="1:16">
       <c r="A124">
         <v>123</v>
       </c>
-      <c r="B124" s="2" t="s">
-        <v>479</v>
+      <c r="B124" t="s">
+        <v>294</v>
       </c>
       <c r="C124" t="s">
-        <v>254</v>
+        <v>295</v>
+      </c>
+      <c r="D124" t="s">
+        <v>5</v>
+      </c>
+      <c r="E124" t="s">
+        <v>16</v>
+      </c>
+      <c r="F124" t="s">
+        <v>296</v>
       </c>
       <c r="G124" t="s">
         <v>7</v>
       </c>
       <c r="H124" t="s">
-        <v>205</v>
-      </c>
-      <c r="I124" s="3" t="s">
-        <v>480</v>
+        <v>8</v>
+      </c>
+      <c r="I124" t="s">
+        <v>297</v>
       </c>
       <c r="J124" t="s">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="K124">
-        <v>121551.47</v>
+        <v>110000</v>
       </c>
       <c r="L124">
-        <v>151.111111111111</v>
+        <v>170.833333333333</v>
       </c>
       <c r="M124">
-        <v>0.800701710970669</v>
+        <v>0.14505645454545399</v>
       </c>
       <c r="N124">
-        <v>97326.47</v>
-      </c>
-      <c r="P124" s="1" t="s">
-        <v>489</v>
+        <v>15956.21</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7178,19 +7228,19 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="C125" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="D125" t="s">
         <v>5</v>
       </c>
       <c r="E125" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F125" t="s">
-        <v>304</v>
+        <v>219</v>
       </c>
       <c r="G125" t="s">
         <v>7</v>
@@ -7199,22 +7249,22 @@
         <v>8</v>
       </c>
       <c r="I125" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="J125" t="s">
-        <v>454</v>
+        <v>444</v>
       </c>
       <c r="K125">
-        <v>110000</v>
+        <v>56000</v>
       </c>
       <c r="L125">
-        <v>170.833333333333</v>
+        <v>154.166666666667</v>
       </c>
       <c r="M125">
-        <v>0.14505645454545399</v>
+        <v>0.11841071428571399</v>
       </c>
       <c r="N125">
-        <v>15956.21</v>
+        <v>6631</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7222,19 +7272,16 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="C126" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="D126" t="s">
         <v>5</v>
       </c>
-      <c r="E126" t="s">
-        <v>23</v>
-      </c>
       <c r="F126" t="s">
-        <v>225</v>
+        <v>192</v>
       </c>
       <c r="G126" t="s">
         <v>7</v>
@@ -7243,22 +7290,22 @@
         <v>8</v>
       </c>
       <c r="I126" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="J126" t="s">
-        <v>454</v>
+        <v>444</v>
       </c>
       <c r="K126">
-        <v>56000</v>
+        <v>89177</v>
       </c>
       <c r="L126">
-        <v>154.166666666667</v>
+        <v>124.861111111111</v>
       </c>
       <c r="M126">
-        <v>0.11841071428571399</v>
+        <v>0.160689976114918</v>
       </c>
       <c r="N126">
-        <v>6631</v>
+        <v>14329.850000000002</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7266,16 +7313,19 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="C127" t="s">
+        <v>295</v>
+      </c>
+      <c r="D127" t="s">
+        <v>5</v>
+      </c>
+      <c r="E127" t="s">
+        <v>23</v>
+      </c>
+      <c r="F127" t="s">
         <v>303</v>
-      </c>
-      <c r="D127" t="s">
-        <v>5</v>
-      </c>
-      <c r="F127" t="s">
-        <v>198</v>
       </c>
       <c r="G127" t="s">
         <v>7</v>
@@ -7284,22 +7334,22 @@
         <v>8</v>
       </c>
       <c r="I127" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="J127" t="s">
-        <v>454</v>
+        <v>444</v>
       </c>
       <c r="K127">
-        <v>89177</v>
+        <v>30000</v>
       </c>
       <c r="L127">
-        <v>124.861111111111</v>
+        <v>163.611111111111</v>
       </c>
       <c r="M127">
-        <v>0.160689976114918</v>
+        <v>0.2198</v>
       </c>
       <c r="N127">
-        <v>14329.850000000002</v>
+        <v>6594</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7307,19 +7357,19 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="C128" t="s">
+        <v>295</v>
+      </c>
+      <c r="D128" t="s">
+        <v>5</v>
+      </c>
+      <c r="E128" t="s">
+        <v>16</v>
+      </c>
+      <c r="F128" t="s">
         <v>303</v>
-      </c>
-      <c r="D128" t="s">
-        <v>5</v>
-      </c>
-      <c r="E128" t="s">
-        <v>23</v>
-      </c>
-      <c r="F128" t="s">
-        <v>311</v>
       </c>
       <c r="G128" t="s">
         <v>7</v>
@@ -7328,22 +7378,22 @@
         <v>8</v>
       </c>
       <c r="I128" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="J128" t="s">
-        <v>454</v>
+        <v>444</v>
       </c>
       <c r="K128">
-        <v>30000</v>
+        <v>54550</v>
       </c>
       <c r="L128">
-        <v>163.611111111111</v>
+        <v>120.833333333333</v>
       </c>
       <c r="M128">
-        <v>0.2198</v>
+        <v>0.183318056828598</v>
       </c>
       <c r="N128">
-        <v>6594</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="129" spans="1:14">
@@ -7351,10 +7401,10 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="C129" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="D129" t="s">
         <v>5</v>
@@ -7363,7 +7413,7 @@
         <v>16</v>
       </c>
       <c r="F129" t="s">
-        <v>311</v>
+        <v>234</v>
       </c>
       <c r="G129" t="s">
         <v>7</v>
@@ -7372,22 +7422,22 @@
         <v>8</v>
       </c>
       <c r="I129" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="J129" t="s">
-        <v>454</v>
+        <v>444</v>
       </c>
       <c r="K129">
-        <v>54550</v>
+        <v>125000</v>
       </c>
       <c r="L129">
-        <v>120.833333333333</v>
+        <v>183.333333333333</v>
       </c>
       <c r="M129">
-        <v>0.183318056828598</v>
+        <v>0.28566256000000001</v>
       </c>
       <c r="N129">
-        <v>10000</v>
+        <v>35707.82</v>
       </c>
     </row>
     <row r="130" spans="1:14">
@@ -7395,10 +7445,10 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="C130" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="D130" t="s">
         <v>5</v>
@@ -7407,7 +7457,7 @@
         <v>16</v>
       </c>
       <c r="F130" t="s">
-        <v>241</v>
+        <v>310</v>
       </c>
       <c r="G130" t="s">
         <v>7</v>
@@ -7416,22 +7466,22 @@
         <v>8</v>
       </c>
       <c r="I130" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="J130" t="s">
-        <v>454</v>
+        <v>444</v>
       </c>
       <c r="K130">
-        <v>125000</v>
+        <v>69100</v>
       </c>
       <c r="L130">
-        <v>183.333333333333</v>
+        <v>155.555555555555</v>
       </c>
       <c r="M130">
-        <v>0.28566256000000001</v>
+        <v>5.9334298118668603E-2</v>
       </c>
       <c r="N130">
-        <v>35707.82</v>
+        <v>4100</v>
       </c>
     </row>
     <row r="131" spans="1:14">
@@ -7439,19 +7489,19 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="C131" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="D131" t="s">
         <v>5</v>
       </c>
       <c r="E131" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F131" t="s">
-        <v>318</v>
+        <v>152</v>
       </c>
       <c r="G131" t="s">
         <v>7</v>
@@ -7460,22 +7510,22 @@
         <v>8</v>
       </c>
       <c r="I131" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="J131" t="s">
-        <v>454</v>
+        <v>444</v>
       </c>
       <c r="K131">
-        <v>69100</v>
+        <v>118290</v>
       </c>
       <c r="L131">
-        <v>155.555555555555</v>
+        <v>153.055555555555</v>
       </c>
       <c r="M131">
-        <v>5.9334298118668603E-2</v>
+        <v>0.166624397666751</v>
       </c>
       <c r="N131">
-        <v>4100</v>
+        <v>19710</v>
       </c>
     </row>
     <row r="132" spans="1:14">
@@ -7483,19 +7533,16 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="C132" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="D132" t="s">
         <v>5</v>
       </c>
-      <c r="E132" t="s">
-        <v>23</v>
-      </c>
       <c r="F132" t="s">
-        <v>156</v>
+        <v>315</v>
       </c>
       <c r="G132" t="s">
         <v>7</v>
@@ -7504,22 +7551,22 @@
         <v>8</v>
       </c>
       <c r="I132" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="J132" t="s">
-        <v>454</v>
+        <v>444</v>
       </c>
       <c r="K132">
-        <v>118290</v>
+        <v>79900</v>
       </c>
       <c r="L132">
-        <v>153.055555555555</v>
+        <v>155.555555555555</v>
       </c>
       <c r="M132">
-        <v>0.166624397666751</v>
+        <v>0.14313241551939901</v>
       </c>
       <c r="N132">
-        <v>19710</v>
+        <v>11436.280000000002</v>
       </c>
     </row>
     <row r="133" spans="1:14">
@@ -7527,16 +7574,16 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="C133" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="D133" t="s">
         <v>5</v>
       </c>
       <c r="F133" t="s">
-        <v>323</v>
+        <v>155</v>
       </c>
       <c r="G133" t="s">
         <v>7</v>
@@ -7545,22 +7592,22 @@
         <v>8</v>
       </c>
       <c r="I133" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="J133" t="s">
-        <v>454</v>
+        <v>444</v>
       </c>
       <c r="K133">
-        <v>79900</v>
+        <v>39742.379999999997</v>
       </c>
       <c r="L133">
-        <v>155.555555555555</v>
+        <v>133.472222222222</v>
       </c>
       <c r="M133">
-        <v>0.14313241551939901</v>
+        <v>0.14746550156281499</v>
       </c>
       <c r="N133">
-        <v>11436.280000000002</v>
+        <v>5860.63</v>
       </c>
     </row>
     <row r="134" spans="1:14">
@@ -7568,16 +7615,19 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="C134" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="D134" t="s">
         <v>5</v>
       </c>
+      <c r="E134" t="s">
+        <v>16</v>
+      </c>
       <c r="F134" t="s">
-        <v>159</v>
+        <v>86</v>
       </c>
       <c r="G134" t="s">
         <v>7</v>
@@ -7586,22 +7636,22 @@
         <v>8</v>
       </c>
       <c r="I134" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="J134" t="s">
-        <v>454</v>
+        <v>444</v>
       </c>
       <c r="K134">
-        <v>39742.379999999997</v>
+        <v>48000</v>
       </c>
       <c r="L134">
-        <v>133.472222222222</v>
+        <v>152.777777777778</v>
       </c>
       <c r="M134">
-        <v>0.14746550156281499</v>
+        <v>0.13894520833333299</v>
       </c>
       <c r="N134">
-        <v>5860.63</v>
+        <v>6669.369999999999</v>
       </c>
     </row>
     <row r="135" spans="1:14">
@@ -7609,19 +7659,16 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="C135" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="D135" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E135" t="s">
-        <v>16</v>
-      </c>
-      <c r="F135" t="s">
-        <v>86</v>
+        <v>23</v>
       </c>
       <c r="G135" t="s">
         <v>7</v>
@@ -7630,22 +7677,22 @@
         <v>8</v>
       </c>
       <c r="I135" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="J135" t="s">
-        <v>454</v>
+        <v>444</v>
       </c>
       <c r="K135">
-        <v>48000</v>
+        <v>74722</v>
       </c>
       <c r="L135">
-        <v>152.777777777778</v>
+        <v>159.444444444445</v>
       </c>
       <c r="M135">
-        <v>0.13894520833333299</v>
+        <v>0.431922325419555</v>
       </c>
       <c r="N135">
-        <v>6669.369999999999</v>
+        <v>32274.100000000002</v>
       </c>
     </row>
     <row r="136" spans="1:14">
@@ -7653,16 +7700,13 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C136" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="D136" t="s">
-        <v>14</v>
-      </c>
-      <c r="E136" t="s">
-        <v>23</v>
+        <v>201</v>
       </c>
       <c r="G136" t="s">
         <v>7</v>
@@ -7671,22 +7715,22 @@
         <v>8</v>
       </c>
       <c r="I136" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="J136" t="s">
-        <v>454</v>
+        <v>444</v>
       </c>
       <c r="K136">
-        <v>74722</v>
+        <v>55000</v>
       </c>
       <c r="L136">
-        <v>159.444444444445</v>
+        <v>120.555555555556</v>
       </c>
       <c r="M136">
-        <v>0.431922325419555</v>
+        <v>3.4563636363636401E-2</v>
       </c>
       <c r="N136">
-        <v>32274.100000000002</v>
+        <v>1901</v>
       </c>
     </row>
     <row r="137" spans="1:14">
@@ -7694,37 +7738,37 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="C137" t="s">
-        <v>303</v>
+        <v>326</v>
       </c>
       <c r="D137" t="s">
-        <v>207</v>
+        <v>5</v>
       </c>
       <c r="G137" t="s">
         <v>7</v>
       </c>
       <c r="H137" t="s">
-        <v>8</v>
+        <v>115</v>
       </c>
       <c r="I137" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="J137" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="K137">
-        <v>55000</v>
+        <v>128000</v>
       </c>
       <c r="L137">
-        <v>120.555555555556</v>
+        <v>197.083333333333</v>
       </c>
       <c r="M137">
-        <v>3.4563636363636401E-2</v>
+        <v>6.7101562500000003E-2</v>
       </c>
       <c r="N137">
-        <v>1901</v>
+        <v>6126</v>
       </c>
     </row>
     <row r="138" spans="1:14">
@@ -7732,37 +7776,43 @@
         <v>137</v>
       </c>
       <c r="B138" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="C138" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="D138" t="s">
         <v>5</v>
       </c>
+      <c r="E138" t="s">
+        <v>16</v>
+      </c>
+      <c r="F138" t="s">
+        <v>59</v>
+      </c>
       <c r="G138" t="s">
         <v>7</v>
       </c>
       <c r="H138" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I138" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="J138" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="K138">
-        <v>128000</v>
+        <v>122000</v>
       </c>
       <c r="L138">
-        <v>197.083333333333</v>
+        <v>195.555555555555</v>
       </c>
       <c r="M138">
-        <v>6.7101562500000003E-2</v>
+        <v>1.7885245901639299E-2</v>
       </c>
       <c r="N138">
-        <v>6126</v>
+        <v>2182</v>
       </c>
     </row>
     <row r="139" spans="1:14">
@@ -7770,43 +7820,40 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="C139" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="D139" t="s">
         <v>5</v>
       </c>
-      <c r="E139" t="s">
-        <v>16</v>
-      </c>
       <c r="F139" t="s">
-        <v>59</v>
+        <v>15</v>
       </c>
       <c r="G139" t="s">
         <v>7</v>
       </c>
       <c r="H139" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I139" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="J139" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="K139">
-        <v>122000</v>
+        <v>22000</v>
       </c>
       <c r="L139">
-        <v>195.555555555555</v>
+        <v>197.083333333333</v>
       </c>
       <c r="M139">
-        <v>1.7885245901639299E-2</v>
+        <v>0.20981818181818199</v>
       </c>
       <c r="N139">
-        <v>2182</v>
+        <v>4616</v>
       </c>
     </row>
     <row r="140" spans="1:14">
@@ -7814,10 +7861,10 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="C140" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="D140" t="s">
         <v>5</v>
@@ -7829,25 +7876,25 @@
         <v>7</v>
       </c>
       <c r="H140" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I140" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="J140" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="K140">
-        <v>22000</v>
+        <v>10000</v>
       </c>
       <c r="L140">
-        <v>197.083333333333</v>
+        <v>255</v>
       </c>
       <c r="M140">
-        <v>0.20981818181818199</v>
+        <v>0</v>
       </c>
       <c r="N140">
-        <v>4616</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141" spans="1:14">
@@ -7855,40 +7902,40 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="C141" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="D141" t="s">
         <v>5</v>
       </c>
       <c r="F141" t="s">
-        <v>15</v>
+        <v>56</v>
       </c>
       <c r="G141" t="s">
         <v>7</v>
       </c>
       <c r="H141" t="s">
-        <v>117</v>
+        <v>8</v>
       </c>
       <c r="I141" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="J141" t="s">
-        <v>467</v>
+        <v>442</v>
       </c>
       <c r="K141">
-        <v>10000</v>
+        <v>64000</v>
       </c>
       <c r="L141">
-        <v>255</v>
+        <v>177.777777777778</v>
       </c>
       <c r="M141">
-        <v>0</v>
+        <v>0.28125</v>
       </c>
       <c r="N141">
-        <v>0</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="142" spans="1:14">
@@ -7896,16 +7943,16 @@
         <v>141</v>
       </c>
       <c r="B142" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="C142" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="D142" t="s">
         <v>5</v>
       </c>
       <c r="F142" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="G142" t="s">
         <v>7</v>
@@ -7914,22 +7961,22 @@
         <v>8</v>
       </c>
       <c r="I142" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="J142" t="s">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="K142">
-        <v>64000</v>
+        <v>95628</v>
       </c>
       <c r="L142">
-        <v>177.777777777778</v>
+        <v>165</v>
       </c>
       <c r="M142">
-        <v>0.28125</v>
+        <v>0.247417074497009</v>
       </c>
       <c r="N142">
-        <v>18000</v>
+        <v>23660</v>
       </c>
     </row>
     <row r="143" spans="1:14">
@@ -7937,16 +7984,16 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="C143" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="D143" t="s">
         <v>5</v>
       </c>
       <c r="F143" t="s">
-        <v>65</v>
+        <v>339</v>
       </c>
       <c r="G143" t="s">
         <v>7</v>
@@ -7955,22 +8002,22 @@
         <v>8</v>
       </c>
       <c r="I143" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="J143" t="s">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="K143">
-        <v>95628</v>
+        <v>39562</v>
       </c>
       <c r="L143">
-        <v>165</v>
+        <v>151.111111111111</v>
       </c>
       <c r="M143">
-        <v>0.247417074497009</v>
+        <v>0.183913856731207</v>
       </c>
       <c r="N143">
-        <v>23660</v>
+        <v>7276</v>
       </c>
     </row>
     <row r="144" spans="1:14">
@@ -7978,16 +8025,19 @@
         <v>143</v>
       </c>
       <c r="B144" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="C144" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="D144" t="s">
         <v>5</v>
       </c>
+      <c r="E144" t="s">
+        <v>16</v>
+      </c>
       <c r="F144" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="G144" t="s">
         <v>7</v>
@@ -7996,42 +8046,42 @@
         <v>8</v>
       </c>
       <c r="I144" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="J144" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="K144">
-        <v>39562</v>
+        <v>105000</v>
       </c>
       <c r="L144">
-        <v>151.111111111111</v>
+        <v>155.555555555555</v>
       </c>
       <c r="M144">
-        <v>0.183913856731207</v>
+        <v>0.75</v>
       </c>
       <c r="N144">
-        <v>7276</v>
+        <v>78750</v>
       </c>
     </row>
     <row r="145" spans="1:14">
       <c r="A145">
         <v>144</v>
       </c>
-      <c r="B145" t="s">
-        <v>349</v>
+      <c r="B145" s="2" t="s">
+        <v>473</v>
       </c>
       <c r="C145" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="D145" t="s">
         <v>5</v>
       </c>
       <c r="E145" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F145" t="s">
-        <v>350</v>
+        <v>310</v>
       </c>
       <c r="G145" t="s">
         <v>7</v>
@@ -8039,43 +8089,40 @@
       <c r="H145" t="s">
         <v>8</v>
       </c>
-      <c r="I145" t="s">
-        <v>351</v>
+      <c r="I145" s="2" t="s">
+        <v>474</v>
       </c>
       <c r="J145" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="K145">
-        <v>105000</v>
+        <v>60000</v>
       </c>
       <c r="L145">
-        <v>155.555555555555</v>
+        <v>204.444444444445</v>
       </c>
       <c r="M145">
-        <v>0.75</v>
+        <v>0.66666666666666696</v>
       </c>
       <c r="N145">
-        <v>78750</v>
+        <v>40000</v>
       </c>
     </row>
     <row r="146" spans="1:14">
       <c r="A146">
         <v>145</v>
       </c>
-      <c r="B146" s="2" t="s">
-        <v>483</v>
+      <c r="B146" t="s">
+        <v>344</v>
       </c>
       <c r="C146" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="D146" t="s">
         <v>5</v>
       </c>
-      <c r="E146" t="s">
-        <v>23</v>
-      </c>
       <c r="F146" t="s">
-        <v>318</v>
+        <v>145</v>
       </c>
       <c r="G146" t="s">
         <v>7</v>
@@ -8083,23 +8130,23 @@
       <c r="H146" t="s">
         <v>8</v>
       </c>
-      <c r="I146" s="2" t="s">
-        <v>484</v>
+      <c r="I146" t="s">
+        <v>345</v>
       </c>
       <c r="J146" t="s">
-        <v>467</v>
+        <v>442</v>
       </c>
       <c r="K146">
-        <v>60000</v>
+        <v>39964</v>
       </c>
       <c r="L146">
-        <v>204.444444444445</v>
+        <v>275</v>
       </c>
       <c r="M146">
-        <v>0.66666666666666696</v>
+        <v>3.2529276348713901E-2</v>
       </c>
       <c r="N146">
-        <v>40000</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="147" spans="1:14">
@@ -8107,16 +8154,16 @@
         <v>146</v>
       </c>
       <c r="B147" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="C147" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="D147" t="s">
         <v>5</v>
       </c>
       <c r="F147" t="s">
-        <v>149</v>
+        <v>19</v>
       </c>
       <c r="G147" t="s">
         <v>7</v>
@@ -8125,39 +8172,42 @@
         <v>8</v>
       </c>
       <c r="I147" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="J147" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="K147">
-        <v>39964</v>
+        <v>94000</v>
       </c>
       <c r="L147">
-        <v>275</v>
+        <v>257.777777777778</v>
       </c>
       <c r="M147">
-        <v>3.2529276348713901E-2</v>
+        <v>0.12765957446808501</v>
       </c>
       <c r="N147">
-        <v>1300</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="148" spans="1:14">
       <c r="A148">
         <v>147</v>
       </c>
-      <c r="B148" t="s">
-        <v>354</v>
+      <c r="B148" s="2" t="s">
+        <v>472</v>
       </c>
       <c r="C148" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="D148" t="s">
         <v>5</v>
       </c>
+      <c r="E148" t="s">
+        <v>23</v>
+      </c>
       <c r="F148" t="s">
-        <v>19</v>
+        <v>149</v>
       </c>
       <c r="G148" t="s">
         <v>7</v>
@@ -8165,23 +8215,23 @@
       <c r="H148" t="s">
         <v>8</v>
       </c>
-      <c r="I148" t="s">
-        <v>355</v>
+      <c r="I148" s="2" t="s">
+        <v>475</v>
       </c>
       <c r="J148" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="K148">
-        <v>94000</v>
+        <v>75000</v>
       </c>
       <c r="L148">
-        <v>257.777777777778</v>
+        <v>166.666666666667</v>
       </c>
       <c r="M148">
-        <v>0.12765957446808501</v>
+        <v>0.41537333333333298</v>
       </c>
       <c r="N148">
-        <v>12000</v>
+        <v>31153</v>
       </c>
     </row>
     <row r="149" spans="1:14">
@@ -8189,84 +8239,84 @@
         <v>148</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>482</v>
+        <v>177</v>
       </c>
       <c r="C149" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="D149" t="s">
         <v>5</v>
       </c>
-      <c r="E149" t="s">
-        <v>23</v>
-      </c>
       <c r="F149" t="s">
-        <v>153</v>
+        <v>348</v>
       </c>
       <c r="G149" t="s">
         <v>7</v>
       </c>
       <c r="H149" t="s">
-        <v>8</v>
+        <v>87</v>
       </c>
       <c r="I149" s="2" t="s">
-        <v>485</v>
+        <v>471</v>
       </c>
       <c r="J149" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="K149">
-        <v>75000</v>
+        <v>48767</v>
       </c>
       <c r="L149">
-        <v>166.666666666667</v>
+        <v>311.66666666666703</v>
       </c>
       <c r="M149">
-        <v>0.41537333333333298</v>
+        <v>1.00477782106753E-2</v>
       </c>
       <c r="N149">
-        <v>31153</v>
+        <v>490</v>
       </c>
     </row>
     <row r="150" spans="1:14">
       <c r="A150">
         <v>149</v>
       </c>
-      <c r="B150" s="2" t="s">
-        <v>183</v>
+      <c r="B150" t="s">
+        <v>349</v>
       </c>
       <c r="C150" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="D150" t="s">
         <v>5</v>
       </c>
+      <c r="E150" t="s">
+        <v>16</v>
+      </c>
       <c r="F150" t="s">
-        <v>356</v>
+        <v>86</v>
       </c>
       <c r="G150" t="s">
         <v>7</v>
       </c>
       <c r="H150" t="s">
-        <v>87</v>
-      </c>
-      <c r="I150" s="2" t="s">
-        <v>481</v>
+        <v>8</v>
+      </c>
+      <c r="I150" t="s">
+        <v>350</v>
       </c>
       <c r="J150" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="K150">
-        <v>48767</v>
+        <v>63824</v>
       </c>
       <c r="L150">
-        <v>311.66666666666703</v>
+        <v>223.888888888889</v>
       </c>
       <c r="M150">
-        <v>1.00477782106753E-2</v>
+        <v>0.144663449486087</v>
       </c>
       <c r="N150">
-        <v>490</v>
+        <v>9233</v>
       </c>
     </row>
     <row r="151" spans="1:14">
@@ -8274,19 +8324,19 @@
         <v>150</v>
       </c>
       <c r="B151" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="C151" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="D151" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E151" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F151" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G151" t="s">
         <v>7</v>
@@ -8295,22 +8345,22 @@
         <v>8</v>
       </c>
       <c r="I151" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="J151" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="K151">
-        <v>63824</v>
+        <v>117000</v>
       </c>
       <c r="L151">
-        <v>223.888888888889</v>
+        <v>311.66666666666703</v>
       </c>
       <c r="M151">
-        <v>0.144663449486087</v>
+        <v>0</v>
       </c>
       <c r="N151">
-        <v>9233</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152" spans="1:14">
@@ -8318,19 +8368,13 @@
         <v>151</v>
       </c>
       <c r="B152" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="C152" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="D152" t="s">
-        <v>14</v>
-      </c>
-      <c r="E152" t="s">
-        <v>23</v>
-      </c>
-      <c r="F152" t="s">
-        <v>90</v>
+        <v>5</v>
       </c>
       <c r="G152" t="s">
         <v>7</v>
@@ -8339,22 +8383,22 @@
         <v>8</v>
       </c>
       <c r="I152" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="J152" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="K152">
-        <v>117000</v>
+        <v>41000</v>
       </c>
       <c r="L152">
-        <v>311.66666666666703</v>
+        <v>204.444444444445</v>
       </c>
       <c r="M152">
-        <v>0</v>
+        <v>0.11219512195122</v>
       </c>
       <c r="N152">
-        <v>0</v>
+        <v>4600</v>
       </c>
     </row>
     <row r="153" spans="1:14">
@@ -8362,10 +8406,10 @@
         <v>152</v>
       </c>
       <c r="B153" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="C153" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="D153" t="s">
         <v>5</v>
@@ -8377,22 +8421,22 @@
         <v>8</v>
       </c>
       <c r="I153" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="J153" t="s">
-        <v>467</v>
+        <v>442</v>
       </c>
       <c r="K153">
-        <v>41000</v>
+        <v>96446</v>
       </c>
       <c r="L153">
-        <v>204.444444444445</v>
+        <v>284.16666666666703</v>
       </c>
       <c r="M153">
-        <v>0.11219512195122</v>
+        <v>0.334902432449246</v>
       </c>
       <c r="N153">
-        <v>4600</v>
+        <v>32300</v>
       </c>
     </row>
     <row r="154" spans="1:14">
@@ -8400,37 +8444,43 @@
         <v>153</v>
       </c>
       <c r="B154" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="C154" t="s">
-        <v>334</v>
+        <v>358</v>
       </c>
       <c r="D154" t="s">
         <v>5</v>
       </c>
+      <c r="E154" t="s">
+        <v>16</v>
+      </c>
+      <c r="F154" t="s">
+        <v>155</v>
+      </c>
       <c r="G154" t="s">
         <v>7</v>
       </c>
       <c r="H154" t="s">
-        <v>8</v>
+        <v>359</v>
       </c>
       <c r="I154" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="J154" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="K154">
-        <v>96446</v>
+        <v>76600</v>
       </c>
       <c r="L154">
-        <v>284.16666666666703</v>
+        <v>131.111111111111</v>
       </c>
       <c r="M154">
-        <v>0.334902432449246</v>
+        <v>0.241919060052219</v>
       </c>
       <c r="N154">
-        <v>32300</v>
+        <v>18531</v>
       </c>
     </row>
     <row r="155" spans="1:14">
@@ -8438,43 +8488,40 @@
         <v>154</v>
       </c>
       <c r="B155" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="C155" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="D155" t="s">
         <v>5</v>
       </c>
-      <c r="E155" t="s">
-        <v>16</v>
-      </c>
       <c r="F155" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="G155" t="s">
         <v>7</v>
       </c>
       <c r="H155" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="I155" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="J155" t="s">
-        <v>467</v>
+        <v>445</v>
       </c>
       <c r="K155">
-        <v>76600</v>
+        <v>125569</v>
       </c>
       <c r="L155">
-        <v>131.111111111111</v>
+        <v>137.5</v>
       </c>
       <c r="M155">
-        <v>0.241919060052219</v>
+        <v>0.25245084375920801</v>
       </c>
       <c r="N155">
-        <v>18531</v>
+        <v>31700</v>
       </c>
     </row>
     <row r="156" spans="1:14">
@@ -8482,40 +8529,40 @@
         <v>155</v>
       </c>
       <c r="B156" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="C156" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="D156" t="s">
         <v>5</v>
       </c>
       <c r="F156" t="s">
-        <v>159</v>
+        <v>364</v>
       </c>
       <c r="G156" t="s">
         <v>7</v>
       </c>
       <c r="H156" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="I156" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="J156" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="K156">
-        <v>125569</v>
+        <v>51234</v>
       </c>
       <c r="L156">
-        <v>137.5</v>
+        <v>120.555555555556</v>
       </c>
       <c r="M156">
-        <v>0.25245084375920801</v>
+        <v>7.9868837100362994E-2</v>
       </c>
       <c r="N156">
-        <v>31700</v>
+        <v>4092</v>
       </c>
     </row>
     <row r="157" spans="1:14">
@@ -8523,40 +8570,43 @@
         <v>156</v>
       </c>
       <c r="B157" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="C157" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="D157" t="s">
         <v>5</v>
       </c>
+      <c r="E157" t="s">
+        <v>16</v>
+      </c>
       <c r="F157" t="s">
-        <v>372</v>
+        <v>90</v>
       </c>
       <c r="G157" t="s">
         <v>7</v>
       </c>
       <c r="H157" t="s">
+        <v>359</v>
+      </c>
+      <c r="I157" t="s">
         <v>367</v>
       </c>
-      <c r="I157" t="s">
-        <v>373</v>
-      </c>
       <c r="J157" t="s">
-        <v>467</v>
+        <v>445</v>
       </c>
       <c r="K157">
-        <v>51234</v>
+        <v>123780</v>
       </c>
       <c r="L157">
-        <v>120.555555555556</v>
+        <v>123.75</v>
       </c>
       <c r="M157">
-        <v>7.9868837100362994E-2</v>
+        <v>0.12417999676846</v>
       </c>
       <c r="N157">
-        <v>4092</v>
+        <v>15371</v>
       </c>
     </row>
     <row r="158" spans="1:14">
@@ -8564,43 +8614,40 @@
         <v>157</v>
       </c>
       <c r="B158" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="C158" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="D158" t="s">
         <v>5</v>
       </c>
-      <c r="E158" t="s">
-        <v>16</v>
-      </c>
       <c r="F158" t="s">
-        <v>90</v>
+        <v>369</v>
       </c>
       <c r="G158" t="s">
         <v>7</v>
       </c>
       <c r="H158" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="I158" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="J158" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="K158">
-        <v>123780</v>
+        <v>46000</v>
       </c>
       <c r="L158">
-        <v>123.75</v>
+        <v>185</v>
       </c>
       <c r="M158">
-        <v>0.12417999676846</v>
+        <v>0</v>
       </c>
       <c r="N158">
-        <v>15371</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159" spans="1:14">
@@ -8608,40 +8655,37 @@
         <v>158</v>
       </c>
       <c r="B159" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="C159" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="D159" t="s">
         <v>5</v>
       </c>
-      <c r="F159" t="s">
-        <v>377</v>
-      </c>
       <c r="G159" t="s">
         <v>7</v>
       </c>
       <c r="H159" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="I159" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="J159" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="K159">
-        <v>46000</v>
+        <v>35600</v>
       </c>
       <c r="L159">
-        <v>185</v>
+        <v>146.388888888889</v>
       </c>
       <c r="M159">
-        <v>0</v>
+        <v>0.12019662921348299</v>
       </c>
       <c r="N159">
-        <v>0</v>
+        <v>4279</v>
       </c>
     </row>
     <row r="160" spans="1:14">
@@ -8649,37 +8693,40 @@
         <v>159</v>
       </c>
       <c r="B160" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="C160" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="D160" t="s">
         <v>5</v>
       </c>
+      <c r="E160" t="s">
+        <v>23</v>
+      </c>
       <c r="G160" t="s">
         <v>7</v>
       </c>
       <c r="H160" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="I160" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="J160" t="s">
-        <v>467</v>
+        <v>445</v>
       </c>
       <c r="K160">
-        <v>35600</v>
+        <v>199950</v>
       </c>
       <c r="L160">
-        <v>146.388888888889</v>
+        <v>145</v>
       </c>
       <c r="M160">
-        <v>0.12019662921348299</v>
+        <v>0.150037509377344</v>
       </c>
       <c r="N160">
-        <v>4279</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="161" spans="1:14">
@@ -8687,40 +8734,40 @@
         <v>160</v>
       </c>
       <c r="B161" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="C161" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="D161" t="s">
         <v>5</v>
       </c>
       <c r="E161" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="G161" t="s">
         <v>7</v>
       </c>
       <c r="H161" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="I161" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="J161" t="s">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="K161">
-        <v>199950</v>
+        <v>108000</v>
       </c>
       <c r="L161">
-        <v>145</v>
+        <v>137.777777777778</v>
       </c>
       <c r="M161">
-        <v>0.150037509377344</v>
+        <v>0.18</v>
       </c>
       <c r="N161">
-        <v>30000</v>
+        <v>19440</v>
       </c>
     </row>
     <row r="162" spans="1:14">
@@ -8728,10 +8775,10 @@
         <v>161</v>
       </c>
       <c r="B162" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="C162" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="D162" t="s">
         <v>5</v>
@@ -8743,25 +8790,25 @@
         <v>7</v>
       </c>
       <c r="H162" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="I162" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="J162" t="s">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="K162">
-        <v>108000</v>
+        <v>142808</v>
       </c>
       <c r="L162">
-        <v>137.777777777778</v>
+        <v>127.5</v>
       </c>
       <c r="M162">
-        <v>0.18</v>
+        <v>7.1186488151924299E-2</v>
       </c>
       <c r="N162">
-        <v>19440</v>
+        <v>10166</v>
       </c>
     </row>
     <row r="163" spans="1:14">
@@ -8769,10 +8816,10 @@
         <v>162</v>
       </c>
       <c r="B163" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="C163" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="D163" t="s">
         <v>5</v>
@@ -8784,25 +8831,25 @@
         <v>7</v>
       </c>
       <c r="H163" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="I163" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="J163" t="s">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="K163">
-        <v>142808</v>
+        <v>80463</v>
       </c>
       <c r="L163">
-        <v>127.5</v>
+        <v>125</v>
       </c>
       <c r="M163">
-        <v>7.1186488151924299E-2</v>
+        <v>0.112026645787505</v>
       </c>
       <c r="N163">
-        <v>10166</v>
+        <v>9014</v>
       </c>
     </row>
     <row r="164" spans="1:14">
@@ -8810,40 +8857,40 @@
         <v>163</v>
       </c>
       <c r="B164" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="C164" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="D164" t="s">
         <v>5</v>
       </c>
       <c r="E164" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G164" t="s">
         <v>7</v>
       </c>
       <c r="H164" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="I164" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="J164" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="K164">
-        <v>80463</v>
+        <v>83000</v>
       </c>
       <c r="L164">
-        <v>125</v>
+        <v>141.666666666667</v>
       </c>
       <c r="M164">
-        <v>0.112026645787505</v>
+        <v>0.60361445783132495</v>
       </c>
       <c r="N164">
-        <v>9014</v>
+        <v>50100</v>
       </c>
     </row>
     <row r="165" spans="1:14">
@@ -8851,40 +8898,37 @@
         <v>164</v>
       </c>
       <c r="B165" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="C165" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="D165" t="s">
         <v>5</v>
       </c>
-      <c r="E165" t="s">
-        <v>23</v>
-      </c>
       <c r="G165" t="s">
         <v>7</v>
       </c>
       <c r="H165" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="I165" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="J165" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="K165">
-        <v>83000</v>
+        <v>129000</v>
       </c>
       <c r="L165">
-        <v>141.666666666667</v>
+        <v>169.166666666667</v>
       </c>
       <c r="M165">
-        <v>0.60361445783132495</v>
+        <v>0.39693023255813897</v>
       </c>
       <c r="N165">
-        <v>50100</v>
+        <v>51204</v>
       </c>
     </row>
     <row r="166" spans="1:14">
@@ -8892,37 +8936,40 @@
         <v>165</v>
       </c>
       <c r="B166" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="C166" t="s">
-        <v>366</v>
+        <v>386</v>
       </c>
       <c r="D166" t="s">
         <v>5</v>
       </c>
+      <c r="F166" t="s">
+        <v>219</v>
+      </c>
       <c r="G166" t="s">
         <v>7</v>
       </c>
       <c r="H166" t="s">
-        <v>367</v>
+        <v>115</v>
       </c>
       <c r="I166" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="J166" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="K166">
-        <v>129000</v>
+        <v>62209</v>
       </c>
       <c r="L166">
-        <v>169.166666666667</v>
+        <v>128.888888888889</v>
       </c>
       <c r="M166">
-        <v>0.39693023255813897</v>
+        <v>0.13806683920333099</v>
       </c>
       <c r="N166">
-        <v>51204</v>
+        <v>8589</v>
       </c>
     </row>
     <row r="167" spans="1:14">
@@ -8930,40 +8977,40 @@
         <v>166</v>
       </c>
       <c r="B167" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="C167" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="D167" t="s">
         <v>5</v>
       </c>
       <c r="F167" t="s">
-        <v>225</v>
+        <v>303</v>
       </c>
       <c r="G167" t="s">
         <v>7</v>
       </c>
       <c r="H167" t="s">
-        <v>117</v>
+        <v>8</v>
       </c>
       <c r="I167" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="J167" t="s">
-        <v>467</v>
+        <v>442</v>
       </c>
       <c r="K167">
-        <v>62209</v>
+        <v>36117</v>
       </c>
       <c r="L167">
-        <v>128.888888888889</v>
+        <v>142.083333333333</v>
       </c>
       <c r="M167">
-        <v>0.13806683920333099</v>
+        <v>0.248276434919844</v>
       </c>
       <c r="N167">
-        <v>8589</v>
+        <v>8967</v>
       </c>
     </row>
     <row r="168" spans="1:14">
@@ -8971,40 +9018,43 @@
         <v>167</v>
       </c>
       <c r="B168" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="C168" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="D168" t="s">
         <v>5</v>
       </c>
+      <c r="E168" t="s">
+        <v>23</v>
+      </c>
       <c r="F168" t="s">
-        <v>311</v>
+        <v>155</v>
       </c>
       <c r="G168" t="s">
         <v>7</v>
       </c>
       <c r="H168" t="s">
-        <v>8</v>
+        <v>87</v>
       </c>
       <c r="I168" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="J168" t="s">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="K168">
-        <v>36117</v>
+        <v>49900</v>
       </c>
       <c r="L168">
-        <v>142.083333333333</v>
+        <v>242.916666666667</v>
       </c>
       <c r="M168">
-        <v>0.248276434919844</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="N168">
-        <v>8967</v>
+        <v>3493</v>
       </c>
     </row>
     <row r="169" spans="1:14">
@@ -9012,19 +9062,19 @@
         <v>168</v>
       </c>
       <c r="B169" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="C169" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="D169" t="s">
         <v>5</v>
       </c>
       <c r="E169" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F169" t="s">
-        <v>159</v>
+        <v>393</v>
       </c>
       <c r="G169" t="s">
         <v>7</v>
@@ -9033,22 +9083,22 @@
         <v>87</v>
       </c>
       <c r="I169" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="J169" t="s">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="K169">
-        <v>49900</v>
+        <v>39000</v>
       </c>
       <c r="L169">
-        <v>242.916666666667</v>
+        <v>244.444444444445</v>
       </c>
       <c r="M169">
-        <v>7.0000000000000007E-2</v>
+        <v>0.43589743589743601</v>
       </c>
       <c r="N169">
-        <v>3493</v>
+        <v>17000</v>
       </c>
     </row>
     <row r="170" spans="1:14">
@@ -9056,43 +9106,40 @@
         <v>169</v>
       </c>
       <c r="B170" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="C170" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="D170" t="s">
         <v>5</v>
       </c>
-      <c r="E170" t="s">
-        <v>16</v>
-      </c>
       <c r="F170" t="s">
-        <v>401</v>
+        <v>364</v>
       </c>
       <c r="G170" t="s">
         <v>7</v>
       </c>
       <c r="H170" t="s">
-        <v>87</v>
+        <v>199</v>
       </c>
       <c r="I170" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="J170" t="s">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="K170">
-        <v>39000</v>
+        <v>49000</v>
       </c>
       <c r="L170">
-        <v>244.444444444445</v>
+        <v>235</v>
       </c>
       <c r="M170">
-        <v>0.43589743589743601</v>
+        <v>2.7142857142857101E-2</v>
       </c>
       <c r="N170">
-        <v>17000</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="171" spans="1:14">
@@ -9100,40 +9147,37 @@
         <v>170</v>
       </c>
       <c r="B171" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="C171" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="D171" t="s">
-        <v>5</v>
-      </c>
-      <c r="F171" t="s">
-        <v>372</v>
+        <v>201</v>
       </c>
       <c r="G171" t="s">
         <v>7</v>
       </c>
       <c r="H171" t="s">
-        <v>205</v>
+        <v>8</v>
       </c>
       <c r="I171" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="J171" t="s">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="K171">
-        <v>49000</v>
+        <v>59400</v>
       </c>
       <c r="L171">
-        <v>235</v>
+        <v>160</v>
       </c>
       <c r="M171">
-        <v>2.7142857142857101E-2</v>
+        <v>0.303686868686869</v>
       </c>
       <c r="N171">
-        <v>1330</v>
+        <v>18039</v>
       </c>
     </row>
     <row r="172" spans="1:14">
@@ -9141,13 +9185,16 @@
         <v>171</v>
       </c>
       <c r="B172" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="C172" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="D172" t="s">
-        <v>207</v>
+        <v>5</v>
+      </c>
+      <c r="E172" t="s">
+        <v>16</v>
       </c>
       <c r="G172" t="s">
         <v>7</v>
@@ -9156,22 +9203,22 @@
         <v>8</v>
       </c>
       <c r="I172" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="J172" t="s">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="K172">
-        <v>59400</v>
+        <v>65000</v>
       </c>
       <c r="L172">
         <v>160</v>
       </c>
       <c r="M172">
-        <v>0.303686868686869</v>
+        <v>0.161953846153846</v>
       </c>
       <c r="N172">
-        <v>18039</v>
+        <v>10527</v>
       </c>
     </row>
     <row r="173" spans="1:14">
@@ -9179,40 +9226,43 @@
         <v>172</v>
       </c>
       <c r="B173" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="C173" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="D173" t="s">
         <v>5</v>
       </c>
       <c r="E173" t="s">
-        <v>16</v>
+        <v>403</v>
+      </c>
+      <c r="F173" t="s">
+        <v>402</v>
       </c>
       <c r="G173" t="s">
         <v>7</v>
       </c>
       <c r="H173" t="s">
-        <v>8</v>
+        <v>404</v>
       </c>
       <c r="I173" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="J173" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="K173">
-        <v>65000</v>
+        <v>47000</v>
       </c>
       <c r="L173">
-        <v>160</v>
+        <v>87.0833333333333</v>
       </c>
       <c r="M173">
-        <v>0.161953846153846</v>
+        <v>0.05</v>
       </c>
       <c r="N173">
-        <v>10527</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="174" spans="1:14">
@@ -9220,43 +9270,40 @@
         <v>173</v>
       </c>
       <c r="B174" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="C174" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="D174" t="s">
         <v>5</v>
       </c>
       <c r="E174" t="s">
-        <v>411</v>
-      </c>
-      <c r="F174" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="G174" t="s">
         <v>7</v>
       </c>
       <c r="H174" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="I174" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="J174" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="K174">
-        <v>47000</v>
+        <v>29000</v>
       </c>
       <c r="L174">
         <v>87.0833333333333</v>
       </c>
       <c r="M174">
-        <v>0.05</v>
+        <v>0.12</v>
       </c>
       <c r="N174">
-        <v>2350</v>
+        <v>3480</v>
       </c>
     </row>
     <row r="175" spans="1:14">
@@ -9264,40 +9311,43 @@
         <v>174</v>
       </c>
       <c r="B175" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="C175" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="D175" t="s">
         <v>5</v>
       </c>
       <c r="E175" t="s">
-        <v>411</v>
+        <v>23</v>
+      </c>
+      <c r="F175" t="s">
+        <v>104</v>
       </c>
       <c r="G175" t="s">
         <v>7</v>
       </c>
       <c r="H175" t="s">
-        <v>412</v>
+        <v>87</v>
       </c>
       <c r="I175" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="J175" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="K175">
-        <v>29000</v>
+        <v>132239</v>
       </c>
       <c r="L175">
         <v>87.0833333333333</v>
       </c>
       <c r="M175">
-        <v>0.12</v>
+        <v>0.21929990396176599</v>
       </c>
       <c r="N175">
-        <v>3480</v>
+        <v>29000</v>
       </c>
     </row>
     <row r="176" spans="1:14">
@@ -9305,43 +9355,40 @@
         <v>175</v>
       </c>
       <c r="B176" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="C176" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="D176" t="s">
         <v>5</v>
       </c>
       <c r="E176" t="s">
-        <v>23</v>
-      </c>
-      <c r="F176" t="s">
-        <v>106</v>
+        <v>16</v>
       </c>
       <c r="G176" t="s">
         <v>7</v>
       </c>
       <c r="H176" t="s">
-        <v>87</v>
+        <v>404</v>
       </c>
       <c r="I176" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="J176" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="K176">
-        <v>132239</v>
+        <v>35016</v>
       </c>
       <c r="L176">
-        <v>87.0833333333333</v>
+        <v>75.5555555555556</v>
       </c>
       <c r="M176">
-        <v>0.21929990396176599</v>
+        <v>1</v>
       </c>
       <c r="N176">
-        <v>29000</v>
+        <v>35016</v>
       </c>
     </row>
     <row r="177" spans="1:14">
@@ -9349,40 +9396,37 @@
         <v>176</v>
       </c>
       <c r="B177" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="C177" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="D177" t="s">
         <v>5</v>
       </c>
-      <c r="E177" t="s">
-        <v>16</v>
-      </c>
       <c r="G177" t="s">
         <v>7</v>
       </c>
       <c r="H177" t="s">
-        <v>412</v>
+        <v>87</v>
       </c>
       <c r="I177" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="J177" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="K177">
-        <v>35016</v>
+        <v>60000</v>
       </c>
       <c r="L177">
-        <v>75.5555555555556</v>
+        <v>220</v>
       </c>
       <c r="M177">
-        <v>1</v>
+        <v>0.14026666666666701</v>
       </c>
       <c r="N177">
-        <v>35016</v>
+        <v>8416</v>
       </c>
     </row>
     <row r="178" spans="1:14">
@@ -9390,37 +9434,40 @@
         <v>177</v>
       </c>
       <c r="B178" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="C178" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="D178" t="s">
         <v>5</v>
       </c>
+      <c r="F178" t="s">
+        <v>415</v>
+      </c>
       <c r="G178" t="s">
         <v>7</v>
       </c>
       <c r="H178" t="s">
-        <v>87</v>
+        <v>359</v>
       </c>
       <c r="I178" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="J178" t="s">
-        <v>467</v>
+        <v>442</v>
       </c>
       <c r="K178">
-        <v>60000</v>
+        <v>90244</v>
       </c>
       <c r="L178">
-        <v>220</v>
+        <v>108.75</v>
       </c>
       <c r="M178">
-        <v>0.14026666666666701</v>
+        <v>0.155134967421657</v>
       </c>
       <c r="N178">
-        <v>8416</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="179" spans="1:14">
@@ -9428,40 +9475,37 @@
         <v>178</v>
       </c>
       <c r="B179" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="C179" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="D179" t="s">
         <v>5</v>
       </c>
-      <c r="F179" t="s">
-        <v>423</v>
-      </c>
       <c r="G179" t="s">
         <v>7</v>
       </c>
       <c r="H179" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="I179" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="J179" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="K179">
-        <v>90244</v>
+        <v>38700</v>
       </c>
       <c r="L179">
-        <v>108.75</v>
+        <v>97.7777777777778</v>
       </c>
       <c r="M179">
-        <v>0.155134967421657</v>
+        <v>0.59204134366925099</v>
       </c>
       <c r="N179">
-        <v>14000</v>
+        <v>22912</v>
       </c>
     </row>
     <row r="180" spans="1:14">
@@ -9469,10 +9513,10 @@
         <v>179</v>
       </c>
       <c r="B180" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="C180" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="D180" t="s">
         <v>5</v>
@@ -9481,25 +9525,25 @@
         <v>7</v>
       </c>
       <c r="H180" t="s">
-        <v>367</v>
-      </c>
-      <c r="I180" t="s">
-        <v>426</v>
+        <v>359</v>
+      </c>
+      <c r="I180" s="1" t="s">
+        <v>487</v>
       </c>
       <c r="J180" t="s">
-        <v>467</v>
+        <v>458</v>
       </c>
       <c r="K180">
-        <v>38700</v>
+        <v>62414</v>
       </c>
       <c r="L180">
-        <v>97.7777777777778</v>
+        <v>215.416666666667</v>
       </c>
       <c r="M180">
-        <v>0.59204134366925099</v>
+        <v>0.253148332104976</v>
       </c>
       <c r="N180">
-        <v>22912</v>
+        <v>15800</v>
       </c>
     </row>
     <row r="181" spans="1:14">
@@ -9507,10 +9551,10 @@
         <v>180</v>
       </c>
       <c r="B181" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="C181" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="D181" t="s">
         <v>5</v>
@@ -9519,25 +9563,25 @@
         <v>7</v>
       </c>
       <c r="H181" t="s">
-        <v>367</v>
+        <v>404</v>
       </c>
       <c r="I181" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="J181" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="K181">
-        <v>62414</v>
+        <v>51000</v>
       </c>
       <c r="L181">
-        <v>215.416666666667</v>
+        <v>75.5555555555556</v>
       </c>
       <c r="M181">
-        <v>0.253148332104976</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="N181">
-        <v>15800</v>
+        <v>28050</v>
       </c>
     </row>
     <row r="182" spans="1:14">
@@ -9545,37 +9589,40 @@
         <v>181</v>
       </c>
       <c r="B182" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="C182" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="D182" t="s">
         <v>5</v>
       </c>
+      <c r="E182" t="s">
+        <v>16</v>
+      </c>
       <c r="G182" t="s">
         <v>7</v>
       </c>
       <c r="H182" t="s">
-        <v>412</v>
+        <v>87</v>
       </c>
       <c r="I182" t="s">
-        <v>430</v>
+        <v>423</v>
       </c>
       <c r="J182" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="K182">
-        <v>51000</v>
+        <v>53115</v>
       </c>
       <c r="L182">
-        <v>75.5555555555556</v>
+        <v>301.38888888888903</v>
       </c>
       <c r="M182">
-        <v>0.55000000000000004</v>
+        <v>0.135554927986445</v>
       </c>
       <c r="N182">
-        <v>28050</v>
+        <v>7200</v>
       </c>
     </row>
     <row r="183" spans="1:14">
@@ -9583,78 +9630,78 @@
         <v>182</v>
       </c>
       <c r="B183" t="s">
-        <v>431</v>
+        <v>424</v>
       </c>
       <c r="C183" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="D183" t="s">
         <v>5</v>
       </c>
-      <c r="E183" t="s">
-        <v>16</v>
-      </c>
       <c r="G183" t="s">
         <v>7</v>
       </c>
       <c r="H183" t="s">
-        <v>87</v>
+        <v>359</v>
       </c>
       <c r="I183" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
       <c r="J183" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="K183">
-        <v>53115</v>
+        <v>120000</v>
       </c>
       <c r="L183">
-        <v>301.38888888888903</v>
+        <v>128.333333333333</v>
       </c>
       <c r="M183">
-        <v>0.135554927986445</v>
+        <v>0.18333333333333299</v>
       </c>
       <c r="N183">
-        <v>7200</v>
+        <v>22000</v>
       </c>
     </row>
     <row r="184" spans="1:14">
       <c r="A184">
         <v>183</v>
       </c>
-      <c r="B184" t="s">
-        <v>433</v>
+      <c r="B184" s="3" t="s">
+        <v>426</v>
       </c>
       <c r="C184" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="D184" t="s">
         <v>5</v>
       </c>
+      <c r="E184" t="s">
+        <v>16</v>
+      </c>
       <c r="G184" t="s">
         <v>7</v>
       </c>
       <c r="H184" t="s">
-        <v>367</v>
-      </c>
-      <c r="I184" t="s">
-        <v>434</v>
+        <v>87</v>
+      </c>
+      <c r="I184" s="3" t="s">
+        <v>486</v>
       </c>
       <c r="J184" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="K184">
-        <v>120000</v>
+        <v>66477</v>
       </c>
       <c r="L184">
-        <v>128.333333333333</v>
+        <v>265.83333333333297</v>
       </c>
       <c r="M184">
-        <v>0.18333333333333299</v>
+        <v>0.90974321945936198</v>
       </c>
       <c r="N184">
-        <v>22000</v>
+        <v>60477</v>
       </c>
     </row>
     <row r="185" spans="1:14">
@@ -9662,10 +9709,10 @@
         <v>184</v>
       </c>
       <c r="B185" t="s">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="C185" t="s">
-        <v>394</v>
+        <v>428</v>
       </c>
       <c r="D185" t="s">
         <v>5</v>
@@ -9677,25 +9724,22 @@
         <v>7</v>
       </c>
       <c r="H185" t="s">
-        <v>87</v>
+        <v>429</v>
       </c>
       <c r="I185" t="s">
-        <v>436</v>
-      </c>
-      <c r="J185" t="s">
-        <v>467</v>
+        <v>430</v>
       </c>
       <c r="K185">
-        <v>66477</v>
+        <v>59300</v>
       </c>
       <c r="L185">
-        <v>265.83333333333297</v>
+        <v>86.1111111111111</v>
       </c>
       <c r="M185">
-        <v>0.90974321945936198</v>
+        <v>0.79089376053962901</v>
       </c>
       <c r="N185">
-        <v>60477</v>
+        <v>46900</v>
       </c>
     </row>
     <row r="186" spans="1:14">
@@ -9703,37 +9747,34 @@
         <v>185</v>
       </c>
       <c r="B186" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="C186" t="s">
-        <v>438</v>
+        <v>428</v>
       </c>
       <c r="D186" t="s">
         <v>5</v>
       </c>
-      <c r="E186" t="s">
-        <v>16</v>
-      </c>
       <c r="G186" t="s">
         <v>7</v>
       </c>
       <c r="H186" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
       <c r="I186" t="s">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="K186">
-        <v>59300</v>
+        <v>44000</v>
       </c>
       <c r="L186">
-        <v>86.1111111111111</v>
+        <v>80</v>
       </c>
       <c r="M186">
-        <v>0.79089376053962901</v>
+        <v>0.45</v>
       </c>
       <c r="N186">
-        <v>46900</v>
+        <v>19800</v>
       </c>
     </row>
     <row r="187" spans="1:14">
@@ -9741,10 +9782,10 @@
         <v>186</v>
       </c>
       <c r="B187" t="s">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="C187" t="s">
-        <v>438</v>
+        <v>428</v>
       </c>
       <c r="D187" t="s">
         <v>5</v>
@@ -9753,22 +9794,22 @@
         <v>7</v>
       </c>
       <c r="H187" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
       <c r="I187" t="s">
-        <v>442</v>
+        <v>434</v>
       </c>
       <c r="K187">
-        <v>44000</v>
+        <v>26528</v>
       </c>
       <c r="L187">
-        <v>80</v>
+        <v>84.3333333333333</v>
       </c>
       <c r="M187">
-        <v>0.45</v>
+        <v>0.331724969843185</v>
       </c>
       <c r="N187">
-        <v>19800</v>
+        <v>8800</v>
       </c>
     </row>
     <row r="188" spans="1:14">
@@ -9776,107 +9817,110 @@
         <v>187</v>
       </c>
       <c r="B188" t="s">
-        <v>443</v>
+        <v>435</v>
       </c>
       <c r="C188" t="s">
-        <v>438</v>
+        <v>428</v>
       </c>
       <c r="D188" t="s">
         <v>5</v>
       </c>
+      <c r="E188" t="s">
+        <v>16</v>
+      </c>
       <c r="G188" t="s">
         <v>7</v>
       </c>
       <c r="H188" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
       <c r="I188" t="s">
-        <v>444</v>
+        <v>436</v>
       </c>
       <c r="K188">
-        <v>26528</v>
+        <v>95684</v>
       </c>
       <c r="L188">
-        <v>84.3333333333333</v>
+        <v>87.0833333333333</v>
       </c>
       <c r="M188">
-        <v>0.331724969843185</v>
+        <v>0.59571088165210495</v>
       </c>
       <c r="N188">
-        <v>8800</v>
+        <v>57000</v>
       </c>
     </row>
     <row r="189" spans="1:14">
       <c r="A189">
         <v>188</v>
       </c>
-      <c r="B189" t="s">
-        <v>445</v>
+      <c r="B189" s="2" t="s">
+        <v>476</v>
       </c>
       <c r="C189" t="s">
-        <v>438</v>
+        <v>428</v>
       </c>
       <c r="D189" t="s">
         <v>5</v>
       </c>
-      <c r="E189" t="s">
-        <v>16</v>
-      </c>
       <c r="G189" t="s">
         <v>7</v>
       </c>
       <c r="H189" t="s">
-        <v>439</v>
-      </c>
-      <c r="I189" t="s">
-        <v>446</v>
+        <v>87</v>
+      </c>
+      <c r="I189" s="4" t="s">
+        <v>477</v>
       </c>
       <c r="K189">
-        <v>95684</v>
+        <v>26737</v>
       </c>
       <c r="L189">
-        <v>87.0833333333333</v>
+        <v>89.8333333333333</v>
       </c>
       <c r="M189">
-        <v>0.59571088165210495</v>
+        <v>0.40019448704043098</v>
       </c>
       <c r="N189">
-        <v>57000</v>
+        <v>10700</v>
       </c>
     </row>
     <row r="190" spans="1:14">
       <c r="A190">
         <v>189</v>
       </c>
-      <c r="B190" s="2" t="s">
-        <v>486</v>
+      <c r="B190" t="s">
+        <v>437</v>
       </c>
       <c r="C190" t="s">
+        <v>428</v>
+      </c>
+      <c r="D190" t="s">
+        <v>5</v>
+      </c>
+      <c r="E190" t="s">
+        <v>16</v>
+      </c>
+      <c r="G190" t="s">
+        <v>7</v>
+      </c>
+      <c r="H190" t="s">
+        <v>429</v>
+      </c>
+      <c r="I190" t="s">
         <v>438</v>
       </c>
-      <c r="D190" t="s">
-        <v>5</v>
-      </c>
-      <c r="G190" t="s">
-        <v>7</v>
-      </c>
-      <c r="H190" t="s">
-        <v>87</v>
-      </c>
-      <c r="I190" s="4" t="s">
-        <v>487</v>
-      </c>
       <c r="K190">
-        <v>26737</v>
+        <v>60000</v>
       </c>
       <c r="L190">
-        <v>89.8333333333333</v>
+        <v>82.5</v>
       </c>
       <c r="M190">
-        <v>0.40019448704043098</v>
+        <v>0.5</v>
       </c>
       <c r="N190">
-        <v>10700</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="191" spans="1:14">
@@ -9884,72 +9928,61 @@
         <v>190</v>
       </c>
       <c r="B191" t="s">
-        <v>447</v>
+        <v>439</v>
       </c>
       <c r="C191" t="s">
-        <v>438</v>
+        <v>428</v>
       </c>
       <c r="D191" t="s">
         <v>5</v>
       </c>
-      <c r="E191" t="s">
-        <v>16</v>
-      </c>
       <c r="G191" t="s">
         <v>7</v>
       </c>
       <c r="H191" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
       <c r="I191" t="s">
-        <v>448</v>
+        <v>440</v>
       </c>
       <c r="K191">
-        <v>60000</v>
+        <v>34895</v>
       </c>
       <c r="L191">
-        <v>82.5</v>
+        <v>77.5</v>
       </c>
       <c r="M191">
-        <v>0.5</v>
+        <v>0.45278693222524702</v>
       </c>
       <c r="N191">
-        <v>30000</v>
+        <v>15800</v>
       </c>
     </row>
     <row r="192" spans="1:14">
-      <c r="A192">
-        <v>191</v>
-      </c>
-      <c r="B192" t="s">
-        <v>449</v>
-      </c>
-      <c r="C192" t="s">
-        <v>438</v>
-      </c>
-      <c r="D192" t="s">
-        <v>5</v>
-      </c>
-      <c r="G192" t="s">
-        <v>7</v>
-      </c>
-      <c r="H192" t="s">
-        <v>439</v>
-      </c>
-      <c r="I192" t="s">
-        <v>450</v>
-      </c>
-      <c r="K192">
-        <v>34895</v>
-      </c>
-      <c r="L192">
-        <v>77.5</v>
-      </c>
-      <c r="M192">
-        <v>0.45278693222524702</v>
-      </c>
-      <c r="N192">
-        <v>15800</v>
+      <c r="B192" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="C192" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="G192" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="H192" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="I192" s="1" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="193" spans="2:2">
+      <c r="B193" s="1" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="194" spans="2:2">
+      <c r="B194" s="1" t="s">
+        <v>500</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yuhang/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F1B8D6E-FF4B-D14D-AF9B-CCE8F54CB829}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C93D5165-38BF-F643-8789-3E20CA16FEBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-7900" yWindow="-28200" windowWidth="25620" windowHeight="28200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1580" uniqueCount="503">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1580" uniqueCount="504">
   <si>
     <t>所在市</t>
   </si>
@@ -233,9 +233,6 @@
     <t>2009 Q4</t>
   </si>
   <si>
-    <t>116.466313,39.891861</t>
-  </si>
-  <si>
     <t>远洋光华国际ABC座-远洋自持</t>
   </si>
   <si>
@@ -680,9 +677,6 @@
     <t>2010 Q1</t>
   </si>
   <si>
-    <t>116.454820,39.961195</t>
-  </si>
-  <si>
     <t>嘉铭中心</t>
   </si>
   <si>
@@ -695,9 +689,6 @@
     <t>2011 Q3</t>
   </si>
   <si>
-    <t>116.455377,39.961514</t>
-  </si>
-  <si>
     <t>友邦金融中心（原凯德 星贸/博瑞大厦）</t>
   </si>
   <si>
@@ -720,9 +711,6 @@
   </si>
   <si>
     <t>冠捷大厦</t>
-  </si>
-  <si>
-    <t>116.444967,39.969875</t>
   </si>
   <si>
     <t>国航世纪大厦</t>
@@ -1583,6 +1571,23 @@
   </si>
   <si>
     <t>116.464467,39.912049</t>
+  </si>
+  <si>
+    <t>116.464674,39.912865</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>116.460321,39.906941</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>116.454891,39.960979</t>
+  </si>
+  <si>
+    <t>116.456886,39.962611</t>
+  </si>
+  <si>
+    <t>116.445694,39.970256</t>
   </si>
 </sst>
 </file>
@@ -2003,22 +2008,22 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" t="s">
+        <v>442</v>
+      </c>
+      <c r="B1" t="s">
+        <v>444</v>
+      </c>
+      <c r="C1" t="s">
+        <v>445</v>
+      </c>
+      <c r="D1" t="s">
         <v>446</v>
       </c>
-      <c r="B1" t="s">
-        <v>448</v>
-      </c>
-      <c r="C1" t="s">
-        <v>449</v>
-      </c>
-      <c r="D1" t="s">
-        <v>450</v>
-      </c>
       <c r="E1" s="1" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="F1" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="G1" t="s">
         <v>0</v>
@@ -2030,19 +2035,19 @@
         <v>2</v>
       </c>
       <c r="J1" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="K1" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="L1" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="M1" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="N1" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -2071,7 +2076,7 @@
         <v>9</v>
       </c>
       <c r="J2" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="K2">
         <v>72308</v>
@@ -2112,7 +2117,7 @@
         <v>12</v>
       </c>
       <c r="J3" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="K3">
         <v>72308</v>
@@ -2156,7 +2161,7 @@
         <v>17</v>
       </c>
       <c r="J4" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="K4">
         <v>130769</v>
@@ -2200,7 +2205,7 @@
         <v>20</v>
       </c>
       <c r="J5" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="K5">
         <v>64615</v>
@@ -2244,7 +2249,7 @@
         <v>24</v>
       </c>
       <c r="J6" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="K6">
         <v>80091</v>
@@ -2285,7 +2290,7 @@
         <v>27</v>
       </c>
       <c r="J7" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="K7">
         <v>70673</v>
@@ -2329,7 +2334,7 @@
         <v>30</v>
       </c>
       <c r="J8" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="K8">
         <v>90466</v>
@@ -2370,7 +2375,7 @@
         <v>32</v>
       </c>
       <c r="J9" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="K9">
         <v>46720</v>
@@ -2414,7 +2419,7 @@
         <v>35</v>
       </c>
       <c r="J10" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="K10">
         <v>95000</v>
@@ -2458,7 +2463,7 @@
         <v>38</v>
       </c>
       <c r="J11" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="K11">
         <v>85300</v>
@@ -2502,7 +2507,7 @@
         <v>41</v>
       </c>
       <c r="J12" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="K12">
         <v>33305</v>
@@ -2546,7 +2551,7 @@
         <v>43</v>
       </c>
       <c r="J13" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="K13">
         <v>120245.21</v>
@@ -2590,7 +2595,7 @@
         <v>43</v>
       </c>
       <c r="J14" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="K14">
         <v>70425.53</v>
@@ -2634,7 +2639,7 @@
         <v>47</v>
       </c>
       <c r="J15" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="K15">
         <v>78000</v>
@@ -2678,7 +2683,7 @@
         <v>50</v>
       </c>
       <c r="J16" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="K16">
         <v>102796</v>
@@ -2722,7 +2727,7 @@
         <v>52</v>
       </c>
       <c r="J17" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="K17">
         <v>49200</v>
@@ -2766,7 +2771,7 @@
         <v>54</v>
       </c>
       <c r="J18" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="K18">
         <v>65096</v>
@@ -2810,7 +2815,7 @@
         <v>57</v>
       </c>
       <c r="J19" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="K19">
         <v>56000</v>
@@ -2854,7 +2859,7 @@
         <v>60</v>
       </c>
       <c r="J20" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="K20">
         <v>177847</v>
@@ -2898,7 +2903,7 @@
         <v>63</v>
       </c>
       <c r="J21" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="K21">
         <v>83000</v>
@@ -2935,11 +2940,11 @@
       <c r="H22" t="s">
         <v>8</v>
       </c>
-      <c r="I22" t="s">
-        <v>66</v>
+      <c r="I22" s="1" t="s">
+        <v>500</v>
       </c>
       <c r="J22" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="K22">
         <v>26000</v>
@@ -2959,7 +2964,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C23" t="s">
         <v>4</v>
@@ -2977,10 +2982,10 @@
         <v>8</v>
       </c>
       <c r="I23" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J23" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="K23">
         <v>85887</v>
@@ -3000,7 +3005,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C24" t="s">
         <v>4</v>
@@ -3018,10 +3023,10 @@
         <v>8</v>
       </c>
       <c r="I24" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J24" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="K24">
         <v>20000</v>
@@ -3041,7 +3046,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C25" t="s">
         <v>4</v>
@@ -3053,7 +3058,7 @@
         <v>23</v>
       </c>
       <c r="F25" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G25" t="s">
         <v>7</v>
@@ -3062,10 +3067,10 @@
         <v>8</v>
       </c>
       <c r="I25" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J25" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="K25">
         <v>146385</v>
@@ -3085,7 +3090,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C26" t="s">
         <v>4</v>
@@ -3097,7 +3102,7 @@
         <v>23</v>
       </c>
       <c r="F26" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G26" t="s">
         <v>7</v>
@@ -3106,10 +3111,10 @@
         <v>8</v>
       </c>
       <c r="I26" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J26" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="K26">
         <v>87000</v>
@@ -3129,7 +3134,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C27" t="s">
         <v>4</v>
@@ -3141,7 +3146,7 @@
         <v>23</v>
       </c>
       <c r="F27" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G27" t="s">
         <v>7</v>
@@ -3150,10 +3155,10 @@
         <v>8</v>
       </c>
       <c r="I27" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J27" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="K27">
         <v>147166.79999999999</v>
@@ -3173,7 +3178,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C28" t="s">
         <v>4</v>
@@ -3185,7 +3190,7 @@
         <v>16</v>
       </c>
       <c r="F28" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G28" t="s">
         <v>7</v>
@@ -3194,10 +3199,10 @@
         <v>8</v>
       </c>
       <c r="I28" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J28" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="K28">
         <v>46063</v>
@@ -3217,7 +3222,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C29" t="s">
         <v>4</v>
@@ -3229,7 +3234,7 @@
         <v>23</v>
       </c>
       <c r="F29" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G29" t="s">
         <v>7</v>
@@ -3238,10 +3243,10 @@
         <v>8</v>
       </c>
       <c r="I29" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J29" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="K29">
         <v>47261</v>
@@ -3261,7 +3266,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="C30" t="s">
         <v>4</v>
@@ -3273,19 +3278,19 @@
         <v>23</v>
       </c>
       <c r="F30" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G30" t="s">
         <v>7</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="J30" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="K30">
         <v>119000</v>
@@ -3305,7 +3310,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C31" t="s">
         <v>4</v>
@@ -3314,7 +3319,7 @@
         <v>5</v>
       </c>
       <c r="F31" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G31" t="s">
         <v>7</v>
@@ -3323,10 +3328,10 @@
         <v>8</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="J31" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="K31">
         <v>47000</v>
@@ -3346,7 +3351,7 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C32" t="s">
         <v>4</v>
@@ -3358,7 +3363,7 @@
         <v>16</v>
       </c>
       <c r="F32" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G32" t="s">
         <v>7</v>
@@ -3367,10 +3372,10 @@
         <v>8</v>
       </c>
       <c r="I32" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J32" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="K32">
         <v>186000</v>
@@ -3390,7 +3395,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C33" t="s">
         <v>4</v>
@@ -3405,10 +3410,10 @@
         <v>8</v>
       </c>
       <c r="I33" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J33" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="K33">
         <v>40800</v>
@@ -3428,7 +3433,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C34" t="s">
         <v>4</v>
@@ -3437,7 +3442,7 @@
         <v>5</v>
       </c>
       <c r="F34" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G34" t="s">
         <v>7</v>
@@ -3445,11 +3450,11 @@
       <c r="H34" t="s">
         <v>8</v>
       </c>
-      <c r="I34" t="s">
-        <v>94</v>
+      <c r="I34" s="1" t="s">
+        <v>499</v>
       </c>
       <c r="J34" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="K34">
         <v>55200</v>
@@ -3469,7 +3474,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C35" t="s">
         <v>4</v>
@@ -3481,7 +3486,7 @@
         <v>16</v>
       </c>
       <c r="F35" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G35" t="s">
         <v>7</v>
@@ -3490,10 +3495,10 @@
         <v>8</v>
       </c>
       <c r="I35" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J35" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="K35">
         <v>350000</v>
@@ -3513,7 +3518,7 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C36" t="s">
         <v>4</v>
@@ -3531,10 +3536,10 @@
         <v>8</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="J36" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="K36">
         <v>65000</v>
@@ -3554,7 +3559,7 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C37" t="s">
         <v>4</v>
@@ -3572,10 +3577,10 @@
         <v>8</v>
       </c>
       <c r="I37" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="J37" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="K37">
         <v>35000</v>
@@ -3595,7 +3600,7 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C38" t="s">
         <v>4</v>
@@ -3613,10 +3618,10 @@
         <v>8</v>
       </c>
       <c r="I38" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J38" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="K38">
         <v>47000</v>
@@ -3636,7 +3641,7 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C39" t="s">
         <v>4</v>
@@ -3648,7 +3653,7 @@
         <v>23</v>
       </c>
       <c r="F39" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G39" t="s">
         <v>7</v>
@@ -3657,10 +3662,10 @@
         <v>8</v>
       </c>
       <c r="I39" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J39" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="K39">
         <v>120000</v>
@@ -3680,7 +3685,7 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C40" t="s">
         <v>4</v>
@@ -3698,10 +3703,10 @@
         <v>8</v>
       </c>
       <c r="I40" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J40" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="K40">
         <v>83000</v>
@@ -3721,7 +3726,7 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C41" t="s">
         <v>4</v>
@@ -3739,10 +3744,10 @@
         <v>8</v>
       </c>
       <c r="I41" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J41" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="K41">
         <v>66030</v>
@@ -3762,7 +3767,7 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C42" t="s">
         <v>4</v>
@@ -3777,10 +3782,10 @@
         <v>8</v>
       </c>
       <c r="I42" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J42" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="K42">
         <v>40000</v>
@@ -3800,10 +3805,10 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
+        <v>111</v>
+      </c>
+      <c r="C43" t="s">
         <v>112</v>
-      </c>
-      <c r="C43" t="s">
-        <v>113</v>
       </c>
       <c r="D43" t="s">
         <v>5</v>
@@ -3812,19 +3817,19 @@
         <v>16</v>
       </c>
       <c r="F43" t="s">
+        <v>113</v>
+      </c>
+      <c r="G43" t="s">
+        <v>7</v>
+      </c>
+      <c r="H43" t="s">
         <v>114</v>
       </c>
-      <c r="G43" t="s">
-        <v>7</v>
-      </c>
-      <c r="H43" t="s">
+      <c r="I43" t="s">
         <v>115</v>
       </c>
-      <c r="I43" t="s">
-        <v>116</v>
-      </c>
       <c r="J43" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="K43">
         <v>40000</v>
@@ -3844,28 +3849,28 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
+        <v>116</v>
+      </c>
+      <c r="C44" t="s">
+        <v>112</v>
+      </c>
+      <c r="D44" t="s">
+        <v>5</v>
+      </c>
+      <c r="F44" t="s">
         <v>117</v>
       </c>
-      <c r="C44" t="s">
-        <v>113</v>
-      </c>
-      <c r="D44" t="s">
-        <v>5</v>
-      </c>
-      <c r="F44" t="s">
+      <c r="G44" t="s">
+        <v>7</v>
+      </c>
+      <c r="H44" t="s">
+        <v>114</v>
+      </c>
+      <c r="I44" t="s">
         <v>118</v>
       </c>
-      <c r="G44" t="s">
-        <v>7</v>
-      </c>
-      <c r="H44" t="s">
-        <v>115</v>
-      </c>
-      <c r="I44" t="s">
-        <v>119</v>
-      </c>
       <c r="J44" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="K44">
         <v>54100</v>
@@ -3885,10 +3890,10 @@
         <v>44</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C45" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D45" t="s">
         <v>5</v>
@@ -3897,19 +3902,19 @@
         <v>23</v>
       </c>
       <c r="F45" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G45" t="s">
         <v>7</v>
       </c>
       <c r="H45" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="J45" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="K45">
         <v>100000</v>
@@ -3929,10 +3934,10 @@
         <v>45</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C46" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D46" t="s">
         <v>5</v>
@@ -3941,19 +3946,19 @@
         <v>23</v>
       </c>
       <c r="F46" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G46" t="s">
         <v>7</v>
       </c>
       <c r="H46" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="J46" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="K46">
         <v>150000</v>
@@ -3973,10 +3978,10 @@
         <v>46</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C47" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D47" t="s">
         <v>5</v>
@@ -3985,19 +3990,19 @@
         <v>23</v>
       </c>
       <c r="F47" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G47" t="s">
         <v>7</v>
       </c>
       <c r="H47" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="J47" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="K47">
         <v>50000</v>
@@ -4017,10 +4022,10 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C48" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D48" t="s">
         <v>5</v>
@@ -4029,19 +4034,19 @@
         <v>23</v>
       </c>
       <c r="F48" t="s">
+        <v>126</v>
+      </c>
+      <c r="G48" t="s">
+        <v>7</v>
+      </c>
+      <c r="H48" t="s">
+        <v>114</v>
+      </c>
+      <c r="I48" t="s">
         <v>127</v>
       </c>
-      <c r="G48" t="s">
-        <v>7</v>
-      </c>
-      <c r="H48" t="s">
-        <v>115</v>
-      </c>
-      <c r="I48" t="s">
-        <v>128</v>
-      </c>
       <c r="J48" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="K48">
         <v>43000</v>
@@ -4061,28 +4066,28 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
+        <v>128</v>
+      </c>
+      <c r="C49" t="s">
+        <v>112</v>
+      </c>
+      <c r="D49" t="s">
+        <v>5</v>
+      </c>
+      <c r="F49" t="s">
         <v>129</v>
       </c>
-      <c r="C49" t="s">
-        <v>113</v>
-      </c>
-      <c r="D49" t="s">
-        <v>5</v>
-      </c>
-      <c r="F49" t="s">
+      <c r="G49" t="s">
+        <v>7</v>
+      </c>
+      <c r="H49" t="s">
+        <v>114</v>
+      </c>
+      <c r="I49" t="s">
         <v>130</v>
       </c>
-      <c r="G49" t="s">
-        <v>7</v>
-      </c>
-      <c r="H49" t="s">
-        <v>115</v>
-      </c>
-      <c r="I49" t="s">
-        <v>131</v>
-      </c>
       <c r="J49" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="K49">
         <v>65000</v>
@@ -4102,10 +4107,10 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C50" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D50" t="s">
         <v>5</v>
@@ -4120,13 +4125,13 @@
         <v>7</v>
       </c>
       <c r="H50" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I50" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J50" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="K50">
         <v>56000</v>
@@ -4146,10 +4151,10 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C51" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D51" t="s">
         <v>5</v>
@@ -4161,13 +4166,13 @@
         <v>7</v>
       </c>
       <c r="H51" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I51" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="J51" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="K51">
         <v>160000</v>
@@ -4187,10 +4192,10 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C52" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D52" t="s">
         <v>5</v>
@@ -4202,13 +4207,13 @@
         <v>7</v>
       </c>
       <c r="H52" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I52" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J52" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="K52">
         <v>33000</v>
@@ -4228,10 +4233,10 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C53" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D53" t="s">
         <v>5</v>
@@ -4240,19 +4245,19 @@
         <v>16</v>
       </c>
       <c r="F53" t="s">
+        <v>139</v>
+      </c>
+      <c r="G53" t="s">
+        <v>7</v>
+      </c>
+      <c r="H53" t="s">
+        <v>114</v>
+      </c>
+      <c r="I53" t="s">
         <v>140</v>
       </c>
-      <c r="G53" t="s">
-        <v>7</v>
-      </c>
-      <c r="H53" t="s">
-        <v>115</v>
-      </c>
-      <c r="I53" t="s">
-        <v>141</v>
-      </c>
       <c r="J53" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="K53">
         <v>41318</v>
@@ -4272,28 +4277,28 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
+        <v>141</v>
+      </c>
+      <c r="C54" t="s">
+        <v>112</v>
+      </c>
+      <c r="D54" t="s">
+        <v>5</v>
+      </c>
+      <c r="F54" t="s">
+        <v>131</v>
+      </c>
+      <c r="G54" t="s">
+        <v>7</v>
+      </c>
+      <c r="H54" t="s">
+        <v>114</v>
+      </c>
+      <c r="I54" t="s">
         <v>142</v>
       </c>
-      <c r="C54" t="s">
-        <v>113</v>
-      </c>
-      <c r="D54" t="s">
-        <v>5</v>
-      </c>
-      <c r="F54" t="s">
-        <v>132</v>
-      </c>
-      <c r="G54" t="s">
-        <v>7</v>
-      </c>
-      <c r="H54" t="s">
-        <v>115</v>
-      </c>
-      <c r="I54" t="s">
-        <v>143</v>
-      </c>
       <c r="J54" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="K54">
         <v>34131</v>
@@ -4313,28 +4318,28 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
+        <v>143</v>
+      </c>
+      <c r="C55" t="s">
+        <v>112</v>
+      </c>
+      <c r="D55" t="s">
+        <v>5</v>
+      </c>
+      <c r="F55" t="s">
         <v>144</v>
       </c>
-      <c r="C55" t="s">
-        <v>113</v>
-      </c>
-      <c r="D55" t="s">
-        <v>5</v>
-      </c>
-      <c r="F55" t="s">
+      <c r="G55" t="s">
+        <v>7</v>
+      </c>
+      <c r="H55" t="s">
+        <v>114</v>
+      </c>
+      <c r="I55" t="s">
         <v>145</v>
       </c>
-      <c r="G55" t="s">
-        <v>7</v>
-      </c>
-      <c r="H55" t="s">
-        <v>115</v>
-      </c>
-      <c r="I55" t="s">
-        <v>146</v>
-      </c>
       <c r="J55" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="K55">
         <v>48000</v>
@@ -4354,10 +4359,10 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C56" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D56" t="s">
         <v>5</v>
@@ -4369,13 +4374,13 @@
         <v>7</v>
       </c>
       <c r="H56" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="J56" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="K56">
         <v>16000</v>
@@ -4395,10 +4400,10 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C57" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D57" t="s">
         <v>5</v>
@@ -4407,19 +4412,19 @@
         <v>16</v>
       </c>
       <c r="F57" t="s">
+        <v>148</v>
+      </c>
+      <c r="G57" t="s">
+        <v>7</v>
+      </c>
+      <c r="H57" t="s">
+        <v>114</v>
+      </c>
+      <c r="I57" t="s">
         <v>149</v>
       </c>
-      <c r="G57" t="s">
-        <v>7</v>
-      </c>
-      <c r="H57" t="s">
-        <v>115</v>
-      </c>
-      <c r="I57" t="s">
-        <v>150</v>
-      </c>
       <c r="J57" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="K57">
         <v>30000</v>
@@ -4439,10 +4444,10 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C58" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D58" t="s">
         <v>5</v>
@@ -4451,19 +4456,19 @@
         <v>16</v>
       </c>
       <c r="F58" t="s">
+        <v>151</v>
+      </c>
+      <c r="G58" t="s">
+        <v>7</v>
+      </c>
+      <c r="H58" t="s">
+        <v>114</v>
+      </c>
+      <c r="I58" t="s">
         <v>152</v>
       </c>
-      <c r="G58" t="s">
-        <v>7</v>
-      </c>
-      <c r="H58" t="s">
-        <v>115</v>
-      </c>
-      <c r="I58" t="s">
-        <v>153</v>
-      </c>
       <c r="J58" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="K58">
         <v>56000</v>
@@ -4483,10 +4488,10 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C59" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D59" t="s">
         <v>5</v>
@@ -4495,19 +4500,19 @@
         <v>16</v>
       </c>
       <c r="F59" t="s">
+        <v>154</v>
+      </c>
+      <c r="G59" t="s">
+        <v>7</v>
+      </c>
+      <c r="H59" t="s">
+        <v>114</v>
+      </c>
+      <c r="I59" t="s">
         <v>155</v>
       </c>
-      <c r="G59" t="s">
-        <v>7</v>
-      </c>
-      <c r="H59" t="s">
-        <v>115</v>
-      </c>
-      <c r="I59" t="s">
-        <v>156</v>
-      </c>
       <c r="J59" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="K59">
         <v>43000</v>
@@ -4527,10 +4532,10 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C60" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D60" t="s">
         <v>5</v>
@@ -4545,10 +4550,10 @@
         <v>8</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="J60" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="K60">
         <v>110000</v>
@@ -4568,25 +4573,25 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
+        <v>157</v>
+      </c>
+      <c r="C61" t="s">
+        <v>112</v>
+      </c>
+      <c r="D61" t="s">
+        <v>5</v>
+      </c>
+      <c r="G61" t="s">
+        <v>7</v>
+      </c>
+      <c r="H61" t="s">
+        <v>114</v>
+      </c>
+      <c r="I61" t="s">
         <v>158</v>
       </c>
-      <c r="C61" t="s">
-        <v>113</v>
-      </c>
-      <c r="D61" t="s">
-        <v>5</v>
-      </c>
-      <c r="G61" t="s">
-        <v>7</v>
-      </c>
-      <c r="H61" t="s">
-        <v>115</v>
-      </c>
-      <c r="I61" t="s">
-        <v>159</v>
-      </c>
       <c r="J61" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="K61">
         <v>56160</v>
@@ -4606,10 +4611,10 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C62" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D62" t="s">
         <v>14</v>
@@ -4621,13 +4626,13 @@
         <v>7</v>
       </c>
       <c r="H62" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I62" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J62" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="K62">
         <v>138444</v>
@@ -4647,10 +4652,10 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
+        <v>161</v>
+      </c>
+      <c r="C63" t="s">
         <v>162</v>
-      </c>
-      <c r="C63" t="s">
-        <v>163</v>
       </c>
       <c r="D63" t="s">
         <v>5</v>
@@ -4659,19 +4664,19 @@
         <v>16</v>
       </c>
       <c r="F63" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G63" t="s">
         <v>7</v>
       </c>
       <c r="H63" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="J63" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="K63">
         <v>31000</v>
@@ -4691,28 +4696,28 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C64" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D64" t="s">
         <v>14</v>
       </c>
       <c r="F64" t="s">
+        <v>165</v>
+      </c>
+      <c r="G64" t="s">
+        <v>7</v>
+      </c>
+      <c r="H64" t="s">
+        <v>86</v>
+      </c>
+      <c r="I64" t="s">
         <v>166</v>
       </c>
-      <c r="G64" t="s">
-        <v>7</v>
-      </c>
-      <c r="H64" t="s">
-        <v>87</v>
-      </c>
-      <c r="I64" t="s">
-        <v>167</v>
-      </c>
       <c r="J64" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="K64">
         <v>120000</v>
@@ -4732,10 +4737,10 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C65" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D65" t="s">
         <v>5</v>
@@ -4747,13 +4752,13 @@
         <v>7</v>
       </c>
       <c r="H65" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I65" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J65" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="K65">
         <v>25900</v>
@@ -4773,28 +4778,28 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
+        <v>169</v>
+      </c>
+      <c r="C66" t="s">
+        <v>162</v>
+      </c>
+      <c r="D66" t="s">
+        <v>5</v>
+      </c>
+      <c r="F66" t="s">
         <v>170</v>
       </c>
-      <c r="C66" t="s">
-        <v>163</v>
-      </c>
-      <c r="D66" t="s">
-        <v>5</v>
-      </c>
-      <c r="F66" t="s">
+      <c r="G66" t="s">
+        <v>7</v>
+      </c>
+      <c r="H66" t="s">
+        <v>86</v>
+      </c>
+      <c r="I66" t="s">
         <v>171</v>
       </c>
-      <c r="G66" t="s">
-        <v>7</v>
-      </c>
-      <c r="H66" t="s">
-        <v>87</v>
-      </c>
-      <c r="I66" t="s">
-        <v>172</v>
-      </c>
       <c r="J66" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="K66">
         <v>47986</v>
@@ -4814,10 +4819,10 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C67" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D67" t="s">
         <v>5</v>
@@ -4832,13 +4837,13 @@
         <v>7</v>
       </c>
       <c r="H67" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I67" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J67" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="K67">
         <v>194000</v>
@@ -4858,10 +4863,10 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C68" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D68" t="s">
         <v>5</v>
@@ -4876,13 +4881,13 @@
         <v>7</v>
       </c>
       <c r="H68" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I68" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J68" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="K68">
         <v>39724</v>
@@ -4902,10 +4907,10 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C69" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D69" t="s">
         <v>5</v>
@@ -4917,13 +4922,13 @@
         <v>7</v>
       </c>
       <c r="H69" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="J69" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="K69">
         <v>48437.45</v>
@@ -4943,28 +4948,28 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
+        <v>177</v>
+      </c>
+      <c r="C70" t="s">
+        <v>162</v>
+      </c>
+      <c r="D70" t="s">
+        <v>5</v>
+      </c>
+      <c r="F70" t="s">
         <v>178</v>
       </c>
-      <c r="C70" t="s">
-        <v>163</v>
-      </c>
-      <c r="D70" t="s">
-        <v>5</v>
-      </c>
-      <c r="F70" t="s">
+      <c r="G70" t="s">
+        <v>7</v>
+      </c>
+      <c r="H70" t="s">
+        <v>86</v>
+      </c>
+      <c r="I70" t="s">
         <v>179</v>
       </c>
-      <c r="G70" t="s">
-        <v>7</v>
-      </c>
-      <c r="H70" t="s">
-        <v>87</v>
-      </c>
-      <c r="I70" t="s">
-        <v>180</v>
-      </c>
       <c r="J70" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="K70">
         <v>37910</v>
@@ -4984,28 +4989,28 @@
         <v>70</v>
       </c>
       <c r="B71" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="C71" t="s">
+        <v>162</v>
+      </c>
+      <c r="D71" t="s">
+        <v>5</v>
+      </c>
+      <c r="F71" t="s">
+        <v>178</v>
+      </c>
+      <c r="G71" t="s">
+        <v>7</v>
+      </c>
+      <c r="H71" t="s">
+        <v>86</v>
+      </c>
+      <c r="I71" s="2" t="s">
         <v>460</v>
       </c>
-      <c r="C71" t="s">
-        <v>163</v>
-      </c>
-      <c r="D71" t="s">
-        <v>5</v>
-      </c>
-      <c r="F71" t="s">
-        <v>179</v>
-      </c>
-      <c r="G71" t="s">
-        <v>7</v>
-      </c>
-      <c r="H71" t="s">
-        <v>87</v>
-      </c>
-      <c r="I71" s="2" t="s">
-        <v>464</v>
-      </c>
       <c r="J71" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="K71">
         <v>21220</v>
@@ -5025,10 +5030,10 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C72" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D72" t="s">
         <v>5</v>
@@ -5040,13 +5045,13 @@
         <v>7</v>
       </c>
       <c r="H72" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I72" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J72" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="K72">
         <v>77877</v>
@@ -5066,10 +5071,10 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C73" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D73" t="s">
         <v>5</v>
@@ -5084,13 +5089,13 @@
         <v>7</v>
       </c>
       <c r="H73" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I73" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="J73" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="K73">
         <v>80311.53</v>
@@ -5110,10 +5115,10 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C74" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D74" t="s">
         <v>5</v>
@@ -5122,19 +5127,19 @@
         <v>23</v>
       </c>
       <c r="F74" t="s">
+        <v>185</v>
+      </c>
+      <c r="G74" t="s">
+        <v>7</v>
+      </c>
+      <c r="H74" t="s">
+        <v>86</v>
+      </c>
+      <c r="I74" t="s">
         <v>186</v>
       </c>
-      <c r="G74" t="s">
-        <v>7</v>
-      </c>
-      <c r="H74" t="s">
-        <v>87</v>
-      </c>
-      <c r="I74" t="s">
-        <v>187</v>
-      </c>
       <c r="J74" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="K74">
         <v>38000</v>
@@ -5154,28 +5159,28 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
+        <v>187</v>
+      </c>
+      <c r="C75" t="s">
+        <v>162</v>
+      </c>
+      <c r="D75" t="s">
+        <v>5</v>
+      </c>
+      <c r="F75" t="s">
         <v>188</v>
       </c>
-      <c r="C75" t="s">
-        <v>163</v>
-      </c>
-      <c r="D75" t="s">
-        <v>5</v>
-      </c>
-      <c r="F75" t="s">
+      <c r="G75" t="s">
+        <v>7</v>
+      </c>
+      <c r="H75" t="s">
+        <v>86</v>
+      </c>
+      <c r="I75" t="s">
         <v>189</v>
       </c>
-      <c r="G75" t="s">
-        <v>7</v>
-      </c>
-      <c r="H75" t="s">
-        <v>87</v>
-      </c>
-      <c r="I75" t="s">
-        <v>190</v>
-      </c>
       <c r="J75" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="K75">
         <v>37800</v>
@@ -5195,10 +5200,10 @@
         <v>75</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C76" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D76" t="s">
         <v>5</v>
@@ -5207,19 +5212,19 @@
         <v>16</v>
       </c>
       <c r="F76" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G76" t="s">
         <v>7</v>
       </c>
       <c r="H76" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="J76" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="K76">
         <v>54581</v>
@@ -5239,10 +5244,10 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C77" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D77" t="s">
         <v>5</v>
@@ -5251,19 +5256,19 @@
         <v>16</v>
       </c>
       <c r="F77" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G77" t="s">
         <v>7</v>
       </c>
       <c r="H77" t="s">
+        <v>86</v>
+      </c>
+      <c r="I77" t="s">
         <v>87</v>
       </c>
-      <c r="I77" t="s">
-        <v>88</v>
-      </c>
       <c r="J77" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="K77">
         <v>25000</v>
@@ -5283,10 +5288,10 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C78" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D78" t="s">
         <v>5</v>
@@ -5295,19 +5300,19 @@
         <v>16</v>
       </c>
       <c r="F78" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G78" t="s">
         <v>7</v>
       </c>
       <c r="H78" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I78" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J78" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="K78">
         <v>52698</v>
@@ -5327,28 +5332,28 @@
         <v>78</v>
       </c>
       <c r="B79" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C79" t="s">
+        <v>162</v>
+      </c>
+      <c r="D79" t="s">
+        <v>5</v>
+      </c>
+      <c r="F79" t="s">
         <v>197</v>
       </c>
-      <c r="C79" t="s">
-        <v>163</v>
-      </c>
-      <c r="D79" t="s">
-        <v>5</v>
-      </c>
-      <c r="F79" t="s">
+      <c r="G79" t="s">
+        <v>7</v>
+      </c>
+      <c r="H79" t="s">
         <v>198</v>
       </c>
-      <c r="G79" t="s">
-        <v>7</v>
-      </c>
-      <c r="H79" t="s">
-        <v>199</v>
-      </c>
       <c r="I79" s="2" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="J79" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="K79">
         <v>38500</v>
@@ -5368,25 +5373,25 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
+        <v>199</v>
+      </c>
+      <c r="C80" t="s">
+        <v>162</v>
+      </c>
+      <c r="D80" t="s">
         <v>200</v>
       </c>
-      <c r="C80" t="s">
-        <v>163</v>
-      </c>
-      <c r="D80" t="s">
+      <c r="G80" t="s">
+        <v>7</v>
+      </c>
+      <c r="H80" t="s">
+        <v>86</v>
+      </c>
+      <c r="I80" t="s">
         <v>201</v>
       </c>
-      <c r="G80" t="s">
-        <v>7</v>
-      </c>
-      <c r="H80" t="s">
-        <v>87</v>
-      </c>
-      <c r="I80" t="s">
-        <v>202</v>
-      </c>
       <c r="J80" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="K80">
         <v>27200</v>
@@ -5406,10 +5411,10 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C81" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D81" t="s">
         <v>5</v>
@@ -5418,7 +5423,7 @@
         <v>16</v>
       </c>
       <c r="F81" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G81" t="s">
         <v>7</v>
@@ -5427,10 +5432,10 @@
         <v>8</v>
       </c>
       <c r="I81" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="J81" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="K81">
         <v>60000</v>
@@ -5450,16 +5455,16 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
+        <v>205</v>
+      </c>
+      <c r="C82" t="s">
+        <v>139</v>
+      </c>
+      <c r="D82" t="s">
+        <v>5</v>
+      </c>
+      <c r="F82" t="s">
         <v>206</v>
-      </c>
-      <c r="C82" t="s">
-        <v>140</v>
-      </c>
-      <c r="D82" t="s">
-        <v>5</v>
-      </c>
-      <c r="F82" t="s">
-        <v>207</v>
       </c>
       <c r="G82" t="s">
         <v>7</v>
@@ -5468,10 +5473,10 @@
         <v>8</v>
       </c>
       <c r="I82" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J82" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="K82">
         <v>50000</v>
@@ -5491,10 +5496,10 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C83" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D83" t="s">
         <v>5</v>
@@ -5503,7 +5508,7 @@
         <v>23</v>
       </c>
       <c r="F83" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G83" t="s">
         <v>7</v>
@@ -5512,10 +5517,10 @@
         <v>8</v>
       </c>
       <c r="I83" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="J83" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="K83">
         <v>131575</v>
@@ -5535,10 +5540,10 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C84" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D84" t="s">
         <v>5</v>
@@ -5553,10 +5558,10 @@
         <v>8</v>
       </c>
       <c r="I84" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="J84" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="K84">
         <v>99500</v>
@@ -5576,16 +5581,16 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
+        <v>212</v>
+      </c>
+      <c r="C85" t="s">
+        <v>139</v>
+      </c>
+      <c r="D85" t="s">
+        <v>5</v>
+      </c>
+      <c r="F85" t="s">
         <v>213</v>
-      </c>
-      <c r="C85" t="s">
-        <v>140</v>
-      </c>
-      <c r="D85" t="s">
-        <v>5</v>
-      </c>
-      <c r="F85" t="s">
-        <v>214</v>
       </c>
       <c r="G85" t="s">
         <v>7</v>
@@ -5594,10 +5599,10 @@
         <v>8</v>
       </c>
       <c r="I85" t="s">
-        <v>215</v>
+        <v>501</v>
       </c>
       <c r="J85" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="K85">
         <v>32000</v>
@@ -5617,10 +5622,10 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C86" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D86" t="s">
         <v>5</v>
@@ -5629,7 +5634,7 @@
         <v>23</v>
       </c>
       <c r="F86" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G86" t="s">
         <v>7</v>
@@ -5638,10 +5643,10 @@
         <v>8</v>
       </c>
       <c r="I86" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="J86" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="K86">
         <v>52170</v>
@@ -5661,16 +5666,16 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C87" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D87" t="s">
         <v>5</v>
       </c>
       <c r="F87" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G87" t="s">
         <v>7</v>
@@ -5679,10 +5684,10 @@
         <v>8</v>
       </c>
       <c r="I87" t="s">
-        <v>220</v>
+        <v>502</v>
       </c>
       <c r="J87" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="K87">
         <v>46000</v>
@@ -5702,10 +5707,10 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C88" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D88" t="s">
         <v>5</v>
@@ -5714,7 +5719,7 @@
         <v>23</v>
       </c>
       <c r="F88" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="G88" t="s">
         <v>7</v>
@@ -5723,10 +5728,10 @@
         <v>8</v>
       </c>
       <c r="I88" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="J88" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="K88">
         <v>45013</v>
@@ -5746,16 +5751,16 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C89" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D89" t="s">
         <v>5</v>
       </c>
       <c r="F89" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G89" t="s">
         <v>7</v>
@@ -5764,10 +5769,10 @@
         <v>8</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="J89" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="K89">
         <v>48566</v>
@@ -5787,16 +5792,16 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C90" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D90" t="s">
         <v>5</v>
       </c>
       <c r="F90" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="G90" t="s">
         <v>7</v>
@@ -5805,10 +5810,10 @@
         <v>8</v>
       </c>
       <c r="I90" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="J90" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="K90">
         <v>55618</v>
@@ -5828,16 +5833,16 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C91" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D91" t="s">
         <v>5</v>
       </c>
       <c r="F91" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G91" t="s">
         <v>7</v>
@@ -5846,10 +5851,10 @@
         <v>8</v>
       </c>
       <c r="I91" t="s">
-        <v>229</v>
+        <v>503</v>
       </c>
       <c r="J91" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="K91">
         <v>47000</v>
@@ -5869,10 +5874,10 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C92" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D92" t="s">
         <v>5</v>
@@ -5881,7 +5886,7 @@
         <v>23</v>
       </c>
       <c r="F92" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G92" t="s">
         <v>7</v>
@@ -5890,10 +5895,10 @@
         <v>8</v>
       </c>
       <c r="I92" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="J92" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="K92">
         <v>87763</v>
@@ -5913,10 +5918,10 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="C93" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D93" t="s">
         <v>14</v>
@@ -5925,7 +5930,7 @@
         <v>16</v>
       </c>
       <c r="F93" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="G93" t="s">
         <v>7</v>
@@ -5934,10 +5939,10 @@
         <v>8</v>
       </c>
       <c r="I93" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="J93" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="K93">
         <v>100658</v>
@@ -5957,16 +5962,16 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="C94" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D94" t="s">
         <v>5</v>
       </c>
       <c r="F94" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="G94" t="s">
         <v>7</v>
@@ -5975,10 +5980,10 @@
         <v>8</v>
       </c>
       <c r="I94" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="J94" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="K94">
         <v>67000</v>
@@ -5998,10 +6003,10 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="C95" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D95" t="s">
         <v>5</v>
@@ -6010,7 +6015,7 @@
         <v>16</v>
       </c>
       <c r="F95" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G95" t="s">
         <v>7</v>
@@ -6019,10 +6024,10 @@
         <v>8</v>
       </c>
       <c r="I95" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="J95" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="K95">
         <v>39431</v>
@@ -6042,16 +6047,16 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="C96" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D96" t="s">
         <v>5</v>
       </c>
       <c r="F96" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G96" t="s">
         <v>7</v>
@@ -6060,10 +6065,10 @@
         <v>8</v>
       </c>
       <c r="I96" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="J96" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="K96">
         <v>34273</v>
@@ -6083,10 +6088,10 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="C97" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D97" t="s">
         <v>5</v>
@@ -6098,10 +6103,10 @@
         <v>8</v>
       </c>
       <c r="I97" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="J97" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="K97">
         <v>40000</v>
@@ -6121,10 +6126,10 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="C98" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D98" t="s">
         <v>5</v>
@@ -6139,10 +6144,10 @@
         <v>8</v>
       </c>
       <c r="I98" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="J98" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="K98">
         <v>65000</v>
@@ -6162,10 +6167,10 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C99" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="D99" t="s">
         <v>5</v>
@@ -6174,19 +6179,19 @@
         <v>23</v>
       </c>
       <c r="F99" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="G99" t="s">
         <v>7</v>
       </c>
       <c r="H99" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I99" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="J99" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="K99">
         <v>49000</v>
@@ -6206,10 +6211,10 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="C100" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="D100" t="s">
         <v>14</v>
@@ -6218,19 +6223,19 @@
         <v>23</v>
       </c>
       <c r="F100" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="G100" t="s">
         <v>7</v>
       </c>
       <c r="H100" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I100" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="J100" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="K100">
         <v>95000</v>
@@ -6250,10 +6255,10 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="C101" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="D101" t="s">
         <v>5</v>
@@ -6262,19 +6267,19 @@
         <v>23</v>
       </c>
       <c r="F101" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="G101" t="s">
         <v>7</v>
       </c>
       <c r="H101" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I101" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="J101" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="K101">
         <v>45000</v>
@@ -6294,10 +6299,10 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="C102" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="D102" t="s">
         <v>5</v>
@@ -6309,13 +6314,13 @@
         <v>7</v>
       </c>
       <c r="H102" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I102" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="J102" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="K102">
         <v>124500</v>
@@ -6335,28 +6340,28 @@
         <v>102</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="C103" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="D103" t="s">
         <v>5</v>
       </c>
       <c r="F103" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G103" t="s">
         <v>7</v>
       </c>
       <c r="H103" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I103" s="2" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="J103" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="K103">
         <v>64000</v>
@@ -6376,10 +6381,10 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C104" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="D104" t="s">
         <v>5</v>
@@ -6391,13 +6396,13 @@
         <v>7</v>
       </c>
       <c r="H104" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I104" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="J104" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="K104">
         <v>25000</v>
@@ -6417,28 +6422,28 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="C105" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="D105" t="s">
         <v>5</v>
       </c>
       <c r="F105" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G105" t="s">
         <v>7</v>
       </c>
       <c r="H105" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I105" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="J105" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="K105">
         <v>38498</v>
@@ -6458,25 +6463,25 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C106" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="D106" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G106" t="s">
         <v>7</v>
       </c>
       <c r="H106" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I106" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="J106" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="K106">
         <v>166433</v>
@@ -6496,10 +6501,10 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="C107" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="D107" t="s">
         <v>14</v>
@@ -6508,19 +6513,19 @@
         <v>23</v>
       </c>
       <c r="F107" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G107" t="s">
         <v>7</v>
       </c>
       <c r="H107" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I107" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="J107" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="K107">
         <v>58000</v>
@@ -6540,28 +6545,28 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C108" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="D108" t="s">
         <v>5</v>
       </c>
       <c r="F108" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="G108" t="s">
         <v>7</v>
       </c>
       <c r="H108" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I108" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="J108" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="K108">
         <v>51872</v>
@@ -6581,28 +6586,28 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="C109" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="D109" t="s">
         <v>5</v>
       </c>
       <c r="F109" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G109" t="s">
         <v>7</v>
       </c>
       <c r="H109" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I109" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="J109" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="K109">
         <v>21632</v>
@@ -6622,28 +6627,28 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="C110" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="D110" t="s">
         <v>5</v>
       </c>
       <c r="F110" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G110" t="s">
         <v>7</v>
       </c>
       <c r="H110" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I110" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="J110" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="K110">
         <v>69000</v>
@@ -6663,28 +6668,28 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="C111" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="D111" t="s">
         <v>5</v>
       </c>
       <c r="F111" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="G111" t="s">
         <v>7</v>
       </c>
       <c r="H111" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I111" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="J111" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="K111">
         <v>54000</v>
@@ -6704,10 +6709,10 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="C112" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="D112" t="s">
         <v>5</v>
@@ -6719,13 +6724,13 @@
         <v>7</v>
       </c>
       <c r="H112" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I112" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="J112" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="K112">
         <v>57400</v>
@@ -6745,10 +6750,10 @@
         <v>112</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="C113" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="D113" t="s">
         <v>14</v>
@@ -6760,13 +6765,13 @@
         <v>7</v>
       </c>
       <c r="H113" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I113" s="2" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="J113" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="K113">
         <v>60000</v>
@@ -6781,7 +6786,7 @@
         <v>427</v>
       </c>
       <c r="P113" s="1" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -6789,10 +6794,10 @@
         <v>113</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="C114" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="D114" t="s">
         <v>14</v>
@@ -6804,13 +6809,13 @@
         <v>7</v>
       </c>
       <c r="H114" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I114" s="2" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="J114" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="K114">
         <v>60000</v>
@@ -6825,7 +6830,7 @@
         <v>11500</v>
       </c>
       <c r="P114" s="1" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -6833,10 +6838,10 @@
         <v>114</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="C115" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="D115" t="s">
         <v>5</v>
@@ -6845,13 +6850,13 @@
         <v>7</v>
       </c>
       <c r="H115" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I115" s="5" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="J115" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="K115">
         <v>33000</v>
@@ -6871,25 +6876,25 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C116" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="D116" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G116" t="s">
         <v>7</v>
       </c>
       <c r="H116" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I116" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="J116" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="K116">
         <v>88786</v>
@@ -6909,25 +6914,25 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="C117" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="D117" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G117" t="s">
         <v>7</v>
       </c>
       <c r="H117" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I117" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="J117" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="K117">
         <v>134000</v>
@@ -6947,25 +6952,25 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="C118" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="D118" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G118" t="s">
         <v>7</v>
       </c>
       <c r="H118" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I118" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="J118" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="K118">
         <v>35000</v>
@@ -6985,25 +6990,25 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="C119" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="D119" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G119" t="s">
         <v>7</v>
       </c>
       <c r="H119" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I119" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="J119" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="K119">
         <v>18000</v>
@@ -7023,13 +7028,13 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="C120" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="D120" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E120" t="s">
         <v>16</v>
@@ -7038,13 +7043,13 @@
         <v>7</v>
       </c>
       <c r="H120" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I120" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J120" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="K120">
         <v>105741</v>
@@ -7064,25 +7069,25 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="C121" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="D121" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G121" t="s">
         <v>7</v>
       </c>
       <c r="H121" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I121" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="J121" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="K121">
         <v>51000</v>
@@ -7102,10 +7107,10 @@
         <v>121</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="C122" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="D122" t="s">
         <v>5</v>
@@ -7117,13 +7122,13 @@
         <v>7</v>
       </c>
       <c r="H122" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I122" s="3" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="J122" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="K122">
         <v>130143</v>
@@ -7138,7 +7143,7 @@
         <v>36000</v>
       </c>
       <c r="P122" s="1" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7146,22 +7151,22 @@
         <v>122</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="C123" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="G123" t="s">
         <v>7</v>
       </c>
       <c r="H123" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I123" s="3" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="J123" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="K123">
         <v>121551.47</v>
@@ -7176,7 +7181,7 @@
         <v>97326.47</v>
       </c>
       <c r="P123" s="1" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7184,10 +7189,10 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="C124" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="D124" t="s">
         <v>5</v>
@@ -7196,7 +7201,7 @@
         <v>16</v>
       </c>
       <c r="F124" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="G124" t="s">
         <v>7</v>
@@ -7205,10 +7210,10 @@
         <v>8</v>
       </c>
       <c r="I124" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="J124" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="K124">
         <v>110000</v>
@@ -7228,10 +7233,10 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="C125" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="D125" t="s">
         <v>5</v>
@@ -7240,7 +7245,7 @@
         <v>23</v>
       </c>
       <c r="F125" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G125" t="s">
         <v>7</v>
@@ -7249,10 +7254,10 @@
         <v>8</v>
       </c>
       <c r="I125" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="J125" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="K125">
         <v>56000</v>
@@ -7272,16 +7277,16 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="C126" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="D126" t="s">
         <v>5</v>
       </c>
       <c r="F126" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G126" t="s">
         <v>7</v>
@@ -7290,10 +7295,10 @@
         <v>8</v>
       </c>
       <c r="I126" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="J126" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="K126">
         <v>89177</v>
@@ -7313,10 +7318,10 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="C127" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="D127" t="s">
         <v>5</v>
@@ -7325,7 +7330,7 @@
         <v>23</v>
       </c>
       <c r="F127" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="G127" t="s">
         <v>7</v>
@@ -7334,10 +7339,10 @@
         <v>8</v>
       </c>
       <c r="I127" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="J127" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="K127">
         <v>30000</v>
@@ -7357,10 +7362,10 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="C128" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="D128" t="s">
         <v>5</v>
@@ -7369,7 +7374,7 @@
         <v>16</v>
       </c>
       <c r="F128" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="G128" t="s">
         <v>7</v>
@@ -7378,10 +7383,10 @@
         <v>8</v>
       </c>
       <c r="I128" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="J128" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="K128">
         <v>54550</v>
@@ -7401,10 +7406,10 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="C129" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="D129" t="s">
         <v>5</v>
@@ -7413,7 +7418,7 @@
         <v>16</v>
       </c>
       <c r="F129" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="G129" t="s">
         <v>7</v>
@@ -7422,10 +7427,10 @@
         <v>8</v>
       </c>
       <c r="I129" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="J129" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="K129">
         <v>125000</v>
@@ -7445,10 +7450,10 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="C130" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="D130" t="s">
         <v>5</v>
@@ -7457,7 +7462,7 @@
         <v>16</v>
       </c>
       <c r="F130" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="G130" t="s">
         <v>7</v>
@@ -7466,10 +7471,10 @@
         <v>8</v>
       </c>
       <c r="I130" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="J130" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="K130">
         <v>69100</v>
@@ -7489,10 +7494,10 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="C131" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="D131" t="s">
         <v>5</v>
@@ -7501,7 +7506,7 @@
         <v>23</v>
       </c>
       <c r="F131" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G131" t="s">
         <v>7</v>
@@ -7510,10 +7515,10 @@
         <v>8</v>
       </c>
       <c r="I131" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="J131" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="K131">
         <v>118290</v>
@@ -7533,16 +7538,16 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="C132" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="D132" t="s">
         <v>5</v>
       </c>
       <c r="F132" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="G132" t="s">
         <v>7</v>
@@ -7551,10 +7556,10 @@
         <v>8</v>
       </c>
       <c r="I132" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="J132" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="K132">
         <v>79900</v>
@@ -7574,16 +7579,16 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="C133" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="D133" t="s">
         <v>5</v>
       </c>
       <c r="F133" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G133" t="s">
         <v>7</v>
@@ -7592,10 +7597,10 @@
         <v>8</v>
       </c>
       <c r="I133" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="J133" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="K133">
         <v>39742.379999999997</v>
@@ -7615,10 +7620,10 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="C134" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="D134" t="s">
         <v>5</v>
@@ -7627,7 +7632,7 @@
         <v>16</v>
       </c>
       <c r="F134" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G134" t="s">
         <v>7</v>
@@ -7636,10 +7641,10 @@
         <v>8</v>
       </c>
       <c r="I134" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="J134" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="K134">
         <v>48000</v>
@@ -7659,10 +7664,10 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="C135" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="D135" t="s">
         <v>14</v>
@@ -7677,10 +7682,10 @@
         <v>8</v>
       </c>
       <c r="I135" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="J135" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="K135">
         <v>74722</v>
@@ -7700,13 +7705,13 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="C136" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="D136" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G136" t="s">
         <v>7</v>
@@ -7715,10 +7720,10 @@
         <v>8</v>
       </c>
       <c r="I136" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="J136" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="K136">
         <v>55000</v>
@@ -7738,10 +7743,10 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="C137" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="D137" t="s">
         <v>5</v>
@@ -7750,13 +7755,13 @@
         <v>7</v>
       </c>
       <c r="H137" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I137" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="J137" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="K137">
         <v>128000</v>
@@ -7776,10 +7781,10 @@
         <v>137</v>
       </c>
       <c r="B138" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="C138" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="D138" t="s">
         <v>5</v>
@@ -7794,13 +7799,13 @@
         <v>7</v>
       </c>
       <c r="H138" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I138" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="J138" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="K138">
         <v>122000</v>
@@ -7820,10 +7825,10 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="C139" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="D139" t="s">
         <v>5</v>
@@ -7835,13 +7840,13 @@
         <v>7</v>
       </c>
       <c r="H139" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I139" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="J139" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="K139">
         <v>22000</v>
@@ -7861,10 +7866,10 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="C140" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="D140" t="s">
         <v>5</v>
@@ -7876,13 +7881,13 @@
         <v>7</v>
       </c>
       <c r="H140" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I140" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="J140" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="K140">
         <v>10000</v>
@@ -7902,10 +7907,10 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="C141" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="D141" t="s">
         <v>5</v>
@@ -7920,10 +7925,10 @@
         <v>8</v>
       </c>
       <c r="I141" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="J141" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="K141">
         <v>64000</v>
@@ -7943,10 +7948,10 @@
         <v>141</v>
       </c>
       <c r="B142" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="C142" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="D142" t="s">
         <v>5</v>
@@ -7961,10 +7966,10 @@
         <v>8</v>
       </c>
       <c r="I142" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="J142" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="K142">
         <v>95628</v>
@@ -7984,16 +7989,16 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="C143" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="D143" t="s">
         <v>5</v>
       </c>
       <c r="F143" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="G143" t="s">
         <v>7</v>
@@ -8002,10 +8007,10 @@
         <v>8</v>
       </c>
       <c r="I143" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="J143" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="K143">
         <v>39562</v>
@@ -8025,10 +8030,10 @@
         <v>143</v>
       </c>
       <c r="B144" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="C144" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="D144" t="s">
         <v>5</v>
@@ -8037,7 +8042,7 @@
         <v>16</v>
       </c>
       <c r="F144" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="G144" t="s">
         <v>7</v>
@@ -8046,10 +8051,10 @@
         <v>8</v>
       </c>
       <c r="I144" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="J144" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="K144">
         <v>105000</v>
@@ -8069,10 +8074,10 @@
         <v>144</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="C145" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="D145" t="s">
         <v>5</v>
@@ -8081,7 +8086,7 @@
         <v>23</v>
       </c>
       <c r="F145" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="G145" t="s">
         <v>7</v>
@@ -8090,10 +8095,10 @@
         <v>8</v>
       </c>
       <c r="I145" s="2" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="J145" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="K145">
         <v>60000</v>
@@ -8113,16 +8118,16 @@
         <v>145</v>
       </c>
       <c r="B146" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="C146" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="D146" t="s">
         <v>5</v>
       </c>
       <c r="F146" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G146" t="s">
         <v>7</v>
@@ -8131,10 +8136,10 @@
         <v>8</v>
       </c>
       <c r="I146" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="J146" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="K146">
         <v>39964</v>
@@ -8154,10 +8159,10 @@
         <v>146</v>
       </c>
       <c r="B147" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="C147" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="D147" t="s">
         <v>5</v>
@@ -8172,10 +8177,10 @@
         <v>8</v>
       </c>
       <c r="I147" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="J147" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="K147">
         <v>94000</v>
@@ -8195,10 +8200,10 @@
         <v>147</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="C148" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="D148" t="s">
         <v>5</v>
@@ -8207,7 +8212,7 @@
         <v>23</v>
       </c>
       <c r="F148" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G148" t="s">
         <v>7</v>
@@ -8216,10 +8221,10 @@
         <v>8</v>
       </c>
       <c r="I148" s="2" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="J148" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="K148">
         <v>75000</v>
@@ -8239,28 +8244,28 @@
         <v>148</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C149" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="D149" t="s">
         <v>5</v>
       </c>
       <c r="F149" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="G149" t="s">
         <v>7</v>
       </c>
       <c r="H149" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I149" s="2" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="J149" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="K149">
         <v>48767</v>
@@ -8280,10 +8285,10 @@
         <v>149</v>
       </c>
       <c r="B150" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="C150" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="D150" t="s">
         <v>5</v>
@@ -8292,7 +8297,7 @@
         <v>16</v>
       </c>
       <c r="F150" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G150" t="s">
         <v>7</v>
@@ -8301,10 +8306,10 @@
         <v>8</v>
       </c>
       <c r="I150" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J150" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="K150">
         <v>63824</v>
@@ -8324,10 +8329,10 @@
         <v>150</v>
       </c>
       <c r="B151" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="C151" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="D151" t="s">
         <v>14</v>
@@ -8336,7 +8341,7 @@
         <v>23</v>
       </c>
       <c r="F151" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G151" t="s">
         <v>7</v>
@@ -8345,10 +8350,10 @@
         <v>8</v>
       </c>
       <c r="I151" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="J151" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="K151">
         <v>117000</v>
@@ -8368,10 +8373,10 @@
         <v>151</v>
       </c>
       <c r="B152" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="C152" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="D152" t="s">
         <v>5</v>
@@ -8383,10 +8388,10 @@
         <v>8</v>
       </c>
       <c r="I152" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="J152" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="K152">
         <v>41000</v>
@@ -8406,10 +8411,10 @@
         <v>152</v>
       </c>
       <c r="B153" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="C153" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="D153" t="s">
         <v>5</v>
@@ -8421,10 +8426,10 @@
         <v>8</v>
       </c>
       <c r="I153" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="J153" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="K153">
         <v>96446</v>
@@ -8444,10 +8449,10 @@
         <v>153</v>
       </c>
       <c r="B154" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="C154" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="D154" t="s">
         <v>5</v>
@@ -8456,19 +8461,19 @@
         <v>16</v>
       </c>
       <c r="F154" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G154" t="s">
         <v>7</v>
       </c>
       <c r="H154" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="I154" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="J154" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="K154">
         <v>76600</v>
@@ -8488,28 +8493,28 @@
         <v>154</v>
       </c>
       <c r="B155" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="C155" t="s">
+        <v>354</v>
+      </c>
+      <c r="D155" t="s">
+        <v>5</v>
+      </c>
+      <c r="F155" t="s">
+        <v>154</v>
+      </c>
+      <c r="G155" t="s">
+        <v>7</v>
+      </c>
+      <c r="H155" t="s">
+        <v>355</v>
+      </c>
+      <c r="I155" t="s">
         <v>358</v>
       </c>
-      <c r="D155" t="s">
-        <v>5</v>
-      </c>
-      <c r="F155" t="s">
-        <v>155</v>
-      </c>
-      <c r="G155" t="s">
-        <v>7</v>
-      </c>
-      <c r="H155" t="s">
-        <v>359</v>
-      </c>
-      <c r="I155" t="s">
-        <v>362</v>
-      </c>
       <c r="J155" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="K155">
         <v>125569</v>
@@ -8529,28 +8534,28 @@
         <v>155</v>
       </c>
       <c r="B156" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="C156" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="D156" t="s">
         <v>5</v>
       </c>
       <c r="F156" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="G156" t="s">
         <v>7</v>
       </c>
       <c r="H156" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="I156" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="J156" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="K156">
         <v>51234</v>
@@ -8570,10 +8575,10 @@
         <v>156</v>
       </c>
       <c r="B157" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="C157" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="D157" t="s">
         <v>5</v>
@@ -8582,19 +8587,19 @@
         <v>16</v>
       </c>
       <c r="F157" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G157" t="s">
         <v>7</v>
       </c>
       <c r="H157" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="I157" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="J157" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="K157">
         <v>123780</v>
@@ -8614,28 +8619,28 @@
         <v>157</v>
       </c>
       <c r="B158" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="C158" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="D158" t="s">
         <v>5</v>
       </c>
       <c r="F158" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="G158" t="s">
         <v>7</v>
       </c>
       <c r="H158" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="I158" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="J158" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="K158">
         <v>46000</v>
@@ -8655,10 +8660,10 @@
         <v>158</v>
       </c>
       <c r="B159" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="C159" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="D159" t="s">
         <v>5</v>
@@ -8667,13 +8672,13 @@
         <v>7</v>
       </c>
       <c r="H159" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="I159" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="J159" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="K159">
         <v>35600</v>
@@ -8693,10 +8698,10 @@
         <v>159</v>
       </c>
       <c r="B160" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="C160" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="D160" t="s">
         <v>5</v>
@@ -8708,13 +8713,13 @@
         <v>7</v>
       </c>
       <c r="H160" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="I160" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="J160" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="K160">
         <v>199950</v>
@@ -8734,10 +8739,10 @@
         <v>160</v>
       </c>
       <c r="B161" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="C161" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="D161" t="s">
         <v>5</v>
@@ -8749,13 +8754,13 @@
         <v>7</v>
       </c>
       <c r="H161" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="I161" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="J161" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="K161">
         <v>108000</v>
@@ -8775,10 +8780,10 @@
         <v>161</v>
       </c>
       <c r="B162" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="C162" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="D162" t="s">
         <v>5</v>
@@ -8790,13 +8795,13 @@
         <v>7</v>
       </c>
       <c r="H162" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="I162" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="J162" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="K162">
         <v>142808</v>
@@ -8816,10 +8821,10 @@
         <v>162</v>
       </c>
       <c r="B163" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="C163" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="D163" t="s">
         <v>5</v>
@@ -8831,13 +8836,13 @@
         <v>7</v>
       </c>
       <c r="H163" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="I163" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="J163" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="K163">
         <v>80463</v>
@@ -8857,10 +8862,10 @@
         <v>163</v>
       </c>
       <c r="B164" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="C164" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="D164" t="s">
         <v>5</v>
@@ -8872,13 +8877,13 @@
         <v>7</v>
       </c>
       <c r="H164" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="I164" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J164" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="K164">
         <v>83000</v>
@@ -8898,10 +8903,10 @@
         <v>164</v>
       </c>
       <c r="B165" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="C165" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="D165" t="s">
         <v>5</v>
@@ -8910,13 +8915,13 @@
         <v>7</v>
       </c>
       <c r="H165" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="I165" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="J165" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="K165">
         <v>129000</v>
@@ -8936,28 +8941,28 @@
         <v>165</v>
       </c>
       <c r="B166" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="C166" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="D166" t="s">
         <v>5</v>
       </c>
       <c r="F166" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G166" t="s">
         <v>7</v>
       </c>
       <c r="H166" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I166" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="J166" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="K166">
         <v>62209</v>
@@ -8977,16 +8982,16 @@
         <v>166</v>
       </c>
       <c r="B167" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="C167" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="D167" t="s">
         <v>5</v>
       </c>
       <c r="F167" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="G167" t="s">
         <v>7</v>
@@ -8995,10 +9000,10 @@
         <v>8</v>
       </c>
       <c r="I167" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="J167" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="K167">
         <v>36117</v>
@@ -9018,10 +9023,10 @@
         <v>167</v>
       </c>
       <c r="B168" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="C168" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="D168" t="s">
         <v>5</v>
@@ -9030,19 +9035,19 @@
         <v>23</v>
       </c>
       <c r="F168" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G168" t="s">
         <v>7</v>
       </c>
       <c r="H168" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I168" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="J168" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="K168">
         <v>49900</v>
@@ -9062,10 +9067,10 @@
         <v>168</v>
       </c>
       <c r="B169" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="C169" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="D169" t="s">
         <v>5</v>
@@ -9074,19 +9079,19 @@
         <v>16</v>
       </c>
       <c r="F169" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="G169" t="s">
         <v>7</v>
       </c>
       <c r="H169" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I169" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="J169" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="K169">
         <v>39000</v>
@@ -9106,28 +9111,28 @@
         <v>169</v>
       </c>
       <c r="B170" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="C170" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="D170" t="s">
         <v>5</v>
       </c>
       <c r="F170" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="G170" t="s">
         <v>7</v>
       </c>
       <c r="H170" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I170" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="J170" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="K170">
         <v>49000</v>
@@ -9147,13 +9152,13 @@
         <v>170</v>
       </c>
       <c r="B171" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="C171" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="D171" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G171" t="s">
         <v>7</v>
@@ -9162,10 +9167,10 @@
         <v>8</v>
       </c>
       <c r="I171" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="J171" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="K171">
         <v>59400</v>
@@ -9185,10 +9190,10 @@
         <v>171</v>
       </c>
       <c r="B172" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="C172" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="D172" t="s">
         <v>5</v>
@@ -9203,10 +9208,10 @@
         <v>8</v>
       </c>
       <c r="I172" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="J172" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="K172">
         <v>65000</v>
@@ -9226,31 +9231,31 @@
         <v>172</v>
       </c>
       <c r="B173" t="s">
+        <v>397</v>
+      </c>
+      <c r="C173" t="s">
+        <v>382</v>
+      </c>
+      <c r="D173" t="s">
+        <v>5</v>
+      </c>
+      <c r="E173" t="s">
+        <v>399</v>
+      </c>
+      <c r="F173" t="s">
+        <v>398</v>
+      </c>
+      <c r="G173" t="s">
+        <v>7</v>
+      </c>
+      <c r="H173" t="s">
+        <v>400</v>
+      </c>
+      <c r="I173" t="s">
         <v>401</v>
       </c>
-      <c r="C173" t="s">
-        <v>386</v>
-      </c>
-      <c r="D173" t="s">
-        <v>5</v>
-      </c>
-      <c r="E173" t="s">
-        <v>403</v>
-      </c>
-      <c r="F173" t="s">
-        <v>402</v>
-      </c>
-      <c r="G173" t="s">
-        <v>7</v>
-      </c>
-      <c r="H173" t="s">
-        <v>404</v>
-      </c>
-      <c r="I173" t="s">
-        <v>405</v>
-      </c>
       <c r="J173" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="K173">
         <v>47000</v>
@@ -9270,28 +9275,28 @@
         <v>173</v>
       </c>
       <c r="B174" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C174" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="D174" t="s">
         <v>5</v>
       </c>
       <c r="E174" t="s">
+        <v>399</v>
+      </c>
+      <c r="G174" t="s">
+        <v>7</v>
+      </c>
+      <c r="H174" t="s">
+        <v>400</v>
+      </c>
+      <c r="I174" t="s">
         <v>403</v>
       </c>
-      <c r="G174" t="s">
-        <v>7</v>
-      </c>
-      <c r="H174" t="s">
-        <v>404</v>
-      </c>
-      <c r="I174" t="s">
-        <v>407</v>
-      </c>
       <c r="J174" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="K174">
         <v>29000</v>
@@ -9311,10 +9316,10 @@
         <v>174</v>
       </c>
       <c r="B175" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="C175" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="D175" t="s">
         <v>5</v>
@@ -9323,19 +9328,19 @@
         <v>23</v>
       </c>
       <c r="F175" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G175" t="s">
         <v>7</v>
       </c>
       <c r="H175" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I175" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="J175" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="K175">
         <v>132239</v>
@@ -9355,10 +9360,10 @@
         <v>175</v>
       </c>
       <c r="B176" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="C176" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="D176" t="s">
         <v>5</v>
@@ -9370,13 +9375,13 @@
         <v>7</v>
       </c>
       <c r="H176" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="I176" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="J176" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="K176">
         <v>35016</v>
@@ -9396,10 +9401,10 @@
         <v>176</v>
       </c>
       <c r="B177" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="C177" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="D177" t="s">
         <v>5</v>
@@ -9408,13 +9413,13 @@
         <v>7</v>
       </c>
       <c r="H177" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I177" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="J177" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="K177">
         <v>60000</v>
@@ -9434,28 +9439,28 @@
         <v>177</v>
       </c>
       <c r="B178" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="C178" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="D178" t="s">
         <v>5</v>
       </c>
       <c r="F178" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="G178" t="s">
         <v>7</v>
       </c>
       <c r="H178" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="I178" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="J178" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="K178">
         <v>90244</v>
@@ -9475,10 +9480,10 @@
         <v>178</v>
       </c>
       <c r="B179" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="C179" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="D179" t="s">
         <v>5</v>
@@ -9487,13 +9492,13 @@
         <v>7</v>
       </c>
       <c r="H179" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="I179" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="J179" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="K179">
         <v>38700</v>
@@ -9513,10 +9518,10 @@
         <v>179</v>
       </c>
       <c r="B180" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="C180" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="D180" t="s">
         <v>5</v>
@@ -9525,13 +9530,13 @@
         <v>7</v>
       </c>
       <c r="H180" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="I180" s="1" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="J180" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="K180">
         <v>62414</v>
@@ -9551,10 +9556,10 @@
         <v>180</v>
       </c>
       <c r="B181" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="C181" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="D181" t="s">
         <v>5</v>
@@ -9563,13 +9568,13 @@
         <v>7</v>
       </c>
       <c r="H181" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="I181" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="J181" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="K181">
         <v>51000</v>
@@ -9589,10 +9594,10 @@
         <v>181</v>
       </c>
       <c r="B182" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="C182" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="D182" t="s">
         <v>5</v>
@@ -9604,13 +9609,13 @@
         <v>7</v>
       </c>
       <c r="H182" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I182" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="J182" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="K182">
         <v>53115</v>
@@ -9630,10 +9635,10 @@
         <v>182</v>
       </c>
       <c r="B183" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="C183" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="D183" t="s">
         <v>5</v>
@@ -9642,13 +9647,13 @@
         <v>7</v>
       </c>
       <c r="H183" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="I183" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="J183" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="K183">
         <v>120000</v>
@@ -9668,10 +9673,10 @@
         <v>183</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="C184" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="D184" t="s">
         <v>5</v>
@@ -9683,13 +9688,13 @@
         <v>7</v>
       </c>
       <c r="H184" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I184" s="3" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="J184" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="K184">
         <v>66477</v>
@@ -9709,10 +9714,10 @@
         <v>184</v>
       </c>
       <c r="B185" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="C185" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="D185" t="s">
         <v>5</v>
@@ -9724,10 +9729,10 @@
         <v>7</v>
       </c>
       <c r="H185" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="I185" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="K185">
         <v>59300</v>
@@ -9747,22 +9752,22 @@
         <v>185</v>
       </c>
       <c r="B186" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="C186" t="s">
+        <v>424</v>
+      </c>
+      <c r="D186" t="s">
+        <v>5</v>
+      </c>
+      <c r="G186" t="s">
+        <v>7</v>
+      </c>
+      <c r="H186" t="s">
+        <v>425</v>
+      </c>
+      <c r="I186" t="s">
         <v>428</v>
-      </c>
-      <c r="D186" t="s">
-        <v>5</v>
-      </c>
-      <c r="G186" t="s">
-        <v>7</v>
-      </c>
-      <c r="H186" t="s">
-        <v>429</v>
-      </c>
-      <c r="I186" t="s">
-        <v>432</v>
       </c>
       <c r="K186">
         <v>44000</v>
@@ -9782,10 +9787,10 @@
         <v>186</v>
       </c>
       <c r="B187" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="C187" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="D187" t="s">
         <v>5</v>
@@ -9794,10 +9799,10 @@
         <v>7</v>
       </c>
       <c r="H187" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="I187" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="K187">
         <v>26528</v>
@@ -9817,10 +9822,10 @@
         <v>187</v>
       </c>
       <c r="B188" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="C188" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="D188" t="s">
         <v>5</v>
@@ -9832,10 +9837,10 @@
         <v>7</v>
       </c>
       <c r="H188" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="I188" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="K188">
         <v>95684</v>
@@ -9855,10 +9860,10 @@
         <v>188</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="C189" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="D189" t="s">
         <v>5</v>
@@ -9867,10 +9872,10 @@
         <v>7</v>
       </c>
       <c r="H189" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I189" s="4" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="K189">
         <v>26737</v>
@@ -9890,10 +9895,10 @@
         <v>189</v>
       </c>
       <c r="B190" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="C190" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="D190" t="s">
         <v>5</v>
@@ -9905,10 +9910,10 @@
         <v>7</v>
       </c>
       <c r="H190" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="I190" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="K190">
         <v>60000</v>
@@ -9928,10 +9933,10 @@
         <v>190</v>
       </c>
       <c r="B191" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="C191" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="D191" t="s">
         <v>5</v>
@@ -9940,10 +9945,10 @@
         <v>7</v>
       </c>
       <c r="H191" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="I191" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="K191">
         <v>34895</v>
@@ -9960,29 +9965,29 @@
     </row>
     <row r="192" spans="1:14">
       <c r="B192" s="1" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="G192" s="1" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="H192" s="1" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="I192" s="1" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
     </row>
     <row r="193" spans="2:2">
       <c r="B193" s="1" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10222"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yuhang/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\intern.bjres\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C93D5165-38BF-F643-8789-3E20CA16FEBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB266823-E62C-4725-A568-99FB550A322A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-7900" yWindow="-28200" windowWidth="25620" windowHeight="28200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -140,9 +140,6 @@
     <t>2006 Q2</t>
   </si>
   <si>
-    <t>116.456470,39.907620</t>
-  </si>
-  <si>
     <t>远洋国际中心A座</t>
   </si>
   <si>
@@ -1392,7 +1389,7 @@
   </si>
   <si>
     <t>LEEDS</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>RSH</t>
@@ -1405,119 +1402,107 @@
   </si>
   <si>
     <t>中国人寿中心</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>朝阳区</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>中国人寿金融中心（国寿金融中心）</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>116.469030,39.911173</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>116.359101,39.916286</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>116.414316,39.909603</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>116.416180,39.909603</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>116.412452,39.909603</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>116.365799,40.001522</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>中关村东升科技园·学北园</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>116.352247,40.015235</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>116.349697,39.932894</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>奥南五号-B座（恒毅大厦）</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>奥南五号-A座（天圆祥泰大厦）</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>116.406387,39.981515</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>116.406387,39.980615</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>合景国际金融广场（4B)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>116.680295,39.907589</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>116.358503,39.931864</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>这个还有问题</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>116.362230,39.920558</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>116.313304,39.982116</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>116.320807,39.956309</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>116.319635,39.956309</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>已经更改</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>116.323984,39.958472</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>116.377078,39.888674</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>116.371113,39.967322</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>116.470221,39.955076</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>116.459281,39.960483</t>
@@ -1527,85 +1512,103 @@
   </si>
   <si>
     <t>CBD</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>北京市</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>IFC国际财源中心</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>116.452709,39.907549</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>116.43926,39.909474</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>116.435881,39.919317</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>116.429644,39.906833</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>华贸中心一座</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>华贸中心二座</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>116.464627,39.912332</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>116.464467,39.912049</t>
+  </si>
+  <si>
+    <t>116.464674,39.912865</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>116.460321,39.906941</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>116.454891,39.960979</t>
+  </si>
+  <si>
+    <t>116.456886,39.962611</t>
+  </si>
+  <si>
+    <t>116.445694,39.970256</t>
   </si>
   <si>
     <t>116.491439,39.914113</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>华贸中心一座</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>华贸中心二座</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>116.464627,39.912332</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>116.464467,39.912049</t>
-  </si>
-  <si>
-    <t>116.464674,39.912865</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>116.460321,39.906941</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>116.454891,39.960979</t>
-  </si>
-  <si>
-    <t>116.456886,39.962611</t>
-  </si>
-  <si>
-    <t>116.445694,39.970256</t>
+  </si>
+  <si>
+    <t>116.456808,39.907696</t>
+  </si>
+  <si>
+    <t>116.412649,39.909443</t>
+  </si>
+  <si>
+    <t>116.416316,39.909562</t>
+  </si>
+  <si>
+    <t>116.414436,39.909474</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1613,14 +1616,22 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1631,14 +1642,13 @@
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1666,20 +1676,22 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2" xfId="1" xr:uid="{81D4EE7A-49F9-4559-B92D-CA7C8AC626DC}"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1696,11 +1708,7 @@
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <person displayName="Lu, Ming" id="{5082D207-AEA0-4BFE-AD66-E999121DF51A}" userId="S::ming.lu@colliers.com::32ed6a1f-6094-49ff-9223-1ec24026be8e" providerId="AD"/>
-  <person displayName="Gao, Cassie" id="{5D34FAD7-9A91-4AF2-9BF2-44013CCF14CA}" userId="S::cassie.gao@colliers.com::4a65d78a-bee0-4019-98ea-63fb6685db53" providerId="AD"/>
-  <person displayName="Zhao, Danni" id="{5427DF3F-99FD-4443-A208-B99A4A464D38}" userId="S::danni.zhao@colliers.com::342a9774-4ff6-4a8f-b5fb-e015adf797d2" providerId="AD"/>
-</personList>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1989,41 +1997,41 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B280671-4AFA-4641-88D4-A51F39483890}">
   <dimension ref="A1:P194"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="5.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="41.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="41.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.1796875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B1" t="s">
+        <v>443</v>
+      </c>
+      <c r="C1" t="s">
         <v>444</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>445</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="F1" t="s">
         <v>446</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>452</v>
-      </c>
-      <c r="F1" t="s">
-        <v>447</v>
       </c>
       <c r="G1" t="s">
         <v>0</v>
@@ -2035,19 +2043,19 @@
         <v>2</v>
       </c>
       <c r="J1" t="s">
+        <v>447</v>
+      </c>
+      <c r="K1" t="s">
+        <v>442</v>
+      </c>
+      <c r="L1" t="s">
         <v>448</v>
       </c>
-      <c r="K1" t="s">
-        <v>443</v>
-      </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>449</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>450</v>
-      </c>
-      <c r="N1" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -2076,7 +2084,7 @@
         <v>9</v>
       </c>
       <c r="J2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K2">
         <v>72308</v>
@@ -2117,7 +2125,7 @@
         <v>12</v>
       </c>
       <c r="J3" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K3">
         <v>72308</v>
@@ -2161,7 +2169,7 @@
         <v>17</v>
       </c>
       <c r="J4" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K4">
         <v>130769</v>
@@ -2205,7 +2213,7 @@
         <v>20</v>
       </c>
       <c r="J5" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K5">
         <v>64615</v>
@@ -2249,7 +2257,7 @@
         <v>24</v>
       </c>
       <c r="J6" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K6">
         <v>80091</v>
@@ -2290,7 +2298,7 @@
         <v>27</v>
       </c>
       <c r="J7" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="K7">
         <v>70673</v>
@@ -2334,7 +2342,7 @@
         <v>30</v>
       </c>
       <c r="J8" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K8">
         <v>90466</v>
@@ -2375,7 +2383,7 @@
         <v>32</v>
       </c>
       <c r="J9" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="K9">
         <v>46720</v>
@@ -2415,11 +2423,11 @@
       <c r="H10" t="s">
         <v>8</v>
       </c>
-      <c r="I10" t="s">
-        <v>35</v>
+      <c r="I10" s="7" t="s">
+        <v>500</v>
       </c>
       <c r="J10" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="K10">
         <v>95000</v>
@@ -2439,7 +2447,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C11" t="s">
         <v>4</v>
@@ -2451,7 +2459,7 @@
         <v>23</v>
       </c>
       <c r="F11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G11" t="s">
         <v>7</v>
@@ -2460,10 +2468,10 @@
         <v>8</v>
       </c>
       <c r="I11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J11" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K11">
         <v>85300</v>
@@ -2483,7 +2491,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C12" t="s">
         <v>4</v>
@@ -2495,7 +2503,7 @@
         <v>16</v>
       </c>
       <c r="F12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G12" t="s">
         <v>7</v>
@@ -2504,10 +2512,10 @@
         <v>8</v>
       </c>
       <c r="I12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="K12">
         <v>33305</v>
@@ -2527,7 +2535,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C13" t="s">
         <v>4</v>
@@ -2539,7 +2547,7 @@
         <v>23</v>
       </c>
       <c r="F13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G13" t="s">
         <v>7</v>
@@ -2548,10 +2556,10 @@
         <v>8</v>
       </c>
       <c r="I13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J13" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K13">
         <v>120245.21</v>
@@ -2571,7 +2579,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C14" t="s">
         <v>4</v>
@@ -2583,7 +2591,7 @@
         <v>23</v>
       </c>
       <c r="F14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G14" t="s">
         <v>7</v>
@@ -2592,10 +2600,10 @@
         <v>8</v>
       </c>
       <c r="I14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J14" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K14">
         <v>70425.53</v>
@@ -2615,7 +2623,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C15" t="s">
         <v>4</v>
@@ -2627,7 +2635,7 @@
         <v>23</v>
       </c>
       <c r="F15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G15" t="s">
         <v>7</v>
@@ -2636,10 +2644,10 @@
         <v>8</v>
       </c>
       <c r="I15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J15" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K15">
         <v>78000</v>
@@ -2659,7 +2667,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C16" t="s">
         <v>4</v>
@@ -2671,7 +2679,7 @@
         <v>23</v>
       </c>
       <c r="F16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G16" t="s">
         <v>7</v>
@@ -2680,10 +2688,10 @@
         <v>8</v>
       </c>
       <c r="I16" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J16" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="K16">
         <v>102796</v>
@@ -2703,7 +2711,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C17" t="s">
         <v>4</v>
@@ -2715,7 +2723,7 @@
         <v>16</v>
       </c>
       <c r="F17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G17" t="s">
         <v>7</v>
@@ -2724,10 +2732,10 @@
         <v>8</v>
       </c>
       <c r="I17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J17" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="K17">
         <v>49200</v>
@@ -2747,7 +2755,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C18" t="s">
         <v>4</v>
@@ -2759,7 +2767,7 @@
         <v>23</v>
       </c>
       <c r="F18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G18" t="s">
         <v>7</v>
@@ -2768,10 +2776,10 @@
         <v>8</v>
       </c>
       <c r="I18" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J18" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="K18">
         <v>65096</v>
@@ -2791,7 +2799,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C19" t="s">
         <v>4</v>
@@ -2803,7 +2811,7 @@
         <v>16</v>
       </c>
       <c r="F19" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G19" t="s">
         <v>7</v>
@@ -2812,10 +2820,10 @@
         <v>8</v>
       </c>
       <c r="I19" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J19" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K19">
         <v>56000</v>
@@ -2835,7 +2843,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C20" t="s">
         <v>4</v>
@@ -2847,7 +2855,7 @@
         <v>23</v>
       </c>
       <c r="F20" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G20" t="s">
         <v>7</v>
@@ -2856,10 +2864,10 @@
         <v>8</v>
       </c>
       <c r="I20" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J20" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="K20">
         <v>177847</v>
@@ -2879,7 +2887,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C21" t="s">
         <v>4</v>
@@ -2891,7 +2899,7 @@
         <v>23</v>
       </c>
       <c r="F21" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G21" t="s">
         <v>7</v>
@@ -2900,10 +2908,10 @@
         <v>8</v>
       </c>
       <c r="I21" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J21" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K21">
         <v>83000</v>
@@ -2923,7 +2931,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C22" t="s">
         <v>4</v>
@@ -2932,7 +2940,7 @@
         <v>5</v>
       </c>
       <c r="F22" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G22" t="s">
         <v>7</v>
@@ -2941,10 +2949,10 @@
         <v>8</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="J22" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="K22">
         <v>26000</v>
@@ -2964,7 +2972,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C23" t="s">
         <v>4</v>
@@ -2982,10 +2990,10 @@
         <v>8</v>
       </c>
       <c r="I23" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J23" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K23">
         <v>85887</v>
@@ -3005,7 +3013,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C24" t="s">
         <v>4</v>
@@ -3023,10 +3031,10 @@
         <v>8</v>
       </c>
       <c r="I24" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J24" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K24">
         <v>20000</v>
@@ -3046,7 +3054,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C25" t="s">
         <v>4</v>
@@ -3058,7 +3066,7 @@
         <v>23</v>
       </c>
       <c r="F25" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G25" t="s">
         <v>7</v>
@@ -3067,10 +3075,10 @@
         <v>8</v>
       </c>
       <c r="I25" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J25" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K25">
         <v>146385</v>
@@ -3090,7 +3098,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C26" t="s">
         <v>4</v>
@@ -3102,7 +3110,7 @@
         <v>23</v>
       </c>
       <c r="F26" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G26" t="s">
         <v>7</v>
@@ -3111,10 +3119,10 @@
         <v>8</v>
       </c>
       <c r="I26" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J26" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K26">
         <v>87000</v>
@@ -3134,7 +3142,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C27" t="s">
         <v>4</v>
@@ -3146,7 +3154,7 @@
         <v>23</v>
       </c>
       <c r="F27" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G27" t="s">
         <v>7</v>
@@ -3155,10 +3163,10 @@
         <v>8</v>
       </c>
       <c r="I27" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J27" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K27">
         <v>147166.79999999999</v>
@@ -3178,7 +3186,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C28" t="s">
         <v>4</v>
@@ -3190,7 +3198,7 @@
         <v>16</v>
       </c>
       <c r="F28" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G28" t="s">
         <v>7</v>
@@ -3199,10 +3207,10 @@
         <v>8</v>
       </c>
       <c r="I28" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J28" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K28">
         <v>46063</v>
@@ -3222,7 +3230,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C29" t="s">
         <v>4</v>
@@ -3234,7 +3242,7 @@
         <v>23</v>
       </c>
       <c r="F29" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G29" t="s">
         <v>7</v>
@@ -3243,10 +3251,10 @@
         <v>8</v>
       </c>
       <c r="I29" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J29" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="K29">
         <v>47261</v>
@@ -3266,7 +3274,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C30" t="s">
         <v>4</v>
@@ -3278,19 +3286,19 @@
         <v>23</v>
       </c>
       <c r="F30" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G30" t="s">
         <v>7</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="J30" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K30">
         <v>119000</v>
@@ -3310,7 +3318,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C31" t="s">
         <v>4</v>
@@ -3319,7 +3327,7 @@
         <v>5</v>
       </c>
       <c r="F31" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G31" t="s">
         <v>7</v>
@@ -3328,10 +3336,10 @@
         <v>8</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="J31" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="K31">
         <v>47000</v>
@@ -3351,7 +3359,7 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C32" t="s">
         <v>4</v>
@@ -3363,7 +3371,7 @@
         <v>16</v>
       </c>
       <c r="F32" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G32" t="s">
         <v>7</v>
@@ -3372,10 +3380,10 @@
         <v>8</v>
       </c>
       <c r="I32" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J32" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="K32">
         <v>186000</v>
@@ -3395,7 +3403,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C33" t="s">
         <v>4</v>
@@ -3410,10 +3418,10 @@
         <v>8</v>
       </c>
       <c r="I33" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J33" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K33">
         <v>40800</v>
@@ -3433,7 +3441,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C34" t="s">
         <v>4</v>
@@ -3442,7 +3450,7 @@
         <v>5</v>
       </c>
       <c r="F34" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G34" t="s">
         <v>7</v>
@@ -3451,10 +3459,10 @@
         <v>8</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="J34" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K34">
         <v>55200</v>
@@ -3474,7 +3482,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C35" t="s">
         <v>4</v>
@@ -3486,7 +3494,7 @@
         <v>16</v>
       </c>
       <c r="F35" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G35" t="s">
         <v>7</v>
@@ -3495,10 +3503,10 @@
         <v>8</v>
       </c>
       <c r="I35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J35" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="K35">
         <v>350000</v>
@@ -3518,7 +3526,7 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C36" t="s">
         <v>4</v>
@@ -3536,10 +3544,10 @@
         <v>8</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="J36" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K36">
         <v>65000</v>
@@ -3559,7 +3567,7 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C37" t="s">
         <v>4</v>
@@ -3577,10 +3585,10 @@
         <v>8</v>
       </c>
       <c r="I37" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="J37" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K37">
         <v>35000</v>
@@ -3600,7 +3608,7 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C38" t="s">
         <v>4</v>
@@ -3618,10 +3626,10 @@
         <v>8</v>
       </c>
       <c r="I38" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="J38" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="K38">
         <v>47000</v>
@@ -3641,7 +3649,7 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C39" t="s">
         <v>4</v>
@@ -3653,7 +3661,7 @@
         <v>23</v>
       </c>
       <c r="F39" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G39" t="s">
         <v>7</v>
@@ -3662,10 +3670,10 @@
         <v>8</v>
       </c>
       <c r="I39" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J39" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="K39">
         <v>120000</v>
@@ -3685,7 +3693,7 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C40" t="s">
         <v>4</v>
@@ -3703,10 +3711,10 @@
         <v>8</v>
       </c>
       <c r="I40" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="J40" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K40">
         <v>83000</v>
@@ -3726,7 +3734,7 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C41" t="s">
         <v>4</v>
@@ -3744,10 +3752,10 @@
         <v>8</v>
       </c>
       <c r="I41" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J41" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="K41">
         <v>66030</v>
@@ -3767,7 +3775,7 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C42" t="s">
         <v>4</v>
@@ -3782,10 +3790,10 @@
         <v>8</v>
       </c>
       <c r="I42" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="J42" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="K42">
         <v>40000</v>
@@ -3805,10 +3813,10 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
+        <v>110</v>
+      </c>
+      <c r="C43" t="s">
         <v>111</v>
-      </c>
-      <c r="C43" t="s">
-        <v>112</v>
       </c>
       <c r="D43" t="s">
         <v>5</v>
@@ -3817,19 +3825,19 @@
         <v>16</v>
       </c>
       <c r="F43" t="s">
+        <v>112</v>
+      </c>
+      <c r="G43" t="s">
+        <v>7</v>
+      </c>
+      <c r="H43" t="s">
         <v>113</v>
       </c>
-      <c r="G43" t="s">
-        <v>7</v>
-      </c>
-      <c r="H43" t="s">
+      <c r="I43" t="s">
         <v>114</v>
       </c>
-      <c r="I43" t="s">
-        <v>115</v>
-      </c>
       <c r="J43" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K43">
         <v>40000</v>
@@ -3849,28 +3857,28 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
+        <v>115</v>
+      </c>
+      <c r="C44" t="s">
+        <v>111</v>
+      </c>
+      <c r="D44" t="s">
+        <v>5</v>
+      </c>
+      <c r="F44" t="s">
         <v>116</v>
       </c>
-      <c r="C44" t="s">
-        <v>112</v>
-      </c>
-      <c r="D44" t="s">
-        <v>5</v>
-      </c>
-      <c r="F44" t="s">
+      <c r="G44" t="s">
+        <v>7</v>
+      </c>
+      <c r="H44" t="s">
+        <v>113</v>
+      </c>
+      <c r="I44" t="s">
         <v>117</v>
       </c>
-      <c r="G44" t="s">
-        <v>7</v>
-      </c>
-      <c r="H44" t="s">
-        <v>114</v>
-      </c>
-      <c r="I44" t="s">
-        <v>118</v>
-      </c>
       <c r="J44" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K44">
         <v>54100</v>
@@ -3890,10 +3898,10 @@
         <v>44</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C45" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D45" t="s">
         <v>5</v>
@@ -3902,19 +3910,19 @@
         <v>23</v>
       </c>
       <c r="F45" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G45" t="s">
         <v>7</v>
       </c>
       <c r="H45" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>463</v>
+        <v>501</v>
       </c>
       <c r="J45" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K45">
         <v>100000</v>
@@ -3934,10 +3942,10 @@
         <v>45</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C46" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D46" t="s">
         <v>5</v>
@@ -3946,19 +3954,19 @@
         <v>23</v>
       </c>
       <c r="F46" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G46" t="s">
         <v>7</v>
       </c>
       <c r="H46" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>462</v>
+        <v>502</v>
       </c>
       <c r="J46" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K46">
         <v>150000</v>
@@ -3978,10 +3986,10 @@
         <v>46</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C47" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D47" t="s">
         <v>5</v>
@@ -3990,19 +3998,19 @@
         <v>23</v>
       </c>
       <c r="F47" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G47" t="s">
         <v>7</v>
       </c>
       <c r="H47" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>461</v>
+        <v>503</v>
       </c>
       <c r="J47" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K47">
         <v>50000</v>
@@ -4022,10 +4030,10 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C48" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D48" t="s">
         <v>5</v>
@@ -4034,19 +4042,19 @@
         <v>23</v>
       </c>
       <c r="F48" t="s">
+        <v>125</v>
+      </c>
+      <c r="G48" t="s">
+        <v>7</v>
+      </c>
+      <c r="H48" t="s">
+        <v>113</v>
+      </c>
+      <c r="I48" t="s">
         <v>126</v>
       </c>
-      <c r="G48" t="s">
-        <v>7</v>
-      </c>
-      <c r="H48" t="s">
-        <v>114</v>
-      </c>
-      <c r="I48" t="s">
-        <v>127</v>
-      </c>
       <c r="J48" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="K48">
         <v>43000</v>
@@ -4066,28 +4074,28 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
+        <v>127</v>
+      </c>
+      <c r="C49" t="s">
+        <v>111</v>
+      </c>
+      <c r="D49" t="s">
+        <v>5</v>
+      </c>
+      <c r="F49" t="s">
         <v>128</v>
       </c>
-      <c r="C49" t="s">
-        <v>112</v>
-      </c>
-      <c r="D49" t="s">
-        <v>5</v>
-      </c>
-      <c r="F49" t="s">
+      <c r="G49" t="s">
+        <v>7</v>
+      </c>
+      <c r="H49" t="s">
+        <v>113</v>
+      </c>
+      <c r="I49" t="s">
         <v>129</v>
       </c>
-      <c r="G49" t="s">
-        <v>7</v>
-      </c>
-      <c r="H49" t="s">
-        <v>114</v>
-      </c>
-      <c r="I49" t="s">
-        <v>130</v>
-      </c>
       <c r="J49" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="K49">
         <v>65000</v>
@@ -4107,10 +4115,10 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C50" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D50" t="s">
         <v>5</v>
@@ -4119,19 +4127,19 @@
         <v>23</v>
       </c>
       <c r="F50" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G50" t="s">
         <v>7</v>
       </c>
       <c r="H50" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I50" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J50" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="K50">
         <v>56000</v>
@@ -4151,28 +4159,28 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
+        <v>133</v>
+      </c>
+      <c r="C51" t="s">
+        <v>111</v>
+      </c>
+      <c r="D51" t="s">
+        <v>5</v>
+      </c>
+      <c r="F51" t="s">
+        <v>58</v>
+      </c>
+      <c r="G51" t="s">
+        <v>7</v>
+      </c>
+      <c r="H51" t="s">
+        <v>113</v>
+      </c>
+      <c r="I51" t="s">
         <v>134</v>
       </c>
-      <c r="C51" t="s">
-        <v>112</v>
-      </c>
-      <c r="D51" t="s">
-        <v>5</v>
-      </c>
-      <c r="F51" t="s">
-        <v>59</v>
-      </c>
-      <c r="G51" t="s">
-        <v>7</v>
-      </c>
-      <c r="H51" t="s">
-        <v>114</v>
-      </c>
-      <c r="I51" t="s">
-        <v>135</v>
-      </c>
       <c r="J51" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="K51">
         <v>160000</v>
@@ -4192,10 +4200,10 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C52" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D52" t="s">
         <v>5</v>
@@ -4207,13 +4215,13 @@
         <v>7</v>
       </c>
       <c r="H52" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I52" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="J52" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="K52">
         <v>33000</v>
@@ -4233,10 +4241,10 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C53" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D53" t="s">
         <v>5</v>
@@ -4245,19 +4253,19 @@
         <v>16</v>
       </c>
       <c r="F53" t="s">
+        <v>138</v>
+      </c>
+      <c r="G53" t="s">
+        <v>7</v>
+      </c>
+      <c r="H53" t="s">
+        <v>113</v>
+      </c>
+      <c r="I53" t="s">
         <v>139</v>
       </c>
-      <c r="G53" t="s">
-        <v>7</v>
-      </c>
-      <c r="H53" t="s">
-        <v>114</v>
-      </c>
-      <c r="I53" t="s">
-        <v>140</v>
-      </c>
       <c r="J53" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="K53">
         <v>41318</v>
@@ -4277,28 +4285,28 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
+        <v>140</v>
+      </c>
+      <c r="C54" t="s">
+        <v>111</v>
+      </c>
+      <c r="D54" t="s">
+        <v>5</v>
+      </c>
+      <c r="F54" t="s">
+        <v>130</v>
+      </c>
+      <c r="G54" t="s">
+        <v>7</v>
+      </c>
+      <c r="H54" t="s">
+        <v>113</v>
+      </c>
+      <c r="I54" t="s">
         <v>141</v>
       </c>
-      <c r="C54" t="s">
-        <v>112</v>
-      </c>
-      <c r="D54" t="s">
-        <v>5</v>
-      </c>
-      <c r="F54" t="s">
-        <v>131</v>
-      </c>
-      <c r="G54" t="s">
-        <v>7</v>
-      </c>
-      <c r="H54" t="s">
-        <v>114</v>
-      </c>
-      <c r="I54" t="s">
-        <v>142</v>
-      </c>
       <c r="J54" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K54">
         <v>34131</v>
@@ -4318,28 +4326,28 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
+        <v>142</v>
+      </c>
+      <c r="C55" t="s">
+        <v>111</v>
+      </c>
+      <c r="D55" t="s">
+        <v>5</v>
+      </c>
+      <c r="F55" t="s">
         <v>143</v>
       </c>
-      <c r="C55" t="s">
-        <v>112</v>
-      </c>
-      <c r="D55" t="s">
-        <v>5</v>
-      </c>
-      <c r="F55" t="s">
+      <c r="G55" t="s">
+        <v>7</v>
+      </c>
+      <c r="H55" t="s">
+        <v>113</v>
+      </c>
+      <c r="I55" t="s">
         <v>144</v>
       </c>
-      <c r="G55" t="s">
-        <v>7</v>
-      </c>
-      <c r="H55" t="s">
-        <v>114</v>
-      </c>
-      <c r="I55" t="s">
-        <v>145</v>
-      </c>
       <c r="J55" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K55">
         <v>48000</v>
@@ -4359,10 +4367,10 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C56" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D56" t="s">
         <v>5</v>
@@ -4374,13 +4382,13 @@
         <v>7</v>
       </c>
       <c r="H56" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="J56" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K56">
         <v>16000</v>
@@ -4400,10 +4408,10 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C57" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D57" t="s">
         <v>5</v>
@@ -4412,19 +4420,19 @@
         <v>16</v>
       </c>
       <c r="F57" t="s">
+        <v>147</v>
+      </c>
+      <c r="G57" t="s">
+        <v>7</v>
+      </c>
+      <c r="H57" t="s">
+        <v>113</v>
+      </c>
+      <c r="I57" t="s">
         <v>148</v>
       </c>
-      <c r="G57" t="s">
-        <v>7</v>
-      </c>
-      <c r="H57" t="s">
-        <v>114</v>
-      </c>
-      <c r="I57" t="s">
-        <v>149</v>
-      </c>
       <c r="J57" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="K57">
         <v>30000</v>
@@ -4444,10 +4452,10 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C58" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D58" t="s">
         <v>5</v>
@@ -4456,19 +4464,19 @@
         <v>16</v>
       </c>
       <c r="F58" t="s">
+        <v>150</v>
+      </c>
+      <c r="G58" t="s">
+        <v>7</v>
+      </c>
+      <c r="H58" t="s">
+        <v>113</v>
+      </c>
+      <c r="I58" t="s">
         <v>151</v>
       </c>
-      <c r="G58" t="s">
-        <v>7</v>
-      </c>
-      <c r="H58" t="s">
-        <v>114</v>
-      </c>
-      <c r="I58" t="s">
-        <v>152</v>
-      </c>
       <c r="J58" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="K58">
         <v>56000</v>
@@ -4488,10 +4496,10 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C59" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D59" t="s">
         <v>5</v>
@@ -4500,19 +4508,19 @@
         <v>16</v>
       </c>
       <c r="F59" t="s">
+        <v>153</v>
+      </c>
+      <c r="G59" t="s">
+        <v>7</v>
+      </c>
+      <c r="H59" t="s">
+        <v>113</v>
+      </c>
+      <c r="I59" t="s">
         <v>154</v>
       </c>
-      <c r="G59" t="s">
-        <v>7</v>
-      </c>
-      <c r="H59" t="s">
-        <v>114</v>
-      </c>
-      <c r="I59" t="s">
-        <v>155</v>
-      </c>
       <c r="J59" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K59">
         <v>43000</v>
@@ -4532,10 +4540,10 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C60" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D60" t="s">
         <v>5</v>
@@ -4550,10 +4558,10 @@
         <v>8</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="J60" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="K60">
         <v>110000</v>
@@ -4573,25 +4581,25 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
+        <v>156</v>
+      </c>
+      <c r="C61" t="s">
+        <v>111</v>
+      </c>
+      <c r="D61" t="s">
+        <v>5</v>
+      </c>
+      <c r="G61" t="s">
+        <v>7</v>
+      </c>
+      <c r="H61" t="s">
+        <v>113</v>
+      </c>
+      <c r="I61" t="s">
         <v>157</v>
       </c>
-      <c r="C61" t="s">
-        <v>112</v>
-      </c>
-      <c r="D61" t="s">
-        <v>5</v>
-      </c>
-      <c r="G61" t="s">
-        <v>7</v>
-      </c>
-      <c r="H61" t="s">
-        <v>114</v>
-      </c>
-      <c r="I61" t="s">
-        <v>158</v>
-      </c>
       <c r="J61" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K61">
         <v>56160</v>
@@ -4611,10 +4619,10 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C62" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D62" t="s">
         <v>14</v>
@@ -4626,13 +4634,13 @@
         <v>7</v>
       </c>
       <c r="H62" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I62" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J62" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K62">
         <v>138444</v>
@@ -4651,11 +4659,11 @@
       <c r="A63">
         <v>62</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B63" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="C63" t="s">
         <v>161</v>
-      </c>
-      <c r="C63" t="s">
-        <v>162</v>
       </c>
       <c r="D63" t="s">
         <v>5</v>
@@ -4664,19 +4672,19 @@
         <v>16</v>
       </c>
       <c r="F63" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G63" t="s">
         <v>7</v>
       </c>
       <c r="H63" t="s">
-        <v>86</v>
-      </c>
-      <c r="I63" s="1" t="s">
-        <v>494</v>
+        <v>85</v>
+      </c>
+      <c r="I63" s="2" t="s">
+        <v>499</v>
       </c>
       <c r="J63" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="K63">
         <v>31000</v>
@@ -4696,28 +4704,28 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C64" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D64" t="s">
         <v>14</v>
       </c>
       <c r="F64" t="s">
+        <v>164</v>
+      </c>
+      <c r="G64" t="s">
+        <v>7</v>
+      </c>
+      <c r="H64" t="s">
+        <v>85</v>
+      </c>
+      <c r="I64" t="s">
         <v>165</v>
       </c>
-      <c r="G64" t="s">
-        <v>7</v>
-      </c>
-      <c r="H64" t="s">
-        <v>86</v>
-      </c>
-      <c r="I64" t="s">
-        <v>166</v>
-      </c>
       <c r="J64" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="K64">
         <v>120000</v>
@@ -4737,10 +4745,10 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C65" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D65" t="s">
         <v>5</v>
@@ -4752,13 +4760,13 @@
         <v>7</v>
       </c>
       <c r="H65" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I65" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J65" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="K65">
         <v>25900</v>
@@ -4778,28 +4786,28 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
+        <v>168</v>
+      </c>
+      <c r="C66" t="s">
+        <v>161</v>
+      </c>
+      <c r="D66" t="s">
+        <v>5</v>
+      </c>
+      <c r="F66" t="s">
         <v>169</v>
       </c>
-      <c r="C66" t="s">
-        <v>162</v>
-      </c>
-      <c r="D66" t="s">
-        <v>5</v>
-      </c>
-      <c r="F66" t="s">
+      <c r="G66" t="s">
+        <v>7</v>
+      </c>
+      <c r="H66" t="s">
+        <v>85</v>
+      </c>
+      <c r="I66" t="s">
         <v>170</v>
       </c>
-      <c r="G66" t="s">
-        <v>7</v>
-      </c>
-      <c r="H66" t="s">
-        <v>86</v>
-      </c>
-      <c r="I66" t="s">
-        <v>171</v>
-      </c>
       <c r="J66" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="K66">
         <v>47986</v>
@@ -4819,10 +4827,10 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C67" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D67" t="s">
         <v>5</v>
@@ -4831,19 +4839,19 @@
         <v>23</v>
       </c>
       <c r="F67" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G67" t="s">
         <v>7</v>
       </c>
       <c r="H67" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I67" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J67" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="K67">
         <v>194000</v>
@@ -4863,10 +4871,10 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C68" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D68" t="s">
         <v>5</v>
@@ -4875,19 +4883,19 @@
         <v>16</v>
       </c>
       <c r="F68" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G68" t="s">
         <v>7</v>
       </c>
       <c r="H68" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I68" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J68" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="K68">
         <v>39724</v>
@@ -4907,28 +4915,28 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C69" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D69" t="s">
         <v>5</v>
       </c>
       <c r="F69" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G69" t="s">
         <v>7</v>
       </c>
       <c r="H69" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="J69" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="K69">
         <v>48437.45</v>
@@ -4948,28 +4956,28 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
+        <v>176</v>
+      </c>
+      <c r="C70" t="s">
+        <v>161</v>
+      </c>
+      <c r="D70" t="s">
+        <v>5</v>
+      </c>
+      <c r="F70" t="s">
         <v>177</v>
       </c>
-      <c r="C70" t="s">
-        <v>162</v>
-      </c>
-      <c r="D70" t="s">
-        <v>5</v>
-      </c>
-      <c r="F70" t="s">
+      <c r="G70" t="s">
+        <v>7</v>
+      </c>
+      <c r="H70" t="s">
+        <v>85</v>
+      </c>
+      <c r="I70" t="s">
         <v>178</v>
       </c>
-      <c r="G70" t="s">
-        <v>7</v>
-      </c>
-      <c r="H70" t="s">
-        <v>86</v>
-      </c>
-      <c r="I70" t="s">
-        <v>179</v>
-      </c>
       <c r="J70" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="K70">
         <v>37910</v>
@@ -4989,28 +4997,28 @@
         <v>70</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C71" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D71" t="s">
         <v>5</v>
       </c>
       <c r="F71" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G71" t="s">
         <v>7</v>
       </c>
       <c r="H71" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="J71" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="K71">
         <v>21220</v>
@@ -5030,28 +5038,28 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
+        <v>179</v>
+      </c>
+      <c r="C72" t="s">
+        <v>161</v>
+      </c>
+      <c r="D72" t="s">
+        <v>5</v>
+      </c>
+      <c r="F72" t="s">
+        <v>55</v>
+      </c>
+      <c r="G72" t="s">
+        <v>7</v>
+      </c>
+      <c r="H72" t="s">
+        <v>85</v>
+      </c>
+      <c r="I72" t="s">
         <v>180</v>
       </c>
-      <c r="C72" t="s">
-        <v>162</v>
-      </c>
-      <c r="D72" t="s">
-        <v>5</v>
-      </c>
-      <c r="F72" t="s">
-        <v>56</v>
-      </c>
-      <c r="G72" t="s">
-        <v>7</v>
-      </c>
-      <c r="H72" t="s">
-        <v>86</v>
-      </c>
-      <c r="I72" t="s">
-        <v>181</v>
-      </c>
       <c r="J72" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="K72">
         <v>77877</v>
@@ -5071,10 +5079,10 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C73" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D73" t="s">
         <v>5</v>
@@ -5083,19 +5091,19 @@
         <v>16</v>
       </c>
       <c r="F73" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G73" t="s">
         <v>7</v>
       </c>
       <c r="H73" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I73" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J73" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="K73">
         <v>80311.53</v>
@@ -5115,10 +5123,10 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C74" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D74" t="s">
         <v>5</v>
@@ -5127,19 +5135,19 @@
         <v>23</v>
       </c>
       <c r="F74" t="s">
+        <v>184</v>
+      </c>
+      <c r="G74" t="s">
+        <v>7</v>
+      </c>
+      <c r="H74" t="s">
+        <v>85</v>
+      </c>
+      <c r="I74" t="s">
         <v>185</v>
       </c>
-      <c r="G74" t="s">
-        <v>7</v>
-      </c>
-      <c r="H74" t="s">
-        <v>86</v>
-      </c>
-      <c r="I74" t="s">
-        <v>186</v>
-      </c>
       <c r="J74" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="K74">
         <v>38000</v>
@@ -5159,28 +5167,28 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
+        <v>186</v>
+      </c>
+      <c r="C75" t="s">
+        <v>161</v>
+      </c>
+      <c r="D75" t="s">
+        <v>5</v>
+      </c>
+      <c r="F75" t="s">
         <v>187</v>
       </c>
-      <c r="C75" t="s">
-        <v>162</v>
-      </c>
-      <c r="D75" t="s">
-        <v>5</v>
-      </c>
-      <c r="F75" t="s">
+      <c r="G75" t="s">
+        <v>7</v>
+      </c>
+      <c r="H75" t="s">
+        <v>85</v>
+      </c>
+      <c r="I75" t="s">
         <v>188</v>
       </c>
-      <c r="G75" t="s">
-        <v>7</v>
-      </c>
-      <c r="H75" t="s">
-        <v>86</v>
-      </c>
-      <c r="I75" t="s">
-        <v>189</v>
-      </c>
       <c r="J75" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="K75">
         <v>37800</v>
@@ -5200,10 +5208,10 @@
         <v>75</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C76" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D76" t="s">
         <v>5</v>
@@ -5212,19 +5220,19 @@
         <v>16</v>
       </c>
       <c r="F76" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G76" t="s">
         <v>7</v>
       </c>
       <c r="H76" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="J76" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="K76">
         <v>54581</v>
@@ -5244,10 +5252,10 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C77" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D77" t="s">
         <v>5</v>
@@ -5256,19 +5264,19 @@
         <v>16</v>
       </c>
       <c r="F77" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G77" t="s">
         <v>7</v>
       </c>
       <c r="H77" t="s">
+        <v>85</v>
+      </c>
+      <c r="I77" t="s">
         <v>86</v>
       </c>
-      <c r="I77" t="s">
-        <v>87</v>
-      </c>
       <c r="J77" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="K77">
         <v>25000</v>
@@ -5288,10 +5296,10 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C78" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D78" t="s">
         <v>5</v>
@@ -5300,19 +5308,19 @@
         <v>16</v>
       </c>
       <c r="F78" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G78" t="s">
         <v>7</v>
       </c>
       <c r="H78" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I78" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J78" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="K78">
         <v>52698</v>
@@ -5332,28 +5340,28 @@
         <v>78</v>
       </c>
       <c r="B79" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C79" t="s">
+        <v>161</v>
+      </c>
+      <c r="D79" t="s">
+        <v>5</v>
+      </c>
+      <c r="F79" t="s">
         <v>196</v>
       </c>
-      <c r="C79" t="s">
-        <v>162</v>
-      </c>
-      <c r="D79" t="s">
-        <v>5</v>
-      </c>
-      <c r="F79" t="s">
+      <c r="G79" t="s">
+        <v>7</v>
+      </c>
+      <c r="H79" t="s">
         <v>197</v>
       </c>
-      <c r="G79" t="s">
-        <v>7</v>
-      </c>
-      <c r="H79" t="s">
-        <v>198</v>
-      </c>
       <c r="I79" s="2" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="J79" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="K79">
         <v>38500</v>
@@ -5373,25 +5381,25 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
+        <v>198</v>
+      </c>
+      <c r="C80" t="s">
+        <v>161</v>
+      </c>
+      <c r="D80" t="s">
         <v>199</v>
       </c>
-      <c r="C80" t="s">
-        <v>162</v>
-      </c>
-      <c r="D80" t="s">
+      <c r="G80" t="s">
+        <v>7</v>
+      </c>
+      <c r="H80" t="s">
+        <v>85</v>
+      </c>
+      <c r="I80" t="s">
         <v>200</v>
       </c>
-      <c r="G80" t="s">
-        <v>7</v>
-      </c>
-      <c r="H80" t="s">
-        <v>86</v>
-      </c>
-      <c r="I80" t="s">
-        <v>201</v>
-      </c>
       <c r="J80" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="K80">
         <v>27200</v>
@@ -5411,10 +5419,10 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C81" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D81" t="s">
         <v>5</v>
@@ -5423,7 +5431,7 @@
         <v>16</v>
       </c>
       <c r="F81" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G81" t="s">
         <v>7</v>
@@ -5432,10 +5440,10 @@
         <v>8</v>
       </c>
       <c r="I81" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="J81" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="K81">
         <v>60000</v>
@@ -5455,16 +5463,16 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
+        <v>204</v>
+      </c>
+      <c r="C82" t="s">
+        <v>138</v>
+      </c>
+      <c r="D82" t="s">
+        <v>5</v>
+      </c>
+      <c r="F82" t="s">
         <v>205</v>
-      </c>
-      <c r="C82" t="s">
-        <v>139</v>
-      </c>
-      <c r="D82" t="s">
-        <v>5</v>
-      </c>
-      <c r="F82" t="s">
-        <v>206</v>
       </c>
       <c r="G82" t="s">
         <v>7</v>
@@ -5473,10 +5481,10 @@
         <v>8</v>
       </c>
       <c r="I82" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="J82" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K82">
         <v>50000</v>
@@ -5496,10 +5504,10 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C83" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D83" t="s">
         <v>5</v>
@@ -5508,7 +5516,7 @@
         <v>23</v>
       </c>
       <c r="F83" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G83" t="s">
         <v>7</v>
@@ -5517,10 +5525,10 @@
         <v>8</v>
       </c>
       <c r="I83" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="J83" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="K83">
         <v>131575</v>
@@ -5540,16 +5548,16 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C84" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D84" t="s">
         <v>5</v>
       </c>
       <c r="F84" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G84" t="s">
         <v>7</v>
@@ -5558,10 +5566,10 @@
         <v>8</v>
       </c>
       <c r="I84" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J84" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K84">
         <v>99500</v>
@@ -5581,16 +5589,16 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
+        <v>211</v>
+      </c>
+      <c r="C85" t="s">
+        <v>138</v>
+      </c>
+      <c r="D85" t="s">
+        <v>5</v>
+      </c>
+      <c r="F85" t="s">
         <v>212</v>
-      </c>
-      <c r="C85" t="s">
-        <v>139</v>
-      </c>
-      <c r="D85" t="s">
-        <v>5</v>
-      </c>
-      <c r="F85" t="s">
-        <v>213</v>
       </c>
       <c r="G85" t="s">
         <v>7</v>
@@ -5599,10 +5607,10 @@
         <v>8</v>
       </c>
       <c r="I85" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="J85" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="K85">
         <v>32000</v>
@@ -5622,10 +5630,10 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C86" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D86" t="s">
         <v>5</v>
@@ -5634,7 +5642,7 @@
         <v>23</v>
       </c>
       <c r="F86" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G86" t="s">
         <v>7</v>
@@ -5643,10 +5651,10 @@
         <v>8</v>
       </c>
       <c r="I86" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="J86" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="K86">
         <v>52170</v>
@@ -5666,16 +5674,16 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
+        <v>215</v>
+      </c>
+      <c r="C87" t="s">
+        <v>138</v>
+      </c>
+      <c r="D87" t="s">
+        <v>5</v>
+      </c>
+      <c r="F87" t="s">
         <v>216</v>
-      </c>
-      <c r="C87" t="s">
-        <v>139</v>
-      </c>
-      <c r="D87" t="s">
-        <v>5</v>
-      </c>
-      <c r="F87" t="s">
-        <v>217</v>
       </c>
       <c r="G87" t="s">
         <v>7</v>
@@ -5684,10 +5692,10 @@
         <v>8</v>
       </c>
       <c r="I87" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="J87" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="K87">
         <v>46000</v>
@@ -5707,10 +5715,10 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C88" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D88" t="s">
         <v>5</v>
@@ -5719,7 +5727,7 @@
         <v>23</v>
       </c>
       <c r="F88" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G88" t="s">
         <v>7</v>
@@ -5728,10 +5736,10 @@
         <v>8</v>
       </c>
       <c r="I88" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="J88" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K88">
         <v>45013</v>
@@ -5751,16 +5759,16 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C89" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D89" t="s">
         <v>5</v>
       </c>
       <c r="F89" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G89" t="s">
         <v>7</v>
@@ -5769,10 +5777,10 @@
         <v>8</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="J89" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="K89">
         <v>48566</v>
@@ -5792,16 +5800,16 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
+        <v>221</v>
+      </c>
+      <c r="C90" t="s">
+        <v>138</v>
+      </c>
+      <c r="D90" t="s">
+        <v>5</v>
+      </c>
+      <c r="F90" t="s">
         <v>222</v>
-      </c>
-      <c r="C90" t="s">
-        <v>139</v>
-      </c>
-      <c r="D90" t="s">
-        <v>5</v>
-      </c>
-      <c r="F90" t="s">
-        <v>223</v>
       </c>
       <c r="G90" t="s">
         <v>7</v>
@@ -5810,10 +5818,10 @@
         <v>8</v>
       </c>
       <c r="I90" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="J90" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K90">
         <v>55618</v>
@@ -5833,16 +5841,16 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C91" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D91" t="s">
         <v>5</v>
       </c>
       <c r="F91" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G91" t="s">
         <v>7</v>
@@ -5851,10 +5859,10 @@
         <v>8</v>
       </c>
       <c r="I91" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="J91" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="K91">
         <v>47000</v>
@@ -5874,10 +5882,10 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C92" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D92" t="s">
         <v>5</v>
@@ -5886,7 +5894,7 @@
         <v>23</v>
       </c>
       <c r="F92" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G92" t="s">
         <v>7</v>
@@ -5895,10 +5903,10 @@
         <v>8</v>
       </c>
       <c r="I92" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="J92" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K92">
         <v>87763</v>
@@ -5918,10 +5926,10 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C93" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D93" t="s">
         <v>14</v>
@@ -5930,7 +5938,7 @@
         <v>16</v>
       </c>
       <c r="F93" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G93" t="s">
         <v>7</v>
@@ -5939,10 +5947,10 @@
         <v>8</v>
       </c>
       <c r="I93" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="J93" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="K93">
         <v>100658</v>
@@ -5962,16 +5970,16 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
+        <v>231</v>
+      </c>
+      <c r="C94" t="s">
+        <v>138</v>
+      </c>
+      <c r="D94" t="s">
+        <v>5</v>
+      </c>
+      <c r="F94" t="s">
         <v>232</v>
-      </c>
-      <c r="C94" t="s">
-        <v>139</v>
-      </c>
-      <c r="D94" t="s">
-        <v>5</v>
-      </c>
-      <c r="F94" t="s">
-        <v>233</v>
       </c>
       <c r="G94" t="s">
         <v>7</v>
@@ -5980,10 +5988,10 @@
         <v>8</v>
       </c>
       <c r="I94" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="J94" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="K94">
         <v>67000</v>
@@ -6003,10 +6011,10 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C95" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D95" t="s">
         <v>5</v>
@@ -6015,7 +6023,7 @@
         <v>16</v>
       </c>
       <c r="F95" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G95" t="s">
         <v>7</v>
@@ -6024,10 +6032,10 @@
         <v>8</v>
       </c>
       <c r="I95" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J95" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="K95">
         <v>39431</v>
@@ -6047,16 +6055,16 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C96" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D96" t="s">
         <v>5</v>
       </c>
       <c r="F96" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G96" t="s">
         <v>7</v>
@@ -6065,10 +6073,10 @@
         <v>8</v>
       </c>
       <c r="I96" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J96" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="K96">
         <v>34273</v>
@@ -6088,10 +6096,10 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C97" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D97" t="s">
         <v>5</v>
@@ -6103,10 +6111,10 @@
         <v>8</v>
       </c>
       <c r="I97" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="J97" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K97">
         <v>40000</v>
@@ -6126,10 +6134,10 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C98" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D98" t="s">
         <v>5</v>
@@ -6144,10 +6152,10 @@
         <v>8</v>
       </c>
       <c r="I98" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="J98" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="K98">
         <v>65000</v>
@@ -6167,10 +6175,10 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
+        <v>240</v>
+      </c>
+      <c r="C99" t="s">
         <v>241</v>
-      </c>
-      <c r="C99" t="s">
-        <v>242</v>
       </c>
       <c r="D99" t="s">
         <v>5</v>
@@ -6179,19 +6187,19 @@
         <v>23</v>
       </c>
       <c r="F99" t="s">
+        <v>242</v>
+      </c>
+      <c r="G99" t="s">
+        <v>7</v>
+      </c>
+      <c r="H99" t="s">
+        <v>197</v>
+      </c>
+      <c r="I99" t="s">
         <v>243</v>
       </c>
-      <c r="G99" t="s">
-        <v>7</v>
-      </c>
-      <c r="H99" t="s">
-        <v>198</v>
-      </c>
-      <c r="I99" t="s">
-        <v>244</v>
-      </c>
       <c r="J99" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="K99">
         <v>49000</v>
@@ -6211,10 +6219,10 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C100" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D100" t="s">
         <v>14</v>
@@ -6223,19 +6231,19 @@
         <v>23</v>
       </c>
       <c r="F100" t="s">
+        <v>245</v>
+      </c>
+      <c r="G100" t="s">
+        <v>7</v>
+      </c>
+      <c r="H100" t="s">
+        <v>197</v>
+      </c>
+      <c r="I100" t="s">
         <v>246</v>
       </c>
-      <c r="G100" t="s">
-        <v>7</v>
-      </c>
-      <c r="H100" t="s">
-        <v>198</v>
-      </c>
-      <c r="I100" t="s">
-        <v>247</v>
-      </c>
       <c r="J100" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="K100">
         <v>95000</v>
@@ -6255,10 +6263,10 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C101" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D101" t="s">
         <v>5</v>
@@ -6267,19 +6275,19 @@
         <v>23</v>
       </c>
       <c r="F101" t="s">
+        <v>248</v>
+      </c>
+      <c r="G101" t="s">
+        <v>7</v>
+      </c>
+      <c r="H101" t="s">
+        <v>197</v>
+      </c>
+      <c r="I101" t="s">
         <v>249</v>
       </c>
-      <c r="G101" t="s">
-        <v>7</v>
-      </c>
-      <c r="H101" t="s">
-        <v>198</v>
-      </c>
-      <c r="I101" t="s">
-        <v>250</v>
-      </c>
       <c r="J101" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="K101">
         <v>45000</v>
@@ -6299,10 +6307,10 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C102" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D102" t="s">
         <v>5</v>
@@ -6314,13 +6322,13 @@
         <v>7</v>
       </c>
       <c r="H102" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="I102" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="J102" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="K102">
         <v>124500</v>
@@ -6340,28 +6348,28 @@
         <v>102</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C103" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D103" t="s">
         <v>5</v>
       </c>
       <c r="F103" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G103" t="s">
         <v>7</v>
       </c>
       <c r="H103" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="I103" s="2" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="J103" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="K103">
         <v>64000</v>
@@ -6381,28 +6389,28 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
+        <v>253</v>
+      </c>
+      <c r="C104" t="s">
+        <v>241</v>
+      </c>
+      <c r="D104" t="s">
+        <v>5</v>
+      </c>
+      <c r="F104" t="s">
+        <v>64</v>
+      </c>
+      <c r="G104" t="s">
+        <v>7</v>
+      </c>
+      <c r="H104" t="s">
+        <v>197</v>
+      </c>
+      <c r="I104" t="s">
         <v>254</v>
       </c>
-      <c r="C104" t="s">
-        <v>242</v>
-      </c>
-      <c r="D104" t="s">
-        <v>5</v>
-      </c>
-      <c r="F104" t="s">
-        <v>65</v>
-      </c>
-      <c r="G104" t="s">
-        <v>7</v>
-      </c>
-      <c r="H104" t="s">
-        <v>198</v>
-      </c>
-      <c r="I104" t="s">
-        <v>255</v>
-      </c>
       <c r="J104" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="K104">
         <v>25000</v>
@@ -6422,28 +6430,28 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
+        <v>255</v>
+      </c>
+      <c r="C105" t="s">
+        <v>241</v>
+      </c>
+      <c r="D105" t="s">
+        <v>5</v>
+      </c>
+      <c r="F105" t="s">
+        <v>79</v>
+      </c>
+      <c r="G105" t="s">
+        <v>7</v>
+      </c>
+      <c r="H105" t="s">
+        <v>197</v>
+      </c>
+      <c r="I105" t="s">
         <v>256</v>
       </c>
-      <c r="C105" t="s">
-        <v>242</v>
-      </c>
-      <c r="D105" t="s">
-        <v>5</v>
-      </c>
-      <c r="F105" t="s">
-        <v>80</v>
-      </c>
-      <c r="G105" t="s">
-        <v>7</v>
-      </c>
-      <c r="H105" t="s">
-        <v>198</v>
-      </c>
-      <c r="I105" t="s">
-        <v>257</v>
-      </c>
       <c r="J105" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="K105">
         <v>38498</v>
@@ -6463,25 +6471,25 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
+        <v>257</v>
+      </c>
+      <c r="C106" t="s">
+        <v>241</v>
+      </c>
+      <c r="D106" t="s">
+        <v>199</v>
+      </c>
+      <c r="G106" t="s">
+        <v>7</v>
+      </c>
+      <c r="H106" t="s">
+        <v>197</v>
+      </c>
+      <c r="I106" t="s">
         <v>258</v>
       </c>
-      <c r="C106" t="s">
-        <v>242</v>
-      </c>
-      <c r="D106" t="s">
-        <v>200</v>
-      </c>
-      <c r="G106" t="s">
-        <v>7</v>
-      </c>
-      <c r="H106" t="s">
-        <v>198</v>
-      </c>
-      <c r="I106" t="s">
-        <v>259</v>
-      </c>
       <c r="J106" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="K106">
         <v>166433</v>
@@ -6501,10 +6509,10 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C107" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D107" t="s">
         <v>14</v>
@@ -6513,19 +6521,19 @@
         <v>23</v>
       </c>
       <c r="F107" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G107" t="s">
         <v>7</v>
       </c>
       <c r="H107" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="I107" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="J107" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="K107">
         <v>58000</v>
@@ -6545,28 +6553,28 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
+        <v>261</v>
+      </c>
+      <c r="C108" t="s">
+        <v>241</v>
+      </c>
+      <c r="D108" t="s">
+        <v>5</v>
+      </c>
+      <c r="F108" t="s">
         <v>262</v>
       </c>
-      <c r="C108" t="s">
-        <v>242</v>
-      </c>
-      <c r="D108" t="s">
-        <v>5</v>
-      </c>
-      <c r="F108" t="s">
+      <c r="G108" t="s">
+        <v>7</v>
+      </c>
+      <c r="H108" t="s">
+        <v>197</v>
+      </c>
+      <c r="I108" t="s">
         <v>263</v>
       </c>
-      <c r="G108" t="s">
-        <v>7</v>
-      </c>
-      <c r="H108" t="s">
-        <v>198</v>
-      </c>
-      <c r="I108" t="s">
-        <v>264</v>
-      </c>
       <c r="J108" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="K108">
         <v>51872</v>
@@ -6586,28 +6594,28 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
+        <v>264</v>
+      </c>
+      <c r="C109" t="s">
+        <v>241</v>
+      </c>
+      <c r="D109" t="s">
+        <v>5</v>
+      </c>
+      <c r="F109" t="s">
+        <v>192</v>
+      </c>
+      <c r="G109" t="s">
+        <v>7</v>
+      </c>
+      <c r="H109" t="s">
+        <v>197</v>
+      </c>
+      <c r="I109" t="s">
         <v>265</v>
       </c>
-      <c r="C109" t="s">
-        <v>242</v>
-      </c>
-      <c r="D109" t="s">
-        <v>5</v>
-      </c>
-      <c r="F109" t="s">
-        <v>193</v>
-      </c>
-      <c r="G109" t="s">
-        <v>7</v>
-      </c>
-      <c r="H109" t="s">
-        <v>198</v>
-      </c>
-      <c r="I109" t="s">
-        <v>266</v>
-      </c>
       <c r="J109" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="K109">
         <v>21632</v>
@@ -6627,28 +6635,28 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
+        <v>266</v>
+      </c>
+      <c r="C110" t="s">
+        <v>241</v>
+      </c>
+      <c r="D110" t="s">
+        <v>5</v>
+      </c>
+      <c r="F110" t="s">
+        <v>192</v>
+      </c>
+      <c r="G110" t="s">
+        <v>7</v>
+      </c>
+      <c r="H110" t="s">
+        <v>197</v>
+      </c>
+      <c r="I110" t="s">
         <v>267</v>
       </c>
-      <c r="C110" t="s">
-        <v>242</v>
-      </c>
-      <c r="D110" t="s">
-        <v>5</v>
-      </c>
-      <c r="F110" t="s">
-        <v>193</v>
-      </c>
-      <c r="G110" t="s">
-        <v>7</v>
-      </c>
-      <c r="H110" t="s">
-        <v>198</v>
-      </c>
-      <c r="I110" t="s">
-        <v>268</v>
-      </c>
       <c r="J110" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="K110">
         <v>69000</v>
@@ -6668,28 +6676,28 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
+        <v>268</v>
+      </c>
+      <c r="C111" t="s">
+        <v>241</v>
+      </c>
+      <c r="D111" t="s">
+        <v>5</v>
+      </c>
+      <c r="F111" t="s">
         <v>269</v>
       </c>
-      <c r="C111" t="s">
-        <v>242</v>
-      </c>
-      <c r="D111" t="s">
-        <v>5</v>
-      </c>
-      <c r="F111" t="s">
+      <c r="G111" t="s">
+        <v>7</v>
+      </c>
+      <c r="H111" t="s">
+        <v>197</v>
+      </c>
+      <c r="I111" t="s">
         <v>270</v>
       </c>
-      <c r="G111" t="s">
-        <v>7</v>
-      </c>
-      <c r="H111" t="s">
-        <v>198</v>
-      </c>
-      <c r="I111" t="s">
-        <v>271</v>
-      </c>
       <c r="J111" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="K111">
         <v>54000</v>
@@ -6709,10 +6717,10 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C112" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D112" t="s">
         <v>5</v>
@@ -6724,13 +6732,13 @@
         <v>7</v>
       </c>
       <c r="H112" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="I112" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="J112" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="K112">
         <v>57400</v>
@@ -6750,10 +6758,10 @@
         <v>112</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C113" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D113" t="s">
         <v>14</v>
@@ -6765,13 +6773,13 @@
         <v>7</v>
       </c>
       <c r="H113" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="I113" s="2" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="J113" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="K113">
         <v>60000</v>
@@ -6786,7 +6794,7 @@
         <v>427</v>
       </c>
       <c r="P113" s="1" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -6794,10 +6802,10 @@
         <v>113</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C114" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D114" t="s">
         <v>14</v>
@@ -6809,13 +6817,13 @@
         <v>7</v>
       </c>
       <c r="H114" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="I114" s="2" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="J114" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="K114">
         <v>60000</v>
@@ -6830,7 +6838,7 @@
         <v>11500</v>
       </c>
       <c r="P114" s="1" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -6838,10 +6846,10 @@
         <v>114</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C115" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D115" t="s">
         <v>5</v>
@@ -6850,13 +6858,13 @@
         <v>7</v>
       </c>
       <c r="H115" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="I115" s="5" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="J115" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="K115">
         <v>33000</v>
@@ -6876,25 +6884,25 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
+        <v>276</v>
+      </c>
+      <c r="C116" t="s">
+        <v>241</v>
+      </c>
+      <c r="D116" t="s">
+        <v>199</v>
+      </c>
+      <c r="G116" t="s">
+        <v>7</v>
+      </c>
+      <c r="H116" t="s">
+        <v>197</v>
+      </c>
+      <c r="I116" t="s">
         <v>277</v>
       </c>
-      <c r="C116" t="s">
-        <v>242</v>
-      </c>
-      <c r="D116" t="s">
-        <v>200</v>
-      </c>
-      <c r="G116" t="s">
-        <v>7</v>
-      </c>
-      <c r="H116" t="s">
-        <v>198</v>
-      </c>
-      <c r="I116" t="s">
-        <v>278</v>
-      </c>
       <c r="J116" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="K116">
         <v>88786</v>
@@ -6914,25 +6922,25 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
+        <v>278</v>
+      </c>
+      <c r="C117" t="s">
+        <v>241</v>
+      </c>
+      <c r="D117" t="s">
+        <v>199</v>
+      </c>
+      <c r="G117" t="s">
+        <v>7</v>
+      </c>
+      <c r="H117" t="s">
+        <v>197</v>
+      </c>
+      <c r="I117" t="s">
         <v>279</v>
       </c>
-      <c r="C117" t="s">
-        <v>242</v>
-      </c>
-      <c r="D117" t="s">
-        <v>200</v>
-      </c>
-      <c r="G117" t="s">
-        <v>7</v>
-      </c>
-      <c r="H117" t="s">
-        <v>198</v>
-      </c>
-      <c r="I117" t="s">
-        <v>280</v>
-      </c>
       <c r="J117" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="K117">
         <v>134000</v>
@@ -6952,25 +6960,25 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
+        <v>280</v>
+      </c>
+      <c r="C118" t="s">
+        <v>241</v>
+      </c>
+      <c r="D118" t="s">
+        <v>199</v>
+      </c>
+      <c r="G118" t="s">
+        <v>7</v>
+      </c>
+      <c r="H118" t="s">
+        <v>197</v>
+      </c>
+      <c r="I118" t="s">
         <v>281</v>
       </c>
-      <c r="C118" t="s">
-        <v>242</v>
-      </c>
-      <c r="D118" t="s">
-        <v>200</v>
-      </c>
-      <c r="G118" t="s">
-        <v>7</v>
-      </c>
-      <c r="H118" t="s">
-        <v>198</v>
-      </c>
-      <c r="I118" t="s">
-        <v>282</v>
-      </c>
       <c r="J118" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="K118">
         <v>35000</v>
@@ -6990,25 +6998,25 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
+        <v>282</v>
+      </c>
+      <c r="C119" t="s">
+        <v>241</v>
+      </c>
+      <c r="D119" t="s">
+        <v>199</v>
+      </c>
+      <c r="G119" t="s">
+        <v>7</v>
+      </c>
+      <c r="H119" t="s">
+        <v>197</v>
+      </c>
+      <c r="I119" t="s">
         <v>283</v>
       </c>
-      <c r="C119" t="s">
-        <v>242</v>
-      </c>
-      <c r="D119" t="s">
-        <v>200</v>
-      </c>
-      <c r="G119" t="s">
-        <v>7</v>
-      </c>
-      <c r="H119" t="s">
-        <v>198</v>
-      </c>
-      <c r="I119" t="s">
-        <v>284</v>
-      </c>
       <c r="J119" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="K119">
         <v>18000</v>
@@ -7028,13 +7036,13 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C120" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D120" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E120" t="s">
         <v>16</v>
@@ -7043,13 +7051,13 @@
         <v>7</v>
       </c>
       <c r="H120" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="I120" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="J120" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="K120">
         <v>105741</v>
@@ -7069,25 +7077,25 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
+        <v>286</v>
+      </c>
+      <c r="C121" t="s">
+        <v>241</v>
+      </c>
+      <c r="D121" t="s">
+        <v>199</v>
+      </c>
+      <c r="G121" t="s">
+        <v>7</v>
+      </c>
+      <c r="H121" t="s">
+        <v>197</v>
+      </c>
+      <c r="I121" t="s">
         <v>287</v>
       </c>
-      <c r="C121" t="s">
-        <v>242</v>
-      </c>
-      <c r="D121" t="s">
-        <v>200</v>
-      </c>
-      <c r="G121" t="s">
-        <v>7</v>
-      </c>
-      <c r="H121" t="s">
-        <v>198</v>
-      </c>
-      <c r="I121" t="s">
-        <v>288</v>
-      </c>
       <c r="J121" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="K121">
         <v>51000</v>
@@ -7107,10 +7115,10 @@
         <v>121</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C122" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D122" t="s">
         <v>5</v>
@@ -7122,13 +7130,13 @@
         <v>7</v>
       </c>
       <c r="H122" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="I122" s="3" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="J122" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="K122">
         <v>130143</v>
@@ -7143,7 +7151,7 @@
         <v>36000</v>
       </c>
       <c r="P122" s="1" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7151,22 +7159,22 @@
         <v>122</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="C123" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G123" t="s">
         <v>7</v>
       </c>
       <c r="H123" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="I123" s="3" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="J123" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="K123">
         <v>121551.47</v>
@@ -7181,7 +7189,7 @@
         <v>97326.47</v>
       </c>
       <c r="P123" s="1" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7189,10 +7197,10 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
+        <v>289</v>
+      </c>
+      <c r="C124" t="s">
         <v>290</v>
-      </c>
-      <c r="C124" t="s">
-        <v>291</v>
       </c>
       <c r="D124" t="s">
         <v>5</v>
@@ -7201,7 +7209,7 @@
         <v>16</v>
       </c>
       <c r="F124" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="G124" t="s">
         <v>7</v>
@@ -7210,10 +7218,10 @@
         <v>8</v>
       </c>
       <c r="I124" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="J124" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="K124">
         <v>110000</v>
@@ -7233,10 +7241,10 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C125" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D125" t="s">
         <v>5</v>
@@ -7245,7 +7253,7 @@
         <v>23</v>
       </c>
       <c r="F125" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G125" t="s">
         <v>7</v>
@@ -7254,10 +7262,10 @@
         <v>8</v>
       </c>
       <c r="I125" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="J125" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="K125">
         <v>56000</v>
@@ -7277,16 +7285,16 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C126" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D126" t="s">
         <v>5</v>
       </c>
       <c r="F126" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G126" t="s">
         <v>7</v>
@@ -7295,10 +7303,10 @@
         <v>8</v>
       </c>
       <c r="I126" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="J126" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="K126">
         <v>89177</v>
@@ -7318,10 +7326,10 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C127" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D127" t="s">
         <v>5</v>
@@ -7330,7 +7338,7 @@
         <v>23</v>
       </c>
       <c r="F127" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="G127" t="s">
         <v>7</v>
@@ -7339,10 +7347,10 @@
         <v>8</v>
       </c>
       <c r="I127" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="J127" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="K127">
         <v>30000</v>
@@ -7362,10 +7370,10 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C128" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D128" t="s">
         <v>5</v>
@@ -7374,7 +7382,7 @@
         <v>16</v>
       </c>
       <c r="F128" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="G128" t="s">
         <v>7</v>
@@ -7383,10 +7391,10 @@
         <v>8</v>
       </c>
       <c r="I128" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="J128" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="K128">
         <v>54550</v>
@@ -7406,10 +7414,10 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C129" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D129" t="s">
         <v>5</v>
@@ -7418,7 +7426,7 @@
         <v>16</v>
       </c>
       <c r="F129" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G129" t="s">
         <v>7</v>
@@ -7427,10 +7435,10 @@
         <v>8</v>
       </c>
       <c r="I129" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="J129" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="K129">
         <v>125000</v>
@@ -7450,10 +7458,10 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C130" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D130" t="s">
         <v>5</v>
@@ -7462,7 +7470,7 @@
         <v>16</v>
       </c>
       <c r="F130" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G130" t="s">
         <v>7</v>
@@ -7471,10 +7479,10 @@
         <v>8</v>
       </c>
       <c r="I130" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="J130" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="K130">
         <v>69100</v>
@@ -7494,10 +7502,10 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C131" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D131" t="s">
         <v>5</v>
@@ -7506,7 +7514,7 @@
         <v>23</v>
       </c>
       <c r="F131" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G131" t="s">
         <v>7</v>
@@ -7515,10 +7523,10 @@
         <v>8</v>
       </c>
       <c r="I131" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="J131" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="K131">
         <v>118290</v>
@@ -7538,16 +7546,16 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
+        <v>309</v>
+      </c>
+      <c r="C132" t="s">
+        <v>290</v>
+      </c>
+      <c r="D132" t="s">
+        <v>5</v>
+      </c>
+      <c r="F132" t="s">
         <v>310</v>
-      </c>
-      <c r="C132" t="s">
-        <v>291</v>
-      </c>
-      <c r="D132" t="s">
-        <v>5</v>
-      </c>
-      <c r="F132" t="s">
-        <v>311</v>
       </c>
       <c r="G132" t="s">
         <v>7</v>
@@ -7556,10 +7564,10 @@
         <v>8</v>
       </c>
       <c r="I132" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J132" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="K132">
         <v>79900</v>
@@ -7579,16 +7587,16 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C133" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D133" t="s">
         <v>5</v>
       </c>
       <c r="F133" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G133" t="s">
         <v>7</v>
@@ -7597,10 +7605,10 @@
         <v>8</v>
       </c>
       <c r="I133" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="J133" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="K133">
         <v>39742.379999999997</v>
@@ -7620,10 +7628,10 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C134" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D134" t="s">
         <v>5</v>
@@ -7632,7 +7640,7 @@
         <v>16</v>
       </c>
       <c r="F134" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G134" t="s">
         <v>7</v>
@@ -7641,10 +7649,10 @@
         <v>8</v>
       </c>
       <c r="I134" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="J134" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="K134">
         <v>48000</v>
@@ -7664,10 +7672,10 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C135" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D135" t="s">
         <v>14</v>
@@ -7682,10 +7690,10 @@
         <v>8</v>
       </c>
       <c r="I135" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="J135" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="K135">
         <v>74722</v>
@@ -7705,13 +7713,13 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C136" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D136" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G136" t="s">
         <v>7</v>
@@ -7720,10 +7728,10 @@
         <v>8</v>
       </c>
       <c r="I136" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="J136" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="K136">
         <v>55000</v>
@@ -7743,25 +7751,25 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
+        <v>320</v>
+      </c>
+      <c r="C137" t="s">
         <v>321</v>
       </c>
-      <c r="C137" t="s">
+      <c r="D137" t="s">
+        <v>5</v>
+      </c>
+      <c r="G137" t="s">
+        <v>7</v>
+      </c>
+      <c r="H137" t="s">
+        <v>113</v>
+      </c>
+      <c r="I137" t="s">
         <v>322</v>
       </c>
-      <c r="D137" t="s">
-        <v>5</v>
-      </c>
-      <c r="G137" t="s">
-        <v>7</v>
-      </c>
-      <c r="H137" t="s">
-        <v>114</v>
-      </c>
-      <c r="I137" t="s">
-        <v>323</v>
-      </c>
       <c r="J137" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K137">
         <v>128000</v>
@@ -7781,10 +7789,10 @@
         <v>137</v>
       </c>
       <c r="B138" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C138" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D138" t="s">
         <v>5</v>
@@ -7793,19 +7801,19 @@
         <v>16</v>
       </c>
       <c r="F138" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G138" t="s">
         <v>7</v>
       </c>
       <c r="H138" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I138" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J138" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K138">
         <v>122000</v>
@@ -7825,10 +7833,10 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C139" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D139" t="s">
         <v>5</v>
@@ -7840,13 +7848,13 @@
         <v>7</v>
       </c>
       <c r="H139" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I139" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="J139" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K139">
         <v>22000</v>
@@ -7866,10 +7874,10 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C140" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D140" t="s">
         <v>5</v>
@@ -7881,13 +7889,13 @@
         <v>7</v>
       </c>
       <c r="H140" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I140" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J140" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K140">
         <v>10000</v>
@@ -7907,16 +7915,16 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C141" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D141" t="s">
         <v>5</v>
       </c>
       <c r="F141" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G141" t="s">
         <v>7</v>
@@ -7925,10 +7933,10 @@
         <v>8</v>
       </c>
       <c r="I141" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="J141" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="K141">
         <v>64000</v>
@@ -7948,16 +7956,16 @@
         <v>141</v>
       </c>
       <c r="B142" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C142" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D142" t="s">
         <v>5</v>
       </c>
       <c r="F142" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G142" t="s">
         <v>7</v>
@@ -7966,10 +7974,10 @@
         <v>8</v>
       </c>
       <c r="I142" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="J142" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="K142">
         <v>95628</v>
@@ -7989,16 +7997,16 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
+        <v>333</v>
+      </c>
+      <c r="C143" t="s">
+        <v>321</v>
+      </c>
+      <c r="D143" t="s">
+        <v>5</v>
+      </c>
+      <c r="F143" t="s">
         <v>334</v>
-      </c>
-      <c r="C143" t="s">
-        <v>322</v>
-      </c>
-      <c r="D143" t="s">
-        <v>5</v>
-      </c>
-      <c r="F143" t="s">
-        <v>335</v>
       </c>
       <c r="G143" t="s">
         <v>7</v>
@@ -8007,10 +8015,10 @@
         <v>8</v>
       </c>
       <c r="I143" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="J143" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="K143">
         <v>39562</v>
@@ -8030,10 +8038,10 @@
         <v>143</v>
       </c>
       <c r="B144" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C144" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D144" t="s">
         <v>5</v>
@@ -8042,7 +8050,7 @@
         <v>16</v>
       </c>
       <c r="F144" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="G144" t="s">
         <v>7</v>
@@ -8051,10 +8059,10 @@
         <v>8</v>
       </c>
       <c r="I144" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="J144" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K144">
         <v>105000</v>
@@ -8074,10 +8082,10 @@
         <v>144</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="C145" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D145" t="s">
         <v>5</v>
@@ -8086,7 +8094,7 @@
         <v>23</v>
       </c>
       <c r="F145" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G145" t="s">
         <v>7</v>
@@ -8095,10 +8103,10 @@
         <v>8</v>
       </c>
       <c r="I145" s="2" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="J145" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K145">
         <v>60000</v>
@@ -8118,16 +8126,16 @@
         <v>145</v>
       </c>
       <c r="B146" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C146" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D146" t="s">
         <v>5</v>
       </c>
       <c r="F146" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G146" t="s">
         <v>7</v>
@@ -8136,10 +8144,10 @@
         <v>8</v>
       </c>
       <c r="I146" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="J146" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="K146">
         <v>39964</v>
@@ -8159,10 +8167,10 @@
         <v>146</v>
       </c>
       <c r="B147" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C147" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D147" t="s">
         <v>5</v>
@@ -8177,10 +8185,10 @@
         <v>8</v>
       </c>
       <c r="I147" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="J147" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K147">
         <v>94000</v>
@@ -8200,10 +8208,10 @@
         <v>147</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="C148" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D148" t="s">
         <v>5</v>
@@ -8212,7 +8220,7 @@
         <v>23</v>
       </c>
       <c r="F148" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G148" t="s">
         <v>7</v>
@@ -8221,10 +8229,10 @@
         <v>8</v>
       </c>
       <c r="I148" s="2" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="J148" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K148">
         <v>75000</v>
@@ -8244,28 +8252,28 @@
         <v>148</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C149" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D149" t="s">
         <v>5</v>
       </c>
       <c r="F149" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="G149" t="s">
         <v>7</v>
       </c>
       <c r="H149" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I149" s="2" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="J149" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K149">
         <v>48767</v>
@@ -8285,10 +8293,10 @@
         <v>149</v>
       </c>
       <c r="B150" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C150" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D150" t="s">
         <v>5</v>
@@ -8297,7 +8305,7 @@
         <v>16</v>
       </c>
       <c r="F150" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G150" t="s">
         <v>7</v>
@@ -8306,10 +8314,10 @@
         <v>8</v>
       </c>
       <c r="I150" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="J150" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K150">
         <v>63824</v>
@@ -8329,10 +8337,10 @@
         <v>150</v>
       </c>
       <c r="B151" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C151" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D151" t="s">
         <v>14</v>
@@ -8341,7 +8349,7 @@
         <v>23</v>
       </c>
       <c r="F151" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G151" t="s">
         <v>7</v>
@@ -8350,10 +8358,10 @@
         <v>8</v>
       </c>
       <c r="I151" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J151" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K151">
         <v>117000</v>
@@ -8373,10 +8381,10 @@
         <v>151</v>
       </c>
       <c r="B152" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C152" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D152" t="s">
         <v>5</v>
@@ -8388,10 +8396,10 @@
         <v>8</v>
       </c>
       <c r="I152" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="J152" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K152">
         <v>41000</v>
@@ -8411,10 +8419,10 @@
         <v>152</v>
       </c>
       <c r="B153" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C153" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D153" t="s">
         <v>5</v>
@@ -8426,10 +8434,10 @@
         <v>8</v>
       </c>
       <c r="I153" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="J153" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="K153">
         <v>96446</v>
@@ -8449,10 +8457,10 @@
         <v>153</v>
       </c>
       <c r="B154" t="s">
+        <v>352</v>
+      </c>
+      <c r="C154" t="s">
         <v>353</v>
-      </c>
-      <c r="C154" t="s">
-        <v>354</v>
       </c>
       <c r="D154" t="s">
         <v>5</v>
@@ -8461,19 +8469,19 @@
         <v>16</v>
       </c>
       <c r="F154" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G154" t="s">
         <v>7</v>
       </c>
       <c r="H154" t="s">
+        <v>354</v>
+      </c>
+      <c r="I154" t="s">
         <v>355</v>
       </c>
-      <c r="I154" t="s">
-        <v>356</v>
-      </c>
       <c r="J154" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K154">
         <v>76600</v>
@@ -8493,28 +8501,28 @@
         <v>154</v>
       </c>
       <c r="B155" t="s">
+        <v>356</v>
+      </c>
+      <c r="C155" t="s">
+        <v>353</v>
+      </c>
+      <c r="D155" t="s">
+        <v>5</v>
+      </c>
+      <c r="F155" t="s">
+        <v>153</v>
+      </c>
+      <c r="G155" t="s">
+        <v>7</v>
+      </c>
+      <c r="H155" t="s">
+        <v>354</v>
+      </c>
+      <c r="I155" t="s">
         <v>357</v>
       </c>
-      <c r="C155" t="s">
-        <v>354</v>
-      </c>
-      <c r="D155" t="s">
-        <v>5</v>
-      </c>
-      <c r="F155" t="s">
-        <v>154</v>
-      </c>
-      <c r="G155" t="s">
-        <v>7</v>
-      </c>
-      <c r="H155" t="s">
-        <v>355</v>
-      </c>
-      <c r="I155" t="s">
-        <v>358</v>
-      </c>
       <c r="J155" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="K155">
         <v>125569</v>
@@ -8534,28 +8542,28 @@
         <v>155</v>
       </c>
       <c r="B156" t="s">
+        <v>358</v>
+      </c>
+      <c r="C156" t="s">
+        <v>353</v>
+      </c>
+      <c r="D156" t="s">
+        <v>5</v>
+      </c>
+      <c r="F156" t="s">
         <v>359</v>
       </c>
-      <c r="C156" t="s">
+      <c r="G156" t="s">
+        <v>7</v>
+      </c>
+      <c r="H156" t="s">
         <v>354</v>
       </c>
-      <c r="D156" t="s">
-        <v>5</v>
-      </c>
-      <c r="F156" t="s">
+      <c r="I156" t="s">
         <v>360</v>
       </c>
-      <c r="G156" t="s">
-        <v>7</v>
-      </c>
-      <c r="H156" t="s">
-        <v>355</v>
-      </c>
-      <c r="I156" t="s">
-        <v>361</v>
-      </c>
       <c r="J156" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K156">
         <v>51234</v>
@@ -8575,10 +8583,10 @@
         <v>156</v>
       </c>
       <c r="B157" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C157" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D157" t="s">
         <v>5</v>
@@ -8587,19 +8595,19 @@
         <v>16</v>
       </c>
       <c r="F157" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G157" t="s">
         <v>7</v>
       </c>
       <c r="H157" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="I157" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="J157" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="K157">
         <v>123780</v>
@@ -8619,28 +8627,28 @@
         <v>157</v>
       </c>
       <c r="B158" t="s">
+        <v>363</v>
+      </c>
+      <c r="C158" t="s">
+        <v>353</v>
+      </c>
+      <c r="D158" t="s">
+        <v>5</v>
+      </c>
+      <c r="F158" t="s">
         <v>364</v>
       </c>
-      <c r="C158" t="s">
+      <c r="G158" t="s">
+        <v>7</v>
+      </c>
+      <c r="H158" t="s">
         <v>354</v>
       </c>
-      <c r="D158" t="s">
-        <v>5</v>
-      </c>
-      <c r="F158" t="s">
+      <c r="I158" t="s">
         <v>365</v>
       </c>
-      <c r="G158" t="s">
-        <v>7</v>
-      </c>
-      <c r="H158" t="s">
-        <v>355</v>
-      </c>
-      <c r="I158" t="s">
-        <v>366</v>
-      </c>
       <c r="J158" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K158">
         <v>46000</v>
@@ -8660,25 +8668,25 @@
         <v>158</v>
       </c>
       <c r="B159" t="s">
+        <v>366</v>
+      </c>
+      <c r="C159" t="s">
+        <v>353</v>
+      </c>
+      <c r="D159" t="s">
+        <v>5</v>
+      </c>
+      <c r="G159" t="s">
+        <v>7</v>
+      </c>
+      <c r="H159" t="s">
+        <v>354</v>
+      </c>
+      <c r="I159" t="s">
         <v>367</v>
       </c>
-      <c r="C159" t="s">
-        <v>354</v>
-      </c>
-      <c r="D159" t="s">
-        <v>5</v>
-      </c>
-      <c r="G159" t="s">
-        <v>7</v>
-      </c>
-      <c r="H159" t="s">
-        <v>355</v>
-      </c>
-      <c r="I159" t="s">
-        <v>368</v>
-      </c>
       <c r="J159" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K159">
         <v>35600</v>
@@ -8698,10 +8706,10 @@
         <v>159</v>
       </c>
       <c r="B160" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C160" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D160" t="s">
         <v>5</v>
@@ -8713,13 +8721,13 @@
         <v>7</v>
       </c>
       <c r="H160" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="I160" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="J160" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="K160">
         <v>199950</v>
@@ -8739,10 +8747,10 @@
         <v>160</v>
       </c>
       <c r="B161" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C161" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D161" t="s">
         <v>5</v>
@@ -8754,13 +8762,13 @@
         <v>7</v>
       </c>
       <c r="H161" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="I161" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="J161" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="K161">
         <v>108000</v>
@@ -8780,10 +8788,10 @@
         <v>161</v>
       </c>
       <c r="B162" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C162" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D162" t="s">
         <v>5</v>
@@ -8795,13 +8803,13 @@
         <v>7</v>
       </c>
       <c r="H162" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="I162" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="J162" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="K162">
         <v>142808</v>
@@ -8821,10 +8829,10 @@
         <v>162</v>
       </c>
       <c r="B163" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C163" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D163" t="s">
         <v>5</v>
@@ -8836,13 +8844,13 @@
         <v>7</v>
       </c>
       <c r="H163" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="I163" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="J163" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="K163">
         <v>80463</v>
@@ -8862,10 +8870,10 @@
         <v>163</v>
       </c>
       <c r="B164" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C164" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D164" t="s">
         <v>5</v>
@@ -8877,13 +8885,13 @@
         <v>7</v>
       </c>
       <c r="H164" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="I164" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J164" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K164">
         <v>83000</v>
@@ -8903,25 +8911,25 @@
         <v>164</v>
       </c>
       <c r="B165" t="s">
+        <v>378</v>
+      </c>
+      <c r="C165" t="s">
+        <v>353</v>
+      </c>
+      <c r="D165" t="s">
+        <v>5</v>
+      </c>
+      <c r="G165" t="s">
+        <v>7</v>
+      </c>
+      <c r="H165" t="s">
+        <v>354</v>
+      </c>
+      <c r="I165" t="s">
         <v>379</v>
       </c>
-      <c r="C165" t="s">
-        <v>354</v>
-      </c>
-      <c r="D165" t="s">
-        <v>5</v>
-      </c>
-      <c r="G165" t="s">
-        <v>7</v>
-      </c>
-      <c r="H165" t="s">
-        <v>355</v>
-      </c>
-      <c r="I165" t="s">
-        <v>380</v>
-      </c>
       <c r="J165" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K165">
         <v>129000</v>
@@ -8941,28 +8949,28 @@
         <v>165</v>
       </c>
       <c r="B166" t="s">
+        <v>380</v>
+      </c>
+      <c r="C166" t="s">
         <v>381</v>
       </c>
-      <c r="C166" t="s">
+      <c r="D166" t="s">
+        <v>5</v>
+      </c>
+      <c r="F166" t="s">
+        <v>216</v>
+      </c>
+      <c r="G166" t="s">
+        <v>7</v>
+      </c>
+      <c r="H166" t="s">
+        <v>113</v>
+      </c>
+      <c r="I166" t="s">
         <v>382</v>
       </c>
-      <c r="D166" t="s">
-        <v>5</v>
-      </c>
-      <c r="F166" t="s">
-        <v>217</v>
-      </c>
-      <c r="G166" t="s">
-        <v>7</v>
-      </c>
-      <c r="H166" t="s">
-        <v>114</v>
-      </c>
-      <c r="I166" t="s">
-        <v>383</v>
-      </c>
       <c r="J166" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K166">
         <v>62209</v>
@@ -8982,16 +8990,16 @@
         <v>166</v>
       </c>
       <c r="B167" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C167" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D167" t="s">
         <v>5</v>
       </c>
       <c r="F167" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="G167" t="s">
         <v>7</v>
@@ -9000,10 +9008,10 @@
         <v>8</v>
       </c>
       <c r="I167" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="J167" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="K167">
         <v>36117</v>
@@ -9023,10 +9031,10 @@
         <v>167</v>
       </c>
       <c r="B168" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C168" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D168" t="s">
         <v>5</v>
@@ -9035,19 +9043,19 @@
         <v>23</v>
       </c>
       <c r="F168" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G168" t="s">
         <v>7</v>
       </c>
       <c r="H168" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I168" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="J168" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="K168">
         <v>49900</v>
@@ -9067,10 +9075,10 @@
         <v>168</v>
       </c>
       <c r="B169" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C169" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D169" t="s">
         <v>5</v>
@@ -9079,19 +9087,19 @@
         <v>16</v>
       </c>
       <c r="F169" t="s">
+        <v>388</v>
+      </c>
+      <c r="G169" t="s">
+        <v>7</v>
+      </c>
+      <c r="H169" t="s">
+        <v>85</v>
+      </c>
+      <c r="I169" t="s">
         <v>389</v>
       </c>
-      <c r="G169" t="s">
-        <v>7</v>
-      </c>
-      <c r="H169" t="s">
-        <v>86</v>
-      </c>
-      <c r="I169" t="s">
-        <v>390</v>
-      </c>
       <c r="J169" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="K169">
         <v>39000</v>
@@ -9111,28 +9119,28 @@
         <v>169</v>
       </c>
       <c r="B170" t="s">
+        <v>390</v>
+      </c>
+      <c r="C170" t="s">
+        <v>381</v>
+      </c>
+      <c r="D170" t="s">
+        <v>5</v>
+      </c>
+      <c r="F170" t="s">
+        <v>359</v>
+      </c>
+      <c r="G170" t="s">
+        <v>7</v>
+      </c>
+      <c r="H170" t="s">
+        <v>197</v>
+      </c>
+      <c r="I170" t="s">
         <v>391</v>
       </c>
-      <c r="C170" t="s">
-        <v>382</v>
-      </c>
-      <c r="D170" t="s">
-        <v>5</v>
-      </c>
-      <c r="F170" t="s">
-        <v>360</v>
-      </c>
-      <c r="G170" t="s">
-        <v>7</v>
-      </c>
-      <c r="H170" t="s">
-        <v>198</v>
-      </c>
-      <c r="I170" t="s">
-        <v>392</v>
-      </c>
       <c r="J170" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="K170">
         <v>49000</v>
@@ -9152,13 +9160,13 @@
         <v>170</v>
       </c>
       <c r="B171" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C171" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D171" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G171" t="s">
         <v>7</v>
@@ -9167,10 +9175,10 @@
         <v>8</v>
       </c>
       <c r="I171" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="J171" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="K171">
         <v>59400</v>
@@ -9190,10 +9198,10 @@
         <v>171</v>
       </c>
       <c r="B172" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C172" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D172" t="s">
         <v>5</v>
@@ -9208,10 +9216,10 @@
         <v>8</v>
       </c>
       <c r="I172" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="J172" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="K172">
         <v>65000</v>
@@ -9231,31 +9239,31 @@
         <v>172</v>
       </c>
       <c r="B173" t="s">
+        <v>396</v>
+      </c>
+      <c r="C173" t="s">
+        <v>381</v>
+      </c>
+      <c r="D173" t="s">
+        <v>5</v>
+      </c>
+      <c r="E173" t="s">
+        <v>398</v>
+      </c>
+      <c r="F173" t="s">
         <v>397</v>
       </c>
-      <c r="C173" t="s">
-        <v>382</v>
-      </c>
-      <c r="D173" t="s">
-        <v>5</v>
-      </c>
-      <c r="E173" t="s">
+      <c r="G173" t="s">
+        <v>7</v>
+      </c>
+      <c r="H173" t="s">
         <v>399</v>
       </c>
-      <c r="F173" t="s">
-        <v>398</v>
-      </c>
-      <c r="G173" t="s">
-        <v>7</v>
-      </c>
-      <c r="H173" t="s">
+      <c r="I173" t="s">
         <v>400</v>
       </c>
-      <c r="I173" t="s">
-        <v>401</v>
-      </c>
       <c r="J173" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K173">
         <v>47000</v>
@@ -9275,28 +9283,28 @@
         <v>173</v>
       </c>
       <c r="B174" t="s">
+        <v>401</v>
+      </c>
+      <c r="C174" t="s">
+        <v>381</v>
+      </c>
+      <c r="D174" t="s">
+        <v>5</v>
+      </c>
+      <c r="E174" t="s">
+        <v>398</v>
+      </c>
+      <c r="G174" t="s">
+        <v>7</v>
+      </c>
+      <c r="H174" t="s">
+        <v>399</v>
+      </c>
+      <c r="I174" t="s">
         <v>402</v>
       </c>
-      <c r="C174" t="s">
-        <v>382</v>
-      </c>
-      <c r="D174" t="s">
-        <v>5</v>
-      </c>
-      <c r="E174" t="s">
-        <v>399</v>
-      </c>
-      <c r="G174" t="s">
-        <v>7</v>
-      </c>
-      <c r="H174" t="s">
-        <v>400</v>
-      </c>
-      <c r="I174" t="s">
-        <v>403</v>
-      </c>
       <c r="J174" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K174">
         <v>29000</v>
@@ -9316,10 +9324,10 @@
         <v>174</v>
       </c>
       <c r="B175" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C175" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D175" t="s">
         <v>5</v>
@@ -9328,19 +9336,19 @@
         <v>23</v>
       </c>
       <c r="F175" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G175" t="s">
         <v>7</v>
       </c>
       <c r="H175" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I175" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="J175" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K175">
         <v>132239</v>
@@ -9360,10 +9368,10 @@
         <v>175</v>
       </c>
       <c r="B176" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C176" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D176" t="s">
         <v>5</v>
@@ -9375,13 +9383,13 @@
         <v>7</v>
       </c>
       <c r="H176" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="I176" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="J176" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K176">
         <v>35016</v>
@@ -9401,25 +9409,25 @@
         <v>176</v>
       </c>
       <c r="B177" t="s">
+        <v>407</v>
+      </c>
+      <c r="C177" t="s">
+        <v>381</v>
+      </c>
+      <c r="D177" t="s">
+        <v>5</v>
+      </c>
+      <c r="G177" t="s">
+        <v>7</v>
+      </c>
+      <c r="H177" t="s">
+        <v>85</v>
+      </c>
+      <c r="I177" t="s">
         <v>408</v>
       </c>
-      <c r="C177" t="s">
-        <v>382</v>
-      </c>
-      <c r="D177" t="s">
-        <v>5</v>
-      </c>
-      <c r="G177" t="s">
-        <v>7</v>
-      </c>
-      <c r="H177" t="s">
-        <v>86</v>
-      </c>
-      <c r="I177" t="s">
-        <v>409</v>
-      </c>
       <c r="J177" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K177">
         <v>60000</v>
@@ -9439,28 +9447,28 @@
         <v>177</v>
       </c>
       <c r="B178" t="s">
+        <v>409</v>
+      </c>
+      <c r="C178" t="s">
+        <v>381</v>
+      </c>
+      <c r="D178" t="s">
+        <v>5</v>
+      </c>
+      <c r="F178" t="s">
         <v>410</v>
       </c>
-      <c r="C178" t="s">
-        <v>382</v>
-      </c>
-      <c r="D178" t="s">
-        <v>5</v>
-      </c>
-      <c r="F178" t="s">
+      <c r="G178" t="s">
+        <v>7</v>
+      </c>
+      <c r="H178" t="s">
+        <v>354</v>
+      </c>
+      <c r="I178" t="s">
         <v>411</v>
       </c>
-      <c r="G178" t="s">
-        <v>7</v>
-      </c>
-      <c r="H178" t="s">
-        <v>355</v>
-      </c>
-      <c r="I178" t="s">
-        <v>412</v>
-      </c>
       <c r="J178" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="K178">
         <v>90244</v>
@@ -9480,25 +9488,25 @@
         <v>178</v>
       </c>
       <c r="B179" t="s">
+        <v>412</v>
+      </c>
+      <c r="C179" t="s">
+        <v>381</v>
+      </c>
+      <c r="D179" t="s">
+        <v>5</v>
+      </c>
+      <c r="G179" t="s">
+        <v>7</v>
+      </c>
+      <c r="H179" t="s">
+        <v>354</v>
+      </c>
+      <c r="I179" t="s">
         <v>413</v>
       </c>
-      <c r="C179" t="s">
-        <v>382</v>
-      </c>
-      <c r="D179" t="s">
-        <v>5</v>
-      </c>
-      <c r="G179" t="s">
-        <v>7</v>
-      </c>
-      <c r="H179" t="s">
-        <v>355</v>
-      </c>
-      <c r="I179" t="s">
-        <v>414</v>
-      </c>
       <c r="J179" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K179">
         <v>38700</v>
@@ -9518,10 +9526,10 @@
         <v>179</v>
       </c>
       <c r="B180" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C180" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D180" t="s">
         <v>5</v>
@@ -9530,13 +9538,13 @@
         <v>7</v>
       </c>
       <c r="H180" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="I180" s="1" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="J180" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="K180">
         <v>62414</v>
@@ -9556,25 +9564,25 @@
         <v>180</v>
       </c>
       <c r="B181" t="s">
+        <v>415</v>
+      </c>
+      <c r="C181" t="s">
+        <v>381</v>
+      </c>
+      <c r="D181" t="s">
+        <v>5</v>
+      </c>
+      <c r="G181" t="s">
+        <v>7</v>
+      </c>
+      <c r="H181" t="s">
+        <v>399</v>
+      </c>
+      <c r="I181" t="s">
         <v>416</v>
       </c>
-      <c r="C181" t="s">
-        <v>382</v>
-      </c>
-      <c r="D181" t="s">
-        <v>5</v>
-      </c>
-      <c r="G181" t="s">
-        <v>7</v>
-      </c>
-      <c r="H181" t="s">
-        <v>400</v>
-      </c>
-      <c r="I181" t="s">
-        <v>417</v>
-      </c>
       <c r="J181" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K181">
         <v>51000</v>
@@ -9594,10 +9602,10 @@
         <v>181</v>
       </c>
       <c r="B182" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C182" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D182" t="s">
         <v>5</v>
@@ -9609,13 +9617,13 @@
         <v>7</v>
       </c>
       <c r="H182" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I182" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J182" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K182">
         <v>53115</v>
@@ -9635,25 +9643,25 @@
         <v>182</v>
       </c>
       <c r="B183" t="s">
+        <v>419</v>
+      </c>
+      <c r="C183" t="s">
+        <v>381</v>
+      </c>
+      <c r="D183" t="s">
+        <v>5</v>
+      </c>
+      <c r="G183" t="s">
+        <v>7</v>
+      </c>
+      <c r="H183" t="s">
+        <v>354</v>
+      </c>
+      <c r="I183" t="s">
         <v>420</v>
       </c>
-      <c r="C183" t="s">
-        <v>382</v>
-      </c>
-      <c r="D183" t="s">
-        <v>5</v>
-      </c>
-      <c r="G183" t="s">
-        <v>7</v>
-      </c>
-      <c r="H183" t="s">
-        <v>355</v>
-      </c>
-      <c r="I183" t="s">
-        <v>421</v>
-      </c>
       <c r="J183" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K183">
         <v>120000</v>
@@ -9673,10 +9681,10 @@
         <v>183</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C184" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D184" t="s">
         <v>5</v>
@@ -9688,13 +9696,13 @@
         <v>7</v>
       </c>
       <c r="H184" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I184" s="3" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="J184" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K184">
         <v>66477</v>
@@ -9714,10 +9722,10 @@
         <v>184</v>
       </c>
       <c r="B185" t="s">
+        <v>422</v>
+      </c>
+      <c r="C185" t="s">
         <v>423</v>
-      </c>
-      <c r="C185" t="s">
-        <v>424</v>
       </c>
       <c r="D185" t="s">
         <v>5</v>
@@ -9729,10 +9737,10 @@
         <v>7</v>
       </c>
       <c r="H185" t="s">
+        <v>424</v>
+      </c>
+      <c r="I185" t="s">
         <v>425</v>
-      </c>
-      <c r="I185" t="s">
-        <v>426</v>
       </c>
       <c r="K185">
         <v>59300</v>
@@ -9752,22 +9760,22 @@
         <v>185</v>
       </c>
       <c r="B186" t="s">
+        <v>426</v>
+      </c>
+      <c r="C186" t="s">
+        <v>423</v>
+      </c>
+      <c r="D186" t="s">
+        <v>5</v>
+      </c>
+      <c r="G186" t="s">
+        <v>7</v>
+      </c>
+      <c r="H186" t="s">
+        <v>424</v>
+      </c>
+      <c r="I186" t="s">
         <v>427</v>
-      </c>
-      <c r="C186" t="s">
-        <v>424</v>
-      </c>
-      <c r="D186" t="s">
-        <v>5</v>
-      </c>
-      <c r="G186" t="s">
-        <v>7</v>
-      </c>
-      <c r="H186" t="s">
-        <v>425</v>
-      </c>
-      <c r="I186" t="s">
-        <v>428</v>
       </c>
       <c r="K186">
         <v>44000</v>
@@ -9787,22 +9795,22 @@
         <v>186</v>
       </c>
       <c r="B187" t="s">
+        <v>428</v>
+      </c>
+      <c r="C187" t="s">
+        <v>423</v>
+      </c>
+      <c r="D187" t="s">
+        <v>5</v>
+      </c>
+      <c r="G187" t="s">
+        <v>7</v>
+      </c>
+      <c r="H187" t="s">
+        <v>424</v>
+      </c>
+      <c r="I187" t="s">
         <v>429</v>
-      </c>
-      <c r="C187" t="s">
-        <v>424</v>
-      </c>
-      <c r="D187" t="s">
-        <v>5</v>
-      </c>
-      <c r="G187" t="s">
-        <v>7</v>
-      </c>
-      <c r="H187" t="s">
-        <v>425</v>
-      </c>
-      <c r="I187" t="s">
-        <v>430</v>
       </c>
       <c r="K187">
         <v>26528</v>
@@ -9822,10 +9830,10 @@
         <v>187</v>
       </c>
       <c r="B188" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C188" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D188" t="s">
         <v>5</v>
@@ -9837,10 +9845,10 @@
         <v>7</v>
       </c>
       <c r="H188" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="I188" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="K188">
         <v>95684</v>
@@ -9855,15 +9863,15 @@
         <v>57000</v>
       </c>
     </row>
-    <row r="189" spans="1:14">
+    <row r="189" spans="1:14" ht="15">
       <c r="A189">
         <v>188</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="C189" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D189" t="s">
         <v>5</v>
@@ -9872,10 +9880,10 @@
         <v>7</v>
       </c>
       <c r="H189" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I189" s="4" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="K189">
         <v>26737</v>
@@ -9895,10 +9903,10 @@
         <v>189</v>
       </c>
       <c r="B190" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C190" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D190" t="s">
         <v>5</v>
@@ -9910,10 +9918,10 @@
         <v>7</v>
       </c>
       <c r="H190" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="I190" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="K190">
         <v>60000</v>
@@ -9933,22 +9941,22 @@
         <v>190</v>
       </c>
       <c r="B191" t="s">
+        <v>434</v>
+      </c>
+      <c r="C191" t="s">
+        <v>423</v>
+      </c>
+      <c r="D191" t="s">
+        <v>5</v>
+      </c>
+      <c r="G191" t="s">
+        <v>7</v>
+      </c>
+      <c r="H191" t="s">
+        <v>424</v>
+      </c>
+      <c r="I191" t="s">
         <v>435</v>
-      </c>
-      <c r="C191" t="s">
-        <v>424</v>
-      </c>
-      <c r="D191" t="s">
-        <v>5</v>
-      </c>
-      <c r="G191" t="s">
-        <v>7</v>
-      </c>
-      <c r="H191" t="s">
-        <v>425</v>
-      </c>
-      <c r="I191" t="s">
-        <v>436</v>
       </c>
       <c r="K191">
         <v>34895</v>
@@ -9965,33 +9973,33 @@
     </row>
     <row r="192" spans="1:14">
       <c r="B192" s="1" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="G192" s="1" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="H192" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="I192" s="1" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
     </row>
     <row r="193" spans="2:2">
       <c r="B193" s="1" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\intern.bjres\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB266823-E62C-4725-A568-99FB550A322A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{687720E7-F6A5-4FA3-B74B-FBC3B004BD5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1421,18 +1421,10 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>116.365799,40.001522</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>中关村东升科技园·学北园</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>116.352247,40.015235</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>116.349697,39.932894</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -1584,6 +1576,12 @@
   </si>
   <si>
     <t>116.414436,39.909474</t>
+  </si>
+  <si>
+    <t>116.365174,40.004451</t>
+  </si>
+  <si>
+    <t>116.351227,40.018578</t>
   </si>
 </sst>
 </file>
@@ -2424,7 +2422,7 @@
         <v>8</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="J10" t="s">
         <v>440</v>
@@ -2949,7 +2947,7 @@
         <v>8</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="J22" t="s">
         <v>440</v>
@@ -3336,7 +3334,7 @@
         <v>8</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="J31" t="s">
         <v>440</v>
@@ -3459,7 +3457,7 @@
         <v>8</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="J34" t="s">
         <v>452</v>
@@ -3544,7 +3542,7 @@
         <v>8</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="J36" t="s">
         <v>452</v>
@@ -3585,7 +3583,7 @@
         <v>8</v>
       </c>
       <c r="I37" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="J37" t="s">
         <v>452</v>
@@ -3919,7 +3917,7 @@
         <v>113</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="J45" t="s">
         <v>452</v>
@@ -3963,7 +3961,7 @@
         <v>113</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="J46" t="s">
         <v>452</v>
@@ -4007,7 +4005,7 @@
         <v>113</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="J47" t="s">
         <v>452</v>
@@ -4385,7 +4383,7 @@
         <v>113</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="J56" t="s">
         <v>452</v>
@@ -4558,7 +4556,7 @@
         <v>8</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="J60" t="s">
         <v>453</v>
@@ -4681,7 +4679,7 @@
         <v>85</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J63" t="s">
         <v>436</v>
@@ -4933,7 +4931,7 @@
         <v>85</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="J69" t="s">
         <v>436</v>
@@ -5229,7 +5227,7 @@
         <v>85</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="J76" t="s">
         <v>436</v>
@@ -5358,7 +5356,7 @@
         <v>197</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="J79" t="s">
         <v>436</v>
@@ -5607,7 +5605,7 @@
         <v>8</v>
       </c>
       <c r="I85" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="J85" t="s">
         <v>437</v>
@@ -5692,7 +5690,7 @@
         <v>8</v>
       </c>
       <c r="I87" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="J87" t="s">
         <v>437</v>
@@ -5777,7 +5775,7 @@
         <v>8</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="J89" t="s">
         <v>437</v>
@@ -5859,7 +5857,7 @@
         <v>8</v>
       </c>
       <c r="I91" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="J91" t="s">
         <v>437</v>
@@ -5988,7 +5986,7 @@
         <v>8</v>
       </c>
       <c r="I94" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="J94" t="s">
         <v>437</v>
@@ -6111,7 +6109,7 @@
         <v>8</v>
       </c>
       <c r="I97" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="J97" t="s">
         <v>452</v>
@@ -6366,7 +6364,7 @@
         <v>197</v>
       </c>
       <c r="I103" s="2" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="J103" t="s">
         <v>454</v>
@@ -6776,7 +6774,7 @@
         <v>197</v>
       </c>
       <c r="I113" s="2" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="J113" t="s">
         <v>438</v>
@@ -6794,7 +6792,7 @@
         <v>427</v>
       </c>
       <c r="P113" s="1" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -6820,7 +6818,7 @@
         <v>197</v>
       </c>
       <c r="I114" s="2" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="J114" t="s">
         <v>438</v>
@@ -6838,7 +6836,7 @@
         <v>11500</v>
       </c>
       <c r="P114" s="1" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -6861,7 +6859,7 @@
         <v>197</v>
       </c>
       <c r="I115" s="5" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="J115" t="s">
         <v>438</v>
@@ -7133,7 +7131,7 @@
         <v>197</v>
       </c>
       <c r="I122" s="3" t="s">
-        <v>460</v>
+        <v>502</v>
       </c>
       <c r="J122" t="s">
         <v>438</v>
@@ -7151,7 +7149,7 @@
         <v>36000</v>
       </c>
       <c r="P122" s="1" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7159,7 +7157,7 @@
         <v>122</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C123" t="s">
         <v>241</v>
@@ -7171,7 +7169,7 @@
         <v>197</v>
       </c>
       <c r="I123" s="3" t="s">
-        <v>462</v>
+        <v>503</v>
       </c>
       <c r="J123" t="s">
         <v>438</v>
@@ -7189,7 +7187,7 @@
         <v>97326.47</v>
       </c>
       <c r="P123" s="1" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -8082,7 +8080,7 @@
         <v>144</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="C145" t="s">
         <v>321</v>
@@ -8103,7 +8101,7 @@
         <v>8</v>
       </c>
       <c r="I145" s="2" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="J145" t="s">
         <v>452</v>
@@ -8208,7 +8206,7 @@
         <v>147</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C148" t="s">
         <v>321</v>
@@ -8229,7 +8227,7 @@
         <v>8</v>
       </c>
       <c r="I148" s="2" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="J148" t="s">
         <v>452</v>
@@ -8270,7 +8268,7 @@
         <v>85</v>
       </c>
       <c r="I149" s="2" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="J149" t="s">
         <v>452</v>
@@ -9541,7 +9539,7 @@
         <v>354</v>
       </c>
       <c r="I180" s="1" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J180" t="s">
         <v>453</v>
@@ -9699,7 +9697,7 @@
         <v>85</v>
       </c>
       <c r="I184" s="3" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="J184" t="s">
         <v>452</v>
@@ -9868,7 +9866,7 @@
         <v>188</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C189" t="s">
         <v>423</v>
@@ -9883,7 +9881,7 @@
         <v>85</v>
       </c>
       <c r="I189" s="4" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K189">
         <v>26737</v>
@@ -9973,29 +9971,29 @@
     </row>
     <row r="192" spans="1:14">
       <c r="B192" s="1" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="G192" s="1" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="H192" s="1" t="s">
         <v>456</v>
       </c>
       <c r="I192" s="1" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
     </row>
     <row r="193" spans="2:2">
       <c r="B193" s="1" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\intern.bjres\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{687720E7-F6A5-4FA3-B74B-FBC3B004BD5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6B0B0C4-4768-4FA7-B6A8-B69A40243FFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1580" uniqueCount="504">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1580" uniqueCount="505">
   <si>
     <t>所在市</t>
   </si>
@@ -1582,6 +1582,9 @@
   </si>
   <si>
     <t>116.351227,40.018578</t>
+  </si>
+  <si>
+    <t>116.406051,39.977725</t>
   </si>
 </sst>
 </file>
@@ -8264,11 +8267,11 @@
       <c r="G149" t="s">
         <v>7</v>
       </c>
-      <c r="H149" t="s">
-        <v>85</v>
+      <c r="H149" s="7" t="s">
+        <v>8</v>
       </c>
       <c r="I149" s="2" t="s">
-        <v>461</v>
+        <v>504</v>
       </c>
       <c r="J149" t="s">
         <v>452</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\intern.bjres\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://colliers.sharepoint.com/teams/Asia_Research/China/Shared Documents/North/Beijing/工作中报告_持续更新中/实习生文档/Ron/0303系统数据/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6B0B0C4-4768-4FA7-B6A8-B69A40243FFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B2126FFC-172F-4569-88A8-F2305D0C9028}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10006,6 +10006,299 @@
 </worksheet>
 </file>
 
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100BC605E6093A30A479FED397EFA867E40" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="55774fc2038cb4dae8fef12431c133f2">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f655991e-a262-4cc2-969f-4b8d0db6a5de" xmlns:ns3="8e40a7e4-94f1-4b05-8c7e-c5111c724f9a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="31482a63ce11ed8a627351d2502cc05d" ns2:_="" ns3:_="">
+    <xsd:import namespace="f655991e-a262-4cc2-969f-4b8d0db6a5de"/>
+    <xsd:import namespace="8e40a7e4-94f1-4b05-8c7e-c5111c724f9a"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns2:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns3:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns2:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceBillingMetadata" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="f655991e-a262-4cc2-969f-4b8d0db6a5de" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="8" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="9" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="22" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{8f2ff732-98c2-48c5-8f70-155633f64b93}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="f655991e-a262-4cc2-969f-4b8d0db6a5de">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e40a7e4-94f1-4b05-8c7e-c5111c724f9a" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="10" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="12" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="13" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="14" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="15" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="16" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="17" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="18" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="19" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="21" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="7ce671e0-2aae-4c8d-b367-8bb3494c1b07" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="23" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="26" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e40a7e4-94f1-4b05-8c7e-c5111c724f9a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="f655991e-a262-4cc2-969f-4b8d0db6a5de" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5BF42E8-7CD6-44A5-B028-608DFC162276}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C7A7DD6C-B285-4C23-BA8C-7CCC252AB8AB}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF6E6A69-6D48-49BB-9E8E-5B96C2738B7E}"/>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{8c970d48-f7b9-48b0-9606-072fbefb514d}" enabled="1" method="Standard" siteId="{049e3382-8cdc-477b-9317-951b04689668}" contentBits="0" removed="0"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://colliers.sharepoint.com/teams/Asia_Research/China/Shared Documents/North/Beijing/工作中报告_持续更新中/实习生文档/Ron/0303系统数据/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B2126FFC-172F-4569-88A8-F2305D0C9028}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="8_{B2126FFC-172F-4569-88A8-F2305D0C9028}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF6D8DFD-B086-4386-86FD-F5F91FA42B30}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -293,9 +293,6 @@
     <t>西城区</t>
   </si>
   <si>
-    <t>116.363957,39.936251</t>
-  </si>
-  <si>
     <t>北京国际俱乐部二期（C座）</t>
   </si>
   <si>
@@ -1425,10 +1422,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>116.349697,39.932894</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>奥南五号-B座（恒毅大厦）</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -1493,10 +1486,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>116.470221,39.955076</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>116.459281,39.960483</t>
   </si>
   <si>
@@ -1585,6 +1574,15 @@
   </si>
   <si>
     <t>116.406051,39.977725</t>
+  </si>
+  <si>
+    <t>116.35467,39.914699</t>
+  </si>
+  <si>
+    <t>116.47137,39.955305</t>
+  </si>
+  <si>
+    <t>116.357285,39.93162</t>
   </si>
 </sst>
 </file>
@@ -1681,7 +1679,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1690,6 +1688,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1706,10 +1705,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2017,22 +2012,22 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B1" t="s">
+        <v>442</v>
+      </c>
+      <c r="C1" t="s">
         <v>443</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>444</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="F1" t="s">
         <v>445</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>451</v>
-      </c>
-      <c r="F1" t="s">
-        <v>446</v>
       </c>
       <c r="G1" t="s">
         <v>0</v>
@@ -2044,19 +2039,19 @@
         <v>2</v>
       </c>
       <c r="J1" t="s">
+        <v>446</v>
+      </c>
+      <c r="K1" t="s">
+        <v>441</v>
+      </c>
+      <c r="L1" t="s">
         <v>447</v>
       </c>
-      <c r="K1" t="s">
-        <v>442</v>
-      </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>448</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>449</v>
-      </c>
-      <c r="N1" t="s">
-        <v>450</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -2085,7 +2080,7 @@
         <v>9</v>
       </c>
       <c r="J2" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K2">
         <v>72308</v>
@@ -2126,7 +2121,7 @@
         <v>12</v>
       </c>
       <c r="J3" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K3">
         <v>72308</v>
@@ -2170,7 +2165,7 @@
         <v>17</v>
       </c>
       <c r="J4" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K4">
         <v>130769</v>
@@ -2214,7 +2209,7 @@
         <v>20</v>
       </c>
       <c r="J5" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K5">
         <v>64615</v>
@@ -2258,7 +2253,7 @@
         <v>24</v>
       </c>
       <c r="J6" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K6">
         <v>80091</v>
@@ -2299,7 +2294,7 @@
         <v>27</v>
       </c>
       <c r="J7" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="K7">
         <v>70673</v>
@@ -2343,7 +2338,7 @@
         <v>30</v>
       </c>
       <c r="J8" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K8">
         <v>90466</v>
@@ -2384,7 +2379,7 @@
         <v>32</v>
       </c>
       <c r="J9" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="K9">
         <v>46720</v>
@@ -2425,10 +2420,10 @@
         <v>8</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="J10" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="K10">
         <v>95000</v>
@@ -2472,7 +2467,7 @@
         <v>37</v>
       </c>
       <c r="J11" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K11">
         <v>85300</v>
@@ -2516,7 +2511,7 @@
         <v>40</v>
       </c>
       <c r="J12" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="K12">
         <v>33305</v>
@@ -2560,7 +2555,7 @@
         <v>42</v>
       </c>
       <c r="J13" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K13">
         <v>120245.21</v>
@@ -2604,7 +2599,7 @@
         <v>42</v>
       </c>
       <c r="J14" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K14">
         <v>70425.53</v>
@@ -2648,7 +2643,7 @@
         <v>46</v>
       </c>
       <c r="J15" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K15">
         <v>78000</v>
@@ -2692,7 +2687,7 @@
         <v>49</v>
       </c>
       <c r="J16" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="K16">
         <v>102796</v>
@@ -2736,7 +2731,7 @@
         <v>51</v>
       </c>
       <c r="J17" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="K17">
         <v>49200</v>
@@ -2780,7 +2775,7 @@
         <v>53</v>
       </c>
       <c r="J18" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="K18">
         <v>65096</v>
@@ -2824,7 +2819,7 @@
         <v>56</v>
       </c>
       <c r="J19" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K19">
         <v>56000</v>
@@ -2868,7 +2863,7 @@
         <v>59</v>
       </c>
       <c r="J20" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="K20">
         <v>177847</v>
@@ -2912,7 +2907,7 @@
         <v>62</v>
       </c>
       <c r="J21" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K21">
         <v>83000</v>
@@ -2950,10 +2945,10 @@
         <v>8</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="J22" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="K22">
         <v>26000</v>
@@ -2994,7 +2989,7 @@
         <v>66</v>
       </c>
       <c r="J23" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K23">
         <v>85887</v>
@@ -3035,7 +3030,7 @@
         <v>68</v>
       </c>
       <c r="J24" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K24">
         <v>20000</v>
@@ -3079,7 +3074,7 @@
         <v>71</v>
       </c>
       <c r="J25" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K25">
         <v>146385</v>
@@ -3123,7 +3118,7 @@
         <v>74</v>
       </c>
       <c r="J26" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K26">
         <v>87000</v>
@@ -3167,7 +3162,7 @@
         <v>77</v>
       </c>
       <c r="J27" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K27">
         <v>147166.79999999999</v>
@@ -3211,7 +3206,7 @@
         <v>80</v>
       </c>
       <c r="J28" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K28">
         <v>46063</v>
@@ -3255,7 +3250,7 @@
         <v>83</v>
       </c>
       <c r="J29" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="K29">
         <v>47261</v>
@@ -3275,7 +3270,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C30" t="s">
         <v>4</v>
@@ -3293,13 +3288,13 @@
         <v>7</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J30" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K30">
         <v>119000</v>
@@ -3319,7 +3314,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C31" t="s">
         <v>4</v>
@@ -3328,7 +3323,7 @@
         <v>5</v>
       </c>
       <c r="F31" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G31" t="s">
         <v>7</v>
@@ -3337,10 +3332,10 @@
         <v>8</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="J31" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="K31">
         <v>47000</v>
@@ -3360,7 +3355,7 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C32" t="s">
         <v>4</v>
@@ -3372,7 +3367,7 @@
         <v>16</v>
       </c>
       <c r="F32" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G32" t="s">
         <v>7</v>
@@ -3381,10 +3376,10 @@
         <v>8</v>
       </c>
       <c r="I32" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J32" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="K32">
         <v>186000</v>
@@ -3404,7 +3399,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C33" t="s">
         <v>4</v>
@@ -3419,10 +3414,10 @@
         <v>8</v>
       </c>
       <c r="I33" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J33" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K33">
         <v>40800</v>
@@ -3442,7 +3437,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C34" t="s">
         <v>4</v>
@@ -3451,7 +3446,7 @@
         <v>5</v>
       </c>
       <c r="F34" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G34" t="s">
         <v>7</v>
@@ -3460,10 +3455,10 @@
         <v>8</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="J34" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K34">
         <v>55200</v>
@@ -3483,7 +3478,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C35" t="s">
         <v>4</v>
@@ -3495,7 +3490,7 @@
         <v>16</v>
       </c>
       <c r="F35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G35" t="s">
         <v>7</v>
@@ -3504,10 +3499,10 @@
         <v>8</v>
       </c>
       <c r="I35" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J35" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="K35">
         <v>350000</v>
@@ -3527,7 +3522,7 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C36" t="s">
         <v>4</v>
@@ -3545,10 +3540,10 @@
         <v>8</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="J36" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K36">
         <v>65000</v>
@@ -3568,7 +3563,7 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C37" t="s">
         <v>4</v>
@@ -3586,10 +3581,10 @@
         <v>8</v>
       </c>
       <c r="I37" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="J37" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K37">
         <v>35000</v>
@@ -3609,7 +3604,7 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C38" t="s">
         <v>4</v>
@@ -3627,10 +3622,10 @@
         <v>8</v>
       </c>
       <c r="I38" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="J38" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="K38">
         <v>47000</v>
@@ -3650,7 +3645,7 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C39" t="s">
         <v>4</v>
@@ -3662,7 +3657,7 @@
         <v>23</v>
       </c>
       <c r="F39" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G39" t="s">
         <v>7</v>
@@ -3671,10 +3666,10 @@
         <v>8</v>
       </c>
       <c r="I39" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J39" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="K39">
         <v>120000</v>
@@ -3694,7 +3689,7 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C40" t="s">
         <v>4</v>
@@ -3712,10 +3707,10 @@
         <v>8</v>
       </c>
       <c r="I40" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J40" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K40">
         <v>83000</v>
@@ -3735,7 +3730,7 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C41" t="s">
         <v>4</v>
@@ -3753,10 +3748,10 @@
         <v>8</v>
       </c>
       <c r="I41" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J41" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="K41">
         <v>66030</v>
@@ -3776,7 +3771,7 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C42" t="s">
         <v>4</v>
@@ -3791,10 +3786,10 @@
         <v>8</v>
       </c>
       <c r="I42" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J42" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="K42">
         <v>40000</v>
@@ -3814,10 +3809,10 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
+        <v>109</v>
+      </c>
+      <c r="C43" t="s">
         <v>110</v>
-      </c>
-      <c r="C43" t="s">
-        <v>111</v>
       </c>
       <c r="D43" t="s">
         <v>5</v>
@@ -3825,20 +3820,20 @@
       <c r="E43" t="s">
         <v>16</v>
       </c>
-      <c r="F43" t="s">
+      <c r="F43" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="G43" t="s">
+        <v>7</v>
+      </c>
+      <c r="H43" t="s">
         <v>112</v>
       </c>
-      <c r="G43" t="s">
-        <v>7</v>
-      </c>
-      <c r="H43" t="s">
+      <c r="I43" t="s">
         <v>113</v>
       </c>
-      <c r="I43" t="s">
-        <v>114</v>
-      </c>
       <c r="J43" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K43">
         <v>40000</v>
@@ -3858,28 +3853,28 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
+        <v>114</v>
+      </c>
+      <c r="C44" t="s">
+        <v>110</v>
+      </c>
+      <c r="D44" t="s">
+        <v>5</v>
+      </c>
+      <c r="F44" t="s">
         <v>115</v>
       </c>
-      <c r="C44" t="s">
-        <v>111</v>
-      </c>
-      <c r="D44" t="s">
-        <v>5</v>
-      </c>
-      <c r="F44" t="s">
+      <c r="G44" t="s">
+        <v>7</v>
+      </c>
+      <c r="H44" t="s">
+        <v>112</v>
+      </c>
+      <c r="I44" t="s">
         <v>116</v>
       </c>
-      <c r="G44" t="s">
-        <v>7</v>
-      </c>
-      <c r="H44" t="s">
-        <v>113</v>
-      </c>
-      <c r="I44" t="s">
-        <v>117</v>
-      </c>
       <c r="J44" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K44">
         <v>54100</v>
@@ -3899,10 +3894,10 @@
         <v>44</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C45" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D45" t="s">
         <v>5</v>
@@ -3911,19 +3906,19 @@
         <v>23</v>
       </c>
       <c r="F45" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G45" t="s">
         <v>7</v>
       </c>
       <c r="H45" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="J45" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K45">
         <v>100000</v>
@@ -3943,10 +3938,10 @@
         <v>45</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C46" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D46" t="s">
         <v>5</v>
@@ -3955,19 +3950,19 @@
         <v>23</v>
       </c>
       <c r="F46" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G46" t="s">
         <v>7</v>
       </c>
       <c r="H46" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="J46" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K46">
         <v>150000</v>
@@ -3987,10 +3982,10 @@
         <v>46</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C47" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D47" t="s">
         <v>5</v>
@@ -3999,19 +3994,19 @@
         <v>23</v>
       </c>
       <c r="F47" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G47" t="s">
         <v>7</v>
       </c>
       <c r="H47" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="J47" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K47">
         <v>50000</v>
@@ -4031,10 +4026,10 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C48" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D48" t="s">
         <v>5</v>
@@ -4043,19 +4038,19 @@
         <v>23</v>
       </c>
       <c r="F48" t="s">
+        <v>124</v>
+      </c>
+      <c r="G48" t="s">
+        <v>7</v>
+      </c>
+      <c r="H48" t="s">
+        <v>112</v>
+      </c>
+      <c r="I48" t="s">
         <v>125</v>
       </c>
-      <c r="G48" t="s">
-        <v>7</v>
-      </c>
-      <c r="H48" t="s">
-        <v>113</v>
-      </c>
-      <c r="I48" t="s">
-        <v>126</v>
-      </c>
       <c r="J48" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K48">
         <v>43000</v>
@@ -4075,28 +4070,28 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
+        <v>126</v>
+      </c>
+      <c r="C49" t="s">
+        <v>110</v>
+      </c>
+      <c r="D49" t="s">
+        <v>5</v>
+      </c>
+      <c r="F49" t="s">
         <v>127</v>
       </c>
-      <c r="C49" t="s">
-        <v>111</v>
-      </c>
-      <c r="D49" t="s">
-        <v>5</v>
-      </c>
-      <c r="F49" t="s">
+      <c r="G49" t="s">
+        <v>7</v>
+      </c>
+      <c r="H49" t="s">
+        <v>112</v>
+      </c>
+      <c r="I49" t="s">
         <v>128</v>
       </c>
-      <c r="G49" t="s">
-        <v>7</v>
-      </c>
-      <c r="H49" t="s">
-        <v>113</v>
-      </c>
-      <c r="I49" t="s">
-        <v>129</v>
-      </c>
       <c r="J49" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K49">
         <v>65000</v>
@@ -4116,10 +4111,10 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C50" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D50" t="s">
         <v>5</v>
@@ -4134,13 +4129,13 @@
         <v>7</v>
       </c>
       <c r="H50" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I50" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="J50" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K50">
         <v>56000</v>
@@ -4160,10 +4155,10 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C51" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D51" t="s">
         <v>5</v>
@@ -4175,13 +4170,13 @@
         <v>7</v>
       </c>
       <c r="H51" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I51" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J51" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K51">
         <v>160000</v>
@@ -4201,10 +4196,10 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C52" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D52" t="s">
         <v>5</v>
@@ -4216,13 +4211,13 @@
         <v>7</v>
       </c>
       <c r="H52" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I52" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="J52" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K52">
         <v>33000</v>
@@ -4242,10 +4237,10 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C53" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D53" t="s">
         <v>5</v>
@@ -4254,19 +4249,19 @@
         <v>16</v>
       </c>
       <c r="F53" t="s">
+        <v>137</v>
+      </c>
+      <c r="G53" t="s">
+        <v>7</v>
+      </c>
+      <c r="H53" t="s">
+        <v>112</v>
+      </c>
+      <c r="I53" t="s">
         <v>138</v>
       </c>
-      <c r="G53" t="s">
-        <v>7</v>
-      </c>
-      <c r="H53" t="s">
-        <v>113</v>
-      </c>
-      <c r="I53" t="s">
-        <v>139</v>
-      </c>
       <c r="J53" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K53">
         <v>41318</v>
@@ -4286,28 +4281,28 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
+        <v>139</v>
+      </c>
+      <c r="C54" t="s">
+        <v>110</v>
+      </c>
+      <c r="D54" t="s">
+        <v>5</v>
+      </c>
+      <c r="F54" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="G54" t="s">
+        <v>7</v>
+      </c>
+      <c r="H54" t="s">
+        <v>112</v>
+      </c>
+      <c r="I54" t="s">
         <v>140</v>
       </c>
-      <c r="C54" t="s">
-        <v>111</v>
-      </c>
-      <c r="D54" t="s">
-        <v>5</v>
-      </c>
-      <c r="F54" t="s">
-        <v>130</v>
-      </c>
-      <c r="G54" t="s">
-        <v>7</v>
-      </c>
-      <c r="H54" t="s">
-        <v>113</v>
-      </c>
-      <c r="I54" t="s">
-        <v>141</v>
-      </c>
       <c r="J54" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K54">
         <v>34131</v>
@@ -4327,28 +4322,28 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
+        <v>141</v>
+      </c>
+      <c r="C55" t="s">
+        <v>110</v>
+      </c>
+      <c r="D55" t="s">
+        <v>5</v>
+      </c>
+      <c r="F55" t="s">
         <v>142</v>
       </c>
-      <c r="C55" t="s">
-        <v>111</v>
-      </c>
-      <c r="D55" t="s">
-        <v>5</v>
-      </c>
-      <c r="F55" t="s">
+      <c r="G55" t="s">
+        <v>7</v>
+      </c>
+      <c r="H55" t="s">
+        <v>112</v>
+      </c>
+      <c r="I55" t="s">
         <v>143</v>
       </c>
-      <c r="G55" t="s">
-        <v>7</v>
-      </c>
-      <c r="H55" t="s">
-        <v>113</v>
-      </c>
-      <c r="I55" t="s">
-        <v>144</v>
-      </c>
       <c r="J55" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K55">
         <v>48000</v>
@@ -4368,10 +4363,10 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C56" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D56" t="s">
         <v>5</v>
@@ -4383,13 +4378,13 @@
         <v>7</v>
       </c>
       <c r="H56" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="J56" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K56">
         <v>16000</v>
@@ -4409,10 +4404,10 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C57" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D57" t="s">
         <v>5</v>
@@ -4421,19 +4416,19 @@
         <v>16</v>
       </c>
       <c r="F57" t="s">
+        <v>146</v>
+      </c>
+      <c r="G57" t="s">
+        <v>7</v>
+      </c>
+      <c r="H57" t="s">
+        <v>112</v>
+      </c>
+      <c r="I57" t="s">
         <v>147</v>
       </c>
-      <c r="G57" t="s">
-        <v>7</v>
-      </c>
-      <c r="H57" t="s">
-        <v>113</v>
-      </c>
-      <c r="I57" t="s">
-        <v>148</v>
-      </c>
       <c r="J57" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K57">
         <v>30000</v>
@@ -4453,10 +4448,10 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C58" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D58" t="s">
         <v>5</v>
@@ -4465,19 +4460,19 @@
         <v>16</v>
       </c>
       <c r="F58" t="s">
+        <v>149</v>
+      </c>
+      <c r="G58" t="s">
+        <v>7</v>
+      </c>
+      <c r="H58" t="s">
+        <v>112</v>
+      </c>
+      <c r="I58" t="s">
         <v>150</v>
       </c>
-      <c r="G58" t="s">
-        <v>7</v>
-      </c>
-      <c r="H58" t="s">
-        <v>113</v>
-      </c>
-      <c r="I58" t="s">
-        <v>151</v>
-      </c>
       <c r="J58" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K58">
         <v>56000</v>
@@ -4497,10 +4492,10 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C59" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D59" t="s">
         <v>5</v>
@@ -4509,19 +4504,19 @@
         <v>16</v>
       </c>
       <c r="F59" t="s">
+        <v>152</v>
+      </c>
+      <c r="G59" t="s">
+        <v>7</v>
+      </c>
+      <c r="H59" t="s">
+        <v>112</v>
+      </c>
+      <c r="I59" t="s">
         <v>153</v>
       </c>
-      <c r="G59" t="s">
-        <v>7</v>
-      </c>
-      <c r="H59" t="s">
-        <v>113</v>
-      </c>
-      <c r="I59" t="s">
-        <v>154</v>
-      </c>
       <c r="J59" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K59">
         <v>43000</v>
@@ -4541,10 +4536,10 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C60" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D60" t="s">
         <v>5</v>
@@ -4559,10 +4554,10 @@
         <v>8</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="J60" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K60">
         <v>110000</v>
@@ -4582,25 +4577,25 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
+        <v>155</v>
+      </c>
+      <c r="C61" t="s">
+        <v>110</v>
+      </c>
+      <c r="D61" t="s">
+        <v>5</v>
+      </c>
+      <c r="G61" t="s">
+        <v>7</v>
+      </c>
+      <c r="H61" t="s">
+        <v>112</v>
+      </c>
+      <c r="I61" t="s">
         <v>156</v>
       </c>
-      <c r="C61" t="s">
-        <v>111</v>
-      </c>
-      <c r="D61" t="s">
-        <v>5</v>
-      </c>
-      <c r="G61" t="s">
-        <v>7</v>
-      </c>
-      <c r="H61" t="s">
-        <v>113</v>
-      </c>
-      <c r="I61" t="s">
-        <v>157</v>
-      </c>
       <c r="J61" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K61">
         <v>56160</v>
@@ -4620,10 +4615,10 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C62" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D62" t="s">
         <v>14</v>
@@ -4635,13 +4630,13 @@
         <v>7</v>
       </c>
       <c r="H62" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I62" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J62" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K62">
         <v>138444</v>
@@ -4661,10 +4656,10 @@
         <v>62</v>
       </c>
       <c r="B63" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="C63" t="s">
         <v>160</v>
-      </c>
-      <c r="C63" t="s">
-        <v>161</v>
       </c>
       <c r="D63" t="s">
         <v>5</v>
@@ -4673,7 +4668,7 @@
         <v>16</v>
       </c>
       <c r="F63" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G63" t="s">
         <v>7</v>
@@ -4682,10 +4677,10 @@
         <v>85</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="J63" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="K63">
         <v>31000</v>
@@ -4705,16 +4700,16 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C64" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D64" t="s">
         <v>14</v>
       </c>
       <c r="F64" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G64" t="s">
         <v>7</v>
@@ -4723,10 +4718,10 @@
         <v>85</v>
       </c>
       <c r="I64" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="J64" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="K64">
         <v>120000</v>
@@ -4746,10 +4741,10 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C65" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D65" t="s">
         <v>5</v>
@@ -4764,10 +4759,10 @@
         <v>85</v>
       </c>
       <c r="I65" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J65" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="K65">
         <v>25900</v>
@@ -4787,16 +4782,16 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
+        <v>167</v>
+      </c>
+      <c r="C66" t="s">
+        <v>160</v>
+      </c>
+      <c r="D66" t="s">
+        <v>5</v>
+      </c>
+      <c r="F66" t="s">
         <v>168</v>
-      </c>
-      <c r="C66" t="s">
-        <v>161</v>
-      </c>
-      <c r="D66" t="s">
-        <v>5</v>
-      </c>
-      <c r="F66" t="s">
-        <v>169</v>
       </c>
       <c r="G66" t="s">
         <v>7</v>
@@ -4805,10 +4800,10 @@
         <v>85</v>
       </c>
       <c r="I66" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J66" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="K66">
         <v>47986</v>
@@ -4828,10 +4823,10 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C67" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D67" t="s">
         <v>5</v>
@@ -4849,10 +4844,10 @@
         <v>85</v>
       </c>
       <c r="I67" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J67" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="K67">
         <v>194000</v>
@@ -4872,10 +4867,10 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C68" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D68" t="s">
         <v>5</v>
@@ -4893,10 +4888,10 @@
         <v>85</v>
       </c>
       <c r="I68" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J68" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="K68">
         <v>39724</v>
@@ -4916,10 +4911,10 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C69" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D69" t="s">
         <v>5</v>
@@ -4934,10 +4929,10 @@
         <v>85</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>461</v>
+        <v>504</v>
       </c>
       <c r="J69" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="K69">
         <v>48437.45</v>
@@ -4957,16 +4952,16 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
+        <v>175</v>
+      </c>
+      <c r="C70" t="s">
+        <v>160</v>
+      </c>
+      <c r="D70" t="s">
+        <v>5</v>
+      </c>
+      <c r="F70" t="s">
         <v>176</v>
-      </c>
-      <c r="C70" t="s">
-        <v>161</v>
-      </c>
-      <c r="D70" t="s">
-        <v>5</v>
-      </c>
-      <c r="F70" t="s">
-        <v>177</v>
       </c>
       <c r="G70" t="s">
         <v>7</v>
@@ -4975,10 +4970,10 @@
         <v>85</v>
       </c>
       <c r="I70" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J70" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="K70">
         <v>37910</v>
@@ -4998,16 +4993,16 @@
         <v>70</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C71" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D71" t="s">
         <v>5</v>
       </c>
       <c r="F71" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G71" t="s">
         <v>7</v>
@@ -5016,10 +5011,10 @@
         <v>85</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="J71" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="K71">
         <v>21220</v>
@@ -5039,10 +5034,10 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C72" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D72" t="s">
         <v>5</v>
@@ -5057,10 +5052,10 @@
         <v>85</v>
       </c>
       <c r="I72" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J72" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="K72">
         <v>77877</v>
@@ -5080,10 +5075,10 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C73" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D73" t="s">
         <v>5</v>
@@ -5101,10 +5096,10 @@
         <v>85</v>
       </c>
       <c r="I73" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J73" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="K73">
         <v>80311.53</v>
@@ -5124,10 +5119,10 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C74" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D74" t="s">
         <v>5</v>
@@ -5136,7 +5131,7 @@
         <v>23</v>
       </c>
       <c r="F74" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G74" t="s">
         <v>7</v>
@@ -5145,10 +5140,10 @@
         <v>85</v>
       </c>
       <c r="I74" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="J74" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="K74">
         <v>38000</v>
@@ -5168,16 +5163,16 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
+        <v>185</v>
+      </c>
+      <c r="C75" t="s">
+        <v>160</v>
+      </c>
+      <c r="D75" t="s">
+        <v>5</v>
+      </c>
+      <c r="F75" t="s">
         <v>186</v>
-      </c>
-      <c r="C75" t="s">
-        <v>161</v>
-      </c>
-      <c r="D75" t="s">
-        <v>5</v>
-      </c>
-      <c r="F75" t="s">
-        <v>187</v>
       </c>
       <c r="G75" t="s">
         <v>7</v>
@@ -5186,10 +5181,10 @@
         <v>85</v>
       </c>
       <c r="I75" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J75" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="K75">
         <v>37800</v>
@@ -5209,10 +5204,10 @@
         <v>75</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C76" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D76" t="s">
         <v>5</v>
@@ -5221,7 +5216,7 @@
         <v>16</v>
       </c>
       <c r="F76" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G76" t="s">
         <v>7</v>
@@ -5230,10 +5225,10 @@
         <v>85</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="J76" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="K76">
         <v>54581</v>
@@ -5253,10 +5248,10 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C77" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D77" t="s">
         <v>5</v>
@@ -5265,7 +5260,7 @@
         <v>16</v>
       </c>
       <c r="F77" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G77" t="s">
         <v>7</v>
@@ -5273,11 +5268,11 @@
       <c r="H77" t="s">
         <v>85</v>
       </c>
-      <c r="I77" t="s">
-        <v>86</v>
+      <c r="I77" s="6" t="s">
+        <v>502</v>
       </c>
       <c r="J77" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="K77">
         <v>25000</v>
@@ -5297,10 +5292,10 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C78" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D78" t="s">
         <v>5</v>
@@ -5309,7 +5304,7 @@
         <v>16</v>
       </c>
       <c r="F78" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G78" t="s">
         <v>7</v>
@@ -5318,10 +5313,10 @@
         <v>85</v>
       </c>
       <c r="I78" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="J78" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="K78">
         <v>52698</v>
@@ -5341,28 +5336,28 @@
         <v>78</v>
       </c>
       <c r="B79" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C79" t="s">
+        <v>160</v>
+      </c>
+      <c r="D79" t="s">
+        <v>5</v>
+      </c>
+      <c r="F79" t="s">
         <v>195</v>
       </c>
-      <c r="C79" t="s">
-        <v>161</v>
-      </c>
-      <c r="D79" t="s">
-        <v>5</v>
-      </c>
-      <c r="F79" t="s">
+      <c r="G79" t="s">
+        <v>7</v>
+      </c>
+      <c r="H79" t="s">
         <v>196</v>
       </c>
-      <c r="G79" t="s">
-        <v>7</v>
-      </c>
-      <c r="H79" t="s">
-        <v>197</v>
-      </c>
       <c r="I79" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="J79" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="K79">
         <v>38500</v>
@@ -5382,13 +5377,13 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
+        <v>197</v>
+      </c>
+      <c r="C80" t="s">
+        <v>160</v>
+      </c>
+      <c r="D80" t="s">
         <v>198</v>
-      </c>
-      <c r="C80" t="s">
-        <v>161</v>
-      </c>
-      <c r="D80" t="s">
-        <v>199</v>
       </c>
       <c r="G80" t="s">
         <v>7</v>
@@ -5397,10 +5392,10 @@
         <v>85</v>
       </c>
       <c r="I80" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="J80" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="K80">
         <v>27200</v>
@@ -5420,10 +5415,10 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C81" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D81" t="s">
         <v>5</v>
@@ -5432,7 +5427,7 @@
         <v>16</v>
       </c>
       <c r="F81" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G81" t="s">
         <v>7</v>
@@ -5441,10 +5436,10 @@
         <v>8</v>
       </c>
       <c r="I81" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="J81" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="K81">
         <v>60000</v>
@@ -5464,16 +5459,16 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
+        <v>203</v>
+      </c>
+      <c r="C82" t="s">
+        <v>137</v>
+      </c>
+      <c r="D82" t="s">
+        <v>5</v>
+      </c>
+      <c r="F82" t="s">
         <v>204</v>
-      </c>
-      <c r="C82" t="s">
-        <v>138</v>
-      </c>
-      <c r="D82" t="s">
-        <v>5</v>
-      </c>
-      <c r="F82" t="s">
-        <v>205</v>
       </c>
       <c r="G82" t="s">
         <v>7</v>
@@ -5482,10 +5477,10 @@
         <v>8</v>
       </c>
       <c r="I82" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="J82" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K82">
         <v>50000</v>
@@ -5505,10 +5500,10 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C83" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D83" t="s">
         <v>5</v>
@@ -5517,7 +5512,7 @@
         <v>23</v>
       </c>
       <c r="F83" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G83" t="s">
         <v>7</v>
@@ -5526,10 +5521,10 @@
         <v>8</v>
       </c>
       <c r="I83" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J83" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="K83">
         <v>131575</v>
@@ -5549,10 +5544,10 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C84" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D84" t="s">
         <v>5</v>
@@ -5567,10 +5562,10 @@
         <v>8</v>
       </c>
       <c r="I84" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="J84" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K84">
         <v>99500</v>
@@ -5590,16 +5585,16 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
+        <v>210</v>
+      </c>
+      <c r="C85" t="s">
+        <v>137</v>
+      </c>
+      <c r="D85" t="s">
+        <v>5</v>
+      </c>
+      <c r="F85" t="s">
         <v>211</v>
-      </c>
-      <c r="C85" t="s">
-        <v>138</v>
-      </c>
-      <c r="D85" t="s">
-        <v>5</v>
-      </c>
-      <c r="F85" t="s">
-        <v>212</v>
       </c>
       <c r="G85" t="s">
         <v>7</v>
@@ -5608,10 +5603,10 @@
         <v>8</v>
       </c>
       <c r="I85" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="J85" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="K85">
         <v>32000</v>
@@ -5631,10 +5626,10 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C86" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D86" t="s">
         <v>5</v>
@@ -5643,7 +5638,7 @@
         <v>23</v>
       </c>
       <c r="F86" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G86" t="s">
         <v>7</v>
@@ -5652,10 +5647,10 @@
         <v>8</v>
       </c>
       <c r="I86" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="J86" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="K86">
         <v>52170</v>
@@ -5675,16 +5670,16 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
+        <v>214</v>
+      </c>
+      <c r="C87" t="s">
+        <v>137</v>
+      </c>
+      <c r="D87" t="s">
+        <v>5</v>
+      </c>
+      <c r="F87" t="s">
         <v>215</v>
-      </c>
-      <c r="C87" t="s">
-        <v>138</v>
-      </c>
-      <c r="D87" t="s">
-        <v>5</v>
-      </c>
-      <c r="F87" t="s">
-        <v>216</v>
       </c>
       <c r="G87" t="s">
         <v>7</v>
@@ -5693,10 +5688,10 @@
         <v>8</v>
       </c>
       <c r="I87" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="J87" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="K87">
         <v>46000</v>
@@ -5716,10 +5711,10 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C88" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D88" t="s">
         <v>5</v>
@@ -5728,7 +5723,7 @@
         <v>23</v>
       </c>
       <c r="F88" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="G88" t="s">
         <v>7</v>
@@ -5737,10 +5732,10 @@
         <v>8</v>
       </c>
       <c r="I88" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="J88" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K88">
         <v>45013</v>
@@ -5760,10 +5755,10 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C89" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D89" t="s">
         <v>5</v>
@@ -5778,10 +5773,10 @@
         <v>8</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>478</v>
+        <v>503</v>
       </c>
       <c r="J89" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="K89">
         <v>48566</v>
@@ -5801,16 +5796,16 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
+        <v>220</v>
+      </c>
+      <c r="C90" t="s">
+        <v>137</v>
+      </c>
+      <c r="D90" t="s">
+        <v>5</v>
+      </c>
+      <c r="F90" t="s">
         <v>221</v>
-      </c>
-      <c r="C90" t="s">
-        <v>138</v>
-      </c>
-      <c r="D90" t="s">
-        <v>5</v>
-      </c>
-      <c r="F90" t="s">
-        <v>222</v>
       </c>
       <c r="G90" t="s">
         <v>7</v>
@@ -5819,10 +5814,10 @@
         <v>8</v>
       </c>
       <c r="I90" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="J90" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K90">
         <v>55618</v>
@@ -5842,16 +5837,16 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C91" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D91" t="s">
         <v>5</v>
       </c>
       <c r="F91" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G91" t="s">
         <v>7</v>
@@ -5860,10 +5855,10 @@
         <v>8</v>
       </c>
       <c r="I91" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="J91" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="K91">
         <v>47000</v>
@@ -5883,10 +5878,10 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C92" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D92" t="s">
         <v>5</v>
@@ -5895,7 +5890,7 @@
         <v>23</v>
       </c>
       <c r="F92" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G92" t="s">
         <v>7</v>
@@ -5904,10 +5899,10 @@
         <v>8</v>
       </c>
       <c r="I92" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="J92" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K92">
         <v>87763</v>
@@ -5927,10 +5922,10 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C93" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D93" t="s">
         <v>14</v>
@@ -5939,7 +5934,7 @@
         <v>16</v>
       </c>
       <c r="F93" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="G93" t="s">
         <v>7</v>
@@ -5948,10 +5943,10 @@
         <v>8</v>
       </c>
       <c r="I93" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="J93" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="K93">
         <v>100658</v>
@@ -5971,16 +5966,16 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
+        <v>230</v>
+      </c>
+      <c r="C94" t="s">
+        <v>137</v>
+      </c>
+      <c r="D94" t="s">
+        <v>5</v>
+      </c>
+      <c r="F94" t="s">
         <v>231</v>
-      </c>
-      <c r="C94" t="s">
-        <v>138</v>
-      </c>
-      <c r="D94" t="s">
-        <v>5</v>
-      </c>
-      <c r="F94" t="s">
-        <v>232</v>
       </c>
       <c r="G94" t="s">
         <v>7</v>
@@ -5989,10 +5984,10 @@
         <v>8</v>
       </c>
       <c r="I94" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="J94" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="K94">
         <v>67000</v>
@@ -6012,10 +6007,10 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C95" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D95" t="s">
         <v>5</v>
@@ -6033,10 +6028,10 @@
         <v>8</v>
       </c>
       <c r="I95" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J95" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="K95">
         <v>39431</v>
@@ -6056,10 +6051,10 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C96" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D96" t="s">
         <v>5</v>
@@ -6074,10 +6069,10 @@
         <v>8</v>
       </c>
       <c r="I96" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J96" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="K96">
         <v>34273</v>
@@ -6097,10 +6092,10 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C97" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D97" t="s">
         <v>5</v>
@@ -6112,10 +6107,10 @@
         <v>8</v>
       </c>
       <c r="I97" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="J97" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K97">
         <v>40000</v>
@@ -6135,10 +6130,10 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C98" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D98" t="s">
         <v>5</v>
@@ -6153,10 +6148,10 @@
         <v>8</v>
       </c>
       <c r="I98" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="J98" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="K98">
         <v>65000</v>
@@ -6176,10 +6171,10 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
+        <v>239</v>
+      </c>
+      <c r="C99" t="s">
         <v>240</v>
-      </c>
-      <c r="C99" t="s">
-        <v>241</v>
       </c>
       <c r="D99" t="s">
         <v>5</v>
@@ -6188,19 +6183,19 @@
         <v>23</v>
       </c>
       <c r="F99" t="s">
+        <v>241</v>
+      </c>
+      <c r="G99" t="s">
+        <v>7</v>
+      </c>
+      <c r="H99" t="s">
+        <v>196</v>
+      </c>
+      <c r="I99" t="s">
         <v>242</v>
       </c>
-      <c r="G99" t="s">
-        <v>7</v>
-      </c>
-      <c r="H99" t="s">
-        <v>197</v>
-      </c>
-      <c r="I99" t="s">
-        <v>243</v>
-      </c>
       <c r="J99" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="K99">
         <v>49000</v>
@@ -6220,10 +6215,10 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C100" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D100" t="s">
         <v>14</v>
@@ -6232,19 +6227,19 @@
         <v>23</v>
       </c>
       <c r="F100" t="s">
+        <v>244</v>
+      </c>
+      <c r="G100" t="s">
+        <v>7</v>
+      </c>
+      <c r="H100" t="s">
+        <v>196</v>
+      </c>
+      <c r="I100" t="s">
         <v>245</v>
       </c>
-      <c r="G100" t="s">
-        <v>7</v>
-      </c>
-      <c r="H100" t="s">
-        <v>197</v>
-      </c>
-      <c r="I100" t="s">
-        <v>246</v>
-      </c>
       <c r="J100" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="K100">
         <v>95000</v>
@@ -6264,10 +6259,10 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C101" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D101" t="s">
         <v>5</v>
@@ -6276,19 +6271,19 @@
         <v>23</v>
       </c>
       <c r="F101" t="s">
+        <v>247</v>
+      </c>
+      <c r="G101" t="s">
+        <v>7</v>
+      </c>
+      <c r="H101" t="s">
+        <v>196</v>
+      </c>
+      <c r="I101" t="s">
         <v>248</v>
       </c>
-      <c r="G101" t="s">
-        <v>7</v>
-      </c>
-      <c r="H101" t="s">
-        <v>197</v>
-      </c>
-      <c r="I101" t="s">
-        <v>249</v>
-      </c>
       <c r="J101" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="K101">
         <v>45000</v>
@@ -6308,10 +6303,10 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C102" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D102" t="s">
         <v>5</v>
@@ -6323,13 +6318,13 @@
         <v>7</v>
       </c>
       <c r="H102" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I102" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J102" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="K102">
         <v>124500</v>
@@ -6349,28 +6344,28 @@
         <v>102</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C103" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D103" t="s">
         <v>5</v>
       </c>
       <c r="F103" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G103" t="s">
         <v>7</v>
       </c>
       <c r="H103" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I103" s="2" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="J103" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="K103">
         <v>64000</v>
@@ -6390,10 +6385,10 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C104" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D104" t="s">
         <v>5</v>
@@ -6405,13 +6400,13 @@
         <v>7</v>
       </c>
       <c r="H104" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I104" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="J104" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="K104">
         <v>25000</v>
@@ -6431,10 +6426,10 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C105" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D105" t="s">
         <v>5</v>
@@ -6446,13 +6441,13 @@
         <v>7</v>
       </c>
       <c r="H105" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I105" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="J105" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="K105">
         <v>38498</v>
@@ -6472,25 +6467,25 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
+        <v>256</v>
+      </c>
+      <c r="C106" t="s">
+        <v>240</v>
+      </c>
+      <c r="D106" t="s">
+        <v>198</v>
+      </c>
+      <c r="G106" t="s">
+        <v>7</v>
+      </c>
+      <c r="H106" t="s">
+        <v>196</v>
+      </c>
+      <c r="I106" t="s">
         <v>257</v>
       </c>
-      <c r="C106" t="s">
-        <v>241</v>
-      </c>
-      <c r="D106" t="s">
-        <v>199</v>
-      </c>
-      <c r="G106" t="s">
-        <v>7</v>
-      </c>
-      <c r="H106" t="s">
-        <v>197</v>
-      </c>
-      <c r="I106" t="s">
-        <v>258</v>
-      </c>
       <c r="J106" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="K106">
         <v>166433</v>
@@ -6510,10 +6505,10 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C107" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D107" t="s">
         <v>14</v>
@@ -6522,19 +6517,19 @@
         <v>23</v>
       </c>
       <c r="F107" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G107" t="s">
         <v>7</v>
       </c>
       <c r="H107" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I107" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="J107" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="K107">
         <v>58000</v>
@@ -6554,28 +6549,28 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
+        <v>260</v>
+      </c>
+      <c r="C108" t="s">
+        <v>240</v>
+      </c>
+      <c r="D108" t="s">
+        <v>5</v>
+      </c>
+      <c r="F108" t="s">
         <v>261</v>
       </c>
-      <c r="C108" t="s">
-        <v>241</v>
-      </c>
-      <c r="D108" t="s">
-        <v>5</v>
-      </c>
-      <c r="F108" t="s">
+      <c r="G108" t="s">
+        <v>7</v>
+      </c>
+      <c r="H108" t="s">
+        <v>196</v>
+      </c>
+      <c r="I108" t="s">
         <v>262</v>
       </c>
-      <c r="G108" t="s">
-        <v>7</v>
-      </c>
-      <c r="H108" t="s">
-        <v>197</v>
-      </c>
-      <c r="I108" t="s">
-        <v>263</v>
-      </c>
       <c r="J108" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="K108">
         <v>51872</v>
@@ -6595,28 +6590,28 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
+        <v>263</v>
+      </c>
+      <c r="C109" t="s">
+        <v>240</v>
+      </c>
+      <c r="D109" t="s">
+        <v>5</v>
+      </c>
+      <c r="F109" t="s">
+        <v>191</v>
+      </c>
+      <c r="G109" t="s">
+        <v>7</v>
+      </c>
+      <c r="H109" t="s">
+        <v>196</v>
+      </c>
+      <c r="I109" t="s">
         <v>264</v>
       </c>
-      <c r="C109" t="s">
-        <v>241</v>
-      </c>
-      <c r="D109" t="s">
-        <v>5</v>
-      </c>
-      <c r="F109" t="s">
-        <v>192</v>
-      </c>
-      <c r="G109" t="s">
-        <v>7</v>
-      </c>
-      <c r="H109" t="s">
-        <v>197</v>
-      </c>
-      <c r="I109" t="s">
-        <v>265</v>
-      </c>
       <c r="J109" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="K109">
         <v>21632</v>
@@ -6636,28 +6631,28 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
+        <v>265</v>
+      </c>
+      <c r="C110" t="s">
+        <v>240</v>
+      </c>
+      <c r="D110" t="s">
+        <v>5</v>
+      </c>
+      <c r="F110" t="s">
+        <v>191</v>
+      </c>
+      <c r="G110" t="s">
+        <v>7</v>
+      </c>
+      <c r="H110" t="s">
+        <v>196</v>
+      </c>
+      <c r="I110" t="s">
         <v>266</v>
       </c>
-      <c r="C110" t="s">
-        <v>241</v>
-      </c>
-      <c r="D110" t="s">
-        <v>5</v>
-      </c>
-      <c r="F110" t="s">
-        <v>192</v>
-      </c>
-      <c r="G110" t="s">
-        <v>7</v>
-      </c>
-      <c r="H110" t="s">
-        <v>197</v>
-      </c>
-      <c r="I110" t="s">
-        <v>267</v>
-      </c>
       <c r="J110" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="K110">
         <v>69000</v>
@@ -6677,28 +6672,28 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
+        <v>267</v>
+      </c>
+      <c r="C111" t="s">
+        <v>240</v>
+      </c>
+      <c r="D111" t="s">
+        <v>5</v>
+      </c>
+      <c r="F111" t="s">
         <v>268</v>
       </c>
-      <c r="C111" t="s">
-        <v>241</v>
-      </c>
-      <c r="D111" t="s">
-        <v>5</v>
-      </c>
-      <c r="F111" t="s">
+      <c r="G111" t="s">
+        <v>7</v>
+      </c>
+      <c r="H111" t="s">
+        <v>196</v>
+      </c>
+      <c r="I111" t="s">
         <v>269</v>
       </c>
-      <c r="G111" t="s">
-        <v>7</v>
-      </c>
-      <c r="H111" t="s">
-        <v>197</v>
-      </c>
-      <c r="I111" t="s">
-        <v>270</v>
-      </c>
       <c r="J111" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="K111">
         <v>54000</v>
@@ -6718,10 +6713,10 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C112" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D112" t="s">
         <v>5</v>
@@ -6733,13 +6728,13 @@
         <v>7</v>
       </c>
       <c r="H112" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I112" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J112" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="K112">
         <v>57400</v>
@@ -6759,10 +6754,10 @@
         <v>112</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C113" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D113" t="s">
         <v>14</v>
@@ -6774,13 +6769,13 @@
         <v>7</v>
       </c>
       <c r="H113" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I113" s="2" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="J113" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="K113">
         <v>60000</v>
@@ -6795,7 +6790,7 @@
         <v>427</v>
       </c>
       <c r="P113" s="1" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -6803,10 +6798,10 @@
         <v>113</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C114" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D114" t="s">
         <v>14</v>
@@ -6818,13 +6813,13 @@
         <v>7</v>
       </c>
       <c r="H114" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I114" s="2" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="J114" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="K114">
         <v>60000</v>
@@ -6839,7 +6834,7 @@
         <v>11500</v>
       </c>
       <c r="P114" s="1" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -6847,10 +6842,10 @@
         <v>114</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C115" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D115" t="s">
         <v>5</v>
@@ -6859,13 +6854,13 @@
         <v>7</v>
       </c>
       <c r="H115" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I115" s="5" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="J115" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="K115">
         <v>33000</v>
@@ -6885,25 +6880,25 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
+        <v>275</v>
+      </c>
+      <c r="C116" t="s">
+        <v>240</v>
+      </c>
+      <c r="D116" t="s">
+        <v>198</v>
+      </c>
+      <c r="G116" t="s">
+        <v>7</v>
+      </c>
+      <c r="H116" t="s">
+        <v>196</v>
+      </c>
+      <c r="I116" t="s">
         <v>276</v>
       </c>
-      <c r="C116" t="s">
-        <v>241</v>
-      </c>
-      <c r="D116" t="s">
-        <v>199</v>
-      </c>
-      <c r="G116" t="s">
-        <v>7</v>
-      </c>
-      <c r="H116" t="s">
-        <v>197</v>
-      </c>
-      <c r="I116" t="s">
-        <v>277</v>
-      </c>
       <c r="J116" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="K116">
         <v>88786</v>
@@ -6923,25 +6918,25 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
+        <v>277</v>
+      </c>
+      <c r="C117" t="s">
+        <v>240</v>
+      </c>
+      <c r="D117" t="s">
+        <v>198</v>
+      </c>
+      <c r="G117" t="s">
+        <v>7</v>
+      </c>
+      <c r="H117" t="s">
+        <v>196</v>
+      </c>
+      <c r="I117" t="s">
         <v>278</v>
       </c>
-      <c r="C117" t="s">
-        <v>241</v>
-      </c>
-      <c r="D117" t="s">
-        <v>199</v>
-      </c>
-      <c r="G117" t="s">
-        <v>7</v>
-      </c>
-      <c r="H117" t="s">
-        <v>197</v>
-      </c>
-      <c r="I117" t="s">
-        <v>279</v>
-      </c>
       <c r="J117" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="K117">
         <v>134000</v>
@@ -6961,25 +6956,25 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
+        <v>279</v>
+      </c>
+      <c r="C118" t="s">
+        <v>240</v>
+      </c>
+      <c r="D118" t="s">
+        <v>198</v>
+      </c>
+      <c r="G118" t="s">
+        <v>7</v>
+      </c>
+      <c r="H118" t="s">
+        <v>196</v>
+      </c>
+      <c r="I118" t="s">
         <v>280</v>
       </c>
-      <c r="C118" t="s">
-        <v>241</v>
-      </c>
-      <c r="D118" t="s">
-        <v>199</v>
-      </c>
-      <c r="G118" t="s">
-        <v>7</v>
-      </c>
-      <c r="H118" t="s">
-        <v>197</v>
-      </c>
-      <c r="I118" t="s">
-        <v>281</v>
-      </c>
       <c r="J118" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="K118">
         <v>35000</v>
@@ -6999,25 +6994,25 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
+        <v>281</v>
+      </c>
+      <c r="C119" t="s">
+        <v>240</v>
+      </c>
+      <c r="D119" t="s">
+        <v>198</v>
+      </c>
+      <c r="G119" t="s">
+        <v>7</v>
+      </c>
+      <c r="H119" t="s">
+        <v>196</v>
+      </c>
+      <c r="I119" t="s">
         <v>282</v>
       </c>
-      <c r="C119" t="s">
-        <v>241</v>
-      </c>
-      <c r="D119" t="s">
-        <v>199</v>
-      </c>
-      <c r="G119" t="s">
-        <v>7</v>
-      </c>
-      <c r="H119" t="s">
-        <v>197</v>
-      </c>
-      <c r="I119" t="s">
-        <v>283</v>
-      </c>
       <c r="J119" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="K119">
         <v>18000</v>
@@ -7037,13 +7032,13 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C120" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D120" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E120" t="s">
         <v>16</v>
@@ -7052,13 +7047,13 @@
         <v>7</v>
       </c>
       <c r="H120" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I120" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="J120" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="K120">
         <v>105741</v>
@@ -7078,25 +7073,25 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
+        <v>285</v>
+      </c>
+      <c r="C121" t="s">
+        <v>240</v>
+      </c>
+      <c r="D121" t="s">
+        <v>198</v>
+      </c>
+      <c r="G121" t="s">
+        <v>7</v>
+      </c>
+      <c r="H121" t="s">
+        <v>196</v>
+      </c>
+      <c r="I121" t="s">
         <v>286</v>
       </c>
-      <c r="C121" t="s">
-        <v>241</v>
-      </c>
-      <c r="D121" t="s">
-        <v>199</v>
-      </c>
-      <c r="G121" t="s">
-        <v>7</v>
-      </c>
-      <c r="H121" t="s">
-        <v>197</v>
-      </c>
-      <c r="I121" t="s">
-        <v>287</v>
-      </c>
       <c r="J121" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="K121">
         <v>51000</v>
@@ -7116,10 +7111,10 @@
         <v>121</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C122" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D122" t="s">
         <v>5</v>
@@ -7131,13 +7126,13 @@
         <v>7</v>
       </c>
       <c r="H122" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I122" s="3" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="J122" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="K122">
         <v>130143</v>
@@ -7152,7 +7147,7 @@
         <v>36000</v>
       </c>
       <c r="P122" s="1" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7160,22 +7155,22 @@
         <v>122</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C123" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G123" t="s">
         <v>7</v>
       </c>
       <c r="H123" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I123" s="3" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="J123" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="K123">
         <v>121551.47</v>
@@ -7190,7 +7185,7 @@
         <v>97326.47</v>
       </c>
       <c r="P123" s="1" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7198,10 +7193,10 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
+        <v>288</v>
+      </c>
+      <c r="C124" t="s">
         <v>289</v>
-      </c>
-      <c r="C124" t="s">
-        <v>290</v>
       </c>
       <c r="D124" t="s">
         <v>5</v>
@@ -7210,7 +7205,7 @@
         <v>16</v>
       </c>
       <c r="F124" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G124" t="s">
         <v>7</v>
@@ -7219,10 +7214,10 @@
         <v>8</v>
       </c>
       <c r="I124" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J124" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="K124">
         <v>110000</v>
@@ -7242,10 +7237,10 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C125" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D125" t="s">
         <v>5</v>
@@ -7254,7 +7249,7 @@
         <v>23</v>
       </c>
       <c r="F125" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G125" t="s">
         <v>7</v>
@@ -7263,10 +7258,10 @@
         <v>8</v>
       </c>
       <c r="I125" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="J125" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="K125">
         <v>56000</v>
@@ -7286,16 +7281,16 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C126" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D126" t="s">
         <v>5</v>
       </c>
       <c r="F126" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G126" t="s">
         <v>7</v>
@@ -7304,10 +7299,10 @@
         <v>8</v>
       </c>
       <c r="I126" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="J126" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="K126">
         <v>89177</v>
@@ -7327,10 +7322,10 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C127" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D127" t="s">
         <v>5</v>
@@ -7339,7 +7334,7 @@
         <v>23</v>
       </c>
       <c r="F127" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="G127" t="s">
         <v>7</v>
@@ -7348,10 +7343,10 @@
         <v>8</v>
       </c>
       <c r="I127" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="J127" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="K127">
         <v>30000</v>
@@ -7371,10 +7366,10 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C128" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D128" t="s">
         <v>5</v>
@@ -7383,7 +7378,7 @@
         <v>16</v>
       </c>
       <c r="F128" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="G128" t="s">
         <v>7</v>
@@ -7392,10 +7387,10 @@
         <v>8</v>
       </c>
       <c r="I128" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="J128" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="K128">
         <v>54550</v>
@@ -7415,10 +7410,10 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C129" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D129" t="s">
         <v>5</v>
@@ -7427,7 +7422,7 @@
         <v>16</v>
       </c>
       <c r="F129" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="G129" t="s">
         <v>7</v>
@@ -7436,10 +7431,10 @@
         <v>8</v>
       </c>
       <c r="I129" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="J129" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="K129">
         <v>125000</v>
@@ -7459,10 +7454,10 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C130" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D130" t="s">
         <v>5</v>
@@ -7471,7 +7466,7 @@
         <v>16</v>
       </c>
       <c r="F130" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G130" t="s">
         <v>7</v>
@@ -7480,10 +7475,10 @@
         <v>8</v>
       </c>
       <c r="I130" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="J130" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="K130">
         <v>69100</v>
@@ -7503,10 +7498,10 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C131" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D131" t="s">
         <v>5</v>
@@ -7515,7 +7510,7 @@
         <v>23</v>
       </c>
       <c r="F131" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G131" t="s">
         <v>7</v>
@@ -7524,10 +7519,10 @@
         <v>8</v>
       </c>
       <c r="I131" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="J131" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="K131">
         <v>118290</v>
@@ -7547,16 +7542,16 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
+        <v>308</v>
+      </c>
+      <c r="C132" t="s">
+        <v>289</v>
+      </c>
+      <c r="D132" t="s">
+        <v>5</v>
+      </c>
+      <c r="F132" t="s">
         <v>309</v>
-      </c>
-      <c r="C132" t="s">
-        <v>290</v>
-      </c>
-      <c r="D132" t="s">
-        <v>5</v>
-      </c>
-      <c r="F132" t="s">
-        <v>310</v>
       </c>
       <c r="G132" t="s">
         <v>7</v>
@@ -7565,10 +7560,10 @@
         <v>8</v>
       </c>
       <c r="I132" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="J132" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="K132">
         <v>79900</v>
@@ -7588,16 +7583,16 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C133" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D133" t="s">
         <v>5</v>
       </c>
       <c r="F133" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G133" t="s">
         <v>7</v>
@@ -7606,10 +7601,10 @@
         <v>8</v>
       </c>
       <c r="I133" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J133" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="K133">
         <v>39742.379999999997</v>
@@ -7629,10 +7624,10 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C134" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D134" t="s">
         <v>5</v>
@@ -7650,10 +7645,10 @@
         <v>8</v>
       </c>
       <c r="I134" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="J134" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="K134">
         <v>48000</v>
@@ -7673,10 +7668,10 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C135" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D135" t="s">
         <v>14</v>
@@ -7691,10 +7686,10 @@
         <v>8</v>
       </c>
       <c r="I135" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="J135" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="K135">
         <v>74722</v>
@@ -7714,13 +7709,13 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C136" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D136" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G136" t="s">
         <v>7</v>
@@ -7729,10 +7724,10 @@
         <v>8</v>
       </c>
       <c r="I136" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="J136" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="K136">
         <v>55000</v>
@@ -7752,25 +7747,25 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
+        <v>319</v>
+      </c>
+      <c r="C137" t="s">
         <v>320</v>
       </c>
-      <c r="C137" t="s">
+      <c r="D137" t="s">
+        <v>5</v>
+      </c>
+      <c r="G137" t="s">
+        <v>7</v>
+      </c>
+      <c r="H137" t="s">
+        <v>112</v>
+      </c>
+      <c r="I137" t="s">
         <v>321</v>
       </c>
-      <c r="D137" t="s">
-        <v>5</v>
-      </c>
-      <c r="G137" t="s">
-        <v>7</v>
-      </c>
-      <c r="H137" t="s">
-        <v>113</v>
-      </c>
-      <c r="I137" t="s">
-        <v>322</v>
-      </c>
       <c r="J137" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K137">
         <v>128000</v>
@@ -7790,10 +7785,10 @@
         <v>137</v>
       </c>
       <c r="B138" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C138" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D138" t="s">
         <v>5</v>
@@ -7808,13 +7803,13 @@
         <v>7</v>
       </c>
       <c r="H138" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I138" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="J138" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K138">
         <v>122000</v>
@@ -7834,10 +7829,10 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C139" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D139" t="s">
         <v>5</v>
@@ -7849,13 +7844,13 @@
         <v>7</v>
       </c>
       <c r="H139" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I139" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J139" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K139">
         <v>22000</v>
@@ -7875,10 +7870,10 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C140" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D140" t="s">
         <v>5</v>
@@ -7890,13 +7885,13 @@
         <v>7</v>
       </c>
       <c r="H140" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I140" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="J140" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K140">
         <v>10000</v>
@@ -7916,10 +7911,10 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C141" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D141" t="s">
         <v>5</v>
@@ -7934,10 +7929,10 @@
         <v>8</v>
       </c>
       <c r="I141" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J141" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="K141">
         <v>64000</v>
@@ -7957,10 +7952,10 @@
         <v>141</v>
       </c>
       <c r="B142" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C142" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D142" t="s">
         <v>5</v>
@@ -7975,10 +7970,10 @@
         <v>8</v>
       </c>
       <c r="I142" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="J142" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="K142">
         <v>95628</v>
@@ -7998,16 +7993,16 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
+        <v>332</v>
+      </c>
+      <c r="C143" t="s">
+        <v>320</v>
+      </c>
+      <c r="D143" t="s">
+        <v>5</v>
+      </c>
+      <c r="F143" t="s">
         <v>333</v>
-      </c>
-      <c r="C143" t="s">
-        <v>321</v>
-      </c>
-      <c r="D143" t="s">
-        <v>5</v>
-      </c>
-      <c r="F143" t="s">
-        <v>334</v>
       </c>
       <c r="G143" t="s">
         <v>7</v>
@@ -8016,10 +8011,10 @@
         <v>8</v>
       </c>
       <c r="I143" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="J143" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="K143">
         <v>39562</v>
@@ -8039,10 +8034,10 @@
         <v>143</v>
       </c>
       <c r="B144" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C144" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D144" t="s">
         <v>5</v>
@@ -8051,7 +8046,7 @@
         <v>16</v>
       </c>
       <c r="F144" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="G144" t="s">
         <v>7</v>
@@ -8060,10 +8055,10 @@
         <v>8</v>
       </c>
       <c r="I144" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J144" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K144">
         <v>105000</v>
@@ -8083,10 +8078,10 @@
         <v>144</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C145" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D145" t="s">
         <v>5</v>
@@ -8095,7 +8090,7 @@
         <v>23</v>
       </c>
       <c r="F145" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G145" t="s">
         <v>7</v>
@@ -8104,10 +8099,10 @@
         <v>8</v>
       </c>
       <c r="I145" s="2" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="J145" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K145">
         <v>60000</v>
@@ -8127,16 +8122,16 @@
         <v>145</v>
       </c>
       <c r="B146" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C146" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D146" t="s">
         <v>5</v>
       </c>
       <c r="F146" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G146" t="s">
         <v>7</v>
@@ -8145,10 +8140,10 @@
         <v>8</v>
       </c>
       <c r="I146" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="J146" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="K146">
         <v>39964</v>
@@ -8168,10 +8163,10 @@
         <v>146</v>
       </c>
       <c r="B147" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C147" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D147" t="s">
         <v>5</v>
@@ -8186,10 +8181,10 @@
         <v>8</v>
       </c>
       <c r="I147" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="J147" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K147">
         <v>94000</v>
@@ -8209,10 +8204,10 @@
         <v>147</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="C148" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D148" t="s">
         <v>5</v>
@@ -8221,7 +8216,7 @@
         <v>23</v>
       </c>
       <c r="F148" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G148" t="s">
         <v>7</v>
@@ -8230,10 +8225,10 @@
         <v>8</v>
       </c>
       <c r="I148" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="J148" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K148">
         <v>75000</v>
@@ -8253,16 +8248,16 @@
         <v>148</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C149" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D149" t="s">
         <v>5</v>
       </c>
       <c r="F149" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G149" t="s">
         <v>7</v>
@@ -8271,10 +8266,10 @@
         <v>8</v>
       </c>
       <c r="I149" s="2" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="J149" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K149">
         <v>48767</v>
@@ -8294,10 +8289,10 @@
         <v>149</v>
       </c>
       <c r="B150" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C150" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D150" t="s">
         <v>5</v>
@@ -8315,10 +8310,10 @@
         <v>8</v>
       </c>
       <c r="I150" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="J150" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K150">
         <v>63824</v>
@@ -8338,10 +8333,10 @@
         <v>150</v>
       </c>
       <c r="B151" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C151" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D151" t="s">
         <v>14</v>
@@ -8350,7 +8345,7 @@
         <v>23</v>
       </c>
       <c r="F151" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G151" t="s">
         <v>7</v>
@@ -8359,10 +8354,10 @@
         <v>8</v>
       </c>
       <c r="I151" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="J151" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K151">
         <v>117000</v>
@@ -8382,10 +8377,10 @@
         <v>151</v>
       </c>
       <c r="B152" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C152" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D152" t="s">
         <v>5</v>
@@ -8397,10 +8392,10 @@
         <v>8</v>
       </c>
       <c r="I152" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="J152" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K152">
         <v>41000</v>
@@ -8420,10 +8415,10 @@
         <v>152</v>
       </c>
       <c r="B153" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C153" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D153" t="s">
         <v>5</v>
@@ -8435,10 +8430,10 @@
         <v>8</v>
       </c>
       <c r="I153" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="J153" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="K153">
         <v>96446</v>
@@ -8458,10 +8453,10 @@
         <v>153</v>
       </c>
       <c r="B154" t="s">
+        <v>351</v>
+      </c>
+      <c r="C154" t="s">
         <v>352</v>
-      </c>
-      <c r="C154" t="s">
-        <v>353</v>
       </c>
       <c r="D154" t="s">
         <v>5</v>
@@ -8470,19 +8465,19 @@
         <v>16</v>
       </c>
       <c r="F154" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G154" t="s">
         <v>7</v>
       </c>
       <c r="H154" t="s">
+        <v>353</v>
+      </c>
+      <c r="I154" t="s">
         <v>354</v>
       </c>
-      <c r="I154" t="s">
-        <v>355</v>
-      </c>
       <c r="J154" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K154">
         <v>76600</v>
@@ -8502,28 +8497,28 @@
         <v>154</v>
       </c>
       <c r="B155" t="s">
+        <v>355</v>
+      </c>
+      <c r="C155" t="s">
+        <v>352</v>
+      </c>
+      <c r="D155" t="s">
+        <v>5</v>
+      </c>
+      <c r="F155" t="s">
+        <v>152</v>
+      </c>
+      <c r="G155" t="s">
+        <v>7</v>
+      </c>
+      <c r="H155" t="s">
+        <v>353</v>
+      </c>
+      <c r="I155" t="s">
         <v>356</v>
       </c>
-      <c r="C155" t="s">
-        <v>353</v>
-      </c>
-      <c r="D155" t="s">
-        <v>5</v>
-      </c>
-      <c r="F155" t="s">
-        <v>153</v>
-      </c>
-      <c r="G155" t="s">
-        <v>7</v>
-      </c>
-      <c r="H155" t="s">
-        <v>354</v>
-      </c>
-      <c r="I155" t="s">
-        <v>357</v>
-      </c>
       <c r="J155" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="K155">
         <v>125569</v>
@@ -8543,28 +8538,28 @@
         <v>155</v>
       </c>
       <c r="B156" t="s">
+        <v>357</v>
+      </c>
+      <c r="C156" t="s">
+        <v>352</v>
+      </c>
+      <c r="D156" t="s">
+        <v>5</v>
+      </c>
+      <c r="F156" t="s">
         <v>358</v>
       </c>
-      <c r="C156" t="s">
+      <c r="G156" t="s">
+        <v>7</v>
+      </c>
+      <c r="H156" t="s">
         <v>353</v>
       </c>
-      <c r="D156" t="s">
-        <v>5</v>
-      </c>
-      <c r="F156" t="s">
+      <c r="I156" t="s">
         <v>359</v>
       </c>
-      <c r="G156" t="s">
-        <v>7</v>
-      </c>
-      <c r="H156" t="s">
-        <v>354</v>
-      </c>
-      <c r="I156" t="s">
-        <v>360</v>
-      </c>
       <c r="J156" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K156">
         <v>51234</v>
@@ -8584,10 +8579,10 @@
         <v>156</v>
       </c>
       <c r="B157" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C157" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D157" t="s">
         <v>5</v>
@@ -8596,19 +8591,19 @@
         <v>16</v>
       </c>
       <c r="F157" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G157" t="s">
         <v>7</v>
       </c>
       <c r="H157" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="I157" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="J157" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="K157">
         <v>123780</v>
@@ -8628,28 +8623,28 @@
         <v>157</v>
       </c>
       <c r="B158" t="s">
+        <v>362</v>
+      </c>
+      <c r="C158" t="s">
+        <v>352</v>
+      </c>
+      <c r="D158" t="s">
+        <v>5</v>
+      </c>
+      <c r="F158" t="s">
         <v>363</v>
       </c>
-      <c r="C158" t="s">
+      <c r="G158" t="s">
+        <v>7</v>
+      </c>
+      <c r="H158" t="s">
         <v>353</v>
       </c>
-      <c r="D158" t="s">
-        <v>5</v>
-      </c>
-      <c r="F158" t="s">
+      <c r="I158" t="s">
         <v>364</v>
       </c>
-      <c r="G158" t="s">
-        <v>7</v>
-      </c>
-      <c r="H158" t="s">
-        <v>354</v>
-      </c>
-      <c r="I158" t="s">
-        <v>365</v>
-      </c>
       <c r="J158" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K158">
         <v>46000</v>
@@ -8669,25 +8664,25 @@
         <v>158</v>
       </c>
       <c r="B159" t="s">
+        <v>365</v>
+      </c>
+      <c r="C159" t="s">
+        <v>352</v>
+      </c>
+      <c r="D159" t="s">
+        <v>5</v>
+      </c>
+      <c r="G159" t="s">
+        <v>7</v>
+      </c>
+      <c r="H159" t="s">
+        <v>353</v>
+      </c>
+      <c r="I159" t="s">
         <v>366</v>
       </c>
-      <c r="C159" t="s">
-        <v>353</v>
-      </c>
-      <c r="D159" t="s">
-        <v>5</v>
-      </c>
-      <c r="G159" t="s">
-        <v>7</v>
-      </c>
-      <c r="H159" t="s">
-        <v>354</v>
-      </c>
-      <c r="I159" t="s">
-        <v>367</v>
-      </c>
       <c r="J159" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K159">
         <v>35600</v>
@@ -8707,10 +8702,10 @@
         <v>159</v>
       </c>
       <c r="B160" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C160" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D160" t="s">
         <v>5</v>
@@ -8722,13 +8717,13 @@
         <v>7</v>
       </c>
       <c r="H160" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="I160" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="J160" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="K160">
         <v>199950</v>
@@ -8748,10 +8743,10 @@
         <v>160</v>
       </c>
       <c r="B161" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C161" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D161" t="s">
         <v>5</v>
@@ -8763,13 +8758,13 @@
         <v>7</v>
       </c>
       <c r="H161" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="I161" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="J161" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="K161">
         <v>108000</v>
@@ -8789,10 +8784,10 @@
         <v>161</v>
       </c>
       <c r="B162" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C162" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D162" t="s">
         <v>5</v>
@@ -8804,13 +8799,13 @@
         <v>7</v>
       </c>
       <c r="H162" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="I162" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="J162" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="K162">
         <v>142808</v>
@@ -8830,10 +8825,10 @@
         <v>162</v>
       </c>
       <c r="B163" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C163" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D163" t="s">
         <v>5</v>
@@ -8845,13 +8840,13 @@
         <v>7</v>
       </c>
       <c r="H163" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="I163" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="J163" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="K163">
         <v>80463</v>
@@ -8871,10 +8866,10 @@
         <v>163</v>
       </c>
       <c r="B164" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C164" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D164" t="s">
         <v>5</v>
@@ -8886,13 +8881,13 @@
         <v>7</v>
       </c>
       <c r="H164" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="I164" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J164" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K164">
         <v>83000</v>
@@ -8912,25 +8907,25 @@
         <v>164</v>
       </c>
       <c r="B165" t="s">
+        <v>377</v>
+      </c>
+      <c r="C165" t="s">
+        <v>352</v>
+      </c>
+      <c r="D165" t="s">
+        <v>5</v>
+      </c>
+      <c r="G165" t="s">
+        <v>7</v>
+      </c>
+      <c r="H165" t="s">
+        <v>353</v>
+      </c>
+      <c r="I165" t="s">
         <v>378</v>
       </c>
-      <c r="C165" t="s">
-        <v>353</v>
-      </c>
-      <c r="D165" t="s">
-        <v>5</v>
-      </c>
-      <c r="G165" t="s">
-        <v>7</v>
-      </c>
-      <c r="H165" t="s">
-        <v>354</v>
-      </c>
-      <c r="I165" t="s">
-        <v>379</v>
-      </c>
       <c r="J165" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K165">
         <v>129000</v>
@@ -8950,28 +8945,28 @@
         <v>165</v>
       </c>
       <c r="B166" t="s">
+        <v>379</v>
+      </c>
+      <c r="C166" t="s">
         <v>380</v>
       </c>
-      <c r="C166" t="s">
+      <c r="D166" t="s">
+        <v>5</v>
+      </c>
+      <c r="F166" t="s">
+        <v>215</v>
+      </c>
+      <c r="G166" t="s">
+        <v>7</v>
+      </c>
+      <c r="H166" t="s">
+        <v>112</v>
+      </c>
+      <c r="I166" t="s">
         <v>381</v>
       </c>
-      <c r="D166" t="s">
-        <v>5</v>
-      </c>
-      <c r="F166" t="s">
-        <v>216</v>
-      </c>
-      <c r="G166" t="s">
-        <v>7</v>
-      </c>
-      <c r="H166" t="s">
-        <v>113</v>
-      </c>
-      <c r="I166" t="s">
-        <v>382</v>
-      </c>
       <c r="J166" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K166">
         <v>62209</v>
@@ -8991,16 +8986,16 @@
         <v>166</v>
       </c>
       <c r="B167" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C167" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D167" t="s">
         <v>5</v>
       </c>
       <c r="F167" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="G167" t="s">
         <v>7</v>
@@ -9009,10 +9004,10 @@
         <v>8</v>
       </c>
       <c r="I167" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="J167" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="K167">
         <v>36117</v>
@@ -9032,10 +9027,10 @@
         <v>167</v>
       </c>
       <c r="B168" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C168" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D168" t="s">
         <v>5</v>
@@ -9044,7 +9039,7 @@
         <v>23</v>
       </c>
       <c r="F168" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G168" t="s">
         <v>7</v>
@@ -9053,10 +9048,10 @@
         <v>85</v>
       </c>
       <c r="I168" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="J168" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="K168">
         <v>49900</v>
@@ -9076,10 +9071,10 @@
         <v>168</v>
       </c>
       <c r="B169" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C169" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D169" t="s">
         <v>5</v>
@@ -9088,7 +9083,7 @@
         <v>16</v>
       </c>
       <c r="F169" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G169" t="s">
         <v>7</v>
@@ -9097,10 +9092,10 @@
         <v>85</v>
       </c>
       <c r="I169" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="J169" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="K169">
         <v>39000</v>
@@ -9120,28 +9115,28 @@
         <v>169</v>
       </c>
       <c r="B170" t="s">
+        <v>389</v>
+      </c>
+      <c r="C170" t="s">
+        <v>380</v>
+      </c>
+      <c r="D170" t="s">
+        <v>5</v>
+      </c>
+      <c r="F170" t="s">
+        <v>358</v>
+      </c>
+      <c r="G170" t="s">
+        <v>7</v>
+      </c>
+      <c r="H170" t="s">
+        <v>196</v>
+      </c>
+      <c r="I170" t="s">
         <v>390</v>
       </c>
-      <c r="C170" t="s">
-        <v>381</v>
-      </c>
-      <c r="D170" t="s">
-        <v>5</v>
-      </c>
-      <c r="F170" t="s">
-        <v>359</v>
-      </c>
-      <c r="G170" t="s">
-        <v>7</v>
-      </c>
-      <c r="H170" t="s">
-        <v>197</v>
-      </c>
-      <c r="I170" t="s">
-        <v>391</v>
-      </c>
       <c r="J170" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="K170">
         <v>49000</v>
@@ -9161,13 +9156,13 @@
         <v>170</v>
       </c>
       <c r="B171" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C171" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D171" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G171" t="s">
         <v>7</v>
@@ -9176,10 +9171,10 @@
         <v>8</v>
       </c>
       <c r="I171" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="J171" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="K171">
         <v>59400</v>
@@ -9199,10 +9194,10 @@
         <v>171</v>
       </c>
       <c r="B172" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C172" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D172" t="s">
         <v>5</v>
@@ -9217,10 +9212,10 @@
         <v>8</v>
       </c>
       <c r="I172" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="J172" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="K172">
         <v>65000</v>
@@ -9240,31 +9235,31 @@
         <v>172</v>
       </c>
       <c r="B173" t="s">
+        <v>395</v>
+      </c>
+      <c r="C173" t="s">
+        <v>380</v>
+      </c>
+      <c r="D173" t="s">
+        <v>5</v>
+      </c>
+      <c r="E173" t="s">
+        <v>397</v>
+      </c>
+      <c r="F173" t="s">
         <v>396</v>
       </c>
-      <c r="C173" t="s">
-        <v>381</v>
-      </c>
-      <c r="D173" t="s">
-        <v>5</v>
-      </c>
-      <c r="E173" t="s">
+      <c r="G173" t="s">
+        <v>7</v>
+      </c>
+      <c r="H173" t="s">
         <v>398</v>
       </c>
-      <c r="F173" t="s">
-        <v>397</v>
-      </c>
-      <c r="G173" t="s">
-        <v>7</v>
-      </c>
-      <c r="H173" t="s">
+      <c r="I173" t="s">
         <v>399</v>
       </c>
-      <c r="I173" t="s">
-        <v>400</v>
-      </c>
       <c r="J173" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K173">
         <v>47000</v>
@@ -9284,28 +9279,28 @@
         <v>173</v>
       </c>
       <c r="B174" t="s">
+        <v>400</v>
+      </c>
+      <c r="C174" t="s">
+        <v>380</v>
+      </c>
+      <c r="D174" t="s">
+        <v>5</v>
+      </c>
+      <c r="E174" t="s">
+        <v>397</v>
+      </c>
+      <c r="G174" t="s">
+        <v>7</v>
+      </c>
+      <c r="H174" t="s">
+        <v>398</v>
+      </c>
+      <c r="I174" t="s">
         <v>401</v>
       </c>
-      <c r="C174" t="s">
-        <v>381</v>
-      </c>
-      <c r="D174" t="s">
-        <v>5</v>
-      </c>
-      <c r="E174" t="s">
-        <v>398</v>
-      </c>
-      <c r="G174" t="s">
-        <v>7</v>
-      </c>
-      <c r="H174" t="s">
-        <v>399</v>
-      </c>
-      <c r="I174" t="s">
-        <v>402</v>
-      </c>
       <c r="J174" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K174">
         <v>29000</v>
@@ -9325,10 +9320,10 @@
         <v>174</v>
       </c>
       <c r="B175" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C175" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D175" t="s">
         <v>5</v>
@@ -9337,7 +9332,7 @@
         <v>23</v>
       </c>
       <c r="F175" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G175" t="s">
         <v>7</v>
@@ -9346,10 +9341,10 @@
         <v>85</v>
       </c>
       <c r="I175" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="J175" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K175">
         <v>132239</v>
@@ -9369,10 +9364,10 @@
         <v>175</v>
       </c>
       <c r="B176" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C176" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D176" t="s">
         <v>5</v>
@@ -9384,13 +9379,13 @@
         <v>7</v>
       </c>
       <c r="H176" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="I176" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="J176" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K176">
         <v>35016</v>
@@ -9410,10 +9405,10 @@
         <v>176</v>
       </c>
       <c r="B177" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C177" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D177" t="s">
         <v>5</v>
@@ -9425,10 +9420,10 @@
         <v>85</v>
       </c>
       <c r="I177" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="J177" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K177">
         <v>60000</v>
@@ -9448,28 +9443,28 @@
         <v>177</v>
       </c>
       <c r="B178" t="s">
+        <v>408</v>
+      </c>
+      <c r="C178" t="s">
+        <v>380</v>
+      </c>
+      <c r="D178" t="s">
+        <v>5</v>
+      </c>
+      <c r="F178" t="s">
         <v>409</v>
       </c>
-      <c r="C178" t="s">
-        <v>381</v>
-      </c>
-      <c r="D178" t="s">
-        <v>5</v>
-      </c>
-      <c r="F178" t="s">
+      <c r="G178" t="s">
+        <v>7</v>
+      </c>
+      <c r="H178" t="s">
+        <v>353</v>
+      </c>
+      <c r="I178" t="s">
         <v>410</v>
       </c>
-      <c r="G178" t="s">
-        <v>7</v>
-      </c>
-      <c r="H178" t="s">
-        <v>354</v>
-      </c>
-      <c r="I178" t="s">
-        <v>411</v>
-      </c>
       <c r="J178" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="K178">
         <v>90244</v>
@@ -9489,25 +9484,25 @@
         <v>178</v>
       </c>
       <c r="B179" t="s">
+        <v>411</v>
+      </c>
+      <c r="C179" t="s">
+        <v>380</v>
+      </c>
+      <c r="D179" t="s">
+        <v>5</v>
+      </c>
+      <c r="G179" t="s">
+        <v>7</v>
+      </c>
+      <c r="H179" t="s">
+        <v>353</v>
+      </c>
+      <c r="I179" t="s">
         <v>412</v>
       </c>
-      <c r="C179" t="s">
-        <v>381</v>
-      </c>
-      <c r="D179" t="s">
-        <v>5</v>
-      </c>
-      <c r="G179" t="s">
-        <v>7</v>
-      </c>
-      <c r="H179" t="s">
-        <v>354</v>
-      </c>
-      <c r="I179" t="s">
-        <v>413</v>
-      </c>
       <c r="J179" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K179">
         <v>38700</v>
@@ -9527,10 +9522,10 @@
         <v>179</v>
       </c>
       <c r="B180" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C180" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D180" t="s">
         <v>5</v>
@@ -9539,13 +9534,13 @@
         <v>7</v>
       </c>
       <c r="H180" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="I180" s="1" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="J180" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K180">
         <v>62414</v>
@@ -9565,25 +9560,25 @@
         <v>180</v>
       </c>
       <c r="B181" t="s">
+        <v>414</v>
+      </c>
+      <c r="C181" t="s">
+        <v>380</v>
+      </c>
+      <c r="D181" t="s">
+        <v>5</v>
+      </c>
+      <c r="G181" t="s">
+        <v>7</v>
+      </c>
+      <c r="H181" t="s">
+        <v>398</v>
+      </c>
+      <c r="I181" t="s">
         <v>415</v>
       </c>
-      <c r="C181" t="s">
-        <v>381</v>
-      </c>
-      <c r="D181" t="s">
-        <v>5</v>
-      </c>
-      <c r="G181" t="s">
-        <v>7</v>
-      </c>
-      <c r="H181" t="s">
-        <v>399</v>
-      </c>
-      <c r="I181" t="s">
-        <v>416</v>
-      </c>
       <c r="J181" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K181">
         <v>51000</v>
@@ -9603,10 +9598,10 @@
         <v>181</v>
       </c>
       <c r="B182" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C182" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D182" t="s">
         <v>5</v>
@@ -9621,10 +9616,10 @@
         <v>85</v>
       </c>
       <c r="I182" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="J182" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K182">
         <v>53115</v>
@@ -9644,25 +9639,25 @@
         <v>182</v>
       </c>
       <c r="B183" t="s">
+        <v>418</v>
+      </c>
+      <c r="C183" t="s">
+        <v>380</v>
+      </c>
+      <c r="D183" t="s">
+        <v>5</v>
+      </c>
+      <c r="G183" t="s">
+        <v>7</v>
+      </c>
+      <c r="H183" t="s">
+        <v>353</v>
+      </c>
+      <c r="I183" t="s">
         <v>419</v>
       </c>
-      <c r="C183" t="s">
-        <v>381</v>
-      </c>
-      <c r="D183" t="s">
-        <v>5</v>
-      </c>
-      <c r="G183" t="s">
-        <v>7</v>
-      </c>
-      <c r="H183" t="s">
-        <v>354</v>
-      </c>
-      <c r="I183" t="s">
-        <v>420</v>
-      </c>
       <c r="J183" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K183">
         <v>120000</v>
@@ -9682,10 +9677,10 @@
         <v>183</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C184" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D184" t="s">
         <v>5</v>
@@ -9700,10 +9695,10 @@
         <v>85</v>
       </c>
       <c r="I184" s="3" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="J184" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K184">
         <v>66477</v>
@@ -9723,10 +9718,10 @@
         <v>184</v>
       </c>
       <c r="B185" t="s">
+        <v>421</v>
+      </c>
+      <c r="C185" t="s">
         <v>422</v>
-      </c>
-      <c r="C185" t="s">
-        <v>423</v>
       </c>
       <c r="D185" t="s">
         <v>5</v>
@@ -9738,10 +9733,10 @@
         <v>7</v>
       </c>
       <c r="H185" t="s">
+        <v>423</v>
+      </c>
+      <c r="I185" t="s">
         <v>424</v>
-      </c>
-      <c r="I185" t="s">
-        <v>425</v>
       </c>
       <c r="K185">
         <v>59300</v>
@@ -9761,22 +9756,22 @@
         <v>185</v>
       </c>
       <c r="B186" t="s">
+        <v>425</v>
+      </c>
+      <c r="C186" t="s">
+        <v>422</v>
+      </c>
+      <c r="D186" t="s">
+        <v>5</v>
+      </c>
+      <c r="G186" t="s">
+        <v>7</v>
+      </c>
+      <c r="H186" t="s">
+        <v>423</v>
+      </c>
+      <c r="I186" t="s">
         <v>426</v>
-      </c>
-      <c r="C186" t="s">
-        <v>423</v>
-      </c>
-      <c r="D186" t="s">
-        <v>5</v>
-      </c>
-      <c r="G186" t="s">
-        <v>7</v>
-      </c>
-      <c r="H186" t="s">
-        <v>424</v>
-      </c>
-      <c r="I186" t="s">
-        <v>427</v>
       </c>
       <c r="K186">
         <v>44000</v>
@@ -9796,22 +9791,22 @@
         <v>186</v>
       </c>
       <c r="B187" t="s">
+        <v>427</v>
+      </c>
+      <c r="C187" t="s">
+        <v>422</v>
+      </c>
+      <c r="D187" t="s">
+        <v>5</v>
+      </c>
+      <c r="G187" t="s">
+        <v>7</v>
+      </c>
+      <c r="H187" t="s">
+        <v>423</v>
+      </c>
+      <c r="I187" t="s">
         <v>428</v>
-      </c>
-      <c r="C187" t="s">
-        <v>423</v>
-      </c>
-      <c r="D187" t="s">
-        <v>5</v>
-      </c>
-      <c r="G187" t="s">
-        <v>7</v>
-      </c>
-      <c r="H187" t="s">
-        <v>424</v>
-      </c>
-      <c r="I187" t="s">
-        <v>429</v>
       </c>
       <c r="K187">
         <v>26528</v>
@@ -9831,10 +9826,10 @@
         <v>187</v>
       </c>
       <c r="B188" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C188" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D188" t="s">
         <v>5</v>
@@ -9846,10 +9841,10 @@
         <v>7</v>
       </c>
       <c r="H188" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="I188" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="K188">
         <v>95684</v>
@@ -9869,10 +9864,10 @@
         <v>188</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="C189" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D189" t="s">
         <v>5</v>
@@ -9884,7 +9879,7 @@
         <v>85</v>
       </c>
       <c r="I189" s="4" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="K189">
         <v>26737</v>
@@ -9904,10 +9899,10 @@
         <v>189</v>
       </c>
       <c r="B190" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C190" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D190" t="s">
         <v>5</v>
@@ -9919,10 +9914,10 @@
         <v>7</v>
       </c>
       <c r="H190" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="I190" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="K190">
         <v>60000</v>
@@ -9942,22 +9937,22 @@
         <v>190</v>
       </c>
       <c r="B191" t="s">
+        <v>433</v>
+      </c>
+      <c r="C191" t="s">
+        <v>422</v>
+      </c>
+      <c r="D191" t="s">
+        <v>5</v>
+      </c>
+      <c r="G191" t="s">
+        <v>7</v>
+      </c>
+      <c r="H191" t="s">
+        <v>423</v>
+      </c>
+      <c r="I191" t="s">
         <v>434</v>
-      </c>
-      <c r="C191" t="s">
-        <v>423</v>
-      </c>
-      <c r="D191" t="s">
-        <v>5</v>
-      </c>
-      <c r="G191" t="s">
-        <v>7</v>
-      </c>
-      <c r="H191" t="s">
-        <v>424</v>
-      </c>
-      <c r="I191" t="s">
-        <v>435</v>
       </c>
       <c r="K191">
         <v>34895</v>
@@ -9974,29 +9969,29 @@
     </row>
     <row r="192" spans="1:14">
       <c r="B192" s="1" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="C192" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="G192" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="H192" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="I192" s="1" t="s">
         <v>481</v>
-      </c>
-      <c r="G192" s="1" t="s">
-        <v>482</v>
-      </c>
-      <c r="H192" s="1" t="s">
-        <v>456</v>
-      </c>
-      <c r="I192" s="1" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="193" spans="2:2">
       <c r="B193" s="1" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
     </row>
   </sheetData>
@@ -10268,15 +10263,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e40a7e4-94f1-4b05-8c7e-c5111c724f9a">
@@ -10287,16 +10273,51 @@
 </p:properties>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5BF42E8-7CD6-44A5-B028-608DFC162276}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5BF42E8-7CD6-44A5-B028-608DFC162276}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="f655991e-a262-4cc2-969f-4b8d0db6a5de"/>
+    <ds:schemaRef ds:uri="8e40a7e4-94f1-4b05-8c7e-c5111c724f9a"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C7A7DD6C-B285-4C23-BA8C-7CCC252AB8AB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF6E6A69-6D48-49BB-9E8E-5B96C2738B7E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="8e40a7e4-94f1-4b05-8c7e-c5111c724f9a"/>
+    <ds:schemaRef ds:uri="f655991e-a262-4cc2-969f-4b8d0db6a5de"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF6E6A69-6D48-49BB-9E8E-5B96C2738B7E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C7A7DD6C-B285-4C23-BA8C-7CCC252AB8AB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://colliers.sharepoint.com/teams/Asia_Research/China/Shared Documents/North/Beijing/工作中报告_持续更新中/实习生文档/Ron/0303系统数据/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="8_{B2126FFC-172F-4569-88A8-F2305D0C9028}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF6D8DFD-B086-4386-86FD-F5F91FA42B30}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="8_{B2126FFC-172F-4569-88A8-F2305D0C9028}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{05EF41CE-C09E-4B35-B915-B4C7D07FB09D}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -641,9 +641,6 @@
     <t>1999 Q1</t>
   </si>
   <si>
-    <t>116.458974,39.932654</t>
-  </si>
-  <si>
     <t>现代汽车大厦</t>
   </si>
   <si>
@@ -1244,9 +1241,6 @@
     <t>中海财富中心</t>
   </si>
   <si>
-    <t>116.363944,39.913461</t>
-  </si>
-  <si>
     <t>泰禾长安中心B座</t>
   </si>
   <si>
@@ -1386,7 +1380,7 @@
   </si>
   <si>
     <t>LEEDS</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>RSH</t>
@@ -1399,91 +1393,91 @@
   </si>
   <si>
     <t>中国人寿中心</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>朝阳区</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>中国人寿金融中心（国寿金融中心）</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>116.469030,39.911173</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>116.359101,39.916286</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>中关村东升科技园·学北园</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>奥南五号-B座（恒毅大厦）</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>奥南五号-A座（天圆祥泰大厦）</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>116.406387,39.981515</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>116.406387,39.980615</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>合景国际金融广场（4B)</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>116.680295,39.907589</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>116.358503,39.931864</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>这个还有问题</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>116.362230,39.920558</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>116.313304,39.982116</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>116.320807,39.956309</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>116.319635,39.956309</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>已经更改</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>116.323984,39.958472</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>116.377078,39.888674</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>116.371113,39.967322</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>116.459281,39.960483</t>
@@ -1493,54 +1487,54 @@
   </si>
   <si>
     <t>CBD</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>北京市</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>IFC国际财源中心</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>116.452709,39.907549</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>116.43926,39.909474</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>116.435881,39.919317</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>116.429644,39.906833</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>华贸中心一座</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>华贸中心二座</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>116.464627,39.912332</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>116.464467,39.912049</t>
   </si>
   <si>
     <t>116.464674,39.912865</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>116.460321,39.906941</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>116.454891,39.960979</t>
@@ -1576,25 +1570,38 @@
     <t>116.406051,39.977725</t>
   </si>
   <si>
-    <t>116.35467,39.914699</t>
-  </si>
-  <si>
     <t>116.47137,39.955305</t>
   </si>
   <si>
     <t>116.357285,39.93162</t>
+  </si>
+  <si>
+    <t>116.353911,39.915055</t>
+  </si>
+  <si>
+    <t>116.163151,39.922934</t>
+  </si>
+  <si>
+    <t>116.458326,39.932928</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1675,20 +1682,22 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2012,22 +2021,22 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" t="s">
+        <v>438</v>
+      </c>
+      <c r="B1" t="s">
         <v>440</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
+        <v>441</v>
+      </c>
+      <c r="D1" t="s">
         <v>442</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="F1" t="s">
         <v>443</v>
-      </c>
-      <c r="D1" t="s">
-        <v>444</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>450</v>
-      </c>
-      <c r="F1" t="s">
-        <v>445</v>
       </c>
       <c r="G1" t="s">
         <v>0</v>
@@ -2039,19 +2048,19 @@
         <v>2</v>
       </c>
       <c r="J1" t="s">
+        <v>444</v>
+      </c>
+      <c r="K1" t="s">
+        <v>439</v>
+      </c>
+      <c r="L1" t="s">
+        <v>445</v>
+      </c>
+      <c r="M1" t="s">
         <v>446</v>
       </c>
-      <c r="K1" t="s">
-        <v>441</v>
-      </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>447</v>
-      </c>
-      <c r="M1" t="s">
-        <v>448</v>
-      </c>
-      <c r="N1" t="s">
-        <v>449</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -2080,7 +2089,7 @@
         <v>9</v>
       </c>
       <c r="J2" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="K2">
         <v>72308</v>
@@ -2121,7 +2130,7 @@
         <v>12</v>
       </c>
       <c r="J3" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="K3">
         <v>72308</v>
@@ -2165,7 +2174,7 @@
         <v>17</v>
       </c>
       <c r="J4" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="K4">
         <v>130769</v>
@@ -2209,7 +2218,7 @@
         <v>20</v>
       </c>
       <c r="J5" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="K5">
         <v>64615</v>
@@ -2253,7 +2262,7 @@
         <v>24</v>
       </c>
       <c r="J6" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="K6">
         <v>80091</v>
@@ -2294,7 +2303,7 @@
         <v>27</v>
       </c>
       <c r="J7" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="K7">
         <v>70673</v>
@@ -2338,7 +2347,7 @@
         <v>30</v>
       </c>
       <c r="J8" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="K8">
         <v>90466</v>
@@ -2379,7 +2388,7 @@
         <v>32</v>
       </c>
       <c r="J9" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="K9">
         <v>46720</v>
@@ -2420,10 +2429,10 @@
         <v>8</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="J10" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="K10">
         <v>95000</v>
@@ -2467,7 +2476,7 @@
         <v>37</v>
       </c>
       <c r="J11" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="K11">
         <v>85300</v>
@@ -2511,7 +2520,7 @@
         <v>40</v>
       </c>
       <c r="J12" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="K12">
         <v>33305</v>
@@ -2555,7 +2564,7 @@
         <v>42</v>
       </c>
       <c r="J13" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="K13">
         <v>120245.21</v>
@@ -2599,7 +2608,7 @@
         <v>42</v>
       </c>
       <c r="J14" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="K14">
         <v>70425.53</v>
@@ -2643,7 +2652,7 @@
         <v>46</v>
       </c>
       <c r="J15" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="K15">
         <v>78000</v>
@@ -2687,7 +2696,7 @@
         <v>49</v>
       </c>
       <c r="J16" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="K16">
         <v>102796</v>
@@ -2731,7 +2740,7 @@
         <v>51</v>
       </c>
       <c r="J17" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="K17">
         <v>49200</v>
@@ -2775,7 +2784,7 @@
         <v>53</v>
       </c>
       <c r="J18" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="K18">
         <v>65096</v>
@@ -2819,7 +2828,7 @@
         <v>56</v>
       </c>
       <c r="J19" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="K19">
         <v>56000</v>
@@ -2863,7 +2872,7 @@
         <v>59</v>
       </c>
       <c r="J20" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="K20">
         <v>177847</v>
@@ -2907,7 +2916,7 @@
         <v>62</v>
       </c>
       <c r="J21" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="K21">
         <v>83000</v>
@@ -2945,10 +2954,10 @@
         <v>8</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="J22" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="K22">
         <v>26000</v>
@@ -2989,7 +2998,7 @@
         <v>66</v>
       </c>
       <c r="J23" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="K23">
         <v>85887</v>
@@ -3030,7 +3039,7 @@
         <v>68</v>
       </c>
       <c r="J24" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="K24">
         <v>20000</v>
@@ -3074,7 +3083,7 @@
         <v>71</v>
       </c>
       <c r="J25" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="K25">
         <v>146385</v>
@@ -3118,7 +3127,7 @@
         <v>74</v>
       </c>
       <c r="J26" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="K26">
         <v>87000</v>
@@ -3162,7 +3171,7 @@
         <v>77</v>
       </c>
       <c r="J27" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="K27">
         <v>147166.79999999999</v>
@@ -3206,7 +3215,7 @@
         <v>80</v>
       </c>
       <c r="J28" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="K28">
         <v>46063</v>
@@ -3250,7 +3259,7 @@
         <v>83</v>
       </c>
       <c r="J29" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="K29">
         <v>47261</v>
@@ -3270,7 +3279,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C30" t="s">
         <v>4</v>
@@ -3288,13 +3297,13 @@
         <v>7</v>
       </c>
       <c r="H30" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="I30" s="2" t="s">
         <v>455</v>
       </c>
-      <c r="I30" s="2" t="s">
-        <v>457</v>
-      </c>
       <c r="J30" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="K30">
         <v>119000</v>
@@ -3332,10 +3341,10 @@
         <v>8</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="J31" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="K31">
         <v>47000</v>
@@ -3379,7 +3388,7 @@
         <v>89</v>
       </c>
       <c r="J32" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="K32">
         <v>186000</v>
@@ -3417,7 +3426,7 @@
         <v>91</v>
       </c>
       <c r="J33" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="K33">
         <v>40800</v>
@@ -3455,10 +3464,10 @@
         <v>8</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="J34" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="K34">
         <v>55200</v>
@@ -3502,7 +3511,7 @@
         <v>95</v>
       </c>
       <c r="J35" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="K35">
         <v>350000</v>
@@ -3540,10 +3549,10 @@
         <v>8</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="J36" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="K36">
         <v>65000</v>
@@ -3581,10 +3590,10 @@
         <v>8</v>
       </c>
       <c r="I37" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="J37" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="K37">
         <v>35000</v>
@@ -3625,7 +3634,7 @@
         <v>99</v>
       </c>
       <c r="J38" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="K38">
         <v>47000</v>
@@ -3669,7 +3678,7 @@
         <v>102</v>
       </c>
       <c r="J39" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="K39">
         <v>120000</v>
@@ -3710,7 +3719,7 @@
         <v>104</v>
       </c>
       <c r="J40" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="K40">
         <v>83000</v>
@@ -3751,7 +3760,7 @@
         <v>106</v>
       </c>
       <c r="J41" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="K41">
         <v>66030</v>
@@ -3789,7 +3798,7 @@
         <v>108</v>
       </c>
       <c r="J42" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="K42">
         <v>40000</v>
@@ -3833,7 +3842,7 @@
         <v>113</v>
       </c>
       <c r="J43" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="K43">
         <v>40000</v>
@@ -3874,7 +3883,7 @@
         <v>116</v>
       </c>
       <c r="J44" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="K44">
         <v>54100</v>
@@ -3915,10 +3924,10 @@
         <v>112</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="J45" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="K45">
         <v>100000</v>
@@ -3959,10 +3968,10 @@
         <v>112</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="J46" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="K46">
         <v>150000</v>
@@ -4003,10 +4012,10 @@
         <v>112</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="J47" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="K47">
         <v>50000</v>
@@ -4050,7 +4059,7 @@
         <v>125</v>
       </c>
       <c r="J48" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="K48">
         <v>43000</v>
@@ -4091,7 +4100,7 @@
         <v>128</v>
       </c>
       <c r="J49" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="K49">
         <v>65000</v>
@@ -4135,7 +4144,7 @@
         <v>131</v>
       </c>
       <c r="J50" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="K50">
         <v>56000</v>
@@ -4176,7 +4185,7 @@
         <v>133</v>
       </c>
       <c r="J51" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="K51">
         <v>160000</v>
@@ -4217,7 +4226,7 @@
         <v>135</v>
       </c>
       <c r="J52" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="K52">
         <v>33000</v>
@@ -4261,7 +4270,7 @@
         <v>138</v>
       </c>
       <c r="J53" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="K53">
         <v>41318</v>
@@ -4302,7 +4311,7 @@
         <v>140</v>
       </c>
       <c r="J54" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="K54">
         <v>34131</v>
@@ -4343,7 +4352,7 @@
         <v>143</v>
       </c>
       <c r="J55" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="K55">
         <v>48000</v>
@@ -4381,10 +4390,10 @@
         <v>112</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="J56" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="K56">
         <v>16000</v>
@@ -4428,7 +4437,7 @@
         <v>147</v>
       </c>
       <c r="J57" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="K57">
         <v>30000</v>
@@ -4472,7 +4481,7 @@
         <v>150</v>
       </c>
       <c r="J58" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="K58">
         <v>56000</v>
@@ -4516,7 +4525,7 @@
         <v>153</v>
       </c>
       <c r="J59" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="K59">
         <v>43000</v>
@@ -4554,10 +4563,10 @@
         <v>8</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="J60" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="K60">
         <v>110000</v>
@@ -4595,7 +4604,7 @@
         <v>156</v>
       </c>
       <c r="J61" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="K61">
         <v>56160</v>
@@ -4636,7 +4645,7 @@
         <v>158</v>
       </c>
       <c r="J62" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="K62">
         <v>138444</v>
@@ -4677,10 +4686,10 @@
         <v>85</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="J63" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="K63">
         <v>31000</v>
@@ -4721,7 +4730,7 @@
         <v>164</v>
       </c>
       <c r="J64" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="K64">
         <v>120000</v>
@@ -4762,7 +4771,7 @@
         <v>166</v>
       </c>
       <c r="J65" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="K65">
         <v>25900</v>
@@ -4803,7 +4812,7 @@
         <v>169</v>
       </c>
       <c r="J66" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="K66">
         <v>47986</v>
@@ -4847,7 +4856,7 @@
         <v>171</v>
       </c>
       <c r="J67" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="K67">
         <v>194000</v>
@@ -4891,7 +4900,7 @@
         <v>173</v>
       </c>
       <c r="J68" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="K68">
         <v>39724</v>
@@ -4929,10 +4938,10 @@
         <v>85</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="J69" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="K69">
         <v>48437.45</v>
@@ -4973,7 +4982,7 @@
         <v>177</v>
       </c>
       <c r="J70" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="K70">
         <v>37910</v>
@@ -4993,7 +5002,7 @@
         <v>70</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C71" t="s">
         <v>160</v>
@@ -5011,10 +5020,10 @@
         <v>85</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="J71" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="K71">
         <v>21220</v>
@@ -5055,7 +5064,7 @@
         <v>179</v>
       </c>
       <c r="J72" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="K72">
         <v>77877</v>
@@ -5099,7 +5108,7 @@
         <v>181</v>
       </c>
       <c r="J73" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="K73">
         <v>80311.53</v>
@@ -5143,7 +5152,7 @@
         <v>184</v>
       </c>
       <c r="J74" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="K74">
         <v>38000</v>
@@ -5184,7 +5193,7 @@
         <v>187</v>
       </c>
       <c r="J75" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="K75">
         <v>37800</v>
@@ -5225,10 +5234,10 @@
         <v>85</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="J76" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="K76">
         <v>54581</v>
@@ -5272,7 +5281,7 @@
         <v>502</v>
       </c>
       <c r="J77" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="K77">
         <v>25000</v>
@@ -5316,7 +5325,7 @@
         <v>193</v>
       </c>
       <c r="J78" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="K78">
         <v>52698</v>
@@ -5354,10 +5363,10 @@
         <v>196</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="J79" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="K79">
         <v>38500</v>
@@ -5395,7 +5404,7 @@
         <v>199</v>
       </c>
       <c r="J80" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="K80">
         <v>27200</v>
@@ -5435,11 +5444,11 @@
       <c r="H81" t="s">
         <v>8</v>
       </c>
-      <c r="I81" t="s">
-        <v>202</v>
+      <c r="I81" s="10" t="s">
+        <v>504</v>
       </c>
       <c r="J81" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="K81">
         <v>60000</v>
@@ -5459,7 +5468,7 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C82" t="s">
         <v>137</v>
@@ -5468,7 +5477,7 @@
         <v>5</v>
       </c>
       <c r="F82" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G82" t="s">
         <v>7</v>
@@ -5477,10 +5486,10 @@
         <v>8</v>
       </c>
       <c r="I82" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="J82" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="K82">
         <v>50000</v>
@@ -5500,7 +5509,7 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C83" t="s">
         <v>137</v>
@@ -5521,10 +5530,10 @@
         <v>8</v>
       </c>
       <c r="I83" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="J83" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="K83">
         <v>131575</v>
@@ -5544,7 +5553,7 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C84" t="s">
         <v>137</v>
@@ -5562,10 +5571,10 @@
         <v>8</v>
       </c>
       <c r="I84" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="J84" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="K84">
         <v>99500</v>
@@ -5585,7 +5594,7 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C85" t="s">
         <v>137</v>
@@ -5594,7 +5603,7 @@
         <v>5</v>
       </c>
       <c r="F85" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G85" t="s">
         <v>7</v>
@@ -5603,10 +5612,10 @@
         <v>8</v>
       </c>
       <c r="I85" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="J85" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="K85">
         <v>32000</v>
@@ -5626,7 +5635,7 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C86" t="s">
         <v>137</v>
@@ -5647,10 +5656,10 @@
         <v>8</v>
       </c>
       <c r="I86" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J86" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="K86">
         <v>52170</v>
@@ -5670,7 +5679,7 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C87" t="s">
         <v>137</v>
@@ -5679,7 +5688,7 @@
         <v>5</v>
       </c>
       <c r="F87" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G87" t="s">
         <v>7</v>
@@ -5688,10 +5697,10 @@
         <v>8</v>
       </c>
       <c r="I87" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="J87" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="K87">
         <v>46000</v>
@@ -5711,7 +5720,7 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C88" t="s">
         <v>137</v>
@@ -5723,7 +5732,7 @@
         <v>23</v>
       </c>
       <c r="F88" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G88" t="s">
         <v>7</v>
@@ -5732,10 +5741,10 @@
         <v>8</v>
       </c>
       <c r="I88" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="J88" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="K88">
         <v>45013</v>
@@ -5755,7 +5764,7 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C89" t="s">
         <v>137</v>
@@ -5773,10 +5782,10 @@
         <v>8</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="J89" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="K89">
         <v>48566</v>
@@ -5796,7 +5805,7 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C90" t="s">
         <v>137</v>
@@ -5805,7 +5814,7 @@
         <v>5</v>
       </c>
       <c r="F90" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G90" t="s">
         <v>7</v>
@@ -5814,10 +5823,10 @@
         <v>8</v>
       </c>
       <c r="I90" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="J90" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="K90">
         <v>55618</v>
@@ -5837,7 +5846,7 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C91" t="s">
         <v>137</v>
@@ -5855,10 +5864,10 @@
         <v>8</v>
       </c>
       <c r="I91" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="J91" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="K91">
         <v>47000</v>
@@ -5878,7 +5887,7 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C92" t="s">
         <v>137</v>
@@ -5890,7 +5899,7 @@
         <v>23</v>
       </c>
       <c r="F92" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G92" t="s">
         <v>7</v>
@@ -5899,10 +5908,10 @@
         <v>8</v>
       </c>
       <c r="I92" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="J92" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="K92">
         <v>87763</v>
@@ -5922,7 +5931,7 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C93" t="s">
         <v>137</v>
@@ -5934,7 +5943,7 @@
         <v>16</v>
       </c>
       <c r="F93" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G93" t="s">
         <v>7</v>
@@ -5943,10 +5952,10 @@
         <v>8</v>
       </c>
       <c r="I93" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="J93" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="K93">
         <v>100658</v>
@@ -5966,7 +5975,7 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C94" t="s">
         <v>137</v>
@@ -5975,7 +5984,7 @@
         <v>5</v>
       </c>
       <c r="F94" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G94" t="s">
         <v>7</v>
@@ -5984,10 +5993,10 @@
         <v>8</v>
       </c>
       <c r="I94" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="J94" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="K94">
         <v>67000</v>
@@ -6007,7 +6016,7 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C95" t="s">
         <v>137</v>
@@ -6028,10 +6037,10 @@
         <v>8</v>
       </c>
       <c r="I95" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="J95" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="K95">
         <v>39431</v>
@@ -6051,7 +6060,7 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C96" t="s">
         <v>137</v>
@@ -6069,10 +6078,10 @@
         <v>8</v>
       </c>
       <c r="I96" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J96" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="K96">
         <v>34273</v>
@@ -6092,7 +6101,7 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C97" t="s">
         <v>137</v>
@@ -6107,10 +6116,10 @@
         <v>8</v>
       </c>
       <c r="I97" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="J97" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="K97">
         <v>40000</v>
@@ -6130,7 +6139,7 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C98" t="s">
         <v>137</v>
@@ -6148,10 +6157,10 @@
         <v>8</v>
       </c>
       <c r="I98" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="J98" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="K98">
         <v>65000</v>
@@ -6171,10 +6180,10 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
+        <v>238</v>
+      </c>
+      <c r="C99" t="s">
         <v>239</v>
-      </c>
-      <c r="C99" t="s">
-        <v>240</v>
       </c>
       <c r="D99" t="s">
         <v>5</v>
@@ -6183,7 +6192,7 @@
         <v>23</v>
       </c>
       <c r="F99" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G99" t="s">
         <v>7</v>
@@ -6192,10 +6201,10 @@
         <v>196</v>
       </c>
       <c r="I99" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J99" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="K99">
         <v>49000</v>
@@ -6215,10 +6224,10 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C100" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D100" t="s">
         <v>14</v>
@@ -6227,7 +6236,7 @@
         <v>23</v>
       </c>
       <c r="F100" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G100" t="s">
         <v>7</v>
@@ -6236,10 +6245,10 @@
         <v>196</v>
       </c>
       <c r="I100" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="J100" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="K100">
         <v>95000</v>
@@ -6259,10 +6268,10 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C101" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D101" t="s">
         <v>5</v>
@@ -6271,7 +6280,7 @@
         <v>23</v>
       </c>
       <c r="F101" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G101" t="s">
         <v>7</v>
@@ -6280,10 +6289,10 @@
         <v>196</v>
       </c>
       <c r="I101" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="J101" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="K101">
         <v>45000</v>
@@ -6303,10 +6312,10 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C102" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D102" t="s">
         <v>5</v>
@@ -6321,10 +6330,10 @@
         <v>196</v>
       </c>
       <c r="I102" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="J102" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="K102">
         <v>124500</v>
@@ -6344,10 +6353,10 @@
         <v>102</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C103" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D103" t="s">
         <v>5</v>
@@ -6362,10 +6371,10 @@
         <v>196</v>
       </c>
       <c r="I103" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="J103" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="K103">
         <v>64000</v>
@@ -6385,10 +6394,10 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C104" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D104" t="s">
         <v>5</v>
@@ -6403,10 +6412,10 @@
         <v>196</v>
       </c>
       <c r="I104" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="J104" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="K104">
         <v>25000</v>
@@ -6426,10 +6435,10 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C105" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D105" t="s">
         <v>5</v>
@@ -6444,10 +6453,10 @@
         <v>196</v>
       </c>
       <c r="I105" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="J105" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="K105">
         <v>38498</v>
@@ -6467,10 +6476,10 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C106" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D106" t="s">
         <v>198</v>
@@ -6482,10 +6491,10 @@
         <v>196</v>
       </c>
       <c r="I106" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="J106" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="K106">
         <v>166433</v>
@@ -6505,10 +6514,10 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C107" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D107" t="s">
         <v>14</v>
@@ -6526,10 +6535,10 @@
         <v>196</v>
       </c>
       <c r="I107" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J107" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="K107">
         <v>58000</v>
@@ -6549,16 +6558,16 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
+        <v>259</v>
+      </c>
+      <c r="C108" t="s">
+        <v>239</v>
+      </c>
+      <c r="D108" t="s">
+        <v>5</v>
+      </c>
+      <c r="F108" t="s">
         <v>260</v>
-      </c>
-      <c r="C108" t="s">
-        <v>240</v>
-      </c>
-      <c r="D108" t="s">
-        <v>5</v>
-      </c>
-      <c r="F108" t="s">
-        <v>261</v>
       </c>
       <c r="G108" t="s">
         <v>7</v>
@@ -6567,10 +6576,10 @@
         <v>196</v>
       </c>
       <c r="I108" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="J108" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="K108">
         <v>51872</v>
@@ -6590,10 +6599,10 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C109" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D109" t="s">
         <v>5</v>
@@ -6608,10 +6617,10 @@
         <v>196</v>
       </c>
       <c r="I109" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="J109" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="K109">
         <v>21632</v>
@@ -6631,10 +6640,10 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C110" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D110" t="s">
         <v>5</v>
@@ -6649,10 +6658,10 @@
         <v>196</v>
       </c>
       <c r="I110" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="J110" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="K110">
         <v>69000</v>
@@ -6672,16 +6681,16 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
+        <v>266</v>
+      </c>
+      <c r="C111" t="s">
+        <v>239</v>
+      </c>
+      <c r="D111" t="s">
+        <v>5</v>
+      </c>
+      <c r="F111" t="s">
         <v>267</v>
-      </c>
-      <c r="C111" t="s">
-        <v>240</v>
-      </c>
-      <c r="D111" t="s">
-        <v>5</v>
-      </c>
-      <c r="F111" t="s">
-        <v>268</v>
       </c>
       <c r="G111" t="s">
         <v>7</v>
@@ -6690,10 +6699,10 @@
         <v>196</v>
       </c>
       <c r="I111" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="J111" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="K111">
         <v>54000</v>
@@ -6713,10 +6722,10 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C112" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D112" t="s">
         <v>5</v>
@@ -6731,10 +6740,10 @@
         <v>196</v>
       </c>
       <c r="I112" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="J112" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="K112">
         <v>57400</v>
@@ -6754,10 +6763,10 @@
         <v>112</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C113" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D113" t="s">
         <v>14</v>
@@ -6772,10 +6781,10 @@
         <v>196</v>
       </c>
       <c r="I113" s="2" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="J113" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="K113">
         <v>60000</v>
@@ -6790,7 +6799,7 @@
         <v>427</v>
       </c>
       <c r="P113" s="1" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -6798,10 +6807,10 @@
         <v>113</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C114" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D114" t="s">
         <v>14</v>
@@ -6816,10 +6825,10 @@
         <v>196</v>
       </c>
       <c r="I114" s="2" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="J114" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="K114">
         <v>60000</v>
@@ -6834,7 +6843,7 @@
         <v>11500</v>
       </c>
       <c r="P114" s="1" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -6842,10 +6851,10 @@
         <v>114</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C115" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D115" t="s">
         <v>5</v>
@@ -6857,10 +6866,10 @@
         <v>196</v>
       </c>
       <c r="I115" s="5" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="J115" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="K115">
         <v>33000</v>
@@ -6880,10 +6889,10 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C116" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D116" t="s">
         <v>198</v>
@@ -6895,10 +6904,10 @@
         <v>196</v>
       </c>
       <c r="I116" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J116" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="K116">
         <v>88786</v>
@@ -6918,10 +6927,10 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C117" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D117" t="s">
         <v>198</v>
@@ -6933,10 +6942,10 @@
         <v>196</v>
       </c>
       <c r="I117" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J117" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="K117">
         <v>134000</v>
@@ -6956,10 +6965,10 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C118" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D118" t="s">
         <v>198</v>
@@ -6971,10 +6980,10 @@
         <v>196</v>
       </c>
       <c r="I118" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="J118" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="K118">
         <v>35000</v>
@@ -6994,10 +7003,10 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C119" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D119" t="s">
         <v>198</v>
@@ -7009,10 +7018,10 @@
         <v>196</v>
       </c>
       <c r="I119" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="J119" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="K119">
         <v>18000</v>
@@ -7032,10 +7041,10 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C120" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D120" t="s">
         <v>198</v>
@@ -7050,10 +7059,10 @@
         <v>196</v>
       </c>
       <c r="I120" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="J120" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="K120">
         <v>105741</v>
@@ -7073,10 +7082,10 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C121" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D121" t="s">
         <v>198</v>
@@ -7088,10 +7097,10 @@
         <v>196</v>
       </c>
       <c r="I121" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="J121" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="K121">
         <v>51000</v>
@@ -7111,10 +7120,10 @@
         <v>121</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C122" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D122" t="s">
         <v>5</v>
@@ -7129,10 +7138,10 @@
         <v>196</v>
       </c>
       <c r="I122" s="3" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J122" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="K122">
         <v>130143</v>
@@ -7147,7 +7156,7 @@
         <v>36000</v>
       </c>
       <c r="P122" s="1" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7155,10 +7164,10 @@
         <v>122</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C123" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G123" t="s">
         <v>7</v>
@@ -7167,10 +7176,10 @@
         <v>196</v>
       </c>
       <c r="I123" s="3" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="J123" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="K123">
         <v>121551.47</v>
@@ -7185,7 +7194,7 @@
         <v>97326.47</v>
       </c>
       <c r="P123" s="1" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7193,10 +7202,10 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
+        <v>287</v>
+      </c>
+      <c r="C124" t="s">
         <v>288</v>
-      </c>
-      <c r="C124" t="s">
-        <v>289</v>
       </c>
       <c r="D124" t="s">
         <v>5</v>
@@ -7205,7 +7214,7 @@
         <v>16</v>
       </c>
       <c r="F124" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G124" t="s">
         <v>7</v>
@@ -7214,10 +7223,10 @@
         <v>8</v>
       </c>
       <c r="I124" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J124" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="K124">
         <v>110000</v>
@@ -7237,10 +7246,10 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C125" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D125" t="s">
         <v>5</v>
@@ -7249,7 +7258,7 @@
         <v>23</v>
       </c>
       <c r="F125" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G125" t="s">
         <v>7</v>
@@ -7258,10 +7267,10 @@
         <v>8</v>
       </c>
       <c r="I125" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="J125" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="K125">
         <v>56000</v>
@@ -7281,10 +7290,10 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C126" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D126" t="s">
         <v>5</v>
@@ -7299,10 +7308,10 @@
         <v>8</v>
       </c>
       <c r="I126" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="J126" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="K126">
         <v>89177</v>
@@ -7322,10 +7331,10 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C127" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D127" t="s">
         <v>5</v>
@@ -7334,7 +7343,7 @@
         <v>23</v>
       </c>
       <c r="F127" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G127" t="s">
         <v>7</v>
@@ -7343,10 +7352,10 @@
         <v>8</v>
       </c>
       <c r="I127" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="J127" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="K127">
         <v>30000</v>
@@ -7366,10 +7375,10 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C128" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D128" t="s">
         <v>5</v>
@@ -7378,7 +7387,7 @@
         <v>16</v>
       </c>
       <c r="F128" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G128" t="s">
         <v>7</v>
@@ -7387,10 +7396,10 @@
         <v>8</v>
       </c>
       <c r="I128" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="J128" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="K128">
         <v>54550</v>
@@ -7410,10 +7419,10 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C129" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D129" t="s">
         <v>5</v>
@@ -7422,7 +7431,7 @@
         <v>16</v>
       </c>
       <c r="F129" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G129" t="s">
         <v>7</v>
@@ -7431,10 +7440,10 @@
         <v>8</v>
       </c>
       <c r="I129" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="J129" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="K129">
         <v>125000</v>
@@ -7454,10 +7463,10 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C130" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D130" t="s">
         <v>5</v>
@@ -7466,7 +7475,7 @@
         <v>16</v>
       </c>
       <c r="F130" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G130" t="s">
         <v>7</v>
@@ -7475,10 +7484,10 @@
         <v>8</v>
       </c>
       <c r="I130" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="J130" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="K130">
         <v>69100</v>
@@ -7498,10 +7507,10 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C131" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D131" t="s">
         <v>5</v>
@@ -7519,10 +7528,10 @@
         <v>8</v>
       </c>
       <c r="I131" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="J131" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="K131">
         <v>118290</v>
@@ -7542,16 +7551,16 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
+        <v>307</v>
+      </c>
+      <c r="C132" t="s">
+        <v>288</v>
+      </c>
+      <c r="D132" t="s">
+        <v>5</v>
+      </c>
+      <c r="F132" t="s">
         <v>308</v>
-      </c>
-      <c r="C132" t="s">
-        <v>289</v>
-      </c>
-      <c r="D132" t="s">
-        <v>5</v>
-      </c>
-      <c r="F132" t="s">
-        <v>309</v>
       </c>
       <c r="G132" t="s">
         <v>7</v>
@@ -7560,10 +7569,10 @@
         <v>8</v>
       </c>
       <c r="I132" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="J132" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="K132">
         <v>79900</v>
@@ -7583,10 +7592,10 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C133" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D133" t="s">
         <v>5</v>
@@ -7601,10 +7610,10 @@
         <v>8</v>
       </c>
       <c r="I133" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J133" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="K133">
         <v>39742.379999999997</v>
@@ -7624,10 +7633,10 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C134" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D134" t="s">
         <v>5</v>
@@ -7645,10 +7654,10 @@
         <v>8</v>
       </c>
       <c r="I134" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="J134" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="K134">
         <v>48000</v>
@@ -7668,10 +7677,10 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C135" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D135" t="s">
         <v>14</v>
@@ -7686,10 +7695,10 @@
         <v>8</v>
       </c>
       <c r="I135" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="J135" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="K135">
         <v>74722</v>
@@ -7709,10 +7718,10 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C136" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D136" t="s">
         <v>198</v>
@@ -7724,10 +7733,10 @@
         <v>8</v>
       </c>
       <c r="I136" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="J136" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="K136">
         <v>55000</v>
@@ -7747,10 +7756,10 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
+        <v>318</v>
+      </c>
+      <c r="C137" t="s">
         <v>319</v>
-      </c>
-      <c r="C137" t="s">
-        <v>320</v>
       </c>
       <c r="D137" t="s">
         <v>5</v>
@@ -7762,10 +7771,10 @@
         <v>112</v>
       </c>
       <c r="I137" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="J137" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="K137">
         <v>128000</v>
@@ -7785,10 +7794,10 @@
         <v>137</v>
       </c>
       <c r="B138" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C138" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D138" t="s">
         <v>5</v>
@@ -7806,10 +7815,10 @@
         <v>112</v>
       </c>
       <c r="I138" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="J138" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="K138">
         <v>122000</v>
@@ -7829,10 +7838,10 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C139" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D139" t="s">
         <v>5</v>
@@ -7847,10 +7856,10 @@
         <v>112</v>
       </c>
       <c r="I139" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J139" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="K139">
         <v>22000</v>
@@ -7870,10 +7879,10 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C140" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D140" t="s">
         <v>5</v>
@@ -7888,10 +7897,10 @@
         <v>112</v>
       </c>
       <c r="I140" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="J140" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="K140">
         <v>10000</v>
@@ -7911,10 +7920,10 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C141" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D141" t="s">
         <v>5</v>
@@ -7929,10 +7938,10 @@
         <v>8</v>
       </c>
       <c r="I141" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J141" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="K141">
         <v>64000</v>
@@ -7952,10 +7961,10 @@
         <v>141</v>
       </c>
       <c r="B142" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C142" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D142" t="s">
         <v>5</v>
@@ -7970,10 +7979,10 @@
         <v>8</v>
       </c>
       <c r="I142" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="J142" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="K142">
         <v>95628</v>
@@ -7993,16 +8002,16 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
+        <v>331</v>
+      </c>
+      <c r="C143" t="s">
+        <v>319</v>
+      </c>
+      <c r="D143" t="s">
+        <v>5</v>
+      </c>
+      <c r="F143" t="s">
         <v>332</v>
-      </c>
-      <c r="C143" t="s">
-        <v>320</v>
-      </c>
-      <c r="D143" t="s">
-        <v>5</v>
-      </c>
-      <c r="F143" t="s">
-        <v>333</v>
       </c>
       <c r="G143" t="s">
         <v>7</v>
@@ -8011,10 +8020,10 @@
         <v>8</v>
       </c>
       <c r="I143" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="J143" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="K143">
         <v>39562</v>
@@ -8034,10 +8043,10 @@
         <v>143</v>
       </c>
       <c r="B144" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C144" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D144" t="s">
         <v>5</v>
@@ -8046,7 +8055,7 @@
         <v>16</v>
       </c>
       <c r="F144" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="G144" t="s">
         <v>7</v>
@@ -8055,10 +8064,10 @@
         <v>8</v>
       </c>
       <c r="I144" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="J144" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="K144">
         <v>105000</v>
@@ -8078,10 +8087,10 @@
         <v>144</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C145" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D145" t="s">
         <v>5</v>
@@ -8090,7 +8099,7 @@
         <v>23</v>
       </c>
       <c r="F145" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G145" t="s">
         <v>7</v>
@@ -8099,10 +8108,10 @@
         <v>8</v>
       </c>
       <c r="I145" s="2" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="J145" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="K145">
         <v>60000</v>
@@ -8122,10 +8131,10 @@
         <v>145</v>
       </c>
       <c r="B146" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C146" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D146" t="s">
         <v>5</v>
@@ -8140,10 +8149,10 @@
         <v>8</v>
       </c>
       <c r="I146" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="J146" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="K146">
         <v>39964</v>
@@ -8163,10 +8172,10 @@
         <v>146</v>
       </c>
       <c r="B147" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C147" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D147" t="s">
         <v>5</v>
@@ -8181,10 +8190,10 @@
         <v>8</v>
       </c>
       <c r="I147" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="J147" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="K147">
         <v>94000</v>
@@ -8204,10 +8213,10 @@
         <v>147</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C148" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D148" t="s">
         <v>5</v>
@@ -8225,10 +8234,10 @@
         <v>8</v>
       </c>
       <c r="I148" s="2" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="J148" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="K148">
         <v>75000</v>
@@ -8251,13 +8260,13 @@
         <v>174</v>
       </c>
       <c r="C149" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D149" t="s">
         <v>5</v>
       </c>
       <c r="F149" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G149" t="s">
         <v>7</v>
@@ -8266,10 +8275,10 @@
         <v>8</v>
       </c>
       <c r="I149" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="J149" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="K149">
         <v>48767</v>
@@ -8289,10 +8298,10 @@
         <v>149</v>
       </c>
       <c r="B150" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C150" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D150" t="s">
         <v>5</v>
@@ -8310,10 +8319,10 @@
         <v>8</v>
       </c>
       <c r="I150" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="J150" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="K150">
         <v>63824</v>
@@ -8333,10 +8342,10 @@
         <v>150</v>
       </c>
       <c r="B151" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C151" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D151" t="s">
         <v>14</v>
@@ -8354,10 +8363,10 @@
         <v>8</v>
       </c>
       <c r="I151" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="J151" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="K151">
         <v>117000</v>
@@ -8377,10 +8386,10 @@
         <v>151</v>
       </c>
       <c r="B152" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C152" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D152" t="s">
         <v>5</v>
@@ -8392,10 +8401,10 @@
         <v>8</v>
       </c>
       <c r="I152" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J152" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="K152">
         <v>41000</v>
@@ -8415,10 +8424,10 @@
         <v>152</v>
       </c>
       <c r="B153" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C153" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D153" t="s">
         <v>5</v>
@@ -8430,10 +8439,10 @@
         <v>8</v>
       </c>
       <c r="I153" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="J153" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="K153">
         <v>96446</v>
@@ -8453,10 +8462,10 @@
         <v>153</v>
       </c>
       <c r="B154" t="s">
+        <v>350</v>
+      </c>
+      <c r="C154" t="s">
         <v>351</v>
-      </c>
-      <c r="C154" t="s">
-        <v>352</v>
       </c>
       <c r="D154" t="s">
         <v>5</v>
@@ -8471,13 +8480,13 @@
         <v>7</v>
       </c>
       <c r="H154" t="s">
+        <v>352</v>
+      </c>
+      <c r="I154" t="s">
         <v>353</v>
       </c>
-      <c r="I154" t="s">
-        <v>354</v>
-      </c>
       <c r="J154" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="K154">
         <v>76600</v>
@@ -8497,10 +8506,10 @@
         <v>154</v>
       </c>
       <c r="B155" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C155" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D155" t="s">
         <v>5</v>
@@ -8512,13 +8521,13 @@
         <v>7</v>
       </c>
       <c r="H155" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="I155" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="J155" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="K155">
         <v>125569</v>
@@ -8538,28 +8547,28 @@
         <v>155</v>
       </c>
       <c r="B156" t="s">
+        <v>356</v>
+      </c>
+      <c r="C156" t="s">
+        <v>351</v>
+      </c>
+      <c r="D156" t="s">
+        <v>5</v>
+      </c>
+      <c r="F156" t="s">
         <v>357</v>
       </c>
-      <c r="C156" t="s">
+      <c r="G156" t="s">
+        <v>7</v>
+      </c>
+      <c r="H156" t="s">
         <v>352</v>
       </c>
-      <c r="D156" t="s">
-        <v>5</v>
-      </c>
-      <c r="F156" t="s">
+      <c r="I156" t="s">
         <v>358</v>
       </c>
-      <c r="G156" t="s">
-        <v>7</v>
-      </c>
-      <c r="H156" t="s">
-        <v>353</v>
-      </c>
-      <c r="I156" t="s">
-        <v>359</v>
-      </c>
       <c r="J156" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="K156">
         <v>51234</v>
@@ -8579,10 +8588,10 @@
         <v>156</v>
       </c>
       <c r="B157" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C157" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D157" t="s">
         <v>5</v>
@@ -8597,13 +8606,13 @@
         <v>7</v>
       </c>
       <c r="H157" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="I157" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="J157" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="K157">
         <v>123780</v>
@@ -8623,28 +8632,28 @@
         <v>157</v>
       </c>
       <c r="B158" t="s">
+        <v>361</v>
+      </c>
+      <c r="C158" t="s">
+        <v>351</v>
+      </c>
+      <c r="D158" t="s">
+        <v>5</v>
+      </c>
+      <c r="F158" t="s">
         <v>362</v>
       </c>
-      <c r="C158" t="s">
+      <c r="G158" t="s">
+        <v>7</v>
+      </c>
+      <c r="H158" t="s">
         <v>352</v>
       </c>
-      <c r="D158" t="s">
-        <v>5</v>
-      </c>
-      <c r="F158" t="s">
+      <c r="I158" t="s">
         <v>363</v>
       </c>
-      <c r="G158" t="s">
-        <v>7</v>
-      </c>
-      <c r="H158" t="s">
-        <v>353</v>
-      </c>
-      <c r="I158" t="s">
-        <v>364</v>
-      </c>
       <c r="J158" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="K158">
         <v>46000</v>
@@ -8664,25 +8673,25 @@
         <v>158</v>
       </c>
       <c r="B159" t="s">
+        <v>364</v>
+      </c>
+      <c r="C159" t="s">
+        <v>351</v>
+      </c>
+      <c r="D159" t="s">
+        <v>5</v>
+      </c>
+      <c r="G159" t="s">
+        <v>7</v>
+      </c>
+      <c r="H159" t="s">
+        <v>352</v>
+      </c>
+      <c r="I159" t="s">
         <v>365</v>
       </c>
-      <c r="C159" t="s">
-        <v>352</v>
-      </c>
-      <c r="D159" t="s">
-        <v>5</v>
-      </c>
-      <c r="G159" t="s">
-        <v>7</v>
-      </c>
-      <c r="H159" t="s">
-        <v>353</v>
-      </c>
-      <c r="I159" t="s">
-        <v>366</v>
-      </c>
       <c r="J159" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="K159">
         <v>35600</v>
@@ -8702,10 +8711,10 @@
         <v>159</v>
       </c>
       <c r="B160" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C160" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D160" t="s">
         <v>5</v>
@@ -8717,13 +8726,13 @@
         <v>7</v>
       </c>
       <c r="H160" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="I160" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="J160" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="K160">
         <v>199950</v>
@@ -8743,10 +8752,10 @@
         <v>160</v>
       </c>
       <c r="B161" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C161" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D161" t="s">
         <v>5</v>
@@ -8758,13 +8767,13 @@
         <v>7</v>
       </c>
       <c r="H161" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="I161" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="J161" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="K161">
         <v>108000</v>
@@ -8784,10 +8793,10 @@
         <v>161</v>
       </c>
       <c r="B162" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C162" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D162" t="s">
         <v>5</v>
@@ -8799,13 +8808,13 @@
         <v>7</v>
       </c>
       <c r="H162" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="I162" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="J162" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="K162">
         <v>142808</v>
@@ -8825,10 +8834,10 @@
         <v>162</v>
       </c>
       <c r="B163" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C163" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D163" t="s">
         <v>5</v>
@@ -8840,13 +8849,13 @@
         <v>7</v>
       </c>
       <c r="H163" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="I163" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="J163" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="K163">
         <v>80463</v>
@@ -8866,10 +8875,10 @@
         <v>163</v>
       </c>
       <c r="B164" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C164" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D164" t="s">
         <v>5</v>
@@ -8881,13 +8890,13 @@
         <v>7</v>
       </c>
       <c r="H164" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="I164" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="J164" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="K164">
         <v>83000</v>
@@ -8907,25 +8916,25 @@
         <v>164</v>
       </c>
       <c r="B165" t="s">
+        <v>376</v>
+      </c>
+      <c r="C165" t="s">
+        <v>351</v>
+      </c>
+      <c r="D165" t="s">
+        <v>5</v>
+      </c>
+      <c r="G165" t="s">
+        <v>7</v>
+      </c>
+      <c r="H165" t="s">
+        <v>352</v>
+      </c>
+      <c r="I165" t="s">
         <v>377</v>
       </c>
-      <c r="C165" t="s">
-        <v>352</v>
-      </c>
-      <c r="D165" t="s">
-        <v>5</v>
-      </c>
-      <c r="G165" t="s">
-        <v>7</v>
-      </c>
-      <c r="H165" t="s">
-        <v>353</v>
-      </c>
-      <c r="I165" t="s">
-        <v>378</v>
-      </c>
       <c r="J165" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="K165">
         <v>129000</v>
@@ -8945,16 +8954,16 @@
         <v>165</v>
       </c>
       <c r="B166" t="s">
+        <v>378</v>
+      </c>
+      <c r="C166" t="s">
         <v>379</v>
       </c>
-      <c r="C166" t="s">
-        <v>380</v>
-      </c>
       <c r="D166" t="s">
         <v>5</v>
       </c>
       <c r="F166" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G166" t="s">
         <v>7</v>
@@ -8963,10 +8972,10 @@
         <v>112</v>
       </c>
       <c r="I166" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J166" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="K166">
         <v>62209</v>
@@ -8986,16 +8995,16 @@
         <v>166</v>
       </c>
       <c r="B167" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C167" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D167" t="s">
         <v>5</v>
       </c>
       <c r="F167" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G167" t="s">
         <v>7</v>
@@ -9004,10 +9013,10 @@
         <v>8</v>
       </c>
       <c r="I167" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="J167" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="K167">
         <v>36117</v>
@@ -9027,10 +9036,10 @@
         <v>167</v>
       </c>
       <c r="B168" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C168" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D168" t="s">
         <v>5</v>
@@ -9048,10 +9057,10 @@
         <v>85</v>
       </c>
       <c r="I168" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="J168" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="K168">
         <v>49900</v>
@@ -9071,10 +9080,10 @@
         <v>168</v>
       </c>
       <c r="B169" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C169" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D169" t="s">
         <v>5</v>
@@ -9083,7 +9092,7 @@
         <v>16</v>
       </c>
       <c r="F169" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="G169" t="s">
         <v>7</v>
@@ -9092,10 +9101,10 @@
         <v>85</v>
       </c>
       <c r="I169" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="J169" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="K169">
         <v>39000</v>
@@ -9115,16 +9124,16 @@
         <v>169</v>
       </c>
       <c r="B170" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C170" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D170" t="s">
         <v>5</v>
       </c>
       <c r="F170" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G170" t="s">
         <v>7</v>
@@ -9133,10 +9142,10 @@
         <v>196</v>
       </c>
       <c r="I170" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="J170" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="K170">
         <v>49000</v>
@@ -9156,10 +9165,10 @@
         <v>170</v>
       </c>
       <c r="B171" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C171" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D171" t="s">
         <v>198</v>
@@ -9171,10 +9180,10 @@
         <v>8</v>
       </c>
       <c r="I171" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="J171" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="K171">
         <v>59400</v>
@@ -9194,10 +9203,10 @@
         <v>171</v>
       </c>
       <c r="B172" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C172" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D172" t="s">
         <v>5</v>
@@ -9212,10 +9221,10 @@
         <v>8</v>
       </c>
       <c r="I172" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="J172" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="K172">
         <v>65000</v>
@@ -9235,31 +9244,31 @@
         <v>172</v>
       </c>
       <c r="B173" t="s">
+        <v>394</v>
+      </c>
+      <c r="C173" t="s">
+        <v>379</v>
+      </c>
+      <c r="D173" t="s">
+        <v>5</v>
+      </c>
+      <c r="E173" t="s">
+        <v>396</v>
+      </c>
+      <c r="F173" t="s">
         <v>395</v>
       </c>
-      <c r="C173" t="s">
-        <v>380</v>
-      </c>
-      <c r="D173" t="s">
-        <v>5</v>
-      </c>
-      <c r="E173" t="s">
+      <c r="G173" t="s">
+        <v>7</v>
+      </c>
+      <c r="H173" t="s">
         <v>397</v>
       </c>
-      <c r="F173" t="s">
-        <v>396</v>
-      </c>
-      <c r="G173" t="s">
-        <v>7</v>
-      </c>
-      <c r="H173" t="s">
+      <c r="I173" t="s">
         <v>398</v>
       </c>
-      <c r="I173" t="s">
-        <v>399</v>
-      </c>
       <c r="J173" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="K173">
         <v>47000</v>
@@ -9279,28 +9288,28 @@
         <v>173</v>
       </c>
       <c r="B174" t="s">
+        <v>399</v>
+      </c>
+      <c r="C174" t="s">
+        <v>379</v>
+      </c>
+      <c r="D174" t="s">
+        <v>5</v>
+      </c>
+      <c r="E174" t="s">
+        <v>396</v>
+      </c>
+      <c r="G174" t="s">
+        <v>7</v>
+      </c>
+      <c r="H174" t="s">
+        <v>397</v>
+      </c>
+      <c r="I174" t="s">
         <v>400</v>
       </c>
-      <c r="C174" t="s">
-        <v>380</v>
-      </c>
-      <c r="D174" t="s">
-        <v>5</v>
-      </c>
-      <c r="E174" t="s">
-        <v>397</v>
-      </c>
-      <c r="G174" t="s">
-        <v>7</v>
-      </c>
-      <c r="H174" t="s">
-        <v>398</v>
-      </c>
-      <c r="I174" t="s">
-        <v>401</v>
-      </c>
       <c r="J174" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="K174">
         <v>29000</v>
@@ -9319,11 +9328,11 @@
       <c r="A175">
         <v>174</v>
       </c>
-      <c r="B175" t="s">
-        <v>402</v>
+      <c r="B175" s="9" t="s">
+        <v>401</v>
       </c>
       <c r="C175" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D175" t="s">
         <v>5</v>
@@ -9337,14 +9346,14 @@
       <c r="G175" t="s">
         <v>7</v>
       </c>
-      <c r="H175" t="s">
-        <v>85</v>
-      </c>
-      <c r="I175" t="s">
-        <v>403</v>
+      <c r="H175" s="10" t="s">
+        <v>397</v>
+      </c>
+      <c r="I175" s="9" t="s">
+        <v>503</v>
       </c>
       <c r="J175" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="K175">
         <v>132239</v>
@@ -9364,10 +9373,10 @@
         <v>175</v>
       </c>
       <c r="B176" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C176" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D176" t="s">
         <v>5</v>
@@ -9379,13 +9388,13 @@
         <v>7</v>
       </c>
       <c r="H176" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="I176" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="J176" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="K176">
         <v>35016</v>
@@ -9405,10 +9414,10 @@
         <v>176</v>
       </c>
       <c r="B177" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C177" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D177" t="s">
         <v>5</v>
@@ -9420,10 +9429,10 @@
         <v>85</v>
       </c>
       <c r="I177" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="J177" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="K177">
         <v>60000</v>
@@ -9443,28 +9452,28 @@
         <v>177</v>
       </c>
       <c r="B178" t="s">
+        <v>406</v>
+      </c>
+      <c r="C178" t="s">
+        <v>379</v>
+      </c>
+      <c r="D178" t="s">
+        <v>5</v>
+      </c>
+      <c r="F178" t="s">
+        <v>407</v>
+      </c>
+      <c r="G178" t="s">
+        <v>7</v>
+      </c>
+      <c r="H178" t="s">
+        <v>352</v>
+      </c>
+      <c r="I178" t="s">
         <v>408</v>
       </c>
-      <c r="C178" t="s">
-        <v>380</v>
-      </c>
-      <c r="D178" t="s">
-        <v>5</v>
-      </c>
-      <c r="F178" t="s">
-        <v>409</v>
-      </c>
-      <c r="G178" t="s">
-        <v>7</v>
-      </c>
-      <c r="H178" t="s">
-        <v>353</v>
-      </c>
-      <c r="I178" t="s">
-        <v>410</v>
-      </c>
       <c r="J178" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="K178">
         <v>90244</v>
@@ -9484,10 +9493,10 @@
         <v>178</v>
       </c>
       <c r="B179" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C179" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D179" t="s">
         <v>5</v>
@@ -9496,13 +9505,13 @@
         <v>7</v>
       </c>
       <c r="H179" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="I179" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="J179" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="K179">
         <v>38700</v>
@@ -9522,10 +9531,10 @@
         <v>179</v>
       </c>
       <c r="B180" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C180" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D180" t="s">
         <v>5</v>
@@ -9534,13 +9543,13 @@
         <v>7</v>
       </c>
       <c r="H180" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="I180" s="1" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="J180" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="K180">
         <v>62414</v>
@@ -9560,10 +9569,10 @@
         <v>180</v>
       </c>
       <c r="B181" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C181" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D181" t="s">
         <v>5</v>
@@ -9572,13 +9581,13 @@
         <v>7</v>
       </c>
       <c r="H181" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="I181" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="J181" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="K181">
         <v>51000</v>
@@ -9598,10 +9607,10 @@
         <v>181</v>
       </c>
       <c r="B182" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C182" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D182" t="s">
         <v>5</v>
@@ -9616,10 +9625,10 @@
         <v>85</v>
       </c>
       <c r="I182" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="J182" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="K182">
         <v>53115</v>
@@ -9639,10 +9648,10 @@
         <v>182</v>
       </c>
       <c r="B183" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C183" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D183" t="s">
         <v>5</v>
@@ -9651,13 +9660,13 @@
         <v>7</v>
       </c>
       <c r="H183" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="I183" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="J183" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="K183">
         <v>120000</v>
@@ -9677,10 +9686,10 @@
         <v>183</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C184" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D184" t="s">
         <v>5</v>
@@ -9695,10 +9704,10 @@
         <v>85</v>
       </c>
       <c r="I184" s="3" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="J184" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="K184">
         <v>66477</v>
@@ -9718,10 +9727,10 @@
         <v>184</v>
       </c>
       <c r="B185" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C185" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D185" t="s">
         <v>5</v>
@@ -9733,10 +9742,10 @@
         <v>7</v>
       </c>
       <c r="H185" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="I185" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="K185">
         <v>59300</v>
@@ -9756,10 +9765,10 @@
         <v>185</v>
       </c>
       <c r="B186" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C186" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D186" t="s">
         <v>5</v>
@@ -9768,10 +9777,10 @@
         <v>7</v>
       </c>
       <c r="H186" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="I186" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="K186">
         <v>44000</v>
@@ -9791,10 +9800,10 @@
         <v>186</v>
       </c>
       <c r="B187" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C187" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D187" t="s">
         <v>5</v>
@@ -9803,10 +9812,10 @@
         <v>7</v>
       </c>
       <c r="H187" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="I187" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="K187">
         <v>26528</v>
@@ -9826,10 +9835,10 @@
         <v>187</v>
       </c>
       <c r="B188" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C188" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D188" t="s">
         <v>5</v>
@@ -9841,10 +9850,10 @@
         <v>7</v>
       </c>
       <c r="H188" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="I188" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="K188">
         <v>95684</v>
@@ -9864,10 +9873,10 @@
         <v>188</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C189" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D189" t="s">
         <v>5</v>
@@ -9879,7 +9888,7 @@
         <v>85</v>
       </c>
       <c r="I189" s="4" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="K189">
         <v>26737</v>
@@ -9899,10 +9908,10 @@
         <v>189</v>
       </c>
       <c r="B190" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C190" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D190" t="s">
         <v>5</v>
@@ -9914,10 +9923,10 @@
         <v>7</v>
       </c>
       <c r="H190" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="I190" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="K190">
         <v>60000</v>
@@ -9937,10 +9946,10 @@
         <v>190</v>
       </c>
       <c r="B191" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C191" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D191" t="s">
         <v>5</v>
@@ -9949,10 +9958,10 @@
         <v>7</v>
       </c>
       <c r="H191" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="I191" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="K191">
         <v>34895</v>
@@ -9969,33 +9978,33 @@
     </row>
     <row r="192" spans="1:14">
       <c r="B192" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="G192" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="H192" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="I192" s="1" t="s">
         <v>479</v>
-      </c>
-      <c r="H192" s="1" t="s">
-        <v>455</v>
-      </c>
-      <c r="I192" s="1" t="s">
-        <v>481</v>
       </c>
     </row>
     <row r="193" spans="2:2">
       <c r="B193" s="1" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://colliers.sharepoint.com/teams/Asia_Research/China/Shared Documents/North/Beijing/工作中报告_持续更新中/实习生文档/Ron/0303系统数据/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="8_{B2126FFC-172F-4569-88A8-F2305D0C9028}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{05EF41CE-C09E-4B35-B915-B4C7D07FB09D}"/>
+  <xr:revisionPtr revIDLastSave="84" documentId="8_{B2126FFC-172F-4569-88A8-F2305D0C9028}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E8C10ACD-5F42-4AFF-8B0E-A3ECE475EF07}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1580" uniqueCount="505">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1646" uniqueCount="509">
   <si>
     <t>所在市</t>
   </si>
@@ -1380,7 +1380,7 @@
   </si>
   <si>
     <t>LEEDS</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>RSH</t>
@@ -1393,91 +1393,91 @@
   </si>
   <si>
     <t>中国人寿中心</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>朝阳区</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>中国人寿金融中心（国寿金融中心）</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>116.469030,39.911173</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>116.359101,39.916286</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>中关村东升科技园·学北园</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>奥南五号-B座（恒毅大厦）</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>奥南五号-A座（天圆祥泰大厦）</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>116.406387,39.981515</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>116.406387,39.980615</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>合景国际金融广场（4B)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>116.680295,39.907589</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>116.358503,39.931864</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>这个还有问题</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>116.362230,39.920558</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>116.313304,39.982116</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>116.320807,39.956309</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>116.319635,39.956309</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>已经更改</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>116.323984,39.958472</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>116.377078,39.888674</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>116.371113,39.967322</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>116.459281,39.960483</t>
@@ -1487,54 +1487,54 @@
   </si>
   <si>
     <t>CBD</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>北京市</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>IFC国际财源中心</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>116.452709,39.907549</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>116.43926,39.909474</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>116.435881,39.919317</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>116.429644,39.906833</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>华贸中心一座</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>华贸中心二座</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>116.464627,39.912332</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>116.464467,39.912049</t>
   </si>
   <si>
     <t>116.464674,39.912865</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>116.460321,39.906941</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>116.454891,39.960979</t>
@@ -1549,9 +1549,6 @@
     <t>116.491439,39.914113</t>
   </si>
   <si>
-    <t>116.456808,39.907696</t>
-  </si>
-  <si>
     <t>116.412649,39.909443</t>
   </si>
   <si>
@@ -1583,18 +1580,40 @@
   </si>
   <si>
     <t>116.458326,39.932928</t>
+  </si>
+  <si>
+    <t>116.456769,39.907882</t>
+  </si>
+  <si>
+    <t>竣工时间1</t>
+  </si>
+  <si>
+    <t>新光大中心5A</t>
+  </si>
+  <si>
+    <t>116.658956,39.916829</t>
+  </si>
+  <si>
+    <t/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1682,22 +1701,24 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2001,7 +2022,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B280671-4AFA-4641-88D4-A51F39483890}">
-  <dimension ref="A1:P194"/>
+  <dimension ref="A1:Q195"/>
   <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="5.6328125" bestFit="1" customWidth="1"/>
@@ -2009,17 +2030,18 @@
     <col min="3" max="3" width="12.1796875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.1796875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.36328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="7.453125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.1796875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.453125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.36328125" customWidth="1"/>
+    <col min="7" max="7" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="23.1796875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" t="s">
         <v>438</v>
       </c>
@@ -2035,35 +2057,38 @@
       <c r="E1" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="G1" t="s">
         <v>443</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>0</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>1</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>2</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>444</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>439</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>445</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>446</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:15">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2079,32 +2104,35 @@
       <c r="F2" t="s">
         <v>6</v>
       </c>
-      <c r="G2" t="s">
-        <v>7</v>
+      <c r="G2" s="12">
+        <v>1990</v>
       </c>
       <c r="H2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" t="s">
         <v>8</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>9</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>449</v>
       </c>
-      <c r="K2">
+      <c r="L2">
         <v>72308</v>
       </c>
-      <c r="L2">
+      <c r="M2">
         <v>288.75</v>
       </c>
-      <c r="M2">
+      <c r="N2">
         <v>0.129999446810865</v>
       </c>
-      <c r="N2">
+      <c r="O2">
         <v>9400</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:15">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2120,32 +2148,35 @@
       <c r="F3" t="s">
         <v>11</v>
       </c>
-      <c r="G3" t="s">
-        <v>7</v>
+      <c r="G3" s="12">
+        <v>1999</v>
       </c>
       <c r="H3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I3" t="s">
         <v>8</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>12</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>449</v>
       </c>
-      <c r="K3">
+      <c r="L3">
         <v>72308</v>
       </c>
-      <c r="L3">
+      <c r="M3">
         <v>307.08333333333297</v>
       </c>
-      <c r="M3">
+      <c r="N3">
         <v>2.0053106156995099E-2</v>
       </c>
-      <c r="N3">
+      <c r="O3">
         <v>1450</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:15">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2159,37 +2190,40 @@
         <v>14</v>
       </c>
       <c r="E4" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F4" t="s">
         <v>15</v>
       </c>
-      <c r="G4" t="s">
-        <v>7</v>
+      <c r="G4" s="12">
+        <v>2010</v>
       </c>
       <c r="H4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I4" t="s">
         <v>8</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>17</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>449</v>
       </c>
-      <c r="K4">
+      <c r="L4">
         <v>130769</v>
       </c>
-      <c r="L4">
+      <c r="M4">
         <v>363.61111111111097</v>
       </c>
-      <c r="M4">
+      <c r="N4">
         <v>0.100176647370554</v>
       </c>
-      <c r="N4">
+      <c r="O4">
         <v>13100</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:15">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2203,37 +2237,40 @@
         <v>14</v>
       </c>
       <c r="E5" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F5" t="s">
         <v>19</v>
       </c>
-      <c r="G5" t="s">
-        <v>7</v>
+      <c r="G5" s="12">
+        <v>2017</v>
       </c>
       <c r="H5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I5" t="s">
         <v>8</v>
       </c>
-      <c r="I5" t="s">
+      <c r="J5" t="s">
         <v>20</v>
       </c>
-      <c r="J5" t="s">
+      <c r="K5" t="s">
         <v>449</v>
       </c>
-      <c r="K5">
+      <c r="L5">
         <v>64615</v>
       </c>
-      <c r="L5">
+      <c r="M5">
         <v>377.777777777778</v>
       </c>
-      <c r="M5">
+      <c r="N5">
         <v>3.01787510639944E-2</v>
       </c>
-      <c r="N5">
+      <c r="O5">
         <v>1950</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:15">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2252,32 +2289,35 @@
       <c r="F6" t="s">
         <v>22</v>
       </c>
-      <c r="G6" t="s">
-        <v>7</v>
+      <c r="G6" s="12">
+        <v>1998</v>
       </c>
       <c r="H6" t="s">
+        <v>7</v>
+      </c>
+      <c r="I6" t="s">
         <v>8</v>
       </c>
-      <c r="I6" t="s">
+      <c r="J6" t="s">
         <v>24</v>
       </c>
-      <c r="J6" t="s">
+      <c r="K6" t="s">
         <v>449</v>
       </c>
-      <c r="K6">
+      <c r="L6">
         <v>80091</v>
       </c>
-      <c r="L6">
+      <c r="M6">
         <v>208.333333333333</v>
       </c>
-      <c r="M6">
+      <c r="N6">
         <v>7.4440324131300598E-2</v>
       </c>
-      <c r="N6">
+      <c r="O6">
         <v>5962</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:15">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2293,32 +2333,35 @@
       <c r="F7" t="s">
         <v>26</v>
       </c>
-      <c r="G7" t="s">
-        <v>7</v>
+      <c r="G7" s="12">
+        <v>2005</v>
       </c>
       <c r="H7" t="s">
+        <v>7</v>
+      </c>
+      <c r="I7" t="s">
         <v>8</v>
       </c>
-      <c r="I7" t="s">
+      <c r="J7" t="s">
         <v>27</v>
       </c>
-      <c r="J7" t="s">
+      <c r="K7" t="s">
         <v>437</v>
       </c>
-      <c r="K7">
+      <c r="L7">
         <v>70673</v>
       </c>
-      <c r="L7">
+      <c r="M7">
         <v>242.916666666667</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
       </c>
       <c r="N7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:14">
+      <c r="O7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2337,32 +2380,35 @@
       <c r="F8" t="s">
         <v>29</v>
       </c>
-      <c r="G8" t="s">
-        <v>7</v>
+      <c r="G8" s="12">
+        <v>2005</v>
       </c>
       <c r="H8" t="s">
+        <v>7</v>
+      </c>
+      <c r="I8" t="s">
         <v>8</v>
       </c>
-      <c r="I8" t="s">
+      <c r="J8" t="s">
         <v>30</v>
       </c>
-      <c r="J8" t="s">
+      <c r="K8" t="s">
         <v>449</v>
       </c>
-      <c r="K8">
+      <c r="L8">
         <v>90466</v>
       </c>
-      <c r="L8">
+      <c r="M8">
         <v>177.777777777778</v>
       </c>
-      <c r="M8">
+      <c r="N8">
         <v>0.239935445360688</v>
       </c>
-      <c r="N8">
+      <c r="O8">
         <v>21706</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:15">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2378,32 +2424,35 @@
       <c r="F9" t="s">
         <v>29</v>
       </c>
-      <c r="G9" t="s">
-        <v>7</v>
+      <c r="G9" s="12">
+        <v>2005</v>
       </c>
       <c r="H9" t="s">
+        <v>7</v>
+      </c>
+      <c r="I9" t="s">
         <v>8</v>
       </c>
-      <c r="I9" t="s">
+      <c r="J9" t="s">
         <v>32</v>
       </c>
-      <c r="J9" t="s">
+      <c r="K9" t="s">
         <v>437</v>
       </c>
-      <c r="K9">
+      <c r="L9">
         <v>46720</v>
       </c>
-      <c r="L9">
+      <c r="M9">
         <v>198.333333333333</v>
       </c>
-      <c r="M9">
+      <c r="N9">
         <v>7.4453553082191801E-2</v>
       </c>
-      <c r="N9">
+      <c r="O9">
         <v>3478.47</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:15">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2422,32 +2471,35 @@
       <c r="F10" t="s">
         <v>34</v>
       </c>
-      <c r="G10" t="s">
-        <v>7</v>
+      <c r="G10" s="12">
+        <v>2006</v>
       </c>
       <c r="H10" t="s">
+        <v>7</v>
+      </c>
+      <c r="I10" t="s">
         <v>8</v>
       </c>
-      <c r="I10" s="7" t="s">
-        <v>493</v>
-      </c>
-      <c r="J10" t="s">
+      <c r="J10" s="11" t="s">
+        <v>504</v>
+      </c>
+      <c r="K10" t="s">
         <v>437</v>
       </c>
-      <c r="K10">
+      <c r="L10">
         <v>95000</v>
       </c>
-      <c r="L10">
+      <c r="M10">
         <v>182.777777777778</v>
       </c>
-      <c r="M10">
+      <c r="N10">
         <v>0.24465263157894701</v>
       </c>
-      <c r="N10">
+      <c r="O10">
         <v>23242</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:15">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2466,32 +2518,35 @@
       <c r="F11" t="s">
         <v>36</v>
       </c>
-      <c r="G11" t="s">
-        <v>7</v>
+      <c r="G11" s="12">
+        <v>2007</v>
       </c>
       <c r="H11" t="s">
+        <v>7</v>
+      </c>
+      <c r="I11" t="s">
         <v>8</v>
       </c>
-      <c r="I11" t="s">
+      <c r="J11" t="s">
         <v>37</v>
       </c>
-      <c r="J11" t="s">
+      <c r="K11" t="s">
         <v>449</v>
       </c>
-      <c r="K11">
+      <c r="L11">
         <v>85300</v>
       </c>
-      <c r="L11">
+      <c r="M11">
         <v>146.388888888889</v>
       </c>
-      <c r="M11">
+      <c r="N11">
         <v>0.19929660023446699</v>
       </c>
-      <c r="N11">
+      <c r="O11">
         <v>17000</v>
       </c>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:15">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2510,32 +2565,35 @@
       <c r="F12" t="s">
         <v>39</v>
       </c>
-      <c r="G12" t="s">
-        <v>7</v>
+      <c r="G12" s="12">
+        <v>2007</v>
       </c>
       <c r="H12" t="s">
+        <v>7</v>
+      </c>
+      <c r="I12" t="s">
         <v>8</v>
       </c>
-      <c r="I12" t="s">
+      <c r="J12" t="s">
         <v>40</v>
       </c>
-      <c r="J12" t="s">
+      <c r="K12" t="s">
         <v>437</v>
       </c>
-      <c r="K12">
+      <c r="L12">
         <v>33305</v>
       </c>
-      <c r="L12">
+      <c r="M12">
         <v>186.666666666667</v>
       </c>
-      <c r="M12">
+      <c r="N12">
         <v>0.14799579642696301</v>
       </c>
-      <c r="N12">
+      <c r="O12">
         <v>4929</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:15">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2554,32 +2612,35 @@
       <c r="F13" t="s">
         <v>39</v>
       </c>
-      <c r="G13" t="s">
-        <v>7</v>
+      <c r="G13" s="12">
+        <v>2007</v>
       </c>
       <c r="H13" t="s">
+        <v>7</v>
+      </c>
+      <c r="I13" t="s">
         <v>8</v>
       </c>
-      <c r="I13" t="s">
+      <c r="J13" t="s">
         <v>42</v>
       </c>
-      <c r="J13" t="s">
+      <c r="K13" t="s">
         <v>449</v>
       </c>
-      <c r="K13">
+      <c r="L13">
         <v>120245.21</v>
       </c>
-      <c r="L13">
+      <c r="M13">
         <v>253.333333333333</v>
       </c>
-      <c r="M13">
+      <c r="N13">
         <v>6.6680410803889797E-2</v>
       </c>
-      <c r="N13">
+      <c r="O13">
         <v>8018</v>
       </c>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:15">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2598,32 +2659,35 @@
       <c r="F14" t="s">
         <v>44</v>
       </c>
-      <c r="G14" t="s">
-        <v>7</v>
+      <c r="G14" s="12">
+        <v>2008</v>
       </c>
       <c r="H14" t="s">
+        <v>7</v>
+      </c>
+      <c r="I14" t="s">
         <v>8</v>
       </c>
-      <c r="I14" t="s">
+      <c r="J14" t="s">
         <v>42</v>
       </c>
-      <c r="J14" t="s">
+      <c r="K14" t="s">
         <v>449</v>
       </c>
-      <c r="K14">
+      <c r="L14">
         <v>70425.53</v>
       </c>
-      <c r="L14">
+      <c r="M14">
         <v>253.333333333333</v>
       </c>
-      <c r="M14">
+      <c r="N14">
         <v>9.3091241201876604E-2</v>
       </c>
-      <c r="N14">
+      <c r="O14">
         <v>6556</v>
       </c>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" spans="1:15">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2642,32 +2706,35 @@
       <c r="F15" t="s">
         <v>39</v>
       </c>
-      <c r="G15" t="s">
-        <v>7</v>
+      <c r="G15" s="12">
+        <v>2007</v>
       </c>
       <c r="H15" t="s">
+        <v>7</v>
+      </c>
+      <c r="I15" t="s">
         <v>8</v>
       </c>
-      <c r="I15" t="s">
+      <c r="J15" t="s">
         <v>46</v>
       </c>
-      <c r="J15" t="s">
+      <c r="K15" t="s">
         <v>449</v>
       </c>
-      <c r="K15">
+      <c r="L15">
         <v>78000</v>
       </c>
-      <c r="L15">
+      <c r="M15">
         <v>258.33333333333297</v>
       </c>
-      <c r="M15">
+      <c r="N15">
         <v>0.15384615384615399</v>
       </c>
-      <c r="N15">
+      <c r="O15">
         <v>12000</v>
       </c>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16" spans="1:15">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2686,32 +2753,35 @@
       <c r="F16" t="s">
         <v>48</v>
       </c>
-      <c r="G16" t="s">
-        <v>7</v>
+      <c r="G16" s="12">
+        <v>2007</v>
       </c>
       <c r="H16" t="s">
+        <v>7</v>
+      </c>
+      <c r="I16" t="s">
         <v>8</v>
       </c>
-      <c r="I16" t="s">
+      <c r="J16" t="s">
         <v>49</v>
       </c>
-      <c r="J16" t="s">
+      <c r="K16" t="s">
         <v>437</v>
       </c>
-      <c r="K16">
+      <c r="L16">
         <v>102796</v>
       </c>
-      <c r="L16">
+      <c r="M16">
         <v>200</v>
       </c>
-      <c r="M16">
+      <c r="N16">
         <v>0.170955095529009</v>
       </c>
-      <c r="N16">
+      <c r="O16">
         <v>17573.5</v>
       </c>
     </row>
-    <row r="17" spans="1:14">
+    <row r="17" spans="1:15">
       <c r="A17">
         <v>16</v>
       </c>
@@ -2730,32 +2800,35 @@
       <c r="F17" t="s">
         <v>48</v>
       </c>
-      <c r="G17" t="s">
-        <v>7</v>
+      <c r="G17" s="12">
+        <v>2007</v>
       </c>
       <c r="H17" t="s">
+        <v>7</v>
+      </c>
+      <c r="I17" t="s">
         <v>8</v>
       </c>
-      <c r="I17" t="s">
+      <c r="J17" t="s">
         <v>51</v>
       </c>
-      <c r="J17" t="s">
+      <c r="K17" t="s">
         <v>437</v>
       </c>
-      <c r="K17">
+      <c r="L17">
         <v>49200</v>
       </c>
-      <c r="L17">
+      <c r="M17">
         <v>191.666666666667</v>
       </c>
-      <c r="M17">
+      <c r="N17">
         <v>9.3665650406504097E-2</v>
       </c>
-      <c r="N17">
+      <c r="O17">
         <v>4608.3500000000004</v>
       </c>
     </row>
-    <row r="18" spans="1:14">
+    <row r="18" spans="1:15">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2774,32 +2847,35 @@
       <c r="F18" t="s">
         <v>44</v>
       </c>
-      <c r="G18" t="s">
-        <v>7</v>
+      <c r="G18" s="12">
+        <v>2008</v>
       </c>
       <c r="H18" t="s">
+        <v>7</v>
+      </c>
+      <c r="I18" t="s">
         <v>8</v>
       </c>
-      <c r="I18" t="s">
+      <c r="J18" t="s">
         <v>53</v>
       </c>
-      <c r="J18" t="s">
+      <c r="K18" t="s">
         <v>437</v>
       </c>
-      <c r="K18">
+      <c r="L18">
         <v>65096</v>
       </c>
-      <c r="L18">
+      <c r="M18">
         <v>186.666666666667</v>
       </c>
-      <c r="M18">
+      <c r="N18">
         <v>0.12122096595796999</v>
       </c>
-      <c r="N18">
+      <c r="O18">
         <v>7891</v>
       </c>
     </row>
-    <row r="19" spans="1:14">
+    <row r="19" spans="1:15">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2818,32 +2894,35 @@
       <c r="F19" t="s">
         <v>55</v>
       </c>
-      <c r="G19" t="s">
-        <v>7</v>
+      <c r="G19" s="12">
+        <v>2008</v>
       </c>
       <c r="H19" t="s">
+        <v>7</v>
+      </c>
+      <c r="I19" t="s">
         <v>8</v>
       </c>
-      <c r="I19" t="s">
+      <c r="J19" t="s">
         <v>56</v>
       </c>
-      <c r="J19" t="s">
+      <c r="K19" t="s">
         <v>449</v>
       </c>
-      <c r="K19">
+      <c r="L19">
         <v>56000</v>
       </c>
-      <c r="L19">
+      <c r="M19">
         <v>177.222222222222</v>
       </c>
-      <c r="M19">
+      <c r="N19">
         <v>8.2446428571428601E-2</v>
       </c>
-      <c r="N19">
+      <c r="O19">
         <v>4617</v>
       </c>
     </row>
-    <row r="20" spans="1:14">
+    <row r="20" spans="1:15">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2862,32 +2941,35 @@
       <c r="F20" t="s">
         <v>58</v>
       </c>
-      <c r="G20" t="s">
-        <v>7</v>
+      <c r="G20" s="12">
+        <v>2008</v>
       </c>
       <c r="H20" t="s">
+        <v>7</v>
+      </c>
+      <c r="I20" t="s">
         <v>8</v>
       </c>
-      <c r="I20" t="s">
+      <c r="J20" t="s">
         <v>59</v>
       </c>
-      <c r="J20" t="s">
+      <c r="K20" t="s">
         <v>437</v>
       </c>
-      <c r="K20">
+      <c r="L20">
         <v>177847</v>
       </c>
-      <c r="L20">
+      <c r="M20">
         <v>200</v>
       </c>
-      <c r="M20">
+      <c r="N20">
         <v>0.27326859604041698</v>
       </c>
-      <c r="N20">
+      <c r="O20">
         <v>48600</v>
       </c>
     </row>
-    <row r="21" spans="1:14">
+    <row r="21" spans="1:15">
       <c r="A21">
         <v>20</v>
       </c>
@@ -2906,32 +2988,35 @@
       <c r="F21" t="s">
         <v>61</v>
       </c>
-      <c r="G21" t="s">
-        <v>7</v>
+      <c r="G21" s="12">
+        <v>2009</v>
       </c>
       <c r="H21" t="s">
+        <v>7</v>
+      </c>
+      <c r="I21" t="s">
         <v>8</v>
       </c>
-      <c r="I21" t="s">
+      <c r="J21" t="s">
         <v>62</v>
       </c>
-      <c r="J21" t="s">
+      <c r="K21" t="s">
         <v>449</v>
       </c>
-      <c r="K21">
+      <c r="L21">
         <v>83000</v>
       </c>
-      <c r="L21">
+      <c r="M21">
         <v>185.138888888889</v>
       </c>
-      <c r="M21">
+      <c r="N21">
         <v>0.120481927710843</v>
       </c>
-      <c r="N21">
+      <c r="O21">
         <v>10000</v>
       </c>
     </row>
-    <row r="22" spans="1:14">
+    <row r="22" spans="1:15">
       <c r="A22">
         <v>21</v>
       </c>
@@ -2947,32 +3032,35 @@
       <c r="F22" t="s">
         <v>64</v>
       </c>
-      <c r="G22" t="s">
-        <v>7</v>
+      <c r="G22" s="12">
+        <v>2009</v>
       </c>
       <c r="H22" t="s">
+        <v>7</v>
+      </c>
+      <c r="I22" t="s">
         <v>8</v>
       </c>
-      <c r="I22" s="1" t="s">
+      <c r="J22" s="1" t="s">
         <v>488</v>
       </c>
-      <c r="J22" t="s">
+      <c r="K22" t="s">
         <v>437</v>
       </c>
-      <c r="K22">
+      <c r="L22">
         <v>26000</v>
       </c>
-      <c r="L22">
+      <c r="M22">
         <v>222.222222222222</v>
       </c>
-      <c r="M22">
+      <c r="N22">
         <v>3.8461538461538498E-2</v>
       </c>
-      <c r="N22">
+      <c r="O22">
         <v>1000</v>
       </c>
     </row>
-    <row r="23" spans="1:14">
+    <row r="23" spans="1:15">
       <c r="A23">
         <v>22</v>
       </c>
@@ -2988,32 +3076,35 @@
       <c r="E23" t="s">
         <v>23</v>
       </c>
-      <c r="G23" t="s">
-        <v>7</v>
+      <c r="G23" s="12">
+        <v>2009</v>
       </c>
       <c r="H23" t="s">
+        <v>7</v>
+      </c>
+      <c r="I23" t="s">
         <v>8</v>
       </c>
-      <c r="I23" t="s">
+      <c r="J23" t="s">
         <v>66</v>
       </c>
-      <c r="J23" t="s">
+      <c r="K23" t="s">
         <v>449</v>
       </c>
-      <c r="K23">
+      <c r="L23">
         <v>85887</v>
       </c>
-      <c r="L23">
+      <c r="M23">
         <v>193.75</v>
       </c>
-      <c r="M23">
+      <c r="N23">
         <v>0.21099817201672</v>
       </c>
-      <c r="N23">
+      <c r="O23">
         <v>18122</v>
       </c>
     </row>
-    <row r="24" spans="1:14">
+    <row r="24" spans="1:15">
       <c r="A24">
         <v>23</v>
       </c>
@@ -3029,32 +3120,35 @@
       <c r="E24" t="s">
         <v>23</v>
       </c>
-      <c r="G24" t="s">
-        <v>7</v>
+      <c r="G24" s="12">
+        <v>2009</v>
       </c>
       <c r="H24" t="s">
+        <v>7</v>
+      </c>
+      <c r="I24" t="s">
         <v>8</v>
       </c>
-      <c r="I24" t="s">
+      <c r="J24" t="s">
         <v>68</v>
       </c>
-      <c r="J24" t="s">
+      <c r="K24" t="s">
         <v>449</v>
       </c>
-      <c r="K24">
+      <c r="L24">
         <v>20000</v>
       </c>
-      <c r="L24">
+      <c r="M24">
         <v>163.611111111111</v>
       </c>
-      <c r="M24">
+      <c r="N24">
         <v>0.58565</v>
       </c>
-      <c r="N24">
+      <c r="O24">
         <v>11713</v>
       </c>
     </row>
-    <row r="25" spans="1:14">
+    <row r="25" spans="1:15">
       <c r="A25">
         <v>24</v>
       </c>
@@ -3073,32 +3167,35 @@
       <c r="F25" t="s">
         <v>70</v>
       </c>
-      <c r="G25" t="s">
-        <v>7</v>
+      <c r="G25" s="12">
+        <v>2011</v>
       </c>
       <c r="H25" t="s">
+        <v>7</v>
+      </c>
+      <c r="I25" t="s">
         <v>8</v>
       </c>
-      <c r="I25" t="s">
+      <c r="J25" t="s">
         <v>71</v>
       </c>
-      <c r="J25" t="s">
+      <c r="K25" t="s">
         <v>449</v>
       </c>
-      <c r="K25">
+      <c r="L25">
         <v>146385</v>
       </c>
-      <c r="L25">
+      <c r="M25">
         <v>236.805555555555</v>
       </c>
-      <c r="M25">
+      <c r="N25">
         <v>7.68931242955221E-2</v>
       </c>
-      <c r="N25">
+      <c r="O25">
         <v>11256</v>
       </c>
     </row>
-    <row r="26" spans="1:14">
+    <row r="26" spans="1:15">
       <c r="A26">
         <v>25</v>
       </c>
@@ -3117,32 +3214,35 @@
       <c r="F26" t="s">
         <v>73</v>
       </c>
-      <c r="G26" t="s">
-        <v>7</v>
+      <c r="G26" s="12">
+        <v>2011</v>
       </c>
       <c r="H26" t="s">
+        <v>7</v>
+      </c>
+      <c r="I26" t="s">
         <v>8</v>
       </c>
-      <c r="I26" t="s">
+      <c r="J26" t="s">
         <v>74</v>
       </c>
-      <c r="J26" t="s">
+      <c r="K26" t="s">
         <v>449</v>
       </c>
-      <c r="K26">
+      <c r="L26">
         <v>87000</v>
       </c>
-      <c r="L26">
+      <c r="M26">
         <v>208.333333333333</v>
       </c>
-      <c r="M26">
+      <c r="N26">
         <v>0.17591954022988501</v>
       </c>
-      <c r="N26">
+      <c r="O26">
         <v>15305</v>
       </c>
     </row>
-    <row r="27" spans="1:14">
+    <row r="27" spans="1:15">
       <c r="A27">
         <v>26</v>
       </c>
@@ -3161,32 +3261,35 @@
       <c r="F27" t="s">
         <v>76</v>
       </c>
-      <c r="G27" t="s">
-        <v>7</v>
+      <c r="G27" s="12">
+        <v>2013</v>
       </c>
       <c r="H27" t="s">
+        <v>7</v>
+      </c>
+      <c r="I27" t="s">
         <v>8</v>
       </c>
-      <c r="I27" t="s">
+      <c r="J27" t="s">
         <v>77</v>
       </c>
-      <c r="J27" t="s">
+      <c r="K27" t="s">
         <v>449</v>
       </c>
-      <c r="K27">
+      <c r="L27">
         <v>147166.79999999999</v>
       </c>
-      <c r="L27">
+      <c r="M27">
         <v>237.638888888889</v>
       </c>
-      <c r="M27">
+      <c r="N27">
         <v>0.139997608156187</v>
       </c>
-      <c r="N27">
+      <c r="O27">
         <v>20603</v>
       </c>
     </row>
-    <row r="28" spans="1:14">
+    <row r="28" spans="1:15">
       <c r="A28">
         <v>27</v>
       </c>
@@ -3205,32 +3308,35 @@
       <c r="F28" t="s">
         <v>79</v>
       </c>
-      <c r="G28" t="s">
-        <v>7</v>
+      <c r="G28" s="12">
+        <v>2014</v>
       </c>
       <c r="H28" t="s">
+        <v>7</v>
+      </c>
+      <c r="I28" t="s">
         <v>8</v>
       </c>
-      <c r="I28" t="s">
+      <c r="J28" t="s">
         <v>80</v>
       </c>
-      <c r="J28" t="s">
+      <c r="K28" t="s">
         <v>449</v>
       </c>
-      <c r="K28">
+      <c r="L28">
         <v>46063</v>
       </c>
-      <c r="L28">
+      <c r="M28">
         <v>160</v>
       </c>
-      <c r="M28">
+      <c r="N28">
         <v>9.1418274971235003E-2</v>
       </c>
-      <c r="N28">
+      <c r="O28">
         <v>4211</v>
       </c>
     </row>
-    <row r="29" spans="1:14">
+    <row r="29" spans="1:15">
       <c r="A29">
         <v>28</v>
       </c>
@@ -3249,32 +3355,35 @@
       <c r="F29" t="s">
         <v>82</v>
       </c>
-      <c r="G29" t="s">
-        <v>7</v>
+      <c r="G29" s="12">
+        <v>2017</v>
       </c>
       <c r="H29" t="s">
+        <v>7</v>
+      </c>
+      <c r="I29" t="s">
         <v>8</v>
       </c>
-      <c r="I29" t="s">
+      <c r="J29" t="s">
         <v>83</v>
       </c>
-      <c r="J29" t="s">
+      <c r="K29" t="s">
         <v>437</v>
       </c>
-      <c r="K29">
+      <c r="L29">
         <v>47261</v>
       </c>
-      <c r="L29">
+      <c r="M29">
         <v>241.666666666667</v>
       </c>
-      <c r="M29">
+      <c r="N29">
         <v>0.23315566746365901</v>
       </c>
-      <c r="N29">
+      <c r="O29">
         <v>11019.17</v>
       </c>
     </row>
-    <row r="30" spans="1:14">
+    <row r="30" spans="1:15">
       <c r="A30">
         <v>29</v>
       </c>
@@ -3293,32 +3402,35 @@
       <c r="F30" t="s">
         <v>84</v>
       </c>
-      <c r="G30" t="s">
-        <v>7</v>
-      </c>
-      <c r="H30" s="2" t="s">
+      <c r="G30" s="12">
+        <v>2019</v>
+      </c>
+      <c r="H30" t="s">
+        <v>7</v>
+      </c>
+      <c r="I30" s="2" t="s">
         <v>453</v>
       </c>
-      <c r="I30" s="2" t="s">
+      <c r="J30" s="2" t="s">
         <v>455</v>
       </c>
-      <c r="J30" t="s">
+      <c r="K30" t="s">
         <v>449</v>
       </c>
-      <c r="K30">
+      <c r="L30">
         <v>119000</v>
       </c>
-      <c r="L30">
+      <c r="M30">
         <v>333.33333333333297</v>
       </c>
-      <c r="M30">
+      <c r="N30">
         <v>0.15546218487395</v>
       </c>
-      <c r="N30">
+      <c r="O30">
         <v>18500</v>
       </c>
     </row>
-    <row r="31" spans="1:14">
+    <row r="31" spans="1:15">
       <c r="A31">
         <v>30</v>
       </c>
@@ -3334,32 +3446,35 @@
       <c r="F31" t="s">
         <v>87</v>
       </c>
-      <c r="G31" t="s">
-        <v>7</v>
+      <c r="G31" s="12">
+        <v>2019</v>
       </c>
       <c r="H31" t="s">
+        <v>7</v>
+      </c>
+      <c r="I31" t="s">
         <v>8</v>
       </c>
-      <c r="I31" s="1" t="s">
+      <c r="J31" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="J31" t="s">
+      <c r="K31" t="s">
         <v>437</v>
       </c>
-      <c r="K31">
+      <c r="L31">
         <v>47000</v>
       </c>
-      <c r="L31">
+      <c r="M31">
         <v>330.55555555555497</v>
       </c>
-      <c r="M31">
+      <c r="N31">
         <v>0.125228723404255</v>
       </c>
-      <c r="N31">
+      <c r="O31">
         <v>5885.75</v>
       </c>
     </row>
-    <row r="32" spans="1:14">
+    <row r="32" spans="1:15">
       <c r="A32">
         <v>31</v>
       </c>
@@ -3378,32 +3493,35 @@
       <c r="F32" t="s">
         <v>87</v>
       </c>
-      <c r="G32" t="s">
-        <v>7</v>
+      <c r="G32" s="12">
+        <v>2019</v>
       </c>
       <c r="H32" t="s">
+        <v>7</v>
+      </c>
+      <c r="I32" t="s">
         <v>8</v>
       </c>
-      <c r="I32" t="s">
+      <c r="J32" t="s">
         <v>89</v>
       </c>
-      <c r="J32" t="s">
+      <c r="K32" t="s">
         <v>437</v>
       </c>
-      <c r="K32">
+      <c r="L32">
         <v>186000</v>
       </c>
-      <c r="L32">
+      <c r="M32">
         <v>258.33333333333297</v>
       </c>
-      <c r="M32">
+      <c r="N32">
         <v>9.6774193548387094E-2</v>
       </c>
-      <c r="N32">
+      <c r="O32">
         <v>18000</v>
       </c>
     </row>
-    <row r="33" spans="1:14">
+    <row r="33" spans="1:15">
       <c r="A33">
         <v>32</v>
       </c>
@@ -3416,32 +3534,35 @@
       <c r="D33" t="s">
         <v>5</v>
       </c>
-      <c r="G33" t="s">
-        <v>7</v>
+      <c r="G33" s="12">
+        <v>2019</v>
       </c>
       <c r="H33" t="s">
+        <v>7</v>
+      </c>
+      <c r="I33" t="s">
         <v>8</v>
       </c>
-      <c r="I33" t="s">
+      <c r="J33" t="s">
         <v>91</v>
       </c>
-      <c r="J33" t="s">
+      <c r="K33" t="s">
         <v>449</v>
       </c>
-      <c r="K33">
+      <c r="L33">
         <v>40800</v>
       </c>
-      <c r="L33">
+      <c r="M33">
         <v>194.555555555555</v>
       </c>
-      <c r="M33">
+      <c r="N33">
         <v>0.49509803921568601</v>
       </c>
-      <c r="N33">
+      <c r="O33">
         <v>20200</v>
       </c>
     </row>
-    <row r="34" spans="1:14">
+    <row r="34" spans="1:15">
       <c r="A34">
         <v>33</v>
       </c>
@@ -3457,32 +3578,35 @@
       <c r="F34" t="s">
         <v>93</v>
       </c>
-      <c r="G34" t="s">
-        <v>7</v>
+      <c r="G34" s="12">
+        <v>2019</v>
       </c>
       <c r="H34" t="s">
+        <v>7</v>
+      </c>
+      <c r="I34" t="s">
         <v>8</v>
       </c>
-      <c r="I34" s="1" t="s">
+      <c r="J34" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="J34" t="s">
+      <c r="K34" t="s">
         <v>449</v>
       </c>
-      <c r="K34">
+      <c r="L34">
         <v>55200</v>
       </c>
-      <c r="L34">
+      <c r="M34">
         <v>198.055555555555</v>
       </c>
-      <c r="M34">
+      <c r="N34">
         <v>0.94927536231884102</v>
       </c>
-      <c r="N34">
+      <c r="O34">
         <v>52400</v>
       </c>
     </row>
-    <row r="35" spans="1:14">
+    <row r="35" spans="1:15">
       <c r="A35">
         <v>34</v>
       </c>
@@ -3501,32 +3625,35 @@
       <c r="F35" t="s">
         <v>93</v>
       </c>
-      <c r="G35" t="s">
-        <v>7</v>
+      <c r="G35" s="12">
+        <v>2019</v>
       </c>
       <c r="H35" t="s">
+        <v>7</v>
+      </c>
+      <c r="I35" t="s">
         <v>8</v>
       </c>
-      <c r="I35" t="s">
+      <c r="J35" t="s">
         <v>95</v>
       </c>
-      <c r="J35" t="s">
+      <c r="K35" t="s">
         <v>437</v>
       </c>
-      <c r="K35">
+      <c r="L35">
         <v>350000</v>
       </c>
-      <c r="L35">
+      <c r="M35">
         <v>462.777777777778</v>
       </c>
-      <c r="M35">
+      <c r="N35">
         <v>6.27571428571429E-2</v>
       </c>
-      <c r="N35">
+      <c r="O35">
         <v>21965</v>
       </c>
     </row>
-    <row r="36" spans="1:14">
+    <row r="36" spans="1:15">
       <c r="A36">
         <v>35</v>
       </c>
@@ -3542,32 +3669,35 @@
       <c r="E36" t="s">
         <v>23</v>
       </c>
-      <c r="G36" t="s">
-        <v>7</v>
+      <c r="G36" s="12">
+        <v>2020</v>
       </c>
       <c r="H36" t="s">
+        <v>7</v>
+      </c>
+      <c r="I36" t="s">
         <v>8</v>
       </c>
-      <c r="I36" s="1" t="s">
+      <c r="J36" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="J36" t="s">
+      <c r="K36" t="s">
         <v>449</v>
       </c>
-      <c r="K36">
+      <c r="L36">
         <v>65000</v>
       </c>
-      <c r="L36">
+      <c r="M36">
         <v>191.666666666667</v>
       </c>
-      <c r="M36">
+      <c r="N36">
         <v>0.31316923076923098</v>
       </c>
-      <c r="N36">
+      <c r="O36">
         <v>20356</v>
       </c>
     </row>
-    <row r="37" spans="1:14">
+    <row r="37" spans="1:15">
       <c r="A37">
         <v>36</v>
       </c>
@@ -3583,32 +3713,35 @@
       <c r="E37" t="s">
         <v>23</v>
       </c>
-      <c r="G37" t="s">
-        <v>7</v>
+      <c r="G37" s="12">
+        <v>2020</v>
       </c>
       <c r="H37" t="s">
+        <v>7</v>
+      </c>
+      <c r="I37" t="s">
         <v>8</v>
       </c>
-      <c r="I37" t="s">
+      <c r="J37" t="s">
         <v>486</v>
       </c>
-      <c r="J37" t="s">
+      <c r="K37" t="s">
         <v>449</v>
       </c>
-      <c r="K37">
+      <c r="L37">
         <v>35000</v>
       </c>
-      <c r="L37">
+      <c r="M37">
         <v>208.333333333333</v>
       </c>
-      <c r="M37">
+      <c r="N37">
         <v>0.23714285714285699</v>
       </c>
-      <c r="N37">
+      <c r="O37">
         <v>8300</v>
       </c>
     </row>
-    <row r="38" spans="1:14">
+    <row r="38" spans="1:15">
       <c r="A38">
         <v>37</v>
       </c>
@@ -3624,32 +3757,35 @@
       <c r="E38" t="s">
         <v>23</v>
       </c>
-      <c r="G38" t="s">
-        <v>7</v>
+      <c r="G38" s="12">
+        <v>2010</v>
       </c>
       <c r="H38" t="s">
+        <v>7</v>
+      </c>
+      <c r="I38" t="s">
         <v>8</v>
       </c>
-      <c r="I38" t="s">
+      <c r="J38" t="s">
         <v>99</v>
       </c>
-      <c r="J38" t="s">
+      <c r="K38" t="s">
         <v>437</v>
       </c>
-      <c r="K38">
+      <c r="L38">
         <v>47000</v>
       </c>
-      <c r="L38">
+      <c r="M38">
         <v>157.5</v>
       </c>
-      <c r="M38">
+      <c r="N38">
         <v>5.7446808510638298E-2</v>
       </c>
-      <c r="N38">
+      <c r="O38">
         <v>2700</v>
       </c>
     </row>
-    <row r="39" spans="1:14">
+    <row r="39" spans="1:15">
       <c r="A39">
         <v>38</v>
       </c>
@@ -3668,32 +3804,35 @@
       <c r="F39" t="s">
         <v>101</v>
       </c>
-      <c r="G39" t="s">
-        <v>7</v>
+      <c r="G39" s="12">
+        <v>2021</v>
       </c>
       <c r="H39" t="s">
+        <v>7</v>
+      </c>
+      <c r="I39" t="s">
         <v>8</v>
       </c>
-      <c r="I39" t="s">
+      <c r="J39" t="s">
         <v>102</v>
       </c>
-      <c r="J39" t="s">
+      <c r="K39" t="s">
         <v>437</v>
       </c>
-      <c r="K39">
+      <c r="L39">
         <v>120000</v>
       </c>
-      <c r="L39">
+      <c r="M39">
         <v>241.666666666667</v>
       </c>
-      <c r="M39">
+      <c r="N39">
         <v>0.03</v>
       </c>
-      <c r="N39">
+      <c r="O39">
         <v>3600</v>
       </c>
     </row>
-    <row r="40" spans="1:14">
+    <row r="40" spans="1:15">
       <c r="A40">
         <v>39</v>
       </c>
@@ -3709,32 +3848,35 @@
       <c r="F40">
         <v>2021</v>
       </c>
-      <c r="G40" t="s">
-        <v>7</v>
+      <c r="G40" s="12">
+        <v>2021</v>
       </c>
       <c r="H40" t="s">
+        <v>7</v>
+      </c>
+      <c r="I40" t="s">
         <v>8</v>
       </c>
-      <c r="I40" t="s">
+      <c r="J40" t="s">
         <v>104</v>
       </c>
-      <c r="J40" t="s">
+      <c r="K40" t="s">
         <v>449</v>
       </c>
-      <c r="K40">
+      <c r="L40">
         <v>83000</v>
       </c>
-      <c r="L40">
+      <c r="M40">
         <v>122.777777777778</v>
       </c>
-      <c r="M40">
+      <c r="N40">
         <v>0.219493975903614</v>
       </c>
-      <c r="N40">
+      <c r="O40">
         <v>18218</v>
       </c>
     </row>
-    <row r="41" spans="1:14">
+    <row r="41" spans="1:15">
       <c r="A41">
         <v>40</v>
       </c>
@@ -3750,32 +3892,35 @@
       <c r="E41" t="s">
         <v>16</v>
       </c>
-      <c r="G41" t="s">
-        <v>7</v>
+      <c r="G41" s="12">
+        <v>2021</v>
       </c>
       <c r="H41" t="s">
+        <v>7</v>
+      </c>
+      <c r="I41" t="s">
         <v>8</v>
       </c>
-      <c r="I41" t="s">
+      <c r="J41" t="s">
         <v>106</v>
       </c>
-      <c r="J41" t="s">
+      <c r="K41" t="s">
         <v>437</v>
       </c>
-      <c r="K41">
+      <c r="L41">
         <v>66030</v>
       </c>
-      <c r="L41">
+      <c r="M41">
         <v>284.16666666666703</v>
       </c>
-      <c r="M41">
+      <c r="N41">
         <v>0.14162153566560701</v>
       </c>
-      <c r="N41">
+      <c r="O41">
         <v>9351.27</v>
       </c>
     </row>
-    <row r="42" spans="1:14">
+    <row r="42" spans="1:15">
       <c r="A42">
         <v>41</v>
       </c>
@@ -3788,32 +3933,38 @@
       <c r="D42" t="s">
         <v>5</v>
       </c>
-      <c r="G42" t="s">
-        <v>7</v>
+      <c r="E42" t="s">
+        <v>23</v>
+      </c>
+      <c r="G42" s="12">
+        <v>2009</v>
       </c>
       <c r="H42" t="s">
+        <v>7</v>
+      </c>
+      <c r="I42" t="s">
         <v>8</v>
       </c>
-      <c r="I42" t="s">
+      <c r="J42" t="s">
         <v>108</v>
       </c>
-      <c r="J42" t="s">
+      <c r="K42" t="s">
         <v>437</v>
       </c>
-      <c r="K42">
+      <c r="L42">
         <v>40000</v>
       </c>
-      <c r="L42">
+      <c r="M42">
         <v>186.666666666667</v>
       </c>
-      <c r="M42">
+      <c r="N42">
         <v>0.06</v>
       </c>
-      <c r="N42">
+      <c r="O42">
         <v>2400</v>
       </c>
     </row>
-    <row r="43" spans="1:14">
+    <row r="43" spans="1:15">
       <c r="A43">
         <v>42</v>
       </c>
@@ -3832,32 +3983,35 @@
       <c r="F43" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="G43" t="s">
-        <v>7</v>
+      <c r="G43" s="12">
+        <v>1996</v>
       </c>
       <c r="H43" t="s">
+        <v>7</v>
+      </c>
+      <c r="I43" t="s">
         <v>112</v>
       </c>
-      <c r="I43" t="s">
+      <c r="J43" t="s">
         <v>113</v>
       </c>
-      <c r="J43" t="s">
+      <c r="K43" t="s">
         <v>449</v>
       </c>
-      <c r="K43">
+      <c r="L43">
         <v>40000</v>
       </c>
-      <c r="L43">
+      <c r="M43">
         <v>178.75</v>
       </c>
-      <c r="M43">
+      <c r="N43">
         <v>0.108875</v>
       </c>
-      <c r="N43">
+      <c r="O43">
         <v>4355</v>
       </c>
     </row>
-    <row r="44" spans="1:14">
+    <row r="44" spans="1:15">
       <c r="A44">
         <v>43</v>
       </c>
@@ -3873,32 +4027,35 @@
       <c r="F44" t="s">
         <v>115</v>
       </c>
-      <c r="G44" t="s">
-        <v>7</v>
+      <c r="G44" s="12">
+        <v>1999</v>
       </c>
       <c r="H44" t="s">
+        <v>7</v>
+      </c>
+      <c r="I44" t="s">
         <v>112</v>
       </c>
-      <c r="I44" t="s">
+      <c r="J44" t="s">
         <v>116</v>
       </c>
-      <c r="J44" t="s">
+      <c r="K44" t="s">
         <v>449</v>
       </c>
-      <c r="K44">
+      <c r="L44">
         <v>54100</v>
       </c>
-      <c r="L44">
+      <c r="M44">
         <v>198.055555555555</v>
       </c>
-      <c r="M44">
+      <c r="N44">
         <v>0.209593345656192</v>
       </c>
-      <c r="N44">
+      <c r="O44">
         <v>11339</v>
       </c>
     </row>
-    <row r="45" spans="1:14">
+    <row r="45" spans="1:15">
       <c r="A45">
         <v>44</v>
       </c>
@@ -3917,32 +4074,35 @@
       <c r="F45" t="s">
         <v>118</v>
       </c>
-      <c r="G45" t="s">
-        <v>7</v>
+      <c r="G45" s="12">
+        <v>2000</v>
       </c>
       <c r="H45" t="s">
+        <v>7</v>
+      </c>
+      <c r="I45" t="s">
         <v>112</v>
       </c>
-      <c r="I45" s="1" t="s">
-        <v>494</v>
-      </c>
-      <c r="J45" t="s">
+      <c r="J45" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="K45" t="s">
         <v>449</v>
       </c>
-      <c r="K45">
+      <c r="L45">
         <v>100000</v>
       </c>
-      <c r="L45">
+      <c r="M45">
         <v>222.222222222222</v>
       </c>
-      <c r="M45">
+      <c r="N45">
         <v>0.1</v>
       </c>
-      <c r="N45">
+      <c r="O45">
         <v>10000</v>
       </c>
     </row>
-    <row r="46" spans="1:14">
+    <row r="46" spans="1:15">
       <c r="A46">
         <v>45</v>
       </c>
@@ -3961,32 +4121,35 @@
       <c r="F46" t="s">
         <v>120</v>
       </c>
-      <c r="G46" t="s">
-        <v>7</v>
+      <c r="G46" s="12">
+        <v>2001</v>
       </c>
       <c r="H46" t="s">
+        <v>7</v>
+      </c>
+      <c r="I46" t="s">
         <v>112</v>
       </c>
-      <c r="I46" s="1" t="s">
-        <v>495</v>
-      </c>
-      <c r="J46" t="s">
+      <c r="J46" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="K46" t="s">
         <v>449</v>
       </c>
-      <c r="K46">
+      <c r="L46">
         <v>150000</v>
       </c>
-      <c r="L46">
+      <c r="M46">
         <v>229.166666666667</v>
       </c>
-      <c r="M46">
+      <c r="N46">
         <v>0.05</v>
       </c>
-      <c r="N46">
+      <c r="O46">
         <v>7500</v>
       </c>
     </row>
-    <row r="47" spans="1:14">
+    <row r="47" spans="1:15">
       <c r="A47">
         <v>46</v>
       </c>
@@ -4005,32 +4168,35 @@
       <c r="F47" t="s">
         <v>122</v>
       </c>
-      <c r="G47" t="s">
-        <v>7</v>
+      <c r="G47" s="12">
+        <v>2002</v>
       </c>
       <c r="H47" t="s">
+        <v>7</v>
+      </c>
+      <c r="I47" t="s">
         <v>112</v>
       </c>
-      <c r="I47" s="1" t="s">
-        <v>496</v>
-      </c>
-      <c r="J47" t="s">
+      <c r="J47" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="K47" t="s">
         <v>449</v>
       </c>
-      <c r="K47">
+      <c r="L47">
         <v>50000</v>
       </c>
-      <c r="L47">
+      <c r="M47">
         <v>231.111111111111</v>
       </c>
-      <c r="M47">
+      <c r="N47">
         <v>0.02</v>
       </c>
-      <c r="N47">
+      <c r="O47">
         <v>1000</v>
       </c>
     </row>
-    <row r="48" spans="1:14">
+    <row r="48" spans="1:15">
       <c r="A48">
         <v>47</v>
       </c>
@@ -4049,32 +4215,35 @@
       <c r="F48" t="s">
         <v>124</v>
       </c>
-      <c r="G48" t="s">
-        <v>7</v>
+      <c r="G48" s="12">
+        <v>2005</v>
       </c>
       <c r="H48" t="s">
+        <v>7</v>
+      </c>
+      <c r="I48" t="s">
         <v>112</v>
       </c>
-      <c r="I48" t="s">
+      <c r="J48" t="s">
         <v>125</v>
       </c>
-      <c r="J48" t="s">
+      <c r="K48" t="s">
         <v>450</v>
       </c>
-      <c r="K48">
+      <c r="L48">
         <v>43000</v>
       </c>
-      <c r="L48">
+      <c r="M48">
         <v>150</v>
       </c>
-      <c r="M48">
+      <c r="N48">
         <v>0.379411395348837</v>
       </c>
-      <c r="N48">
+      <c r="O48">
         <v>16314.69</v>
       </c>
     </row>
-    <row r="49" spans="1:14">
+    <row r="49" spans="1:15">
       <c r="A49">
         <v>48</v>
       </c>
@@ -4090,32 +4259,35 @@
       <c r="F49" t="s">
         <v>127</v>
       </c>
-      <c r="G49" t="s">
-        <v>7</v>
+      <c r="G49" s="12">
+        <v>2006</v>
       </c>
       <c r="H49" t="s">
+        <v>7</v>
+      </c>
+      <c r="I49" t="s">
         <v>112</v>
       </c>
-      <c r="I49" t="s">
+      <c r="J49" t="s">
         <v>128</v>
       </c>
-      <c r="J49" t="s">
+      <c r="K49" t="s">
         <v>450</v>
       </c>
-      <c r="K49">
+      <c r="L49">
         <v>65000</v>
       </c>
-      <c r="L49">
+      <c r="M49">
         <v>255</v>
       </c>
-      <c r="M49">
+      <c r="N49">
         <v>9.8461538461538503E-2</v>
       </c>
-      <c r="N49">
+      <c r="O49">
         <v>6400</v>
       </c>
     </row>
-    <row r="50" spans="1:14">
+    <row r="50" spans="1:15">
       <c r="A50">
         <v>49</v>
       </c>
@@ -4134,32 +4306,35 @@
       <c r="F50" t="s">
         <v>44</v>
       </c>
-      <c r="G50" t="s">
-        <v>7</v>
+      <c r="G50" s="12">
+        <v>2008</v>
       </c>
       <c r="H50" t="s">
+        <v>7</v>
+      </c>
+      <c r="I50" t="s">
         <v>112</v>
       </c>
-      <c r="I50" t="s">
+      <c r="J50" t="s">
         <v>131</v>
       </c>
-      <c r="J50" t="s">
+      <c r="K50" t="s">
         <v>450</v>
       </c>
-      <c r="K50">
+      <c r="L50">
         <v>56000</v>
       </c>
-      <c r="L50">
+      <c r="M50">
         <v>311.66666666666703</v>
-      </c>
-      <c r="M50">
-        <v>0</v>
       </c>
       <c r="N50">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="1:14">
+      <c r="O50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15">
       <c r="A51">
         <v>50</v>
       </c>
@@ -4175,32 +4350,35 @@
       <c r="F51" t="s">
         <v>58</v>
       </c>
-      <c r="G51" t="s">
-        <v>7</v>
+      <c r="G51" s="12">
+        <v>2008</v>
       </c>
       <c r="H51" t="s">
+        <v>7</v>
+      </c>
+      <c r="I51" t="s">
         <v>112</v>
       </c>
-      <c r="I51" t="s">
+      <c r="J51" t="s">
         <v>133</v>
       </c>
-      <c r="J51" t="s">
+      <c r="K51" t="s">
         <v>450</v>
       </c>
-      <c r="K51">
+      <c r="L51">
         <v>160000</v>
       </c>
-      <c r="L51">
+      <c r="M51">
         <v>198.055555555555</v>
       </c>
-      <c r="M51">
+      <c r="N51">
         <v>0.48831249999999998</v>
       </c>
-      <c r="N51">
+      <c r="O51">
         <v>78130</v>
       </c>
     </row>
-    <row r="52" spans="1:14">
+    <row r="52" spans="1:15">
       <c r="A52">
         <v>51</v>
       </c>
@@ -4216,32 +4394,35 @@
       <c r="F52" t="s">
         <v>4</v>
       </c>
-      <c r="G52" t="s">
-        <v>7</v>
+      <c r="G52" s="12">
+        <v>2008</v>
       </c>
       <c r="H52" t="s">
+        <v>7</v>
+      </c>
+      <c r="I52" t="s">
         <v>112</v>
       </c>
-      <c r="I52" t="s">
+      <c r="J52" t="s">
         <v>135</v>
       </c>
-      <c r="J52" t="s">
+      <c r="K52" t="s">
         <v>450</v>
       </c>
-      <c r="K52">
+      <c r="L52">
         <v>33000</v>
       </c>
-      <c r="L52">
+      <c r="M52">
         <v>175</v>
       </c>
-      <c r="M52">
+      <c r="N52">
         <v>0.42424242424242398</v>
       </c>
-      <c r="N52">
+      <c r="O52">
         <v>14000</v>
       </c>
     </row>
-    <row r="53" spans="1:14">
+    <row r="53" spans="1:15">
       <c r="A53">
         <v>52</v>
       </c>
@@ -4260,32 +4441,35 @@
       <c r="F53" t="s">
         <v>137</v>
       </c>
-      <c r="G53" t="s">
-        <v>7</v>
+      <c r="G53" s="12">
+        <v>2009</v>
       </c>
       <c r="H53" t="s">
+        <v>7</v>
+      </c>
+      <c r="I53" t="s">
         <v>112</v>
       </c>
-      <c r="I53" t="s">
+      <c r="J53" t="s">
         <v>138</v>
       </c>
-      <c r="J53" t="s">
+      <c r="K53" t="s">
         <v>450</v>
       </c>
-      <c r="K53">
+      <c r="L53">
         <v>41318</v>
       </c>
-      <c r="L53">
+      <c r="M53">
         <v>186.666666666667</v>
       </c>
-      <c r="M53">
+      <c r="N53">
         <v>0.148885715668716</v>
       </c>
-      <c r="N53">
+      <c r="O53">
         <v>6151.66</v>
       </c>
     </row>
-    <row r="54" spans="1:14">
+    <row r="54" spans="1:15">
       <c r="A54">
         <v>53</v>
       </c>
@@ -4301,32 +4485,35 @@
       <c r="F54" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="G54" t="s">
-        <v>7</v>
+      <c r="G54" s="12">
+        <v>2007</v>
       </c>
       <c r="H54" t="s">
+        <v>7</v>
+      </c>
+      <c r="I54" t="s">
         <v>112</v>
       </c>
-      <c r="I54" t="s">
+      <c r="J54" t="s">
         <v>140</v>
       </c>
-      <c r="J54" t="s">
+      <c r="K54" t="s">
         <v>449</v>
       </c>
-      <c r="K54">
+      <c r="L54">
         <v>34131</v>
       </c>
-      <c r="L54">
+      <c r="M54">
         <v>175</v>
       </c>
-      <c r="M54">
+      <c r="N54">
         <v>0.61237584600509798</v>
       </c>
-      <c r="N54">
+      <c r="O54">
         <v>20901</v>
       </c>
     </row>
-    <row r="55" spans="1:14">
+    <row r="55" spans="1:15">
       <c r="A55">
         <v>54</v>
       </c>
@@ -4339,35 +4526,41 @@
       <c r="D55" t="s">
         <v>5</v>
       </c>
+      <c r="E55" t="s">
+        <v>16</v>
+      </c>
       <c r="F55" t="s">
         <v>142</v>
       </c>
-      <c r="G55" t="s">
-        <v>7</v>
+      <c r="G55" s="12">
+        <v>2016</v>
       </c>
       <c r="H55" t="s">
+        <v>7</v>
+      </c>
+      <c r="I55" t="s">
         <v>112</v>
       </c>
-      <c r="I55" t="s">
+      <c r="J55" t="s">
         <v>143</v>
       </c>
-      <c r="J55" t="s">
+      <c r="K55" t="s">
         <v>449</v>
       </c>
-      <c r="K55">
+      <c r="L55">
         <v>48000</v>
       </c>
-      <c r="L55">
+      <c r="M55">
         <v>175</v>
       </c>
-      <c r="M55">
+      <c r="N55">
         <v>0.26214583333333302</v>
       </c>
-      <c r="N55">
+      <c r="O55">
         <v>12583</v>
       </c>
     </row>
-    <row r="56" spans="1:14">
+    <row r="56" spans="1:15">
       <c r="A56">
         <v>55</v>
       </c>
@@ -4380,35 +4573,41 @@
       <c r="D56" t="s">
         <v>5</v>
       </c>
+      <c r="E56" t="s">
+        <v>16</v>
+      </c>
       <c r="F56">
         <v>2017</v>
       </c>
-      <c r="G56" t="s">
-        <v>7</v>
+      <c r="G56" s="12">
+        <v>2017</v>
       </c>
       <c r="H56" t="s">
+        <v>7</v>
+      </c>
+      <c r="I56" t="s">
         <v>112</v>
       </c>
-      <c r="I56" s="1" t="s">
+      <c r="J56" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="J56" t="s">
+      <c r="K56" t="s">
         <v>449</v>
       </c>
-      <c r="K56">
+      <c r="L56">
         <v>16000</v>
       </c>
-      <c r="L56">
+      <c r="M56">
         <v>197.083333333333</v>
       </c>
-      <c r="M56">
+      <c r="N56">
         <v>0.25131249999999999</v>
       </c>
-      <c r="N56">
+      <c r="O56">
         <v>4021</v>
       </c>
     </row>
-    <row r="57" spans="1:14">
+    <row r="57" spans="1:15">
       <c r="A57">
         <v>56</v>
       </c>
@@ -4427,32 +4626,35 @@
       <c r="F57" t="s">
         <v>146</v>
       </c>
-      <c r="G57" t="s">
-        <v>7</v>
+      <c r="G57" s="12">
+        <v>2017</v>
       </c>
       <c r="H57" t="s">
+        <v>7</v>
+      </c>
+      <c r="I57" t="s">
         <v>112</v>
       </c>
-      <c r="I57" t="s">
+      <c r="J57" t="s">
         <v>147</v>
       </c>
-      <c r="J57" t="s">
+      <c r="K57" t="s">
         <v>450</v>
       </c>
-      <c r="K57">
+      <c r="L57">
         <v>30000</v>
       </c>
-      <c r="L57">
+      <c r="M57">
         <v>145</v>
       </c>
-      <c r="M57">
+      <c r="N57">
         <v>0.242352333333333</v>
       </c>
-      <c r="N57">
+      <c r="O57">
         <v>7270.57</v>
       </c>
     </row>
-    <row r="58" spans="1:14">
+    <row r="58" spans="1:15">
       <c r="A58">
         <v>57</v>
       </c>
@@ -4471,32 +4673,35 @@
       <c r="F58" t="s">
         <v>149</v>
       </c>
-      <c r="G58" t="s">
-        <v>7</v>
+      <c r="G58" s="12">
+        <v>2018</v>
       </c>
       <c r="H58" t="s">
+        <v>7</v>
+      </c>
+      <c r="I58" t="s">
         <v>112</v>
       </c>
-      <c r="I58" t="s">
+      <c r="J58" t="s">
         <v>150</v>
       </c>
-      <c r="J58" t="s">
+      <c r="K58" t="s">
         <v>450</v>
       </c>
-      <c r="K58">
+      <c r="L58">
         <v>56000</v>
       </c>
-      <c r="L58">
+      <c r="M58">
         <v>145</v>
       </c>
-      <c r="M58">
+      <c r="N58">
         <v>0.37934464285714298</v>
       </c>
-      <c r="N58">
+      <c r="O58">
         <v>21243.3</v>
       </c>
     </row>
-    <row r="59" spans="1:14">
+    <row r="59" spans="1:15">
       <c r="A59">
         <v>58</v>
       </c>
@@ -4515,32 +4720,35 @@
       <c r="F59" t="s">
         <v>152</v>
       </c>
-      <c r="G59" t="s">
-        <v>7</v>
+      <c r="G59" s="12">
+        <v>2018</v>
       </c>
       <c r="H59" t="s">
+        <v>7</v>
+      </c>
+      <c r="I59" t="s">
         <v>112</v>
       </c>
-      <c r="I59" t="s">
+      <c r="J59" t="s">
         <v>153</v>
       </c>
-      <c r="J59" t="s">
+      <c r="K59" t="s">
         <v>449</v>
       </c>
-      <c r="K59">
+      <c r="L59">
         <v>43000</v>
       </c>
-      <c r="L59">
+      <c r="M59">
         <v>261.25</v>
       </c>
-      <c r="M59">
+      <c r="N59">
         <v>8.6837209302325594E-2</v>
       </c>
-      <c r="N59">
+      <c r="O59">
         <v>3734</v>
       </c>
     </row>
-    <row r="60" spans="1:14">
+    <row r="60" spans="1:15">
       <c r="A60">
         <v>59</v>
       </c>
@@ -4557,31 +4765,34 @@
         <v>16</v>
       </c>
       <c r="G60" t="s">
-        <v>7</v>
+        <v>508</v>
       </c>
       <c r="H60" t="s">
+        <v>7</v>
+      </c>
+      <c r="I60" t="s">
         <v>8</v>
       </c>
-      <c r="I60" s="1" t="s">
+      <c r="J60" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J60" t="s">
+      <c r="K60" t="s">
         <v>450</v>
       </c>
-      <c r="K60">
+      <c r="L60">
         <v>110000</v>
       </c>
-      <c r="L60">
+      <c r="M60">
         <v>240</v>
       </c>
-      <c r="M60">
+      <c r="N60">
         <v>2.7453545454545401E-2</v>
       </c>
-      <c r="N60">
+      <c r="O60">
         <v>3019.89</v>
       </c>
     </row>
-    <row r="61" spans="1:14">
+    <row r="61" spans="1:15">
       <c r="A61">
         <v>60</v>
       </c>
@@ -4595,31 +4806,34 @@
         <v>5</v>
       </c>
       <c r="G61" t="s">
-        <v>7</v>
+        <v>508</v>
       </c>
       <c r="H61" t="s">
+        <v>7</v>
+      </c>
+      <c r="I61" t="s">
         <v>112</v>
       </c>
-      <c r="I61" t="s">
+      <c r="J61" t="s">
         <v>156</v>
       </c>
-      <c r="J61" t="s">
+      <c r="K61" t="s">
         <v>449</v>
       </c>
-      <c r="K61">
+      <c r="L61">
         <v>56160</v>
       </c>
-      <c r="L61">
+      <c r="M61">
         <v>266.94444444444503</v>
       </c>
-      <c r="M61">
+      <c r="N61">
         <v>7.4928774928774894E-2</v>
       </c>
-      <c r="N61">
+      <c r="O61">
         <v>4208</v>
       </c>
     </row>
-    <row r="62" spans="1:14">
+    <row r="62" spans="1:15">
       <c r="A62">
         <v>61</v>
       </c>
@@ -4636,31 +4850,34 @@
         <v>23</v>
       </c>
       <c r="G62" t="s">
-        <v>7</v>
+        <v>508</v>
       </c>
       <c r="H62" t="s">
+        <v>7</v>
+      </c>
+      <c r="I62" t="s">
         <v>112</v>
       </c>
-      <c r="I62" t="s">
+      <c r="J62" t="s">
         <v>158</v>
       </c>
-      <c r="J62" t="s">
+      <c r="K62" t="s">
         <v>449</v>
       </c>
-      <c r="K62">
+      <c r="L62">
         <v>138444</v>
       </c>
-      <c r="L62">
+      <c r="M62">
         <v>297.91666666666703</v>
       </c>
-      <c r="M62">
+      <c r="N62">
         <v>0.42616509202276698</v>
       </c>
-      <c r="N62">
+      <c r="O62">
         <v>59000</v>
       </c>
     </row>
-    <row r="63" spans="1:14">
+    <row r="63" spans="1:15">
       <c r="A63">
         <v>62</v>
       </c>
@@ -4679,32 +4896,35 @@
       <c r="F63" t="s">
         <v>161</v>
       </c>
-      <c r="G63" t="s">
-        <v>7</v>
+      <c r="G63" s="12">
+        <v>2000</v>
       </c>
       <c r="H63" t="s">
+        <v>7</v>
+      </c>
+      <c r="I63" t="s">
         <v>85</v>
       </c>
-      <c r="I63" s="2" t="s">
+      <c r="J63" s="2" t="s">
         <v>492</v>
       </c>
-      <c r="J63" t="s">
+      <c r="K63" t="s">
         <v>433</v>
       </c>
-      <c r="K63">
+      <c r="L63">
         <v>31000</v>
       </c>
-      <c r="L63">
+      <c r="M63">
         <v>281.94444444444503</v>
       </c>
-      <c r="M63">
+      <c r="N63">
         <v>0.154838709677419</v>
       </c>
-      <c r="N63">
+      <c r="O63">
         <v>4800</v>
       </c>
     </row>
-    <row r="64" spans="1:14">
+    <row r="64" spans="1:15">
       <c r="A64">
         <v>63</v>
       </c>
@@ -4717,35 +4937,41 @@
       <c r="D64" t="s">
         <v>14</v>
       </c>
+      <c r="E64" t="s">
+        <v>16</v>
+      </c>
       <c r="F64" t="s">
         <v>163</v>
       </c>
-      <c r="G64" t="s">
-        <v>7</v>
+      <c r="G64" s="12">
+        <v>2005</v>
       </c>
       <c r="H64" t="s">
+        <v>7</v>
+      </c>
+      <c r="I64" t="s">
         <v>85</v>
       </c>
-      <c r="I64" t="s">
+      <c r="J64" t="s">
         <v>164</v>
       </c>
-      <c r="J64" t="s">
+      <c r="K64" t="s">
         <v>433</v>
       </c>
-      <c r="K64">
+      <c r="L64">
         <v>120000</v>
       </c>
-      <c r="L64">
+      <c r="M64">
         <v>471.11111111111097</v>
       </c>
-      <c r="M64">
+      <c r="N64">
         <v>8.7499999999999994E-2</v>
       </c>
-      <c r="N64">
+      <c r="O64">
         <v>10500</v>
       </c>
     </row>
-    <row r="65" spans="1:14">
+    <row r="65" spans="1:15">
       <c r="A65">
         <v>64</v>
       </c>
@@ -4761,32 +4987,35 @@
       <c r="F65" t="s">
         <v>34</v>
       </c>
-      <c r="G65" t="s">
-        <v>7</v>
+      <c r="G65" s="12">
+        <v>2006</v>
       </c>
       <c r="H65" t="s">
+        <v>7</v>
+      </c>
+      <c r="I65" t="s">
         <v>85</v>
       </c>
-      <c r="I65" t="s">
+      <c r="J65" t="s">
         <v>166</v>
       </c>
-      <c r="J65" t="s">
+      <c r="K65" t="s">
         <v>433</v>
       </c>
-      <c r="K65">
+      <c r="L65">
         <v>25900</v>
       </c>
-      <c r="L65">
+      <c r="M65">
         <v>311.66666666666703</v>
       </c>
-      <c r="M65">
+      <c r="N65">
         <v>0.29289575289575298</v>
       </c>
-      <c r="N65">
+      <c r="O65">
         <v>7586</v>
       </c>
     </row>
-    <row r="66" spans="1:14">
+    <row r="66" spans="1:15">
       <c r="A66">
         <v>65</v>
       </c>
@@ -4802,32 +5031,35 @@
       <c r="F66" t="s">
         <v>168</v>
       </c>
-      <c r="G66" t="s">
-        <v>7</v>
+      <c r="G66" s="12">
+        <v>2006</v>
       </c>
       <c r="H66" t="s">
+        <v>7</v>
+      </c>
+      <c r="I66" t="s">
         <v>85</v>
       </c>
-      <c r="I66" t="s">
+      <c r="J66" t="s">
         <v>169</v>
       </c>
-      <c r="J66" t="s">
+      <c r="K66" t="s">
         <v>433</v>
       </c>
-      <c r="K66">
+      <c r="L66">
         <v>47986</v>
       </c>
-      <c r="L66">
+      <c r="M66">
         <v>316.66666666666703</v>
       </c>
-      <c r="M66">
+      <c r="N66">
         <v>8.9609469428583305E-2</v>
       </c>
-      <c r="N66">
+      <c r="O66">
         <v>4300</v>
       </c>
     </row>
-    <row r="67" spans="1:14">
+    <row r="67" spans="1:15">
       <c r="A67">
         <v>66</v>
       </c>
@@ -4846,32 +5078,35 @@
       <c r="F67" t="s">
         <v>36</v>
       </c>
-      <c r="G67" t="s">
-        <v>7</v>
+      <c r="G67" s="12">
+        <v>2007</v>
       </c>
       <c r="H67" t="s">
+        <v>7</v>
+      </c>
+      <c r="I67" t="s">
         <v>85</v>
       </c>
-      <c r="I67" t="s">
+      <c r="J67" t="s">
         <v>171</v>
       </c>
-      <c r="J67" t="s">
+      <c r="K67" t="s">
         <v>433</v>
       </c>
-      <c r="K67">
+      <c r="L67">
         <v>194000</v>
       </c>
-      <c r="L67">
+      <c r="M67">
         <v>416.66666666666703</v>
       </c>
-      <c r="M67">
+      <c r="N67">
         <v>8.9783505154639204E-2</v>
       </c>
-      <c r="N67">
+      <c r="O67">
         <v>17418</v>
       </c>
     </row>
-    <row r="68" spans="1:14">
+    <row r="68" spans="1:15">
       <c r="A68">
         <v>67</v>
       </c>
@@ -4890,32 +5125,35 @@
       <c r="F68" t="s">
         <v>39</v>
       </c>
-      <c r="G68" t="s">
-        <v>7</v>
+      <c r="G68" s="12">
+        <v>2007</v>
       </c>
       <c r="H68" t="s">
+        <v>7</v>
+      </c>
+      <c r="I68" t="s">
         <v>85</v>
       </c>
-      <c r="I68" t="s">
+      <c r="J68" t="s">
         <v>173</v>
       </c>
-      <c r="J68" t="s">
+      <c r="K68" t="s">
         <v>433</v>
       </c>
-      <c r="K68">
+      <c r="L68">
         <v>39724</v>
       </c>
-      <c r="L68">
+      <c r="M68">
         <v>281.94444444444503</v>
       </c>
-      <c r="M68">
+      <c r="N68">
         <v>9.0625314671231499E-2</v>
       </c>
-      <c r="N68">
+      <c r="O68">
         <v>3600</v>
       </c>
     </row>
-    <row r="69" spans="1:14">
+    <row r="69" spans="1:15">
       <c r="A69">
         <v>68</v>
       </c>
@@ -4931,32 +5169,35 @@
       <c r="F69" t="s">
         <v>48</v>
       </c>
-      <c r="G69" t="s">
-        <v>7</v>
+      <c r="G69" s="12">
+        <v>2007</v>
       </c>
       <c r="H69" t="s">
+        <v>7</v>
+      </c>
+      <c r="I69" t="s">
         <v>85</v>
       </c>
-      <c r="I69" s="1" t="s">
-        <v>501</v>
-      </c>
-      <c r="J69" t="s">
+      <c r="J69" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="K69" t="s">
         <v>433</v>
       </c>
-      <c r="K69">
+      <c r="L69">
         <v>48437.45</v>
       </c>
-      <c r="L69">
+      <c r="M69">
         <v>266.66666666666703</v>
       </c>
-      <c r="M69">
+      <c r="N69">
         <v>7.7398789572944104E-2</v>
       </c>
-      <c r="N69">
+      <c r="O69">
         <v>3749</v>
       </c>
     </row>
-    <row r="70" spans="1:14">
+    <row r="70" spans="1:15">
       <c r="A70">
         <v>69</v>
       </c>
@@ -4972,32 +5213,35 @@
       <c r="F70" t="s">
         <v>176</v>
       </c>
-      <c r="G70" t="s">
-        <v>7</v>
+      <c r="G70" s="12">
+        <v>2007</v>
       </c>
       <c r="H70" t="s">
+        <v>7</v>
+      </c>
+      <c r="I70" t="s">
         <v>85</v>
       </c>
-      <c r="I70" t="s">
+      <c r="J70" t="s">
         <v>177</v>
       </c>
-      <c r="J70" t="s">
+      <c r="K70" t="s">
         <v>433</v>
       </c>
-      <c r="K70">
+      <c r="L70">
         <v>37910</v>
       </c>
-      <c r="L70">
+      <c r="M70">
         <v>275</v>
       </c>
-      <c r="M70">
+      <c r="N70">
         <v>6.5945660775520998E-2</v>
       </c>
-      <c r="N70">
+      <c r="O70">
         <v>2500</v>
       </c>
     </row>
-    <row r="71" spans="1:14">
+    <row r="71" spans="1:15">
       <c r="A71">
         <v>70</v>
       </c>
@@ -5013,32 +5257,35 @@
       <c r="F71" t="s">
         <v>176</v>
       </c>
-      <c r="G71" t="s">
-        <v>7</v>
+      <c r="G71" s="12">
+        <v>2007</v>
       </c>
       <c r="H71" t="s">
+        <v>7</v>
+      </c>
+      <c r="I71" t="s">
         <v>85</v>
       </c>
-      <c r="I71" s="2" t="s">
+      <c r="J71" s="2" t="s">
         <v>456</v>
       </c>
-      <c r="J71" t="s">
+      <c r="K71" t="s">
         <v>433</v>
       </c>
-      <c r="K71">
+      <c r="L71">
         <v>21220</v>
       </c>
-      <c r="L71">
+      <c r="M71">
         <v>513.33333333333303</v>
-      </c>
-      <c r="M71">
-        <v>0</v>
       </c>
       <c r="N71">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="1:14">
+      <c r="O71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15">
       <c r="A72">
         <v>71</v>
       </c>
@@ -5054,32 +5301,35 @@
       <c r="F72" t="s">
         <v>55</v>
       </c>
-      <c r="G72" t="s">
-        <v>7</v>
+      <c r="G72" s="12">
+        <v>2008</v>
       </c>
       <c r="H72" t="s">
+        <v>7</v>
+      </c>
+      <c r="I72" t="s">
         <v>85</v>
       </c>
-      <c r="I72" t="s">
+      <c r="J72" t="s">
         <v>179</v>
       </c>
-      <c r="J72" t="s">
+      <c r="K72" t="s">
         <v>433</v>
       </c>
-      <c r="K72">
+      <c r="L72">
         <v>77877</v>
       </c>
-      <c r="L72">
+      <c r="M72">
         <v>350</v>
       </c>
-      <c r="M72">
+      <c r="N72">
         <v>6.42038085699244E-2</v>
       </c>
-      <c r="N72">
+      <c r="O72">
         <v>5000</v>
       </c>
     </row>
-    <row r="73" spans="1:14">
+    <row r="73" spans="1:15">
       <c r="A73">
         <v>72</v>
       </c>
@@ -5098,32 +5348,35 @@
       <c r="F73" t="s">
         <v>61</v>
       </c>
-      <c r="G73" t="s">
-        <v>7</v>
+      <c r="G73" s="12">
+        <v>2009</v>
       </c>
       <c r="H73" t="s">
+        <v>7</v>
+      </c>
+      <c r="I73" t="s">
         <v>85</v>
       </c>
-      <c r="I73" t="s">
+      <c r="J73" t="s">
         <v>181</v>
       </c>
-      <c r="J73" t="s">
+      <c r="K73" t="s">
         <v>433</v>
       </c>
-      <c r="K73">
+      <c r="L73">
         <v>80311.53</v>
       </c>
-      <c r="L73">
+      <c r="M73">
         <v>430.55555555555497</v>
       </c>
-      <c r="M73">
+      <c r="N73">
         <v>0.110581880335239</v>
       </c>
-      <c r="N73">
+      <c r="O73">
         <v>8881</v>
       </c>
     </row>
-    <row r="74" spans="1:14">
+    <row r="74" spans="1:15">
       <c r="A74">
         <v>73</v>
       </c>
@@ -5142,32 +5395,35 @@
       <c r="F74" t="s">
         <v>183</v>
       </c>
-      <c r="G74" t="s">
-        <v>7</v>
+      <c r="G74" s="12">
+        <v>2010</v>
       </c>
       <c r="H74" t="s">
+        <v>7</v>
+      </c>
+      <c r="I74" t="s">
         <v>85</v>
       </c>
-      <c r="I74" t="s">
+      <c r="J74" t="s">
         <v>184</v>
       </c>
-      <c r="J74" t="s">
+      <c r="K74" t="s">
         <v>433</v>
       </c>
-      <c r="K74">
+      <c r="L74">
         <v>38000</v>
       </c>
-      <c r="L74">
+      <c r="M74">
         <v>350</v>
       </c>
-      <c r="M74">
+      <c r="N74">
         <v>0.34210526315789502</v>
       </c>
-      <c r="N74">
+      <c r="O74">
         <v>13000</v>
       </c>
     </row>
-    <row r="75" spans="1:14">
+    <row r="75" spans="1:15">
       <c r="A75">
         <v>74</v>
       </c>
@@ -5183,32 +5439,35 @@
       <c r="F75" t="s">
         <v>186</v>
       </c>
-      <c r="G75" t="s">
-        <v>7</v>
+      <c r="G75" s="12">
+        <v>2013</v>
       </c>
       <c r="H75" t="s">
+        <v>7</v>
+      </c>
+      <c r="I75" t="s">
         <v>85</v>
       </c>
-      <c r="I75" t="s">
+      <c r="J75" t="s">
         <v>187</v>
       </c>
-      <c r="J75" t="s">
+      <c r="K75" t="s">
         <v>433</v>
       </c>
-      <c r="K75">
+      <c r="L75">
         <v>37800</v>
       </c>
-      <c r="L75">
+      <c r="M75">
         <v>387.5</v>
-      </c>
-      <c r="M75">
-        <v>0</v>
       </c>
       <c r="N75">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="1:14">
+      <c r="O75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15">
       <c r="A76">
         <v>75</v>
       </c>
@@ -5227,32 +5486,35 @@
       <c r="F76" t="s">
         <v>189</v>
       </c>
-      <c r="G76" t="s">
-        <v>7</v>
+      <c r="G76" s="12">
+        <v>2015</v>
       </c>
       <c r="H76" t="s">
+        <v>7</v>
+      </c>
+      <c r="I76" t="s">
         <v>85</v>
       </c>
-      <c r="I76" s="2" t="s">
+      <c r="J76" s="2" t="s">
         <v>466</v>
       </c>
-      <c r="J76" t="s">
+      <c r="K76" t="s">
         <v>433</v>
       </c>
-      <c r="K76">
+      <c r="L76">
         <v>54581</v>
       </c>
-      <c r="L76">
+      <c r="M76">
         <v>350</v>
       </c>
-      <c r="M76">
+      <c r="N76">
         <v>5.7840640515930401E-2</v>
       </c>
-      <c r="N76">
+      <c r="O76">
         <v>3157</v>
       </c>
     </row>
-    <row r="77" spans="1:14">
+    <row r="77" spans="1:15">
       <c r="A77">
         <v>76</v>
       </c>
@@ -5271,32 +5533,35 @@
       <c r="F77" t="s">
         <v>191</v>
       </c>
-      <c r="G77" t="s">
-        <v>7</v>
+      <c r="G77" s="12">
+        <v>2016</v>
       </c>
       <c r="H77" t="s">
+        <v>7</v>
+      </c>
+      <c r="I77" t="s">
         <v>85</v>
       </c>
-      <c r="I77" s="6" t="s">
-        <v>502</v>
-      </c>
-      <c r="J77" t="s">
+      <c r="J77" s="6" t="s">
+        <v>501</v>
+      </c>
+      <c r="K77" t="s">
         <v>433</v>
       </c>
-      <c r="K77">
+      <c r="L77">
         <v>25000</v>
       </c>
-      <c r="L77">
+      <c r="M77">
         <v>362.5</v>
       </c>
-      <c r="M77">
+      <c r="N77">
         <v>0.38147999999999999</v>
       </c>
-      <c r="N77">
+      <c r="O77">
         <v>9537</v>
       </c>
     </row>
-    <row r="78" spans="1:14">
+    <row r="78" spans="1:15">
       <c r="A78">
         <v>77</v>
       </c>
@@ -5315,32 +5580,35 @@
       <c r="F78" t="s">
         <v>87</v>
       </c>
-      <c r="G78" t="s">
-        <v>7</v>
+      <c r="G78" s="12">
+        <v>2019</v>
       </c>
       <c r="H78" t="s">
+        <v>7</v>
+      </c>
+      <c r="I78" t="s">
         <v>85</v>
       </c>
-      <c r="I78" t="s">
+      <c r="J78" t="s">
         <v>193</v>
       </c>
-      <c r="J78" t="s">
+      <c r="K78" t="s">
         <v>433</v>
       </c>
-      <c r="K78">
+      <c r="L78">
         <v>52698</v>
       </c>
-      <c r="L78">
+      <c r="M78">
         <v>540.83333333333303</v>
       </c>
-      <c r="M78">
+      <c r="N78">
         <v>6.4518577555125398E-2</v>
       </c>
-      <c r="N78">
+      <c r="O78">
         <v>3400</v>
       </c>
     </row>
-    <row r="79" spans="1:14">
+    <row r="79" spans="1:15">
       <c r="A79">
         <v>78</v>
       </c>
@@ -5356,32 +5624,35 @@
       <c r="F79" t="s">
         <v>195</v>
       </c>
-      <c r="G79" t="s">
-        <v>7</v>
+      <c r="G79" s="12">
+        <v>2007</v>
       </c>
       <c r="H79" t="s">
+        <v>7</v>
+      </c>
+      <c r="I79" t="s">
         <v>196</v>
       </c>
-      <c r="I79" s="2" t="s">
+      <c r="J79" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="J79" t="s">
+      <c r="K79" t="s">
         <v>433</v>
       </c>
-      <c r="K79">
+      <c r="L79">
         <v>38500</v>
       </c>
-      <c r="L79">
+      <c r="M79">
         <v>210.833333333333</v>
       </c>
-      <c r="M79">
+      <c r="N79">
         <v>0.22270129870129901</v>
       </c>
-      <c r="N79">
+      <c r="O79">
         <v>8574</v>
       </c>
     </row>
-    <row r="80" spans="1:14">
+    <row r="80" spans="1:15">
       <c r="A80">
         <v>79</v>
       </c>
@@ -5395,31 +5666,34 @@
         <v>198</v>
       </c>
       <c r="G80" t="s">
-        <v>7</v>
+        <v>508</v>
       </c>
       <c r="H80" t="s">
+        <v>7</v>
+      </c>
+      <c r="I80" t="s">
         <v>85</v>
       </c>
-      <c r="I80" t="s">
+      <c r="J80" t="s">
         <v>199</v>
       </c>
-      <c r="J80" t="s">
+      <c r="K80" t="s">
         <v>433</v>
       </c>
-      <c r="K80">
+      <c r="L80">
         <v>27200</v>
       </c>
-      <c r="L80">
+      <c r="M80">
         <v>195.555555555555</v>
       </c>
-      <c r="M80">
+      <c r="N80">
         <v>0.26286764705882298</v>
       </c>
-      <c r="N80">
+      <c r="O80">
         <v>7150</v>
       </c>
     </row>
-    <row r="81" spans="1:14">
+    <row r="81" spans="1:15">
       <c r="A81">
         <v>80</v>
       </c>
@@ -5438,32 +5712,35 @@
       <c r="F81" t="s">
         <v>201</v>
       </c>
-      <c r="G81" t="s">
-        <v>7</v>
+      <c r="G81" s="12">
+        <v>1999</v>
       </c>
       <c r="H81" t="s">
+        <v>7</v>
+      </c>
+      <c r="I81" t="s">
         <v>8</v>
       </c>
-      <c r="I81" s="10" t="s">
-        <v>504</v>
-      </c>
-      <c r="J81" t="s">
+      <c r="J81" s="10" t="s">
+        <v>503</v>
+      </c>
+      <c r="K81" t="s">
         <v>434</v>
       </c>
-      <c r="K81">
+      <c r="L81">
         <v>60000</v>
       </c>
-      <c r="L81">
+      <c r="M81">
         <v>200</v>
       </c>
-      <c r="M81">
+      <c r="N81">
         <v>0.320583333333333</v>
       </c>
-      <c r="N81">
+      <c r="O81">
         <v>19235</v>
       </c>
     </row>
-    <row r="82" spans="1:14">
+    <row r="82" spans="1:15">
       <c r="A82">
         <v>81</v>
       </c>
@@ -5476,35 +5753,41 @@
       <c r="D82" t="s">
         <v>5</v>
       </c>
+      <c r="E82" t="s">
+        <v>23</v>
+      </c>
       <c r="F82" t="s">
         <v>203</v>
       </c>
-      <c r="G82" t="s">
-        <v>7</v>
+      <c r="G82" s="12">
+        <v>2000</v>
       </c>
       <c r="H82" t="s">
+        <v>7</v>
+      </c>
+      <c r="I82" t="s">
         <v>8</v>
       </c>
-      <c r="I82" t="s">
+      <c r="J82" t="s">
         <v>204</v>
       </c>
-      <c r="J82" t="s">
+      <c r="K82" t="s">
         <v>449</v>
       </c>
-      <c r="K82">
+      <c r="L82">
         <v>50000</v>
       </c>
-      <c r="L82">
+      <c r="M82">
         <v>195.555555555555</v>
       </c>
-      <c r="M82">
+      <c r="N82">
         <v>0.15</v>
       </c>
-      <c r="N82">
+      <c r="O82">
         <v>7500</v>
       </c>
     </row>
-    <row r="83" spans="1:14">
+    <row r="83" spans="1:15">
       <c r="A83">
         <v>82</v>
       </c>
@@ -5523,32 +5806,35 @@
       <c r="F83" t="s">
         <v>124</v>
       </c>
-      <c r="G83" t="s">
-        <v>7</v>
+      <c r="G83" s="12">
+        <v>2005</v>
       </c>
       <c r="H83" t="s">
+        <v>7</v>
+      </c>
+      <c r="I83" t="s">
         <v>8</v>
       </c>
-      <c r="I83" t="s">
+      <c r="J83" t="s">
         <v>206</v>
       </c>
-      <c r="J83" t="s">
+      <c r="K83" t="s">
         <v>434</v>
       </c>
-      <c r="K83">
+      <c r="L83">
         <v>131575</v>
       </c>
-      <c r="L83">
+      <c r="M83">
         <v>204.444444444445</v>
       </c>
-      <c r="M83">
+      <c r="N83">
         <v>7.6002280068402095E-2</v>
       </c>
-      <c r="N83">
+      <c r="O83">
         <v>10000</v>
       </c>
     </row>
-    <row r="84" spans="1:14">
+    <row r="84" spans="1:15">
       <c r="A84">
         <v>83</v>
       </c>
@@ -5561,35 +5847,41 @@
       <c r="D84" t="s">
         <v>5</v>
       </c>
+      <c r="E84" t="s">
+        <v>23</v>
+      </c>
       <c r="F84" t="s">
         <v>55</v>
       </c>
-      <c r="G84" t="s">
-        <v>7</v>
+      <c r="G84" s="12">
+        <v>2008</v>
       </c>
       <c r="H84" t="s">
+        <v>7</v>
+      </c>
+      <c r="I84" t="s">
         <v>8</v>
       </c>
-      <c r="I84" t="s">
+      <c r="J84" t="s">
         <v>208</v>
       </c>
-      <c r="J84" t="s">
+      <c r="K84" t="s">
         <v>449</v>
       </c>
-      <c r="K84">
+      <c r="L84">
         <v>99500</v>
       </c>
-      <c r="L84">
+      <c r="M84">
         <v>195.555555555555</v>
       </c>
-      <c r="M84">
+      <c r="N84">
         <v>0.23086432160803999</v>
       </c>
-      <c r="N84">
+      <c r="O84">
         <v>22971</v>
       </c>
     </row>
-    <row r="85" spans="1:14">
+    <row r="85" spans="1:15">
       <c r="A85">
         <v>84</v>
       </c>
@@ -5605,32 +5897,35 @@
       <c r="F85" t="s">
         <v>210</v>
       </c>
-      <c r="G85" t="s">
-        <v>7</v>
+      <c r="G85" s="12">
+        <v>2010</v>
       </c>
       <c r="H85" t="s">
+        <v>7</v>
+      </c>
+      <c r="I85" t="s">
         <v>8</v>
       </c>
-      <c r="I85" t="s">
+      <c r="J85" t="s">
         <v>489</v>
       </c>
-      <c r="J85" t="s">
+      <c r="K85" t="s">
         <v>434</v>
       </c>
-      <c r="K85">
+      <c r="L85">
         <v>32000</v>
       </c>
-      <c r="L85">
+      <c r="M85">
         <v>178.888888888889</v>
       </c>
-      <c r="M85">
+      <c r="N85">
         <v>0.11874999999999999</v>
       </c>
-      <c r="N85">
+      <c r="O85">
         <v>3800</v>
       </c>
     </row>
-    <row r="86" spans="1:14">
+    <row r="86" spans="1:15">
       <c r="A86">
         <v>85</v>
       </c>
@@ -5649,32 +5944,35 @@
       <c r="F86" t="s">
         <v>183</v>
       </c>
-      <c r="G86" t="s">
-        <v>7</v>
+      <c r="G86" s="12">
+        <v>2010</v>
       </c>
       <c r="H86" t="s">
+        <v>7</v>
+      </c>
+      <c r="I86" t="s">
         <v>8</v>
       </c>
-      <c r="I86" t="s">
+      <c r="J86" t="s">
         <v>212</v>
       </c>
-      <c r="J86" t="s">
+      <c r="K86" t="s">
         <v>434</v>
       </c>
-      <c r="K86">
+      <c r="L86">
         <v>52170</v>
       </c>
-      <c r="L86">
+      <c r="M86">
         <v>208.333333333333</v>
       </c>
-      <c r="M86">
+      <c r="N86">
         <v>0.156009200690052</v>
       </c>
-      <c r="N86">
+      <c r="O86">
         <v>8139</v>
       </c>
     </row>
-    <row r="87" spans="1:14">
+    <row r="87" spans="1:15">
       <c r="A87">
         <v>86</v>
       </c>
@@ -5690,32 +5988,35 @@
       <c r="F87" t="s">
         <v>214</v>
       </c>
-      <c r="G87" t="s">
-        <v>7</v>
+      <c r="G87" s="12">
+        <v>2011</v>
       </c>
       <c r="H87" t="s">
+        <v>7</v>
+      </c>
+      <c r="I87" t="s">
         <v>8</v>
       </c>
-      <c r="I87" t="s">
+      <c r="J87" t="s">
         <v>490</v>
       </c>
-      <c r="J87" t="s">
+      <c r="K87" t="s">
         <v>434</v>
       </c>
-      <c r="K87">
+      <c r="L87">
         <v>46000</v>
       </c>
-      <c r="L87">
+      <c r="M87">
         <v>186.666666666667</v>
       </c>
-      <c r="M87">
+      <c r="N87">
         <v>0.102173913043478</v>
       </c>
-      <c r="N87">
+      <c r="O87">
         <v>4700</v>
       </c>
     </row>
-    <row r="88" spans="1:14">
+    <row r="88" spans="1:15">
       <c r="A88">
         <v>87</v>
       </c>
@@ -5734,32 +6035,35 @@
       <c r="F88" t="s">
         <v>216</v>
       </c>
-      <c r="G88" t="s">
-        <v>7</v>
+      <c r="G88" s="12">
+        <v>2012</v>
       </c>
       <c r="H88" t="s">
+        <v>7</v>
+      </c>
+      <c r="I88" t="s">
         <v>8</v>
       </c>
-      <c r="I88" t="s">
+      <c r="J88" t="s">
         <v>217</v>
       </c>
-      <c r="J88" t="s">
+      <c r="K88" t="s">
         <v>449</v>
       </c>
-      <c r="K88">
+      <c r="L88">
         <v>45013</v>
       </c>
-      <c r="L88">
+      <c r="M88">
         <v>206.25</v>
       </c>
-      <c r="M88">
+      <c r="N88">
         <v>0.13995956723613201</v>
       </c>
-      <c r="N88">
+      <c r="O88">
         <v>6300</v>
       </c>
     </row>
-    <row r="89" spans="1:14">
+    <row r="89" spans="1:15">
       <c r="A89">
         <v>88</v>
       </c>
@@ -5775,32 +6079,35 @@
       <c r="F89" t="s">
         <v>76</v>
       </c>
-      <c r="G89" t="s">
-        <v>7</v>
+      <c r="G89" s="12">
+        <v>2013</v>
       </c>
       <c r="H89" t="s">
+        <v>7</v>
+      </c>
+      <c r="I89" t="s">
         <v>8</v>
       </c>
-      <c r="I89" s="1" t="s">
-        <v>500</v>
-      </c>
-      <c r="J89" t="s">
+      <c r="J89" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="K89" t="s">
         <v>434</v>
       </c>
-      <c r="K89">
+      <c r="L89">
         <v>48566</v>
       </c>
-      <c r="L89">
+      <c r="M89">
         <v>220</v>
       </c>
-      <c r="M89">
+      <c r="N89">
         <v>0.76040851624593297</v>
       </c>
-      <c r="N89">
+      <c r="O89">
         <v>36930</v>
       </c>
     </row>
-    <row r="90" spans="1:14">
+    <row r="90" spans="1:15">
       <c r="A90">
         <v>89</v>
       </c>
@@ -5816,32 +6123,35 @@
       <c r="F90" t="s">
         <v>220</v>
       </c>
-      <c r="G90" t="s">
-        <v>7</v>
+      <c r="G90" s="12">
+        <v>2014</v>
       </c>
       <c r="H90" t="s">
+        <v>7</v>
+      </c>
+      <c r="I90" t="s">
         <v>8</v>
       </c>
-      <c r="I90" t="s">
+      <c r="J90" t="s">
         <v>221</v>
       </c>
-      <c r="J90" t="s">
+      <c r="K90" t="s">
         <v>449</v>
       </c>
-      <c r="K90">
+      <c r="L90">
         <v>55618</v>
       </c>
-      <c r="L90">
+      <c r="M90">
         <v>238.333333333333</v>
       </c>
-      <c r="M90">
+      <c r="N90">
         <v>0.2</v>
       </c>
-      <c r="N90">
+      <c r="O90">
         <v>11123.6</v>
       </c>
     </row>
-    <row r="91" spans="1:14">
+    <row r="91" spans="1:15">
       <c r="A91">
         <v>90</v>
       </c>
@@ -5857,32 +6167,35 @@
       <c r="F91" t="s">
         <v>189</v>
       </c>
-      <c r="G91" t="s">
-        <v>7</v>
+      <c r="G91" s="12">
+        <v>2015</v>
       </c>
       <c r="H91" t="s">
+        <v>7</v>
+      </c>
+      <c r="I91" t="s">
         <v>8</v>
       </c>
-      <c r="I91" t="s">
+      <c r="J91" t="s">
         <v>491</v>
       </c>
-      <c r="J91" t="s">
+      <c r="K91" t="s">
         <v>434</v>
       </c>
-      <c r="K91">
+      <c r="L91">
         <v>47000</v>
       </c>
-      <c r="L91">
+      <c r="M91">
         <v>229.166666666667</v>
       </c>
-      <c r="M91">
+      <c r="N91">
         <v>4.0382978723404302E-2</v>
       </c>
-      <c r="N91">
+      <c r="O91">
         <v>1898</v>
       </c>
     </row>
-    <row r="92" spans="1:14">
+    <row r="92" spans="1:15">
       <c r="A92">
         <v>91</v>
       </c>
@@ -5901,32 +6214,35 @@
       <c r="F92" t="s">
         <v>224</v>
       </c>
-      <c r="G92" t="s">
-        <v>7</v>
+      <c r="G92" s="12">
+        <v>2016</v>
       </c>
       <c r="H92" t="s">
+        <v>7</v>
+      </c>
+      <c r="I92" t="s">
         <v>8</v>
       </c>
-      <c r="I92" t="s">
+      <c r="J92" t="s">
         <v>225</v>
       </c>
-      <c r="J92" t="s">
+      <c r="K92" t="s">
         <v>449</v>
       </c>
-      <c r="K92">
+      <c r="L92">
         <v>87763</v>
       </c>
-      <c r="L92">
+      <c r="M92">
         <v>177.777777777778</v>
       </c>
-      <c r="M92">
+      <c r="N92">
         <v>0.227886466962159</v>
       </c>
-      <c r="N92">
+      <c r="O92">
         <v>20000</v>
       </c>
     </row>
-    <row r="93" spans="1:14">
+    <row r="93" spans="1:15">
       <c r="A93">
         <v>92</v>
       </c>
@@ -5945,32 +6261,35 @@
       <c r="F93" t="s">
         <v>227</v>
       </c>
-      <c r="G93" t="s">
-        <v>7</v>
+      <c r="G93" s="12">
+        <v>2016</v>
       </c>
       <c r="H93" t="s">
+        <v>7</v>
+      </c>
+      <c r="I93" t="s">
         <v>8</v>
       </c>
-      <c r="I93" t="s">
+      <c r="J93" t="s">
         <v>228</v>
       </c>
-      <c r="J93" t="s">
+      <c r="K93" t="s">
         <v>434</v>
       </c>
-      <c r="K93">
+      <c r="L93">
         <v>100658</v>
       </c>
-      <c r="L93">
+      <c r="M93">
         <v>275.55555555555497</v>
       </c>
-      <c r="M93">
+      <c r="N93">
         <v>0.33777742454648402</v>
       </c>
-      <c r="N93">
+      <c r="O93">
         <v>34000</v>
       </c>
     </row>
-    <row r="94" spans="1:14">
+    <row r="94" spans="1:15">
       <c r="A94">
         <v>93</v>
       </c>
@@ -5983,35 +6302,41 @@
       <c r="D94" t="s">
         <v>5</v>
       </c>
+      <c r="E94" t="s">
+        <v>16</v>
+      </c>
       <c r="F94" t="s">
         <v>230</v>
       </c>
-      <c r="G94" t="s">
-        <v>7</v>
+      <c r="G94" s="12">
+        <v>2015</v>
       </c>
       <c r="H94" t="s">
+        <v>7</v>
+      </c>
+      <c r="I94" t="s">
         <v>8</v>
       </c>
-      <c r="I94" t="s">
+      <c r="J94" t="s">
         <v>475</v>
       </c>
-      <c r="J94" t="s">
+      <c r="K94" t="s">
         <v>434</v>
       </c>
-      <c r="K94">
+      <c r="L94">
         <v>67000</v>
       </c>
-      <c r="L94">
+      <c r="M94">
         <v>206.666666666667</v>
       </c>
-      <c r="M94">
+      <c r="N94">
         <v>0.178820895522388</v>
       </c>
-      <c r="N94">
+      <c r="O94">
         <v>11981</v>
       </c>
     </row>
-    <row r="95" spans="1:14">
+    <row r="95" spans="1:15">
       <c r="A95">
         <v>94</v>
       </c>
@@ -6030,32 +6355,35 @@
       <c r="F95" t="s">
         <v>82</v>
       </c>
-      <c r="G95" t="s">
-        <v>7</v>
+      <c r="G95" s="12">
+        <v>2017</v>
       </c>
       <c r="H95" t="s">
+        <v>7</v>
+      </c>
+      <c r="I95" t="s">
         <v>8</v>
       </c>
-      <c r="I95" t="s">
+      <c r="J95" t="s">
         <v>232</v>
       </c>
-      <c r="J95" t="s">
+      <c r="K95" t="s">
         <v>434</v>
       </c>
-      <c r="K95">
+      <c r="L95">
         <v>39431</v>
       </c>
-      <c r="L95">
+      <c r="M95">
         <v>216.666666666667</v>
       </c>
-      <c r="M95">
+      <c r="N95">
         <v>0.30432908117978202</v>
       </c>
-      <c r="N95">
+      <c r="O95">
         <v>12000</v>
       </c>
     </row>
-    <row r="96" spans="1:14">
+    <row r="96" spans="1:15">
       <c r="A96">
         <v>95</v>
       </c>
@@ -6071,32 +6399,35 @@
       <c r="F96" t="s">
         <v>84</v>
       </c>
-      <c r="G96" t="s">
-        <v>7</v>
+      <c r="G96" s="12">
+        <v>2019</v>
       </c>
       <c r="H96" t="s">
+        <v>7</v>
+      </c>
+      <c r="I96" t="s">
         <v>8</v>
       </c>
-      <c r="I96" t="s">
+      <c r="J96" t="s">
         <v>234</v>
       </c>
-      <c r="J96" t="s">
+      <c r="K96" t="s">
         <v>434</v>
       </c>
-      <c r="K96">
+      <c r="L96">
         <v>34273</v>
       </c>
-      <c r="L96">
+      <c r="M96">
         <v>166.666666666667</v>
       </c>
-      <c r="M96">
+      <c r="N96">
         <v>0.145887433256499</v>
       </c>
-      <c r="N96">
+      <c r="O96">
         <v>5000</v>
       </c>
     </row>
-    <row r="97" spans="1:14">
+    <row r="97" spans="1:15">
       <c r="A97">
         <v>96</v>
       </c>
@@ -6110,31 +6441,34 @@
         <v>5</v>
       </c>
       <c r="G97" t="s">
-        <v>7</v>
+        <v>508</v>
       </c>
       <c r="H97" t="s">
+        <v>7</v>
+      </c>
+      <c r="I97" t="s">
         <v>8</v>
       </c>
-      <c r="I97" t="s">
+      <c r="J97" t="s">
         <v>474</v>
       </c>
-      <c r="J97" t="s">
+      <c r="K97" t="s">
         <v>449</v>
       </c>
-      <c r="K97">
+      <c r="L97">
         <v>40000</v>
       </c>
-      <c r="L97">
+      <c r="M97">
         <v>200</v>
       </c>
-      <c r="M97">
+      <c r="N97">
         <v>1</v>
       </c>
-      <c r="N97">
+      <c r="O97">
         <v>40000</v>
       </c>
     </row>
-    <row r="98" spans="1:14">
+    <row r="98" spans="1:15">
       <c r="A98">
         <v>97</v>
       </c>
@@ -6151,31 +6485,34 @@
         <v>16</v>
       </c>
       <c r="G98" t="s">
-        <v>7</v>
+        <v>508</v>
       </c>
       <c r="H98" t="s">
+        <v>7</v>
+      </c>
+      <c r="I98" t="s">
         <v>8</v>
       </c>
-      <c r="I98" t="s">
+      <c r="J98" t="s">
         <v>237</v>
       </c>
-      <c r="J98" t="s">
+      <c r="K98" t="s">
         <v>434</v>
       </c>
-      <c r="K98">
+      <c r="L98">
         <v>65000</v>
       </c>
-      <c r="L98">
+      <c r="M98">
         <v>201.388888888889</v>
       </c>
-      <c r="M98">
+      <c r="N98">
         <v>0.480738461538462</v>
       </c>
-      <c r="N98">
+      <c r="O98">
         <v>31248</v>
       </c>
     </row>
-    <row r="99" spans="1:14">
+    <row r="99" spans="1:15">
       <c r="A99">
         <v>98</v>
       </c>
@@ -6194,32 +6531,35 @@
       <c r="F99" t="s">
         <v>240</v>
       </c>
-      <c r="G99" t="s">
-        <v>7</v>
+      <c r="G99" s="12">
+        <v>2002</v>
       </c>
       <c r="H99" t="s">
+        <v>7</v>
+      </c>
+      <c r="I99" t="s">
         <v>196</v>
       </c>
-      <c r="I99" t="s">
+      <c r="J99" t="s">
         <v>241</v>
       </c>
-      <c r="J99" t="s">
+      <c r="K99" t="s">
         <v>451</v>
       </c>
-      <c r="K99">
+      <c r="L99">
         <v>49000</v>
       </c>
-      <c r="L99">
+      <c r="M99">
         <v>335.83333333333297</v>
       </c>
-      <c r="M99">
+      <c r="N99">
         <v>0.24397959183673501</v>
       </c>
-      <c r="N99">
+      <c r="O99">
         <v>11955</v>
       </c>
     </row>
-    <row r="100" spans="1:14">
+    <row r="100" spans="1:15">
       <c r="A100">
         <v>99</v>
       </c>
@@ -6238,32 +6578,35 @@
       <c r="F100" t="s">
         <v>243</v>
       </c>
-      <c r="G100" t="s">
-        <v>7</v>
+      <c r="G100" s="12">
+        <v>2004</v>
       </c>
       <c r="H100" t="s">
+        <v>7</v>
+      </c>
+      <c r="I100" t="s">
         <v>196</v>
       </c>
-      <c r="I100" t="s">
+      <c r="J100" t="s">
         <v>244</v>
       </c>
-      <c r="J100" t="s">
+      <c r="K100" t="s">
         <v>451</v>
       </c>
-      <c r="K100">
+      <c r="L100">
         <v>95000</v>
       </c>
-      <c r="L100">
+      <c r="M100">
         <v>335.83333333333297</v>
       </c>
-      <c r="M100">
+      <c r="N100">
         <v>0.123347368421053</v>
       </c>
-      <c r="N100">
+      <c r="O100">
         <v>11718</v>
       </c>
     </row>
-    <row r="101" spans="1:14">
+    <row r="101" spans="1:15">
       <c r="A101">
         <v>100</v>
       </c>
@@ -6282,32 +6625,35 @@
       <c r="F101" t="s">
         <v>246</v>
       </c>
-      <c r="G101" t="s">
-        <v>7</v>
+      <c r="G101" s="12">
+        <v>2004</v>
       </c>
       <c r="H101" t="s">
+        <v>7</v>
+      </c>
+      <c r="I101" t="s">
         <v>196</v>
       </c>
-      <c r="I101" t="s">
+      <c r="J101" t="s">
         <v>247</v>
       </c>
-      <c r="J101" t="s">
+      <c r="K101" t="s">
         <v>451</v>
       </c>
-      <c r="K101">
+      <c r="L101">
         <v>45000</v>
       </c>
-      <c r="L101">
+      <c r="M101">
         <v>241.111111111111</v>
       </c>
-      <c r="M101">
+      <c r="N101">
         <v>0.31568888888888902</v>
       </c>
-      <c r="N101">
+      <c r="O101">
         <v>14206</v>
       </c>
     </row>
-    <row r="102" spans="1:14">
+    <row r="102" spans="1:15">
       <c r="A102">
         <v>101</v>
       </c>
@@ -6323,32 +6669,35 @@
       <c r="F102" t="s">
         <v>26</v>
       </c>
-      <c r="G102" t="s">
-        <v>7</v>
+      <c r="G102" s="12">
+        <v>2005</v>
       </c>
       <c r="H102" t="s">
+        <v>7</v>
+      </c>
+      <c r="I102" t="s">
         <v>196</v>
       </c>
-      <c r="I102" t="s">
+      <c r="J102" t="s">
         <v>249</v>
       </c>
-      <c r="J102" t="s">
+      <c r="K102" t="s">
         <v>451</v>
       </c>
-      <c r="K102">
+      <c r="L102">
         <v>124500</v>
       </c>
-      <c r="L102">
+      <c r="M102">
         <v>172.222222222222</v>
       </c>
-      <c r="M102">
+      <c r="N102">
         <v>5.62489959839357E-2</v>
       </c>
-      <c r="N102">
+      <c r="O102">
         <v>7003</v>
       </c>
     </row>
-    <row r="103" spans="1:14">
+    <row r="103" spans="1:15">
       <c r="A103">
         <v>102</v>
       </c>
@@ -6364,32 +6713,35 @@
       <c r="F103" t="s">
         <v>124</v>
       </c>
-      <c r="G103" t="s">
-        <v>7</v>
+      <c r="G103" s="12">
+        <v>2005</v>
       </c>
       <c r="H103" t="s">
+        <v>7</v>
+      </c>
+      <c r="I103" t="s">
         <v>196</v>
       </c>
-      <c r="I103" s="2" t="s">
+      <c r="J103" s="2" t="s">
         <v>467</v>
       </c>
-      <c r="J103" t="s">
+      <c r="K103" t="s">
         <v>451</v>
       </c>
-      <c r="K103">
+      <c r="L103">
         <v>64000</v>
       </c>
-      <c r="L103">
+      <c r="M103">
         <v>183.333333333333</v>
       </c>
-      <c r="M103">
+      <c r="N103">
         <v>9.1593750000000002E-2</v>
       </c>
-      <c r="N103">
+      <c r="O103">
         <v>5862</v>
       </c>
     </row>
-    <row r="104" spans="1:14">
+    <row r="104" spans="1:15">
       <c r="A104">
         <v>103</v>
       </c>
@@ -6405,32 +6757,35 @@
       <c r="F104" t="s">
         <v>64</v>
       </c>
-      <c r="G104" t="s">
-        <v>7</v>
+      <c r="G104" s="12">
+        <v>2009</v>
       </c>
       <c r="H104" t="s">
+        <v>7</v>
+      </c>
+      <c r="I104" t="s">
         <v>196</v>
       </c>
-      <c r="I104" t="s">
+      <c r="J104" t="s">
         <v>252</v>
       </c>
-      <c r="J104" t="s">
+      <c r="K104" t="s">
         <v>451</v>
       </c>
-      <c r="K104">
+      <c r="L104">
         <v>25000</v>
       </c>
-      <c r="L104">
+      <c r="M104">
         <v>284.16666666666703</v>
-      </c>
-      <c r="M104">
-        <v>0</v>
       </c>
       <c r="N104">
         <v>0</v>
       </c>
-    </row>
-    <row r="105" spans="1:14">
+      <c r="O104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:15">
       <c r="A105">
         <v>104</v>
       </c>
@@ -6446,32 +6801,35 @@
       <c r="F105" t="s">
         <v>79</v>
       </c>
-      <c r="G105" t="s">
-        <v>7</v>
+      <c r="G105" s="12">
+        <v>2014</v>
       </c>
       <c r="H105" t="s">
+        <v>7</v>
+      </c>
+      <c r="I105" t="s">
         <v>196</v>
       </c>
-      <c r="I105" t="s">
+      <c r="J105" t="s">
         <v>254</v>
       </c>
-      <c r="J105" t="s">
+      <c r="K105" t="s">
         <v>451</v>
       </c>
-      <c r="K105">
+      <c r="L105">
         <v>38498</v>
       </c>
-      <c r="L105">
+      <c r="M105">
         <v>177.777777777778</v>
       </c>
-      <c r="M105">
+      <c r="N105">
         <v>3.1404228791106002E-3</v>
       </c>
-      <c r="N105">
+      <c r="O105">
         <v>120.9</v>
       </c>
     </row>
-    <row r="106" spans="1:14">
+    <row r="106" spans="1:15">
       <c r="A106">
         <v>105</v>
       </c>
@@ -6485,31 +6843,34 @@
         <v>198</v>
       </c>
       <c r="G106" t="s">
-        <v>7</v>
+        <v>508</v>
       </c>
       <c r="H106" t="s">
+        <v>7</v>
+      </c>
+      <c r="I106" t="s">
         <v>196</v>
       </c>
-      <c r="I106" t="s">
+      <c r="J106" t="s">
         <v>256</v>
       </c>
-      <c r="J106" t="s">
+      <c r="K106" t="s">
         <v>435</v>
       </c>
-      <c r="K106">
+      <c r="L106">
         <v>166433</v>
       </c>
-      <c r="L106">
+      <c r="M106">
         <v>186.666666666667</v>
       </c>
-      <c r="M106">
+      <c r="N106">
         <v>0.13939543239621899</v>
       </c>
-      <c r="N106">
+      <c r="O106">
         <v>23200</v>
       </c>
     </row>
-    <row r="107" spans="1:14">
+    <row r="107" spans="1:15">
       <c r="A107">
         <v>106</v>
       </c>
@@ -6528,32 +6889,35 @@
       <c r="F107" t="s">
         <v>189</v>
       </c>
-      <c r="G107" t="s">
-        <v>7</v>
+      <c r="G107" s="12">
+        <v>2015</v>
       </c>
       <c r="H107" t="s">
+        <v>7</v>
+      </c>
+      <c r="I107" t="s">
         <v>196</v>
       </c>
-      <c r="I107" t="s">
+      <c r="J107" t="s">
         <v>258</v>
       </c>
-      <c r="J107" t="s">
+      <c r="K107" t="s">
         <v>451</v>
       </c>
-      <c r="K107">
+      <c r="L107">
         <v>58000</v>
       </c>
-      <c r="L107">
+      <c r="M107">
         <v>373.33333333333297</v>
       </c>
-      <c r="M107">
+      <c r="N107">
         <v>2.5862068965517199E-2</v>
       </c>
-      <c r="N107">
+      <c r="O107">
         <v>1500</v>
       </c>
     </row>
-    <row r="108" spans="1:14">
+    <row r="108" spans="1:15">
       <c r="A108">
         <v>107</v>
       </c>
@@ -6569,32 +6933,35 @@
       <c r="F108" t="s">
         <v>260</v>
       </c>
-      <c r="G108" t="s">
-        <v>7</v>
+      <c r="G108" s="12">
+        <v>2015</v>
       </c>
       <c r="H108" t="s">
+        <v>7</v>
+      </c>
+      <c r="I108" t="s">
         <v>196</v>
       </c>
-      <c r="I108" t="s">
+      <c r="J108" t="s">
         <v>261</v>
       </c>
-      <c r="J108" t="s">
+      <c r="K108" t="s">
         <v>435</v>
       </c>
-      <c r="K108">
+      <c r="L108">
         <v>51872</v>
       </c>
-      <c r="L108">
+      <c r="M108">
         <v>302.5</v>
-      </c>
-      <c r="M108">
-        <v>0</v>
       </c>
       <c r="N108">
         <v>0</v>
       </c>
-    </row>
-    <row r="109" spans="1:14">
+      <c r="O108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:15">
       <c r="A109">
         <v>108</v>
       </c>
@@ -6610,32 +6977,35 @@
       <c r="F109" t="s">
         <v>191</v>
       </c>
-      <c r="G109" t="s">
-        <v>7</v>
+      <c r="G109" s="12">
+        <v>2016</v>
       </c>
       <c r="H109" t="s">
+        <v>7</v>
+      </c>
+      <c r="I109" t="s">
         <v>196</v>
       </c>
-      <c r="I109" t="s">
+      <c r="J109" t="s">
         <v>263</v>
       </c>
-      <c r="J109" t="s">
+      <c r="K109" t="s">
         <v>435</v>
       </c>
-      <c r="K109">
+      <c r="L109">
         <v>21632</v>
       </c>
-      <c r="L109">
+      <c r="M109">
         <v>229.5</v>
-      </c>
-      <c r="M109">
-        <v>0</v>
       </c>
       <c r="N109">
         <v>0</v>
       </c>
-    </row>
-    <row r="110" spans="1:14">
+      <c r="O109">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:15">
       <c r="A110">
         <v>109</v>
       </c>
@@ -6651,32 +7021,35 @@
       <c r="F110" t="s">
         <v>191</v>
       </c>
-      <c r="G110" t="s">
-        <v>7</v>
+      <c r="G110" s="12">
+        <v>2016</v>
       </c>
       <c r="H110" t="s">
+        <v>7</v>
+      </c>
+      <c r="I110" t="s">
         <v>196</v>
       </c>
-      <c r="I110" t="s">
+      <c r="J110" t="s">
         <v>265</v>
       </c>
-      <c r="J110" t="s">
+      <c r="K110" t="s">
         <v>435</v>
       </c>
-      <c r="K110">
+      <c r="L110">
         <v>69000</v>
       </c>
-      <c r="L110">
+      <c r="M110">
         <v>186.666666666667</v>
       </c>
-      <c r="M110">
+      <c r="N110">
         <v>0.22942028985507301</v>
       </c>
-      <c r="N110">
+      <c r="O110">
         <v>15830</v>
       </c>
     </row>
-    <row r="111" spans="1:14">
+    <row r="111" spans="1:15">
       <c r="A111">
         <v>110</v>
       </c>
@@ -6692,32 +7065,35 @@
       <c r="F111" t="s">
         <v>267</v>
       </c>
-      <c r="G111" t="s">
-        <v>7</v>
+      <c r="G111" s="12">
+        <v>2017</v>
       </c>
       <c r="H111" t="s">
+        <v>7</v>
+      </c>
+      <c r="I111" t="s">
         <v>196</v>
       </c>
-      <c r="I111" t="s">
+      <c r="J111" t="s">
         <v>268</v>
       </c>
-      <c r="J111" t="s">
+      <c r="K111" t="s">
         <v>435</v>
       </c>
-      <c r="K111">
+      <c r="L111">
         <v>54000</v>
       </c>
-      <c r="L111">
+      <c r="M111">
         <v>151.111111111111</v>
       </c>
-      <c r="M111">
+      <c r="N111">
         <v>0.36928703703703702</v>
       </c>
-      <c r="N111">
+      <c r="O111">
         <v>19941.5</v>
       </c>
     </row>
-    <row r="112" spans="1:14">
+    <row r="112" spans="1:15">
       <c r="A112">
         <v>111</v>
       </c>
@@ -6733,32 +7109,35 @@
       <c r="E112" t="s">
         <v>16</v>
       </c>
-      <c r="G112" t="s">
-        <v>7</v>
+      <c r="G112" s="12">
+        <v>2021</v>
       </c>
       <c r="H112" t="s">
+        <v>7</v>
+      </c>
+      <c r="I112" t="s">
         <v>196</v>
       </c>
-      <c r="I112" t="s">
+      <c r="J112" t="s">
         <v>270</v>
       </c>
-      <c r="J112" t="s">
+      <c r="K112" t="s">
         <v>435</v>
       </c>
-      <c r="K112">
+      <c r="L112">
         <v>57400</v>
       </c>
-      <c r="L112">
+      <c r="M112">
         <v>280</v>
       </c>
-      <c r="M112">
+      <c r="N112">
         <v>1.74216027874564E-2</v>
       </c>
-      <c r="N112">
+      <c r="O112">
         <v>1000</v>
       </c>
     </row>
-    <row r="113" spans="1:16">
+    <row r="113" spans="1:17">
       <c r="A113">
         <v>112</v>
       </c>
@@ -6774,35 +7153,38 @@
       <c r="E113" t="s">
         <v>16</v>
       </c>
-      <c r="G113" t="s">
-        <v>7</v>
+      <c r="G113" s="12">
+        <v>2023</v>
       </c>
       <c r="H113" t="s">
+        <v>7</v>
+      </c>
+      <c r="I113" t="s">
         <v>196</v>
       </c>
-      <c r="I113" s="2" t="s">
+      <c r="J113" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="J113" t="s">
+      <c r="K113" t="s">
         <v>435</v>
       </c>
-      <c r="K113">
+      <c r="L113">
         <v>60000</v>
       </c>
-      <c r="L113">
+      <c r="M113">
         <v>284.16666666666703</v>
       </c>
-      <c r="M113">
+      <c r="N113">
         <v>7.1166666666666696E-3</v>
       </c>
-      <c r="N113">
+      <c r="O113">
         <v>427</v>
       </c>
-      <c r="P113" s="1" t="s">
+      <c r="Q113" s="1" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="114" spans="1:16">
+    <row r="114" spans="1:17">
       <c r="A114">
         <v>113</v>
       </c>
@@ -6818,35 +7200,38 @@
       <c r="E114" t="s">
         <v>16</v>
       </c>
-      <c r="G114" t="s">
-        <v>7</v>
+      <c r="G114" s="12">
+        <v>2023</v>
       </c>
       <c r="H114" t="s">
+        <v>7</v>
+      </c>
+      <c r="I114" t="s">
         <v>196</v>
       </c>
-      <c r="I114" s="2" t="s">
+      <c r="J114" s="2" t="s">
         <v>468</v>
       </c>
-      <c r="J114" t="s">
+      <c r="K114" t="s">
         <v>435</v>
       </c>
-      <c r="K114">
+      <c r="L114">
         <v>60000</v>
       </c>
-      <c r="L114">
+      <c r="M114">
         <v>231.388888888889</v>
       </c>
-      <c r="M114">
+      <c r="N114">
         <v>0.19166666666666701</v>
       </c>
-      <c r="N114">
+      <c r="O114">
         <v>11500</v>
       </c>
-      <c r="P114" s="1" t="s">
+      <c r="Q114" s="1" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="115" spans="1:16">
+    <row r="115" spans="1:17">
       <c r="A115">
         <v>114</v>
       </c>
@@ -6859,32 +7244,35 @@
       <c r="D115" t="s">
         <v>5</v>
       </c>
-      <c r="G115" t="s">
-        <v>7</v>
+      <c r="G115" s="12">
+        <v>2023</v>
       </c>
       <c r="H115" t="s">
+        <v>7</v>
+      </c>
+      <c r="I115" t="s">
         <v>196</v>
       </c>
-      <c r="I115" s="5" t="s">
+      <c r="J115" s="5" t="s">
         <v>471</v>
       </c>
-      <c r="J115" t="s">
+      <c r="K115" t="s">
         <v>435</v>
       </c>
-      <c r="K115">
+      <c r="L115">
         <v>33000</v>
       </c>
-      <c r="L115">
+      <c r="M115">
         <v>311.66666666666703</v>
-      </c>
-      <c r="M115">
-        <v>0</v>
       </c>
       <c r="N115">
         <v>0</v>
       </c>
-    </row>
-    <row r="116" spans="1:16">
+      <c r="O115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:17">
       <c r="A116">
         <v>115</v>
       </c>
@@ -6897,32 +7285,35 @@
       <c r="D116" t="s">
         <v>198</v>
       </c>
-      <c r="G116" t="s">
-        <v>7</v>
+      <c r="G116" s="12">
+        <v>2009</v>
       </c>
       <c r="H116" t="s">
+        <v>7</v>
+      </c>
+      <c r="I116" t="s">
         <v>196</v>
       </c>
-      <c r="I116" t="s">
+      <c r="J116" t="s">
         <v>275</v>
       </c>
-      <c r="J116" t="s">
+      <c r="K116" t="s">
         <v>435</v>
       </c>
-      <c r="K116">
+      <c r="L116">
         <v>88786</v>
       </c>
-      <c r="L116">
+      <c r="M116">
         <v>180.833333333333</v>
       </c>
-      <c r="M116">
+      <c r="N116">
         <v>0.23652377627103399</v>
       </c>
-      <c r="N116">
+      <c r="O116">
         <v>21000</v>
       </c>
     </row>
-    <row r="117" spans="1:16">
+    <row r="117" spans="1:17">
       <c r="A117">
         <v>116</v>
       </c>
@@ -6935,32 +7326,35 @@
       <c r="D117" t="s">
         <v>198</v>
       </c>
-      <c r="G117" t="s">
-        <v>7</v>
+      <c r="G117" s="12">
+        <v>2016</v>
       </c>
       <c r="H117" t="s">
+        <v>7</v>
+      </c>
+      <c r="I117" t="s">
         <v>196</v>
       </c>
-      <c r="I117" t="s">
+      <c r="J117" t="s">
         <v>277</v>
       </c>
-      <c r="J117" t="s">
+      <c r="K117" t="s">
         <v>435</v>
       </c>
-      <c r="K117">
+      <c r="L117">
         <v>134000</v>
       </c>
-      <c r="L117">
+      <c r="M117">
         <v>193.75</v>
       </c>
-      <c r="M117">
+      <c r="N117">
         <v>0.23798507462686599</v>
       </c>
-      <c r="N117">
+      <c r="O117">
         <v>31890</v>
       </c>
     </row>
-    <row r="118" spans="1:16">
+    <row r="118" spans="1:17">
       <c r="A118">
         <v>117</v>
       </c>
@@ -6973,32 +7367,35 @@
       <c r="D118" t="s">
         <v>198</v>
       </c>
-      <c r="G118" t="s">
-        <v>7</v>
+      <c r="G118" s="12">
+        <v>2021</v>
       </c>
       <c r="H118" t="s">
+        <v>7</v>
+      </c>
+      <c r="I118" t="s">
         <v>196</v>
       </c>
-      <c r="I118" t="s">
+      <c r="J118" t="s">
         <v>279</v>
       </c>
-      <c r="J118" t="s">
+      <c r="K118" t="s">
         <v>435</v>
       </c>
-      <c r="K118">
+      <c r="L118">
         <v>35000</v>
       </c>
-      <c r="L118">
+      <c r="M118">
         <v>225</v>
       </c>
-      <c r="M118">
+      <c r="N118">
         <v>3.1885714285714302E-2</v>
       </c>
-      <c r="N118">
+      <c r="O118">
         <v>1116</v>
       </c>
     </row>
-    <row r="119" spans="1:16">
+    <row r="119" spans="1:17">
       <c r="A119">
         <v>118</v>
       </c>
@@ -7011,32 +7408,35 @@
       <c r="D119" t="s">
         <v>198</v>
       </c>
-      <c r="G119" t="s">
-        <v>7</v>
+      <c r="G119" s="12">
+        <v>2004</v>
       </c>
       <c r="H119" t="s">
+        <v>7</v>
+      </c>
+      <c r="I119" t="s">
         <v>196</v>
       </c>
-      <c r="I119" t="s">
+      <c r="J119" t="s">
         <v>281</v>
       </c>
-      <c r="J119" t="s">
+      <c r="K119" t="s">
         <v>435</v>
       </c>
-      <c r="K119">
+      <c r="L119">
         <v>18000</v>
       </c>
-      <c r="L119">
+      <c r="M119">
         <v>232.5</v>
-      </c>
-      <c r="M119">
-        <v>0</v>
       </c>
       <c r="N119">
         <v>0</v>
       </c>
-    </row>
-    <row r="120" spans="1:16">
+      <c r="O119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:17">
       <c r="A120">
         <v>119</v>
       </c>
@@ -7052,32 +7452,35 @@
       <c r="E120" t="s">
         <v>16</v>
       </c>
-      <c r="G120" t="s">
-        <v>7</v>
+      <c r="G120" s="12">
+        <v>2006</v>
       </c>
       <c r="H120" t="s">
+        <v>7</v>
+      </c>
+      <c r="I120" t="s">
         <v>196</v>
       </c>
-      <c r="I120" t="s">
+      <c r="J120" t="s">
         <v>283</v>
       </c>
-      <c r="J120" t="s">
+      <c r="K120" t="s">
         <v>435</v>
       </c>
-      <c r="K120">
+      <c r="L120">
         <v>105741</v>
       </c>
-      <c r="L120">
+      <c r="M120">
         <v>172.222222222222</v>
       </c>
-      <c r="M120">
+      <c r="N120">
         <v>5.2959589941460702E-2</v>
       </c>
-      <c r="N120">
+      <c r="O120">
         <v>5600</v>
       </c>
     </row>
-    <row r="121" spans="1:16">
+    <row r="121" spans="1:17">
       <c r="A121">
         <v>120</v>
       </c>
@@ -7090,32 +7493,38 @@
       <c r="D121" t="s">
         <v>198</v>
       </c>
-      <c r="G121" t="s">
-        <v>7</v>
+      <c r="E121" t="s">
+        <v>16</v>
+      </c>
+      <c r="G121" s="12">
+        <v>2024</v>
       </c>
       <c r="H121" t="s">
+        <v>7</v>
+      </c>
+      <c r="I121" t="s">
         <v>196</v>
       </c>
-      <c r="I121" t="s">
+      <c r="J121" t="s">
         <v>285</v>
       </c>
-      <c r="J121" t="s">
+      <c r="K121" t="s">
         <v>435</v>
       </c>
-      <c r="K121">
+      <c r="L121">
         <v>51000</v>
       </c>
-      <c r="L121">
+      <c r="M121">
         <v>250</v>
-      </c>
-      <c r="M121">
-        <v>0</v>
       </c>
       <c r="N121">
         <v>0</v>
       </c>
-    </row>
-    <row r="122" spans="1:16">
+      <c r="O121">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:17">
       <c r="A122">
         <v>121</v>
       </c>
@@ -7131,35 +7540,38 @@
       <c r="E122" t="s">
         <v>16</v>
       </c>
-      <c r="G122" t="s">
-        <v>7</v>
+      <c r="G122" s="12">
+        <v>2024</v>
       </c>
       <c r="H122" t="s">
+        <v>7</v>
+      </c>
+      <c r="I122" t="s">
         <v>196</v>
       </c>
-      <c r="I122" s="3" t="s">
-        <v>497</v>
-      </c>
-      <c r="J122" t="s">
+      <c r="J122" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="K122" t="s">
         <v>435</v>
       </c>
-      <c r="K122">
+      <c r="L122">
         <v>130143</v>
       </c>
-      <c r="L122">
+      <c r="M122">
         <v>125</v>
       </c>
-      <c r="M122">
+      <c r="N122">
         <v>0.27661879624720498</v>
       </c>
-      <c r="N122">
+      <c r="O122">
         <v>36000</v>
       </c>
-      <c r="P122" s="1" t="s">
+      <c r="Q122" s="1" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="123" spans="1:16">
+    <row r="123" spans="1:17">
       <c r="A123">
         <v>122</v>
       </c>
@@ -7169,35 +7581,38 @@
       <c r="C123" t="s">
         <v>239</v>
       </c>
-      <c r="G123" t="s">
-        <v>7</v>
+      <c r="G123" s="12">
+        <v>2025</v>
       </c>
       <c r="H123" t="s">
+        <v>7</v>
+      </c>
+      <c r="I123" t="s">
         <v>196</v>
       </c>
-      <c r="I123" s="3" t="s">
-        <v>498</v>
-      </c>
-      <c r="J123" t="s">
+      <c r="J123" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="K123" t="s">
         <v>435</v>
       </c>
-      <c r="K123">
+      <c r="L123">
         <v>121551.47</v>
       </c>
-      <c r="L123">
+      <c r="M123">
         <v>151.111111111111</v>
       </c>
-      <c r="M123">
+      <c r="N123">
         <v>0.800701710970669</v>
       </c>
-      <c r="N123">
+      <c r="O123">
         <v>97326.47</v>
       </c>
-      <c r="P123" s="1" t="s">
+      <c r="Q123" s="1" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="124" spans="1:16">
+    <row r="124" spans="1:17">
       <c r="A124">
         <v>123</v>
       </c>
@@ -7216,32 +7631,35 @@
       <c r="F124" t="s">
         <v>289</v>
       </c>
-      <c r="G124" t="s">
-        <v>7</v>
+      <c r="G124" s="12">
+        <v>2008</v>
       </c>
       <c r="H124" t="s">
+        <v>7</v>
+      </c>
+      <c r="I124" t="s">
         <v>8</v>
       </c>
-      <c r="I124" t="s">
+      <c r="J124" t="s">
         <v>290</v>
       </c>
-      <c r="J124" t="s">
+      <c r="K124" t="s">
         <v>436</v>
       </c>
-      <c r="K124">
+      <c r="L124">
         <v>110000</v>
       </c>
-      <c r="L124">
+      <c r="M124">
         <v>170.833333333333</v>
       </c>
-      <c r="M124">
+      <c r="N124">
         <v>0.14505645454545399</v>
       </c>
-      <c r="N124">
+      <c r="O124">
         <v>15956.21</v>
       </c>
     </row>
-    <row r="125" spans="1:16">
+    <row r="125" spans="1:17">
       <c r="A125">
         <v>124</v>
       </c>
@@ -7260,32 +7678,35 @@
       <c r="F125" t="s">
         <v>214</v>
       </c>
-      <c r="G125" t="s">
-        <v>7</v>
+      <c r="G125" s="12">
+        <v>2011</v>
       </c>
       <c r="H125" t="s">
+        <v>7</v>
+      </c>
+      <c r="I125" t="s">
         <v>8</v>
       </c>
-      <c r="I125" t="s">
+      <c r="J125" t="s">
         <v>292</v>
       </c>
-      <c r="J125" t="s">
+      <c r="K125" t="s">
         <v>436</v>
       </c>
-      <c r="K125">
+      <c r="L125">
         <v>56000</v>
       </c>
-      <c r="L125">
+      <c r="M125">
         <v>154.166666666667</v>
       </c>
-      <c r="M125">
+      <c r="N125">
         <v>0.11841071428571399</v>
       </c>
-      <c r="N125">
+      <c r="O125">
         <v>6631</v>
       </c>
     </row>
-    <row r="126" spans="1:16">
+    <row r="126" spans="1:17">
       <c r="A126">
         <v>125</v>
       </c>
@@ -7301,32 +7722,35 @@
       <c r="F126" t="s">
         <v>189</v>
       </c>
-      <c r="G126" t="s">
-        <v>7</v>
+      <c r="G126" s="12">
+        <v>2015</v>
       </c>
       <c r="H126" t="s">
+        <v>7</v>
+      </c>
+      <c r="I126" t="s">
         <v>8</v>
       </c>
-      <c r="I126" t="s">
+      <c r="J126" t="s">
         <v>294</v>
       </c>
-      <c r="J126" t="s">
+      <c r="K126" t="s">
         <v>436</v>
       </c>
-      <c r="K126">
+      <c r="L126">
         <v>89177</v>
       </c>
-      <c r="L126">
+      <c r="M126">
         <v>124.861111111111</v>
       </c>
-      <c r="M126">
+      <c r="N126">
         <v>0.160689976114918</v>
       </c>
-      <c r="N126">
+      <c r="O126">
         <v>14329.850000000002</v>
       </c>
     </row>
-    <row r="127" spans="1:16">
+    <row r="127" spans="1:17">
       <c r="A127">
         <v>126</v>
       </c>
@@ -7345,32 +7769,35 @@
       <c r="F127" t="s">
         <v>296</v>
       </c>
-      <c r="G127" t="s">
-        <v>7</v>
+      <c r="G127" s="12">
+        <v>2015</v>
       </c>
       <c r="H127" t="s">
+        <v>7</v>
+      </c>
+      <c r="I127" t="s">
         <v>8</v>
       </c>
-      <c r="I127" t="s">
+      <c r="J127" t="s">
         <v>297</v>
       </c>
-      <c r="J127" t="s">
+      <c r="K127" t="s">
         <v>436</v>
       </c>
-      <c r="K127">
+      <c r="L127">
         <v>30000</v>
       </c>
-      <c r="L127">
+      <c r="M127">
         <v>163.611111111111</v>
       </c>
-      <c r="M127">
+      <c r="N127">
         <v>0.2198</v>
       </c>
-      <c r="N127">
+      <c r="O127">
         <v>6594</v>
       </c>
     </row>
-    <row r="128" spans="1:16">
+    <row r="128" spans="1:17">
       <c r="A128">
         <v>127</v>
       </c>
@@ -7389,32 +7816,35 @@
       <c r="F128" t="s">
         <v>296</v>
       </c>
-      <c r="G128" t="s">
-        <v>7</v>
+      <c r="G128" s="12">
+        <v>2015</v>
       </c>
       <c r="H128" t="s">
+        <v>7</v>
+      </c>
+      <c r="I128" t="s">
         <v>8</v>
       </c>
-      <c r="I128" t="s">
+      <c r="J128" t="s">
         <v>299</v>
       </c>
-      <c r="J128" t="s">
+      <c r="K128" t="s">
         <v>436</v>
       </c>
-      <c r="K128">
+      <c r="L128">
         <v>54550</v>
       </c>
-      <c r="L128">
+      <c r="M128">
         <v>120.833333333333</v>
       </c>
-      <c r="M128">
+      <c r="N128">
         <v>0.183318056828598</v>
       </c>
-      <c r="N128">
+      <c r="O128">
         <v>10000</v>
       </c>
     </row>
-    <row r="129" spans="1:14">
+    <row r="129" spans="1:15">
       <c r="A129">
         <v>128</v>
       </c>
@@ -7433,32 +7863,35 @@
       <c r="F129" t="s">
         <v>227</v>
       </c>
-      <c r="G129" t="s">
-        <v>7</v>
+      <c r="G129" s="12">
+        <v>2016</v>
       </c>
       <c r="H129" t="s">
+        <v>7</v>
+      </c>
+      <c r="I129" t="s">
         <v>8</v>
       </c>
-      <c r="I129" t="s">
+      <c r="J129" t="s">
         <v>301</v>
       </c>
-      <c r="J129" t="s">
+      <c r="K129" t="s">
         <v>436</v>
       </c>
-      <c r="K129">
+      <c r="L129">
         <v>125000</v>
       </c>
-      <c r="L129">
+      <c r="M129">
         <v>183.333333333333</v>
       </c>
-      <c r="M129">
+      <c r="N129">
         <v>0.28566256000000001</v>
       </c>
-      <c r="N129">
+      <c r="O129">
         <v>35707.82</v>
       </c>
     </row>
-    <row r="130" spans="1:14">
+    <row r="130" spans="1:15">
       <c r="A130">
         <v>129</v>
       </c>
@@ -7477,32 +7910,35 @@
       <c r="F130" t="s">
         <v>303</v>
       </c>
-      <c r="G130" t="s">
-        <v>7</v>
+      <c r="G130" s="12">
+        <v>2016</v>
       </c>
       <c r="H130" t="s">
+        <v>7</v>
+      </c>
+      <c r="I130" t="s">
         <v>8</v>
       </c>
-      <c r="I130" t="s">
+      <c r="J130" t="s">
         <v>304</v>
       </c>
-      <c r="J130" t="s">
+      <c r="K130" t="s">
         <v>436</v>
       </c>
-      <c r="K130">
+      <c r="L130">
         <v>69100</v>
       </c>
-      <c r="L130">
+      <c r="M130">
         <v>155.555555555555</v>
       </c>
-      <c r="M130">
+      <c r="N130">
         <v>5.9334298118668603E-2</v>
       </c>
-      <c r="N130">
+      <c r="O130">
         <v>4100</v>
       </c>
     </row>
-    <row r="131" spans="1:14">
+    <row r="131" spans="1:15">
       <c r="A131">
         <v>130</v>
       </c>
@@ -7521,32 +7957,35 @@
       <c r="F131" t="s">
         <v>149</v>
       </c>
-      <c r="G131" t="s">
-        <v>7</v>
+      <c r="G131" s="12">
+        <v>2018</v>
       </c>
       <c r="H131" t="s">
+        <v>7</v>
+      </c>
+      <c r="I131" t="s">
         <v>8</v>
       </c>
-      <c r="I131" t="s">
+      <c r="J131" t="s">
         <v>306</v>
       </c>
-      <c r="J131" t="s">
+      <c r="K131" t="s">
         <v>436</v>
       </c>
-      <c r="K131">
+      <c r="L131">
         <v>118290</v>
       </c>
-      <c r="L131">
+      <c r="M131">
         <v>153.055555555555</v>
       </c>
-      <c r="M131">
+      <c r="N131">
         <v>0.166624397666751</v>
       </c>
-      <c r="N131">
+      <c r="O131">
         <v>19710</v>
       </c>
     </row>
-    <row r="132" spans="1:14">
+    <row r="132" spans="1:15">
       <c r="A132">
         <v>131</v>
       </c>
@@ -7559,35 +7998,41 @@
       <c r="D132" t="s">
         <v>5</v>
       </c>
+      <c r="E132" t="s">
+        <v>16</v>
+      </c>
       <c r="F132" t="s">
         <v>308</v>
       </c>
-      <c r="G132" t="s">
-        <v>7</v>
+      <c r="G132" s="12">
+        <v>2018</v>
       </c>
       <c r="H132" t="s">
+        <v>7</v>
+      </c>
+      <c r="I132" t="s">
         <v>8</v>
       </c>
-      <c r="I132" t="s">
+      <c r="J132" t="s">
         <v>309</v>
       </c>
-      <c r="J132" t="s">
+      <c r="K132" t="s">
         <v>436</v>
       </c>
-      <c r="K132">
+      <c r="L132">
         <v>79900</v>
       </c>
-      <c r="L132">
+      <c r="M132">
         <v>155.555555555555</v>
       </c>
-      <c r="M132">
+      <c r="N132">
         <v>0.14313241551939901</v>
       </c>
-      <c r="N132">
+      <c r="O132">
         <v>11436.280000000002</v>
       </c>
     </row>
-    <row r="133" spans="1:14">
+    <row r="133" spans="1:15">
       <c r="A133">
         <v>132</v>
       </c>
@@ -7600,35 +8045,41 @@
       <c r="D133" t="s">
         <v>5</v>
       </c>
+      <c r="E133" t="s">
+        <v>16</v>
+      </c>
       <c r="F133" t="s">
         <v>152</v>
       </c>
-      <c r="G133" t="s">
-        <v>7</v>
+      <c r="G133" s="12">
+        <v>2018</v>
       </c>
       <c r="H133" t="s">
+        <v>7</v>
+      </c>
+      <c r="I133" t="s">
         <v>8</v>
       </c>
-      <c r="I133" t="s">
+      <c r="J133" t="s">
         <v>311</v>
       </c>
-      <c r="J133" t="s">
+      <c r="K133" t="s">
         <v>436</v>
       </c>
-      <c r="K133">
+      <c r="L133">
         <v>39742.379999999997</v>
       </c>
-      <c r="L133">
+      <c r="M133">
         <v>133.472222222222</v>
       </c>
-      <c r="M133">
+      <c r="N133">
         <v>0.14746550156281499</v>
       </c>
-      <c r="N133">
+      <c r="O133">
         <v>5860.63</v>
       </c>
     </row>
-    <row r="134" spans="1:14">
+    <row r="134" spans="1:15">
       <c r="A134">
         <v>133</v>
       </c>
@@ -7647,32 +8098,35 @@
       <c r="F134" t="s">
         <v>84</v>
       </c>
-      <c r="G134" t="s">
-        <v>7</v>
+      <c r="G134" s="12">
+        <v>2019</v>
       </c>
       <c r="H134" t="s">
+        <v>7</v>
+      </c>
+      <c r="I134" t="s">
         <v>8</v>
       </c>
-      <c r="I134" t="s">
+      <c r="J134" t="s">
         <v>313</v>
       </c>
-      <c r="J134" t="s">
+      <c r="K134" t="s">
         <v>436</v>
       </c>
-      <c r="K134">
+      <c r="L134">
         <v>48000</v>
       </c>
-      <c r="L134">
+      <c r="M134">
         <v>152.777777777778</v>
       </c>
-      <c r="M134">
+      <c r="N134">
         <v>0.13894520833333299</v>
       </c>
-      <c r="N134">
+      <c r="O134">
         <v>6669.369999999999</v>
       </c>
     </row>
-    <row r="135" spans="1:14">
+    <row r="135" spans="1:15">
       <c r="A135">
         <v>134</v>
       </c>
@@ -7689,31 +8143,34 @@
         <v>23</v>
       </c>
       <c r="G135" t="s">
-        <v>7</v>
+        <v>508</v>
       </c>
       <c r="H135" t="s">
+        <v>7</v>
+      </c>
+      <c r="I135" t="s">
         <v>8</v>
       </c>
-      <c r="I135" t="s">
+      <c r="J135" t="s">
         <v>315</v>
       </c>
-      <c r="J135" t="s">
+      <c r="K135" t="s">
         <v>436</v>
       </c>
-      <c r="K135">
+      <c r="L135">
         <v>74722</v>
       </c>
-      <c r="L135">
+      <c r="M135">
         <v>159.444444444445</v>
       </c>
-      <c r="M135">
+      <c r="N135">
         <v>0.431922325419555</v>
       </c>
-      <c r="N135">
+      <c r="O135">
         <v>32274.100000000002</v>
       </c>
     </row>
-    <row r="136" spans="1:14">
+    <row r="136" spans="1:15">
       <c r="A136">
         <v>135</v>
       </c>
@@ -7726,32 +8183,38 @@
       <c r="D136" t="s">
         <v>198</v>
       </c>
+      <c r="E136" t="s">
+        <v>396</v>
+      </c>
       <c r="G136" t="s">
-        <v>7</v>
+        <v>508</v>
       </c>
       <c r="H136" t="s">
+        <v>7</v>
+      </c>
+      <c r="I136" t="s">
         <v>8</v>
       </c>
-      <c r="I136" t="s">
+      <c r="J136" t="s">
         <v>317</v>
       </c>
-      <c r="J136" t="s">
+      <c r="K136" t="s">
         <v>436</v>
       </c>
-      <c r="K136">
+      <c r="L136">
         <v>55000</v>
       </c>
-      <c r="L136">
+      <c r="M136">
         <v>120.555555555556</v>
       </c>
-      <c r="M136">
+      <c r="N136">
         <v>3.4563636363636401E-2</v>
       </c>
-      <c r="N136">
+      <c r="O136">
         <v>1901</v>
       </c>
     </row>
-    <row r="137" spans="1:14">
+    <row r="137" spans="1:15">
       <c r="A137">
         <v>136</v>
       </c>
@@ -7765,31 +8228,34 @@
         <v>5</v>
       </c>
       <c r="G137" t="s">
-        <v>7</v>
+        <v>508</v>
       </c>
       <c r="H137" t="s">
+        <v>7</v>
+      </c>
+      <c r="I137" t="s">
         <v>112</v>
       </c>
-      <c r="I137" t="s">
+      <c r="J137" t="s">
         <v>320</v>
       </c>
-      <c r="J137" t="s">
+      <c r="K137" t="s">
         <v>449</v>
       </c>
-      <c r="K137">
+      <c r="L137">
         <v>128000</v>
       </c>
-      <c r="L137">
+      <c r="M137">
         <v>197.083333333333</v>
       </c>
-      <c r="M137">
+      <c r="N137">
         <v>6.7101562500000003E-2</v>
       </c>
-      <c r="N137">
+      <c r="O137">
         <v>6126</v>
       </c>
     </row>
-    <row r="138" spans="1:14">
+    <row r="138" spans="1:15">
       <c r="A138">
         <v>137</v>
       </c>
@@ -7808,32 +8274,35 @@
       <c r="F138" t="s">
         <v>58</v>
       </c>
-      <c r="G138" t="s">
-        <v>7</v>
+      <c r="G138" s="12">
+        <v>2008</v>
       </c>
       <c r="H138" t="s">
+        <v>7</v>
+      </c>
+      <c r="I138" t="s">
         <v>112</v>
       </c>
-      <c r="I138" t="s">
+      <c r="J138" t="s">
         <v>322</v>
       </c>
-      <c r="J138" t="s">
+      <c r="K138" t="s">
         <v>449</v>
       </c>
-      <c r="K138">
+      <c r="L138">
         <v>122000</v>
       </c>
-      <c r="L138">
+      <c r="M138">
         <v>195.555555555555</v>
       </c>
-      <c r="M138">
+      <c r="N138">
         <v>1.7885245901639299E-2</v>
       </c>
-      <c r="N138">
+      <c r="O138">
         <v>2182</v>
       </c>
     </row>
-    <row r="139" spans="1:14">
+    <row r="139" spans="1:15">
       <c r="A139">
         <v>138</v>
       </c>
@@ -7849,32 +8318,35 @@
       <c r="F139" t="s">
         <v>15</v>
       </c>
-      <c r="G139" t="s">
-        <v>7</v>
+      <c r="G139" s="12">
+        <v>2010</v>
       </c>
       <c r="H139" t="s">
+        <v>7</v>
+      </c>
+      <c r="I139" t="s">
         <v>112</v>
       </c>
-      <c r="I139" t="s">
+      <c r="J139" t="s">
         <v>324</v>
       </c>
-      <c r="J139" t="s">
+      <c r="K139" t="s">
         <v>449</v>
       </c>
-      <c r="K139">
+      <c r="L139">
         <v>22000</v>
       </c>
-      <c r="L139">
+      <c r="M139">
         <v>197.083333333333</v>
       </c>
-      <c r="M139">
+      <c r="N139">
         <v>0.20981818181818199</v>
       </c>
-      <c r="N139">
+      <c r="O139">
         <v>4616</v>
       </c>
     </row>
-    <row r="140" spans="1:14">
+    <row r="140" spans="1:15">
       <c r="A140">
         <v>139</v>
       </c>
@@ -7890,32 +8362,35 @@
       <c r="F140" t="s">
         <v>15</v>
       </c>
-      <c r="G140" t="s">
-        <v>7</v>
+      <c r="G140" s="12">
+        <v>2010</v>
       </c>
       <c r="H140" t="s">
+        <v>7</v>
+      </c>
+      <c r="I140" t="s">
         <v>112</v>
       </c>
-      <c r="I140" t="s">
+      <c r="J140" t="s">
         <v>326</v>
       </c>
-      <c r="J140" t="s">
+      <c r="K140" t="s">
         <v>449</v>
       </c>
-      <c r="K140">
+      <c r="L140">
         <v>10000</v>
       </c>
-      <c r="L140">
+      <c r="M140">
         <v>255</v>
-      </c>
-      <c r="M140">
-        <v>0</v>
       </c>
       <c r="N140">
         <v>0</v>
       </c>
-    </row>
-    <row r="141" spans="1:14">
+      <c r="O140">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:15">
       <c r="A141">
         <v>140</v>
       </c>
@@ -7931,32 +8406,35 @@
       <c r="F141" t="s">
         <v>55</v>
       </c>
-      <c r="G141" t="s">
-        <v>7</v>
+      <c r="G141" s="12">
+        <v>2008</v>
       </c>
       <c r="H141" t="s">
+        <v>7</v>
+      </c>
+      <c r="I141" t="s">
         <v>8</v>
       </c>
-      <c r="I141" t="s">
+      <c r="J141" t="s">
         <v>328</v>
       </c>
-      <c r="J141" t="s">
+      <c r="K141" t="s">
         <v>434</v>
       </c>
-      <c r="K141">
+      <c r="L141">
         <v>64000</v>
       </c>
-      <c r="L141">
+      <c r="M141">
         <v>177.777777777778</v>
       </c>
-      <c r="M141">
+      <c r="N141">
         <v>0.28125</v>
       </c>
-      <c r="N141">
+      <c r="O141">
         <v>18000</v>
       </c>
     </row>
-    <row r="142" spans="1:14">
+    <row r="142" spans="1:15">
       <c r="A142">
         <v>141</v>
       </c>
@@ -7972,32 +8450,35 @@
       <c r="F142" t="s">
         <v>64</v>
       </c>
-      <c r="G142" t="s">
-        <v>7</v>
+      <c r="G142" s="12">
+        <v>2009</v>
       </c>
       <c r="H142" t="s">
+        <v>7</v>
+      </c>
+      <c r="I142" t="s">
         <v>8</v>
       </c>
-      <c r="I142" t="s">
+      <c r="J142" t="s">
         <v>330</v>
       </c>
-      <c r="J142" t="s">
+      <c r="K142" t="s">
         <v>434</v>
       </c>
-      <c r="K142">
+      <c r="L142">
         <v>95628</v>
       </c>
-      <c r="L142">
+      <c r="M142">
         <v>165</v>
       </c>
-      <c r="M142">
+      <c r="N142">
         <v>0.247417074497009</v>
       </c>
-      <c r="N142">
+      <c r="O142">
         <v>23660</v>
       </c>
     </row>
-    <row r="143" spans="1:14">
+    <row r="143" spans="1:15">
       <c r="A143">
         <v>142</v>
       </c>
@@ -8013,32 +8494,35 @@
       <c r="F143" t="s">
         <v>332</v>
       </c>
-      <c r="G143" t="s">
-        <v>7</v>
+      <c r="G143" s="12">
+        <v>2009</v>
       </c>
       <c r="H143" t="s">
+        <v>7</v>
+      </c>
+      <c r="I143" t="s">
         <v>8</v>
       </c>
-      <c r="I143" t="s">
+      <c r="J143" t="s">
         <v>333</v>
       </c>
-      <c r="J143" t="s">
+      <c r="K143" t="s">
         <v>434</v>
       </c>
-      <c r="K143">
+      <c r="L143">
         <v>39562</v>
       </c>
-      <c r="L143">
+      <c r="M143">
         <v>151.111111111111</v>
       </c>
-      <c r="M143">
+      <c r="N143">
         <v>0.183913856731207</v>
       </c>
-      <c r="N143">
+      <c r="O143">
         <v>7276</v>
       </c>
     </row>
-    <row r="144" spans="1:14">
+    <row r="144" spans="1:15">
       <c r="A144">
         <v>143</v>
       </c>
@@ -8057,32 +8541,35 @@
       <c r="F144" t="s">
         <v>335</v>
       </c>
-      <c r="G144" t="s">
-        <v>7</v>
+      <c r="G144" s="12">
+        <v>2010</v>
       </c>
       <c r="H144" t="s">
+        <v>7</v>
+      </c>
+      <c r="I144" t="s">
         <v>8</v>
       </c>
-      <c r="I144" t="s">
+      <c r="J144" t="s">
         <v>336</v>
       </c>
-      <c r="J144" t="s">
+      <c r="K144" t="s">
         <v>449</v>
       </c>
-      <c r="K144">
+      <c r="L144">
         <v>105000</v>
       </c>
-      <c r="L144">
+      <c r="M144">
         <v>155.555555555555</v>
       </c>
-      <c r="M144">
+      <c r="N144">
         <v>0.75</v>
       </c>
-      <c r="N144">
+      <c r="O144">
         <v>78750</v>
       </c>
     </row>
-    <row r="145" spans="1:14">
+    <row r="145" spans="1:15">
       <c r="A145">
         <v>144</v>
       </c>
@@ -8101,32 +8588,35 @@
       <c r="F145" t="s">
         <v>303</v>
       </c>
-      <c r="G145" t="s">
-        <v>7</v>
+      <c r="G145" s="12">
+        <v>2016</v>
       </c>
       <c r="H145" t="s">
+        <v>7</v>
+      </c>
+      <c r="I145" t="s">
         <v>8</v>
       </c>
-      <c r="I145" s="2" t="s">
+      <c r="J145" s="2" t="s">
         <v>460</v>
       </c>
-      <c r="J145" t="s">
+      <c r="K145" t="s">
         <v>449</v>
       </c>
-      <c r="K145">
+      <c r="L145">
         <v>60000</v>
       </c>
-      <c r="L145">
+      <c r="M145">
         <v>204.444444444445</v>
       </c>
-      <c r="M145">
+      <c r="N145">
         <v>0.66666666666666696</v>
       </c>
-      <c r="N145">
+      <c r="O145">
         <v>40000</v>
       </c>
     </row>
-    <row r="146" spans="1:14">
+    <row r="146" spans="1:15">
       <c r="A146">
         <v>145</v>
       </c>
@@ -8142,32 +8632,35 @@
       <c r="F146" t="s">
         <v>142</v>
       </c>
-      <c r="G146" t="s">
-        <v>7</v>
+      <c r="G146" s="12">
+        <v>2016</v>
       </c>
       <c r="H146" t="s">
+        <v>7</v>
+      </c>
+      <c r="I146" t="s">
         <v>8</v>
       </c>
-      <c r="I146" t="s">
+      <c r="J146" t="s">
         <v>338</v>
       </c>
-      <c r="J146" t="s">
+      <c r="K146" t="s">
         <v>434</v>
       </c>
-      <c r="K146">
+      <c r="L146">
         <v>39964</v>
       </c>
-      <c r="L146">
+      <c r="M146">
         <v>275</v>
       </c>
-      <c r="M146">
+      <c r="N146">
         <v>3.2529276348713901E-2</v>
       </c>
-      <c r="N146">
+      <c r="O146">
         <v>1300</v>
       </c>
     </row>
-    <row r="147" spans="1:14">
+    <row r="147" spans="1:15">
       <c r="A147">
         <v>146</v>
       </c>
@@ -8180,35 +8673,41 @@
       <c r="D147" t="s">
         <v>5</v>
       </c>
+      <c r="E147" t="s">
+        <v>16</v>
+      </c>
       <c r="F147" t="s">
         <v>19</v>
       </c>
-      <c r="G147" t="s">
-        <v>7</v>
+      <c r="G147" s="12">
+        <v>2017</v>
       </c>
       <c r="H147" t="s">
+        <v>7</v>
+      </c>
+      <c r="I147" t="s">
         <v>8</v>
       </c>
-      <c r="I147" t="s">
+      <c r="J147" t="s">
         <v>340</v>
       </c>
-      <c r="J147" t="s">
+      <c r="K147" t="s">
         <v>449</v>
       </c>
-      <c r="K147">
+      <c r="L147">
         <v>94000</v>
       </c>
-      <c r="L147">
+      <c r="M147">
         <v>257.777777777778</v>
       </c>
-      <c r="M147">
+      <c r="N147">
         <v>0.12765957446808501</v>
       </c>
-      <c r="N147">
+      <c r="O147">
         <v>12000</v>
       </c>
     </row>
-    <row r="148" spans="1:14">
+    <row r="148" spans="1:15">
       <c r="A148">
         <v>147</v>
       </c>
@@ -8227,32 +8726,35 @@
       <c r="F148" t="s">
         <v>146</v>
       </c>
-      <c r="G148" t="s">
-        <v>7</v>
+      <c r="G148" s="12">
+        <v>2017</v>
       </c>
       <c r="H148" t="s">
+        <v>7</v>
+      </c>
+      <c r="I148" t="s">
         <v>8</v>
       </c>
-      <c r="I148" s="2" t="s">
+      <c r="J148" s="2" t="s">
         <v>461</v>
       </c>
-      <c r="J148" t="s">
+      <c r="K148" t="s">
         <v>449</v>
       </c>
-      <c r="K148">
+      <c r="L148">
         <v>75000</v>
       </c>
-      <c r="L148">
+      <c r="M148">
         <v>166.666666666667</v>
       </c>
-      <c r="M148">
+      <c r="N148">
         <v>0.41537333333333298</v>
       </c>
-      <c r="N148">
+      <c r="O148">
         <v>31153</v>
       </c>
     </row>
-    <row r="149" spans="1:14">
+    <row r="149" spans="1:15">
       <c r="A149">
         <v>148</v>
       </c>
@@ -8265,35 +8767,41 @@
       <c r="D149" t="s">
         <v>5</v>
       </c>
+      <c r="E149" t="s">
+        <v>16</v>
+      </c>
       <c r="F149" t="s">
         <v>341</v>
       </c>
-      <c r="G149" t="s">
-        <v>7</v>
-      </c>
-      <c r="H149" s="7" t="s">
+      <c r="G149" s="12">
+        <v>2017</v>
+      </c>
+      <c r="H149" t="s">
+        <v>7</v>
+      </c>
+      <c r="I149" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="I149" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="J149" t="s">
+      <c r="J149" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="K149" t="s">
         <v>449</v>
       </c>
-      <c r="K149">
+      <c r="L149">
         <v>48767</v>
       </c>
-      <c r="L149">
+      <c r="M149">
         <v>311.66666666666703</v>
       </c>
-      <c r="M149">
+      <c r="N149">
         <v>1.00477782106753E-2</v>
       </c>
-      <c r="N149">
+      <c r="O149">
         <v>490</v>
       </c>
     </row>
-    <row r="150" spans="1:14">
+    <row r="150" spans="1:15">
       <c r="A150">
         <v>149</v>
       </c>
@@ -8312,32 +8820,35 @@
       <c r="F150" t="s">
         <v>84</v>
       </c>
-      <c r="G150" t="s">
-        <v>7</v>
+      <c r="G150" s="12">
+        <v>2019</v>
       </c>
       <c r="H150" t="s">
+        <v>7</v>
+      </c>
+      <c r="I150" t="s">
         <v>8</v>
       </c>
-      <c r="I150" t="s">
+      <c r="J150" t="s">
         <v>343</v>
       </c>
-      <c r="J150" t="s">
+      <c r="K150" t="s">
         <v>449</v>
       </c>
-      <c r="K150">
+      <c r="L150">
         <v>63824</v>
       </c>
-      <c r="L150">
+      <c r="M150">
         <v>223.888888888889</v>
       </c>
-      <c r="M150">
+      <c r="N150">
         <v>0.144663449486087</v>
       </c>
-      <c r="N150">
+      <c r="O150">
         <v>9233</v>
       </c>
     </row>
-    <row r="151" spans="1:14">
+    <row r="151" spans="1:15">
       <c r="A151">
         <v>150</v>
       </c>
@@ -8356,32 +8867,35 @@
       <c r="F151" t="s">
         <v>87</v>
       </c>
-      <c r="G151" t="s">
-        <v>7</v>
+      <c r="G151" s="12">
+        <v>2019</v>
       </c>
       <c r="H151" t="s">
+        <v>7</v>
+      </c>
+      <c r="I151" t="s">
         <v>8</v>
       </c>
-      <c r="I151" t="s">
+      <c r="J151" t="s">
         <v>345</v>
       </c>
-      <c r="J151" t="s">
+      <c r="K151" t="s">
         <v>449</v>
       </c>
-      <c r="K151">
+      <c r="L151">
         <v>117000</v>
       </c>
-      <c r="L151">
+      <c r="M151">
         <v>311.66666666666703</v>
-      </c>
-      <c r="M151">
-        <v>0</v>
       </c>
       <c r="N151">
         <v>0</v>
       </c>
-    </row>
-    <row r="152" spans="1:14">
+      <c r="O151">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:15">
       <c r="A152">
         <v>151</v>
       </c>
@@ -8395,31 +8909,34 @@
         <v>5</v>
       </c>
       <c r="G152" t="s">
-        <v>7</v>
+        <v>508</v>
       </c>
       <c r="H152" t="s">
+        <v>7</v>
+      </c>
+      <c r="I152" t="s">
         <v>8</v>
       </c>
-      <c r="I152" t="s">
+      <c r="J152" t="s">
         <v>347</v>
       </c>
-      <c r="J152" t="s">
+      <c r="K152" t="s">
         <v>449</v>
       </c>
-      <c r="K152">
+      <c r="L152">
         <v>41000</v>
       </c>
-      <c r="L152">
+      <c r="M152">
         <v>204.444444444445</v>
       </c>
-      <c r="M152">
+      <c r="N152">
         <v>0.11219512195122</v>
       </c>
-      <c r="N152">
+      <c r="O152">
         <v>4600</v>
       </c>
     </row>
-    <row r="153" spans="1:14">
+    <row r="153" spans="1:15">
       <c r="A153">
         <v>152</v>
       </c>
@@ -8432,32 +8949,38 @@
       <c r="D153" t="s">
         <v>5</v>
       </c>
+      <c r="E153" t="s">
+        <v>23</v>
+      </c>
       <c r="G153" t="s">
-        <v>7</v>
+        <v>508</v>
       </c>
       <c r="H153" t="s">
+        <v>7</v>
+      </c>
+      <c r="I153" t="s">
         <v>8</v>
       </c>
-      <c r="I153" t="s">
+      <c r="J153" t="s">
         <v>349</v>
       </c>
-      <c r="J153" t="s">
+      <c r="K153" t="s">
         <v>434</v>
       </c>
-      <c r="K153">
+      <c r="L153">
         <v>96446</v>
       </c>
-      <c r="L153">
+      <c r="M153">
         <v>284.16666666666703</v>
       </c>
-      <c r="M153">
+      <c r="N153">
         <v>0.334902432449246</v>
       </c>
-      <c r="N153">
+      <c r="O153">
         <v>32300</v>
       </c>
     </row>
-    <row r="154" spans="1:14">
+    <row r="154" spans="1:15">
       <c r="A154">
         <v>153</v>
       </c>
@@ -8476,32 +8999,35 @@
       <c r="F154" t="s">
         <v>152</v>
       </c>
-      <c r="G154" t="s">
-        <v>7</v>
+      <c r="G154" s="12">
+        <v>2018</v>
       </c>
       <c r="H154" t="s">
+        <v>7</v>
+      </c>
+      <c r="I154" t="s">
         <v>352</v>
       </c>
-      <c r="I154" t="s">
+      <c r="J154" t="s">
         <v>353</v>
       </c>
-      <c r="J154" t="s">
+      <c r="K154" t="s">
         <v>449</v>
       </c>
-      <c r="K154">
+      <c r="L154">
         <v>76600</v>
       </c>
-      <c r="L154">
+      <c r="M154">
         <v>131.111111111111</v>
       </c>
-      <c r="M154">
+      <c r="N154">
         <v>0.241919060052219</v>
       </c>
-      <c r="N154">
+      <c r="O154">
         <v>18531</v>
       </c>
     </row>
-    <row r="155" spans="1:14">
+    <row r="155" spans="1:15">
       <c r="A155">
         <v>154</v>
       </c>
@@ -8514,35 +9040,41 @@
       <c r="D155" t="s">
         <v>5</v>
       </c>
+      <c r="E155" t="s">
+        <v>16</v>
+      </c>
       <c r="F155" t="s">
         <v>152</v>
       </c>
-      <c r="G155" t="s">
-        <v>7</v>
+      <c r="G155" s="12">
+        <v>2018</v>
       </c>
       <c r="H155" t="s">
+        <v>7</v>
+      </c>
+      <c r="I155" t="s">
         <v>352</v>
       </c>
-      <c r="I155" t="s">
+      <c r="J155" t="s">
         <v>355</v>
       </c>
-      <c r="J155" t="s">
+      <c r="K155" t="s">
         <v>437</v>
       </c>
-      <c r="K155">
+      <c r="L155">
         <v>125569</v>
       </c>
-      <c r="L155">
+      <c r="M155">
         <v>137.5</v>
       </c>
-      <c r="M155">
+      <c r="N155">
         <v>0.25245084375920801</v>
       </c>
-      <c r="N155">
+      <c r="O155">
         <v>31700</v>
       </c>
     </row>
-    <row r="156" spans="1:14">
+    <row r="156" spans="1:15">
       <c r="A156">
         <v>155</v>
       </c>
@@ -8555,35 +9087,41 @@
       <c r="D156" t="s">
         <v>5</v>
       </c>
+      <c r="E156" t="s">
+        <v>16</v>
+      </c>
       <c r="F156" t="s">
         <v>357</v>
       </c>
-      <c r="G156" t="s">
-        <v>7</v>
+      <c r="G156" s="12">
+        <v>2019</v>
       </c>
       <c r="H156" t="s">
+        <v>7</v>
+      </c>
+      <c r="I156" t="s">
         <v>352</v>
       </c>
-      <c r="I156" t="s">
+      <c r="J156" t="s">
         <v>358</v>
       </c>
-      <c r="J156" t="s">
+      <c r="K156" t="s">
         <v>449</v>
       </c>
-      <c r="K156">
+      <c r="L156">
         <v>51234</v>
       </c>
-      <c r="L156">
+      <c r="M156">
         <v>120.555555555556</v>
       </c>
-      <c r="M156">
+      <c r="N156">
         <v>7.9868837100362994E-2</v>
       </c>
-      <c r="N156">
+      <c r="O156">
         <v>4092</v>
       </c>
     </row>
-    <row r="157" spans="1:14">
+    <row r="157" spans="1:15">
       <c r="A157">
         <v>156</v>
       </c>
@@ -8602,32 +9140,35 @@
       <c r="F157" t="s">
         <v>87</v>
       </c>
-      <c r="G157" t="s">
-        <v>7</v>
+      <c r="G157" s="12">
+        <v>2019</v>
       </c>
       <c r="H157" t="s">
+        <v>7</v>
+      </c>
+      <c r="I157" t="s">
         <v>352</v>
       </c>
-      <c r="I157" t="s">
+      <c r="J157" t="s">
         <v>360</v>
       </c>
-      <c r="J157" t="s">
+      <c r="K157" t="s">
         <v>437</v>
       </c>
-      <c r="K157">
+      <c r="L157">
         <v>123780</v>
       </c>
-      <c r="L157">
+      <c r="M157">
         <v>123.75</v>
       </c>
-      <c r="M157">
+      <c r="N157">
         <v>0.12417999676846</v>
       </c>
-      <c r="N157">
+      <c r="O157">
         <v>15371</v>
       </c>
     </row>
-    <row r="158" spans="1:14">
+    <row r="158" spans="1:15">
       <c r="A158">
         <v>157</v>
       </c>
@@ -8643,32 +9184,35 @@
       <c r="F158" t="s">
         <v>362</v>
       </c>
-      <c r="G158" t="s">
-        <v>7</v>
+      <c r="G158" s="12">
+        <v>2019</v>
       </c>
       <c r="H158" t="s">
+        <v>7</v>
+      </c>
+      <c r="I158" t="s">
         <v>352</v>
       </c>
-      <c r="I158" t="s">
+      <c r="J158" t="s">
         <v>363</v>
       </c>
-      <c r="J158" t="s">
+      <c r="K158" t="s">
         <v>449</v>
       </c>
-      <c r="K158">
+      <c r="L158">
         <v>46000</v>
       </c>
-      <c r="L158">
+      <c r="M158">
         <v>185</v>
-      </c>
-      <c r="M158">
-        <v>0</v>
       </c>
       <c r="N158">
         <v>0</v>
       </c>
-    </row>
-    <row r="159" spans="1:14">
+      <c r="O158">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="1:15">
       <c r="A159">
         <v>158</v>
       </c>
@@ -8681,32 +9225,38 @@
       <c r="D159" t="s">
         <v>5</v>
       </c>
+      <c r="E159" t="s">
+        <v>16</v>
+      </c>
       <c r="G159" t="s">
-        <v>7</v>
+        <v>508</v>
       </c>
       <c r="H159" t="s">
+        <v>7</v>
+      </c>
+      <c r="I159" t="s">
         <v>352</v>
       </c>
-      <c r="I159" t="s">
+      <c r="J159" t="s">
         <v>365</v>
       </c>
-      <c r="J159" t="s">
+      <c r="K159" t="s">
         <v>449</v>
       </c>
-      <c r="K159">
+      <c r="L159">
         <v>35600</v>
       </c>
-      <c r="L159">
+      <c r="M159">
         <v>146.388888888889</v>
       </c>
-      <c r="M159">
+      <c r="N159">
         <v>0.12019662921348299</v>
       </c>
-      <c r="N159">
+      <c r="O159">
         <v>4279</v>
       </c>
     </row>
-    <row r="160" spans="1:14">
+    <row r="160" spans="1:15">
       <c r="A160">
         <v>159</v>
       </c>
@@ -8723,31 +9273,34 @@
         <v>23</v>
       </c>
       <c r="G160" t="s">
-        <v>7</v>
+        <v>508</v>
       </c>
       <c r="H160" t="s">
+        <v>7</v>
+      </c>
+      <c r="I160" t="s">
         <v>352</v>
       </c>
-      <c r="I160" t="s">
+      <c r="J160" t="s">
         <v>367</v>
       </c>
-      <c r="J160" t="s">
+      <c r="K160" t="s">
         <v>437</v>
       </c>
-      <c r="K160">
+      <c r="L160">
         <v>199950</v>
       </c>
-      <c r="L160">
+      <c r="M160">
         <v>145</v>
       </c>
-      <c r="M160">
+      <c r="N160">
         <v>0.150037509377344</v>
       </c>
-      <c r="N160">
+      <c r="O160">
         <v>30000</v>
       </c>
     </row>
-    <row r="161" spans="1:14">
+    <row r="161" spans="1:15">
       <c r="A161">
         <v>160</v>
       </c>
@@ -8764,31 +9317,34 @@
         <v>16</v>
       </c>
       <c r="G161" t="s">
-        <v>7</v>
+        <v>508</v>
       </c>
       <c r="H161" t="s">
+        <v>7</v>
+      </c>
+      <c r="I161" t="s">
         <v>352</v>
       </c>
-      <c r="I161" t="s">
+      <c r="J161" t="s">
         <v>369</v>
       </c>
-      <c r="J161" t="s">
+      <c r="K161" t="s">
         <v>437</v>
       </c>
-      <c r="K161">
+      <c r="L161">
         <v>108000</v>
       </c>
-      <c r="L161">
+      <c r="M161">
         <v>137.777777777778</v>
       </c>
-      <c r="M161">
+      <c r="N161">
         <v>0.18</v>
       </c>
-      <c r="N161">
+      <c r="O161">
         <v>19440</v>
       </c>
     </row>
-    <row r="162" spans="1:14">
+    <row r="162" spans="1:15">
       <c r="A162">
         <v>161</v>
       </c>
@@ -8805,31 +9361,34 @@
         <v>16</v>
       </c>
       <c r="G162" t="s">
-        <v>7</v>
+        <v>508</v>
       </c>
       <c r="H162" t="s">
+        <v>7</v>
+      </c>
+      <c r="I162" t="s">
         <v>352</v>
       </c>
-      <c r="I162" t="s">
+      <c r="J162" t="s">
         <v>371</v>
       </c>
-      <c r="J162" t="s">
+      <c r="K162" t="s">
         <v>437</v>
       </c>
-      <c r="K162">
+      <c r="L162">
         <v>142808</v>
       </c>
-      <c r="L162">
+      <c r="M162">
         <v>127.5</v>
       </c>
-      <c r="M162">
+      <c r="N162">
         <v>7.1186488151924299E-2</v>
       </c>
-      <c r="N162">
+      <c r="O162">
         <v>10166</v>
       </c>
     </row>
-    <row r="163" spans="1:14">
+    <row r="163" spans="1:15">
       <c r="A163">
         <v>162</v>
       </c>
@@ -8846,31 +9405,34 @@
         <v>16</v>
       </c>
       <c r="G163" t="s">
-        <v>7</v>
+        <v>508</v>
       </c>
       <c r="H163" t="s">
+        <v>7</v>
+      </c>
+      <c r="I163" t="s">
         <v>352</v>
       </c>
-      <c r="I163" t="s">
+      <c r="J163" t="s">
         <v>373</v>
       </c>
-      <c r="J163" t="s">
+      <c r="K163" t="s">
         <v>437</v>
       </c>
-      <c r="K163">
+      <c r="L163">
         <v>80463</v>
       </c>
-      <c r="L163">
+      <c r="M163">
         <v>125</v>
       </c>
-      <c r="M163">
+      <c r="N163">
         <v>0.112026645787505</v>
       </c>
-      <c r="N163">
+      <c r="O163">
         <v>9014</v>
       </c>
     </row>
-    <row r="164" spans="1:14">
+    <row r="164" spans="1:15">
       <c r="A164">
         <v>163</v>
       </c>
@@ -8887,31 +9449,34 @@
         <v>23</v>
       </c>
       <c r="G164" t="s">
-        <v>7</v>
+        <v>508</v>
       </c>
       <c r="H164" t="s">
+        <v>7</v>
+      </c>
+      <c r="I164" t="s">
         <v>352</v>
       </c>
-      <c r="I164" t="s">
+      <c r="J164" t="s">
         <v>375</v>
       </c>
-      <c r="J164" t="s">
+      <c r="K164" t="s">
         <v>449</v>
       </c>
-      <c r="K164">
+      <c r="L164">
         <v>83000</v>
       </c>
-      <c r="L164">
+      <c r="M164">
         <v>141.666666666667</v>
       </c>
-      <c r="M164">
+      <c r="N164">
         <v>0.60361445783132495</v>
       </c>
-      <c r="N164">
+      <c r="O164">
         <v>50100</v>
       </c>
     </row>
-    <row r="165" spans="1:14">
+    <row r="165" spans="1:15">
       <c r="A165">
         <v>164</v>
       </c>
@@ -8925,31 +9490,34 @@
         <v>5</v>
       </c>
       <c r="G165" t="s">
-        <v>7</v>
+        <v>508</v>
       </c>
       <c r="H165" t="s">
+        <v>7</v>
+      </c>
+      <c r="I165" t="s">
         <v>352</v>
       </c>
-      <c r="I165" t="s">
+      <c r="J165" t="s">
         <v>377</v>
       </c>
-      <c r="J165" t="s">
+      <c r="K165" t="s">
         <v>449</v>
       </c>
-      <c r="K165">
+      <c r="L165">
         <v>129000</v>
       </c>
-      <c r="L165">
+      <c r="M165">
         <v>169.166666666667</v>
       </c>
-      <c r="M165">
+      <c r="N165">
         <v>0.39693023255813897</v>
       </c>
-      <c r="N165">
+      <c r="O165">
         <v>51204</v>
       </c>
     </row>
-    <row r="166" spans="1:14">
+    <row r="166" spans="1:15">
       <c r="A166">
         <v>165</v>
       </c>
@@ -8962,35 +9530,41 @@
       <c r="D166" t="s">
         <v>5</v>
       </c>
+      <c r="E166" t="s">
+        <v>16</v>
+      </c>
       <c r="F166" t="s">
         <v>214</v>
       </c>
-      <c r="G166" t="s">
-        <v>7</v>
+      <c r="G166" s="12">
+        <v>2011</v>
       </c>
       <c r="H166" t="s">
+        <v>7</v>
+      </c>
+      <c r="I166" t="s">
         <v>112</v>
       </c>
-      <c r="I166" t="s">
+      <c r="J166" t="s">
         <v>380</v>
       </c>
-      <c r="J166" t="s">
+      <c r="K166" t="s">
         <v>449</v>
       </c>
-      <c r="K166">
+      <c r="L166">
         <v>62209</v>
       </c>
-      <c r="L166">
+      <c r="M166">
         <v>128.888888888889</v>
       </c>
-      <c r="M166">
+      <c r="N166">
         <v>0.13806683920333099</v>
       </c>
-      <c r="N166">
+      <c r="O166">
         <v>8589</v>
       </c>
     </row>
-    <row r="167" spans="1:14">
+    <row r="167" spans="1:15">
       <c r="A167">
         <v>166</v>
       </c>
@@ -9006,32 +9580,35 @@
       <c r="F167" t="s">
         <v>296</v>
       </c>
-      <c r="G167" t="s">
-        <v>7</v>
+      <c r="G167" s="12">
+        <v>2015</v>
       </c>
       <c r="H167" t="s">
+        <v>7</v>
+      </c>
+      <c r="I167" t="s">
         <v>8</v>
       </c>
-      <c r="I167" t="s">
+      <c r="J167" t="s">
         <v>382</v>
       </c>
-      <c r="J167" t="s">
+      <c r="K167" t="s">
         <v>434</v>
       </c>
-      <c r="K167">
+      <c r="L167">
         <v>36117</v>
       </c>
-      <c r="L167">
+      <c r="M167">
         <v>142.083333333333</v>
       </c>
-      <c r="M167">
+      <c r="N167">
         <v>0.248276434919844</v>
       </c>
-      <c r="N167">
+      <c r="O167">
         <v>8967</v>
       </c>
     </row>
-    <row r="168" spans="1:14">
+    <row r="168" spans="1:15">
       <c r="A168">
         <v>167</v>
       </c>
@@ -9050,32 +9627,35 @@
       <c r="F168" t="s">
         <v>152</v>
       </c>
-      <c r="G168" t="s">
-        <v>7</v>
+      <c r="G168" s="12">
+        <v>2018</v>
       </c>
       <c r="H168" t="s">
+        <v>7</v>
+      </c>
+      <c r="I168" t="s">
         <v>85</v>
       </c>
-      <c r="I168" t="s">
+      <c r="J168" t="s">
         <v>384</v>
       </c>
-      <c r="J168" t="s">
+      <c r="K168" t="s">
         <v>434</v>
       </c>
-      <c r="K168">
+      <c r="L168">
         <v>49900</v>
       </c>
-      <c r="L168">
+      <c r="M168">
         <v>242.916666666667</v>
       </c>
-      <c r="M168">
+      <c r="N168">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="N168">
+      <c r="O168">
         <v>3493</v>
       </c>
     </row>
-    <row r="169" spans="1:14">
+    <row r="169" spans="1:15">
       <c r="A169">
         <v>168</v>
       </c>
@@ -9094,32 +9674,35 @@
       <c r="F169" t="s">
         <v>386</v>
       </c>
-      <c r="G169" t="s">
-        <v>7</v>
+      <c r="G169" s="12">
+        <v>2018</v>
       </c>
       <c r="H169" t="s">
+        <v>7</v>
+      </c>
+      <c r="I169" t="s">
         <v>85</v>
       </c>
-      <c r="I169" t="s">
+      <c r="J169" t="s">
         <v>387</v>
       </c>
-      <c r="J169" t="s">
+      <c r="K169" t="s">
         <v>434</v>
       </c>
-      <c r="K169">
+      <c r="L169">
         <v>39000</v>
       </c>
-      <c r="L169">
+      <c r="M169">
         <v>244.444444444445</v>
       </c>
-      <c r="M169">
+      <c r="N169">
         <v>0.43589743589743601</v>
       </c>
-      <c r="N169">
+      <c r="O169">
         <v>17000</v>
       </c>
     </row>
-    <row r="170" spans="1:14">
+    <row r="170" spans="1:15">
       <c r="A170">
         <v>169</v>
       </c>
@@ -9135,32 +9718,35 @@
       <c r="F170" t="s">
         <v>357</v>
       </c>
-      <c r="G170" t="s">
-        <v>7</v>
+      <c r="G170" s="12">
+        <v>2019</v>
       </c>
       <c r="H170" t="s">
+        <v>7</v>
+      </c>
+      <c r="I170" t="s">
         <v>196</v>
       </c>
-      <c r="I170" t="s">
+      <c r="J170" t="s">
         <v>389</v>
       </c>
-      <c r="J170" t="s">
+      <c r="K170" t="s">
         <v>434</v>
       </c>
-      <c r="K170">
+      <c r="L170">
         <v>49000</v>
       </c>
-      <c r="L170">
+      <c r="M170">
         <v>235</v>
       </c>
-      <c r="M170">
+      <c r="N170">
         <v>2.7142857142857101E-2</v>
       </c>
-      <c r="N170">
+      <c r="O170">
         <v>1330</v>
       </c>
     </row>
-    <row r="171" spans="1:14">
+    <row r="171" spans="1:15">
       <c r="A171">
         <v>170</v>
       </c>
@@ -9174,31 +9760,34 @@
         <v>198</v>
       </c>
       <c r="G171" t="s">
-        <v>7</v>
+        <v>508</v>
       </c>
       <c r="H171" t="s">
+        <v>7</v>
+      </c>
+      <c r="I171" t="s">
         <v>8</v>
       </c>
-      <c r="I171" t="s">
+      <c r="J171" t="s">
         <v>391</v>
       </c>
-      <c r="J171" t="s">
+      <c r="K171" t="s">
         <v>434</v>
       </c>
-      <c r="K171">
+      <c r="L171">
         <v>59400</v>
       </c>
-      <c r="L171">
+      <c r="M171">
         <v>160</v>
       </c>
-      <c r="M171">
+      <c r="N171">
         <v>0.303686868686869</v>
       </c>
-      <c r="N171">
+      <c r="O171">
         <v>18039</v>
       </c>
     </row>
-    <row r="172" spans="1:14">
+    <row r="172" spans="1:15">
       <c r="A172">
         <v>171</v>
       </c>
@@ -9215,31 +9804,34 @@
         <v>16</v>
       </c>
       <c r="G172" t="s">
-        <v>7</v>
+        <v>508</v>
       </c>
       <c r="H172" t="s">
+        <v>7</v>
+      </c>
+      <c r="I172" t="s">
         <v>8</v>
       </c>
-      <c r="I172" t="s">
+      <c r="J172" t="s">
         <v>393</v>
       </c>
-      <c r="J172" t="s">
+      <c r="K172" t="s">
         <v>434</v>
       </c>
-      <c r="K172">
+      <c r="L172">
         <v>65000</v>
       </c>
-      <c r="L172">
+      <c r="M172">
         <v>160</v>
       </c>
-      <c r="M172">
+      <c r="N172">
         <v>0.161953846153846</v>
       </c>
-      <c r="N172">
+      <c r="O172">
         <v>10527</v>
       </c>
     </row>
-    <row r="173" spans="1:14">
+    <row r="173" spans="1:15">
       <c r="A173">
         <v>172</v>
       </c>
@@ -9258,32 +9850,35 @@
       <c r="F173" t="s">
         <v>395</v>
       </c>
-      <c r="G173" t="s">
-        <v>7</v>
+      <c r="G173" s="12">
+        <v>2020</v>
       </c>
       <c r="H173" t="s">
+        <v>7</v>
+      </c>
+      <c r="I173" t="s">
         <v>397</v>
       </c>
-      <c r="I173" t="s">
+      <c r="J173" t="s">
         <v>398</v>
       </c>
-      <c r="J173" t="s">
+      <c r="K173" t="s">
         <v>449</v>
       </c>
-      <c r="K173">
+      <c r="L173">
         <v>47000</v>
       </c>
-      <c r="L173">
+      <c r="M173">
         <v>87.0833333333333</v>
       </c>
-      <c r="M173">
+      <c r="N173">
         <v>0.05</v>
       </c>
-      <c r="N173">
+      <c r="O173">
         <v>2350</v>
       </c>
     </row>
-    <row r="174" spans="1:14">
+    <row r="174" spans="1:15">
       <c r="A174">
         <v>173</v>
       </c>
@@ -9300,31 +9895,34 @@
         <v>396</v>
       </c>
       <c r="G174" t="s">
-        <v>7</v>
+        <v>508</v>
       </c>
       <c r="H174" t="s">
+        <v>7</v>
+      </c>
+      <c r="I174" t="s">
         <v>397</v>
       </c>
-      <c r="I174" t="s">
+      <c r="J174" t="s">
         <v>400</v>
       </c>
-      <c r="J174" t="s">
+      <c r="K174" t="s">
         <v>449</v>
       </c>
-      <c r="K174">
+      <c r="L174">
         <v>29000</v>
       </c>
-      <c r="L174">
+      <c r="M174">
         <v>87.0833333333333</v>
       </c>
-      <c r="M174">
+      <c r="N174">
         <v>0.12</v>
       </c>
-      <c r="N174">
+      <c r="O174">
         <v>3480</v>
       </c>
     </row>
-    <row r="175" spans="1:14">
+    <row r="175" spans="1:15">
       <c r="A175">
         <v>174</v>
       </c>
@@ -9343,32 +9941,35 @@
       <c r="F175" t="s">
         <v>101</v>
       </c>
-      <c r="G175" t="s">
-        <v>7</v>
-      </c>
-      <c r="H175" s="10" t="s">
+      <c r="G175" s="12">
+        <v>2021</v>
+      </c>
+      <c r="H175" t="s">
+        <v>7</v>
+      </c>
+      <c r="I175" s="10" t="s">
         <v>397</v>
       </c>
-      <c r="I175" s="9" t="s">
-        <v>503</v>
-      </c>
-      <c r="J175" t="s">
+      <c r="J175" s="9" t="s">
+        <v>502</v>
+      </c>
+      <c r="K175" t="s">
         <v>449</v>
       </c>
-      <c r="K175">
+      <c r="L175">
         <v>132239</v>
       </c>
-      <c r="L175">
+      <c r="M175">
         <v>87.0833333333333</v>
       </c>
-      <c r="M175">
+      <c r="N175">
         <v>0.21929990396176599</v>
       </c>
-      <c r="N175">
+      <c r="O175">
         <v>29000</v>
       </c>
     </row>
-    <row r="176" spans="1:14">
+    <row r="176" spans="1:15">
       <c r="A176">
         <v>175</v>
       </c>
@@ -9385,31 +9986,34 @@
         <v>16</v>
       </c>
       <c r="G176" t="s">
-        <v>7</v>
+        <v>508</v>
       </c>
       <c r="H176" t="s">
+        <v>7</v>
+      </c>
+      <c r="I176" t="s">
         <v>397</v>
       </c>
-      <c r="I176" t="s">
+      <c r="J176" t="s">
         <v>403</v>
       </c>
-      <c r="J176" t="s">
+      <c r="K176" t="s">
         <v>449</v>
       </c>
-      <c r="K176">
+      <c r="L176">
         <v>35016</v>
       </c>
-      <c r="L176">
+      <c r="M176">
         <v>75.5555555555556</v>
       </c>
-      <c r="M176">
+      <c r="N176">
         <v>1</v>
       </c>
-      <c r="N176">
+      <c r="O176">
         <v>35016</v>
       </c>
     </row>
-    <row r="177" spans="1:14">
+    <row r="177" spans="1:15">
       <c r="A177">
         <v>176</v>
       </c>
@@ -9423,31 +10027,34 @@
         <v>5</v>
       </c>
       <c r="G177" t="s">
-        <v>7</v>
+        <v>508</v>
       </c>
       <c r="H177" t="s">
+        <v>7</v>
+      </c>
+      <c r="I177" t="s">
         <v>85</v>
       </c>
-      <c r="I177" t="s">
+      <c r="J177" t="s">
         <v>405</v>
       </c>
-      <c r="J177" t="s">
+      <c r="K177" t="s">
         <v>449</v>
       </c>
-      <c r="K177">
+      <c r="L177">
         <v>60000</v>
       </c>
-      <c r="L177">
+      <c r="M177">
         <v>220</v>
       </c>
-      <c r="M177">
+      <c r="N177">
         <v>0.14026666666666701</v>
       </c>
-      <c r="N177">
+      <c r="O177">
         <v>8416</v>
       </c>
     </row>
-    <row r="178" spans="1:14">
+    <row r="178" spans="1:15">
       <c r="A178">
         <v>177</v>
       </c>
@@ -9460,35 +10067,41 @@
       <c r="D178" t="s">
         <v>5</v>
       </c>
+      <c r="E178" t="s">
+        <v>16</v>
+      </c>
       <c r="F178" t="s">
         <v>407</v>
       </c>
-      <c r="G178" t="s">
-        <v>7</v>
+      <c r="G178" s="12">
+        <v>2023</v>
       </c>
       <c r="H178" t="s">
+        <v>7</v>
+      </c>
+      <c r="I178" t="s">
         <v>352</v>
       </c>
-      <c r="I178" t="s">
+      <c r="J178" t="s">
         <v>408</v>
       </c>
-      <c r="J178" t="s">
+      <c r="K178" t="s">
         <v>434</v>
       </c>
-      <c r="K178">
+      <c r="L178">
         <v>90244</v>
       </c>
-      <c r="L178">
+      <c r="M178">
         <v>108.75</v>
       </c>
-      <c r="M178">
+      <c r="N178">
         <v>0.155134967421657</v>
       </c>
-      <c r="N178">
+      <c r="O178">
         <v>14000</v>
       </c>
     </row>
-    <row r="179" spans="1:14">
+    <row r="179" spans="1:15">
       <c r="A179">
         <v>178</v>
       </c>
@@ -9502,31 +10115,34 @@
         <v>5</v>
       </c>
       <c r="G179" t="s">
-        <v>7</v>
+        <v>508</v>
       </c>
       <c r="H179" t="s">
+        <v>7</v>
+      </c>
+      <c r="I179" t="s">
         <v>352</v>
       </c>
-      <c r="I179" t="s">
+      <c r="J179" t="s">
         <v>410</v>
       </c>
-      <c r="J179" t="s">
+      <c r="K179" t="s">
         <v>449</v>
       </c>
-      <c r="K179">
+      <c r="L179">
         <v>38700</v>
       </c>
-      <c r="L179">
+      <c r="M179">
         <v>97.7777777777778</v>
       </c>
-      <c r="M179">
+      <c r="N179">
         <v>0.59204134366925099</v>
       </c>
-      <c r="N179">
+      <c r="O179">
         <v>22912</v>
       </c>
     </row>
-    <row r="180" spans="1:14">
+    <row r="180" spans="1:15">
       <c r="A180">
         <v>179</v>
       </c>
@@ -9540,31 +10156,34 @@
         <v>5</v>
       </c>
       <c r="G180" t="s">
-        <v>7</v>
+        <v>508</v>
       </c>
       <c r="H180" t="s">
+        <v>7</v>
+      </c>
+      <c r="I180" t="s">
         <v>352</v>
       </c>
-      <c r="I180" s="1" t="s">
+      <c r="J180" s="1" t="s">
         <v>473</v>
       </c>
-      <c r="J180" t="s">
+      <c r="K180" t="s">
         <v>450</v>
       </c>
-      <c r="K180">
+      <c r="L180">
         <v>62414</v>
       </c>
-      <c r="L180">
+      <c r="M180">
         <v>215.416666666667</v>
       </c>
-      <c r="M180">
+      <c r="N180">
         <v>0.253148332104976</v>
       </c>
-      <c r="N180">
+      <c r="O180">
         <v>15800</v>
       </c>
     </row>
-    <row r="181" spans="1:14">
+    <row r="181" spans="1:15">
       <c r="A181">
         <v>180</v>
       </c>
@@ -9577,32 +10196,38 @@
       <c r="D181" t="s">
         <v>5</v>
       </c>
+      <c r="E181" t="s">
+        <v>16</v>
+      </c>
       <c r="G181" t="s">
-        <v>7</v>
+        <v>508</v>
       </c>
       <c r="H181" t="s">
+        <v>7</v>
+      </c>
+      <c r="I181" t="s">
         <v>397</v>
       </c>
-      <c r="I181" t="s">
+      <c r="J181" t="s">
         <v>413</v>
       </c>
-      <c r="J181" t="s">
+      <c r="K181" t="s">
         <v>449</v>
       </c>
-      <c r="K181">
+      <c r="L181">
         <v>51000</v>
       </c>
-      <c r="L181">
+      <c r="M181">
         <v>75.5555555555556</v>
       </c>
-      <c r="M181">
+      <c r="N181">
         <v>0.55000000000000004</v>
       </c>
-      <c r="N181">
+      <c r="O181">
         <v>28050</v>
       </c>
     </row>
-    <row r="182" spans="1:14">
+    <row r="182" spans="1:15">
       <c r="A182">
         <v>181</v>
       </c>
@@ -9619,31 +10244,34 @@
         <v>16</v>
       </c>
       <c r="G182" t="s">
-        <v>7</v>
+        <v>508</v>
       </c>
       <c r="H182" t="s">
+        <v>7</v>
+      </c>
+      <c r="I182" t="s">
         <v>85</v>
       </c>
-      <c r="I182" t="s">
+      <c r="J182" t="s">
         <v>415</v>
       </c>
-      <c r="J182" t="s">
+      <c r="K182" t="s">
         <v>449</v>
       </c>
-      <c r="K182">
+      <c r="L182">
         <v>53115</v>
       </c>
-      <c r="L182">
+      <c r="M182">
         <v>301.38888888888903</v>
       </c>
-      <c r="M182">
+      <c r="N182">
         <v>0.135554927986445</v>
       </c>
-      <c r="N182">
+      <c r="O182">
         <v>7200</v>
       </c>
     </row>
-    <row r="183" spans="1:14">
+    <row r="183" spans="1:15">
       <c r="A183">
         <v>182</v>
       </c>
@@ -9657,31 +10285,34 @@
         <v>5</v>
       </c>
       <c r="G183" t="s">
-        <v>7</v>
+        <v>508</v>
       </c>
       <c r="H183" t="s">
+        <v>7</v>
+      </c>
+      <c r="I183" t="s">
         <v>352</v>
       </c>
-      <c r="I183" t="s">
+      <c r="J183" t="s">
         <v>417</v>
       </c>
-      <c r="J183" t="s">
+      <c r="K183" t="s">
         <v>449</v>
       </c>
-      <c r="K183">
+      <c r="L183">
         <v>120000</v>
       </c>
-      <c r="L183">
+      <c r="M183">
         <v>128.333333333333</v>
       </c>
-      <c r="M183">
+      <c r="N183">
         <v>0.18333333333333299</v>
       </c>
-      <c r="N183">
+      <c r="O183">
         <v>22000</v>
       </c>
     </row>
-    <row r="184" spans="1:14">
+    <row r="184" spans="1:15">
       <c r="A184">
         <v>183</v>
       </c>
@@ -9698,31 +10329,34 @@
         <v>16</v>
       </c>
       <c r="G184" t="s">
-        <v>7</v>
+        <v>508</v>
       </c>
       <c r="H184" t="s">
+        <v>7</v>
+      </c>
+      <c r="I184" t="s">
         <v>85</v>
       </c>
-      <c r="I184" s="3" t="s">
+      <c r="J184" s="3" t="s">
         <v>472</v>
       </c>
-      <c r="J184" t="s">
+      <c r="K184" t="s">
         <v>449</v>
       </c>
-      <c r="K184">
+      <c r="L184">
         <v>66477</v>
       </c>
-      <c r="L184">
+      <c r="M184">
         <v>265.83333333333297</v>
       </c>
-      <c r="M184">
+      <c r="N184">
         <v>0.90974321945936198</v>
       </c>
-      <c r="N184">
+      <c r="O184">
         <v>60477</v>
       </c>
     </row>
-    <row r="185" spans="1:14">
+    <row r="185" spans="1:15">
       <c r="A185">
         <v>184</v>
       </c>
@@ -9739,28 +10373,31 @@
         <v>16</v>
       </c>
       <c r="G185" t="s">
-        <v>7</v>
+        <v>508</v>
       </c>
       <c r="H185" t="s">
+        <v>7</v>
+      </c>
+      <c r="I185" t="s">
         <v>421</v>
       </c>
-      <c r="I185" t="s">
+      <c r="J185" t="s">
         <v>422</v>
       </c>
-      <c r="K185">
+      <c r="L185">
         <v>59300</v>
       </c>
-      <c r="L185">
+      <c r="M185">
         <v>86.1111111111111</v>
       </c>
-      <c r="M185">
+      <c r="N185">
         <v>0.79089376053962901</v>
       </c>
-      <c r="N185">
+      <c r="O185">
         <v>46900</v>
       </c>
     </row>
-    <row r="186" spans="1:14">
+    <row r="186" spans="1:15">
       <c r="A186">
         <v>185</v>
       </c>
@@ -9774,28 +10411,31 @@
         <v>5</v>
       </c>
       <c r="G186" t="s">
-        <v>7</v>
+        <v>508</v>
       </c>
       <c r="H186" t="s">
+        <v>7</v>
+      </c>
+      <c r="I186" t="s">
         <v>421</v>
       </c>
-      <c r="I186" t="s">
+      <c r="J186" t="s">
         <v>424</v>
       </c>
-      <c r="K186">
+      <c r="L186">
         <v>44000</v>
       </c>
-      <c r="L186">
+      <c r="M186">
         <v>80</v>
       </c>
-      <c r="M186">
+      <c r="N186">
         <v>0.45</v>
       </c>
-      <c r="N186">
+      <c r="O186">
         <v>19800</v>
       </c>
     </row>
-    <row r="187" spans="1:14">
+    <row r="187" spans="1:15">
       <c r="A187">
         <v>186</v>
       </c>
@@ -9809,28 +10449,31 @@
         <v>5</v>
       </c>
       <c r="G187" t="s">
-        <v>7</v>
+        <v>508</v>
       </c>
       <c r="H187" t="s">
+        <v>7</v>
+      </c>
+      <c r="I187" t="s">
         <v>421</v>
       </c>
-      <c r="I187" t="s">
+      <c r="J187" t="s">
         <v>426</v>
       </c>
-      <c r="K187">
+      <c r="L187">
         <v>26528</v>
       </c>
-      <c r="L187">
+      <c r="M187">
         <v>84.3333333333333</v>
       </c>
-      <c r="M187">
+      <c r="N187">
         <v>0.331724969843185</v>
       </c>
-      <c r="N187">
+      <c r="O187">
         <v>8800</v>
       </c>
     </row>
-    <row r="188" spans="1:14">
+    <row r="188" spans="1:15">
       <c r="A188">
         <v>187</v>
       </c>
@@ -9847,28 +10490,31 @@
         <v>16</v>
       </c>
       <c r="G188" t="s">
-        <v>7</v>
+        <v>508</v>
       </c>
       <c r="H188" t="s">
+        <v>7</v>
+      </c>
+      <c r="I188" t="s">
         <v>421</v>
       </c>
-      <c r="I188" t="s">
+      <c r="J188" t="s">
         <v>428</v>
       </c>
-      <c r="K188">
+      <c r="L188">
         <v>95684</v>
       </c>
-      <c r="L188">
+      <c r="M188">
         <v>87.0833333333333</v>
       </c>
-      <c r="M188">
+      <c r="N188">
         <v>0.59571088165210495</v>
       </c>
-      <c r="N188">
+      <c r="O188">
         <v>57000</v>
       </c>
     </row>
-    <row r="189" spans="1:14" ht="15">
+    <row r="189" spans="1:15" ht="15">
       <c r="A189">
         <v>188</v>
       </c>
@@ -9882,28 +10528,31 @@
         <v>5</v>
       </c>
       <c r="G189" t="s">
-        <v>7</v>
+        <v>508</v>
       </c>
       <c r="H189" t="s">
+        <v>7</v>
+      </c>
+      <c r="I189" t="s">
         <v>85</v>
       </c>
-      <c r="I189" s="4" t="s">
+      <c r="J189" s="4" t="s">
         <v>463</v>
       </c>
-      <c r="K189">
+      <c r="L189">
         <v>26737</v>
       </c>
-      <c r="L189">
+      <c r="M189">
         <v>89.8333333333333</v>
       </c>
-      <c r="M189">
+      <c r="N189">
         <v>0.40019448704043098</v>
       </c>
-      <c r="N189">
+      <c r="O189">
         <v>10700</v>
       </c>
     </row>
-    <row r="190" spans="1:14">
+    <row r="190" spans="1:15">
       <c r="A190">
         <v>189</v>
       </c>
@@ -9920,28 +10569,31 @@
         <v>16</v>
       </c>
       <c r="G190" t="s">
-        <v>7</v>
+        <v>508</v>
       </c>
       <c r="H190" t="s">
+        <v>7</v>
+      </c>
+      <c r="I190" t="s">
         <v>421</v>
       </c>
-      <c r="I190" t="s">
+      <c r="J190" t="s">
         <v>430</v>
       </c>
-      <c r="K190">
+      <c r="L190">
         <v>60000</v>
       </c>
-      <c r="L190">
+      <c r="M190">
         <v>82.5</v>
       </c>
-      <c r="M190">
+      <c r="N190">
         <v>0.5</v>
       </c>
-      <c r="N190">
+      <c r="O190">
         <v>30000</v>
       </c>
     </row>
-    <row r="191" spans="1:14">
+    <row r="191" spans="1:15">
       <c r="A191">
         <v>190</v>
       </c>
@@ -9955,62 +10607,114 @@
         <v>5</v>
       </c>
       <c r="G191" t="s">
-        <v>7</v>
+        <v>508</v>
       </c>
       <c r="H191" t="s">
+        <v>7</v>
+      </c>
+      <c r="I191" t="s">
         <v>421</v>
       </c>
-      <c r="I191" t="s">
+      <c r="J191" t="s">
         <v>432</v>
       </c>
-      <c r="K191">
+      <c r="L191">
         <v>34895</v>
       </c>
-      <c r="L191">
+      <c r="M191">
         <v>77.5</v>
       </c>
-      <c r="M191">
+      <c r="N191">
         <v>0.45278693222524702</v>
       </c>
-      <c r="N191">
+      <c r="O191">
         <v>15800</v>
       </c>
     </row>
-    <row r="192" spans="1:14">
-      <c r="B192" s="1" t="s">
+    <row r="192" spans="1:15">
+      <c r="A192">
+        <v>191</v>
+      </c>
+      <c r="B192" t="s">
+        <v>506</v>
+      </c>
+      <c r="C192" t="s">
+        <v>420</v>
+      </c>
+      <c r="D192" t="s">
+        <v>5</v>
+      </c>
+      <c r="E192" t="s">
+        <v>16</v>
+      </c>
+      <c r="H192" t="s">
+        <v>7</v>
+      </c>
+      <c r="I192" t="s">
+        <v>421</v>
+      </c>
+      <c r="J192" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="193" spans="1:10">
+      <c r="A193">
+        <v>192</v>
+      </c>
+      <c r="B193" s="1" t="s">
         <v>478</v>
       </c>
-      <c r="C192" s="1" t="s">
+      <c r="C193" s="1" t="s">
         <v>476</v>
       </c>
-      <c r="G192" s="1" t="s">
+      <c r="G193" t="s">
+        <v>508</v>
+      </c>
+      <c r="H193" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="H192" s="1" t="s">
+      <c r="I193" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="I192" s="1" t="s">
+      <c r="J193" s="1" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="193" spans="2:2">
-      <c r="B193" s="1" t="s">
+    <row r="194" spans="1:10">
+      <c r="A194">
+        <v>193</v>
+      </c>
+      <c r="B194" s="1" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="194" spans="2:2">
-      <c r="B194" s="1" t="s">
+    <row r="195" spans="1:10">
+      <c r="A195">
+        <v>194</v>
+      </c>
+      <c r="B195" s="1" t="s">
         <v>484</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e40a7e4-94f1-4b05-8c7e-c5111c724f9a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="f655991e-a262-4cc2-969f-4b8d0db6a5de" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100BC605E6093A30A479FED397EFA867E40" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="55774fc2038cb4dae8fef12431c133f2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f655991e-a262-4cc2-969f-4b8d0db6a5de" xmlns:ns3="8e40a7e4-94f1-4b05-8c7e-c5111c724f9a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="31482a63ce11ed8a627351d2502cc05d" ns2:_="" ns3:_="">
     <xsd:import namespace="f655991e-a262-4cc2-969f-4b8d0db6a5de"/>
@@ -10271,17 +10975,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e40a7e4-94f1-4b05-8c7e-c5111c724f9a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="f655991e-a262-4cc2-969f-4b8d0db6a5de" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -10292,6 +10985,17 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF6E6A69-6D48-49BB-9E8E-5B96C2738B7E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="8e40a7e4-94f1-4b05-8c7e-c5111c724f9a"/>
+    <ds:schemaRef ds:uri="f655991e-a262-4cc2-969f-4b8d0db6a5de"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5BF42E8-7CD6-44A5-B028-608DFC162276}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -10310,17 +11014,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF6E6A69-6D48-49BB-9E8E-5B96C2738B7E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="8e40a7e4-94f1-4b05-8c7e-c5111c724f9a"/>
-    <ds:schemaRef ds:uri="f655991e-a262-4cc2-969f-4b8d0db6a5de"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C7A7DD6C-B285-4C23-BA8C-7CCC252AB8AB}">
   <ds:schemaRefs>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yuhang/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61A1193A-6C0D-F84B-BFF2-52DDA6137E9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFA15F44-7F32-FD43-833A-D3E4D0699469}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="380" yWindow="1140" windowWidth="28800" windowHeight="16100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -1083,7 +1083,7 @@
   </si>
   <si>
     <t>LEEDS</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>RSH</t>
@@ -1096,71 +1096,71 @@
   </si>
   <si>
     <t>中国人寿中心</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>朝阳区</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>116.469030,39.911173</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>116.359101,39.916286</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>中关村东升科技园·学北园</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>116.406387,39.981515</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>116.406387,39.980615</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>合景国际金融广场（4B)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>116.680295,39.907589</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>116.358503,39.931864</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>116.362230,39.920558</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>116.313304,39.982116</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>116.320807,39.956309</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>116.319635,39.956309</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>116.323984,39.958472</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>116.377078,39.888674</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>116.371113,39.967322</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>116.459281,39.960483</t>
@@ -1170,30 +1170,30 @@
   </si>
   <si>
     <t>116.43926,39.909474</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>116.435881,39.919317</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>116.429644,39.906833</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>116.464627,39.912332</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>116.464467,39.912049</t>
   </si>
   <si>
     <t>116.464674,39.912865</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>116.460321,39.906941</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>116.454891,39.960979</t>
@@ -1350,34 +1350,34 @@
   </si>
   <si>
     <t>业主</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>物业</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>报价</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>物业费</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>表面</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>免租期</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1390,35 +1390,6 @@
       <color theme="1"/>
       <name val="宋体"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1431,39 +1402,17 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
+      <name val="宋体 (正文)"/>
       <family val="3"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -1492,23 +1441,13 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -4049,7 +3988,7 @@
       <c r="D1" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>347</v>
       </c>
       <c r="F1" s="1" t="s">
@@ -4064,10 +4003,10 @@
       <c r="I1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>429</v>
       </c>
       <c r="L1" s="1" t="s">
@@ -4076,16 +4015,16 @@
       <c r="M1" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="1" t="s">
         <v>433</v>
       </c>
       <c r="R1" s="1" t="s">
@@ -4515,11 +4454,11 @@
       <c r="H10" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I10" s="3" t="s">
+      <c r="I10" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
       <c r="L10" s="1" t="s">
         <v>336</v>
       </c>
@@ -4665,11 +4604,11 @@
       <c r="H13" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I13" s="4" t="s">
+      <c r="I13" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="J13" s="4"/>
-      <c r="K13" s="4"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
       <c r="L13" s="1" t="s">
         <v>348</v>
       </c>
@@ -4715,11 +4654,11 @@
       <c r="H14" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I14" s="4" t="s">
+      <c r="I14" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="J14" s="4"/>
-      <c r="K14" s="4"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
       <c r="L14" s="1" t="s">
         <v>348</v>
       </c>
@@ -5113,11 +5052,11 @@
       <c r="H22" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I22" s="2" t="s">
+      <c r="I22" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="J22" s="2"/>
-      <c r="K22" s="2"/>
+      <c r="J22" s="1"/>
+      <c r="K22" s="1"/>
       <c r="L22" s="1" t="s">
         <v>336</v>
       </c>
@@ -5242,7 +5181,7 @@
       <c r="A25" s="1">
         <v>24</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="1" t="s">
         <v>398</v>
       </c>
       <c r="C25" s="1" t="s">
@@ -5263,11 +5202,11 @@
       <c r="H25" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I25" s="4" t="s">
+      <c r="I25" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="J25" s="4"/>
-      <c r="K25" s="4"/>
+      <c r="J25" s="1"/>
+      <c r="K25" s="1"/>
       <c r="L25" s="1" t="s">
         <v>348</v>
       </c>
@@ -5492,7 +5431,7 @@
       <c r="A30" s="1">
         <v>29</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="1" t="s">
         <v>399</v>
       </c>
       <c r="C30" s="1" t="s">
@@ -5510,14 +5449,14 @@
       <c r="G30" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H30" s="5" t="s">
+      <c r="H30" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="I30" s="5" t="s">
+      <c r="I30" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="J30" s="5"/>
-      <c r="K30" s="5"/>
+      <c r="J30" s="1"/>
+      <c r="K30" s="1"/>
       <c r="L30" s="1" t="s">
         <v>348</v>
       </c>
@@ -5561,11 +5500,11 @@
       <c r="H31" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I31" s="2" t="s">
+      <c r="I31" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="J31" s="2"/>
-      <c r="K31" s="2"/>
+      <c r="J31" s="1"/>
+      <c r="K31" s="1"/>
       <c r="L31" s="1" t="s">
         <v>336</v>
       </c>
@@ -5707,11 +5646,11 @@
       <c r="H34" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I34" s="2" t="s">
+      <c r="I34" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="J34" s="2"/>
-      <c r="K34" s="2"/>
+      <c r="J34" s="1"/>
+      <c r="K34" s="1"/>
       <c r="L34" s="1" t="s">
         <v>348</v>
       </c>
@@ -5807,11 +5746,11 @@
       <c r="H36" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I36" s="2" t="s">
+      <c r="I36" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="J36" s="2"/>
-      <c r="K36" s="2"/>
+      <c r="J36" s="1"/>
+      <c r="K36" s="1"/>
       <c r="L36" s="1" t="s">
         <v>348</v>
       </c>
@@ -6232,7 +6171,7 @@
       <c r="A45" s="1">
         <v>44</v>
       </c>
-      <c r="B45" s="5" t="s">
+      <c r="B45" s="1" t="s">
         <v>84</v>
       </c>
       <c r="C45" s="1" t="s">
@@ -6253,11 +6192,11 @@
       <c r="H45" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="I45" s="2" t="s">
+      <c r="I45" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="J45" s="2"/>
-      <c r="K45" s="2"/>
+      <c r="J45" s="1"/>
+      <c r="K45" s="1"/>
       <c r="L45" s="1" t="s">
         <v>348</v>
       </c>
@@ -6282,7 +6221,7 @@
       <c r="A46" s="1">
         <v>45</v>
       </c>
-      <c r="B46" s="5" t="s">
+      <c r="B46" s="1" t="s">
         <v>85</v>
       </c>
       <c r="C46" s="1" t="s">
@@ -6303,11 +6242,11 @@
       <c r="H46" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="I46" s="2" t="s">
+      <c r="I46" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="J46" s="2"/>
-      <c r="K46" s="2"/>
+      <c r="J46" s="1"/>
+      <c r="K46" s="1"/>
       <c r="L46" s="1" t="s">
         <v>348</v>
       </c>
@@ -6332,7 +6271,7 @@
       <c r="A47" s="1">
         <v>46</v>
       </c>
-      <c r="B47" s="5" t="s">
+      <c r="B47" s="1" t="s">
         <v>86</v>
       </c>
       <c r="C47" s="1" t="s">
@@ -6353,11 +6292,11 @@
       <c r="H47" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="I47" s="2" t="s">
+      <c r="I47" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="J47" s="2"/>
-      <c r="K47" s="2"/>
+      <c r="J47" s="1"/>
+      <c r="K47" s="1"/>
       <c r="L47" s="1" t="s">
         <v>348</v>
       </c>
@@ -6843,11 +6782,11 @@
       <c r="H56" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="I56" s="2" t="s">
+      <c r="I56" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="J56" s="2"/>
-      <c r="K56" s="2"/>
+      <c r="J56" s="1"/>
+      <c r="K56" s="1"/>
       <c r="L56" s="1" t="s">
         <v>348</v>
       </c>
@@ -7059,11 +6998,11 @@
       <c r="H60" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I60" s="2" t="s">
+      <c r="I60" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="J60" s="2"/>
-      <c r="K60" s="2"/>
+      <c r="J60" s="1"/>
+      <c r="K60" s="1"/>
       <c r="L60" s="1" t="s">
         <v>349</v>
       </c>
@@ -7194,7 +7133,7 @@
       <c r="A63" s="1">
         <v>62</v>
       </c>
-      <c r="B63" s="4" t="s">
+      <c r="B63" s="1" t="s">
         <v>112</v>
       </c>
       <c r="C63" s="1" t="s">
@@ -7215,11 +7154,11 @@
       <c r="H63" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="I63" s="5" t="s">
+      <c r="I63" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="J63" s="5"/>
-      <c r="K63" s="5"/>
+      <c r="J63" s="1"/>
+      <c r="K63" s="1"/>
       <c r="L63" s="1" t="s">
         <v>332</v>
       </c>
@@ -7509,11 +7448,11 @@
       <c r="H69" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="I69" s="2" t="s">
+      <c r="I69" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="J69" s="2"/>
-      <c r="K69" s="2"/>
+      <c r="J69" s="1"/>
+      <c r="K69" s="1"/>
       <c r="L69" s="1" t="s">
         <v>332</v>
       </c>
@@ -7586,7 +7525,7 @@
       <c r="A71" s="1">
         <v>70</v>
       </c>
-      <c r="B71" s="5" t="s">
+      <c r="B71" s="1" t="s">
         <v>351</v>
       </c>
       <c r="C71" s="1" t="s">
@@ -7605,11 +7544,11 @@
       <c r="H71" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="I71" s="5" t="s">
+      <c r="I71" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="J71" s="5"/>
-      <c r="K71" s="5"/>
+      <c r="J71" s="1"/>
+      <c r="K71" s="1"/>
       <c r="L71" s="1" t="s">
         <v>332</v>
       </c>
@@ -7830,7 +7769,7 @@
       <c r="A76" s="1">
         <v>75</v>
       </c>
-      <c r="B76" s="5" t="s">
+      <c r="B76" s="1" t="s">
         <v>134</v>
       </c>
       <c r="C76" s="1" t="s">
@@ -7851,11 +7790,11 @@
       <c r="H76" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="I76" s="5" t="s">
+      <c r="I76" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="J76" s="5"/>
-      <c r="K76" s="5"/>
+      <c r="J76" s="1"/>
+      <c r="K76" s="1"/>
       <c r="L76" s="1" t="s">
         <v>332</v>
       </c>
@@ -7901,11 +7840,11 @@
       <c r="H77" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="I77" s="4" t="s">
+      <c r="I77" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="J77" s="4"/>
-      <c r="K77" s="4"/>
+      <c r="J77" s="1"/>
+      <c r="K77" s="1"/>
       <c r="L77" s="1" t="s">
         <v>332</v>
       </c>
@@ -7980,7 +7919,7 @@
       <c r="A79" s="1">
         <v>78</v>
       </c>
-      <c r="B79" s="5" t="s">
+      <c r="B79" s="1" t="s">
         <v>138</v>
       </c>
       <c r="C79" s="1" t="s">
@@ -7999,11 +7938,11 @@
       <c r="H79" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="I79" s="5" t="s">
+      <c r="I79" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="J79" s="5"/>
-      <c r="K79" s="5"/>
+      <c r="J79" s="1"/>
+      <c r="K79" s="1"/>
       <c r="L79" s="1" t="s">
         <v>332</v>
       </c>
@@ -8098,11 +8037,11 @@
       <c r="H81" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I81" s="6" t="s">
+      <c r="I81" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="J81" s="6"/>
-      <c r="K81" s="6"/>
+      <c r="J81" s="1"/>
+      <c r="K81" s="1"/>
       <c r="L81" s="1" t="s">
         <v>333</v>
       </c>
@@ -8492,11 +8431,11 @@
       <c r="H89" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I89" s="2" t="s">
+      <c r="I89" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="J89" s="2"/>
-      <c r="K89" s="2"/>
+      <c r="J89" s="1"/>
+      <c r="K89" s="1"/>
       <c r="L89" s="1" t="s">
         <v>333</v>
       </c>
@@ -9163,7 +9102,7 @@
       <c r="A103" s="1">
         <v>102</v>
       </c>
-      <c r="B103" s="5" t="s">
+      <c r="B103" s="1" t="s">
         <v>177</v>
       </c>
       <c r="C103" s="1" t="s">
@@ -9182,11 +9121,11 @@
       <c r="H103" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="I103" s="5" t="s">
+      <c r="I103" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="J103" s="5"/>
-      <c r="K103" s="5"/>
+      <c r="J103" s="1"/>
+      <c r="K103" s="1"/>
       <c r="L103" s="1" t="s">
         <v>350</v>
       </c>
@@ -9648,7 +9587,7 @@
       <c r="A113" s="1">
         <v>112</v>
       </c>
-      <c r="B113" s="5" t="s">
+      <c r="B113" s="1" t="s">
         <v>413</v>
       </c>
       <c r="C113" s="1" t="s">
@@ -9669,11 +9608,11 @@
       <c r="H113" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="I113" s="5" t="s">
+      <c r="I113" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="J113" s="5"/>
-      <c r="K113" s="5"/>
+      <c r="J113" s="1"/>
+      <c r="K113" s="1"/>
       <c r="L113" s="1" t="s">
         <v>334</v>
       </c>
@@ -9698,7 +9637,7 @@
       <c r="A114" s="1">
         <v>113</v>
       </c>
-      <c r="B114" s="5" t="s">
+      <c r="B114" s="1" t="s">
         <v>414</v>
       </c>
       <c r="C114" s="1" t="s">
@@ -9719,11 +9658,11 @@
       <c r="H114" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="I114" s="5" t="s">
+      <c r="I114" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="J114" s="5"/>
-      <c r="K114" s="5"/>
+      <c r="J114" s="1"/>
+      <c r="K114" s="1"/>
       <c r="L114" s="1" t="s">
         <v>334</v>
       </c>
@@ -9748,7 +9687,7 @@
       <c r="A115" s="1">
         <v>114</v>
       </c>
-      <c r="B115" s="5" t="s">
+      <c r="B115" s="1" t="s">
         <v>415</v>
       </c>
       <c r="C115" s="1" t="s">
@@ -9767,11 +9706,11 @@
       <c r="H115" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="I115" s="7" t="s">
+      <c r="I115" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="J115" s="7"/>
-      <c r="K115" s="7"/>
+      <c r="J115" s="1"/>
+      <c r="K115" s="1"/>
       <c r="L115" s="1" t="s">
         <v>334</v>
       </c>
@@ -10088,7 +10027,7 @@
       <c r="A122" s="1">
         <v>121</v>
       </c>
-      <c r="B122" s="5" t="s">
+      <c r="B122" s="1" t="s">
         <v>416</v>
       </c>
       <c r="C122" s="1" t="s">
@@ -10109,11 +10048,11 @@
       <c r="H122" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="I122" s="8" t="s">
+      <c r="I122" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="J122" s="8"/>
-      <c r="K122" s="8"/>
+      <c r="J122" s="1"/>
+      <c r="K122" s="1"/>
       <c r="L122" s="1" t="s">
         <v>334</v>
       </c>
@@ -10138,7 +10077,7 @@
       <c r="A123" s="1">
         <v>122</v>
       </c>
-      <c r="B123" s="5" t="s">
+      <c r="B123" s="1" t="s">
         <v>355</v>
       </c>
       <c r="C123" s="1" t="s">
@@ -10155,11 +10094,11 @@
       <c r="H123" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="I123" s="8" t="s">
+      <c r="I123" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="J123" s="8"/>
-      <c r="K123" s="8"/>
+      <c r="J123" s="1"/>
+      <c r="K123" s="1"/>
       <c r="L123" s="1" t="s">
         <v>334</v>
       </c>
@@ -11222,7 +11161,7 @@
       <c r="A145" s="1">
         <v>144</v>
       </c>
-      <c r="B145" s="5" t="s">
+      <c r="B145" s="1" t="s">
         <v>423</v>
       </c>
       <c r="C145" s="1" t="s">
@@ -11243,11 +11182,11 @@
       <c r="H145" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I145" s="5" t="s">
+      <c r="I145" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="J145" s="5"/>
-      <c r="K145" s="5"/>
+      <c r="J145" s="1"/>
+      <c r="K145" s="1"/>
       <c r="L145" s="1" t="s">
         <v>348</v>
       </c>
@@ -11370,7 +11309,7 @@
       <c r="A148" s="1">
         <v>147</v>
       </c>
-      <c r="B148" s="5" t="s">
+      <c r="B148" s="1" t="s">
         <v>425</v>
       </c>
       <c r="C148" s="1" t="s">
@@ -11391,11 +11330,11 @@
       <c r="H148" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I148" s="5" t="s">
+      <c r="I148" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="J148" s="5"/>
-      <c r="K148" s="5"/>
+      <c r="J148" s="1"/>
+      <c r="K148" s="1"/>
       <c r="L148" s="1" t="s">
         <v>348</v>
       </c>
@@ -11420,7 +11359,7 @@
       <c r="A149" s="1">
         <v>148</v>
       </c>
-      <c r="B149" s="5" t="s">
+      <c r="B149" s="1" t="s">
         <v>124</v>
       </c>
       <c r="C149" s="1" t="s">
@@ -11438,14 +11377,14 @@
       <c r="G149" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H149" s="9" t="s">
+      <c r="H149" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I149" s="5" t="s">
+      <c r="I149" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="J149" s="5"/>
-      <c r="K149" s="5"/>
+      <c r="J149" s="1"/>
+      <c r="K149" s="1"/>
       <c r="L149" s="1" t="s">
         <v>348</v>
       </c>
@@ -12708,7 +12647,7 @@
       <c r="A175" s="1">
         <v>174</v>
       </c>
-      <c r="B175" s="10" t="s">
+      <c r="B175" s="1" t="s">
         <v>302</v>
       </c>
       <c r="C175" s="1" t="s">
@@ -12726,14 +12665,14 @@
       <c r="G175" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H175" s="6" t="s">
+      <c r="H175" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="I175" s="10" t="s">
+      <c r="I175" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="J175" s="10"/>
-      <c r="K175" s="10"/>
+      <c r="J175" s="1"/>
+      <c r="K175" s="1"/>
       <c r="L175" s="1" t="s">
         <v>348</v>
       </c>
@@ -12973,11 +12912,11 @@
       <c r="H180" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="I180" s="2" t="s">
+      <c r="I180" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="J180" s="2"/>
-      <c r="K180" s="2"/>
+      <c r="J180" s="1"/>
+      <c r="K180" s="1"/>
       <c r="L180" s="1" t="s">
         <v>349</v>
       </c>
@@ -13158,7 +13097,7 @@
       <c r="A184" s="1">
         <v>183</v>
       </c>
-      <c r="B184" s="8" t="s">
+      <c r="B184" s="1" t="s">
         <v>318</v>
       </c>
       <c r="C184" s="1" t="s">
@@ -13179,11 +13118,11 @@
       <c r="H184" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="I184" s="8" t="s">
+      <c r="I184" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="J184" s="8"/>
-      <c r="K184" s="8"/>
+      <c r="J184" s="1"/>
+      <c r="K184" s="1"/>
       <c r="L184" s="1" t="s">
         <v>348</v>
       </c>
@@ -13396,7 +13335,7 @@
       <c r="A189" s="1">
         <v>188</v>
       </c>
-      <c r="B189" s="5" t="s">
+      <c r="B189" s="1" t="s">
         <v>358</v>
       </c>
       <c r="C189" s="1" t="s">
@@ -13415,11 +13354,11 @@
       <c r="H189" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="I189" s="11" t="s">
+      <c r="I189" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="J189" s="11"/>
-      <c r="K189" s="11"/>
+      <c r="J189" s="1"/>
+      <c r="K189" s="1"/>
       <c r="L189" s="1"/>
       <c r="M189" s="1">
         <v>26737</v>
@@ -13574,13 +13513,33 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:V192" xr:uid="{7B280671-4AFA-4641-88D4-A51F39483890}"/>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e40a7e4-94f1-4b05-8c7e-c5111c724f9a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="f655991e-a262-4cc2-969f-4b8d0db6a5de" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100BC605E6093A30A479FED397EFA867E40" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="55774fc2038cb4dae8fef12431c133f2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f655991e-a262-4cc2-969f-4b8d0db6a5de" xmlns:ns3="8e40a7e4-94f1-4b05-8c7e-c5111c724f9a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="31482a63ce11ed8a627351d2502cc05d" ns2:_="" ns3:_="">
     <xsd:import namespace="f655991e-a262-4cc2-969f-4b8d0db6a5de"/>
@@ -13841,27 +13800,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e40a7e4-94f1-4b05-8c7e-c5111c724f9a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="f655991e-a262-4cc2-969f-4b8d0db6a5de" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C7A7DD6C-B285-4C23-BA8C-7CCC252AB8AB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF6E6A69-6D48-49BB-9E8E-5B96C2738B7E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="8e40a7e4-94f1-4b05-8c7e-c5111c724f9a"/>
+    <ds:schemaRef ds:uri="f655991e-a262-4cc2-969f-4b8d0db6a5de"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5BF42E8-7CD6-44A5-B028-608DFC162276}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -13880,25 +13838,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF6E6A69-6D48-49BB-9E8E-5B96C2738B7E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="8e40a7e4-94f1-4b05-8c7e-c5111c724f9a"/>
-    <ds:schemaRef ds:uri="f655991e-a262-4cc2-969f-4b8d0db6a5de"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C7A7DD6C-B285-4C23-BA8C-7CCC252AB8AB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{8c970d48-f7b9-48b0-9606-072fbefb514d}" enabled="1" method="Standard" siteId="{049e3382-8cdc-477b-9317-951b04689668}" contentBits="0" removed="0"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10302"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\intern.bjres\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yuhang/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D51D560A-F786-427D-8FA3-7320A38ADF23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2063C6AF-73C1-484D-B920-0CE2859F626F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -1202,9 +1202,6 @@
     <t>116.445694,39.970256</t>
   </si>
   <si>
-    <t>116.491439,39.914113</t>
-  </si>
-  <si>
     <t>116.412649,39.909443</t>
   </si>
   <si>
@@ -1367,6 +1364,10 @@
   </si>
   <si>
     <t>免租期</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>116.359885,39.906007</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1374,25 +1375,25 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1400,6 +1401,12 @@
     <font>
       <sz val="11"/>
       <name val="宋体 (正文)"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
     </font>
@@ -1442,7 +1449,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
@@ -1453,9 +1460,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2" xfId="1" xr:uid="{81D4EE7A-49F9-4559-B92D-CA7C8AC626DC}"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1761,28 +1771,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B280671-4AFA-4641-88D4-A51F39483890}">
   <dimension ref="A1:T192"/>
-  <sheetFormatPr defaultColWidth="10.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="5.6328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="42.36328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.6328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.1796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.1796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.1796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.1796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.1796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.453125" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="6.1796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.1796875" style="2" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="10.1796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="17" width="10.1796875" style="2" customWidth="1"/>
+    <col min="1" max="1" width="5.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="42.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="6.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.1640625" style="2" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="10.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="17" width="10.1640625" style="2" customWidth="1"/>
     <col min="18" max="18" width="11" style="2" customWidth="1"/>
-    <col min="19" max="19" width="12.1796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="9.1796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="10.81640625" style="2"/>
+    <col min="19" max="19" width="12.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="10.83203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="15">
+    <row r="1" spans="1:20">
       <c r="A1" s="3" t="s">
         <v>337</v>
       </c>
@@ -1811,10 +1821,10 @@
         <v>2</v>
       </c>
       <c r="J1" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="K1" s="3" t="s">
         <v>428</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>429</v>
       </c>
       <c r="L1" s="3" t="s">
         <v>343</v>
@@ -1823,16 +1833,16 @@
         <v>338</v>
       </c>
       <c r="N1" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="O1" s="3" t="s">
         <v>430</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="P1" s="3" t="s">
         <v>431</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
         <v>432</v>
-      </c>
-      <c r="Q1" s="3" t="s">
-        <v>433</v>
       </c>
       <c r="R1" s="3" t="s">
         <v>344</v>
@@ -1844,7 +1854,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="15">
+    <row r="2" spans="1:20">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -1900,7 +1910,7 @@
         <v>9400</v>
       </c>
     </row>
-    <row r="3" spans="1:20" ht="15">
+    <row r="3" spans="1:20">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -1956,7 +1966,7 @@
         <v>1450</v>
       </c>
     </row>
-    <row r="4" spans="1:20" ht="15">
+    <row r="4" spans="1:20">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -2014,7 +2024,7 @@
         <v>13100</v>
       </c>
     </row>
-    <row r="5" spans="1:20" ht="15">
+    <row r="5" spans="1:20">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -2072,7 +2082,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="6" spans="1:20" ht="15">
+    <row r="6" spans="1:20">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -2130,7 +2140,7 @@
         <v>5962</v>
       </c>
     </row>
-    <row r="7" spans="1:20" ht="15">
+    <row r="7" spans="1:20">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -2186,7 +2196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:20" ht="15">
+    <row r="8" spans="1:20">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -2244,7 +2254,7 @@
         <v>21706</v>
       </c>
     </row>
-    <row r="9" spans="1:20" ht="15">
+    <row r="9" spans="1:20">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -2300,12 +2310,12 @@
         <v>3478.47</v>
       </c>
     </row>
-    <row r="10" spans="1:20" ht="15">
+    <row r="10" spans="1:20">
       <c r="A10" s="3">
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>4</v>
@@ -2326,7 +2336,7 @@
         <v>7</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
@@ -2358,7 +2368,7 @@
         <v>23242</v>
       </c>
     </row>
-    <row r="11" spans="1:20" ht="15">
+    <row r="11" spans="1:20">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -2416,7 +2426,7 @@
         <v>17000</v>
       </c>
     </row>
-    <row r="12" spans="1:20" ht="15">
+    <row r="12" spans="1:20">
       <c r="A12" s="3">
         <v>11</v>
       </c>
@@ -2474,7 +2484,7 @@
         <v>4929</v>
       </c>
     </row>
-    <row r="13" spans="1:20" ht="15">
+    <row r="13" spans="1:20">
       <c r="A13" s="3">
         <v>12</v>
       </c>
@@ -2532,7 +2542,7 @@
         <v>8018</v>
       </c>
     </row>
-    <row r="14" spans="1:20" ht="15">
+    <row r="14" spans="1:20">
       <c r="A14" s="3">
         <v>13</v>
       </c>
@@ -2590,7 +2600,7 @@
         <v>6556</v>
       </c>
     </row>
-    <row r="15" spans="1:20" ht="15">
+    <row r="15" spans="1:20">
       <c r="A15" s="3">
         <v>14</v>
       </c>
@@ -2648,7 +2658,7 @@
         <v>12000</v>
       </c>
     </row>
-    <row r="16" spans="1:20" ht="15">
+    <row r="16" spans="1:20">
       <c r="A16" s="3">
         <v>15</v>
       </c>
@@ -2706,7 +2716,7 @@
         <v>17573.5</v>
       </c>
     </row>
-    <row r="17" spans="1:20" ht="15">
+    <row r="17" spans="1:20">
       <c r="A17" s="3">
         <v>16</v>
       </c>
@@ -2764,7 +2774,7 @@
         <v>4608.3500000000004</v>
       </c>
     </row>
-    <row r="18" spans="1:20" ht="15">
+    <row r="18" spans="1:20">
       <c r="A18" s="3">
         <v>17</v>
       </c>
@@ -2822,7 +2832,7 @@
         <v>7891</v>
       </c>
     </row>
-    <row r="19" spans="1:20" ht="15">
+    <row r="19" spans="1:20">
       <c r="A19" s="3">
         <v>18</v>
       </c>
@@ -2880,7 +2890,7 @@
         <v>4617</v>
       </c>
     </row>
-    <row r="20" spans="1:20" ht="15">
+    <row r="20" spans="1:20">
       <c r="A20" s="3">
         <v>19</v>
       </c>
@@ -2938,7 +2948,7 @@
         <v>48600</v>
       </c>
     </row>
-    <row r="21" spans="1:20" ht="15">
+    <row r="21" spans="1:20">
       <c r="A21" s="3">
         <v>20</v>
       </c>
@@ -2996,7 +3006,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="22" spans="1:20" ht="15">
+    <row r="22" spans="1:20">
       <c r="A22" s="3">
         <v>21</v>
       </c>
@@ -3052,7 +3062,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="23" spans="1:20" ht="15">
+    <row r="23" spans="1:20">
       <c r="A23" s="3">
         <v>22</v>
       </c>
@@ -3110,7 +3120,7 @@
         <v>18122</v>
       </c>
     </row>
-    <row r="24" spans="1:20" ht="15">
+    <row r="24" spans="1:20">
       <c r="A24" s="3">
         <v>23</v>
       </c>
@@ -3168,12 +3178,12 @@
         <v>11713</v>
       </c>
     </row>
-    <row r="25" spans="1:20" ht="15">
+    <row r="25" spans="1:20">
       <c r="A25" s="3">
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>4</v>
@@ -3194,7 +3204,7 @@
         <v>7</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
@@ -3226,7 +3236,7 @@
         <v>11256</v>
       </c>
     </row>
-    <row r="26" spans="1:20" ht="15">
+    <row r="26" spans="1:20">
       <c r="A26" s="3">
         <v>25</v>
       </c>
@@ -3284,7 +3294,7 @@
         <v>15305</v>
       </c>
     </row>
-    <row r="27" spans="1:20" ht="15">
+    <row r="27" spans="1:20">
       <c r="A27" s="3">
         <v>26</v>
       </c>
@@ -3342,7 +3352,7 @@
         <v>20603</v>
       </c>
     </row>
-    <row r="28" spans="1:20" ht="15">
+    <row r="28" spans="1:20">
       <c r="A28" s="3">
         <v>27</v>
       </c>
@@ -3400,7 +3410,7 @@
         <v>4211</v>
       </c>
     </row>
-    <row r="29" spans="1:20" ht="15">
+    <row r="29" spans="1:20">
       <c r="A29" s="3">
         <v>28</v>
       </c>
@@ -3458,12 +3468,12 @@
         <v>11019.17</v>
       </c>
     </row>
-    <row r="30" spans="1:20" ht="15">
+    <row r="30" spans="1:20">
       <c r="A30" s="3">
         <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>4</v>
@@ -3516,7 +3526,7 @@
         <v>18500</v>
       </c>
     </row>
-    <row r="31" spans="1:20" ht="15">
+    <row r="31" spans="1:20">
       <c r="A31" s="3">
         <v>30</v>
       </c>
@@ -3572,7 +3582,7 @@
         <v>5885.75</v>
       </c>
     </row>
-    <row r="32" spans="1:20" ht="15">
+    <row r="32" spans="1:20">
       <c r="A32" s="3">
         <v>31</v>
       </c>
@@ -3630,7 +3640,7 @@
         <v>18000</v>
       </c>
     </row>
-    <row r="33" spans="1:20" ht="15">
+    <row r="33" spans="1:20">
       <c r="A33" s="3">
         <v>32</v>
       </c>
@@ -3686,7 +3696,7 @@
         <v>20200</v>
       </c>
     </row>
-    <row r="34" spans="1:20" ht="15">
+    <row r="34" spans="1:20">
       <c r="A34" s="3">
         <v>33</v>
       </c>
@@ -3742,7 +3752,7 @@
         <v>52400</v>
       </c>
     </row>
-    <row r="35" spans="1:20" ht="15">
+    <row r="35" spans="1:20">
       <c r="A35" s="3">
         <v>34</v>
       </c>
@@ -3800,7 +3810,7 @@
         <v>21965</v>
       </c>
     </row>
-    <row r="36" spans="1:20" ht="15">
+    <row r="36" spans="1:20">
       <c r="A36" s="3">
         <v>35</v>
       </c>
@@ -3858,7 +3868,7 @@
         <v>20356</v>
       </c>
     </row>
-    <row r="37" spans="1:20" ht="15">
+    <row r="37" spans="1:20">
       <c r="A37" s="3">
         <v>36</v>
       </c>
@@ -3916,7 +3926,7 @@
         <v>8300</v>
       </c>
     </row>
-    <row r="38" spans="1:20" ht="15">
+    <row r="38" spans="1:20">
       <c r="A38" s="3">
         <v>37</v>
       </c>
@@ -3974,7 +3984,7 @@
         <v>2700</v>
       </c>
     </row>
-    <row r="39" spans="1:20" ht="15">
+    <row r="39" spans="1:20">
       <c r="A39" s="3">
         <v>38</v>
       </c>
@@ -4032,12 +4042,12 @@
         <v>3600</v>
       </c>
     </row>
-    <row r="40" spans="1:20" ht="15">
+    <row r="40" spans="1:20">
       <c r="A40" s="3">
         <v>39</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>4</v>
@@ -4088,7 +4098,7 @@
         <v>18218</v>
       </c>
     </row>
-    <row r="41" spans="1:20" ht="15">
+    <row r="41" spans="1:20">
       <c r="A41" s="3">
         <v>40</v>
       </c>
@@ -4146,7 +4156,7 @@
         <v>9351.27</v>
       </c>
     </row>
-    <row r="42" spans="1:20" ht="15">
+    <row r="42" spans="1:20">
       <c r="A42" s="3">
         <v>41</v>
       </c>
@@ -4204,12 +4214,12 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="43" spans="1:20" ht="15">
+    <row r="43" spans="1:20">
       <c r="A43" s="3">
         <v>42</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>80</v>
@@ -4262,12 +4272,12 @@
         <v>4355</v>
       </c>
     </row>
-    <row r="44" spans="1:20" ht="15">
+    <row r="44" spans="1:20">
       <c r="A44" s="3">
         <v>43</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>80</v>
@@ -4318,7 +4328,7 @@
         <v>11339</v>
       </c>
     </row>
-    <row r="45" spans="1:20" ht="15">
+    <row r="45" spans="1:20">
       <c r="A45" s="3">
         <v>44</v>
       </c>
@@ -4344,7 +4354,7 @@
         <v>81</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J45" s="1"/>
       <c r="K45" s="1"/>
@@ -4376,7 +4386,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="46" spans="1:20" ht="15">
+    <row r="46" spans="1:20">
       <c r="A46" s="3">
         <v>45</v>
       </c>
@@ -4402,7 +4412,7 @@
         <v>81</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="J46" s="1"/>
       <c r="K46" s="1"/>
@@ -4434,7 +4444,7 @@
         <v>7500</v>
       </c>
     </row>
-    <row r="47" spans="1:20" ht="15">
+    <row r="47" spans="1:20">
       <c r="A47" s="3">
         <v>46</v>
       </c>
@@ -4460,7 +4470,7 @@
         <v>81</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="J47" s="1"/>
       <c r="K47" s="1"/>
@@ -4492,7 +4502,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="48" spans="1:20" ht="15">
+    <row r="48" spans="1:20">
       <c r="A48" s="3">
         <v>47</v>
       </c>
@@ -4550,7 +4560,7 @@
         <v>16314.69</v>
       </c>
     </row>
-    <row r="49" spans="1:20" ht="15">
+    <row r="49" spans="1:20">
       <c r="A49" s="3">
         <v>48</v>
       </c>
@@ -4606,7 +4616,7 @@
         <v>6400</v>
       </c>
     </row>
-    <row r="50" spans="1:20" ht="15">
+    <row r="50" spans="1:20">
       <c r="A50" s="3">
         <v>49</v>
       </c>
@@ -4664,7 +4674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:20" ht="15">
+    <row r="51" spans="1:20">
       <c r="A51" s="3">
         <v>50</v>
       </c>
@@ -4720,12 +4730,12 @@
         <v>78130</v>
       </c>
     </row>
-    <row r="52" spans="1:20" ht="15">
+    <row r="52" spans="1:20">
       <c r="A52" s="3">
         <v>51</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>80</v>
@@ -4776,7 +4786,7 @@
         <v>14000</v>
       </c>
     </row>
-    <row r="53" spans="1:20" ht="15">
+    <row r="53" spans="1:20">
       <c r="A53" s="3">
         <v>52</v>
       </c>
@@ -4834,7 +4844,7 @@
         <v>6151.66</v>
       </c>
     </row>
-    <row r="54" spans="1:20" ht="15">
+    <row r="54" spans="1:20">
       <c r="A54" s="3">
         <v>53</v>
       </c>
@@ -4890,7 +4900,7 @@
         <v>20901</v>
       </c>
     </row>
-    <row r="55" spans="1:20" ht="15">
+    <row r="55" spans="1:20">
       <c r="A55" s="3">
         <v>54</v>
       </c>
@@ -4948,12 +4958,12 @@
         <v>12583</v>
       </c>
     </row>
-    <row r="56" spans="1:20" ht="15">
+    <row r="56" spans="1:20">
       <c r="A56" s="3">
         <v>55</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>80</v>
@@ -5006,7 +5016,7 @@
         <v>4021</v>
       </c>
     </row>
-    <row r="57" spans="1:20" ht="15">
+    <row r="57" spans="1:20">
       <c r="A57" s="3">
         <v>56</v>
       </c>
@@ -5064,7 +5074,7 @@
         <v>7270.57</v>
       </c>
     </row>
-    <row r="58" spans="1:20" ht="15">
+    <row r="58" spans="1:20">
       <c r="A58" s="3">
         <v>57</v>
       </c>
@@ -5122,12 +5132,12 @@
         <v>21243.3</v>
       </c>
     </row>
-    <row r="59" spans="1:20" ht="15">
+    <row r="59" spans="1:20">
       <c r="A59" s="3">
         <v>58</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C59" s="3" t="s">
         <v>80</v>
@@ -5180,12 +5190,12 @@
         <v>3734</v>
       </c>
     </row>
-    <row r="60" spans="1:20" ht="15">
+    <row r="60" spans="1:20">
       <c r="A60" s="3">
         <v>59</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C60" s="3" t="s">
         <v>80</v>
@@ -5238,7 +5248,7 @@
         <v>3019.89</v>
       </c>
     </row>
-    <row r="61" spans="1:20" ht="15">
+    <row r="61" spans="1:20">
       <c r="A61" s="3">
         <v>60</v>
       </c>
@@ -5294,7 +5304,7 @@
         <v>4208</v>
       </c>
     </row>
-    <row r="62" spans="1:20" ht="15">
+    <row r="62" spans="1:20">
       <c r="A62" s="3">
         <v>61</v>
       </c>
@@ -5352,7 +5362,7 @@
         <v>59000</v>
       </c>
     </row>
-    <row r="63" spans="1:20" ht="15">
+    <row r="63" spans="1:20">
       <c r="A63" s="3">
         <v>62</v>
       </c>
@@ -5377,8 +5387,8 @@
       <c r="H63" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="I63" s="3" t="s">
-        <v>380</v>
+      <c r="I63" s="4" t="s">
+        <v>433</v>
       </c>
       <c r="J63" s="1"/>
       <c r="K63" s="1"/>
@@ -5410,7 +5420,7 @@
         <v>4800</v>
       </c>
     </row>
-    <row r="64" spans="1:20" ht="15">
+    <row r="64" spans="1:20">
       <c r="A64" s="3">
         <v>63</v>
       </c>
@@ -5468,7 +5478,7 @@
         <v>10500</v>
       </c>
     </row>
-    <row r="65" spans="1:20" ht="15">
+    <row r="65" spans="1:20">
       <c r="A65" s="3">
         <v>64</v>
       </c>
@@ -5524,7 +5534,7 @@
         <v>7586</v>
       </c>
     </row>
-    <row r="66" spans="1:20" ht="15">
+    <row r="66" spans="1:20">
       <c r="A66" s="3">
         <v>65</v>
       </c>
@@ -5580,7 +5590,7 @@
         <v>4300</v>
       </c>
     </row>
-    <row r="67" spans="1:20" ht="15">
+    <row r="67" spans="1:20">
       <c r="A67" s="3">
         <v>66</v>
       </c>
@@ -5638,7 +5648,7 @@
         <v>17418</v>
       </c>
     </row>
-    <row r="68" spans="1:20" ht="15">
+    <row r="68" spans="1:20">
       <c r="A68" s="3">
         <v>67</v>
       </c>
@@ -5696,7 +5706,7 @@
         <v>3600</v>
       </c>
     </row>
-    <row r="69" spans="1:20" ht="15">
+    <row r="69" spans="1:20">
       <c r="A69" s="3">
         <v>68</v>
       </c>
@@ -5720,7 +5730,7 @@
         <v>60</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="J69" s="1"/>
       <c r="K69" s="1"/>
@@ -5752,7 +5762,7 @@
         <v>3749</v>
       </c>
     </row>
-    <row r="70" spans="1:20" ht="15">
+    <row r="70" spans="1:20">
       <c r="A70" s="3">
         <v>69</v>
       </c>
@@ -5808,7 +5818,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="71" spans="1:20" ht="15">
+    <row r="71" spans="1:20">
       <c r="A71" s="3">
         <v>70</v>
       </c>
@@ -5864,12 +5874,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:20" ht="15">
+    <row r="72" spans="1:20">
       <c r="A72" s="3">
         <v>71</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C72" s="3" t="s">
         <v>113</v>
@@ -5920,7 +5930,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="73" spans="1:20" ht="15">
+    <row r="73" spans="1:20">
       <c r="A73" s="3">
         <v>72</v>
       </c>
@@ -5978,7 +5988,7 @@
         <v>8881</v>
       </c>
     </row>
-    <row r="74" spans="1:20" ht="15">
+    <row r="74" spans="1:20">
       <c r="A74" s="3">
         <v>73</v>
       </c>
@@ -6036,7 +6046,7 @@
         <v>13000</v>
       </c>
     </row>
-    <row r="75" spans="1:20" ht="15">
+    <row r="75" spans="1:20">
       <c r="A75" s="3">
         <v>74</v>
       </c>
@@ -6092,7 +6102,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:20" ht="15">
+    <row r="76" spans="1:20">
       <c r="A76" s="3">
         <v>75</v>
       </c>
@@ -6150,7 +6160,7 @@
         <v>3157</v>
       </c>
     </row>
-    <row r="77" spans="1:20" ht="15">
+    <row r="77" spans="1:20">
       <c r="A77" s="3">
         <v>76</v>
       </c>
@@ -6176,7 +6186,7 @@
         <v>60</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="J77" s="1"/>
       <c r="K77" s="1"/>
@@ -6208,7 +6218,7 @@
         <v>9537</v>
       </c>
     </row>
-    <row r="78" spans="1:20" ht="15">
+    <row r="78" spans="1:20">
       <c r="A78" s="3">
         <v>77</v>
       </c>
@@ -6266,7 +6276,7 @@
         <v>3400</v>
       </c>
     </row>
-    <row r="79" spans="1:20" ht="15">
+    <row r="79" spans="1:20">
       <c r="A79" s="3">
         <v>78</v>
       </c>
@@ -6322,7 +6332,7 @@
         <v>8574</v>
       </c>
     </row>
-    <row r="80" spans="1:20" ht="15">
+    <row r="80" spans="1:20">
       <c r="A80" s="3">
         <v>79</v>
       </c>
@@ -6378,7 +6388,7 @@
         <v>7150</v>
       </c>
     </row>
-    <row r="81" spans="1:20" ht="15">
+    <row r="81" spans="1:20">
       <c r="A81" s="3">
         <v>80</v>
       </c>
@@ -6404,7 +6414,7 @@
         <v>7</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="J81" s="1"/>
       <c r="K81" s="1"/>
@@ -6436,7 +6446,7 @@
         <v>19235</v>
       </c>
     </row>
-    <row r="82" spans="1:20" ht="15">
+    <row r="82" spans="1:20">
       <c r="A82" s="3">
         <v>81</v>
       </c>
@@ -6494,7 +6504,7 @@
         <v>7500</v>
       </c>
     </row>
-    <row r="83" spans="1:20" ht="15">
+    <row r="83" spans="1:20">
       <c r="A83" s="3">
         <v>82</v>
       </c>
@@ -6552,7 +6562,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="84" spans="1:20" ht="15">
+    <row r="84" spans="1:20">
       <c r="A84" s="3">
         <v>83</v>
       </c>
@@ -6610,7 +6620,7 @@
         <v>22971</v>
       </c>
     </row>
-    <row r="85" spans="1:20" ht="15">
+    <row r="85" spans="1:20">
       <c r="A85" s="3">
         <v>84</v>
       </c>
@@ -6666,7 +6676,7 @@
         <v>3800</v>
       </c>
     </row>
-    <row r="86" spans="1:20" ht="15">
+    <row r="86" spans="1:20">
       <c r="A86" s="3">
         <v>85</v>
       </c>
@@ -6724,7 +6734,7 @@
         <v>8139</v>
       </c>
     </row>
-    <row r="87" spans="1:20" ht="15">
+    <row r="87" spans="1:20">
       <c r="A87" s="3">
         <v>86</v>
       </c>
@@ -6780,12 +6790,12 @@
         <v>4700</v>
       </c>
     </row>
-    <row r="88" spans="1:20" ht="15">
+    <row r="88" spans="1:20">
       <c r="A88" s="3">
         <v>87</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C88" s="3" t="s">
         <v>97</v>
@@ -6838,7 +6848,7 @@
         <v>6300</v>
       </c>
     </row>
-    <row r="89" spans="1:20" ht="15">
+    <row r="89" spans="1:20">
       <c r="A89" s="3">
         <v>88</v>
       </c>
@@ -6862,7 +6872,7 @@
         <v>7</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="J89" s="1"/>
       <c r="K89" s="1"/>
@@ -6894,7 +6904,7 @@
         <v>36930</v>
       </c>
     </row>
-    <row r="90" spans="1:20" ht="15">
+    <row r="90" spans="1:20">
       <c r="A90" s="3">
         <v>89</v>
       </c>
@@ -6950,7 +6960,7 @@
         <v>11123.6</v>
       </c>
     </row>
-    <row r="91" spans="1:20" ht="15">
+    <row r="91" spans="1:20">
       <c r="A91" s="3">
         <v>90</v>
       </c>
@@ -7006,7 +7016,7 @@
         <v>1898</v>
       </c>
     </row>
-    <row r="92" spans="1:20" ht="15">
+    <row r="92" spans="1:20">
       <c r="A92" s="3">
         <v>91</v>
       </c>
@@ -7064,7 +7074,7 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="93" spans="1:20" ht="15">
+    <row r="93" spans="1:20">
       <c r="A93" s="3">
         <v>92</v>
       </c>
@@ -7122,12 +7132,12 @@
         <v>34000</v>
       </c>
     </row>
-    <row r="94" spans="1:20" ht="15">
+    <row r="94" spans="1:20">
       <c r="A94" s="3">
         <v>93</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C94" s="3" t="s">
         <v>97</v>
@@ -7180,7 +7190,7 @@
         <v>11981</v>
       </c>
     </row>
-    <row r="95" spans="1:20" ht="15">
+    <row r="95" spans="1:20">
       <c r="A95" s="3">
         <v>94</v>
       </c>
@@ -7238,12 +7248,12 @@
         <v>12000</v>
       </c>
     </row>
-    <row r="96" spans="1:20" ht="15">
+    <row r="96" spans="1:20">
       <c r="A96" s="3">
         <v>95</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C96" s="3" t="s">
         <v>97</v>
@@ -7294,7 +7304,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="97" spans="1:20" ht="15">
+    <row r="97" spans="1:20">
       <c r="A97" s="3">
         <v>96</v>
       </c>
@@ -7350,12 +7360,12 @@
         <v>40000</v>
       </c>
     </row>
-    <row r="98" spans="1:20" ht="15">
+    <row r="98" spans="1:20">
       <c r="A98" s="3">
         <v>97</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C98" s="3" t="s">
         <v>97</v>
@@ -7408,7 +7418,7 @@
         <v>31248</v>
       </c>
     </row>
-    <row r="99" spans="1:20" ht="15">
+    <row r="99" spans="1:20">
       <c r="A99" s="3">
         <v>98</v>
       </c>
@@ -7466,7 +7476,7 @@
         <v>11955</v>
       </c>
     </row>
-    <row r="100" spans="1:20" ht="15">
+    <row r="100" spans="1:20">
       <c r="A100" s="3">
         <v>99</v>
       </c>
@@ -7524,7 +7534,7 @@
         <v>11718</v>
       </c>
     </row>
-    <row r="101" spans="1:20" ht="15">
+    <row r="101" spans="1:20">
       <c r="A101" s="3">
         <v>100</v>
       </c>
@@ -7582,7 +7592,7 @@
         <v>14206</v>
       </c>
     </row>
-    <row r="102" spans="1:20" ht="15">
+    <row r="102" spans="1:20">
       <c r="A102" s="3">
         <v>101</v>
       </c>
@@ -7638,7 +7648,7 @@
         <v>7003</v>
       </c>
     </row>
-    <row r="103" spans="1:20" ht="15">
+    <row r="103" spans="1:20">
       <c r="A103" s="3">
         <v>102</v>
       </c>
@@ -7694,7 +7704,7 @@
         <v>5862</v>
       </c>
     </row>
-    <row r="104" spans="1:20" ht="15">
+    <row r="104" spans="1:20">
       <c r="A104" s="3">
         <v>103</v>
       </c>
@@ -7750,7 +7760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:20" ht="15">
+    <row r="105" spans="1:20">
       <c r="A105" s="3">
         <v>104</v>
       </c>
@@ -7806,12 +7816,12 @@
         <v>120.9</v>
       </c>
     </row>
-    <row r="106" spans="1:20" ht="15">
+    <row r="106" spans="1:20">
       <c r="A106" s="3">
         <v>105</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C106" s="3" t="s">
         <v>169</v>
@@ -7862,7 +7872,7 @@
         <v>23200</v>
       </c>
     </row>
-    <row r="107" spans="1:20" ht="15">
+    <row r="107" spans="1:20">
       <c r="A107" s="3">
         <v>106</v>
       </c>
@@ -7920,7 +7930,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="108" spans="1:20" ht="15">
+    <row r="108" spans="1:20">
       <c r="A108" s="3">
         <v>107</v>
       </c>
@@ -7976,7 +7986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:20" ht="15">
+    <row r="109" spans="1:20">
       <c r="A109" s="3">
         <v>108</v>
       </c>
@@ -8032,7 +8042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:20" ht="15">
+    <row r="110" spans="1:20">
       <c r="A110" s="3">
         <v>109</v>
       </c>
@@ -8088,7 +8098,7 @@
         <v>15830</v>
       </c>
     </row>
-    <row r="111" spans="1:20" ht="15">
+    <row r="111" spans="1:20">
       <c r="A111" s="3">
         <v>110</v>
       </c>
@@ -8144,7 +8154,7 @@
         <v>19941.5</v>
       </c>
     </row>
-    <row r="112" spans="1:20" ht="15">
+    <row r="112" spans="1:20">
       <c r="A112" s="3">
         <v>111</v>
       </c>
@@ -8202,12 +8212,12 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="113" spans="1:20" ht="15">
+    <row r="113" spans="1:20">
       <c r="A113" s="3">
         <v>112</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C113" s="3" t="s">
         <v>169</v>
@@ -8260,12 +8270,12 @@
         <v>427</v>
       </c>
     </row>
-    <row r="114" spans="1:20" ht="15">
+    <row r="114" spans="1:20">
       <c r="A114" s="3">
         <v>113</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C114" s="3" t="s">
         <v>169</v>
@@ -8318,12 +8328,12 @@
         <v>11500</v>
       </c>
     </row>
-    <row r="115" spans="1:20" ht="15">
+    <row r="115" spans="1:20">
       <c r="A115" s="3">
         <v>114</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C115" s="3" t="s">
         <v>169</v>
@@ -8374,7 +8384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:20" ht="15">
+    <row r="116" spans="1:20">
       <c r="A116" s="3">
         <v>115</v>
       </c>
@@ -8430,7 +8440,7 @@
         <v>21000</v>
       </c>
     </row>
-    <row r="117" spans="1:20" ht="15">
+    <row r="117" spans="1:20">
       <c r="A117" s="3">
         <v>116</v>
       </c>
@@ -8486,7 +8496,7 @@
         <v>31890</v>
       </c>
     </row>
-    <row r="118" spans="1:20" ht="15">
+    <row r="118" spans="1:20">
       <c r="A118" s="3">
         <v>117</v>
       </c>
@@ -8542,7 +8552,7 @@
         <v>1116</v>
       </c>
     </row>
-    <row r="119" spans="1:20" ht="15">
+    <row r="119" spans="1:20">
       <c r="A119" s="3">
         <v>118</v>
       </c>
@@ -8598,7 +8608,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:20" ht="15">
+    <row r="120" spans="1:20">
       <c r="A120" s="3">
         <v>119</v>
       </c>
@@ -8656,7 +8666,7 @@
         <v>5600</v>
       </c>
     </row>
-    <row r="121" spans="1:20" ht="15">
+    <row r="121" spans="1:20">
       <c r="A121" s="3">
         <v>120</v>
       </c>
@@ -8714,12 +8724,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:20" ht="15">
+    <row r="122" spans="1:20">
       <c r="A122" s="3">
         <v>121</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C122" s="3" t="s">
         <v>169</v>
@@ -8740,7 +8750,7 @@
         <v>139</v>
       </c>
       <c r="I122" s="3" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="J122" s="1"/>
       <c r="K122" s="1"/>
@@ -8772,7 +8782,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="123" spans="1:20" ht="15">
+    <row r="123" spans="1:20">
       <c r="A123" s="3">
         <v>122</v>
       </c>
@@ -8794,7 +8804,7 @@
         <v>139</v>
       </c>
       <c r="I123" s="3" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="J123" s="1"/>
       <c r="K123" s="1"/>
@@ -8824,12 +8834,12 @@
         <v>97326.47</v>
       </c>
     </row>
-    <row r="124" spans="1:20" ht="15">
+    <row r="124" spans="1:20">
       <c r="A124" s="3">
         <v>123</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C124" s="3" t="s">
         <v>207</v>
@@ -8882,7 +8892,7 @@
         <v>15956.21</v>
       </c>
     </row>
-    <row r="125" spans="1:20" ht="15">
+    <row r="125" spans="1:20">
       <c r="A125" s="3">
         <v>124</v>
       </c>
@@ -8940,7 +8950,7 @@
         <v>6631</v>
       </c>
     </row>
-    <row r="126" spans="1:20" ht="15">
+    <row r="126" spans="1:20">
       <c r="A126" s="3">
         <v>125</v>
       </c>
@@ -8996,7 +9006,7 @@
         <v>14329.850000000002</v>
       </c>
     </row>
-    <row r="127" spans="1:20" ht="15">
+    <row r="127" spans="1:20">
       <c r="A127" s="3">
         <v>126</v>
       </c>
@@ -9054,7 +9064,7 @@
         <v>6594</v>
       </c>
     </row>
-    <row r="128" spans="1:20" ht="15">
+    <row r="128" spans="1:20">
       <c r="A128" s="3">
         <v>127</v>
       </c>
@@ -9112,12 +9122,12 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="129" spans="1:20" ht="15">
+    <row r="129" spans="1:20">
       <c r="A129" s="3">
         <v>128</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C129" s="3" t="s">
         <v>207</v>
@@ -9170,7 +9180,7 @@
         <v>35707.82</v>
       </c>
     </row>
-    <row r="130" spans="1:20" ht="15">
+    <row r="130" spans="1:20">
       <c r="A130" s="3">
         <v>129</v>
       </c>
@@ -9228,7 +9238,7 @@
         <v>4100</v>
       </c>
     </row>
-    <row r="131" spans="1:20" ht="15">
+    <row r="131" spans="1:20">
       <c r="A131" s="3">
         <v>130</v>
       </c>
@@ -9286,12 +9296,12 @@
         <v>19710</v>
       </c>
     </row>
-    <row r="132" spans="1:20" ht="15">
+    <row r="132" spans="1:20">
       <c r="A132" s="3">
         <v>131</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C132" s="3" t="s">
         <v>207</v>
@@ -9344,7 +9354,7 @@
         <v>11436.280000000002</v>
       </c>
     </row>
-    <row r="133" spans="1:20" ht="15">
+    <row r="133" spans="1:20">
       <c r="A133" s="3">
         <v>132</v>
       </c>
@@ -9402,7 +9412,7 @@
         <v>5860.63</v>
       </c>
     </row>
-    <row r="134" spans="1:20" ht="15">
+    <row r="134" spans="1:20">
       <c r="A134" s="3">
         <v>133</v>
       </c>
@@ -9460,12 +9470,12 @@
         <v>6669.369999999999</v>
       </c>
     </row>
-    <row r="135" spans="1:20" ht="15">
+    <row r="135" spans="1:20">
       <c r="A135" s="3">
         <v>134</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C135" s="3" t="s">
         <v>207</v>
@@ -9518,12 +9528,12 @@
         <v>32274.100000000002</v>
       </c>
     </row>
-    <row r="136" spans="1:20" ht="15">
+    <row r="136" spans="1:20">
       <c r="A136" s="3">
         <v>135</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C136" s="3" t="s">
         <v>207</v>
@@ -9576,7 +9586,7 @@
         <v>1901</v>
       </c>
     </row>
-    <row r="137" spans="1:20" ht="15">
+    <row r="137" spans="1:20">
       <c r="A137" s="3">
         <v>136</v>
       </c>
@@ -9591,7 +9601,7 @@
       </c>
       <c r="E137" s="3"/>
       <c r="F137" s="3" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G137" s="3" t="s">
         <v>6</v>
@@ -9632,7 +9642,7 @@
         <v>6126</v>
       </c>
     </row>
-    <row r="138" spans="1:20" ht="15">
+    <row r="138" spans="1:20">
       <c r="A138" s="3">
         <v>137</v>
       </c>
@@ -9690,7 +9700,7 @@
         <v>2182</v>
       </c>
     </row>
-    <row r="139" spans="1:20" ht="15">
+    <row r="139" spans="1:20">
       <c r="A139" s="3">
         <v>138</v>
       </c>
@@ -9746,7 +9756,7 @@
         <v>4616</v>
       </c>
     </row>
-    <row r="140" spans="1:20" ht="15">
+    <row r="140" spans="1:20">
       <c r="A140" s="3">
         <v>139</v>
       </c>
@@ -9802,7 +9812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:20" ht="15">
+    <row r="141" spans="1:20">
       <c r="A141" s="3">
         <v>140</v>
       </c>
@@ -9858,7 +9868,7 @@
         <v>18000</v>
       </c>
     </row>
-    <row r="142" spans="1:20" ht="15">
+    <row r="142" spans="1:20">
       <c r="A142" s="3">
         <v>141</v>
       </c>
@@ -9914,7 +9924,7 @@
         <v>23660</v>
       </c>
     </row>
-    <row r="143" spans="1:20" ht="15">
+    <row r="143" spans="1:20">
       <c r="A143" s="3">
         <v>142</v>
       </c>
@@ -9970,12 +9980,12 @@
         <v>7276</v>
       </c>
     </row>
-    <row r="144" spans="1:20" ht="15">
+    <row r="144" spans="1:20">
       <c r="A144" s="3">
         <v>143</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C144" s="3" t="s">
         <v>230</v>
@@ -10028,12 +10038,12 @@
         <v>78750</v>
       </c>
     </row>
-    <row r="145" spans="1:20" ht="15">
+    <row r="145" spans="1:20">
       <c r="A145" s="3">
         <v>144</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C145" s="3" t="s">
         <v>230</v>
@@ -10086,12 +10096,12 @@
         <v>40000</v>
       </c>
     </row>
-    <row r="146" spans="1:20" ht="15">
+    <row r="146" spans="1:20">
       <c r="A146" s="3">
         <v>145</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C146" s="3" t="s">
         <v>230</v>
@@ -10142,7 +10152,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="147" spans="1:20" ht="15">
+    <row r="147" spans="1:20">
       <c r="A147" s="3">
         <v>146</v>
       </c>
@@ -10200,12 +10210,12 @@
         <v>12000</v>
       </c>
     </row>
-    <row r="148" spans="1:20" ht="15">
+    <row r="148" spans="1:20">
       <c r="A148" s="3">
         <v>147</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C148" s="3" t="s">
         <v>230</v>
@@ -10258,7 +10268,7 @@
         <v>31153</v>
       </c>
     </row>
-    <row r="149" spans="1:20" ht="15">
+    <row r="149" spans="1:20">
       <c r="A149" s="3">
         <v>148</v>
       </c>
@@ -10284,7 +10294,7 @@
         <v>7</v>
       </c>
       <c r="I149" s="3" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="J149" s="1"/>
       <c r="K149" s="1"/>
@@ -10316,7 +10326,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="150" spans="1:20" ht="15">
+    <row r="150" spans="1:20">
       <c r="A150" s="3">
         <v>149</v>
       </c>
@@ -10374,7 +10384,7 @@
         <v>9233</v>
       </c>
     </row>
-    <row r="151" spans="1:20" ht="15">
+    <row r="151" spans="1:20">
       <c r="A151" s="3">
         <v>150</v>
       </c>
@@ -10432,7 +10442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:20" ht="15">
+    <row r="152" spans="1:20">
       <c r="A152" s="3">
         <v>151</v>
       </c>
@@ -10488,7 +10498,7 @@
         <v>4600</v>
       </c>
     </row>
-    <row r="153" spans="1:20" ht="15">
+    <row r="153" spans="1:20">
       <c r="A153" s="3">
         <v>152</v>
       </c>
@@ -10546,7 +10556,7 @@
         <v>32300</v>
       </c>
     </row>
-    <row r="154" spans="1:20" ht="15">
+    <row r="154" spans="1:20">
       <c r="A154" s="3">
         <v>153</v>
       </c>
@@ -10604,7 +10614,7 @@
         <v>18531</v>
       </c>
     </row>
-    <row r="155" spans="1:20" ht="15">
+    <row r="155" spans="1:20">
       <c r="A155" s="3">
         <v>154</v>
       </c>
@@ -10662,7 +10672,7 @@
         <v>31700</v>
       </c>
     </row>
-    <row r="156" spans="1:20" ht="15">
+    <row r="156" spans="1:20">
       <c r="A156" s="3">
         <v>155</v>
       </c>
@@ -10720,7 +10730,7 @@
         <v>4092</v>
       </c>
     </row>
-    <row r="157" spans="1:20" ht="15">
+    <row r="157" spans="1:20">
       <c r="A157" s="3">
         <v>156</v>
       </c>
@@ -10778,7 +10788,7 @@
         <v>15371</v>
       </c>
     </row>
-    <row r="158" spans="1:20" ht="15">
+    <row r="158" spans="1:20">
       <c r="A158" s="3">
         <v>157</v>
       </c>
@@ -10834,7 +10844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:20" ht="15">
+    <row r="159" spans="1:20">
       <c r="A159" s="3">
         <v>158</v>
       </c>
@@ -10892,7 +10902,7 @@
         <v>4279</v>
       </c>
     </row>
-    <row r="160" spans="1:20" ht="15">
+    <row r="160" spans="1:20">
       <c r="A160" s="3">
         <v>159</v>
       </c>
@@ -10950,7 +10960,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="161" spans="1:20" ht="15">
+    <row r="161" spans="1:20">
       <c r="A161" s="3">
         <v>160</v>
       </c>
@@ -11008,7 +11018,7 @@
         <v>19440</v>
       </c>
     </row>
-    <row r="162" spans="1:20" ht="15">
+    <row r="162" spans="1:20">
       <c r="A162" s="3">
         <v>161</v>
       </c>
@@ -11066,7 +11076,7 @@
         <v>10166</v>
       </c>
     </row>
-    <row r="163" spans="1:20" ht="15">
+    <row r="163" spans="1:20">
       <c r="A163" s="3">
         <v>162</v>
       </c>
@@ -11124,12 +11134,12 @@
         <v>9014</v>
       </c>
     </row>
-    <row r="164" spans="1:20" ht="15">
+    <row r="164" spans="1:20">
       <c r="A164" s="3">
         <v>163</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C164" s="3" t="s">
         <v>257</v>
@@ -11182,7 +11192,7 @@
         <v>50100</v>
       </c>
     </row>
-    <row r="165" spans="1:20" ht="15">
+    <row r="165" spans="1:20">
       <c r="A165" s="3">
         <v>164</v>
       </c>
@@ -11234,7 +11244,7 @@
         <v>51204</v>
       </c>
     </row>
-    <row r="166" spans="1:20" ht="15">
+    <row r="166" spans="1:20">
       <c r="A166" s="3">
         <v>165</v>
       </c>
@@ -11292,7 +11302,7 @@
         <v>8589</v>
       </c>
     </row>
-    <row r="167" spans="1:20" ht="15">
+    <row r="167" spans="1:20">
       <c r="A167" s="3">
         <v>166</v>
       </c>
@@ -11348,7 +11358,7 @@
         <v>8967</v>
       </c>
     </row>
-    <row r="168" spans="1:20" ht="15">
+    <row r="168" spans="1:20">
       <c r="A168" s="3">
         <v>167</v>
       </c>
@@ -11406,7 +11416,7 @@
         <v>3493</v>
       </c>
     </row>
-    <row r="169" spans="1:20" ht="15">
+    <row r="169" spans="1:20">
       <c r="A169" s="3">
         <v>168</v>
       </c>
@@ -11464,7 +11474,7 @@
         <v>17000</v>
       </c>
     </row>
-    <row r="170" spans="1:20" ht="15">
+    <row r="170" spans="1:20">
       <c r="A170" s="3">
         <v>169</v>
       </c>
@@ -11520,7 +11530,7 @@
         <v>1330</v>
       </c>
     </row>
-    <row r="171" spans="1:20" ht="15">
+    <row r="171" spans="1:20">
       <c r="A171" s="3">
         <v>170</v>
       </c>
@@ -11576,7 +11586,7 @@
         <v>18039</v>
       </c>
     </row>
-    <row r="172" spans="1:20" ht="15">
+    <row r="172" spans="1:20">
       <c r="A172" s="3">
         <v>171</v>
       </c>
@@ -11634,7 +11644,7 @@
         <v>10527</v>
       </c>
     </row>
-    <row r="173" spans="1:20" ht="15">
+    <row r="173" spans="1:20">
       <c r="A173" s="3">
         <v>172</v>
       </c>
@@ -11692,7 +11702,7 @@
         <v>2350</v>
       </c>
     </row>
-    <row r="174" spans="1:20" ht="15">
+    <row r="174" spans="1:20">
       <c r="A174" s="3">
         <v>173</v>
       </c>
@@ -11750,7 +11760,7 @@
         <v>3480</v>
       </c>
     </row>
-    <row r="175" spans="1:20" ht="15">
+    <row r="175" spans="1:20">
       <c r="A175" s="3">
         <v>174</v>
       </c>
@@ -11776,7 +11786,7 @@
         <v>298</v>
       </c>
       <c r="I175" s="3" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="J175" s="1"/>
       <c r="K175" s="1"/>
@@ -11808,7 +11818,7 @@
         <v>29000</v>
       </c>
     </row>
-    <row r="176" spans="1:20" ht="15">
+    <row r="176" spans="1:20">
       <c r="A176" s="3">
         <v>175</v>
       </c>
@@ -11866,7 +11876,7 @@
         <v>35016</v>
       </c>
     </row>
-    <row r="177" spans="1:20" ht="15">
+    <row r="177" spans="1:20">
       <c r="A177" s="3">
         <v>176</v>
       </c>
@@ -11922,7 +11932,7 @@
         <v>8416</v>
       </c>
     </row>
-    <row r="178" spans="1:20" ht="15">
+    <row r="178" spans="1:20">
       <c r="A178" s="3">
         <v>177</v>
       </c>
@@ -11980,7 +11990,7 @@
         <v>14000</v>
       </c>
     </row>
-    <row r="179" spans="1:20" ht="15">
+    <row r="179" spans="1:20">
       <c r="A179" s="3">
         <v>178</v>
       </c>
@@ -12036,7 +12046,7 @@
         <v>22912</v>
       </c>
     </row>
-    <row r="180" spans="1:20" ht="15">
+    <row r="180" spans="1:20">
       <c r="A180" s="3">
         <v>179</v>
       </c>
@@ -12092,7 +12102,7 @@
         <v>15800</v>
       </c>
     </row>
-    <row r="181" spans="1:20" ht="15">
+    <row r="181" spans="1:20">
       <c r="A181" s="3">
         <v>180</v>
       </c>
@@ -12150,7 +12160,7 @@
         <v>28050</v>
       </c>
     </row>
-    <row r="182" spans="1:20" ht="15">
+    <row r="182" spans="1:20">
       <c r="A182" s="3">
         <v>181</v>
       </c>
@@ -12208,7 +12218,7 @@
         <v>7200</v>
       </c>
     </row>
-    <row r="183" spans="1:20" ht="15">
+    <row r="183" spans="1:20">
       <c r="A183" s="3">
         <v>182</v>
       </c>
@@ -12264,7 +12274,7 @@
         <v>22000</v>
       </c>
     </row>
-    <row r="184" spans="1:20" ht="15">
+    <row r="184" spans="1:20">
       <c r="A184" s="3">
         <v>183</v>
       </c>
@@ -12322,7 +12332,7 @@
         <v>60477</v>
       </c>
     </row>
-    <row r="185" spans="1:20" ht="15">
+    <row r="185" spans="1:20">
       <c r="A185" s="3">
         <v>184</v>
       </c>
@@ -12378,7 +12388,7 @@
         <v>46900</v>
       </c>
     </row>
-    <row r="186" spans="1:20" ht="15">
+    <row r="186" spans="1:20">
       <c r="A186" s="3">
         <v>185</v>
       </c>
@@ -12432,7 +12442,7 @@
         <v>19800</v>
       </c>
     </row>
-    <row r="187" spans="1:20" ht="15">
+    <row r="187" spans="1:20">
       <c r="A187" s="3">
         <v>186</v>
       </c>
@@ -12486,7 +12496,7 @@
         <v>8800</v>
       </c>
     </row>
-    <row r="188" spans="1:20" ht="15">
+    <row r="188" spans="1:20">
       <c r="A188" s="3">
         <v>187</v>
       </c>
@@ -12542,7 +12552,7 @@
         <v>57000</v>
       </c>
     </row>
-    <row r="189" spans="1:20" ht="15">
+    <row r="189" spans="1:20">
       <c r="A189" s="3">
         <v>188</v>
       </c>
@@ -12596,12 +12606,12 @@
         <v>10700</v>
       </c>
     </row>
-    <row r="190" spans="1:20" ht="15">
+    <row r="190" spans="1:20">
       <c r="A190" s="3">
         <v>189</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C190" s="3" t="s">
         <v>320</v>
@@ -12652,7 +12662,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="191" spans="1:20" ht="15">
+    <row r="191" spans="1:20">
       <c r="A191" s="3">
         <v>190</v>
       </c>
@@ -12706,12 +12716,12 @@
         <v>15800</v>
       </c>
     </row>
-    <row r="192" spans="1:20" ht="15">
+    <row r="192" spans="1:20">
       <c r="A192" s="3">
         <v>191</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C192" s="3" t="s">
         <v>320</v>
@@ -12732,7 +12742,7 @@
         <v>321</v>
       </c>
       <c r="I192" s="3" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="J192" s="1"/>
       <c r="K192" s="1"/>
@@ -12753,7 +12763,6 @@
       <c r="T192" s="1"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="EYAWn+nqEiYVHTM3Rf5HED43hoYlnyr6pPaKvobibbgq2Zv6I27bS01P0RjYZoCpvEC0zMPCZdjXdxeBiD2uJw==" saltValue="QSImVvjldcRGS4sSsC+y4A==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <autoFilter ref="A1:V192" xr:uid="{7B280671-4AFA-4641-88D4-A51F39483890}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12762,12 +12771,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e40a7e4-94f1-4b05-8c7e-c5111c724f9a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="f655991e-a262-4cc2-969f-4b8d0db6a5de" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -13032,20 +13043,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e40a7e4-94f1-4b05-8c7e-c5111c724f9a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="f655991e-a262-4cc2-969f-4b8d0db6a5de" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C7A7DD6C-B285-4C23-BA8C-7CCC252AB8AB}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF6E6A69-6D48-49BB-9E8E-5B96C2738B7E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="8e40a7e4-94f1-4b05-8c7e-c5111c724f9a"/>
+    <ds:schemaRef ds:uri="f655991e-a262-4cc2-969f-4b8d0db6a5de"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -13070,12 +13082,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF6E6A69-6D48-49BB-9E8E-5B96C2738B7E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C7A7DD6C-B285-4C23-BA8C-7CCC252AB8AB}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="8e40a7e4-94f1-4b05-8c7e-c5111c724f9a"/>
-    <ds:schemaRef ds:uri="f655991e-a262-4cc2-969f-4b8d0db6a5de"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yuhang/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2063C6AF-73C1-484D-B920-0CE2859F626F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80CB7D00-4488-6041-9950-1654A4F788B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20" yWindow="620" windowWidth="14420" windowHeight="15940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$V$192</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$U$192</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1472" uniqueCount="434">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1663" uniqueCount="445">
   <si>
     <t>所在市</t>
   </si>
@@ -1250,9 +1250,6 @@
     <t>116.452709,39.907549</t>
   </si>
   <si>
-    <t>WWT世界财富中心</t>
-  </si>
-  <si>
     <t>国际财源中心（IFC）</t>
   </si>
   <si>
@@ -1307,9 +1304,6 @@
     <t>和泓大厦南塔</t>
   </si>
   <si>
-    <t>中关村东升科技园三期·东畔创新中心</t>
-  </si>
-  <si>
     <t>利星行广场</t>
   </si>
   <si>
@@ -1328,16 +1322,7 @@
     <t>钰珵大厦</t>
   </si>
   <si>
-    <t>奥南五号大厦A座</t>
-  </si>
-  <si>
     <t>招商局广场</t>
-  </si>
-  <si>
-    <t>奥南五号大厦B座</t>
-  </si>
-  <si>
-    <t>丽金中心（AB栋）</t>
   </si>
   <si>
     <t>通州C01</t>
@@ -1368,6 +1353,60 @@
   </si>
   <si>
     <t>116.359885,39.906007</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>负责人</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ming Lu</t>
+  </si>
+  <si>
+    <t>Lily Liu</t>
+  </si>
+  <si>
+    <t>Cassie Gao</t>
+  </si>
+  <si>
+    <t>Reuben Xu</t>
+  </si>
+  <si>
+    <t>Linda Yang</t>
+  </si>
+  <si>
+    <t>Monica Guo</t>
+  </si>
+  <si>
+    <t>Titus Rong</t>
+  </si>
+  <si>
+    <t>Jayden Kang</t>
+  </si>
+  <si>
+    <t>Iris Liu</t>
+  </si>
+  <si>
+    <t>David Dai</t>
+  </si>
+  <si>
+    <t>WWT世界财富大厦</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>中关村东升科技园·东畔科创中心</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>奥南五号大厦A座（天圆祥泰大厦）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>奥南五号大厦B座（恒毅大厦）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>丽金中心（AB座）</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1375,7 +1414,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1409,6 +1448,14 @@
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1449,7 +1496,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
@@ -1462,6 +1509,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
       <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1770,7 +1820,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B280671-4AFA-4641-88D4-A51F39483890}">
-  <dimension ref="A1:T192"/>
+  <dimension ref="A1:U192"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="5.6640625" style="2" bestFit="1" customWidth="1"/>
@@ -1792,7 +1842,7 @@
     <col min="21" max="16384" width="10.83203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20">
+    <row r="1" spans="1:21">
       <c r="A1" s="3" t="s">
         <v>337</v>
       </c>
@@ -1821,10 +1871,10 @@
         <v>2</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="L1" s="3" t="s">
         <v>343</v>
@@ -1833,16 +1883,16 @@
         <v>338</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="R1" s="3" t="s">
         <v>344</v>
@@ -1853,8 +1903,11 @@
       <c r="T1" s="3" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="2" spans="1:20">
+      <c r="U1" s="5" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -1909,8 +1962,11 @@
       <c r="T2" s="1">
         <v>9400</v>
       </c>
-    </row>
-    <row r="3" spans="1:20">
+      <c r="U2" s="2" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -1965,8 +2021,11 @@
       <c r="T3" s="1">
         <v>1450</v>
       </c>
-    </row>
-    <row r="4" spans="1:20">
+      <c r="U3" s="2" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -2023,8 +2082,11 @@
       <c r="T4" s="1">
         <v>13100</v>
       </c>
-    </row>
-    <row r="5" spans="1:20">
+      <c r="U4" s="2" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -2081,8 +2143,11 @@
       <c r="T5" s="1">
         <v>1950</v>
       </c>
-    </row>
-    <row r="6" spans="1:20">
+      <c r="U5" s="2" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -2139,8 +2204,11 @@
       <c r="T6" s="1">
         <v>5962</v>
       </c>
-    </row>
-    <row r="7" spans="1:20">
+      <c r="U6" s="2" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -2195,8 +2263,11 @@
       <c r="T7" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:20">
+      <c r="U7" s="2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -2253,8 +2324,11 @@
       <c r="T8" s="1">
         <v>21706</v>
       </c>
-    </row>
-    <row r="9" spans="1:20">
+      <c r="U8" s="2" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -2309,13 +2383,16 @@
       <c r="T9" s="1">
         <v>3478.47</v>
       </c>
-    </row>
-    <row r="10" spans="1:20">
+      <c r="U9" s="2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21">
       <c r="A10" s="3">
         <v>9</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>396</v>
+      <c r="B10" s="4" t="s">
+        <v>440</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>4</v>
@@ -2367,8 +2444,11 @@
       <c r="T10" s="1">
         <v>23242</v>
       </c>
-    </row>
-    <row r="11" spans="1:20">
+      <c r="U10" s="2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -2425,8 +2505,11 @@
       <c r="T11" s="1">
         <v>17000</v>
       </c>
-    </row>
-    <row r="12" spans="1:20">
+      <c r="U11" s="2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21">
       <c r="A12" s="3">
         <v>11</v>
       </c>
@@ -2483,8 +2566,11 @@
       <c r="T12" s="1">
         <v>4929</v>
       </c>
-    </row>
-    <row r="13" spans="1:20">
+      <c r="U12" s="2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21">
       <c r="A13" s="3">
         <v>12</v>
       </c>
@@ -2541,8 +2627,11 @@
       <c r="T13" s="1">
         <v>8018</v>
       </c>
-    </row>
-    <row r="14" spans="1:20">
+      <c r="U13" s="2" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21">
       <c r="A14" s="3">
         <v>13</v>
       </c>
@@ -2599,8 +2688,11 @@
       <c r="T14" s="1">
         <v>6556</v>
       </c>
-    </row>
-    <row r="15" spans="1:20">
+      <c r="U14" s="2" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21">
       <c r="A15" s="3">
         <v>14</v>
       </c>
@@ -2657,8 +2749,11 @@
       <c r="T15" s="1">
         <v>12000</v>
       </c>
-    </row>
-    <row r="16" spans="1:20">
+      <c r="U15" s="2" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21">
       <c r="A16" s="3">
         <v>15</v>
       </c>
@@ -2715,8 +2810,11 @@
       <c r="T16" s="1">
         <v>17573.5</v>
       </c>
-    </row>
-    <row r="17" spans="1:20">
+      <c r="U16" s="2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21">
       <c r="A17" s="3">
         <v>16</v>
       </c>
@@ -2773,8 +2871,11 @@
       <c r="T17" s="1">
         <v>4608.3500000000004</v>
       </c>
-    </row>
-    <row r="18" spans="1:20">
+      <c r="U17" s="2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21">
       <c r="A18" s="3">
         <v>17</v>
       </c>
@@ -2831,8 +2932,11 @@
       <c r="T18" s="1">
         <v>7891</v>
       </c>
-    </row>
-    <row r="19" spans="1:20">
+      <c r="U18" s="2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21">
       <c r="A19" s="3">
         <v>18</v>
       </c>
@@ -2889,8 +2993,11 @@
       <c r="T19" s="1">
         <v>4617</v>
       </c>
-    </row>
-    <row r="20" spans="1:20">
+      <c r="U19" s="2" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21">
       <c r="A20" s="3">
         <v>19</v>
       </c>
@@ -2947,8 +3054,11 @@
       <c r="T20" s="1">
         <v>48600</v>
       </c>
-    </row>
-    <row r="21" spans="1:20">
+      <c r="U20" s="2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21">
       <c r="A21" s="3">
         <v>20</v>
       </c>
@@ -3005,8 +3115,11 @@
       <c r="T21" s="1">
         <v>10000</v>
       </c>
-    </row>
-    <row r="22" spans="1:20">
+      <c r="U21" s="2" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21">
       <c r="A22" s="3">
         <v>21</v>
       </c>
@@ -3061,8 +3174,11 @@
       <c r="T22" s="1">
         <v>1000</v>
       </c>
-    </row>
-    <row r="23" spans="1:20">
+      <c r="U22" s="2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21">
       <c r="A23" s="3">
         <v>22</v>
       </c>
@@ -3119,8 +3235,11 @@
       <c r="T23" s="1">
         <v>18122</v>
       </c>
-    </row>
-    <row r="24" spans="1:20">
+      <c r="U23" s="2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21">
       <c r="A24" s="3">
         <v>23</v>
       </c>
@@ -3177,13 +3296,16 @@
       <c r="T24" s="1">
         <v>11713</v>
       </c>
-    </row>
-    <row r="25" spans="1:20">
+      <c r="U24" s="2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21">
       <c r="A25" s="3">
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>4</v>
@@ -3235,8 +3357,11 @@
       <c r="T25" s="1">
         <v>11256</v>
       </c>
-    </row>
-    <row r="26" spans="1:20">
+      <c r="U25" s="2" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21">
       <c r="A26" s="3">
         <v>25</v>
       </c>
@@ -3293,8 +3418,11 @@
       <c r="T26" s="1">
         <v>15305</v>
       </c>
-    </row>
-    <row r="27" spans="1:20">
+      <c r="U26" s="2" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21">
       <c r="A27" s="3">
         <v>26</v>
       </c>
@@ -3351,8 +3479,11 @@
       <c r="T27" s="1">
         <v>20603</v>
       </c>
-    </row>
-    <row r="28" spans="1:20">
+      <c r="U27" s="2" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21">
       <c r="A28" s="3">
         <v>27</v>
       </c>
@@ -3409,8 +3540,11 @@
       <c r="T28" s="1">
         <v>4211</v>
       </c>
-    </row>
-    <row r="29" spans="1:20">
+      <c r="U28" s="2" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21">
       <c r="A29" s="3">
         <v>28</v>
       </c>
@@ -3467,13 +3601,16 @@
       <c r="T29" s="1">
         <v>11019.17</v>
       </c>
-    </row>
-    <row r="30" spans="1:20">
+      <c r="U29" s="2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21">
       <c r="A30" s="3">
         <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>4</v>
@@ -3525,8 +3662,11 @@
       <c r="T30" s="1">
         <v>18500</v>
       </c>
-    </row>
-    <row r="31" spans="1:20">
+      <c r="U30" s="2" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21">
       <c r="A31" s="3">
         <v>30</v>
       </c>
@@ -3581,8 +3721,11 @@
       <c r="T31" s="1">
         <v>5885.75</v>
       </c>
-    </row>
-    <row r="32" spans="1:20">
+      <c r="U31" s="2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21">
       <c r="A32" s="3">
         <v>31</v>
       </c>
@@ -3639,8 +3782,11 @@
       <c r="T32" s="1">
         <v>18000</v>
       </c>
-    </row>
-    <row r="33" spans="1:20">
+      <c r="U32" s="2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21">
       <c r="A33" s="3">
         <v>32</v>
       </c>
@@ -3695,8 +3841,11 @@
       <c r="T33" s="1">
         <v>20200</v>
       </c>
-    </row>
-    <row r="34" spans="1:20">
+      <c r="U33" s="2" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21">
       <c r="A34" s="3">
         <v>33</v>
       </c>
@@ -3751,8 +3900,11 @@
       <c r="T34" s="1">
         <v>52400</v>
       </c>
-    </row>
-    <row r="35" spans="1:20">
+      <c r="U34" s="2" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21">
       <c r="A35" s="3">
         <v>34</v>
       </c>
@@ -3809,8 +3961,11 @@
       <c r="T35" s="1">
         <v>21965</v>
       </c>
-    </row>
-    <row r="36" spans="1:20">
+      <c r="U35" s="2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21">
       <c r="A36" s="3">
         <v>35</v>
       </c>
@@ -3867,8 +4022,11 @@
       <c r="T36" s="1">
         <v>20356</v>
       </c>
-    </row>
-    <row r="37" spans="1:20">
+      <c r="U36" s="2" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21">
       <c r="A37" s="3">
         <v>36</v>
       </c>
@@ -3925,8 +4083,11 @@
       <c r="T37" s="1">
         <v>8300</v>
       </c>
-    </row>
-    <row r="38" spans="1:20">
+      <c r="U37" s="2" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21">
       <c r="A38" s="3">
         <v>37</v>
       </c>
@@ -3983,8 +4144,11 @@
       <c r="T38" s="1">
         <v>2700</v>
       </c>
-    </row>
-    <row r="39" spans="1:20">
+      <c r="U38" s="2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="39" spans="1:21">
       <c r="A39" s="3">
         <v>38</v>
       </c>
@@ -4041,13 +4205,16 @@
       <c r="T39" s="1">
         <v>3600</v>
       </c>
-    </row>
-    <row r="40" spans="1:20">
+      <c r="U39" s="2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="40" spans="1:21">
       <c r="A40" s="3">
         <v>39</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>4</v>
@@ -4097,8 +4264,11 @@
       <c r="T40" s="1">
         <v>18218</v>
       </c>
-    </row>
-    <row r="41" spans="1:20">
+      <c r="U40" s="2" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="41" spans="1:21">
       <c r="A41" s="3">
         <v>40</v>
       </c>
@@ -4155,8 +4325,11 @@
       <c r="T41" s="1">
         <v>9351.27</v>
       </c>
-    </row>
-    <row r="42" spans="1:20">
+      <c r="U41" s="2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="42" spans="1:21">
       <c r="A42" s="3">
         <v>41</v>
       </c>
@@ -4213,13 +4386,16 @@
       <c r="T42" s="1">
         <v>2400</v>
       </c>
-    </row>
-    <row r="43" spans="1:20">
+      <c r="U42" s="2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="43" spans="1:21">
       <c r="A43" s="3">
         <v>42</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>80</v>
@@ -4271,13 +4447,16 @@
       <c r="T43" s="1">
         <v>4355</v>
       </c>
-    </row>
-    <row r="44" spans="1:20">
+      <c r="U43" s="2" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="44" spans="1:21">
       <c r="A44" s="3">
         <v>43</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>80</v>
@@ -4327,8 +4506,11 @@
       <c r="T44" s="1">
         <v>11339</v>
       </c>
-    </row>
-    <row r="45" spans="1:20">
+      <c r="U44" s="2" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="45" spans="1:21">
       <c r="A45" s="3">
         <v>44</v>
       </c>
@@ -4385,8 +4567,11 @@
       <c r="T45" s="1">
         <v>10000</v>
       </c>
-    </row>
-    <row r="46" spans="1:20">
+      <c r="U45" s="2" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="46" spans="1:21">
       <c r="A46" s="3">
         <v>45</v>
       </c>
@@ -4443,8 +4628,11 @@
       <c r="T46" s="1">
         <v>7500</v>
       </c>
-    </row>
-    <row r="47" spans="1:20">
+      <c r="U46" s="2" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="47" spans="1:21">
       <c r="A47" s="3">
         <v>46</v>
       </c>
@@ -4501,8 +4689,11 @@
       <c r="T47" s="1">
         <v>1000</v>
       </c>
-    </row>
-    <row r="48" spans="1:20">
+      <c r="U47" s="2" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="48" spans="1:21">
       <c r="A48" s="3">
         <v>47</v>
       </c>
@@ -4559,8 +4750,11 @@
       <c r="T48" s="1">
         <v>16314.69</v>
       </c>
-    </row>
-    <row r="49" spans="1:20">
+      <c r="U48" s="2" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="49" spans="1:21">
       <c r="A49" s="3">
         <v>48</v>
       </c>
@@ -4615,8 +4809,11 @@
       <c r="T49" s="1">
         <v>6400</v>
       </c>
-    </row>
-    <row r="50" spans="1:20">
+      <c r="U49" s="2" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="50" spans="1:21">
       <c r="A50" s="3">
         <v>49</v>
       </c>
@@ -4673,8 +4870,11 @@
       <c r="T50" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="1:20">
+      <c r="U50" s="2" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="51" spans="1:21">
       <c r="A51" s="3">
         <v>50</v>
       </c>
@@ -4729,13 +4929,16 @@
       <c r="T51" s="1">
         <v>78130</v>
       </c>
-    </row>
-    <row r="52" spans="1:20">
+      <c r="U51" s="2" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="52" spans="1:21">
       <c r="A52" s="3">
         <v>51</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>80</v>
@@ -4785,8 +4988,11 @@
       <c r="T52" s="1">
         <v>14000</v>
       </c>
-    </row>
-    <row r="53" spans="1:20">
+      <c r="U52" s="2" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="53" spans="1:21">
       <c r="A53" s="3">
         <v>52</v>
       </c>
@@ -4843,8 +5049,11 @@
       <c r="T53" s="1">
         <v>6151.66</v>
       </c>
-    </row>
-    <row r="54" spans="1:20">
+      <c r="U53" s="2" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="54" spans="1:21">
       <c r="A54" s="3">
         <v>53</v>
       </c>
@@ -4899,8 +5108,11 @@
       <c r="T54" s="1">
         <v>20901</v>
       </c>
-    </row>
-    <row r="55" spans="1:20">
+      <c r="U54" s="2" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="55" spans="1:21">
       <c r="A55" s="3">
         <v>54</v>
       </c>
@@ -4957,13 +5169,16 @@
       <c r="T55" s="1">
         <v>12583</v>
       </c>
-    </row>
-    <row r="56" spans="1:20">
+      <c r="U55" s="2" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="56" spans="1:21">
       <c r="A56" s="3">
         <v>55</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>80</v>
@@ -5015,8 +5230,11 @@
       <c r="T56" s="1">
         <v>4021</v>
       </c>
-    </row>
-    <row r="57" spans="1:20">
+      <c r="U56" s="2" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="57" spans="1:21">
       <c r="A57" s="3">
         <v>56</v>
       </c>
@@ -5073,8 +5291,11 @@
       <c r="T57" s="1">
         <v>7270.57</v>
       </c>
-    </row>
-    <row r="58" spans="1:20">
+      <c r="U57" s="2" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="58" spans="1:21">
       <c r="A58" s="3">
         <v>57</v>
       </c>
@@ -5131,13 +5352,16 @@
       <c r="T58" s="1">
         <v>21243.3</v>
       </c>
-    </row>
-    <row r="59" spans="1:20">
+      <c r="U58" s="2" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="59" spans="1:21">
       <c r="A59" s="3">
         <v>58</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C59" s="3" t="s">
         <v>80</v>
@@ -5189,13 +5413,16 @@
       <c r="T59" s="1">
         <v>3734</v>
       </c>
-    </row>
-    <row r="60" spans="1:20">
+      <c r="U59" s="2" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="60" spans="1:21">
       <c r="A60" s="3">
         <v>59</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C60" s="3" t="s">
         <v>80</v>
@@ -5247,8 +5474,11 @@
       <c r="T60" s="1">
         <v>3019.89</v>
       </c>
-    </row>
-    <row r="61" spans="1:20">
+      <c r="U60" s="2" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="61" spans="1:21">
       <c r="A61" s="3">
         <v>60</v>
       </c>
@@ -5303,8 +5533,11 @@
       <c r="T61" s="1">
         <v>4208</v>
       </c>
-    </row>
-    <row r="62" spans="1:20">
+      <c r="U61" s="2" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="62" spans="1:21">
       <c r="A62" s="3">
         <v>61</v>
       </c>
@@ -5361,8 +5594,11 @@
       <c r="T62" s="1">
         <v>59000</v>
       </c>
-    </row>
-    <row r="63" spans="1:20">
+      <c r="U62" s="2" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="63" spans="1:21">
       <c r="A63" s="3">
         <v>62</v>
       </c>
@@ -5388,7 +5624,7 @@
         <v>60</v>
       </c>
       <c r="I63" s="4" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="J63" s="1"/>
       <c r="K63" s="1"/>
@@ -5419,8 +5655,11 @@
       <c r="T63" s="1">
         <v>4800</v>
       </c>
-    </row>
-    <row r="64" spans="1:20">
+      <c r="U63" s="2" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="64" spans="1:21">
       <c r="A64" s="3">
         <v>63</v>
       </c>
@@ -5477,8 +5716,11 @@
       <c r="T64" s="1">
         <v>10500</v>
       </c>
-    </row>
-    <row r="65" spans="1:20">
+      <c r="U64" s="2" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="65" spans="1:21">
       <c r="A65" s="3">
         <v>64</v>
       </c>
@@ -5533,8 +5775,11 @@
       <c r="T65" s="1">
         <v>7586</v>
       </c>
-    </row>
-    <row r="66" spans="1:20">
+      <c r="U65" s="2" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="66" spans="1:21">
       <c r="A66" s="3">
         <v>65</v>
       </c>
@@ -5589,8 +5834,11 @@
       <c r="T66" s="1">
         <v>4300</v>
       </c>
-    </row>
-    <row r="67" spans="1:20">
+      <c r="U66" s="2" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="67" spans="1:21">
       <c r="A67" s="3">
         <v>66</v>
       </c>
@@ -5647,8 +5895,11 @@
       <c r="T67" s="1">
         <v>17418</v>
       </c>
-    </row>
-    <row r="68" spans="1:20">
+      <c r="U67" s="2" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="68" spans="1:21">
       <c r="A68" s="3">
         <v>67</v>
       </c>
@@ -5705,8 +5956,11 @@
       <c r="T68" s="1">
         <v>3600</v>
       </c>
-    </row>
-    <row r="69" spans="1:20">
+      <c r="U68" s="2" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="69" spans="1:21">
       <c r="A69" s="3">
         <v>68</v>
       </c>
@@ -5761,8 +6015,11 @@
       <c r="T69" s="1">
         <v>3749</v>
       </c>
-    </row>
-    <row r="70" spans="1:20">
+      <c r="U69" s="2" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="70" spans="1:21">
       <c r="A70" s="3">
         <v>69</v>
       </c>
@@ -5817,8 +6074,11 @@
       <c r="T70" s="1">
         <v>2500</v>
       </c>
-    </row>
-    <row r="71" spans="1:20">
+      <c r="U70" s="2" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="71" spans="1:21">
       <c r="A71" s="3">
         <v>70</v>
       </c>
@@ -5873,13 +6133,16 @@
       <c r="T71" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="1:20">
+      <c r="U71" s="2" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="72" spans="1:21">
       <c r="A72" s="3">
         <v>71</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C72" s="3" t="s">
         <v>113</v>
@@ -5929,8 +6192,11 @@
       <c r="T72" s="1">
         <v>5000</v>
       </c>
-    </row>
-    <row r="73" spans="1:20">
+      <c r="U72" s="2" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="73" spans="1:21">
       <c r="A73" s="3">
         <v>72</v>
       </c>
@@ -5987,8 +6253,11 @@
       <c r="T73" s="1">
         <v>8881</v>
       </c>
-    </row>
-    <row r="74" spans="1:20">
+      <c r="U73" s="2" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="74" spans="1:21">
       <c r="A74" s="3">
         <v>73</v>
       </c>
@@ -6045,8 +6314,11 @@
       <c r="T74" s="1">
         <v>13000</v>
       </c>
-    </row>
-    <row r="75" spans="1:20">
+      <c r="U74" s="2" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="75" spans="1:21">
       <c r="A75" s="3">
         <v>74</v>
       </c>
@@ -6101,8 +6373,11 @@
       <c r="T75" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="1:20">
+      <c r="U75" s="2" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="76" spans="1:21">
       <c r="A76" s="3">
         <v>75</v>
       </c>
@@ -6159,8 +6434,11 @@
       <c r="T76" s="1">
         <v>3157</v>
       </c>
-    </row>
-    <row r="77" spans="1:20">
+      <c r="U76" s="2" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="77" spans="1:21">
       <c r="A77" s="3">
         <v>76</v>
       </c>
@@ -6217,8 +6495,11 @@
       <c r="T77" s="1">
         <v>9537</v>
       </c>
-    </row>
-    <row r="78" spans="1:20">
+      <c r="U77" s="2" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="78" spans="1:21">
       <c r="A78" s="3">
         <v>77</v>
       </c>
@@ -6275,8 +6556,11 @@
       <c r="T78" s="1">
         <v>3400</v>
       </c>
-    </row>
-    <row r="79" spans="1:20">
+      <c r="U78" s="2" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="79" spans="1:21">
       <c r="A79" s="3">
         <v>78</v>
       </c>
@@ -6331,8 +6615,11 @@
       <c r="T79" s="1">
         <v>8574</v>
       </c>
-    </row>
-    <row r="80" spans="1:20">
+      <c r="U79" s="2" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="80" spans="1:21">
       <c r="A80" s="3">
         <v>79</v>
       </c>
@@ -6387,8 +6674,11 @@
       <c r="T80" s="1">
         <v>7150</v>
       </c>
-    </row>
-    <row r="81" spans="1:20">
+      <c r="U80" s="2" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="81" spans="1:21">
       <c r="A81" s="3">
         <v>80</v>
       </c>
@@ -6445,8 +6735,11 @@
       <c r="T81" s="1">
         <v>19235</v>
       </c>
-    </row>
-    <row r="82" spans="1:20">
+      <c r="U81" s="2" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="82" spans="1:21">
       <c r="A82" s="3">
         <v>81</v>
       </c>
@@ -6503,8 +6796,11 @@
       <c r="T82" s="1">
         <v>7500</v>
       </c>
-    </row>
-    <row r="83" spans="1:20">
+      <c r="U82" s="2" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="83" spans="1:21">
       <c r="A83" s="3">
         <v>82</v>
       </c>
@@ -6561,8 +6857,11 @@
       <c r="T83" s="1">
         <v>10000</v>
       </c>
-    </row>
-    <row r="84" spans="1:20">
+      <c r="U83" s="2" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="84" spans="1:21">
       <c r="A84" s="3">
         <v>83</v>
       </c>
@@ -6619,8 +6918,11 @@
       <c r="T84" s="1">
         <v>22971</v>
       </c>
-    </row>
-    <row r="85" spans="1:20">
+      <c r="U84" s="2" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="85" spans="1:21">
       <c r="A85" s="3">
         <v>84</v>
       </c>
@@ -6675,8 +6977,11 @@
       <c r="T85" s="1">
         <v>3800</v>
       </c>
-    </row>
-    <row r="86" spans="1:20">
+      <c r="U85" s="2" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="86" spans="1:21">
       <c r="A86" s="3">
         <v>85</v>
       </c>
@@ -6733,8 +7038,11 @@
       <c r="T86" s="1">
         <v>8139</v>
       </c>
-    </row>
-    <row r="87" spans="1:20">
+      <c r="U86" s="2" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="87" spans="1:21">
       <c r="A87" s="3">
         <v>86</v>
       </c>
@@ -6789,13 +7097,16 @@
       <c r="T87" s="1">
         <v>4700</v>
       </c>
-    </row>
-    <row r="88" spans="1:20">
+      <c r="U87" s="2" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="88" spans="1:21">
       <c r="A88" s="3">
         <v>87</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C88" s="3" t="s">
         <v>97</v>
@@ -6847,8 +7158,11 @@
       <c r="T88" s="1">
         <v>6300</v>
       </c>
-    </row>
-    <row r="89" spans="1:20">
+      <c r="U88" s="2" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="89" spans="1:21">
       <c r="A89" s="3">
         <v>88</v>
       </c>
@@ -6903,8 +7217,11 @@
       <c r="T89" s="1">
         <v>36930</v>
       </c>
-    </row>
-    <row r="90" spans="1:20">
+      <c r="U89" s="2" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="90" spans="1:21">
       <c r="A90" s="3">
         <v>89</v>
       </c>
@@ -6959,8 +7276,11 @@
       <c r="T90" s="1">
         <v>11123.6</v>
       </c>
-    </row>
-    <row r="91" spans="1:20">
+      <c r="U90" s="2" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="91" spans="1:21">
       <c r="A91" s="3">
         <v>90</v>
       </c>
@@ -7015,8 +7335,11 @@
       <c r="T91" s="1">
         <v>1898</v>
       </c>
-    </row>
-    <row r="92" spans="1:20">
+      <c r="U91" s="2" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="92" spans="1:21">
       <c r="A92" s="3">
         <v>91</v>
       </c>
@@ -7073,8 +7396,11 @@
       <c r="T92" s="1">
         <v>20000</v>
       </c>
-    </row>
-    <row r="93" spans="1:20">
+      <c r="U92" s="2" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="93" spans="1:21">
       <c r="A93" s="3">
         <v>92</v>
       </c>
@@ -7131,13 +7457,16 @@
       <c r="T93" s="1">
         <v>34000</v>
       </c>
-    </row>
-    <row r="94" spans="1:20">
+      <c r="U93" s="2" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="94" spans="1:21">
       <c r="A94" s="3">
         <v>93</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C94" s="3" t="s">
         <v>97</v>
@@ -7189,8 +7518,11 @@
       <c r="T94" s="1">
         <v>11981</v>
       </c>
-    </row>
-    <row r="95" spans="1:20">
+      <c r="U94" s="2" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="95" spans="1:21">
       <c r="A95" s="3">
         <v>94</v>
       </c>
@@ -7247,13 +7579,16 @@
       <c r="T95" s="1">
         <v>12000</v>
       </c>
-    </row>
-    <row r="96" spans="1:20">
+      <c r="U95" s="2" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="96" spans="1:21">
       <c r="A96" s="3">
         <v>95</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C96" s="3" t="s">
         <v>97</v>
@@ -7303,8 +7638,11 @@
       <c r="T96" s="1">
         <v>5000</v>
       </c>
-    </row>
-    <row r="97" spans="1:20">
+      <c r="U96" s="2" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="97" spans="1:21">
       <c r="A97" s="3">
         <v>96</v>
       </c>
@@ -7359,13 +7697,16 @@
       <c r="T97" s="1">
         <v>40000</v>
       </c>
-    </row>
-    <row r="98" spans="1:20">
+      <c r="U97" s="2" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="98" spans="1:21">
       <c r="A98" s="3">
         <v>97</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C98" s="3" t="s">
         <v>97</v>
@@ -7417,8 +7758,11 @@
       <c r="T98" s="1">
         <v>31248</v>
       </c>
-    </row>
-    <row r="99" spans="1:20">
+      <c r="U98" s="2" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="99" spans="1:21">
       <c r="A99" s="3">
         <v>98</v>
       </c>
@@ -7475,8 +7819,11 @@
       <c r="T99" s="1">
         <v>11955</v>
       </c>
-    </row>
-    <row r="100" spans="1:20">
+      <c r="U99" s="2" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="100" spans="1:21">
       <c r="A100" s="3">
         <v>99</v>
       </c>
@@ -7533,8 +7880,11 @@
       <c r="T100" s="1">
         <v>11718</v>
       </c>
-    </row>
-    <row r="101" spans="1:20">
+      <c r="U100" s="2" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="101" spans="1:21">
       <c r="A101" s="3">
         <v>100</v>
       </c>
@@ -7591,8 +7941,11 @@
       <c r="T101" s="1">
         <v>14206</v>
       </c>
-    </row>
-    <row r="102" spans="1:20">
+      <c r="U101" s="2" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="102" spans="1:21">
       <c r="A102" s="3">
         <v>101</v>
       </c>
@@ -7647,8 +8000,11 @@
       <c r="T102" s="1">
         <v>7003</v>
       </c>
-    </row>
-    <row r="103" spans="1:20">
+      <c r="U102" s="2" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="103" spans="1:21">
       <c r="A103" s="3">
         <v>102</v>
       </c>
@@ -7703,8 +8059,11 @@
       <c r="T103" s="1">
         <v>5862</v>
       </c>
-    </row>
-    <row r="104" spans="1:20">
+      <c r="U103" s="2" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="104" spans="1:21">
       <c r="A104" s="3">
         <v>103</v>
       </c>
@@ -7759,8 +8118,11 @@
       <c r="T104" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="105" spans="1:20">
+      <c r="U104" s="2" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="105" spans="1:21">
       <c r="A105" s="3">
         <v>104</v>
       </c>
@@ -7815,13 +8177,16 @@
       <c r="T105" s="1">
         <v>120.9</v>
       </c>
-    </row>
-    <row r="106" spans="1:20">
+      <c r="U105" s="2" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="106" spans="1:21">
       <c r="A106" s="3">
         <v>105</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C106" s="3" t="s">
         <v>169</v>
@@ -7871,8 +8236,11 @@
       <c r="T106" s="1">
         <v>23200</v>
       </c>
-    </row>
-    <row r="107" spans="1:20">
+      <c r="U106" s="2" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="107" spans="1:21">
       <c r="A107" s="3">
         <v>106</v>
       </c>
@@ -7929,8 +8297,11 @@
       <c r="T107" s="1">
         <v>1500</v>
       </c>
-    </row>
-    <row r="108" spans="1:20">
+      <c r="U107" s="2" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="108" spans="1:21">
       <c r="A108" s="3">
         <v>107</v>
       </c>
@@ -7985,8 +8356,11 @@
       <c r="T108" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="109" spans="1:20">
+      <c r="U108" s="2" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="109" spans="1:21">
       <c r="A109" s="3">
         <v>108</v>
       </c>
@@ -8041,8 +8415,11 @@
       <c r="T109" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="110" spans="1:20">
+      <c r="U109" s="2" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="110" spans="1:21">
       <c r="A110" s="3">
         <v>109</v>
       </c>
@@ -8097,8 +8474,11 @@
       <c r="T110" s="1">
         <v>15830</v>
       </c>
-    </row>
-    <row r="111" spans="1:20">
+      <c r="U110" s="2" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="111" spans="1:21">
       <c r="A111" s="3">
         <v>110</v>
       </c>
@@ -8153,8 +8533,11 @@
       <c r="T111" s="1">
         <v>19941.5</v>
       </c>
-    </row>
-    <row r="112" spans="1:20">
+      <c r="U111" s="2" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="112" spans="1:21">
       <c r="A112" s="3">
         <v>111</v>
       </c>
@@ -8211,13 +8594,16 @@
       <c r="T112" s="1">
         <v>1000</v>
       </c>
-    </row>
-    <row r="113" spans="1:20">
+      <c r="U112" s="2" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="113" spans="1:21">
       <c r="A113" s="3">
         <v>112</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C113" s="3" t="s">
         <v>169</v>
@@ -8269,13 +8655,16 @@
       <c r="T113" s="1">
         <v>427</v>
       </c>
-    </row>
-    <row r="114" spans="1:20">
+      <c r="U113" s="2" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="114" spans="1:21">
       <c r="A114" s="3">
         <v>113</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C114" s="3" t="s">
         <v>169</v>
@@ -8327,13 +8716,16 @@
       <c r="T114" s="1">
         <v>11500</v>
       </c>
-    </row>
-    <row r="115" spans="1:20">
+      <c r="U114" s="2" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="115" spans="1:21">
       <c r="A115" s="3">
         <v>114</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C115" s="3" t="s">
         <v>169</v>
@@ -8383,8 +8775,11 @@
       <c r="T115" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="116" spans="1:20">
+      <c r="U115" s="2" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="116" spans="1:21">
       <c r="A116" s="3">
         <v>115</v>
       </c>
@@ -8439,8 +8834,11 @@
       <c r="T116" s="1">
         <v>21000</v>
       </c>
-    </row>
-    <row r="117" spans="1:20">
+      <c r="U116" s="2" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="117" spans="1:21">
       <c r="A117" s="3">
         <v>116</v>
       </c>
@@ -8495,8 +8893,11 @@
       <c r="T117" s="1">
         <v>31890</v>
       </c>
-    </row>
-    <row r="118" spans="1:20">
+      <c r="U117" s="2" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="118" spans="1:21">
       <c r="A118" s="3">
         <v>117</v>
       </c>
@@ -8551,8 +8952,11 @@
       <c r="T118" s="1">
         <v>1116</v>
       </c>
-    </row>
-    <row r="119" spans="1:20">
+      <c r="U118" s="2" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="119" spans="1:21">
       <c r="A119" s="3">
         <v>118</v>
       </c>
@@ -8607,8 +9011,11 @@
       <c r="T119" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="120" spans="1:20">
+      <c r="U119" s="2" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="120" spans="1:21">
       <c r="A120" s="3">
         <v>119</v>
       </c>
@@ -8665,8 +9072,11 @@
       <c r="T120" s="1">
         <v>5600</v>
       </c>
-    </row>
-    <row r="121" spans="1:20">
+      <c r="U120" s="2" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="121" spans="1:21">
       <c r="A121" s="3">
         <v>120</v>
       </c>
@@ -8723,13 +9133,16 @@
       <c r="T121" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="122" spans="1:20">
+      <c r="U121" s="2" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="122" spans="1:21">
       <c r="A122" s="3">
         <v>121</v>
       </c>
-      <c r="B122" s="3" t="s">
-        <v>415</v>
+      <c r="B122" s="4" t="s">
+        <v>441</v>
       </c>
       <c r="C122" s="3" t="s">
         <v>169</v>
@@ -8781,8 +9194,11 @@
       <c r="T122" s="1">
         <v>36000</v>
       </c>
-    </row>
-    <row r="123" spans="1:20">
+      <c r="U122" s="2" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="123" spans="1:21">
       <c r="A123" s="3">
         <v>122</v>
       </c>
@@ -8833,13 +9249,16 @@
       <c r="T123" s="1">
         <v>97326.47</v>
       </c>
-    </row>
-    <row r="124" spans="1:20">
+      <c r="U123" s="2" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="124" spans="1:21">
       <c r="A124" s="3">
         <v>123</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C124" s="3" t="s">
         <v>207</v>
@@ -8891,8 +9310,11 @@
       <c r="T124" s="1">
         <v>15956.21</v>
       </c>
-    </row>
-    <row r="125" spans="1:20">
+      <c r="U124" s="2" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="125" spans="1:21">
       <c r="A125" s="3">
         <v>124</v>
       </c>
@@ -8949,8 +9371,11 @@
       <c r="T125" s="1">
         <v>6631</v>
       </c>
-    </row>
-    <row r="126" spans="1:20">
+      <c r="U125" s="2" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="126" spans="1:21">
       <c r="A126" s="3">
         <v>125</v>
       </c>
@@ -9005,8 +9430,11 @@
       <c r="T126" s="1">
         <v>14329.850000000002</v>
       </c>
-    </row>
-    <row r="127" spans="1:20">
+      <c r="U126" s="2" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="127" spans="1:21">
       <c r="A127" s="3">
         <v>126</v>
       </c>
@@ -9063,8 +9491,11 @@
       <c r="T127" s="1">
         <v>6594</v>
       </c>
-    </row>
-    <row r="128" spans="1:20">
+      <c r="U127" s="2" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="128" spans="1:21">
       <c r="A128" s="3">
         <v>127</v>
       </c>
@@ -9121,13 +9552,16 @@
       <c r="T128" s="1">
         <v>10000</v>
       </c>
-    </row>
-    <row r="129" spans="1:20">
+      <c r="U128" s="2" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="129" spans="1:21">
       <c r="A129" s="3">
         <v>128</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C129" s="3" t="s">
         <v>207</v>
@@ -9179,8 +9613,11 @@
       <c r="T129" s="1">
         <v>35707.82</v>
       </c>
-    </row>
-    <row r="130" spans="1:20">
+      <c r="U129" s="2" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="130" spans="1:21">
       <c r="A130" s="3">
         <v>129</v>
       </c>
@@ -9237,8 +9674,11 @@
       <c r="T130" s="1">
         <v>4100</v>
       </c>
-    </row>
-    <row r="131" spans="1:20">
+      <c r="U130" s="2" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="131" spans="1:21">
       <c r="A131" s="3">
         <v>130</v>
       </c>
@@ -9295,13 +9735,16 @@
       <c r="T131" s="1">
         <v>19710</v>
       </c>
-    </row>
-    <row r="132" spans="1:20">
+      <c r="U131" s="2" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="132" spans="1:21">
       <c r="A132" s="3">
         <v>131</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C132" s="3" t="s">
         <v>207</v>
@@ -9353,8 +9796,11 @@
       <c r="T132" s="1">
         <v>11436.280000000002</v>
       </c>
-    </row>
-    <row r="133" spans="1:20">
+      <c r="U132" s="2" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="133" spans="1:21">
       <c r="A133" s="3">
         <v>132</v>
       </c>
@@ -9411,8 +9857,11 @@
       <c r="T133" s="1">
         <v>5860.63</v>
       </c>
-    </row>
-    <row r="134" spans="1:20">
+      <c r="U133" s="2" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="134" spans="1:21">
       <c r="A134" s="3">
         <v>133</v>
       </c>
@@ -9469,13 +9918,16 @@
       <c r="T134" s="1">
         <v>6669.369999999999</v>
       </c>
-    </row>
-    <row r="135" spans="1:20">
+      <c r="U134" s="2" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="135" spans="1:21">
       <c r="A135" s="3">
         <v>134</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C135" s="3" t="s">
         <v>207</v>
@@ -9527,13 +9979,16 @@
       <c r="T135" s="1">
         <v>32274.100000000002</v>
       </c>
-    </row>
-    <row r="136" spans="1:20">
+      <c r="U135" s="2" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="136" spans="1:21">
       <c r="A136" s="3">
         <v>135</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C136" s="3" t="s">
         <v>207</v>
@@ -9585,8 +10040,11 @@
       <c r="T136" s="1">
         <v>1901</v>
       </c>
-    </row>
-    <row r="137" spans="1:20">
+      <c r="U136" s="2" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="137" spans="1:21">
       <c r="A137" s="3">
         <v>136</v>
       </c>
@@ -9641,8 +10099,11 @@
       <c r="T137" s="1">
         <v>6126</v>
       </c>
-    </row>
-    <row r="138" spans="1:20">
+      <c r="U137" s="2" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="138" spans="1:21">
       <c r="A138" s="3">
         <v>137</v>
       </c>
@@ -9699,8 +10160,11 @@
       <c r="T138" s="1">
         <v>2182</v>
       </c>
-    </row>
-    <row r="139" spans="1:20">
+      <c r="U138" s="2" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="139" spans="1:21">
       <c r="A139" s="3">
         <v>138</v>
       </c>
@@ -9755,8 +10219,11 @@
       <c r="T139" s="1">
         <v>4616</v>
       </c>
-    </row>
-    <row r="140" spans="1:20">
+      <c r="U139" s="2" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="140" spans="1:21">
       <c r="A140" s="3">
         <v>139</v>
       </c>
@@ -9811,8 +10278,11 @@
       <c r="T140" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="141" spans="1:20">
+      <c r="U140" s="2" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="141" spans="1:21">
       <c r="A141" s="3">
         <v>140</v>
       </c>
@@ -9867,8 +10337,11 @@
       <c r="T141" s="1">
         <v>18000</v>
       </c>
-    </row>
-    <row r="142" spans="1:20">
+      <c r="U141" s="2" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="142" spans="1:21">
       <c r="A142" s="3">
         <v>141</v>
       </c>
@@ -9923,8 +10396,11 @@
       <c r="T142" s="1">
         <v>23660</v>
       </c>
-    </row>
-    <row r="143" spans="1:20">
+      <c r="U142" s="2" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="143" spans="1:21">
       <c r="A143" s="3">
         <v>142</v>
       </c>
@@ -9979,13 +10455,16 @@
       <c r="T143" s="1">
         <v>7276</v>
       </c>
-    </row>
-    <row r="144" spans="1:20">
+      <c r="U143" s="2" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="144" spans="1:21">
       <c r="A144" s="3">
         <v>143</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C144" s="3" t="s">
         <v>230</v>
@@ -10037,13 +10516,16 @@
       <c r="T144" s="1">
         <v>78750</v>
       </c>
-    </row>
-    <row r="145" spans="1:20">
+      <c r="U144" s="2" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="145" spans="1:21">
       <c r="A145" s="3">
         <v>144</v>
       </c>
-      <c r="B145" s="3" t="s">
-        <v>422</v>
+      <c r="B145" s="4" t="s">
+        <v>442</v>
       </c>
       <c r="C145" s="3" t="s">
         <v>230</v>
@@ -10095,13 +10577,16 @@
       <c r="T145" s="1">
         <v>40000</v>
       </c>
-    </row>
-    <row r="146" spans="1:20">
+      <c r="U145" s="2" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="146" spans="1:21">
       <c r="A146" s="3">
         <v>145</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="C146" s="3" t="s">
         <v>230</v>
@@ -10151,8 +10636,11 @@
       <c r="T146" s="1">
         <v>1300</v>
       </c>
-    </row>
-    <row r="147" spans="1:20">
+      <c r="U146" s="2" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="147" spans="1:21">
       <c r="A147" s="3">
         <v>146</v>
       </c>
@@ -10209,13 +10697,16 @@
       <c r="T147" s="1">
         <v>12000</v>
       </c>
-    </row>
-    <row r="148" spans="1:20">
+      <c r="U147" s="2" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="148" spans="1:21">
       <c r="A148" s="3">
         <v>147</v>
       </c>
-      <c r="B148" s="3" t="s">
-        <v>424</v>
+      <c r="B148" s="4" t="s">
+        <v>443</v>
       </c>
       <c r="C148" s="3" t="s">
         <v>230</v>
@@ -10267,8 +10758,11 @@
       <c r="T148" s="1">
         <v>31153</v>
       </c>
-    </row>
-    <row r="149" spans="1:20">
+      <c r="U148" s="2" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="149" spans="1:21">
       <c r="A149" s="3">
         <v>148</v>
       </c>
@@ -10325,8 +10819,11 @@
       <c r="T149" s="1">
         <v>490</v>
       </c>
-    </row>
-    <row r="150" spans="1:20">
+      <c r="U149" s="2" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="150" spans="1:21">
       <c r="A150" s="3">
         <v>149</v>
       </c>
@@ -10383,8 +10880,11 @@
       <c r="T150" s="1">
         <v>9233</v>
       </c>
-    </row>
-    <row r="151" spans="1:20">
+      <c r="U150" s="2" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="151" spans="1:21">
       <c r="A151" s="3">
         <v>150</v>
       </c>
@@ -10441,8 +10941,11 @@
       <c r="T151" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="152" spans="1:20">
+      <c r="U151" s="2" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="152" spans="1:21">
       <c r="A152" s="3">
         <v>151</v>
       </c>
@@ -10497,8 +11000,11 @@
       <c r="T152" s="1">
         <v>4600</v>
       </c>
-    </row>
-    <row r="153" spans="1:20">
+      <c r="U152" s="2" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="153" spans="1:21">
       <c r="A153" s="3">
         <v>152</v>
       </c>
@@ -10555,8 +11061,11 @@
       <c r="T153" s="1">
         <v>32300</v>
       </c>
-    </row>
-    <row r="154" spans="1:20">
+      <c r="U153" s="2" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="154" spans="1:21">
       <c r="A154" s="3">
         <v>153</v>
       </c>
@@ -10613,8 +11122,11 @@
       <c r="T154" s="1">
         <v>18531</v>
       </c>
-    </row>
-    <row r="155" spans="1:20">
+      <c r="U154" s="2" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="155" spans="1:21">
       <c r="A155" s="3">
         <v>154</v>
       </c>
@@ -10671,8 +11183,11 @@
       <c r="T155" s="1">
         <v>31700</v>
       </c>
-    </row>
-    <row r="156" spans="1:20">
+      <c r="U155" s="2" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="156" spans="1:21">
       <c r="A156" s="3">
         <v>155</v>
       </c>
@@ -10729,8 +11244,11 @@
       <c r="T156" s="1">
         <v>4092</v>
       </c>
-    </row>
-    <row r="157" spans="1:20">
+      <c r="U156" s="2" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="157" spans="1:21">
       <c r="A157" s="3">
         <v>156</v>
       </c>
@@ -10787,8 +11305,11 @@
       <c r="T157" s="1">
         <v>15371</v>
       </c>
-    </row>
-    <row r="158" spans="1:20">
+      <c r="U157" s="2" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="158" spans="1:21">
       <c r="A158" s="3">
         <v>157</v>
       </c>
@@ -10843,8 +11364,11 @@
       <c r="T158" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="159" spans="1:20">
+      <c r="U158" s="2" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="159" spans="1:21">
       <c r="A159" s="3">
         <v>158</v>
       </c>
@@ -10901,8 +11425,11 @@
       <c r="T159" s="1">
         <v>4279</v>
       </c>
-    </row>
-    <row r="160" spans="1:20">
+      <c r="U159" s="2" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="160" spans="1:21">
       <c r="A160" s="3">
         <v>159</v>
       </c>
@@ -10959,8 +11486,11 @@
       <c r="T160" s="1">
         <v>30000</v>
       </c>
-    </row>
-    <row r="161" spans="1:20">
+      <c r="U160" s="2" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="161" spans="1:21">
       <c r="A161" s="3">
         <v>160</v>
       </c>
@@ -11017,8 +11547,11 @@
       <c r="T161" s="1">
         <v>19440</v>
       </c>
-    </row>
-    <row r="162" spans="1:20">
+      <c r="U161" s="2" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="162" spans="1:21">
       <c r="A162" s="3">
         <v>161</v>
       </c>
@@ -11075,8 +11608,11 @@
       <c r="T162" s="1">
         <v>10166</v>
       </c>
-    </row>
-    <row r="163" spans="1:20">
+      <c r="U162" s="2" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="163" spans="1:21">
       <c r="A163" s="3">
         <v>162</v>
       </c>
@@ -11133,13 +11669,16 @@
       <c r="T163" s="1">
         <v>9014</v>
       </c>
-    </row>
-    <row r="164" spans="1:20">
+      <c r="U163" s="2" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="164" spans="1:21">
       <c r="A164" s="3">
         <v>163</v>
       </c>
-      <c r="B164" s="3" t="s">
-        <v>425</v>
+      <c r="B164" s="4" t="s">
+        <v>444</v>
       </c>
       <c r="C164" s="3" t="s">
         <v>257</v>
@@ -11191,8 +11730,11 @@
       <c r="T164" s="1">
         <v>50100</v>
       </c>
-    </row>
-    <row r="165" spans="1:20">
+      <c r="U164" s="2" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="165" spans="1:21">
       <c r="A165" s="3">
         <v>164</v>
       </c>
@@ -11243,8 +11785,11 @@
       <c r="T165" s="1">
         <v>51204</v>
       </c>
-    </row>
-    <row r="166" spans="1:20">
+      <c r="U165" s="2" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="166" spans="1:21">
       <c r="A166" s="3">
         <v>165</v>
       </c>
@@ -11301,8 +11846,11 @@
       <c r="T166" s="1">
         <v>8589</v>
       </c>
-    </row>
-    <row r="167" spans="1:20">
+      <c r="U166" s="2" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="167" spans="1:21">
       <c r="A167" s="3">
         <v>166</v>
       </c>
@@ -11357,8 +11905,11 @@
       <c r="T167" s="1">
         <v>8967</v>
       </c>
-    </row>
-    <row r="168" spans="1:20">
+      <c r="U167" s="2" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="168" spans="1:21">
       <c r="A168" s="3">
         <v>167</v>
       </c>
@@ -11415,8 +11966,11 @@
       <c r="T168" s="1">
         <v>3493</v>
       </c>
-    </row>
-    <row r="169" spans="1:20">
+      <c r="U168" s="2" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="169" spans="1:21">
       <c r="A169" s="3">
         <v>168</v>
       </c>
@@ -11473,8 +12027,11 @@
       <c r="T169" s="1">
         <v>17000</v>
       </c>
-    </row>
-    <row r="170" spans="1:20">
+      <c r="U169" s="2" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="170" spans="1:21">
       <c r="A170" s="3">
         <v>169</v>
       </c>
@@ -11529,8 +12086,11 @@
       <c r="T170" s="1">
         <v>1330</v>
       </c>
-    </row>
-    <row r="171" spans="1:20">
+      <c r="U170" s="2" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="171" spans="1:21">
       <c r="A171" s="3">
         <v>170</v>
       </c>
@@ -11585,8 +12145,11 @@
       <c r="T171" s="1">
         <v>18039</v>
       </c>
-    </row>
-    <row r="172" spans="1:20">
+      <c r="U171" s="2" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="172" spans="1:21">
       <c r="A172" s="3">
         <v>171</v>
       </c>
@@ -11643,8 +12206,11 @@
       <c r="T172" s="1">
         <v>10527</v>
       </c>
-    </row>
-    <row r="173" spans="1:20">
+      <c r="U172" s="2" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="173" spans="1:21">
       <c r="A173" s="3">
         <v>172</v>
       </c>
@@ -11701,8 +12267,11 @@
       <c r="T173" s="1">
         <v>2350</v>
       </c>
-    </row>
-    <row r="174" spans="1:20">
+      <c r="U173" s="2" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="174" spans="1:21">
       <c r="A174" s="3">
         <v>173</v>
       </c>
@@ -11759,8 +12328,11 @@
       <c r="T174" s="1">
         <v>3480</v>
       </c>
-    </row>
-    <row r="175" spans="1:20">
+      <c r="U174" s="2" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="175" spans="1:21">
       <c r="A175" s="3">
         <v>174</v>
       </c>
@@ -11817,8 +12389,11 @@
       <c r="T175" s="1">
         <v>29000</v>
       </c>
-    </row>
-    <row r="176" spans="1:20">
+      <c r="U175" s="2" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="176" spans="1:21">
       <c r="A176" s="3">
         <v>175</v>
       </c>
@@ -11875,8 +12450,11 @@
       <c r="T176" s="1">
         <v>35016</v>
       </c>
-    </row>
-    <row r="177" spans="1:20">
+      <c r="U176" s="2" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="177" spans="1:21">
       <c r="A177" s="3">
         <v>176</v>
       </c>
@@ -11931,8 +12509,11 @@
       <c r="T177" s="1">
         <v>8416</v>
       </c>
-    </row>
-    <row r="178" spans="1:20">
+      <c r="U177" s="2" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="178" spans="1:21">
       <c r="A178" s="3">
         <v>177</v>
       </c>
@@ -11989,8 +12570,11 @@
       <c r="T178" s="1">
         <v>14000</v>
       </c>
-    </row>
-    <row r="179" spans="1:20">
+      <c r="U178" s="2" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="179" spans="1:21">
       <c r="A179" s="3">
         <v>178</v>
       </c>
@@ -12045,8 +12629,11 @@
       <c r="T179" s="1">
         <v>22912</v>
       </c>
-    </row>
-    <row r="180" spans="1:20">
+      <c r="U179" s="2" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="180" spans="1:21">
       <c r="A180" s="3">
         <v>179</v>
       </c>
@@ -12101,8 +12688,11 @@
       <c r="T180" s="1">
         <v>15800</v>
       </c>
-    </row>
-    <row r="181" spans="1:20">
+      <c r="U180" s="2" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="181" spans="1:21">
       <c r="A181" s="3">
         <v>180</v>
       </c>
@@ -12159,8 +12749,11 @@
       <c r="T181" s="1">
         <v>28050</v>
       </c>
-    </row>
-    <row r="182" spans="1:20">
+      <c r="U181" s="2" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="182" spans="1:21">
       <c r="A182" s="3">
         <v>181</v>
       </c>
@@ -12217,8 +12810,11 @@
       <c r="T182" s="1">
         <v>7200</v>
       </c>
-    </row>
-    <row r="183" spans="1:20">
+      <c r="U182" s="2" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="183" spans="1:21">
       <c r="A183" s="3">
         <v>182</v>
       </c>
@@ -12273,8 +12869,11 @@
       <c r="T183" s="1">
         <v>22000</v>
       </c>
-    </row>
-    <row r="184" spans="1:20">
+      <c r="U183" s="2" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="184" spans="1:21">
       <c r="A184" s="3">
         <v>183</v>
       </c>
@@ -12331,8 +12930,11 @@
       <c r="T184" s="1">
         <v>60477</v>
       </c>
-    </row>
-    <row r="185" spans="1:20">
+      <c r="U184" s="2" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="185" spans="1:21">
       <c r="A185" s="3">
         <v>184</v>
       </c>
@@ -12387,8 +12989,11 @@
       <c r="T185" s="1">
         <v>46900</v>
       </c>
-    </row>
-    <row r="186" spans="1:20">
+      <c r="U185" s="2" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="186" spans="1:21">
       <c r="A186" s="3">
         <v>185</v>
       </c>
@@ -12441,8 +13046,11 @@
       <c r="T186" s="1">
         <v>19800</v>
       </c>
-    </row>
-    <row r="187" spans="1:20">
+      <c r="U186" s="2" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="187" spans="1:21">
       <c r="A187" s="3">
         <v>186</v>
       </c>
@@ -12495,8 +13103,11 @@
       <c r="T187" s="1">
         <v>8800</v>
       </c>
-    </row>
-    <row r="188" spans="1:20">
+      <c r="U187" s="2" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="188" spans="1:21">
       <c r="A188" s="3">
         <v>187</v>
       </c>
@@ -12551,8 +13162,11 @@
       <c r="T188" s="1">
         <v>57000</v>
       </c>
-    </row>
-    <row r="189" spans="1:20">
+      <c r="U188" s="2" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="189" spans="1:21">
       <c r="A189" s="3">
         <v>188</v>
       </c>
@@ -12605,13 +13219,16 @@
       <c r="T189" s="1">
         <v>10700</v>
       </c>
-    </row>
-    <row r="190" spans="1:20">
+      <c r="U189" s="2" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="190" spans="1:21">
       <c r="A190" s="3">
         <v>189</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="C190" s="3" t="s">
         <v>320</v>
@@ -12661,8 +13278,11 @@
       <c r="T190" s="1">
         <v>30000</v>
       </c>
-    </row>
-    <row r="191" spans="1:20">
+      <c r="U190" s="2" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="191" spans="1:21">
       <c r="A191" s="3">
         <v>190</v>
       </c>
@@ -12715,8 +13335,11 @@
       <c r="T191" s="1">
         <v>15800</v>
       </c>
-    </row>
-    <row r="192" spans="1:20">
+      <c r="U191" s="2" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="192" spans="1:21">
       <c r="A192" s="3">
         <v>191</v>
       </c>
@@ -12763,7 +13386,7 @@
       <c r="T192" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V192" xr:uid="{7B280671-4AFA-4641-88D4-A51F39483890}"/>
+  <autoFilter ref="A1:U192" xr:uid="{7B280671-4AFA-4641-88D4-A51F39483890}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -12771,17 +13394,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e40a7e4-94f1-4b05-8c7e-c5111c724f9a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="f655991e-a262-4cc2-969f-4b8d0db6a5de" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100BC605E6093A30A479FED397EFA867E40" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="55774fc2038cb4dae8fef12431c133f2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f655991e-a262-4cc2-969f-4b8d0db6a5de" xmlns:ns3="8e40a7e4-94f1-4b05-8c7e-c5111c724f9a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="31482a63ce11ed8a627351d2502cc05d" ns2:_="" ns3:_="">
     <xsd:import namespace="f655991e-a262-4cc2-969f-4b8d0db6a5de"/>
@@ -13042,6 +13654,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e40a7e4-94f1-4b05-8c7e-c5111c724f9a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="f655991e-a262-4cc2-969f-4b8d0db6a5de" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -13052,17 +13675,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF6E6A69-6D48-49BB-9E8E-5B96C2738B7E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="8e40a7e4-94f1-4b05-8c7e-c5111c724f9a"/>
-    <ds:schemaRef ds:uri="f655991e-a262-4cc2-969f-4b8d0db6a5de"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5BF42E8-7CD6-44A5-B028-608DFC162276}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -13081,6 +13693,17 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF6E6A69-6D48-49BB-9E8E-5B96C2738B7E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="8e40a7e4-94f1-4b05-8c7e-c5111c724f9a"/>
+    <ds:schemaRef ds:uri="f655991e-a262-4cc2-969f-4b8d0db6a5de"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C7A7DD6C-B285-4C23-BA8C-7CCC252AB8AB}">
   <ds:schemaRefs>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yuhang/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAEA7256-53DB-7C41-8204-AC505DD7B259}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83F60C94-7016-E549-9FC1-0CFD8E38A724}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20" yWindow="620" windowWidth="28060" windowHeight="15940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">Sheet1!$A$1:$T$192</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$T$192</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -3638,7 +3638,7 @@
         <v>560</v>
       </c>
       <c r="O30" s="15">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="P30" s="15">
         <v>400</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yuhang/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83F60C94-7016-E549-9FC1-0CFD8E38A724}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{095C2ECE-7366-E342-B377-93C375E6DD26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1390,7 +1390,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <numFmts count="2">
+    <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="178" formatCode="0_);[Red]\(0\)"/>
+  </numFmts>
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1424,6 +1428,14 @@
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1513,13 +1525,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
       <protection locked="0"/>
@@ -1530,13 +1545,13 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1545,27 +1560,27 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
@@ -1595,8 +1610,39 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="176" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="5" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="5" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="5" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="178" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="百分比" xfId="2" builtinId="5"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2" xfId="1" xr:uid="{81D4EE7A-49F9-4559-B92D-CA7C8AC626DC}"/>
   </cellStyles>
@@ -1911,14 +1957,14 @@
     <col min="9" max="9" width="36.83203125" style="6" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14.33203125" style="6" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="14" style="16" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.6640625" style="16" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.6640625" style="30" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14" style="16" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="16.6640625" style="16" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="14" style="16" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="16.6640625" style="16" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="22.33203125" style="16" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.6640625" style="16" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="19.33203125" style="16" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="22.33203125" style="24" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.6640625" style="27" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="19.33203125" style="30" bestFit="1" customWidth="1"/>
     <col min="21" max="16384" width="10.83203125" style="2"/>
   </cols>
   <sheetData>
@@ -1959,7 +2005,7 @@
       <c r="L1" s="14" t="s">
         <v>415</v>
       </c>
-      <c r="M1" s="14" t="s">
+      <c r="M1" s="28" t="s">
         <v>334</v>
       </c>
       <c r="N1" s="14" t="s">
@@ -1974,13 +2020,13 @@
       <c r="Q1" s="14" t="s">
         <v>419</v>
       </c>
-      <c r="R1" s="14" t="s">
+      <c r="R1" s="22" t="s">
         <v>339</v>
       </c>
-      <c r="S1" s="14" t="s">
+      <c r="S1" s="25" t="s">
         <v>340</v>
       </c>
-      <c r="T1" s="14" t="s">
+      <c r="T1" s="28" t="s">
         <v>341</v>
       </c>
     </row>
@@ -2015,7 +2061,7 @@
       </c>
       <c r="K2" s="15"/>
       <c r="L2" s="15"/>
-      <c r="M2" s="15">
+      <c r="M2" s="29">
         <v>72308</v>
       </c>
       <c r="N2" s="15">
@@ -2030,13 +2076,13 @@
       <c r="Q2" s="15">
         <v>3</v>
       </c>
-      <c r="R2" s="15">
+      <c r="R2" s="23">
         <v>288.75</v>
       </c>
-      <c r="S2" s="15">
+      <c r="S2" s="26">
         <v>0.129999446810865</v>
       </c>
-      <c r="T2" s="15">
+      <c r="T2" s="29">
         <v>9400</v>
       </c>
     </row>
@@ -2071,7 +2117,7 @@
       </c>
       <c r="K3" s="15"/>
       <c r="L3" s="15"/>
-      <c r="M3" s="15">
+      <c r="M3" s="29">
         <v>72308</v>
       </c>
       <c r="N3" s="15">
@@ -2086,13 +2132,13 @@
       <c r="Q3" s="15">
         <v>3</v>
       </c>
-      <c r="R3" s="15">
+      <c r="R3" s="23">
         <v>307.08333333333297</v>
       </c>
-      <c r="S3" s="15">
+      <c r="S3" s="26">
         <v>2.0053106156995099E-2</v>
       </c>
-      <c r="T3" s="15">
+      <c r="T3" s="29">
         <v>1450</v>
       </c>
     </row>
@@ -2129,7 +2175,7 @@
       </c>
       <c r="K4" s="15"/>
       <c r="L4" s="15"/>
-      <c r="M4" s="15">
+      <c r="M4" s="29">
         <v>130769</v>
       </c>
       <c r="N4" s="15">
@@ -2144,13 +2190,13 @@
       <c r="Q4" s="15">
         <v>2</v>
       </c>
-      <c r="R4" s="15">
+      <c r="R4" s="23">
         <v>363.61111111111097</v>
       </c>
-      <c r="S4" s="15">
+      <c r="S4" s="26">
         <v>0.100176647370554</v>
       </c>
-      <c r="T4" s="15">
+      <c r="T4" s="29">
         <v>13100</v>
       </c>
     </row>
@@ -2187,7 +2233,7 @@
       </c>
       <c r="K5" s="15"/>
       <c r="L5" s="15"/>
-      <c r="M5" s="15">
+      <c r="M5" s="29">
         <v>64615</v>
       </c>
       <c r="N5" s="15">
@@ -2202,13 +2248,13 @@
       <c r="Q5" s="15">
         <v>2</v>
       </c>
-      <c r="R5" s="15">
+      <c r="R5" s="23">
         <v>377.777777777778</v>
       </c>
-      <c r="S5" s="15">
+      <c r="S5" s="26">
         <v>3.01787510639944E-2</v>
       </c>
-      <c r="T5" s="15">
+      <c r="T5" s="29">
         <v>1950</v>
       </c>
     </row>
@@ -2245,7 +2291,7 @@
       </c>
       <c r="K6" s="15"/>
       <c r="L6" s="15"/>
-      <c r="M6" s="15">
+      <c r="M6" s="29">
         <v>80091</v>
       </c>
       <c r="N6" s="15">
@@ -2260,13 +2306,13 @@
       <c r="Q6" s="15">
         <v>6</v>
       </c>
-      <c r="R6" s="15">
+      <c r="R6" s="23">
         <v>208.333333333333</v>
       </c>
-      <c r="S6" s="15">
+      <c r="S6" s="26">
         <v>7.4440324131300598E-2</v>
       </c>
-      <c r="T6" s="15">
+      <c r="T6" s="29">
         <v>5962</v>
       </c>
     </row>
@@ -2301,7 +2347,7 @@
       </c>
       <c r="K7" s="15"/>
       <c r="L7" s="15"/>
-      <c r="M7" s="15">
+      <c r="M7" s="29">
         <v>70673</v>
       </c>
       <c r="N7" s="15">
@@ -2316,13 +2362,13 @@
       <c r="Q7" s="15">
         <v>3</v>
       </c>
-      <c r="R7" s="15">
+      <c r="R7" s="23">
         <v>242.916666666667</v>
       </c>
-      <c r="S7" s="15">
+      <c r="S7" s="26">
         <v>0</v>
       </c>
-      <c r="T7" s="15">
+      <c r="T7" s="29">
         <v>0</v>
       </c>
     </row>
@@ -2359,7 +2405,7 @@
       </c>
       <c r="K8" s="15"/>
       <c r="L8" s="15"/>
-      <c r="M8" s="15">
+      <c r="M8" s="29">
         <v>90466</v>
       </c>
       <c r="N8" s="15">
@@ -2374,13 +2420,13 @@
       <c r="Q8" s="15">
         <v>4</v>
       </c>
-      <c r="R8" s="15">
+      <c r="R8" s="23">
         <v>177.777777777778</v>
       </c>
-      <c r="S8" s="15">
+      <c r="S8" s="26">
         <v>0.239935445360688</v>
       </c>
-      <c r="T8" s="15">
+      <c r="T8" s="29">
         <v>21706</v>
       </c>
     </row>
@@ -2415,7 +2461,7 @@
       </c>
       <c r="K9" s="15"/>
       <c r="L9" s="15"/>
-      <c r="M9" s="15">
+      <c r="M9" s="29">
         <v>46720</v>
       </c>
       <c r="N9" s="15">
@@ -2430,13 +2476,13 @@
       <c r="Q9" s="15">
         <v>8</v>
       </c>
-      <c r="R9" s="15">
+      <c r="R9" s="23">
         <v>198.333333333333</v>
       </c>
-      <c r="S9" s="15">
+      <c r="S9" s="26">
         <v>7.4453553082191801E-2</v>
       </c>
-      <c r="T9" s="15">
+      <c r="T9" s="29">
         <v>3478.47</v>
       </c>
     </row>
@@ -2473,7 +2519,7 @@
       </c>
       <c r="K10" s="15"/>
       <c r="L10" s="15"/>
-      <c r="M10" s="15">
+      <c r="M10" s="29">
         <v>95000</v>
       </c>
       <c r="N10" s="15">
@@ -2488,13 +2534,13 @@
       <c r="Q10" s="15">
         <v>8</v>
       </c>
-      <c r="R10" s="15">
+      <c r="R10" s="23">
         <v>182.777777777778</v>
       </c>
-      <c r="S10" s="15">
+      <c r="S10" s="26">
         <v>0.24465263157894701</v>
       </c>
-      <c r="T10" s="15">
+      <c r="T10" s="29">
         <v>23242</v>
       </c>
     </row>
@@ -2531,7 +2577,7 @@
       </c>
       <c r="K11" s="15"/>
       <c r="L11" s="15"/>
-      <c r="M11" s="15">
+      <c r="M11" s="29">
         <v>85300</v>
       </c>
       <c r="N11" s="15">
@@ -2546,13 +2592,13 @@
       <c r="Q11" s="15">
         <v>5</v>
       </c>
-      <c r="R11" s="15">
+      <c r="R11" s="23">
         <v>146.388888888889</v>
       </c>
-      <c r="S11" s="15">
+      <c r="S11" s="26">
         <v>0.19929660023446699</v>
       </c>
-      <c r="T11" s="15">
+      <c r="T11" s="29">
         <v>17000</v>
       </c>
     </row>
@@ -2589,7 +2635,7 @@
       </c>
       <c r="K12" s="15"/>
       <c r="L12" s="15"/>
-      <c r="M12" s="15">
+      <c r="M12" s="29">
         <v>33305</v>
       </c>
       <c r="N12" s="15">
@@ -2604,13 +2650,13 @@
       <c r="Q12" s="15">
         <v>4</v>
       </c>
-      <c r="R12" s="15">
+      <c r="R12" s="23">
         <v>186.666666666667</v>
       </c>
-      <c r="S12" s="15">
+      <c r="S12" s="26">
         <v>0.14799579642696301</v>
       </c>
-      <c r="T12" s="15">
+      <c r="T12" s="29">
         <v>4929</v>
       </c>
     </row>
@@ -2647,7 +2693,7 @@
       </c>
       <c r="K13" s="15"/>
       <c r="L13" s="15"/>
-      <c r="M13" s="15">
+      <c r="M13" s="29">
         <v>120245.21</v>
       </c>
       <c r="N13" s="15">
@@ -2662,13 +2708,13 @@
       <c r="Q13" s="15">
         <v>4</v>
       </c>
-      <c r="R13" s="15">
+      <c r="R13" s="23">
         <v>253.333333333333</v>
       </c>
-      <c r="S13" s="15">
+      <c r="S13" s="26">
         <v>6.6680410803889797E-2</v>
       </c>
-      <c r="T13" s="15">
+      <c r="T13" s="29">
         <v>8018</v>
       </c>
     </row>
@@ -2705,7 +2751,7 @@
       </c>
       <c r="K14" s="15"/>
       <c r="L14" s="15"/>
-      <c r="M14" s="15">
+      <c r="M14" s="29">
         <v>70425.53</v>
       </c>
       <c r="N14" s="15">
@@ -2720,13 +2766,13 @@
       <c r="Q14" s="15">
         <v>4</v>
       </c>
-      <c r="R14" s="15">
+      <c r="R14" s="23">
         <v>253.333333333333</v>
       </c>
-      <c r="S14" s="15">
+      <c r="S14" s="26">
         <v>9.3091241201876604E-2</v>
       </c>
-      <c r="T14" s="15">
+      <c r="T14" s="29">
         <v>6556</v>
       </c>
     </row>
@@ -2763,7 +2809,7 @@
       </c>
       <c r="K15" s="15"/>
       <c r="L15" s="15"/>
-      <c r="M15" s="15">
+      <c r="M15" s="29">
         <v>78000</v>
       </c>
       <c r="N15" s="15">
@@ -2778,13 +2824,13 @@
       <c r="Q15" s="15">
         <v>6</v>
       </c>
-      <c r="R15" s="15">
+      <c r="R15" s="23">
         <v>258.33333333333297</v>
       </c>
-      <c r="S15" s="15">
+      <c r="S15" s="26">
         <v>0.15384615384615399</v>
       </c>
-      <c r="T15" s="15">
+      <c r="T15" s="29">
         <v>12000</v>
       </c>
     </row>
@@ -2821,7 +2867,7 @@
       </c>
       <c r="K16" s="15"/>
       <c r="L16" s="15"/>
-      <c r="M16" s="15">
+      <c r="M16" s="29">
         <v>102796</v>
       </c>
       <c r="N16" s="15">
@@ -2836,13 +2882,13 @@
       <c r="Q16" s="15">
         <v>6</v>
       </c>
-      <c r="R16" s="15">
+      <c r="R16" s="23">
         <v>200</v>
       </c>
-      <c r="S16" s="15">
+      <c r="S16" s="26">
         <v>0.170955095529009</v>
       </c>
-      <c r="T16" s="15">
+      <c r="T16" s="29">
         <v>17573.5</v>
       </c>
     </row>
@@ -2879,7 +2925,7 @@
       </c>
       <c r="K17" s="15"/>
       <c r="L17" s="15"/>
-      <c r="M17" s="15">
+      <c r="M17" s="29">
         <v>49200</v>
       </c>
       <c r="N17" s="15">
@@ -2894,13 +2940,13 @@
       <c r="Q17" s="15">
         <v>6</v>
       </c>
-      <c r="R17" s="15">
+      <c r="R17" s="23">
         <v>191.666666666667</v>
       </c>
-      <c r="S17" s="15">
+      <c r="S17" s="26">
         <v>9.3665650406504097E-2</v>
       </c>
-      <c r="T17" s="15">
+      <c r="T17" s="29">
         <v>4608.3500000000004</v>
       </c>
     </row>
@@ -2937,7 +2983,7 @@
       </c>
       <c r="K18" s="15"/>
       <c r="L18" s="15"/>
-      <c r="M18" s="15">
+      <c r="M18" s="29">
         <v>65096</v>
       </c>
       <c r="N18" s="15">
@@ -2952,13 +2998,13 @@
       <c r="Q18" s="15">
         <v>8</v>
       </c>
-      <c r="R18" s="15">
+      <c r="R18" s="23">
         <v>186.666666666667</v>
       </c>
-      <c r="S18" s="15">
+      <c r="S18" s="26">
         <v>0.12122096595796999</v>
       </c>
-      <c r="T18" s="15">
+      <c r="T18" s="29">
         <v>7891</v>
       </c>
     </row>
@@ -2995,7 +3041,7 @@
       </c>
       <c r="K19" s="15"/>
       <c r="L19" s="15"/>
-      <c r="M19" s="15">
+      <c r="M19" s="29">
         <v>56000</v>
       </c>
       <c r="N19" s="15">
@@ -3010,13 +3056,13 @@
       <c r="Q19" s="15">
         <v>7</v>
       </c>
-      <c r="R19" s="15">
+      <c r="R19" s="23">
         <v>177.222222222222</v>
       </c>
-      <c r="S19" s="15">
+      <c r="S19" s="26">
         <v>8.2446428571428601E-2</v>
       </c>
-      <c r="T19" s="15">
+      <c r="T19" s="29">
         <v>4617</v>
       </c>
     </row>
@@ -3053,7 +3099,7 @@
       </c>
       <c r="K20" s="15"/>
       <c r="L20" s="15"/>
-      <c r="M20" s="15">
+      <c r="M20" s="29">
         <v>177847</v>
       </c>
       <c r="N20" s="15">
@@ -3068,13 +3114,13 @@
       <c r="Q20" s="15">
         <v>12</v>
       </c>
-      <c r="R20" s="15">
+      <c r="R20" s="23">
         <v>200</v>
       </c>
-      <c r="S20" s="15">
+      <c r="S20" s="26">
         <v>0.27326859604041698</v>
       </c>
-      <c r="T20" s="15">
+      <c r="T20" s="29">
         <v>48600</v>
       </c>
     </row>
@@ -3111,7 +3157,7 @@
       </c>
       <c r="K21" s="15"/>
       <c r="L21" s="15"/>
-      <c r="M21" s="15">
+      <c r="M21" s="29">
         <v>83000</v>
       </c>
       <c r="N21" s="15">
@@ -3126,13 +3172,13 @@
       <c r="Q21" s="15">
         <v>5</v>
       </c>
-      <c r="R21" s="15">
+      <c r="R21" s="23">
         <v>185.138888888889</v>
       </c>
-      <c r="S21" s="15">
+      <c r="S21" s="26">
         <v>0.120481927710843</v>
       </c>
-      <c r="T21" s="15">
+      <c r="T21" s="29">
         <v>10000</v>
       </c>
     </row>
@@ -3167,7 +3213,7 @@
       </c>
       <c r="K22" s="15"/>
       <c r="L22" s="15"/>
-      <c r="M22" s="15">
+      <c r="M22" s="29">
         <v>26000</v>
       </c>
       <c r="N22" s="15">
@@ -3182,13 +3228,13 @@
       <c r="Q22" s="15">
         <v>4</v>
       </c>
-      <c r="R22" s="15">
+      <c r="R22" s="23">
         <v>222.222222222222</v>
       </c>
-      <c r="S22" s="15">
+      <c r="S22" s="26">
         <v>3.8461538461538498E-2</v>
       </c>
-      <c r="T22" s="15">
+      <c r="T22" s="29">
         <v>1000</v>
       </c>
     </row>
@@ -3225,7 +3271,7 @@
       </c>
       <c r="K23" s="15"/>
       <c r="L23" s="15"/>
-      <c r="M23" s="15">
+      <c r="M23" s="29">
         <v>85887</v>
       </c>
       <c r="N23" s="15">
@@ -3240,13 +3286,13 @@
       <c r="Q23" s="15">
         <v>5</v>
       </c>
-      <c r="R23" s="15">
+      <c r="R23" s="23">
         <v>193.75</v>
       </c>
-      <c r="S23" s="15">
+      <c r="S23" s="26">
         <v>0.21099817201672</v>
       </c>
-      <c r="T23" s="15">
+      <c r="T23" s="29">
         <v>18122</v>
       </c>
     </row>
@@ -3283,7 +3329,7 @@
       </c>
       <c r="K24" s="15"/>
       <c r="L24" s="15"/>
-      <c r="M24" s="15">
+      <c r="M24" s="29">
         <v>20000</v>
       </c>
       <c r="N24" s="15">
@@ -3298,13 +3344,13 @@
       <c r="Q24" s="15">
         <v>5</v>
       </c>
-      <c r="R24" s="15">
+      <c r="R24" s="23">
         <v>163.611111111111</v>
       </c>
-      <c r="S24" s="15">
+      <c r="S24" s="26">
         <v>0.58565</v>
       </c>
-      <c r="T24" s="15">
+      <c r="T24" s="29">
         <v>11713</v>
       </c>
     </row>
@@ -3341,7 +3387,7 @@
       </c>
       <c r="K25" s="15"/>
       <c r="L25" s="15"/>
-      <c r="M25" s="15">
+      <c r="M25" s="29">
         <v>146385</v>
       </c>
       <c r="N25" s="15">
@@ -3356,13 +3402,13 @@
       <c r="Q25" s="15">
         <v>5</v>
       </c>
-      <c r="R25" s="15">
+      <c r="R25" s="23">
         <v>236.805555555555</v>
       </c>
-      <c r="S25" s="15">
+      <c r="S25" s="26">
         <v>7.68931242955221E-2</v>
       </c>
-      <c r="T25" s="15">
+      <c r="T25" s="29">
         <v>11256</v>
       </c>
     </row>
@@ -3399,7 +3445,7 @@
       </c>
       <c r="K26" s="15"/>
       <c r="L26" s="15"/>
-      <c r="M26" s="15">
+      <c r="M26" s="29">
         <v>87000</v>
       </c>
       <c r="N26" s="15">
@@ -3414,13 +3460,13 @@
       <c r="Q26" s="15">
         <v>6</v>
       </c>
-      <c r="R26" s="15">
+      <c r="R26" s="23">
         <v>208.333333333333</v>
       </c>
-      <c r="S26" s="15">
+      <c r="S26" s="26">
         <v>0.17591954022988501</v>
       </c>
-      <c r="T26" s="15">
+      <c r="T26" s="29">
         <v>15305</v>
       </c>
     </row>
@@ -3457,7 +3503,7 @@
       </c>
       <c r="K27" s="15"/>
       <c r="L27" s="15"/>
-      <c r="M27" s="15">
+      <c r="M27" s="29">
         <v>147166.79999999999</v>
       </c>
       <c r="N27" s="15">
@@ -3472,13 +3518,13 @@
       <c r="Q27" s="15">
         <v>7</v>
       </c>
-      <c r="R27" s="15">
+      <c r="R27" s="23">
         <v>237.638888888889</v>
       </c>
-      <c r="S27" s="15">
+      <c r="S27" s="26">
         <v>0.139997608156187</v>
       </c>
-      <c r="T27" s="15">
+      <c r="T27" s="29">
         <v>20603</v>
       </c>
     </row>
@@ -3515,7 +3561,7 @@
       </c>
       <c r="K28" s="15"/>
       <c r="L28" s="15"/>
-      <c r="M28" s="15">
+      <c r="M28" s="29">
         <v>46063</v>
       </c>
       <c r="N28" s="15">
@@ -3530,13 +3576,13 @@
       <c r="Q28" s="15">
         <v>4</v>
       </c>
-      <c r="R28" s="15">
+      <c r="R28" s="23">
         <v>160</v>
       </c>
-      <c r="S28" s="15">
+      <c r="S28" s="26">
         <v>9.1418274971235003E-2</v>
       </c>
-      <c r="T28" s="15">
+      <c r="T28" s="29">
         <v>4211</v>
       </c>
     </row>
@@ -3573,7 +3619,7 @@
       </c>
       <c r="K29" s="15"/>
       <c r="L29" s="15"/>
-      <c r="M29" s="15">
+      <c r="M29" s="29">
         <v>47261</v>
       </c>
       <c r="N29" s="15">
@@ -3588,13 +3634,13 @@
       <c r="Q29" s="15">
         <v>7</v>
       </c>
-      <c r="R29" s="15">
+      <c r="R29" s="23">
         <v>241.666666666667</v>
       </c>
-      <c r="S29" s="15">
+      <c r="S29" s="26">
         <v>0.23315566746365901</v>
       </c>
-      <c r="T29" s="15">
+      <c r="T29" s="29">
         <v>11019.17</v>
       </c>
     </row>
@@ -3631,7 +3677,7 @@
       </c>
       <c r="K30" s="15"/>
       <c r="L30" s="15"/>
-      <c r="M30" s="15">
+      <c r="M30" s="29">
         <v>119000</v>
       </c>
       <c r="N30" s="15">
@@ -3646,13 +3692,13 @@
       <c r="Q30" s="15">
         <v>6</v>
       </c>
-      <c r="R30" s="15">
+      <c r="R30" s="23">
         <v>333.33333333333297</v>
       </c>
-      <c r="S30" s="15">
+      <c r="S30" s="26">
         <v>0.15546218487395</v>
       </c>
-      <c r="T30" s="15">
+      <c r="T30" s="29">
         <v>18500</v>
       </c>
     </row>
@@ -3687,7 +3733,7 @@
       </c>
       <c r="K31" s="15"/>
       <c r="L31" s="15"/>
-      <c r="M31" s="15">
+      <c r="M31" s="29">
         <v>47000</v>
       </c>
       <c r="N31" s="15">
@@ -3702,13 +3748,13 @@
       <c r="Q31" s="15">
         <v>2</v>
       </c>
-      <c r="R31" s="15">
+      <c r="R31" s="23">
         <v>330.55555555555497</v>
       </c>
-      <c r="S31" s="15">
+      <c r="S31" s="26">
         <v>0.125228723404255</v>
       </c>
-      <c r="T31" s="15">
+      <c r="T31" s="29">
         <v>5885.75</v>
       </c>
     </row>
@@ -3745,7 +3791,7 @@
       </c>
       <c r="K32" s="15"/>
       <c r="L32" s="15"/>
-      <c r="M32" s="15">
+      <c r="M32" s="29">
         <v>186000</v>
       </c>
       <c r="N32" s="15">
@@ -3760,13 +3806,13 @@
       <c r="Q32" s="15">
         <v>5</v>
       </c>
-      <c r="R32" s="15">
+      <c r="R32" s="23">
         <v>258.33333333333297</v>
       </c>
-      <c r="S32" s="15">
+      <c r="S32" s="26">
         <v>9.6774193548387094E-2</v>
       </c>
-      <c r="T32" s="15">
+      <c r="T32" s="29">
         <v>18000</v>
       </c>
     </row>
@@ -3801,7 +3847,7 @@
       </c>
       <c r="K33" s="15"/>
       <c r="L33" s="15"/>
-      <c r="M33" s="15">
+      <c r="M33" s="29">
         <v>40800</v>
       </c>
       <c r="N33" s="15">
@@ -3816,13 +3862,13 @@
       <c r="Q33" s="15">
         <v>2</v>
       </c>
-      <c r="R33" s="15">
+      <c r="R33" s="23">
         <v>194.555555555555</v>
       </c>
-      <c r="S33" s="15">
+      <c r="S33" s="26">
         <v>0.49509803921568601</v>
       </c>
-      <c r="T33" s="15">
+      <c r="T33" s="29">
         <v>20200</v>
       </c>
     </row>
@@ -3857,7 +3903,7 @@
       </c>
       <c r="K34" s="15"/>
       <c r="L34" s="15"/>
-      <c r="M34" s="15">
+      <c r="M34" s="29">
         <v>55200</v>
       </c>
       <c r="N34" s="15">
@@ -3872,13 +3918,13 @@
       <c r="Q34" s="15">
         <v>5</v>
       </c>
-      <c r="R34" s="15">
+      <c r="R34" s="23">
         <v>198.055555555555</v>
       </c>
-      <c r="S34" s="15">
+      <c r="S34" s="26">
         <v>0.94927536231884102</v>
       </c>
-      <c r="T34" s="15">
+      <c r="T34" s="29">
         <v>52400</v>
       </c>
     </row>
@@ -3915,7 +3961,7 @@
       </c>
       <c r="K35" s="15"/>
       <c r="L35" s="15"/>
-      <c r="M35" s="15">
+      <c r="M35" s="29">
         <v>350000</v>
       </c>
       <c r="N35" s="15">
@@ -3930,13 +3976,13 @@
       <c r="Q35" s="15">
         <v>2</v>
       </c>
-      <c r="R35" s="15">
+      <c r="R35" s="23">
         <v>462.777777777778</v>
       </c>
-      <c r="S35" s="15">
+      <c r="S35" s="26">
         <v>6.27571428571429E-2</v>
       </c>
-      <c r="T35" s="15">
+      <c r="T35" s="29">
         <v>21965</v>
       </c>
     </row>
@@ -3973,7 +4019,7 @@
       </c>
       <c r="K36" s="15"/>
       <c r="L36" s="15"/>
-      <c r="M36" s="15">
+      <c r="M36" s="29">
         <v>65000</v>
       </c>
       <c r="N36" s="15">
@@ -3988,13 +4034,13 @@
       <c r="Q36" s="15">
         <v>6</v>
       </c>
-      <c r="R36" s="15">
+      <c r="R36" s="23">
         <v>191.666666666667</v>
       </c>
-      <c r="S36" s="15">
+      <c r="S36" s="26">
         <v>0.31316923076923098</v>
       </c>
-      <c r="T36" s="15">
+      <c r="T36" s="29">
         <v>20356</v>
       </c>
     </row>
@@ -4031,7 +4077,7 @@
       </c>
       <c r="K37" s="15"/>
       <c r="L37" s="15"/>
-      <c r="M37" s="15">
+      <c r="M37" s="29">
         <v>35000</v>
       </c>
       <c r="N37" s="15">
@@ -4046,13 +4092,13 @@
       <c r="Q37" s="15">
         <v>6</v>
       </c>
-      <c r="R37" s="15">
+      <c r="R37" s="23">
         <v>208.333333333333</v>
       </c>
-      <c r="S37" s="15">
+      <c r="S37" s="26">
         <v>0.23714285714285699</v>
       </c>
-      <c r="T37" s="15">
+      <c r="T37" s="29">
         <v>8300</v>
       </c>
     </row>
@@ -4089,7 +4135,7 @@
       </c>
       <c r="K38" s="15"/>
       <c r="L38" s="15"/>
-      <c r="M38" s="15">
+      <c r="M38" s="29">
         <v>47000</v>
       </c>
       <c r="N38" s="15">
@@ -4104,13 +4150,13 @@
       <c r="Q38" s="15">
         <v>9</v>
       </c>
-      <c r="R38" s="15">
+      <c r="R38" s="23">
         <v>157.5</v>
       </c>
-      <c r="S38" s="15">
+      <c r="S38" s="26">
         <v>5.7446808510638298E-2</v>
       </c>
-      <c r="T38" s="15">
+      <c r="T38" s="29">
         <v>2700</v>
       </c>
     </row>
@@ -4147,7 +4193,7 @@
       </c>
       <c r="K39" s="15"/>
       <c r="L39" s="15"/>
-      <c r="M39" s="15">
+      <c r="M39" s="29">
         <v>120000</v>
       </c>
       <c r="N39" s="15">
@@ -4162,13 +4208,13 @@
       <c r="Q39" s="15">
         <v>7</v>
       </c>
-      <c r="R39" s="15">
+      <c r="R39" s="23">
         <v>241.666666666667</v>
       </c>
-      <c r="S39" s="15">
+      <c r="S39" s="26">
         <v>0.03</v>
       </c>
-      <c r="T39" s="15">
+      <c r="T39" s="29">
         <v>3600</v>
       </c>
     </row>
@@ -4203,7 +4249,7 @@
       </c>
       <c r="K40" s="15"/>
       <c r="L40" s="15"/>
-      <c r="M40" s="15">
+      <c r="M40" s="29">
         <v>83000</v>
       </c>
       <c r="N40" s="15">
@@ -4218,13 +4264,13 @@
       <c r="Q40" s="15">
         <v>2</v>
       </c>
-      <c r="R40" s="15">
+      <c r="R40" s="23">
         <v>122.777777777778</v>
       </c>
-      <c r="S40" s="15">
+      <c r="S40" s="26">
         <v>0.219493975903614</v>
       </c>
-      <c r="T40" s="15">
+      <c r="T40" s="29">
         <v>18218</v>
       </c>
     </row>
@@ -4261,7 +4307,7 @@
       </c>
       <c r="K41" s="15"/>
       <c r="L41" s="15"/>
-      <c r="M41" s="15">
+      <c r="M41" s="29">
         <v>66030</v>
       </c>
       <c r="N41" s="15">
@@ -4276,13 +4322,13 @@
       <c r="Q41" s="15">
         <v>5</v>
       </c>
-      <c r="R41" s="15">
+      <c r="R41" s="23">
         <v>284.16666666666703</v>
       </c>
-      <c r="S41" s="15">
+      <c r="S41" s="26">
         <v>0.14162153566560701</v>
       </c>
-      <c r="T41" s="15">
+      <c r="T41" s="29">
         <v>9351.27</v>
       </c>
     </row>
@@ -4319,7 +4365,7 @@
       </c>
       <c r="K42" s="15"/>
       <c r="L42" s="15"/>
-      <c r="M42" s="15">
+      <c r="M42" s="29">
         <v>40000</v>
       </c>
       <c r="N42" s="15">
@@ -4334,13 +4380,13 @@
       <c r="Q42" s="15">
         <v>4</v>
       </c>
-      <c r="R42" s="15">
+      <c r="R42" s="23">
         <v>186.666666666667</v>
       </c>
-      <c r="S42" s="15">
+      <c r="S42" s="26">
         <v>0.06</v>
       </c>
-      <c r="T42" s="15">
+      <c r="T42" s="29">
         <v>2400</v>
       </c>
     </row>
@@ -4377,7 +4423,7 @@
       </c>
       <c r="K43" s="15"/>
       <c r="L43" s="15"/>
-      <c r="M43" s="15">
+      <c r="M43" s="29">
         <v>40000</v>
       </c>
       <c r="N43" s="15">
@@ -4392,13 +4438,13 @@
       <c r="Q43" s="15">
         <v>3</v>
       </c>
-      <c r="R43" s="15">
+      <c r="R43" s="23">
         <v>178.75</v>
       </c>
-      <c r="S43" s="15">
+      <c r="S43" s="26">
         <v>0.108875</v>
       </c>
-      <c r="T43" s="15">
+      <c r="T43" s="29">
         <v>4355</v>
       </c>
     </row>
@@ -4433,7 +4479,7 @@
       </c>
       <c r="K44" s="15"/>
       <c r="L44" s="15"/>
-      <c r="M44" s="15">
+      <c r="M44" s="29">
         <v>54100</v>
       </c>
       <c r="N44" s="15">
@@ -4448,13 +4494,13 @@
       <c r="Q44" s="15">
         <v>5</v>
       </c>
-      <c r="R44" s="15">
+      <c r="R44" s="23">
         <v>198.055555555555</v>
       </c>
-      <c r="S44" s="15">
+      <c r="S44" s="26">
         <v>0.209593345656192</v>
       </c>
-      <c r="T44" s="15">
+      <c r="T44" s="29">
         <v>11339</v>
       </c>
     </row>
@@ -4491,7 +4537,7 @@
       </c>
       <c r="K45" s="15"/>
       <c r="L45" s="15"/>
-      <c r="M45" s="15">
+      <c r="M45" s="29">
         <v>100000</v>
       </c>
       <c r="N45" s="15">
@@ -4506,13 +4552,13 @@
       <c r="Q45" s="15">
         <v>4</v>
       </c>
-      <c r="R45" s="15">
+      <c r="R45" s="23">
         <v>222.222222222222</v>
       </c>
-      <c r="S45" s="15">
+      <c r="S45" s="26">
         <v>0.1</v>
       </c>
-      <c r="T45" s="15">
+      <c r="T45" s="29">
         <v>10000</v>
       </c>
     </row>
@@ -4549,7 +4595,7 @@
       </c>
       <c r="K46" s="15"/>
       <c r="L46" s="15"/>
-      <c r="M46" s="15">
+      <c r="M46" s="29">
         <v>150000</v>
       </c>
       <c r="N46" s="15">
@@ -4564,13 +4610,13 @@
       <c r="Q46" s="15">
         <v>3</v>
       </c>
-      <c r="R46" s="15">
+      <c r="R46" s="23">
         <v>229.166666666667</v>
       </c>
-      <c r="S46" s="15">
+      <c r="S46" s="26">
         <v>0.05</v>
       </c>
-      <c r="T46" s="15">
+      <c r="T46" s="29">
         <v>7500</v>
       </c>
     </row>
@@ -4607,7 +4653,7 @@
       </c>
       <c r="K47" s="15"/>
       <c r="L47" s="15"/>
-      <c r="M47" s="15">
+      <c r="M47" s="29">
         <v>50000</v>
       </c>
       <c r="N47" s="15">
@@ -4622,13 +4668,13 @@
       <c r="Q47" s="15">
         <v>4</v>
       </c>
-      <c r="R47" s="15">
+      <c r="R47" s="23">
         <v>231.111111111111</v>
       </c>
-      <c r="S47" s="15">
+      <c r="S47" s="26">
         <v>0.02</v>
       </c>
-      <c r="T47" s="15">
+      <c r="T47" s="29">
         <v>1000</v>
       </c>
     </row>
@@ -4665,7 +4711,7 @@
       </c>
       <c r="K48" s="15"/>
       <c r="L48" s="15"/>
-      <c r="M48" s="15">
+      <c r="M48" s="29">
         <v>43000</v>
       </c>
       <c r="N48" s="15">
@@ -4680,13 +4726,13 @@
       <c r="Q48" s="15">
         <v>6</v>
       </c>
-      <c r="R48" s="15">
+      <c r="R48" s="23">
         <v>150</v>
       </c>
-      <c r="S48" s="15">
+      <c r="S48" s="26">
         <v>0.379411395348837</v>
       </c>
-      <c r="T48" s="15">
+      <c r="T48" s="29">
         <v>16314.69</v>
       </c>
     </row>
@@ -4721,7 +4767,7 @@
       </c>
       <c r="K49" s="15"/>
       <c r="L49" s="15"/>
-      <c r="M49" s="15">
+      <c r="M49" s="29">
         <v>65000</v>
       </c>
       <c r="N49" s="15">
@@ -4736,13 +4782,13 @@
       <c r="Q49" s="15">
         <v>2</v>
       </c>
-      <c r="R49" s="15">
+      <c r="R49" s="23">
         <v>255</v>
       </c>
-      <c r="S49" s="15">
+      <c r="S49" s="26">
         <v>9.8461538461538503E-2</v>
       </c>
-      <c r="T49" s="15">
+      <c r="T49" s="29">
         <v>6400</v>
       </c>
     </row>
@@ -4779,7 +4825,7 @@
       </c>
       <c r="K50" s="15"/>
       <c r="L50" s="15"/>
-      <c r="M50" s="15">
+      <c r="M50" s="29">
         <v>56000</v>
       </c>
       <c r="N50" s="15">
@@ -4794,13 +4840,13 @@
       <c r="Q50" s="15">
         <v>3</v>
       </c>
-      <c r="R50" s="15">
+      <c r="R50" s="23">
         <v>311.66666666666703</v>
       </c>
-      <c r="S50" s="15">
+      <c r="S50" s="26">
         <v>0</v>
       </c>
-      <c r="T50" s="15">
+      <c r="T50" s="29">
         <v>0</v>
       </c>
     </row>
@@ -4835,7 +4881,7 @@
       </c>
       <c r="K51" s="15"/>
       <c r="L51" s="15"/>
-      <c r="M51" s="15">
+      <c r="M51" s="29">
         <v>160000</v>
       </c>
       <c r="N51" s="15">
@@ -4850,13 +4896,13 @@
       <c r="Q51" s="15">
         <v>5</v>
       </c>
-      <c r="R51" s="15">
+      <c r="R51" s="23">
         <v>198.055555555555</v>
       </c>
-      <c r="S51" s="15">
+      <c r="S51" s="26">
         <v>0.48831249999999998</v>
       </c>
-      <c r="T51" s="15">
+      <c r="T51" s="29">
         <v>78130</v>
       </c>
     </row>
@@ -4891,7 +4937,7 @@
       </c>
       <c r="K52" s="15"/>
       <c r="L52" s="15"/>
-      <c r="M52" s="15">
+      <c r="M52" s="29">
         <v>33000</v>
       </c>
       <c r="N52" s="15">
@@ -4906,13 +4952,13 @@
       <c r="Q52" s="15">
         <v>6</v>
       </c>
-      <c r="R52" s="15">
+      <c r="R52" s="23">
         <v>175</v>
       </c>
-      <c r="S52" s="15">
+      <c r="S52" s="26">
         <v>0.42424242424242398</v>
       </c>
-      <c r="T52" s="15">
+      <c r="T52" s="29">
         <v>14000</v>
       </c>
     </row>
@@ -4949,7 +4995,7 @@
       </c>
       <c r="K53" s="15"/>
       <c r="L53" s="15"/>
-      <c r="M53" s="15">
+      <c r="M53" s="29">
         <v>41318</v>
       </c>
       <c r="N53" s="15">
@@ -4964,13 +5010,13 @@
       <c r="Q53" s="15">
         <v>8</v>
       </c>
-      <c r="R53" s="15">
+      <c r="R53" s="23">
         <v>186.666666666667</v>
       </c>
-      <c r="S53" s="15">
+      <c r="S53" s="26">
         <v>0.148885715668716</v>
       </c>
-      <c r="T53" s="15">
+      <c r="T53" s="29">
         <v>6151.66</v>
       </c>
     </row>
@@ -5005,7 +5051,7 @@
       </c>
       <c r="K54" s="15"/>
       <c r="L54" s="15"/>
-      <c r="M54" s="15">
+      <c r="M54" s="29">
         <v>34131</v>
       </c>
       <c r="N54" s="15">
@@ -5020,13 +5066,13 @@
       <c r="Q54" s="15">
         <v>6</v>
       </c>
-      <c r="R54" s="15">
+      <c r="R54" s="23">
         <v>175</v>
       </c>
-      <c r="S54" s="15">
+      <c r="S54" s="26">
         <v>0.61237584600509798</v>
       </c>
-      <c r="T54" s="15">
+      <c r="T54" s="29">
         <v>20901</v>
       </c>
     </row>
@@ -5063,7 +5109,7 @@
       </c>
       <c r="K55" s="15"/>
       <c r="L55" s="15"/>
-      <c r="M55" s="15">
+      <c r="M55" s="29">
         <v>48000</v>
       </c>
       <c r="N55" s="15">
@@ -5078,13 +5124,13 @@
       <c r="Q55" s="15">
         <v>6</v>
       </c>
-      <c r="R55" s="15">
+      <c r="R55" s="23">
         <v>175</v>
       </c>
-      <c r="S55" s="15">
+      <c r="S55" s="26">
         <v>0.26214583333333302</v>
       </c>
-      <c r="T55" s="15">
+      <c r="T55" s="29">
         <v>12583</v>
       </c>
     </row>
@@ -5121,7 +5167,7 @@
       </c>
       <c r="K56" s="15"/>
       <c r="L56" s="15"/>
-      <c r="M56" s="15">
+      <c r="M56" s="29">
         <v>16000</v>
       </c>
       <c r="N56" s="15">
@@ -5136,13 +5182,13 @@
       <c r="Q56" s="15">
         <v>3</v>
       </c>
-      <c r="R56" s="15">
+      <c r="R56" s="23">
         <v>197.083333333333</v>
       </c>
-      <c r="S56" s="15">
+      <c r="S56" s="26">
         <v>0.25131249999999999</v>
       </c>
-      <c r="T56" s="15">
+      <c r="T56" s="29">
         <v>4021</v>
       </c>
     </row>
@@ -5179,7 +5225,7 @@
       </c>
       <c r="K57" s="15"/>
       <c r="L57" s="15"/>
-      <c r="M57" s="15">
+      <c r="M57" s="29">
         <v>30000</v>
       </c>
       <c r="N57" s="15">
@@ -5194,13 +5240,13 @@
       <c r="Q57" s="15">
         <v>7</v>
       </c>
-      <c r="R57" s="15">
+      <c r="R57" s="23">
         <v>145</v>
       </c>
-      <c r="S57" s="15">
+      <c r="S57" s="26">
         <v>0.242352333333333</v>
       </c>
-      <c r="T57" s="15">
+      <c r="T57" s="29">
         <v>7270.57</v>
       </c>
     </row>
@@ -5237,7 +5283,7 @@
       </c>
       <c r="K58" s="15"/>
       <c r="L58" s="15"/>
-      <c r="M58" s="15">
+      <c r="M58" s="29">
         <v>56000</v>
       </c>
       <c r="N58" s="15">
@@ -5252,13 +5298,13 @@
       <c r="Q58" s="15">
         <v>7</v>
       </c>
-      <c r="R58" s="15">
+      <c r="R58" s="23">
         <v>145</v>
       </c>
-      <c r="S58" s="15">
+      <c r="S58" s="26">
         <v>0.37934464285714298</v>
       </c>
-      <c r="T58" s="15">
+      <c r="T58" s="29">
         <v>21243.3</v>
       </c>
     </row>
@@ -5295,7 +5341,7 @@
       </c>
       <c r="K59" s="15"/>
       <c r="L59" s="15"/>
-      <c r="M59" s="15">
+      <c r="M59" s="29">
         <v>43000</v>
       </c>
       <c r="N59" s="15">
@@ -5310,13 +5356,13 @@
       <c r="Q59" s="15">
         <v>3</v>
       </c>
-      <c r="R59" s="15">
+      <c r="R59" s="23">
         <v>261.25</v>
       </c>
-      <c r="S59" s="15">
+      <c r="S59" s="26">
         <v>8.6837209302325594E-2</v>
       </c>
-      <c r="T59" s="15">
+      <c r="T59" s="29">
         <v>3734</v>
       </c>
     </row>
@@ -5353,7 +5399,7 @@
       </c>
       <c r="K60" s="15"/>
       <c r="L60" s="15"/>
-      <c r="M60" s="15">
+      <c r="M60" s="29">
         <v>110000</v>
       </c>
       <c r="N60" s="15">
@@ -5368,13 +5414,13 @@
       <c r="Q60" s="15">
         <v>4</v>
       </c>
-      <c r="R60" s="15">
+      <c r="R60" s="23">
         <v>240</v>
       </c>
-      <c r="S60" s="15">
+      <c r="S60" s="26">
         <v>2.7453545454545401E-2</v>
       </c>
-      <c r="T60" s="15">
+      <c r="T60" s="29">
         <v>3019.89</v>
       </c>
     </row>
@@ -5409,7 +5455,7 @@
       </c>
       <c r="K61" s="15"/>
       <c r="L61" s="15"/>
-      <c r="M61" s="15">
+      <c r="M61" s="29">
         <v>56160</v>
       </c>
       <c r="N61" s="15">
@@ -5424,13 +5470,13 @@
       <c r="Q61" s="15">
         <v>5</v>
       </c>
-      <c r="R61" s="15">
+      <c r="R61" s="23">
         <v>266.94444444444503</v>
       </c>
-      <c r="S61" s="15">
+      <c r="S61" s="26">
         <v>7.4928774928774894E-2</v>
       </c>
-      <c r="T61" s="15">
+      <c r="T61" s="29">
         <v>4208</v>
       </c>
     </row>
@@ -5467,7 +5513,7 @@
       </c>
       <c r="K62" s="15"/>
       <c r="L62" s="15"/>
-      <c r="M62" s="15">
+      <c r="M62" s="29">
         <v>138444</v>
       </c>
       <c r="N62" s="15">
@@ -5482,13 +5528,13 @@
       <c r="Q62" s="15">
         <v>3</v>
       </c>
-      <c r="R62" s="15">
+      <c r="R62" s="23">
         <v>297.91666666666703</v>
       </c>
-      <c r="S62" s="15">
+      <c r="S62" s="26">
         <v>0.42616509202276698</v>
       </c>
-      <c r="T62" s="15">
+      <c r="T62" s="29">
         <v>59000</v>
       </c>
     </row>
@@ -5525,7 +5571,7 @@
       </c>
       <c r="K63" s="15"/>
       <c r="L63" s="15"/>
-      <c r="M63" s="15">
+      <c r="M63" s="29">
         <v>31000</v>
       </c>
       <c r="N63" s="15">
@@ -5540,13 +5586,13 @@
       <c r="Q63" s="15">
         <v>7</v>
       </c>
-      <c r="R63" s="15">
+      <c r="R63" s="23">
         <v>281.94444444444503</v>
       </c>
-      <c r="S63" s="15">
+      <c r="S63" s="26">
         <v>0.154838709677419</v>
       </c>
-      <c r="T63" s="15">
+      <c r="T63" s="29">
         <v>4800</v>
       </c>
     </row>
@@ -5583,7 +5629,7 @@
       </c>
       <c r="K64" s="15"/>
       <c r="L64" s="15"/>
-      <c r="M64" s="15">
+      <c r="M64" s="29">
         <v>120000</v>
       </c>
       <c r="N64" s="15">
@@ -5598,13 +5644,13 @@
       <c r="Q64" s="15">
         <v>4</v>
       </c>
-      <c r="R64" s="15">
+      <c r="R64" s="23">
         <v>471.11111111111097</v>
       </c>
-      <c r="S64" s="15">
+      <c r="S64" s="26">
         <v>8.7499999999999994E-2</v>
       </c>
-      <c r="T64" s="15">
+      <c r="T64" s="29">
         <v>10500</v>
       </c>
     </row>
@@ -5639,7 +5685,7 @@
       </c>
       <c r="K65" s="15"/>
       <c r="L65" s="15"/>
-      <c r="M65" s="15">
+      <c r="M65" s="29">
         <v>25900</v>
       </c>
       <c r="N65" s="15">
@@ -5654,13 +5700,13 @@
       <c r="Q65" s="15">
         <v>3</v>
       </c>
-      <c r="R65" s="15">
+      <c r="R65" s="23">
         <v>311.66666666666703</v>
       </c>
-      <c r="S65" s="15">
+      <c r="S65" s="26">
         <v>0.29289575289575298</v>
       </c>
-      <c r="T65" s="15">
+      <c r="T65" s="29">
         <v>7586</v>
       </c>
     </row>
@@ -5695,7 +5741,7 @@
       </c>
       <c r="K66" s="15"/>
       <c r="L66" s="15"/>
-      <c r="M66" s="15">
+      <c r="M66" s="29">
         <v>47986</v>
       </c>
       <c r="N66" s="15">
@@ -5710,13 +5756,13 @@
       <c r="Q66" s="15">
         <v>6</v>
       </c>
-      <c r="R66" s="15">
+      <c r="R66" s="23">
         <v>316.66666666666703</v>
       </c>
-      <c r="S66" s="15">
+      <c r="S66" s="26">
         <v>8.9609469428583305E-2</v>
       </c>
-      <c r="T66" s="15">
+      <c r="T66" s="29">
         <v>4300</v>
       </c>
     </row>
@@ -5753,7 +5799,7 @@
       </c>
       <c r="K67" s="15"/>
       <c r="L67" s="15"/>
-      <c r="M67" s="15">
+      <c r="M67" s="29">
         <v>194000</v>
       </c>
       <c r="N67" s="15">
@@ -5768,13 +5814,13 @@
       <c r="Q67" s="15">
         <v>6</v>
       </c>
-      <c r="R67" s="15">
+      <c r="R67" s="23">
         <v>416.66666666666703</v>
       </c>
-      <c r="S67" s="15">
+      <c r="S67" s="26">
         <v>8.9783505154639204E-2</v>
       </c>
-      <c r="T67" s="15">
+      <c r="T67" s="29">
         <v>17418</v>
       </c>
     </row>
@@ -5811,7 +5857,7 @@
       </c>
       <c r="K68" s="15"/>
       <c r="L68" s="15"/>
-      <c r="M68" s="15">
+      <c r="M68" s="29">
         <v>39724</v>
       </c>
       <c r="N68" s="15">
@@ -5826,13 +5872,13 @@
       <c r="Q68" s="15">
         <v>7</v>
       </c>
-      <c r="R68" s="15">
+      <c r="R68" s="23">
         <v>281.94444444444503</v>
       </c>
-      <c r="S68" s="15">
+      <c r="S68" s="26">
         <v>9.0625314671231499E-2</v>
       </c>
-      <c r="T68" s="15">
+      <c r="T68" s="29">
         <v>3600</v>
       </c>
     </row>
@@ -5867,7 +5913,7 @@
       </c>
       <c r="K69" s="15"/>
       <c r="L69" s="15"/>
-      <c r="M69" s="15">
+      <c r="M69" s="29">
         <v>48437.45</v>
       </c>
       <c r="N69" s="15">
@@ -5882,13 +5928,13 @@
       <c r="Q69" s="15">
         <v>6</v>
       </c>
-      <c r="R69" s="15">
+      <c r="R69" s="23">
         <v>266.66666666666703</v>
       </c>
-      <c r="S69" s="15">
+      <c r="S69" s="26">
         <v>7.7398789572944104E-2</v>
       </c>
-      <c r="T69" s="15">
+      <c r="T69" s="29">
         <v>3749</v>
       </c>
     </row>
@@ -5923,7 +5969,7 @@
       </c>
       <c r="K70" s="15"/>
       <c r="L70" s="15"/>
-      <c r="M70" s="15">
+      <c r="M70" s="29">
         <v>37910</v>
       </c>
       <c r="N70" s="15">
@@ -5938,13 +5984,13 @@
       <c r="Q70" s="15">
         <v>6</v>
       </c>
-      <c r="R70" s="15">
+      <c r="R70" s="23">
         <v>275</v>
       </c>
-      <c r="S70" s="15">
+      <c r="S70" s="26">
         <v>6.5945660775520998E-2</v>
       </c>
-      <c r="T70" s="15">
+      <c r="T70" s="29">
         <v>2500</v>
       </c>
     </row>
@@ -5979,7 +6025,7 @@
       </c>
       <c r="K71" s="15"/>
       <c r="L71" s="15"/>
-      <c r="M71" s="15">
+      <c r="M71" s="29">
         <v>21220</v>
       </c>
       <c r="N71" s="15">
@@ -5994,13 +6040,13 @@
       <c r="Q71" s="15">
         <v>3</v>
       </c>
-      <c r="R71" s="15">
+      <c r="R71" s="23">
         <v>513.33333333333303</v>
       </c>
-      <c r="S71" s="15">
+      <c r="S71" s="26">
         <v>0</v>
       </c>
-      <c r="T71" s="15">
+      <c r="T71" s="29">
         <v>0</v>
       </c>
     </row>
@@ -6035,7 +6081,7 @@
       </c>
       <c r="K72" s="15"/>
       <c r="L72" s="15"/>
-      <c r="M72" s="15">
+      <c r="M72" s="29">
         <v>77877</v>
       </c>
       <c r="N72" s="15">
@@ -6050,13 +6096,13 @@
       <c r="Q72" s="15">
         <v>6</v>
       </c>
-      <c r="R72" s="15">
+      <c r="R72" s="23">
         <v>350</v>
       </c>
-      <c r="S72" s="15">
+      <c r="S72" s="26">
         <v>6.42038085699244E-2</v>
       </c>
-      <c r="T72" s="15">
+      <c r="T72" s="29">
         <v>5000</v>
       </c>
     </row>
@@ -6093,7 +6139,7 @@
       </c>
       <c r="K73" s="15"/>
       <c r="L73" s="15"/>
-      <c r="M73" s="15">
+      <c r="M73" s="29">
         <v>80311.53</v>
       </c>
       <c r="N73" s="15">
@@ -6108,13 +6154,13 @@
       <c r="Q73" s="15">
         <v>5</v>
       </c>
-      <c r="R73" s="15">
+      <c r="R73" s="23">
         <v>430.55555555555497</v>
       </c>
-      <c r="S73" s="15">
+      <c r="S73" s="26">
         <v>0.110581880335239</v>
       </c>
-      <c r="T73" s="15">
+      <c r="T73" s="29">
         <v>8881</v>
       </c>
     </row>
@@ -6151,7 +6197,7 @@
       </c>
       <c r="K74" s="15"/>
       <c r="L74" s="15"/>
-      <c r="M74" s="15">
+      <c r="M74" s="29">
         <v>38000</v>
       </c>
       <c r="N74" s="15">
@@ -6166,13 +6212,13 @@
       <c r="Q74" s="15">
         <v>6</v>
       </c>
-      <c r="R74" s="15">
+      <c r="R74" s="23">
         <v>350</v>
       </c>
-      <c r="S74" s="15">
+      <c r="S74" s="26">
         <v>0.34210526315789502</v>
       </c>
-      <c r="T74" s="15">
+      <c r="T74" s="29">
         <v>13000</v>
       </c>
     </row>
@@ -6207,7 +6253,7 @@
       </c>
       <c r="K75" s="15"/>
       <c r="L75" s="15"/>
-      <c r="M75" s="15">
+      <c r="M75" s="29">
         <v>37800</v>
       </c>
       <c r="N75" s="15">
@@ -6222,13 +6268,13 @@
       <c r="Q75" s="15">
         <v>5</v>
       </c>
-      <c r="R75" s="15">
+      <c r="R75" s="23">
         <v>387.5</v>
       </c>
-      <c r="S75" s="15">
+      <c r="S75" s="26">
         <v>0</v>
       </c>
-      <c r="T75" s="15">
+      <c r="T75" s="29">
         <v>0</v>
       </c>
     </row>
@@ -6265,7 +6311,7 @@
       </c>
       <c r="K76" s="15"/>
       <c r="L76" s="15"/>
-      <c r="M76" s="15">
+      <c r="M76" s="29">
         <v>54581</v>
       </c>
       <c r="N76" s="15">
@@ -6280,13 +6326,13 @@
       <c r="Q76" s="15">
         <v>6</v>
       </c>
-      <c r="R76" s="15">
+      <c r="R76" s="23">
         <v>350</v>
       </c>
-      <c r="S76" s="15">
+      <c r="S76" s="26">
         <v>5.7840640515930401E-2</v>
       </c>
-      <c r="T76" s="15">
+      <c r="T76" s="29">
         <v>3157</v>
       </c>
     </row>
@@ -6323,7 +6369,7 @@
       </c>
       <c r="K77" s="15"/>
       <c r="L77" s="15"/>
-      <c r="M77" s="15">
+      <c r="M77" s="29">
         <v>25000</v>
       </c>
       <c r="N77" s="15">
@@ -6338,13 +6384,13 @@
       <c r="Q77" s="15">
         <v>7</v>
       </c>
-      <c r="R77" s="15">
+      <c r="R77" s="23">
         <v>362.5</v>
       </c>
-      <c r="S77" s="15">
+      <c r="S77" s="26">
         <v>0.38147999999999999</v>
       </c>
-      <c r="T77" s="15">
+      <c r="T77" s="29">
         <v>9537</v>
       </c>
     </row>
@@ -6381,7 +6427,7 @@
       </c>
       <c r="K78" s="15"/>
       <c r="L78" s="15"/>
-      <c r="M78" s="15">
+      <c r="M78" s="29">
         <v>52698</v>
       </c>
       <c r="N78" s="15">
@@ -6396,13 +6442,13 @@
       <c r="Q78" s="15">
         <v>3</v>
       </c>
-      <c r="R78" s="15">
+      <c r="R78" s="23">
         <v>540.83333333333303</v>
       </c>
-      <c r="S78" s="15">
+      <c r="S78" s="26">
         <v>6.4518577555125398E-2</v>
       </c>
-      <c r="T78" s="15">
+      <c r="T78" s="29">
         <v>3400</v>
       </c>
     </row>
@@ -6437,7 +6483,7 @@
       </c>
       <c r="K79" s="15"/>
       <c r="L79" s="15"/>
-      <c r="M79" s="15">
+      <c r="M79" s="29">
         <v>38500</v>
       </c>
       <c r="N79" s="15">
@@ -6452,13 +6498,13 @@
       <c r="Q79" s="15">
         <v>3</v>
       </c>
-      <c r="R79" s="15">
+      <c r="R79" s="23">
         <v>210.833333333333</v>
       </c>
-      <c r="S79" s="15">
+      <c r="S79" s="26">
         <v>0.22270129870129901</v>
       </c>
-      <c r="T79" s="15">
+      <c r="T79" s="29">
         <v>8574</v>
       </c>
     </row>
@@ -6493,7 +6539,7 @@
       </c>
       <c r="K80" s="15"/>
       <c r="L80" s="15"/>
-      <c r="M80" s="15">
+      <c r="M80" s="29">
         <v>27200</v>
       </c>
       <c r="N80" s="15">
@@ -6508,13 +6554,13 @@
       <c r="Q80" s="15">
         <v>4</v>
       </c>
-      <c r="R80" s="15">
+      <c r="R80" s="23">
         <v>195.555555555555</v>
       </c>
-      <c r="S80" s="15">
+      <c r="S80" s="26">
         <v>0.26286764705882298</v>
       </c>
-      <c r="T80" s="15">
+      <c r="T80" s="29">
         <v>7150</v>
       </c>
     </row>
@@ -6551,7 +6597,7 @@
       </c>
       <c r="K81" s="15"/>
       <c r="L81" s="15"/>
-      <c r="M81" s="15">
+      <c r="M81" s="29">
         <v>60000</v>
       </c>
       <c r="N81" s="15">
@@ -6566,13 +6612,13 @@
       <c r="Q81" s="15">
         <v>6</v>
       </c>
-      <c r="R81" s="15">
+      <c r="R81" s="23">
         <v>200</v>
       </c>
-      <c r="S81" s="15">
+      <c r="S81" s="26">
         <v>0.320583333333333</v>
       </c>
-      <c r="T81" s="15">
+      <c r="T81" s="29">
         <v>19235</v>
       </c>
     </row>
@@ -6609,7 +6655,7 @@
       </c>
       <c r="K82" s="15"/>
       <c r="L82" s="15"/>
-      <c r="M82" s="15">
+      <c r="M82" s="29">
         <v>50000</v>
       </c>
       <c r="N82" s="15">
@@ -6624,13 +6670,13 @@
       <c r="Q82" s="15">
         <v>4</v>
       </c>
-      <c r="R82" s="15">
+      <c r="R82" s="23">
         <v>195.555555555555</v>
       </c>
-      <c r="S82" s="15">
+      <c r="S82" s="26">
         <v>0.15</v>
       </c>
-      <c r="T82" s="15">
+      <c r="T82" s="29">
         <v>7500</v>
       </c>
     </row>
@@ -6667,7 +6713,7 @@
       </c>
       <c r="K83" s="15"/>
       <c r="L83" s="15"/>
-      <c r="M83" s="15">
+      <c r="M83" s="29">
         <v>131575</v>
       </c>
       <c r="N83" s="15">
@@ -6682,13 +6728,13 @@
       <c r="Q83" s="15">
         <v>4</v>
       </c>
-      <c r="R83" s="15">
+      <c r="R83" s="23">
         <v>204.444444444445</v>
       </c>
-      <c r="S83" s="15">
+      <c r="S83" s="26">
         <v>7.6002280068402095E-2</v>
       </c>
-      <c r="T83" s="15">
+      <c r="T83" s="29">
         <v>10000</v>
       </c>
     </row>
@@ -6725,7 +6771,7 @@
       </c>
       <c r="K84" s="15"/>
       <c r="L84" s="15"/>
-      <c r="M84" s="15">
+      <c r="M84" s="29">
         <v>99500</v>
       </c>
       <c r="N84" s="15">
@@ -6740,13 +6786,13 @@
       <c r="Q84" s="15">
         <v>4</v>
       </c>
-      <c r="R84" s="15">
+      <c r="R84" s="23">
         <v>195.555555555555</v>
       </c>
-      <c r="S84" s="15">
+      <c r="S84" s="26">
         <v>0.23086432160803999</v>
       </c>
-      <c r="T84" s="15">
+      <c r="T84" s="29">
         <v>22971</v>
       </c>
     </row>
@@ -6781,7 +6827,7 @@
       </c>
       <c r="K85" s="15"/>
       <c r="L85" s="15"/>
-      <c r="M85" s="15">
+      <c r="M85" s="29">
         <v>32000</v>
       </c>
       <c r="N85" s="15">
@@ -6796,13 +6842,13 @@
       <c r="Q85" s="15">
         <v>8</v>
       </c>
-      <c r="R85" s="15">
+      <c r="R85" s="23">
         <v>178.888888888889</v>
       </c>
-      <c r="S85" s="15">
+      <c r="S85" s="26">
         <v>0.11874999999999999</v>
       </c>
-      <c r="T85" s="15">
+      <c r="T85" s="29">
         <v>3800</v>
       </c>
     </row>
@@ -6839,7 +6885,7 @@
       </c>
       <c r="K86" s="15"/>
       <c r="L86" s="15"/>
-      <c r="M86" s="15">
+      <c r="M86" s="29">
         <v>52170</v>
       </c>
       <c r="N86" s="15">
@@ -6854,13 +6900,13 @@
       <c r="Q86" s="15">
         <v>6</v>
       </c>
-      <c r="R86" s="15">
+      <c r="R86" s="23">
         <v>208.333333333333</v>
       </c>
-      <c r="S86" s="15">
+      <c r="S86" s="26">
         <v>0.156009200690052</v>
       </c>
-      <c r="T86" s="15">
+      <c r="T86" s="29">
         <v>8139</v>
       </c>
     </row>
@@ -6895,7 +6941,7 @@
       </c>
       <c r="K87" s="15"/>
       <c r="L87" s="15"/>
-      <c r="M87" s="15">
+      <c r="M87" s="29">
         <v>46000</v>
       </c>
       <c r="N87" s="15">
@@ -6910,13 +6956,13 @@
       <c r="Q87" s="15">
         <v>8</v>
       </c>
-      <c r="R87" s="15">
+      <c r="R87" s="23">
         <v>186.666666666667</v>
       </c>
-      <c r="S87" s="15">
+      <c r="S87" s="26">
         <v>0.102173913043478</v>
       </c>
-      <c r="T87" s="15">
+      <c r="T87" s="29">
         <v>4700</v>
       </c>
     </row>
@@ -6953,7 +6999,7 @@
       </c>
       <c r="K88" s="15"/>
       <c r="L88" s="15"/>
-      <c r="M88" s="15">
+      <c r="M88" s="29">
         <v>45013</v>
       </c>
       <c r="N88" s="15">
@@ -6968,13 +7014,13 @@
       <c r="Q88" s="15">
         <v>3</v>
       </c>
-      <c r="R88" s="15">
+      <c r="R88" s="23">
         <v>206.25</v>
       </c>
-      <c r="S88" s="15">
+      <c r="S88" s="26">
         <v>0.13995956723613201</v>
       </c>
-      <c r="T88" s="15">
+      <c r="T88" s="29">
         <v>6300</v>
       </c>
     </row>
@@ -7009,7 +7055,7 @@
       </c>
       <c r="K89" s="15"/>
       <c r="L89" s="15"/>
-      <c r="M89" s="15">
+      <c r="M89" s="29">
         <v>48566</v>
       </c>
       <c r="N89" s="15">
@@ -7024,13 +7070,13 @@
       <c r="Q89" s="15">
         <v>3</v>
       </c>
-      <c r="R89" s="15">
+      <c r="R89" s="23">
         <v>220</v>
       </c>
-      <c r="S89" s="15">
+      <c r="S89" s="26">
         <v>0.76040851624593297</v>
       </c>
-      <c r="T89" s="15">
+      <c r="T89" s="29">
         <v>36930</v>
       </c>
     </row>
@@ -7065,7 +7111,7 @@
       </c>
       <c r="K90" s="15"/>
       <c r="L90" s="15"/>
-      <c r="M90" s="15">
+      <c r="M90" s="29">
         <v>55618</v>
       </c>
       <c r="N90" s="15">
@@ -7080,13 +7126,13 @@
       <c r="Q90" s="15">
         <v>3</v>
       </c>
-      <c r="R90" s="15">
+      <c r="R90" s="23">
         <v>238.333333333333</v>
       </c>
-      <c r="S90" s="15">
+      <c r="S90" s="26">
         <v>0.2</v>
       </c>
-      <c r="T90" s="15">
+      <c r="T90" s="29">
         <v>11123.6</v>
       </c>
     </row>
@@ -7121,7 +7167,7 @@
       </c>
       <c r="K91" s="15"/>
       <c r="L91" s="15"/>
-      <c r="M91" s="15">
+      <c r="M91" s="29">
         <v>47000</v>
       </c>
       <c r="N91" s="15">
@@ -7136,13 +7182,13 @@
       <c r="Q91" s="15">
         <v>3</v>
       </c>
-      <c r="R91" s="15">
+      <c r="R91" s="23">
         <v>229.166666666667</v>
       </c>
-      <c r="S91" s="15">
+      <c r="S91" s="26">
         <v>4.0382978723404302E-2</v>
       </c>
-      <c r="T91" s="15">
+      <c r="T91" s="29">
         <v>1898</v>
       </c>
     </row>
@@ -7179,7 +7225,7 @@
       </c>
       <c r="K92" s="15"/>
       <c r="L92" s="15"/>
-      <c r="M92" s="15">
+      <c r="M92" s="29">
         <v>87763</v>
       </c>
       <c r="N92" s="15">
@@ -7194,13 +7240,13 @@
       <c r="Q92" s="15">
         <v>4</v>
       </c>
-      <c r="R92" s="15">
+      <c r="R92" s="23">
         <v>177.777777777778</v>
       </c>
-      <c r="S92" s="15">
+      <c r="S92" s="26">
         <v>0.227886466962159</v>
       </c>
-      <c r="T92" s="15">
+      <c r="T92" s="29">
         <v>20000</v>
       </c>
     </row>
@@ -7237,7 +7283,7 @@
       </c>
       <c r="K93" s="15"/>
       <c r="L93" s="15"/>
-      <c r="M93" s="15">
+      <c r="M93" s="29">
         <v>100658</v>
       </c>
       <c r="N93" s="15">
@@ -7252,13 +7298,13 @@
       <c r="Q93" s="15">
         <v>4</v>
       </c>
-      <c r="R93" s="15">
+      <c r="R93" s="23">
         <v>275.55555555555497</v>
       </c>
-      <c r="S93" s="15">
+      <c r="S93" s="26">
         <v>0.33777742454648402</v>
       </c>
-      <c r="T93" s="15">
+      <c r="T93" s="29">
         <v>34000</v>
       </c>
     </row>
@@ -7295,7 +7341,7 @@
       </c>
       <c r="K94" s="15"/>
       <c r="L94" s="15"/>
-      <c r="M94" s="15">
+      <c r="M94" s="29">
         <v>67000</v>
       </c>
       <c r="N94" s="15">
@@ -7310,13 +7356,13 @@
       <c r="Q94" s="15">
         <v>5</v>
       </c>
-      <c r="R94" s="15">
+      <c r="R94" s="23">
         <v>206.666666666667</v>
       </c>
-      <c r="S94" s="15">
+      <c r="S94" s="26">
         <v>0.178820895522388</v>
       </c>
-      <c r="T94" s="15">
+      <c r="T94" s="29">
         <v>11981</v>
       </c>
     </row>
@@ -7353,7 +7399,7 @@
       </c>
       <c r="K95" s="15"/>
       <c r="L95" s="15"/>
-      <c r="M95" s="15">
+      <c r="M95" s="29">
         <v>39431</v>
       </c>
       <c r="N95" s="15">
@@ -7368,13 +7414,13 @@
       <c r="Q95" s="15">
         <v>6</v>
       </c>
-      <c r="R95" s="15">
+      <c r="R95" s="23">
         <v>216.666666666667</v>
       </c>
-      <c r="S95" s="15">
+      <c r="S95" s="26">
         <v>0.30432908117978202</v>
       </c>
-      <c r="T95" s="15">
+      <c r="T95" s="29">
         <v>12000</v>
       </c>
     </row>
@@ -7409,7 +7455,7 @@
       </c>
       <c r="K96" s="15"/>
       <c r="L96" s="15"/>
-      <c r="M96" s="15">
+      <c r="M96" s="29">
         <v>34273</v>
       </c>
       <c r="N96" s="15">
@@ -7424,13 +7470,13 @@
       <c r="Q96" s="15">
         <v>6</v>
       </c>
-      <c r="R96" s="15">
+      <c r="R96" s="23">
         <v>166.666666666667</v>
       </c>
-      <c r="S96" s="15">
+      <c r="S96" s="26">
         <v>0.145887433256499</v>
       </c>
-      <c r="T96" s="15">
+      <c r="T96" s="29">
         <v>5000</v>
       </c>
     </row>
@@ -7465,7 +7511,7 @@
       </c>
       <c r="K97" s="15"/>
       <c r="L97" s="15"/>
-      <c r="M97" s="15">
+      <c r="M97" s="29">
         <v>40000</v>
       </c>
       <c r="N97" s="15">
@@ -7480,13 +7526,13 @@
       <c r="Q97" s="15">
         <v>0</v>
       </c>
-      <c r="R97" s="15">
+      <c r="R97" s="23">
         <v>200</v>
       </c>
-      <c r="S97" s="15">
+      <c r="S97" s="26">
         <v>1</v>
       </c>
-      <c r="T97" s="15">
+      <c r="T97" s="29">
         <v>40000</v>
       </c>
     </row>
@@ -7523,7 +7569,7 @@
       </c>
       <c r="K98" s="15"/>
       <c r="L98" s="15"/>
-      <c r="M98" s="15">
+      <c r="M98" s="29">
         <v>65000</v>
       </c>
       <c r="N98" s="15">
@@ -7538,13 +7584,13 @@
       <c r="Q98" s="15">
         <v>7</v>
       </c>
-      <c r="R98" s="15">
+      <c r="R98" s="23">
         <v>201.388888888889</v>
       </c>
-      <c r="S98" s="15">
+      <c r="S98" s="26">
         <v>0.480738461538462</v>
       </c>
-      <c r="T98" s="15">
+      <c r="T98" s="29">
         <v>31248</v>
       </c>
     </row>
@@ -7581,7 +7627,7 @@
       </c>
       <c r="K99" s="15"/>
       <c r="L99" s="15"/>
-      <c r="M99" s="15">
+      <c r="M99" s="29">
         <v>49000</v>
       </c>
       <c r="N99" s="15">
@@ -7596,13 +7642,13 @@
       <c r="Q99" s="15">
         <v>5</v>
       </c>
-      <c r="R99" s="15">
+      <c r="R99" s="23">
         <v>335.83333333333297</v>
       </c>
-      <c r="S99" s="15">
+      <c r="S99" s="26">
         <v>0.24397959183673501</v>
       </c>
-      <c r="T99" s="15">
+      <c r="T99" s="29">
         <v>11955</v>
       </c>
     </row>
@@ -7639,7 +7685,7 @@
       </c>
       <c r="K100" s="15"/>
       <c r="L100" s="15"/>
-      <c r="M100" s="15">
+      <c r="M100" s="29">
         <v>95000</v>
       </c>
       <c r="N100" s="15">
@@ -7654,13 +7700,13 @@
       <c r="Q100" s="15">
         <v>5</v>
       </c>
-      <c r="R100" s="15">
+      <c r="R100" s="23">
         <v>335.83333333333297</v>
       </c>
-      <c r="S100" s="15">
+      <c r="S100" s="26">
         <v>0.123347368421053</v>
       </c>
-      <c r="T100" s="15">
+      <c r="T100" s="29">
         <v>11718</v>
       </c>
     </row>
@@ -7697,7 +7743,7 @@
       </c>
       <c r="K101" s="15"/>
       <c r="L101" s="15"/>
-      <c r="M101" s="15">
+      <c r="M101" s="29">
         <v>45000</v>
       </c>
       <c r="N101" s="15">
@@ -7712,13 +7758,13 @@
       <c r="Q101" s="15">
         <v>5</v>
       </c>
-      <c r="R101" s="15">
+      <c r="R101" s="23">
         <v>241.111111111111</v>
       </c>
-      <c r="S101" s="15">
+      <c r="S101" s="26">
         <v>0.31568888888888902</v>
       </c>
-      <c r="T101" s="15">
+      <c r="T101" s="29">
         <v>14206</v>
       </c>
     </row>
@@ -7753,7 +7799,7 @@
       </c>
       <c r="K102" s="15"/>
       <c r="L102" s="15"/>
-      <c r="M102" s="15">
+      <c r="M102" s="29">
         <v>124500</v>
       </c>
       <c r="N102" s="15">
@@ -7768,13 +7814,13 @@
       <c r="Q102" s="15">
         <v>5</v>
       </c>
-      <c r="R102" s="15">
+      <c r="R102" s="23">
         <v>172.222222222222</v>
       </c>
-      <c r="S102" s="15">
+      <c r="S102" s="26">
         <v>5.62489959839357E-2</v>
       </c>
-      <c r="T102" s="15">
+      <c r="T102" s="29">
         <v>7003</v>
       </c>
     </row>
@@ -7809,7 +7855,7 @@
       </c>
       <c r="K103" s="15"/>
       <c r="L103" s="15"/>
-      <c r="M103" s="15">
+      <c r="M103" s="29">
         <v>64000</v>
       </c>
       <c r="N103" s="15">
@@ -7824,13 +7870,13 @@
       <c r="Q103" s="15">
         <v>6</v>
       </c>
-      <c r="R103" s="15">
+      <c r="R103" s="23">
         <v>183.333333333333</v>
       </c>
-      <c r="S103" s="15">
+      <c r="S103" s="26">
         <v>9.1593750000000002E-2</v>
       </c>
-      <c r="T103" s="15">
+      <c r="T103" s="29">
         <v>5862</v>
       </c>
     </row>
@@ -7865,7 +7911,7 @@
       </c>
       <c r="K104" s="15"/>
       <c r="L104" s="15"/>
-      <c r="M104" s="15">
+      <c r="M104" s="29">
         <v>25000</v>
       </c>
       <c r="N104" s="15">
@@ -7880,13 +7926,13 @@
       <c r="Q104" s="15">
         <v>3</v>
       </c>
-      <c r="R104" s="15">
+      <c r="R104" s="23">
         <v>284.16666666666703</v>
       </c>
-      <c r="S104" s="15">
+      <c r="S104" s="26">
         <v>0</v>
       </c>
-      <c r="T104" s="15">
+      <c r="T104" s="29">
         <v>0</v>
       </c>
     </row>
@@ -7921,7 +7967,7 @@
       </c>
       <c r="K105" s="15"/>
       <c r="L105" s="15"/>
-      <c r="M105" s="15">
+      <c r="M105" s="29">
         <v>38498</v>
       </c>
       <c r="N105" s="15">
@@ -7936,13 +7982,13 @@
       <c r="Q105" s="15">
         <v>4</v>
       </c>
-      <c r="R105" s="15">
+      <c r="R105" s="23">
         <v>177.777777777778</v>
       </c>
-      <c r="S105" s="15">
+      <c r="S105" s="26">
         <v>3.1404228791106002E-3</v>
       </c>
-      <c r="T105" s="15">
+      <c r="T105" s="29">
         <v>120.9</v>
       </c>
     </row>
@@ -7977,7 +8023,7 @@
       </c>
       <c r="K106" s="15"/>
       <c r="L106" s="15"/>
-      <c r="M106" s="15">
+      <c r="M106" s="29">
         <v>166433</v>
       </c>
       <c r="N106" s="15">
@@ -7992,13 +8038,13 @@
       <c r="Q106" s="15">
         <v>4</v>
       </c>
-      <c r="R106" s="15">
+      <c r="R106" s="23">
         <v>186.666666666667</v>
       </c>
-      <c r="S106" s="15">
+      <c r="S106" s="26">
         <v>0.13939543239621899</v>
       </c>
-      <c r="T106" s="15">
+      <c r="T106" s="29">
         <v>23200</v>
       </c>
     </row>
@@ -8035,7 +8081,7 @@
       </c>
       <c r="K107" s="15"/>
       <c r="L107" s="15"/>
-      <c r="M107" s="15">
+      <c r="M107" s="29">
         <v>58000</v>
       </c>
       <c r="N107" s="15">
@@ -8050,13 +8096,13 @@
       <c r="Q107" s="15">
         <v>4</v>
       </c>
-      <c r="R107" s="15">
+      <c r="R107" s="23">
         <v>373.33333333333297</v>
       </c>
-      <c r="S107" s="15">
+      <c r="S107" s="26">
         <v>2.5862068965517199E-2</v>
       </c>
-      <c r="T107" s="15">
+      <c r="T107" s="29">
         <v>1500</v>
       </c>
     </row>
@@ -8091,7 +8137,7 @@
       </c>
       <c r="K108" s="15"/>
       <c r="L108" s="15"/>
-      <c r="M108" s="15">
+      <c r="M108" s="29">
         <v>51872</v>
       </c>
       <c r="N108" s="15">
@@ -8106,13 +8152,13 @@
       <c r="Q108" s="15">
         <v>3</v>
       </c>
-      <c r="R108" s="15">
+      <c r="R108" s="23">
         <v>302.5</v>
       </c>
-      <c r="S108" s="15">
+      <c r="S108" s="26">
         <v>0</v>
       </c>
-      <c r="T108" s="15">
+      <c r="T108" s="29">
         <v>0</v>
       </c>
     </row>
@@ -8147,7 +8193,7 @@
       </c>
       <c r="K109" s="15"/>
       <c r="L109" s="15"/>
-      <c r="M109" s="15">
+      <c r="M109" s="29">
         <v>21632</v>
       </c>
       <c r="N109" s="15">
@@ -8162,13 +8208,13 @@
       <c r="Q109" s="15">
         <v>2</v>
       </c>
-      <c r="R109" s="15">
+      <c r="R109" s="23">
         <v>229.5</v>
       </c>
-      <c r="S109" s="15">
+      <c r="S109" s="26">
         <v>0</v>
       </c>
-      <c r="T109" s="15">
+      <c r="T109" s="29">
         <v>0</v>
       </c>
     </row>
@@ -8203,7 +8249,7 @@
       </c>
       <c r="K110" s="15"/>
       <c r="L110" s="15"/>
-      <c r="M110" s="15">
+      <c r="M110" s="29">
         <v>69000</v>
       </c>
       <c r="N110" s="15">
@@ -8218,13 +8264,13 @@
       <c r="Q110" s="15">
         <v>4</v>
       </c>
-      <c r="R110" s="15">
+      <c r="R110" s="23">
         <v>186.666666666667</v>
       </c>
-      <c r="S110" s="15">
+      <c r="S110" s="26">
         <v>0.22942028985507301</v>
       </c>
-      <c r="T110" s="15">
+      <c r="T110" s="29">
         <v>15830</v>
       </c>
     </row>
@@ -8259,7 +8305,7 @@
       </c>
       <c r="K111" s="15"/>
       <c r="L111" s="15"/>
-      <c r="M111" s="15">
+      <c r="M111" s="29">
         <v>54000</v>
       </c>
       <c r="N111" s="15">
@@ -8274,13 +8320,13 @@
       <c r="Q111" s="15">
         <v>4</v>
       </c>
-      <c r="R111" s="15">
+      <c r="R111" s="23">
         <v>151.111111111111</v>
       </c>
-      <c r="S111" s="15">
+      <c r="S111" s="26">
         <v>0.36928703703703702</v>
       </c>
-      <c r="T111" s="15">
+      <c r="T111" s="29">
         <v>19941.5</v>
       </c>
     </row>
@@ -8317,7 +8363,7 @@
       </c>
       <c r="K112" s="15"/>
       <c r="L112" s="15"/>
-      <c r="M112" s="15">
+      <c r="M112" s="29">
         <v>57400</v>
       </c>
       <c r="N112" s="15">
@@ -8332,13 +8378,13 @@
       <c r="Q112" s="15">
         <v>8</v>
       </c>
-      <c r="R112" s="15">
+      <c r="R112" s="23">
         <v>280</v>
       </c>
-      <c r="S112" s="15">
+      <c r="S112" s="26">
         <v>1.74216027874564E-2</v>
       </c>
-      <c r="T112" s="15">
+      <c r="T112" s="29">
         <v>1000</v>
       </c>
     </row>
@@ -8375,7 +8421,7 @@
       </c>
       <c r="K113" s="15"/>
       <c r="L113" s="15"/>
-      <c r="M113" s="15">
+      <c r="M113" s="29">
         <v>60000</v>
       </c>
       <c r="N113" s="15">
@@ -8390,13 +8436,13 @@
       <c r="Q113" s="15">
         <v>5</v>
       </c>
-      <c r="R113" s="15">
+      <c r="R113" s="23">
         <v>284.16666666666703</v>
       </c>
-      <c r="S113" s="15">
+      <c r="S113" s="26">
         <v>7.1166666666666696E-3</v>
       </c>
-      <c r="T113" s="15">
+      <c r="T113" s="29">
         <v>427</v>
       </c>
     </row>
@@ -8433,7 +8479,7 @@
       </c>
       <c r="K114" s="15"/>
       <c r="L114" s="15"/>
-      <c r="M114" s="15">
+      <c r="M114" s="29">
         <v>60000</v>
       </c>
       <c r="N114" s="15">
@@ -8448,13 +8494,13 @@
       <c r="Q114" s="15">
         <v>2</v>
       </c>
-      <c r="R114" s="15">
+      <c r="R114" s="23">
         <v>231.388888888889</v>
       </c>
-      <c r="S114" s="15">
+      <c r="S114" s="26">
         <v>0.19166666666666701</v>
       </c>
-      <c r="T114" s="15">
+      <c r="T114" s="29">
         <v>11500</v>
       </c>
     </row>
@@ -8489,7 +8535,7 @@
       </c>
       <c r="K115" s="15"/>
       <c r="L115" s="15"/>
-      <c r="M115" s="15">
+      <c r="M115" s="29">
         <v>33000</v>
       </c>
       <c r="N115" s="15">
@@ -8504,13 +8550,13 @@
       <c r="Q115" s="15">
         <v>3</v>
       </c>
-      <c r="R115" s="15">
+      <c r="R115" s="23">
         <v>311.66666666666703</v>
       </c>
-      <c r="S115" s="15">
+      <c r="S115" s="26">
         <v>0</v>
       </c>
-      <c r="T115" s="15">
+      <c r="T115" s="29">
         <v>0</v>
       </c>
     </row>
@@ -8545,7 +8591,7 @@
       </c>
       <c r="K116" s="15"/>
       <c r="L116" s="15"/>
-      <c r="M116" s="15">
+      <c r="M116" s="29">
         <v>88786</v>
       </c>
       <c r="N116" s="15">
@@ -8560,13 +8606,13 @@
       <c r="Q116" s="15">
         <v>5</v>
       </c>
-      <c r="R116" s="15">
+      <c r="R116" s="23">
         <v>180.833333333333</v>
       </c>
-      <c r="S116" s="15">
+      <c r="S116" s="26">
         <v>0.23652377627103399</v>
       </c>
-      <c r="T116" s="15">
+      <c r="T116" s="29">
         <v>21000</v>
       </c>
     </row>
@@ -8601,7 +8647,7 @@
       </c>
       <c r="K117" s="15"/>
       <c r="L117" s="15"/>
-      <c r="M117" s="15">
+      <c r="M117" s="29">
         <v>134000</v>
       </c>
       <c r="N117" s="15">
@@ -8616,13 +8662,13 @@
       <c r="Q117" s="15">
         <v>5</v>
       </c>
-      <c r="R117" s="15">
+      <c r="R117" s="23">
         <v>193.75</v>
       </c>
-      <c r="S117" s="15">
+      <c r="S117" s="26">
         <v>0.23798507462686599</v>
       </c>
-      <c r="T117" s="15">
+      <c r="T117" s="29">
         <v>31890</v>
       </c>
     </row>
@@ -8657,7 +8703,7 @@
       </c>
       <c r="K118" s="15"/>
       <c r="L118" s="15"/>
-      <c r="M118" s="15">
+      <c r="M118" s="29">
         <v>35000</v>
       </c>
       <c r="N118" s="15">
@@ -8672,13 +8718,13 @@
       <c r="Q118" s="15">
         <v>6</v>
       </c>
-      <c r="R118" s="15">
+      <c r="R118" s="23">
         <v>225</v>
       </c>
-      <c r="S118" s="15">
+      <c r="S118" s="26">
         <v>3.1885714285714302E-2</v>
       </c>
-      <c r="T118" s="15">
+      <c r="T118" s="29">
         <v>1116</v>
       </c>
     </row>
@@ -8713,7 +8759,7 @@
       </c>
       <c r="K119" s="15"/>
       <c r="L119" s="15"/>
-      <c r="M119" s="15">
+      <c r="M119" s="29">
         <v>18000</v>
       </c>
       <c r="N119" s="15">
@@ -8728,13 +8774,13 @@
       <c r="Q119" s="15">
         <v>5</v>
       </c>
-      <c r="R119" s="15">
+      <c r="R119" s="23">
         <v>232.5</v>
       </c>
-      <c r="S119" s="15">
+      <c r="S119" s="26">
         <v>0</v>
       </c>
-      <c r="T119" s="15">
+      <c r="T119" s="29">
         <v>0</v>
       </c>
     </row>
@@ -8771,7 +8817,7 @@
       </c>
       <c r="K120" s="15"/>
       <c r="L120" s="15"/>
-      <c r="M120" s="15">
+      <c r="M120" s="29">
         <v>105741</v>
       </c>
       <c r="N120" s="15">
@@ -8786,13 +8832,13 @@
       <c r="Q120" s="15">
         <v>5</v>
       </c>
-      <c r="R120" s="15">
+      <c r="R120" s="23">
         <v>172.222222222222</v>
       </c>
-      <c r="S120" s="15">
+      <c r="S120" s="26">
         <v>5.2959589941460702E-2</v>
       </c>
-      <c r="T120" s="15">
+      <c r="T120" s="29">
         <v>5600</v>
       </c>
     </row>
@@ -8829,7 +8875,7 @@
       </c>
       <c r="K121" s="15"/>
       <c r="L121" s="15"/>
-      <c r="M121" s="15">
+      <c r="M121" s="29">
         <v>51000</v>
       </c>
       <c r="N121" s="15">
@@ -8844,13 +8890,13 @@
       <c r="Q121" s="15">
         <v>6</v>
       </c>
-      <c r="R121" s="15">
+      <c r="R121" s="23">
         <v>250</v>
       </c>
-      <c r="S121" s="15">
+      <c r="S121" s="26">
         <v>0</v>
       </c>
-      <c r="T121" s="15">
+      <c r="T121" s="29">
         <v>0</v>
       </c>
     </row>
@@ -8887,7 +8933,7 @@
       </c>
       <c r="K122" s="15"/>
       <c r="L122" s="15"/>
-      <c r="M122" s="15">
+      <c r="M122" s="29">
         <v>130143</v>
       </c>
       <c r="N122" s="15">
@@ -8902,13 +8948,13 @@
       <c r="Q122" s="15">
         <v>6</v>
       </c>
-      <c r="R122" s="15">
+      <c r="R122" s="23">
         <v>125</v>
       </c>
-      <c r="S122" s="15">
+      <c r="S122" s="26">
         <v>0.27661879624720498</v>
       </c>
-      <c r="T122" s="15">
+      <c r="T122" s="29">
         <v>36000</v>
       </c>
     </row>
@@ -8941,7 +8987,7 @@
       </c>
       <c r="K123" s="15"/>
       <c r="L123" s="15"/>
-      <c r="M123" s="15">
+      <c r="M123" s="29">
         <v>121551.47</v>
       </c>
       <c r="N123" s="15"/>
@@ -8954,13 +9000,13 @@
       <c r="Q123" s="15">
         <v>4</v>
       </c>
-      <c r="R123" s="15">
+      <c r="R123" s="23">
         <v>151.111111111111</v>
       </c>
-      <c r="S123" s="15">
+      <c r="S123" s="26">
         <v>0.800701710970669</v>
       </c>
-      <c r="T123" s="15">
+      <c r="T123" s="29">
         <v>97326.47</v>
       </c>
     </row>
@@ -8997,7 +9043,7 @@
       </c>
       <c r="K124" s="15"/>
       <c r="L124" s="15"/>
-      <c r="M124" s="15">
+      <c r="M124" s="29">
         <v>110000</v>
       </c>
       <c r="N124" s="15">
@@ -9012,13 +9058,13 @@
       <c r="Q124" s="15">
         <v>6</v>
       </c>
-      <c r="R124" s="15">
+      <c r="R124" s="23">
         <v>170.833333333333</v>
       </c>
-      <c r="S124" s="15">
+      <c r="S124" s="26">
         <v>0.14505645454545399</v>
       </c>
-      <c r="T124" s="15">
+      <c r="T124" s="29">
         <v>15956.21</v>
       </c>
     </row>
@@ -9055,7 +9101,7 @@
       </c>
       <c r="K125" s="15"/>
       <c r="L125" s="15"/>
-      <c r="M125" s="15">
+      <c r="M125" s="29">
         <v>56000</v>
       </c>
       <c r="N125" s="15">
@@ -9070,13 +9116,13 @@
       <c r="Q125" s="15">
         <v>6</v>
       </c>
-      <c r="R125" s="15">
+      <c r="R125" s="23">
         <v>154.166666666667</v>
       </c>
-      <c r="S125" s="15">
+      <c r="S125" s="26">
         <v>0.11841071428571399</v>
       </c>
-      <c r="T125" s="15">
+      <c r="T125" s="29">
         <v>6631</v>
       </c>
     </row>
@@ -9111,7 +9157,7 @@
       </c>
       <c r="K126" s="15"/>
       <c r="L126" s="15"/>
-      <c r="M126" s="15">
+      <c r="M126" s="29">
         <v>89177</v>
       </c>
       <c r="N126" s="15">
@@ -9126,13 +9172,13 @@
       <c r="Q126" s="15">
         <v>5</v>
       </c>
-      <c r="R126" s="15">
+      <c r="R126" s="23">
         <v>124.861111111111</v>
       </c>
-      <c r="S126" s="15">
+      <c r="S126" s="26">
         <v>0.160689976114918</v>
       </c>
-      <c r="T126" s="15">
+      <c r="T126" s="29">
         <v>14329.850000000002</v>
       </c>
     </row>
@@ -9169,7 +9215,7 @@
       </c>
       <c r="K127" s="15"/>
       <c r="L127" s="15"/>
-      <c r="M127" s="15">
+      <c r="M127" s="29">
         <v>30000</v>
       </c>
       <c r="N127" s="15">
@@ -9184,13 +9230,13 @@
       <c r="Q127" s="15">
         <v>5</v>
       </c>
-      <c r="R127" s="15">
+      <c r="R127" s="23">
         <v>163.611111111111</v>
       </c>
-      <c r="S127" s="15">
+      <c r="S127" s="26">
         <v>0.2198</v>
       </c>
-      <c r="T127" s="15">
+      <c r="T127" s="29">
         <v>6594</v>
       </c>
     </row>
@@ -9227,7 +9273,7 @@
       </c>
       <c r="K128" s="15"/>
       <c r="L128" s="15"/>
-      <c r="M128" s="15">
+      <c r="M128" s="29">
         <v>54550</v>
       </c>
       <c r="N128" s="15">
@@ -9242,13 +9288,13 @@
       <c r="Q128" s="15">
         <v>6</v>
       </c>
-      <c r="R128" s="15">
+      <c r="R128" s="23">
         <v>120.833333333333</v>
       </c>
-      <c r="S128" s="15">
+      <c r="S128" s="26">
         <v>0.183318056828598</v>
       </c>
-      <c r="T128" s="15">
+      <c r="T128" s="29">
         <v>10000</v>
       </c>
     </row>
@@ -9285,7 +9331,7 @@
       </c>
       <c r="K129" s="15"/>
       <c r="L129" s="15"/>
-      <c r="M129" s="15">
+      <c r="M129" s="29">
         <v>125000</v>
       </c>
       <c r="N129" s="15">
@@ -9300,13 +9346,13 @@
       <c r="Q129" s="15">
         <v>6</v>
       </c>
-      <c r="R129" s="15">
+      <c r="R129" s="23">
         <v>183.333333333333</v>
       </c>
-      <c r="S129" s="15">
+      <c r="S129" s="26">
         <v>0.28566256000000001</v>
       </c>
-      <c r="T129" s="15">
+      <c r="T129" s="29">
         <v>35707.82</v>
       </c>
     </row>
@@ -9343,7 +9389,7 @@
       </c>
       <c r="K130" s="15"/>
       <c r="L130" s="15"/>
-      <c r="M130" s="15">
+      <c r="M130" s="29">
         <v>69100</v>
       </c>
       <c r="N130" s="15">
@@ -9358,13 +9404,13 @@
       <c r="Q130" s="15">
         <v>8</v>
       </c>
-      <c r="R130" s="15">
+      <c r="R130" s="23">
         <v>155.555555555555</v>
       </c>
-      <c r="S130" s="15">
+      <c r="S130" s="26">
         <v>5.9334298118668603E-2</v>
       </c>
-      <c r="T130" s="15">
+      <c r="T130" s="29">
         <v>4100</v>
       </c>
     </row>
@@ -9401,7 +9447,7 @@
       </c>
       <c r="K131" s="15"/>
       <c r="L131" s="15"/>
-      <c r="M131" s="15">
+      <c r="M131" s="29">
         <v>118290</v>
       </c>
       <c r="N131" s="15">
@@ -9416,13 +9462,13 @@
       <c r="Q131" s="15">
         <v>7</v>
       </c>
-      <c r="R131" s="15">
+      <c r="R131" s="23">
         <v>153.055555555555</v>
       </c>
-      <c r="S131" s="15">
+      <c r="S131" s="26">
         <v>0.166624397666751</v>
       </c>
-      <c r="T131" s="15">
+      <c r="T131" s="29">
         <v>19710</v>
       </c>
     </row>
@@ -9459,7 +9505,7 @@
       </c>
       <c r="K132" s="15"/>
       <c r="L132" s="15"/>
-      <c r="M132" s="15">
+      <c r="M132" s="29">
         <v>79900</v>
       </c>
       <c r="N132" s="15">
@@ -9474,13 +9520,13 @@
       <c r="Q132" s="15">
         <v>8</v>
       </c>
-      <c r="R132" s="15">
+      <c r="R132" s="23">
         <v>155.555555555555</v>
       </c>
-      <c r="S132" s="15">
+      <c r="S132" s="26">
         <v>0.14313241551939901</v>
       </c>
-      <c r="T132" s="15">
+      <c r="T132" s="29">
         <v>11436.280000000002</v>
       </c>
     </row>
@@ -9517,7 +9563,7 @@
       </c>
       <c r="K133" s="15"/>
       <c r="L133" s="15"/>
-      <c r="M133" s="15">
+      <c r="M133" s="29">
         <v>39742.379999999997</v>
       </c>
       <c r="N133" s="15">
@@ -9532,13 +9578,13 @@
       <c r="Q133" s="15">
         <v>5</v>
       </c>
-      <c r="R133" s="15">
+      <c r="R133" s="23">
         <v>133.472222222222</v>
       </c>
-      <c r="S133" s="15">
+      <c r="S133" s="26">
         <v>0.14746550156281499</v>
       </c>
-      <c r="T133" s="15">
+      <c r="T133" s="29">
         <v>5860.63</v>
       </c>
     </row>
@@ -9575,7 +9621,7 @@
       </c>
       <c r="K134" s="15"/>
       <c r="L134" s="15"/>
-      <c r="M134" s="15">
+      <c r="M134" s="29">
         <v>48000</v>
       </c>
       <c r="N134" s="15">
@@ -9590,13 +9636,13 @@
       <c r="Q134" s="15">
         <v>11</v>
       </c>
-      <c r="R134" s="15">
+      <c r="R134" s="23">
         <v>152.777777777778</v>
       </c>
-      <c r="S134" s="15">
+      <c r="S134" s="26">
         <v>0.13894520833333299</v>
       </c>
-      <c r="T134" s="15">
+      <c r="T134" s="29">
         <v>6669.369999999999</v>
       </c>
     </row>
@@ -9633,7 +9679,7 @@
       </c>
       <c r="K135" s="15"/>
       <c r="L135" s="15"/>
-      <c r="M135" s="15">
+      <c r="M135" s="29">
         <v>74722</v>
       </c>
       <c r="N135" s="15">
@@ -9648,13 +9694,13 @@
       <c r="Q135" s="15">
         <v>8</v>
       </c>
-      <c r="R135" s="15">
+      <c r="R135" s="23">
         <v>159.444444444445</v>
       </c>
-      <c r="S135" s="15">
+      <c r="S135" s="26">
         <v>0.431922325419555</v>
       </c>
-      <c r="T135" s="15">
+      <c r="T135" s="29">
         <v>32274.100000000002</v>
       </c>
     </row>
@@ -9691,7 +9737,7 @@
       </c>
       <c r="K136" s="15"/>
       <c r="L136" s="15"/>
-      <c r="M136" s="15">
+      <c r="M136" s="29">
         <v>55000</v>
       </c>
       <c r="N136" s="15">
@@ -9706,13 +9752,13 @@
       <c r="Q136" s="15">
         <v>5</v>
       </c>
-      <c r="R136" s="15">
+      <c r="R136" s="23">
         <v>120.555555555556</v>
       </c>
-      <c r="S136" s="15">
+      <c r="S136" s="26">
         <v>3.4563636363636401E-2</v>
       </c>
-      <c r="T136" s="15">
+      <c r="T136" s="29">
         <v>1901</v>
       </c>
     </row>
@@ -9747,7 +9793,7 @@
       </c>
       <c r="K137" s="15"/>
       <c r="L137" s="15"/>
-      <c r="M137" s="15">
+      <c r="M137" s="29">
         <v>128000</v>
       </c>
       <c r="N137" s="15">
@@ -9762,13 +9808,13 @@
       <c r="Q137" s="15">
         <v>3</v>
       </c>
-      <c r="R137" s="15">
+      <c r="R137" s="23">
         <v>197.083333333333</v>
       </c>
-      <c r="S137" s="15">
+      <c r="S137" s="26">
         <v>6.7101562500000003E-2</v>
       </c>
-      <c r="T137" s="15">
+      <c r="T137" s="29">
         <v>6126</v>
       </c>
     </row>
@@ -9805,7 +9851,7 @@
       </c>
       <c r="K138" s="15"/>
       <c r="L138" s="15"/>
-      <c r="M138" s="15">
+      <c r="M138" s="29">
         <v>122000</v>
       </c>
       <c r="N138" s="15">
@@ -9820,13 +9866,13 @@
       <c r="Q138" s="15">
         <v>4</v>
       </c>
-      <c r="R138" s="15">
+      <c r="R138" s="23">
         <v>195.555555555555</v>
       </c>
-      <c r="S138" s="15">
+      <c r="S138" s="26">
         <v>1.7885245901639299E-2</v>
       </c>
-      <c r="T138" s="15">
+      <c r="T138" s="29">
         <v>2182</v>
       </c>
     </row>
@@ -9861,7 +9907,7 @@
       </c>
       <c r="K139" s="15"/>
       <c r="L139" s="15"/>
-      <c r="M139" s="15">
+      <c r="M139" s="29">
         <v>22000</v>
       </c>
       <c r="N139" s="15">
@@ -9876,13 +9922,13 @@
       <c r="Q139" s="15">
         <v>3</v>
       </c>
-      <c r="R139" s="15">
+      <c r="R139" s="23">
         <v>197.083333333333</v>
       </c>
-      <c r="S139" s="15">
+      <c r="S139" s="26">
         <v>0.20981818181818199</v>
       </c>
-      <c r="T139" s="15">
+      <c r="T139" s="29">
         <v>4616</v>
       </c>
     </row>
@@ -9917,7 +9963,7 @@
       </c>
       <c r="K140" s="15"/>
       <c r="L140" s="15"/>
-      <c r="M140" s="15">
+      <c r="M140" s="29">
         <v>10000</v>
       </c>
       <c r="N140" s="15">
@@ -9932,13 +9978,13 @@
       <c r="Q140" s="15">
         <v>2</v>
       </c>
-      <c r="R140" s="15">
+      <c r="R140" s="23">
         <v>255</v>
       </c>
-      <c r="S140" s="15">
+      <c r="S140" s="26">
         <v>0</v>
       </c>
-      <c r="T140" s="15">
+      <c r="T140" s="29">
         <v>0</v>
       </c>
     </row>
@@ -9973,7 +10019,7 @@
       </c>
       <c r="K141" s="15"/>
       <c r="L141" s="15"/>
-      <c r="M141" s="15">
+      <c r="M141" s="29">
         <v>64000</v>
       </c>
       <c r="N141" s="15">
@@ -9988,13 +10034,13 @@
       <c r="Q141" s="15">
         <v>4</v>
       </c>
-      <c r="R141" s="15">
+      <c r="R141" s="23">
         <v>177.777777777778</v>
       </c>
-      <c r="S141" s="15">
+      <c r="S141" s="26">
         <v>0.28125</v>
       </c>
-      <c r="T141" s="15">
+      <c r="T141" s="29">
         <v>18000</v>
       </c>
     </row>
@@ -10029,7 +10075,7 @@
       </c>
       <c r="K142" s="15"/>
       <c r="L142" s="15"/>
-      <c r="M142" s="15">
+      <c r="M142" s="29">
         <v>95628</v>
       </c>
       <c r="N142" s="15">
@@ -10044,13 +10090,13 @@
       <c r="Q142" s="15">
         <v>3</v>
       </c>
-      <c r="R142" s="15">
+      <c r="R142" s="23">
         <v>165</v>
       </c>
-      <c r="S142" s="15">
+      <c r="S142" s="26">
         <v>0.247417074497009</v>
       </c>
-      <c r="T142" s="15">
+      <c r="T142" s="29">
         <v>23660</v>
       </c>
     </row>
@@ -10085,7 +10131,7 @@
       </c>
       <c r="K143" s="15"/>
       <c r="L143" s="15"/>
-      <c r="M143" s="15">
+      <c r="M143" s="29">
         <v>39562</v>
       </c>
       <c r="N143" s="15">
@@ -10100,13 +10146,13 @@
       <c r="Q143" s="15">
         <v>4</v>
       </c>
-      <c r="R143" s="15">
+      <c r="R143" s="23">
         <v>151.111111111111</v>
       </c>
-      <c r="S143" s="15">
+      <c r="S143" s="26">
         <v>0.183913856731207</v>
       </c>
-      <c r="T143" s="15">
+      <c r="T143" s="29">
         <v>7276</v>
       </c>
     </row>
@@ -10143,7 +10189,7 @@
       </c>
       <c r="K144" s="15"/>
       <c r="L144" s="15"/>
-      <c r="M144" s="15">
+      <c r="M144" s="29">
         <v>105000</v>
       </c>
       <c r="N144" s="15">
@@ -10158,13 +10204,13 @@
       <c r="Q144" s="15">
         <v>8</v>
       </c>
-      <c r="R144" s="15">
+      <c r="R144" s="23">
         <v>155.555555555555</v>
       </c>
-      <c r="S144" s="15">
+      <c r="S144" s="26">
         <v>0.75</v>
       </c>
-      <c r="T144" s="15">
+      <c r="T144" s="29">
         <v>78750</v>
       </c>
     </row>
@@ -10201,7 +10247,7 @@
       </c>
       <c r="K145" s="15"/>
       <c r="L145" s="15"/>
-      <c r="M145" s="15">
+      <c r="M145" s="29">
         <v>60000</v>
       </c>
       <c r="N145" s="15">
@@ -10216,13 +10262,13 @@
       <c r="Q145" s="15">
         <v>4</v>
       </c>
-      <c r="R145" s="15">
+      <c r="R145" s="23">
         <v>204.444444444445</v>
       </c>
-      <c r="S145" s="15">
+      <c r="S145" s="26">
         <v>0.66666666666666696</v>
       </c>
-      <c r="T145" s="15">
+      <c r="T145" s="29">
         <v>40000</v>
       </c>
     </row>
@@ -10257,7 +10303,7 @@
       </c>
       <c r="K146" s="15"/>
       <c r="L146" s="15"/>
-      <c r="M146" s="15">
+      <c r="M146" s="29">
         <v>39964</v>
       </c>
       <c r="N146" s="15">
@@ -10272,13 +10318,13 @@
       <c r="Q146" s="15">
         <v>3</v>
       </c>
-      <c r="R146" s="15">
+      <c r="R146" s="23">
         <v>275</v>
       </c>
-      <c r="S146" s="15">
+      <c r="S146" s="26">
         <v>3.2529276348713901E-2</v>
       </c>
-      <c r="T146" s="15">
+      <c r="T146" s="29">
         <v>1300</v>
       </c>
     </row>
@@ -10315,7 +10361,7 @@
       </c>
       <c r="K147" s="15"/>
       <c r="L147" s="15"/>
-      <c r="M147" s="15">
+      <c r="M147" s="29">
         <v>94000</v>
       </c>
       <c r="N147" s="15">
@@ -10330,13 +10376,13 @@
       <c r="Q147" s="15">
         <v>4</v>
       </c>
-      <c r="R147" s="15">
+      <c r="R147" s="23">
         <v>257.777777777778</v>
       </c>
-      <c r="S147" s="15">
+      <c r="S147" s="26">
         <v>0.12765957446808501</v>
       </c>
-      <c r="T147" s="15">
+      <c r="T147" s="29">
         <v>12000</v>
       </c>
     </row>
@@ -10373,7 +10419,7 @@
       </c>
       <c r="K148" s="15"/>
       <c r="L148" s="15"/>
-      <c r="M148" s="15">
+      <c r="M148" s="29">
         <v>75000</v>
       </c>
       <c r="N148" s="15">
@@ -10388,13 +10434,13 @@
       <c r="Q148" s="15">
         <v>6</v>
       </c>
-      <c r="R148" s="15">
+      <c r="R148" s="23">
         <v>166.666666666667</v>
       </c>
-      <c r="S148" s="15">
+      <c r="S148" s="26">
         <v>0.41537333333333298</v>
       </c>
-      <c r="T148" s="15">
+      <c r="T148" s="29">
         <v>31153</v>
       </c>
     </row>
@@ -10431,7 +10477,7 @@
       </c>
       <c r="K149" s="15"/>
       <c r="L149" s="15"/>
-      <c r="M149" s="15">
+      <c r="M149" s="29">
         <v>48767</v>
       </c>
       <c r="N149" s="15">
@@ -10446,13 +10492,13 @@
       <c r="Q149" s="15">
         <v>2</v>
       </c>
-      <c r="R149" s="15">
+      <c r="R149" s="23">
         <v>311.66666666666703</v>
       </c>
-      <c r="S149" s="15">
+      <c r="S149" s="26">
         <v>1.00477782106753E-2</v>
       </c>
-      <c r="T149" s="15">
+      <c r="T149" s="29">
         <v>490</v>
       </c>
     </row>
@@ -10489,7 +10535,7 @@
       </c>
       <c r="K150" s="15"/>
       <c r="L150" s="15"/>
-      <c r="M150" s="15">
+      <c r="M150" s="29">
         <v>63824</v>
       </c>
       <c r="N150" s="15">
@@ -10504,13 +10550,13 @@
       <c r="Q150" s="15">
         <v>5</v>
       </c>
-      <c r="R150" s="15">
+      <c r="R150" s="23">
         <v>223.888888888889</v>
       </c>
-      <c r="S150" s="15">
+      <c r="S150" s="26">
         <v>0.144663449486087</v>
       </c>
-      <c r="T150" s="15">
+      <c r="T150" s="29">
         <v>9233</v>
       </c>
     </row>
@@ -10547,7 +10593,7 @@
       </c>
       <c r="K151" s="15"/>
       <c r="L151" s="15"/>
-      <c r="M151" s="15">
+      <c r="M151" s="29">
         <v>117000</v>
       </c>
       <c r="N151" s="15">
@@ -10562,13 +10608,13 @@
       <c r="Q151" s="15">
         <v>3</v>
       </c>
-      <c r="R151" s="15">
+      <c r="R151" s="23">
         <v>311.66666666666703</v>
       </c>
-      <c r="S151" s="15">
+      <c r="S151" s="26">
         <v>0</v>
       </c>
-      <c r="T151" s="15">
+      <c r="T151" s="29">
         <v>0</v>
       </c>
     </row>
@@ -10603,7 +10649,7 @@
       </c>
       <c r="K152" s="15"/>
       <c r="L152" s="15"/>
-      <c r="M152" s="15">
+      <c r="M152" s="29">
         <v>41000</v>
       </c>
       <c r="N152" s="15">
@@ -10618,13 +10664,13 @@
       <c r="Q152" s="15">
         <v>4</v>
       </c>
-      <c r="R152" s="15">
+      <c r="R152" s="23">
         <v>204.444444444445</v>
       </c>
-      <c r="S152" s="15">
+      <c r="S152" s="26">
         <v>0.11219512195122</v>
       </c>
-      <c r="T152" s="15">
+      <c r="T152" s="29">
         <v>4600</v>
       </c>
     </row>
@@ -10661,7 +10707,7 @@
       </c>
       <c r="K153" s="15"/>
       <c r="L153" s="15"/>
-      <c r="M153" s="15">
+      <c r="M153" s="29">
         <v>96446</v>
       </c>
       <c r="N153" s="15">
@@ -10676,13 +10722,13 @@
       <c r="Q153" s="15">
         <v>3</v>
       </c>
-      <c r="R153" s="15">
+      <c r="R153" s="23">
         <v>284.16666666666703</v>
       </c>
-      <c r="S153" s="15">
+      <c r="S153" s="26">
         <v>0.334902432449246</v>
       </c>
-      <c r="T153" s="15">
+      <c r="T153" s="29">
         <v>32300</v>
       </c>
     </row>
@@ -10719,7 +10765,7 @@
       </c>
       <c r="K154" s="15"/>
       <c r="L154" s="15"/>
-      <c r="M154" s="15">
+      <c r="M154" s="29">
         <v>76600</v>
       </c>
       <c r="N154" s="15">
@@ -10734,13 +10780,13 @@
       <c r="Q154" s="15">
         <v>6.5</v>
       </c>
-      <c r="R154" s="15">
+      <c r="R154" s="23">
         <v>131.111111111111</v>
       </c>
-      <c r="S154" s="15">
+      <c r="S154" s="26">
         <v>0.241919060052219</v>
       </c>
-      <c r="T154" s="15">
+      <c r="T154" s="29">
         <v>18531</v>
       </c>
     </row>
@@ -10777,7 +10823,7 @@
       </c>
       <c r="K155" s="15"/>
       <c r="L155" s="15"/>
-      <c r="M155" s="15">
+      <c r="M155" s="29">
         <v>125569</v>
       </c>
       <c r="N155" s="15">
@@ -10792,13 +10838,13 @@
       <c r="Q155" s="15">
         <v>6</v>
       </c>
-      <c r="R155" s="15">
+      <c r="R155" s="23">
         <v>137.5</v>
       </c>
-      <c r="S155" s="15">
+      <c r="S155" s="26">
         <v>0.25245084375920801</v>
       </c>
-      <c r="T155" s="15">
+      <c r="T155" s="29">
         <v>31700</v>
       </c>
     </row>
@@ -10835,7 +10881,7 @@
       </c>
       <c r="K156" s="15"/>
       <c r="L156" s="15"/>
-      <c r="M156" s="15">
+      <c r="M156" s="29">
         <v>51234</v>
       </c>
       <c r="N156" s="15">
@@ -10850,13 +10896,13 @@
       <c r="Q156" s="15">
         <v>5</v>
       </c>
-      <c r="R156" s="15">
+      <c r="R156" s="23">
         <v>120.555555555556</v>
       </c>
-      <c r="S156" s="15">
+      <c r="S156" s="26">
         <v>7.9868837100362994E-2</v>
       </c>
-      <c r="T156" s="15">
+      <c r="T156" s="29">
         <v>4092</v>
       </c>
     </row>
@@ -10893,7 +10939,7 @@
       </c>
       <c r="K157" s="15"/>
       <c r="L157" s="15"/>
-      <c r="M157" s="15">
+      <c r="M157" s="29">
         <v>123780</v>
       </c>
       <c r="N157" s="15">
@@ -10908,13 +10954,13 @@
       <c r="Q157" s="15">
         <v>3</v>
       </c>
-      <c r="R157" s="15">
+      <c r="R157" s="23">
         <v>123.75</v>
       </c>
-      <c r="S157" s="15">
+      <c r="S157" s="26">
         <v>0.12417999676846</v>
       </c>
-      <c r="T157" s="15">
+      <c r="T157" s="29">
         <v>15371</v>
       </c>
     </row>
@@ -10949,7 +10995,7 @@
       </c>
       <c r="K158" s="15"/>
       <c r="L158" s="15"/>
-      <c r="M158" s="15">
+      <c r="M158" s="29">
         <v>46000</v>
       </c>
       <c r="N158" s="15">
@@ -10964,13 +11010,13 @@
       <c r="Q158" s="15">
         <v>0</v>
       </c>
-      <c r="R158" s="15">
+      <c r="R158" s="23">
         <v>185</v>
       </c>
-      <c r="S158" s="15">
+      <c r="S158" s="26">
         <v>0</v>
       </c>
-      <c r="T158" s="15">
+      <c r="T158" s="29">
         <v>0</v>
       </c>
     </row>
@@ -11007,7 +11053,7 @@
       </c>
       <c r="K159" s="15"/>
       <c r="L159" s="15"/>
-      <c r="M159" s="15">
+      <c r="M159" s="29">
         <v>35600</v>
       </c>
       <c r="N159" s="15">
@@ -11022,13 +11068,13 @@
       <c r="Q159" s="15">
         <v>5</v>
       </c>
-      <c r="R159" s="15">
+      <c r="R159" s="23">
         <v>146.388888888889</v>
       </c>
-      <c r="S159" s="15">
+      <c r="S159" s="26">
         <v>0.12019662921348299</v>
       </c>
-      <c r="T159" s="15">
+      <c r="T159" s="29">
         <v>4279</v>
       </c>
     </row>
@@ -11065,7 +11111,7 @@
       </c>
       <c r="K160" s="15"/>
       <c r="L160" s="15"/>
-      <c r="M160" s="15">
+      <c r="M160" s="29">
         <v>199950</v>
       </c>
       <c r="N160" s="15">
@@ -11080,13 +11126,13 @@
       <c r="Q160" s="15">
         <v>7</v>
       </c>
-      <c r="R160" s="15">
+      <c r="R160" s="23">
         <v>145</v>
       </c>
-      <c r="S160" s="15">
+      <c r="S160" s="26">
         <v>0.150037509377344</v>
       </c>
-      <c r="T160" s="15">
+      <c r="T160" s="29">
         <v>30000</v>
       </c>
     </row>
@@ -11123,7 +11169,7 @@
       </c>
       <c r="K161" s="15"/>
       <c r="L161" s="15"/>
-      <c r="M161" s="15">
+      <c r="M161" s="29">
         <v>108000</v>
       </c>
       <c r="N161" s="15">
@@ -11138,13 +11184,13 @@
       <c r="Q161" s="15">
         <v>5</v>
       </c>
-      <c r="R161" s="15">
+      <c r="R161" s="23">
         <v>137.777777777778</v>
       </c>
-      <c r="S161" s="15">
+      <c r="S161" s="26">
         <v>0.18</v>
       </c>
-      <c r="T161" s="15">
+      <c r="T161" s="29">
         <v>19440</v>
       </c>
     </row>
@@ -11181,7 +11227,7 @@
       </c>
       <c r="K162" s="15"/>
       <c r="L162" s="15"/>
-      <c r="M162" s="15">
+      <c r="M162" s="29">
         <v>142808</v>
       </c>
       <c r="N162" s="15">
@@ -11196,13 +11242,13 @@
       <c r="Q162" s="15">
         <v>9</v>
       </c>
-      <c r="R162" s="15">
+      <c r="R162" s="23">
         <v>127.5</v>
       </c>
-      <c r="S162" s="15">
+      <c r="S162" s="26">
         <v>7.1186488151924299E-2</v>
       </c>
-      <c r="T162" s="15">
+      <c r="T162" s="29">
         <v>10166</v>
       </c>
     </row>
@@ -11239,7 +11285,7 @@
       </c>
       <c r="K163" s="15"/>
       <c r="L163" s="15"/>
-      <c r="M163" s="15">
+      <c r="M163" s="29">
         <v>80463</v>
       </c>
       <c r="N163" s="15">
@@ -11254,13 +11300,13 @@
       <c r="Q163" s="15">
         <v>6</v>
       </c>
-      <c r="R163" s="15">
+      <c r="R163" s="23">
         <v>125</v>
       </c>
-      <c r="S163" s="15">
+      <c r="S163" s="26">
         <v>0.112026645787505</v>
       </c>
-      <c r="T163" s="15">
+      <c r="T163" s="29">
         <v>9014</v>
       </c>
     </row>
@@ -11297,7 +11343,7 @@
       </c>
       <c r="K164" s="15"/>
       <c r="L164" s="15"/>
-      <c r="M164" s="15">
+      <c r="M164" s="29">
         <v>83000</v>
       </c>
       <c r="N164" s="15">
@@ -11312,13 +11358,13 @@
       <c r="Q164" s="15">
         <v>6</v>
       </c>
-      <c r="R164" s="15">
+      <c r="R164" s="23">
         <v>141.666666666667</v>
       </c>
-      <c r="S164" s="15">
+      <c r="S164" s="26">
         <v>0.60361445783132495</v>
       </c>
-      <c r="T164" s="15">
+      <c r="T164" s="29">
         <v>50100</v>
       </c>
     </row>
@@ -11353,7 +11399,7 @@
       </c>
       <c r="K165" s="15"/>
       <c r="L165" s="15"/>
-      <c r="M165" s="15">
+      <c r="M165" s="29">
         <v>129000</v>
       </c>
       <c r="N165" s="15"/>
@@ -11364,13 +11410,13 @@
       <c r="Q165" s="15">
         <v>7</v>
       </c>
-      <c r="R165" s="15">
+      <c r="R165" s="23">
         <v>169.166666666667</v>
       </c>
-      <c r="S165" s="15">
+      <c r="S165" s="26">
         <v>0.39693023255813897</v>
       </c>
-      <c r="T165" s="15">
+      <c r="T165" s="29">
         <v>51204</v>
       </c>
     </row>
@@ -11407,7 +11453,7 @@
       </c>
       <c r="K166" s="15"/>
       <c r="L166" s="15"/>
-      <c r="M166" s="15">
+      <c r="M166" s="29">
         <v>62209</v>
       </c>
       <c r="N166" s="15">
@@ -11422,13 +11468,13 @@
       <c r="Q166" s="15">
         <v>4</v>
       </c>
-      <c r="R166" s="15">
+      <c r="R166" s="23">
         <v>128.888888888889</v>
       </c>
-      <c r="S166" s="15">
+      <c r="S166" s="26">
         <v>0.13806683920333099</v>
       </c>
-      <c r="T166" s="15">
+      <c r="T166" s="29">
         <v>8589</v>
       </c>
     </row>
@@ -11463,7 +11509,7 @@
       </c>
       <c r="K167" s="15"/>
       <c r="L167" s="15"/>
-      <c r="M167" s="15">
+      <c r="M167" s="29">
         <v>36117</v>
       </c>
       <c r="N167" s="15">
@@ -11478,13 +11524,13 @@
       <c r="Q167" s="15">
         <v>3</v>
       </c>
-      <c r="R167" s="15">
+      <c r="R167" s="23">
         <v>142.083333333333</v>
       </c>
-      <c r="S167" s="15">
+      <c r="S167" s="26">
         <v>0.248276434919844</v>
       </c>
-      <c r="T167" s="15">
+      <c r="T167" s="29">
         <v>8967</v>
       </c>
     </row>
@@ -11521,7 +11567,7 @@
       </c>
       <c r="K168" s="15"/>
       <c r="L168" s="15"/>
-      <c r="M168" s="15">
+      <c r="M168" s="29">
         <v>49900</v>
       </c>
       <c r="N168" s="15">
@@ -11536,13 +11582,13 @@
       <c r="Q168" s="15">
         <v>3</v>
       </c>
-      <c r="R168" s="15">
+      <c r="R168" s="23">
         <v>242.916666666667</v>
       </c>
-      <c r="S168" s="15">
+      <c r="S168" s="26">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="T168" s="15">
+      <c r="T168" s="29">
         <v>3493</v>
       </c>
     </row>
@@ -11579,7 +11625,7 @@
       </c>
       <c r="K169" s="15"/>
       <c r="L169" s="15"/>
-      <c r="M169" s="15">
+      <c r="M169" s="29">
         <v>39000</v>
       </c>
       <c r="N169" s="15">
@@ -11594,13 +11640,13 @@
       <c r="Q169" s="15">
         <v>4</v>
       </c>
-      <c r="R169" s="15">
+      <c r="R169" s="23">
         <v>244.444444444445</v>
       </c>
-      <c r="S169" s="15">
+      <c r="S169" s="26">
         <v>0.43589743589743601</v>
       </c>
-      <c r="T169" s="15">
+      <c r="T169" s="29">
         <v>17000</v>
       </c>
     </row>
@@ -11635,7 +11681,7 @@
       </c>
       <c r="K170" s="15"/>
       <c r="L170" s="15"/>
-      <c r="M170" s="15">
+      <c r="M170" s="29">
         <v>49000</v>
       </c>
       <c r="N170" s="15">
@@ -11650,13 +11696,13 @@
       <c r="Q170" s="15">
         <v>0</v>
       </c>
-      <c r="R170" s="15">
+      <c r="R170" s="23">
         <v>235</v>
       </c>
-      <c r="S170" s="15">
+      <c r="S170" s="26">
         <v>2.7142857142857101E-2</v>
       </c>
-      <c r="T170" s="15">
+      <c r="T170" s="29">
         <v>1330</v>
       </c>
     </row>
@@ -11691,7 +11737,7 @@
       </c>
       <c r="K171" s="15"/>
       <c r="L171" s="15"/>
-      <c r="M171" s="15">
+      <c r="M171" s="29">
         <v>59400</v>
       </c>
       <c r="N171" s="15">
@@ -11706,13 +11752,13 @@
       <c r="Q171" s="15">
         <v>4</v>
       </c>
-      <c r="R171" s="15">
+      <c r="R171" s="23">
         <v>160</v>
       </c>
-      <c r="S171" s="15">
+      <c r="S171" s="26">
         <v>0.303686868686869</v>
       </c>
-      <c r="T171" s="15">
+      <c r="T171" s="29">
         <v>18039</v>
       </c>
     </row>
@@ -11749,7 +11795,7 @@
       </c>
       <c r="K172" s="15"/>
       <c r="L172" s="15"/>
-      <c r="M172" s="15">
+      <c r="M172" s="29">
         <v>65000</v>
       </c>
       <c r="N172" s="15">
@@ -11764,13 +11810,13 @@
       <c r="Q172" s="15">
         <v>4</v>
       </c>
-      <c r="R172" s="15">
+      <c r="R172" s="23">
         <v>160</v>
       </c>
-      <c r="S172" s="15">
+      <c r="S172" s="26">
         <v>0.161953846153846</v>
       </c>
-      <c r="T172" s="15">
+      <c r="T172" s="29">
         <v>10527</v>
       </c>
     </row>
@@ -11807,7 +11853,7 @@
       </c>
       <c r="K173" s="15"/>
       <c r="L173" s="15"/>
-      <c r="M173" s="15">
+      <c r="M173" s="29">
         <v>47000</v>
       </c>
       <c r="N173" s="15">
@@ -11822,13 +11868,13 @@
       <c r="Q173" s="15">
         <v>3</v>
       </c>
-      <c r="R173" s="15">
+      <c r="R173" s="23">
         <v>87.0833333333333</v>
       </c>
-      <c r="S173" s="15">
+      <c r="S173" s="26">
         <v>0.05</v>
       </c>
-      <c r="T173" s="15">
+      <c r="T173" s="29">
         <v>2350</v>
       </c>
     </row>
@@ -11865,7 +11911,7 @@
       </c>
       <c r="K174" s="15"/>
       <c r="L174" s="15"/>
-      <c r="M174" s="15">
+      <c r="M174" s="29">
         <v>29000</v>
       </c>
       <c r="N174" s="15">
@@ -11880,13 +11926,13 @@
       <c r="Q174" s="15">
         <v>3</v>
       </c>
-      <c r="R174" s="15">
+      <c r="R174" s="23">
         <v>87.0833333333333</v>
       </c>
-      <c r="S174" s="15">
+      <c r="S174" s="26">
         <v>0.12</v>
       </c>
-      <c r="T174" s="15">
+      <c r="T174" s="29">
         <v>3480</v>
       </c>
     </row>
@@ -11923,7 +11969,7 @@
       </c>
       <c r="K175" s="15"/>
       <c r="L175" s="15"/>
-      <c r="M175" s="15">
+      <c r="M175" s="29">
         <v>132239</v>
       </c>
       <c r="N175" s="15">
@@ -11938,13 +11984,13 @@
       <c r="Q175" s="15">
         <v>3</v>
       </c>
-      <c r="R175" s="15">
+      <c r="R175" s="23">
         <v>87.0833333333333</v>
       </c>
-      <c r="S175" s="15">
+      <c r="S175" s="26">
         <v>0.21929990396176599</v>
       </c>
-      <c r="T175" s="15">
+      <c r="T175" s="29">
         <v>29000</v>
       </c>
     </row>
@@ -11981,7 +12027,7 @@
       </c>
       <c r="K176" s="15"/>
       <c r="L176" s="15"/>
-      <c r="M176" s="15">
+      <c r="M176" s="29">
         <v>35016</v>
       </c>
       <c r="N176" s="15">
@@ -11996,13 +12042,13 @@
       <c r="Q176" s="15">
         <v>2</v>
       </c>
-      <c r="R176" s="15">
+      <c r="R176" s="23">
         <v>75.5555555555556</v>
       </c>
-      <c r="S176" s="15">
+      <c r="S176" s="26">
         <v>1</v>
       </c>
-      <c r="T176" s="15">
+      <c r="T176" s="29">
         <v>35016</v>
       </c>
     </row>
@@ -12037,7 +12083,7 @@
       </c>
       <c r="K177" s="15"/>
       <c r="L177" s="15"/>
-      <c r="M177" s="15">
+      <c r="M177" s="29">
         <v>60000</v>
       </c>
       <c r="N177" s="15">
@@ -12052,13 +12098,13 @@
       <c r="Q177" s="15">
         <v>3</v>
       </c>
-      <c r="R177" s="15">
+      <c r="R177" s="23">
         <v>220</v>
       </c>
-      <c r="S177" s="15">
+      <c r="S177" s="26">
         <v>0.14026666666666701</v>
       </c>
-      <c r="T177" s="15">
+      <c r="T177" s="29">
         <v>8416</v>
       </c>
     </row>
@@ -12095,7 +12141,7 @@
       </c>
       <c r="K178" s="15"/>
       <c r="L178" s="15"/>
-      <c r="M178" s="15">
+      <c r="M178" s="29">
         <v>90244</v>
       </c>
       <c r="N178" s="15">
@@ -12110,13 +12156,13 @@
       <c r="Q178" s="15">
         <v>7</v>
       </c>
-      <c r="R178" s="15">
+      <c r="R178" s="23">
         <v>108.75</v>
       </c>
-      <c r="S178" s="15">
+      <c r="S178" s="26">
         <v>0.155134967421657</v>
       </c>
-      <c r="T178" s="15">
+      <c r="T178" s="29">
         <v>14000</v>
       </c>
     </row>
@@ -12151,7 +12197,7 @@
       </c>
       <c r="K179" s="15"/>
       <c r="L179" s="15"/>
-      <c r="M179" s="15">
+      <c r="M179" s="29">
         <v>38700</v>
       </c>
       <c r="N179" s="15">
@@ -12166,13 +12212,13 @@
       <c r="Q179" s="15">
         <v>4</v>
       </c>
-      <c r="R179" s="15">
+      <c r="R179" s="23">
         <v>97.7777777777778</v>
       </c>
-      <c r="S179" s="15">
+      <c r="S179" s="26">
         <v>0.59204134366925099</v>
       </c>
-      <c r="T179" s="15">
+      <c r="T179" s="29">
         <v>22912</v>
       </c>
     </row>
@@ -12207,7 +12253,7 @@
       </c>
       <c r="K180" s="15"/>
       <c r="L180" s="15"/>
-      <c r="M180" s="15">
+      <c r="M180" s="29">
         <v>62414</v>
       </c>
       <c r="N180" s="15">
@@ -12222,13 +12268,13 @@
       <c r="Q180" s="15">
         <v>3</v>
       </c>
-      <c r="R180" s="15">
+      <c r="R180" s="23">
         <v>215.416666666667</v>
       </c>
-      <c r="S180" s="15">
+      <c r="S180" s="26">
         <v>0.253148332104976</v>
       </c>
-      <c r="T180" s="15">
+      <c r="T180" s="29">
         <v>15800</v>
       </c>
     </row>
@@ -12265,7 +12311,7 @@
       </c>
       <c r="K181" s="15"/>
       <c r="L181" s="15"/>
-      <c r="M181" s="15">
+      <c r="M181" s="29">
         <v>51000</v>
       </c>
       <c r="N181" s="15">
@@ -12280,13 +12326,13 @@
       <c r="Q181" s="15">
         <v>4</v>
       </c>
-      <c r="R181" s="15">
+      <c r="R181" s="23">
         <v>75.5555555555556</v>
       </c>
-      <c r="S181" s="15">
+      <c r="S181" s="26">
         <v>0.55000000000000004</v>
       </c>
-      <c r="T181" s="15">
+      <c r="T181" s="29">
         <v>28050</v>
       </c>
     </row>
@@ -12323,7 +12369,7 @@
       </c>
       <c r="K182" s="15"/>
       <c r="L182" s="15"/>
-      <c r="M182" s="15">
+      <c r="M182" s="29">
         <v>53115</v>
       </c>
       <c r="N182" s="15">
@@ -12338,13 +12384,13 @@
       <c r="Q182" s="15">
         <v>5</v>
       </c>
-      <c r="R182" s="15">
+      <c r="R182" s="23">
         <v>301.38888888888903</v>
       </c>
-      <c r="S182" s="15">
+      <c r="S182" s="26">
         <v>0.135554927986445</v>
       </c>
-      <c r="T182" s="15">
+      <c r="T182" s="29">
         <v>7200</v>
       </c>
     </row>
@@ -12379,7 +12425,7 @@
       </c>
       <c r="K183" s="15"/>
       <c r="L183" s="15"/>
-      <c r="M183" s="15">
+      <c r="M183" s="29">
         <v>120000</v>
       </c>
       <c r="N183" s="15">
@@ -12394,13 +12440,13 @@
       <c r="Q183" s="15">
         <v>3</v>
       </c>
-      <c r="R183" s="15">
+      <c r="R183" s="23">
         <v>128.333333333333</v>
       </c>
-      <c r="S183" s="15">
+      <c r="S183" s="26">
         <v>0.18333333333333299</v>
       </c>
-      <c r="T183" s="15">
+      <c r="T183" s="29">
         <v>22000</v>
       </c>
     </row>
@@ -12437,7 +12483,7 @@
       </c>
       <c r="K184" s="15"/>
       <c r="L184" s="15"/>
-      <c r="M184" s="15">
+      <c r="M184" s="29">
         <v>66477</v>
       </c>
       <c r="N184" s="15">
@@ -12452,13 +12498,13 @@
       <c r="Q184" s="15">
         <v>3</v>
       </c>
-      <c r="R184" s="15">
+      <c r="R184" s="23">
         <v>265.83333333333297</v>
       </c>
-      <c r="S184" s="15">
+      <c r="S184" s="26">
         <v>0.90974321945936198</v>
       </c>
-      <c r="T184" s="15">
+      <c r="T184" s="29">
         <v>60477</v>
       </c>
     </row>
@@ -12495,7 +12541,7 @@
       </c>
       <c r="K185" s="15"/>
       <c r="L185" s="15"/>
-      <c r="M185" s="15">
+      <c r="M185" s="29">
         <v>59300</v>
       </c>
       <c r="N185" s="15">
@@ -12510,13 +12556,13 @@
       <c r="Q185" s="15">
         <v>5</v>
       </c>
-      <c r="R185" s="15">
+      <c r="R185" s="23">
         <v>86.1111111111111</v>
       </c>
-      <c r="S185" s="15">
+      <c r="S185" s="26">
         <v>0.79089376053962901</v>
       </c>
-      <c r="T185" s="15">
+      <c r="T185" s="29">
         <v>46900</v>
       </c>
     </row>
@@ -12551,7 +12597,7 @@
       </c>
       <c r="K186" s="15"/>
       <c r="L186" s="15"/>
-      <c r="M186" s="15">
+      <c r="M186" s="29">
         <v>44000</v>
       </c>
       <c r="N186" s="15">
@@ -12566,13 +12612,13 @@
       <c r="Q186" s="15">
         <v>4</v>
       </c>
-      <c r="R186" s="15">
+      <c r="R186" s="23">
         <v>80</v>
       </c>
-      <c r="S186" s="15">
+      <c r="S186" s="26">
         <v>0.45</v>
       </c>
-      <c r="T186" s="15">
+      <c r="T186" s="29">
         <v>19800</v>
       </c>
     </row>
@@ -12607,7 +12653,7 @@
       </c>
       <c r="K187" s="15"/>
       <c r="L187" s="15"/>
-      <c r="M187" s="15">
+      <c r="M187" s="29">
         <v>26528</v>
       </c>
       <c r="N187" s="15">
@@ -12622,13 +12668,13 @@
       <c r="Q187" s="15">
         <v>3</v>
       </c>
-      <c r="R187" s="15">
+      <c r="R187" s="23">
         <v>84.3333333333333</v>
       </c>
-      <c r="S187" s="15">
+      <c r="S187" s="26">
         <v>0.331724969843185</v>
       </c>
-      <c r="T187" s="15">
+      <c r="T187" s="29">
         <v>8800</v>
       </c>
     </row>
@@ -12665,7 +12711,7 @@
       </c>
       <c r="K188" s="15"/>
       <c r="L188" s="15"/>
-      <c r="M188" s="15">
+      <c r="M188" s="29">
         <v>95684</v>
       </c>
       <c r="N188" s="15">
@@ -12680,13 +12726,13 @@
       <c r="Q188" s="15">
         <v>3</v>
       </c>
-      <c r="R188" s="15">
+      <c r="R188" s="23">
         <v>87.0833333333333</v>
       </c>
-      <c r="S188" s="15">
+      <c r="S188" s="26">
         <v>0.59571088165210495</v>
       </c>
-      <c r="T188" s="15">
+      <c r="T188" s="29">
         <v>57000</v>
       </c>
     </row>
@@ -12721,7 +12767,7 @@
       </c>
       <c r="K189" s="15"/>
       <c r="L189" s="15"/>
-      <c r="M189" s="15">
+      <c r="M189" s="29">
         <v>26737</v>
       </c>
       <c r="N189" s="15">
@@ -12736,13 +12782,13 @@
       <c r="Q189" s="15">
         <v>3</v>
       </c>
-      <c r="R189" s="15">
+      <c r="R189" s="23">
         <v>89.8333333333333</v>
       </c>
-      <c r="S189" s="15">
+      <c r="S189" s="26">
         <v>0.40019448704043098</v>
       </c>
-      <c r="T189" s="15">
+      <c r="T189" s="29">
         <v>10700</v>
       </c>
     </row>
@@ -12779,7 +12825,7 @@
       </c>
       <c r="K190" s="15"/>
       <c r="L190" s="15"/>
-      <c r="M190" s="15">
+      <c r="M190" s="29">
         <v>60000</v>
       </c>
       <c r="N190" s="15">
@@ -12794,13 +12840,13 @@
       <c r="Q190" s="15">
         <v>3</v>
       </c>
-      <c r="R190" s="15">
+      <c r="R190" s="23">
         <v>82.5</v>
       </c>
-      <c r="S190" s="15">
+      <c r="S190" s="26">
         <v>0.5</v>
       </c>
-      <c r="T190" s="15">
+      <c r="T190" s="29">
         <v>30000</v>
       </c>
     </row>
@@ -12835,7 +12881,7 @@
       </c>
       <c r="K191" s="15"/>
       <c r="L191" s="15"/>
-      <c r="M191" s="15">
+      <c r="M191" s="29">
         <v>34895</v>
       </c>
       <c r="N191" s="15">
@@ -12850,13 +12896,13 @@
       <c r="Q191" s="15">
         <v>5</v>
       </c>
-      <c r="R191" s="15">
+      <c r="R191" s="23">
         <v>77.5</v>
       </c>
-      <c r="S191" s="15">
+      <c r="S191" s="26">
         <v>0.45278693222524702</v>
       </c>
-      <c r="T191" s="15">
+      <c r="T191" s="29">
         <v>15800</v>
       </c>
     </row>
@@ -12891,7 +12937,7 @@
       <c r="J192" s="4"/>
       <c r="K192" s="15"/>
       <c r="L192" s="15"/>
-      <c r="M192" s="15"/>
+      <c r="M192" s="29"/>
       <c r="N192" s="15"/>
       <c r="O192" s="15">
         <v>35</v>
@@ -12902,9 +12948,9 @@
       <c r="Q192" s="15">
         <v>4</v>
       </c>
-      <c r="R192" s="15"/>
-      <c r="S192" s="15"/>
-      <c r="T192" s="15"/>
+      <c r="R192" s="23"/>
+      <c r="S192" s="26"/>
+      <c r="T192" s="29"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:T192" xr:uid="{7B280671-4AFA-4641-88D4-A51F39483890}"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\intern.bjres\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AC30D9D-CD15-4DEF-BA83-015F7289B6A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0BA3A43C-84AC-491A-A8E8-41971A0E5D1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$T$192</definedName>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1479" uniqueCount="437">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1481" uniqueCount="439">
   <si>
     <t>所在市</t>
   </si>
@@ -1384,6 +1385,12 @@
   <si>
     <t>USER</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>坐标拾取器 | 高德地图API</t>
+  </si>
+  <si>
+    <t>高德地图坐标拾取器地址</t>
   </si>
 </sst>
 </file>
@@ -1394,7 +1401,7 @@
     <numFmt numFmtId="164" formatCode="0.00_);[Red]\(0.00\)"/>
     <numFmt numFmtId="165" formatCode="0_);[Red]\(0\)"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1474,6 +1481,14 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -1525,7 +1540,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
       <alignment vertical="center"/>
@@ -1533,8 +1548,9 @@
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
@@ -1574,26 +1590,6 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="165" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1637,8 +1633,30 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3"/>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
+    <cellStyle name="Hyperlink" xfId="3" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
     <cellStyle name="常规 2" xfId="1" xr:uid="{81D4EE7A-49F9-4559-B92D-CA7C8AC626DC}"/>
@@ -1946,19 +1964,19 @@
   <cols>
     <col min="1" max="1" width="9.453125" style="3" customWidth="1"/>
     <col min="2" max="6" width="9.453125" style="10" customWidth="1"/>
-    <col min="7" max="7" width="19.08984375" style="24" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.7265625" style="23" customWidth="1"/>
-    <col min="9" max="9" width="36.81640625" style="29" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.36328125" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.08984375" style="18" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.7265625" style="17" customWidth="1"/>
+    <col min="9" max="9" width="36.81640625" style="23" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.36328125" style="23" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="14" style="8" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.6328125" style="20" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.6328125" style="14" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14" style="8" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="16.6328125" style="8" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="14" style="8" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="16.6328125" style="8" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="22.36328125" style="14" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.6328125" style="17" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="19.36328125" style="20" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="22.36328125" style="28" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.6328125" style="29" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="19.36328125" style="14" bestFit="1" customWidth="1"/>
     <col min="21" max="16384" width="10.81640625" style="1"/>
   </cols>
   <sheetData>
@@ -1981,16 +1999,16 @@
       <c r="F1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="21" t="s">
+      <c r="G1" s="15" t="s">
         <v>338</v>
       </c>
-      <c r="H1" s="21" t="s">
+      <c r="H1" s="15" t="s">
         <v>342</v>
       </c>
-      <c r="I1" s="21" t="s">
+      <c r="I1" s="15" t="s">
         <v>335</v>
       </c>
-      <c r="J1" s="25" t="s">
+      <c r="J1" s="19" t="s">
         <v>436</v>
       </c>
       <c r="K1" s="6" t="s">
@@ -1999,7 +2017,7 @@
       <c r="L1" s="6" t="s">
         <v>415</v>
       </c>
-      <c r="M1" s="18" t="s">
+      <c r="M1" s="12" t="s">
         <v>334</v>
       </c>
       <c r="N1" s="6" t="s">
@@ -2014,13 +2032,13 @@
       <c r="Q1" s="6" t="s">
         <v>419</v>
       </c>
-      <c r="R1" s="12" t="s">
+      <c r="R1" s="24" t="s">
         <v>339</v>
       </c>
-      <c r="S1" s="15" t="s">
+      <c r="S1" s="25" t="s">
         <v>340</v>
       </c>
-      <c r="T1" s="18" t="s">
+      <c r="T1" s="12" t="s">
         <v>341</v>
       </c>
     </row>
@@ -2043,19 +2061,19 @@
       <c r="F2" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="22">
+      <c r="G2" s="16">
         <v>1990</v>
       </c>
-      <c r="H2" s="22"/>
-      <c r="I2" s="26" t="s">
+      <c r="H2" s="16"/>
+      <c r="I2" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="J2" s="27" t="s">
+      <c r="J2" s="21" t="s">
         <v>421</v>
       </c>
       <c r="K2" s="7"/>
       <c r="L2" s="7"/>
-      <c r="M2" s="19">
+      <c r="M2" s="13">
         <v>72308</v>
       </c>
       <c r="N2" s="7">
@@ -2070,13 +2088,15 @@
       <c r="Q2" s="7">
         <v>3</v>
       </c>
-      <c r="R2" s="13">
+      <c r="R2" s="26">
+        <f>P2*(36-Q2)/36</f>
         <v>288.75</v>
       </c>
-      <c r="S2" s="16">
-        <v>0.129999446810865</v>
-      </c>
-      <c r="T2" s="19">
+      <c r="S2" s="27">
+        <f>T2/M2</f>
+        <v>0.12999944681086464</v>
+      </c>
+      <c r="T2" s="13">
         <v>9400</v>
       </c>
     </row>
@@ -2099,19 +2119,19 @@
       <c r="F3" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="22">
+      <c r="G3" s="16">
         <v>1999</v>
       </c>
-      <c r="H3" s="22"/>
-      <c r="I3" s="26" t="s">
+      <c r="H3" s="16"/>
+      <c r="I3" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="J3" s="27" t="s">
+      <c r="J3" s="21" t="s">
         <v>421</v>
       </c>
       <c r="K3" s="7"/>
       <c r="L3" s="7"/>
-      <c r="M3" s="19">
+      <c r="M3" s="13">
         <v>72308</v>
       </c>
       <c r="N3" s="7">
@@ -2126,13 +2146,15 @@
       <c r="Q3" s="7">
         <v>3</v>
       </c>
-      <c r="R3" s="13">
-        <v>307.08333333333297</v>
-      </c>
-      <c r="S3" s="16">
-        <v>2.0053106156995099E-2</v>
-      </c>
-      <c r="T3" s="19">
+      <c r="R3" s="26">
+        <f>P3*(36-Q3)/36</f>
+        <v>307.08333333333331</v>
+      </c>
+      <c r="S3" s="27">
+        <f t="shared" ref="S3:S66" si="0">T3/M3</f>
+        <v>2.0053106156995078E-2</v>
+      </c>
+      <c r="T3" s="13">
         <v>1450</v>
       </c>
     </row>
@@ -2155,21 +2177,21 @@
       <c r="F4" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="G4" s="22">
+      <c r="G4" s="16">
         <v>2010</v>
       </c>
-      <c r="H4" s="22" t="s">
+      <c r="H4" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="I4" s="26" t="s">
+      <c r="I4" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="J4" s="27" t="s">
+      <c r="J4" s="21" t="s">
         <v>421</v>
       </c>
       <c r="K4" s="7"/>
       <c r="L4" s="7"/>
-      <c r="M4" s="19">
+      <c r="M4" s="13">
         <v>130769</v>
       </c>
       <c r="N4" s="7">
@@ -2184,13 +2206,15 @@
       <c r="Q4" s="7">
         <v>2</v>
       </c>
-      <c r="R4" s="13">
-        <v>363.61111111111097</v>
-      </c>
-      <c r="S4" s="16">
-        <v>0.100176647370554</v>
-      </c>
-      <c r="T4" s="19">
+      <c r="R4" s="26">
+        <f>P4*(36-Q4)/36</f>
+        <v>363.61111111111109</v>
+      </c>
+      <c r="S4" s="27">
+        <f t="shared" si="0"/>
+        <v>0.10017664737055418</v>
+      </c>
+      <c r="T4" s="13">
         <v>13100</v>
       </c>
     </row>
@@ -2213,21 +2237,21 @@
       <c r="F5" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="G5" s="22">
+      <c r="G5" s="16">
         <v>2017</v>
       </c>
-      <c r="H5" s="22" t="s">
+      <c r="H5" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="I5" s="26" t="s">
+      <c r="I5" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="J5" s="27" t="s">
+      <c r="J5" s="21" t="s">
         <v>421</v>
       </c>
       <c r="K5" s="7"/>
       <c r="L5" s="7"/>
-      <c r="M5" s="19">
+      <c r="M5" s="13">
         <v>64615</v>
       </c>
       <c r="N5" s="7">
@@ -2242,13 +2266,15 @@
       <c r="Q5" s="7">
         <v>2</v>
       </c>
-      <c r="R5" s="13">
-        <v>377.777777777778</v>
-      </c>
-      <c r="S5" s="16">
-        <v>3.01787510639944E-2</v>
-      </c>
-      <c r="T5" s="19">
+      <c r="R5" s="26">
+        <f>P5*(36-Q5)/36</f>
+        <v>377.77777777777777</v>
+      </c>
+      <c r="S5" s="27">
+        <f t="shared" si="0"/>
+        <v>3.0178751063994428E-2</v>
+      </c>
+      <c r="T5" s="13">
         <v>1950</v>
       </c>
     </row>
@@ -2271,21 +2297,21 @@
       <c r="F6" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="G6" s="22">
+      <c r="G6" s="16">
         <v>1998</v>
       </c>
-      <c r="H6" s="22" t="s">
+      <c r="H6" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="I6" s="26" t="s">
+      <c r="I6" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="J6" s="27" t="s">
+      <c r="J6" s="21" t="s">
         <v>421</v>
       </c>
       <c r="K6" s="7"/>
       <c r="L6" s="7"/>
-      <c r="M6" s="19">
+      <c r="M6" s="13">
         <v>80091</v>
       </c>
       <c r="N6" s="7">
@@ -2300,13 +2326,15 @@
       <c r="Q6" s="7">
         <v>6</v>
       </c>
-      <c r="R6" s="13">
-        <v>208.333333333333</v>
-      </c>
-      <c r="S6" s="16">
-        <v>7.4440324131300598E-2</v>
-      </c>
-      <c r="T6" s="19">
+      <c r="R6" s="26">
+        <f t="shared" ref="R6:R69" si="1">P6*(36-Q6)/36</f>
+        <v>208.33333333333334</v>
+      </c>
+      <c r="S6" s="27">
+        <f t="shared" si="0"/>
+        <v>7.4440324131300639E-2</v>
+      </c>
+      <c r="T6" s="13">
         <v>5962</v>
       </c>
     </row>
@@ -2329,19 +2357,19 @@
       <c r="F7" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="G7" s="22">
+      <c r="G7" s="16">
         <v>2005</v>
       </c>
-      <c r="H7" s="22"/>
-      <c r="I7" s="26" t="s">
+      <c r="H7" s="16"/>
+      <c r="I7" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="J7" s="27" t="s">
+      <c r="J7" s="21" t="s">
         <v>422</v>
       </c>
       <c r="K7" s="7"/>
       <c r="L7" s="7"/>
-      <c r="M7" s="19">
+      <c r="M7" s="13">
         <v>70673</v>
       </c>
       <c r="N7" s="7">
@@ -2356,13 +2384,15 @@
       <c r="Q7" s="7">
         <v>3</v>
       </c>
-      <c r="R7" s="13">
-        <v>242.916666666667</v>
-      </c>
-      <c r="S7" s="16">
+      <c r="R7" s="26">
+        <f t="shared" si="1"/>
+        <v>242.91666666666666</v>
+      </c>
+      <c r="S7" s="27">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="T7" s="19">
+      <c r="T7" s="13">
         <v>0</v>
       </c>
     </row>
@@ -2385,21 +2415,21 @@
       <c r="F8" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="G8" s="22">
+      <c r="G8" s="16">
         <v>2005</v>
       </c>
-      <c r="H8" s="22" t="s">
+      <c r="H8" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="I8" s="26" t="s">
+      <c r="I8" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="J8" s="27" t="s">
+      <c r="J8" s="21" t="s">
         <v>421</v>
       </c>
       <c r="K8" s="7"/>
       <c r="L8" s="7"/>
-      <c r="M8" s="19">
+      <c r="M8" s="13">
         <v>90466</v>
       </c>
       <c r="N8" s="7">
@@ -2414,13 +2444,15 @@
       <c r="Q8" s="7">
         <v>4</v>
       </c>
-      <c r="R8" s="13">
-        <v>177.777777777778</v>
-      </c>
-      <c r="S8" s="16">
+      <c r="R8" s="26">
+        <f t="shared" si="1"/>
+        <v>177.77777777777777</v>
+      </c>
+      <c r="S8" s="27">
+        <f t="shared" si="0"/>
         <v>0.239935445360688</v>
       </c>
-      <c r="T8" s="19">
+      <c r="T8" s="13">
         <v>21706</v>
       </c>
     </row>
@@ -2443,19 +2475,19 @@
       <c r="F9" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="G9" s="22">
+      <c r="G9" s="16">
         <v>2005</v>
       </c>
-      <c r="H9" s="22"/>
-      <c r="I9" s="26" t="s">
+      <c r="H9" s="16"/>
+      <c r="I9" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="J9" s="27" t="s">
+      <c r="J9" s="21" t="s">
         <v>422</v>
       </c>
       <c r="K9" s="7"/>
       <c r="L9" s="7"/>
-      <c r="M9" s="19">
+      <c r="M9" s="13">
         <v>46720</v>
       </c>
       <c r="N9" s="7">
@@ -2470,13 +2502,15 @@
       <c r="Q9" s="7">
         <v>8</v>
       </c>
-      <c r="R9" s="13">
-        <v>198.333333333333</v>
-      </c>
-      <c r="S9" s="16">
-        <v>7.4453553082191801E-2</v>
-      </c>
-      <c r="T9" s="19">
+      <c r="R9" s="26">
+        <f t="shared" si="1"/>
+        <v>198.33333333333334</v>
+      </c>
+      <c r="S9" s="27">
+        <f t="shared" si="0"/>
+        <v>7.4453553082191773E-2</v>
+      </c>
+      <c r="T9" s="13">
         <v>3478.47</v>
       </c>
     </row>
@@ -2499,21 +2533,21 @@
       <c r="F10" s="9" t="s">
         <v>383</v>
       </c>
-      <c r="G10" s="22">
+      <c r="G10" s="16">
         <v>2006</v>
       </c>
-      <c r="H10" s="22" t="s">
+      <c r="H10" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="I10" s="28" t="s">
+      <c r="I10" s="22" t="s">
         <v>431</v>
       </c>
-      <c r="J10" s="27" t="s">
+      <c r="J10" s="21" t="s">
         <v>422</v>
       </c>
       <c r="K10" s="7"/>
       <c r="L10" s="7"/>
-      <c r="M10" s="19">
+      <c r="M10" s="13">
         <v>95000</v>
       </c>
       <c r="N10" s="7">
@@ -2528,13 +2562,15 @@
       <c r="Q10" s="7">
         <v>8</v>
       </c>
-      <c r="R10" s="13">
-        <v>182.777777777778</v>
-      </c>
-      <c r="S10" s="16">
-        <v>0.24465263157894701</v>
-      </c>
-      <c r="T10" s="19">
+      <c r="R10" s="26">
+        <f t="shared" si="1"/>
+        <v>182.77777777777777</v>
+      </c>
+      <c r="S10" s="27">
+        <f t="shared" si="0"/>
+        <v>0.24465263157894737</v>
+      </c>
+      <c r="T10" s="13">
         <v>23242</v>
       </c>
     </row>
@@ -2557,21 +2593,21 @@
       <c r="F11" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="G11" s="22">
+      <c r="G11" s="16">
         <v>2007</v>
       </c>
-      <c r="H11" s="22" t="s">
+      <c r="H11" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="I11" s="26" t="s">
+      <c r="I11" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="J11" s="27" t="s">
+      <c r="J11" s="21" t="s">
         <v>422</v>
       </c>
       <c r="K11" s="7"/>
       <c r="L11" s="7"/>
-      <c r="M11" s="19">
+      <c r="M11" s="13">
         <v>85300</v>
       </c>
       <c r="N11" s="7">
@@ -2586,13 +2622,15 @@
       <c r="Q11" s="7">
         <v>5</v>
       </c>
-      <c r="R11" s="13">
-        <v>146.388888888889</v>
-      </c>
-      <c r="S11" s="16">
-        <v>0.19929660023446699</v>
-      </c>
-      <c r="T11" s="19">
+      <c r="R11" s="26">
+        <f t="shared" si="1"/>
+        <v>146.38888888888889</v>
+      </c>
+      <c r="S11" s="27">
+        <f t="shared" si="0"/>
+        <v>0.19929660023446658</v>
+      </c>
+      <c r="T11" s="13">
         <v>17000</v>
       </c>
     </row>
@@ -2615,21 +2653,21 @@
       <c r="F12" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="G12" s="22">
+      <c r="G12" s="16">
         <v>2007</v>
       </c>
-      <c r="H12" s="22" t="s">
+      <c r="H12" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="I12" s="26" t="s">
+      <c r="I12" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="J12" s="27" t="s">
+      <c r="J12" s="21" t="s">
         <v>422</v>
       </c>
       <c r="K12" s="7"/>
       <c r="L12" s="7"/>
-      <c r="M12" s="19">
+      <c r="M12" s="13">
         <v>33305</v>
       </c>
       <c r="N12" s="7">
@@ -2644,13 +2682,15 @@
       <c r="Q12" s="7">
         <v>4</v>
       </c>
-      <c r="R12" s="13">
-        <v>186.666666666667</v>
-      </c>
-      <c r="S12" s="16">
-        <v>0.14799579642696301</v>
-      </c>
-      <c r="T12" s="19">
+      <c r="R12" s="26">
+        <f t="shared" si="1"/>
+        <v>186.66666666666666</v>
+      </c>
+      <c r="S12" s="27">
+        <f t="shared" si="0"/>
+        <v>0.14799579642696292</v>
+      </c>
+      <c r="T12" s="13">
         <v>4929</v>
       </c>
     </row>
@@ -2673,21 +2713,21 @@
       <c r="F13" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="G13" s="22">
+      <c r="G13" s="16">
         <v>2007</v>
       </c>
-      <c r="H13" s="22" t="s">
+      <c r="H13" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="I13" s="26" t="s">
+      <c r="I13" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="J13" s="27" t="s">
+      <c r="J13" s="21" t="s">
         <v>421</v>
       </c>
       <c r="K13" s="7"/>
       <c r="L13" s="7"/>
-      <c r="M13" s="19">
+      <c r="M13" s="13">
         <v>120245.21</v>
       </c>
       <c r="N13" s="7">
@@ -2702,13 +2742,15 @@
       <c r="Q13" s="7">
         <v>4</v>
       </c>
-      <c r="R13" s="13">
-        <v>253.333333333333</v>
-      </c>
-      <c r="S13" s="16">
-        <v>6.6680410803889797E-2</v>
-      </c>
-      <c r="T13" s="19">
+      <c r="R13" s="26">
+        <f t="shared" si="1"/>
+        <v>253.33333333333334</v>
+      </c>
+      <c r="S13" s="27">
+        <f t="shared" si="0"/>
+        <v>6.6680410803889811E-2</v>
+      </c>
+      <c r="T13" s="13">
         <v>8018</v>
       </c>
     </row>
@@ -2731,21 +2773,21 @@
       <c r="F14" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="G14" s="22">
+      <c r="G14" s="16">
         <v>2008</v>
       </c>
-      <c r="H14" s="22" t="s">
+      <c r="H14" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="I14" s="26" t="s">
+      <c r="I14" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="J14" s="27" t="s">
+      <c r="J14" s="21" t="s">
         <v>421</v>
       </c>
       <c r="K14" s="7"/>
       <c r="L14" s="7"/>
-      <c r="M14" s="19">
+      <c r="M14" s="13">
         <v>70425.53</v>
       </c>
       <c r="N14" s="7">
@@ -2760,13 +2802,15 @@
       <c r="Q14" s="7">
         <v>4</v>
       </c>
-      <c r="R14" s="13">
-        <v>253.333333333333</v>
-      </c>
-      <c r="S14" s="16">
-        <v>9.3091241201876604E-2</v>
-      </c>
-      <c r="T14" s="19">
+      <c r="R14" s="26">
+        <f t="shared" si="1"/>
+        <v>253.33333333333334</v>
+      </c>
+      <c r="S14" s="27">
+        <f t="shared" si="0"/>
+        <v>9.3091241201876646E-2</v>
+      </c>
+      <c r="T14" s="13">
         <v>6556</v>
       </c>
     </row>
@@ -2789,21 +2833,21 @@
       <c r="F15" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="G15" s="22">
+      <c r="G15" s="16">
         <v>2007</v>
       </c>
-      <c r="H15" s="22" t="s">
+      <c r="H15" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="I15" s="26" t="s">
+      <c r="I15" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="J15" s="27" t="s">
+      <c r="J15" s="21" t="s">
         <v>421</v>
       </c>
       <c r="K15" s="7"/>
       <c r="L15" s="7"/>
-      <c r="M15" s="19">
+      <c r="M15" s="13">
         <v>78000</v>
       </c>
       <c r="N15" s="7">
@@ -2818,13 +2862,15 @@
       <c r="Q15" s="7">
         <v>6</v>
       </c>
-      <c r="R15" s="13">
-        <v>258.33333333333297</v>
-      </c>
-      <c r="S15" s="16">
-        <v>0.15384615384615399</v>
-      </c>
-      <c r="T15" s="19">
+      <c r="R15" s="26">
+        <f t="shared" si="1"/>
+        <v>258.33333333333331</v>
+      </c>
+      <c r="S15" s="27">
+        <f t="shared" si="0"/>
+        <v>0.15384615384615385</v>
+      </c>
+      <c r="T15" s="13">
         <v>12000</v>
       </c>
     </row>
@@ -2847,21 +2893,21 @@
       <c r="F16" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="G16" s="22">
+      <c r="G16" s="16">
         <v>2007</v>
       </c>
-      <c r="H16" s="22" t="s">
+      <c r="H16" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="I16" s="26" t="s">
+      <c r="I16" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="J16" s="27" t="s">
+      <c r="J16" s="21" t="s">
         <v>422</v>
       </c>
       <c r="K16" s="7"/>
       <c r="L16" s="7"/>
-      <c r="M16" s="19">
+      <c r="M16" s="13">
         <v>102796</v>
       </c>
       <c r="N16" s="7">
@@ -2876,13 +2922,15 @@
       <c r="Q16" s="7">
         <v>6</v>
       </c>
-      <c r="R16" s="13">
+      <c r="R16" s="26">
+        <f t="shared" si="1"/>
         <v>200</v>
       </c>
-      <c r="S16" s="16">
-        <v>0.170955095529009</v>
-      </c>
-      <c r="T16" s="19">
+      <c r="S16" s="27">
+        <f t="shared" si="0"/>
+        <v>0.17095509552900892</v>
+      </c>
+      <c r="T16" s="13">
         <v>17573.5</v>
       </c>
     </row>
@@ -2905,21 +2953,21 @@
       <c r="F17" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="G17" s="22">
+      <c r="G17" s="16">
         <v>2007</v>
       </c>
-      <c r="H17" s="22" t="s">
+      <c r="H17" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="I17" s="26" t="s">
+      <c r="I17" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="J17" s="27" t="s">
+      <c r="J17" s="21" t="s">
         <v>422</v>
       </c>
       <c r="K17" s="7"/>
       <c r="L17" s="7"/>
-      <c r="M17" s="19">
+      <c r="M17" s="13">
         <v>49200</v>
       </c>
       <c r="N17" s="7">
@@ -2934,13 +2982,15 @@
       <c r="Q17" s="7">
         <v>6</v>
       </c>
-      <c r="R17" s="13">
-        <v>191.666666666667</v>
-      </c>
-      <c r="S17" s="16">
-        <v>9.3665650406504097E-2</v>
-      </c>
-      <c r="T17" s="19">
+      <c r="R17" s="26">
+        <f t="shared" si="1"/>
+        <v>191.66666666666666</v>
+      </c>
+      <c r="S17" s="27">
+        <f t="shared" si="0"/>
+        <v>9.366565040650407E-2</v>
+      </c>
+      <c r="T17" s="13">
         <v>4608.3500000000004</v>
       </c>
     </row>
@@ -2963,21 +3013,21 @@
       <c r="F18" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="G18" s="22">
+      <c r="G18" s="16">
         <v>2008</v>
       </c>
-      <c r="H18" s="22" t="s">
+      <c r="H18" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="I18" s="26" t="s">
+      <c r="I18" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="J18" s="27" t="s">
+      <c r="J18" s="21" t="s">
         <v>422</v>
       </c>
       <c r="K18" s="7"/>
       <c r="L18" s="7"/>
-      <c r="M18" s="19">
+      <c r="M18" s="13">
         <v>65096</v>
       </c>
       <c r="N18" s="7">
@@ -2992,13 +3042,15 @@
       <c r="Q18" s="7">
         <v>8</v>
       </c>
-      <c r="R18" s="13">
-        <v>186.666666666667</v>
-      </c>
-      <c r="S18" s="16">
-        <v>0.12122096595796999</v>
-      </c>
-      <c r="T18" s="19">
+      <c r="R18" s="26">
+        <f t="shared" si="1"/>
+        <v>186.66666666666666</v>
+      </c>
+      <c r="S18" s="27">
+        <f t="shared" si="0"/>
+        <v>0.12122096595796977</v>
+      </c>
+      <c r="T18" s="13">
         <v>7891</v>
       </c>
     </row>
@@ -3021,21 +3073,21 @@
       <c r="F19" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G19" s="22">
+      <c r="G19" s="16">
         <v>2008</v>
       </c>
-      <c r="H19" s="22" t="s">
+      <c r="H19" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="I19" s="26" t="s">
+      <c r="I19" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="J19" s="27" t="s">
+      <c r="J19" s="21" t="s">
         <v>421</v>
       </c>
       <c r="K19" s="7"/>
       <c r="L19" s="7"/>
-      <c r="M19" s="19">
+      <c r="M19" s="13">
         <v>56000</v>
       </c>
       <c r="N19" s="7">
@@ -3050,13 +3102,15 @@
       <c r="Q19" s="7">
         <v>7</v>
       </c>
-      <c r="R19" s="13">
-        <v>177.222222222222</v>
-      </c>
-      <c r="S19" s="16">
-        <v>8.2446428571428601E-2</v>
-      </c>
-      <c r="T19" s="19">
+      <c r="R19" s="26">
+        <f t="shared" si="1"/>
+        <v>177.22222222222223</v>
+      </c>
+      <c r="S19" s="27">
+        <f t="shared" si="0"/>
+        <v>8.2446428571428573E-2</v>
+      </c>
+      <c r="T19" s="13">
         <v>4617</v>
       </c>
     </row>
@@ -3079,21 +3133,21 @@
       <c r="F20" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G20" s="22">
+      <c r="G20" s="16">
         <v>2008</v>
       </c>
-      <c r="H20" s="22" t="s">
+      <c r="H20" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="I20" s="26" t="s">
+      <c r="I20" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="J20" s="27" t="s">
+      <c r="J20" s="21" t="s">
         <v>422</v>
       </c>
       <c r="K20" s="7"/>
       <c r="L20" s="7"/>
-      <c r="M20" s="19">
+      <c r="M20" s="13">
         <v>177847</v>
       </c>
       <c r="N20" s="7">
@@ -3108,13 +3162,15 @@
       <c r="Q20" s="7">
         <v>12</v>
       </c>
-      <c r="R20" s="13">
+      <c r="R20" s="26">
+        <f t="shared" si="1"/>
         <v>200</v>
       </c>
-      <c r="S20" s="16">
-        <v>0.27326859604041698</v>
-      </c>
-      <c r="T20" s="19">
+      <c r="S20" s="27">
+        <f t="shared" si="0"/>
+        <v>0.27326859604041676</v>
+      </c>
+      <c r="T20" s="13">
         <v>48600</v>
       </c>
     </row>
@@ -3137,21 +3193,21 @@
       <c r="F21" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G21" s="22">
+      <c r="G21" s="16">
         <v>2009</v>
       </c>
-      <c r="H21" s="22" t="s">
+      <c r="H21" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="I21" s="26" t="s">
+      <c r="I21" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="J21" s="27" t="s">
+      <c r="J21" s="21" t="s">
         <v>421</v>
       </c>
       <c r="K21" s="7"/>
       <c r="L21" s="7"/>
-      <c r="M21" s="19">
+      <c r="M21" s="13">
         <v>83000</v>
       </c>
       <c r="N21" s="7">
@@ -3166,13 +3222,15 @@
       <c r="Q21" s="7">
         <v>5</v>
       </c>
-      <c r="R21" s="13">
-        <v>185.138888888889</v>
-      </c>
-      <c r="S21" s="16">
-        <v>0.120481927710843</v>
-      </c>
-      <c r="T21" s="19">
+      <c r="R21" s="26">
+        <f t="shared" si="1"/>
+        <v>185.13888888888889</v>
+      </c>
+      <c r="S21" s="27">
+        <f t="shared" si="0"/>
+        <v>0.12048192771084337</v>
+      </c>
+      <c r="T21" s="13">
         <v>10000</v>
       </c>
     </row>
@@ -3195,19 +3253,19 @@
       <c r="F22" s="9" t="s">
         <v>368</v>
       </c>
-      <c r="G22" s="22">
+      <c r="G22" s="16">
         <v>2009</v>
       </c>
-      <c r="H22" s="22"/>
-      <c r="I22" s="26" t="s">
+      <c r="H22" s="16"/>
+      <c r="I22" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="J22" s="27" t="s">
+      <c r="J22" s="21" t="s">
         <v>422</v>
       </c>
       <c r="K22" s="7"/>
       <c r="L22" s="7"/>
-      <c r="M22" s="19">
+      <c r="M22" s="13">
         <v>26000</v>
       </c>
       <c r="N22" s="7">
@@ -3222,13 +3280,15 @@
       <c r="Q22" s="7">
         <v>4</v>
       </c>
-      <c r="R22" s="13">
-        <v>222.222222222222</v>
-      </c>
-      <c r="S22" s="16">
-        <v>3.8461538461538498E-2</v>
-      </c>
-      <c r="T22" s="19">
+      <c r="R22" s="26">
+        <f t="shared" si="1"/>
+        <v>222.22222222222223</v>
+      </c>
+      <c r="S22" s="27">
+        <f t="shared" si="0"/>
+        <v>3.8461538461538464E-2</v>
+      </c>
+      <c r="T22" s="13">
         <v>1000</v>
       </c>
     </row>
@@ -3251,21 +3311,21 @@
       <c r="F23" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="G23" s="22">
+      <c r="G23" s="16">
         <v>2009</v>
       </c>
-      <c r="H23" s="22" t="s">
+      <c r="H23" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="I23" s="26" t="s">
+      <c r="I23" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="J23" s="27" t="s">
+      <c r="J23" s="21" t="s">
         <v>422</v>
       </c>
       <c r="K23" s="7"/>
       <c r="L23" s="7"/>
-      <c r="M23" s="19">
+      <c r="M23" s="13">
         <v>85887</v>
       </c>
       <c r="N23" s="7">
@@ -3280,13 +3340,15 @@
       <c r="Q23" s="7">
         <v>5</v>
       </c>
-      <c r="R23" s="13">
+      <c r="R23" s="26">
+        <f t="shared" si="1"/>
         <v>193.75</v>
       </c>
-      <c r="S23" s="16">
-        <v>0.21099817201672</v>
-      </c>
-      <c r="T23" s="19">
+      <c r="S23" s="27">
+        <f t="shared" si="0"/>
+        <v>0.21099817201671964</v>
+      </c>
+      <c r="T23" s="13">
         <v>18122</v>
       </c>
     </row>
@@ -3309,21 +3371,21 @@
       <c r="F24" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="G24" s="22">
+      <c r="G24" s="16">
         <v>2009</v>
       </c>
-      <c r="H24" s="22" t="s">
+      <c r="H24" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="I24" s="26" t="s">
+      <c r="I24" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="J24" s="27" t="s">
+      <c r="J24" s="21" t="s">
         <v>422</v>
       </c>
       <c r="K24" s="7"/>
       <c r="L24" s="7"/>
-      <c r="M24" s="19">
+      <c r="M24" s="13">
         <v>20000</v>
       </c>
       <c r="N24" s="7">
@@ -3338,13 +3400,15 @@
       <c r="Q24" s="7">
         <v>5</v>
       </c>
-      <c r="R24" s="13">
-        <v>163.611111111111</v>
-      </c>
-      <c r="S24" s="16">
+      <c r="R24" s="26">
+        <f t="shared" si="1"/>
+        <v>163.61111111111111</v>
+      </c>
+      <c r="S24" s="27">
+        <f t="shared" si="0"/>
         <v>0.58565</v>
       </c>
-      <c r="T24" s="19">
+      <c r="T24" s="13">
         <v>11713</v>
       </c>
     </row>
@@ -3367,21 +3431,21 @@
       <c r="F25" s="9" t="s">
         <v>387</v>
       </c>
-      <c r="G25" s="22">
+      <c r="G25" s="16">
         <v>2011</v>
       </c>
-      <c r="H25" s="22" t="s">
+      <c r="H25" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="I25" s="26" t="s">
+      <c r="I25" s="20" t="s">
         <v>388</v>
       </c>
-      <c r="J25" s="27" t="s">
+      <c r="J25" s="21" t="s">
         <v>421</v>
       </c>
       <c r="K25" s="7"/>
       <c r="L25" s="7"/>
-      <c r="M25" s="19">
+      <c r="M25" s="13">
         <v>146385</v>
       </c>
       <c r="N25" s="7">
@@ -3396,13 +3460,15 @@
       <c r="Q25" s="7">
         <v>5</v>
       </c>
-      <c r="R25" s="13">
-        <v>236.805555555555</v>
-      </c>
-      <c r="S25" s="16">
-        <v>7.68931242955221E-2</v>
-      </c>
-      <c r="T25" s="19">
+      <c r="R25" s="26">
+        <f t="shared" si="1"/>
+        <v>236.80555555555554</v>
+      </c>
+      <c r="S25" s="27">
+        <f t="shared" si="0"/>
+        <v>7.6893124295522086E-2</v>
+      </c>
+      <c r="T25" s="13">
         <v>11256</v>
       </c>
     </row>
@@ -3425,21 +3491,21 @@
       <c r="F26" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G26" s="22">
+      <c r="G26" s="16">
         <v>2011</v>
       </c>
-      <c r="H26" s="22" t="s">
+      <c r="H26" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="I26" s="26" t="s">
+      <c r="I26" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="J26" s="27" t="s">
+      <c r="J26" s="21" t="s">
         <v>421</v>
       </c>
       <c r="K26" s="7"/>
       <c r="L26" s="7"/>
-      <c r="M26" s="19">
+      <c r="M26" s="13">
         <v>87000</v>
       </c>
       <c r="N26" s="7">
@@ -3454,13 +3520,15 @@
       <c r="Q26" s="7">
         <v>6</v>
       </c>
-      <c r="R26" s="13">
-        <v>208.333333333333</v>
-      </c>
-      <c r="S26" s="16">
-        <v>0.17591954022988501</v>
-      </c>
-      <c r="T26" s="19">
+      <c r="R26" s="26">
+        <f t="shared" si="1"/>
+        <v>208.33333333333334</v>
+      </c>
+      <c r="S26" s="27">
+        <f t="shared" si="0"/>
+        <v>0.17591954022988507</v>
+      </c>
+      <c r="T26" s="13">
         <v>15305</v>
       </c>
     </row>
@@ -3483,21 +3551,21 @@
       <c r="F27" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="G27" s="22">
+      <c r="G27" s="16">
         <v>2013</v>
       </c>
-      <c r="H27" s="22" t="s">
+      <c r="H27" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="I27" s="26" t="s">
+      <c r="I27" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="J27" s="27" t="s">
+      <c r="J27" s="21" t="s">
         <v>421</v>
       </c>
       <c r="K27" s="7"/>
       <c r="L27" s="7"/>
-      <c r="M27" s="19">
+      <c r="M27" s="13">
         <v>147166.79999999999</v>
       </c>
       <c r="N27" s="7">
@@ -3512,13 +3580,15 @@
       <c r="Q27" s="7">
         <v>7</v>
       </c>
-      <c r="R27" s="13">
-        <v>237.638888888889</v>
-      </c>
-      <c r="S27" s="16">
-        <v>0.139997608156187</v>
-      </c>
-      <c r="T27" s="19">
+      <c r="R27" s="26">
+        <f t="shared" si="1"/>
+        <v>237.63888888888889</v>
+      </c>
+      <c r="S27" s="27">
+        <f t="shared" si="0"/>
+        <v>0.13999760815618742</v>
+      </c>
+      <c r="T27" s="13">
         <v>20603</v>
       </c>
     </row>
@@ -3541,21 +3611,21 @@
       <c r="F28" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G28" s="22">
+      <c r="G28" s="16">
         <v>2014</v>
       </c>
-      <c r="H28" s="22" t="s">
+      <c r="H28" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="I28" s="26" t="s">
+      <c r="I28" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="J28" s="27" t="s">
+      <c r="J28" s="21" t="s">
         <v>421</v>
       </c>
       <c r="K28" s="7"/>
       <c r="L28" s="7"/>
-      <c r="M28" s="19">
+      <c r="M28" s="13">
         <v>46063</v>
       </c>
       <c r="N28" s="7">
@@ -3570,13 +3640,15 @@
       <c r="Q28" s="7">
         <v>4</v>
       </c>
-      <c r="R28" s="13">
+      <c r="R28" s="26">
+        <f t="shared" si="1"/>
         <v>160</v>
       </c>
-      <c r="S28" s="16">
-        <v>9.1418274971235003E-2</v>
-      </c>
-      <c r="T28" s="19">
+      <c r="S28" s="27">
+        <f t="shared" si="0"/>
+        <v>9.1418274971235045E-2</v>
+      </c>
+      <c r="T28" s="13">
         <v>4211</v>
       </c>
     </row>
@@ -3599,21 +3671,21 @@
       <c r="F29" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G29" s="22">
+      <c r="G29" s="16">
         <v>2017</v>
       </c>
-      <c r="H29" s="22" t="s">
+      <c r="H29" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="I29" s="26" t="s">
+      <c r="I29" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="J29" s="27" t="s">
+      <c r="J29" s="21" t="s">
         <v>422</v>
       </c>
       <c r="K29" s="7"/>
       <c r="L29" s="7"/>
-      <c r="M29" s="19">
+      <c r="M29" s="13">
         <v>47261</v>
       </c>
       <c r="N29" s="7">
@@ -3628,13 +3700,15 @@
       <c r="Q29" s="7">
         <v>7</v>
       </c>
-      <c r="R29" s="13">
-        <v>241.666666666667</v>
-      </c>
-      <c r="S29" s="16">
-        <v>0.23315566746365901</v>
-      </c>
-      <c r="T29" s="19">
+      <c r="R29" s="26">
+        <f t="shared" si="1"/>
+        <v>241.66666666666666</v>
+      </c>
+      <c r="S29" s="27">
+        <f t="shared" si="0"/>
+        <v>0.23315566746365926</v>
+      </c>
+      <c r="T29" s="13">
         <v>11019.17</v>
       </c>
     </row>
@@ -3657,21 +3731,21 @@
       <c r="F30" s="9" t="s">
         <v>345</v>
       </c>
-      <c r="G30" s="22">
+      <c r="G30" s="16">
         <v>2019</v>
       </c>
-      <c r="H30" s="22" t="s">
+      <c r="H30" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="I30" s="26" t="s">
+      <c r="I30" s="20" t="s">
         <v>389</v>
       </c>
-      <c r="J30" s="27" t="s">
+      <c r="J30" s="21" t="s">
         <v>421</v>
       </c>
       <c r="K30" s="7"/>
       <c r="L30" s="7"/>
-      <c r="M30" s="19">
+      <c r="M30" s="13">
         <v>119000</v>
       </c>
       <c r="N30" s="7">
@@ -3686,13 +3760,15 @@
       <c r="Q30" s="7">
         <v>6</v>
       </c>
-      <c r="R30" s="13">
-        <v>333.33333333333297</v>
-      </c>
-      <c r="S30" s="16">
-        <v>0.15546218487395</v>
-      </c>
-      <c r="T30" s="19">
+      <c r="R30" s="26">
+        <f t="shared" si="1"/>
+        <v>333.33333333333331</v>
+      </c>
+      <c r="S30" s="27">
+        <f t="shared" si="0"/>
+        <v>0.15546218487394958</v>
+      </c>
+      <c r="T30" s="13">
         <v>18500</v>
       </c>
     </row>
@@ -3715,19 +3791,19 @@
       <c r="F31" s="9" t="s">
         <v>362</v>
       </c>
-      <c r="G31" s="22">
+      <c r="G31" s="16">
         <v>2019</v>
       </c>
-      <c r="H31" s="22"/>
-      <c r="I31" s="26" t="s">
+      <c r="H31" s="16"/>
+      <c r="I31" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="J31" s="27" t="s">
+      <c r="J31" s="21" t="s">
         <v>422</v>
       </c>
       <c r="K31" s="7"/>
       <c r="L31" s="7"/>
-      <c r="M31" s="19">
+      <c r="M31" s="13">
         <v>47000</v>
       </c>
       <c r="N31" s="7">
@@ -3742,13 +3818,15 @@
       <c r="Q31" s="7">
         <v>2</v>
       </c>
-      <c r="R31" s="13">
-        <v>330.55555555555497</v>
-      </c>
-      <c r="S31" s="16">
-        <v>0.125228723404255</v>
-      </c>
-      <c r="T31" s="19">
+      <c r="R31" s="26">
+        <f t="shared" si="1"/>
+        <v>330.55555555555554</v>
+      </c>
+      <c r="S31" s="27">
+        <f t="shared" si="0"/>
+        <v>0.12522872340425531</v>
+      </c>
+      <c r="T31" s="13">
         <v>5885.75</v>
       </c>
     </row>
@@ -3771,21 +3849,21 @@
       <c r="F32" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="G32" s="22">
+      <c r="G32" s="16">
         <v>2019</v>
       </c>
-      <c r="H32" s="22" t="s">
+      <c r="H32" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="I32" s="26" t="s">
+      <c r="I32" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="J32" s="27" t="s">
+      <c r="J32" s="21" t="s">
         <v>422</v>
       </c>
       <c r="K32" s="7"/>
       <c r="L32" s="7"/>
-      <c r="M32" s="19">
+      <c r="M32" s="13">
         <v>186000</v>
       </c>
       <c r="N32" s="7">
@@ -3800,13 +3878,15 @@
       <c r="Q32" s="7">
         <v>5</v>
       </c>
-      <c r="R32" s="13">
-        <v>258.33333333333297</v>
-      </c>
-      <c r="S32" s="16">
+      <c r="R32" s="26">
+        <f t="shared" si="1"/>
+        <v>258.33333333333331</v>
+      </c>
+      <c r="S32" s="27">
+        <f t="shared" si="0"/>
         <v>9.6774193548387094E-2</v>
       </c>
-      <c r="T32" s="19">
+      <c r="T32" s="13">
         <v>18000</v>
       </c>
     </row>
@@ -3829,19 +3909,19 @@
       <c r="F33" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="G33" s="22">
+      <c r="G33" s="16">
         <v>2019</v>
       </c>
-      <c r="H33" s="22"/>
-      <c r="I33" s="26" t="s">
+      <c r="H33" s="16"/>
+      <c r="I33" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="J33" s="27" t="s">
+      <c r="J33" s="21" t="s">
         <v>421</v>
       </c>
       <c r="K33" s="7"/>
       <c r="L33" s="7"/>
-      <c r="M33" s="19">
+      <c r="M33" s="13">
         <v>40800</v>
       </c>
       <c r="N33" s="7">
@@ -3856,13 +3936,15 @@
       <c r="Q33" s="7">
         <v>2</v>
       </c>
-      <c r="R33" s="13">
-        <v>194.555555555555</v>
-      </c>
-      <c r="S33" s="16">
-        <v>0.49509803921568601</v>
-      </c>
-      <c r="T33" s="19">
+      <c r="R33" s="26">
+        <f t="shared" si="1"/>
+        <v>194.55555555555554</v>
+      </c>
+      <c r="S33" s="27">
+        <f t="shared" si="0"/>
+        <v>0.49509803921568629</v>
+      </c>
+      <c r="T33" s="13">
         <v>20200</v>
       </c>
     </row>
@@ -3885,19 +3967,19 @@
       <c r="F34" s="9" t="s">
         <v>367</v>
       </c>
-      <c r="G34" s="22">
+      <c r="G34" s="16">
         <v>2019</v>
       </c>
-      <c r="H34" s="22"/>
-      <c r="I34" s="26" t="s">
+      <c r="H34" s="16"/>
+      <c r="I34" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="J34" s="27" t="s">
+      <c r="J34" s="21" t="s">
         <v>421</v>
       </c>
       <c r="K34" s="7"/>
       <c r="L34" s="7"/>
-      <c r="M34" s="19">
+      <c r="M34" s="13">
         <v>55200</v>
       </c>
       <c r="N34" s="7">
@@ -3912,13 +3994,15 @@
       <c r="Q34" s="7">
         <v>5</v>
       </c>
-      <c r="R34" s="13">
-        <v>198.055555555555</v>
-      </c>
-      <c r="S34" s="16">
-        <v>0.94927536231884102</v>
-      </c>
-      <c r="T34" s="19">
+      <c r="R34" s="26">
+        <f t="shared" si="1"/>
+        <v>198.05555555555554</v>
+      </c>
+      <c r="S34" s="27">
+        <f t="shared" si="0"/>
+        <v>0.94927536231884058</v>
+      </c>
+      <c r="T34" s="13">
         <v>52400</v>
       </c>
     </row>
@@ -3941,21 +4025,21 @@
       <c r="F35" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="G35" s="22">
+      <c r="G35" s="16">
         <v>2019</v>
       </c>
-      <c r="H35" s="22" t="s">
+      <c r="H35" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="I35" s="26" t="s">
+      <c r="I35" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="J35" s="27" t="s">
+      <c r="J35" s="21" t="s">
         <v>422</v>
       </c>
       <c r="K35" s="7"/>
       <c r="L35" s="7"/>
-      <c r="M35" s="19">
+      <c r="M35" s="13">
         <v>350000</v>
       </c>
       <c r="N35" s="7">
@@ -3970,13 +4054,15 @@
       <c r="Q35" s="7">
         <v>2</v>
       </c>
-